--- a/1.xlsx
+++ b/1.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="\\wh.local\fs\UserProfile_TSSWH19\_TSSWH19_redirected_folders\HunyaCs1\Desktop\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3FE3FF22-0F63-40A3-B98B-2115A1EFEDC9}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A62A5808-5B61-4459-AA1A-DFC1BE4C641F}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="0" windowWidth="22260" windowHeight="12648" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1147" uniqueCount="600">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1165" uniqueCount="605">
   <si>
     <t>IRSZ</t>
   </si>
@@ -1827,7 +1827,22 @@
     <t>159995579537957834</t>
   </si>
   <si>
-    <t>26-00/00211</t>
+    <t>267004091</t>
+  </si>
+  <si>
+    <t>267004116</t>
+  </si>
+  <si>
+    <t>267004055</t>
+  </si>
+  <si>
+    <t>267004038</t>
+  </si>
+  <si>
+    <t>267004103</t>
+  </si>
+  <si>
+    <t>267004092</t>
   </si>
 </sst>
 </file>
@@ -2147,7 +2162,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <sheetPr codeName="Munka1"/>
-  <dimension ref="A1:H164"/>
+  <dimension ref="A1:H169"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="25.44140625" style="1" bestFit="1" customWidth="1"/>
@@ -5910,22 +5925,86 @@
       </c>
     </row>
     <row r="164" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A164" s="1" t="s">
+        <v>599</v>
+      </c>
       <c r="C164" s="1" t="s">
-        <v>14</v>
+        <v>22</v>
       </c>
       <c r="D164" s="1" t="s">
         <v>599</v>
       </c>
-      <c r="E164" s="1" t="s">
-        <v>311</v>
-      </c>
-      <c r="F164" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="G164" s="1" t="s">
-        <v>312</v>
-      </c>
       <c r="H164" s="1" t="s">
+        <v>129</v>
+      </c>
+    </row>
+    <row r="165" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A165" s="1" t="s">
+        <v>600</v>
+      </c>
+      <c r="C165" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="D165" s="1" t="s">
+        <v>600</v>
+      </c>
+      <c r="H165" s="1" t="s">
+        <v>129</v>
+      </c>
+    </row>
+    <row r="166" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A166" s="1" t="s">
+        <v>601</v>
+      </c>
+      <c r="C166" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="D166" s="1" t="s">
+        <v>601</v>
+      </c>
+      <c r="H166" s="1" t="s">
+        <v>129</v>
+      </c>
+    </row>
+    <row r="167" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A167" s="1" t="s">
+        <v>602</v>
+      </c>
+      <c r="C167" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="D167" s="1" t="s">
+        <v>602</v>
+      </c>
+      <c r="H167" s="1" t="s">
+        <v>129</v>
+      </c>
+    </row>
+    <row r="168" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A168" s="1" t="s">
+        <v>603</v>
+      </c>
+      <c r="C168" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="D168" s="1" t="s">
+        <v>603</v>
+      </c>
+      <c r="H168" s="1" t="s">
+        <v>129</v>
+      </c>
+    </row>
+    <row r="169" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A169" s="1" t="s">
+        <v>604</v>
+      </c>
+      <c r="C169" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="D169" s="1" t="s">
+        <v>604</v>
+      </c>
+      <c r="H169" s="1" t="s">
         <v>129</v>
       </c>
     </row>

--- a/1.xlsx
+++ b/1.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="\\wh.local\fs\UserProfile_TSSWH19\_TSSWH19_redirected_folders\HunyaCs1\Desktop\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A62A5808-5B61-4459-AA1A-DFC1BE4C641F}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D2316BF2-B66C-48EB-9EF7-DB63125B4249}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="0" windowWidth="22260" windowHeight="12648" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1165" uniqueCount="605">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1175" uniqueCount="625">
   <si>
     <t>IRSZ</t>
   </si>
@@ -66,9 +66,6 @@
     <t>MEDIAMARKT</t>
   </si>
   <si>
-    <t>SZ-818</t>
-  </si>
-  <si>
     <t>AUCHAN</t>
   </si>
   <si>
@@ -105,9 +102,6 @@
     <t>SZ-835</t>
   </si>
   <si>
-    <t>1148</t>
-  </si>
-  <si>
     <t>1139</t>
   </si>
   <si>
@@ -117,18 +111,9 @@
     <t>SZ-822</t>
   </si>
   <si>
-    <t>SZ-827</t>
-  </si>
-  <si>
     <t>1138</t>
   </si>
   <si>
-    <t>1145</t>
-  </si>
-  <si>
-    <t>1201</t>
-  </si>
-  <si>
     <t>Széchenyi utca</t>
   </si>
   <si>
@@ -144,21 +129,12 @@
     <t>1203</t>
   </si>
   <si>
-    <t>Kossuth Lajos utca</t>
-  </si>
-  <si>
     <t>SZ-823</t>
   </si>
   <si>
     <t>1048</t>
   </si>
   <si>
-    <t>2119</t>
-  </si>
-  <si>
-    <t>PÉCEL</t>
-  </si>
-  <si>
     <t>INSPORT</t>
   </si>
   <si>
@@ -171,81 +147,27 @@
     <t>SZ-830</t>
   </si>
   <si>
-    <t>2038</t>
-  </si>
-  <si>
-    <t>SÓSKÚT</t>
-  </si>
-  <si>
     <t>Ceglédi út</t>
   </si>
   <si>
     <t>SZ-834</t>
   </si>
   <si>
-    <t>1075</t>
-  </si>
-  <si>
     <t>1039</t>
   </si>
   <si>
     <t>1112</t>
   </si>
   <si>
-    <t>2740</t>
-  </si>
-  <si>
-    <t>ABONY</t>
-  </si>
-  <si>
     <t>1237</t>
   </si>
   <si>
-    <t>2000</t>
-  </si>
-  <si>
-    <t>SZENTENDRE</t>
-  </si>
-  <si>
-    <t>Frangepán utca</t>
-  </si>
-  <si>
-    <t>1171</t>
-  </si>
-  <si>
-    <t>Szabadság utca</t>
-  </si>
-  <si>
-    <t>1055</t>
-  </si>
-  <si>
-    <t>PICIGURMAN</t>
-  </si>
-  <si>
-    <t>SZ-860</t>
-  </si>
-  <si>
     <t>1092</t>
   </si>
   <si>
-    <t>Ráday utca</t>
-  </si>
-  <si>
-    <t>69b51c186967eb2a8b5ce304</t>
-  </si>
-  <si>
-    <t>260308-F00002662</t>
-  </si>
-  <si>
     <t>1149</t>
   </si>
   <si>
-    <t>Répásy Mihály utca</t>
-  </si>
-  <si>
-    <t>1025</t>
-  </si>
-  <si>
     <t>SZ-832</t>
   </si>
   <si>
@@ -255,126 +177,33 @@
     <t>VERESEGYHÁZ</t>
   </si>
   <si>
-    <t>1156</t>
-  </si>
-  <si>
-    <t>69b314476967eb2a8b5cccd8</t>
-  </si>
-  <si>
-    <t>260312-W00010636</t>
-  </si>
-  <si>
-    <t>Bacsó Béla utca</t>
-  </si>
-  <si>
-    <t>Kölcsey utca</t>
-  </si>
-  <si>
     <t>2220</t>
   </si>
   <si>
     <t>VECSÉS</t>
   </si>
   <si>
-    <t>Nyárfa utca</t>
-  </si>
-  <si>
     <t>1032</t>
   </si>
   <si>
-    <t>Szél utca</t>
-  </si>
-  <si>
-    <t>1077</t>
-  </si>
-  <si>
-    <t>69b5679d6967eb2a8b5ce915</t>
-  </si>
-  <si>
-    <t>260314-F00004515</t>
-  </si>
-  <si>
     <t>1194</t>
   </si>
   <si>
-    <t>Szabadka utca</t>
-  </si>
-  <si>
-    <t>1104</t>
-  </si>
-  <si>
-    <t>Harmat utca</t>
-  </si>
-  <si>
-    <t>2730</t>
-  </si>
-  <si>
-    <t>ALBERTIRSA</t>
-  </si>
-  <si>
-    <t>2131</t>
-  </si>
-  <si>
     <t>GÖD</t>
   </si>
   <si>
-    <t>Lehel utca</t>
-  </si>
-  <si>
-    <t>2209</t>
-  </si>
-  <si>
-    <t>PÉTERI</t>
-  </si>
-  <si>
     <t>1162</t>
   </si>
   <si>
-    <t>304248184/1</t>
-  </si>
-  <si>
-    <t>304248184</t>
-  </si>
-  <si>
-    <t>Dinnyehegyi köz</t>
-  </si>
-  <si>
-    <t>304248184/2</t>
-  </si>
-  <si>
     <t>2143</t>
   </si>
   <si>
     <t>KISTARCSA</t>
   </si>
   <si>
-    <t>Ferenc utca</t>
-  </si>
-  <si>
-    <t>2096</t>
-  </si>
-  <si>
-    <t>ÜRÖM</t>
-  </si>
-  <si>
-    <t>1164</t>
-  </si>
-  <si>
-    <t>304429684/1</t>
-  </si>
-  <si>
-    <t>304429684</t>
-  </si>
-  <si>
     <t>1042</t>
   </si>
   <si>
-    <t>Árpád út</t>
-  </si>
-  <si>
-    <t>Bajcsy-Zsilinszky utca</t>
-  </si>
-  <si>
     <t>2230</t>
   </si>
   <si>
@@ -387,51 +216,24 @@
     <t>SZIGETHALOM</t>
   </si>
   <si>
-    <t>Bethlen utca</t>
-  </si>
-  <si>
     <t>2162</t>
   </si>
   <si>
     <t>ŐRBOTTYÁN</t>
   </si>
   <si>
-    <t>2200</t>
-  </si>
-  <si>
-    <t>MONOR</t>
-  </si>
-  <si>
-    <t>Wesselényi utca</t>
-  </si>
-  <si>
     <t>2440</t>
   </si>
   <si>
     <t>SZÁZHALOMBATTA</t>
   </si>
   <si>
-    <t>1154</t>
-  </si>
-  <si>
     <t>1204</t>
   </si>
   <si>
     <t>SELEX</t>
   </si>
   <si>
-    <t>159995579538264658</t>
-  </si>
-  <si>
-    <t>1-2230/2026</t>
-  </si>
-  <si>
-    <t>Dessewffy Arisztid utca</t>
-  </si>
-  <si>
-    <t>EUROTRESOR</t>
-  </si>
-  <si>
     <t>159995579538236723</t>
   </si>
   <si>
@@ -447,234 +249,24 @@
     <t>HERCEGHALOM</t>
   </si>
   <si>
-    <t>Boroka</t>
-  </si>
-  <si>
-    <t>248743260/1</t>
-  </si>
-  <si>
-    <t>248743260</t>
-  </si>
-  <si>
-    <t>Mester utca</t>
-  </si>
-  <si>
-    <t>248743260/2</t>
-  </si>
-  <si>
-    <t>248744005/1</t>
-  </si>
-  <si>
-    <t>248744005</t>
-  </si>
-  <si>
-    <t>Őzgida utca</t>
-  </si>
-  <si>
-    <t>69b4261c6967eb2a8b5cdce6</t>
-  </si>
-  <si>
-    <t>260306-W00000386</t>
-  </si>
-  <si>
-    <t>Aulich Lajos utca</t>
-  </si>
-  <si>
     <t>69b7e2616967eb2a8b5cfd02</t>
   </si>
   <si>
     <t>260307-F00000745</t>
   </si>
   <si>
-    <t>69b457856967eb2a8b5ce07b</t>
-  </si>
-  <si>
-    <t>260308-F00002506-1</t>
-  </si>
-  <si>
-    <t>Eperfasor utca</t>
-  </si>
-  <si>
-    <t>69afc2ea51e7020fc80ca938</t>
-  </si>
-  <si>
-    <t>260310-F00000429</t>
-  </si>
-  <si>
     <t>2254</t>
   </si>
   <si>
     <t>SZENTMÁRTONKÁTA</t>
   </si>
   <si>
-    <t>Somogyi Béla út</t>
-  </si>
-  <si>
-    <t>69b40a186967eb2a8b5cd933</t>
-  </si>
-  <si>
-    <t>260310-F00004279</t>
-  </si>
-  <si>
-    <t>2381</t>
-  </si>
-  <si>
-    <t>TÁBORFALVA</t>
-  </si>
-  <si>
-    <t>Tarcsay út</t>
-  </si>
-  <si>
-    <t>69b90df4d96b4f4a2437c591</t>
-  </si>
-  <si>
-    <t>260310-F00007519</t>
-  </si>
-  <si>
-    <t>69b806fad96b4f4a2437b967</t>
-  </si>
-  <si>
-    <t>260310-F00009043</t>
-  </si>
-  <si>
-    <t>Szőlő köz</t>
-  </si>
-  <si>
-    <t>69b914a8d96b4f4a2437c6b9</t>
-  </si>
-  <si>
-    <t>260311-F00013052</t>
-  </si>
-  <si>
-    <t>1044</t>
-  </si>
-  <si>
-    <t>Váci út</t>
-  </si>
-  <si>
-    <t>69b547866967eb2a8b5ce70e</t>
-  </si>
-  <si>
-    <t>260311-F00013754</t>
-  </si>
-  <si>
-    <t>Drégelyi utca</t>
-  </si>
-  <si>
-    <t>69b92325d96b4f4a2437c8ef</t>
-  </si>
-  <si>
-    <t>260312-F00004510-1</t>
-  </si>
-  <si>
-    <t>1029</t>
-  </si>
-  <si>
-    <t>Csatlós utca</t>
-  </si>
-  <si>
-    <t>69b838a4d96b4f4a2437c075</t>
-  </si>
-  <si>
-    <t>260312-F00005457</t>
-  </si>
-  <si>
-    <t>Alíz utca</t>
-  </si>
-  <si>
-    <t>69b2d7596967eb2a8b5cc782</t>
-  </si>
-  <si>
-    <t>260312-F00013770</t>
-  </si>
-  <si>
-    <t>Bertalan utca</t>
-  </si>
-  <si>
-    <t>69b40f176967eb2a8b5cd9d4</t>
-  </si>
-  <si>
-    <t>260313-F00008802</t>
-  </si>
-  <si>
-    <t>Petőfi Sándor utca</t>
-  </si>
-  <si>
-    <t>69b421f96967eb2a8b5cdc5f</t>
-  </si>
-  <si>
-    <t>260313-F00010065</t>
-  </si>
-  <si>
     <t>2760</t>
   </si>
   <si>
     <t>NAGYKÁTA</t>
   </si>
   <si>
-    <t>Nefelejcs utca</t>
-  </si>
-  <si>
-    <t>69b42eba6967eb2a8b5cddbc</t>
-  </si>
-  <si>
-    <t>260313-F00011522</t>
-  </si>
-  <si>
-    <t>2049</t>
-  </si>
-  <si>
-    <t>DIÓSD</t>
-  </si>
-  <si>
-    <t>Tó utca</t>
-  </si>
-  <si>
-    <t>69b42eba6967eb2a8b5cddbd</t>
-  </si>
-  <si>
-    <t>69b4336a6967eb2a8b5cde4a</t>
-  </si>
-  <si>
-    <t>260313-F00012033</t>
-  </si>
-  <si>
-    <t>Zászló utca</t>
-  </si>
-  <si>
-    <t>69b458ec6967eb2a8b5ce09d</t>
-  </si>
-  <si>
-    <t>260313-F00013572</t>
-  </si>
-  <si>
-    <t>2337</t>
-  </si>
-  <si>
-    <t>DÉLEGYHÁZA</t>
-  </si>
-  <si>
-    <t>Csepp köz</t>
-  </si>
-  <si>
-    <t>69b483136967eb2a8b5ce1c2</t>
-  </si>
-  <si>
-    <t>260313-W00010692</t>
-  </si>
-  <si>
-    <t>2638</t>
-  </si>
-  <si>
-    <t>KEMENCE</t>
-  </si>
-  <si>
-    <t>69b47c126967eb2a8b5ce18e</t>
-  </si>
-  <si>
-    <t>260313-W00011034</t>
-  </si>
-  <si>
     <t>Rákóczi út</t>
   </si>
   <si>
@@ -690,129 +282,12 @@
     <t>69b538bd6967eb2a8b5ce5fd</t>
   </si>
   <si>
-    <t>69b56c4c6967eb2a8b5ce964</t>
-  </si>
-  <si>
-    <t>260314-F00004660</t>
-  </si>
-  <si>
     <t>2132</t>
   </si>
   <si>
-    <t>Lenkey utca</t>
-  </si>
-  <si>
-    <t>69b580396967eb2a8b5cea90</t>
-  </si>
-  <si>
-    <t>260314-F00005356</t>
-  </si>
-  <si>
-    <t>2768</t>
-  </si>
-  <si>
-    <t>ÚJSZILVÁS</t>
-  </si>
-  <si>
-    <t>69b50e896967eb2a8b5ce271</t>
-  </si>
-  <si>
-    <t>260314-W00001380</t>
-  </si>
-  <si>
-    <t>Szélmalom út</t>
-  </si>
-  <si>
-    <t>69b524286967eb2a8b5ce3d6</t>
-  </si>
-  <si>
-    <t>260314-W00002394</t>
-  </si>
-  <si>
-    <t>Kőfaragó utca</t>
-  </si>
-  <si>
-    <t>69b582976967eb2a8b5cead5</t>
-  </si>
-  <si>
-    <t>260314-W00006492</t>
-  </si>
-  <si>
-    <t>Hamvas Béla utca</t>
-  </si>
-  <si>
-    <t>69b5cc666967eb2a8b5ced24</t>
-  </si>
-  <si>
-    <t>260314-W00009608</t>
-  </si>
-  <si>
     <t>Kisfaludy utca</t>
   </si>
   <si>
-    <t>69b5dbbc6967eb2a8b5ced60</t>
-  </si>
-  <si>
-    <t>260314-W00010316</t>
-  </si>
-  <si>
-    <t>Pulykaház utca</t>
-  </si>
-  <si>
-    <t>69b6a7876967eb2a8b5cf04a</t>
-  </si>
-  <si>
-    <t>260315-F00001229</t>
-  </si>
-  <si>
-    <t>Gábor utca</t>
-  </si>
-  <si>
-    <t>69b646476967eb2a8b5ced9f</t>
-  </si>
-  <si>
-    <t>260315-W00000504</t>
-  </si>
-  <si>
-    <t>Rózsa utca</t>
-  </si>
-  <si>
-    <t>69b7066f6967eb2a8b5cf35f</t>
-  </si>
-  <si>
-    <t>260315-W00008720</t>
-  </si>
-  <si>
-    <t>2321</t>
-  </si>
-  <si>
-    <t>SZIGETBECSE</t>
-  </si>
-  <si>
-    <t>Lórévi út</t>
-  </si>
-  <si>
-    <t>69b70a346967eb2a8b5cf393</t>
-  </si>
-  <si>
-    <t>260315-W00008821</t>
-  </si>
-  <si>
-    <t>2363</t>
-  </si>
-  <si>
-    <t>FELSŐPAKONY</t>
-  </si>
-  <si>
-    <t>Zrínyi Miklós utca</t>
-  </si>
-  <si>
-    <t>69b718056967eb2a8b5cf3ed</t>
-  </si>
-  <si>
-    <t>260315-W00009155</t>
-  </si>
-  <si>
     <t>2344</t>
   </si>
   <si>
@@ -822,1027 +297,1612 @@
     <t>Bercsényi utca</t>
   </si>
   <si>
-    <t>69b7d4c36967eb2a8b5cfaac</t>
-  </si>
-  <si>
-    <t>260316-F00004226-2</t>
-  </si>
-  <si>
-    <t>Csokonai utca</t>
-  </si>
-  <si>
-    <t>69b7d4c36967eb2a8b5cfaad</t>
-  </si>
-  <si>
-    <t>69b7fc90d96b4f4a2437b79c</t>
-  </si>
-  <si>
-    <t>260316-F00008490</t>
-  </si>
-  <si>
-    <t>Király utca</t>
-  </si>
-  <si>
-    <t>69b80714d96b4f4a2437b972</t>
-  </si>
-  <si>
-    <t>260316-F00009736</t>
-  </si>
-  <si>
-    <t>Pesti út</t>
-  </si>
-  <si>
-    <t>69b80977d96b4f4a2437b9f2</t>
-  </si>
-  <si>
-    <t>260316-F00010312</t>
-  </si>
-  <si>
     <t>1122</t>
   </si>
   <si>
-    <t>Krisztina körút</t>
-  </si>
-  <si>
-    <t>69b849e3d96b4f4a2437c197</t>
-  </si>
-  <si>
-    <t>260316-F00015388</t>
-  </si>
-  <si>
-    <t>Kabar utca</t>
-  </si>
-  <si>
-    <t>69b849e3d96b4f4a2437c198</t>
-  </si>
-  <si>
-    <t>69b85b98d96b4f4a2437c256</t>
-  </si>
-  <si>
-    <t>260316-F00015812</t>
-  </si>
-  <si>
     <t>1121</t>
   </si>
   <si>
-    <t>Rácz Aladár út</t>
-  </si>
-  <si>
-    <t>69b7c0c86967eb2a8b5cf6e2</t>
-  </si>
-  <si>
-    <t>260316-W00001829</t>
-  </si>
-  <si>
-    <t>1041</t>
-  </si>
-  <si>
-    <t>Szigeti József utca</t>
-  </si>
-  <si>
-    <t>69b93d97d96b4f4a2437cd08</t>
-  </si>
-  <si>
-    <t>260316-W00007873</t>
-  </si>
-  <si>
-    <t>Török Flóris utca</t>
-  </si>
-  <si>
-    <t>69b849e3d96b4f4a2437c19b</t>
-  </si>
-  <si>
-    <t>260316-W00009270</t>
-  </si>
-  <si>
-    <t>1134</t>
-  </si>
-  <si>
-    <t>Bulcsú utca</t>
-  </si>
-  <si>
-    <t>69b8779dd96b4f4a2437c318</t>
-  </si>
-  <si>
-    <t>260316-W00009749</t>
-  </si>
-  <si>
-    <t>1215</t>
-  </si>
-  <si>
     <t>Árpád utca</t>
   </si>
   <si>
-    <t>69b863b0d96b4f4a2437c290</t>
-  </si>
-  <si>
-    <t>260316-W00009799</t>
-  </si>
-  <si>
     <t>1222</t>
   </si>
   <si>
-    <t>Háros utca</t>
-  </si>
-  <si>
-    <t>69b856c9d96b4f4a2437c22b</t>
-  </si>
-  <si>
-    <t>260316-W00010301</t>
-  </si>
-  <si>
     <t>1026</t>
   </si>
   <si>
-    <t>Radna utca</t>
-  </si>
-  <si>
-    <t>FIZZ-1000825747_2</t>
-  </si>
-  <si>
-    <t>267004149</t>
-  </si>
-  <si>
-    <t>1098</t>
-  </si>
-  <si>
-    <t>Ecseri Út</t>
-  </si>
-  <si>
-    <t>26MPE0003027/1</t>
-  </si>
-  <si>
-    <t>26MPE0003027</t>
-  </si>
-  <si>
     <t>2100</t>
   </si>
   <si>
     <t>GÖDÖLLŐ</t>
   </si>
   <si>
-    <t>Hegy utca,</t>
-  </si>
-  <si>
     <t>MEGAPLACE</t>
   </si>
   <si>
-    <t>303536248/1</t>
-  </si>
-  <si>
-    <t>303536248</t>
-  </si>
-  <si>
-    <t>2300</t>
-  </si>
-  <si>
-    <t>RÁCKEVE</t>
-  </si>
-  <si>
-    <t>Báthory István utca</t>
-  </si>
-  <si>
-    <t>303710089/1</t>
-  </si>
-  <si>
-    <t>303710089</t>
-  </si>
-  <si>
-    <t>Lengyel utca</t>
-  </si>
-  <si>
-    <t>303710089/2</t>
-  </si>
-  <si>
-    <t>303710089/3</t>
-  </si>
-  <si>
-    <t>303795481/1</t>
-  </si>
-  <si>
-    <t>303795481</t>
-  </si>
-  <si>
-    <t>1054</t>
-  </si>
-  <si>
-    <t>Széchenyi rakpart</t>
-  </si>
-  <si>
-    <t>303795481/2</t>
-  </si>
-  <si>
-    <t>303838529/1</t>
-  </si>
-  <si>
-    <t>303838529</t>
-  </si>
-  <si>
-    <t>Ond vezér utca</t>
-  </si>
-  <si>
-    <t>303838529/2</t>
-  </si>
-  <si>
-    <t>303838529/3</t>
-  </si>
-  <si>
-    <t>304012943/1</t>
-  </si>
-  <si>
-    <t>304012943</t>
-  </si>
-  <si>
     <t>1181</t>
   </si>
   <si>
-    <t>Szélmalom utca</t>
-  </si>
-  <si>
-    <t>304105423/1</t>
-  </si>
-  <si>
-    <t>304105423</t>
-  </si>
-  <si>
-    <t>Röppentyű utca</t>
-  </si>
-  <si>
-    <t>304149784/1</t>
-  </si>
-  <si>
-    <t>304149784</t>
-  </si>
-  <si>
     <t>2085</t>
   </si>
   <si>
     <t>PILISVÖRÖSVÁR</t>
   </si>
   <si>
-    <t>Piliscsabai utca</t>
-  </si>
-  <si>
-    <t>304149784/2</t>
-  </si>
-  <si>
-    <t>304149784/3</t>
-  </si>
-  <si>
-    <t>304198600/1</t>
-  </si>
-  <si>
-    <t>304198600</t>
-  </si>
-  <si>
-    <t>1141</t>
-  </si>
-  <si>
-    <t>Szilágysomlyó utca</t>
-  </si>
-  <si>
-    <t>304198600/2</t>
-  </si>
-  <si>
-    <t>304198600/3</t>
-  </si>
-  <si>
-    <t>304198657/1</t>
-  </si>
-  <si>
-    <t>304198657</t>
-  </si>
-  <si>
-    <t>Kolozsvári utca</t>
-  </si>
-  <si>
-    <t>304198774/1</t>
-  </si>
-  <si>
-    <t>304198774</t>
-  </si>
-  <si>
-    <t>304198801/1</t>
-  </si>
-  <si>
-    <t>304198801</t>
-  </si>
-  <si>
-    <t>Nagykőbnya utca</t>
-  </si>
-  <si>
-    <t>304198801/2</t>
-  </si>
-  <si>
-    <t>304248693/1</t>
-  </si>
-  <si>
-    <t>304248693</t>
-  </si>
-  <si>
     <t>1188</t>
   </si>
   <si>
-    <t>304309583/1</t>
-  </si>
-  <si>
-    <t>304309583</t>
-  </si>
-  <si>
-    <t>1081</t>
-  </si>
-  <si>
-    <t>Népszínház utca</t>
-  </si>
-  <si>
-    <t>304309706/1</t>
-  </si>
-  <si>
-    <t>304309706</t>
-  </si>
-  <si>
-    <t>Megyeri út</t>
-  </si>
-  <si>
-    <t>304309706/2</t>
-  </si>
-  <si>
-    <t>304309706/3</t>
-  </si>
-  <si>
-    <t>304309794/1</t>
-  </si>
-  <si>
-    <t>304309794</t>
-  </si>
-  <si>
-    <t>Gesztenye utca</t>
-  </si>
-  <si>
-    <t>304309904/1</t>
-  </si>
-  <si>
-    <t>304309904</t>
-  </si>
-  <si>
-    <t>Kavics utca</t>
-  </si>
-  <si>
-    <t>304309911/1</t>
-  </si>
-  <si>
-    <t>304309911</t>
-  </si>
-  <si>
-    <t>Kazinczy utca</t>
-  </si>
-  <si>
-    <t>304429580/1</t>
-  </si>
-  <si>
-    <t>304429580</t>
-  </si>
-  <si>
-    <t>Nápoly utca</t>
-  </si>
-  <si>
-    <t>304429580/2</t>
-  </si>
-  <si>
-    <t>304429700/1</t>
-  </si>
-  <si>
-    <t>304429700</t>
-  </si>
-  <si>
     <t>1027</t>
   </si>
   <si>
-    <t>Kacsa utca</t>
-  </si>
-  <si>
-    <t>304430496/1</t>
-  </si>
-  <si>
-    <t>304430496</t>
-  </si>
-  <si>
-    <t>304430496/2</t>
-  </si>
-  <si>
-    <t>304487030/1</t>
-  </si>
-  <si>
-    <t>304487030</t>
-  </si>
-  <si>
     <t>2225</t>
   </si>
   <si>
     <t>ÜLLŐ</t>
   </si>
   <si>
-    <t>Bozsik József körút</t>
-  </si>
-  <si>
-    <t>304487174/1</t>
-  </si>
-  <si>
-    <t>304487174</t>
-  </si>
-  <si>
-    <t>Ötvös utca</t>
-  </si>
-  <si>
-    <t>304487263/1</t>
-  </si>
-  <si>
-    <t>304487263</t>
-  </si>
-  <si>
-    <t>1182</t>
-  </si>
-  <si>
-    <t>Háromszéki utca</t>
-  </si>
-  <si>
-    <t>304487527/1</t>
-  </si>
-  <si>
-    <t>304487527</t>
-  </si>
-  <si>
-    <t>Páskomliget utca</t>
-  </si>
-  <si>
-    <t>304487531/1</t>
-  </si>
-  <si>
-    <t>304487531</t>
-  </si>
-  <si>
-    <t>Guyon Richárd utca</t>
-  </si>
-  <si>
-    <t>304487531/2</t>
-  </si>
-  <si>
-    <t>304487531/3</t>
-  </si>
-  <si>
-    <t>304487557/1</t>
-  </si>
-  <si>
-    <t>304487557</t>
-  </si>
-  <si>
-    <t>2251</t>
-  </si>
-  <si>
-    <t>TÁPIÓSZECSŐ</t>
-  </si>
-  <si>
-    <t>Balassi Bálint utca</t>
-  </si>
-  <si>
-    <t>304487596/1</t>
-  </si>
-  <si>
-    <t>304487596</t>
-  </si>
-  <si>
-    <t>Honfoglalás utca</t>
-  </si>
-  <si>
-    <t>304487622/1</t>
-  </si>
-  <si>
-    <t>304487622</t>
-  </si>
-  <si>
     <t>1214</t>
   </si>
   <si>
-    <t>Kossuth Lajos Utca</t>
-  </si>
-  <si>
-    <t>304487693/1</t>
-  </si>
-  <si>
-    <t>304487693</t>
-  </si>
-  <si>
-    <t>Balaton utca</t>
-  </si>
-  <si>
-    <t>304487754/1</t>
-  </si>
-  <si>
-    <t>304487754</t>
-  </si>
-  <si>
-    <t>2360</t>
-  </si>
-  <si>
-    <t>GYÁL</t>
-  </si>
-  <si>
-    <t>Kőrösi út</t>
-  </si>
-  <si>
-    <t>304487842/1</t>
-  </si>
-  <si>
-    <t>304487842</t>
-  </si>
-  <si>
-    <t>Törökőr utca</t>
-  </si>
-  <si>
-    <t>304487946/1</t>
-  </si>
-  <si>
-    <t>304487946</t>
-  </si>
-  <si>
-    <t>304487984/1</t>
-  </si>
-  <si>
-    <t>304487984</t>
-  </si>
-  <si>
-    <t>1195</t>
-  </si>
-  <si>
     <t>Zrínyi utca</t>
   </si>
   <si>
-    <t>304488013/1</t>
-  </si>
-  <si>
-    <t>304488013</t>
-  </si>
-  <si>
-    <t>Csömöri út</t>
-  </si>
-  <si>
-    <t>304543850/1</t>
-  </si>
-  <si>
-    <t>304543850</t>
-  </si>
-  <si>
-    <t>Petneházy utca</t>
-  </si>
-  <si>
-    <t>304544037/1</t>
-  </si>
-  <si>
-    <t>304544037</t>
-  </si>
-  <si>
-    <t>1095</t>
-  </si>
-  <si>
-    <t>304544088/1</t>
-  </si>
-  <si>
-    <t>304544088</t>
-  </si>
-  <si>
-    <t>Vezér Utca</t>
-  </si>
-  <si>
-    <t>304544088/2</t>
-  </si>
-  <si>
-    <t>304544148/1</t>
-  </si>
-  <si>
-    <t>304544148</t>
-  </si>
-  <si>
-    <t>1196</t>
-  </si>
-  <si>
-    <t>Templom tér</t>
-  </si>
-  <si>
-    <t>304544221/1</t>
-  </si>
-  <si>
-    <t>304544221</t>
-  </si>
-  <si>
     <t>2051</t>
   </si>
   <si>
     <t>BIATORBÁGY</t>
   </si>
   <si>
-    <t>304544432/1</t>
-  </si>
-  <si>
-    <t>304544432</t>
-  </si>
-  <si>
-    <t>Tázerdő dűlő</t>
-  </si>
-  <si>
-    <t>304544500/1</t>
-  </si>
-  <si>
-    <t>304544500</t>
-  </si>
-  <si>
-    <t>Róbert Károly körút</t>
-  </si>
-  <si>
-    <t>304544529/1</t>
-  </si>
-  <si>
-    <t>304544529</t>
-  </si>
-  <si>
-    <t>Mádi utca</t>
-  </si>
-  <si>
-    <t>304544573/1</t>
-  </si>
-  <si>
-    <t>304544573</t>
-  </si>
-  <si>
-    <t>Páfrányliget utca</t>
-  </si>
-  <si>
-    <t>304544655/1</t>
-  </si>
-  <si>
-    <t>304544655</t>
-  </si>
-  <si>
-    <t>Brassói utca</t>
-  </si>
-  <si>
-    <t>304544655/2</t>
-  </si>
-  <si>
-    <t>304544726/1</t>
-  </si>
-  <si>
-    <t>304544726</t>
-  </si>
-  <si>
-    <t>Kárókatona utca</t>
-  </si>
-  <si>
-    <t>304577138/1</t>
-  </si>
-  <si>
-    <t>304577138</t>
-  </si>
-  <si>
-    <t>1021</t>
-  </si>
-  <si>
-    <t>Budakeszi út</t>
-  </si>
-  <si>
-    <t>304577138/2</t>
-  </si>
-  <si>
-    <t>304577375/1</t>
-  </si>
-  <si>
-    <t>304577375</t>
-  </si>
-  <si>
-    <t>Virág utca</t>
-  </si>
-  <si>
-    <t>304618750/1</t>
-  </si>
-  <si>
-    <t>304618750</t>
-  </si>
-  <si>
-    <t>Madarász Viktor utca</t>
-  </si>
-  <si>
-    <t>304618762/1</t>
-  </si>
-  <si>
-    <t>304618762</t>
-  </si>
-  <si>
-    <t>99002215/1</t>
-  </si>
-  <si>
-    <t>99002215</t>
-  </si>
-  <si>
-    <t>1193</t>
-  </si>
-  <si>
-    <t>Bóné András utca</t>
-  </si>
-  <si>
-    <t>202603162600560501</t>
-  </si>
-  <si>
-    <t>NFD6-03-06-JW48</t>
-  </si>
-  <si>
-    <t>Alkotás utca</t>
-  </si>
-  <si>
-    <t>202603162600560502</t>
-  </si>
-  <si>
-    <t>159995579537972639</t>
-  </si>
-  <si>
-    <t>NFD6-03-08-5T23/XD</t>
-  </si>
-  <si>
-    <t>2097</t>
-  </si>
-  <si>
-    <t>PILISBOROSJENŐ</t>
-  </si>
-  <si>
-    <t>Kendermag utca</t>
-  </si>
-  <si>
-    <t>159995579537972707</t>
-  </si>
-  <si>
-    <t>202603172600581901</t>
-  </si>
-  <si>
-    <t>NFD6-03-09-Z4RJ</t>
-  </si>
-  <si>
-    <t>Köves út</t>
-  </si>
-  <si>
-    <t>202603172600581902</t>
-  </si>
-  <si>
-    <t>202603172600581903</t>
-  </si>
-  <si>
-    <t>202603162600591501</t>
-  </si>
-  <si>
-    <t>NFD6-03-11-BMYG</t>
-  </si>
-  <si>
     <t>Liliom utca</t>
   </si>
   <si>
-    <t>202603162600600001</t>
-  </si>
-  <si>
-    <t>NFD6-03-12-W9CB</t>
-  </si>
-  <si>
-    <t>2084</t>
-  </si>
-  <si>
-    <t>PILISSZENTIVÁN</t>
-  </si>
-  <si>
-    <t>Jószerencsét lakótelep</t>
-  </si>
-  <si>
-    <t>202603162600605201</t>
-  </si>
-  <si>
-    <t>NFD6-03-13-APKE</t>
-  </si>
-  <si>
-    <t>2095</t>
-  </si>
-  <si>
-    <t>PILISSZÁNTÓ</t>
-  </si>
-  <si>
-    <t>202603172600624301</t>
-  </si>
-  <si>
-    <t>NFD6-03-14-877R</t>
-  </si>
-  <si>
     <t>2339</t>
   </si>
   <si>
     <t>MAJOSHÁZA</t>
   </si>
   <si>
-    <t>Kossuth utca</t>
-  </si>
-  <si>
-    <t>202603162600614301</t>
-  </si>
-  <si>
-    <t>NFD6-03-14-8PSM</t>
-  </si>
-  <si>
-    <t>Csongor utca</t>
-  </si>
-  <si>
-    <t>202603172600614601</t>
-  </si>
-  <si>
-    <t>NFD6-03-14-RE4Z</t>
-  </si>
-  <si>
-    <t>1102</t>
-  </si>
-  <si>
-    <t>Halom utca</t>
-  </si>
-  <si>
-    <t>202603172600640101</t>
-  </si>
-  <si>
-    <t>NFD6-03-16-3VEY</t>
-  </si>
-  <si>
     <t>1046</t>
   </si>
   <si>
-    <t>Mikes Kelemen köz</t>
-  </si>
-  <si>
-    <t>202603172600640701</t>
-  </si>
-  <si>
-    <t>NFD6-03-16-8C2M</t>
-  </si>
-  <si>
-    <t>Bőröndös utca</t>
-  </si>
-  <si>
-    <t>202603172600632001</t>
-  </si>
-  <si>
-    <t>NFD6-03-16-9PSK</t>
-  </si>
-  <si>
-    <t>1213</t>
-  </si>
-  <si>
-    <t>Szentmiklósi út</t>
-  </si>
-  <si>
-    <t>202603172600635501</t>
-  </si>
-  <si>
-    <t>NFD6-03-16-C9JA</t>
-  </si>
-  <si>
     <t>1223</t>
   </si>
   <si>
-    <t>Szent István utca</t>
-  </si>
-  <si>
-    <t>202603172600633001</t>
-  </si>
-  <si>
-    <t>NFD6-03-16-ECAG</t>
-  </si>
-  <si>
-    <t>1047</t>
-  </si>
-  <si>
-    <t>Irányi Dániel utca</t>
-  </si>
-  <si>
-    <t>202603172600633002</t>
-  </si>
-  <si>
-    <t>202603172600633003</t>
-  </si>
-  <si>
-    <t>202603172600635001</t>
-  </si>
-  <si>
-    <t>NFD6-03-16-GYWA</t>
-  </si>
-  <si>
     <t>2141</t>
   </si>
   <si>
     <t>CSÖMÖR</t>
   </si>
   <si>
-    <t>202603172600637801</t>
-  </si>
-  <si>
-    <t>NFD6-03-16-JVWS</t>
-  </si>
-  <si>
     <t>1165</t>
   </si>
   <si>
-    <t>Mátyásdomb tér</t>
-  </si>
-  <si>
-    <t>202603172600639201</t>
-  </si>
-  <si>
-    <t>NFD6-03-16-L63L</t>
-  </si>
-  <si>
-    <t>István út</t>
-  </si>
-  <si>
-    <t>202603172600638001</t>
-  </si>
-  <si>
-    <t>NFD6-03-16-Y6M6</t>
-  </si>
-  <si>
-    <t>Március utca</t>
-  </si>
-  <si>
-    <t>202603172600636901</t>
-  </si>
-  <si>
-    <t>NFD6-03-16-ZHNK</t>
-  </si>
-  <si>
-    <t>1114</t>
-  </si>
-  <si>
-    <t>Bocskai út</t>
-  </si>
-  <si>
-    <t>202603172600577001</t>
-  </si>
-  <si>
-    <t>NFE6-03-09-EEYZ</t>
-  </si>
-  <si>
-    <t>202603162600629901</t>
-  </si>
-  <si>
-    <t>NFE6-03-15-QRLT</t>
-  </si>
-  <si>
-    <t>202603172600632601</t>
-  </si>
-  <si>
-    <t>NFE6-03-16-28D6</t>
-  </si>
-  <si>
-    <t>János utca</t>
-  </si>
-  <si>
-    <t>202603172600634801</t>
-  </si>
-  <si>
-    <t>NFE6-03-16-6K3E</t>
-  </si>
-  <si>
-    <t>202603172600636701</t>
-  </si>
-  <si>
-    <t>NFE6-03-16-UT6R</t>
-  </si>
-  <si>
-    <t>Kápolna út</t>
-  </si>
-  <si>
-    <t>159995579537957827</t>
-  </si>
-  <si>
-    <t>SA26/H000996</t>
-  </si>
-  <si>
-    <t>159995579537957834</t>
-  </si>
-  <si>
-    <t>267004091</t>
-  </si>
-  <si>
-    <t>267004116</t>
-  </si>
-  <si>
-    <t>267004055</t>
-  </si>
-  <si>
-    <t>267004038</t>
-  </si>
-  <si>
-    <t>267004103</t>
-  </si>
-  <si>
-    <t>267004092</t>
+    <t>69b3d65b6967eb2a8b5cd169</t>
+  </si>
+  <si>
+    <t>260211-F00013682</t>
+  </si>
+  <si>
+    <t>2045</t>
+  </si>
+  <si>
+    <t>TÖRÖKBÁLINT</t>
+  </si>
+  <si>
+    <t>Nádasdy köz</t>
+  </si>
+  <si>
+    <t>69a6d6b851e7020fc80c1786</t>
+  </si>
+  <si>
+    <t>260303-F00008211</t>
+  </si>
+  <si>
+    <t>1031</t>
+  </si>
+  <si>
+    <t>Őrlő utca</t>
+  </si>
+  <si>
+    <t>69aa854851e7020fc80c5adc</t>
+  </si>
+  <si>
+    <t>260306-W00001194</t>
+  </si>
+  <si>
+    <t>2767</t>
+  </si>
+  <si>
+    <t>TÁPIÓGYÖRGYE</t>
+  </si>
+  <si>
+    <t>Ady Endre út</t>
+  </si>
+  <si>
+    <t>69b3d6d36967eb2a8b5cd16c</t>
+  </si>
+  <si>
+    <t>260308-F00001696</t>
+  </si>
+  <si>
+    <t>Szőlő utca</t>
+  </si>
+  <si>
+    <t>69b0414851e7020fc80cc057</t>
+  </si>
+  <si>
+    <t>260310-F00013434</t>
+  </si>
+  <si>
+    <t>Hunyadi János utca</t>
+  </si>
+  <si>
+    <t>69b0414851e7020fc80cc058</t>
+  </si>
+  <si>
+    <t>69b93b68d96b4f4a2437cce0</t>
+  </si>
+  <si>
+    <t>260310-W00009301</t>
+  </si>
+  <si>
+    <t>69ba371ad96b4f4a2437db56</t>
+  </si>
+  <si>
+    <t>260310-W00009315</t>
+  </si>
+  <si>
+    <t>1035</t>
+  </si>
+  <si>
+    <t>Kórház utca</t>
+  </si>
+  <si>
+    <t>69b05e8951e7020fc80cc390</t>
+  </si>
+  <si>
+    <t>260310-W00010882</t>
+  </si>
+  <si>
+    <t>2017</t>
+  </si>
+  <si>
+    <t>PÓCSMEGYER</t>
+  </si>
+  <si>
+    <t>Kossuth út</t>
+  </si>
+  <si>
+    <t>69b29d536967eb2a8b5cbf82</t>
+  </si>
+  <si>
+    <t>260311-F00000568-1</t>
+  </si>
+  <si>
+    <t>2013</t>
+  </si>
+  <si>
+    <t>POMÁZ</t>
+  </si>
+  <si>
+    <t>Beniczky utca</t>
+  </si>
+  <si>
+    <t>69b95688d96b4f4a2437d0bb</t>
+  </si>
+  <si>
+    <t>260311-F00009142-1</t>
+  </si>
+  <si>
+    <t>1157</t>
+  </si>
+  <si>
+    <t>Nyírpalota út</t>
+  </si>
+  <si>
+    <t>69b1469551e7020fc80ccffc</t>
+  </si>
+  <si>
+    <t>260311-W00004220</t>
+  </si>
+  <si>
+    <t>2310</t>
+  </si>
+  <si>
+    <t>SZIGETSZENTMIKLÓS</t>
+  </si>
+  <si>
+    <t>Dobó István utca</t>
+  </si>
+  <si>
+    <t>69b1469551e7020fc80ccffe</t>
+  </si>
+  <si>
+    <t>69b1aa6751e7020fc80ce0f4</t>
+  </si>
+  <si>
+    <t>260311-W00010324</t>
+  </si>
+  <si>
+    <t>Erdősor utca</t>
+  </si>
+  <si>
+    <t>69b96685d96b4f4a2437d364</t>
+  </si>
+  <si>
+    <t>260313-F00006586</t>
+  </si>
+  <si>
+    <t>1135</t>
+  </si>
+  <si>
+    <t>Csata utca</t>
+  </si>
+  <si>
+    <t>69b405ba6967eb2a8b5cd895</t>
+  </si>
+  <si>
+    <t>260313-F00007753</t>
+  </si>
+  <si>
+    <t>2023</t>
+  </si>
+  <si>
+    <t>DUNABOGDÁNY</t>
+  </si>
+  <si>
+    <t>Kert utca</t>
+  </si>
+  <si>
+    <t>69b423056967eb2a8b5cdc74</t>
+  </si>
+  <si>
+    <t>260313-F00010680</t>
+  </si>
+  <si>
+    <t>Nagy utca</t>
+  </si>
+  <si>
+    <t>69b51efd6967eb2a8b5ce356</t>
+  </si>
+  <si>
+    <t>260314-F00001044</t>
+  </si>
+  <si>
+    <t>Dózsa György út</t>
+  </si>
+  <si>
+    <t>69b53d6b6967eb2a8b5ce670</t>
+  </si>
+  <si>
+    <t>260314-F00002864</t>
+  </si>
+  <si>
+    <t>1028</t>
+  </si>
+  <si>
+    <t>Hidegkúti út</t>
+  </si>
+  <si>
+    <t>69b926a9d96b4f4a2437c995</t>
+  </si>
+  <si>
+    <t>260314-F00004193</t>
+  </si>
+  <si>
+    <t>Pacsirta utca</t>
+  </si>
+  <si>
+    <t>69b65c8c6967eb2a8b5cee01</t>
+  </si>
+  <si>
+    <t>260315-W00001007</t>
+  </si>
+  <si>
+    <t>2700</t>
+  </si>
+  <si>
+    <t>CEGLÉD</t>
+  </si>
+  <si>
+    <t>Árpa utca</t>
+  </si>
+  <si>
+    <t>69b90922d96b4f4a2437c50f</t>
+  </si>
+  <si>
+    <t>260315-W00003743</t>
+  </si>
+  <si>
+    <t>2336</t>
+  </si>
+  <si>
+    <t>DUNAVARSÁNY</t>
+  </si>
+  <si>
+    <t>Homok utca</t>
+  </si>
+  <si>
+    <t>69b7f327d96b4f4a2437b648</t>
+  </si>
+  <si>
+    <t>SZ-815</t>
+  </si>
+  <si>
+    <t>260316-F00007232</t>
+  </si>
+  <si>
+    <t>1143</t>
+  </si>
+  <si>
+    <t>Francia út</t>
+  </si>
+  <si>
+    <t>69b7fb69d96b4f4a2437b76d</t>
+  </si>
+  <si>
+    <t>260316-F00008378</t>
+  </si>
+  <si>
+    <t>2213</t>
+  </si>
+  <si>
+    <t>MONORIERDŐ</t>
+  </si>
+  <si>
+    <t>Bokor utca</t>
+  </si>
+  <si>
+    <t>69b80cffd96b4f4a2437ba9f</t>
+  </si>
+  <si>
+    <t>260316-F00010713</t>
+  </si>
+  <si>
+    <t>2711</t>
+  </si>
+  <si>
+    <t>TÁPIÓSZENTMÁRTON</t>
+  </si>
+  <si>
+    <t>Sashegy</t>
+  </si>
+  <si>
+    <t>69b812e5d96b4f4a2437bb88</t>
+  </si>
+  <si>
+    <t>260316-F00011135</t>
+  </si>
+  <si>
+    <t>Erdőszőlő</t>
+  </si>
+  <si>
+    <t>69ba5edad96b4f4a2437dcee</t>
+  </si>
+  <si>
+    <t>260316-F00013280</t>
+  </si>
+  <si>
+    <t>1115</t>
+  </si>
+  <si>
+    <t>Fejér Lipót utca</t>
+  </si>
+  <si>
+    <t>69b840a7d96b4f4a2437c10c</t>
+  </si>
+  <si>
+    <t>260316-F00014833</t>
+  </si>
+  <si>
+    <t>Táncsics Mihály utca</t>
+  </si>
+  <si>
+    <t>69b840a7d96b4f4a2437c10d</t>
+  </si>
+  <si>
+    <t>69b99012d96b4f4a2437d86c</t>
+  </si>
+  <si>
+    <t>260316-F00015387</t>
+  </si>
+  <si>
+    <t>1118</t>
+  </si>
+  <si>
+    <t>Törökugrató utca</t>
+  </si>
+  <si>
+    <t>69b7b6396967eb2a8b5cf59a</t>
+  </si>
+  <si>
+    <t>260316-W00001447</t>
+  </si>
+  <si>
+    <t>Káposztáskert utca</t>
+  </si>
+  <si>
+    <t>69b8152cd96b4f4a2437bbe0</t>
+  </si>
+  <si>
+    <t>260316-W00006639</t>
+  </si>
+  <si>
+    <t>2373</t>
+  </si>
+  <si>
+    <t>DABAS</t>
+  </si>
+  <si>
+    <t>Örkényi út</t>
+  </si>
+  <si>
+    <t>69b8152cd96b4f4a2437bbe4</t>
+  </si>
+  <si>
+    <t>69b85920d96b4f4a2437c238</t>
+  </si>
+  <si>
+    <t>260316-W00009595</t>
+  </si>
+  <si>
+    <t>2173</t>
+  </si>
+  <si>
+    <t>KARTAL</t>
+  </si>
+  <si>
+    <t>Mártírok útja</t>
+  </si>
+  <si>
+    <t>69b85920d96b4f4a2437c239</t>
+  </si>
+  <si>
+    <t>69b85a52d96b4f4a2437c23f</t>
+  </si>
+  <si>
+    <t>260316-W00010388</t>
+  </si>
+  <si>
+    <t>Tábornok utca</t>
+  </si>
+  <si>
+    <t>69b85a52d96b4f4a2437c240</t>
+  </si>
+  <si>
+    <t>69b97292d96b4f4a2437d51c</t>
+  </si>
+  <si>
+    <t>260317-F00012345</t>
+  </si>
+  <si>
+    <t>1082</t>
+  </si>
+  <si>
+    <t>Baross utca</t>
+  </si>
+  <si>
+    <t>69b9aaa1d96b4f4a2437d9fe</t>
+  </si>
+  <si>
+    <t>260317-F00015151</t>
+  </si>
+  <si>
+    <t>Párkány utca</t>
+  </si>
+  <si>
+    <t>69b95198d96b4f4a2437cfdd</t>
+  </si>
+  <si>
+    <t>260317-W00005454</t>
+  </si>
+  <si>
+    <t>Teve utca</t>
+  </si>
+  <si>
+    <t>69b97290d96b4f4a2437d4f9</t>
+  </si>
+  <si>
+    <t>260317-W00007012</t>
+  </si>
+  <si>
+    <t>1158</t>
+  </si>
+  <si>
+    <t>Neptun utca</t>
+  </si>
+  <si>
+    <t>69b98523d96b4f4a2437d74c</t>
+  </si>
+  <si>
+    <t>260317-W00008316</t>
+  </si>
+  <si>
+    <t>Sárpatak utca</t>
+  </si>
+  <si>
+    <t>69b9b429d96b4f4a2437da5b</t>
+  </si>
+  <si>
+    <t>260317-W00010937</t>
+  </si>
+  <si>
+    <t>1113</t>
+  </si>
+  <si>
+    <t>Dinnye utca</t>
+  </si>
+  <si>
+    <t>69b9b429d96b4f4a2437da5d</t>
+  </si>
+  <si>
+    <t>69b9c594d96b4f4a2437daca</t>
+  </si>
+  <si>
+    <t>SZ-820</t>
+  </si>
+  <si>
+    <t>260317-W00011768</t>
+  </si>
+  <si>
+    <t>Nagyszeben utca</t>
+  </si>
+  <si>
+    <t>69ba5366d96b4f4a2437dbee</t>
+  </si>
+  <si>
+    <t>260318-F00000469</t>
+  </si>
+  <si>
+    <t>Szilaspatak utca</t>
+  </si>
+  <si>
+    <t>69ba77bbd96b4f4a2437e12b</t>
+  </si>
+  <si>
+    <t>260318-W00003476</t>
+  </si>
+  <si>
+    <t>FIZZ-1000826603</t>
+  </si>
+  <si>
+    <t>267003822</t>
+  </si>
+  <si>
+    <t>József Attila utca</t>
+  </si>
+  <si>
+    <t>1449-135794</t>
+  </si>
+  <si>
+    <t>267004130</t>
+  </si>
+  <si>
+    <t>Bem rakpart</t>
+  </si>
+  <si>
+    <t>FIZZ-1000838075</t>
+  </si>
+  <si>
+    <t>267004139</t>
+  </si>
+  <si>
+    <t>2115</t>
+  </si>
+  <si>
+    <t>VÁCSZENTLÁSZLÓ</t>
+  </si>
+  <si>
+    <t>Váci Mihály utca</t>
+  </si>
+  <si>
+    <t>FIZZ-1000838632</t>
+  </si>
+  <si>
+    <t>267004163</t>
+  </si>
+  <si>
+    <t>Kincsem U</t>
+  </si>
+  <si>
+    <t>FIZZ-1000838792</t>
+  </si>
+  <si>
+    <t>267004169</t>
+  </si>
+  <si>
+    <t>TABÁN UTCA</t>
+  </si>
+  <si>
+    <t>FIZZ-1000839110</t>
+  </si>
+  <si>
+    <t>267004175</t>
+  </si>
+  <si>
+    <t>2330</t>
+  </si>
+  <si>
+    <t>DUNAHARASZTI</t>
+  </si>
+  <si>
+    <t>FIZZ-1000839256</t>
+  </si>
+  <si>
+    <t>267004177</t>
+  </si>
+  <si>
+    <t>2634</t>
+  </si>
+  <si>
+    <t>NAGYBÖRZSÖNY</t>
+  </si>
+  <si>
+    <t>Petőfi utca</t>
+  </si>
+  <si>
+    <t>26MPE0002981/1</t>
+  </si>
+  <si>
+    <t>26MPE0002981</t>
+  </si>
+  <si>
+    <t>Petőfi Sándor utca,</t>
+  </si>
+  <si>
+    <t>303277688/1</t>
+  </si>
+  <si>
+    <t>303277688</t>
+  </si>
+  <si>
+    <t>Zsélyi Aladár utca</t>
+  </si>
+  <si>
+    <t>303753487/1</t>
+  </si>
+  <si>
+    <t>303753487</t>
+  </si>
+  <si>
+    <t>Kőrisfa utca</t>
+  </si>
+  <si>
+    <t>303753487/2</t>
+  </si>
+  <si>
+    <t>303753487/3</t>
+  </si>
+  <si>
+    <t>303838421/1</t>
+  </si>
+  <si>
+    <t>303838421</t>
+  </si>
+  <si>
+    <t>Homoktövis utca</t>
+  </si>
+  <si>
+    <t>303838421/2</t>
+  </si>
+  <si>
+    <t>304104709/1</t>
+  </si>
+  <si>
+    <t>304104709</t>
+  </si>
+  <si>
+    <t>2151</t>
+  </si>
+  <si>
+    <t>FÓT</t>
+  </si>
+  <si>
+    <t>I. András utca</t>
+  </si>
+  <si>
+    <t>304149239/1</t>
+  </si>
+  <si>
+    <t>304149239</t>
+  </si>
+  <si>
+    <t>2113</t>
+  </si>
+  <si>
+    <t>ERDŐKERTES</t>
+  </si>
+  <si>
+    <t>Fő út</t>
+  </si>
+  <si>
+    <t>304149445/1</t>
+  </si>
+  <si>
+    <t>304149445</t>
+  </si>
+  <si>
+    <t>Balassa Bálint utca</t>
+  </si>
+  <si>
+    <t>304248355/1</t>
+  </si>
+  <si>
+    <t>304248355</t>
+  </si>
+  <si>
+    <t>Muhar utca</t>
+  </si>
+  <si>
+    <t>304248670/1</t>
+  </si>
+  <si>
+    <t>304248670</t>
+  </si>
+  <si>
+    <t>Tábor utca</t>
+  </si>
+  <si>
+    <t>304309284/1</t>
+  </si>
+  <si>
+    <t>304309284</t>
+  </si>
+  <si>
+    <t>Jegenye utca</t>
+  </si>
+  <si>
+    <t>304309284/2</t>
+  </si>
+  <si>
+    <t>304309359/1</t>
+  </si>
+  <si>
+    <t>304309359</t>
+  </si>
+  <si>
+    <t>2365</t>
+  </si>
+  <si>
+    <t>INÁRCS</t>
+  </si>
+  <si>
+    <t>Írisz utca /</t>
+  </si>
+  <si>
+    <t>304309626/2/1</t>
+  </si>
+  <si>
+    <t>304309626/2</t>
+  </si>
+  <si>
+    <t>2635</t>
+  </si>
+  <si>
+    <t>VÁMOSMIKOLA</t>
+  </si>
+  <si>
+    <t>304362446/1</t>
+  </si>
+  <si>
+    <t>304362446</t>
+  </si>
+  <si>
+    <t>2340</t>
+  </si>
+  <si>
+    <t>KISKUNLACHÁZA</t>
+  </si>
+  <si>
+    <t>Platán sor</t>
+  </si>
+  <si>
+    <t>304362446/2</t>
+  </si>
+  <si>
+    <t>304362446/3</t>
+  </si>
+  <si>
+    <t>304362553/1</t>
+  </si>
+  <si>
+    <t>304362553</t>
+  </si>
+  <si>
+    <t>2600</t>
+  </si>
+  <si>
+    <t>VÁC</t>
+  </si>
+  <si>
+    <t>Cserhát utca</t>
+  </si>
+  <si>
+    <t>304362553/2</t>
+  </si>
+  <si>
+    <t>304362553/3</t>
+  </si>
+  <si>
+    <t>304362648/1</t>
+  </si>
+  <si>
+    <t>304362648</t>
+  </si>
+  <si>
+    <t>304362715/1</t>
+  </si>
+  <si>
+    <t>304362715</t>
+  </si>
+  <si>
+    <t>2040</t>
+  </si>
+  <si>
+    <t>BUDAÖRS</t>
+  </si>
+  <si>
+    <t>Panoráma utca</t>
+  </si>
+  <si>
+    <t>304429908/1</t>
+  </si>
+  <si>
+    <t>304429908</t>
+  </si>
+  <si>
+    <t>1084</t>
+  </si>
+  <si>
+    <t>Nagy Fuvaros utca</t>
+  </si>
+  <si>
+    <t>304430114/1</t>
+  </si>
+  <si>
+    <t>304430114</t>
+  </si>
+  <si>
+    <t>Süvöltő utca</t>
+  </si>
+  <si>
+    <t>304430270/1</t>
+  </si>
+  <si>
+    <t>304430270</t>
+  </si>
+  <si>
+    <t>Zsókavár utca</t>
+  </si>
+  <si>
+    <t>304430270/2</t>
+  </si>
+  <si>
+    <t>304487425/1</t>
+  </si>
+  <si>
+    <t>304487425</t>
+  </si>
+  <si>
+    <t>2234</t>
+  </si>
+  <si>
+    <t>MAGLÓD</t>
+  </si>
+  <si>
+    <t>Perczel Mór utca</t>
+  </si>
+  <si>
+    <t>304487643/1</t>
+  </si>
+  <si>
+    <t>304487643</t>
+  </si>
+  <si>
+    <t>Némedi út</t>
+  </si>
+  <si>
+    <t>304487829/1</t>
+  </si>
+  <si>
+    <t>304487829</t>
+  </si>
+  <si>
+    <t>Pácoló utca</t>
+  </si>
+  <si>
+    <t>304487980/1</t>
+  </si>
+  <si>
+    <t>304487980</t>
+  </si>
+  <si>
+    <t>Újlak utca</t>
+  </si>
+  <si>
+    <t>304487980/2</t>
+  </si>
+  <si>
+    <t>304543914/1</t>
+  </si>
+  <si>
+    <t>304543914</t>
+  </si>
+  <si>
+    <t>Csontváry Kosztka Tivadar utca</t>
+  </si>
+  <si>
+    <t>304544031/1</t>
+  </si>
+  <si>
+    <t>304544031</t>
+  </si>
+  <si>
+    <t>Rudolf utca</t>
+  </si>
+  <si>
+    <t>304544210/1</t>
+  </si>
+  <si>
+    <t>304544210</t>
+  </si>
+  <si>
+    <t>304544278/1</t>
+  </si>
+  <si>
+    <t>304544278</t>
+  </si>
+  <si>
+    <t>2712</t>
+  </si>
+  <si>
+    <t>NYÁRSAPÁT</t>
+  </si>
+  <si>
+    <t>Köz dűlő</t>
+  </si>
+  <si>
+    <t>304544293/1</t>
+  </si>
+  <si>
+    <t>304544293</t>
+  </si>
+  <si>
+    <t>1136</t>
+  </si>
+  <si>
+    <t>Hegedűs Gyula utca</t>
+  </si>
+  <si>
+    <t>304544578/1</t>
+  </si>
+  <si>
+    <t>304544578</t>
+  </si>
+  <si>
+    <t>Amfiteátrum utca</t>
+  </si>
+  <si>
+    <t>304576505/1</t>
+  </si>
+  <si>
+    <t>304576505</t>
+  </si>
+  <si>
+    <t>1133</t>
+  </si>
+  <si>
+    <t>Bessenyei utca</t>
+  </si>
+  <si>
+    <t>304577027/1</t>
+  </si>
+  <si>
+    <t>304577027</t>
+  </si>
+  <si>
+    <t>Csokonai Vitéz Mihály utca</t>
+  </si>
+  <si>
+    <t>304577027/2</t>
+  </si>
+  <si>
+    <t>304577027/3</t>
+  </si>
+  <si>
+    <t>304577084/1</t>
+  </si>
+  <si>
+    <t>304577084</t>
+  </si>
+  <si>
+    <t>Hermina út</t>
+  </si>
+  <si>
+    <t>304577105/1</t>
+  </si>
+  <si>
+    <t>304577105</t>
+  </si>
+  <si>
+    <t>304577256/1</t>
+  </si>
+  <si>
+    <t>304577256</t>
+  </si>
+  <si>
+    <t>304577393/1</t>
+  </si>
+  <si>
+    <t>304577393</t>
+  </si>
+  <si>
+    <t>Pillangó park</t>
+  </si>
+  <si>
+    <t>304618651/1</t>
+  </si>
+  <si>
+    <t>304618651</t>
+  </si>
+  <si>
+    <t>Ady Endre utca</t>
+  </si>
+  <si>
+    <t>304618854/1</t>
+  </si>
+  <si>
+    <t>304618854</t>
+  </si>
+  <si>
+    <t>1211</t>
+  </si>
+  <si>
+    <t>Duna lejáró</t>
+  </si>
+  <si>
+    <t>304618872/1</t>
+  </si>
+  <si>
+    <t>304618872</t>
+  </si>
+  <si>
+    <t>1083</t>
+  </si>
+  <si>
+    <t>Füvészkert utca</t>
+  </si>
+  <si>
+    <t>304619007/1</t>
+  </si>
+  <si>
+    <t>304619007</t>
+  </si>
+  <si>
+    <t>304619126/1</t>
+  </si>
+  <si>
+    <t>304619126</t>
+  </si>
+  <si>
+    <t>1108</t>
+  </si>
+  <si>
+    <t>Agyagfejtő utca</t>
+  </si>
+  <si>
+    <t>304619200/1</t>
+  </si>
+  <si>
+    <t>304619200</t>
+  </si>
+  <si>
+    <t>Szent Erzsébet utca</t>
+  </si>
+  <si>
+    <t>304619203/1</t>
+  </si>
+  <si>
+    <t>304619203</t>
+  </si>
+  <si>
+    <t>fenyvesi nagy út</t>
+  </si>
+  <si>
+    <t>304619224/1</t>
+  </si>
+  <si>
+    <t>SZ-836</t>
+  </si>
+  <si>
+    <t>304619224</t>
+  </si>
+  <si>
+    <t>Kútvölgyi út</t>
+  </si>
+  <si>
+    <t>304619291/1</t>
+  </si>
+  <si>
+    <t>304619291</t>
+  </si>
+  <si>
+    <t>Fehérvári út</t>
+  </si>
+  <si>
+    <t>304619390/1</t>
+  </si>
+  <si>
+    <t>304619390</t>
+  </si>
+  <si>
+    <t>304619429/1</t>
+  </si>
+  <si>
+    <t>304619429</t>
+  </si>
+  <si>
+    <t>Lenke utca</t>
+  </si>
+  <si>
+    <t>304619536/1</t>
+  </si>
+  <si>
+    <t>304619536</t>
+  </si>
+  <si>
+    <t>1064</t>
+  </si>
+  <si>
+    <t>Vörösmarty utca</t>
+  </si>
+  <si>
+    <t>304619625/1</t>
+  </si>
+  <si>
+    <t>304619625</t>
+  </si>
+  <si>
+    <t>1101</t>
+  </si>
+  <si>
+    <t>Kőbányai út</t>
+  </si>
+  <si>
+    <t>304675694/1</t>
+  </si>
+  <si>
+    <t>304675694</t>
+  </si>
+  <si>
+    <t>2071</t>
+  </si>
+  <si>
+    <t>PÁTY</t>
+  </si>
+  <si>
+    <t>Móricz Zsigmond utca</t>
+  </si>
+  <si>
+    <t>304675801/1</t>
+  </si>
+  <si>
+    <t>304675801</t>
+  </si>
+  <si>
+    <t>1131</t>
+  </si>
+  <si>
+    <t>Tomori Utca</t>
+  </si>
+  <si>
+    <t>304675844/1</t>
+  </si>
+  <si>
+    <t>304675844</t>
+  </si>
+  <si>
+    <t>1184</t>
+  </si>
+  <si>
+    <t>Mikszáth Kálmán utca</t>
+  </si>
+  <si>
+    <t>304675872/1</t>
+  </si>
+  <si>
+    <t>304675872</t>
+  </si>
+  <si>
+    <t>Kiránduló utca</t>
+  </si>
+  <si>
+    <t>304675954/1</t>
+  </si>
+  <si>
+    <t>304675954</t>
+  </si>
+  <si>
+    <t>1071</t>
+  </si>
+  <si>
+    <t>304675981/1</t>
+  </si>
+  <si>
+    <t>304675981</t>
+  </si>
+  <si>
+    <t>Ugró Gyula sor</t>
+  </si>
+  <si>
+    <t>304675981/2</t>
+  </si>
+  <si>
+    <t>304675981/3</t>
+  </si>
+  <si>
+    <t>304675997/1</t>
+  </si>
+  <si>
+    <t>304675997</t>
+  </si>
+  <si>
+    <t>Jókai utca</t>
+  </si>
+  <si>
+    <t>304676140/1</t>
+  </si>
+  <si>
+    <t>304676140</t>
+  </si>
+  <si>
+    <t>Liszt Ferenc sétány</t>
+  </si>
+  <si>
+    <t>304676159/1</t>
+  </si>
+  <si>
+    <t>304676159</t>
+  </si>
+  <si>
+    <t>Tabán utca</t>
+  </si>
+  <si>
+    <t>304676205/1</t>
+  </si>
+  <si>
+    <t>304676205</t>
+  </si>
+  <si>
+    <t>Felsőhatár út</t>
+  </si>
+  <si>
+    <t>304676304/1</t>
+  </si>
+  <si>
+    <t>304676304</t>
+  </si>
+  <si>
+    <t>Toboz utca</t>
+  </si>
+  <si>
+    <t>304676401/1</t>
+  </si>
+  <si>
+    <t>304676401</t>
+  </si>
+  <si>
+    <t>2094</t>
+  </si>
+  <si>
+    <t>NAGYKOVÁCSI</t>
+  </si>
+  <si>
+    <t>Bánya utca</t>
+  </si>
+  <si>
+    <t>304676417/1</t>
+  </si>
+  <si>
+    <t>304676417</t>
+  </si>
+  <si>
+    <t>1116</t>
+  </si>
+  <si>
+    <t>Kondorosi út</t>
+  </si>
+  <si>
+    <t>304676454/1</t>
+  </si>
+  <si>
+    <t>304676454</t>
+  </si>
+  <si>
+    <t>Kinizsi utca</t>
+  </si>
+  <si>
+    <t>304726779/1</t>
+  </si>
+  <si>
+    <t>304726779</t>
+  </si>
+  <si>
+    <t>Riadó utca</t>
+  </si>
+  <si>
+    <t>304726908/1</t>
+  </si>
+  <si>
+    <t>304726908</t>
+  </si>
+  <si>
+    <t>Vak Bottyán utca</t>
+  </si>
+  <si>
+    <t>304726908/2</t>
+  </si>
+  <si>
+    <t>304726908/3</t>
+  </si>
+  <si>
+    <t>304726958/1</t>
+  </si>
+  <si>
+    <t>304726958</t>
+  </si>
+  <si>
+    <t>1144</t>
+  </si>
+  <si>
+    <t>Gvadányi utca</t>
+  </si>
+  <si>
+    <t>304727007/1</t>
+  </si>
+  <si>
+    <t>304727007</t>
+  </si>
+  <si>
+    <t>Margit körút</t>
+  </si>
+  <si>
+    <t>304727116/1</t>
+  </si>
+  <si>
+    <t>304727116</t>
+  </si>
+  <si>
+    <t>1086</t>
+  </si>
+  <si>
+    <t>Teleki László tér</t>
+  </si>
+  <si>
+    <t>304727116/2</t>
+  </si>
+  <si>
+    <t>159995579538324383</t>
+  </si>
+  <si>
+    <t>ID4993_XD</t>
+  </si>
+  <si>
+    <t>BUDAPEST VII. KER</t>
+  </si>
+  <si>
+    <t>Peterdy utca</t>
+  </si>
+  <si>
+    <t>159995579538311185</t>
+  </si>
+  <si>
+    <t>NFD6-03-01-CD3V/CSXD</t>
+  </si>
+  <si>
+    <t>2083</t>
+  </si>
+  <si>
+    <t>SOLYMÁR</t>
+  </si>
+  <si>
+    <t>Marcibányi utca</t>
+  </si>
+  <si>
+    <t>202603162600618501</t>
+  </si>
+  <si>
+    <t>NFD6-03-14-ARE6</t>
+  </si>
+  <si>
+    <t>Kápolna utca</t>
+  </si>
+  <si>
+    <t>202603162600619301</t>
+  </si>
+  <si>
+    <t>NFD6-03-14-EXMJ</t>
+  </si>
+  <si>
+    <t>2192</t>
+  </si>
+  <si>
+    <t>HÉVÍZGYÖRK</t>
+  </si>
+  <si>
+    <t>Orgona utca</t>
+  </si>
+  <si>
+    <t>202603162600615501</t>
+  </si>
+  <si>
+    <t>NFD6-03-14-XK5S</t>
+  </si>
+  <si>
+    <t>Dobó Katica utca</t>
+  </si>
+  <si>
+    <t>202603172600638801</t>
+  </si>
+  <si>
+    <t>NFD6-03-16-SHJH</t>
+  </si>
+  <si>
+    <t>Iskola utca</t>
+  </si>
+  <si>
+    <t>202603172600637101</t>
+  </si>
+  <si>
+    <t>NFD6-03-16-ZZNQ</t>
+  </si>
+  <si>
+    <t>2135</t>
+  </si>
+  <si>
+    <t>CSÖRÖG</t>
+  </si>
+  <si>
+    <t>202603182600646401</t>
+  </si>
+  <si>
+    <t>NFD6-03-17-545T</t>
+  </si>
+  <si>
+    <t>1036</t>
+  </si>
+  <si>
+    <t>Nagyszombat utca</t>
+  </si>
+  <si>
+    <t>202603182600650901</t>
+  </si>
+  <si>
+    <t>NFD6-03-17-8NSY</t>
+  </si>
+  <si>
+    <t>1238</t>
+  </si>
+  <si>
+    <t>Láng Endre utca</t>
+  </si>
+  <si>
+    <t>202603182600651901</t>
+  </si>
+  <si>
+    <t>NFD6-03-17-9ALH</t>
+  </si>
+  <si>
+    <t>Hajnóczy József utca</t>
+  </si>
+  <si>
+    <t>202603182600651902</t>
+  </si>
+  <si>
+    <t>202603182600651903</t>
+  </si>
+  <si>
+    <t>202603182600646201</t>
+  </si>
+  <si>
+    <t>NFD6-03-17-ALAA</t>
+  </si>
+  <si>
+    <t>Szilágyi Dezső utca</t>
+  </si>
+  <si>
+    <t>202603182600654401</t>
+  </si>
+  <si>
+    <t>NFD6-03-17-AR33</t>
+  </si>
+  <si>
+    <t>Nagykőrösi út</t>
+  </si>
+  <si>
+    <t>202603182600654402</t>
+  </si>
+  <si>
+    <t>202603182600646301</t>
+  </si>
+  <si>
+    <t>NFD6-03-17-KEES</t>
+  </si>
+  <si>
+    <t>Juhász Gyula utca</t>
+  </si>
+  <si>
+    <t>202603182600648301</t>
+  </si>
+  <si>
+    <t>NFD6-03-17-KW5E</t>
+  </si>
+  <si>
+    <t>Gát utca</t>
+  </si>
+  <si>
+    <t>202603182600649801</t>
+  </si>
+  <si>
+    <t>NFD6-03-17-LMM5</t>
+  </si>
+  <si>
+    <t>Darányi Ignác utca</t>
+  </si>
+  <si>
+    <t>202603182600653001</t>
+  </si>
+  <si>
+    <t>NFD6-03-17-TQMA</t>
+  </si>
+  <si>
+    <t>202603172600635901</t>
+  </si>
+  <si>
+    <t>NFE6-03-16-QMH5</t>
+  </si>
+  <si>
+    <t>1192</t>
+  </si>
+  <si>
+    <t>202603182600649301</t>
+  </si>
+  <si>
+    <t>NFE6-03-17-C2S3</t>
+  </si>
+  <si>
+    <t>1221</t>
+  </si>
+  <si>
+    <t>202603182600649302</t>
+  </si>
+  <si>
+    <t>202603182600650001</t>
+  </si>
+  <si>
+    <t>NFE6-03-17-GVR7</t>
+  </si>
+  <si>
+    <t>1045</t>
+  </si>
+  <si>
+    <t>Lebstück Mária utca</t>
+  </si>
+  <si>
+    <t>202603182600653801</t>
+  </si>
+  <si>
+    <t>NFE6-03-17-JC4T</t>
+  </si>
+  <si>
+    <t>202603182600648901</t>
+  </si>
+  <si>
+    <t>NFE6-03-17-SH2T</t>
+  </si>
+  <si>
+    <t>Bazsarózsa utca</t>
   </si>
 </sst>
 </file>
@@ -2162,16 +2222,16 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <sheetPr codeName="Munka1"/>
-  <dimension ref="A1:H169"/>
+  <dimension ref="A1:H168"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="25.44140625" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="9.109375" style="1"/>
     <col min="3" max="3" width="6.88671875" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="20.109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="22.5546875" style="1" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="5" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="19" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="34.44140625" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="20" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="34.5546875" style="1" bestFit="1" customWidth="1"/>
     <col min="8" max="8" width="19.88671875" style="1" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
@@ -2200,137 +2260,134 @@
     </row>
     <row r="2" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A2" s="1" t="s">
-        <v>130</v>
+        <v>68</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>9</v>
+        <v>26</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>131</v>
+        <v>70</v>
       </c>
       <c r="E2" s="1" t="s">
-        <v>127</v>
+        <v>71</v>
       </c>
       <c r="F2" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="G2" s="1" t="s">
-        <v>132</v>
+        <v>72</v>
       </c>
       <c r="H2" s="1" t="s">
-        <v>133</v>
+        <v>35</v>
       </c>
     </row>
     <row r="3" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A3" s="1" t="s">
-        <v>134</v>
+        <v>116</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>135</v>
+        <v>26</v>
       </c>
       <c r="D3" s="1" t="s">
-        <v>136</v>
+        <v>117</v>
       </c>
       <c r="E3" s="1" t="s">
-        <v>137</v>
+        <v>118</v>
       </c>
       <c r="F3" s="1" t="s">
-        <v>138</v>
+        <v>119</v>
       </c>
       <c r="G3" s="1" t="s">
-        <v>139</v>
+        <v>120</v>
       </c>
       <c r="H3" s="1" t="s">
-        <v>43</v>
+        <v>8</v>
       </c>
     </row>
     <row r="4" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A4" s="1" t="s">
-        <v>140</v>
+        <v>121</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>27</v>
+        <v>20</v>
       </c>
       <c r="D4" s="1" t="s">
-        <v>141</v>
+        <v>122</v>
       </c>
       <c r="E4" s="1" t="s">
-        <v>104</v>
+        <v>123</v>
       </c>
       <c r="F4" s="1" t="s">
-        <v>105</v>
+        <v>7</v>
       </c>
       <c r="G4" s="1" t="s">
-        <v>142</v>
+        <v>124</v>
       </c>
       <c r="H4" s="1" t="s">
-        <v>11</v>
+        <v>8</v>
       </c>
     </row>
     <row r="5" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A5" s="1" t="s">
-        <v>143</v>
+        <v>125</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>27</v>
+        <v>13</v>
       </c>
       <c r="D5" s="1" t="s">
-        <v>141</v>
+        <v>126</v>
       </c>
       <c r="E5" s="1" t="s">
-        <v>104</v>
+        <v>127</v>
       </c>
       <c r="F5" s="1" t="s">
-        <v>105</v>
+        <v>128</v>
       </c>
       <c r="G5" s="1" t="s">
-        <v>142</v>
+        <v>129</v>
       </c>
       <c r="H5" s="1" t="s">
-        <v>11</v>
+        <v>8</v>
       </c>
     </row>
     <row r="6" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A6" s="1" t="s">
-        <v>144</v>
+        <v>73</v>
       </c>
       <c r="C6" s="1" t="s">
-        <v>24</v>
+        <v>37</v>
       </c>
       <c r="D6" s="1" t="s">
-        <v>145</v>
+        <v>74</v>
       </c>
       <c r="E6" s="1" t="s">
-        <v>71</v>
+        <v>29</v>
       </c>
       <c r="F6" s="1" t="s">
-        <v>7</v>
+        <v>30</v>
       </c>
       <c r="G6" s="1" t="s">
-        <v>146</v>
+        <v>39</v>
       </c>
       <c r="H6" s="1" t="s">
-        <v>11</v>
+        <v>8</v>
       </c>
     </row>
     <row r="7" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A7" s="1" t="s">
-        <v>147</v>
+        <v>130</v>
       </c>
       <c r="C7" s="1" t="s">
-        <v>12</v>
+        <v>46</v>
       </c>
       <c r="D7" s="1" t="s">
-        <v>148</v>
+        <v>131</v>
       </c>
       <c r="E7" s="1" t="s">
-        <v>80</v>
+        <v>51</v>
       </c>
       <c r="F7" s="1" t="s">
-        <v>81</v>
+        <v>7</v>
       </c>
       <c r="G7" s="1" t="s">
-        <v>149</v>
+        <v>132</v>
       </c>
       <c r="H7" s="1" t="s">
         <v>8</v>
@@ -2338,22 +2395,22 @@
     </row>
     <row r="8" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A8" s="1" t="s">
-        <v>150</v>
+        <v>133</v>
       </c>
       <c r="C8" s="1" t="s">
-        <v>12</v>
+        <v>25</v>
       </c>
       <c r="D8" s="1" t="s">
-        <v>151</v>
+        <v>134</v>
       </c>
       <c r="E8" s="1" t="s">
-        <v>34</v>
+        <v>17</v>
       </c>
       <c r="F8" s="1" t="s">
-        <v>35</v>
+        <v>18</v>
       </c>
       <c r="G8" s="1" t="s">
-        <v>49</v>
+        <v>135</v>
       </c>
       <c r="H8" s="1" t="s">
         <v>8</v>
@@ -2361,22 +2418,22 @@
     </row>
     <row r="9" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A9" s="1" t="s">
-        <v>152</v>
+        <v>136</v>
       </c>
       <c r="C9" s="1" t="s">
-        <v>29</v>
+        <v>25</v>
       </c>
       <c r="D9" s="1" t="s">
-        <v>153</v>
+        <v>134</v>
       </c>
       <c r="E9" s="1" t="s">
-        <v>115</v>
+        <v>17</v>
       </c>
       <c r="F9" s="1" t="s">
-        <v>116</v>
+        <v>18</v>
       </c>
       <c r="G9" s="1" t="s">
-        <v>154</v>
+        <v>135</v>
       </c>
       <c r="H9" s="1" t="s">
         <v>8</v>
@@ -2384,22 +2441,22 @@
     </row>
     <row r="10" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A10" s="1" t="s">
-        <v>67</v>
+        <v>137</v>
       </c>
       <c r="C10" s="1" t="s">
-        <v>21</v>
+        <v>9</v>
       </c>
       <c r="D10" s="1" t="s">
-        <v>68</v>
+        <v>138</v>
       </c>
       <c r="E10" s="1" t="s">
-        <v>69</v>
+        <v>55</v>
       </c>
       <c r="F10" s="1" t="s">
-        <v>7</v>
+        <v>56</v>
       </c>
       <c r="G10" s="1" t="s">
-        <v>70</v>
+        <v>108</v>
       </c>
       <c r="H10" s="1" t="s">
         <v>8</v>
@@ -2407,22 +2464,22 @@
     </row>
     <row r="11" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A11" s="1" t="s">
-        <v>155</v>
+        <v>139</v>
       </c>
       <c r="C11" s="1" t="s">
-        <v>29</v>
+        <v>20</v>
       </c>
       <c r="D11" s="1" t="s">
-        <v>156</v>
+        <v>140</v>
       </c>
       <c r="E11" s="1" t="s">
-        <v>157</v>
+        <v>141</v>
       </c>
       <c r="F11" s="1" t="s">
-        <v>158</v>
+        <v>7</v>
       </c>
       <c r="G11" s="1" t="s">
-        <v>159</v>
+        <v>142</v>
       </c>
       <c r="H11" s="1" t="s">
         <v>8</v>
@@ -2430,22 +2487,22 @@
     </row>
     <row r="12" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A12" s="1" t="s">
-        <v>160</v>
+        <v>143</v>
       </c>
       <c r="C12" s="1" t="s">
-        <v>39</v>
+        <v>20</v>
       </c>
       <c r="D12" s="1" t="s">
-        <v>161</v>
+        <v>144</v>
       </c>
       <c r="E12" s="1" t="s">
-        <v>162</v>
+        <v>145</v>
       </c>
       <c r="F12" s="1" t="s">
-        <v>163</v>
+        <v>146</v>
       </c>
       <c r="G12" s="1" t="s">
-        <v>164</v>
+        <v>147</v>
       </c>
       <c r="H12" s="1" t="s">
         <v>8</v>
@@ -2453,22 +2510,22 @@
     </row>
     <row r="13" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A13" s="1" t="s">
-        <v>165</v>
+        <v>148</v>
       </c>
       <c r="C13" s="1" t="s">
-        <v>50</v>
+        <v>20</v>
       </c>
       <c r="D13" s="1" t="s">
-        <v>166</v>
+        <v>149</v>
       </c>
       <c r="E13" s="1" t="s">
-        <v>26</v>
+        <v>150</v>
       </c>
       <c r="F13" s="1" t="s">
-        <v>7</v>
+        <v>151</v>
       </c>
       <c r="G13" s="1" t="s">
-        <v>59</v>
+        <v>152</v>
       </c>
       <c r="H13" s="1" t="s">
         <v>8</v>
@@ -2476,22 +2533,22 @@
     </row>
     <row r="14" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A14" s="1" t="s">
-        <v>167</v>
+        <v>153</v>
       </c>
       <c r="C14" s="1" t="s">
-        <v>64</v>
+        <v>38</v>
       </c>
       <c r="D14" s="1" t="s">
-        <v>168</v>
+        <v>154</v>
       </c>
       <c r="E14" s="1" t="s">
-        <v>83</v>
+        <v>155</v>
       </c>
       <c r="F14" s="1" t="s">
         <v>7</v>
       </c>
       <c r="G14" s="1" t="s">
-        <v>169</v>
+        <v>156</v>
       </c>
       <c r="H14" s="1" t="s">
         <v>8</v>
@@ -2499,22 +2556,22 @@
     </row>
     <row r="15" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A15" s="1" t="s">
-        <v>170</v>
+        <v>157</v>
       </c>
       <c r="C15" s="1" t="s">
-        <v>36</v>
+        <v>21</v>
       </c>
       <c r="D15" s="1" t="s">
-        <v>171</v>
+        <v>158</v>
       </c>
       <c r="E15" s="1" t="s">
-        <v>172</v>
+        <v>159</v>
       </c>
       <c r="F15" s="1" t="s">
-        <v>7</v>
+        <v>160</v>
       </c>
       <c r="G15" s="1" t="s">
-        <v>173</v>
+        <v>161</v>
       </c>
       <c r="H15" s="1" t="s">
         <v>8</v>
@@ -2522,22 +2579,22 @@
     </row>
     <row r="16" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A16" s="1" t="s">
-        <v>174</v>
+        <v>162</v>
       </c>
       <c r="C16" s="1" t="s">
-        <v>135</v>
+        <v>21</v>
       </c>
       <c r="D16" s="1" t="s">
-        <v>175</v>
+        <v>158</v>
       </c>
       <c r="E16" s="1" t="s">
-        <v>16</v>
+        <v>159</v>
       </c>
       <c r="F16" s="1" t="s">
-        <v>17</v>
+        <v>160</v>
       </c>
       <c r="G16" s="1" t="s">
-        <v>176</v>
+        <v>161</v>
       </c>
       <c r="H16" s="1" t="s">
         <v>8</v>
@@ -2545,22 +2602,22 @@
     </row>
     <row r="17" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A17" s="1" t="s">
-        <v>177</v>
+        <v>163</v>
       </c>
       <c r="C17" s="1" t="s">
-        <v>64</v>
+        <v>21</v>
       </c>
       <c r="D17" s="1" t="s">
-        <v>178</v>
+        <v>164</v>
       </c>
       <c r="E17" s="1" t="s">
-        <v>179</v>
+        <v>104</v>
       </c>
       <c r="F17" s="1" t="s">
         <v>7</v>
       </c>
       <c r="G17" s="1" t="s">
-        <v>180</v>
+        <v>165</v>
       </c>
       <c r="H17" s="1" t="s">
         <v>8</v>
@@ -2568,22 +2625,22 @@
     </row>
     <row r="18" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A18" s="1" t="s">
-        <v>181</v>
+        <v>166</v>
       </c>
       <c r="C18" s="1" t="s">
-        <v>45</v>
+        <v>40</v>
       </c>
       <c r="D18" s="1" t="s">
-        <v>182</v>
+        <v>167</v>
       </c>
       <c r="E18" s="1" t="s">
-        <v>23</v>
+        <v>168</v>
       </c>
       <c r="F18" s="1" t="s">
         <v>7</v>
       </c>
       <c r="G18" s="1" t="s">
-        <v>183</v>
+        <v>169</v>
       </c>
       <c r="H18" s="1" t="s">
         <v>8</v>
@@ -2591,22 +2648,22 @@
     </row>
     <row r="19" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A19" s="1" t="s">
-        <v>184</v>
+        <v>170</v>
       </c>
       <c r="C19" s="1" t="s">
-        <v>12</v>
+        <v>20</v>
       </c>
       <c r="D19" s="1" t="s">
-        <v>185</v>
+        <v>171</v>
       </c>
       <c r="E19" s="1" t="s">
-        <v>80</v>
+        <v>172</v>
       </c>
       <c r="F19" s="1" t="s">
-        <v>81</v>
+        <v>173</v>
       </c>
       <c r="G19" s="1" t="s">
-        <v>186</v>
+        <v>174</v>
       </c>
       <c r="H19" s="1" t="s">
         <v>8</v>
@@ -2614,22 +2671,22 @@
     </row>
     <row r="20" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A20" s="1" t="s">
-        <v>76</v>
+        <v>175</v>
       </c>
       <c r="C20" s="1" t="s">
-        <v>29</v>
+        <v>26</v>
       </c>
       <c r="D20" s="1" t="s">
-        <v>77</v>
+        <v>176</v>
       </c>
       <c r="E20" s="1" t="s">
-        <v>41</v>
+        <v>106</v>
       </c>
       <c r="F20" s="1" t="s">
-        <v>42</v>
+        <v>107</v>
       </c>
       <c r="G20" s="1" t="s">
-        <v>78</v>
+        <v>177</v>
       </c>
       <c r="H20" s="1" t="s">
         <v>8</v>
@@ -2637,22 +2694,22 @@
     </row>
     <row r="21" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A21" s="1" t="s">
-        <v>187</v>
+        <v>178</v>
       </c>
       <c r="C21" s="1" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="D21" s="1" t="s">
-        <v>188</v>
+        <v>179</v>
       </c>
       <c r="E21" s="1" t="s">
-        <v>97</v>
+        <v>75</v>
       </c>
       <c r="F21" s="1" t="s">
-        <v>98</v>
+        <v>76</v>
       </c>
       <c r="G21" s="1" t="s">
-        <v>189</v>
+        <v>180</v>
       </c>
       <c r="H21" s="1" t="s">
         <v>8</v>
@@ -2660,22 +2717,22 @@
     </row>
     <row r="22" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A22" s="1" t="s">
-        <v>190</v>
+        <v>80</v>
       </c>
       <c r="C22" s="1" t="s">
-        <v>29</v>
+        <v>33</v>
       </c>
       <c r="D22" s="1" t="s">
-        <v>191</v>
+        <v>81</v>
       </c>
       <c r="E22" s="1" t="s">
-        <v>192</v>
+        <v>32</v>
       </c>
       <c r="F22" s="1" t="s">
-        <v>193</v>
+        <v>7</v>
       </c>
       <c r="G22" s="1" t="s">
-        <v>194</v>
+        <v>82</v>
       </c>
       <c r="H22" s="1" t="s">
         <v>8</v>
@@ -2683,22 +2740,22 @@
     </row>
     <row r="23" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A23" s="1" t="s">
-        <v>195</v>
+        <v>83</v>
       </c>
       <c r="C23" s="1" t="s">
-        <v>135</v>
+        <v>33</v>
       </c>
       <c r="D23" s="1" t="s">
-        <v>196</v>
+        <v>81</v>
       </c>
       <c r="E23" s="1" t="s">
-        <v>197</v>
+        <v>32</v>
       </c>
       <c r="F23" s="1" t="s">
-        <v>198</v>
+        <v>7</v>
       </c>
       <c r="G23" s="1" t="s">
-        <v>199</v>
+        <v>82</v>
       </c>
       <c r="H23" s="1" t="s">
         <v>8</v>
@@ -2706,22 +2763,22 @@
     </row>
     <row r="24" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A24" s="1" t="s">
-        <v>200</v>
+        <v>181</v>
       </c>
       <c r="C24" s="1" t="s">
-        <v>135</v>
+        <v>46</v>
       </c>
       <c r="D24" s="1" t="s">
-        <v>196</v>
+        <v>182</v>
       </c>
       <c r="E24" s="1" t="s">
-        <v>197</v>
+        <v>183</v>
       </c>
       <c r="F24" s="1" t="s">
-        <v>198</v>
+        <v>7</v>
       </c>
       <c r="G24" s="1" t="s">
-        <v>199</v>
+        <v>184</v>
       </c>
       <c r="H24" s="1" t="s">
         <v>8</v>
@@ -2729,22 +2786,22 @@
     </row>
     <row r="25" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A25" s="1" t="s">
-        <v>201</v>
+        <v>185</v>
       </c>
       <c r="C25" s="1" t="s">
-        <v>12</v>
+        <v>25</v>
       </c>
       <c r="D25" s="1" t="s">
-        <v>202</v>
+        <v>186</v>
       </c>
       <c r="E25" s="1" t="s">
-        <v>92</v>
+        <v>84</v>
       </c>
       <c r="F25" s="1" t="s">
-        <v>93</v>
+        <v>53</v>
       </c>
       <c r="G25" s="1" t="s">
-        <v>203</v>
+        <v>187</v>
       </c>
       <c r="H25" s="1" t="s">
         <v>8</v>
@@ -2752,22 +2809,22 @@
     </row>
     <row r="26" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A26" s="1" t="s">
-        <v>204</v>
+        <v>188</v>
       </c>
       <c r="C26" s="1" t="s">
-        <v>44</v>
+        <v>37</v>
       </c>
       <c r="D26" s="1" t="s">
-        <v>205</v>
+        <v>189</v>
       </c>
       <c r="E26" s="1" t="s">
-        <v>206</v>
+        <v>190</v>
       </c>
       <c r="F26" s="1" t="s">
-        <v>207</v>
+        <v>191</v>
       </c>
       <c r="G26" s="1" t="s">
-        <v>208</v>
+        <v>192</v>
       </c>
       <c r="H26" s="1" t="s">
         <v>8</v>
@@ -2775,22 +2832,22 @@
     </row>
     <row r="27" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A27" s="1" t="s">
-        <v>209</v>
+        <v>193</v>
       </c>
       <c r="C27" s="1" t="s">
-        <v>46</v>
+        <v>14</v>
       </c>
       <c r="D27" s="1" t="s">
-        <v>210</v>
+        <v>194</v>
       </c>
       <c r="E27" s="1" t="s">
-        <v>211</v>
+        <v>195</v>
       </c>
       <c r="F27" s="1" t="s">
-        <v>212</v>
+        <v>196</v>
       </c>
       <c r="G27" s="1" t="s">
-        <v>61</v>
+        <v>197</v>
       </c>
       <c r="H27" s="1" t="s">
         <v>8</v>
@@ -2798,22 +2855,22 @@
     </row>
     <row r="28" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A28" s="1" t="s">
-        <v>213</v>
+        <v>198</v>
       </c>
       <c r="C28" s="1" t="s">
-        <v>46</v>
+        <v>199</v>
       </c>
       <c r="D28" s="1" t="s">
-        <v>214</v>
+        <v>200</v>
       </c>
       <c r="E28" s="1" t="s">
-        <v>18</v>
+        <v>201</v>
       </c>
       <c r="F28" s="1" t="s">
-        <v>19</v>
+        <v>7</v>
       </c>
       <c r="G28" s="1" t="s">
-        <v>215</v>
+        <v>202</v>
       </c>
       <c r="H28" s="1" t="s">
         <v>8</v>
@@ -2821,22 +2878,22 @@
     </row>
     <row r="29" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A29" s="1" t="s">
-        <v>216</v>
+        <v>203</v>
       </c>
       <c r="C29" s="1" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="D29" s="1" t="s">
-        <v>217</v>
+        <v>204</v>
       </c>
       <c r="E29" s="1" t="s">
-        <v>37</v>
+        <v>205</v>
       </c>
       <c r="F29" s="1" t="s">
-        <v>7</v>
+        <v>206</v>
       </c>
       <c r="G29" s="1" t="s">
-        <v>218</v>
+        <v>207</v>
       </c>
       <c r="H29" s="1" t="s">
         <v>8</v>
@@ -2844,22 +2901,22 @@
     </row>
     <row r="30" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A30" s="1" t="s">
-        <v>219</v>
+        <v>208</v>
       </c>
       <c r="C30" s="1" t="s">
-        <v>39</v>
+        <v>13</v>
       </c>
       <c r="D30" s="1" t="s">
-        <v>217</v>
+        <v>209</v>
       </c>
       <c r="E30" s="1" t="s">
-        <v>37</v>
+        <v>210</v>
       </c>
       <c r="F30" s="1" t="s">
-        <v>7</v>
+        <v>211</v>
       </c>
       <c r="G30" s="1" t="s">
-        <v>218</v>
+        <v>212</v>
       </c>
       <c r="H30" s="1" t="s">
         <v>8</v>
@@ -2867,22 +2924,22 @@
     </row>
     <row r="31" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A31" s="1" t="s">
-        <v>86</v>
+        <v>213</v>
       </c>
       <c r="C31" s="1" t="s">
-        <v>72</v>
+        <v>13</v>
       </c>
       <c r="D31" s="1" t="s">
-        <v>87</v>
+        <v>214</v>
       </c>
       <c r="E31" s="1" t="s">
-        <v>88</v>
+        <v>77</v>
       </c>
       <c r="F31" s="1" t="s">
-        <v>7</v>
+        <v>78</v>
       </c>
       <c r="G31" s="1" t="s">
-        <v>89</v>
+        <v>215</v>
       </c>
       <c r="H31" s="1" t="s">
         <v>8</v>
@@ -2890,22 +2947,22 @@
     </row>
     <row r="32" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A32" s="1" t="s">
-        <v>220</v>
+        <v>216</v>
       </c>
       <c r="C32" s="1" t="s">
-        <v>46</v>
+        <v>36</v>
       </c>
       <c r="D32" s="1" t="s">
-        <v>221</v>
+        <v>217</v>
       </c>
       <c r="E32" s="1" t="s">
-        <v>222</v>
+        <v>218</v>
       </c>
       <c r="F32" s="1" t="s">
-        <v>95</v>
+        <v>7</v>
       </c>
       <c r="G32" s="1" t="s">
-        <v>223</v>
+        <v>219</v>
       </c>
       <c r="H32" s="1" t="s">
         <v>8</v>
@@ -2913,22 +2970,22 @@
     </row>
     <row r="33" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A33" s="1" t="s">
-        <v>224</v>
+        <v>220</v>
       </c>
       <c r="C33" s="1" t="s">
-        <v>29</v>
+        <v>37</v>
       </c>
       <c r="D33" s="1" t="s">
-        <v>225</v>
+        <v>221</v>
       </c>
       <c r="E33" s="1" t="s">
-        <v>226</v>
+        <v>102</v>
       </c>
       <c r="F33" s="1" t="s">
-        <v>227</v>
+        <v>103</v>
       </c>
       <c r="G33" s="1" t="s">
-        <v>82</v>
+        <v>222</v>
       </c>
       <c r="H33" s="1" t="s">
         <v>8</v>
@@ -2936,22 +2993,22 @@
     </row>
     <row r="34" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A34" s="1" t="s">
-        <v>228</v>
+        <v>223</v>
       </c>
       <c r="C34" s="1" t="s">
-        <v>12</v>
+        <v>37</v>
       </c>
       <c r="D34" s="1" t="s">
-        <v>229</v>
+        <v>221</v>
       </c>
       <c r="E34" s="1" t="s">
-        <v>122</v>
+        <v>102</v>
       </c>
       <c r="F34" s="1" t="s">
-        <v>123</v>
+        <v>103</v>
       </c>
       <c r="G34" s="1" t="s">
-        <v>230</v>
+        <v>222</v>
       </c>
       <c r="H34" s="1" t="s">
         <v>8</v>
@@ -2959,22 +3016,22 @@
     </row>
     <row r="35" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A35" s="1" t="s">
-        <v>231</v>
+        <v>224</v>
       </c>
       <c r="C35" s="1" t="s">
-        <v>15</v>
+        <v>36</v>
       </c>
       <c r="D35" s="1" t="s">
-        <v>232</v>
+        <v>225</v>
       </c>
       <c r="E35" s="1" t="s">
-        <v>57</v>
+        <v>226</v>
       </c>
       <c r="F35" s="1" t="s">
-        <v>58</v>
+        <v>7</v>
       </c>
       <c r="G35" s="1" t="s">
-        <v>233</v>
+        <v>227</v>
       </c>
       <c r="H35" s="1" t="s">
         <v>8</v>
@@ -2982,22 +3039,22 @@
     </row>
     <row r="36" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A36" s="1" t="s">
-        <v>234</v>
+        <v>228</v>
       </c>
       <c r="C36" s="1" t="s">
-        <v>15</v>
+        <v>26</v>
       </c>
       <c r="D36" s="1" t="s">
-        <v>235</v>
+        <v>229</v>
       </c>
       <c r="E36" s="1" t="s">
-        <v>57</v>
+        <v>106</v>
       </c>
       <c r="F36" s="1" t="s">
-        <v>58</v>
+        <v>107</v>
       </c>
       <c r="G36" s="1" t="s">
-        <v>236</v>
+        <v>230</v>
       </c>
       <c r="H36" s="1" t="s">
         <v>8</v>
@@ -3005,22 +3062,22 @@
     </row>
     <row r="37" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A37" s="1" t="s">
-        <v>237</v>
+        <v>231</v>
       </c>
       <c r="C37" s="1" t="s">
-        <v>22</v>
+        <v>33</v>
       </c>
       <c r="D37" s="1" t="s">
-        <v>238</v>
+        <v>232</v>
       </c>
       <c r="E37" s="1" t="s">
-        <v>117</v>
+        <v>233</v>
       </c>
       <c r="F37" s="1" t="s">
-        <v>118</v>
+        <v>234</v>
       </c>
       <c r="G37" s="1" t="s">
-        <v>239</v>
+        <v>235</v>
       </c>
       <c r="H37" s="1" t="s">
         <v>8</v>
@@ -3028,22 +3085,22 @@
     </row>
     <row r="38" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A38" s="1" t="s">
-        <v>240</v>
+        <v>236</v>
       </c>
       <c r="C38" s="1" t="s">
-        <v>46</v>
+        <v>33</v>
       </c>
       <c r="D38" s="1" t="s">
-        <v>241</v>
+        <v>232</v>
       </c>
       <c r="E38" s="1" t="s">
-        <v>94</v>
+        <v>233</v>
       </c>
       <c r="F38" s="1" t="s">
-        <v>95</v>
+        <v>234</v>
       </c>
       <c r="G38" s="1" t="s">
-        <v>242</v>
+        <v>235</v>
       </c>
       <c r="H38" s="1" t="s">
         <v>8</v>
@@ -3051,22 +3108,22 @@
     </row>
     <row r="39" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A39" s="1" t="s">
-        <v>243</v>
+        <v>237</v>
       </c>
       <c r="C39" s="1" t="s">
-        <v>135</v>
+        <v>38</v>
       </c>
       <c r="D39" s="1" t="s">
-        <v>244</v>
+        <v>238</v>
       </c>
       <c r="E39" s="1" t="s">
-        <v>16</v>
+        <v>239</v>
       </c>
       <c r="F39" s="1" t="s">
-        <v>17</v>
+        <v>240</v>
       </c>
       <c r="G39" s="1" t="s">
-        <v>245</v>
+        <v>241</v>
       </c>
       <c r="H39" s="1" t="s">
         <v>8</v>
@@ -3074,22 +3131,22 @@
     </row>
     <row r="40" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A40" s="1" t="s">
-        <v>246</v>
+        <v>242</v>
       </c>
       <c r="C40" s="1" t="s">
-        <v>29</v>
+        <v>38</v>
       </c>
       <c r="D40" s="1" t="s">
-        <v>247</v>
+        <v>238</v>
       </c>
       <c r="E40" s="1" t="s">
-        <v>115</v>
+        <v>239</v>
       </c>
       <c r="F40" s="1" t="s">
-        <v>116</v>
+        <v>240</v>
       </c>
       <c r="G40" s="1" t="s">
-        <v>248</v>
+        <v>241</v>
       </c>
       <c r="H40" s="1" t="s">
         <v>8</v>
@@ -3097,22 +3154,22 @@
     </row>
     <row r="41" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A41" s="1" t="s">
-        <v>249</v>
+        <v>243</v>
       </c>
       <c r="C41" s="1" t="s">
-        <v>44</v>
+        <v>199</v>
       </c>
       <c r="D41" s="1" t="s">
-        <v>250</v>
+        <v>244</v>
       </c>
       <c r="E41" s="1" t="s">
-        <v>251</v>
+        <v>201</v>
       </c>
       <c r="F41" s="1" t="s">
-        <v>252</v>
+        <v>7</v>
       </c>
       <c r="G41" s="1" t="s">
-        <v>253</v>
+        <v>245</v>
       </c>
       <c r="H41" s="1" t="s">
         <v>8</v>
@@ -3120,22 +3177,22 @@
     </row>
     <row r="42" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A42" s="1" t="s">
-        <v>254</v>
+        <v>246</v>
       </c>
       <c r="C42" s="1" t="s">
-        <v>39</v>
+        <v>199</v>
       </c>
       <c r="D42" s="1" t="s">
-        <v>255</v>
+        <v>244</v>
       </c>
       <c r="E42" s="1" t="s">
-        <v>256</v>
+        <v>201</v>
       </c>
       <c r="F42" s="1" t="s">
-        <v>257</v>
+        <v>7</v>
       </c>
       <c r="G42" s="1" t="s">
-        <v>258</v>
+        <v>245</v>
       </c>
       <c r="H42" s="1" t="s">
         <v>8</v>
@@ -3143,22 +3200,22 @@
     </row>
     <row r="43" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A43" s="1" t="s">
-        <v>259</v>
+        <v>247</v>
       </c>
       <c r="C43" s="1" t="s">
-        <v>44</v>
+        <v>23</v>
       </c>
       <c r="D43" s="1" t="s">
-        <v>260</v>
+        <v>248</v>
       </c>
       <c r="E43" s="1" t="s">
-        <v>261</v>
+        <v>249</v>
       </c>
       <c r="F43" s="1" t="s">
-        <v>262</v>
+        <v>7</v>
       </c>
       <c r="G43" s="1" t="s">
-        <v>263</v>
+        <v>250</v>
       </c>
       <c r="H43" s="1" t="s">
         <v>8</v>
@@ -3166,22 +3223,22 @@
     </row>
     <row r="44" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A44" s="1" t="s">
-        <v>264</v>
+        <v>251</v>
       </c>
       <c r="C44" s="1" t="s">
-        <v>46</v>
+        <v>40</v>
       </c>
       <c r="D44" s="1" t="s">
-        <v>265</v>
+        <v>252</v>
       </c>
       <c r="E44" s="1" t="s">
-        <v>18</v>
+        <v>27</v>
       </c>
       <c r="F44" s="1" t="s">
-        <v>19</v>
+        <v>7</v>
       </c>
       <c r="G44" s="1" t="s">
-        <v>266</v>
+        <v>253</v>
       </c>
       <c r="H44" s="1" t="s">
         <v>8</v>
@@ -3189,22 +3246,22 @@
     </row>
     <row r="45" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A45" s="1" t="s">
-        <v>267</v>
+        <v>254</v>
       </c>
       <c r="C45" s="1" t="s">
-        <v>46</v>
+        <v>31</v>
       </c>
       <c r="D45" s="1" t="s">
-        <v>265</v>
+        <v>255</v>
       </c>
       <c r="E45" s="1" t="s">
-        <v>18</v>
+        <v>24</v>
       </c>
       <c r="F45" s="1" t="s">
-        <v>19</v>
+        <v>7</v>
       </c>
       <c r="G45" s="1" t="s">
-        <v>266</v>
+        <v>256</v>
       </c>
       <c r="H45" s="1" t="s">
         <v>8</v>
@@ -3212,22 +3269,22 @@
     </row>
     <row r="46" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A46" s="1" t="s">
-        <v>268</v>
+        <v>257</v>
       </c>
       <c r="C46" s="1" t="s">
-        <v>28</v>
+        <v>38</v>
       </c>
       <c r="D46" s="1" t="s">
-        <v>269</v>
+        <v>258</v>
       </c>
       <c r="E46" s="1" t="s">
-        <v>51</v>
+        <v>259</v>
       </c>
       <c r="F46" s="1" t="s">
         <v>7</v>
       </c>
       <c r="G46" s="1" t="s">
-        <v>270</v>
+        <v>260</v>
       </c>
       <c r="H46" s="1" t="s">
         <v>8</v>
@@ -3235,22 +3292,22 @@
     </row>
     <row r="47" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A47" s="1" t="s">
-        <v>271</v>
+        <v>261</v>
       </c>
       <c r="C47" s="1" t="s">
-        <v>10</v>
+        <v>31</v>
       </c>
       <c r="D47" s="1" t="s">
-        <v>272</v>
+        <v>262</v>
       </c>
       <c r="E47" s="1" t="s">
-        <v>20</v>
+        <v>34</v>
       </c>
       <c r="F47" s="1" t="s">
         <v>7</v>
       </c>
       <c r="G47" s="1" t="s">
-        <v>273</v>
+        <v>263</v>
       </c>
       <c r="H47" s="1" t="s">
         <v>8</v>
@@ -3258,22 +3315,22 @@
     </row>
     <row r="48" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A48" s="1" t="s">
-        <v>274</v>
+        <v>264</v>
       </c>
       <c r="C48" s="1" t="s">
-        <v>45</v>
+        <v>36</v>
       </c>
       <c r="D48" s="1" t="s">
-        <v>275</v>
+        <v>265</v>
       </c>
       <c r="E48" s="1" t="s">
-        <v>276</v>
+        <v>266</v>
       </c>
       <c r="F48" s="1" t="s">
         <v>7</v>
       </c>
       <c r="G48" s="1" t="s">
-        <v>277</v>
+        <v>267</v>
       </c>
       <c r="H48" s="1" t="s">
         <v>8</v>
@@ -3281,22 +3338,22 @@
     </row>
     <row r="49" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A49" s="1" t="s">
-        <v>278</v>
+        <v>268</v>
       </c>
       <c r="C49" s="1" t="s">
-        <v>15</v>
+        <v>36</v>
       </c>
       <c r="D49" s="1" t="s">
-        <v>279</v>
+        <v>265</v>
       </c>
       <c r="E49" s="1" t="s">
-        <v>52</v>
+        <v>266</v>
       </c>
       <c r="F49" s="1" t="s">
         <v>7</v>
       </c>
       <c r="G49" s="1" t="s">
-        <v>280</v>
+        <v>267</v>
       </c>
       <c r="H49" s="1" t="s">
         <v>8</v>
@@ -3304,13 +3361,13 @@
     </row>
     <row r="50" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A50" s="1" t="s">
-        <v>281</v>
+        <v>269</v>
       </c>
       <c r="C50" s="1" t="s">
-        <v>15</v>
+        <v>270</v>
       </c>
       <c r="D50" s="1" t="s">
-        <v>279</v>
+        <v>271</v>
       </c>
       <c r="E50" s="1" t="s">
         <v>52</v>
@@ -3319,7 +3376,7 @@
         <v>7</v>
       </c>
       <c r="G50" s="1" t="s">
-        <v>280</v>
+        <v>272</v>
       </c>
       <c r="H50" s="1" t="s">
         <v>8</v>
@@ -3327,22 +3384,22 @@
     </row>
     <row r="51" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A51" s="1" t="s">
-        <v>282</v>
+        <v>273</v>
       </c>
       <c r="C51" s="1" t="s">
-        <v>45</v>
+        <v>9</v>
       </c>
       <c r="D51" s="1" t="s">
-        <v>283</v>
+        <v>274</v>
       </c>
       <c r="E51" s="1" t="s">
-        <v>284</v>
+        <v>54</v>
       </c>
       <c r="F51" s="1" t="s">
         <v>7</v>
       </c>
       <c r="G51" s="1" t="s">
-        <v>285</v>
+        <v>275</v>
       </c>
       <c r="H51" s="1" t="s">
         <v>8</v>
@@ -3350,22 +3407,22 @@
     </row>
     <row r="52" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A52" s="1" t="s">
-        <v>286</v>
+        <v>276</v>
       </c>
       <c r="C52" s="1" t="s">
-        <v>36</v>
+        <v>20</v>
       </c>
       <c r="D52" s="1" t="s">
-        <v>287</v>
+        <v>277</v>
       </c>
       <c r="E52" s="1" t="s">
-        <v>288</v>
+        <v>41</v>
       </c>
       <c r="F52" s="1" t="s">
         <v>7</v>
       </c>
       <c r="G52" s="1" t="s">
-        <v>289</v>
+        <v>91</v>
       </c>
       <c r="H52" s="1" t="s">
         <v>8</v>
@@ -3373,206 +3430,206 @@
     </row>
     <row r="53" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A53" s="1" t="s">
-        <v>290</v>
+        <v>278</v>
       </c>
       <c r="C53" s="1" t="s">
-        <v>39</v>
+        <v>31</v>
       </c>
       <c r="D53" s="1" t="s">
-        <v>291</v>
+        <v>279</v>
       </c>
       <c r="E53" s="1" t="s">
-        <v>32</v>
+        <v>57</v>
       </c>
       <c r="F53" s="1" t="s">
         <v>7</v>
       </c>
       <c r="G53" s="1" t="s">
-        <v>292</v>
+        <v>280</v>
       </c>
       <c r="H53" s="1" t="s">
-        <v>8</v>
+        <v>67</v>
       </c>
     </row>
     <row r="54" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A54" s="1" t="s">
-        <v>293</v>
+        <v>281</v>
       </c>
       <c r="C54" s="1" t="s">
-        <v>36</v>
+        <v>46</v>
       </c>
       <c r="D54" s="1" t="s">
-        <v>294</v>
+        <v>282</v>
       </c>
       <c r="E54" s="1" t="s">
-        <v>295</v>
+        <v>101</v>
       </c>
       <c r="F54" s="1" t="s">
         <v>7</v>
       </c>
       <c r="G54" s="1" t="s">
-        <v>296</v>
+        <v>283</v>
       </c>
       <c r="H54" s="1" t="s">
-        <v>8</v>
+        <v>67</v>
       </c>
     </row>
     <row r="55" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A55" s="1" t="s">
-        <v>297</v>
+        <v>284</v>
       </c>
       <c r="C55" s="1" t="s">
-        <v>22</v>
+        <v>9</v>
       </c>
       <c r="D55" s="1" t="s">
-        <v>298</v>
+        <v>285</v>
       </c>
       <c r="E55" s="1" t="s">
-        <v>299</v>
+        <v>286</v>
       </c>
       <c r="F55" s="1" t="s">
-        <v>7</v>
+        <v>287</v>
       </c>
       <c r="G55" s="1" t="s">
-        <v>300</v>
+        <v>288</v>
       </c>
       <c r="H55" s="1" t="s">
-        <v>8</v>
+        <v>67</v>
       </c>
     </row>
     <row r="56" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A56" s="1" t="s">
-        <v>301</v>
+        <v>289</v>
       </c>
       <c r="C56" s="1" t="s">
-        <v>45</v>
+        <v>13</v>
       </c>
       <c r="D56" s="1" t="s">
-        <v>302</v>
+        <v>290</v>
       </c>
       <c r="E56" s="1" t="s">
-        <v>303</v>
+        <v>210</v>
       </c>
       <c r="F56" s="1" t="s">
-        <v>7</v>
+        <v>211</v>
       </c>
       <c r="G56" s="1" t="s">
-        <v>304</v>
+        <v>291</v>
       </c>
       <c r="H56" s="1" t="s">
-        <v>8</v>
+        <v>67</v>
       </c>
     </row>
     <row r="57" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A57" s="1" t="s">
-        <v>305</v>
+        <v>292</v>
       </c>
       <c r="C57" s="1" t="s">
-        <v>15</v>
+        <v>37</v>
       </c>
       <c r="D57" s="1" t="s">
-        <v>306</v>
+        <v>293</v>
       </c>
       <c r="E57" s="1" t="s">
-        <v>307</v>
+        <v>190</v>
       </c>
       <c r="F57" s="1" t="s">
-        <v>7</v>
+        <v>191</v>
       </c>
       <c r="G57" s="1" t="s">
-        <v>308</v>
+        <v>294</v>
       </c>
       <c r="H57" s="1" t="s">
-        <v>8</v>
+        <v>67</v>
       </c>
     </row>
     <row r="58" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A58" s="1" t="s">
-        <v>309</v>
+        <v>295</v>
       </c>
       <c r="C58" s="1" t="s">
         <v>14</v>
       </c>
       <c r="D58" s="1" t="s">
-        <v>310</v>
+        <v>296</v>
       </c>
       <c r="E58" s="1" t="s">
-        <v>311</v>
+        <v>297</v>
       </c>
       <c r="F58" s="1" t="s">
-        <v>7</v>
+        <v>298</v>
       </c>
       <c r="G58" s="1" t="s">
-        <v>312</v>
+        <v>222</v>
       </c>
       <c r="H58" s="1" t="s">
-        <v>129</v>
+        <v>67</v>
       </c>
     </row>
     <row r="59" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A59" s="1" t="s">
-        <v>313</v>
+        <v>299</v>
       </c>
       <c r="C59" s="1" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="D59" s="1" t="s">
-        <v>314</v>
+        <v>300</v>
       </c>
       <c r="E59" s="1" t="s">
-        <v>315</v>
+        <v>301</v>
       </c>
       <c r="F59" s="1" t="s">
-        <v>316</v>
+        <v>302</v>
       </c>
       <c r="G59" s="1" t="s">
-        <v>317</v>
+        <v>303</v>
       </c>
       <c r="H59" s="1" t="s">
-        <v>318</v>
+        <v>67</v>
       </c>
     </row>
     <row r="60" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A60" s="1" t="s">
-        <v>319</v>
+        <v>304</v>
       </c>
       <c r="C60" s="1" t="s">
-        <v>44</v>
+        <v>9</v>
       </c>
       <c r="D60" s="1" t="s">
-        <v>320</v>
+        <v>305</v>
       </c>
       <c r="E60" s="1" t="s">
-        <v>321</v>
+        <v>113</v>
       </c>
       <c r="F60" s="1" t="s">
-        <v>322</v>
+        <v>114</v>
       </c>
       <c r="G60" s="1" t="s">
-        <v>323</v>
+        <v>306</v>
       </c>
       <c r="H60" s="1" t="s">
-        <v>11</v>
+        <v>96</v>
       </c>
     </row>
     <row r="61" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A61" s="1" t="s">
-        <v>324</v>
+        <v>307</v>
       </c>
       <c r="C61" s="1" t="s">
-        <v>21</v>
+        <v>9</v>
       </c>
       <c r="D61" s="1" t="s">
-        <v>325</v>
+        <v>308</v>
       </c>
       <c r="E61" s="1" t="s">
-        <v>25</v>
+        <v>115</v>
       </c>
       <c r="F61" s="1" t="s">
         <v>7</v>
       </c>
       <c r="G61" s="1" t="s">
-        <v>326</v>
+        <v>309</v>
       </c>
       <c r="H61" s="1" t="s">
         <v>11</v>
@@ -3580,22 +3637,22 @@
     </row>
     <row r="62" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A62" s="1" t="s">
-        <v>327</v>
+        <v>310</v>
       </c>
       <c r="C62" s="1" t="s">
-        <v>21</v>
+        <v>26</v>
       </c>
       <c r="D62" s="1" t="s">
-        <v>325</v>
+        <v>311</v>
       </c>
       <c r="E62" s="1" t="s">
-        <v>25</v>
+        <v>64</v>
       </c>
       <c r="F62" s="1" t="s">
-        <v>7</v>
+        <v>65</v>
       </c>
       <c r="G62" s="1" t="s">
-        <v>326</v>
+        <v>312</v>
       </c>
       <c r="H62" s="1" t="s">
         <v>11</v>
@@ -3603,22 +3660,22 @@
     </row>
     <row r="63" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A63" s="1" t="s">
-        <v>328</v>
+        <v>313</v>
       </c>
       <c r="C63" s="1" t="s">
-        <v>21</v>
+        <v>26</v>
       </c>
       <c r="D63" s="1" t="s">
-        <v>325</v>
+        <v>311</v>
       </c>
       <c r="E63" s="1" t="s">
-        <v>25</v>
+        <v>64</v>
       </c>
       <c r="F63" s="1" t="s">
-        <v>7</v>
+        <v>65</v>
       </c>
       <c r="G63" s="1" t="s">
-        <v>326</v>
+        <v>312</v>
       </c>
       <c r="H63" s="1" t="s">
         <v>11</v>
@@ -3626,22 +3683,22 @@
     </row>
     <row r="64" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A64" s="1" t="s">
-        <v>329</v>
+        <v>314</v>
       </c>
       <c r="C64" s="1" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="D64" s="1" t="s">
-        <v>330</v>
+        <v>311</v>
       </c>
       <c r="E64" s="1" t="s">
-        <v>331</v>
+        <v>64</v>
       </c>
       <c r="F64" s="1" t="s">
-        <v>7</v>
+        <v>65</v>
       </c>
       <c r="G64" s="1" t="s">
-        <v>332</v>
+        <v>312</v>
       </c>
       <c r="H64" s="1" t="s">
         <v>11</v>
@@ -3649,22 +3706,22 @@
     </row>
     <row r="65" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A65" s="1" t="s">
-        <v>333</v>
+        <v>315</v>
       </c>
       <c r="C65" s="1" t="s">
-        <v>28</v>
+        <v>31</v>
       </c>
       <c r="D65" s="1" t="s">
-        <v>330</v>
+        <v>316</v>
       </c>
       <c r="E65" s="1" t="s">
-        <v>331</v>
+        <v>34</v>
       </c>
       <c r="F65" s="1" t="s">
         <v>7</v>
       </c>
       <c r="G65" s="1" t="s">
-        <v>332</v>
+        <v>317</v>
       </c>
       <c r="H65" s="1" t="s">
         <v>11</v>
@@ -3672,22 +3729,22 @@
     </row>
     <row r="66" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A66" s="1" t="s">
-        <v>334</v>
+        <v>318</v>
       </c>
       <c r="C66" s="1" t="s">
-        <v>9</v>
+        <v>31</v>
       </c>
       <c r="D66" s="1" t="s">
-        <v>335</v>
+        <v>316</v>
       </c>
       <c r="E66" s="1" t="s">
-        <v>73</v>
+        <v>34</v>
       </c>
       <c r="F66" s="1" t="s">
-        <v>74</v>
+        <v>7</v>
       </c>
       <c r="G66" s="1" t="s">
-        <v>336</v>
+        <v>317</v>
       </c>
       <c r="H66" s="1" t="s">
         <v>11</v>
@@ -3695,22 +3752,22 @@
     </row>
     <row r="67" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A67" s="1" t="s">
-        <v>337</v>
+        <v>319</v>
       </c>
       <c r="C67" s="1" t="s">
-        <v>9</v>
+        <v>38</v>
       </c>
       <c r="D67" s="1" t="s">
-        <v>335</v>
+        <v>320</v>
       </c>
       <c r="E67" s="1" t="s">
-        <v>73</v>
+        <v>321</v>
       </c>
       <c r="F67" s="1" t="s">
-        <v>74</v>
+        <v>322</v>
       </c>
       <c r="G67" s="1" t="s">
-        <v>336</v>
+        <v>323</v>
       </c>
       <c r="H67" s="1" t="s">
         <v>11</v>
@@ -3718,22 +3775,22 @@
     </row>
     <row r="68" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A68" s="1" t="s">
-        <v>338</v>
+        <v>324</v>
       </c>
       <c r="C68" s="1" t="s">
-        <v>9</v>
+        <v>38</v>
       </c>
       <c r="D68" s="1" t="s">
-        <v>335</v>
+        <v>325</v>
       </c>
       <c r="E68" s="1" t="s">
-        <v>73</v>
+        <v>326</v>
       </c>
       <c r="F68" s="1" t="s">
-        <v>74</v>
+        <v>327</v>
       </c>
       <c r="G68" s="1" t="s">
-        <v>336</v>
+        <v>328</v>
       </c>
       <c r="H68" s="1" t="s">
         <v>11</v>
@@ -3741,22 +3798,22 @@
     </row>
     <row r="69" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A69" s="1" t="s">
-        <v>339</v>
+        <v>329</v>
       </c>
       <c r="C69" s="1" t="s">
-        <v>72</v>
+        <v>38</v>
       </c>
       <c r="D69" s="1" t="s">
-        <v>340</v>
+        <v>330</v>
       </c>
       <c r="E69" s="1" t="s">
-        <v>341</v>
+        <v>321</v>
       </c>
       <c r="F69" s="1" t="s">
-        <v>7</v>
+        <v>322</v>
       </c>
       <c r="G69" s="1" t="s">
-        <v>342</v>
+        <v>331</v>
       </c>
       <c r="H69" s="1" t="s">
         <v>11</v>
@@ -3764,22 +3821,22 @@
     </row>
     <row r="70" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A70" s="1" t="s">
-        <v>343</v>
+        <v>332</v>
       </c>
       <c r="C70" s="1" t="s">
-        <v>50</v>
+        <v>21</v>
       </c>
       <c r="D70" s="1" t="s">
-        <v>344</v>
+        <v>333</v>
       </c>
       <c r="E70" s="1" t="s">
-        <v>26</v>
+        <v>159</v>
       </c>
       <c r="F70" s="1" t="s">
-        <v>7</v>
+        <v>160</v>
       </c>
       <c r="G70" s="1" t="s">
-        <v>345</v>
+        <v>334</v>
       </c>
       <c r="H70" s="1" t="s">
         <v>11</v>
@@ -3787,22 +3844,22 @@
     </row>
     <row r="71" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A71" s="1" t="s">
-        <v>346</v>
+        <v>335</v>
       </c>
       <c r="C71" s="1" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="D71" s="1" t="s">
-        <v>347</v>
+        <v>336</v>
       </c>
       <c r="E71" s="1" t="s">
-        <v>348</v>
+        <v>17</v>
       </c>
       <c r="F71" s="1" t="s">
-        <v>349</v>
+        <v>18</v>
       </c>
       <c r="G71" s="1" t="s">
-        <v>350</v>
+        <v>337</v>
       </c>
       <c r="H71" s="1" t="s">
         <v>11</v>
@@ -3810,22 +3867,22 @@
     </row>
     <row r="72" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A72" s="1" t="s">
-        <v>351</v>
+        <v>338</v>
       </c>
       <c r="C72" s="1" t="s">
-        <v>24</v>
+        <v>38</v>
       </c>
       <c r="D72" s="1" t="s">
-        <v>347</v>
+        <v>339</v>
       </c>
       <c r="E72" s="1" t="s">
-        <v>348</v>
+        <v>47</v>
       </c>
       <c r="F72" s="1" t="s">
-        <v>349</v>
+        <v>48</v>
       </c>
       <c r="G72" s="1" t="s">
-        <v>350</v>
+        <v>340</v>
       </c>
       <c r="H72" s="1" t="s">
         <v>11</v>
@@ -3833,22 +3890,22 @@
     </row>
     <row r="73" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A73" s="1" t="s">
-        <v>352</v>
+        <v>341</v>
       </c>
       <c r="C73" s="1" t="s">
-        <v>24</v>
+        <v>38</v>
       </c>
       <c r="D73" s="1" t="s">
-        <v>347</v>
+        <v>339</v>
       </c>
       <c r="E73" s="1" t="s">
-        <v>348</v>
+        <v>47</v>
       </c>
       <c r="F73" s="1" t="s">
-        <v>349</v>
+        <v>48</v>
       </c>
       <c r="G73" s="1" t="s">
-        <v>350</v>
+        <v>340</v>
       </c>
       <c r="H73" s="1" t="s">
         <v>11</v>
@@ -3856,22 +3913,22 @@
     </row>
     <row r="74" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A74" s="1" t="s">
-        <v>353</v>
+        <v>342</v>
       </c>
       <c r="C74" s="1" t="s">
-        <v>21</v>
+        <v>33</v>
       </c>
       <c r="D74" s="1" t="s">
-        <v>354</v>
+        <v>343</v>
       </c>
       <c r="E74" s="1" t="s">
-        <v>355</v>
+        <v>344</v>
       </c>
       <c r="F74" s="1" t="s">
-        <v>7</v>
+        <v>345</v>
       </c>
       <c r="G74" s="1" t="s">
-        <v>356</v>
+        <v>346</v>
       </c>
       <c r="H74" s="1" t="s">
         <v>11</v>
@@ -3879,22 +3936,22 @@
     </row>
     <row r="75" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A75" s="1" t="s">
-        <v>357</v>
+        <v>347</v>
       </c>
       <c r="C75" s="1" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="D75" s="1" t="s">
-        <v>354</v>
+        <v>348</v>
       </c>
       <c r="E75" s="1" t="s">
-        <v>355</v>
+        <v>349</v>
       </c>
       <c r="F75" s="1" t="s">
-        <v>7</v>
+        <v>350</v>
       </c>
       <c r="G75" s="1" t="s">
-        <v>356</v>
+        <v>303</v>
       </c>
       <c r="H75" s="1" t="s">
         <v>11</v>
@@ -3902,22 +3959,22 @@
     </row>
     <row r="76" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A76" s="1" t="s">
-        <v>358</v>
+        <v>351</v>
       </c>
       <c r="C76" s="1" t="s">
-        <v>21</v>
+        <v>14</v>
       </c>
       <c r="D76" s="1" t="s">
+        <v>352</v>
+      </c>
+      <c r="E76" s="1" t="s">
+        <v>353</v>
+      </c>
+      <c r="F76" s="1" t="s">
         <v>354</v>
       </c>
-      <c r="E76" s="1" t="s">
+      <c r="G76" s="1" t="s">
         <v>355</v>
-      </c>
-      <c r="F76" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="G76" s="1" t="s">
-        <v>356</v>
       </c>
       <c r="H76" s="1" t="s">
         <v>11</v>
@@ -3925,22 +3982,22 @@
     </row>
     <row r="77" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A77" s="1" t="s">
-        <v>359</v>
+        <v>356</v>
       </c>
       <c r="C77" s="1" t="s">
-        <v>27</v>
+        <v>14</v>
       </c>
       <c r="D77" s="1" t="s">
-        <v>360</v>
+        <v>352</v>
       </c>
       <c r="E77" s="1" t="s">
-        <v>104</v>
+        <v>353</v>
       </c>
       <c r="F77" s="1" t="s">
-        <v>105</v>
+        <v>354</v>
       </c>
       <c r="G77" s="1" t="s">
-        <v>361</v>
+        <v>355</v>
       </c>
       <c r="H77" s="1" t="s">
         <v>11</v>
@@ -3948,22 +4005,22 @@
     </row>
     <row r="78" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A78" s="1" t="s">
-        <v>362</v>
+        <v>357</v>
       </c>
       <c r="C78" s="1" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="D78" s="1" t="s">
-        <v>363</v>
+        <v>352</v>
       </c>
       <c r="E78" s="1" t="s">
-        <v>107</v>
+        <v>353</v>
       </c>
       <c r="F78" s="1" t="s">
-        <v>108</v>
+        <v>354</v>
       </c>
       <c r="G78" s="1" t="s">
-        <v>38</v>
+        <v>355</v>
       </c>
       <c r="H78" s="1" t="s">
         <v>11</v>
@@ -3971,22 +4028,22 @@
     </row>
     <row r="79" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A79" s="1" t="s">
-        <v>364</v>
+        <v>358</v>
       </c>
       <c r="C79" s="1" t="s">
-        <v>45</v>
+        <v>25</v>
       </c>
       <c r="D79" s="1" t="s">
-        <v>365</v>
+        <v>359</v>
       </c>
       <c r="E79" s="1" t="s">
-        <v>303</v>
+        <v>360</v>
       </c>
       <c r="F79" s="1" t="s">
-        <v>7</v>
+        <v>361</v>
       </c>
       <c r="G79" s="1" t="s">
-        <v>366</v>
+        <v>362</v>
       </c>
       <c r="H79" s="1" t="s">
         <v>11</v>
@@ -3994,22 +4051,22 @@
     </row>
     <row r="80" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A80" s="1" t="s">
-        <v>367</v>
+        <v>363</v>
       </c>
       <c r="C80" s="1" t="s">
-        <v>45</v>
+        <v>25</v>
       </c>
       <c r="D80" s="1" t="s">
-        <v>365</v>
+        <v>359</v>
       </c>
       <c r="E80" s="1" t="s">
-        <v>303</v>
+        <v>360</v>
       </c>
       <c r="F80" s="1" t="s">
-        <v>7</v>
+        <v>361</v>
       </c>
       <c r="G80" s="1" t="s">
-        <v>366</v>
+        <v>362</v>
       </c>
       <c r="H80" s="1" t="s">
         <v>11</v>
@@ -4017,22 +4074,22 @@
     </row>
     <row r="81" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A81" s="1" t="s">
-        <v>100</v>
+        <v>364</v>
       </c>
       <c r="C81" s="1" t="s">
-        <v>39</v>
+        <v>25</v>
       </c>
       <c r="D81" s="1" t="s">
-        <v>101</v>
+        <v>359</v>
       </c>
       <c r="E81" s="1" t="s">
-        <v>56</v>
+        <v>360</v>
       </c>
       <c r="F81" s="1" t="s">
-        <v>7</v>
+        <v>361</v>
       </c>
       <c r="G81" s="1" t="s">
-        <v>102</v>
+        <v>362</v>
       </c>
       <c r="H81" s="1" t="s">
         <v>11</v>
@@ -4040,22 +4097,22 @@
     </row>
     <row r="82" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A82" s="1" t="s">
-        <v>103</v>
+        <v>365</v>
       </c>
       <c r="C82" s="1" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="D82" s="1" t="s">
-        <v>101</v>
+        <v>366</v>
       </c>
       <c r="E82" s="1" t="s">
-        <v>56</v>
+        <v>190</v>
       </c>
       <c r="F82" s="1" t="s">
-        <v>7</v>
+        <v>191</v>
       </c>
       <c r="G82" s="1" t="s">
-        <v>102</v>
+        <v>79</v>
       </c>
       <c r="H82" s="1" t="s">
         <v>11</v>
@@ -4063,22 +4120,22 @@
     </row>
     <row r="83" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A83" s="1" t="s">
+        <v>367</v>
+      </c>
+      <c r="C83" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="D83" s="1" t="s">
         <v>368</v>
       </c>
-      <c r="C83" s="1" t="s">
-        <v>72</v>
-      </c>
-      <c r="D83" s="1" t="s">
+      <c r="E83" s="1" t="s">
         <v>369</v>
       </c>
-      <c r="E83" s="1" t="s">
+      <c r="F83" s="1" t="s">
         <v>370</v>
       </c>
-      <c r="F83" s="1" t="s">
-        <v>7</v>
-      </c>
       <c r="G83" s="1" t="s">
-        <v>79</v>
+        <v>371</v>
       </c>
       <c r="H83" s="1" t="s">
         <v>11</v>
@@ -4086,22 +4143,22 @@
     </row>
     <row r="84" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A84" s="1" t="s">
-        <v>371</v>
+        <v>372</v>
       </c>
       <c r="C84" s="1" t="s">
-        <v>14</v>
+        <v>23</v>
       </c>
       <c r="D84" s="1" t="s">
-        <v>372</v>
+        <v>373</v>
       </c>
       <c r="E84" s="1" t="s">
-        <v>373</v>
+        <v>374</v>
       </c>
       <c r="F84" s="1" t="s">
         <v>7</v>
       </c>
       <c r="G84" s="1" t="s">
-        <v>374</v>
+        <v>375</v>
       </c>
       <c r="H84" s="1" t="s">
         <v>11</v>
@@ -4109,22 +4166,22 @@
     </row>
     <row r="85" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A85" s="1" t="s">
-        <v>375</v>
+        <v>376</v>
       </c>
       <c r="C85" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D85" s="1" t="s">
-        <v>376</v>
+        <v>377</v>
       </c>
       <c r="E85" s="1" t="s">
-        <v>172</v>
+        <v>112</v>
       </c>
       <c r="F85" s="1" t="s">
         <v>7</v>
       </c>
       <c r="G85" s="1" t="s">
-        <v>377</v>
+        <v>378</v>
       </c>
       <c r="H85" s="1" t="s">
         <v>11</v>
@@ -4132,22 +4189,22 @@
     </row>
     <row r="86" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A86" s="1" t="s">
-        <v>378</v>
+        <v>379</v>
       </c>
       <c r="C86" s="1" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="D86" s="1" t="s">
-        <v>376</v>
+        <v>380</v>
       </c>
       <c r="E86" s="1" t="s">
-        <v>172</v>
+        <v>155</v>
       </c>
       <c r="F86" s="1" t="s">
         <v>7</v>
       </c>
       <c r="G86" s="1" t="s">
-        <v>377</v>
+        <v>381</v>
       </c>
       <c r="H86" s="1" t="s">
         <v>11</v>
@@ -4155,22 +4212,22 @@
     </row>
     <row r="87" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A87" s="1" t="s">
-        <v>379</v>
+        <v>382</v>
       </c>
       <c r="C87" s="1" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="D87" s="1" t="s">
-        <v>376</v>
+        <v>380</v>
       </c>
       <c r="E87" s="1" t="s">
-        <v>172</v>
+        <v>155</v>
       </c>
       <c r="F87" s="1" t="s">
         <v>7</v>
       </c>
       <c r="G87" s="1" t="s">
-        <v>377</v>
+        <v>381</v>
       </c>
       <c r="H87" s="1" t="s">
         <v>11</v>
@@ -4178,22 +4235,22 @@
     </row>
     <row r="88" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A88" s="1" t="s">
-        <v>380</v>
+        <v>383</v>
       </c>
       <c r="C88" s="1" t="s">
-        <v>27</v>
+        <v>13</v>
       </c>
       <c r="D88" s="1" t="s">
-        <v>381</v>
+        <v>384</v>
       </c>
       <c r="E88" s="1" t="s">
-        <v>109</v>
+        <v>385</v>
       </c>
       <c r="F88" s="1" t="s">
-        <v>7</v>
+        <v>386</v>
       </c>
       <c r="G88" s="1" t="s">
-        <v>382</v>
+        <v>387</v>
       </c>
       <c r="H88" s="1" t="s">
         <v>11</v>
@@ -4201,22 +4258,22 @@
     </row>
     <row r="89" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A89" s="1" t="s">
-        <v>383</v>
+        <v>388</v>
       </c>
       <c r="C89" s="1" t="s">
-        <v>46</v>
+        <v>14</v>
       </c>
       <c r="D89" s="1" t="s">
-        <v>384</v>
+        <v>389</v>
       </c>
       <c r="E89" s="1" t="s">
-        <v>18</v>
+        <v>297</v>
       </c>
       <c r="F89" s="1" t="s">
-        <v>19</v>
+        <v>298</v>
       </c>
       <c r="G89" s="1" t="s">
-        <v>385</v>
+        <v>390</v>
       </c>
       <c r="H89" s="1" t="s">
         <v>11</v>
@@ -4224,22 +4281,22 @@
     </row>
     <row r="90" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A90" s="1" t="s">
-        <v>386</v>
+        <v>391</v>
       </c>
       <c r="C90" s="1" t="s">
-        <v>28</v>
+        <v>31</v>
       </c>
       <c r="D90" s="1" t="s">
-        <v>387</v>
+        <v>392</v>
       </c>
       <c r="E90" s="1" t="s">
-        <v>51</v>
+        <v>34</v>
       </c>
       <c r="F90" s="1" t="s">
         <v>7</v>
       </c>
       <c r="G90" s="1" t="s">
-        <v>388</v>
+        <v>393</v>
       </c>
       <c r="H90" s="1" t="s">
         <v>11</v>
@@ -4247,22 +4304,22 @@
     </row>
     <row r="91" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A91" s="1" t="s">
-        <v>389</v>
+        <v>394</v>
       </c>
       <c r="C91" s="1" t="s">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="D91" s="1" t="s">
-        <v>390</v>
+        <v>395</v>
       </c>
       <c r="E91" s="1" t="s">
-        <v>60</v>
+        <v>19</v>
       </c>
       <c r="F91" s="1" t="s">
         <v>7</v>
       </c>
       <c r="G91" s="1" t="s">
-        <v>391</v>
+        <v>396</v>
       </c>
       <c r="H91" s="1" t="s">
         <v>11</v>
@@ -4270,22 +4327,22 @@
     </row>
     <row r="92" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A92" s="1" t="s">
-        <v>392</v>
+        <v>397</v>
       </c>
       <c r="C92" s="1" t="s">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="D92" s="1" t="s">
-        <v>390</v>
+        <v>395</v>
       </c>
       <c r="E92" s="1" t="s">
-        <v>60</v>
+        <v>19</v>
       </c>
       <c r="F92" s="1" t="s">
         <v>7</v>
       </c>
       <c r="G92" s="1" t="s">
-        <v>391</v>
+        <v>396</v>
       </c>
       <c r="H92" s="1" t="s">
         <v>11</v>
@@ -4293,22 +4350,22 @@
     </row>
     <row r="93" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A93" s="1" t="s">
-        <v>110</v>
+        <v>398</v>
       </c>
       <c r="C93" s="1" t="s">
-        <v>46</v>
+        <v>37</v>
       </c>
       <c r="D93" s="1" t="s">
-        <v>111</v>
+        <v>399</v>
       </c>
       <c r="E93" s="1" t="s">
-        <v>112</v>
+        <v>97</v>
       </c>
       <c r="F93" s="1" t="s">
         <v>7</v>
       </c>
       <c r="G93" s="1" t="s">
-        <v>113</v>
+        <v>400</v>
       </c>
       <c r="H93" s="1" t="s">
         <v>11</v>
@@ -4316,22 +4373,22 @@
     </row>
     <row r="94" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A94" s="1" t="s">
-        <v>393</v>
+        <v>401</v>
       </c>
       <c r="C94" s="1" t="s">
-        <v>64</v>
+        <v>13</v>
       </c>
       <c r="D94" s="1" t="s">
-        <v>394</v>
+        <v>402</v>
       </c>
       <c r="E94" s="1" t="s">
-        <v>395</v>
+        <v>58</v>
       </c>
       <c r="F94" s="1" t="s">
-        <v>7</v>
+        <v>59</v>
       </c>
       <c r="G94" s="1" t="s">
-        <v>396</v>
+        <v>403</v>
       </c>
       <c r="H94" s="1" t="s">
         <v>11</v>
@@ -4339,22 +4396,22 @@
     </row>
     <row r="95" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A95" s="1" t="s">
-        <v>397</v>
+        <v>404</v>
       </c>
       <c r="C95" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="D95" s="1" t="s">
+        <v>405</v>
+      </c>
+      <c r="E95" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="F95" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="G95" s="1" t="s">
         <v>28</v>
-      </c>
-      <c r="D95" s="1" t="s">
-        <v>398</v>
-      </c>
-      <c r="E95" s="1" t="s">
-        <v>85</v>
-      </c>
-      <c r="F95" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="G95" s="1" t="s">
-        <v>124</v>
       </c>
       <c r="H95" s="1" t="s">
         <v>11</v>
@@ -4362,22 +4419,22 @@
     </row>
     <row r="96" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A96" s="1" t="s">
-        <v>399</v>
+        <v>406</v>
       </c>
       <c r="C96" s="1" t="s">
-        <v>28</v>
+        <v>37</v>
       </c>
       <c r="D96" s="1" t="s">
-        <v>398</v>
+        <v>407</v>
       </c>
       <c r="E96" s="1" t="s">
-        <v>85</v>
+        <v>408</v>
       </c>
       <c r="F96" s="1" t="s">
-        <v>7</v>
+        <v>409</v>
       </c>
       <c r="G96" s="1" t="s">
-        <v>124</v>
+        <v>410</v>
       </c>
       <c r="H96" s="1" t="s">
         <v>11</v>
@@ -4385,22 +4442,22 @@
     </row>
     <row r="97" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A97" s="1" t="s">
-        <v>400</v>
+        <v>411</v>
       </c>
       <c r="C97" s="1" t="s">
-        <v>12</v>
+        <v>40</v>
       </c>
       <c r="D97" s="1" t="s">
-        <v>401</v>
+        <v>412</v>
       </c>
       <c r="E97" s="1" t="s">
-        <v>402</v>
+        <v>413</v>
       </c>
       <c r="F97" s="1" t="s">
-        <v>403</v>
+        <v>7</v>
       </c>
       <c r="G97" s="1" t="s">
-        <v>404</v>
+        <v>414</v>
       </c>
       <c r="H97" s="1" t="s">
         <v>11</v>
@@ -4408,22 +4465,22 @@
     </row>
     <row r="98" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A98" s="1" t="s">
-        <v>405</v>
+        <v>415</v>
       </c>
       <c r="C98" s="1" t="s">
-        <v>135</v>
+        <v>20</v>
       </c>
       <c r="D98" s="1" t="s">
-        <v>406</v>
+        <v>416</v>
       </c>
       <c r="E98" s="1" t="s">
-        <v>16</v>
+        <v>123</v>
       </c>
       <c r="F98" s="1" t="s">
-        <v>17</v>
+        <v>7</v>
       </c>
       <c r="G98" s="1" t="s">
-        <v>407</v>
+        <v>417</v>
       </c>
       <c r="H98" s="1" t="s">
         <v>11</v>
@@ -4431,22 +4488,22 @@
     </row>
     <row r="99" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A99" s="1" t="s">
-        <v>408</v>
+        <v>418</v>
       </c>
       <c r="C99" s="1" t="s">
-        <v>72</v>
+        <v>40</v>
       </c>
       <c r="D99" s="1" t="s">
-        <v>409</v>
+        <v>419</v>
       </c>
       <c r="E99" s="1" t="s">
-        <v>410</v>
+        <v>420</v>
       </c>
       <c r="F99" s="1" t="s">
         <v>7</v>
       </c>
       <c r="G99" s="1" t="s">
-        <v>411</v>
+        <v>421</v>
       </c>
       <c r="H99" s="1" t="s">
         <v>11</v>
@@ -4454,22 +4511,22 @@
     </row>
     <row r="100" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A100" s="1" t="s">
-        <v>412</v>
+        <v>422</v>
       </c>
       <c r="C100" s="1" t="s">
-        <v>9</v>
+        <v>26</v>
       </c>
       <c r="D100" s="1" t="s">
-        <v>413</v>
+        <v>423</v>
       </c>
       <c r="E100" s="1" t="s">
-        <v>75</v>
+        <v>64</v>
       </c>
       <c r="F100" s="1" t="s">
-        <v>7</v>
+        <v>65</v>
       </c>
       <c r="G100" s="1" t="s">
-        <v>414</v>
+        <v>424</v>
       </c>
       <c r="H100" s="1" t="s">
         <v>11</v>
@@ -4477,22 +4534,22 @@
     </row>
     <row r="101" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A101" s="1" t="s">
-        <v>415</v>
+        <v>425</v>
       </c>
       <c r="C101" s="1" t="s">
-        <v>15</v>
+        <v>26</v>
       </c>
       <c r="D101" s="1" t="s">
-        <v>416</v>
+        <v>423</v>
       </c>
       <c r="E101" s="1" t="s">
-        <v>307</v>
+        <v>64</v>
       </c>
       <c r="F101" s="1" t="s">
-        <v>7</v>
+        <v>65</v>
       </c>
       <c r="G101" s="1" t="s">
-        <v>417</v>
+        <v>424</v>
       </c>
       <c r="H101" s="1" t="s">
         <v>11</v>
@@ -4500,22 +4557,22 @@
     </row>
     <row r="102" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A102" s="1" t="s">
-        <v>418</v>
+        <v>426</v>
       </c>
       <c r="C102" s="1" t="s">
-        <v>15</v>
+        <v>26</v>
       </c>
       <c r="D102" s="1" t="s">
-        <v>416</v>
+        <v>423</v>
       </c>
       <c r="E102" s="1" t="s">
-        <v>307</v>
+        <v>64</v>
       </c>
       <c r="F102" s="1" t="s">
-        <v>7</v>
+        <v>65</v>
       </c>
       <c r="G102" s="1" t="s">
-        <v>417</v>
+        <v>424</v>
       </c>
       <c r="H102" s="1" t="s">
         <v>11</v>
@@ -4523,22 +4580,22 @@
     </row>
     <row r="103" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A103" s="1" t="s">
-        <v>419</v>
+        <v>427</v>
       </c>
       <c r="C103" s="1" t="s">
-        <v>15</v>
+        <v>9</v>
       </c>
       <c r="D103" s="1" t="s">
-        <v>416</v>
+        <v>428</v>
       </c>
       <c r="E103" s="1" t="s">
-        <v>307</v>
+        <v>54</v>
       </c>
       <c r="F103" s="1" t="s">
         <v>7</v>
       </c>
       <c r="G103" s="1" t="s">
-        <v>417</v>
+        <v>429</v>
       </c>
       <c r="H103" s="1" t="s">
         <v>11</v>
@@ -4546,22 +4603,22 @@
     </row>
     <row r="104" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A104" s="1" t="s">
-        <v>420</v>
+        <v>430</v>
       </c>
       <c r="C104" s="1" t="s">
-        <v>29</v>
+        <v>9</v>
       </c>
       <c r="D104" s="1" t="s">
-        <v>421</v>
+        <v>431</v>
       </c>
       <c r="E104" s="1" t="s">
-        <v>422</v>
+        <v>54</v>
       </c>
       <c r="F104" s="1" t="s">
-        <v>423</v>
+        <v>7</v>
       </c>
       <c r="G104" s="1" t="s">
-        <v>424</v>
+        <v>250</v>
       </c>
       <c r="H104" s="1" t="s">
         <v>11</v>
@@ -4569,22 +4626,22 @@
     </row>
     <row r="105" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A105" s="1" t="s">
-        <v>425</v>
+        <v>432</v>
       </c>
       <c r="C105" s="1" t="s">
-        <v>135</v>
+        <v>14</v>
       </c>
       <c r="D105" s="1" t="s">
-        <v>426</v>
+        <v>433</v>
       </c>
       <c r="E105" s="1" t="s">
-        <v>125</v>
+        <v>86</v>
       </c>
       <c r="F105" s="1" t="s">
-        <v>126</v>
+        <v>87</v>
       </c>
       <c r="G105" s="1" t="s">
-        <v>427</v>
+        <v>105</v>
       </c>
       <c r="H105" s="1" t="s">
         <v>11</v>
@@ -4592,22 +4649,22 @@
     </row>
     <row r="106" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A106" s="1" t="s">
-        <v>428</v>
+        <v>434</v>
       </c>
       <c r="C106" s="1" t="s">
-        <v>22</v>
+        <v>199</v>
       </c>
       <c r="D106" s="1" t="s">
-        <v>429</v>
+        <v>435</v>
       </c>
       <c r="E106" s="1" t="s">
-        <v>430</v>
+        <v>45</v>
       </c>
       <c r="F106" s="1" t="s">
         <v>7</v>
       </c>
       <c r="G106" s="1" t="s">
-        <v>431</v>
+        <v>436</v>
       </c>
       <c r="H106" s="1" t="s">
         <v>11</v>
@@ -4615,22 +4672,22 @@
     </row>
     <row r="107" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A107" s="1" t="s">
-        <v>432</v>
+        <v>437</v>
       </c>
       <c r="C107" s="1" t="s">
-        <v>28</v>
+        <v>33</v>
       </c>
       <c r="D107" s="1" t="s">
-        <v>433</v>
+        <v>438</v>
       </c>
       <c r="E107" s="1" t="s">
-        <v>62</v>
+        <v>66</v>
       </c>
       <c r="F107" s="1" t="s">
         <v>7</v>
       </c>
       <c r="G107" s="1" t="s">
-        <v>434</v>
+        <v>439</v>
       </c>
       <c r="H107" s="1" t="s">
         <v>11</v>
@@ -4638,22 +4695,22 @@
     </row>
     <row r="108" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A108" s="1" t="s">
-        <v>435</v>
+        <v>440</v>
       </c>
       <c r="C108" s="1" t="s">
-        <v>39</v>
+        <v>21</v>
       </c>
       <c r="D108" s="1" t="s">
-        <v>436</v>
+        <v>441</v>
       </c>
       <c r="E108" s="1" t="s">
-        <v>437</v>
+        <v>442</v>
       </c>
       <c r="F108" s="1" t="s">
-        <v>438</v>
+        <v>7</v>
       </c>
       <c r="G108" s="1" t="s">
-        <v>439</v>
+        <v>443</v>
       </c>
       <c r="H108" s="1" t="s">
         <v>11</v>
@@ -4661,22 +4718,22 @@
     </row>
     <row r="109" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A109" s="1" t="s">
-        <v>440</v>
+        <v>444</v>
       </c>
       <c r="C109" s="1" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="D109" s="1" t="s">
-        <v>441</v>
+        <v>445</v>
       </c>
       <c r="E109" s="1" t="s">
-        <v>31</v>
+        <v>446</v>
       </c>
       <c r="F109" s="1" t="s">
         <v>7</v>
       </c>
       <c r="G109" s="1" t="s">
-        <v>442</v>
+        <v>447</v>
       </c>
       <c r="H109" s="1" t="s">
         <v>11</v>
@@ -4684,22 +4741,22 @@
     </row>
     <row r="110" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A110" s="1" t="s">
-        <v>443</v>
+        <v>448</v>
       </c>
       <c r="C110" s="1" t="s">
-        <v>14</v>
+        <v>40</v>
       </c>
       <c r="D110" s="1" t="s">
-        <v>444</v>
+        <v>449</v>
       </c>
       <c r="E110" s="1" t="s">
-        <v>65</v>
+        <v>168</v>
       </c>
       <c r="F110" s="1" t="s">
         <v>7</v>
       </c>
       <c r="G110" s="1" t="s">
-        <v>66</v>
+        <v>169</v>
       </c>
       <c r="H110" s="1" t="s">
         <v>11</v>
@@ -4707,22 +4764,22 @@
     </row>
     <row r="111" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A111" s="1" t="s">
-        <v>445</v>
+        <v>450</v>
       </c>
       <c r="C111" s="1" t="s">
-        <v>72</v>
+        <v>10</v>
       </c>
       <c r="D111" s="1" t="s">
-        <v>446</v>
+        <v>451</v>
       </c>
       <c r="E111" s="1" t="s">
-        <v>447</v>
+        <v>452</v>
       </c>
       <c r="F111" s="1" t="s">
         <v>7</v>
       </c>
       <c r="G111" s="1" t="s">
-        <v>448</v>
+        <v>453</v>
       </c>
       <c r="H111" s="1" t="s">
         <v>11</v>
@@ -4730,22 +4787,22 @@
     </row>
     <row r="112" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A112" s="1" t="s">
-        <v>449</v>
+        <v>454</v>
       </c>
       <c r="C112" s="1" t="s">
-        <v>27</v>
+        <v>46</v>
       </c>
       <c r="D112" s="1" t="s">
-        <v>450</v>
+        <v>455</v>
       </c>
       <c r="E112" s="1" t="s">
+        <v>98</v>
+      </c>
+      <c r="F112" s="1" t="s">
         <v>99</v>
       </c>
-      <c r="F112" s="1" t="s">
-        <v>7</v>
-      </c>
       <c r="G112" s="1" t="s">
-        <v>451</v>
+        <v>456</v>
       </c>
       <c r="H112" s="1" t="s">
         <v>11</v>
@@ -4753,22 +4810,22 @@
     </row>
     <row r="113" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A113" s="1" t="s">
-        <v>452</v>
+        <v>457</v>
       </c>
       <c r="C113" s="1" t="s">
-        <v>50</v>
+        <v>9</v>
       </c>
       <c r="D113" s="1" t="s">
-        <v>453</v>
+        <v>458</v>
       </c>
       <c r="E113" s="1" t="s">
-        <v>26</v>
+        <v>94</v>
       </c>
       <c r="F113" s="1" t="s">
-        <v>7</v>
+        <v>95</v>
       </c>
       <c r="G113" s="1" t="s">
-        <v>454</v>
+        <v>459</v>
       </c>
       <c r="H113" s="1" t="s">
         <v>11</v>
@@ -4776,22 +4833,22 @@
     </row>
     <row r="114" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A114" s="1" t="s">
-        <v>455</v>
+        <v>460</v>
       </c>
       <c r="C114" s="1" t="s">
-        <v>22</v>
+        <v>461</v>
       </c>
       <c r="D114" s="1" t="s">
-        <v>456</v>
+        <v>462</v>
       </c>
       <c r="E114" s="1" t="s">
-        <v>457</v>
+        <v>90</v>
       </c>
       <c r="F114" s="1" t="s">
         <v>7</v>
       </c>
       <c r="G114" s="1" t="s">
-        <v>142</v>
+        <v>463</v>
       </c>
       <c r="H114" s="1" t="s">
         <v>11</v>
@@ -4799,22 +4856,22 @@
     </row>
     <row r="115" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A115" s="1" t="s">
-        <v>458</v>
+        <v>464</v>
       </c>
       <c r="C115" s="1" t="s">
-        <v>21</v>
+        <v>36</v>
       </c>
       <c r="D115" s="1" t="s">
-        <v>459</v>
+        <v>465</v>
       </c>
       <c r="E115" s="1" t="s">
-        <v>355</v>
+        <v>22</v>
       </c>
       <c r="F115" s="1" t="s">
         <v>7</v>
       </c>
       <c r="G115" s="1" t="s">
-        <v>460</v>
+        <v>466</v>
       </c>
       <c r="H115" s="1" t="s">
         <v>11</v>
@@ -4822,22 +4879,22 @@
     </row>
     <row r="116" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A116" s="1" t="s">
-        <v>461</v>
+        <v>467</v>
       </c>
       <c r="C116" s="1" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="D116" s="1" t="s">
-        <v>459</v>
+        <v>468</v>
       </c>
       <c r="E116" s="1" t="s">
-        <v>355</v>
+        <v>17</v>
       </c>
       <c r="F116" s="1" t="s">
-        <v>7</v>
+        <v>18</v>
       </c>
       <c r="G116" s="1" t="s">
-        <v>460</v>
+        <v>85</v>
       </c>
       <c r="H116" s="1" t="s">
         <v>11</v>
@@ -4845,22 +4902,22 @@
     </row>
     <row r="117" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A117" s="1" t="s">
-        <v>462</v>
+        <v>469</v>
       </c>
       <c r="C117" s="1" t="s">
-        <v>72</v>
+        <v>270</v>
       </c>
       <c r="D117" s="1" t="s">
-        <v>463</v>
+        <v>470</v>
       </c>
       <c r="E117" s="1" t="s">
-        <v>464</v>
+        <v>100</v>
       </c>
       <c r="F117" s="1" t="s">
         <v>7</v>
       </c>
       <c r="G117" s="1" t="s">
-        <v>465</v>
+        <v>471</v>
       </c>
       <c r="H117" s="1" t="s">
         <v>11</v>
@@ -4868,22 +4925,22 @@
     </row>
     <row r="118" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A118" s="1" t="s">
-        <v>466</v>
+        <v>472</v>
       </c>
       <c r="C118" s="1" t="s">
-        <v>135</v>
+        <v>69</v>
       </c>
       <c r="D118" s="1" t="s">
-        <v>467</v>
+        <v>473</v>
       </c>
       <c r="E118" s="1" t="s">
-        <v>468</v>
+        <v>474</v>
       </c>
       <c r="F118" s="1" t="s">
-        <v>469</v>
+        <v>7</v>
       </c>
       <c r="G118" s="1" t="s">
-        <v>106</v>
+        <v>475</v>
       </c>
       <c r="H118" s="1" t="s">
         <v>11</v>
@@ -4891,22 +4948,22 @@
     </row>
     <row r="119" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A119" s="1" t="s">
-        <v>470</v>
+        <v>476</v>
       </c>
       <c r="C119" s="1" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="D119" s="1" t="s">
-        <v>471</v>
+        <v>477</v>
       </c>
       <c r="E119" s="1" t="s">
-        <v>34</v>
+        <v>478</v>
       </c>
       <c r="F119" s="1" t="s">
-        <v>35</v>
+        <v>7</v>
       </c>
       <c r="G119" s="1" t="s">
-        <v>472</v>
+        <v>479</v>
       </c>
       <c r="H119" s="1" t="s">
         <v>11</v>
@@ -4914,22 +4971,22 @@
     </row>
     <row r="120" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A120" s="1" t="s">
-        <v>473</v>
+        <v>480</v>
       </c>
       <c r="C120" s="1" t="s">
-        <v>50</v>
+        <v>461</v>
       </c>
       <c r="D120" s="1" t="s">
-        <v>474</v>
+        <v>481</v>
       </c>
       <c r="E120" s="1" t="s">
-        <v>30</v>
+        <v>482</v>
       </c>
       <c r="F120" s="1" t="s">
-        <v>7</v>
+        <v>483</v>
       </c>
       <c r="G120" s="1" t="s">
-        <v>475</v>
+        <v>484</v>
       </c>
       <c r="H120" s="1" t="s">
         <v>11</v>
@@ -4937,22 +4994,22 @@
     </row>
     <row r="121" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A121" s="1" t="s">
-        <v>476</v>
+        <v>485</v>
       </c>
       <c r="C121" s="1" t="s">
-        <v>10</v>
+        <v>31</v>
       </c>
       <c r="D121" s="1" t="s">
-        <v>477</v>
+        <v>486</v>
       </c>
       <c r="E121" s="1" t="s">
-        <v>90</v>
+        <v>487</v>
       </c>
       <c r="F121" s="1" t="s">
         <v>7</v>
       </c>
       <c r="G121" s="1" t="s">
-        <v>478</v>
+        <v>488</v>
       </c>
       <c r="H121" s="1" t="s">
         <v>11</v>
@@ -4960,22 +5017,22 @@
     </row>
     <row r="122" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A122" s="1" t="s">
-        <v>479</v>
+        <v>489</v>
       </c>
       <c r="C122" s="1" t="s">
-        <v>24</v>
+        <v>270</v>
       </c>
       <c r="D122" s="1" t="s">
-        <v>480</v>
+        <v>490</v>
       </c>
       <c r="E122" s="1" t="s">
-        <v>71</v>
+        <v>491</v>
       </c>
       <c r="F122" s="1" t="s">
         <v>7</v>
       </c>
       <c r="G122" s="1" t="s">
-        <v>481</v>
+        <v>492</v>
       </c>
       <c r="H122" s="1" t="s">
         <v>11</v>
@@ -4983,22 +5040,22 @@
     </row>
     <row r="123" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A123" s="1" t="s">
-        <v>482</v>
+        <v>493</v>
       </c>
       <c r="C123" s="1" t="s">
-        <v>39</v>
+        <v>36</v>
       </c>
       <c r="D123" s="1" t="s">
-        <v>483</v>
+        <v>494</v>
       </c>
       <c r="E123" s="1" t="s">
-        <v>437</v>
+        <v>92</v>
       </c>
       <c r="F123" s="1" t="s">
-        <v>438</v>
+        <v>7</v>
       </c>
       <c r="G123" s="1" t="s">
-        <v>484</v>
+        <v>495</v>
       </c>
       <c r="H123" s="1" t="s">
         <v>11</v>
@@ -5006,22 +5063,22 @@
     </row>
     <row r="124" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A124" s="1" t="s">
-        <v>485</v>
+        <v>496</v>
       </c>
       <c r="C124" s="1" t="s">
-        <v>39</v>
+        <v>69</v>
       </c>
       <c r="D124" s="1" t="s">
-        <v>483</v>
+        <v>497</v>
       </c>
       <c r="E124" s="1" t="s">
-        <v>437</v>
+        <v>498</v>
       </c>
       <c r="F124" s="1" t="s">
-        <v>438</v>
+        <v>7</v>
       </c>
       <c r="G124" s="1" t="s">
-        <v>484</v>
+        <v>180</v>
       </c>
       <c r="H124" s="1" t="s">
         <v>11</v>
@@ -5029,22 +5086,22 @@
     </row>
     <row r="125" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A125" s="1" t="s">
-        <v>486</v>
+        <v>499</v>
       </c>
       <c r="C125" s="1" t="s">
-        <v>15</v>
+        <v>31</v>
       </c>
       <c r="D125" s="1" t="s">
-        <v>487</v>
+        <v>500</v>
       </c>
       <c r="E125" s="1" t="s">
-        <v>107</v>
+        <v>111</v>
       </c>
       <c r="F125" s="1" t="s">
-        <v>108</v>
+        <v>7</v>
       </c>
       <c r="G125" s="1" t="s">
-        <v>488</v>
+        <v>501</v>
       </c>
       <c r="H125" s="1" t="s">
         <v>11</v>
@@ -5052,22 +5109,22 @@
     </row>
     <row r="126" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A126" s="1" t="s">
-        <v>489</v>
+        <v>502</v>
       </c>
       <c r="C126" s="1" t="s">
-        <v>24</v>
+        <v>31</v>
       </c>
       <c r="D126" s="1" t="s">
-        <v>490</v>
+        <v>500</v>
       </c>
       <c r="E126" s="1" t="s">
-        <v>491</v>
+        <v>111</v>
       </c>
       <c r="F126" s="1" t="s">
         <v>7</v>
       </c>
       <c r="G126" s="1" t="s">
-        <v>492</v>
+        <v>501</v>
       </c>
       <c r="H126" s="1" t="s">
         <v>11</v>
@@ -5075,22 +5132,22 @@
     </row>
     <row r="127" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A127" s="1" t="s">
-        <v>493</v>
+        <v>503</v>
       </c>
       <c r="C127" s="1" t="s">
-        <v>24</v>
+        <v>31</v>
       </c>
       <c r="D127" s="1" t="s">
-        <v>490</v>
+        <v>500</v>
       </c>
       <c r="E127" s="1" t="s">
-        <v>491</v>
+        <v>111</v>
       </c>
       <c r="F127" s="1" t="s">
         <v>7</v>
       </c>
       <c r="G127" s="1" t="s">
-        <v>492</v>
+        <v>501</v>
       </c>
       <c r="H127" s="1" t="s">
         <v>11</v>
@@ -5098,22 +5155,22 @@
     </row>
     <row r="128" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A128" s="1" t="s">
-        <v>494</v>
+        <v>504</v>
       </c>
       <c r="C128" s="1" t="s">
-        <v>39</v>
+        <v>46</v>
       </c>
       <c r="D128" s="1" t="s">
-        <v>495</v>
+        <v>505</v>
       </c>
       <c r="E128" s="1" t="s">
-        <v>437</v>
+        <v>98</v>
       </c>
       <c r="F128" s="1" t="s">
-        <v>438</v>
+        <v>99</v>
       </c>
       <c r="G128" s="1" t="s">
-        <v>496</v>
+        <v>506</v>
       </c>
       <c r="H128" s="1" t="s">
         <v>11</v>
@@ -5121,22 +5178,22 @@
     </row>
     <row r="129" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A129" s="1" t="s">
-        <v>497</v>
+        <v>507</v>
       </c>
       <c r="C129" s="1" t="s">
-        <v>50</v>
+        <v>26</v>
       </c>
       <c r="D129" s="1" t="s">
-        <v>498</v>
+        <v>508</v>
       </c>
       <c r="E129" s="1" t="s">
-        <v>30</v>
+        <v>64</v>
       </c>
       <c r="F129" s="1" t="s">
-        <v>7</v>
+        <v>65</v>
       </c>
       <c r="G129" s="1" t="s">
-        <v>499</v>
+        <v>509</v>
       </c>
       <c r="H129" s="1" t="s">
         <v>11</v>
@@ -5144,22 +5201,22 @@
     </row>
     <row r="130" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A130" s="1" t="s">
-        <v>500</v>
+        <v>510</v>
       </c>
       <c r="C130" s="1" t="s">
-        <v>135</v>
+        <v>25</v>
       </c>
       <c r="D130" s="1" t="s">
-        <v>501</v>
+        <v>511</v>
       </c>
       <c r="E130" s="1" t="s">
-        <v>47</v>
+        <v>360</v>
       </c>
       <c r="F130" s="1" t="s">
-        <v>48</v>
+        <v>361</v>
       </c>
       <c r="G130" s="1" t="s">
-        <v>114</v>
+        <v>512</v>
       </c>
       <c r="H130" s="1" t="s">
         <v>11</v>
@@ -5167,22 +5224,22 @@
     </row>
     <row r="131" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A131" s="1" t="s">
-        <v>502</v>
+        <v>513</v>
       </c>
       <c r="C131" s="1" t="s">
-        <v>72</v>
+        <v>36</v>
       </c>
       <c r="D131" s="1" t="s">
-        <v>503</v>
+        <v>514</v>
       </c>
       <c r="E131" s="1" t="s">
-        <v>504</v>
+        <v>42</v>
       </c>
       <c r="F131" s="1" t="s">
         <v>7</v>
       </c>
       <c r="G131" s="1" t="s">
-        <v>505</v>
+        <v>515</v>
       </c>
       <c r="H131" s="1" t="s">
         <v>11</v>
@@ -5190,822 +5247,853 @@
     </row>
     <row r="132" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A132" s="1" t="s">
-        <v>506</v>
+        <v>516</v>
       </c>
       <c r="C132" s="1" t="s">
-        <v>12</v>
+        <v>26</v>
       </c>
       <c r="D132" s="1" t="s">
-        <v>507</v>
+        <v>517</v>
       </c>
       <c r="E132" s="1" t="s">
-        <v>54</v>
+        <v>15</v>
       </c>
       <c r="F132" s="1" t="s">
-        <v>55</v>
+        <v>16</v>
       </c>
       <c r="G132" s="1" t="s">
-        <v>508</v>
+        <v>518</v>
       </c>
       <c r="H132" s="1" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
     </row>
     <row r="133" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A133" s="1" t="s">
-        <v>509</v>
+        <v>519</v>
       </c>
       <c r="C133" s="1" t="s">
-        <v>12</v>
+        <v>46</v>
       </c>
       <c r="D133" s="1" t="s">
-        <v>507</v>
+        <v>520</v>
       </c>
       <c r="E133" s="1" t="s">
-        <v>54</v>
+        <v>521</v>
       </c>
       <c r="F133" s="1" t="s">
-        <v>55</v>
+        <v>522</v>
       </c>
       <c r="G133" s="1" t="s">
-        <v>508</v>
+        <v>523</v>
       </c>
       <c r="H133" s="1" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
     </row>
     <row r="134" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A134" s="1" t="s">
-        <v>510</v>
+        <v>524</v>
       </c>
       <c r="C134" s="1" t="s">
-        <v>15</v>
+        <v>36</v>
       </c>
       <c r="D134" s="1" t="s">
-        <v>511</v>
+        <v>525</v>
       </c>
       <c r="E134" s="1" t="s">
-        <v>512</v>
+        <v>526</v>
       </c>
       <c r="F134" s="1" t="s">
-        <v>513</v>
+        <v>7</v>
       </c>
       <c r="G134" s="1" t="s">
-        <v>514</v>
+        <v>527</v>
       </c>
       <c r="H134" s="1" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
     </row>
     <row r="135" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A135" s="1" t="s">
-        <v>515</v>
+        <v>528</v>
       </c>
       <c r="C135" s="1" t="s">
-        <v>15</v>
+        <v>23</v>
       </c>
       <c r="D135" s="1" t="s">
-        <v>511</v>
+        <v>529</v>
       </c>
       <c r="E135" s="1" t="s">
-        <v>512</v>
+        <v>44</v>
       </c>
       <c r="F135" s="1" t="s">
-        <v>513</v>
+        <v>7</v>
       </c>
       <c r="G135" s="1" t="s">
-        <v>514</v>
+        <v>530</v>
       </c>
       <c r="H135" s="1" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
     </row>
     <row r="136" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A136" s="1" t="s">
-        <v>516</v>
+        <v>531</v>
       </c>
       <c r="C136" s="1" t="s">
-        <v>39</v>
+        <v>46</v>
       </c>
       <c r="D136" s="1" t="s">
-        <v>517</v>
+        <v>532</v>
       </c>
       <c r="E136" s="1" t="s">
-        <v>128</v>
+        <v>93</v>
       </c>
       <c r="F136" s="1" t="s">
         <v>7</v>
       </c>
       <c r="G136" s="1" t="s">
-        <v>518</v>
+        <v>533</v>
       </c>
       <c r="H136" s="1" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
     </row>
     <row r="137" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A137" s="1" t="s">
-        <v>519</v>
+        <v>534</v>
       </c>
       <c r="C137" s="1" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="D137" s="1" t="s">
-        <v>517</v>
+        <v>535</v>
       </c>
       <c r="E137" s="1" t="s">
-        <v>128</v>
+        <v>62</v>
       </c>
       <c r="F137" s="1" t="s">
-        <v>7</v>
+        <v>63</v>
       </c>
       <c r="G137" s="1" t="s">
-        <v>518</v>
+        <v>536</v>
       </c>
       <c r="H137" s="1" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
     </row>
     <row r="138" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A138" s="1" t="s">
-        <v>520</v>
+        <v>537</v>
       </c>
       <c r="C138" s="1" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="D138" s="1" t="s">
-        <v>517</v>
+        <v>535</v>
       </c>
       <c r="E138" s="1" t="s">
-        <v>128</v>
+        <v>62</v>
       </c>
       <c r="F138" s="1" t="s">
-        <v>7</v>
+        <v>63</v>
       </c>
       <c r="G138" s="1" t="s">
-        <v>518</v>
+        <v>536</v>
       </c>
       <c r="H138" s="1" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
     </row>
     <row r="139" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A139" s="1" t="s">
-        <v>521</v>
+        <v>538</v>
       </c>
       <c r="C139" s="1" t="s">
-        <v>15</v>
+        <v>38</v>
       </c>
       <c r="D139" s="1" t="s">
-        <v>522</v>
+        <v>535</v>
       </c>
       <c r="E139" s="1" t="s">
-        <v>57</v>
+        <v>62</v>
       </c>
       <c r="F139" s="1" t="s">
-        <v>58</v>
+        <v>63</v>
       </c>
       <c r="G139" s="1" t="s">
-        <v>523</v>
+        <v>536</v>
       </c>
       <c r="H139" s="1" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
     </row>
     <row r="140" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A140" s="1" t="s">
-        <v>524</v>
+        <v>539</v>
       </c>
       <c r="C140" s="1" t="s">
-        <v>24</v>
+        <v>199</v>
       </c>
       <c r="D140" s="1" t="s">
-        <v>525</v>
+        <v>540</v>
       </c>
       <c r="E140" s="1" t="s">
-        <v>526</v>
+        <v>541</v>
       </c>
       <c r="F140" s="1" t="s">
-        <v>527</v>
+        <v>7</v>
       </c>
       <c r="G140" s="1" t="s">
-        <v>528</v>
+        <v>542</v>
       </c>
       <c r="H140" s="1" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
     </row>
     <row r="141" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A141" s="1" t="s">
-        <v>529</v>
+        <v>543</v>
       </c>
       <c r="C141" s="1" t="s">
-        <v>24</v>
+        <v>46</v>
       </c>
       <c r="D141" s="1" t="s">
-        <v>530</v>
+        <v>544</v>
       </c>
       <c r="E141" s="1" t="s">
-        <v>531</v>
+        <v>101</v>
       </c>
       <c r="F141" s="1" t="s">
-        <v>532</v>
+        <v>7</v>
       </c>
       <c r="G141" s="1" t="s">
-        <v>84</v>
+        <v>545</v>
       </c>
       <c r="H141" s="1" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
     </row>
     <row r="142" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A142" s="1" t="s">
-        <v>533</v>
+        <v>546</v>
       </c>
       <c r="C142" s="1" t="s">
-        <v>44</v>
+        <v>23</v>
       </c>
       <c r="D142" s="1" t="s">
-        <v>534</v>
+        <v>547</v>
       </c>
       <c r="E142" s="1" t="s">
-        <v>535</v>
+        <v>548</v>
       </c>
       <c r="F142" s="1" t="s">
-        <v>536</v>
+        <v>7</v>
       </c>
       <c r="G142" s="1" t="s">
-        <v>537</v>
+        <v>549</v>
       </c>
       <c r="H142" s="1" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
     </row>
     <row r="143" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A143" s="1" t="s">
-        <v>538</v>
+        <v>550</v>
       </c>
       <c r="C143" s="1" t="s">
-        <v>50</v>
+        <v>23</v>
       </c>
       <c r="D143" s="1" t="s">
-        <v>539</v>
+        <v>547</v>
       </c>
       <c r="E143" s="1" t="s">
-        <v>26</v>
+        <v>548</v>
       </c>
       <c r="F143" s="1" t="s">
         <v>7</v>
       </c>
       <c r="G143" s="1" t="s">
-        <v>540</v>
+        <v>549</v>
       </c>
       <c r="H143" s="1" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
     </row>
     <row r="144" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A144" s="1" t="s">
-        <v>541</v>
+        <v>551</v>
       </c>
       <c r="C144" s="1" t="s">
-        <v>10</v>
+        <v>69</v>
       </c>
       <c r="D144" s="1" t="s">
-        <v>542</v>
+        <v>552</v>
       </c>
       <c r="E144" s="1" t="s">
-        <v>543</v>
+        <v>498</v>
       </c>
       <c r="F144" s="1" t="s">
-        <v>7</v>
+        <v>553</v>
       </c>
       <c r="G144" s="1" t="s">
-        <v>544</v>
+        <v>554</v>
       </c>
       <c r="H144" s="1" t="s">
-        <v>13</v>
+        <v>8</v>
       </c>
     </row>
     <row r="145" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A145" s="1" t="s">
-        <v>545</v>
+        <v>555</v>
       </c>
       <c r="C145" s="1" t="s">
         <v>46</v>
       </c>
       <c r="D145" s="1" t="s">
-        <v>546</v>
+        <v>556</v>
       </c>
       <c r="E145" s="1" t="s">
-        <v>547</v>
+        <v>557</v>
       </c>
       <c r="F145" s="1" t="s">
-        <v>7</v>
+        <v>558</v>
       </c>
       <c r="G145" s="1" t="s">
-        <v>548</v>
+        <v>559</v>
       </c>
       <c r="H145" s="1" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
     </row>
     <row r="146" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A146" s="1" t="s">
-        <v>549</v>
+        <v>560</v>
       </c>
       <c r="C146" s="1" t="s">
-        <v>46</v>
+        <v>25</v>
       </c>
       <c r="D146" s="1" t="s">
-        <v>550</v>
+        <v>561</v>
       </c>
       <c r="E146" s="1" t="s">
-        <v>40</v>
+        <v>17</v>
       </c>
       <c r="F146" s="1" t="s">
-        <v>7</v>
+        <v>18</v>
       </c>
       <c r="G146" s="1" t="s">
-        <v>551</v>
+        <v>562</v>
       </c>
       <c r="H146" s="1" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
     </row>
     <row r="147" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A147" s="1" t="s">
-        <v>552</v>
+        <v>563</v>
       </c>
       <c r="C147" s="1" t="s">
-        <v>22</v>
+        <v>9</v>
       </c>
       <c r="D147" s="1" t="s">
-        <v>553</v>
+        <v>564</v>
       </c>
       <c r="E147" s="1" t="s">
-        <v>554</v>
+        <v>565</v>
       </c>
       <c r="F147" s="1" t="s">
-        <v>7</v>
+        <v>566</v>
       </c>
       <c r="G147" s="1" t="s">
-        <v>555</v>
+        <v>567</v>
       </c>
       <c r="H147" s="1" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
     </row>
     <row r="148" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A148" s="1" t="s">
-        <v>556</v>
+        <v>568</v>
       </c>
       <c r="C148" s="1" t="s">
-        <v>45</v>
+        <v>14</v>
       </c>
       <c r="D148" s="1" t="s">
-        <v>557</v>
+        <v>569</v>
       </c>
       <c r="E148" s="1" t="s">
-        <v>558</v>
+        <v>60</v>
       </c>
       <c r="F148" s="1" t="s">
-        <v>7</v>
+        <v>61</v>
       </c>
       <c r="G148" s="1" t="s">
-        <v>559</v>
+        <v>570</v>
       </c>
       <c r="H148" s="1" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
     </row>
     <row r="149" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A149" s="1" t="s">
-        <v>560</v>
+        <v>571</v>
       </c>
       <c r="C149" s="1" t="s">
-        <v>46</v>
+        <v>25</v>
       </c>
       <c r="D149" s="1" t="s">
-        <v>561</v>
+        <v>572</v>
       </c>
       <c r="E149" s="1" t="s">
-        <v>562</v>
+        <v>17</v>
       </c>
       <c r="F149" s="1" t="s">
-        <v>7</v>
+        <v>18</v>
       </c>
       <c r="G149" s="1" t="s">
-        <v>563</v>
+        <v>573</v>
       </c>
       <c r="H149" s="1" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
     </row>
     <row r="150" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A150" s="1" t="s">
-        <v>564</v>
+        <v>574</v>
       </c>
       <c r="C150" s="1" t="s">
-        <v>46</v>
+        <v>25</v>
       </c>
       <c r="D150" s="1" t="s">
-        <v>561</v>
+        <v>575</v>
       </c>
       <c r="E150" s="1" t="s">
-        <v>562</v>
+        <v>576</v>
       </c>
       <c r="F150" s="1" t="s">
-        <v>7</v>
+        <v>577</v>
       </c>
       <c r="G150" s="1" t="s">
-        <v>563</v>
+        <v>85</v>
       </c>
       <c r="H150" s="1" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
     </row>
     <row r="151" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A151" s="1" t="s">
-        <v>565</v>
+        <v>578</v>
       </c>
       <c r="C151" s="1" t="s">
-        <v>46</v>
+        <v>20</v>
       </c>
       <c r="D151" s="1" t="s">
-        <v>561</v>
+        <v>579</v>
       </c>
       <c r="E151" s="1" t="s">
-        <v>562</v>
+        <v>580</v>
       </c>
       <c r="F151" s="1" t="s">
         <v>7</v>
       </c>
       <c r="G151" s="1" t="s">
-        <v>563</v>
+        <v>581</v>
       </c>
       <c r="H151" s="1" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
     </row>
     <row r="152" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A152" s="1" t="s">
-        <v>566</v>
+        <v>582</v>
       </c>
       <c r="C152" s="1" t="s">
-        <v>27</v>
+        <v>33</v>
       </c>
       <c r="D152" s="1" t="s">
-        <v>567</v>
+        <v>583</v>
       </c>
       <c r="E152" s="1" t="s">
-        <v>568</v>
+        <v>584</v>
       </c>
       <c r="F152" s="1" t="s">
-        <v>569</v>
+        <v>7</v>
       </c>
       <c r="G152" s="1" t="s">
-        <v>33</v>
+        <v>585</v>
       </c>
       <c r="H152" s="1" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
     </row>
     <row r="153" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A153" s="1" t="s">
-        <v>570</v>
+        <v>586</v>
       </c>
       <c r="C153" s="1" t="s">
-        <v>27</v>
+        <v>461</v>
       </c>
       <c r="D153" s="1" t="s">
-        <v>571</v>
+        <v>587</v>
       </c>
       <c r="E153" s="1" t="s">
-        <v>572</v>
+        <v>89</v>
       </c>
       <c r="F153" s="1" t="s">
         <v>7</v>
       </c>
       <c r="G153" s="1" t="s">
-        <v>573</v>
+        <v>588</v>
       </c>
       <c r="H153" s="1" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
     </row>
     <row r="154" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A154" s="1" t="s">
-        <v>574</v>
+        <v>589</v>
       </c>
       <c r="C154" s="1" t="s">
-        <v>46</v>
+        <v>461</v>
       </c>
       <c r="D154" s="1" t="s">
-        <v>575</v>
+        <v>587</v>
       </c>
       <c r="E154" s="1" t="s">
-        <v>112</v>
+        <v>89</v>
       </c>
       <c r="F154" s="1" t="s">
         <v>7</v>
       </c>
       <c r="G154" s="1" t="s">
-        <v>576</v>
+        <v>588</v>
       </c>
       <c r="H154" s="1" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
     </row>
     <row r="155" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A155" s="1" t="s">
-        <v>577</v>
+        <v>590</v>
       </c>
       <c r="C155" s="1" t="s">
-        <v>29</v>
+        <v>461</v>
       </c>
       <c r="D155" s="1" t="s">
-        <v>578</v>
+        <v>587</v>
       </c>
       <c r="E155" s="1" t="s">
-        <v>41</v>
+        <v>89</v>
       </c>
       <c r="F155" s="1" t="s">
-        <v>42</v>
+        <v>7</v>
       </c>
       <c r="G155" s="1" t="s">
-        <v>579</v>
+        <v>588</v>
       </c>
       <c r="H155" s="1" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
     </row>
     <row r="156" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A156" s="1" t="s">
-        <v>580</v>
+        <v>591</v>
       </c>
       <c r="C156" s="1" t="s">
-        <v>45</v>
+        <v>33</v>
       </c>
       <c r="D156" s="1" t="s">
-        <v>581</v>
+        <v>592</v>
       </c>
       <c r="E156" s="1" t="s">
-        <v>582</v>
+        <v>43</v>
       </c>
       <c r="F156" s="1" t="s">
         <v>7</v>
       </c>
       <c r="G156" s="1" t="s">
-        <v>583</v>
+        <v>593</v>
       </c>
       <c r="H156" s="1" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
     </row>
     <row r="157" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A157" s="1" t="s">
-        <v>584</v>
+        <v>594</v>
       </c>
       <c r="C157" s="1" t="s">
+        <v>270</v>
+      </c>
+      <c r="D157" s="1" t="s">
+        <v>595</v>
+      </c>
+      <c r="E157" s="1" t="s">
+        <v>100</v>
+      </c>
+      <c r="F157" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="G157" s="1" t="s">
+        <v>596</v>
+      </c>
+      <c r="H157" s="1" t="s">
         <v>12</v>
-      </c>
-      <c r="D157" s="1" t="s">
-        <v>585</v>
-      </c>
-      <c r="E157" s="1" t="s">
-        <v>92</v>
-      </c>
-      <c r="F157" s="1" t="s">
-        <v>93</v>
-      </c>
-      <c r="G157" s="1" t="s">
-        <v>273</v>
-      </c>
-      <c r="H157" s="1" t="s">
-        <v>13</v>
       </c>
     </row>
     <row r="158" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A158" s="1" t="s">
-        <v>586</v>
+        <v>597</v>
       </c>
       <c r="C158" s="1" t="s">
-        <v>39</v>
+        <v>270</v>
       </c>
       <c r="D158" s="1" t="s">
-        <v>587</v>
+        <v>595</v>
       </c>
       <c r="E158" s="1" t="s">
-        <v>32</v>
+        <v>100</v>
       </c>
       <c r="F158" s="1" t="s">
         <v>7</v>
       </c>
       <c r="G158" s="1" t="s">
-        <v>96</v>
+        <v>596</v>
       </c>
       <c r="H158" s="1" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
     </row>
     <row r="159" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A159" s="1" t="s">
-        <v>588</v>
+        <v>598</v>
       </c>
       <c r="C159" s="1" t="s">
-        <v>27</v>
+        <v>20</v>
       </c>
       <c r="D159" s="1" t="s">
-        <v>589</v>
+        <v>599</v>
       </c>
       <c r="E159" s="1" t="s">
-        <v>99</v>
+        <v>41</v>
       </c>
       <c r="F159" s="1" t="s">
         <v>7</v>
       </c>
       <c r="G159" s="1" t="s">
-        <v>590</v>
+        <v>600</v>
       </c>
       <c r="H159" s="1" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
     </row>
     <row r="160" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A160" s="1" t="s">
-        <v>591</v>
+        <v>601</v>
       </c>
       <c r="C160" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="D160" s="1" t="s">
+        <v>602</v>
+      </c>
+      <c r="E160" s="1" t="s">
+        <v>159</v>
+      </c>
+      <c r="F160" s="1" t="s">
+        <v>160</v>
+      </c>
+      <c r="G160" s="1" t="s">
+        <v>603</v>
+      </c>
+      <c r="H160" s="1" t="s">
         <v>12</v>
-      </c>
-      <c r="D160" s="1" t="s">
-        <v>592</v>
-      </c>
-      <c r="E160" s="1" t="s">
-        <v>80</v>
-      </c>
-      <c r="F160" s="1" t="s">
-        <v>81</v>
-      </c>
-      <c r="G160" s="1" t="s">
-        <v>119</v>
-      </c>
-      <c r="H160" s="1" t="s">
-        <v>13</v>
       </c>
     </row>
     <row r="161" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A161" s="1" t="s">
-        <v>593</v>
+        <v>604</v>
       </c>
       <c r="C161" s="1" t="s">
-        <v>45</v>
+        <v>37</v>
       </c>
       <c r="D161" s="1" t="s">
-        <v>594</v>
+        <v>605</v>
       </c>
       <c r="E161" s="1" t="s">
-        <v>53</v>
+        <v>97</v>
       </c>
       <c r="F161" s="1" t="s">
         <v>7</v>
       </c>
       <c r="G161" s="1" t="s">
-        <v>595</v>
+        <v>606</v>
       </c>
       <c r="H161" s="1" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
     </row>
     <row r="162" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A162" s="1" t="s">
-        <v>596</v>
+        <v>607</v>
       </c>
       <c r="C162" s="1" t="s">
-        <v>9</v>
+        <v>21</v>
       </c>
       <c r="D162" s="1" t="s">
-        <v>597</v>
+        <v>608</v>
       </c>
       <c r="E162" s="1" t="s">
-        <v>120</v>
+        <v>159</v>
       </c>
       <c r="F162" s="1" t="s">
-        <v>121</v>
+        <v>160</v>
       </c>
       <c r="G162" s="1" t="s">
-        <v>91</v>
+        <v>506</v>
       </c>
       <c r="H162" s="1" t="s">
-        <v>63</v>
+        <v>12</v>
       </c>
     </row>
     <row r="163" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A163" s="1" t="s">
-        <v>598</v>
+        <v>609</v>
       </c>
       <c r="C163" s="1" t="s">
-        <v>9</v>
+        <v>270</v>
       </c>
       <c r="D163" s="1" t="s">
-        <v>597</v>
+        <v>610</v>
       </c>
       <c r="E163" s="1" t="s">
-        <v>120</v>
+        <v>611</v>
       </c>
       <c r="F163" s="1" t="s">
-        <v>121</v>
+        <v>7</v>
       </c>
       <c r="G163" s="1" t="s">
-        <v>91</v>
+        <v>88</v>
       </c>
       <c r="H163" s="1" t="s">
-        <v>63</v>
+        <v>12</v>
       </c>
     </row>
     <row r="164" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A164" s="1" t="s">
-        <v>599</v>
+        <v>612</v>
       </c>
       <c r="C164" s="1" t="s">
-        <v>22</v>
+        <v>36</v>
       </c>
       <c r="D164" s="1" t="s">
-        <v>599</v>
+        <v>613</v>
+      </c>
+      <c r="E164" s="1" t="s">
+        <v>614</v>
+      </c>
+      <c r="F164" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="G164" s="1" t="s">
+        <v>129</v>
       </c>
       <c r="H164" s="1" t="s">
-        <v>129</v>
+        <v>12</v>
       </c>
     </row>
     <row r="165" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A165" s="1" t="s">
-        <v>600</v>
+        <v>615</v>
       </c>
       <c r="C165" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="D165" s="1" t="s">
+        <v>613</v>
+      </c>
+      <c r="E165" s="1" t="s">
+        <v>614</v>
+      </c>
+      <c r="F165" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="G165" s="1" t="s">
+        <v>129</v>
+      </c>
+      <c r="H165" s="1" t="s">
         <v>12</v>
-      </c>
-      <c r="D165" s="1" t="s">
-        <v>600</v>
-      </c>
-      <c r="H165" s="1" t="s">
-        <v>129</v>
       </c>
     </row>
     <row r="166" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A166" s="1" t="s">
-        <v>601</v>
+        <v>616</v>
       </c>
       <c r="C166" s="1" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="D166" s="1" t="s">
-        <v>601</v>
+        <v>617</v>
+      </c>
+      <c r="E166" s="1" t="s">
+        <v>618</v>
+      </c>
+      <c r="F166" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="G166" s="1" t="s">
+        <v>619</v>
       </c>
       <c r="H166" s="1" t="s">
-        <v>129</v>
+        <v>12</v>
       </c>
     </row>
     <row r="167" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A167" s="1" t="s">
-        <v>602</v>
+        <v>620</v>
       </c>
       <c r="C167" s="1" t="s">
-        <v>29</v>
+        <v>14</v>
       </c>
       <c r="D167" s="1" t="s">
-        <v>602</v>
+        <v>621</v>
+      </c>
+      <c r="E167" s="1" t="s">
+        <v>109</v>
+      </c>
+      <c r="F167" s="1" t="s">
+        <v>110</v>
+      </c>
+      <c r="G167" s="1" t="s">
+        <v>439</v>
       </c>
       <c r="H167" s="1" t="s">
-        <v>129</v>
+        <v>12</v>
       </c>
     </row>
     <row r="168" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A168" s="1" t="s">
-        <v>603</v>
+        <v>622</v>
       </c>
       <c r="C168" s="1" t="s">
-        <v>44</v>
+        <v>26</v>
       </c>
       <c r="D168" s="1" t="s">
-        <v>603</v>
+        <v>623</v>
+      </c>
+      <c r="E168" s="1" t="s">
+        <v>369</v>
+      </c>
+      <c r="F168" s="1" t="s">
+        <v>370</v>
+      </c>
+      <c r="G168" s="1" t="s">
+        <v>624</v>
       </c>
       <c r="H168" s="1" t="s">
-        <v>129</v>
-      </c>
-    </row>
-    <row r="169" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A169" s="1" t="s">
-        <v>604</v>
-      </c>
-      <c r="C169" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="D169" s="1" t="s">
-        <v>604</v>
-      </c>
-      <c r="H169" s="1" t="s">
-        <v>129</v>
+        <v>12</v>
       </c>
     </row>
   </sheetData>

--- a/1.xlsx
+++ b/1.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="\\wh.local\fs\UserProfile_TSSWH19\_TSSWH19_redirected_folders\HunyaCs1\Desktop\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D2316BF2-B66C-48EB-9EF7-DB63125B4249}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D401A223-DB93-44AF-B52E-5E388003B0A6}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="0" windowWidth="22260" windowHeight="12648" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1175" uniqueCount="625">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1187" uniqueCount="629">
   <si>
     <t>IRSZ</t>
   </si>
@@ -1903,6 +1903,18 @@
   </si>
   <si>
     <t>Bazsarózsa utca</t>
+  </si>
+  <si>
+    <t>NFD6-03-07-KVGL</t>
+  </si>
+  <si>
+    <t>AUCHAN_ÁRUHÁZI</t>
+  </si>
+  <si>
+    <t>267004104</t>
+  </si>
+  <si>
+    <t>267003977</t>
   </si>
 </sst>
 </file>
@@ -2222,7 +2234,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <sheetPr codeName="Munka1"/>
-  <dimension ref="A1:H168"/>
+  <dimension ref="A1:H171"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="25.44140625" style="1" bestFit="1" customWidth="1"/>
@@ -6096,6 +6108,48 @@
         <v>12</v>
       </c>
     </row>
+    <row r="169" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A169" s="1" t="s">
+        <v>625</v>
+      </c>
+      <c r="C169" s="1" t="s">
+        <v>69</v>
+      </c>
+      <c r="D169" s="1" t="s">
+        <v>625</v>
+      </c>
+      <c r="H169" s="1" t="s">
+        <v>626</v>
+      </c>
+    </row>
+    <row r="170" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A170" s="1" t="s">
+        <v>627</v>
+      </c>
+      <c r="C170" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="D170" s="1" t="s">
+        <v>627</v>
+      </c>
+      <c r="H170" s="1" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="171" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A171" s="1" t="s">
+        <v>628</v>
+      </c>
+      <c r="C171" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="D171" s="1" t="s">
+        <v>628</v>
+      </c>
+      <c r="H171" s="1" t="s">
+        <v>67</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>

--- a/1.xlsx
+++ b/1.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="\\wh.local\fs\UserProfile_TSSWH19\_TSSWH19_redirected_folders\HunyaCs1\Desktop\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B266EB29-2E90-4BFF-B47D-06B3A5EFB29B}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A183398F-D8F4-443E-9B5F-B1CF2181C535}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="0" windowWidth="22260" windowHeight="12648" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="945" uniqueCount="515">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="933" uniqueCount="508">
   <si>
     <t>IRSZ</t>
   </si>
@@ -1432,27 +1432,6 @@
   </si>
   <si>
     <t>Hatvany Lajos utca</t>
-  </si>
-  <si>
-    <t>NFD6-03-19-BH7S-1</t>
-  </si>
-  <si>
-    <t>NFD6-03-19-BH7S</t>
-  </si>
-  <si>
-    <t>Rét utca</t>
-  </si>
-  <si>
-    <t>NFD6-03-19-YBYG-1</t>
-  </si>
-  <si>
-    <t>NFD6-03-19-YBYG</t>
-  </si>
-  <si>
-    <t>1114</t>
-  </si>
-  <si>
-    <t>Szabolcska Mihály utca</t>
   </si>
   <si>
     <t>202603182600645001</t>
@@ -1608,8 +1587,9 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normál" xfId="0" builtinId="0"/>
@@ -1891,3122 +1871,3090 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <sheetPr codeName="Munka1"/>
-  <dimension ref="A1:H135"/>
+  <dimension ref="A1:H134"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="25.44140625" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="9.109375"/>
-    <col min="3" max="3" width="6.88671875" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="20.109375" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="5" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="20.21875" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="32.6640625" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="19.88671875" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="25.44140625" style="1" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="9.109375" style="1"/>
+    <col min="3" max="3" width="6.88671875" style="1" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="20.109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="5" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="20.21875" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="32.6640625" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="19.88671875" style="1" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A1" t="s">
+      <c r="A1" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="C1" t="s">
+      <c r="C1" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="D1" t="s">
+      <c r="D1" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="E1" t="s">
+      <c r="E1" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="F1" t="s">
+      <c r="F1" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="G1" t="s">
+      <c r="G1" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="H1" t="s">
+      <c r="H1" s="1" t="s">
         <v>3</v>
       </c>
     </row>
     <row r="2" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A2" t="s">
+      <c r="A2" s="1" t="s">
         <v>105</v>
       </c>
-      <c r="C2" t="s">
+      <c r="C2" s="1" t="s">
         <v>23</v>
       </c>
-      <c r="D2" t="s">
+      <c r="D2" s="1" t="s">
         <v>106</v>
       </c>
-      <c r="E2" t="s">
+      <c r="E2" s="1" t="s">
         <v>47</v>
       </c>
-      <c r="F2" t="s">
+      <c r="F2" s="1" t="s">
         <v>48</v>
       </c>
-      <c r="G2" t="s">
+      <c r="G2" s="1" t="s">
         <v>107</v>
       </c>
-      <c r="H2" t="s">
+      <c r="H2" s="1" t="s">
         <v>11</v>
       </c>
     </row>
     <row r="3" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A3" t="s">
+      <c r="A3" s="1" t="s">
         <v>108</v>
       </c>
-      <c r="C3" t="s">
+      <c r="C3" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="D3" t="s">
+      <c r="D3" s="1" t="s">
         <v>109</v>
       </c>
-      <c r="E3" t="s">
+      <c r="E3" s="1" t="s">
         <v>110</v>
       </c>
-      <c r="F3" t="s">
-        <v>7</v>
-      </c>
-      <c r="G3" t="s">
+      <c r="F3" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="G3" s="1" t="s">
         <v>111</v>
       </c>
-      <c r="H3" t="s">
+      <c r="H3" s="1" t="s">
         <v>11</v>
       </c>
     </row>
     <row r="4" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A4" t="s">
+      <c r="A4" s="1" t="s">
         <v>112</v>
       </c>
-      <c r="C4" t="s">
+      <c r="C4" s="1" t="s">
         <v>28</v>
       </c>
-      <c r="D4" t="s">
+      <c r="D4" s="1" t="s">
         <v>113</v>
       </c>
-      <c r="E4" t="s">
+      <c r="E4" s="1" t="s">
         <v>114</v>
       </c>
-      <c r="F4" t="s">
-        <v>7</v>
-      </c>
-      <c r="G4" t="s">
+      <c r="F4" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="G4" s="1" t="s">
         <v>115</v>
       </c>
-      <c r="H4" t="s">
+      <c r="H4" s="1" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="5" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A5" t="s">
+      <c r="A5" s="1" t="s">
         <v>116</v>
       </c>
-      <c r="C5" t="s">
+      <c r="C5" s="1" t="s">
         <v>38</v>
       </c>
-      <c r="D5" t="s">
+      <c r="D5" s="1" t="s">
         <v>117</v>
       </c>
-      <c r="E5" t="s">
+      <c r="E5" s="1" t="s">
         <v>118</v>
       </c>
-      <c r="F5" t="s">
+      <c r="F5" s="1" t="s">
         <v>119</v>
       </c>
-      <c r="G5" t="s">
+      <c r="G5" s="1" t="s">
         <v>120</v>
       </c>
-      <c r="H5" t="s">
+      <c r="H5" s="1" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="6" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A6" t="s">
+      <c r="A6" s="1" t="s">
         <v>66</v>
       </c>
-      <c r="C6" t="s">
+      <c r="C6" s="1" t="s">
         <v>38</v>
       </c>
-      <c r="D6" t="s">
+      <c r="D6" s="1" t="s">
         <v>67</v>
       </c>
-      <c r="E6" t="s">
+      <c r="E6" s="1" t="s">
         <v>68</v>
       </c>
-      <c r="F6" t="s">
+      <c r="F6" s="1" t="s">
         <v>69</v>
       </c>
-      <c r="G6" t="s">
+      <c r="G6" s="1" t="s">
         <v>70</v>
       </c>
-      <c r="H6" t="s">
+      <c r="H6" s="1" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="7" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A7" t="s">
+      <c r="A7" s="1" t="s">
         <v>71</v>
       </c>
-      <c r="C7" t="s">
+      <c r="C7" s="1" t="s">
         <v>38</v>
       </c>
-      <c r="D7" t="s">
+      <c r="D7" s="1" t="s">
         <v>67</v>
       </c>
-      <c r="E7" t="s">
+      <c r="E7" s="1" t="s">
         <v>68</v>
       </c>
-      <c r="F7" t="s">
+      <c r="F7" s="1" t="s">
         <v>69</v>
       </c>
-      <c r="G7" t="s">
+      <c r="G7" s="1" t="s">
         <v>70</v>
       </c>
-      <c r="H7" t="s">
+      <c r="H7" s="1" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="8" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A8" t="s">
+      <c r="A8" s="1" t="s">
         <v>121</v>
       </c>
-      <c r="C8" t="s">
+      <c r="C8" s="1" t="s">
         <v>28</v>
       </c>
-      <c r="D8" t="s">
+      <c r="D8" s="1" t="s">
         <v>122</v>
       </c>
-      <c r="E8" t="s">
+      <c r="E8" s="1" t="s">
         <v>123</v>
       </c>
-      <c r="F8" t="s">
-        <v>7</v>
-      </c>
-      <c r="G8" t="s">
+      <c r="F8" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="G8" s="1" t="s">
         <v>124</v>
       </c>
-      <c r="H8" t="s">
+      <c r="H8" s="1" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="9" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A9" t="s">
+      <c r="A9" s="1" t="s">
         <v>125</v>
       </c>
-      <c r="C9" t="s">
+      <c r="C9" s="1" t="s">
         <v>76</v>
       </c>
-      <c r="D9" t="s">
+      <c r="D9" s="1" t="s">
         <v>126</v>
       </c>
-      <c r="E9" t="s">
+      <c r="E9" s="1" t="s">
         <v>127</v>
       </c>
-      <c r="F9" t="s">
+      <c r="F9" s="1" t="s">
         <v>128</v>
       </c>
-      <c r="G9" t="s">
+      <c r="G9" s="1" t="s">
         <v>129</v>
       </c>
-      <c r="H9" t="s">
+      <c r="H9" s="1" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="10" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A10" t="s">
+      <c r="A10" s="1" t="s">
         <v>130</v>
       </c>
-      <c r="C10" t="s">
+      <c r="C10" s="1" t="s">
         <v>131</v>
       </c>
-      <c r="D10" t="s">
+      <c r="D10" s="1" t="s">
         <v>132</v>
       </c>
-      <c r="E10" t="s">
+      <c r="E10" s="1" t="s">
         <v>133</v>
       </c>
-      <c r="F10" t="s">
+      <c r="F10" s="1" t="s">
         <v>134</v>
       </c>
-      <c r="G10" t="s">
+      <c r="G10" s="1" t="s">
         <v>92</v>
       </c>
-      <c r="H10" t="s">
+      <c r="H10" s="1" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="11" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A11" t="s">
+      <c r="A11" s="1" t="s">
         <v>135</v>
       </c>
-      <c r="C11" t="s">
+      <c r="C11" s="1" t="s">
         <v>76</v>
       </c>
-      <c r="D11" t="s">
+      <c r="D11" s="1" t="s">
         <v>136</v>
       </c>
-      <c r="E11" t="s">
+      <c r="E11" s="1" t="s">
         <v>103</v>
       </c>
-      <c r="F11" t="s">
-        <v>7</v>
-      </c>
-      <c r="G11" t="s">
+      <c r="F11" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="G11" s="1" t="s">
         <v>137</v>
       </c>
-      <c r="H11" t="s">
+      <c r="H11" s="1" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="12" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A12" t="s">
+      <c r="A12" s="1" t="s">
         <v>138</v>
       </c>
-      <c r="C12" t="s">
+      <c r="C12" s="1" t="s">
         <v>29</v>
       </c>
-      <c r="D12" t="s">
+      <c r="D12" s="1" t="s">
         <v>139</v>
       </c>
-      <c r="E12" t="s">
+      <c r="E12" s="1" t="s">
         <v>140</v>
       </c>
-      <c r="F12" t="s">
+      <c r="F12" s="1" t="s">
         <v>141</v>
       </c>
-      <c r="G12" t="s">
+      <c r="G12" s="1" t="s">
         <v>142</v>
       </c>
-      <c r="H12" t="s">
+      <c r="H12" s="1" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="13" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A13" t="s">
+      <c r="A13" s="1" t="s">
         <v>143</v>
       </c>
-      <c r="C13" t="s">
+      <c r="C13" s="1" t="s">
         <v>23</v>
       </c>
-      <c r="D13" t="s">
+      <c r="D13" s="1" t="s">
         <v>144</v>
       </c>
-      <c r="E13" t="s">
+      <c r="E13" s="1" t="s">
         <v>145</v>
       </c>
-      <c r="F13" t="s">
+      <c r="F13" s="1" t="s">
         <v>146</v>
       </c>
-      <c r="G13" t="s">
+      <c r="G13" s="1" t="s">
         <v>147</v>
       </c>
-      <c r="H13" t="s">
+      <c r="H13" s="1" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="14" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A14" t="s">
+      <c r="A14" s="1" t="s">
         <v>148</v>
       </c>
-      <c r="C14" t="s">
+      <c r="C14" s="1" t="s">
         <v>23</v>
       </c>
-      <c r="D14" t="s">
+      <c r="D14" s="1" t="s">
         <v>144</v>
       </c>
-      <c r="E14" t="s">
+      <c r="E14" s="1" t="s">
         <v>145</v>
       </c>
-      <c r="F14" t="s">
+      <c r="F14" s="1" t="s">
         <v>146</v>
       </c>
-      <c r="G14" t="s">
+      <c r="G14" s="1" t="s">
         <v>147</v>
       </c>
-      <c r="H14" t="s">
+      <c r="H14" s="1" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="15" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A15" t="s">
+      <c r="A15" s="1" t="s">
         <v>149</v>
       </c>
-      <c r="C15" t="s">
+      <c r="C15" s="1" t="s">
         <v>50</v>
       </c>
-      <c r="D15" t="s">
+      <c r="D15" s="1" t="s">
         <v>150</v>
       </c>
-      <c r="E15" t="s">
+      <c r="E15" s="1" t="s">
         <v>74</v>
       </c>
-      <c r="F15" t="s">
+      <c r="F15" s="1" t="s">
         <v>75</v>
       </c>
-      <c r="G15" t="s">
+      <c r="G15" s="1" t="s">
         <v>151</v>
       </c>
-      <c r="H15" t="s">
+      <c r="H15" s="1" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="16" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A16" t="s">
+      <c r="A16" s="1" t="s">
         <v>152</v>
       </c>
-      <c r="C16" t="s">
+      <c r="C16" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="D16" t="s">
+      <c r="D16" s="1" t="s">
         <v>153</v>
       </c>
-      <c r="E16" t="s">
+      <c r="E16" s="1" t="s">
         <v>86</v>
       </c>
-      <c r="F16" t="s">
+      <c r="F16" s="1" t="s">
         <v>87</v>
       </c>
-      <c r="G16" t="s">
+      <c r="G16" s="1" t="s">
         <v>154</v>
       </c>
-      <c r="H16" t="s">
+      <c r="H16" s="1" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="17" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A17" t="s">
+      <c r="A17" s="1" t="s">
         <v>155</v>
       </c>
-      <c r="C17" t="s">
+      <c r="C17" s="1" t="s">
         <v>29</v>
       </c>
-      <c r="D17" t="s">
+      <c r="D17" s="1" t="s">
         <v>156</v>
       </c>
-      <c r="E17" t="s">
+      <c r="E17" s="1" t="s">
         <v>157</v>
       </c>
-      <c r="F17" t="s">
+      <c r="F17" s="1" t="s">
         <v>158</v>
       </c>
-      <c r="G17" t="s">
+      <c r="G17" s="1" t="s">
         <v>95</v>
       </c>
-      <c r="H17" t="s">
+      <c r="H17" s="1" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="18" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A18" t="s">
+      <c r="A18" s="1" t="s">
         <v>159</v>
       </c>
-      <c r="C18" t="s">
+      <c r="C18" s="1" t="s">
         <v>50</v>
       </c>
-      <c r="D18" t="s">
+      <c r="D18" s="1" t="s">
         <v>160</v>
       </c>
-      <c r="E18" t="s">
+      <c r="E18" s="1" t="s">
         <v>161</v>
       </c>
-      <c r="F18" t="s">
+      <c r="F18" s="1" t="s">
         <v>162</v>
       </c>
-      <c r="G18" t="s">
+      <c r="G18" s="1" t="s">
         <v>163</v>
       </c>
-      <c r="H18" t="s">
+      <c r="H18" s="1" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="19" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A19" t="s">
+      <c r="A19" s="1" t="s">
         <v>164</v>
       </c>
-      <c r="C19" t="s">
+      <c r="C19" s="1" t="s">
         <v>165</v>
       </c>
-      <c r="D19" t="s">
+      <c r="D19" s="1" t="s">
         <v>166</v>
       </c>
-      <c r="E19" t="s">
+      <c r="E19" s="1" t="s">
         <v>167</v>
       </c>
-      <c r="F19" t="s">
-        <v>7</v>
-      </c>
-      <c r="G19" t="s">
+      <c r="F19" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="G19" s="1" t="s">
         <v>168</v>
       </c>
-      <c r="H19" t="s">
+      <c r="H19" s="1" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="20" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A20" t="s">
+      <c r="A20" s="1" t="s">
         <v>169</v>
       </c>
-      <c r="C20" t="s">
+      <c r="C20" s="1" t="s">
         <v>20</v>
       </c>
-      <c r="D20" t="s">
+      <c r="D20" s="1" t="s">
         <v>170</v>
       </c>
-      <c r="E20" t="s">
+      <c r="E20" s="1" t="s">
         <v>171</v>
       </c>
-      <c r="F20" t="s">
-        <v>7</v>
-      </c>
-      <c r="G20" t="s">
+      <c r="F20" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="G20" s="1" t="s">
         <v>172</v>
       </c>
-      <c r="H20" t="s">
+      <c r="H20" s="1" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="21" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A21" t="s">
+      <c r="A21" s="1" t="s">
         <v>173</v>
       </c>
-      <c r="C21" t="s">
+      <c r="C21" s="1" t="s">
         <v>38</v>
       </c>
-      <c r="D21" t="s">
+      <c r="D21" s="1" t="s">
         <v>174</v>
       </c>
-      <c r="E21" t="s">
+      <c r="E21" s="1" t="s">
         <v>45</v>
       </c>
-      <c r="F21" t="s">
+      <c r="F21" s="1" t="s">
         <v>46</v>
       </c>
-      <c r="G21" t="s">
+      <c r="G21" s="1" t="s">
         <v>175</v>
       </c>
-      <c r="H21" t="s">
+      <c r="H21" s="1" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="22" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A22" t="s">
+      <c r="A22" s="1" t="s">
         <v>176</v>
       </c>
-      <c r="C22" t="s">
+      <c r="C22" s="1" t="s">
         <v>38</v>
       </c>
-      <c r="D22" t="s">
+      <c r="D22" s="1" t="s">
         <v>177</v>
       </c>
-      <c r="E22" t="s">
+      <c r="E22" s="1" t="s">
         <v>45</v>
       </c>
-      <c r="F22" t="s">
+      <c r="F22" s="1" t="s">
         <v>46</v>
       </c>
-      <c r="G22" t="s">
+      <c r="G22" s="1" t="s">
         <v>25</v>
       </c>
-      <c r="H22" t="s">
+      <c r="H22" s="1" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="23" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A23" t="s">
+      <c r="A23" s="1" t="s">
         <v>178</v>
       </c>
-      <c r="C23" t="s">
+      <c r="C23" s="1" t="s">
         <v>38</v>
       </c>
-      <c r="D23" t="s">
+      <c r="D23" s="1" t="s">
         <v>179</v>
       </c>
-      <c r="E23" t="s">
+      <c r="E23" s="1" t="s">
         <v>83</v>
       </c>
-      <c r="F23" t="s">
+      <c r="F23" s="1" t="s">
         <v>84</v>
       </c>
-      <c r="G23" t="s">
+      <c r="G23" s="1" t="s">
         <v>88</v>
       </c>
-      <c r="H23" t="s">
+      <c r="H23" s="1" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="24" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A24" t="s">
+      <c r="A24" s="1" t="s">
         <v>180</v>
       </c>
-      <c r="C24" t="s">
+      <c r="C24" s="1" t="s">
         <v>21</v>
       </c>
-      <c r="D24" t="s">
+      <c r="D24" s="1" t="s">
         <v>181</v>
       </c>
-      <c r="E24" t="s">
+      <c r="E24" s="1" t="s">
         <v>182</v>
       </c>
-      <c r="F24" t="s">
+      <c r="F24" s="1" t="s">
         <v>183</v>
       </c>
-      <c r="G24" t="s">
+      <c r="G24" s="1" t="s">
         <v>52</v>
       </c>
-      <c r="H24" t="s">
+      <c r="H24" s="1" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="25" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A25" t="s">
+      <c r="A25" s="1" t="s">
         <v>184</v>
       </c>
-      <c r="C25" t="s">
+      <c r="C25" s="1" t="s">
         <v>50</v>
       </c>
-      <c r="D25" t="s">
+      <c r="D25" s="1" t="s">
         <v>185</v>
       </c>
-      <c r="E25" t="s">
+      <c r="E25" s="1" t="s">
         <v>74</v>
       </c>
-      <c r="F25" t="s">
+      <c r="F25" s="1" t="s">
         <v>75</v>
       </c>
-      <c r="G25" t="s">
+      <c r="G25" s="1" t="s">
         <v>186</v>
       </c>
-      <c r="H25" t="s">
+      <c r="H25" s="1" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="26" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A26" t="s">
+      <c r="A26" s="1" t="s">
         <v>187</v>
       </c>
-      <c r="C26" t="s">
+      <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
-      <c r="D26" t="s">
+      <c r="D26" s="1" t="s">
         <v>188</v>
       </c>
-      <c r="E26" t="s">
+      <c r="E26" s="1" t="s">
         <v>189</v>
       </c>
-      <c r="F26" t="s">
+      <c r="F26" s="1" t="s">
         <v>190</v>
       </c>
-      <c r="G26" t="s">
+      <c r="G26" s="1" t="s">
         <v>191</v>
       </c>
-      <c r="H26" t="s">
+      <c r="H26" s="1" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="27" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A27" t="s">
+      <c r="A27" s="1" t="s">
         <v>192</v>
       </c>
-      <c r="C27" t="s">
+      <c r="C27" s="1" t="s">
         <v>50</v>
       </c>
-      <c r="D27" t="s">
+      <c r="D27" s="1" t="s">
         <v>193</v>
       </c>
-      <c r="E27" t="s">
+      <c r="E27" s="1" t="s">
         <v>74</v>
       </c>
-      <c r="F27" t="s">
+      <c r="F27" s="1" t="s">
         <v>75</v>
       </c>
-      <c r="G27" t="s">
+      <c r="G27" s="1" t="s">
         <v>194</v>
       </c>
-      <c r="H27" t="s">
+      <c r="H27" s="1" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="28" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A28" t="s">
+      <c r="A28" s="1" t="s">
         <v>195</v>
       </c>
-      <c r="C28" t="s">
+      <c r="C28" s="1" t="s">
         <v>28</v>
       </c>
-      <c r="D28" t="s">
+      <c r="D28" s="1" t="s">
         <v>196</v>
       </c>
-      <c r="E28" t="s">
+      <c r="E28" s="1" t="s">
         <v>100</v>
       </c>
-      <c r="F28" t="s">
+      <c r="F28" s="1" t="s">
         <v>101</v>
       </c>
-      <c r="G28" t="s">
+      <c r="G28" s="1" t="s">
         <v>197</v>
       </c>
-      <c r="H28" t="s">
+      <c r="H28" s="1" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="29" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A29" t="s">
+      <c r="A29" s="1" t="s">
         <v>198</v>
       </c>
-      <c r="C29" t="s">
+      <c r="C29" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="D29" t="s">
+      <c r="D29" s="1" t="s">
         <v>199</v>
       </c>
-      <c r="E29" t="s">
+      <c r="E29" s="1" t="s">
         <v>86</v>
       </c>
-      <c r="F29" t="s">
+      <c r="F29" s="1" t="s">
         <v>87</v>
       </c>
-      <c r="G29" t="s">
+      <c r="G29" s="1" t="s">
         <v>200</v>
       </c>
-      <c r="H29" t="s">
+      <c r="H29" s="1" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="30" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A30" t="s">
+      <c r="A30" s="1" t="s">
         <v>201</v>
       </c>
-      <c r="C30" t="s">
+      <c r="C30" s="1" t="s">
         <v>21</v>
       </c>
-      <c r="D30" t="s">
+      <c r="D30" s="1" t="s">
         <v>202</v>
       </c>
-      <c r="E30" t="s">
+      <c r="E30" s="1" t="s">
         <v>203</v>
       </c>
-      <c r="F30" t="s">
+      <c r="F30" s="1" t="s">
         <v>204</v>
       </c>
-      <c r="G30" t="s">
+      <c r="G30" s="1" t="s">
         <v>85</v>
       </c>
-      <c r="H30" t="s">
+      <c r="H30" s="1" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="31" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A31" t="s">
+      <c r="A31" s="1" t="s">
         <v>205</v>
       </c>
-      <c r="C31" t="s">
+      <c r="C31" s="1" t="s">
         <v>22</v>
       </c>
-      <c r="D31" t="s">
+      <c r="D31" s="1" t="s">
         <v>206</v>
       </c>
-      <c r="E31" t="s">
+      <c r="E31" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="F31" t="s">
+      <c r="F31" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="G31" t="s">
+      <c r="G31" s="1" t="s">
         <v>207</v>
       </c>
-      <c r="H31" t="s">
+      <c r="H31" s="1" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="32" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A32" t="s">
+      <c r="A32" s="1" t="s">
         <v>208</v>
       </c>
-      <c r="C32" t="s">
+      <c r="C32" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="D32" t="s">
+      <c r="D32" s="1" t="s">
         <v>209</v>
       </c>
-      <c r="E32" t="s">
+      <c r="E32" s="1" t="s">
         <v>210</v>
       </c>
-      <c r="F32" t="s">
-        <v>7</v>
-      </c>
-      <c r="G32" t="s">
+      <c r="F32" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="G32" s="1" t="s">
         <v>211</v>
       </c>
-      <c r="H32" t="s">
+      <c r="H32" s="1" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="33" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A33" t="s">
+      <c r="A33" s="1" t="s">
         <v>212</v>
       </c>
-      <c r="C33" t="s">
+      <c r="C33" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="D33" t="s">
+      <c r="D33" s="1" t="s">
         <v>209</v>
       </c>
-      <c r="E33" t="s">
+      <c r="E33" s="1" t="s">
         <v>210</v>
       </c>
-      <c r="F33" t="s">
-        <v>7</v>
-      </c>
-      <c r="G33" t="s">
+      <c r="F33" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="G33" s="1" t="s">
         <v>211</v>
       </c>
-      <c r="H33" t="s">
+      <c r="H33" s="1" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="34" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A34" t="s">
+      <c r="A34" s="1" t="s">
         <v>80</v>
       </c>
-      <c r="C34" t="s">
+      <c r="C34" s="1" t="s">
         <v>28</v>
       </c>
-      <c r="D34" t="s">
+      <c r="D34" s="1" t="s">
         <v>81</v>
       </c>
-      <c r="E34" t="s">
+      <c r="E34" s="1" t="s">
         <v>58</v>
       </c>
-      <c r="F34" t="s">
-        <v>7</v>
-      </c>
-      <c r="G34" t="s">
+      <c r="F34" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="G34" s="1" t="s">
         <v>82</v>
       </c>
-      <c r="H34" t="s">
+      <c r="H34" s="1" t="s">
         <v>49</v>
       </c>
     </row>
     <row r="35" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A35" t="s">
+      <c r="A35" s="1" t="s">
         <v>213</v>
       </c>
-      <c r="C35" t="s">
+      <c r="C35" s="1" t="s">
         <v>31</v>
       </c>
-      <c r="D35" t="s">
+      <c r="D35" s="1" t="s">
         <v>214</v>
       </c>
-      <c r="E35" t="s">
+      <c r="E35" s="1" t="s">
         <v>77</v>
       </c>
-      <c r="F35" t="s">
-        <v>7</v>
-      </c>
-      <c r="G35" t="s">
+      <c r="F35" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="G35" s="1" t="s">
         <v>215</v>
       </c>
-      <c r="H35" t="s">
+      <c r="H35" s="1" t="s">
         <v>49</v>
       </c>
     </row>
     <row r="36" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A36" t="s">
+      <c r="A36" s="1" t="s">
         <v>216</v>
       </c>
-      <c r="C36" t="s">
+      <c r="C36" s="1" t="s">
         <v>76</v>
       </c>
-      <c r="D36" t="s">
+      <c r="D36" s="1" t="s">
         <v>217</v>
       </c>
-      <c r="E36" t="s">
+      <c r="E36" s="1" t="s">
         <v>34</v>
       </c>
-      <c r="F36" t="s">
-        <v>7</v>
-      </c>
-      <c r="G36" t="s">
+      <c r="F36" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="G36" s="1" t="s">
         <v>218</v>
       </c>
-      <c r="H36" t="s">
+      <c r="H36" s="1" t="s">
         <v>49</v>
       </c>
     </row>
     <row r="37" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A37" t="s">
+      <c r="A37" s="1" t="s">
         <v>219</v>
       </c>
-      <c r="C37" t="s">
+      <c r="C37" s="1" t="s">
         <v>29</v>
       </c>
-      <c r="D37" t="s">
+      <c r="D37" s="1" t="s">
         <v>220</v>
       </c>
-      <c r="E37" t="s">
+      <c r="E37" s="1" t="s">
         <v>140</v>
       </c>
-      <c r="F37" t="s">
+      <c r="F37" s="1" t="s">
         <v>141</v>
       </c>
-      <c r="G37" t="s">
+      <c r="G37" s="1" t="s">
         <v>120</v>
       </c>
-      <c r="H37" t="s">
+      <c r="H37" s="1" t="s">
         <v>56</v>
       </c>
     </row>
     <row r="38" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A38" t="s">
+      <c r="A38" s="1" t="s">
         <v>221</v>
       </c>
-      <c r="C38" t="s">
+      <c r="C38" s="1" t="s">
         <v>28</v>
       </c>
-      <c r="D38" t="s">
+      <c r="D38" s="1" t="s">
         <v>222</v>
       </c>
-      <c r="E38" t="s">
+      <c r="E38" s="1" t="s">
         <v>51</v>
       </c>
-      <c r="F38" t="s">
-        <v>7</v>
-      </c>
-      <c r="G38" t="s">
+      <c r="F38" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="G38" s="1" t="s">
         <v>223</v>
       </c>
-      <c r="H38" t="s">
+      <c r="H38" s="1" t="s">
         <v>56</v>
       </c>
     </row>
     <row r="39" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A39" t="s">
+      <c r="A39" s="1" t="s">
         <v>224</v>
       </c>
-      <c r="C39" t="s">
+      <c r="C39" s="1" t="s">
         <v>50</v>
       </c>
-      <c r="D39" t="s">
+      <c r="D39" s="1" t="s">
         <v>225</v>
       </c>
-      <c r="E39" t="s">
+      <c r="E39" s="1" t="s">
         <v>226</v>
       </c>
-      <c r="F39" t="s">
+      <c r="F39" s="1" t="s">
         <v>227</v>
       </c>
-      <c r="G39" t="s">
+      <c r="G39" s="1" t="s">
         <v>228</v>
       </c>
-      <c r="H39" t="s">
+      <c r="H39" s="1" t="s">
         <v>56</v>
       </c>
     </row>
     <row r="40" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A40" t="s">
+      <c r="A40" s="1" t="s">
         <v>229</v>
       </c>
-      <c r="C40" t="s">
+      <c r="C40" s="1" t="s">
         <v>29</v>
       </c>
-      <c r="D40" t="s">
+      <c r="D40" s="1" t="s">
         <v>230</v>
       </c>
-      <c r="E40" t="s">
+      <c r="E40" s="1" t="s">
         <v>78</v>
       </c>
-      <c r="F40" t="s">
+      <c r="F40" s="1" t="s">
         <v>79</v>
       </c>
-      <c r="G40" t="s">
+      <c r="G40" s="1" t="s">
         <v>63</v>
       </c>
-      <c r="H40" t="s">
+      <c r="H40" s="1" t="s">
         <v>56</v>
       </c>
     </row>
     <row r="41" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A41" t="s">
+      <c r="A41" s="1" t="s">
         <v>231</v>
       </c>
-      <c r="C41" t="s">
+      <c r="C41" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="D41" t="s">
+      <c r="D41" s="1" t="s">
         <v>232</v>
       </c>
-      <c r="E41" t="s">
+      <c r="E41" s="1" t="s">
         <v>99</v>
       </c>
-      <c r="F41" t="s">
-        <v>7</v>
-      </c>
-      <c r="G41" t="s">
+      <c r="F41" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="G41" s="1" t="s">
         <v>233</v>
       </c>
-      <c r="H41" t="s">
+      <c r="H41" s="1" t="s">
         <v>11</v>
       </c>
     </row>
     <row r="42" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A42" t="s">
+      <c r="A42" s="1" t="s">
         <v>234</v>
       </c>
-      <c r="C42" t="s">
+      <c r="C42" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="D42" t="s">
+      <c r="D42" s="1" t="s">
         <v>232</v>
       </c>
-      <c r="E42" t="s">
+      <c r="E42" s="1" t="s">
         <v>99</v>
       </c>
-      <c r="F42" t="s">
-        <v>7</v>
-      </c>
-      <c r="G42" t="s">
+      <c r="F42" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="G42" s="1" t="s">
         <v>233</v>
       </c>
-      <c r="H42" t="s">
+      <c r="H42" s="1" t="s">
         <v>11</v>
       </c>
     </row>
     <row r="43" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A43" t="s">
+      <c r="A43" s="1" t="s">
         <v>235</v>
       </c>
-      <c r="C43" t="s">
+      <c r="C43" s="1" t="s">
         <v>21</v>
       </c>
-      <c r="D43" t="s">
+      <c r="D43" s="1" t="s">
         <v>236</v>
       </c>
-      <c r="E43" t="s">
+      <c r="E43" s="1" t="s">
         <v>54</v>
       </c>
-      <c r="F43" t="s">
+      <c r="F43" s="1" t="s">
         <v>55</v>
       </c>
-      <c r="G43" t="s">
+      <c r="G43" s="1" t="s">
         <v>237</v>
       </c>
-      <c r="H43" t="s">
+      <c r="H43" s="1" t="s">
         <v>11</v>
       </c>
     </row>
     <row r="44" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A44" t="s">
+      <c r="A44" s="1" t="s">
         <v>238</v>
       </c>
-      <c r="C44" t="s">
+      <c r="C44" s="1" t="s">
         <v>31</v>
       </c>
-      <c r="D44" t="s">
+      <c r="D44" s="1" t="s">
         <v>239</v>
       </c>
-      <c r="E44" t="s">
+      <c r="E44" s="1" t="s">
         <v>35</v>
       </c>
-      <c r="F44" t="s">
-        <v>7</v>
-      </c>
-      <c r="G44" t="s">
+      <c r="F44" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="G44" s="1" t="s">
         <v>240</v>
       </c>
-      <c r="H44" t="s">
+      <c r="H44" s="1" t="s">
         <v>11</v>
       </c>
     </row>
     <row r="45" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A45" t="s">
+      <c r="A45" s="1" t="s">
         <v>241</v>
       </c>
-      <c r="C45" t="s">
+      <c r="C45" s="1" t="s">
         <v>32</v>
       </c>
-      <c r="D45" t="s">
+      <c r="D45" s="1" t="s">
         <v>242</v>
       </c>
-      <c r="E45" t="s">
+      <c r="E45" s="1" t="s">
         <v>243</v>
       </c>
-      <c r="F45" t="s">
-        <v>7</v>
-      </c>
-      <c r="G45" t="s">
+      <c r="F45" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="G45" s="1" t="s">
         <v>244</v>
       </c>
-      <c r="H45" t="s">
+      <c r="H45" s="1" t="s">
         <v>11</v>
       </c>
     </row>
     <row r="46" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A46" t="s">
+      <c r="A46" s="1" t="s">
         <v>245</v>
       </c>
-      <c r="C46" t="s">
+      <c r="C46" s="1" t="s">
         <v>76</v>
       </c>
-      <c r="D46" t="s">
+      <c r="D46" s="1" t="s">
         <v>246</v>
       </c>
-      <c r="E46" t="s">
+      <c r="E46" s="1" t="s">
         <v>247</v>
       </c>
-      <c r="F46" t="s">
-        <v>7</v>
-      </c>
-      <c r="G46" t="s">
+      <c r="F46" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="G46" s="1" t="s">
         <v>248</v>
       </c>
-      <c r="H46" t="s">
+      <c r="H46" s="1" t="s">
         <v>11</v>
       </c>
     </row>
     <row r="47" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A47" t="s">
+      <c r="A47" s="1" t="s">
         <v>249</v>
       </c>
-      <c r="C47" t="s">
+      <c r="C47" s="1" t="s">
         <v>131</v>
       </c>
-      <c r="D47" t="s">
+      <c r="D47" s="1" t="s">
         <v>250</v>
       </c>
-      <c r="E47" t="s">
+      <c r="E47" s="1" t="s">
         <v>43</v>
       </c>
-      <c r="F47" t="s">
+      <c r="F47" s="1" t="s">
         <v>44</v>
       </c>
-      <c r="G47" t="s">
+      <c r="G47" s="1" t="s">
         <v>251</v>
       </c>
-      <c r="H47" t="s">
+      <c r="H47" s="1" t="s">
         <v>11</v>
       </c>
     </row>
     <row r="48" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A48" t="s">
+      <c r="A48" s="1" t="s">
         <v>252</v>
       </c>
-      <c r="C48" t="s">
+      <c r="C48" s="1" t="s">
         <v>131</v>
       </c>
-      <c r="D48" t="s">
+      <c r="D48" s="1" t="s">
         <v>250</v>
       </c>
-      <c r="E48" t="s">
+      <c r="E48" s="1" t="s">
         <v>43</v>
       </c>
-      <c r="F48" t="s">
+      <c r="F48" s="1" t="s">
         <v>44</v>
       </c>
-      <c r="G48" t="s">
+      <c r="G48" s="1" t="s">
         <v>251</v>
       </c>
-      <c r="H48" t="s">
+      <c r="H48" s="1" t="s">
         <v>11</v>
       </c>
     </row>
     <row r="49" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A49" t="s">
+      <c r="A49" s="1" t="s">
         <v>253</v>
       </c>
-      <c r="C49" t="s">
+      <c r="C49" s="1" t="s">
         <v>131</v>
       </c>
-      <c r="D49" t="s">
+      <c r="D49" s="1" t="s">
         <v>250</v>
       </c>
-      <c r="E49" t="s">
+      <c r="E49" s="1" t="s">
         <v>43</v>
       </c>
-      <c r="F49" t="s">
+      <c r="F49" s="1" t="s">
         <v>44</v>
       </c>
-      <c r="G49" t="s">
+      <c r="G49" s="1" t="s">
         <v>251</v>
       </c>
-      <c r="H49" t="s">
+      <c r="H49" s="1" t="s">
         <v>11</v>
       </c>
     </row>
     <row r="50" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A50" t="s">
+      <c r="A50" s="1" t="s">
         <v>254</v>
       </c>
-      <c r="C50" t="s">
+      <c r="C50" s="1" t="s">
         <v>20</v>
       </c>
-      <c r="D50" t="s">
+      <c r="D50" s="1" t="s">
         <v>255</v>
       </c>
-      <c r="E50" t="s">
+      <c r="E50" s="1" t="s">
         <v>256</v>
       </c>
-      <c r="F50" t="s">
-        <v>7</v>
-      </c>
-      <c r="G50" t="s">
+      <c r="F50" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="G50" s="1" t="s">
         <v>257</v>
       </c>
-      <c r="H50" t="s">
+      <c r="H50" s="1" t="s">
         <v>11</v>
       </c>
     </row>
     <row r="51" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A51" t="s">
+      <c r="A51" s="1" t="s">
         <v>258</v>
       </c>
-      <c r="C51" t="s">
+      <c r="C51" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="D51" t="s">
+      <c r="D51" s="1" t="s">
         <v>259</v>
       </c>
-      <c r="E51" t="s">
+      <c r="E51" s="1" t="s">
         <v>39</v>
       </c>
-      <c r="F51" t="s">
+      <c r="F51" s="1" t="s">
         <v>40</v>
       </c>
-      <c r="G51" t="s">
+      <c r="G51" s="1" t="s">
         <v>260</v>
       </c>
-      <c r="H51" t="s">
+      <c r="H51" s="1" t="s">
         <v>11</v>
       </c>
     </row>
     <row r="52" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A52" t="s">
+      <c r="A52" s="1" t="s">
         <v>261</v>
       </c>
-      <c r="C52" t="s">
+      <c r="C52" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="D52" t="s">
+      <c r="D52" s="1" t="s">
         <v>259</v>
       </c>
-      <c r="E52" t="s">
+      <c r="E52" s="1" t="s">
         <v>39</v>
       </c>
-      <c r="F52" t="s">
+      <c r="F52" s="1" t="s">
         <v>40</v>
       </c>
-      <c r="G52" t="s">
+      <c r="G52" s="1" t="s">
         <v>260</v>
       </c>
-      <c r="H52" t="s">
+      <c r="H52" s="1" t="s">
         <v>11</v>
       </c>
     </row>
     <row r="53" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A53" t="s">
+      <c r="A53" s="1" t="s">
         <v>262</v>
       </c>
-      <c r="C53" t="s">
+      <c r="C53" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="D53" t="s">
+      <c r="D53" s="1" t="s">
         <v>259</v>
       </c>
-      <c r="E53" t="s">
+      <c r="E53" s="1" t="s">
         <v>39</v>
       </c>
-      <c r="F53" t="s">
+      <c r="F53" s="1" t="s">
         <v>40</v>
       </c>
-      <c r="G53" t="s">
+      <c r="G53" s="1" t="s">
         <v>260</v>
       </c>
-      <c r="H53" t="s">
+      <c r="H53" s="1" t="s">
         <v>11</v>
       </c>
     </row>
     <row r="54" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A54" t="s">
+      <c r="A54" s="1" t="s">
         <v>263</v>
       </c>
-      <c r="C54" t="s">
+      <c r="C54" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="D54" t="s">
+      <c r="D54" s="1" t="s">
         <v>264</v>
       </c>
-      <c r="E54" t="s">
+      <c r="E54" s="1" t="s">
         <v>37</v>
       </c>
-      <c r="F54" t="s">
-        <v>7</v>
-      </c>
-      <c r="G54" t="s">
+      <c r="F54" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="G54" s="1" t="s">
         <v>265</v>
       </c>
-      <c r="H54" t="s">
+      <c r="H54" s="1" t="s">
         <v>11</v>
       </c>
     </row>
     <row r="55" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A55" t="s">
+      <c r="A55" s="1" t="s">
         <v>266</v>
       </c>
-      <c r="C55" t="s">
+      <c r="C55" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="D55" t="s">
+      <c r="D55" s="1" t="s">
         <v>264</v>
       </c>
-      <c r="E55" t="s">
+      <c r="E55" s="1" t="s">
         <v>37</v>
       </c>
-      <c r="F55" t="s">
-        <v>7</v>
-      </c>
-      <c r="G55" t="s">
+      <c r="F55" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="G55" s="1" t="s">
         <v>265</v>
       </c>
-      <c r="H55" t="s">
+      <c r="H55" s="1" t="s">
         <v>11</v>
       </c>
     </row>
     <row r="56" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A56" t="s">
+      <c r="A56" s="1" t="s">
         <v>267</v>
       </c>
-      <c r="C56" t="s">
+      <c r="C56" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="D56" t="s">
+      <c r="D56" s="1" t="s">
         <v>264</v>
       </c>
-      <c r="E56" t="s">
+      <c r="E56" s="1" t="s">
         <v>37</v>
       </c>
-      <c r="F56" t="s">
-        <v>7</v>
-      </c>
-      <c r="G56" t="s">
+      <c r="F56" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="G56" s="1" t="s">
         <v>265</v>
       </c>
-      <c r="H56" t="s">
+      <c r="H56" s="1" t="s">
         <v>11</v>
       </c>
     </row>
     <row r="57" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A57" t="s">
+      <c r="A57" s="1" t="s">
         <v>268</v>
       </c>
-      <c r="C57" t="s">
+      <c r="C57" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="D57" t="s">
+      <c r="D57" s="1" t="s">
         <v>269</v>
       </c>
-      <c r="E57" t="s">
+      <c r="E57" s="1" t="s">
         <v>270</v>
       </c>
-      <c r="F57" t="s">
-        <v>7</v>
-      </c>
-      <c r="G57" t="s">
+      <c r="F57" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="G57" s="1" t="s">
         <v>271</v>
       </c>
-      <c r="H57" t="s">
+      <c r="H57" s="1" t="s">
         <v>11</v>
       </c>
     </row>
     <row r="58" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A58" t="s">
+      <c r="A58" s="1" t="s">
         <v>272</v>
       </c>
-      <c r="C58" t="s">
+      <c r="C58" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="D58" t="s">
+      <c r="D58" s="1" t="s">
         <v>269</v>
       </c>
-      <c r="E58" t="s">
+      <c r="E58" s="1" t="s">
         <v>270</v>
       </c>
-      <c r="F58" t="s">
-        <v>7</v>
-      </c>
-      <c r="G58" t="s">
+      <c r="F58" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="G58" s="1" t="s">
         <v>271</v>
       </c>
-      <c r="H58" t="s">
+      <c r="H58" s="1" t="s">
         <v>11</v>
       </c>
     </row>
     <row r="59" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A59" t="s">
+      <c r="A59" s="1" t="s">
         <v>273</v>
       </c>
-      <c r="C59" t="s">
+      <c r="C59" s="1" t="s">
         <v>28</v>
       </c>
-      <c r="D59" t="s">
+      <c r="D59" s="1" t="s">
         <v>274</v>
       </c>
-      <c r="E59" t="s">
+      <c r="E59" s="1" t="s">
         <v>275</v>
       </c>
-      <c r="F59" t="s">
+      <c r="F59" s="1" t="s">
         <v>276</v>
       </c>
-      <c r="G59" t="s">
+      <c r="G59" s="1" t="s">
         <v>102</v>
       </c>
-      <c r="H59" t="s">
+      <c r="H59" s="1" t="s">
         <v>11</v>
       </c>
     </row>
     <row r="60" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A60" t="s">
+      <c r="A60" s="1" t="s">
         <v>277</v>
       </c>
-      <c r="C60" t="s">
+      <c r="C60" s="1" t="s">
         <v>28</v>
       </c>
-      <c r="D60" t="s">
+      <c r="D60" s="1" t="s">
         <v>274</v>
       </c>
-      <c r="E60" t="s">
+      <c r="E60" s="1" t="s">
         <v>275</v>
       </c>
-      <c r="F60" t="s">
+      <c r="F60" s="1" t="s">
         <v>276</v>
       </c>
-      <c r="G60" t="s">
+      <c r="G60" s="1" t="s">
         <v>102</v>
       </c>
-      <c r="H60" t="s">
+      <c r="H60" s="1" t="s">
         <v>11</v>
       </c>
     </row>
     <row r="61" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A61" t="s">
+      <c r="A61" s="1" t="s">
         <v>278</v>
       </c>
-      <c r="C61" t="s">
+      <c r="C61" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="D61" t="s">
+      <c r="D61" s="1" t="s">
         <v>279</v>
       </c>
-      <c r="E61" t="s">
+      <c r="E61" s="1" t="s">
         <v>280</v>
       </c>
-      <c r="F61" t="s">
-        <v>7</v>
-      </c>
-      <c r="G61" t="s">
+      <c r="F61" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="G61" s="1" t="s">
         <v>281</v>
       </c>
-      <c r="H61" t="s">
+      <c r="H61" s="1" t="s">
         <v>11</v>
       </c>
     </row>
     <row r="62" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A62" t="s">
+      <c r="A62" s="1" t="s">
         <v>282</v>
       </c>
-      <c r="C62" t="s">
+      <c r="C62" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="D62" t="s">
+      <c r="D62" s="1" t="s">
         <v>279</v>
       </c>
-      <c r="E62" t="s">
+      <c r="E62" s="1" t="s">
         <v>280</v>
       </c>
-      <c r="F62" t="s">
-        <v>7</v>
-      </c>
-      <c r="G62" t="s">
+      <c r="F62" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="G62" s="1" t="s">
         <v>281</v>
       </c>
-      <c r="H62" t="s">
+      <c r="H62" s="1" t="s">
         <v>11</v>
       </c>
     </row>
     <row r="63" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A63" t="s">
+      <c r="A63" s="1" t="s">
         <v>283</v>
       </c>
-      <c r="C63" t="s">
+      <c r="C63" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="D63" t="s">
+      <c r="D63" s="1" t="s">
         <v>284</v>
       </c>
-      <c r="E63" t="s">
+      <c r="E63" s="1" t="s">
         <v>285</v>
       </c>
-      <c r="F63" t="s">
-        <v>7</v>
-      </c>
-      <c r="G63" t="s">
+      <c r="F63" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="G63" s="1" t="s">
         <v>72</v>
       </c>
-      <c r="H63" t="s">
+      <c r="H63" s="1" t="s">
         <v>11</v>
       </c>
     </row>
     <row r="64" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A64" t="s">
+      <c r="A64" s="1" t="s">
         <v>286</v>
       </c>
-      <c r="C64" t="s">
+      <c r="C64" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="D64" t="s">
+      <c r="D64" s="1" t="s">
         <v>287</v>
       </c>
-      <c r="E64" t="s">
+      <c r="E64" s="1" t="s">
         <v>288</v>
       </c>
-      <c r="F64" t="s">
-        <v>7</v>
-      </c>
-      <c r="G64" t="s">
+      <c r="F64" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="G64" s="1" t="s">
         <v>289</v>
       </c>
-      <c r="H64" t="s">
+      <c r="H64" s="1" t="s">
         <v>11</v>
       </c>
     </row>
     <row r="65" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A65" t="s">
+      <c r="A65" s="1" t="s">
         <v>290</v>
       </c>
-      <c r="C65" t="s">
+      <c r="C65" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="D65" t="s">
+      <c r="D65" s="1" t="s">
         <v>291</v>
       </c>
-      <c r="E65" t="s">
+      <c r="E65" s="1" t="s">
         <v>65</v>
       </c>
-      <c r="F65" t="s">
-        <v>7</v>
-      </c>
-      <c r="G65" t="s">
+      <c r="F65" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="G65" s="1" t="s">
         <v>292</v>
       </c>
-      <c r="H65" t="s">
+      <c r="H65" s="1" t="s">
         <v>11</v>
       </c>
     </row>
     <row r="66" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A66" t="s">
+      <c r="A66" s="1" t="s">
         <v>293</v>
       </c>
-      <c r="C66" t="s">
+      <c r="C66" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="D66" t="s">
+      <c r="D66" s="1" t="s">
         <v>291</v>
       </c>
-      <c r="E66" t="s">
+      <c r="E66" s="1" t="s">
         <v>65</v>
       </c>
-      <c r="F66" t="s">
-        <v>7</v>
-      </c>
-      <c r="G66" t="s">
+      <c r="F66" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="G66" s="1" t="s">
         <v>292</v>
       </c>
-      <c r="H66" t="s">
+      <c r="H66" s="1" t="s">
         <v>11</v>
       </c>
     </row>
     <row r="67" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A67" t="s">
+      <c r="A67" s="1" t="s">
         <v>294</v>
       </c>
-      <c r="C67" t="s">
+      <c r="C67" s="1" t="s">
         <v>29</v>
       </c>
-      <c r="D67" t="s">
+      <c r="D67" s="1" t="s">
         <v>295</v>
       </c>
-      <c r="E67" t="s">
+      <c r="E67" s="1" t="s">
         <v>36</v>
       </c>
-      <c r="F67" t="s">
-        <v>7</v>
-      </c>
-      <c r="G67" t="s">
+      <c r="F67" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="G67" s="1" t="s">
         <v>296</v>
       </c>
-      <c r="H67" t="s">
+      <c r="H67" s="1" t="s">
         <v>11</v>
       </c>
     </row>
     <row r="68" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A68" t="s">
+      <c r="A68" s="1" t="s">
         <v>297</v>
       </c>
-      <c r="C68" t="s">
+      <c r="C68" s="1" t="s">
         <v>165</v>
       </c>
-      <c r="D68" t="s">
+      <c r="D68" s="1" t="s">
         <v>298</v>
       </c>
-      <c r="E68" t="s">
+      <c r="E68" s="1" t="s">
         <v>299</v>
       </c>
-      <c r="F68" t="s">
-        <v>7</v>
-      </c>
-      <c r="G68" t="s">
+      <c r="F68" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="G68" s="1" t="s">
         <v>300</v>
       </c>
-      <c r="H68" t="s">
+      <c r="H68" s="1" t="s">
         <v>11</v>
       </c>
     </row>
     <row r="69" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A69" t="s">
+      <c r="A69" s="1" t="s">
         <v>301</v>
       </c>
-      <c r="C69" t="s">
+      <c r="C69" s="1" t="s">
         <v>165</v>
       </c>
-      <c r="D69" t="s">
+      <c r="D69" s="1" t="s">
         <v>302</v>
       </c>
-      <c r="E69" t="s">
+      <c r="E69" s="1" t="s">
         <v>303</v>
       </c>
-      <c r="F69" t="s">
-        <v>7</v>
-      </c>
-      <c r="G69" t="s">
+      <c r="F69" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="G69" s="1" t="s">
         <v>304</v>
       </c>
-      <c r="H69" t="s">
+      <c r="H69" s="1" t="s">
         <v>11</v>
       </c>
     </row>
     <row r="70" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A70" t="s">
+      <c r="A70" s="1" t="s">
         <v>305</v>
       </c>
-      <c r="C70" t="s">
+      <c r="C70" s="1" t="s">
         <v>50</v>
       </c>
-      <c r="D70" t="s">
+      <c r="D70" s="1" t="s">
         <v>306</v>
       </c>
-      <c r="E70" t="s">
+      <c r="E70" s="1" t="s">
         <v>307</v>
       </c>
-      <c r="F70" t="s">
+      <c r="F70" s="1" t="s">
         <v>308</v>
       </c>
-      <c r="G70" t="s">
+      <c r="G70" s="1" t="s">
         <v>309</v>
       </c>
-      <c r="H70" t="s">
+      <c r="H70" s="1" t="s">
         <v>11</v>
       </c>
     </row>
     <row r="71" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A71" t="s">
+      <c r="A71" s="1" t="s">
         <v>310</v>
       </c>
-      <c r="C71" t="s">
+      <c r="C71" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="D71" t="s">
+      <c r="D71" s="1" t="s">
         <v>311</v>
       </c>
-      <c r="E71" t="s">
+      <c r="E71" s="1" t="s">
         <v>312</v>
       </c>
-      <c r="F71" t="s">
+      <c r="F71" s="1" t="s">
         <v>313</v>
       </c>
-      <c r="G71" t="s">
+      <c r="G71" s="1" t="s">
         <v>314</v>
       </c>
-      <c r="H71" t="s">
+      <c r="H71" s="1" t="s">
         <v>11</v>
       </c>
     </row>
     <row r="72" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A72" t="s">
+      <c r="A72" s="1" t="s">
         <v>315</v>
       </c>
-      <c r="C72" t="s">
+      <c r="C72" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="D72" t="s">
+      <c r="D72" s="1" t="s">
         <v>316</v>
       </c>
-      <c r="E72" t="s">
+      <c r="E72" s="1" t="s">
         <v>317</v>
       </c>
-      <c r="F72" t="s">
-        <v>7</v>
-      </c>
-      <c r="G72" t="s">
+      <c r="F72" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="G72" s="1" t="s">
         <v>318</v>
       </c>
-      <c r="H72" t="s">
+      <c r="H72" s="1" t="s">
         <v>11</v>
       </c>
     </row>
     <row r="73" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A73" t="s">
+      <c r="A73" s="1" t="s">
         <v>319</v>
       </c>
-      <c r="C73" t="s">
+      <c r="C73" s="1" t="s">
         <v>23</v>
       </c>
-      <c r="D73" t="s">
+      <c r="D73" s="1" t="s">
         <v>320</v>
       </c>
-      <c r="E73" t="s">
+      <c r="E73" s="1" t="s">
         <v>47</v>
       </c>
-      <c r="F73" t="s">
+      <c r="F73" s="1" t="s">
         <v>48</v>
       </c>
-      <c r="G73" t="s">
+      <c r="G73" s="1" t="s">
         <v>321</v>
       </c>
-      <c r="H73" t="s">
+      <c r="H73" s="1" t="s">
         <v>11</v>
       </c>
     </row>
     <row r="74" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A74" t="s">
+      <c r="A74" s="1" t="s">
         <v>322</v>
       </c>
-      <c r="C74" t="s">
+      <c r="C74" s="1" t="s">
         <v>23</v>
       </c>
-      <c r="D74" t="s">
+      <c r="D74" s="1" t="s">
         <v>320</v>
       </c>
-      <c r="E74" t="s">
+      <c r="E74" s="1" t="s">
         <v>47</v>
       </c>
-      <c r="F74" t="s">
+      <c r="F74" s="1" t="s">
         <v>48</v>
       </c>
-      <c r="G74" t="s">
+      <c r="G74" s="1" t="s">
         <v>321</v>
       </c>
-      <c r="H74" t="s">
+      <c r="H74" s="1" t="s">
         <v>11</v>
       </c>
     </row>
     <row r="75" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A75" t="s">
+      <c r="A75" s="1" t="s">
         <v>323</v>
       </c>
-      <c r="C75" t="s">
+      <c r="C75" s="1" t="s">
         <v>22</v>
       </c>
-      <c r="D75" t="s">
+      <c r="D75" s="1" t="s">
         <v>324</v>
       </c>
-      <c r="E75" t="s">
+      <c r="E75" s="1" t="s">
         <v>325</v>
       </c>
-      <c r="F75" t="s">
+      <c r="F75" s="1" t="s">
         <v>326</v>
       </c>
-      <c r="G75" t="s">
+      <c r="G75" s="1" t="s">
         <v>327</v>
       </c>
-      <c r="H75" t="s">
+      <c r="H75" s="1" t="s">
         <v>11</v>
       </c>
     </row>
     <row r="76" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A76" t="s">
+      <c r="A76" s="1" t="s">
         <v>328</v>
       </c>
-      <c r="C76" t="s">
+      <c r="C76" s="1" t="s">
         <v>22</v>
       </c>
-      <c r="D76" t="s">
+      <c r="D76" s="1" t="s">
         <v>324</v>
       </c>
-      <c r="E76" t="s">
+      <c r="E76" s="1" t="s">
         <v>325</v>
       </c>
-      <c r="F76" t="s">
+      <c r="F76" s="1" t="s">
         <v>326</v>
       </c>
-      <c r="G76" t="s">
+      <c r="G76" s="1" t="s">
         <v>327</v>
       </c>
-      <c r="H76" t="s">
+      <c r="H76" s="1" t="s">
         <v>11</v>
       </c>
     </row>
     <row r="77" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A77" t="s">
+      <c r="A77" s="1" t="s">
         <v>329</v>
       </c>
-      <c r="C77" t="s">
+      <c r="C77" s="1" t="s">
         <v>22</v>
       </c>
-      <c r="D77" t="s">
+      <c r="D77" s="1" t="s">
         <v>324</v>
       </c>
-      <c r="E77" t="s">
+      <c r="E77" s="1" t="s">
         <v>325</v>
       </c>
-      <c r="F77" t="s">
+      <c r="F77" s="1" t="s">
         <v>326</v>
       </c>
-      <c r="G77" t="s">
+      <c r="G77" s="1" t="s">
         <v>327</v>
       </c>
-      <c r="H77" t="s">
+      <c r="H77" s="1" t="s">
         <v>11</v>
       </c>
     </row>
     <row r="78" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A78" t="s">
+      <c r="A78" s="1" t="s">
         <v>330</v>
       </c>
-      <c r="C78" t="s">
+      <c r="C78" s="1" t="s">
         <v>38</v>
       </c>
-      <c r="D78" t="s">
+      <c r="D78" s="1" t="s">
         <v>331</v>
       </c>
-      <c r="E78" t="s">
+      <c r="E78" s="1" t="s">
         <v>83</v>
       </c>
-      <c r="F78" t="s">
+      <c r="F78" s="1" t="s">
         <v>84</v>
       </c>
-      <c r="G78" t="s">
+      <c r="G78" s="1" t="s">
         <v>332</v>
       </c>
-      <c r="H78" t="s">
+      <c r="H78" s="1" t="s">
         <v>11</v>
       </c>
     </row>
     <row r="79" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A79" t="s">
+      <c r="A79" s="1" t="s">
         <v>333</v>
       </c>
-      <c r="C79" t="s">
+      <c r="C79" s="1" t="s">
         <v>131</v>
       </c>
-      <c r="D79" t="s">
+      <c r="D79" s="1" t="s">
         <v>334</v>
       </c>
-      <c r="E79" t="s">
+      <c r="E79" s="1" t="s">
         <v>335</v>
       </c>
-      <c r="F79" t="s">
+      <c r="F79" s="1" t="s">
         <v>336</v>
       </c>
-      <c r="G79" t="s">
+      <c r="G79" s="1" t="s">
         <v>72</v>
       </c>
-      <c r="H79" t="s">
+      <c r="H79" s="1" t="s">
         <v>11</v>
       </c>
     </row>
     <row r="80" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A80" t="s">
+      <c r="A80" s="1" t="s">
         <v>337</v>
       </c>
-      <c r="C80" t="s">
+      <c r="C80" s="1" t="s">
         <v>29</v>
       </c>
-      <c r="D80" t="s">
+      <c r="D80" s="1" t="s">
         <v>338</v>
       </c>
-      <c r="E80" t="s">
+      <c r="E80" s="1" t="s">
         <v>339</v>
       </c>
-      <c r="F80" t="s">
-        <v>7</v>
-      </c>
-      <c r="G80" t="s">
+      <c r="F80" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="G80" s="1" t="s">
         <v>340</v>
       </c>
-      <c r="H80" t="s">
+      <c r="H80" s="1" t="s">
         <v>11</v>
       </c>
     </row>
     <row r="81" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A81" t="s">
+      <c r="A81" s="1" t="s">
         <v>341</v>
       </c>
-      <c r="C81" t="s">
+      <c r="C81" s="1" t="s">
         <v>29</v>
       </c>
-      <c r="D81" t="s">
+      <c r="D81" s="1" t="s">
         <v>342</v>
       </c>
-      <c r="E81" t="s">
+      <c r="E81" s="1" t="s">
         <v>343</v>
       </c>
-      <c r="F81" t="s">
+      <c r="F81" s="1" t="s">
         <v>344</v>
       </c>
-      <c r="G81" t="s">
+      <c r="G81" s="1" t="s">
         <v>345</v>
       </c>
-      <c r="H81" t="s">
+      <c r="H81" s="1" t="s">
         <v>11</v>
       </c>
     </row>
     <row r="82" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A82" t="s">
+      <c r="A82" s="1" t="s">
         <v>346</v>
       </c>
-      <c r="C82" t="s">
+      <c r="C82" s="1" t="s">
         <v>29</v>
       </c>
-      <c r="D82" t="s">
+      <c r="D82" s="1" t="s">
         <v>342</v>
       </c>
-      <c r="E82" t="s">
+      <c r="E82" s="1" t="s">
         <v>343</v>
       </c>
-      <c r="F82" t="s">
+      <c r="F82" s="1" t="s">
         <v>344</v>
       </c>
-      <c r="G82" t="s">
+      <c r="G82" s="1" t="s">
         <v>345</v>
       </c>
-      <c r="H82" t="s">
+      <c r="H82" s="1" t="s">
         <v>11</v>
       </c>
     </row>
     <row r="83" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A83" t="s">
+      <c r="A83" s="1" t="s">
         <v>347</v>
       </c>
-      <c r="C83" t="s">
+      <c r="C83" s="1" t="s">
         <v>28</v>
       </c>
-      <c r="D83" t="s">
+      <c r="D83" s="1" t="s">
         <v>348</v>
       </c>
-      <c r="E83" t="s">
+      <c r="E83" s="1" t="s">
         <v>53</v>
       </c>
-      <c r="F83" t="s">
-        <v>7</v>
-      </c>
-      <c r="G83" t="s">
+      <c r="F83" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="G83" s="1" t="s">
         <v>349</v>
       </c>
-      <c r="H83" t="s">
+      <c r="H83" s="1" t="s">
         <v>11</v>
       </c>
     </row>
     <row r="84" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A84" t="s">
+      <c r="A84" s="1" t="s">
         <v>350</v>
       </c>
-      <c r="C84" t="s">
+      <c r="C84" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="D84" t="s">
+      <c r="D84" s="1" t="s">
         <v>351</v>
       </c>
-      <c r="E84" t="s">
+      <c r="E84" s="1" t="s">
         <v>352</v>
       </c>
-      <c r="F84" t="s">
-        <v>7</v>
-      </c>
-      <c r="G84" t="s">
+      <c r="F84" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="G84" s="1" t="s">
         <v>271</v>
       </c>
-      <c r="H84" t="s">
+      <c r="H84" s="1" t="s">
         <v>11</v>
       </c>
     </row>
     <row r="85" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A85" t="s">
+      <c r="A85" s="1" t="s">
         <v>353</v>
       </c>
-      <c r="C85" t="s">
+      <c r="C85" s="1" t="s">
         <v>23</v>
       </c>
-      <c r="D85" t="s">
+      <c r="D85" s="1" t="s">
         <v>354</v>
       </c>
-      <c r="E85" t="s">
+      <c r="E85" s="1" t="s">
         <v>355</v>
       </c>
-      <c r="F85" t="s">
+      <c r="F85" s="1" t="s">
         <v>356</v>
       </c>
-      <c r="G85" t="s">
+      <c r="G85" s="1" t="s">
         <v>357</v>
       </c>
-      <c r="H85" t="s">
+      <c r="H85" s="1" t="s">
         <v>11</v>
       </c>
     </row>
     <row r="86" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A86" t="s">
+      <c r="A86" s="1" t="s">
         <v>358</v>
       </c>
-      <c r="C86" t="s">
+      <c r="C86" s="1" t="s">
         <v>29</v>
       </c>
-      <c r="D86" t="s">
+      <c r="D86" s="1" t="s">
         <v>359</v>
       </c>
-      <c r="E86" t="s">
+      <c r="E86" s="1" t="s">
         <v>360</v>
       </c>
-      <c r="F86" t="s">
+      <c r="F86" s="1" t="s">
         <v>79</v>
       </c>
-      <c r="G86" t="s">
+      <c r="G86" s="1" t="s">
         <v>361</v>
       </c>
-      <c r="H86" t="s">
+      <c r="H86" s="1" t="s">
         <v>11</v>
       </c>
     </row>
     <row r="87" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A87" t="s">
+      <c r="A87" s="1" t="s">
         <v>362</v>
       </c>
-      <c r="C87" t="s">
+      <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
-      <c r="D87" t="s">
+      <c r="D87" s="1" t="s">
         <v>363</v>
       </c>
-      <c r="E87" t="s">
+      <c r="E87" s="1" t="s">
         <v>103</v>
       </c>
-      <c r="F87" t="s">
-        <v>7</v>
-      </c>
-      <c r="G87" t="s">
+      <c r="F87" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="G87" s="1" t="s">
         <v>364</v>
       </c>
-      <c r="H87" t="s">
+      <c r="H87" s="1" t="s">
         <v>11</v>
       </c>
     </row>
     <row r="88" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A88" t="s">
+      <c r="A88" s="1" t="s">
         <v>365</v>
       </c>
-      <c r="C88" t="s">
+      <c r="C88" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="D88" t="s">
+      <c r="D88" s="1" t="s">
         <v>366</v>
       </c>
-      <c r="E88" t="s">
+      <c r="E88" s="1" t="s">
         <v>367</v>
       </c>
-      <c r="F88" t="s">
-        <v>7</v>
-      </c>
-      <c r="G88" t="s">
+      <c r="F88" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="G88" s="1" t="s">
         <v>368</v>
       </c>
-      <c r="H88" t="s">
+      <c r="H88" s="1" t="s">
         <v>11</v>
       </c>
     </row>
     <row r="89" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A89" t="s">
+      <c r="A89" s="1" t="s">
         <v>369</v>
       </c>
-      <c r="C89" t="s">
+      <c r="C89" s="1" t="s">
         <v>29</v>
       </c>
-      <c r="D89" t="s">
+      <c r="D89" s="1" t="s">
         <v>370</v>
       </c>
-      <c r="E89" t="s">
+      <c r="E89" s="1" t="s">
         <v>371</v>
       </c>
-      <c r="F89" t="s">
-        <v>7</v>
-      </c>
-      <c r="G89" t="s">
+      <c r="F89" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="G89" s="1" t="s">
         <v>372</v>
       </c>
-      <c r="H89" t="s">
+      <c r="H89" s="1" t="s">
         <v>11</v>
       </c>
     </row>
     <row r="90" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A90" t="s">
+      <c r="A90" s="1" t="s">
         <v>373</v>
       </c>
-      <c r="C90" t="s">
+      <c r="C90" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="D90" t="s">
+      <c r="D90" s="1" t="s">
         <v>374</v>
       </c>
-      <c r="E90" t="s">
+      <c r="E90" s="1" t="s">
         <v>375</v>
       </c>
-      <c r="F90" t="s">
-        <v>7</v>
-      </c>
-      <c r="G90" t="s">
+      <c r="F90" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="G90" s="1" t="s">
         <v>376</v>
       </c>
-      <c r="H90" t="s">
+      <c r="H90" s="1" t="s">
         <v>11</v>
       </c>
     </row>
     <row r="91" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A91" t="s">
+      <c r="A91" s="1" t="s">
         <v>377</v>
       </c>
-      <c r="C91" t="s">
+      <c r="C91" s="1" t="s">
         <v>20</v>
       </c>
-      <c r="D91" t="s">
+      <c r="D91" s="1" t="s">
         <v>378</v>
       </c>
-      <c r="E91" t="s">
+      <c r="E91" s="1" t="s">
         <v>93</v>
       </c>
-      <c r="F91" t="s">
-        <v>7</v>
-      </c>
-      <c r="G91" t="s">
+      <c r="F91" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="G91" s="1" t="s">
         <v>379</v>
       </c>
-      <c r="H91" t="s">
+      <c r="H91" s="1" t="s">
         <v>11</v>
       </c>
     </row>
     <row r="92" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A92" t="s">
+      <c r="A92" s="1" t="s">
         <v>380</v>
       </c>
-      <c r="C92" t="s">
+      <c r="C92" s="1" t="s">
         <v>23</v>
       </c>
-      <c r="D92" t="s">
+      <c r="D92" s="1" t="s">
         <v>381</v>
       </c>
-      <c r="E92" t="s">
+      <c r="E92" s="1" t="s">
         <v>145</v>
       </c>
-      <c r="F92" t="s">
+      <c r="F92" s="1" t="s">
         <v>146</v>
       </c>
-      <c r="G92" t="s">
+      <c r="G92" s="1" t="s">
         <v>382</v>
       </c>
-      <c r="H92" t="s">
+      <c r="H92" s="1" t="s">
         <v>11</v>
       </c>
     </row>
     <row r="93" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A93" t="s">
+      <c r="A93" s="1" t="s">
         <v>383</v>
       </c>
-      <c r="C93" t="s">
+      <c r="C93" s="1" t="s">
         <v>28</v>
       </c>
-      <c r="D93" t="s">
+      <c r="D93" s="1" t="s">
         <v>384</v>
       </c>
-      <c r="E93" t="s">
+      <c r="E93" s="1" t="s">
         <v>73</v>
       </c>
-      <c r="F93" t="s">
-        <v>7</v>
-      </c>
-      <c r="G93" t="s">
+      <c r="F93" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="G93" s="1" t="s">
         <v>385</v>
       </c>
-      <c r="H93" t="s">
+      <c r="H93" s="1" t="s">
         <v>11</v>
       </c>
     </row>
     <row r="94" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A94" t="s">
+      <c r="A94" s="1" t="s">
         <v>386</v>
       </c>
-      <c r="C94" t="s">
+      <c r="C94" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="D94" t="s">
+      <c r="D94" s="1" t="s">
         <v>387</v>
       </c>
-      <c r="E94" t="s">
+      <c r="E94" s="1" t="s">
         <v>18</v>
       </c>
-      <c r="F94" t="s">
-        <v>7</v>
-      </c>
-      <c r="G94" t="s">
+      <c r="F94" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="G94" s="1" t="s">
         <v>388</v>
       </c>
-      <c r="H94" t="s">
+      <c r="H94" s="1" t="s">
         <v>11</v>
       </c>
     </row>
     <row r="95" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A95" t="s">
+      <c r="A95" s="1" t="s">
         <v>389</v>
       </c>
-      <c r="C95" t="s">
+      <c r="C95" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="D95" t="s">
+      <c r="D95" s="1" t="s">
         <v>390</v>
       </c>
-      <c r="E95" t="s">
+      <c r="E95" s="1" t="s">
         <v>110</v>
       </c>
-      <c r="F95" t="s">
-        <v>7</v>
-      </c>
-      <c r="G95" t="s">
+      <c r="F95" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="G95" s="1" t="s">
         <v>391</v>
       </c>
-      <c r="H95" t="s">
+      <c r="H95" s="1" t="s">
         <v>11</v>
       </c>
     </row>
     <row r="96" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A96" t="s">
+      <c r="A96" s="1" t="s">
         <v>392</v>
       </c>
-      <c r="C96" t="s">
+      <c r="C96" s="1" t="s">
         <v>33</v>
       </c>
-      <c r="D96" t="s">
+      <c r="D96" s="1" t="s">
         <v>393</v>
       </c>
-      <c r="E96" t="s">
+      <c r="E96" s="1" t="s">
         <v>24</v>
       </c>
-      <c r="F96" t="s">
-        <v>7</v>
-      </c>
-      <c r="G96" t="s">
+      <c r="F96" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="G96" s="1" t="s">
         <v>394</v>
       </c>
-      <c r="H96" t="s">
+      <c r="H96" s="1" t="s">
         <v>11</v>
       </c>
     </row>
     <row r="97" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A97" t="s">
+      <c r="A97" s="1" t="s">
         <v>395</v>
       </c>
-      <c r="C97" t="s">
+      <c r="C97" s="1" t="s">
         <v>20</v>
       </c>
-      <c r="D97" t="s">
+      <c r="D97" s="1" t="s">
         <v>396</v>
       </c>
-      <c r="E97" t="s">
+      <c r="E97" s="1" t="s">
         <v>256</v>
       </c>
-      <c r="F97" t="s">
-        <v>7</v>
-      </c>
-      <c r="G97" t="s">
+      <c r="F97" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="G97" s="1" t="s">
         <v>397</v>
       </c>
-      <c r="H97" t="s">
+      <c r="H97" s="1" t="s">
         <v>11</v>
       </c>
     </row>
     <row r="98" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A98" t="s">
+      <c r="A98" s="1" t="s">
         <v>398</v>
       </c>
-      <c r="C98" t="s">
+      <c r="C98" s="1" t="s">
         <v>32</v>
       </c>
-      <c r="D98" t="s">
+      <c r="D98" s="1" t="s">
         <v>399</v>
       </c>
-      <c r="E98" t="s">
+      <c r="E98" s="1" t="s">
         <v>57</v>
       </c>
-      <c r="F98" t="s">
-        <v>7</v>
-      </c>
-      <c r="G98" t="s">
+      <c r="F98" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="G98" s="1" t="s">
         <v>104</v>
       </c>
-      <c r="H98" t="s">
+      <c r="H98" s="1" t="s">
         <v>11</v>
       </c>
     </row>
     <row r="99" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A99" t="s">
+      <c r="A99" s="1" t="s">
         <v>400</v>
       </c>
-      <c r="C99" t="s">
+      <c r="C99" s="1" t="s">
         <v>32</v>
       </c>
-      <c r="D99" t="s">
+      <c r="D99" s="1" t="s">
         <v>399</v>
       </c>
-      <c r="E99" t="s">
+      <c r="E99" s="1" t="s">
         <v>57</v>
       </c>
-      <c r="F99" t="s">
-        <v>7</v>
-      </c>
-      <c r="G99" t="s">
+      <c r="F99" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="G99" s="1" t="s">
         <v>104</v>
       </c>
-      <c r="H99" t="s">
+      <c r="H99" s="1" t="s">
         <v>11</v>
       </c>
     </row>
     <row r="100" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A100" t="s">
+      <c r="A100" s="1" t="s">
         <v>401</v>
       </c>
-      <c r="C100" t="s">
+      <c r="C100" s="1" t="s">
         <v>50</v>
       </c>
-      <c r="D100" t="s">
+      <c r="D100" s="1" t="s">
         <v>402</v>
       </c>
-      <c r="E100" t="s">
+      <c r="E100" s="1" t="s">
         <v>26</v>
       </c>
-      <c r="F100" t="s">
+      <c r="F100" s="1" t="s">
         <v>27</v>
       </c>
-      <c r="G100" t="s">
+      <c r="G100" s="1" t="s">
         <v>403</v>
       </c>
-      <c r="H100" t="s">
+      <c r="H100" s="1" t="s">
         <v>11</v>
       </c>
     </row>
     <row r="101" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A101" t="s">
+      <c r="A101" s="1" t="s">
         <v>404</v>
       </c>
-      <c r="C101" t="s">
+      <c r="C101" s="1" t="s">
         <v>50</v>
       </c>
-      <c r="D101" t="s">
+      <c r="D101" s="1" t="s">
         <v>402</v>
       </c>
-      <c r="E101" t="s">
+      <c r="E101" s="1" t="s">
         <v>26</v>
       </c>
-      <c r="F101" t="s">
+      <c r="F101" s="1" t="s">
         <v>27</v>
       </c>
-      <c r="G101" t="s">
+      <c r="G101" s="1" t="s">
         <v>403</v>
       </c>
-      <c r="H101" t="s">
+      <c r="H101" s="1" t="s">
         <v>11</v>
       </c>
     </row>
     <row r="102" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A102" t="s">
+      <c r="A102" s="1" t="s">
         <v>405</v>
       </c>
-      <c r="C102" t="s">
+      <c r="C102" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="D102" t="s">
+      <c r="D102" s="1" t="s">
         <v>406</v>
       </c>
-      <c r="E102" t="s">
+      <c r="E102" s="1" t="s">
         <v>407</v>
       </c>
-      <c r="F102" t="s">
-        <v>7</v>
-      </c>
-      <c r="G102" t="s">
+      <c r="F102" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="G102" s="1" t="s">
         <v>408</v>
       </c>
-      <c r="H102" t="s">
+      <c r="H102" s="1" t="s">
         <v>11</v>
       </c>
     </row>
     <row r="103" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A103" t="s">
+      <c r="A103" s="1" t="s">
         <v>409</v>
       </c>
-      <c r="C103" t="s">
+      <c r="C103" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="D103" t="s">
+      <c r="D103" s="1" t="s">
         <v>410</v>
       </c>
-      <c r="E103" t="s">
+      <c r="E103" s="1" t="s">
         <v>411</v>
       </c>
-      <c r="F103" t="s">
-        <v>7</v>
-      </c>
-      <c r="G103" t="s">
+      <c r="F103" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="G103" s="1" t="s">
         <v>412</v>
       </c>
-      <c r="H103" t="s">
+      <c r="H103" s="1" t="s">
         <v>11</v>
       </c>
     </row>
     <row r="104" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A104" t="s">
+      <c r="A104" s="1" t="s">
         <v>413</v>
       </c>
-      <c r="C104" t="s">
+      <c r="C104" s="1" t="s">
         <v>22</v>
       </c>
-      <c r="D104" t="s">
+      <c r="D104" s="1" t="s">
         <v>414</v>
       </c>
-      <c r="E104" t="s">
+      <c r="E104" s="1" t="s">
         <v>89</v>
       </c>
-      <c r="F104" t="s">
+      <c r="F104" s="1" t="s">
         <v>90</v>
       </c>
-      <c r="G104" t="s">
+      <c r="G104" s="1" t="s">
         <v>91</v>
       </c>
-      <c r="H104" t="s">
+      <c r="H104" s="1" t="s">
         <v>11</v>
       </c>
     </row>
     <row r="105" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A105" t="s">
+      <c r="A105" s="1" t="s">
         <v>415</v>
       </c>
-      <c r="C105" t="s">
+      <c r="C105" s="1" t="s">
         <v>22</v>
       </c>
-      <c r="D105" t="s">
+      <c r="D105" s="1" t="s">
         <v>414</v>
       </c>
-      <c r="E105" t="s">
+      <c r="E105" s="1" t="s">
         <v>89</v>
       </c>
-      <c r="F105" t="s">
+      <c r="F105" s="1" t="s">
         <v>90</v>
       </c>
-      <c r="G105" t="s">
+      <c r="G105" s="1" t="s">
         <v>91</v>
       </c>
-      <c r="H105" t="s">
+      <c r="H105" s="1" t="s">
         <v>11</v>
       </c>
     </row>
     <row r="106" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A106" t="s">
+      <c r="A106" s="1" t="s">
         <v>416</v>
       </c>
-      <c r="C106" t="s">
+      <c r="C106" s="1" t="s">
         <v>21</v>
       </c>
-      <c r="D106" t="s">
+      <c r="D106" s="1" t="s">
         <v>417</v>
       </c>
-      <c r="E106" t="s">
+      <c r="E106" s="1" t="s">
         <v>61</v>
       </c>
-      <c r="F106" t="s">
-        <v>7</v>
-      </c>
-      <c r="G106" t="s">
+      <c r="F106" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="G106" s="1" t="s">
         <v>98</v>
       </c>
-      <c r="H106" t="s">
+      <c r="H106" s="1" t="s">
         <v>11</v>
       </c>
     </row>
     <row r="107" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A107" t="s">
+      <c r="A107" s="1" t="s">
         <v>418</v>
       </c>
-      <c r="C107" t="s">
+      <c r="C107" s="1" t="s">
         <v>23</v>
       </c>
-      <c r="D107" t="s">
+      <c r="D107" s="1" t="s">
         <v>419</v>
       </c>
-      <c r="E107" t="s">
+      <c r="E107" s="1" t="s">
         <v>14</v>
       </c>
-      <c r="F107" t="s">
+      <c r="F107" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="G107" t="s">
+      <c r="G107" s="1" t="s">
         <v>420</v>
       </c>
-      <c r="H107" t="s">
+      <c r="H107" s="1" t="s">
         <v>11</v>
       </c>
     </row>
     <row r="108" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A108" t="s">
+      <c r="A108" s="1" t="s">
         <v>421</v>
       </c>
-      <c r="C108" t="s">
+      <c r="C108" s="1" t="s">
         <v>22</v>
       </c>
-      <c r="D108" t="s">
+      <c r="D108" s="1" t="s">
         <v>422</v>
       </c>
-      <c r="E108" t="s">
+      <c r="E108" s="1" t="s">
         <v>89</v>
       </c>
-      <c r="F108" t="s">
+      <c r="F108" s="1" t="s">
         <v>90</v>
       </c>
-      <c r="G108" t="s">
+      <c r="G108" s="1" t="s">
         <v>423</v>
       </c>
-      <c r="H108" t="s">
+      <c r="H108" s="1" t="s">
         <v>11</v>
       </c>
     </row>
     <row r="109" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A109" t="s">
+      <c r="A109" s="1" t="s">
         <v>424</v>
       </c>
-      <c r="C109" t="s">
+      <c r="C109" s="1" t="s">
         <v>21</v>
       </c>
-      <c r="D109" t="s">
+      <c r="D109" s="1" t="s">
         <v>425</v>
       </c>
-      <c r="E109" t="s">
+      <c r="E109" s="1" t="s">
         <v>426</v>
       </c>
-      <c r="F109" t="s">
-        <v>7</v>
-      </c>
-      <c r="G109" t="s">
+      <c r="F109" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="G109" s="1" t="s">
         <v>427</v>
       </c>
-      <c r="H109" t="s">
+      <c r="H109" s="1" t="s">
         <v>11</v>
       </c>
     </row>
     <row r="110" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A110" t="s">
+      <c r="A110" s="1" t="s">
         <v>428</v>
       </c>
-      <c r="C110" t="s">
+      <c r="C110" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="D110" t="s">
+      <c r="D110" s="1" t="s">
         <v>429</v>
       </c>
-      <c r="E110" t="s">
+      <c r="E110" s="1" t="s">
         <v>430</v>
       </c>
-      <c r="F110" t="s">
-        <v>7</v>
-      </c>
-      <c r="G110" t="s">
+      <c r="F110" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="G110" s="1" t="s">
         <v>431</v>
       </c>
-      <c r="H110" t="s">
+      <c r="H110" s="1" t="s">
         <v>11</v>
       </c>
     </row>
     <row r="111" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A111" t="s">
+      <c r="A111" s="1" t="s">
         <v>432</v>
       </c>
-      <c r="C111" t="s">
+      <c r="C111" s="1" t="s">
         <v>76</v>
       </c>
-      <c r="D111" t="s">
+      <c r="D111" s="1" t="s">
         <v>433</v>
       </c>
-      <c r="E111" t="s">
+      <c r="E111" s="1" t="s">
         <v>64</v>
       </c>
-      <c r="F111" t="s">
-        <v>7</v>
-      </c>
-      <c r="G111" t="s">
+      <c r="F111" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="G111" s="1" t="s">
         <v>434</v>
       </c>
-      <c r="H111" t="s">
+      <c r="H111" s="1" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="112" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A112" t="s">
+      <c r="A112" s="1" t="s">
         <v>435</v>
       </c>
-      <c r="C112" t="s">
+      <c r="C112" s="1" t="s">
         <v>94</v>
       </c>
-      <c r="D112" t="s">
+      <c r="D112" s="1" t="s">
         <v>436</v>
       </c>
-      <c r="E112" t="s">
+      <c r="E112" s="1" t="s">
         <v>42</v>
       </c>
-      <c r="F112" t="s">
-        <v>7</v>
-      </c>
-      <c r="G112" t="s">
+      <c r="F112" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="G112" s="1" t="s">
         <v>437</v>
       </c>
-      <c r="H112" t="s">
+      <c r="H112" s="1" t="s">
         <v>12</v>
       </c>
     </row>
     <row r="113" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A113" t="s">
+      <c r="A113" s="1" t="s">
         <v>438</v>
       </c>
-      <c r="C113" t="s">
+      <c r="C113" s="1" t="s">
         <v>21</v>
       </c>
-      <c r="D113" t="s">
+      <c r="D113" s="1" t="s">
         <v>439</v>
       </c>
-      <c r="E113" t="s">
+      <c r="E113" s="1" t="s">
         <v>41</v>
       </c>
-      <c r="F113" t="s">
-        <v>7</v>
-      </c>
-      <c r="G113" t="s">
+      <c r="F113" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="G113" s="1" t="s">
         <v>440</v>
       </c>
-      <c r="H113" t="s">
+      <c r="H113" s="1" t="s">
         <v>12</v>
       </c>
     </row>
     <row r="114" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A114" t="s">
+      <c r="A114" s="1" t="s">
         <v>441</v>
       </c>
-      <c r="C114" t="s">
+      <c r="C114" s="1" t="s">
         <v>131</v>
       </c>
-      <c r="D114" t="s">
+      <c r="D114" s="1" t="s">
         <v>442</v>
       </c>
-      <c r="E114" t="s">
+      <c r="E114" s="1" t="s">
         <v>133</v>
       </c>
-      <c r="F114" t="s">
+      <c r="F114" s="1" t="s">
         <v>134</v>
       </c>
-      <c r="G114" t="s">
+      <c r="G114" s="1" t="s">
         <v>443</v>
       </c>
-      <c r="H114" t="s">
+      <c r="H114" s="1" t="s">
         <v>12</v>
       </c>
     </row>
     <row r="115" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A115" t="s">
+      <c r="A115" s="1" t="s">
         <v>444</v>
       </c>
-      <c r="C115" t="s">
+      <c r="C115" s="1" t="s">
         <v>131</v>
       </c>
-      <c r="D115" t="s">
+      <c r="D115" s="1" t="s">
         <v>445</v>
       </c>
-      <c r="E115" t="s">
+      <c r="E115" s="1" t="s">
         <v>446</v>
       </c>
-      <c r="F115" t="s">
+      <c r="F115" s="1" t="s">
         <v>447</v>
       </c>
-      <c r="G115" t="s">
+      <c r="G115" s="1" t="s">
         <v>63</v>
       </c>
-      <c r="H115" t="s">
+      <c r="H115" s="1" t="s">
         <v>12</v>
       </c>
     </row>
     <row r="116" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A116" t="s">
+      <c r="A116" s="1" t="s">
         <v>448</v>
       </c>
-      <c r="C116" t="s">
+      <c r="C116" s="1" t="s">
         <v>76</v>
       </c>
-      <c r="D116" t="s">
+      <c r="D116" s="1" t="s">
         <v>449</v>
       </c>
-      <c r="E116" t="s">
+      <c r="E116" s="1" t="s">
         <v>62</v>
       </c>
-      <c r="F116" t="s">
-        <v>7</v>
-      </c>
-      <c r="G116" t="s">
+      <c r="F116" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="G116" s="1" t="s">
         <v>450</v>
       </c>
-      <c r="H116" t="s">
+      <c r="H116" s="1" t="s">
         <v>12</v>
       </c>
     </row>
     <row r="117" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A117" t="s">
+      <c r="A117" s="1" t="s">
         <v>451</v>
       </c>
-      <c r="C117" t="s">
+      <c r="C117" s="1" t="s">
         <v>50</v>
       </c>
-      <c r="D117" t="s">
+      <c r="D117" s="1" t="s">
         <v>452</v>
       </c>
-      <c r="E117" t="s">
+      <c r="E117" s="1" t="s">
         <v>453</v>
       </c>
-      <c r="F117" t="s">
+      <c r="F117" s="1" t="s">
         <v>454</v>
       </c>
-      <c r="G117" t="s">
+      <c r="G117" s="1" t="s">
         <v>455</v>
       </c>
-      <c r="H117" t="s">
+      <c r="H117" s="1" t="s">
         <v>12</v>
       </c>
     </row>
     <row r="118" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A118" t="s">
+      <c r="A118" s="1" t="s">
         <v>456</v>
       </c>
-      <c r="C118" t="s">
+      <c r="C118" s="1" t="s">
         <v>131</v>
       </c>
-      <c r="D118" t="s">
+      <c r="D118" s="1" t="s">
         <v>457</v>
       </c>
-      <c r="E118" t="s">
+      <c r="E118" s="1" t="s">
         <v>335</v>
       </c>
-      <c r="F118" t="s">
+      <c r="F118" s="1" t="s">
         <v>336</v>
       </c>
-      <c r="G118" t="s">
+      <c r="G118" s="1" t="s">
         <v>458</v>
       </c>
-      <c r="H118" t="s">
+      <c r="H118" s="1" t="s">
         <v>12</v>
       </c>
     </row>
     <row r="119" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A119" t="s">
+      <c r="A119" s="1" t="s">
         <v>459</v>
       </c>
-      <c r="C119" t="s">
+      <c r="C119" s="1" t="s">
         <v>31</v>
       </c>
-      <c r="D119" t="s">
+      <c r="D119" s="1" t="s">
         <v>460</v>
       </c>
-      <c r="E119" t="s">
+      <c r="E119" s="1" t="s">
         <v>77</v>
       </c>
-      <c r="F119" t="s">
-        <v>7</v>
-      </c>
-      <c r="G119" t="s">
+      <c r="F119" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="G119" s="1" t="s">
         <v>461</v>
       </c>
-      <c r="H119" t="s">
+      <c r="H119" s="1" t="s">
         <v>12</v>
       </c>
     </row>
     <row r="120" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A120" t="s">
+      <c r="A120" s="1" t="s">
         <v>462</v>
       </c>
-      <c r="C120" t="s">
+      <c r="C120" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="D120" t="s">
+      <c r="D120" s="1" t="s">
         <v>463</v>
       </c>
-      <c r="E120" t="s">
+      <c r="E120" s="1" t="s">
         <v>18</v>
       </c>
-      <c r="F120" t="s">
-        <v>7</v>
-      </c>
-      <c r="G120" t="s">
+      <c r="F120" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="G120" s="1" t="s">
         <v>464</v>
       </c>
-      <c r="H120" t="s">
+      <c r="H120" s="1" t="s">
         <v>12</v>
       </c>
     </row>
     <row r="121" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A121" t="s">
+      <c r="A121" s="1" t="s">
         <v>465</v>
       </c>
-      <c r="C121" t="s">
+      <c r="C121" s="1" t="s">
         <v>76</v>
       </c>
-      <c r="D121" t="s">
+      <c r="D121" s="1" t="s">
         <v>466</v>
       </c>
-      <c r="E121" t="s">
+      <c r="E121" s="1" t="s">
         <v>34</v>
       </c>
-      <c r="F121" t="s">
-        <v>7</v>
-      </c>
-      <c r="G121" t="s">
+      <c r="F121" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="G121" s="1" t="s">
         <v>467</v>
       </c>
-      <c r="H121" t="s">
+      <c r="H121" s="1" t="s">
         <v>12</v>
       </c>
     </row>
     <row r="122" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A122" t="s">
+      <c r="A122" s="1" t="s">
         <v>468</v>
       </c>
-      <c r="C122" t="s">
+      <c r="C122" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="D122" s="1" t="s">
+        <v>469</v>
+      </c>
+      <c r="E122" s="1" t="s">
+        <v>96</v>
+      </c>
+      <c r="F122" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="G122" s="1" t="s">
+        <v>97</v>
+      </c>
+      <c r="H122" s="1" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="123" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A123" s="1" t="s">
+        <v>470</v>
+      </c>
+      <c r="C123" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="D123" s="1" t="s">
+        <v>471</v>
+      </c>
+      <c r="E123" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="F123" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="G123" s="1" t="s">
+        <v>472</v>
+      </c>
+      <c r="H123" s="1" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="124" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A124" s="1" t="s">
+        <v>473</v>
+      </c>
+      <c r="C124" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="D124" s="1" t="s">
+        <v>471</v>
+      </c>
+      <c r="E124" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="F124" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="G124" s="1" t="s">
+        <v>472</v>
+      </c>
+      <c r="H124" s="1" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="125" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A125" s="1" t="s">
+        <v>474</v>
+      </c>
+      <c r="C125" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="D125" s="1" t="s">
+        <v>475</v>
+      </c>
+      <c r="E125" s="1" t="s">
+        <v>59</v>
+      </c>
+      <c r="F125" s="1" t="s">
+        <v>60</v>
+      </c>
+      <c r="G125" s="1" t="s">
+        <v>172</v>
+      </c>
+      <c r="H125" s="1" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="126" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A126" s="1" t="s">
+        <v>476</v>
+      </c>
+      <c r="C126" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="D126" s="1" t="s">
+        <v>477</v>
+      </c>
+      <c r="E126" s="1" t="s">
+        <v>203</v>
+      </c>
+      <c r="F126" s="1" t="s">
+        <v>204</v>
+      </c>
+      <c r="G126" s="1" t="s">
+        <v>478</v>
+      </c>
+      <c r="H126" s="1" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="127" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A127" s="1" t="s">
+        <v>479</v>
+      </c>
+      <c r="C127" s="1" t="s">
+        <v>131</v>
+      </c>
+      <c r="D127" s="1" t="s">
+        <v>480</v>
+      </c>
+      <c r="E127" s="1" t="s">
+        <v>481</v>
+      </c>
+      <c r="F127" s="1" t="s">
+        <v>482</v>
+      </c>
+      <c r="G127" s="1" t="s">
+        <v>483</v>
+      </c>
+      <c r="H127" s="1" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="128" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A128" s="1" t="s">
+        <v>484</v>
+      </c>
+      <c r="C128" s="1" t="s">
+        <v>131</v>
+      </c>
+      <c r="D128" s="1" t="s">
+        <v>480</v>
+      </c>
+      <c r="E128" s="1" t="s">
+        <v>481</v>
+      </c>
+      <c r="F128" s="1" t="s">
+        <v>482</v>
+      </c>
+      <c r="G128" s="1" t="s">
+        <v>483</v>
+      </c>
+      <c r="H128" s="1" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="129" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A129" s="1" t="s">
+        <v>485</v>
+      </c>
+      <c r="C129" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="D129" s="1" t="s">
+        <v>486</v>
+      </c>
+      <c r="E129" s="1" t="s">
+        <v>487</v>
+      </c>
+      <c r="F129" s="1" t="s">
+        <v>488</v>
+      </c>
+      <c r="G129" s="1" t="s">
+        <v>489</v>
+      </c>
+      <c r="H129" s="1" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="130" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A130" s="1" t="s">
+        <v>490</v>
+      </c>
+      <c r="C130" s="1" t="s">
         <v>29</v>
       </c>
-      <c r="D122" t="s">
-        <v>469</v>
-      </c>
-      <c r="E122" t="s">
-        <v>157</v>
-      </c>
-      <c r="F122" t="s">
-        <v>158</v>
-      </c>
-      <c r="G122" t="s">
-        <v>470</v>
-      </c>
-      <c r="H122" t="s">
+      <c r="D130" s="1" t="s">
+        <v>491</v>
+      </c>
+      <c r="E130" s="1" t="s">
+        <v>492</v>
+      </c>
+      <c r="F130" s="1" t="s">
+        <v>493</v>
+      </c>
+      <c r="G130" s="1" t="s">
+        <v>494</v>
+      </c>
+      <c r="H130" s="1" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="123" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A123" t="s">
-        <v>471</v>
-      </c>
-      <c r="C123" t="s">
-        <v>31</v>
-      </c>
-      <c r="D123" t="s">
-        <v>472</v>
-      </c>
-      <c r="E123" t="s">
-        <v>473</v>
-      </c>
-      <c r="F123" t="s">
-        <v>7</v>
-      </c>
-      <c r="G123" t="s">
-        <v>474</v>
-      </c>
-      <c r="H123" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="124" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A124" t="s">
-        <v>475</v>
-      </c>
-      <c r="C124" t="s">
-        <v>31</v>
-      </c>
-      <c r="D124" t="s">
-        <v>476</v>
-      </c>
-      <c r="E124" t="s">
-        <v>96</v>
-      </c>
-      <c r="F124" t="s">
-        <v>7</v>
-      </c>
-      <c r="G124" t="s">
-        <v>97</v>
-      </c>
-      <c r="H124" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="125" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A125" t="s">
-        <v>477</v>
-      </c>
-      <c r="C125" t="s">
-        <v>23</v>
-      </c>
-      <c r="D125" t="s">
-        <v>478</v>
-      </c>
-      <c r="E125" t="s">
-        <v>14</v>
-      </c>
-      <c r="F125" t="s">
-        <v>15</v>
-      </c>
-      <c r="G125" t="s">
-        <v>479</v>
-      </c>
-      <c r="H125" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="126" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A126" t="s">
-        <v>480</v>
-      </c>
-      <c r="C126" t="s">
-        <v>23</v>
-      </c>
-      <c r="D126" t="s">
-        <v>478</v>
-      </c>
-      <c r="E126" t="s">
-        <v>14</v>
-      </c>
-      <c r="F126" t="s">
-        <v>15</v>
-      </c>
-      <c r="G126" t="s">
-        <v>479</v>
-      </c>
-      <c r="H126" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="127" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A127" t="s">
-        <v>481</v>
-      </c>
-      <c r="C127" t="s">
+    <row r="131" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A131" s="1" t="s">
+        <v>495</v>
+      </c>
+      <c r="C131" s="1" t="s">
         <v>50</v>
       </c>
-      <c r="D127" t="s">
-        <v>482</v>
-      </c>
-      <c r="E127" t="s">
-        <v>59</v>
-      </c>
-      <c r="F127" t="s">
-        <v>60</v>
-      </c>
-      <c r="G127" t="s">
-        <v>172</v>
-      </c>
-      <c r="H127" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="128" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A128" t="s">
-        <v>483</v>
-      </c>
-      <c r="C128" t="s">
-        <v>21</v>
-      </c>
-      <c r="D128" t="s">
-        <v>484</v>
-      </c>
-      <c r="E128" t="s">
-        <v>203</v>
-      </c>
-      <c r="F128" t="s">
-        <v>204</v>
-      </c>
-      <c r="G128" t="s">
-        <v>485</v>
-      </c>
-      <c r="H128" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="129" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A129" t="s">
-        <v>486</v>
-      </c>
-      <c r="C129" t="s">
+      <c r="D131" s="1" t="s">
+        <v>496</v>
+      </c>
+      <c r="E131" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="F131" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="G131" s="1" t="s">
+        <v>497</v>
+      </c>
+      <c r="H131" s="1" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="132" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A132" s="1" t="s">
+        <v>498</v>
+      </c>
+      <c r="C132" s="1" t="s">
         <v>131</v>
       </c>
-      <c r="D129" t="s">
-        <v>487</v>
-      </c>
-      <c r="E129" t="s">
-        <v>488</v>
-      </c>
-      <c r="F129" t="s">
-        <v>489</v>
-      </c>
-      <c r="G129" t="s">
-        <v>490</v>
-      </c>
-      <c r="H129" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="130" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A130" t="s">
-        <v>491</v>
-      </c>
-      <c r="C130" t="s">
-        <v>131</v>
-      </c>
-      <c r="D130" t="s">
-        <v>487</v>
-      </c>
-      <c r="E130" t="s">
-        <v>488</v>
-      </c>
-      <c r="F130" t="s">
-        <v>489</v>
-      </c>
-      <c r="G130" t="s">
-        <v>490</v>
-      </c>
-      <c r="H130" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="131" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A131" t="s">
-        <v>492</v>
-      </c>
-      <c r="C131" t="s">
-        <v>50</v>
-      </c>
-      <c r="D131" t="s">
-        <v>493</v>
-      </c>
-      <c r="E131" t="s">
-        <v>494</v>
-      </c>
-      <c r="F131" t="s">
-        <v>495</v>
-      </c>
-      <c r="G131" t="s">
-        <v>496</v>
-      </c>
-      <c r="H131" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="132" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A132" t="s">
-        <v>497</v>
-      </c>
-      <c r="C132" t="s">
-        <v>29</v>
-      </c>
-      <c r="D132" t="s">
-        <v>498</v>
-      </c>
-      <c r="E132" t="s">
+      <c r="D132" s="1" t="s">
         <v>499</v>
       </c>
-      <c r="F132" t="s">
+      <c r="E132" s="1" t="s">
         <v>500</v>
       </c>
-      <c r="G132" t="s">
+      <c r="F132" s="1" t="s">
         <v>501</v>
       </c>
-      <c r="H132" t="s">
-        <v>12</v>
+      <c r="G132" s="1" t="s">
+        <v>502</v>
+      </c>
+      <c r="H132" s="1" t="s">
+        <v>30</v>
       </c>
     </row>
     <row r="133" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A133" t="s">
-        <v>502</v>
-      </c>
-      <c r="C133" t="s">
-        <v>50</v>
-      </c>
-      <c r="D133" t="s">
+      <c r="A133" s="1" t="s">
         <v>503</v>
       </c>
-      <c r="E133" t="s">
-        <v>26</v>
-      </c>
-      <c r="F133" t="s">
-        <v>27</v>
-      </c>
-      <c r="G133" t="s">
+      <c r="C133" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="D133" s="1" t="s">
         <v>504</v>
       </c>
-      <c r="H133" t="s">
-        <v>30</v>
+      <c r="E133" s="1" t="s">
+        <v>505</v>
+      </c>
+      <c r="F133" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="G133" s="1" t="s">
+        <v>506</v>
+      </c>
+      <c r="H133" s="1" t="s">
+        <v>507</v>
       </c>
     </row>
     <row r="134" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A134" t="s">
-        <v>505</v>
-      </c>
-      <c r="C134" t="s">
-        <v>131</v>
-      </c>
-      <c r="D134" t="s">
-        <v>506</v>
-      </c>
-      <c r="E134" t="s">
-        <v>507</v>
-      </c>
-      <c r="F134" t="s">
-        <v>508</v>
-      </c>
-      <c r="G134" t="s">
-        <v>509</v>
-      </c>
-      <c r="H134" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="135" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A135" t="s">
-        <v>510</v>
-      </c>
-      <c r="C135" t="s">
-        <v>28</v>
-      </c>
-      <c r="D135" t="s">
-        <v>511</v>
-      </c>
-      <c r="E135" t="s">
-        <v>512</v>
-      </c>
-      <c r="F135" t="s">
-        <v>7</v>
-      </c>
-      <c r="G135" t="s">
-        <v>513</v>
-      </c>
-      <c r="H135" t="s">
-        <v>514</v>
+      <c r="A134" s="1">
+        <v>267004008</v>
+      </c>
+      <c r="C134" s="1" t="s">
+        <v>76</v>
+      </c>
+      <c r="D134" s="1">
+        <v>267004008</v>
+      </c>
+      <c r="H134" s="1" t="s">
+        <v>49</v>
       </c>
     </row>
   </sheetData>

--- a/1.xlsx
+++ b/1.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="\\wh.local\fs\UserProfile_TSSWH19\_TSSWH19_redirected_folders\HunyaCs1\Desktop\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9BEC1ACE-114A-414F-8A02-E21CF5EAE16D}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D46C736C-AA45-42BA-BDBC-CB327730ED3A}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="0" windowWidth="22260" windowHeight="12648" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="868" uniqueCount="462">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="858" uniqueCount="455">
   <si>
     <t>IRSZ</t>
   </si>
@@ -81,9 +81,6 @@
     <t>1173</t>
   </si>
   <si>
-    <t>SZ-829</t>
-  </si>
-  <si>
     <t>SZ-809</t>
   </si>
   <si>
@@ -234,9 +231,6 @@
     <t>Pusztakúti út</t>
   </si>
   <si>
-    <t>1107</t>
-  </si>
-  <si>
     <t>1172</t>
   </si>
   <si>
@@ -1320,27 +1314,6 @@
     <t>Telepes utca</t>
   </si>
   <si>
-    <t>NFD6-03-20-8NVZ-1</t>
-  </si>
-  <si>
-    <t>NFD6-03-20-8NVZ</t>
-  </si>
-  <si>
-    <t>1181</t>
-  </si>
-  <si>
-    <t>Darus utca</t>
-  </si>
-  <si>
-    <t>NFD6-03-20-LWT7-1</t>
-  </si>
-  <si>
-    <t>NFD6-03-20-LWT7</t>
-  </si>
-  <si>
-    <t>Makk utca</t>
-  </si>
-  <si>
     <t>202603202600673301</t>
   </si>
   <si>
@@ -1414,6 +1387,12 @@
   </si>
   <si>
     <t>159995579538415531</t>
+  </si>
+  <si>
+    <t>NFD6-03-19-J6L3</t>
+  </si>
+  <si>
+    <t>AUCHAN_ÁRUHÁZI</t>
   </si>
 </sst>
 </file>
@@ -1732,7 +1711,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <sheetPr codeName="Munka1"/>
-  <dimension ref="A1:H124"/>
+  <dimension ref="A1:H123"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="24.88671875" bestFit="1" customWidth="1"/>
@@ -1770,114 +1749,114 @@
     </row>
     <row r="2" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
+        <v>88</v>
+      </c>
+      <c r="C2" t="s">
+        <v>21</v>
+      </c>
+      <c r="D2" t="s">
+        <v>89</v>
+      </c>
+      <c r="E2" t="s">
+        <v>61</v>
+      </c>
+      <c r="F2" t="s">
+        <v>7</v>
+      </c>
+      <c r="G2" t="s">
         <v>90</v>
       </c>
-      <c r="C2" t="s">
-        <v>22</v>
-      </c>
-      <c r="D2" t="s">
+      <c r="H2" t="s">
         <v>91</v>
-      </c>
-      <c r="E2" t="s">
-        <v>62</v>
-      </c>
-      <c r="F2" t="s">
-        <v>7</v>
-      </c>
-      <c r="G2" t="s">
-        <v>92</v>
-      </c>
-      <c r="H2" t="s">
-        <v>93</v>
       </c>
     </row>
     <row r="3" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
+        <v>92</v>
+      </c>
+      <c r="C3" t="s">
+        <v>22</v>
+      </c>
+      <c r="D3" t="s">
+        <v>93</v>
+      </c>
+      <c r="E3" t="s">
+        <v>73</v>
+      </c>
+      <c r="F3" t="s">
+        <v>74</v>
+      </c>
+      <c r="G3" t="s">
         <v>94</v>
       </c>
-      <c r="C3" t="s">
-        <v>23</v>
-      </c>
-      <c r="D3" t="s">
-        <v>95</v>
-      </c>
-      <c r="E3" t="s">
-        <v>75</v>
-      </c>
-      <c r="F3" t="s">
-        <v>76</v>
-      </c>
-      <c r="G3" t="s">
-        <v>96</v>
-      </c>
       <c r="H3" t="s">
-        <v>93</v>
+        <v>91</v>
       </c>
     </row>
     <row r="4" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
+        <v>95</v>
+      </c>
+      <c r="C4" t="s">
+        <v>20</v>
+      </c>
+      <c r="D4" t="s">
+        <v>96</v>
+      </c>
+      <c r="E4" t="s">
         <v>97</v>
       </c>
-      <c r="C4" t="s">
-        <v>21</v>
-      </c>
-      <c r="D4" t="s">
+      <c r="F4" t="s">
         <v>98</v>
       </c>
-      <c r="E4" t="s">
+      <c r="G4" t="s">
         <v>99</v>
       </c>
-      <c r="F4" t="s">
-        <v>100</v>
-      </c>
-      <c r="G4" t="s">
-        <v>101</v>
-      </c>
       <c r="H4" t="s">
-        <v>93</v>
+        <v>91</v>
       </c>
     </row>
     <row r="5" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
-        <v>102</v>
+        <v>100</v>
       </c>
       <c r="C5" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="D5" t="s">
+        <v>96</v>
+      </c>
+      <c r="E5" t="s">
+        <v>97</v>
+      </c>
+      <c r="F5" t="s">
         <v>98</v>
       </c>
-      <c r="E5" t="s">
+      <c r="G5" t="s">
         <v>99</v>
       </c>
-      <c r="F5" t="s">
-        <v>100</v>
-      </c>
-      <c r="G5" t="s">
-        <v>101</v>
-      </c>
       <c r="H5" t="s">
-        <v>93</v>
+        <v>91</v>
       </c>
     </row>
     <row r="6" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
+        <v>101</v>
+      </c>
+      <c r="C6" t="s">
+        <v>29</v>
+      </c>
+      <c r="D6" t="s">
+        <v>102</v>
+      </c>
+      <c r="E6" t="s">
+        <v>69</v>
+      </c>
+      <c r="F6" t="s">
+        <v>70</v>
+      </c>
+      <c r="G6" t="s">
         <v>103</v>
-      </c>
-      <c r="C6" t="s">
-        <v>30</v>
-      </c>
-      <c r="D6" t="s">
-        <v>104</v>
-      </c>
-      <c r="E6" t="s">
-        <v>71</v>
-      </c>
-      <c r="F6" t="s">
-        <v>72</v>
-      </c>
-      <c r="G6" t="s">
-        <v>105</v>
       </c>
       <c r="H6" t="s">
         <v>8</v>
@@ -1885,22 +1864,22 @@
     </row>
     <row r="7" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
+        <v>104</v>
+      </c>
+      <c r="C7" t="s">
+        <v>22</v>
+      </c>
+      <c r="D7" t="s">
+        <v>105</v>
+      </c>
+      <c r="E7" t="s">
         <v>106</v>
       </c>
-      <c r="C7" t="s">
-        <v>23</v>
-      </c>
-      <c r="D7" t="s">
+      <c r="F7" t="s">
         <v>107</v>
       </c>
-      <c r="E7" t="s">
+      <c r="G7" t="s">
         <v>108</v>
-      </c>
-      <c r="F7" t="s">
-        <v>109</v>
-      </c>
-      <c r="G7" t="s">
-        <v>110</v>
       </c>
       <c r="H7" t="s">
         <v>8</v>
@@ -1908,22 +1887,22 @@
     </row>
     <row r="8" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="C8" t="s">
         <v>9</v>
       </c>
       <c r="D8" t="s">
+        <v>110</v>
+      </c>
+      <c r="E8" t="s">
+        <v>111</v>
+      </c>
+      <c r="F8" t="s">
         <v>112</v>
       </c>
-      <c r="E8" t="s">
+      <c r="G8" t="s">
         <v>113</v>
-      </c>
-      <c r="F8" t="s">
-        <v>114</v>
-      </c>
-      <c r="G8" t="s">
-        <v>115</v>
       </c>
       <c r="H8" t="s">
         <v>8</v>
@@ -1931,22 +1910,22 @@
     </row>
     <row r="9" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
+        <v>114</v>
+      </c>
+      <c r="C9" t="s">
+        <v>29</v>
+      </c>
+      <c r="D9" t="s">
+        <v>115</v>
+      </c>
+      <c r="E9" t="s">
         <v>116</v>
       </c>
-      <c r="C9" t="s">
-        <v>30</v>
-      </c>
-      <c r="D9" t="s">
+      <c r="F9" t="s">
         <v>117</v>
       </c>
-      <c r="E9" t="s">
+      <c r="G9" t="s">
         <v>118</v>
-      </c>
-      <c r="F9" t="s">
-        <v>119</v>
-      </c>
-      <c r="G9" t="s">
-        <v>120</v>
       </c>
       <c r="H9" t="s">
         <v>8</v>
@@ -1954,22 +1933,22 @@
     </row>
     <row r="10" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
-        <v>121</v>
+        <v>119</v>
       </c>
       <c r="C10" t="s">
         <v>10</v>
       </c>
       <c r="D10" t="s">
+        <v>120</v>
+      </c>
+      <c r="E10" t="s">
+        <v>121</v>
+      </c>
+      <c r="F10" t="s">
         <v>122</v>
       </c>
-      <c r="E10" t="s">
+      <c r="G10" t="s">
         <v>123</v>
-      </c>
-      <c r="F10" t="s">
-        <v>124</v>
-      </c>
-      <c r="G10" t="s">
-        <v>125</v>
       </c>
       <c r="H10" t="s">
         <v>8</v>
@@ -1977,22 +1956,22 @@
     </row>
     <row r="11" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A11" t="s">
+        <v>124</v>
+      </c>
+      <c r="C11" t="s">
+        <v>125</v>
+      </c>
+      <c r="D11" t="s">
         <v>126</v>
       </c>
-      <c r="C11" t="s">
+      <c r="E11" t="s">
+        <v>36</v>
+      </c>
+      <c r="F11" t="s">
+        <v>37</v>
+      </c>
+      <c r="G11" t="s">
         <v>127</v>
-      </c>
-      <c r="D11" t="s">
-        <v>128</v>
-      </c>
-      <c r="E11" t="s">
-        <v>37</v>
-      </c>
-      <c r="F11" t="s">
-        <v>38</v>
-      </c>
-      <c r="G11" t="s">
-        <v>129</v>
       </c>
       <c r="H11" t="s">
         <v>8</v>
@@ -2000,22 +1979,22 @@
     </row>
     <row r="12" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A12" t="s">
-        <v>130</v>
+        <v>128</v>
       </c>
       <c r="C12" t="s">
         <v>9</v>
       </c>
       <c r="D12" t="s">
+        <v>129</v>
+      </c>
+      <c r="E12" t="s">
+        <v>130</v>
+      </c>
+      <c r="F12" t="s">
         <v>131</v>
       </c>
-      <c r="E12" t="s">
+      <c r="G12" t="s">
         <v>132</v>
-      </c>
-      <c r="F12" t="s">
-        <v>133</v>
-      </c>
-      <c r="G12" t="s">
-        <v>134</v>
       </c>
       <c r="H12" t="s">
         <v>8</v>
@@ -2023,22 +2002,22 @@
     </row>
     <row r="13" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A13" t="s">
+        <v>133</v>
+      </c>
+      <c r="C13" t="s">
+        <v>21</v>
+      </c>
+      <c r="D13" t="s">
+        <v>134</v>
+      </c>
+      <c r="E13" t="s">
         <v>135</v>
       </c>
-      <c r="C13" t="s">
-        <v>22</v>
-      </c>
-      <c r="D13" t="s">
+      <c r="F13" t="s">
+        <v>7</v>
+      </c>
+      <c r="G13" t="s">
         <v>136</v>
-      </c>
-      <c r="E13" t="s">
-        <v>137</v>
-      </c>
-      <c r="F13" t="s">
-        <v>7</v>
-      </c>
-      <c r="G13" t="s">
-        <v>138</v>
       </c>
       <c r="H13" t="s">
         <v>8</v>
@@ -2046,22 +2025,22 @@
     </row>
     <row r="14" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A14" t="s">
+        <v>137</v>
+      </c>
+      <c r="C14" t="s">
+        <v>63</v>
+      </c>
+      <c r="D14" t="s">
+        <v>138</v>
+      </c>
+      <c r="E14" t="s">
         <v>139</v>
       </c>
-      <c r="C14" t="s">
-        <v>64</v>
-      </c>
-      <c r="D14" t="s">
+      <c r="F14" t="s">
         <v>140</v>
       </c>
-      <c r="E14" t="s">
+      <c r="G14" t="s">
         <v>141</v>
-      </c>
-      <c r="F14" t="s">
-        <v>142</v>
-      </c>
-      <c r="G14" t="s">
-        <v>143</v>
       </c>
       <c r="H14" t="s">
         <v>8</v>
@@ -2069,22 +2048,22 @@
     </row>
     <row r="15" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A15" t="s">
-        <v>144</v>
+        <v>142</v>
       </c>
       <c r="C15" t="s">
         <v>13</v>
       </c>
       <c r="D15" t="s">
-        <v>145</v>
+        <v>143</v>
       </c>
       <c r="E15" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="F15" t="s">
         <v>7</v>
       </c>
       <c r="G15" t="s">
-        <v>146</v>
+        <v>144</v>
       </c>
       <c r="H15" t="s">
         <v>8</v>
@@ -2092,22 +2071,22 @@
     </row>
     <row r="16" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A16" t="s">
+        <v>145</v>
+      </c>
+      <c r="C16" t="s">
+        <v>25</v>
+      </c>
+      <c r="D16" t="s">
+        <v>146</v>
+      </c>
+      <c r="E16" t="s">
         <v>147</v>
       </c>
-      <c r="C16" t="s">
-        <v>26</v>
-      </c>
-      <c r="D16" t="s">
+      <c r="F16" t="s">
+        <v>7</v>
+      </c>
+      <c r="G16" t="s">
         <v>148</v>
-      </c>
-      <c r="E16" t="s">
-        <v>149</v>
-      </c>
-      <c r="F16" t="s">
-        <v>7</v>
-      </c>
-      <c r="G16" t="s">
-        <v>150</v>
       </c>
       <c r="H16" t="s">
         <v>8</v>
@@ -2115,22 +2094,22 @@
     </row>
     <row r="17" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A17" t="s">
+        <v>149</v>
+      </c>
+      <c r="C17" t="s">
+        <v>21</v>
+      </c>
+      <c r="D17" t="s">
+        <v>150</v>
+      </c>
+      <c r="E17" t="s">
         <v>151</v>
       </c>
-      <c r="C17" t="s">
-        <v>22</v>
-      </c>
-      <c r="D17" t="s">
+      <c r="F17" t="s">
         <v>152</v>
       </c>
-      <c r="E17" t="s">
-        <v>153</v>
-      </c>
-      <c r="F17" t="s">
-        <v>154</v>
-      </c>
       <c r="G17" t="s">
-        <v>88</v>
+        <v>86</v>
       </c>
       <c r="H17" t="s">
         <v>8</v>
@@ -2138,22 +2117,22 @@
     </row>
     <row r="18" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A18" t="s">
+        <v>153</v>
+      </c>
+      <c r="C18" t="s">
+        <v>29</v>
+      </c>
+      <c r="D18" t="s">
+        <v>154</v>
+      </c>
+      <c r="E18" t="s">
+        <v>69</v>
+      </c>
+      <c r="F18" t="s">
+        <v>70</v>
+      </c>
+      <c r="G18" t="s">
         <v>155</v>
-      </c>
-      <c r="C18" t="s">
-        <v>30</v>
-      </c>
-      <c r="D18" t="s">
-        <v>156</v>
-      </c>
-      <c r="E18" t="s">
-        <v>71</v>
-      </c>
-      <c r="F18" t="s">
-        <v>72</v>
-      </c>
-      <c r="G18" t="s">
-        <v>157</v>
       </c>
       <c r="H18" t="s">
         <v>8</v>
@@ -2161,22 +2140,22 @@
     </row>
     <row r="19" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A19" t="s">
+        <v>156</v>
+      </c>
+      <c r="C19" t="s">
+        <v>125</v>
+      </c>
+      <c r="D19" t="s">
+        <v>157</v>
+      </c>
+      <c r="E19" t="s">
+        <v>36</v>
+      </c>
+      <c r="F19" t="s">
+        <v>37</v>
+      </c>
+      <c r="G19" t="s">
         <v>158</v>
-      </c>
-      <c r="C19" t="s">
-        <v>127</v>
-      </c>
-      <c r="D19" t="s">
-        <v>159</v>
-      </c>
-      <c r="E19" t="s">
-        <v>37</v>
-      </c>
-      <c r="F19" t="s">
-        <v>38</v>
-      </c>
-      <c r="G19" t="s">
-        <v>160</v>
       </c>
       <c r="H19" t="s">
         <v>8</v>
@@ -2184,22 +2163,22 @@
     </row>
     <row r="20" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A20" t="s">
-        <v>161</v>
+        <v>159</v>
       </c>
       <c r="C20" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="D20" t="s">
-        <v>162</v>
+        <v>160</v>
       </c>
       <c r="E20" t="s">
+        <v>42</v>
+      </c>
+      <c r="F20" t="s">
         <v>43</v>
       </c>
-      <c r="F20" t="s">
-        <v>44</v>
-      </c>
       <c r="G20" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="H20" t="s">
         <v>8</v>
@@ -2207,22 +2186,22 @@
     </row>
     <row r="21" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A21" t="s">
+        <v>161</v>
+      </c>
+      <c r="C21" t="s">
+        <v>48</v>
+      </c>
+      <c r="D21" t="s">
+        <v>162</v>
+      </c>
+      <c r="E21" t="s">
+        <v>28</v>
+      </c>
+      <c r="F21" t="s">
+        <v>7</v>
+      </c>
+      <c r="G21" t="s">
         <v>163</v>
-      </c>
-      <c r="C21" t="s">
-        <v>49</v>
-      </c>
-      <c r="D21" t="s">
-        <v>164</v>
-      </c>
-      <c r="E21" t="s">
-        <v>29</v>
-      </c>
-      <c r="F21" t="s">
-        <v>7</v>
-      </c>
-      <c r="G21" t="s">
-        <v>165</v>
       </c>
       <c r="H21" t="s">
         <v>8</v>
@@ -2230,22 +2209,22 @@
     </row>
     <row r="22" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A22" t="s">
-        <v>166</v>
+        <v>164</v>
       </c>
       <c r="C22" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="D22" t="s">
-        <v>164</v>
+        <v>162</v>
       </c>
       <c r="E22" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="F22" t="s">
         <v>7</v>
       </c>
       <c r="G22" t="s">
-        <v>165</v>
+        <v>163</v>
       </c>
       <c r="H22" t="s">
         <v>8</v>
@@ -2253,22 +2232,22 @@
     </row>
     <row r="23" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A23" t="s">
+        <v>165</v>
+      </c>
+      <c r="C23" t="s">
+        <v>18</v>
+      </c>
+      <c r="D23" t="s">
+        <v>166</v>
+      </c>
+      <c r="E23" t="s">
+        <v>49</v>
+      </c>
+      <c r="F23" t="s">
+        <v>7</v>
+      </c>
+      <c r="G23" t="s">
         <v>167</v>
-      </c>
-      <c r="C23" t="s">
-        <v>19</v>
-      </c>
-      <c r="D23" t="s">
-        <v>168</v>
-      </c>
-      <c r="E23" t="s">
-        <v>50</v>
-      </c>
-      <c r="F23" t="s">
-        <v>7</v>
-      </c>
-      <c r="G23" t="s">
-        <v>169</v>
       </c>
       <c r="H23" t="s">
         <v>8</v>
@@ -2276,22 +2255,22 @@
     </row>
     <row r="24" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A24" t="s">
-        <v>170</v>
+        <v>168</v>
       </c>
       <c r="C24" t="s">
-        <v>127</v>
+        <v>125</v>
       </c>
       <c r="D24" t="s">
-        <v>171</v>
+        <v>169</v>
       </c>
       <c r="E24" t="s">
+        <v>36</v>
+      </c>
+      <c r="F24" t="s">
         <v>37</v>
       </c>
-      <c r="F24" t="s">
-        <v>38</v>
-      </c>
       <c r="G24" t="s">
-        <v>77</v>
+        <v>75</v>
       </c>
       <c r="H24" t="s">
         <v>8</v>
@@ -2299,22 +2278,22 @@
     </row>
     <row r="25" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A25" t="s">
+        <v>170</v>
+      </c>
+      <c r="C25" t="s">
+        <v>24</v>
+      </c>
+      <c r="D25" t="s">
+        <v>171</v>
+      </c>
+      <c r="E25" t="s">
         <v>172</v>
       </c>
-      <c r="C25" t="s">
-        <v>25</v>
-      </c>
-      <c r="D25" t="s">
+      <c r="F25" t="s">
+        <v>7</v>
+      </c>
+      <c r="G25" t="s">
         <v>173</v>
-      </c>
-      <c r="E25" t="s">
-        <v>174</v>
-      </c>
-      <c r="F25" t="s">
-        <v>7</v>
-      </c>
-      <c r="G25" t="s">
-        <v>175</v>
       </c>
       <c r="H25" t="s">
         <v>8</v>
@@ -2322,22 +2301,22 @@
     </row>
     <row r="26" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A26" t="s">
+        <v>174</v>
+      </c>
+      <c r="C26" t="s">
+        <v>18</v>
+      </c>
+      <c r="D26" t="s">
+        <v>175</v>
+      </c>
+      <c r="E26" t="s">
         <v>176</v>
       </c>
-      <c r="C26" t="s">
-        <v>19</v>
-      </c>
-      <c r="D26" t="s">
+      <c r="F26" t="s">
+        <v>7</v>
+      </c>
+      <c r="G26" t="s">
         <v>177</v>
-      </c>
-      <c r="E26" t="s">
-        <v>178</v>
-      </c>
-      <c r="F26" t="s">
-        <v>7</v>
-      </c>
-      <c r="G26" t="s">
-        <v>179</v>
       </c>
       <c r="H26" t="s">
         <v>8</v>
@@ -2345,22 +2324,22 @@
     </row>
     <row r="27" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A27" t="s">
+        <v>178</v>
+      </c>
+      <c r="C27" t="s">
+        <v>24</v>
+      </c>
+      <c r="D27" t="s">
+        <v>179</v>
+      </c>
+      <c r="E27" t="s">
+        <v>54</v>
+      </c>
+      <c r="F27" t="s">
+        <v>7</v>
+      </c>
+      <c r="G27" t="s">
         <v>180</v>
-      </c>
-      <c r="C27" t="s">
-        <v>25</v>
-      </c>
-      <c r="D27" t="s">
-        <v>181</v>
-      </c>
-      <c r="E27" t="s">
-        <v>55</v>
-      </c>
-      <c r="F27" t="s">
-        <v>7</v>
-      </c>
-      <c r="G27" t="s">
-        <v>182</v>
       </c>
       <c r="H27" t="s">
         <v>8</v>
@@ -2368,91 +2347,91 @@
     </row>
     <row r="28" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A28" t="s">
+        <v>181</v>
+      </c>
+      <c r="C28" t="s">
+        <v>21</v>
+      </c>
+      <c r="D28" t="s">
+        <v>182</v>
+      </c>
+      <c r="E28" t="s">
+        <v>61</v>
+      </c>
+      <c r="F28" t="s">
+        <v>7</v>
+      </c>
+      <c r="G28" t="s">
         <v>183</v>
       </c>
-      <c r="C28" t="s">
-        <v>22</v>
-      </c>
-      <c r="D28" t="s">
-        <v>184</v>
-      </c>
-      <c r="E28" t="s">
-        <v>62</v>
-      </c>
-      <c r="F28" t="s">
-        <v>7</v>
-      </c>
-      <c r="G28" t="s">
-        <v>185</v>
-      </c>
       <c r="H28" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
     </row>
     <row r="29" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A29" t="s">
+        <v>184</v>
+      </c>
+      <c r="C29" t="s">
+        <v>22</v>
+      </c>
+      <c r="D29" t="s">
+        <v>185</v>
+      </c>
+      <c r="E29" t="s">
         <v>186</v>
       </c>
-      <c r="C29" t="s">
-        <v>23</v>
-      </c>
-      <c r="D29" t="s">
+      <c r="F29" t="s">
         <v>187</v>
       </c>
-      <c r="E29" t="s">
+      <c r="G29" t="s">
         <v>188</v>
       </c>
-      <c r="F29" t="s">
-        <v>189</v>
-      </c>
-      <c r="G29" t="s">
-        <v>190</v>
-      </c>
       <c r="H29" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
     </row>
     <row r="30" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A30" t="s">
+        <v>189</v>
+      </c>
+      <c r="C30" t="s">
+        <v>26</v>
+      </c>
+      <c r="D30" t="s">
+        <v>190</v>
+      </c>
+      <c r="E30" t="s">
         <v>191</v>
       </c>
-      <c r="C30" t="s">
-        <v>27</v>
-      </c>
-      <c r="D30" t="s">
+      <c r="F30" t="s">
+        <v>7</v>
+      </c>
+      <c r="G30" t="s">
         <v>192</v>
       </c>
-      <c r="E30" t="s">
-        <v>193</v>
-      </c>
-      <c r="F30" t="s">
-        <v>7</v>
-      </c>
-      <c r="G30" t="s">
-        <v>194</v>
-      </c>
       <c r="H30" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
     </row>
     <row r="31" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A31" t="s">
+        <v>193</v>
+      </c>
+      <c r="C31" t="s">
+        <v>19</v>
+      </c>
+      <c r="D31" t="s">
+        <v>194</v>
+      </c>
+      <c r="E31" t="s">
         <v>195</v>
       </c>
-      <c r="C31" t="s">
-        <v>20</v>
-      </c>
-      <c r="D31" t="s">
+      <c r="F31" t="s">
         <v>196</v>
       </c>
-      <c r="E31" t="s">
+      <c r="G31" t="s">
         <v>197</v>
-      </c>
-      <c r="F31" t="s">
-        <v>198</v>
-      </c>
-      <c r="G31" t="s">
-        <v>199</v>
       </c>
       <c r="H31" t="s">
         <v>11</v>
@@ -2460,22 +2439,22 @@
     </row>
     <row r="32" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A32" t="s">
+        <v>198</v>
+      </c>
+      <c r="C32" t="s">
+        <v>48</v>
+      </c>
+      <c r="D32" t="s">
+        <v>199</v>
+      </c>
+      <c r="E32" t="s">
         <v>200</v>
       </c>
-      <c r="C32" t="s">
-        <v>49</v>
-      </c>
-      <c r="D32" t="s">
+      <c r="F32" t="s">
+        <v>7</v>
+      </c>
+      <c r="G32" t="s">
         <v>201</v>
-      </c>
-      <c r="E32" t="s">
-        <v>202</v>
-      </c>
-      <c r="F32" t="s">
-        <v>7</v>
-      </c>
-      <c r="G32" t="s">
-        <v>203</v>
       </c>
       <c r="H32" t="s">
         <v>11</v>
@@ -2483,22 +2462,22 @@
     </row>
     <row r="33" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A33" t="s">
-        <v>204</v>
+        <v>202</v>
       </c>
       <c r="C33" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="D33" t="s">
-        <v>205</v>
+        <v>203</v>
       </c>
       <c r="E33" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="F33" t="s">
         <v>7</v>
       </c>
       <c r="G33" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="H33" t="s">
         <v>11</v>
@@ -2506,22 +2485,22 @@
     </row>
     <row r="34" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A34" t="s">
+        <v>204</v>
+      </c>
+      <c r="C34" t="s">
+        <v>205</v>
+      </c>
+      <c r="D34" t="s">
         <v>206</v>
       </c>
-      <c r="C34" t="s">
-        <v>207</v>
-      </c>
-      <c r="D34" t="s">
-        <v>208</v>
-      </c>
       <c r="E34" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="F34" t="s">
         <v>7</v>
       </c>
       <c r="G34" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="H34" t="s">
         <v>11</v>
@@ -2529,22 +2508,22 @@
     </row>
     <row r="35" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A35" t="s">
-        <v>209</v>
+        <v>207</v>
       </c>
       <c r="C35" t="s">
-        <v>207</v>
+        <v>205</v>
       </c>
       <c r="D35" t="s">
-        <v>208</v>
+        <v>206</v>
       </c>
       <c r="E35" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="F35" t="s">
         <v>7</v>
       </c>
       <c r="G35" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="H35" t="s">
         <v>11</v>
@@ -2552,22 +2531,22 @@
     </row>
     <row r="36" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A36" t="s">
-        <v>210</v>
+        <v>208</v>
       </c>
       <c r="C36" t="s">
-        <v>207</v>
+        <v>205</v>
       </c>
       <c r="D36" t="s">
-        <v>208</v>
+        <v>206</v>
       </c>
       <c r="E36" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="F36" t="s">
         <v>7</v>
       </c>
       <c r="G36" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="H36" t="s">
         <v>11</v>
@@ -2575,13 +2554,13 @@
     </row>
     <row r="37" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A37" t="s">
-        <v>211</v>
+        <v>209</v>
       </c>
       <c r="C37" t="s">
-        <v>207</v>
+        <v>205</v>
       </c>
       <c r="D37" t="s">
-        <v>212</v>
+        <v>210</v>
       </c>
       <c r="E37" t="s">
         <v>14</v>
@@ -2590,7 +2569,7 @@
         <v>15</v>
       </c>
       <c r="G37" t="s">
-        <v>213</v>
+        <v>211</v>
       </c>
       <c r="H37" t="s">
         <v>11</v>
@@ -2598,22 +2577,22 @@
     </row>
     <row r="38" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A38" t="s">
+        <v>212</v>
+      </c>
+      <c r="C38" t="s">
+        <v>18</v>
+      </c>
+      <c r="D38" t="s">
+        <v>213</v>
+      </c>
+      <c r="E38" t="s">
         <v>214</v>
       </c>
-      <c r="C38" t="s">
-        <v>19</v>
-      </c>
-      <c r="D38" t="s">
+      <c r="F38" t="s">
+        <v>7</v>
+      </c>
+      <c r="G38" t="s">
         <v>215</v>
-      </c>
-      <c r="E38" t="s">
-        <v>216</v>
-      </c>
-      <c r="F38" t="s">
-        <v>7</v>
-      </c>
-      <c r="G38" t="s">
-        <v>217</v>
       </c>
       <c r="H38" t="s">
         <v>11</v>
@@ -2621,22 +2600,22 @@
     </row>
     <row r="39" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A39" t="s">
-        <v>218</v>
+        <v>216</v>
       </c>
       <c r="C39" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="D39" t="s">
+        <v>213</v>
+      </c>
+      <c r="E39" t="s">
+        <v>214</v>
+      </c>
+      <c r="F39" t="s">
+        <v>7</v>
+      </c>
+      <c r="G39" t="s">
         <v>215</v>
-      </c>
-      <c r="E39" t="s">
-        <v>216</v>
-      </c>
-      <c r="F39" t="s">
-        <v>7</v>
-      </c>
-      <c r="G39" t="s">
-        <v>217</v>
       </c>
       <c r="H39" t="s">
         <v>11</v>
@@ -2644,22 +2623,22 @@
     </row>
     <row r="40" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A40" t="s">
+        <v>217</v>
+      </c>
+      <c r="C40" t="s">
+        <v>25</v>
+      </c>
+      <c r="D40" t="s">
+        <v>218</v>
+      </c>
+      <c r="E40" t="s">
         <v>219</v>
       </c>
-      <c r="C40" t="s">
-        <v>26</v>
-      </c>
-      <c r="D40" t="s">
+      <c r="F40" t="s">
+        <v>7</v>
+      </c>
+      <c r="G40" t="s">
         <v>220</v>
-      </c>
-      <c r="E40" t="s">
-        <v>221</v>
-      </c>
-      <c r="F40" t="s">
-        <v>7</v>
-      </c>
-      <c r="G40" t="s">
-        <v>222</v>
       </c>
       <c r="H40" t="s">
         <v>11</v>
@@ -2667,22 +2646,22 @@
     </row>
     <row r="41" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A41" t="s">
-        <v>223</v>
+        <v>221</v>
       </c>
       <c r="C41" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="D41" t="s">
+        <v>218</v>
+      </c>
+      <c r="E41" t="s">
+        <v>219</v>
+      </c>
+      <c r="F41" t="s">
+        <v>7</v>
+      </c>
+      <c r="G41" t="s">
         <v>220</v>
-      </c>
-      <c r="E41" t="s">
-        <v>221</v>
-      </c>
-      <c r="F41" t="s">
-        <v>7</v>
-      </c>
-      <c r="G41" t="s">
-        <v>222</v>
       </c>
       <c r="H41" t="s">
         <v>11</v>
@@ -2690,22 +2669,22 @@
     </row>
     <row r="42" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A42" t="s">
+        <v>222</v>
+      </c>
+      <c r="C42" t="s">
+        <v>17</v>
+      </c>
+      <c r="D42" t="s">
+        <v>223</v>
+      </c>
+      <c r="E42" t="s">
+        <v>67</v>
+      </c>
+      <c r="F42" t="s">
+        <v>7</v>
+      </c>
+      <c r="G42" t="s">
         <v>224</v>
-      </c>
-      <c r="C42" t="s">
-        <v>18</v>
-      </c>
-      <c r="D42" t="s">
-        <v>225</v>
-      </c>
-      <c r="E42" t="s">
-        <v>69</v>
-      </c>
-      <c r="F42" t="s">
-        <v>7</v>
-      </c>
-      <c r="G42" t="s">
-        <v>226</v>
       </c>
       <c r="H42" t="s">
         <v>11</v>
@@ -2713,22 +2692,22 @@
     </row>
     <row r="43" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A43" t="s">
-        <v>227</v>
+        <v>225</v>
       </c>
       <c r="C43" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="D43" t="s">
-        <v>225</v>
+        <v>223</v>
       </c>
       <c r="E43" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
       <c r="F43" t="s">
         <v>7</v>
       </c>
       <c r="G43" t="s">
-        <v>226</v>
+        <v>224</v>
       </c>
       <c r="H43" t="s">
         <v>11</v>
@@ -2736,22 +2715,22 @@
     </row>
     <row r="44" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A44" t="s">
-        <v>228</v>
+        <v>226</v>
       </c>
       <c r="C44" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="D44" t="s">
-        <v>229</v>
+        <v>227</v>
       </c>
       <c r="E44" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="F44" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="G44" t="s">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="H44" t="s">
         <v>11</v>
@@ -2759,22 +2738,22 @@
     </row>
     <row r="45" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A45" t="s">
-        <v>230</v>
+        <v>228</v>
       </c>
       <c r="C45" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="D45" t="s">
-        <v>229</v>
+        <v>227</v>
       </c>
       <c r="E45" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="F45" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="G45" t="s">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="H45" t="s">
         <v>11</v>
@@ -2782,22 +2761,22 @@
     </row>
     <row r="46" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A46" t="s">
+        <v>229</v>
+      </c>
+      <c r="C46" t="s">
+        <v>125</v>
+      </c>
+      <c r="D46" t="s">
+        <v>230</v>
+      </c>
+      <c r="E46" t="s">
         <v>231</v>
       </c>
-      <c r="C46" t="s">
-        <v>127</v>
-      </c>
-      <c r="D46" t="s">
+      <c r="F46" t="s">
         <v>232</v>
       </c>
-      <c r="E46" t="s">
+      <c r="G46" t="s">
         <v>233</v>
-      </c>
-      <c r="F46" t="s">
-        <v>234</v>
-      </c>
-      <c r="G46" t="s">
-        <v>235</v>
       </c>
       <c r="H46" t="s">
         <v>11</v>
@@ -2805,22 +2784,22 @@
     </row>
     <row r="47" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A47" t="s">
-        <v>236</v>
+        <v>234</v>
       </c>
       <c r="C47" t="s">
         <v>13</v>
       </c>
       <c r="D47" t="s">
+        <v>235</v>
+      </c>
+      <c r="E47" t="s">
+        <v>236</v>
+      </c>
+      <c r="F47" t="s">
+        <v>7</v>
+      </c>
+      <c r="G47" t="s">
         <v>237</v>
-      </c>
-      <c r="E47" t="s">
-        <v>238</v>
-      </c>
-      <c r="F47" t="s">
-        <v>7</v>
-      </c>
-      <c r="G47" t="s">
-        <v>239</v>
       </c>
       <c r="H47" t="s">
         <v>11</v>
@@ -2828,22 +2807,22 @@
     </row>
     <row r="48" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A48" t="s">
-        <v>240</v>
+        <v>238</v>
       </c>
       <c r="C48" t="s">
         <v>13</v>
       </c>
       <c r="D48" t="s">
+        <v>235</v>
+      </c>
+      <c r="E48" t="s">
+        <v>236</v>
+      </c>
+      <c r="F48" t="s">
+        <v>7</v>
+      </c>
+      <c r="G48" t="s">
         <v>237</v>
-      </c>
-      <c r="E48" t="s">
-        <v>238</v>
-      </c>
-      <c r="F48" t="s">
-        <v>7</v>
-      </c>
-      <c r="G48" t="s">
-        <v>239</v>
       </c>
       <c r="H48" t="s">
         <v>11</v>
@@ -2851,22 +2830,22 @@
     </row>
     <row r="49" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A49" t="s">
+        <v>239</v>
+      </c>
+      <c r="C49" t="s">
+        <v>24</v>
+      </c>
+      <c r="D49" t="s">
+        <v>240</v>
+      </c>
+      <c r="E49" t="s">
         <v>241</v>
       </c>
-      <c r="C49" t="s">
-        <v>25</v>
-      </c>
-      <c r="D49" t="s">
+      <c r="F49" t="s">
+        <v>7</v>
+      </c>
+      <c r="G49" t="s">
         <v>242</v>
-      </c>
-      <c r="E49" t="s">
-        <v>243</v>
-      </c>
-      <c r="F49" t="s">
-        <v>7</v>
-      </c>
-      <c r="G49" t="s">
-        <v>244</v>
       </c>
       <c r="H49" t="s">
         <v>11</v>
@@ -2874,22 +2853,22 @@
     </row>
     <row r="50" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A50" t="s">
+        <v>243</v>
+      </c>
+      <c r="C50" t="s">
+        <v>125</v>
+      </c>
+      <c r="D50" t="s">
+        <v>244</v>
+      </c>
+      <c r="E50" t="s">
         <v>245</v>
       </c>
-      <c r="C50" t="s">
-        <v>127</v>
-      </c>
-      <c r="D50" t="s">
+      <c r="F50" t="s">
         <v>246</v>
       </c>
-      <c r="E50" t="s">
-        <v>247</v>
-      </c>
-      <c r="F50" t="s">
-        <v>248</v>
-      </c>
       <c r="G50" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="H50" t="s">
         <v>11</v>
@@ -2897,22 +2876,22 @@
     </row>
     <row r="51" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A51" t="s">
+        <v>247</v>
+      </c>
+      <c r="C51" t="s">
+        <v>125</v>
+      </c>
+      <c r="D51" t="s">
+        <v>248</v>
+      </c>
+      <c r="E51" t="s">
+        <v>46</v>
+      </c>
+      <c r="F51" t="s">
+        <v>47</v>
+      </c>
+      <c r="G51" t="s">
         <v>249</v>
-      </c>
-      <c r="C51" t="s">
-        <v>127</v>
-      </c>
-      <c r="D51" t="s">
-        <v>250</v>
-      </c>
-      <c r="E51" t="s">
-        <v>47</v>
-      </c>
-      <c r="F51" t="s">
-        <v>48</v>
-      </c>
-      <c r="G51" t="s">
-        <v>251</v>
       </c>
       <c r="H51" t="s">
         <v>11</v>
@@ -2920,22 +2899,22 @@
     </row>
     <row r="52" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A52" t="s">
+        <v>250</v>
+      </c>
+      <c r="C52" t="s">
+        <v>53</v>
+      </c>
+      <c r="D52" t="s">
+        <v>251</v>
+      </c>
+      <c r="E52" t="s">
+        <v>76</v>
+      </c>
+      <c r="F52" t="s">
+        <v>7</v>
+      </c>
+      <c r="G52" t="s">
         <v>252</v>
-      </c>
-      <c r="C52" t="s">
-        <v>54</v>
-      </c>
-      <c r="D52" t="s">
-        <v>253</v>
-      </c>
-      <c r="E52" t="s">
-        <v>78</v>
-      </c>
-      <c r="F52" t="s">
-        <v>7</v>
-      </c>
-      <c r="G52" t="s">
-        <v>254</v>
       </c>
       <c r="H52" t="s">
         <v>11</v>
@@ -2943,22 +2922,22 @@
     </row>
     <row r="53" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A53" t="s">
+        <v>253</v>
+      </c>
+      <c r="C53" t="s">
+        <v>63</v>
+      </c>
+      <c r="D53" t="s">
+        <v>254</v>
+      </c>
+      <c r="E53" t="s">
         <v>255</v>
       </c>
-      <c r="C53" t="s">
-        <v>64</v>
-      </c>
-      <c r="D53" t="s">
+      <c r="F53" t="s">
         <v>256</v>
       </c>
-      <c r="E53" t="s">
+      <c r="G53" t="s">
         <v>257</v>
-      </c>
-      <c r="F53" t="s">
-        <v>258</v>
-      </c>
-      <c r="G53" t="s">
-        <v>259</v>
       </c>
       <c r="H53" t="s">
         <v>11</v>
@@ -2966,22 +2945,22 @@
     </row>
     <row r="54" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A54" t="s">
-        <v>260</v>
+        <v>258</v>
       </c>
       <c r="C54" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="D54" t="s">
+        <v>254</v>
+      </c>
+      <c r="E54" t="s">
+        <v>255</v>
+      </c>
+      <c r="F54" t="s">
         <v>256</v>
       </c>
-      <c r="E54" t="s">
+      <c r="G54" t="s">
         <v>257</v>
-      </c>
-      <c r="F54" t="s">
-        <v>258</v>
-      </c>
-      <c r="G54" t="s">
-        <v>259</v>
       </c>
       <c r="H54" t="s">
         <v>11</v>
@@ -2989,22 +2968,22 @@
     </row>
     <row r="55" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A55" t="s">
+        <v>259</v>
+      </c>
+      <c r="C55" t="s">
+        <v>26</v>
+      </c>
+      <c r="D55" t="s">
+        <v>260</v>
+      </c>
+      <c r="E55" t="s">
         <v>261</v>
       </c>
-      <c r="C55" t="s">
-        <v>27</v>
-      </c>
-      <c r="D55" t="s">
+      <c r="F55" t="s">
+        <v>7</v>
+      </c>
+      <c r="G55" t="s">
         <v>262</v>
-      </c>
-      <c r="E55" t="s">
-        <v>263</v>
-      </c>
-      <c r="F55" t="s">
-        <v>7</v>
-      </c>
-      <c r="G55" t="s">
-        <v>264</v>
       </c>
       <c r="H55" t="s">
         <v>11</v>
@@ -3012,22 +2991,22 @@
     </row>
     <row r="56" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A56" t="s">
-        <v>265</v>
+        <v>263</v>
       </c>
       <c r="C56" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="D56" t="s">
+        <v>260</v>
+      </c>
+      <c r="E56" t="s">
+        <v>261</v>
+      </c>
+      <c r="F56" t="s">
+        <v>7</v>
+      </c>
+      <c r="G56" t="s">
         <v>262</v>
-      </c>
-      <c r="E56" t="s">
-        <v>263</v>
-      </c>
-      <c r="F56" t="s">
-        <v>7</v>
-      </c>
-      <c r="G56" t="s">
-        <v>264</v>
       </c>
       <c r="H56" t="s">
         <v>11</v>
@@ -3035,22 +3014,22 @@
     </row>
     <row r="57" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A57" t="s">
+        <v>264</v>
+      </c>
+      <c r="C57" t="s">
+        <v>125</v>
+      </c>
+      <c r="D57" t="s">
+        <v>265</v>
+      </c>
+      <c r="E57" t="s">
+        <v>36</v>
+      </c>
+      <c r="F57" t="s">
+        <v>37</v>
+      </c>
+      <c r="G57" t="s">
         <v>266</v>
-      </c>
-      <c r="C57" t="s">
-        <v>127</v>
-      </c>
-      <c r="D57" t="s">
-        <v>267</v>
-      </c>
-      <c r="E57" t="s">
-        <v>37</v>
-      </c>
-      <c r="F57" t="s">
-        <v>38</v>
-      </c>
-      <c r="G57" t="s">
-        <v>268</v>
       </c>
       <c r="H57" t="s">
         <v>11</v>
@@ -3058,22 +3037,22 @@
     </row>
     <row r="58" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A58" t="s">
+        <v>267</v>
+      </c>
+      <c r="C58" t="s">
+        <v>17</v>
+      </c>
+      <c r="D58" t="s">
+        <v>268</v>
+      </c>
+      <c r="E58" t="s">
+        <v>67</v>
+      </c>
+      <c r="F58" t="s">
+        <v>7</v>
+      </c>
+      <c r="G58" t="s">
         <v>269</v>
-      </c>
-      <c r="C58" t="s">
-        <v>18</v>
-      </c>
-      <c r="D58" t="s">
-        <v>270</v>
-      </c>
-      <c r="E58" t="s">
-        <v>69</v>
-      </c>
-      <c r="F58" t="s">
-        <v>7</v>
-      </c>
-      <c r="G58" t="s">
-        <v>271</v>
       </c>
       <c r="H58" t="s">
         <v>11</v>
@@ -3081,22 +3060,22 @@
     </row>
     <row r="59" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A59" t="s">
+        <v>270</v>
+      </c>
+      <c r="C59" t="s">
+        <v>26</v>
+      </c>
+      <c r="D59" t="s">
+        <v>271</v>
+      </c>
+      <c r="E59" t="s">
+        <v>261</v>
+      </c>
+      <c r="F59" t="s">
+        <v>7</v>
+      </c>
+      <c r="G59" t="s">
         <v>272</v>
-      </c>
-      <c r="C59" t="s">
-        <v>27</v>
-      </c>
-      <c r="D59" t="s">
-        <v>273</v>
-      </c>
-      <c r="E59" t="s">
-        <v>263</v>
-      </c>
-      <c r="F59" t="s">
-        <v>7</v>
-      </c>
-      <c r="G59" t="s">
-        <v>274</v>
       </c>
       <c r="H59" t="s">
         <v>11</v>
@@ -3104,22 +3083,22 @@
     </row>
     <row r="60" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A60" t="s">
-        <v>275</v>
+        <v>273</v>
       </c>
       <c r="C60" t="s">
         <v>13</v>
       </c>
       <c r="D60" t="s">
-        <v>276</v>
+        <v>274</v>
       </c>
       <c r="E60" t="s">
+        <v>57</v>
+      </c>
+      <c r="F60" t="s">
+        <v>7</v>
+      </c>
+      <c r="G60" t="s">
         <v>58</v>
-      </c>
-      <c r="F60" t="s">
-        <v>7</v>
-      </c>
-      <c r="G60" t="s">
-        <v>59</v>
       </c>
       <c r="H60" t="s">
         <v>11</v>
@@ -3127,22 +3106,22 @@
     </row>
     <row r="61" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A61" t="s">
+        <v>275</v>
+      </c>
+      <c r="C61" t="s">
+        <v>125</v>
+      </c>
+      <c r="D61" t="s">
+        <v>276</v>
+      </c>
+      <c r="E61" t="s">
         <v>277</v>
       </c>
-      <c r="C61" t="s">
-        <v>127</v>
-      </c>
-      <c r="D61" t="s">
+      <c r="F61" t="s">
         <v>278</v>
       </c>
-      <c r="E61" t="s">
+      <c r="G61" t="s">
         <v>279</v>
-      </c>
-      <c r="F61" t="s">
-        <v>280</v>
-      </c>
-      <c r="G61" t="s">
-        <v>281</v>
       </c>
       <c r="H61" t="s">
         <v>11</v>
@@ -3150,22 +3129,22 @@
     </row>
     <row r="62" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A62" t="s">
-        <v>282</v>
+        <v>280</v>
       </c>
       <c r="C62" t="s">
-        <v>127</v>
+        <v>125</v>
       </c>
       <c r="D62" t="s">
+        <v>276</v>
+      </c>
+      <c r="E62" t="s">
+        <v>277</v>
+      </c>
+      <c r="F62" t="s">
         <v>278</v>
       </c>
-      <c r="E62" t="s">
+      <c r="G62" t="s">
         <v>279</v>
-      </c>
-      <c r="F62" t="s">
-        <v>280</v>
-      </c>
-      <c r="G62" t="s">
-        <v>281</v>
       </c>
       <c r="H62" t="s">
         <v>11</v>
@@ -3173,22 +3152,22 @@
     </row>
     <row r="63" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A63" t="s">
-        <v>283</v>
+        <v>281</v>
       </c>
       <c r="C63" t="s">
         <v>13</v>
       </c>
       <c r="D63" t="s">
+        <v>282</v>
+      </c>
+      <c r="E63" t="s">
+        <v>283</v>
+      </c>
+      <c r="F63" t="s">
+        <v>7</v>
+      </c>
+      <c r="G63" t="s">
         <v>284</v>
-      </c>
-      <c r="E63" t="s">
-        <v>285</v>
-      </c>
-      <c r="F63" t="s">
-        <v>7</v>
-      </c>
-      <c r="G63" t="s">
-        <v>286</v>
       </c>
       <c r="H63" t="s">
         <v>11</v>
@@ -3196,22 +3175,22 @@
     </row>
     <row r="64" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A64" t="s">
-        <v>287</v>
+        <v>285</v>
       </c>
       <c r="C64" t="s">
         <v>13</v>
       </c>
       <c r="D64" t="s">
+        <v>282</v>
+      </c>
+      <c r="E64" t="s">
+        <v>283</v>
+      </c>
+      <c r="F64" t="s">
+        <v>7</v>
+      </c>
+      <c r="G64" t="s">
         <v>284</v>
-      </c>
-      <c r="E64" t="s">
-        <v>285</v>
-      </c>
-      <c r="F64" t="s">
-        <v>7</v>
-      </c>
-      <c r="G64" t="s">
-        <v>286</v>
       </c>
       <c r="H64" t="s">
         <v>11</v>
@@ -3219,22 +3198,22 @@
     </row>
     <row r="65" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A65" t="s">
-        <v>288</v>
+        <v>286</v>
       </c>
       <c r="C65" t="s">
-        <v>127</v>
+        <v>125</v>
       </c>
       <c r="D65" t="s">
-        <v>289</v>
+        <v>287</v>
       </c>
       <c r="E65" t="s">
+        <v>59</v>
+      </c>
+      <c r="F65" t="s">
         <v>60</v>
       </c>
-      <c r="F65" t="s">
-        <v>61</v>
-      </c>
       <c r="G65" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="H65" t="s">
         <v>11</v>
@@ -3242,22 +3221,22 @@
     </row>
     <row r="66" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A66" t="s">
+        <v>288</v>
+      </c>
+      <c r="C66" t="s">
+        <v>289</v>
+      </c>
+      <c r="D66" t="s">
         <v>290</v>
       </c>
-      <c r="C66" t="s">
-        <v>291</v>
-      </c>
-      <c r="D66" t="s">
-        <v>292</v>
-      </c>
       <c r="E66" t="s">
+        <v>65</v>
+      </c>
+      <c r="F66" t="s">
+        <v>7</v>
+      </c>
+      <c r="G66" t="s">
         <v>66</v>
-      </c>
-      <c r="F66" t="s">
-        <v>7</v>
-      </c>
-      <c r="G66" t="s">
-        <v>67</v>
       </c>
       <c r="H66" t="s">
         <v>11</v>
@@ -3265,22 +3244,22 @@
     </row>
     <row r="67" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A67" t="s">
+        <v>291</v>
+      </c>
+      <c r="C67" t="s">
+        <v>48</v>
+      </c>
+      <c r="D67" t="s">
+        <v>292</v>
+      </c>
+      <c r="E67" t="s">
+        <v>68</v>
+      </c>
+      <c r="F67" t="s">
+        <v>7</v>
+      </c>
+      <c r="G67" t="s">
         <v>293</v>
-      </c>
-      <c r="C67" t="s">
-        <v>49</v>
-      </c>
-      <c r="D67" t="s">
-        <v>294</v>
-      </c>
-      <c r="E67" t="s">
-        <v>70</v>
-      </c>
-      <c r="F67" t="s">
-        <v>7</v>
-      </c>
-      <c r="G67" t="s">
-        <v>295</v>
       </c>
       <c r="H67" t="s">
         <v>11</v>
@@ -3288,22 +3267,22 @@
     </row>
     <row r="68" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A68" t="s">
+        <v>294</v>
+      </c>
+      <c r="C68" t="s">
+        <v>53</v>
+      </c>
+      <c r="D68" t="s">
+        <v>295</v>
+      </c>
+      <c r="E68" t="s">
+        <v>76</v>
+      </c>
+      <c r="F68" t="s">
+        <v>7</v>
+      </c>
+      <c r="G68" t="s">
         <v>296</v>
-      </c>
-      <c r="C68" t="s">
-        <v>54</v>
-      </c>
-      <c r="D68" t="s">
-        <v>297</v>
-      </c>
-      <c r="E68" t="s">
-        <v>78</v>
-      </c>
-      <c r="F68" t="s">
-        <v>7</v>
-      </c>
-      <c r="G68" t="s">
-        <v>298</v>
       </c>
       <c r="H68" t="s">
         <v>11</v>
@@ -3311,22 +3290,22 @@
     </row>
     <row r="69" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A69" t="s">
+        <v>297</v>
+      </c>
+      <c r="C69" t="s">
+        <v>63</v>
+      </c>
+      <c r="D69" t="s">
+        <v>298</v>
+      </c>
+      <c r="E69" t="s">
+        <v>80</v>
+      </c>
+      <c r="F69" t="s">
+        <v>81</v>
+      </c>
+      <c r="G69" t="s">
         <v>299</v>
-      </c>
-      <c r="C69" t="s">
-        <v>64</v>
-      </c>
-      <c r="D69" t="s">
-        <v>300</v>
-      </c>
-      <c r="E69" t="s">
-        <v>82</v>
-      </c>
-      <c r="F69" t="s">
-        <v>83</v>
-      </c>
-      <c r="G69" t="s">
-        <v>301</v>
       </c>
       <c r="H69" t="s">
         <v>11</v>
@@ -3334,22 +3313,22 @@
     </row>
     <row r="70" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A70" t="s">
+        <v>300</v>
+      </c>
+      <c r="C70" t="s">
+        <v>63</v>
+      </c>
+      <c r="D70" t="s">
+        <v>301</v>
+      </c>
+      <c r="E70" t="s">
+        <v>80</v>
+      </c>
+      <c r="F70" t="s">
+        <v>81</v>
+      </c>
+      <c r="G70" t="s">
         <v>302</v>
-      </c>
-      <c r="C70" t="s">
-        <v>64</v>
-      </c>
-      <c r="D70" t="s">
-        <v>303</v>
-      </c>
-      <c r="E70" t="s">
-        <v>82</v>
-      </c>
-      <c r="F70" t="s">
-        <v>83</v>
-      </c>
-      <c r="G70" t="s">
-        <v>304</v>
       </c>
       <c r="H70" t="s">
         <v>11</v>
@@ -3357,22 +3336,22 @@
     </row>
     <row r="71" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A71" t="s">
-        <v>305</v>
+        <v>303</v>
       </c>
       <c r="C71" t="s">
         <v>9</v>
       </c>
       <c r="D71" t="s">
-        <v>306</v>
+        <v>304</v>
       </c>
       <c r="E71" t="s">
+        <v>130</v>
+      </c>
+      <c r="F71" t="s">
+        <v>131</v>
+      </c>
+      <c r="G71" t="s">
         <v>132</v>
-      </c>
-      <c r="F71" t="s">
-        <v>133</v>
-      </c>
-      <c r="G71" t="s">
-        <v>134</v>
       </c>
       <c r="H71" t="s">
         <v>11</v>
@@ -3380,22 +3359,22 @@
     </row>
     <row r="72" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A72" t="s">
-        <v>307</v>
+        <v>305</v>
       </c>
       <c r="C72" t="s">
         <v>9</v>
       </c>
       <c r="D72" t="s">
-        <v>306</v>
+        <v>304</v>
       </c>
       <c r="E72" t="s">
+        <v>130</v>
+      </c>
+      <c r="F72" t="s">
+        <v>131</v>
+      </c>
+      <c r="G72" t="s">
         <v>132</v>
-      </c>
-      <c r="F72" t="s">
-        <v>133</v>
-      </c>
-      <c r="G72" t="s">
-        <v>134</v>
       </c>
       <c r="H72" t="s">
         <v>11</v>
@@ -3403,22 +3382,22 @@
     </row>
     <row r="73" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A73" t="s">
-        <v>308</v>
+        <v>306</v>
       </c>
       <c r="C73" t="s">
         <v>9</v>
       </c>
       <c r="D73" t="s">
-        <v>306</v>
+        <v>304</v>
       </c>
       <c r="E73" t="s">
+        <v>130</v>
+      </c>
+      <c r="F73" t="s">
+        <v>131</v>
+      </c>
+      <c r="G73" t="s">
         <v>132</v>
-      </c>
-      <c r="F73" t="s">
-        <v>133</v>
-      </c>
-      <c r="G73" t="s">
-        <v>134</v>
       </c>
       <c r="H73" t="s">
         <v>11</v>
@@ -3426,22 +3405,22 @@
     </row>
     <row r="74" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A74" t="s">
+        <v>307</v>
+      </c>
+      <c r="C74" t="s">
+        <v>21</v>
+      </c>
+      <c r="D74" t="s">
+        <v>308</v>
+      </c>
+      <c r="E74" t="s">
+        <v>61</v>
+      </c>
+      <c r="F74" t="s">
+        <v>7</v>
+      </c>
+      <c r="G74" t="s">
         <v>309</v>
-      </c>
-      <c r="C74" t="s">
-        <v>22</v>
-      </c>
-      <c r="D74" t="s">
-        <v>310</v>
-      </c>
-      <c r="E74" t="s">
-        <v>62</v>
-      </c>
-      <c r="F74" t="s">
-        <v>7</v>
-      </c>
-      <c r="G74" t="s">
-        <v>311</v>
       </c>
       <c r="H74" t="s">
         <v>11</v>
@@ -3449,22 +3428,22 @@
     </row>
     <row r="75" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A75" t="s">
-        <v>312</v>
+        <v>310</v>
       </c>
       <c r="C75" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="D75" t="s">
-        <v>310</v>
+        <v>308</v>
       </c>
       <c r="E75" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="F75" t="s">
         <v>7</v>
       </c>
       <c r="G75" t="s">
-        <v>311</v>
+        <v>309</v>
       </c>
       <c r="H75" t="s">
         <v>11</v>
@@ -3472,22 +3451,22 @@
     </row>
     <row r="76" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A76" t="s">
+        <v>311</v>
+      </c>
+      <c r="C76" t="s">
+        <v>205</v>
+      </c>
+      <c r="D76" t="s">
+        <v>312</v>
+      </c>
+      <c r="E76" t="s">
         <v>313</v>
       </c>
-      <c r="C76" t="s">
-        <v>207</v>
-      </c>
-      <c r="D76" t="s">
+      <c r="F76" t="s">
+        <v>7</v>
+      </c>
+      <c r="G76" t="s">
         <v>314</v>
-      </c>
-      <c r="E76" t="s">
-        <v>315</v>
-      </c>
-      <c r="F76" t="s">
-        <v>7</v>
-      </c>
-      <c r="G76" t="s">
-        <v>316</v>
       </c>
       <c r="H76" t="s">
         <v>11</v>
@@ -3495,22 +3474,22 @@
     </row>
     <row r="77" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A77" t="s">
+        <v>315</v>
+      </c>
+      <c r="C77" t="s">
+        <v>48</v>
+      </c>
+      <c r="D77" t="s">
+        <v>316</v>
+      </c>
+      <c r="E77" t="s">
         <v>317</v>
       </c>
-      <c r="C77" t="s">
-        <v>49</v>
-      </c>
-      <c r="D77" t="s">
+      <c r="F77" t="s">
+        <v>7</v>
+      </c>
+      <c r="G77" t="s">
         <v>318</v>
-      </c>
-      <c r="E77" t="s">
-        <v>319</v>
-      </c>
-      <c r="F77" t="s">
-        <v>7</v>
-      </c>
-      <c r="G77" t="s">
-        <v>320</v>
       </c>
       <c r="H77" t="s">
         <v>11</v>
@@ -3518,22 +3497,22 @@
     </row>
     <row r="78" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A78" t="s">
+        <v>319</v>
+      </c>
+      <c r="C78" t="s">
+        <v>53</v>
+      </c>
+      <c r="D78" t="s">
+        <v>320</v>
+      </c>
+      <c r="E78" t="s">
         <v>321</v>
       </c>
-      <c r="C78" t="s">
-        <v>54</v>
-      </c>
-      <c r="D78" t="s">
+      <c r="F78" t="s">
+        <v>7</v>
+      </c>
+      <c r="G78" t="s">
         <v>322</v>
-      </c>
-      <c r="E78" t="s">
-        <v>323</v>
-      </c>
-      <c r="F78" t="s">
-        <v>7</v>
-      </c>
-      <c r="G78" t="s">
-        <v>324</v>
       </c>
       <c r="H78" t="s">
         <v>11</v>
@@ -3541,22 +3520,22 @@
     </row>
     <row r="79" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A79" t="s">
+        <v>323</v>
+      </c>
+      <c r="C79" t="s">
+        <v>125</v>
+      </c>
+      <c r="D79" t="s">
+        <v>324</v>
+      </c>
+      <c r="E79" t="s">
+        <v>46</v>
+      </c>
+      <c r="F79" t="s">
+        <v>47</v>
+      </c>
+      <c r="G79" t="s">
         <v>325</v>
-      </c>
-      <c r="C79" t="s">
-        <v>127</v>
-      </c>
-      <c r="D79" t="s">
-        <v>326</v>
-      </c>
-      <c r="E79" t="s">
-        <v>47</v>
-      </c>
-      <c r="F79" t="s">
-        <v>48</v>
-      </c>
-      <c r="G79" t="s">
-        <v>327</v>
       </c>
       <c r="H79" t="s">
         <v>11</v>
@@ -3564,22 +3543,22 @@
     </row>
     <row r="80" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A80" t="s">
-        <v>328</v>
+        <v>326</v>
       </c>
       <c r="C80" t="s">
         <v>13</v>
       </c>
       <c r="D80" t="s">
+        <v>327</v>
+      </c>
+      <c r="E80" t="s">
+        <v>328</v>
+      </c>
+      <c r="F80" t="s">
+        <v>7</v>
+      </c>
+      <c r="G80" t="s">
         <v>329</v>
-      </c>
-      <c r="E80" t="s">
-        <v>330</v>
-      </c>
-      <c r="F80" t="s">
-        <v>7</v>
-      </c>
-      <c r="G80" t="s">
-        <v>331</v>
       </c>
       <c r="H80" t="s">
         <v>11</v>
@@ -3587,22 +3566,22 @@
     </row>
     <row r="81" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A81" t="s">
+        <v>330</v>
+      </c>
+      <c r="C81" t="s">
+        <v>63</v>
+      </c>
+      <c r="D81" t="s">
+        <v>331</v>
+      </c>
+      <c r="E81" t="s">
         <v>332</v>
       </c>
-      <c r="C81" t="s">
-        <v>64</v>
-      </c>
-      <c r="D81" t="s">
+      <c r="F81" t="s">
         <v>333</v>
       </c>
-      <c r="E81" t="s">
+      <c r="G81" t="s">
         <v>334</v>
-      </c>
-      <c r="F81" t="s">
-        <v>335</v>
-      </c>
-      <c r="G81" t="s">
-        <v>336</v>
       </c>
       <c r="H81" t="s">
         <v>11</v>
@@ -3610,22 +3589,22 @@
     </row>
     <row r="82" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A82" t="s">
+        <v>335</v>
+      </c>
+      <c r="C82" t="s">
+        <v>19</v>
+      </c>
+      <c r="D82" t="s">
+        <v>336</v>
+      </c>
+      <c r="E82" t="s">
+        <v>30</v>
+      </c>
+      <c r="F82" t="s">
+        <v>31</v>
+      </c>
+      <c r="G82" t="s">
         <v>337</v>
-      </c>
-      <c r="C82" t="s">
-        <v>20</v>
-      </c>
-      <c r="D82" t="s">
-        <v>338</v>
-      </c>
-      <c r="E82" t="s">
-        <v>31</v>
-      </c>
-      <c r="F82" t="s">
-        <v>32</v>
-      </c>
-      <c r="G82" t="s">
-        <v>339</v>
       </c>
       <c r="H82" t="s">
         <v>11</v>
@@ -3633,22 +3612,22 @@
     </row>
     <row r="83" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A83" t="s">
-        <v>340</v>
+        <v>338</v>
       </c>
       <c r="C83" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="D83" t="s">
-        <v>341</v>
+        <v>339</v>
       </c>
       <c r="E83" t="s">
-        <v>216</v>
+        <v>214</v>
       </c>
       <c r="F83" t="s">
         <v>7</v>
       </c>
       <c r="G83" t="s">
-        <v>217</v>
+        <v>215</v>
       </c>
       <c r="H83" t="s">
         <v>11</v>
@@ -3656,22 +3635,22 @@
     </row>
     <row r="84" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A84" t="s">
+        <v>340</v>
+      </c>
+      <c r="C84" t="s">
+        <v>53</v>
+      </c>
+      <c r="D84" t="s">
+        <v>341</v>
+      </c>
+      <c r="E84" t="s">
         <v>342</v>
       </c>
-      <c r="C84" t="s">
-        <v>54</v>
-      </c>
-      <c r="D84" t="s">
+      <c r="F84" t="s">
+        <v>7</v>
+      </c>
+      <c r="G84" t="s">
         <v>343</v>
-      </c>
-      <c r="E84" t="s">
-        <v>344</v>
-      </c>
-      <c r="F84" t="s">
-        <v>7</v>
-      </c>
-      <c r="G84" t="s">
-        <v>345</v>
       </c>
       <c r="H84" t="s">
         <v>11</v>
@@ -3679,22 +3658,22 @@
     </row>
     <row r="85" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A85" t="s">
-        <v>346</v>
+        <v>344</v>
       </c>
       <c r="C85" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="D85" t="s">
-        <v>347</v>
+        <v>345</v>
       </c>
       <c r="E85" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="F85" t="s">
         <v>7</v>
       </c>
       <c r="G85" t="s">
-        <v>165</v>
+        <v>163</v>
       </c>
       <c r="H85" t="s">
         <v>11</v>
@@ -3702,22 +3681,22 @@
     </row>
     <row r="86" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A86" t="s">
+        <v>346</v>
+      </c>
+      <c r="C86" t="s">
+        <v>125</v>
+      </c>
+      <c r="D86" t="s">
+        <v>347</v>
+      </c>
+      <c r="E86" t="s">
+        <v>231</v>
+      </c>
+      <c r="F86" t="s">
+        <v>232</v>
+      </c>
+      <c r="G86" t="s">
         <v>348</v>
-      </c>
-      <c r="C86" t="s">
-        <v>127</v>
-      </c>
-      <c r="D86" t="s">
-        <v>349</v>
-      </c>
-      <c r="E86" t="s">
-        <v>233</v>
-      </c>
-      <c r="F86" t="s">
-        <v>234</v>
-      </c>
-      <c r="G86" t="s">
-        <v>350</v>
       </c>
       <c r="H86" t="s">
         <v>11</v>
@@ -3725,22 +3704,22 @@
     </row>
     <row r="87" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A87" t="s">
+        <v>349</v>
+      </c>
+      <c r="C87" t="s">
+        <v>21</v>
+      </c>
+      <c r="D87" t="s">
+        <v>350</v>
+      </c>
+      <c r="E87" t="s">
+        <v>41</v>
+      </c>
+      <c r="F87" t="s">
+        <v>7</v>
+      </c>
+      <c r="G87" t="s">
         <v>351</v>
-      </c>
-      <c r="C87" t="s">
-        <v>22</v>
-      </c>
-      <c r="D87" t="s">
-        <v>352</v>
-      </c>
-      <c r="E87" t="s">
-        <v>42</v>
-      </c>
-      <c r="F87" t="s">
-        <v>7</v>
-      </c>
-      <c r="G87" t="s">
-        <v>353</v>
       </c>
       <c r="H87" t="s">
         <v>11</v>
@@ -3748,22 +3727,22 @@
     </row>
     <row r="88" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A88" t="s">
+        <v>352</v>
+      </c>
+      <c r="C88" t="s">
+        <v>24</v>
+      </c>
+      <c r="D88" t="s">
+        <v>353</v>
+      </c>
+      <c r="E88" t="s">
         <v>354</v>
       </c>
-      <c r="C88" t="s">
-        <v>25</v>
-      </c>
-      <c r="D88" t="s">
+      <c r="F88" t="s">
+        <v>7</v>
+      </c>
+      <c r="G88" t="s">
         <v>355</v>
-      </c>
-      <c r="E88" t="s">
-        <v>356</v>
-      </c>
-      <c r="F88" t="s">
-        <v>7</v>
-      </c>
-      <c r="G88" t="s">
-        <v>357</v>
       </c>
       <c r="H88" t="s">
         <v>11</v>
@@ -3771,22 +3750,22 @@
     </row>
     <row r="89" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A89" t="s">
+        <v>356</v>
+      </c>
+      <c r="C89" t="s">
+        <v>24</v>
+      </c>
+      <c r="D89" t="s">
+        <v>357</v>
+      </c>
+      <c r="E89" t="s">
         <v>358</v>
       </c>
-      <c r="C89" t="s">
-        <v>25</v>
-      </c>
-      <c r="D89" t="s">
+      <c r="F89" t="s">
+        <v>7</v>
+      </c>
+      <c r="G89" t="s">
         <v>359</v>
-      </c>
-      <c r="E89" t="s">
-        <v>360</v>
-      </c>
-      <c r="F89" t="s">
-        <v>7</v>
-      </c>
-      <c r="G89" t="s">
-        <v>361</v>
       </c>
       <c r="H89" t="s">
         <v>11</v>
@@ -3794,22 +3773,22 @@
     </row>
     <row r="90" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A90" t="s">
+        <v>360</v>
+      </c>
+      <c r="C90" t="s">
+        <v>22</v>
+      </c>
+      <c r="D90" t="s">
+        <v>361</v>
+      </c>
+      <c r="E90" t="s">
+        <v>186</v>
+      </c>
+      <c r="F90" t="s">
+        <v>187</v>
+      </c>
+      <c r="G90" t="s">
         <v>362</v>
-      </c>
-      <c r="C90" t="s">
-        <v>23</v>
-      </c>
-      <c r="D90" t="s">
-        <v>363</v>
-      </c>
-      <c r="E90" t="s">
-        <v>188</v>
-      </c>
-      <c r="F90" t="s">
-        <v>189</v>
-      </c>
-      <c r="G90" t="s">
-        <v>364</v>
       </c>
       <c r="H90" t="s">
         <v>11</v>
@@ -3817,22 +3796,22 @@
     </row>
     <row r="91" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A91" t="s">
+        <v>363</v>
+      </c>
+      <c r="C91" t="s">
+        <v>39</v>
+      </c>
+      <c r="D91" t="s">
+        <v>364</v>
+      </c>
+      <c r="E91" t="s">
         <v>365</v>
       </c>
-      <c r="C91" t="s">
-        <v>40</v>
-      </c>
-      <c r="D91" t="s">
+      <c r="F91" t="s">
+        <v>7</v>
+      </c>
+      <c r="G91" t="s">
         <v>366</v>
-      </c>
-      <c r="E91" t="s">
-        <v>367</v>
-      </c>
-      <c r="F91" t="s">
-        <v>7</v>
-      </c>
-      <c r="G91" t="s">
-        <v>368</v>
       </c>
       <c r="H91" t="s">
         <v>11</v>
@@ -3840,22 +3819,22 @@
     </row>
     <row r="92" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A92" t="s">
-        <v>369</v>
+        <v>367</v>
       </c>
       <c r="C92" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="D92" t="s">
+        <v>364</v>
+      </c>
+      <c r="E92" t="s">
+        <v>365</v>
+      </c>
+      <c r="F92" t="s">
+        <v>7</v>
+      </c>
+      <c r="G92" t="s">
         <v>366</v>
-      </c>
-      <c r="E92" t="s">
-        <v>367</v>
-      </c>
-      <c r="F92" t="s">
-        <v>7</v>
-      </c>
-      <c r="G92" t="s">
-        <v>368</v>
       </c>
       <c r="H92" t="s">
         <v>11</v>
@@ -3863,22 +3842,22 @@
     </row>
     <row r="93" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A93" t="s">
-        <v>370</v>
+        <v>368</v>
       </c>
       <c r="C93" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="D93" t="s">
+        <v>364</v>
+      </c>
+      <c r="E93" t="s">
+        <v>365</v>
+      </c>
+      <c r="F93" t="s">
+        <v>7</v>
+      </c>
+      <c r="G93" t="s">
         <v>366</v>
-      </c>
-      <c r="E93" t="s">
-        <v>367</v>
-      </c>
-      <c r="F93" t="s">
-        <v>7</v>
-      </c>
-      <c r="G93" t="s">
-        <v>368</v>
       </c>
       <c r="H93" t="s">
         <v>11</v>
@@ -3886,13 +3865,13 @@
     </row>
     <row r="94" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A94" t="s">
-        <v>371</v>
+        <v>369</v>
       </c>
       <c r="C94" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="D94" t="s">
-        <v>372</v>
+        <v>370</v>
       </c>
       <c r="E94" t="s">
         <v>16</v>
@@ -3901,7 +3880,7 @@
         <v>7</v>
       </c>
       <c r="G94" t="s">
-        <v>81</v>
+        <v>79</v>
       </c>
       <c r="H94" t="s">
         <v>11</v>
@@ -3909,13 +3888,13 @@
     </row>
     <row r="95" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A95" t="s">
-        <v>373</v>
+        <v>371</v>
       </c>
       <c r="C95" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="D95" t="s">
-        <v>372</v>
+        <v>370</v>
       </c>
       <c r="E95" t="s">
         <v>16</v>
@@ -3924,7 +3903,7 @@
         <v>7</v>
       </c>
       <c r="G95" t="s">
-        <v>81</v>
+        <v>79</v>
       </c>
       <c r="H95" t="s">
         <v>11</v>
@@ -3932,22 +3911,22 @@
     </row>
     <row r="96" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A96" t="s">
+        <v>372</v>
+      </c>
+      <c r="C96" t="s">
+        <v>24</v>
+      </c>
+      <c r="D96" t="s">
+        <v>373</v>
+      </c>
+      <c r="E96" t="s">
         <v>374</v>
       </c>
-      <c r="C96" t="s">
-        <v>25</v>
-      </c>
-      <c r="D96" t="s">
+      <c r="F96" t="s">
+        <v>7</v>
+      </c>
+      <c r="G96" t="s">
         <v>375</v>
-      </c>
-      <c r="E96" t="s">
-        <v>376</v>
-      </c>
-      <c r="F96" t="s">
-        <v>7</v>
-      </c>
-      <c r="G96" t="s">
-        <v>377</v>
       </c>
       <c r="H96" t="s">
         <v>12</v>
@@ -3955,22 +3934,22 @@
     </row>
     <row r="97" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A97" t="s">
+        <v>376</v>
+      </c>
+      <c r="C97" t="s">
+        <v>39</v>
+      </c>
+      <c r="D97" t="s">
+        <v>377</v>
+      </c>
+      <c r="E97" t="s">
+        <v>365</v>
+      </c>
+      <c r="F97" t="s">
+        <v>7</v>
+      </c>
+      <c r="G97" t="s">
         <v>378</v>
-      </c>
-      <c r="C97" t="s">
-        <v>40</v>
-      </c>
-      <c r="D97" t="s">
-        <v>379</v>
-      </c>
-      <c r="E97" t="s">
-        <v>367</v>
-      </c>
-      <c r="F97" t="s">
-        <v>7</v>
-      </c>
-      <c r="G97" t="s">
-        <v>380</v>
       </c>
       <c r="H97" t="s">
         <v>12</v>
@@ -3978,22 +3957,22 @@
     </row>
     <row r="98" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A98" t="s">
-        <v>381</v>
+        <v>379</v>
       </c>
       <c r="C98" t="s">
         <v>9</v>
       </c>
       <c r="D98" t="s">
-        <v>382</v>
+        <v>380</v>
       </c>
       <c r="E98" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="F98" t="s">
         <v>7</v>
       </c>
       <c r="G98" t="s">
-        <v>383</v>
+        <v>381</v>
       </c>
       <c r="H98" t="s">
         <v>12</v>
@@ -4001,22 +3980,22 @@
     </row>
     <row r="99" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A99" t="s">
+        <v>382</v>
+      </c>
+      <c r="C99" t="s">
+        <v>205</v>
+      </c>
+      <c r="D99" t="s">
+        <v>383</v>
+      </c>
+      <c r="E99" t="s">
         <v>384</v>
       </c>
-      <c r="C99" t="s">
-        <v>207</v>
-      </c>
-      <c r="D99" t="s">
+      <c r="F99" t="s">
+        <v>7</v>
+      </c>
+      <c r="G99" t="s">
         <v>385</v>
-      </c>
-      <c r="E99" t="s">
-        <v>386</v>
-      </c>
-      <c r="F99" t="s">
-        <v>7</v>
-      </c>
-      <c r="G99" t="s">
-        <v>387</v>
       </c>
       <c r="H99" t="s">
         <v>12</v>
@@ -4024,22 +4003,22 @@
     </row>
     <row r="100" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A100" t="s">
+        <v>386</v>
+      </c>
+      <c r="C100" t="s">
+        <v>63</v>
+      </c>
+      <c r="D100" t="s">
+        <v>387</v>
+      </c>
+      <c r="E100" t="s">
         <v>388</v>
       </c>
-      <c r="C100" t="s">
-        <v>64</v>
-      </c>
-      <c r="D100" t="s">
+      <c r="F100" t="s">
         <v>389</v>
       </c>
-      <c r="E100" t="s">
+      <c r="G100" t="s">
         <v>390</v>
-      </c>
-      <c r="F100" t="s">
-        <v>391</v>
-      </c>
-      <c r="G100" t="s">
-        <v>392</v>
       </c>
       <c r="H100" t="s">
         <v>12</v>
@@ -4047,22 +4026,22 @@
     </row>
     <row r="101" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A101" t="s">
-        <v>393</v>
+        <v>391</v>
       </c>
       <c r="C101" t="s">
         <v>9</v>
       </c>
       <c r="D101" t="s">
+        <v>392</v>
+      </c>
+      <c r="E101" t="s">
+        <v>393</v>
+      </c>
+      <c r="F101" t="s">
         <v>394</v>
       </c>
-      <c r="E101" t="s">
+      <c r="G101" t="s">
         <v>395</v>
-      </c>
-      <c r="F101" t="s">
-        <v>396</v>
-      </c>
-      <c r="G101" t="s">
-        <v>397</v>
       </c>
       <c r="H101" t="s">
         <v>12</v>
@@ -4070,22 +4049,22 @@
     </row>
     <row r="102" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A102" t="s">
+        <v>396</v>
+      </c>
+      <c r="C102" t="s">
+        <v>19</v>
+      </c>
+      <c r="D102" t="s">
+        <v>397</v>
+      </c>
+      <c r="E102" t="s">
         <v>398</v>
       </c>
-      <c r="C102" t="s">
-        <v>20</v>
-      </c>
-      <c r="D102" t="s">
+      <c r="F102" t="s">
+        <v>7</v>
+      </c>
+      <c r="G102" t="s">
         <v>399</v>
-      </c>
-      <c r="E102" t="s">
-        <v>400</v>
-      </c>
-      <c r="F102" t="s">
-        <v>7</v>
-      </c>
-      <c r="G102" t="s">
-        <v>401</v>
       </c>
       <c r="H102" t="s">
         <v>12</v>
@@ -4093,22 +4072,22 @@
     </row>
     <row r="103" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A103" t="s">
+        <v>400</v>
+      </c>
+      <c r="C103" t="s">
+        <v>21</v>
+      </c>
+      <c r="D103" t="s">
+        <v>401</v>
+      </c>
+      <c r="E103" t="s">
+        <v>55</v>
+      </c>
+      <c r="F103" t="s">
+        <v>56</v>
+      </c>
+      <c r="G103" t="s">
         <v>402</v>
-      </c>
-      <c r="C103" t="s">
-        <v>22</v>
-      </c>
-      <c r="D103" t="s">
-        <v>403</v>
-      </c>
-      <c r="E103" t="s">
-        <v>56</v>
-      </c>
-      <c r="F103" t="s">
-        <v>57</v>
-      </c>
-      <c r="G103" t="s">
-        <v>404</v>
       </c>
       <c r="H103" t="s">
         <v>12</v>
@@ -4116,22 +4095,22 @@
     </row>
     <row r="104" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A104" t="s">
+        <v>403</v>
+      </c>
+      <c r="C104" t="s">
+        <v>19</v>
+      </c>
+      <c r="D104" t="s">
+        <v>404</v>
+      </c>
+      <c r="E104" t="s">
         <v>405</v>
       </c>
-      <c r="C104" t="s">
-        <v>20</v>
-      </c>
-      <c r="D104" t="s">
+      <c r="F104" t="s">
         <v>406</v>
       </c>
-      <c r="E104" t="s">
-        <v>407</v>
-      </c>
-      <c r="F104" t="s">
-        <v>408</v>
-      </c>
       <c r="G104" t="s">
-        <v>77</v>
+        <v>75</v>
       </c>
       <c r="H104" t="s">
         <v>12</v>
@@ -4139,13 +4118,13 @@
     </row>
     <row r="105" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A105" t="s">
-        <v>409</v>
+        <v>407</v>
       </c>
       <c r="C105" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="D105" t="s">
-        <v>410</v>
+        <v>408</v>
       </c>
       <c r="E105" t="s">
         <v>16</v>
@@ -4154,7 +4133,7 @@
         <v>7</v>
       </c>
       <c r="G105" t="s">
-        <v>411</v>
+        <v>409</v>
       </c>
       <c r="H105" t="s">
         <v>12</v>
@@ -4162,22 +4141,22 @@
     </row>
     <row r="106" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A106" t="s">
+        <v>410</v>
+      </c>
+      <c r="C106" t="s">
+        <v>24</v>
+      </c>
+      <c r="D106" t="s">
+        <v>411</v>
+      </c>
+      <c r="E106" t="s">
+        <v>54</v>
+      </c>
+      <c r="F106" t="s">
+        <v>7</v>
+      </c>
+      <c r="G106" t="s">
         <v>412</v>
-      </c>
-      <c r="C106" t="s">
-        <v>25</v>
-      </c>
-      <c r="D106" t="s">
-        <v>413</v>
-      </c>
-      <c r="E106" t="s">
-        <v>55</v>
-      </c>
-      <c r="F106" t="s">
-        <v>7</v>
-      </c>
-      <c r="G106" t="s">
-        <v>414</v>
       </c>
       <c r="H106" t="s">
         <v>12</v>
@@ -4185,22 +4164,22 @@
     </row>
     <row r="107" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A107" t="s">
+        <v>413</v>
+      </c>
+      <c r="C107" t="s">
+        <v>29</v>
+      </c>
+      <c r="D107" t="s">
+        <v>414</v>
+      </c>
+      <c r="E107" t="s">
+        <v>42</v>
+      </c>
+      <c r="F107" t="s">
+        <v>43</v>
+      </c>
+      <c r="G107" t="s">
         <v>415</v>
-      </c>
-      <c r="C107" t="s">
-        <v>30</v>
-      </c>
-      <c r="D107" t="s">
-        <v>416</v>
-      </c>
-      <c r="E107" t="s">
-        <v>43</v>
-      </c>
-      <c r="F107" t="s">
-        <v>44</v>
-      </c>
-      <c r="G107" t="s">
-        <v>417</v>
       </c>
       <c r="H107" t="s">
         <v>12</v>
@@ -4208,22 +4187,22 @@
     </row>
     <row r="108" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A108" t="s">
-        <v>418</v>
+        <v>416</v>
       </c>
       <c r="C108" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="D108" t="s">
-        <v>416</v>
+        <v>414</v>
       </c>
       <c r="E108" t="s">
+        <v>42</v>
+      </c>
+      <c r="F108" t="s">
         <v>43</v>
       </c>
-      <c r="F108" t="s">
-        <v>44</v>
-      </c>
       <c r="G108" t="s">
-        <v>417</v>
+        <v>415</v>
       </c>
       <c r="H108" t="s">
         <v>12</v>
@@ -4231,22 +4210,22 @@
     </row>
     <row r="109" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A109" t="s">
-        <v>419</v>
+        <v>417</v>
       </c>
       <c r="C109" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="D109" t="s">
-        <v>416</v>
+        <v>414</v>
       </c>
       <c r="E109" t="s">
+        <v>42</v>
+      </c>
+      <c r="F109" t="s">
         <v>43</v>
       </c>
-      <c r="F109" t="s">
-        <v>44</v>
-      </c>
       <c r="G109" t="s">
-        <v>417</v>
+        <v>415</v>
       </c>
       <c r="H109" t="s">
         <v>12</v>
@@ -4254,22 +4233,22 @@
     </row>
     <row r="110" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A110" t="s">
+        <v>418</v>
+      </c>
+      <c r="C110" t="s">
+        <v>63</v>
+      </c>
+      <c r="D110" t="s">
+        <v>419</v>
+      </c>
+      <c r="E110" t="s">
+        <v>34</v>
+      </c>
+      <c r="F110" t="s">
+        <v>35</v>
+      </c>
+      <c r="G110" t="s">
         <v>420</v>
-      </c>
-      <c r="C110" t="s">
-        <v>64</v>
-      </c>
-      <c r="D110" t="s">
-        <v>421</v>
-      </c>
-      <c r="E110" t="s">
-        <v>35</v>
-      </c>
-      <c r="F110" t="s">
-        <v>36</v>
-      </c>
-      <c r="G110" t="s">
-        <v>422</v>
       </c>
       <c r="H110" t="s">
         <v>12</v>
@@ -4277,22 +4256,22 @@
     </row>
     <row r="111" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A111" t="s">
-        <v>423</v>
+        <v>421</v>
       </c>
       <c r="C111" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="D111" t="s">
-        <v>421</v>
+        <v>419</v>
       </c>
       <c r="E111" t="s">
+        <v>34</v>
+      </c>
+      <c r="F111" t="s">
         <v>35</v>
       </c>
-      <c r="F111" t="s">
-        <v>36</v>
-      </c>
       <c r="G111" t="s">
-        <v>422</v>
+        <v>420</v>
       </c>
       <c r="H111" t="s">
         <v>12</v>
@@ -4300,22 +4279,22 @@
     </row>
     <row r="112" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A112" t="s">
+        <v>422</v>
+      </c>
+      <c r="C112" t="s">
+        <v>289</v>
+      </c>
+      <c r="D112" t="s">
+        <v>423</v>
+      </c>
+      <c r="E112" t="s">
+        <v>45</v>
+      </c>
+      <c r="F112" t="s">
+        <v>7</v>
+      </c>
+      <c r="G112" t="s">
         <v>424</v>
-      </c>
-      <c r="C112" t="s">
-        <v>291</v>
-      </c>
-      <c r="D112" t="s">
-        <v>425</v>
-      </c>
-      <c r="E112" t="s">
-        <v>46</v>
-      </c>
-      <c r="F112" t="s">
-        <v>7</v>
-      </c>
-      <c r="G112" t="s">
-        <v>426</v>
       </c>
       <c r="H112" t="s">
         <v>12</v>
@@ -4323,22 +4302,22 @@
     </row>
     <row r="113" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A113" t="s">
+        <v>425</v>
+      </c>
+      <c r="C113" t="s">
+        <v>48</v>
+      </c>
+      <c r="D113" t="s">
+        <v>426</v>
+      </c>
+      <c r="E113" t="s">
+        <v>77</v>
+      </c>
+      <c r="F113" t="s">
+        <v>7</v>
+      </c>
+      <c r="G113" t="s">
         <v>427</v>
-      </c>
-      <c r="C113" t="s">
-        <v>49</v>
-      </c>
-      <c r="D113" t="s">
-        <v>428</v>
-      </c>
-      <c r="E113" t="s">
-        <v>79</v>
-      </c>
-      <c r="F113" t="s">
-        <v>7</v>
-      </c>
-      <c r="G113" t="s">
-        <v>429</v>
       </c>
       <c r="H113" t="s">
         <v>12</v>
@@ -4346,22 +4325,22 @@
     </row>
     <row r="114" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A114" t="s">
+        <v>428</v>
+      </c>
+      <c r="C114" t="s">
+        <v>39</v>
+      </c>
+      <c r="D114" t="s">
+        <v>429</v>
+      </c>
+      <c r="E114" t="s">
+        <v>50</v>
+      </c>
+      <c r="F114" t="s">
+        <v>51</v>
+      </c>
+      <c r="G114" t="s">
         <v>430</v>
-      </c>
-      <c r="C114" t="s">
-        <v>54</v>
-      </c>
-      <c r="D114" t="s">
-        <v>431</v>
-      </c>
-      <c r="E114" t="s">
-        <v>432</v>
-      </c>
-      <c r="F114" t="s">
-        <v>7</v>
-      </c>
-      <c r="G114" t="s">
-        <v>433</v>
       </c>
       <c r="H114" t="s">
         <v>12</v>
@@ -4369,22 +4348,22 @@
     </row>
     <row r="115" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A115" t="s">
+        <v>431</v>
+      </c>
+      <c r="C115" t="s">
+        <v>13</v>
+      </c>
+      <c r="D115" t="s">
+        <v>432</v>
+      </c>
+      <c r="E115" t="s">
+        <v>433</v>
+      </c>
+      <c r="F115" t="s">
+        <v>7</v>
+      </c>
+      <c r="G115" t="s">
         <v>434</v>
-      </c>
-      <c r="C115" t="s">
-        <v>17</v>
-      </c>
-      <c r="D115" t="s">
-        <v>435</v>
-      </c>
-      <c r="E115" t="s">
-        <v>68</v>
-      </c>
-      <c r="F115" t="s">
-        <v>7</v>
-      </c>
-      <c r="G115" t="s">
-        <v>436</v>
       </c>
       <c r="H115" t="s">
         <v>12</v>
@@ -4392,19 +4371,19 @@
     </row>
     <row r="116" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A116" t="s">
+        <v>435</v>
+      </c>
+      <c r="C116" t="s">
+        <v>63</v>
+      </c>
+      <c r="D116" t="s">
+        <v>436</v>
+      </c>
+      <c r="E116" t="s">
         <v>437</v>
       </c>
-      <c r="C116" t="s">
-        <v>40</v>
-      </c>
-      <c r="D116" t="s">
+      <c r="F116" t="s">
         <v>438</v>
-      </c>
-      <c r="E116" t="s">
-        <v>51</v>
-      </c>
-      <c r="F116" t="s">
-        <v>52</v>
       </c>
       <c r="G116" t="s">
         <v>439</v>
@@ -4418,19 +4397,19 @@
         <v>440</v>
       </c>
       <c r="C117" t="s">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="D117" t="s">
         <v>441</v>
       </c>
       <c r="E117" t="s">
+        <v>44</v>
+      </c>
+      <c r="F117" t="s">
+        <v>7</v>
+      </c>
+      <c r="G117" t="s">
         <v>442</v>
-      </c>
-      <c r="F117" t="s">
-        <v>7</v>
-      </c>
-      <c r="G117" t="s">
-        <v>443</v>
       </c>
       <c r="H117" t="s">
         <v>12</v>
@@ -4438,22 +4417,22 @@
     </row>
     <row r="118" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A118" t="s">
-        <v>444</v>
+        <v>443</v>
       </c>
       <c r="C118" t="s">
-        <v>64</v>
+        <v>9</v>
       </c>
       <c r="D118" t="s">
-        <v>445</v>
+        <v>441</v>
       </c>
       <c r="E118" t="s">
-        <v>446</v>
+        <v>44</v>
       </c>
       <c r="F118" t="s">
-        <v>447</v>
+        <v>7</v>
       </c>
       <c r="G118" t="s">
-        <v>448</v>
+        <v>442</v>
       </c>
       <c r="H118" t="s">
         <v>12</v>
@@ -4461,22 +4440,22 @@
     </row>
     <row r="119" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A119" t="s">
-        <v>449</v>
+        <v>444</v>
       </c>
       <c r="C119" t="s">
-        <v>9</v>
+        <v>29</v>
       </c>
       <c r="D119" t="s">
-        <v>450</v>
+        <v>445</v>
       </c>
       <c r="E119" t="s">
-        <v>45</v>
+        <v>446</v>
       </c>
       <c r="F119" t="s">
-        <v>7</v>
+        <v>447</v>
       </c>
       <c r="G119" t="s">
-        <v>451</v>
+        <v>448</v>
       </c>
       <c r="H119" t="s">
         <v>12</v>
@@ -4484,117 +4463,85 @@
     </row>
     <row r="120" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A120" t="s">
-        <v>452</v>
+        <v>82</v>
       </c>
       <c r="C120" t="s">
-        <v>9</v>
+        <v>63</v>
       </c>
       <c r="D120" t="s">
-        <v>450</v>
+        <v>83</v>
       </c>
       <c r="E120" t="s">
-        <v>45</v>
+        <v>84</v>
       </c>
       <c r="F120" t="s">
-        <v>7</v>
+        <v>85</v>
       </c>
       <c r="G120" t="s">
-        <v>451</v>
+        <v>86</v>
       </c>
       <c r="H120" t="s">
-        <v>12</v>
+        <v>23</v>
       </c>
     </row>
     <row r="121" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A121" t="s">
-        <v>453</v>
+        <v>449</v>
       </c>
       <c r="C121" t="s">
-        <v>30</v>
+        <v>48</v>
       </c>
       <c r="D121" t="s">
-        <v>454</v>
+        <v>450</v>
       </c>
       <c r="E121" t="s">
-        <v>455</v>
+        <v>317</v>
       </c>
       <c r="F121" t="s">
-        <v>456</v>
+        <v>7</v>
       </c>
       <c r="G121" t="s">
-        <v>457</v>
+        <v>451</v>
       </c>
       <c r="H121" t="s">
-        <v>12</v>
+        <v>87</v>
       </c>
     </row>
     <row r="122" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A122" t="s">
-        <v>84</v>
+        <v>452</v>
       </c>
       <c r="C122" t="s">
-        <v>64</v>
+        <v>48</v>
       </c>
       <c r="D122" t="s">
-        <v>85</v>
+        <v>450</v>
       </c>
       <c r="E122" t="s">
-        <v>86</v>
+        <v>317</v>
       </c>
       <c r="F122" t="s">
+        <v>7</v>
+      </c>
+      <c r="G122" t="s">
+        <v>451</v>
+      </c>
+      <c r="H122" t="s">
         <v>87</v>
-      </c>
-      <c r="G122" t="s">
-        <v>88</v>
-      </c>
-      <c r="H122" t="s">
-        <v>24</v>
       </c>
     </row>
     <row r="123" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A123" t="s">
-        <v>458</v>
+        <v>453</v>
       </c>
       <c r="C123" t="s">
-        <v>49</v>
+        <v>22</v>
       </c>
       <c r="D123" t="s">
-        <v>459</v>
-      </c>
-      <c r="E123" t="s">
-        <v>319</v>
-      </c>
-      <c r="F123" t="s">
-        <v>7</v>
-      </c>
-      <c r="G123" t="s">
-        <v>460</v>
+        <v>453</v>
       </c>
       <c r="H123" t="s">
-        <v>89</v>
-      </c>
-    </row>
-    <row r="124" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A124" t="s">
-        <v>461</v>
-      </c>
-      <c r="C124" t="s">
-        <v>49</v>
-      </c>
-      <c r="D124" t="s">
-        <v>459</v>
-      </c>
-      <c r="E124" t="s">
-        <v>319</v>
-      </c>
-      <c r="F124" t="s">
-        <v>7</v>
-      </c>
-      <c r="G124" t="s">
-        <v>460</v>
-      </c>
-      <c r="H124" t="s">
-        <v>89</v>
+        <v>454</v>
       </c>
     </row>
   </sheetData>

--- a/1.xlsx
+++ b/1.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="\\wh.local\fs\UserProfile_TSSWH19\_TSSWH19_redirected_folders\HunyaCs1\Desktop\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D46C736C-AA45-42BA-BDBC-CB327730ED3A}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2BE92842-8654-4110-A006-242C72732005}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="0" windowWidth="22260" windowHeight="12648" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="858" uniqueCount="455">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1413" uniqueCount="729">
   <si>
     <t>IRSZ</t>
   </si>
@@ -78,9 +78,6 @@
     <t>DUNAKESZI</t>
   </si>
   <si>
-    <t>1173</t>
-  </si>
-  <si>
     <t>SZ-809</t>
   </si>
   <si>
@@ -96,9 +93,6 @@
     <t>SZ-819</t>
   </si>
   <si>
-    <t>SZ-823</t>
-  </si>
-  <si>
     <t>INSPORT</t>
   </si>
   <si>
@@ -111,12 +105,6 @@
     <t>SZ-834</t>
   </si>
   <si>
-    <t>1237</t>
-  </si>
-  <si>
-    <t>1149</t>
-  </si>
-  <si>
     <t>SZ-832</t>
   </si>
   <si>
@@ -138,30 +126,15 @@
     <t>GYÖMRŐ</t>
   </si>
   <si>
-    <t>2315</t>
-  </si>
-  <si>
-    <t>SZIGETHALOM</t>
-  </si>
-  <si>
     <t>SELEX</t>
   </si>
   <si>
     <t>SZ-814</t>
   </si>
   <si>
-    <t>Árpád utca</t>
-  </si>
-  <si>
     <t>1026</t>
   </si>
   <si>
-    <t>2225</t>
-  </si>
-  <si>
-    <t>ÜLLŐ</t>
-  </si>
-  <si>
     <t>1165</t>
   </si>
   <si>
@@ -177,9 +150,6 @@
     <t>SZ-815</t>
   </si>
   <si>
-    <t>1118</t>
-  </si>
-  <si>
     <t>2330</t>
   </si>
   <si>
@@ -201,12 +171,6 @@
     <t>SOLYMÁR</t>
   </si>
   <si>
-    <t>1095</t>
-  </si>
-  <si>
-    <t>Soroksári út</t>
-  </si>
-  <si>
     <t>2316</t>
   </si>
   <si>
@@ -216,210 +180,51 @@
     <t>1024</t>
   </si>
   <si>
-    <t>Szent László utca</t>
-  </si>
-  <si>
     <t>SZ-818</t>
   </si>
   <si>
     <t>1102</t>
   </si>
   <si>
-    <t>1038</t>
-  </si>
-  <si>
-    <t>Pusztakúti út</t>
-  </si>
-  <si>
     <t>1172</t>
   </si>
   <si>
     <t>1146</t>
   </si>
   <si>
-    <t>2730</t>
-  </si>
-  <si>
-    <t>ALBERTIRSA</t>
-  </si>
-  <si>
     <t>2235</t>
   </si>
   <si>
     <t>MENDE</t>
   </si>
   <si>
-    <t>2375</t>
-  </si>
-  <si>
-    <t>TATÁRSZENTGYÖRGY</t>
-  </si>
-  <si>
-    <t>Nyár utca</t>
-  </si>
-  <si>
     <t>1191</t>
   </si>
   <si>
-    <t>1147</t>
-  </si>
-  <si>
-    <t>Kossuth Lajos utca</t>
-  </si>
-  <si>
-    <t>Pesti út</t>
-  </si>
-  <si>
     <t>2119</t>
   </si>
   <si>
     <t>PÉCEL</t>
   </si>
   <si>
-    <t>159995579538332470</t>
-  </si>
-  <si>
-    <t>R413591</t>
-  </si>
-  <si>
-    <t>2769</t>
-  </si>
-  <si>
-    <t>TÁPIÓSZŐLŐS</t>
-  </si>
-  <si>
     <t>Petőfi Sándor utca</t>
   </si>
   <si>
-    <t>PICIGURMAN</t>
-  </si>
-  <si>
-    <t>159995579538377198</t>
-  </si>
-  <si>
-    <t>1-2318/2026</t>
-  </si>
-  <si>
-    <t>Keleti K. utca</t>
-  </si>
-  <si>
-    <t>EUROTRESOR</t>
-  </si>
-  <si>
-    <t>159995579538409998</t>
-  </si>
-  <si>
-    <t>1-2339/2026</t>
-  </si>
-  <si>
-    <t>Sarlóspuszta hrsz.</t>
-  </si>
-  <si>
-    <t>159995579538470851</t>
-  </si>
-  <si>
-    <t>1-2396/2026</t>
-  </si>
-  <si>
-    <t>2040</t>
-  </si>
-  <si>
-    <t>BUDAÖRS</t>
-  </si>
-  <si>
-    <t>Templom tér</t>
-  </si>
-  <si>
-    <t>159995579538470868</t>
-  </si>
-  <si>
-    <t>69bbe0d6d96b4f4a2437fb39</t>
-  </si>
-  <si>
-    <t>260220-F00004478</t>
-  </si>
-  <si>
-    <t>Győzelem köz</t>
-  </si>
-  <si>
-    <t>69bab0acd96b4f4a2437e983</t>
-  </si>
-  <si>
-    <t>260226-F00007209-1</t>
-  </si>
-  <si>
-    <t>2365</t>
-  </si>
-  <si>
-    <t>INÁRCS</t>
-  </si>
-  <si>
-    <t>Bajcsy-Zsilinszky út</t>
-  </si>
-  <si>
-    <t>69bbb6e0d96b4f4a2437f4aa</t>
-  </si>
-  <si>
-    <t>260311-F00012755</t>
-  </si>
-  <si>
-    <t>2141</t>
-  </si>
-  <si>
-    <t>CSÖMÖR</t>
-  </si>
-  <si>
-    <t>Mező utca</t>
-  </si>
-  <si>
-    <t>69baac9dd96b4f4a2437e911</t>
-  </si>
-  <si>
-    <t>260312-W00011237</t>
-  </si>
-  <si>
     <t>2721</t>
   </si>
   <si>
     <t>PILIS</t>
   </si>
   <si>
-    <t>Nagy Lajos utca</t>
-  </si>
-  <si>
-    <t>69bbc6e2d96b4f4a2437f713</t>
-  </si>
-  <si>
-    <t>260317-F00000403</t>
-  </si>
-  <si>
     <t>2022</t>
   </si>
   <si>
     <t>TAHITÓTFALU</t>
   </si>
   <si>
-    <t>Pollack Mihály utca</t>
-  </si>
-  <si>
-    <t>69bbb20ed96b4f4a2437f3f2</t>
-  </si>
-  <si>
     <t>SZ-801</t>
   </si>
   <si>
-    <t>260317-F00003177</t>
-  </si>
-  <si>
-    <t>Mű út</t>
-  </si>
-  <si>
-    <t>69b96a2bd96b4f4a2437d3f5</t>
-  </si>
-  <si>
-    <t>260317-F00011087</t>
-  </si>
-  <si>
     <t>2191</t>
   </si>
   <si>
@@ -429,273 +234,24 @@
     <t>Szent András utca</t>
   </si>
   <si>
-    <t>69ba93dad96b4f4a2437e55f</t>
-  </si>
-  <si>
-    <t>260318-F00006965</t>
-  </si>
-  <si>
-    <t>1029</t>
-  </si>
-  <si>
-    <t>Torda utca</t>
-  </si>
-  <si>
-    <t>69baa1eed96b4f4a2437e74c</t>
-  </si>
-  <si>
-    <t>260318-F00008197</t>
-  </si>
-  <si>
-    <t>2253</t>
-  </si>
-  <si>
-    <t>TÁPIÓSÁG</t>
-  </si>
-  <si>
-    <t>Forgács utca</t>
-  </si>
-  <si>
-    <t>69bc1a6fd96b4f4a24380361</t>
-  </si>
-  <si>
-    <t>260318-F00009463</t>
-  </si>
-  <si>
-    <t>Kőrösi Csoma sétány</t>
-  </si>
-  <si>
-    <t>69bd30fbd96b4f4a24381084</t>
-  </si>
-  <si>
-    <t>260318-F00012744-2</t>
-  </si>
-  <si>
-    <t>1053</t>
-  </si>
-  <si>
-    <t>Vámház körút</t>
-  </si>
-  <si>
-    <t>69bad0c9d96b4f4a2437edda</t>
-  </si>
-  <si>
-    <t>260318-F00012908</t>
-  </si>
-  <si>
-    <t>2095</t>
-  </si>
-  <si>
-    <t>PILISSZÁNTÓ</t>
-  </si>
-  <si>
-    <t>69baf06bd96b4f4a2437f068</t>
-  </si>
-  <si>
-    <t>260318-W00009316</t>
-  </si>
-  <si>
-    <t>Szeleczky Márton utca</t>
-  </si>
-  <si>
-    <t>69bb196cd96b4f4a2437f1e2</t>
-  </si>
-  <si>
-    <t>260318-W00010963</t>
-  </si>
-  <si>
-    <t>Fiumei utca</t>
-  </si>
-  <si>
-    <t>69bbd9a7d96b4f4a2437fa41</t>
-  </si>
-  <si>
-    <t>260319-F00005386</t>
-  </si>
-  <si>
-    <t>69bc2f24d96b4f4a24380549</t>
-  </si>
-  <si>
-    <t>260319-F00012871</t>
-  </si>
-  <si>
-    <t>Egressy út</t>
-  </si>
-  <si>
-    <t>69bc2f24d96b4f4a2438054a</t>
-  </si>
-  <si>
-    <t>69bb5538d96b4f4a2437f233</t>
-  </si>
-  <si>
-    <t>260319-W00000218</t>
-  </si>
-  <si>
-    <t>Törökugrató utca</t>
-  </si>
-  <si>
-    <t>69bbae44d96b4f4a2437f38b</t>
-  </si>
-  <si>
-    <t>260319-W00001389</t>
-  </si>
-  <si>
-    <t>69bd34a2d96b4f4a243810f9</t>
-  </si>
-  <si>
-    <t>260320-F00006288</t>
-  </si>
-  <si>
-    <t>1115</t>
-  </si>
-  <si>
-    <t>Keveháza utca</t>
-  </si>
-  <si>
-    <t>69bd3932d96b4f4a24381183</t>
-  </si>
-  <si>
-    <t>260320-F00006610</t>
-  </si>
-  <si>
-    <t>1126</t>
-  </si>
-  <si>
-    <t>Böszörményi út</t>
-  </si>
-  <si>
-    <t>69bc92c7d96b4f4a24380794</t>
-  </si>
-  <si>
-    <t>260320-W00000088</t>
-  </si>
-  <si>
-    <t>Kővirág sor</t>
-  </si>
-  <si>
-    <t>FIZZ-1000841311</t>
-  </si>
-  <si>
-    <t>267004232</t>
-  </si>
-  <si>
-    <t>Margit körút</t>
-  </si>
-  <si>
-    <t>FIZZ-1000841952</t>
-  </si>
-  <si>
-    <t>267004251</t>
-  </si>
-  <si>
-    <t>2364</t>
-  </si>
-  <si>
-    <t>ÓCSA</t>
-  </si>
-  <si>
-    <t>Szabó Dezső utca</t>
-  </si>
-  <si>
-    <t>FIZZ-1000842506</t>
-  </si>
-  <si>
-    <t>267004257</t>
-  </si>
-  <si>
     <t>1139</t>
   </si>
   <si>
-    <t>Hajdú utca</t>
-  </si>
-  <si>
-    <t>303931206/1</t>
-  </si>
-  <si>
-    <t>303931206</t>
-  </si>
-  <si>
     <t>2151</t>
   </si>
   <si>
     <t>FÓT</t>
   </si>
   <si>
-    <t>Szent Benedek utca</t>
-  </si>
-  <si>
-    <t>304012890/1</t>
-  </si>
-  <si>
-    <t>304012890</t>
-  </si>
-  <si>
     <t>1148</t>
   </si>
   <si>
-    <t>Lengyel utca</t>
-  </si>
-  <si>
-    <t>304148849/1</t>
-  </si>
-  <si>
-    <t>304148849</t>
-  </si>
-  <si>
-    <t>304248173/1</t>
-  </si>
-  <si>
     <t>SZ-830</t>
   </si>
   <si>
-    <t>304248173</t>
-  </si>
-  <si>
-    <t>304248173/2</t>
-  </si>
-  <si>
-    <t>304248173/3</t>
-  </si>
-  <si>
-    <t>304248471/1</t>
-  </si>
-  <si>
-    <t>304248471</t>
-  </si>
-  <si>
-    <t>Ábrahám Pál utca</t>
-  </si>
-  <si>
-    <t>304362759/1</t>
-  </si>
-  <si>
-    <t>304362759</t>
-  </si>
-  <si>
     <t>1012</t>
   </si>
   <si>
-    <t>Márvány utca</t>
-  </si>
-  <si>
-    <t>304362759/2</t>
-  </si>
-  <si>
-    <t>304487710/1</t>
-  </si>
-  <si>
-    <t>304487710</t>
-  </si>
-  <si>
-    <t>1072</t>
-  </si>
-  <si>
-    <t>Klauzál tér</t>
-  </si>
-  <si>
-    <t>304487710/2</t>
-  </si>
-  <si>
     <t>304576799/1</t>
   </si>
   <si>
@@ -708,691 +264,1957 @@
     <t>304576799/2</t>
   </si>
   <si>
-    <t>304618804/1</t>
-  </si>
-  <si>
-    <t>304618804</t>
-  </si>
-  <si>
-    <t>304618804/2</t>
-  </si>
-  <si>
-    <t>304727040/1</t>
-  </si>
-  <si>
-    <t>304727040</t>
-  </si>
-  <si>
     <t>2300</t>
   </si>
   <si>
     <t>RÁCKEVE</t>
   </si>
   <si>
-    <t>Berkenye utca</t>
-  </si>
-  <si>
-    <t>304781237/1</t>
-  </si>
-  <si>
-    <t>304781237</t>
-  </si>
-  <si>
     <t>1106</t>
   </si>
   <si>
-    <t>Jászberényi út</t>
-  </si>
-  <si>
-    <t>304781237/2</t>
-  </si>
-  <si>
-    <t>304781551/1</t>
-  </si>
-  <si>
-    <t>304781551</t>
-  </si>
-  <si>
-    <t>1114</t>
-  </si>
-  <si>
-    <t>Kanizsai utca</t>
-  </si>
-  <si>
-    <t>304781628/1</t>
-  </si>
-  <si>
-    <t>304781628</t>
-  </si>
-  <si>
     <t>2337</t>
   </si>
   <si>
     <t>DÉLEGYHÁZA</t>
   </si>
   <si>
-    <t>304826294/1</t>
-  </si>
-  <si>
-    <t>304826294</t>
-  </si>
-  <si>
-    <t>Paptag utca</t>
-  </si>
-  <si>
-    <t>304826727/1</t>
-  </si>
-  <si>
-    <t>304826727</t>
-  </si>
-  <si>
-    <t>Dobó Katica utca</t>
-  </si>
-  <si>
-    <t>304874878/1</t>
-  </si>
-  <si>
-    <t>304874878</t>
-  </si>
-  <si>
-    <t>2254</t>
-  </si>
-  <si>
-    <t>SZENTMÁRTONKÁTA</t>
-  </si>
-  <si>
-    <t>Sport utca</t>
-  </si>
-  <si>
-    <t>304874878/2</t>
-  </si>
-  <si>
-    <t>304874917/1</t>
-  </si>
-  <si>
-    <t>304874917</t>
-  </si>
-  <si>
     <t>1134</t>
   </si>
   <si>
-    <t>Rózsafa utca</t>
-  </si>
-  <si>
-    <t>304874917/2</t>
-  </si>
-  <si>
-    <t>304875141/1</t>
-  </si>
-  <si>
-    <t>304875141</t>
-  </si>
-  <si>
-    <t>Diófa utca</t>
-  </si>
-  <si>
-    <t>304875152/1</t>
-  </si>
-  <si>
-    <t>304875152</t>
-  </si>
-  <si>
-    <t/>
-  </si>
-  <si>
-    <t>304875163/1</t>
-  </si>
-  <si>
-    <t>304875163</t>
-  </si>
-  <si>
-    <t>Kassák Lajos utca</t>
-  </si>
-  <si>
-    <t>304875262/1</t>
-  </si>
-  <si>
-    <t>304875262</t>
-  </si>
-  <si>
-    <t>304875287/1</t>
-  </si>
-  <si>
-    <t>304875287</t>
-  </si>
-  <si>
     <t>2317</t>
   </si>
   <si>
     <t>SZIGETCSÉP</t>
   </si>
   <si>
-    <t>Orgona Utca</t>
-  </si>
-  <si>
-    <t>304875287/2</t>
-  </si>
-  <si>
-    <t>304875341/1</t>
-  </si>
-  <si>
-    <t>304875341</t>
-  </si>
-  <si>
-    <t>1082</t>
-  </si>
-  <si>
-    <t>Corvin sétány</t>
-  </si>
-  <si>
-    <t>304875341/2</t>
-  </si>
-  <si>
-    <t>304875452/1</t>
-  </si>
-  <si>
-    <t>304875452</t>
-  </si>
-  <si>
-    <t>304875603/1</t>
-  </si>
-  <si>
     <t>SZ-860</t>
   </si>
   <si>
-    <t>304875603</t>
-  </si>
-  <si>
-    <t>304875730/1</t>
-  </si>
-  <si>
-    <t>304875730</t>
-  </si>
-  <si>
-    <t>Gyertyán utca</t>
-  </si>
-  <si>
-    <t>304875842/1</t>
-  </si>
-  <si>
-    <t>304875842</t>
-  </si>
-  <si>
     <t>Fő utca</t>
   </si>
   <si>
-    <t>304924480/1</t>
-  </si>
-  <si>
-    <t>304924480</t>
-  </si>
-  <si>
-    <t>Madách utca</t>
-  </si>
-  <si>
-    <t>304924614/1</t>
-  </si>
-  <si>
-    <t>304924614</t>
-  </si>
-  <si>
     <t>Faiskola utca</t>
   </si>
   <si>
-    <t>304924641/1</t>
-  </si>
-  <si>
-    <t>304924641</t>
-  </si>
-  <si>
-    <t>304924641/2</t>
-  </si>
-  <si>
-    <t>304924641/3</t>
-  </si>
-  <si>
-    <t>304924674/1</t>
-  </si>
-  <si>
-    <t>304924674</t>
-  </si>
-  <si>
-    <t>Lövőház utca</t>
-  </si>
-  <si>
-    <t>304924674/2</t>
-  </si>
-  <si>
-    <t>304924720/1</t>
-  </si>
-  <si>
-    <t>304924720</t>
-  </si>
-  <si>
-    <t>1043</t>
-  </si>
-  <si>
-    <t>Erzsébet utca</t>
-  </si>
-  <si>
-    <t>304924771/1</t>
-  </si>
-  <si>
-    <t>304924771</t>
-  </si>
-  <si>
-    <t>1141</t>
-  </si>
-  <si>
-    <t>Bartl János</t>
-  </si>
-  <si>
-    <t>304924814/1</t>
-  </si>
-  <si>
-    <t>304924814</t>
-  </si>
-  <si>
-    <t>1192</t>
-  </si>
-  <si>
-    <t>Kenyérmező utca</t>
-  </si>
-  <si>
-    <t>304924864/1</t>
-  </si>
-  <si>
-    <t>304924864</t>
-  </si>
-  <si>
-    <t>Bajcsy-Zsilinszky utca</t>
-  </si>
-  <si>
-    <t>304924934/1</t>
-  </si>
-  <si>
-    <t>304924934</t>
-  </si>
-  <si>
-    <t>1083</t>
-  </si>
-  <si>
-    <t>Práter utca</t>
-  </si>
-  <si>
-    <t>304924985/1</t>
-  </si>
-  <si>
-    <t>304924985</t>
-  </si>
-  <si>
-    <t>2251</t>
-  </si>
-  <si>
-    <t>TÁPIÓSZECSŐ</t>
-  </si>
-  <si>
     <t>József Attila utca</t>
   </si>
   <si>
-    <t>304925001/1</t>
-  </si>
-  <si>
-    <t>304925001</t>
-  </si>
-  <si>
-    <t>Majális utca</t>
-  </si>
-  <si>
-    <t>304925050/1</t>
-  </si>
-  <si>
-    <t>304925050</t>
-  </si>
-  <si>
-    <t>304925174/1</t>
-  </si>
-  <si>
-    <t>304925174</t>
-  </si>
-  <si>
-    <t>1194</t>
-  </si>
-  <si>
-    <t>Varjú Kálmán utca</t>
-  </si>
-  <si>
-    <t>304925244/1</t>
-  </si>
-  <si>
-    <t>304925244</t>
-  </si>
-  <si>
-    <t>304925358/1</t>
-  </si>
-  <si>
-    <t>304925358</t>
-  </si>
-  <si>
-    <t>Akácos utca</t>
-  </si>
-  <si>
-    <t>304925456/1</t>
-  </si>
-  <si>
-    <t>304925456</t>
-  </si>
-  <si>
-    <t>Júlia utca</t>
-  </si>
-  <si>
-    <t>304962977/1</t>
-  </si>
-  <si>
-    <t>304962977</t>
-  </si>
-  <si>
-    <t>1117</t>
-  </si>
-  <si>
-    <t>Nándorfejérvári út</t>
-  </si>
-  <si>
-    <t>304963294/1</t>
-  </si>
-  <si>
-    <t>304963294</t>
-  </si>
-  <si>
-    <t>1111</t>
-  </si>
-  <si>
-    <t>Budafoki út</t>
-  </si>
-  <si>
-    <t>304963389/1</t>
-  </si>
-  <si>
-    <t>304963389</t>
-  </si>
-  <si>
-    <t>Halászy Károly</t>
-  </si>
-  <si>
-    <t>305056382/1</t>
-  </si>
-  <si>
-    <t>305056382</t>
-  </si>
-  <si>
     <t>1211</t>
   </si>
   <si>
-    <t>Ady Endre</t>
-  </si>
-  <si>
-    <t>305056382/2</t>
-  </si>
-  <si>
-    <t>305056382/3</t>
-  </si>
-  <si>
-    <t>305272710/1</t>
-  </si>
-  <si>
-    <t>305272710</t>
-  </si>
-  <si>
-    <t>305272710/2</t>
-  </si>
-  <si>
-    <t>202603202600608601</t>
-  </si>
-  <si>
-    <t>NFD6-03-13-Z5VZ</t>
-  </si>
-  <si>
-    <t>1221</t>
-  </si>
-  <si>
-    <t>Leányka utca</t>
-  </si>
-  <si>
-    <t>202603202600623401</t>
-  </si>
-  <si>
-    <t>NFD6-03-14-72L8</t>
-  </si>
-  <si>
     <t>Kiss János altábornagy utca</t>
   </si>
   <si>
-    <t>202603202600624501</t>
-  </si>
-  <si>
-    <t>NFD6-03-14-S3R2</t>
-  </si>
-  <si>
-    <t>Béla utca</t>
-  </si>
-  <si>
-    <t>202603202600659501</t>
-  </si>
-  <si>
-    <t>NFD6-03-18-QZ9G</t>
-  </si>
-  <si>
-    <t>1046</t>
-  </si>
-  <si>
-    <t>Erdősor út</t>
-  </si>
-  <si>
-    <t>202603202600667101</t>
-  </si>
-  <si>
-    <t>NFD6-03-19-2ENJ</t>
-  </si>
-  <si>
-    <t>2244</t>
-  </si>
-  <si>
-    <t>ÚRI</t>
-  </si>
-  <si>
-    <t>Hold utca</t>
-  </si>
-  <si>
-    <t>202603202600671301</t>
-  </si>
-  <si>
-    <t>NFD6-03-19-3MWZ</t>
-  </si>
-  <si>
-    <t>2194</t>
-  </si>
-  <si>
-    <t>TURA</t>
-  </si>
-  <si>
-    <t>Széchenyi István utca</t>
-  </si>
-  <si>
-    <t>202603202600667401</t>
-  </si>
-  <si>
-    <t>NFD6-03-19-6L2T</t>
-  </si>
-  <si>
-    <t>1151</t>
-  </si>
-  <si>
-    <t>Énekes utca</t>
-  </si>
-  <si>
-    <t>202603202600667501</t>
-  </si>
-  <si>
-    <t>NFD6-03-19-78C2</t>
-  </si>
-  <si>
-    <t>Terstyánszky Ödön utca</t>
-  </si>
-  <si>
-    <t>202603202600673901</t>
-  </si>
-  <si>
-    <t>NFD6-03-19-9N67</t>
-  </si>
-  <si>
     <t>2162</t>
   </si>
   <si>
     <t>ŐRBOTTYÁN</t>
   </si>
   <si>
-    <t>202603202600668401</t>
-  </si>
-  <si>
-    <t>NFD6-03-19-AHUS</t>
-  </si>
-  <si>
-    <t>Felsőbánya utca</t>
-  </si>
-  <si>
-    <t>202603202600667901</t>
-  </si>
-  <si>
-    <t>NFD6-03-19-CKBY</t>
-  </si>
-  <si>
     <t>Albert utca</t>
   </si>
   <si>
-    <t>202603202600668701</t>
-  </si>
-  <si>
-    <t>NFD6-03-19-JWYF</t>
-  </si>
-  <si>
-    <t>Tölgyfa utca</t>
-  </si>
-  <si>
-    <t>202603202600668702</t>
-  </si>
-  <si>
-    <t>202603202600668703</t>
-  </si>
-  <si>
-    <t>202603202600671201</t>
-  </si>
-  <si>
-    <t>NFD6-03-19-LXNY</t>
-  </si>
-  <si>
-    <t>Gróf Teleki utca</t>
-  </si>
-  <si>
-    <t>202603202600671202</t>
-  </si>
-  <si>
-    <t>202603202600672201</t>
-  </si>
-  <si>
-    <t>NFD6-03-19-R6E6</t>
-  </si>
-  <si>
     <t>Vízimolnár utca</t>
   </si>
   <si>
-    <t>202603202600666301</t>
-  </si>
-  <si>
-    <t>NFD6-03-19-VNAZ</t>
-  </si>
-  <si>
-    <t>Telepes utca</t>
-  </si>
-  <si>
-    <t>202603202600673301</t>
-  </si>
-  <si>
-    <t>NFE6-03-19-4427</t>
-  </si>
-  <si>
-    <t>Rónai György utca</t>
-  </si>
-  <si>
-    <t>202603202600673101</t>
-  </si>
-  <si>
-    <t>NFE6-03-19-5GAC</t>
-  </si>
-  <si>
-    <t>1087</t>
-  </si>
-  <si>
-    <t>Tbiliszi tér</t>
-  </si>
-  <si>
-    <t>202603202600675001</t>
-  </si>
-  <si>
-    <t>NFE6-03-19-AVHC</t>
-  </si>
-  <si>
-    <t>2241</t>
-  </si>
-  <si>
-    <t>SÜLYSÁP</t>
-  </si>
-  <si>
-    <t>Dózsa György köz</t>
-  </si>
-  <si>
-    <t>202603202600674001</t>
-  </si>
-  <si>
-    <t>NFE6-03-19-GXVH</t>
-  </si>
-  <si>
-    <t>Atlasz utca</t>
-  </si>
-  <si>
-    <t>202603202600674002</t>
-  </si>
-  <si>
-    <t>202603202600674601</t>
-  </si>
-  <si>
-    <t>NFE6-03-19-QE2A</t>
-  </si>
-  <si>
-    <t>2747</t>
-  </si>
-  <si>
-    <t>TÖRTEL</t>
-  </si>
-  <si>
     <t>Kossuth Lajos út</t>
   </si>
   <si>
-    <t>159995579538415524</t>
-  </si>
-  <si>
-    <t>SA26/H001271</t>
-  </si>
-  <si>
-    <t>Mirtusz utca</t>
-  </si>
-  <si>
-    <t>159995579538415531</t>
-  </si>
-  <si>
-    <t>NFD6-03-19-J6L3</t>
-  </si>
-  <si>
-    <t>AUCHAN_ÁRUHÁZI</t>
+    <t>69bbf23fd96b4f4a2437fdc6</t>
+  </si>
+  <si>
+    <t>260226-W00011690</t>
+  </si>
+  <si>
+    <t>Bánki Donát utca</t>
+  </si>
+  <si>
+    <t>69b538f86967eb2a8b5ce608</t>
+  </si>
+  <si>
+    <t>260310-F00003841</t>
+  </si>
+  <si>
+    <t>Istvánmezei út</t>
+  </si>
+  <si>
+    <t>69ba9de8d96b4f4a2437e6da</t>
+  </si>
+  <si>
+    <t>260314-F00002801</t>
+  </si>
+  <si>
+    <t>1155</t>
+  </si>
+  <si>
+    <t>Mézeskalács tér</t>
+  </si>
+  <si>
+    <t>69bd2dc5d96b4f4a2438101b</t>
+  </si>
+  <si>
+    <t>260316-F00009354</t>
+  </si>
+  <si>
+    <t>69c10f9dd96b4f4a2438383b</t>
+  </si>
+  <si>
+    <t>260316-F00010130</t>
+  </si>
+  <si>
+    <t>1034</t>
+  </si>
+  <si>
+    <t>Bécsi út</t>
+  </si>
+  <si>
+    <t>69be9ea6d96b4f4a243823a8</t>
+  </si>
+  <si>
+    <t>260317-F00006815</t>
+  </si>
+  <si>
+    <t>Forrásmajori utca B ép.</t>
+  </si>
+  <si>
+    <t>69bd3be0d96b4f4a24381202</t>
+  </si>
+  <si>
+    <t>260317-W00004291</t>
+  </si>
+  <si>
+    <t>Mátyás király utca</t>
+  </si>
+  <si>
+    <t>69c112c0d96b4f4a243838c0</t>
+  </si>
+  <si>
+    <t>260318-F00004640-2</t>
+  </si>
+  <si>
+    <t>Dévai utca</t>
+  </si>
+  <si>
+    <t>69baa7c8d96b4f4a2437e827</t>
+  </si>
+  <si>
+    <t>260318-F00009029</t>
+  </si>
+  <si>
+    <t>1131</t>
+  </si>
+  <si>
+    <t>Futár utca</t>
+  </si>
+  <si>
+    <t>69bacae9d96b4f4a2437ed41</t>
+  </si>
+  <si>
+    <t>260318-W00007404</t>
+  </si>
+  <si>
+    <t>Ároktő utca</t>
+  </si>
+  <si>
+    <t>69bacae9d96b4f4a2437ed42</t>
+  </si>
+  <si>
+    <t>69bb0201d96b4f4a2437f153</t>
+  </si>
+  <si>
+    <t>260318-W00010468</t>
+  </si>
+  <si>
+    <t>2161</t>
+  </si>
+  <si>
+    <t>CSOMÁD</t>
+  </si>
+  <si>
+    <t>Vitéz utca</t>
+  </si>
+  <si>
+    <t>69bc4201d96b4f4a2438069e</t>
+  </si>
+  <si>
+    <t>SZ-827</t>
+  </si>
+  <si>
+    <t>260319-F00013523</t>
+  </si>
+  <si>
+    <t>2768</t>
+  </si>
+  <si>
+    <t>ÚJSZILVÁS</t>
+  </si>
+  <si>
+    <t>Alkotmány utca</t>
+  </si>
+  <si>
+    <t>69bc4201d96b4f4a2438069f</t>
+  </si>
+  <si>
+    <t>69bbdaccd96b4f4a2437fa69</t>
+  </si>
+  <si>
+    <t>260319-W00003828</t>
+  </si>
+  <si>
+    <t>2015</t>
+  </si>
+  <si>
+    <t>SZIGETMONOSTOR</t>
+  </si>
+  <si>
+    <t>Füzeserdő utca</t>
+  </si>
+  <si>
+    <t>69bc0e60d96b4f4a24380202</t>
+  </si>
+  <si>
+    <t>SZ-820</t>
+  </si>
+  <si>
+    <t>260319-W00006527</t>
+  </si>
+  <si>
+    <t>2351</t>
+  </si>
+  <si>
+    <t>ALSÓNÉMEDI</t>
+  </si>
+  <si>
+    <t>Haraszti út</t>
+  </si>
+  <si>
+    <t>69bcfb18d96b4f4a2438084f</t>
+  </si>
+  <si>
+    <t>260320-F00000605</t>
+  </si>
+  <si>
+    <t>Huszka Jenő utca</t>
+  </si>
+  <si>
+    <t>69bd186cd96b4f4a24380ce1</t>
+  </si>
+  <si>
+    <t>260320-F00003438-5</t>
+  </si>
+  <si>
+    <t>Balassa Bálint utca</t>
+  </si>
+  <si>
+    <t>69bd186cd96b4f4a24380ce2</t>
+  </si>
+  <si>
+    <t>69bd3a60d96b4f4a243811d2</t>
+  </si>
+  <si>
+    <t>260320-F00006708-1</t>
+  </si>
+  <si>
+    <t>Mester utca</t>
+  </si>
+  <si>
+    <t>69bd4d20d96b4f4a2438144b</t>
+  </si>
+  <si>
+    <t>260320-F00008368</t>
+  </si>
+  <si>
+    <t>Ivánka Pál utca</t>
+  </si>
+  <si>
+    <t>69bd6234d96b4f4a24381725</t>
+  </si>
+  <si>
+    <t>260320-F00010949</t>
+  </si>
+  <si>
+    <t>69bd66fad96b4f4a24381785</t>
+  </si>
+  <si>
+    <t>260320-F00011230</t>
+  </si>
+  <si>
+    <t>1171</t>
+  </si>
+  <si>
+    <t>Vízforrás utca</t>
+  </si>
+  <si>
+    <t>69bd66fad96b4f4a24381786</t>
+  </si>
+  <si>
+    <t>69bd0804d96b4f4a24380a2e</t>
+  </si>
+  <si>
+    <t>260320-W00002265</t>
+  </si>
+  <si>
+    <t>2600</t>
+  </si>
+  <si>
+    <t>VÁC</t>
+  </si>
+  <si>
+    <t>Dr. Csányi László körút</t>
+  </si>
+  <si>
+    <t>69bd2eaed96b4f4a2438102b</t>
+  </si>
+  <si>
+    <t>260320-W00004231</t>
+  </si>
+  <si>
+    <t>1183</t>
+  </si>
+  <si>
+    <t>Szent Lőrinc sétány</t>
+  </si>
+  <si>
+    <t>69bd4999d96b4f4a243813b2</t>
+  </si>
+  <si>
+    <t>260320-W00005323</t>
+  </si>
+  <si>
+    <t>Virág utca</t>
+  </si>
+  <si>
+    <t>69bd4999d96b4f4a243813b5</t>
+  </si>
+  <si>
+    <t>69bfbd9ed96b4f4a24382a70</t>
+  </si>
+  <si>
+    <t>260320-W00007434</t>
+  </si>
+  <si>
+    <t>1185</t>
+  </si>
+  <si>
+    <t>Fráter Lóránd utca</t>
+  </si>
+  <si>
+    <t>69bd7172d96b4f4a243818ab</t>
+  </si>
+  <si>
+    <t>260320-W00007515</t>
+  </si>
+  <si>
+    <t>1071</t>
+  </si>
+  <si>
+    <t>Bajza utca</t>
+  </si>
+  <si>
+    <t>69be678dd96b4f4a24381f25</t>
+  </si>
+  <si>
+    <t>260321-F00001884</t>
+  </si>
+  <si>
+    <t>Farkasfa utca</t>
+  </si>
+  <si>
+    <t>69bebabad96b4f4a24382569</t>
+  </si>
+  <si>
+    <t>260321-F00005399</t>
+  </si>
+  <si>
+    <t>Gyékényes utca</t>
+  </si>
+  <si>
+    <t>69be6534d96b4f4a24381ed4</t>
+  </si>
+  <si>
+    <t>260321-W00002983</t>
+  </si>
+  <si>
+    <t>69be733dd96b4f4a24382065</t>
+  </si>
+  <si>
+    <t>260321-W00003681</t>
+  </si>
+  <si>
+    <t>1048</t>
+  </si>
+  <si>
+    <t>Székes utca</t>
+  </si>
+  <si>
+    <t>69bea475d96b4f4a24382412</t>
+  </si>
+  <si>
+    <t>260321-W00005895</t>
+  </si>
+  <si>
+    <t>1112</t>
+  </si>
+  <si>
+    <t>Rétköz utca</t>
+  </si>
+  <si>
+    <t>69bebe42d96b4f4a243825c1</t>
+  </si>
+  <si>
+    <t>260321-W00006434</t>
+  </si>
+  <si>
+    <t>1225</t>
+  </si>
+  <si>
+    <t>Angeli utca</t>
+  </si>
+  <si>
+    <t>69bef9ffd96b4f4a24382820</t>
+  </si>
+  <si>
+    <t>260321-W00009502</t>
+  </si>
+  <si>
+    <t>1153</t>
+  </si>
+  <si>
+    <t>Pázmány Péter utca</t>
+  </si>
+  <si>
+    <t>69bef9ffd96b4f4a24382821</t>
+  </si>
+  <si>
+    <t>69bfc13dd96b4f4a24382ac9</t>
+  </si>
+  <si>
+    <t>260322-W00003148</t>
+  </si>
+  <si>
+    <t>1212</t>
+  </si>
+  <si>
+    <t>Dunadűlő út</t>
+  </si>
+  <si>
+    <t>69bfc133d96b4f4a24382ac2</t>
+  </si>
+  <si>
+    <t>260322-W00003155</t>
+  </si>
+  <si>
+    <t>Dolmány utca</t>
+  </si>
+  <si>
+    <t>69bfdfafd96b4f4a24382c9d</t>
+  </si>
+  <si>
+    <t>260322-W00004465</t>
+  </si>
+  <si>
+    <t>1182</t>
+  </si>
+  <si>
+    <t>Batthyány Lajos utca</t>
+  </si>
+  <si>
+    <t>69c001aad96b4f4a24382e88</t>
+  </si>
+  <si>
+    <t>260322-W00005710</t>
+  </si>
+  <si>
+    <t>Lakkozó utca</t>
+  </si>
+  <si>
+    <t>69c0227ed96b4f4a2438303a</t>
+  </si>
+  <si>
+    <t>260322-W00007489</t>
+  </si>
+  <si>
+    <t>1144</t>
+  </si>
+  <si>
+    <t>Ond vezér útja</t>
+  </si>
+  <si>
+    <t>69c1300ad96b4f4a24383e04</t>
+  </si>
+  <si>
+    <t>260323-F00007391</t>
+  </si>
+  <si>
+    <t>FIZZ-1000843894</t>
+  </si>
+  <si>
+    <t>267004290</t>
+  </si>
+  <si>
+    <t>Irinyi utca</t>
+  </si>
+  <si>
+    <t>1449-372868</t>
+  </si>
+  <si>
+    <t>267004308</t>
+  </si>
+  <si>
+    <t>301062942/1</t>
+  </si>
+  <si>
+    <t>301062942</t>
+  </si>
+  <si>
+    <t>2163</t>
+  </si>
+  <si>
+    <t>VÁCRÁTÓT</t>
+  </si>
+  <si>
+    <t>Hunyadi utca</t>
+  </si>
+  <si>
+    <t>301062942/2</t>
+  </si>
+  <si>
+    <t>303795664/1</t>
+  </si>
+  <si>
+    <t>303795664</t>
+  </si>
+  <si>
+    <t>2094</t>
+  </si>
+  <si>
+    <t>NAGYKOVÁCSI</t>
+  </si>
+  <si>
+    <t>Greszl Ferenc utca</t>
+  </si>
+  <si>
+    <t>304148816/1</t>
+  </si>
+  <si>
+    <t>304148816</t>
+  </si>
+  <si>
+    <t>2093</t>
+  </si>
+  <si>
+    <t>BUDAJENŐ</t>
+  </si>
+  <si>
+    <t>Pacsirta Utca</t>
+  </si>
+  <si>
+    <t>304487218/1</t>
+  </si>
+  <si>
+    <t>304487218</t>
+  </si>
+  <si>
+    <t>Szent Miklós</t>
+  </si>
+  <si>
+    <t>304577257/1</t>
+  </si>
+  <si>
+    <t>304577257</t>
+  </si>
+  <si>
+    <t>Kerektó utca</t>
+  </si>
+  <si>
+    <t>304619242/1</t>
+  </si>
+  <si>
+    <t>304619242</t>
+  </si>
+  <si>
+    <t>Lövölde tér</t>
+  </si>
+  <si>
+    <t>304675745/1</t>
+  </si>
+  <si>
+    <t>304675745</t>
+  </si>
+  <si>
+    <t>Zoltán utca</t>
+  </si>
+  <si>
+    <t>304675801/1</t>
+  </si>
+  <si>
+    <t>304675801</t>
+  </si>
+  <si>
+    <t>Tomori Utca</t>
+  </si>
+  <si>
+    <t>304726503/1</t>
+  </si>
+  <si>
+    <t>304726503</t>
+  </si>
+  <si>
+    <t>1202</t>
+  </si>
+  <si>
+    <t>Zombor utca</t>
+  </si>
+  <si>
+    <t>304726779/1</t>
+  </si>
+  <si>
+    <t>304726779</t>
+  </si>
+  <si>
+    <t>Riadó utca</t>
+  </si>
+  <si>
+    <t>304827063/1</t>
+  </si>
+  <si>
+    <t>304827063</t>
+  </si>
+  <si>
+    <t>Kökény utca</t>
+  </si>
+  <si>
+    <t>304874981/1</t>
+  </si>
+  <si>
+    <t>304874981</t>
+  </si>
+  <si>
+    <t>Szabadság UTCA</t>
+  </si>
+  <si>
+    <t>304875420/1</t>
+  </si>
+  <si>
+    <t>304875420</t>
+  </si>
+  <si>
+    <t>1156</t>
+  </si>
+  <si>
+    <t>Nádastó park</t>
+  </si>
+  <si>
+    <t>304875448/1</t>
+  </si>
+  <si>
+    <t>304875448</t>
+  </si>
+  <si>
+    <t>2085</t>
+  </si>
+  <si>
+    <t>PILISVÖRÖSVÁR</t>
+  </si>
+  <si>
+    <t>Fácán utca</t>
+  </si>
+  <si>
+    <t>304875448/2</t>
+  </si>
+  <si>
+    <t>304875776/1</t>
+  </si>
+  <si>
+    <t>304875776</t>
+  </si>
+  <si>
+    <t>2092</t>
+  </si>
+  <si>
+    <t>BUDAKESZI</t>
+  </si>
+  <si>
+    <t>Angol utca</t>
+  </si>
+  <si>
+    <t>304924541/1</t>
+  </si>
+  <si>
+    <t>304924541</t>
+  </si>
+  <si>
+    <t>1133</t>
+  </si>
+  <si>
+    <t>Kárpát utca</t>
+  </si>
+  <si>
+    <t>304925144/1</t>
+  </si>
+  <si>
+    <t>304925144</t>
+  </si>
+  <si>
+    <t>Ady Endre út</t>
+  </si>
+  <si>
+    <t>304925145/1</t>
+  </si>
+  <si>
+    <t>304925145</t>
+  </si>
+  <si>
+    <t>2096</t>
+  </si>
+  <si>
+    <t>ÜRÖM</t>
+  </si>
+  <si>
+    <t>Görgey utca</t>
+  </si>
+  <si>
+    <t>304925314/1</t>
+  </si>
+  <si>
+    <t>304925314</t>
+  </si>
+  <si>
+    <t>Rákóczi Ferenc utca</t>
+  </si>
+  <si>
+    <t>304925314/2</t>
+  </si>
+  <si>
+    <t>304962957/1</t>
+  </si>
+  <si>
+    <t>304962957</t>
+  </si>
+  <si>
+    <t>2100</t>
+  </si>
+  <si>
+    <t>GÖDÖLLŐ</t>
+  </si>
+  <si>
+    <t>Búzavirág utca</t>
+  </si>
+  <si>
+    <t>304962957/2</t>
+  </si>
+  <si>
+    <t>304963075/1</t>
+  </si>
+  <si>
+    <t>304963075</t>
+  </si>
+  <si>
+    <t>1044</t>
+  </si>
+  <si>
+    <t>Kisfaludy utca</t>
+  </si>
+  <si>
+    <t>304963094/1</t>
+  </si>
+  <si>
+    <t>304963094</t>
+  </si>
+  <si>
+    <t>Állomás utca</t>
+  </si>
+  <si>
+    <t>304963473/1</t>
+  </si>
+  <si>
+    <t>304963473</t>
+  </si>
+  <si>
+    <t>Keresztúri út</t>
+  </si>
+  <si>
+    <t>304963618/1</t>
+  </si>
+  <si>
+    <t>304963618</t>
+  </si>
+  <si>
+    <t>2143</t>
+  </si>
+  <si>
+    <t>KISTARCSA</t>
+  </si>
+  <si>
+    <t>Bethlen Gábor utca</t>
+  </si>
+  <si>
+    <t>304963679/1</t>
+  </si>
+  <si>
+    <t>SZ-810</t>
+  </si>
+  <si>
+    <t>304963679</t>
+  </si>
+  <si>
+    <t>1136</t>
+  </si>
+  <si>
+    <t>Pannónia utca</t>
+  </si>
+  <si>
+    <t>304963838/1</t>
+  </si>
+  <si>
+    <t>304963838</t>
+  </si>
+  <si>
+    <t>1073</t>
+  </si>
+  <si>
+    <t>Kertész utca</t>
+  </si>
+  <si>
+    <t>305006980/1</t>
+  </si>
+  <si>
+    <t>305006980</t>
+  </si>
+  <si>
+    <t>Nagyszénás utca</t>
+  </si>
+  <si>
+    <t>305007072/1</t>
+  </si>
+  <si>
+    <t>305007072</t>
+  </si>
+  <si>
+    <t>2234</t>
+  </si>
+  <si>
+    <t>MAGLÓD</t>
+  </si>
+  <si>
+    <t>Dózsa György utca</t>
+  </si>
+  <si>
+    <t>305007198/1</t>
+  </si>
+  <si>
+    <t>305007198</t>
+  </si>
+  <si>
+    <t>1163</t>
+  </si>
+  <si>
+    <t>Kicsi utca</t>
+  </si>
+  <si>
+    <t>305007418/1</t>
+  </si>
+  <si>
+    <t>305007418</t>
+  </si>
+  <si>
+    <t>1056</t>
+  </si>
+  <si>
+    <t>Nyáry Pál</t>
+  </si>
+  <si>
+    <t>305007473/1</t>
+  </si>
+  <si>
+    <t>305007473</t>
+  </si>
+  <si>
+    <t>2144</t>
+  </si>
+  <si>
+    <t>KEREPES</t>
+  </si>
+  <si>
+    <t>Szőlő utca</t>
+  </si>
+  <si>
+    <t>305007473/2</t>
+  </si>
+  <si>
+    <t>305007533/1</t>
+  </si>
+  <si>
+    <t>305007533</t>
+  </si>
+  <si>
+    <t>Szendrey Júlia utca</t>
+  </si>
+  <si>
+    <t>305007826/1</t>
+  </si>
+  <si>
+    <t>305007826</t>
+  </si>
+  <si>
+    <t>2173</t>
+  </si>
+  <si>
+    <t>KARTAL</t>
+  </si>
+  <si>
+    <t>Béke utca</t>
+  </si>
+  <si>
+    <t>305007893/1</t>
+  </si>
+  <si>
+    <t>305007893</t>
+  </si>
+  <si>
+    <t>Zsélyi Aladár utca</t>
+  </si>
+  <si>
+    <t>305007918/1</t>
+  </si>
+  <si>
+    <t>305007918</t>
+  </si>
+  <si>
+    <t>1201</t>
+  </si>
+  <si>
+    <t>Alsóteleki utca</t>
+  </si>
+  <si>
+    <t>305007918/2</t>
+  </si>
+  <si>
+    <t>305056393/1</t>
+  </si>
+  <si>
+    <t>305056393</t>
+  </si>
+  <si>
+    <t>1113</t>
+  </si>
+  <si>
+    <t>Ulászló utca</t>
+  </si>
+  <si>
+    <t>305056393/2</t>
+  </si>
+  <si>
+    <t>305056393/3</t>
+  </si>
+  <si>
+    <t>305056609/1</t>
+  </si>
+  <si>
+    <t>SZ-800</t>
+  </si>
+  <si>
+    <t>305056609</t>
+  </si>
+  <si>
+    <t>1039</t>
+  </si>
+  <si>
+    <t>Jókai utca</t>
+  </si>
+  <si>
+    <t>305056694/1</t>
+  </si>
+  <si>
+    <t>305056694</t>
+  </si>
+  <si>
+    <t>Berkenye sétány</t>
+  </si>
+  <si>
+    <t>305056694/2</t>
+  </si>
+  <si>
+    <t>305056816/1</t>
+  </si>
+  <si>
+    <t>305056816</t>
+  </si>
+  <si>
+    <t>Sziget utca</t>
+  </si>
+  <si>
+    <t>305056905/1</t>
+  </si>
+  <si>
+    <t>305056905</t>
+  </si>
+  <si>
+    <t>Ganz Ábrahám utca</t>
+  </si>
+  <si>
+    <t>305056929/1</t>
+  </si>
+  <si>
+    <t>SZ-829</t>
+  </si>
+  <si>
+    <t>305056929</t>
+  </si>
+  <si>
+    <t>1094</t>
+  </si>
+  <si>
+    <t>Bokréta utca</t>
+  </si>
+  <si>
+    <t>305057012/1</t>
+  </si>
+  <si>
+    <t>305057012</t>
+  </si>
+  <si>
+    <t>2131</t>
+  </si>
+  <si>
+    <t>GÖD</t>
+  </si>
+  <si>
+    <t>Nemeskéri-Kiss Miklós Út</t>
+  </si>
+  <si>
+    <t>305057251/1</t>
+  </si>
+  <si>
+    <t>305057251</t>
+  </si>
+  <si>
+    <t>Táncsics Mihály utca</t>
+  </si>
+  <si>
+    <t>305113867/1</t>
+  </si>
+  <si>
+    <t>305113867</t>
+  </si>
+  <si>
+    <t>Átlós utca</t>
+  </si>
+  <si>
+    <t>305113867/2</t>
+  </si>
+  <si>
+    <t>305113879/1</t>
+  </si>
+  <si>
+    <t>305113879</t>
+  </si>
+  <si>
+    <t>2089</t>
+  </si>
+  <si>
+    <t>TELKI</t>
+  </si>
+  <si>
+    <t>Vadrózsa utca</t>
+  </si>
+  <si>
+    <t>305114069/1</t>
+  </si>
+  <si>
+    <t>305114069</t>
+  </si>
+  <si>
+    <t>1105</t>
+  </si>
+  <si>
+    <t>Kőrösi Csoma Sándor út</t>
+  </si>
+  <si>
+    <t>305114112/1</t>
+  </si>
+  <si>
+    <t>305114112</t>
+  </si>
+  <si>
+    <t>1152</t>
+  </si>
+  <si>
+    <t>Mátyás utca</t>
+  </si>
+  <si>
+    <t>305114335/1</t>
+  </si>
+  <si>
+    <t>305114335</t>
+  </si>
+  <si>
+    <t>2080</t>
+  </si>
+  <si>
+    <t>PILISJÁSZFALU</t>
+  </si>
+  <si>
+    <t>Liliom utca</t>
+  </si>
+  <si>
+    <t>305114363/1</t>
+  </si>
+  <si>
+    <t>305114363</t>
+  </si>
+  <si>
+    <t>2440</t>
+  </si>
+  <si>
+    <t>SZÁZHALOMBATTA</t>
+  </si>
+  <si>
+    <t>Erkel Ferenc Körút</t>
+  </si>
+  <si>
+    <t>305114406/1</t>
+  </si>
+  <si>
+    <t>305114406</t>
+  </si>
+  <si>
+    <t>305114499/1</t>
+  </si>
+  <si>
+    <t>305114499</t>
+  </si>
+  <si>
+    <t>2132</t>
+  </si>
+  <si>
+    <t>Széchenyi utca</t>
+  </si>
+  <si>
+    <t>305169885/1</t>
+  </si>
+  <si>
+    <t>305169885</t>
+  </si>
+  <si>
+    <t>Napsugár utca</t>
+  </si>
+  <si>
+    <t>305170207/1</t>
+  </si>
+  <si>
+    <t>305170207</t>
+  </si>
+  <si>
+    <t>1119</t>
+  </si>
+  <si>
+    <t>305170237/1</t>
+  </si>
+  <si>
+    <t>305170237</t>
+  </si>
+  <si>
+    <t>1213</t>
+  </si>
+  <si>
+    <t>Kőrösi Sándor utca</t>
+  </si>
+  <si>
+    <t>305170260/1</t>
+  </si>
+  <si>
+    <t>305170260</t>
+  </si>
+  <si>
+    <t>Andrássy út</t>
+  </si>
+  <si>
+    <t>305170312/1</t>
+  </si>
+  <si>
+    <t>305170312</t>
+  </si>
+  <si>
+    <t>Cziráki utca</t>
+  </si>
+  <si>
+    <t>305170315/1</t>
+  </si>
+  <si>
+    <t>305170315</t>
+  </si>
+  <si>
+    <t>Viola utca</t>
+  </si>
+  <si>
+    <t>305170484/1</t>
+  </si>
+  <si>
+    <t>305170484</t>
+  </si>
+  <si>
+    <t>Attila utca</t>
+  </si>
+  <si>
+    <t>305170526/1</t>
+  </si>
+  <si>
+    <t>305170526</t>
+  </si>
+  <si>
+    <t>2700</t>
+  </si>
+  <si>
+    <t>CEGLÉD</t>
+  </si>
+  <si>
+    <t>Molnár utca</t>
+  </si>
+  <si>
+    <t>305170526/2</t>
+  </si>
+  <si>
+    <t>305170526/3</t>
+  </si>
+  <si>
+    <t>305170683/1</t>
+  </si>
+  <si>
+    <t>305170683</t>
+  </si>
+  <si>
+    <t>Lugas Utca</t>
+  </si>
+  <si>
+    <t>305225367/1</t>
+  </si>
+  <si>
+    <t>305225367</t>
+  </si>
+  <si>
+    <t>Madách Imre utca</t>
+  </si>
+  <si>
+    <t>305225558/1</t>
+  </si>
+  <si>
+    <t>305225558</t>
+  </si>
+  <si>
+    <t>1124</t>
+  </si>
+  <si>
+    <t>Németvölgyi út</t>
+  </si>
+  <si>
+    <t>305225584/1</t>
+  </si>
+  <si>
+    <t>305225584</t>
+  </si>
+  <si>
+    <t>2737</t>
+  </si>
+  <si>
+    <t>CEGLÉDBERCEL</t>
+  </si>
+  <si>
+    <t>305225973/1</t>
+  </si>
+  <si>
+    <t>305225973</t>
+  </si>
+  <si>
+    <t>2750</t>
+  </si>
+  <si>
+    <t>NAGYKŐRÖS</t>
+  </si>
+  <si>
+    <t>Vízállás Gátér</t>
+  </si>
+  <si>
+    <t>305225973/2</t>
+  </si>
+  <si>
+    <t>305226201/1</t>
+  </si>
+  <si>
+    <t>305226201</t>
+  </si>
+  <si>
+    <t>1223</t>
+  </si>
+  <si>
+    <t>Tűzliliom utca</t>
+  </si>
+  <si>
+    <t>305226259/1</t>
+  </si>
+  <si>
+    <t>305226259</t>
+  </si>
+  <si>
+    <t>Rozália utca</t>
+  </si>
+  <si>
+    <t>305272882/1</t>
+  </si>
+  <si>
+    <t>305272882</t>
+  </si>
+  <si>
+    <t>2073</t>
+  </si>
+  <si>
+    <t>TÖK</t>
+  </si>
+  <si>
+    <t>Széchenyi utca utca</t>
+  </si>
+  <si>
+    <t>305272973/1</t>
+  </si>
+  <si>
+    <t>305272973</t>
+  </si>
+  <si>
+    <t>2740</t>
+  </si>
+  <si>
+    <t>ABONY</t>
+  </si>
+  <si>
+    <t>Magyar Benigna utca</t>
+  </si>
+  <si>
+    <t>305272999/1</t>
+  </si>
+  <si>
+    <t>305272999</t>
+  </si>
+  <si>
+    <t>1021</t>
+  </si>
+  <si>
+    <t>Zuhatag sor</t>
+  </si>
+  <si>
+    <t>305273069/1</t>
+  </si>
+  <si>
+    <t>305273069</t>
+  </si>
+  <si>
+    <t>1098</t>
+  </si>
+  <si>
+    <t>Csengettyű utca</t>
+  </si>
+  <si>
+    <t>305273073/1</t>
+  </si>
+  <si>
+    <t>305273073</t>
+  </si>
+  <si>
+    <t>Füst Milán utca</t>
+  </si>
+  <si>
+    <t>305273117/1</t>
+  </si>
+  <si>
+    <t>305273117</t>
+  </si>
+  <si>
+    <t>Fényes Elek utca</t>
+  </si>
+  <si>
+    <t>305273161/1</t>
+  </si>
+  <si>
+    <t>305273161</t>
+  </si>
+  <si>
+    <t>1092</t>
+  </si>
+  <si>
+    <t>Hőgyes Endre</t>
+  </si>
+  <si>
+    <t>305273347/1</t>
+  </si>
+  <si>
+    <t>305273347</t>
+  </si>
+  <si>
+    <t>2340</t>
+  </si>
+  <si>
+    <t>KISKUNLACHÁZA</t>
+  </si>
+  <si>
+    <t>305273428/1</t>
+  </si>
+  <si>
+    <t>305273428</t>
+  </si>
+  <si>
+    <t>Várfok utca</t>
+  </si>
+  <si>
+    <t>305315218/1</t>
+  </si>
+  <si>
+    <t>305315218</t>
+  </si>
+  <si>
+    <t>Vadász utca</t>
+  </si>
+  <si>
+    <t>305315354/1</t>
+  </si>
+  <si>
+    <t>305315354</t>
+  </si>
+  <si>
+    <t>1033</t>
+  </si>
+  <si>
+    <t>Huszti út</t>
+  </si>
+  <si>
+    <t>305315368/1</t>
+  </si>
+  <si>
+    <t>305315368</t>
+  </si>
+  <si>
+    <t>Huba utca</t>
+  </si>
+  <si>
+    <t>305315375/1</t>
+  </si>
+  <si>
+    <t>305315375</t>
+  </si>
+  <si>
+    <t>Nárcisz utca</t>
+  </si>
+  <si>
+    <t>305315429/1</t>
+  </si>
+  <si>
+    <t>305315429</t>
+  </si>
+  <si>
+    <t>Kert utca</t>
+  </si>
+  <si>
+    <t>202603202600673001</t>
+  </si>
+  <si>
+    <t>NFD6-03-19-D7CM</t>
+  </si>
+  <si>
+    <t>Gábor Áron utca</t>
+  </si>
+  <si>
+    <t>202603202600668901</t>
+  </si>
+  <si>
+    <t>NFD6-03-19-H65W</t>
+  </si>
+  <si>
+    <t>202603202600666501</t>
+  </si>
+  <si>
+    <t>NFD6-03-19-PW6A</t>
+  </si>
+  <si>
+    <t>1224</t>
+  </si>
+  <si>
+    <t>XV. utca</t>
+  </si>
+  <si>
+    <t>202603232600682601</t>
+  </si>
+  <si>
+    <t>NFD6-03-20-5UXK</t>
+  </si>
+  <si>
+    <t>2713</t>
+  </si>
+  <si>
+    <t>CSEMŐ</t>
+  </si>
+  <si>
+    <t>Arany János utca</t>
+  </si>
+  <si>
+    <t>202603232600676701</t>
+  </si>
+  <si>
+    <t>NFD6-03-20-F4QY</t>
+  </si>
+  <si>
+    <t>1222</t>
+  </si>
+  <si>
+    <t>Dévény utca</t>
+  </si>
+  <si>
+    <t>202603232600677501</t>
+  </si>
+  <si>
+    <t>NFD6-03-20-HWHZ</t>
+  </si>
+  <si>
+    <t>1075</t>
+  </si>
+  <si>
+    <t>Károly körút</t>
+  </si>
+  <si>
+    <t>202603232600679801</t>
+  </si>
+  <si>
+    <t>NFD6-03-20-KJVA</t>
+  </si>
+  <si>
+    <t>1035</t>
+  </si>
+  <si>
+    <t>Szentendrei út</t>
+  </si>
+  <si>
+    <t>202603232600679701</t>
+  </si>
+  <si>
+    <t>NFD6-03-20-M4M8</t>
+  </si>
+  <si>
+    <t>1214</t>
+  </si>
+  <si>
+    <t>Reggel utca</t>
+  </si>
+  <si>
+    <t>202603232600679702</t>
+  </si>
+  <si>
+    <t>202603232600676901</t>
+  </si>
+  <si>
+    <t>NFD6-03-20-XTR7</t>
+  </si>
+  <si>
+    <t>1181</t>
+  </si>
+  <si>
+    <t>202603232600691301</t>
+  </si>
+  <si>
+    <t>NFD6-03-21-4QW5</t>
+  </si>
+  <si>
+    <t>1016</t>
+  </si>
+  <si>
+    <t>Zsolt utca</t>
+  </si>
+  <si>
+    <t>202603232600691901</t>
+  </si>
+  <si>
+    <t>NFD6-03-21-8HG2</t>
+  </si>
+  <si>
+    <t>Bőröndös utca</t>
+  </si>
+  <si>
+    <t>202603232600692001</t>
+  </si>
+  <si>
+    <t>NFD6-03-21-AFZ3</t>
+  </si>
+  <si>
+    <t>Erdőhegy utca</t>
+  </si>
+  <si>
+    <t>202603232600692002</t>
+  </si>
+  <si>
+    <t>202603232600690001</t>
+  </si>
+  <si>
+    <t>NFD6-03-21-C38J</t>
+  </si>
+  <si>
+    <t>Esze Tamás utca</t>
+  </si>
+  <si>
+    <t>202603232600684501</t>
+  </si>
+  <si>
+    <t>NFD6-03-21-H8RU</t>
+  </si>
+  <si>
+    <t>Posta utca</t>
+  </si>
+  <si>
+    <t>202603232600686601</t>
+  </si>
+  <si>
+    <t>NFD6-03-21-HRZA</t>
+  </si>
+  <si>
+    <t>Dési Huber utca</t>
+  </si>
+  <si>
+    <t>202603232600685201</t>
+  </si>
+  <si>
+    <t>NFD6-03-21-S8DZ</t>
+  </si>
+  <si>
+    <t>Ugró Gyula sor</t>
+  </si>
+  <si>
+    <t>202603232600688401</t>
+  </si>
+  <si>
+    <t>NFD6-03-21-T5AQ</t>
+  </si>
+  <si>
+    <t>2339</t>
+  </si>
+  <si>
+    <t>MAJOSHÁZA</t>
+  </si>
+  <si>
+    <t>Széchenyi sétány</t>
+  </si>
+  <si>
+    <t>202603232600690501</t>
+  </si>
+  <si>
+    <t>NFD6-03-21-VFQP</t>
+  </si>
+  <si>
+    <t>Tóth József utca</t>
+  </si>
+  <si>
+    <t>202603232600694101</t>
+  </si>
+  <si>
+    <t>NFD6-03-22-4EQ9</t>
+  </si>
+  <si>
+    <t>2023</t>
+  </si>
+  <si>
+    <t>DUNABOGDÁNY</t>
+  </si>
+  <si>
+    <t>202603232600700501</t>
+  </si>
+  <si>
+    <t>NFD6-03-22-8MMT</t>
+  </si>
+  <si>
+    <t>2314</t>
+  </si>
+  <si>
+    <t>HALÁSZTELEK</t>
+  </si>
+  <si>
+    <t>202603232600702601</t>
+  </si>
+  <si>
+    <t>NFD6-03-22-EJCF</t>
+  </si>
+  <si>
+    <t>Bezerédj utca</t>
+  </si>
+  <si>
+    <t>202603232600696701</t>
+  </si>
+  <si>
+    <t>NFD6-03-22-MAFW</t>
+  </si>
+  <si>
+    <t>Hátszeg utca</t>
+  </si>
+  <si>
+    <t>202603232600697701</t>
+  </si>
+  <si>
+    <t>NFD6-03-22-P68V</t>
+  </si>
+  <si>
+    <t>202603232600693601</t>
+  </si>
+  <si>
+    <t>NFD6-03-22-TSVT</t>
+  </si>
+  <si>
+    <t>Lajosház utca</t>
+  </si>
+  <si>
+    <t>202603232600693602</t>
+  </si>
+  <si>
+    <t>202603232600694401</t>
+  </si>
+  <si>
+    <t>NFD6-03-22-X5E6</t>
+  </si>
+  <si>
+    <t>2243</t>
+  </si>
+  <si>
+    <t>KÓKA</t>
+  </si>
+  <si>
+    <t>Körtefa utca</t>
+  </si>
+  <si>
+    <t>NFD6-03-23-JHSK-1</t>
+  </si>
+  <si>
+    <t>NFD6-03-23-JHSK</t>
+  </si>
+  <si>
+    <t>202603172600632601</t>
+  </si>
+  <si>
+    <t>NFE6-03-16-28D6</t>
+  </si>
+  <si>
+    <t>János utca</t>
+  </si>
+  <si>
+    <t>202603182600650001</t>
+  </si>
+  <si>
+    <t>NFE6-03-17-GVR7</t>
+  </si>
+  <si>
+    <t>1045</t>
+  </si>
+  <si>
+    <t>Lebstück Mária utca</t>
+  </si>
+  <si>
+    <t>202603192600665401</t>
+  </si>
+  <si>
+    <t>NFE6-03-18-HQXJ</t>
+  </si>
+  <si>
+    <t>2366</t>
+  </si>
+  <si>
+    <t>KAKUCS</t>
+  </si>
+  <si>
+    <t>Rózsa utca</t>
+  </si>
+  <si>
+    <t>202603192600665402</t>
+  </si>
+  <si>
+    <t>202603202600663801</t>
+  </si>
+  <si>
+    <t>NFE6-03-18-YW4X</t>
+  </si>
+  <si>
+    <t>2145</t>
+  </si>
+  <si>
+    <t>Wéber Ede park</t>
+  </si>
+  <si>
+    <t>202603232600682201</t>
+  </si>
+  <si>
+    <t>NFE6-03-20-8ZG3</t>
+  </si>
+  <si>
+    <t>1011</t>
+  </si>
+  <si>
+    <t>202603232600680101</t>
+  </si>
+  <si>
+    <t>NFE6-03-20-9GFB</t>
+  </si>
+  <si>
+    <t>202603232600680102</t>
+  </si>
+  <si>
+    <t>202603232600675901</t>
+  </si>
+  <si>
+    <t>NFE6-03-20-WPBY</t>
+  </si>
+  <si>
+    <t>1142</t>
+  </si>
+  <si>
+    <t>Pándorfalu utca</t>
+  </si>
+  <si>
+    <t>202603232600690401</t>
+  </si>
+  <si>
+    <t>NFE6-03-21-JHD9</t>
+  </si>
+  <si>
+    <t>Jókai Mór utca</t>
+  </si>
+  <si>
+    <t>202603232600690402</t>
+  </si>
+  <si>
+    <t>202603232600692801</t>
+  </si>
+  <si>
+    <t>NFE6-03-21-PV3H</t>
+  </si>
+  <si>
+    <t>2764</t>
+  </si>
+  <si>
+    <t>TÁPIÓBICSKE</t>
+  </si>
+  <si>
+    <t>202603232600692802</t>
+  </si>
+  <si>
+    <t>202603232600696501</t>
+  </si>
+  <si>
+    <t>NFE6-03-22-86ZU</t>
+  </si>
+  <si>
+    <t>Somlói utca</t>
+  </si>
+  <si>
+    <t>202603232600696502</t>
+  </si>
+  <si>
+    <t>202603232600703001</t>
+  </si>
+  <si>
+    <t>NFE6-03-22-9KGH</t>
+  </si>
+  <si>
+    <t>Puskás Ferenc utca</t>
+  </si>
+  <si>
+    <t>202603232600702001</t>
+  </si>
+  <si>
+    <t>NFE6-03-22-CQ2S</t>
+  </si>
+  <si>
+    <t>2213</t>
+  </si>
+  <si>
+    <t>MONORIERDŐ</t>
+  </si>
+  <si>
+    <t>Barátság köz</t>
+  </si>
+  <si>
+    <t>202603232600699501</t>
+  </si>
+  <si>
+    <t>NFE6-03-22-CWQN</t>
+  </si>
+  <si>
+    <t>Budai Nagy Antal utca</t>
+  </si>
+  <si>
+    <t>202603232600693401</t>
+  </si>
+  <si>
+    <t>NFE6-03-22-DNSQ</t>
+  </si>
+  <si>
+    <t>202603232600693402</t>
+  </si>
+  <si>
+    <t>202603232600704001</t>
+  </si>
+  <si>
+    <t>NFE6-03-22-V4YL</t>
+  </si>
+  <si>
+    <t>Csongor utca</t>
+  </si>
+  <si>
+    <t>202603232600693101</t>
+  </si>
+  <si>
+    <t>NFE6-03-22-ZTXH</t>
+  </si>
+  <si>
+    <t>202603232600693102</t>
+  </si>
+  <si>
+    <t>202603232600693103</t>
+  </si>
+  <si>
+    <t>202603232600693104</t>
+  </si>
+  <si>
+    <t>202603232600693105</t>
+  </si>
+  <si>
+    <t>202603232600693106</t>
+  </si>
+  <si>
+    <t>159995579538482274</t>
+  </si>
+  <si>
+    <t>R413353</t>
+  </si>
+  <si>
+    <t>1028</t>
+  </si>
+  <si>
+    <t>Hidegkúti út</t>
+  </si>
+  <si>
+    <t>159995579538482281</t>
+  </si>
+  <si>
+    <t>159995579538481987</t>
+  </si>
+  <si>
+    <t>R413552</t>
+  </si>
+  <si>
+    <t>2071</t>
+  </si>
+  <si>
+    <t>PÁTY</t>
+  </si>
+  <si>
+    <t>Benedek Elek utca</t>
+  </si>
+  <si>
+    <t>26-00/00211</t>
+  </si>
+  <si>
+    <t>Ecseri Út</t>
   </si>
 </sst>
 </file>
@@ -1711,7 +2533,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <sheetPr codeName="Munka1"/>
-  <dimension ref="A1:H123"/>
+  <dimension ref="A1:H202"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="24.88671875" bestFit="1" customWidth="1"/>
@@ -1719,8 +2541,8 @@
     <col min="3" max="3" width="6.88671875" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="20.109375" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="5" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="20.21875" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="36.109375" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="20" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="35.44140625" bestFit="1" customWidth="1"/>
     <col min="8" max="8" width="19.88671875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
@@ -1749,114 +2571,114 @@
     </row>
     <row r="2" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
-        <v>88</v>
+        <v>97</v>
       </c>
       <c r="C2" t="s">
-        <v>21</v>
+        <v>39</v>
       </c>
       <c r="D2" t="s">
-        <v>89</v>
+        <v>98</v>
       </c>
       <c r="E2" t="s">
-        <v>61</v>
+        <v>71</v>
       </c>
       <c r="F2" t="s">
         <v>7</v>
       </c>
       <c r="G2" t="s">
-        <v>90</v>
+        <v>99</v>
       </c>
       <c r="H2" t="s">
-        <v>91</v>
+        <v>8</v>
       </c>
     </row>
     <row r="3" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
-        <v>92</v>
+        <v>100</v>
       </c>
       <c r="C3" t="s">
-        <v>22</v>
+        <v>39</v>
       </c>
       <c r="D3" t="s">
-        <v>93</v>
+        <v>101</v>
       </c>
       <c r="E3" t="s">
-        <v>73</v>
+        <v>53</v>
       </c>
       <c r="F3" t="s">
-        <v>74</v>
+        <v>7</v>
       </c>
       <c r="G3" t="s">
-        <v>94</v>
+        <v>102</v>
       </c>
       <c r="H3" t="s">
-        <v>91</v>
+        <v>8</v>
       </c>
     </row>
     <row r="4" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
-        <v>95</v>
+        <v>103</v>
       </c>
       <c r="C4" t="s">
-        <v>20</v>
+        <v>86</v>
       </c>
       <c r="D4" t="s">
-        <v>96</v>
+        <v>104</v>
       </c>
       <c r="E4" t="s">
-        <v>97</v>
+        <v>105</v>
       </c>
       <c r="F4" t="s">
-        <v>98</v>
+        <v>7</v>
       </c>
       <c r="G4" t="s">
-        <v>99</v>
+        <v>106</v>
       </c>
       <c r="H4" t="s">
-        <v>91</v>
+        <v>8</v>
       </c>
     </row>
     <row r="5" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
-        <v>100</v>
+        <v>107</v>
       </c>
       <c r="C5" t="s">
-        <v>20</v>
+        <v>50</v>
       </c>
       <c r="D5" t="s">
-        <v>96</v>
+        <v>108</v>
       </c>
       <c r="E5" t="s">
-        <v>97</v>
+        <v>81</v>
       </c>
       <c r="F5" t="s">
-        <v>98</v>
+        <v>82</v>
       </c>
       <c r="G5" t="s">
-        <v>99</v>
+        <v>42</v>
       </c>
       <c r="H5" t="s">
-        <v>91</v>
+        <v>8</v>
       </c>
     </row>
     <row r="6" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
-        <v>101</v>
+        <v>109</v>
       </c>
       <c r="C6" t="s">
-        <v>29</v>
+        <v>13</v>
       </c>
       <c r="D6" t="s">
-        <v>102</v>
+        <v>110</v>
       </c>
       <c r="E6" t="s">
-        <v>69</v>
+        <v>111</v>
       </c>
       <c r="F6" t="s">
-        <v>70</v>
+        <v>7</v>
       </c>
       <c r="G6" t="s">
-        <v>103</v>
+        <v>112</v>
       </c>
       <c r="H6" t="s">
         <v>8</v>
@@ -1864,22 +2686,22 @@
     </row>
     <row r="7" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
-        <v>104</v>
+        <v>113</v>
       </c>
       <c r="C7" t="s">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="D7" t="s">
-        <v>105</v>
+        <v>114</v>
       </c>
       <c r="E7" t="s">
-        <v>106</v>
+        <v>52</v>
       </c>
       <c r="F7" t="s">
-        <v>107</v>
+        <v>7</v>
       </c>
       <c r="G7" t="s">
-        <v>108</v>
+        <v>115</v>
       </c>
       <c r="H7" t="s">
         <v>8</v>
@@ -1887,22 +2709,22 @@
     </row>
     <row r="8" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
-        <v>109</v>
+        <v>116</v>
       </c>
       <c r="C8" t="s">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="D8" t="s">
-        <v>110</v>
+        <v>117</v>
       </c>
       <c r="E8" t="s">
-        <v>111</v>
+        <v>62</v>
       </c>
       <c r="F8" t="s">
-        <v>112</v>
+        <v>63</v>
       </c>
       <c r="G8" t="s">
-        <v>113</v>
+        <v>118</v>
       </c>
       <c r="H8" t="s">
         <v>8</v>
@@ -1910,22 +2732,22 @@
     </row>
     <row r="9" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
-        <v>114</v>
+        <v>119</v>
       </c>
       <c r="C9" t="s">
-        <v>29</v>
+        <v>24</v>
       </c>
       <c r="D9" t="s">
-        <v>115</v>
+        <v>120</v>
       </c>
       <c r="E9" t="s">
-        <v>116</v>
+        <v>83</v>
       </c>
       <c r="F9" t="s">
-        <v>117</v>
+        <v>7</v>
       </c>
       <c r="G9" t="s">
-        <v>118</v>
+        <v>121</v>
       </c>
       <c r="H9" t="s">
         <v>8</v>
@@ -1933,22 +2755,22 @@
     </row>
     <row r="10" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
-        <v>119</v>
+        <v>122</v>
       </c>
       <c r="C10" t="s">
-        <v>10</v>
+        <v>24</v>
       </c>
       <c r="D10" t="s">
-        <v>120</v>
+        <v>123</v>
       </c>
       <c r="E10" t="s">
-        <v>121</v>
+        <v>124</v>
       </c>
       <c r="F10" t="s">
-        <v>122</v>
+        <v>7</v>
       </c>
       <c r="G10" t="s">
-        <v>123</v>
+        <v>125</v>
       </c>
       <c r="H10" t="s">
         <v>8</v>
@@ -1956,22 +2778,22 @@
     </row>
     <row r="11" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A11" t="s">
-        <v>124</v>
+        <v>126</v>
       </c>
       <c r="C11" t="s">
-        <v>125</v>
+        <v>25</v>
       </c>
       <c r="D11" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="E11" t="s">
-        <v>36</v>
+        <v>52</v>
       </c>
       <c r="F11" t="s">
-        <v>37</v>
+        <v>7</v>
       </c>
       <c r="G11" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="H11" t="s">
         <v>8</v>
@@ -1979,22 +2801,22 @@
     </row>
     <row r="12" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A12" t="s">
+        <v>129</v>
+      </c>
+      <c r="C12" t="s">
+        <v>25</v>
+      </c>
+      <c r="D12" t="s">
+        <v>127</v>
+      </c>
+      <c r="E12" t="s">
+        <v>52</v>
+      </c>
+      <c r="F12" t="s">
+        <v>7</v>
+      </c>
+      <c r="G12" t="s">
         <v>128</v>
-      </c>
-      <c r="C12" t="s">
-        <v>9</v>
-      </c>
-      <c r="D12" t="s">
-        <v>129</v>
-      </c>
-      <c r="E12" t="s">
-        <v>130</v>
-      </c>
-      <c r="F12" t="s">
-        <v>131</v>
-      </c>
-      <c r="G12" t="s">
-        <v>132</v>
       </c>
       <c r="H12" t="s">
         <v>8</v>
@@ -2002,22 +2824,22 @@
     </row>
     <row r="13" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A13" t="s">
+        <v>130</v>
+      </c>
+      <c r="C13" t="s">
+        <v>9</v>
+      </c>
+      <c r="D13" t="s">
+        <v>131</v>
+      </c>
+      <c r="E13" t="s">
+        <v>132</v>
+      </c>
+      <c r="F13" t="s">
         <v>133</v>
       </c>
-      <c r="C13" t="s">
-        <v>21</v>
-      </c>
-      <c r="D13" t="s">
+      <c r="G13" t="s">
         <v>134</v>
-      </c>
-      <c r="E13" t="s">
-        <v>135</v>
-      </c>
-      <c r="F13" t="s">
-        <v>7</v>
-      </c>
-      <c r="G13" t="s">
-        <v>136</v>
       </c>
       <c r="H13" t="s">
         <v>8</v>
@@ -2025,22 +2847,22 @@
     </row>
     <row r="14" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A14" t="s">
+        <v>135</v>
+      </c>
+      <c r="C14" t="s">
+        <v>136</v>
+      </c>
+      <c r="D14" t="s">
         <v>137</v>
       </c>
-      <c r="C14" t="s">
-        <v>63</v>
-      </c>
-      <c r="D14" t="s">
+      <c r="E14" t="s">
         <v>138</v>
       </c>
-      <c r="E14" t="s">
+      <c r="F14" t="s">
         <v>139</v>
       </c>
-      <c r="F14" t="s">
+      <c r="G14" t="s">
         <v>140</v>
-      </c>
-      <c r="G14" t="s">
-        <v>141</v>
       </c>
       <c r="H14" t="s">
         <v>8</v>
@@ -2048,22 +2870,22 @@
     </row>
     <row r="15" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A15" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="C15" t="s">
-        <v>13</v>
+        <v>136</v>
       </c>
       <c r="D15" t="s">
-        <v>143</v>
+        <v>137</v>
       </c>
       <c r="E15" t="s">
-        <v>64</v>
+        <v>138</v>
       </c>
       <c r="F15" t="s">
-        <v>7</v>
+        <v>139</v>
       </c>
       <c r="G15" t="s">
-        <v>144</v>
+        <v>140</v>
       </c>
       <c r="H15" t="s">
         <v>8</v>
@@ -2071,22 +2893,22 @@
     </row>
     <row r="16" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A16" t="s">
+        <v>142</v>
+      </c>
+      <c r="C16" t="s">
+        <v>13</v>
+      </c>
+      <c r="D16" t="s">
+        <v>143</v>
+      </c>
+      <c r="E16" t="s">
+        <v>144</v>
+      </c>
+      <c r="F16" t="s">
         <v>145</v>
       </c>
-      <c r="C16" t="s">
-        <v>25</v>
-      </c>
-      <c r="D16" t="s">
+      <c r="G16" t="s">
         <v>146</v>
-      </c>
-      <c r="E16" t="s">
-        <v>147</v>
-      </c>
-      <c r="F16" t="s">
-        <v>7</v>
-      </c>
-      <c r="G16" t="s">
-        <v>148</v>
       </c>
       <c r="H16" t="s">
         <v>8</v>
@@ -2094,22 +2916,22 @@
     </row>
     <row r="17" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A17" t="s">
+        <v>147</v>
+      </c>
+      <c r="C17" t="s">
+        <v>148</v>
+      </c>
+      <c r="D17" t="s">
         <v>149</v>
       </c>
-      <c r="C17" t="s">
-        <v>21</v>
-      </c>
-      <c r="D17" t="s">
+      <c r="E17" t="s">
         <v>150</v>
       </c>
-      <c r="E17" t="s">
+      <c r="F17" t="s">
         <v>151</v>
       </c>
-      <c r="F17" t="s">
+      <c r="G17" t="s">
         <v>152</v>
-      </c>
-      <c r="G17" t="s">
-        <v>86</v>
       </c>
       <c r="H17" t="s">
         <v>8</v>
@@ -2120,16 +2942,16 @@
         <v>153</v>
       </c>
       <c r="C18" t="s">
-        <v>29</v>
+        <v>18</v>
       </c>
       <c r="D18" t="s">
         <v>154</v>
       </c>
       <c r="E18" t="s">
-        <v>69</v>
+        <v>14</v>
       </c>
       <c r="F18" t="s">
-        <v>70</v>
+        <v>15</v>
       </c>
       <c r="G18" t="s">
         <v>155</v>
@@ -2143,16 +2965,16 @@
         <v>156</v>
       </c>
       <c r="C19" t="s">
-        <v>125</v>
+        <v>9</v>
       </c>
       <c r="D19" t="s">
         <v>157</v>
       </c>
       <c r="E19" t="s">
-        <v>36</v>
+        <v>69</v>
       </c>
       <c r="F19" t="s">
-        <v>37</v>
+        <v>70</v>
       </c>
       <c r="G19" t="s">
         <v>158</v>
@@ -2166,19 +2988,19 @@
         <v>159</v>
       </c>
       <c r="C20" t="s">
-        <v>29</v>
+        <v>9</v>
       </c>
       <c r="D20" t="s">
-        <v>160</v>
+        <v>157</v>
       </c>
       <c r="E20" t="s">
-        <v>42</v>
+        <v>69</v>
       </c>
       <c r="F20" t="s">
-        <v>43</v>
+        <v>70</v>
       </c>
       <c r="G20" t="s">
-        <v>40</v>
+        <v>158</v>
       </c>
       <c r="H20" t="s">
         <v>8</v>
@@ -2186,22 +3008,22 @@
     </row>
     <row r="21" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A21" t="s">
+        <v>160</v>
+      </c>
+      <c r="C21" t="s">
+        <v>50</v>
+      </c>
+      <c r="D21" t="s">
         <v>161</v>
       </c>
-      <c r="C21" t="s">
+      <c r="E21" t="s">
+        <v>47</v>
+      </c>
+      <c r="F21" t="s">
         <v>48</v>
       </c>
-      <c r="D21" t="s">
+      <c r="G21" t="s">
         <v>162</v>
-      </c>
-      <c r="E21" t="s">
-        <v>28</v>
-      </c>
-      <c r="F21" t="s">
-        <v>7</v>
-      </c>
-      <c r="G21" t="s">
-        <v>163</v>
       </c>
       <c r="H21" t="s">
         <v>8</v>
@@ -2209,22 +3031,22 @@
     </row>
     <row r="22" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A22" t="s">
+        <v>163</v>
+      </c>
+      <c r="C22" t="s">
+        <v>86</v>
+      </c>
+      <c r="D22" t="s">
         <v>164</v>
       </c>
-      <c r="C22" t="s">
-        <v>48</v>
-      </c>
-      <c r="D22" t="s">
-        <v>162</v>
-      </c>
       <c r="E22" t="s">
-        <v>28</v>
+        <v>105</v>
       </c>
       <c r="F22" t="s">
         <v>7</v>
       </c>
       <c r="G22" t="s">
-        <v>163</v>
+        <v>165</v>
       </c>
       <c r="H22" t="s">
         <v>8</v>
@@ -2232,22 +3054,22 @@
     </row>
     <row r="23" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A23" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="C23" t="s">
-        <v>18</v>
+        <v>86</v>
       </c>
       <c r="D23" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="E23" t="s">
-        <v>49</v>
+        <v>105</v>
       </c>
       <c r="F23" t="s">
         <v>7</v>
       </c>
       <c r="G23" t="s">
-        <v>167</v>
+        <v>106</v>
       </c>
       <c r="H23" t="s">
         <v>8</v>
@@ -2258,19 +3080,19 @@
         <v>168</v>
       </c>
       <c r="C24" t="s">
-        <v>125</v>
+        <v>25</v>
       </c>
       <c r="D24" t="s">
         <v>169</v>
       </c>
       <c r="E24" t="s">
-        <v>36</v>
+        <v>170</v>
       </c>
       <c r="F24" t="s">
-        <v>37</v>
+        <v>7</v>
       </c>
       <c r="G24" t="s">
-        <v>75</v>
+        <v>171</v>
       </c>
       <c r="H24" t="s">
         <v>8</v>
@@ -2278,22 +3100,22 @@
     </row>
     <row r="25" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A25" t="s">
+        <v>172</v>
+      </c>
+      <c r="C25" t="s">
+        <v>25</v>
+      </c>
+      <c r="D25" t="s">
+        <v>169</v>
+      </c>
+      <c r="E25" t="s">
         <v>170</v>
       </c>
-      <c r="C25" t="s">
-        <v>24</v>
-      </c>
-      <c r="D25" t="s">
+      <c r="F25" t="s">
+        <v>7</v>
+      </c>
+      <c r="G25" t="s">
         <v>171</v>
-      </c>
-      <c r="E25" t="s">
-        <v>172</v>
-      </c>
-      <c r="F25" t="s">
-        <v>7</v>
-      </c>
-      <c r="G25" t="s">
-        <v>173</v>
       </c>
       <c r="H25" t="s">
         <v>8</v>
@@ -2301,19 +3123,19 @@
     </row>
     <row r="26" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A26" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="C26" t="s">
         <v>18</v>
       </c>
       <c r="D26" t="s">
+        <v>174</v>
+      </c>
+      <c r="E26" t="s">
         <v>175</v>
       </c>
-      <c r="E26" t="s">
+      <c r="F26" t="s">
         <v>176</v>
-      </c>
-      <c r="F26" t="s">
-        <v>7</v>
       </c>
       <c r="G26" t="s">
         <v>177</v>
@@ -2327,19 +3149,19 @@
         <v>178</v>
       </c>
       <c r="C27" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="D27" t="s">
         <v>179</v>
       </c>
       <c r="E27" t="s">
-        <v>54</v>
+        <v>180</v>
       </c>
       <c r="F27" t="s">
         <v>7</v>
       </c>
       <c r="G27" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="H27" t="s">
         <v>8</v>
@@ -2347,482 +3169,482 @@
     </row>
     <row r="28" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A28" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="C28" t="s">
-        <v>21</v>
+        <v>64</v>
       </c>
       <c r="D28" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="E28" t="s">
-        <v>61</v>
+        <v>29</v>
       </c>
       <c r="F28" t="s">
         <v>7</v>
       </c>
       <c r="G28" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="H28" t="s">
-        <v>38</v>
+        <v>8</v>
       </c>
     </row>
     <row r="29" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A29" t="s">
+        <v>185</v>
+      </c>
+      <c r="C29" t="s">
+        <v>64</v>
+      </c>
+      <c r="D29" t="s">
+        <v>183</v>
+      </c>
+      <c r="E29" t="s">
+        <v>29</v>
+      </c>
+      <c r="F29" t="s">
+        <v>7</v>
+      </c>
+      <c r="G29" t="s">
         <v>184</v>
       </c>
-      <c r="C29" t="s">
-        <v>22</v>
-      </c>
-      <c r="D29" t="s">
-        <v>185</v>
-      </c>
-      <c r="E29" t="s">
-        <v>186</v>
-      </c>
-      <c r="F29" t="s">
-        <v>187</v>
-      </c>
-      <c r="G29" t="s">
-        <v>188</v>
-      </c>
       <c r="H29" t="s">
-        <v>38</v>
+        <v>8</v>
       </c>
     </row>
     <row r="30" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A30" t="s">
+        <v>186</v>
+      </c>
+      <c r="C30" t="s">
+        <v>24</v>
+      </c>
+      <c r="D30" t="s">
+        <v>187</v>
+      </c>
+      <c r="E30" t="s">
+        <v>188</v>
+      </c>
+      <c r="F30" t="s">
+        <v>7</v>
+      </c>
+      <c r="G30" t="s">
         <v>189</v>
       </c>
-      <c r="C30" t="s">
-        <v>26</v>
-      </c>
-      <c r="D30" t="s">
-        <v>190</v>
-      </c>
-      <c r="E30" t="s">
-        <v>191</v>
-      </c>
-      <c r="F30" t="s">
-        <v>7</v>
-      </c>
-      <c r="G30" t="s">
-        <v>192</v>
-      </c>
       <c r="H30" t="s">
-        <v>38</v>
+        <v>8</v>
       </c>
     </row>
     <row r="31" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A31" t="s">
+        <v>190</v>
+      </c>
+      <c r="C31" t="s">
+        <v>22</v>
+      </c>
+      <c r="D31" t="s">
+        <v>191</v>
+      </c>
+      <c r="E31" t="s">
+        <v>192</v>
+      </c>
+      <c r="F31" t="s">
+        <v>7</v>
+      </c>
+      <c r="G31" t="s">
         <v>193</v>
       </c>
-      <c r="C31" t="s">
-        <v>19</v>
-      </c>
-      <c r="D31" t="s">
-        <v>194</v>
-      </c>
-      <c r="E31" t="s">
-        <v>195</v>
-      </c>
-      <c r="F31" t="s">
-        <v>196</v>
-      </c>
-      <c r="G31" t="s">
-        <v>197</v>
-      </c>
       <c r="H31" t="s">
-        <v>11</v>
+        <v>8</v>
       </c>
     </row>
     <row r="32" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A32" t="s">
-        <v>198</v>
+        <v>194</v>
       </c>
       <c r="C32" t="s">
-        <v>48</v>
+        <v>43</v>
       </c>
       <c r="D32" t="s">
-        <v>199</v>
+        <v>195</v>
       </c>
       <c r="E32" t="s">
-        <v>200</v>
+        <v>35</v>
       </c>
       <c r="F32" t="s">
         <v>7</v>
       </c>
       <c r="G32" t="s">
-        <v>201</v>
+        <v>196</v>
       </c>
       <c r="H32" t="s">
-        <v>11</v>
+        <v>8</v>
       </c>
     </row>
     <row r="33" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A33" t="s">
-        <v>202</v>
+        <v>197</v>
       </c>
       <c r="C33" t="s">
-        <v>22</v>
+        <v>16</v>
       </c>
       <c r="D33" t="s">
-        <v>203</v>
+        <v>198</v>
       </c>
       <c r="E33" t="s">
-        <v>27</v>
+        <v>44</v>
       </c>
       <c r="F33" t="s">
         <v>7</v>
       </c>
       <c r="G33" t="s">
-        <v>62</v>
+        <v>199</v>
       </c>
       <c r="H33" t="s">
-        <v>11</v>
+        <v>8</v>
       </c>
     </row>
     <row r="34" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A34" t="s">
-        <v>204</v>
+        <v>200</v>
       </c>
       <c r="C34" t="s">
-        <v>205</v>
+        <v>43</v>
       </c>
       <c r="D34" t="s">
-        <v>206</v>
+        <v>201</v>
       </c>
       <c r="E34" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="F34" t="s">
         <v>7</v>
       </c>
       <c r="G34" t="s">
-        <v>52</v>
+        <v>196</v>
       </c>
       <c r="H34" t="s">
-        <v>11</v>
+        <v>8</v>
       </c>
     </row>
     <row r="35" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A35" t="s">
-        <v>207</v>
+        <v>202</v>
       </c>
       <c r="C35" t="s">
+        <v>64</v>
+      </c>
+      <c r="D35" t="s">
+        <v>203</v>
+      </c>
+      <c r="E35" t="s">
+        <v>204</v>
+      </c>
+      <c r="F35" t="s">
+        <v>7</v>
+      </c>
+      <c r="G35" t="s">
         <v>205</v>
       </c>
-      <c r="D35" t="s">
-        <v>206</v>
-      </c>
-      <c r="E35" t="s">
-        <v>33</v>
-      </c>
-      <c r="F35" t="s">
-        <v>7</v>
-      </c>
-      <c r="G35" t="s">
-        <v>52</v>
-      </c>
       <c r="H35" t="s">
-        <v>11</v>
+        <v>8</v>
       </c>
     </row>
     <row r="36" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A36" t="s">
+        <v>206</v>
+      </c>
+      <c r="C36" t="s">
+        <v>16</v>
+      </c>
+      <c r="D36" t="s">
+        <v>207</v>
+      </c>
+      <c r="E36" t="s">
         <v>208</v>
       </c>
-      <c r="C36" t="s">
-        <v>205</v>
-      </c>
-      <c r="D36" t="s">
-        <v>206</v>
-      </c>
-      <c r="E36" t="s">
-        <v>33</v>
-      </c>
       <c r="F36" t="s">
         <v>7</v>
       </c>
       <c r="G36" t="s">
-        <v>52</v>
+        <v>209</v>
       </c>
       <c r="H36" t="s">
-        <v>11</v>
+        <v>8</v>
       </c>
     </row>
     <row r="37" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A37" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="C37" t="s">
-        <v>205</v>
+        <v>19</v>
       </c>
       <c r="D37" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="E37" t="s">
-        <v>14</v>
+        <v>212</v>
       </c>
       <c r="F37" t="s">
-        <v>15</v>
+        <v>7</v>
       </c>
       <c r="G37" t="s">
-        <v>211</v>
+        <v>213</v>
       </c>
       <c r="H37" t="s">
-        <v>11</v>
+        <v>8</v>
       </c>
     </row>
     <row r="38" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A38" t="s">
-        <v>212</v>
+        <v>214</v>
       </c>
       <c r="C38" t="s">
-        <v>18</v>
+        <v>86</v>
       </c>
       <c r="D38" t="s">
-        <v>213</v>
+        <v>215</v>
       </c>
       <c r="E38" t="s">
-        <v>214</v>
+        <v>216</v>
       </c>
       <c r="F38" t="s">
         <v>7</v>
       </c>
       <c r="G38" t="s">
-        <v>215</v>
+        <v>217</v>
       </c>
       <c r="H38" t="s">
-        <v>11</v>
+        <v>8</v>
       </c>
     </row>
     <row r="39" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A39" t="s">
+        <v>218</v>
+      </c>
+      <c r="C39" t="s">
+        <v>86</v>
+      </c>
+      <c r="D39" t="s">
+        <v>215</v>
+      </c>
+      <c r="E39" t="s">
         <v>216</v>
       </c>
-      <c r="C39" t="s">
-        <v>18</v>
-      </c>
-      <c r="D39" t="s">
-        <v>213</v>
-      </c>
-      <c r="E39" t="s">
-        <v>214</v>
-      </c>
       <c r="F39" t="s">
         <v>7</v>
       </c>
       <c r="G39" t="s">
-        <v>215</v>
+        <v>217</v>
       </c>
       <c r="H39" t="s">
-        <v>11</v>
+        <v>8</v>
       </c>
     </row>
     <row r="40" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A40" t="s">
-        <v>217</v>
+        <v>219</v>
       </c>
       <c r="C40" t="s">
-        <v>25</v>
+        <v>33</v>
       </c>
       <c r="D40" t="s">
-        <v>218</v>
+        <v>220</v>
       </c>
       <c r="E40" t="s">
-        <v>219</v>
+        <v>221</v>
       </c>
       <c r="F40" t="s">
         <v>7</v>
       </c>
       <c r="G40" t="s">
-        <v>220</v>
+        <v>222</v>
       </c>
       <c r="H40" t="s">
-        <v>11</v>
+        <v>8</v>
       </c>
     </row>
     <row r="41" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A41" t="s">
-        <v>221</v>
+        <v>223</v>
       </c>
       <c r="C41" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="D41" t="s">
-        <v>218</v>
+        <v>224</v>
       </c>
       <c r="E41" t="s">
-        <v>219</v>
+        <v>124</v>
       </c>
       <c r="F41" t="s">
         <v>7</v>
       </c>
       <c r="G41" t="s">
-        <v>220</v>
+        <v>225</v>
       </c>
       <c r="H41" t="s">
-        <v>11</v>
+        <v>8</v>
       </c>
     </row>
     <row r="42" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A42" t="s">
-        <v>222</v>
+        <v>226</v>
       </c>
       <c r="C42" t="s">
-        <v>17</v>
+        <v>23</v>
       </c>
       <c r="D42" t="s">
-        <v>223</v>
+        <v>227</v>
       </c>
       <c r="E42" t="s">
-        <v>67</v>
+        <v>228</v>
       </c>
       <c r="F42" t="s">
         <v>7</v>
       </c>
       <c r="G42" t="s">
-        <v>224</v>
+        <v>229</v>
       </c>
       <c r="H42" t="s">
-        <v>11</v>
+        <v>8</v>
       </c>
     </row>
     <row r="43" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A43" t="s">
-        <v>225</v>
+        <v>230</v>
       </c>
       <c r="C43" t="s">
-        <v>17</v>
+        <v>64</v>
       </c>
       <c r="D43" t="s">
-        <v>223</v>
+        <v>231</v>
       </c>
       <c r="E43" t="s">
-        <v>67</v>
+        <v>204</v>
       </c>
       <c r="F43" t="s">
         <v>7</v>
       </c>
       <c r="G43" t="s">
-        <v>224</v>
+        <v>232</v>
       </c>
       <c r="H43" t="s">
-        <v>11</v>
+        <v>8</v>
       </c>
     </row>
     <row r="44" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A44" t="s">
-        <v>226</v>
+        <v>233</v>
       </c>
       <c r="C44" t="s">
-        <v>63</v>
+        <v>39</v>
       </c>
       <c r="D44" t="s">
-        <v>227</v>
+        <v>234</v>
       </c>
       <c r="E44" t="s">
-        <v>71</v>
+        <v>235</v>
       </c>
       <c r="F44" t="s">
-        <v>72</v>
+        <v>7</v>
       </c>
       <c r="G44" t="s">
-        <v>78</v>
+        <v>236</v>
       </c>
       <c r="H44" t="s">
-        <v>11</v>
+        <v>8</v>
       </c>
     </row>
     <row r="45" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A45" t="s">
-        <v>228</v>
+        <v>237</v>
       </c>
       <c r="C45" t="s">
-        <v>63</v>
+        <v>33</v>
       </c>
       <c r="D45" t="s">
-        <v>227</v>
+        <v>238</v>
       </c>
       <c r="E45" t="s">
-        <v>71</v>
+        <v>90</v>
       </c>
       <c r="F45" t="s">
-        <v>72</v>
+        <v>7</v>
       </c>
       <c r="G45" t="s">
-        <v>78</v>
+        <v>91</v>
       </c>
       <c r="H45" t="s">
-        <v>11</v>
+        <v>8</v>
       </c>
     </row>
     <row r="46" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A46" t="s">
-        <v>229</v>
+        <v>239</v>
       </c>
       <c r="C46" t="s">
-        <v>125</v>
+        <v>50</v>
       </c>
       <c r="D46" t="s">
-        <v>230</v>
+        <v>240</v>
       </c>
       <c r="E46" t="s">
-        <v>231</v>
+        <v>78</v>
       </c>
       <c r="F46" t="s">
-        <v>232</v>
+        <v>79</v>
       </c>
       <c r="G46" t="s">
-        <v>233</v>
+        <v>241</v>
       </c>
       <c r="H46" t="s">
-        <v>11</v>
+        <v>32</v>
       </c>
     </row>
     <row r="47" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A47" t="s">
-        <v>234</v>
+        <v>242</v>
       </c>
       <c r="C47" t="s">
-        <v>13</v>
+        <v>136</v>
       </c>
       <c r="D47" t="s">
-        <v>235</v>
+        <v>243</v>
       </c>
       <c r="E47" t="s">
-        <v>236</v>
+        <v>54</v>
       </c>
       <c r="F47" t="s">
-        <v>7</v>
+        <v>55</v>
       </c>
       <c r="G47" t="s">
-        <v>237</v>
+        <v>87</v>
       </c>
       <c r="H47" t="s">
-        <v>11</v>
+        <v>32</v>
       </c>
     </row>
     <row r="48" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A48" t="s">
-        <v>238</v>
+        <v>244</v>
       </c>
       <c r="C48" t="s">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="D48" t="s">
-        <v>235</v>
+        <v>245</v>
       </c>
       <c r="E48" t="s">
-        <v>236</v>
+        <v>246</v>
       </c>
       <c r="F48" t="s">
-        <v>7</v>
+        <v>247</v>
       </c>
       <c r="G48" t="s">
-        <v>237</v>
+        <v>248</v>
       </c>
       <c r="H48" t="s">
         <v>11</v>
@@ -2830,22 +3652,22 @@
     </row>
     <row r="49" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A49" t="s">
-        <v>239</v>
+        <v>249</v>
       </c>
       <c r="C49" t="s">
-        <v>24</v>
+        <v>9</v>
       </c>
       <c r="D49" t="s">
-        <v>240</v>
+        <v>245</v>
       </c>
       <c r="E49" t="s">
-        <v>241</v>
+        <v>246</v>
       </c>
       <c r="F49" t="s">
-        <v>7</v>
+        <v>247</v>
       </c>
       <c r="G49" t="s">
-        <v>242</v>
+        <v>248</v>
       </c>
       <c r="H49" t="s">
         <v>11</v>
@@ -2853,22 +3675,22 @@
     </row>
     <row r="50" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A50" t="s">
-        <v>243</v>
+        <v>250</v>
       </c>
       <c r="C50" t="s">
-        <v>125</v>
+        <v>20</v>
       </c>
       <c r="D50" t="s">
-        <v>244</v>
+        <v>251</v>
       </c>
       <c r="E50" t="s">
-        <v>245</v>
+        <v>252</v>
       </c>
       <c r="F50" t="s">
-        <v>246</v>
+        <v>253</v>
       </c>
       <c r="G50" t="s">
-        <v>52</v>
+        <v>254</v>
       </c>
       <c r="H50" t="s">
         <v>11</v>
@@ -2876,22 +3698,22 @@
     </row>
     <row r="51" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A51" t="s">
-        <v>247</v>
+        <v>255</v>
       </c>
       <c r="C51" t="s">
-        <v>125</v>
+        <v>72</v>
       </c>
       <c r="D51" t="s">
-        <v>248</v>
+        <v>256</v>
       </c>
       <c r="E51" t="s">
-        <v>46</v>
+        <v>257</v>
       </c>
       <c r="F51" t="s">
-        <v>47</v>
+        <v>258</v>
       </c>
       <c r="G51" t="s">
-        <v>249</v>
+        <v>259</v>
       </c>
       <c r="H51" t="s">
         <v>11</v>
@@ -2899,22 +3721,22 @@
     </row>
     <row r="52" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A52" t="s">
-        <v>250</v>
+        <v>260</v>
       </c>
       <c r="C52" t="s">
-        <v>53</v>
+        <v>33</v>
       </c>
       <c r="D52" t="s">
-        <v>251</v>
+        <v>261</v>
       </c>
       <c r="E52" t="s">
-        <v>76</v>
+        <v>37</v>
       </c>
       <c r="F52" t="s">
-        <v>7</v>
+        <v>38</v>
       </c>
       <c r="G52" t="s">
-        <v>252</v>
+        <v>262</v>
       </c>
       <c r="H52" t="s">
         <v>11</v>
@@ -2922,22 +3744,22 @@
     </row>
     <row r="53" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A53" t="s">
-        <v>253</v>
+        <v>74</v>
       </c>
       <c r="C53" t="s">
-        <v>63</v>
+        <v>25</v>
       </c>
       <c r="D53" t="s">
-        <v>254</v>
+        <v>75</v>
       </c>
       <c r="E53" t="s">
-        <v>255</v>
+        <v>52</v>
       </c>
       <c r="F53" t="s">
-        <v>256</v>
+        <v>7</v>
       </c>
       <c r="G53" t="s">
-        <v>257</v>
+        <v>76</v>
       </c>
       <c r="H53" t="s">
         <v>11</v>
@@ -2945,22 +3767,22 @@
     </row>
     <row r="54" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A54" t="s">
-        <v>258</v>
+        <v>77</v>
       </c>
       <c r="C54" t="s">
-        <v>63</v>
+        <v>25</v>
       </c>
       <c r="D54" t="s">
-        <v>254</v>
+        <v>75</v>
       </c>
       <c r="E54" t="s">
-        <v>255</v>
+        <v>52</v>
       </c>
       <c r="F54" t="s">
-        <v>256</v>
+        <v>7</v>
       </c>
       <c r="G54" t="s">
-        <v>257</v>
+        <v>76</v>
       </c>
       <c r="H54" t="s">
         <v>11</v>
@@ -2968,22 +3790,22 @@
     </row>
     <row r="55" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A55" t="s">
-        <v>259</v>
+        <v>263</v>
       </c>
       <c r="C55" t="s">
-        <v>26</v>
+        <v>33</v>
       </c>
       <c r="D55" t="s">
-        <v>260</v>
+        <v>264</v>
       </c>
       <c r="E55" t="s">
-        <v>261</v>
+        <v>37</v>
       </c>
       <c r="F55" t="s">
-        <v>7</v>
+        <v>38</v>
       </c>
       <c r="G55" t="s">
-        <v>262</v>
+        <v>265</v>
       </c>
       <c r="H55" t="s">
         <v>11</v>
@@ -2991,22 +3813,22 @@
     </row>
     <row r="56" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A56" t="s">
-        <v>263</v>
+        <v>266</v>
       </c>
       <c r="C56" t="s">
-        <v>26</v>
+        <v>22</v>
       </c>
       <c r="D56" t="s">
-        <v>260</v>
+        <v>267</v>
       </c>
       <c r="E56" t="s">
-        <v>261</v>
+        <v>192</v>
       </c>
       <c r="F56" t="s">
         <v>7</v>
       </c>
       <c r="G56" t="s">
-        <v>262</v>
+        <v>268</v>
       </c>
       <c r="H56" t="s">
         <v>11</v>
@@ -3014,22 +3836,22 @@
     </row>
     <row r="57" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A57" t="s">
-        <v>264</v>
+        <v>269</v>
       </c>
       <c r="C57" t="s">
-        <v>125</v>
+        <v>136</v>
       </c>
       <c r="D57" t="s">
-        <v>265</v>
+        <v>270</v>
       </c>
       <c r="E57" t="s">
-        <v>36</v>
+        <v>57</v>
       </c>
       <c r="F57" t="s">
-        <v>37</v>
+        <v>58</v>
       </c>
       <c r="G57" t="s">
-        <v>266</v>
+        <v>271</v>
       </c>
       <c r="H57" t="s">
         <v>11</v>
@@ -3037,22 +3859,22 @@
     </row>
     <row r="58" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A58" t="s">
-        <v>267</v>
+        <v>272</v>
       </c>
       <c r="C58" t="s">
-        <v>17</v>
+        <v>24</v>
       </c>
       <c r="D58" t="s">
-        <v>268</v>
+        <v>273</v>
       </c>
       <c r="E58" t="s">
-        <v>67</v>
+        <v>124</v>
       </c>
       <c r="F58" t="s">
         <v>7</v>
       </c>
       <c r="G58" t="s">
-        <v>269</v>
+        <v>274</v>
       </c>
       <c r="H58" t="s">
         <v>11</v>
@@ -3060,22 +3882,22 @@
     </row>
     <row r="59" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A59" t="s">
-        <v>270</v>
+        <v>275</v>
       </c>
       <c r="C59" t="s">
-        <v>26</v>
+        <v>148</v>
       </c>
       <c r="D59" t="s">
-        <v>271</v>
+        <v>276</v>
       </c>
       <c r="E59" t="s">
-        <v>261</v>
+        <v>277</v>
       </c>
       <c r="F59" t="s">
         <v>7</v>
       </c>
       <c r="G59" t="s">
-        <v>272</v>
+        <v>278</v>
       </c>
       <c r="H59" t="s">
         <v>11</v>
@@ -3083,22 +3905,22 @@
     </row>
     <row r="60" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A60" t="s">
-        <v>273</v>
+        <v>279</v>
       </c>
       <c r="C60" t="s">
-        <v>13</v>
+        <v>20</v>
       </c>
       <c r="D60" t="s">
-        <v>274</v>
+        <v>280</v>
       </c>
       <c r="E60" t="s">
-        <v>57</v>
+        <v>34</v>
       </c>
       <c r="F60" t="s">
         <v>7</v>
       </c>
       <c r="G60" t="s">
-        <v>58</v>
+        <v>281</v>
       </c>
       <c r="H60" t="s">
         <v>11</v>
@@ -3106,22 +3928,22 @@
     </row>
     <row r="61" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A61" t="s">
-        <v>275</v>
+        <v>282</v>
       </c>
       <c r="C61" t="s">
-        <v>125</v>
+        <v>9</v>
       </c>
       <c r="D61" t="s">
-        <v>276</v>
+        <v>283</v>
       </c>
       <c r="E61" t="s">
-        <v>277</v>
+        <v>26</v>
       </c>
       <c r="F61" t="s">
-        <v>278</v>
+        <v>27</v>
       </c>
       <c r="G61" t="s">
-        <v>279</v>
+        <v>284</v>
       </c>
       <c r="H61" t="s">
         <v>11</v>
@@ -3129,22 +3951,22 @@
     </row>
     <row r="62" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A62" t="s">
-        <v>280</v>
+        <v>285</v>
       </c>
       <c r="C62" t="s">
-        <v>125</v>
+        <v>50</v>
       </c>
       <c r="D62" t="s">
-        <v>276</v>
+        <v>286</v>
       </c>
       <c r="E62" t="s">
-        <v>277</v>
+        <v>84</v>
       </c>
       <c r="F62" t="s">
-        <v>278</v>
+        <v>85</v>
       </c>
       <c r="G62" t="s">
-        <v>279</v>
+        <v>287</v>
       </c>
       <c r="H62" t="s">
         <v>11</v>
@@ -3152,22 +3974,22 @@
     </row>
     <row r="63" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A63" t="s">
-        <v>281</v>
+        <v>288</v>
       </c>
       <c r="C63" t="s">
-        <v>13</v>
+        <v>86</v>
       </c>
       <c r="D63" t="s">
-        <v>282</v>
+        <v>289</v>
       </c>
       <c r="E63" t="s">
-        <v>283</v>
+        <v>290</v>
       </c>
       <c r="F63" t="s">
         <v>7</v>
       </c>
       <c r="G63" t="s">
-        <v>284</v>
+        <v>291</v>
       </c>
       <c r="H63" t="s">
         <v>11</v>
@@ -3175,22 +3997,22 @@
     </row>
     <row r="64" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A64" t="s">
-        <v>285</v>
+        <v>292</v>
       </c>
       <c r="C64" t="s">
-        <v>13</v>
+        <v>20</v>
       </c>
       <c r="D64" t="s">
-        <v>282</v>
+        <v>293</v>
       </c>
       <c r="E64" t="s">
-        <v>283</v>
+        <v>294</v>
       </c>
       <c r="F64" t="s">
-        <v>7</v>
+        <v>295</v>
       </c>
       <c r="G64" t="s">
-        <v>284</v>
+        <v>296</v>
       </c>
       <c r="H64" t="s">
         <v>11</v>
@@ -3198,22 +4020,22 @@
     </row>
     <row r="65" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A65" t="s">
-        <v>286</v>
+        <v>297</v>
       </c>
       <c r="C65" t="s">
-        <v>125</v>
+        <v>20</v>
       </c>
       <c r="D65" t="s">
-        <v>287</v>
+        <v>293</v>
       </c>
       <c r="E65" t="s">
-        <v>59</v>
+        <v>294</v>
       </c>
       <c r="F65" t="s">
-        <v>60</v>
+        <v>295</v>
       </c>
       <c r="G65" t="s">
-        <v>52</v>
+        <v>296</v>
       </c>
       <c r="H65" t="s">
         <v>11</v>
@@ -3221,22 +4043,22 @@
     </row>
     <row r="66" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A66" t="s">
-        <v>288</v>
+        <v>298</v>
       </c>
       <c r="C66" t="s">
-        <v>289</v>
+        <v>72</v>
       </c>
       <c r="D66" t="s">
-        <v>290</v>
+        <v>299</v>
       </c>
       <c r="E66" t="s">
-        <v>65</v>
+        <v>300</v>
       </c>
       <c r="F66" t="s">
-        <v>7</v>
+        <v>301</v>
       </c>
       <c r="G66" t="s">
-        <v>66</v>
+        <v>302</v>
       </c>
       <c r="H66" t="s">
         <v>11</v>
@@ -3244,22 +4066,22 @@
     </row>
     <row r="67" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A67" t="s">
-        <v>291</v>
+        <v>303</v>
       </c>
       <c r="C67" t="s">
-        <v>48</v>
+        <v>24</v>
       </c>
       <c r="D67" t="s">
-        <v>292</v>
+        <v>304</v>
       </c>
       <c r="E67" t="s">
-        <v>68</v>
+        <v>305</v>
       </c>
       <c r="F67" t="s">
         <v>7</v>
       </c>
       <c r="G67" t="s">
-        <v>293</v>
+        <v>306</v>
       </c>
       <c r="H67" t="s">
         <v>11</v>
@@ -3267,22 +4089,22 @@
     </row>
     <row r="68" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A68" t="s">
-        <v>294</v>
+        <v>307</v>
       </c>
       <c r="C68" t="s">
-        <v>53</v>
+        <v>148</v>
       </c>
       <c r="D68" t="s">
-        <v>295</v>
+        <v>308</v>
       </c>
       <c r="E68" t="s">
-        <v>76</v>
+        <v>56</v>
       </c>
       <c r="F68" t="s">
         <v>7</v>
       </c>
       <c r="G68" t="s">
-        <v>296</v>
+        <v>309</v>
       </c>
       <c r="H68" t="s">
         <v>11</v>
@@ -3290,22 +4112,22 @@
     </row>
     <row r="69" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A69" t="s">
-        <v>297</v>
+        <v>310</v>
       </c>
       <c r="C69" t="s">
-        <v>63</v>
+        <v>13</v>
       </c>
       <c r="D69" t="s">
-        <v>298</v>
+        <v>311</v>
       </c>
       <c r="E69" t="s">
-        <v>80</v>
+        <v>312</v>
       </c>
       <c r="F69" t="s">
-        <v>81</v>
+        <v>313</v>
       </c>
       <c r="G69" t="s">
-        <v>299</v>
+        <v>314</v>
       </c>
       <c r="H69" t="s">
         <v>11</v>
@@ -3313,22 +4135,22 @@
     </row>
     <row r="70" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A70" t="s">
-        <v>300</v>
+        <v>315</v>
       </c>
       <c r="C70" t="s">
-        <v>63</v>
+        <v>13</v>
       </c>
       <c r="D70" t="s">
-        <v>301</v>
+        <v>316</v>
       </c>
       <c r="E70" t="s">
-        <v>80</v>
+        <v>312</v>
       </c>
       <c r="F70" t="s">
-        <v>81</v>
+        <v>313</v>
       </c>
       <c r="G70" t="s">
-        <v>302</v>
+        <v>317</v>
       </c>
       <c r="H70" t="s">
         <v>11</v>
@@ -3336,22 +4158,22 @@
     </row>
     <row r="71" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A71" t="s">
-        <v>303</v>
+        <v>318</v>
       </c>
       <c r="C71" t="s">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="D71" t="s">
-        <v>304</v>
+        <v>316</v>
       </c>
       <c r="E71" t="s">
-        <v>130</v>
+        <v>312</v>
       </c>
       <c r="F71" t="s">
-        <v>131</v>
+        <v>313</v>
       </c>
       <c r="G71" t="s">
-        <v>132</v>
+        <v>317</v>
       </c>
       <c r="H71" t="s">
         <v>11</v>
@@ -3359,22 +4181,22 @@
     </row>
     <row r="72" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A72" t="s">
-        <v>305</v>
+        <v>319</v>
       </c>
       <c r="C72" t="s">
-        <v>9</v>
+        <v>43</v>
       </c>
       <c r="D72" t="s">
-        <v>304</v>
+        <v>320</v>
       </c>
       <c r="E72" t="s">
-        <v>130</v>
+        <v>321</v>
       </c>
       <c r="F72" t="s">
-        <v>131</v>
+        <v>322</v>
       </c>
       <c r="G72" t="s">
-        <v>132</v>
+        <v>323</v>
       </c>
       <c r="H72" t="s">
         <v>11</v>
@@ -3382,22 +4204,22 @@
     </row>
     <row r="73" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A73" t="s">
-        <v>306</v>
+        <v>324</v>
       </c>
       <c r="C73" t="s">
-        <v>9</v>
+        <v>43</v>
       </c>
       <c r="D73" t="s">
-        <v>304</v>
+        <v>320</v>
       </c>
       <c r="E73" t="s">
-        <v>130</v>
+        <v>321</v>
       </c>
       <c r="F73" t="s">
-        <v>131</v>
+        <v>322</v>
       </c>
       <c r="G73" t="s">
-        <v>132</v>
+        <v>323</v>
       </c>
       <c r="H73" t="s">
         <v>11</v>
@@ -3405,22 +4227,22 @@
     </row>
     <row r="74" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A74" t="s">
-        <v>307</v>
+        <v>325</v>
       </c>
       <c r="C74" t="s">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="D74" t="s">
-        <v>308</v>
+        <v>326</v>
       </c>
       <c r="E74" t="s">
-        <v>61</v>
+        <v>327</v>
       </c>
       <c r="F74" t="s">
         <v>7</v>
       </c>
       <c r="G74" t="s">
-        <v>309</v>
+        <v>328</v>
       </c>
       <c r="H74" t="s">
         <v>11</v>
@@ -3428,22 +4250,22 @@
     </row>
     <row r="75" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A75" t="s">
-        <v>310</v>
+        <v>329</v>
       </c>
       <c r="C75" t="s">
-        <v>21</v>
+        <v>10</v>
       </c>
       <c r="D75" t="s">
-        <v>308</v>
+        <v>330</v>
       </c>
       <c r="E75" t="s">
-        <v>61</v>
+        <v>51</v>
       </c>
       <c r="F75" t="s">
         <v>7</v>
       </c>
       <c r="G75" t="s">
-        <v>309</v>
+        <v>331</v>
       </c>
       <c r="H75" t="s">
         <v>11</v>
@@ -3451,22 +4273,22 @@
     </row>
     <row r="76" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A76" t="s">
-        <v>311</v>
+        <v>332</v>
       </c>
       <c r="C76" t="s">
-        <v>205</v>
+        <v>10</v>
       </c>
       <c r="D76" t="s">
-        <v>312</v>
+        <v>333</v>
       </c>
       <c r="E76" t="s">
-        <v>313</v>
+        <v>80</v>
       </c>
       <c r="F76" t="s">
         <v>7</v>
       </c>
       <c r="G76" t="s">
-        <v>314</v>
+        <v>334</v>
       </c>
       <c r="H76" t="s">
         <v>11</v>
@@ -3474,22 +4296,22 @@
     </row>
     <row r="77" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A77" t="s">
-        <v>315</v>
+        <v>335</v>
       </c>
       <c r="C77" t="s">
-        <v>48</v>
+        <v>43</v>
       </c>
       <c r="D77" t="s">
-        <v>316</v>
+        <v>336</v>
       </c>
       <c r="E77" t="s">
-        <v>317</v>
+        <v>337</v>
       </c>
       <c r="F77" t="s">
-        <v>7</v>
+        <v>338</v>
       </c>
       <c r="G77" t="s">
-        <v>318</v>
+        <v>339</v>
       </c>
       <c r="H77" t="s">
         <v>11</v>
@@ -3497,22 +4319,22 @@
     </row>
     <row r="78" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A78" t="s">
-        <v>319</v>
+        <v>340</v>
       </c>
       <c r="C78" t="s">
-        <v>53</v>
+        <v>341</v>
       </c>
       <c r="D78" t="s">
-        <v>320</v>
+        <v>342</v>
       </c>
       <c r="E78" t="s">
-        <v>321</v>
+        <v>343</v>
       </c>
       <c r="F78" t="s">
         <v>7</v>
       </c>
       <c r="G78" t="s">
-        <v>322</v>
+        <v>344</v>
       </c>
       <c r="H78" t="s">
         <v>11</v>
@@ -3520,22 +4342,22 @@
     </row>
     <row r="79" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A79" t="s">
-        <v>323</v>
+        <v>345</v>
       </c>
       <c r="C79" t="s">
-        <v>125</v>
+        <v>22</v>
       </c>
       <c r="D79" t="s">
-        <v>324</v>
+        <v>346</v>
       </c>
       <c r="E79" t="s">
-        <v>46</v>
+        <v>347</v>
       </c>
       <c r="F79" t="s">
-        <v>47</v>
+        <v>7</v>
       </c>
       <c r="G79" t="s">
-        <v>325</v>
+        <v>348</v>
       </c>
       <c r="H79" t="s">
         <v>11</v>
@@ -3543,22 +4365,22 @@
     </row>
     <row r="80" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A80" t="s">
-        <v>326</v>
+        <v>349</v>
       </c>
       <c r="C80" t="s">
-        <v>13</v>
+        <v>72</v>
       </c>
       <c r="D80" t="s">
-        <v>327</v>
+        <v>350</v>
       </c>
       <c r="E80" t="s">
-        <v>328</v>
+        <v>300</v>
       </c>
       <c r="F80" t="s">
-        <v>7</v>
+        <v>301</v>
       </c>
       <c r="G80" t="s">
-        <v>329</v>
+        <v>351</v>
       </c>
       <c r="H80" t="s">
         <v>11</v>
@@ -3566,22 +4388,22 @@
     </row>
     <row r="81" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A81" t="s">
-        <v>330</v>
+        <v>352</v>
       </c>
       <c r="C81" t="s">
-        <v>63</v>
+        <v>136</v>
       </c>
       <c r="D81" t="s">
-        <v>331</v>
+        <v>353</v>
       </c>
       <c r="E81" t="s">
-        <v>332</v>
+        <v>354</v>
       </c>
       <c r="F81" t="s">
-        <v>333</v>
+        <v>355</v>
       </c>
       <c r="G81" t="s">
-        <v>334</v>
+        <v>356</v>
       </c>
       <c r="H81" t="s">
         <v>11</v>
@@ -3589,22 +4411,22 @@
     </row>
     <row r="82" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A82" t="s">
-        <v>335</v>
+        <v>357</v>
       </c>
       <c r="C82" t="s">
-        <v>19</v>
+        <v>43</v>
       </c>
       <c r="D82" t="s">
-        <v>336</v>
+        <v>358</v>
       </c>
       <c r="E82" t="s">
-        <v>30</v>
+        <v>359</v>
       </c>
       <c r="F82" t="s">
-        <v>31</v>
+        <v>7</v>
       </c>
       <c r="G82" t="s">
-        <v>337</v>
+        <v>360</v>
       </c>
       <c r="H82" t="s">
         <v>11</v>
@@ -3612,22 +4434,22 @@
     </row>
     <row r="83" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A83" t="s">
-        <v>338</v>
+        <v>361</v>
       </c>
       <c r="C83" t="s">
-        <v>18</v>
+        <v>22</v>
       </c>
       <c r="D83" t="s">
-        <v>339</v>
+        <v>362</v>
       </c>
       <c r="E83" t="s">
-        <v>214</v>
+        <v>363</v>
       </c>
       <c r="F83" t="s">
         <v>7</v>
       </c>
       <c r="G83" t="s">
-        <v>215</v>
+        <v>364</v>
       </c>
       <c r="H83" t="s">
         <v>11</v>
@@ -3635,22 +4457,22 @@
     </row>
     <row r="84" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A84" t="s">
-        <v>340</v>
+        <v>365</v>
       </c>
       <c r="C84" t="s">
-        <v>53</v>
+        <v>43</v>
       </c>
       <c r="D84" t="s">
-        <v>341</v>
+        <v>366</v>
       </c>
       <c r="E84" t="s">
-        <v>342</v>
+        <v>367</v>
       </c>
       <c r="F84" t="s">
-        <v>7</v>
+        <v>368</v>
       </c>
       <c r="G84" t="s">
-        <v>343</v>
+        <v>369</v>
       </c>
       <c r="H84" t="s">
         <v>11</v>
@@ -3658,22 +4480,22 @@
     </row>
     <row r="85" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A85" t="s">
-        <v>344</v>
+        <v>370</v>
       </c>
       <c r="C85" t="s">
-        <v>48</v>
+        <v>43</v>
       </c>
       <c r="D85" t="s">
-        <v>345</v>
+        <v>366</v>
       </c>
       <c r="E85" t="s">
-        <v>28</v>
+        <v>367</v>
       </c>
       <c r="F85" t="s">
-        <v>7</v>
+        <v>368</v>
       </c>
       <c r="G85" t="s">
-        <v>163</v>
+        <v>369</v>
       </c>
       <c r="H85" t="s">
         <v>11</v>
@@ -3681,22 +4503,22 @@
     </row>
     <row r="86" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A86" t="s">
-        <v>346</v>
+        <v>371</v>
       </c>
       <c r="C86" t="s">
-        <v>125</v>
+        <v>9</v>
       </c>
       <c r="D86" t="s">
-        <v>347</v>
+        <v>372</v>
       </c>
       <c r="E86" t="s">
-        <v>231</v>
+        <v>92</v>
       </c>
       <c r="F86" t="s">
-        <v>232</v>
+        <v>93</v>
       </c>
       <c r="G86" t="s">
-        <v>348</v>
+        <v>373</v>
       </c>
       <c r="H86" t="s">
         <v>11</v>
@@ -3704,22 +4526,22 @@
     </row>
     <row r="87" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A87" t="s">
-        <v>349</v>
+        <v>374</v>
       </c>
       <c r="C87" t="s">
-        <v>21</v>
+        <v>9</v>
       </c>
       <c r="D87" t="s">
-        <v>350</v>
+        <v>375</v>
       </c>
       <c r="E87" t="s">
-        <v>41</v>
+        <v>376</v>
       </c>
       <c r="F87" t="s">
-        <v>7</v>
+        <v>377</v>
       </c>
       <c r="G87" t="s">
-        <v>351</v>
+        <v>378</v>
       </c>
       <c r="H87" t="s">
         <v>11</v>
@@ -3727,22 +4549,22 @@
     </row>
     <row r="88" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A88" t="s">
-        <v>352</v>
+        <v>379</v>
       </c>
       <c r="C88" t="s">
-        <v>24</v>
+        <v>43</v>
       </c>
       <c r="D88" t="s">
-        <v>353</v>
+        <v>380</v>
       </c>
       <c r="E88" t="s">
-        <v>354</v>
+        <v>35</v>
       </c>
       <c r="F88" t="s">
         <v>7</v>
       </c>
       <c r="G88" t="s">
-        <v>355</v>
+        <v>381</v>
       </c>
       <c r="H88" t="s">
         <v>11</v>
@@ -3750,22 +4572,22 @@
     </row>
     <row r="89" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A89" t="s">
-        <v>356</v>
+        <v>382</v>
       </c>
       <c r="C89" t="s">
-        <v>24</v>
+        <v>148</v>
       </c>
       <c r="D89" t="s">
-        <v>357</v>
+        <v>383</v>
       </c>
       <c r="E89" t="s">
-        <v>358</v>
+        <v>384</v>
       </c>
       <c r="F89" t="s">
         <v>7</v>
       </c>
       <c r="G89" t="s">
-        <v>359</v>
+        <v>385</v>
       </c>
       <c r="H89" t="s">
         <v>11</v>
@@ -3773,22 +4595,22 @@
     </row>
     <row r="90" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A90" t="s">
-        <v>360</v>
+        <v>386</v>
       </c>
       <c r="C90" t="s">
-        <v>22</v>
+        <v>148</v>
       </c>
       <c r="D90" t="s">
-        <v>361</v>
+        <v>383</v>
       </c>
       <c r="E90" t="s">
-        <v>186</v>
+        <v>384</v>
       </c>
       <c r="F90" t="s">
-        <v>187</v>
+        <v>7</v>
       </c>
       <c r="G90" t="s">
-        <v>362</v>
+        <v>385</v>
       </c>
       <c r="H90" t="s">
         <v>11</v>
@@ -3796,22 +4618,22 @@
     </row>
     <row r="91" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A91" t="s">
-        <v>363</v>
+        <v>387</v>
       </c>
       <c r="C91" t="s">
-        <v>39</v>
+        <v>16</v>
       </c>
       <c r="D91" t="s">
-        <v>364</v>
+        <v>388</v>
       </c>
       <c r="E91" t="s">
-        <v>365</v>
+        <v>389</v>
       </c>
       <c r="F91" t="s">
         <v>7</v>
       </c>
       <c r="G91" t="s">
-        <v>366</v>
+        <v>390</v>
       </c>
       <c r="H91" t="s">
         <v>11</v>
@@ -3819,22 +4641,22 @@
     </row>
     <row r="92" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A92" t="s">
-        <v>367</v>
+        <v>391</v>
       </c>
       <c r="C92" t="s">
-        <v>39</v>
+        <v>16</v>
       </c>
       <c r="D92" t="s">
-        <v>364</v>
+        <v>388</v>
       </c>
       <c r="E92" t="s">
-        <v>365</v>
+        <v>389</v>
       </c>
       <c r="F92" t="s">
         <v>7</v>
       </c>
       <c r="G92" t="s">
-        <v>366</v>
+        <v>390</v>
       </c>
       <c r="H92" t="s">
         <v>11</v>
@@ -3842,22 +4664,22 @@
     </row>
     <row r="93" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A93" t="s">
-        <v>368</v>
+        <v>392</v>
       </c>
       <c r="C93" t="s">
-        <v>39</v>
+        <v>16</v>
       </c>
       <c r="D93" t="s">
-        <v>364</v>
+        <v>388</v>
       </c>
       <c r="E93" t="s">
-        <v>365</v>
+        <v>389</v>
       </c>
       <c r="F93" t="s">
         <v>7</v>
       </c>
       <c r="G93" t="s">
-        <v>366</v>
+        <v>390</v>
       </c>
       <c r="H93" t="s">
         <v>11</v>
@@ -3865,22 +4687,22 @@
     </row>
     <row r="94" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A94" t="s">
-        <v>369</v>
+        <v>393</v>
       </c>
       <c r="C94" t="s">
-        <v>17</v>
+        <v>394</v>
       </c>
       <c r="D94" t="s">
-        <v>370</v>
+        <v>395</v>
       </c>
       <c r="E94" t="s">
-        <v>16</v>
+        <v>396</v>
       </c>
       <c r="F94" t="s">
         <v>7</v>
       </c>
       <c r="G94" t="s">
-        <v>79</v>
+        <v>397</v>
       </c>
       <c r="H94" t="s">
         <v>11</v>
@@ -3888,22 +4710,22 @@
     </row>
     <row r="95" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A95" t="s">
-        <v>371</v>
+        <v>398</v>
       </c>
       <c r="C95" t="s">
-        <v>17</v>
+        <v>148</v>
       </c>
       <c r="D95" t="s">
-        <v>370</v>
+        <v>399</v>
       </c>
       <c r="E95" t="s">
-        <v>16</v>
+        <v>384</v>
       </c>
       <c r="F95" t="s">
         <v>7</v>
       </c>
       <c r="G95" t="s">
-        <v>79</v>
+        <v>400</v>
       </c>
       <c r="H95" t="s">
         <v>11</v>
@@ -3911,637 +4733,2460 @@
     </row>
     <row r="96" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A96" t="s">
-        <v>372</v>
+        <v>401</v>
       </c>
       <c r="C96" t="s">
-        <v>24</v>
+        <v>148</v>
       </c>
       <c r="D96" t="s">
-        <v>373</v>
+        <v>399</v>
       </c>
       <c r="E96" t="s">
-        <v>374</v>
+        <v>384</v>
       </c>
       <c r="F96" t="s">
         <v>7</v>
       </c>
       <c r="G96" t="s">
-        <v>375</v>
+        <v>400</v>
       </c>
       <c r="H96" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
     </row>
     <row r="97" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A97" t="s">
-        <v>376</v>
+        <v>402</v>
       </c>
       <c r="C97" t="s">
-        <v>39</v>
+        <v>50</v>
       </c>
       <c r="D97" t="s">
-        <v>377</v>
+        <v>403</v>
       </c>
       <c r="E97" t="s">
-        <v>365</v>
+        <v>40</v>
       </c>
       <c r="F97" t="s">
-        <v>7</v>
+        <v>41</v>
       </c>
       <c r="G97" t="s">
-        <v>378</v>
+        <v>404</v>
       </c>
       <c r="H97" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
     </row>
     <row r="98" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A98" t="s">
-        <v>379</v>
+        <v>405</v>
       </c>
       <c r="C98" t="s">
-        <v>9</v>
+        <v>23</v>
       </c>
       <c r="D98" t="s">
-        <v>380</v>
+        <v>406</v>
       </c>
       <c r="E98" t="s">
-        <v>32</v>
+        <v>228</v>
       </c>
       <c r="F98" t="s">
         <v>7</v>
       </c>
       <c r="G98" t="s">
-        <v>381</v>
+        <v>407</v>
       </c>
       <c r="H98" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
     </row>
     <row r="99" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A99" t="s">
-        <v>382</v>
+        <v>408</v>
       </c>
       <c r="C99" t="s">
-        <v>205</v>
+        <v>409</v>
       </c>
       <c r="D99" t="s">
-        <v>383</v>
+        <v>410</v>
       </c>
       <c r="E99" t="s">
-        <v>384</v>
+        <v>411</v>
       </c>
       <c r="F99" t="s">
         <v>7</v>
       </c>
       <c r="G99" t="s">
-        <v>385</v>
+        <v>412</v>
       </c>
       <c r="H99" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
     </row>
     <row r="100" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A100" t="s">
-        <v>386</v>
+        <v>413</v>
       </c>
       <c r="C100" t="s">
-        <v>63</v>
+        <v>18</v>
       </c>
       <c r="D100" t="s">
-        <v>387</v>
+        <v>414</v>
       </c>
       <c r="E100" t="s">
-        <v>388</v>
+        <v>415</v>
       </c>
       <c r="F100" t="s">
-        <v>389</v>
+        <v>416</v>
       </c>
       <c r="G100" t="s">
-        <v>390</v>
+        <v>417</v>
       </c>
       <c r="H100" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
     </row>
     <row r="101" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A101" t="s">
-        <v>391</v>
+        <v>418</v>
       </c>
       <c r="C101" t="s">
-        <v>9</v>
+        <v>17</v>
       </c>
       <c r="D101" t="s">
-        <v>392</v>
+        <v>419</v>
       </c>
       <c r="E101" t="s">
-        <v>393</v>
+        <v>60</v>
       </c>
       <c r="F101" t="s">
-        <v>394</v>
+        <v>61</v>
       </c>
       <c r="G101" t="s">
-        <v>395</v>
+        <v>420</v>
       </c>
       <c r="H101" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
     </row>
     <row r="102" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A102" t="s">
-        <v>396</v>
+        <v>421</v>
       </c>
       <c r="C102" t="s">
-        <v>19</v>
+        <v>148</v>
       </c>
       <c r="D102" t="s">
-        <v>397</v>
+        <v>422</v>
       </c>
       <c r="E102" t="s">
-        <v>398</v>
+        <v>384</v>
       </c>
       <c r="F102" t="s">
         <v>7</v>
       </c>
       <c r="G102" t="s">
-        <v>399</v>
+        <v>423</v>
       </c>
       <c r="H102" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
     </row>
     <row r="103" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A103" t="s">
-        <v>400</v>
+        <v>424</v>
       </c>
       <c r="C103" t="s">
-        <v>21</v>
+        <v>148</v>
       </c>
       <c r="D103" t="s">
-        <v>401</v>
+        <v>422</v>
       </c>
       <c r="E103" t="s">
-        <v>55</v>
+        <v>384</v>
       </c>
       <c r="F103" t="s">
-        <v>56</v>
+        <v>7</v>
       </c>
       <c r="G103" t="s">
-        <v>402</v>
+        <v>423</v>
       </c>
       <c r="H103" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
     </row>
     <row r="104" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A104" t="s">
-        <v>403</v>
+        <v>425</v>
       </c>
       <c r="C104" t="s">
-        <v>19</v>
+        <v>72</v>
       </c>
       <c r="D104" t="s">
-        <v>404</v>
+        <v>426</v>
       </c>
       <c r="E104" t="s">
-        <v>405</v>
+        <v>427</v>
       </c>
       <c r="F104" t="s">
-        <v>406</v>
+        <v>428</v>
       </c>
       <c r="G104" t="s">
-        <v>75</v>
+        <v>429</v>
       </c>
       <c r="H104" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
     </row>
     <row r="105" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A105" t="s">
-        <v>407</v>
+        <v>430</v>
       </c>
       <c r="C105" t="s">
-        <v>17</v>
+        <v>10</v>
       </c>
       <c r="D105" t="s">
-        <v>408</v>
+        <v>431</v>
       </c>
       <c r="E105" t="s">
-        <v>16</v>
+        <v>432</v>
       </c>
       <c r="F105" t="s">
         <v>7</v>
       </c>
       <c r="G105" t="s">
-        <v>409</v>
+        <v>433</v>
       </c>
       <c r="H105" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
     </row>
     <row r="106" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A106" t="s">
-        <v>410</v>
+        <v>434</v>
       </c>
       <c r="C106" t="s">
-        <v>24</v>
+        <v>64</v>
       </c>
       <c r="D106" t="s">
-        <v>411</v>
+        <v>435</v>
       </c>
       <c r="E106" t="s">
-        <v>54</v>
+        <v>436</v>
       </c>
       <c r="F106" t="s">
         <v>7</v>
       </c>
       <c r="G106" t="s">
-        <v>412</v>
+        <v>437</v>
       </c>
       <c r="H106" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
     </row>
     <row r="107" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A107" t="s">
-        <v>413</v>
+        <v>438</v>
       </c>
       <c r="C107" t="s">
-        <v>29</v>
+        <v>20</v>
       </c>
       <c r="D107" t="s">
-        <v>414</v>
+        <v>439</v>
       </c>
       <c r="E107" t="s">
-        <v>42</v>
+        <v>440</v>
       </c>
       <c r="F107" t="s">
-        <v>43</v>
+        <v>441</v>
       </c>
       <c r="G107" t="s">
-        <v>415</v>
+        <v>442</v>
       </c>
       <c r="H107" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
     </row>
     <row r="108" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A108" t="s">
-        <v>416</v>
+        <v>443</v>
       </c>
       <c r="C108" t="s">
-        <v>29</v>
+        <v>19</v>
       </c>
       <c r="D108" t="s">
-        <v>414</v>
+        <v>444</v>
       </c>
       <c r="E108" t="s">
-        <v>42</v>
+        <v>445</v>
       </c>
       <c r="F108" t="s">
-        <v>43</v>
+        <v>446</v>
       </c>
       <c r="G108" t="s">
-        <v>415</v>
+        <v>447</v>
       </c>
       <c r="H108" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
     </row>
     <row r="109" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A109" t="s">
-        <v>417</v>
+        <v>448</v>
       </c>
       <c r="C109" t="s">
-        <v>29</v>
+        <v>19</v>
       </c>
       <c r="D109" t="s">
-        <v>414</v>
+        <v>449</v>
       </c>
       <c r="E109" t="s">
-        <v>42</v>
+        <v>445</v>
       </c>
       <c r="F109" t="s">
-        <v>43</v>
+        <v>446</v>
       </c>
       <c r="G109" t="s">
-        <v>415</v>
+        <v>59</v>
       </c>
       <c r="H109" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
     </row>
     <row r="110" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A110" t="s">
-        <v>418</v>
+        <v>450</v>
       </c>
       <c r="C110" t="s">
-        <v>63</v>
+        <v>18</v>
       </c>
       <c r="D110" t="s">
-        <v>419</v>
+        <v>451</v>
       </c>
       <c r="E110" t="s">
-        <v>34</v>
+        <v>452</v>
       </c>
       <c r="F110" t="s">
-        <v>35</v>
+        <v>416</v>
       </c>
       <c r="G110" t="s">
-        <v>420</v>
+        <v>453</v>
       </c>
       <c r="H110" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
     </row>
     <row r="111" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A111" t="s">
-        <v>421</v>
+        <v>454</v>
       </c>
       <c r="C111" t="s">
-        <v>63</v>
+        <v>50</v>
       </c>
       <c r="D111" t="s">
-        <v>419</v>
+        <v>455</v>
       </c>
       <c r="E111" t="s">
-        <v>34</v>
+        <v>81</v>
       </c>
       <c r="F111" t="s">
-        <v>35</v>
+        <v>82</v>
       </c>
       <c r="G111" t="s">
-        <v>420</v>
+        <v>456</v>
       </c>
       <c r="H111" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
     </row>
     <row r="112" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A112" t="s">
-        <v>422</v>
+        <v>457</v>
       </c>
       <c r="C112" t="s">
-        <v>289</v>
+        <v>16</v>
       </c>
       <c r="D112" t="s">
-        <v>423</v>
+        <v>458</v>
       </c>
       <c r="E112" t="s">
-        <v>45</v>
+        <v>459</v>
       </c>
       <c r="F112" t="s">
         <v>7</v>
       </c>
       <c r="G112" t="s">
-        <v>424</v>
+        <v>94</v>
       </c>
       <c r="H112" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
     </row>
     <row r="113" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A113" t="s">
-        <v>425</v>
+        <v>460</v>
       </c>
       <c r="C113" t="s">
-        <v>48</v>
+        <v>33</v>
       </c>
       <c r="D113" t="s">
-        <v>426</v>
+        <v>461</v>
       </c>
       <c r="E113" t="s">
-        <v>77</v>
+        <v>462</v>
       </c>
       <c r="F113" t="s">
         <v>7</v>
       </c>
       <c r="G113" t="s">
-        <v>427</v>
+        <v>463</v>
       </c>
       <c r="H113" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
     </row>
     <row r="114" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A114" t="s">
-        <v>428</v>
+        <v>464</v>
       </c>
       <c r="C114" t="s">
-        <v>39</v>
+        <v>9</v>
       </c>
       <c r="D114" t="s">
-        <v>429</v>
+        <v>465</v>
       </c>
       <c r="E114" t="s">
-        <v>50</v>
+        <v>26</v>
       </c>
       <c r="F114" t="s">
-        <v>51</v>
+        <v>27</v>
       </c>
       <c r="G114" t="s">
-        <v>430</v>
+        <v>466</v>
       </c>
       <c r="H114" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
     </row>
     <row r="115" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A115" t="s">
-        <v>431</v>
+        <v>467</v>
       </c>
       <c r="C115" t="s">
-        <v>13</v>
+        <v>43</v>
       </c>
       <c r="D115" t="s">
-        <v>432</v>
+        <v>468</v>
       </c>
       <c r="E115" t="s">
-        <v>433</v>
+        <v>359</v>
       </c>
       <c r="F115" t="s">
         <v>7</v>
       </c>
       <c r="G115" t="s">
-        <v>434</v>
+        <v>469</v>
       </c>
       <c r="H115" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
     </row>
     <row r="116" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A116" t="s">
-        <v>435</v>
+        <v>470</v>
       </c>
       <c r="C116" t="s">
-        <v>63</v>
+        <v>409</v>
       </c>
       <c r="D116" t="s">
-        <v>436</v>
+        <v>471</v>
       </c>
       <c r="E116" t="s">
-        <v>437</v>
+        <v>411</v>
       </c>
       <c r="F116" t="s">
-        <v>438</v>
+        <v>7</v>
       </c>
       <c r="G116" t="s">
-        <v>439</v>
+        <v>472</v>
       </c>
       <c r="H116" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
     </row>
     <row r="117" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A117" t="s">
-        <v>440</v>
+        <v>473</v>
       </c>
       <c r="C117" t="s">
-        <v>9</v>
+        <v>17</v>
       </c>
       <c r="D117" t="s">
-        <v>441</v>
+        <v>474</v>
       </c>
       <c r="E117" t="s">
-        <v>44</v>
+        <v>60</v>
       </c>
       <c r="F117" t="s">
-        <v>7</v>
+        <v>61</v>
       </c>
       <c r="G117" t="s">
-        <v>442</v>
+        <v>475</v>
       </c>
       <c r="H117" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
     </row>
     <row r="118" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A118" t="s">
-        <v>443</v>
+        <v>476</v>
       </c>
       <c r="C118" t="s">
-        <v>9</v>
+        <v>17</v>
       </c>
       <c r="D118" t="s">
-        <v>441</v>
+        <v>477</v>
       </c>
       <c r="E118" t="s">
-        <v>44</v>
+        <v>478</v>
       </c>
       <c r="F118" t="s">
-        <v>7</v>
+        <v>479</v>
       </c>
       <c r="G118" t="s">
-        <v>442</v>
+        <v>480</v>
       </c>
       <c r="H118" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
     </row>
     <row r="119" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A119" t="s">
-        <v>444</v>
+        <v>481</v>
       </c>
       <c r="C119" t="s">
-        <v>29</v>
+        <v>17</v>
       </c>
       <c r="D119" t="s">
-        <v>445</v>
+        <v>477</v>
       </c>
       <c r="E119" t="s">
-        <v>446</v>
+        <v>478</v>
       </c>
       <c r="F119" t="s">
-        <v>447</v>
+        <v>479</v>
       </c>
       <c r="G119" t="s">
-        <v>448</v>
+        <v>480</v>
       </c>
       <c r="H119" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
     </row>
     <row r="120" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A120" t="s">
-        <v>82</v>
+        <v>482</v>
       </c>
       <c r="C120" t="s">
-        <v>63</v>
+        <v>17</v>
       </c>
       <c r="D120" t="s">
-        <v>83</v>
+        <v>477</v>
       </c>
       <c r="E120" t="s">
-        <v>84</v>
+        <v>478</v>
       </c>
       <c r="F120" t="s">
-        <v>85</v>
+        <v>479</v>
       </c>
       <c r="G120" t="s">
-        <v>86</v>
+        <v>480</v>
       </c>
       <c r="H120" t="s">
-        <v>23</v>
+        <v>11</v>
       </c>
     </row>
     <row r="121" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A121" t="s">
-        <v>449</v>
+        <v>483</v>
       </c>
       <c r="C121" t="s">
-        <v>48</v>
+        <v>25</v>
       </c>
       <c r="D121" t="s">
-        <v>450</v>
+        <v>484</v>
       </c>
       <c r="E121" t="s">
-        <v>317</v>
+        <v>170</v>
       </c>
       <c r="F121" t="s">
         <v>7</v>
       </c>
       <c r="G121" t="s">
-        <v>451</v>
+        <v>485</v>
       </c>
       <c r="H121" t="s">
-        <v>87</v>
+        <v>11</v>
       </c>
     </row>
     <row r="122" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A122" t="s">
-        <v>452</v>
+        <v>486</v>
       </c>
       <c r="C122" t="s">
-        <v>48</v>
+        <v>18</v>
       </c>
       <c r="D122" t="s">
-        <v>450</v>
+        <v>487</v>
       </c>
       <c r="E122" t="s">
-        <v>317</v>
+        <v>14</v>
       </c>
       <c r="F122" t="s">
-        <v>7</v>
+        <v>15</v>
       </c>
       <c r="G122" t="s">
-        <v>451</v>
+        <v>488</v>
       </c>
       <c r="H122" t="s">
-        <v>87</v>
+        <v>11</v>
       </c>
     </row>
     <row r="123" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A123" t="s">
-        <v>453</v>
+        <v>489</v>
       </c>
       <c r="C123" t="s">
+        <v>72</v>
+      </c>
+      <c r="D123" t="s">
+        <v>490</v>
+      </c>
+      <c r="E123" t="s">
+        <v>491</v>
+      </c>
+      <c r="F123" t="s">
+        <v>7</v>
+      </c>
+      <c r="G123" t="s">
+        <v>492</v>
+      </c>
+      <c r="H123" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="124" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A124" t="s">
+        <v>493</v>
+      </c>
+      <c r="C124" t="s">
+        <v>17</v>
+      </c>
+      <c r="D124" t="s">
+        <v>494</v>
+      </c>
+      <c r="E124" t="s">
+        <v>495</v>
+      </c>
+      <c r="F124" t="s">
+        <v>496</v>
+      </c>
+      <c r="G124" t="s">
+        <v>89</v>
+      </c>
+      <c r="H124" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="125" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A125" t="s">
+        <v>497</v>
+      </c>
+      <c r="C125" t="s">
+        <v>17</v>
+      </c>
+      <c r="D125" t="s">
+        <v>498</v>
+      </c>
+      <c r="E125" t="s">
+        <v>499</v>
+      </c>
+      <c r="F125" t="s">
+        <v>500</v>
+      </c>
+      <c r="G125" t="s">
+        <v>501</v>
+      </c>
+      <c r="H125" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="126" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A126" t="s">
+        <v>502</v>
+      </c>
+      <c r="C126" t="s">
+        <v>17</v>
+      </c>
+      <c r="D126" t="s">
+        <v>498</v>
+      </c>
+      <c r="E126" t="s">
+        <v>499</v>
+      </c>
+      <c r="F126" t="s">
+        <v>500</v>
+      </c>
+      <c r="G126" t="s">
+        <v>501</v>
+      </c>
+      <c r="H126" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="127" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A127" t="s">
+        <v>503</v>
+      </c>
+      <c r="C127" t="s">
+        <v>19</v>
+      </c>
+      <c r="D127" t="s">
+        <v>504</v>
+      </c>
+      <c r="E127" t="s">
+        <v>505</v>
+      </c>
+      <c r="F127" t="s">
+        <v>7</v>
+      </c>
+      <c r="G127" t="s">
+        <v>506</v>
+      </c>
+      <c r="H127" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="128" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A128" t="s">
+        <v>507</v>
+      </c>
+      <c r="C128" t="s">
+        <v>394</v>
+      </c>
+      <c r="D128" t="s">
+        <v>508</v>
+      </c>
+      <c r="E128" t="s">
+        <v>36</v>
+      </c>
+      <c r="F128" t="s">
+        <v>7</v>
+      </c>
+      <c r="G128" t="s">
+        <v>509</v>
+      </c>
+      <c r="H128" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="129" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A129" t="s">
+        <v>510</v>
+      </c>
+      <c r="C129" t="s">
+        <v>72</v>
+      </c>
+      <c r="D129" t="s">
+        <v>511</v>
+      </c>
+      <c r="E129" t="s">
+        <v>512</v>
+      </c>
+      <c r="F129" t="s">
+        <v>513</v>
+      </c>
+      <c r="G129" t="s">
+        <v>514</v>
+      </c>
+      <c r="H129" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="130" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A130" t="s">
+        <v>515</v>
+      </c>
+      <c r="C130" t="s">
+        <v>17</v>
+      </c>
+      <c r="D130" t="s">
+        <v>516</v>
+      </c>
+      <c r="E130" t="s">
+        <v>517</v>
+      </c>
+      <c r="F130" t="s">
+        <v>518</v>
+      </c>
+      <c r="G130" t="s">
+        <v>519</v>
+      </c>
+      <c r="H130" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="131" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A131" t="s">
+        <v>520</v>
+      </c>
+      <c r="C131" t="s">
+        <v>20</v>
+      </c>
+      <c r="D131" t="s">
+        <v>521</v>
+      </c>
+      <c r="E131" t="s">
+        <v>522</v>
+      </c>
+      <c r="F131" t="s">
+        <v>7</v>
+      </c>
+      <c r="G131" t="s">
+        <v>523</v>
+      </c>
+      <c r="H131" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="132" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A132" t="s">
+        <v>524</v>
+      </c>
+      <c r="C132" t="s">
+        <v>409</v>
+      </c>
+      <c r="D132" t="s">
+        <v>525</v>
+      </c>
+      <c r="E132" t="s">
+        <v>526</v>
+      </c>
+      <c r="F132" t="s">
+        <v>7</v>
+      </c>
+      <c r="G132" t="s">
+        <v>527</v>
+      </c>
+      <c r="H132" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="133" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A133" t="s">
+        <v>528</v>
+      </c>
+      <c r="C133" t="s">
+        <v>394</v>
+      </c>
+      <c r="D133" t="s">
+        <v>529</v>
+      </c>
+      <c r="E133" t="s">
+        <v>396</v>
+      </c>
+      <c r="F133" t="s">
+        <v>7</v>
+      </c>
+      <c r="G133" t="s">
+        <v>530</v>
+      </c>
+      <c r="H133" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="134" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A134" t="s">
+        <v>531</v>
+      </c>
+      <c r="C134" t="s">
+        <v>20</v>
+      </c>
+      <c r="D134" t="s">
+        <v>532</v>
+      </c>
+      <c r="E134" t="s">
+        <v>49</v>
+      </c>
+      <c r="F134" t="s">
+        <v>7</v>
+      </c>
+      <c r="G134" t="s">
+        <v>533</v>
+      </c>
+      <c r="H134" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="135" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A135" t="s">
+        <v>534</v>
+      </c>
+      <c r="C135" t="s">
+        <v>409</v>
+      </c>
+      <c r="D135" t="s">
+        <v>535</v>
+      </c>
+      <c r="E135" t="s">
+        <v>536</v>
+      </c>
+      <c r="F135" t="s">
+        <v>7</v>
+      </c>
+      <c r="G135" t="s">
+        <v>537</v>
+      </c>
+      <c r="H135" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="136" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A136" t="s">
+        <v>538</v>
+      </c>
+      <c r="C136" t="s">
+        <v>50</v>
+      </c>
+      <c r="D136" t="s">
+        <v>539</v>
+      </c>
+      <c r="E136" t="s">
+        <v>540</v>
+      </c>
+      <c r="F136" t="s">
+        <v>541</v>
+      </c>
+      <c r="G136" t="s">
+        <v>96</v>
+      </c>
+      <c r="H136" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="137" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A137" t="s">
+        <v>542</v>
+      </c>
+      <c r="C137" t="s">
+        <v>72</v>
+      </c>
+      <c r="D137" t="s">
+        <v>543</v>
+      </c>
+      <c r="E137" t="s">
+        <v>73</v>
+      </c>
+      <c r="F137" t="s">
+        <v>7</v>
+      </c>
+      <c r="G137" t="s">
+        <v>544</v>
+      </c>
+      <c r="H137" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="138" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A138" t="s">
+        <v>545</v>
+      </c>
+      <c r="C138" t="s">
+        <v>136</v>
+      </c>
+      <c r="D138" t="s">
+        <v>546</v>
+      </c>
+      <c r="E138" t="s">
+        <v>57</v>
+      </c>
+      <c r="F138" t="s">
+        <v>58</v>
+      </c>
+      <c r="G138" t="s">
+        <v>547</v>
+      </c>
+      <c r="H138" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="139" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A139" t="s">
+        <v>548</v>
+      </c>
+      <c r="C139" t="s">
+        <v>13</v>
+      </c>
+      <c r="D139" t="s">
+        <v>549</v>
+      </c>
+      <c r="E139" t="s">
+        <v>550</v>
+      </c>
+      <c r="F139" t="s">
+        <v>7</v>
+      </c>
+      <c r="G139" t="s">
+        <v>551</v>
+      </c>
+      <c r="H139" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="140" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A140" t="s">
+        <v>552</v>
+      </c>
+      <c r="C140" t="s">
+        <v>17</v>
+      </c>
+      <c r="D140" t="s">
+        <v>553</v>
+      </c>
+      <c r="E140" t="s">
+        <v>60</v>
+      </c>
+      <c r="F140" t="s">
+        <v>61</v>
+      </c>
+      <c r="G140" t="s">
+        <v>554</v>
+      </c>
+      <c r="H140" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="141" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A141" t="s">
+        <v>555</v>
+      </c>
+      <c r="C141" t="s">
+        <v>33</v>
+      </c>
+      <c r="D141" t="s">
+        <v>556</v>
+      </c>
+      <c r="E141" t="s">
+        <v>37</v>
+      </c>
+      <c r="F141" t="s">
+        <v>38</v>
+      </c>
+      <c r="G141" t="s">
+        <v>557</v>
+      </c>
+      <c r="H141" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="142" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A142" t="s">
+        <v>558</v>
+      </c>
+      <c r="C142" t="s">
+        <v>50</v>
+      </c>
+      <c r="D142" t="s">
+        <v>559</v>
+      </c>
+      <c r="E142" t="s">
+        <v>78</v>
+      </c>
+      <c r="F142" t="s">
+        <v>79</v>
+      </c>
+      <c r="G142" t="s">
+        <v>560</v>
+      </c>
+      <c r="H142" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="143" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A143" t="s">
+        <v>561</v>
+      </c>
+      <c r="C143" t="s">
+        <v>136</v>
+      </c>
+      <c r="D143" t="s">
+        <v>562</v>
+      </c>
+      <c r="E143" t="s">
+        <v>354</v>
+      </c>
+      <c r="F143" t="s">
+        <v>355</v>
+      </c>
+      <c r="G143" t="s">
+        <v>563</v>
+      </c>
+      <c r="H143" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="144" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A144" t="s">
+        <v>564</v>
+      </c>
+      <c r="C144" t="s">
+        <v>136</v>
+      </c>
+      <c r="D144" t="s">
+        <v>565</v>
+      </c>
+      <c r="E144" t="s">
+        <v>57</v>
+      </c>
+      <c r="F144" t="s">
+        <v>58</v>
+      </c>
+      <c r="G144" t="s">
+        <v>88</v>
+      </c>
+      <c r="H144" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="145" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A145" t="s">
+        <v>566</v>
+      </c>
+      <c r="C145" t="s">
+        <v>19</v>
+      </c>
+      <c r="D145" t="s">
+        <v>567</v>
+      </c>
+      <c r="E145" t="s">
+        <v>568</v>
+      </c>
+      <c r="F145" t="s">
+        <v>7</v>
+      </c>
+      <c r="G145" t="s">
+        <v>569</v>
+      </c>
+      <c r="H145" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="146" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A146" t="s">
+        <v>570</v>
+      </c>
+      <c r="C146" t="s">
+        <v>17</v>
+      </c>
+      <c r="D146" t="s">
+        <v>571</v>
+      </c>
+      <c r="E146" t="s">
+        <v>572</v>
+      </c>
+      <c r="F146" t="s">
+        <v>573</v>
+      </c>
+      <c r="G146" t="s">
+        <v>574</v>
+      </c>
+      <c r="H146" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="147" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A147" t="s">
+        <v>575</v>
+      </c>
+      <c r="C147" t="s">
+        <v>16</v>
+      </c>
+      <c r="D147" t="s">
+        <v>576</v>
+      </c>
+      <c r="E147" t="s">
+        <v>577</v>
+      </c>
+      <c r="F147" t="s">
+        <v>7</v>
+      </c>
+      <c r="G147" t="s">
+        <v>578</v>
+      </c>
+      <c r="H147" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="148" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A148" t="s">
+        <v>579</v>
+      </c>
+      <c r="C148" t="s">
         <v>22</v>
       </c>
-      <c r="D123" t="s">
-        <v>453</v>
-      </c>
-      <c r="H123" t="s">
-        <v>454</v>
+      <c r="D148" t="s">
+        <v>580</v>
+      </c>
+      <c r="E148" t="s">
+        <v>581</v>
+      </c>
+      <c r="F148" t="s">
+        <v>7</v>
+      </c>
+      <c r="G148" t="s">
+        <v>582</v>
+      </c>
+      <c r="H148" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="149" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A149" t="s">
+        <v>583</v>
+      </c>
+      <c r="C149" t="s">
+        <v>394</v>
+      </c>
+      <c r="D149" t="s">
+        <v>584</v>
+      </c>
+      <c r="E149" t="s">
+        <v>585</v>
+      </c>
+      <c r="F149" t="s">
+        <v>7</v>
+      </c>
+      <c r="G149" t="s">
+        <v>586</v>
+      </c>
+      <c r="H149" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="150" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A150" t="s">
+        <v>587</v>
+      </c>
+      <c r="C150" t="s">
+        <v>33</v>
+      </c>
+      <c r="D150" t="s">
+        <v>588</v>
+      </c>
+      <c r="E150" t="s">
+        <v>589</v>
+      </c>
+      <c r="F150" t="s">
+        <v>7</v>
+      </c>
+      <c r="G150" t="s">
+        <v>590</v>
+      </c>
+      <c r="H150" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="151" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A151" t="s">
+        <v>591</v>
+      </c>
+      <c r="C151" t="s">
+        <v>33</v>
+      </c>
+      <c r="D151" t="s">
+        <v>588</v>
+      </c>
+      <c r="E151" t="s">
+        <v>589</v>
+      </c>
+      <c r="F151" t="s">
+        <v>7</v>
+      </c>
+      <c r="G151" t="s">
+        <v>590</v>
+      </c>
+      <c r="H151" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="152" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A152" t="s">
+        <v>592</v>
+      </c>
+      <c r="C152" t="s">
+        <v>23</v>
+      </c>
+      <c r="D152" t="s">
+        <v>593</v>
+      </c>
+      <c r="E152" t="s">
+        <v>594</v>
+      </c>
+      <c r="F152" t="s">
+        <v>7</v>
+      </c>
+      <c r="G152" t="s">
+        <v>229</v>
+      </c>
+      <c r="H152" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="153" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A153" t="s">
+        <v>595</v>
+      </c>
+      <c r="C153" t="s">
+        <v>72</v>
+      </c>
+      <c r="D153" t="s">
+        <v>596</v>
+      </c>
+      <c r="E153" t="s">
+        <v>597</v>
+      </c>
+      <c r="F153" t="s">
+        <v>7</v>
+      </c>
+      <c r="G153" t="s">
+        <v>598</v>
+      </c>
+      <c r="H153" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="154" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A154" t="s">
+        <v>599</v>
+      </c>
+      <c r="C154" t="s">
+        <v>64</v>
+      </c>
+      <c r="D154" t="s">
+        <v>600</v>
+      </c>
+      <c r="E154" t="s">
+        <v>204</v>
+      </c>
+      <c r="F154" t="s">
+        <v>7</v>
+      </c>
+      <c r="G154" t="s">
+        <v>601</v>
+      </c>
+      <c r="H154" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="155" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A155" t="s">
+        <v>602</v>
+      </c>
+      <c r="C155" t="s">
+        <v>25</v>
+      </c>
+      <c r="D155" t="s">
+        <v>603</v>
+      </c>
+      <c r="E155" t="s">
+        <v>170</v>
+      </c>
+      <c r="F155" t="s">
+        <v>7</v>
+      </c>
+      <c r="G155" t="s">
+        <v>604</v>
+      </c>
+      <c r="H155" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="156" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A156" t="s">
+        <v>605</v>
+      </c>
+      <c r="C156" t="s">
+        <v>25</v>
+      </c>
+      <c r="D156" t="s">
+        <v>603</v>
+      </c>
+      <c r="E156" t="s">
+        <v>170</v>
+      </c>
+      <c r="F156" t="s">
+        <v>7</v>
+      </c>
+      <c r="G156" t="s">
+        <v>604</v>
+      </c>
+      <c r="H156" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="157" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A157" t="s">
+        <v>606</v>
+      </c>
+      <c r="C157" t="s">
+        <v>18</v>
+      </c>
+      <c r="D157" t="s">
+        <v>607</v>
+      </c>
+      <c r="E157" t="s">
+        <v>14</v>
+      </c>
+      <c r="F157" t="s">
+        <v>15</v>
+      </c>
+      <c r="G157" t="s">
+        <v>608</v>
+      </c>
+      <c r="H157" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="158" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A158" t="s">
+        <v>609</v>
+      </c>
+      <c r="C158" t="s">
+        <v>18</v>
+      </c>
+      <c r="D158" t="s">
+        <v>610</v>
+      </c>
+      <c r="E158" t="s">
+        <v>14</v>
+      </c>
+      <c r="F158" t="s">
+        <v>15</v>
+      </c>
+      <c r="G158" t="s">
+        <v>611</v>
+      </c>
+      <c r="H158" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="159" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A159" t="s">
+        <v>612</v>
+      </c>
+      <c r="C159" t="s">
+        <v>409</v>
+      </c>
+      <c r="D159" t="s">
+        <v>613</v>
+      </c>
+      <c r="E159" t="s">
+        <v>526</v>
+      </c>
+      <c r="F159" t="s">
+        <v>7</v>
+      </c>
+      <c r="G159" t="s">
+        <v>614</v>
+      </c>
+      <c r="H159" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="160" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A160" t="s">
+        <v>615</v>
+      </c>
+      <c r="C160" t="s">
+        <v>18</v>
+      </c>
+      <c r="D160" t="s">
+        <v>616</v>
+      </c>
+      <c r="E160" t="s">
+        <v>327</v>
+      </c>
+      <c r="F160" t="s">
+        <v>7</v>
+      </c>
+      <c r="G160" t="s">
+        <v>617</v>
+      </c>
+      <c r="H160" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="161" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A161" t="s">
+        <v>618</v>
+      </c>
+      <c r="C161" t="s">
+        <v>50</v>
+      </c>
+      <c r="D161" t="s">
+        <v>619</v>
+      </c>
+      <c r="E161" t="s">
+        <v>620</v>
+      </c>
+      <c r="F161" t="s">
+        <v>621</v>
+      </c>
+      <c r="G161" t="s">
+        <v>622</v>
+      </c>
+      <c r="H161" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="162" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A162" t="s">
+        <v>623</v>
+      </c>
+      <c r="C162" t="s">
+        <v>136</v>
+      </c>
+      <c r="D162" t="s">
+        <v>624</v>
+      </c>
+      <c r="E162" t="s">
+        <v>30</v>
+      </c>
+      <c r="F162" t="s">
+        <v>31</v>
+      </c>
+      <c r="G162" t="s">
+        <v>625</v>
+      </c>
+      <c r="H162" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="163" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A163" t="s">
+        <v>626</v>
+      </c>
+      <c r="C163" t="s">
+        <v>13</v>
+      </c>
+      <c r="D163" t="s">
+        <v>627</v>
+      </c>
+      <c r="E163" t="s">
+        <v>628</v>
+      </c>
+      <c r="F163" t="s">
+        <v>629</v>
+      </c>
+      <c r="G163" t="s">
+        <v>96</v>
+      </c>
+      <c r="H163" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="164" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A164" t="s">
+        <v>630</v>
+      </c>
+      <c r="C164" t="s">
+        <v>50</v>
+      </c>
+      <c r="D164" t="s">
+        <v>631</v>
+      </c>
+      <c r="E164" t="s">
+        <v>632</v>
+      </c>
+      <c r="F164" t="s">
+        <v>633</v>
+      </c>
+      <c r="G164" t="s">
+        <v>378</v>
+      </c>
+      <c r="H164" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="165" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A165" t="s">
+        <v>634</v>
+      </c>
+      <c r="C165" t="s">
+        <v>18</v>
+      </c>
+      <c r="D165" t="s">
+        <v>635</v>
+      </c>
+      <c r="E165" t="s">
+        <v>327</v>
+      </c>
+      <c r="F165" t="s">
+        <v>7</v>
+      </c>
+      <c r="G165" t="s">
+        <v>636</v>
+      </c>
+      <c r="H165" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="166" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A166" t="s">
+        <v>637</v>
+      </c>
+      <c r="C166" t="s">
+        <v>148</v>
+      </c>
+      <c r="D166" t="s">
+        <v>638</v>
+      </c>
+      <c r="E166" t="s">
+        <v>277</v>
+      </c>
+      <c r="F166" t="s">
+        <v>7</v>
+      </c>
+      <c r="G166" t="s">
+        <v>639</v>
+      </c>
+      <c r="H166" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="167" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A167" t="s">
+        <v>640</v>
+      </c>
+      <c r="C167" t="s">
+        <v>136</v>
+      </c>
+      <c r="D167" t="s">
+        <v>641</v>
+      </c>
+      <c r="E167" t="s">
+        <v>354</v>
+      </c>
+      <c r="F167" t="s">
+        <v>355</v>
+      </c>
+      <c r="G167" t="s">
+        <v>488</v>
+      </c>
+      <c r="H167" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="168" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A168" t="s">
+        <v>642</v>
+      </c>
+      <c r="C168" t="s">
+        <v>25</v>
+      </c>
+      <c r="D168" t="s">
+        <v>643</v>
+      </c>
+      <c r="E168" t="s">
+        <v>170</v>
+      </c>
+      <c r="F168" t="s">
+        <v>7</v>
+      </c>
+      <c r="G168" t="s">
+        <v>644</v>
+      </c>
+      <c r="H168" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="169" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A169" t="s">
+        <v>645</v>
+      </c>
+      <c r="C169" t="s">
+        <v>25</v>
+      </c>
+      <c r="D169" t="s">
+        <v>643</v>
+      </c>
+      <c r="E169" t="s">
+        <v>170</v>
+      </c>
+      <c r="F169" t="s">
+        <v>7</v>
+      </c>
+      <c r="G169" t="s">
+        <v>644</v>
+      </c>
+      <c r="H169" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="170" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A170" t="s">
+        <v>646</v>
+      </c>
+      <c r="C170" t="s">
+        <v>136</v>
+      </c>
+      <c r="D170" t="s">
+        <v>647</v>
+      </c>
+      <c r="E170" t="s">
+        <v>648</v>
+      </c>
+      <c r="F170" t="s">
+        <v>649</v>
+      </c>
+      <c r="G170" t="s">
+        <v>650</v>
+      </c>
+      <c r="H170" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="171" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A171" t="s">
+        <v>651</v>
+      </c>
+      <c r="C171" t="s">
+        <v>13</v>
+      </c>
+      <c r="D171" t="s">
+        <v>652</v>
+      </c>
+      <c r="E171" t="s">
+        <v>36</v>
+      </c>
+      <c r="F171" t="s">
+        <v>7</v>
+      </c>
+      <c r="G171" t="s">
+        <v>95</v>
+      </c>
+      <c r="H171" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="172" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A172" t="s">
+        <v>653</v>
+      </c>
+      <c r="C172" t="s">
+        <v>43</v>
+      </c>
+      <c r="D172" t="s">
+        <v>654</v>
+      </c>
+      <c r="E172" t="s">
+        <v>28</v>
+      </c>
+      <c r="F172" t="s">
+        <v>7</v>
+      </c>
+      <c r="G172" t="s">
+        <v>655</v>
+      </c>
+      <c r="H172" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="173" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A173" t="s">
+        <v>656</v>
+      </c>
+      <c r="C173" t="s">
+        <v>64</v>
+      </c>
+      <c r="D173" t="s">
+        <v>657</v>
+      </c>
+      <c r="E173" t="s">
+        <v>658</v>
+      </c>
+      <c r="F173" t="s">
+        <v>7</v>
+      </c>
+      <c r="G173" t="s">
+        <v>659</v>
+      </c>
+      <c r="H173" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="174" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A174" t="s">
+        <v>660</v>
+      </c>
+      <c r="C174" t="s">
+        <v>148</v>
+      </c>
+      <c r="D174" t="s">
+        <v>661</v>
+      </c>
+      <c r="E174" t="s">
+        <v>662</v>
+      </c>
+      <c r="F174" t="s">
+        <v>663</v>
+      </c>
+      <c r="G174" t="s">
+        <v>664</v>
+      </c>
+      <c r="H174" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="175" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A175" t="s">
+        <v>665</v>
+      </c>
+      <c r="C175" t="s">
+        <v>148</v>
+      </c>
+      <c r="D175" t="s">
+        <v>661</v>
+      </c>
+      <c r="E175" t="s">
+        <v>662</v>
+      </c>
+      <c r="F175" t="s">
+        <v>663</v>
+      </c>
+      <c r="G175" t="s">
+        <v>664</v>
+      </c>
+      <c r="H175" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="176" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A176" t="s">
+        <v>666</v>
+      </c>
+      <c r="C176" t="s">
+        <v>43</v>
+      </c>
+      <c r="D176" t="s">
+        <v>667</v>
+      </c>
+      <c r="E176" t="s">
+        <v>668</v>
+      </c>
+      <c r="F176" t="s">
+        <v>368</v>
+      </c>
+      <c r="G176" t="s">
+        <v>669</v>
+      </c>
+      <c r="H176" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="177" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A177" t="s">
+        <v>670</v>
+      </c>
+      <c r="C177" t="s">
+        <v>72</v>
+      </c>
+      <c r="D177" t="s">
+        <v>671</v>
+      </c>
+      <c r="E177" t="s">
+        <v>672</v>
+      </c>
+      <c r="F177" t="s">
+        <v>7</v>
+      </c>
+      <c r="G177" t="s">
+        <v>87</v>
+      </c>
+      <c r="H177" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="178" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A178" t="s">
+        <v>673</v>
+      </c>
+      <c r="C178" t="s">
+        <v>43</v>
+      </c>
+      <c r="D178" t="s">
+        <v>674</v>
+      </c>
+      <c r="E178" t="s">
+        <v>65</v>
+      </c>
+      <c r="F178" t="s">
+        <v>66</v>
+      </c>
+      <c r="G178" t="s">
+        <v>67</v>
+      </c>
+      <c r="H178" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="179" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A179" t="s">
+        <v>675</v>
+      </c>
+      <c r="C179" t="s">
+        <v>43</v>
+      </c>
+      <c r="D179" t="s">
+        <v>674</v>
+      </c>
+      <c r="E179" t="s">
+        <v>65</v>
+      </c>
+      <c r="F179" t="s">
+        <v>66</v>
+      </c>
+      <c r="G179" t="s">
+        <v>67</v>
+      </c>
+      <c r="H179" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="180" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A180" t="s">
+        <v>676</v>
+      </c>
+      <c r="C180" t="s">
+        <v>39</v>
+      </c>
+      <c r="D180" t="s">
+        <v>677</v>
+      </c>
+      <c r="E180" t="s">
+        <v>678</v>
+      </c>
+      <c r="F180" t="s">
+        <v>7</v>
+      </c>
+      <c r="G180" t="s">
+        <v>679</v>
+      </c>
+      <c r="H180" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="181" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A181" t="s">
+        <v>680</v>
+      </c>
+      <c r="C181" t="s">
+        <v>17</v>
+      </c>
+      <c r="D181" t="s">
+        <v>681</v>
+      </c>
+      <c r="E181" t="s">
+        <v>60</v>
+      </c>
+      <c r="F181" t="s">
+        <v>61</v>
+      </c>
+      <c r="G181" t="s">
+        <v>682</v>
+      </c>
+      <c r="H181" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="182" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A182" t="s">
+        <v>683</v>
+      </c>
+      <c r="C182" t="s">
+        <v>17</v>
+      </c>
+      <c r="D182" t="s">
+        <v>681</v>
+      </c>
+      <c r="E182" t="s">
+        <v>60</v>
+      </c>
+      <c r="F182" t="s">
+        <v>61</v>
+      </c>
+      <c r="G182" t="s">
+        <v>682</v>
+      </c>
+      <c r="H182" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="183" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A183" t="s">
+        <v>684</v>
+      </c>
+      <c r="C183" t="s">
+        <v>136</v>
+      </c>
+      <c r="D183" t="s">
+        <v>685</v>
+      </c>
+      <c r="E183" t="s">
+        <v>686</v>
+      </c>
+      <c r="F183" t="s">
+        <v>687</v>
+      </c>
+      <c r="G183" t="s">
+        <v>682</v>
+      </c>
+      <c r="H183" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="184" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A184" t="s">
+        <v>688</v>
+      </c>
+      <c r="C184" t="s">
+        <v>136</v>
+      </c>
+      <c r="D184" t="s">
+        <v>685</v>
+      </c>
+      <c r="E184" t="s">
+        <v>686</v>
+      </c>
+      <c r="F184" t="s">
+        <v>687</v>
+      </c>
+      <c r="G184" t="s">
+        <v>682</v>
+      </c>
+      <c r="H184" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="185" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A185" t="s">
+        <v>689</v>
+      </c>
+      <c r="C185" t="s">
+        <v>9</v>
+      </c>
+      <c r="D185" t="s">
+        <v>690</v>
+      </c>
+      <c r="E185" t="s">
+        <v>69</v>
+      </c>
+      <c r="F185" t="s">
+        <v>70</v>
+      </c>
+      <c r="G185" t="s">
+        <v>691</v>
+      </c>
+      <c r="H185" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="186" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A186" t="s">
+        <v>692</v>
+      </c>
+      <c r="C186" t="s">
+        <v>9</v>
+      </c>
+      <c r="D186" t="s">
+        <v>690</v>
+      </c>
+      <c r="E186" t="s">
+        <v>69</v>
+      </c>
+      <c r="F186" t="s">
+        <v>70</v>
+      </c>
+      <c r="G186" t="s">
+        <v>691</v>
+      </c>
+      <c r="H186" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="187" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A187" t="s">
+        <v>693</v>
+      </c>
+      <c r="C187" t="s">
+        <v>50</v>
+      </c>
+      <c r="D187" t="s">
+        <v>694</v>
+      </c>
+      <c r="E187" t="s">
+        <v>47</v>
+      </c>
+      <c r="F187" t="s">
+        <v>48</v>
+      </c>
+      <c r="G187" t="s">
+        <v>695</v>
+      </c>
+      <c r="H187" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="188" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A188" t="s">
+        <v>696</v>
+      </c>
+      <c r="C188" t="s">
+        <v>23</v>
+      </c>
+      <c r="D188" t="s">
+        <v>697</v>
+      </c>
+      <c r="E188" t="s">
+        <v>698</v>
+      </c>
+      <c r="F188" t="s">
+        <v>699</v>
+      </c>
+      <c r="G188" t="s">
+        <v>700</v>
+      </c>
+      <c r="H188" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="189" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A189" t="s">
+        <v>701</v>
+      </c>
+      <c r="C189" t="s">
+        <v>20</v>
+      </c>
+      <c r="D189" t="s">
+        <v>702</v>
+      </c>
+      <c r="E189" t="s">
+        <v>45</v>
+      </c>
+      <c r="F189" t="s">
+        <v>46</v>
+      </c>
+      <c r="G189" t="s">
+        <v>703</v>
+      </c>
+      <c r="H189" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="190" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A190" t="s">
+        <v>704</v>
+      </c>
+      <c r="C190" t="s">
+        <v>33</v>
+      </c>
+      <c r="D190" t="s">
+        <v>705</v>
+      </c>
+      <c r="E190" t="s">
+        <v>37</v>
+      </c>
+      <c r="F190" t="s">
+        <v>38</v>
+      </c>
+      <c r="G190" t="s">
+        <v>560</v>
+      </c>
+      <c r="H190" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="191" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A191" t="s">
+        <v>706</v>
+      </c>
+      <c r="C191" t="s">
+        <v>33</v>
+      </c>
+      <c r="D191" t="s">
+        <v>705</v>
+      </c>
+      <c r="E191" t="s">
+        <v>37</v>
+      </c>
+      <c r="F191" t="s">
+        <v>38</v>
+      </c>
+      <c r="G191" t="s">
+        <v>560</v>
+      </c>
+      <c r="H191" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="192" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A192" t="s">
+        <v>707</v>
+      </c>
+      <c r="C192" t="s">
+        <v>24</v>
+      </c>
+      <c r="D192" t="s">
+        <v>708</v>
+      </c>
+      <c r="E192" t="s">
+        <v>68</v>
+      </c>
+      <c r="F192" t="s">
+        <v>7</v>
+      </c>
+      <c r="G192" t="s">
+        <v>709</v>
+      </c>
+      <c r="H192" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="193" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A193" t="s">
+        <v>710</v>
+      </c>
+      <c r="C193" t="s">
+        <v>50</v>
+      </c>
+      <c r="D193" t="s">
+        <v>711</v>
+      </c>
+      <c r="E193" t="s">
+        <v>81</v>
+      </c>
+      <c r="F193" t="s">
+        <v>82</v>
+      </c>
+      <c r="G193" t="s">
+        <v>89</v>
+      </c>
+      <c r="H193" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="194" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A194" t="s">
+        <v>712</v>
+      </c>
+      <c r="C194" t="s">
+        <v>50</v>
+      </c>
+      <c r="D194" t="s">
+        <v>711</v>
+      </c>
+      <c r="E194" t="s">
+        <v>81</v>
+      </c>
+      <c r="F194" t="s">
+        <v>82</v>
+      </c>
+      <c r="G194" t="s">
+        <v>89</v>
+      </c>
+      <c r="H194" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="195" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A195" t="s">
+        <v>713</v>
+      </c>
+      <c r="C195" t="s">
+        <v>50</v>
+      </c>
+      <c r="D195" t="s">
+        <v>711</v>
+      </c>
+      <c r="E195" t="s">
+        <v>81</v>
+      </c>
+      <c r="F195" t="s">
+        <v>82</v>
+      </c>
+      <c r="G195" t="s">
+        <v>89</v>
+      </c>
+      <c r="H195" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="196" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A196" t="s">
+        <v>714</v>
+      </c>
+      <c r="C196" t="s">
+        <v>50</v>
+      </c>
+      <c r="D196" t="s">
+        <v>711</v>
+      </c>
+      <c r="E196" t="s">
+        <v>81</v>
+      </c>
+      <c r="F196" t="s">
+        <v>82</v>
+      </c>
+      <c r="G196" t="s">
+        <v>89</v>
+      </c>
+      <c r="H196" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="197" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A197" t="s">
+        <v>715</v>
+      </c>
+      <c r="C197" t="s">
+        <v>50</v>
+      </c>
+      <c r="D197" t="s">
+        <v>711</v>
+      </c>
+      <c r="E197" t="s">
+        <v>81</v>
+      </c>
+      <c r="F197" t="s">
+        <v>82</v>
+      </c>
+      <c r="G197" t="s">
+        <v>89</v>
+      </c>
+      <c r="H197" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="198" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A198" t="s">
+        <v>716</v>
+      </c>
+      <c r="C198" t="s">
+        <v>50</v>
+      </c>
+      <c r="D198" t="s">
+        <v>711</v>
+      </c>
+      <c r="E198" t="s">
+        <v>81</v>
+      </c>
+      <c r="F198" t="s">
+        <v>82</v>
+      </c>
+      <c r="G198" t="s">
+        <v>89</v>
+      </c>
+      <c r="H198" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="199" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A199" t="s">
+        <v>717</v>
+      </c>
+      <c r="C199" t="s">
+        <v>20</v>
+      </c>
+      <c r="D199" t="s">
+        <v>718</v>
+      </c>
+      <c r="E199" t="s">
+        <v>719</v>
+      </c>
+      <c r="F199" t="s">
+        <v>7</v>
+      </c>
+      <c r="G199" t="s">
+        <v>720</v>
+      </c>
+      <c r="H199" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="200" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A200" t="s">
+        <v>721</v>
+      </c>
+      <c r="C200" t="s">
+        <v>20</v>
+      </c>
+      <c r="D200" t="s">
+        <v>718</v>
+      </c>
+      <c r="E200" t="s">
+        <v>719</v>
+      </c>
+      <c r="F200" t="s">
+        <v>7</v>
+      </c>
+      <c r="G200" t="s">
+        <v>720</v>
+      </c>
+      <c r="H200" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="201" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A201" t="s">
+        <v>722</v>
+      </c>
+      <c r="C201" t="s">
+        <v>72</v>
+      </c>
+      <c r="D201" t="s">
+        <v>723</v>
+      </c>
+      <c r="E201" t="s">
+        <v>724</v>
+      </c>
+      <c r="F201" t="s">
+        <v>725</v>
+      </c>
+      <c r="G201" t="s">
+        <v>726</v>
+      </c>
+      <c r="H201" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="202" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="C202" t="s">
+        <v>409</v>
+      </c>
+      <c r="D202" t="s">
+        <v>727</v>
+      </c>
+      <c r="E202" t="s">
+        <v>526</v>
+      </c>
+      <c r="F202" t="s">
+        <v>7</v>
+      </c>
+      <c r="G202" t="s">
+        <v>728</v>
+      </c>
+      <c r="H202" t="s">
+        <v>32</v>
       </c>
     </row>
   </sheetData>

--- a/1.xlsx
+++ b/1.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="\\wh.local\fs\UserProfile_TSSWH19\_TSSWH19_redirected_folders\HunyaCs1\Desktop\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2BE92842-8654-4110-A006-242C72732005}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{828DC122-A5D5-450A-B6DB-B0D20969BDC7}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="0" windowWidth="22260" windowHeight="12648" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1413" uniqueCount="729">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1408" uniqueCount="727">
   <si>
     <t>IRSZ</t>
   </si>
@@ -315,9 +315,6 @@
     <t>Albert utca</t>
   </si>
   <si>
-    <t>Vízimolnár utca</t>
-  </si>
-  <si>
     <t>Kossuth Lajos út</t>
   </si>
   <si>
@@ -1983,12 +1980,6 @@
     <t>Körtefa utca</t>
   </si>
   <si>
-    <t>NFD6-03-23-JHSK-1</t>
-  </si>
-  <si>
-    <t>NFD6-03-23-JHSK</t>
-  </si>
-  <si>
     <t>202603172600632601</t>
   </si>
   <si>
@@ -2211,10 +2202,13 @@
     <t>Benedek Elek utca</t>
   </si>
   <si>
-    <t>26-00/00211</t>
-  </si>
-  <si>
-    <t>Ecseri Út</t>
+    <t>NFD6-03-19-JZFM</t>
+  </si>
+  <si>
+    <t>AUCHAN_ÁRUHÁZI</t>
+  </si>
+  <si>
+    <t>NFD6-03-18-6Z4W</t>
   </si>
 </sst>
 </file>
@@ -2571,13 +2565,13 @@
     </row>
     <row r="2" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="C2" t="s">
         <v>39</v>
       </c>
       <c r="D2" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="E2" t="s">
         <v>71</v>
@@ -2586,7 +2580,7 @@
         <v>7</v>
       </c>
       <c r="G2" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="H2" t="s">
         <v>8</v>
@@ -2594,13 +2588,13 @@
     </row>
     <row r="3" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="C3" t="s">
         <v>39</v>
       </c>
       <c r="D3" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="E3" t="s">
         <v>53</v>
@@ -2609,7 +2603,7 @@
         <v>7</v>
       </c>
       <c r="G3" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="H3" t="s">
         <v>8</v>
@@ -2617,22 +2611,22 @@
     </row>
     <row r="4" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="C4" t="s">
         <v>86</v>
       </c>
       <c r="D4" t="s">
+        <v>103</v>
+      </c>
+      <c r="E4" t="s">
         <v>104</v>
       </c>
-      <c r="E4" t="s">
+      <c r="F4" t="s">
+        <v>7</v>
+      </c>
+      <c r="G4" t="s">
         <v>105</v>
-      </c>
-      <c r="F4" t="s">
-        <v>7</v>
-      </c>
-      <c r="G4" t="s">
-        <v>106</v>
       </c>
       <c r="H4" t="s">
         <v>8</v>
@@ -2640,13 +2634,13 @@
     </row>
     <row r="5" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="C5" t="s">
         <v>50</v>
       </c>
       <c r="D5" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="E5" t="s">
         <v>81</v>
@@ -2663,22 +2657,22 @@
     </row>
     <row r="6" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="C6" t="s">
         <v>13</v>
       </c>
       <c r="D6" t="s">
+        <v>109</v>
+      </c>
+      <c r="E6" t="s">
         <v>110</v>
       </c>
-      <c r="E6" t="s">
+      <c r="F6" t="s">
+        <v>7</v>
+      </c>
+      <c r="G6" t="s">
         <v>111</v>
-      </c>
-      <c r="F6" t="s">
-        <v>7</v>
-      </c>
-      <c r="G6" t="s">
-        <v>112</v>
       </c>
       <c r="H6" t="s">
         <v>8</v>
@@ -2686,13 +2680,13 @@
     </row>
     <row r="7" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="C7" t="s">
         <v>25</v>
       </c>
       <c r="D7" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="E7" t="s">
         <v>52</v>
@@ -2701,7 +2695,7 @@
         <v>7</v>
       </c>
       <c r="G7" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="H7" t="s">
         <v>8</v>
@@ -2709,13 +2703,13 @@
     </row>
     <row r="8" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="C8" t="s">
         <v>13</v>
       </c>
       <c r="D8" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="E8" t="s">
         <v>62</v>
@@ -2724,7 +2718,7 @@
         <v>63</v>
       </c>
       <c r="G8" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="H8" t="s">
         <v>8</v>
@@ -2732,13 +2726,13 @@
     </row>
     <row r="9" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="C9" t="s">
         <v>24</v>
       </c>
       <c r="D9" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="E9" t="s">
         <v>83</v>
@@ -2747,7 +2741,7 @@
         <v>7</v>
       </c>
       <c r="G9" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="H9" t="s">
         <v>8</v>
@@ -2755,22 +2749,22 @@
     </row>
     <row r="10" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="C10" t="s">
         <v>24</v>
       </c>
       <c r="D10" t="s">
+        <v>122</v>
+      </c>
+      <c r="E10" t="s">
         <v>123</v>
       </c>
-      <c r="E10" t="s">
+      <c r="F10" t="s">
+        <v>7</v>
+      </c>
+      <c r="G10" t="s">
         <v>124</v>
-      </c>
-      <c r="F10" t="s">
-        <v>7</v>
-      </c>
-      <c r="G10" t="s">
-        <v>125</v>
       </c>
       <c r="H10" t="s">
         <v>8</v>
@@ -2778,13 +2772,13 @@
     </row>
     <row r="11" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A11" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="C11" t="s">
         <v>25</v>
       </c>
       <c r="D11" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="E11" t="s">
         <v>52</v>
@@ -2793,7 +2787,7 @@
         <v>7</v>
       </c>
       <c r="G11" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="H11" t="s">
         <v>8</v>
@@ -2801,13 +2795,13 @@
     </row>
     <row r="12" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A12" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="C12" t="s">
         <v>25</v>
       </c>
       <c r="D12" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="E12" t="s">
         <v>52</v>
@@ -2816,7 +2810,7 @@
         <v>7</v>
       </c>
       <c r="G12" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="H12" t="s">
         <v>8</v>
@@ -2824,22 +2818,22 @@
     </row>
     <row r="13" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A13" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="C13" t="s">
         <v>9</v>
       </c>
       <c r="D13" t="s">
+        <v>130</v>
+      </c>
+      <c r="E13" t="s">
         <v>131</v>
       </c>
-      <c r="E13" t="s">
+      <c r="F13" t="s">
         <v>132</v>
       </c>
-      <c r="F13" t="s">
+      <c r="G13" t="s">
         <v>133</v>
-      </c>
-      <c r="G13" t="s">
-        <v>134</v>
       </c>
       <c r="H13" t="s">
         <v>8</v>
@@ -2847,22 +2841,22 @@
     </row>
     <row r="14" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A14" t="s">
+        <v>134</v>
+      </c>
+      <c r="C14" t="s">
         <v>135</v>
       </c>
-      <c r="C14" t="s">
+      <c r="D14" t="s">
         <v>136</v>
       </c>
-      <c r="D14" t="s">
+      <c r="E14" t="s">
         <v>137</v>
       </c>
-      <c r="E14" t="s">
+      <c r="F14" t="s">
         <v>138</v>
       </c>
-      <c r="F14" t="s">
+      <c r="G14" t="s">
         <v>139</v>
-      </c>
-      <c r="G14" t="s">
-        <v>140</v>
       </c>
       <c r="H14" t="s">
         <v>8</v>
@@ -2870,22 +2864,22 @@
     </row>
     <row r="15" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A15" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="C15" t="s">
+        <v>135</v>
+      </c>
+      <c r="D15" t="s">
         <v>136</v>
       </c>
-      <c r="D15" t="s">
+      <c r="E15" t="s">
         <v>137</v>
       </c>
-      <c r="E15" t="s">
+      <c r="F15" t="s">
         <v>138</v>
       </c>
-      <c r="F15" t="s">
+      <c r="G15" t="s">
         <v>139</v>
-      </c>
-      <c r="G15" t="s">
-        <v>140</v>
       </c>
       <c r="H15" t="s">
         <v>8</v>
@@ -2893,22 +2887,22 @@
     </row>
     <row r="16" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A16" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="C16" t="s">
         <v>13</v>
       </c>
       <c r="D16" t="s">
+        <v>142</v>
+      </c>
+      <c r="E16" t="s">
         <v>143</v>
       </c>
-      <c r="E16" t="s">
+      <c r="F16" t="s">
         <v>144</v>
       </c>
-      <c r="F16" t="s">
+      <c r="G16" t="s">
         <v>145</v>
-      </c>
-      <c r="G16" t="s">
-        <v>146</v>
       </c>
       <c r="H16" t="s">
         <v>8</v>
@@ -2916,22 +2910,22 @@
     </row>
     <row r="17" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A17" t="s">
+        <v>146</v>
+      </c>
+      <c r="C17" t="s">
         <v>147</v>
       </c>
-      <c r="C17" t="s">
+      <c r="D17" t="s">
         <v>148</v>
       </c>
-      <c r="D17" t="s">
+      <c r="E17" t="s">
         <v>149</v>
       </c>
-      <c r="E17" t="s">
+      <c r="F17" t="s">
         <v>150</v>
       </c>
-      <c r="F17" t="s">
+      <c r="G17" t="s">
         <v>151</v>
-      </c>
-      <c r="G17" t="s">
-        <v>152</v>
       </c>
       <c r="H17" t="s">
         <v>8</v>
@@ -2939,13 +2933,13 @@
     </row>
     <row r="18" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A18" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="C18" t="s">
         <v>18</v>
       </c>
       <c r="D18" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="E18" t="s">
         <v>14</v>
@@ -2954,7 +2948,7 @@
         <v>15</v>
       </c>
       <c r="G18" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="H18" t="s">
         <v>8</v>
@@ -2962,13 +2956,13 @@
     </row>
     <row r="19" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A19" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="C19" t="s">
         <v>9</v>
       </c>
       <c r="D19" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="E19" t="s">
         <v>69</v>
@@ -2977,7 +2971,7 @@
         <v>70</v>
       </c>
       <c r="G19" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="H19" t="s">
         <v>8</v>
@@ -2985,13 +2979,13 @@
     </row>
     <row r="20" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A20" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="C20" t="s">
         <v>9</v>
       </c>
       <c r="D20" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="E20" t="s">
         <v>69</v>
@@ -3000,7 +2994,7 @@
         <v>70</v>
       </c>
       <c r="G20" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="H20" t="s">
         <v>8</v>
@@ -3008,13 +3002,13 @@
     </row>
     <row r="21" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A21" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="C21" t="s">
         <v>50</v>
       </c>
       <c r="D21" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="E21" t="s">
         <v>47</v>
@@ -3023,7 +3017,7 @@
         <v>48</v>
       </c>
       <c r="G21" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="H21" t="s">
         <v>8</v>
@@ -3031,22 +3025,22 @@
     </row>
     <row r="22" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A22" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="C22" t="s">
         <v>86</v>
       </c>
       <c r="D22" t="s">
+        <v>163</v>
+      </c>
+      <c r="E22" t="s">
+        <v>104</v>
+      </c>
+      <c r="F22" t="s">
+        <v>7</v>
+      </c>
+      <c r="G22" t="s">
         <v>164</v>
-      </c>
-      <c r="E22" t="s">
-        <v>105</v>
-      </c>
-      <c r="F22" t="s">
-        <v>7</v>
-      </c>
-      <c r="G22" t="s">
-        <v>165</v>
       </c>
       <c r="H22" t="s">
         <v>8</v>
@@ -3054,22 +3048,22 @@
     </row>
     <row r="23" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A23" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="C23" t="s">
         <v>86</v>
       </c>
       <c r="D23" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="E23" t="s">
+        <v>104</v>
+      </c>
+      <c r="F23" t="s">
+        <v>7</v>
+      </c>
+      <c r="G23" t="s">
         <v>105</v>
-      </c>
-      <c r="F23" t="s">
-        <v>7</v>
-      </c>
-      <c r="G23" t="s">
-        <v>106</v>
       </c>
       <c r="H23" t="s">
         <v>8</v>
@@ -3077,22 +3071,22 @@
     </row>
     <row r="24" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A24" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="C24" t="s">
         <v>25</v>
       </c>
       <c r="D24" t="s">
+        <v>168</v>
+      </c>
+      <c r="E24" t="s">
         <v>169</v>
       </c>
-      <c r="E24" t="s">
+      <c r="F24" t="s">
+        <v>7</v>
+      </c>
+      <c r="G24" t="s">
         <v>170</v>
-      </c>
-      <c r="F24" t="s">
-        <v>7</v>
-      </c>
-      <c r="G24" t="s">
-        <v>171</v>
       </c>
       <c r="H24" t="s">
         <v>8</v>
@@ -3100,22 +3094,22 @@
     </row>
     <row r="25" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A25" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="C25" t="s">
         <v>25</v>
       </c>
       <c r="D25" t="s">
+        <v>168</v>
+      </c>
+      <c r="E25" t="s">
         <v>169</v>
       </c>
-      <c r="E25" t="s">
+      <c r="F25" t="s">
+        <v>7</v>
+      </c>
+      <c r="G25" t="s">
         <v>170</v>
-      </c>
-      <c r="F25" t="s">
-        <v>7</v>
-      </c>
-      <c r="G25" t="s">
-        <v>171</v>
       </c>
       <c r="H25" t="s">
         <v>8</v>
@@ -3123,22 +3117,22 @@
     </row>
     <row r="26" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A26" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="C26" t="s">
         <v>18</v>
       </c>
       <c r="D26" t="s">
+        <v>173</v>
+      </c>
+      <c r="E26" t="s">
         <v>174</v>
       </c>
-      <c r="E26" t="s">
+      <c r="F26" t="s">
         <v>175</v>
       </c>
-      <c r="F26" t="s">
+      <c r="G26" t="s">
         <v>176</v>
-      </c>
-      <c r="G26" t="s">
-        <v>177</v>
       </c>
       <c r="H26" t="s">
         <v>8</v>
@@ -3146,22 +3140,22 @@
     </row>
     <row r="27" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A27" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="C27" t="s">
         <v>23</v>
       </c>
       <c r="D27" t="s">
+        <v>178</v>
+      </c>
+      <c r="E27" t="s">
         <v>179</v>
       </c>
-      <c r="E27" t="s">
+      <c r="F27" t="s">
+        <v>7</v>
+      </c>
+      <c r="G27" t="s">
         <v>180</v>
-      </c>
-      <c r="F27" t="s">
-        <v>7</v>
-      </c>
-      <c r="G27" t="s">
-        <v>181</v>
       </c>
       <c r="H27" t="s">
         <v>8</v>
@@ -3169,13 +3163,13 @@
     </row>
     <row r="28" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A28" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="C28" t="s">
         <v>64</v>
       </c>
       <c r="D28" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="E28" t="s">
         <v>29</v>
@@ -3184,7 +3178,7 @@
         <v>7</v>
       </c>
       <c r="G28" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="H28" t="s">
         <v>8</v>
@@ -3192,13 +3186,13 @@
     </row>
     <row r="29" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A29" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="C29" t="s">
         <v>64</v>
       </c>
       <c r="D29" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="E29" t="s">
         <v>29</v>
@@ -3207,7 +3201,7 @@
         <v>7</v>
       </c>
       <c r="G29" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="H29" t="s">
         <v>8</v>
@@ -3215,22 +3209,22 @@
     </row>
     <row r="30" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A30" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="C30" t="s">
         <v>24</v>
       </c>
       <c r="D30" t="s">
+        <v>186</v>
+      </c>
+      <c r="E30" t="s">
         <v>187</v>
       </c>
-      <c r="E30" t="s">
+      <c r="F30" t="s">
+        <v>7</v>
+      </c>
+      <c r="G30" t="s">
         <v>188</v>
-      </c>
-      <c r="F30" t="s">
-        <v>7</v>
-      </c>
-      <c r="G30" t="s">
-        <v>189</v>
       </c>
       <c r="H30" t="s">
         <v>8</v>
@@ -3238,22 +3232,22 @@
     </row>
     <row r="31" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A31" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="C31" t="s">
         <v>22</v>
       </c>
       <c r="D31" t="s">
+        <v>190</v>
+      </c>
+      <c r="E31" t="s">
         <v>191</v>
       </c>
-      <c r="E31" t="s">
+      <c r="F31" t="s">
+        <v>7</v>
+      </c>
+      <c r="G31" t="s">
         <v>192</v>
-      </c>
-      <c r="F31" t="s">
-        <v>7</v>
-      </c>
-      <c r="G31" t="s">
-        <v>193</v>
       </c>
       <c r="H31" t="s">
         <v>8</v>
@@ -3261,13 +3255,13 @@
     </row>
     <row r="32" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A32" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="C32" t="s">
         <v>43</v>
       </c>
       <c r="D32" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="E32" t="s">
         <v>35</v>
@@ -3276,7 +3270,7 @@
         <v>7</v>
       </c>
       <c r="G32" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="H32" t="s">
         <v>8</v>
@@ -3284,13 +3278,13 @@
     </row>
     <row r="33" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A33" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="C33" t="s">
         <v>16</v>
       </c>
       <c r="D33" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="E33" t="s">
         <v>44</v>
@@ -3299,7 +3293,7 @@
         <v>7</v>
       </c>
       <c r="G33" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="H33" t="s">
         <v>8</v>
@@ -3307,13 +3301,13 @@
     </row>
     <row r="34" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A34" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="C34" t="s">
         <v>43</v>
       </c>
       <c r="D34" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="E34" t="s">
         <v>35</v>
@@ -3322,7 +3316,7 @@
         <v>7</v>
       </c>
       <c r="G34" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="H34" t="s">
         <v>8</v>
@@ -3330,22 +3324,22 @@
     </row>
     <row r="35" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A35" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c r="C35" t="s">
         <v>64</v>
       </c>
       <c r="D35" t="s">
+        <v>202</v>
+      </c>
+      <c r="E35" t="s">
         <v>203</v>
       </c>
-      <c r="E35" t="s">
+      <c r="F35" t="s">
+        <v>7</v>
+      </c>
+      <c r="G35" t="s">
         <v>204</v>
-      </c>
-      <c r="F35" t="s">
-        <v>7</v>
-      </c>
-      <c r="G35" t="s">
-        <v>205</v>
       </c>
       <c r="H35" t="s">
         <v>8</v>
@@ -3353,22 +3347,22 @@
     </row>
     <row r="36" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A36" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="C36" t="s">
         <v>16</v>
       </c>
       <c r="D36" t="s">
+        <v>206</v>
+      </c>
+      <c r="E36" t="s">
         <v>207</v>
       </c>
-      <c r="E36" t="s">
+      <c r="F36" t="s">
+        <v>7</v>
+      </c>
+      <c r="G36" t="s">
         <v>208</v>
-      </c>
-      <c r="F36" t="s">
-        <v>7</v>
-      </c>
-      <c r="G36" t="s">
-        <v>209</v>
       </c>
       <c r="H36" t="s">
         <v>8</v>
@@ -3376,22 +3370,22 @@
     </row>
     <row r="37" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A37" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="C37" t="s">
         <v>19</v>
       </c>
       <c r="D37" t="s">
+        <v>210</v>
+      </c>
+      <c r="E37" t="s">
         <v>211</v>
       </c>
-      <c r="E37" t="s">
+      <c r="F37" t="s">
+        <v>7</v>
+      </c>
+      <c r="G37" t="s">
         <v>212</v>
-      </c>
-      <c r="F37" t="s">
-        <v>7</v>
-      </c>
-      <c r="G37" t="s">
-        <v>213</v>
       </c>
       <c r="H37" t="s">
         <v>8</v>
@@ -3399,22 +3393,22 @@
     </row>
     <row r="38" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A38" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="C38" t="s">
         <v>86</v>
       </c>
       <c r="D38" t="s">
+        <v>214</v>
+      </c>
+      <c r="E38" t="s">
         <v>215</v>
       </c>
-      <c r="E38" t="s">
+      <c r="F38" t="s">
+        <v>7</v>
+      </c>
+      <c r="G38" t="s">
         <v>216</v>
-      </c>
-      <c r="F38" t="s">
-        <v>7</v>
-      </c>
-      <c r="G38" t="s">
-        <v>217</v>
       </c>
       <c r="H38" t="s">
         <v>8</v>
@@ -3422,22 +3416,22 @@
     </row>
     <row r="39" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A39" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="C39" t="s">
         <v>86</v>
       </c>
       <c r="D39" t="s">
+        <v>214</v>
+      </c>
+      <c r="E39" t="s">
         <v>215</v>
       </c>
-      <c r="E39" t="s">
+      <c r="F39" t="s">
+        <v>7</v>
+      </c>
+      <c r="G39" t="s">
         <v>216</v>
-      </c>
-      <c r="F39" t="s">
-        <v>7</v>
-      </c>
-      <c r="G39" t="s">
-        <v>217</v>
       </c>
       <c r="H39" t="s">
         <v>8</v>
@@ -3445,22 +3439,22 @@
     </row>
     <row r="40" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A40" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="C40" t="s">
         <v>33</v>
       </c>
       <c r="D40" t="s">
+        <v>219</v>
+      </c>
+      <c r="E40" t="s">
         <v>220</v>
       </c>
-      <c r="E40" t="s">
+      <c r="F40" t="s">
+        <v>7</v>
+      </c>
+      <c r="G40" t="s">
         <v>221</v>
-      </c>
-      <c r="F40" t="s">
-        <v>7</v>
-      </c>
-      <c r="G40" t="s">
-        <v>222</v>
       </c>
       <c r="H40" t="s">
         <v>8</v>
@@ -3468,22 +3462,22 @@
     </row>
     <row r="41" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A41" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
       <c r="C41" t="s">
         <v>24</v>
       </c>
       <c r="D41" t="s">
+        <v>223</v>
+      </c>
+      <c r="E41" t="s">
+        <v>123</v>
+      </c>
+      <c r="F41" t="s">
+        <v>7</v>
+      </c>
+      <c r="G41" t="s">
         <v>224</v>
-      </c>
-      <c r="E41" t="s">
-        <v>124</v>
-      </c>
-      <c r="F41" t="s">
-        <v>7</v>
-      </c>
-      <c r="G41" t="s">
-        <v>225</v>
       </c>
       <c r="H41" t="s">
         <v>8</v>
@@ -3491,22 +3485,22 @@
     </row>
     <row r="42" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A42" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="C42" t="s">
         <v>23</v>
       </c>
       <c r="D42" t="s">
+        <v>226</v>
+      </c>
+      <c r="E42" t="s">
         <v>227</v>
       </c>
-      <c r="E42" t="s">
+      <c r="F42" t="s">
+        <v>7</v>
+      </c>
+      <c r="G42" t="s">
         <v>228</v>
-      </c>
-      <c r="F42" t="s">
-        <v>7</v>
-      </c>
-      <c r="G42" t="s">
-        <v>229</v>
       </c>
       <c r="H42" t="s">
         <v>8</v>
@@ -3514,22 +3508,22 @@
     </row>
     <row r="43" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A43" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="C43" t="s">
         <v>64</v>
       </c>
       <c r="D43" t="s">
+        <v>230</v>
+      </c>
+      <c r="E43" t="s">
+        <v>203</v>
+      </c>
+      <c r="F43" t="s">
+        <v>7</v>
+      </c>
+      <c r="G43" t="s">
         <v>231</v>
-      </c>
-      <c r="E43" t="s">
-        <v>204</v>
-      </c>
-      <c r="F43" t="s">
-        <v>7</v>
-      </c>
-      <c r="G43" t="s">
-        <v>232</v>
       </c>
       <c r="H43" t="s">
         <v>8</v>
@@ -3537,22 +3531,22 @@
     </row>
     <row r="44" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A44" t="s">
-        <v>233</v>
+        <v>232</v>
       </c>
       <c r="C44" t="s">
         <v>39</v>
       </c>
       <c r="D44" t="s">
+        <v>233</v>
+      </c>
+      <c r="E44" t="s">
         <v>234</v>
       </c>
-      <c r="E44" t="s">
+      <c r="F44" t="s">
+        <v>7</v>
+      </c>
+      <c r="G44" t="s">
         <v>235</v>
-      </c>
-      <c r="F44" t="s">
-        <v>7</v>
-      </c>
-      <c r="G44" t="s">
-        <v>236</v>
       </c>
       <c r="H44" t="s">
         <v>8</v>
@@ -3560,13 +3554,13 @@
     </row>
     <row r="45" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A45" t="s">
-        <v>237</v>
+        <v>236</v>
       </c>
       <c r="C45" t="s">
         <v>33</v>
       </c>
       <c r="D45" t="s">
-        <v>238</v>
+        <v>237</v>
       </c>
       <c r="E45" t="s">
         <v>90</v>
@@ -3583,13 +3577,13 @@
     </row>
     <row r="46" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A46" t="s">
-        <v>239</v>
+        <v>238</v>
       </c>
       <c r="C46" t="s">
         <v>50</v>
       </c>
       <c r="D46" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
       <c r="E46" t="s">
         <v>78</v>
@@ -3598,7 +3592,7 @@
         <v>79</v>
       </c>
       <c r="G46" t="s">
-        <v>241</v>
+        <v>240</v>
       </c>
       <c r="H46" t="s">
         <v>32</v>
@@ -3606,13 +3600,13 @@
     </row>
     <row r="47" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A47" t="s">
+        <v>241</v>
+      </c>
+      <c r="C47" t="s">
+        <v>135</v>
+      </c>
+      <c r="D47" t="s">
         <v>242</v>
-      </c>
-      <c r="C47" t="s">
-        <v>136</v>
-      </c>
-      <c r="D47" t="s">
-        <v>243</v>
       </c>
       <c r="E47" t="s">
         <v>54</v>
@@ -3629,22 +3623,22 @@
     </row>
     <row r="48" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A48" t="s">
-        <v>244</v>
+        <v>243</v>
       </c>
       <c r="C48" t="s">
         <v>9</v>
       </c>
       <c r="D48" t="s">
+        <v>244</v>
+      </c>
+      <c r="E48" t="s">
         <v>245</v>
       </c>
-      <c r="E48" t="s">
+      <c r="F48" t="s">
         <v>246</v>
       </c>
-      <c r="F48" t="s">
+      <c r="G48" t="s">
         <v>247</v>
-      </c>
-      <c r="G48" t="s">
-        <v>248</v>
       </c>
       <c r="H48" t="s">
         <v>11</v>
@@ -3652,22 +3646,22 @@
     </row>
     <row r="49" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A49" t="s">
-        <v>249</v>
+        <v>248</v>
       </c>
       <c r="C49" t="s">
         <v>9</v>
       </c>
       <c r="D49" t="s">
+        <v>244</v>
+      </c>
+      <c r="E49" t="s">
         <v>245</v>
       </c>
-      <c r="E49" t="s">
+      <c r="F49" t="s">
         <v>246</v>
       </c>
-      <c r="F49" t="s">
+      <c r="G49" t="s">
         <v>247</v>
-      </c>
-      <c r="G49" t="s">
-        <v>248</v>
       </c>
       <c r="H49" t="s">
         <v>11</v>
@@ -3675,22 +3669,22 @@
     </row>
     <row r="50" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A50" t="s">
-        <v>250</v>
+        <v>249</v>
       </c>
       <c r="C50" t="s">
         <v>20</v>
       </c>
       <c r="D50" t="s">
+        <v>250</v>
+      </c>
+      <c r="E50" t="s">
         <v>251</v>
       </c>
-      <c r="E50" t="s">
+      <c r="F50" t="s">
         <v>252</v>
       </c>
-      <c r="F50" t="s">
+      <c r="G50" t="s">
         <v>253</v>
-      </c>
-      <c r="G50" t="s">
-        <v>254</v>
       </c>
       <c r="H50" t="s">
         <v>11</v>
@@ -3698,22 +3692,22 @@
     </row>
     <row r="51" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A51" t="s">
-        <v>255</v>
+        <v>254</v>
       </c>
       <c r="C51" t="s">
         <v>72</v>
       </c>
       <c r="D51" t="s">
+        <v>255</v>
+      </c>
+      <c r="E51" t="s">
         <v>256</v>
       </c>
-      <c r="E51" t="s">
+      <c r="F51" t="s">
         <v>257</v>
       </c>
-      <c r="F51" t="s">
+      <c r="G51" t="s">
         <v>258</v>
-      </c>
-      <c r="G51" t="s">
-        <v>259</v>
       </c>
       <c r="H51" t="s">
         <v>11</v>
@@ -3721,13 +3715,13 @@
     </row>
     <row r="52" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A52" t="s">
-        <v>260</v>
+        <v>259</v>
       </c>
       <c r="C52" t="s">
         <v>33</v>
       </c>
       <c r="D52" t="s">
-        <v>261</v>
+        <v>260</v>
       </c>
       <c r="E52" t="s">
         <v>37</v>
@@ -3736,7 +3730,7 @@
         <v>38</v>
       </c>
       <c r="G52" t="s">
-        <v>262</v>
+        <v>261</v>
       </c>
       <c r="H52" t="s">
         <v>11</v>
@@ -3790,13 +3784,13 @@
     </row>
     <row r="55" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A55" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="C55" t="s">
         <v>33</v>
       </c>
       <c r="D55" t="s">
-        <v>264</v>
+        <v>263</v>
       </c>
       <c r="E55" t="s">
         <v>37</v>
@@ -3805,7 +3799,7 @@
         <v>38</v>
       </c>
       <c r="G55" t="s">
-        <v>265</v>
+        <v>264</v>
       </c>
       <c r="H55" t="s">
         <v>11</v>
@@ -3813,22 +3807,22 @@
     </row>
     <row r="56" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A56" t="s">
-        <v>266</v>
+        <v>265</v>
       </c>
       <c r="C56" t="s">
         <v>22</v>
       </c>
       <c r="D56" t="s">
+        <v>266</v>
+      </c>
+      <c r="E56" t="s">
+        <v>191</v>
+      </c>
+      <c r="F56" t="s">
+        <v>7</v>
+      </c>
+      <c r="G56" t="s">
         <v>267</v>
-      </c>
-      <c r="E56" t="s">
-        <v>192</v>
-      </c>
-      <c r="F56" t="s">
-        <v>7</v>
-      </c>
-      <c r="G56" t="s">
-        <v>268</v>
       </c>
       <c r="H56" t="s">
         <v>11</v>
@@ -3836,13 +3830,13 @@
     </row>
     <row r="57" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A57" t="s">
+        <v>268</v>
+      </c>
+      <c r="C57" t="s">
+        <v>135</v>
+      </c>
+      <c r="D57" t="s">
         <v>269</v>
-      </c>
-      <c r="C57" t="s">
-        <v>136</v>
-      </c>
-      <c r="D57" t="s">
-        <v>270</v>
       </c>
       <c r="E57" t="s">
         <v>57</v>
@@ -3851,7 +3845,7 @@
         <v>58</v>
       </c>
       <c r="G57" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
       <c r="H57" t="s">
         <v>11</v>
@@ -3859,22 +3853,22 @@
     </row>
     <row r="58" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A58" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
       <c r="C58" t="s">
         <v>24</v>
       </c>
       <c r="D58" t="s">
+        <v>272</v>
+      </c>
+      <c r="E58" t="s">
+        <v>123</v>
+      </c>
+      <c r="F58" t="s">
+        <v>7</v>
+      </c>
+      <c r="G58" t="s">
         <v>273</v>
-      </c>
-      <c r="E58" t="s">
-        <v>124</v>
-      </c>
-      <c r="F58" t="s">
-        <v>7</v>
-      </c>
-      <c r="G58" t="s">
-        <v>274</v>
       </c>
       <c r="H58" t="s">
         <v>11</v>
@@ -3882,22 +3876,22 @@
     </row>
     <row r="59" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A59" t="s">
+        <v>274</v>
+      </c>
+      <c r="C59" t="s">
+        <v>147</v>
+      </c>
+      <c r="D59" t="s">
         <v>275</v>
       </c>
-      <c r="C59" t="s">
-        <v>148</v>
-      </c>
-      <c r="D59" t="s">
+      <c r="E59" t="s">
         <v>276</v>
       </c>
-      <c r="E59" t="s">
+      <c r="F59" t="s">
+        <v>7</v>
+      </c>
+      <c r="G59" t="s">
         <v>277</v>
-      </c>
-      <c r="F59" t="s">
-        <v>7</v>
-      </c>
-      <c r="G59" t="s">
-        <v>278</v>
       </c>
       <c r="H59" t="s">
         <v>11</v>
@@ -3905,13 +3899,13 @@
     </row>
     <row r="60" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A60" t="s">
-        <v>279</v>
+        <v>278</v>
       </c>
       <c r="C60" t="s">
         <v>20</v>
       </c>
       <c r="D60" t="s">
-        <v>280</v>
+        <v>279</v>
       </c>
       <c r="E60" t="s">
         <v>34</v>
@@ -3920,7 +3914,7 @@
         <v>7</v>
       </c>
       <c r="G60" t="s">
-        <v>281</v>
+        <v>280</v>
       </c>
       <c r="H60" t="s">
         <v>11</v>
@@ -3928,13 +3922,13 @@
     </row>
     <row r="61" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A61" t="s">
-        <v>282</v>
+        <v>281</v>
       </c>
       <c r="C61" t="s">
         <v>9</v>
       </c>
       <c r="D61" t="s">
-        <v>283</v>
+        <v>282</v>
       </c>
       <c r="E61" t="s">
         <v>26</v>
@@ -3943,7 +3937,7 @@
         <v>27</v>
       </c>
       <c r="G61" t="s">
-        <v>284</v>
+        <v>283</v>
       </c>
       <c r="H61" t="s">
         <v>11</v>
@@ -3951,13 +3945,13 @@
     </row>
     <row r="62" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A62" t="s">
-        <v>285</v>
+        <v>284</v>
       </c>
       <c r="C62" t="s">
         <v>50</v>
       </c>
       <c r="D62" t="s">
-        <v>286</v>
+        <v>285</v>
       </c>
       <c r="E62" t="s">
         <v>84</v>
@@ -3966,7 +3960,7 @@
         <v>85</v>
       </c>
       <c r="G62" t="s">
-        <v>287</v>
+        <v>286</v>
       </c>
       <c r="H62" t="s">
         <v>11</v>
@@ -3974,22 +3968,22 @@
     </row>
     <row r="63" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A63" t="s">
-        <v>288</v>
+        <v>287</v>
       </c>
       <c r="C63" t="s">
         <v>86</v>
       </c>
       <c r="D63" t="s">
+        <v>288</v>
+      </c>
+      <c r="E63" t="s">
         <v>289</v>
       </c>
-      <c r="E63" t="s">
+      <c r="F63" t="s">
+        <v>7</v>
+      </c>
+      <c r="G63" t="s">
         <v>290</v>
-      </c>
-      <c r="F63" t="s">
-        <v>7</v>
-      </c>
-      <c r="G63" t="s">
-        <v>291</v>
       </c>
       <c r="H63" t="s">
         <v>11</v>
@@ -3997,22 +3991,22 @@
     </row>
     <row r="64" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A64" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
       <c r="C64" t="s">
         <v>20</v>
       </c>
       <c r="D64" t="s">
+        <v>292</v>
+      </c>
+      <c r="E64" t="s">
         <v>293</v>
       </c>
-      <c r="E64" t="s">
+      <c r="F64" t="s">
         <v>294</v>
       </c>
-      <c r="F64" t="s">
+      <c r="G64" t="s">
         <v>295</v>
-      </c>
-      <c r="G64" t="s">
-        <v>296</v>
       </c>
       <c r="H64" t="s">
         <v>11</v>
@@ -4020,22 +4014,22 @@
     </row>
     <row r="65" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A65" t="s">
-        <v>297</v>
+        <v>296</v>
       </c>
       <c r="C65" t="s">
         <v>20</v>
       </c>
       <c r="D65" t="s">
+        <v>292</v>
+      </c>
+      <c r="E65" t="s">
         <v>293</v>
       </c>
-      <c r="E65" t="s">
+      <c r="F65" t="s">
         <v>294</v>
       </c>
-      <c r="F65" t="s">
+      <c r="G65" t="s">
         <v>295</v>
-      </c>
-      <c r="G65" t="s">
-        <v>296</v>
       </c>
       <c r="H65" t="s">
         <v>11</v>
@@ -4043,22 +4037,22 @@
     </row>
     <row r="66" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A66" t="s">
-        <v>298</v>
+        <v>297</v>
       </c>
       <c r="C66" t="s">
         <v>72</v>
       </c>
       <c r="D66" t="s">
+        <v>298</v>
+      </c>
+      <c r="E66" t="s">
         <v>299</v>
       </c>
-      <c r="E66" t="s">
+      <c r="F66" t="s">
         <v>300</v>
       </c>
-      <c r="F66" t="s">
+      <c r="G66" t="s">
         <v>301</v>
-      </c>
-      <c r="G66" t="s">
-        <v>302</v>
       </c>
       <c r="H66" t="s">
         <v>11</v>
@@ -4066,22 +4060,22 @@
     </row>
     <row r="67" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A67" t="s">
-        <v>303</v>
+        <v>302</v>
       </c>
       <c r="C67" t="s">
         <v>24</v>
       </c>
       <c r="D67" t="s">
+        <v>303</v>
+      </c>
+      <c r="E67" t="s">
         <v>304</v>
       </c>
-      <c r="E67" t="s">
+      <c r="F67" t="s">
+        <v>7</v>
+      </c>
+      <c r="G67" t="s">
         <v>305</v>
-      </c>
-      <c r="F67" t="s">
-        <v>7</v>
-      </c>
-      <c r="G67" t="s">
-        <v>306</v>
       </c>
       <c r="H67" t="s">
         <v>11</v>
@@ -4089,13 +4083,13 @@
     </row>
     <row r="68" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A68" t="s">
+        <v>306</v>
+      </c>
+      <c r="C68" t="s">
+        <v>147</v>
+      </c>
+      <c r="D68" t="s">
         <v>307</v>
-      </c>
-      <c r="C68" t="s">
-        <v>148</v>
-      </c>
-      <c r="D68" t="s">
-        <v>308</v>
       </c>
       <c r="E68" t="s">
         <v>56</v>
@@ -4104,7 +4098,7 @@
         <v>7</v>
       </c>
       <c r="G68" t="s">
-        <v>309</v>
+        <v>308</v>
       </c>
       <c r="H68" t="s">
         <v>11</v>
@@ -4112,22 +4106,22 @@
     </row>
     <row r="69" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A69" t="s">
-        <v>310</v>
+        <v>309</v>
       </c>
       <c r="C69" t="s">
         <v>13</v>
       </c>
       <c r="D69" t="s">
+        <v>310</v>
+      </c>
+      <c r="E69" t="s">
         <v>311</v>
       </c>
-      <c r="E69" t="s">
+      <c r="F69" t="s">
         <v>312</v>
       </c>
-      <c r="F69" t="s">
+      <c r="G69" t="s">
         <v>313</v>
-      </c>
-      <c r="G69" t="s">
-        <v>314</v>
       </c>
       <c r="H69" t="s">
         <v>11</v>
@@ -4135,22 +4129,22 @@
     </row>
     <row r="70" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A70" t="s">
-        <v>315</v>
+        <v>314</v>
       </c>
       <c r="C70" t="s">
         <v>13</v>
       </c>
       <c r="D70" t="s">
+        <v>315</v>
+      </c>
+      <c r="E70" t="s">
+        <v>311</v>
+      </c>
+      <c r="F70" t="s">
+        <v>312</v>
+      </c>
+      <c r="G70" t="s">
         <v>316</v>
-      </c>
-      <c r="E70" t="s">
-        <v>312</v>
-      </c>
-      <c r="F70" t="s">
-        <v>313</v>
-      </c>
-      <c r="G70" t="s">
-        <v>317</v>
       </c>
       <c r="H70" t="s">
         <v>11</v>
@@ -4158,22 +4152,22 @@
     </row>
     <row r="71" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A71" t="s">
-        <v>318</v>
+        <v>317</v>
       </c>
       <c r="C71" t="s">
         <v>13</v>
       </c>
       <c r="D71" t="s">
+        <v>315</v>
+      </c>
+      <c r="E71" t="s">
+        <v>311</v>
+      </c>
+      <c r="F71" t="s">
+        <v>312</v>
+      </c>
+      <c r="G71" t="s">
         <v>316</v>
-      </c>
-      <c r="E71" t="s">
-        <v>312</v>
-      </c>
-      <c r="F71" t="s">
-        <v>313</v>
-      </c>
-      <c r="G71" t="s">
-        <v>317</v>
       </c>
       <c r="H71" t="s">
         <v>11</v>
@@ -4181,22 +4175,22 @@
     </row>
     <row r="72" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A72" t="s">
-        <v>319</v>
+        <v>318</v>
       </c>
       <c r="C72" t="s">
         <v>43</v>
       </c>
       <c r="D72" t="s">
+        <v>319</v>
+      </c>
+      <c r="E72" t="s">
         <v>320</v>
       </c>
-      <c r="E72" t="s">
+      <c r="F72" t="s">
         <v>321</v>
       </c>
-      <c r="F72" t="s">
+      <c r="G72" t="s">
         <v>322</v>
-      </c>
-      <c r="G72" t="s">
-        <v>323</v>
       </c>
       <c r="H72" t="s">
         <v>11</v>
@@ -4204,22 +4198,22 @@
     </row>
     <row r="73" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A73" t="s">
-        <v>324</v>
+        <v>323</v>
       </c>
       <c r="C73" t="s">
         <v>43</v>
       </c>
       <c r="D73" t="s">
+        <v>319</v>
+      </c>
+      <c r="E73" t="s">
         <v>320</v>
       </c>
-      <c r="E73" t="s">
+      <c r="F73" t="s">
         <v>321</v>
       </c>
-      <c r="F73" t="s">
+      <c r="G73" t="s">
         <v>322</v>
-      </c>
-      <c r="G73" t="s">
-        <v>323</v>
       </c>
       <c r="H73" t="s">
         <v>11</v>
@@ -4227,22 +4221,22 @@
     </row>
     <row r="74" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A74" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
       <c r="C74" t="s">
         <v>18</v>
       </c>
       <c r="D74" t="s">
+        <v>325</v>
+      </c>
+      <c r="E74" t="s">
         <v>326</v>
       </c>
-      <c r="E74" t="s">
+      <c r="F74" t="s">
+        <v>7</v>
+      </c>
+      <c r="G74" t="s">
         <v>327</v>
-      </c>
-      <c r="F74" t="s">
-        <v>7</v>
-      </c>
-      <c r="G74" t="s">
-        <v>328</v>
       </c>
       <c r="H74" t="s">
         <v>11</v>
@@ -4250,13 +4244,13 @@
     </row>
     <row r="75" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A75" t="s">
-        <v>329</v>
+        <v>328</v>
       </c>
       <c r="C75" t="s">
         <v>10</v>
       </c>
       <c r="D75" t="s">
-        <v>330</v>
+        <v>329</v>
       </c>
       <c r="E75" t="s">
         <v>51</v>
@@ -4265,7 +4259,7 @@
         <v>7</v>
       </c>
       <c r="G75" t="s">
-        <v>331</v>
+        <v>330</v>
       </c>
       <c r="H75" t="s">
         <v>11</v>
@@ -4273,13 +4267,13 @@
     </row>
     <row r="76" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A76" t="s">
-        <v>332</v>
+        <v>331</v>
       </c>
       <c r="C76" t="s">
         <v>10</v>
       </c>
       <c r="D76" t="s">
-        <v>333</v>
+        <v>332</v>
       </c>
       <c r="E76" t="s">
         <v>80</v>
@@ -4288,7 +4282,7 @@
         <v>7</v>
       </c>
       <c r="G76" t="s">
-        <v>334</v>
+        <v>333</v>
       </c>
       <c r="H76" t="s">
         <v>11</v>
@@ -4296,22 +4290,22 @@
     </row>
     <row r="77" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A77" t="s">
-        <v>335</v>
+        <v>334</v>
       </c>
       <c r="C77" t="s">
         <v>43</v>
       </c>
       <c r="D77" t="s">
+        <v>335</v>
+      </c>
+      <c r="E77" t="s">
         <v>336</v>
       </c>
-      <c r="E77" t="s">
+      <c r="F77" t="s">
         <v>337</v>
       </c>
-      <c r="F77" t="s">
+      <c r="G77" t="s">
         <v>338</v>
-      </c>
-      <c r="G77" t="s">
-        <v>339</v>
       </c>
       <c r="H77" t="s">
         <v>11</v>
@@ -4319,22 +4313,22 @@
     </row>
     <row r="78" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A78" t="s">
+        <v>339</v>
+      </c>
+      <c r="C78" t="s">
         <v>340</v>
       </c>
-      <c r="C78" t="s">
+      <c r="D78" t="s">
         <v>341</v>
       </c>
-      <c r="D78" t="s">
+      <c r="E78" t="s">
         <v>342</v>
       </c>
-      <c r="E78" t="s">
+      <c r="F78" t="s">
+        <v>7</v>
+      </c>
+      <c r="G78" t="s">
         <v>343</v>
-      </c>
-      <c r="F78" t="s">
-        <v>7</v>
-      </c>
-      <c r="G78" t="s">
-        <v>344</v>
       </c>
       <c r="H78" t="s">
         <v>11</v>
@@ -4342,22 +4336,22 @@
     </row>
     <row r="79" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A79" t="s">
-        <v>345</v>
+        <v>344</v>
       </c>
       <c r="C79" t="s">
         <v>22</v>
       </c>
       <c r="D79" t="s">
+        <v>345</v>
+      </c>
+      <c r="E79" t="s">
         <v>346</v>
       </c>
-      <c r="E79" t="s">
+      <c r="F79" t="s">
+        <v>7</v>
+      </c>
+      <c r="G79" t="s">
         <v>347</v>
-      </c>
-      <c r="F79" t="s">
-        <v>7</v>
-      </c>
-      <c r="G79" t="s">
-        <v>348</v>
       </c>
       <c r="H79" t="s">
         <v>11</v>
@@ -4365,22 +4359,22 @@
     </row>
     <row r="80" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A80" t="s">
-        <v>349</v>
+        <v>348</v>
       </c>
       <c r="C80" t="s">
         <v>72</v>
       </c>
       <c r="D80" t="s">
+        <v>349</v>
+      </c>
+      <c r="E80" t="s">
+        <v>299</v>
+      </c>
+      <c r="F80" t="s">
+        <v>300</v>
+      </c>
+      <c r="G80" t="s">
         <v>350</v>
-      </c>
-      <c r="E80" t="s">
-        <v>300</v>
-      </c>
-      <c r="F80" t="s">
-        <v>301</v>
-      </c>
-      <c r="G80" t="s">
-        <v>351</v>
       </c>
       <c r="H80" t="s">
         <v>11</v>
@@ -4388,22 +4382,22 @@
     </row>
     <row r="81" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A81" t="s">
+        <v>351</v>
+      </c>
+      <c r="C81" t="s">
+        <v>135</v>
+      </c>
+      <c r="D81" t="s">
         <v>352</v>
       </c>
-      <c r="C81" t="s">
-        <v>136</v>
-      </c>
-      <c r="D81" t="s">
+      <c r="E81" t="s">
         <v>353</v>
       </c>
-      <c r="E81" t="s">
+      <c r="F81" t="s">
         <v>354</v>
       </c>
-      <c r="F81" t="s">
+      <c r="G81" t="s">
         <v>355</v>
-      </c>
-      <c r="G81" t="s">
-        <v>356</v>
       </c>
       <c r="H81" t="s">
         <v>11</v>
@@ -4411,22 +4405,22 @@
     </row>
     <row r="82" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A82" t="s">
-        <v>357</v>
+        <v>356</v>
       </c>
       <c r="C82" t="s">
         <v>43</v>
       </c>
       <c r="D82" t="s">
+        <v>357</v>
+      </c>
+      <c r="E82" t="s">
         <v>358</v>
       </c>
-      <c r="E82" t="s">
+      <c r="F82" t="s">
+        <v>7</v>
+      </c>
+      <c r="G82" t="s">
         <v>359</v>
-      </c>
-      <c r="F82" t="s">
-        <v>7</v>
-      </c>
-      <c r="G82" t="s">
-        <v>360</v>
       </c>
       <c r="H82" t="s">
         <v>11</v>
@@ -4434,22 +4428,22 @@
     </row>
     <row r="83" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A83" t="s">
-        <v>361</v>
+        <v>360</v>
       </c>
       <c r="C83" t="s">
         <v>22</v>
       </c>
       <c r="D83" t="s">
+        <v>361</v>
+      </c>
+      <c r="E83" t="s">
         <v>362</v>
       </c>
-      <c r="E83" t="s">
+      <c r="F83" t="s">
+        <v>7</v>
+      </c>
+      <c r="G83" t="s">
         <v>363</v>
-      </c>
-      <c r="F83" t="s">
-        <v>7</v>
-      </c>
-      <c r="G83" t="s">
-        <v>364</v>
       </c>
       <c r="H83" t="s">
         <v>11</v>
@@ -4457,22 +4451,22 @@
     </row>
     <row r="84" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A84" t="s">
-        <v>365</v>
+        <v>364</v>
       </c>
       <c r="C84" t="s">
         <v>43</v>
       </c>
       <c r="D84" t="s">
+        <v>365</v>
+      </c>
+      <c r="E84" t="s">
         <v>366</v>
       </c>
-      <c r="E84" t="s">
+      <c r="F84" t="s">
         <v>367</v>
       </c>
-      <c r="F84" t="s">
+      <c r="G84" t="s">
         <v>368</v>
-      </c>
-      <c r="G84" t="s">
-        <v>369</v>
       </c>
       <c r="H84" t="s">
         <v>11</v>
@@ -4480,22 +4474,22 @@
     </row>
     <row r="85" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A85" t="s">
-        <v>370</v>
+        <v>369</v>
       </c>
       <c r="C85" t="s">
         <v>43</v>
       </c>
       <c r="D85" t="s">
+        <v>365</v>
+      </c>
+      <c r="E85" t="s">
         <v>366</v>
       </c>
-      <c r="E85" t="s">
+      <c r="F85" t="s">
         <v>367</v>
       </c>
-      <c r="F85" t="s">
+      <c r="G85" t="s">
         <v>368</v>
-      </c>
-      <c r="G85" t="s">
-        <v>369</v>
       </c>
       <c r="H85" t="s">
         <v>11</v>
@@ -4503,13 +4497,13 @@
     </row>
     <row r="86" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A86" t="s">
-        <v>371</v>
+        <v>370</v>
       </c>
       <c r="C86" t="s">
         <v>9</v>
       </c>
       <c r="D86" t="s">
-        <v>372</v>
+        <v>371</v>
       </c>
       <c r="E86" t="s">
         <v>92</v>
@@ -4518,7 +4512,7 @@
         <v>93</v>
       </c>
       <c r="G86" t="s">
-        <v>373</v>
+        <v>372</v>
       </c>
       <c r="H86" t="s">
         <v>11</v>
@@ -4526,22 +4520,22 @@
     </row>
     <row r="87" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A87" t="s">
-        <v>374</v>
+        <v>373</v>
       </c>
       <c r="C87" t="s">
         <v>9</v>
       </c>
       <c r="D87" t="s">
+        <v>374</v>
+      </c>
+      <c r="E87" t="s">
         <v>375</v>
       </c>
-      <c r="E87" t="s">
+      <c r="F87" t="s">
         <v>376</v>
       </c>
-      <c r="F87" t="s">
+      <c r="G87" t="s">
         <v>377</v>
-      </c>
-      <c r="G87" t="s">
-        <v>378</v>
       </c>
       <c r="H87" t="s">
         <v>11</v>
@@ -4549,13 +4543,13 @@
     </row>
     <row r="88" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A88" t="s">
-        <v>379</v>
+        <v>378</v>
       </c>
       <c r="C88" t="s">
         <v>43</v>
       </c>
       <c r="D88" t="s">
-        <v>380</v>
+        <v>379</v>
       </c>
       <c r="E88" t="s">
         <v>35</v>
@@ -4564,7 +4558,7 @@
         <v>7</v>
       </c>
       <c r="G88" t="s">
-        <v>381</v>
+        <v>380</v>
       </c>
       <c r="H88" t="s">
         <v>11</v>
@@ -4572,22 +4566,22 @@
     </row>
     <row r="89" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A89" t="s">
+        <v>381</v>
+      </c>
+      <c r="C89" t="s">
+        <v>147</v>
+      </c>
+      <c r="D89" t="s">
         <v>382</v>
       </c>
-      <c r="C89" t="s">
-        <v>148</v>
-      </c>
-      <c r="D89" t="s">
+      <c r="E89" t="s">
         <v>383</v>
       </c>
-      <c r="E89" t="s">
+      <c r="F89" t="s">
+        <v>7</v>
+      </c>
+      <c r="G89" t="s">
         <v>384</v>
-      </c>
-      <c r="F89" t="s">
-        <v>7</v>
-      </c>
-      <c r="G89" t="s">
-        <v>385</v>
       </c>
       <c r="H89" t="s">
         <v>11</v>
@@ -4595,22 +4589,22 @@
     </row>
     <row r="90" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A90" t="s">
-        <v>386</v>
+        <v>385</v>
       </c>
       <c r="C90" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="D90" t="s">
+        <v>382</v>
+      </c>
+      <c r="E90" t="s">
         <v>383</v>
       </c>
-      <c r="E90" t="s">
+      <c r="F90" t="s">
+        <v>7</v>
+      </c>
+      <c r="G90" t="s">
         <v>384</v>
-      </c>
-      <c r="F90" t="s">
-        <v>7</v>
-      </c>
-      <c r="G90" t="s">
-        <v>385</v>
       </c>
       <c r="H90" t="s">
         <v>11</v>
@@ -4618,22 +4612,22 @@
     </row>
     <row r="91" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A91" t="s">
-        <v>387</v>
+        <v>386</v>
       </c>
       <c r="C91" t="s">
         <v>16</v>
       </c>
       <c r="D91" t="s">
+        <v>387</v>
+      </c>
+      <c r="E91" t="s">
         <v>388</v>
       </c>
-      <c r="E91" t="s">
+      <c r="F91" t="s">
+        <v>7</v>
+      </c>
+      <c r="G91" t="s">
         <v>389</v>
-      </c>
-      <c r="F91" t="s">
-        <v>7</v>
-      </c>
-      <c r="G91" t="s">
-        <v>390</v>
       </c>
       <c r="H91" t="s">
         <v>11</v>
@@ -4641,22 +4635,22 @@
     </row>
     <row r="92" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A92" t="s">
-        <v>391</v>
+        <v>390</v>
       </c>
       <c r="C92" t="s">
         <v>16</v>
       </c>
       <c r="D92" t="s">
+        <v>387</v>
+      </c>
+      <c r="E92" t="s">
         <v>388</v>
       </c>
-      <c r="E92" t="s">
+      <c r="F92" t="s">
+        <v>7</v>
+      </c>
+      <c r="G92" t="s">
         <v>389</v>
-      </c>
-      <c r="F92" t="s">
-        <v>7</v>
-      </c>
-      <c r="G92" t="s">
-        <v>390</v>
       </c>
       <c r="H92" t="s">
         <v>11</v>
@@ -4664,22 +4658,22 @@
     </row>
     <row r="93" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A93" t="s">
-        <v>392</v>
+        <v>391</v>
       </c>
       <c r="C93" t="s">
         <v>16</v>
       </c>
       <c r="D93" t="s">
+        <v>387</v>
+      </c>
+      <c r="E93" t="s">
         <v>388</v>
       </c>
-      <c r="E93" t="s">
+      <c r="F93" t="s">
+        <v>7</v>
+      </c>
+      <c r="G93" t="s">
         <v>389</v>
-      </c>
-      <c r="F93" t="s">
-        <v>7</v>
-      </c>
-      <c r="G93" t="s">
-        <v>390</v>
       </c>
       <c r="H93" t="s">
         <v>11</v>
@@ -4687,22 +4681,22 @@
     </row>
     <row r="94" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A94" t="s">
+        <v>392</v>
+      </c>
+      <c r="C94" t="s">
         <v>393</v>
       </c>
-      <c r="C94" t="s">
+      <c r="D94" t="s">
         <v>394</v>
       </c>
-      <c r="D94" t="s">
+      <c r="E94" t="s">
         <v>395</v>
       </c>
-      <c r="E94" t="s">
+      <c r="F94" t="s">
+        <v>7</v>
+      </c>
+      <c r="G94" t="s">
         <v>396</v>
-      </c>
-      <c r="F94" t="s">
-        <v>7</v>
-      </c>
-      <c r="G94" t="s">
-        <v>397</v>
       </c>
       <c r="H94" t="s">
         <v>11</v>
@@ -4710,22 +4704,22 @@
     </row>
     <row r="95" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A95" t="s">
+        <v>397</v>
+      </c>
+      <c r="C95" t="s">
+        <v>147</v>
+      </c>
+      <c r="D95" t="s">
         <v>398</v>
       </c>
-      <c r="C95" t="s">
-        <v>148</v>
-      </c>
-      <c r="D95" t="s">
+      <c r="E95" t="s">
+        <v>383</v>
+      </c>
+      <c r="F95" t="s">
+        <v>7</v>
+      </c>
+      <c r="G95" t="s">
         <v>399</v>
-      </c>
-      <c r="E95" t="s">
-        <v>384</v>
-      </c>
-      <c r="F95" t="s">
-        <v>7</v>
-      </c>
-      <c r="G95" t="s">
-        <v>400</v>
       </c>
       <c r="H95" t="s">
         <v>11</v>
@@ -4733,22 +4727,22 @@
     </row>
     <row r="96" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A96" t="s">
-        <v>401</v>
+        <v>400</v>
       </c>
       <c r="C96" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="D96" t="s">
+        <v>398</v>
+      </c>
+      <c r="E96" t="s">
+        <v>383</v>
+      </c>
+      <c r="F96" t="s">
+        <v>7</v>
+      </c>
+      <c r="G96" t="s">
         <v>399</v>
-      </c>
-      <c r="E96" t="s">
-        <v>384</v>
-      </c>
-      <c r="F96" t="s">
-        <v>7</v>
-      </c>
-      <c r="G96" t="s">
-        <v>400</v>
       </c>
       <c r="H96" t="s">
         <v>11</v>
@@ -4756,13 +4750,13 @@
     </row>
     <row r="97" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A97" t="s">
-        <v>402</v>
+        <v>401</v>
       </c>
       <c r="C97" t="s">
         <v>50</v>
       </c>
       <c r="D97" t="s">
-        <v>403</v>
+        <v>402</v>
       </c>
       <c r="E97" t="s">
         <v>40</v>
@@ -4771,7 +4765,7 @@
         <v>41</v>
       </c>
       <c r="G97" t="s">
-        <v>404</v>
+        <v>403</v>
       </c>
       <c r="H97" t="s">
         <v>11</v>
@@ -4779,22 +4773,22 @@
     </row>
     <row r="98" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A98" t="s">
-        <v>405</v>
+        <v>404</v>
       </c>
       <c r="C98" t="s">
         <v>23</v>
       </c>
       <c r="D98" t="s">
+        <v>405</v>
+      </c>
+      <c r="E98" t="s">
+        <v>227</v>
+      </c>
+      <c r="F98" t="s">
+        <v>7</v>
+      </c>
+      <c r="G98" t="s">
         <v>406</v>
-      </c>
-      <c r="E98" t="s">
-        <v>228</v>
-      </c>
-      <c r="F98" t="s">
-        <v>7</v>
-      </c>
-      <c r="G98" t="s">
-        <v>407</v>
       </c>
       <c r="H98" t="s">
         <v>11</v>
@@ -4802,22 +4796,22 @@
     </row>
     <row r="99" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A99" t="s">
+        <v>407</v>
+      </c>
+      <c r="C99" t="s">
         <v>408</v>
       </c>
-      <c r="C99" t="s">
+      <c r="D99" t="s">
         <v>409</v>
       </c>
-      <c r="D99" t="s">
+      <c r="E99" t="s">
         <v>410</v>
       </c>
-      <c r="E99" t="s">
+      <c r="F99" t="s">
+        <v>7</v>
+      </c>
+      <c r="G99" t="s">
         <v>411</v>
-      </c>
-      <c r="F99" t="s">
-        <v>7</v>
-      </c>
-      <c r="G99" t="s">
-        <v>412</v>
       </c>
       <c r="H99" t="s">
         <v>11</v>
@@ -4825,22 +4819,22 @@
     </row>
     <row r="100" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A100" t="s">
-        <v>413</v>
+        <v>412</v>
       </c>
       <c r="C100" t="s">
         <v>18</v>
       </c>
       <c r="D100" t="s">
+        <v>413</v>
+      </c>
+      <c r="E100" t="s">
         <v>414</v>
       </c>
-      <c r="E100" t="s">
+      <c r="F100" t="s">
         <v>415</v>
       </c>
-      <c r="F100" t="s">
+      <c r="G100" t="s">
         <v>416</v>
-      </c>
-      <c r="G100" t="s">
-        <v>417</v>
       </c>
       <c r="H100" t="s">
         <v>11</v>
@@ -4848,13 +4842,13 @@
     </row>
     <row r="101" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A101" t="s">
-        <v>418</v>
+        <v>417</v>
       </c>
       <c r="C101" t="s">
         <v>17</v>
       </c>
       <c r="D101" t="s">
-        <v>419</v>
+        <v>418</v>
       </c>
       <c r="E101" t="s">
         <v>60</v>
@@ -4863,7 +4857,7 @@
         <v>61</v>
       </c>
       <c r="G101" t="s">
-        <v>420</v>
+        <v>419</v>
       </c>
       <c r="H101" t="s">
         <v>11</v>
@@ -4871,22 +4865,22 @@
     </row>
     <row r="102" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A102" t="s">
+        <v>420</v>
+      </c>
+      <c r="C102" t="s">
+        <v>147</v>
+      </c>
+      <c r="D102" t="s">
         <v>421</v>
       </c>
-      <c r="C102" t="s">
-        <v>148</v>
-      </c>
-      <c r="D102" t="s">
+      <c r="E102" t="s">
+        <v>383</v>
+      </c>
+      <c r="F102" t="s">
+        <v>7</v>
+      </c>
+      <c r="G102" t="s">
         <v>422</v>
-      </c>
-      <c r="E102" t="s">
-        <v>384</v>
-      </c>
-      <c r="F102" t="s">
-        <v>7</v>
-      </c>
-      <c r="G102" t="s">
-        <v>423</v>
       </c>
       <c r="H102" t="s">
         <v>11</v>
@@ -4894,22 +4888,22 @@
     </row>
     <row r="103" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A103" t="s">
-        <v>424</v>
+        <v>423</v>
       </c>
       <c r="C103" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="D103" t="s">
+        <v>421</v>
+      </c>
+      <c r="E103" t="s">
+        <v>383</v>
+      </c>
+      <c r="F103" t="s">
+        <v>7</v>
+      </c>
+      <c r="G103" t="s">
         <v>422</v>
-      </c>
-      <c r="E103" t="s">
-        <v>384</v>
-      </c>
-      <c r="F103" t="s">
-        <v>7</v>
-      </c>
-      <c r="G103" t="s">
-        <v>423</v>
       </c>
       <c r="H103" t="s">
         <v>11</v>
@@ -4917,22 +4911,22 @@
     </row>
     <row r="104" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A104" t="s">
-        <v>425</v>
+        <v>424</v>
       </c>
       <c r="C104" t="s">
         <v>72</v>
       </c>
       <c r="D104" t="s">
+        <v>425</v>
+      </c>
+      <c r="E104" t="s">
         <v>426</v>
       </c>
-      <c r="E104" t="s">
+      <c r="F104" t="s">
         <v>427</v>
       </c>
-      <c r="F104" t="s">
+      <c r="G104" t="s">
         <v>428</v>
-      </c>
-      <c r="G104" t="s">
-        <v>429</v>
       </c>
       <c r="H104" t="s">
         <v>11</v>
@@ -4940,22 +4934,22 @@
     </row>
     <row r="105" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A105" t="s">
-        <v>430</v>
+        <v>429</v>
       </c>
       <c r="C105" t="s">
         <v>10</v>
       </c>
       <c r="D105" t="s">
+        <v>430</v>
+      </c>
+      <c r="E105" t="s">
         <v>431</v>
       </c>
-      <c r="E105" t="s">
+      <c r="F105" t="s">
+        <v>7</v>
+      </c>
+      <c r="G105" t="s">
         <v>432</v>
-      </c>
-      <c r="F105" t="s">
-        <v>7</v>
-      </c>
-      <c r="G105" t="s">
-        <v>433</v>
       </c>
       <c r="H105" t="s">
         <v>11</v>
@@ -4963,22 +4957,22 @@
     </row>
     <row r="106" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A106" t="s">
-        <v>434</v>
+        <v>433</v>
       </c>
       <c r="C106" t="s">
         <v>64</v>
       </c>
       <c r="D106" t="s">
+        <v>434</v>
+      </c>
+      <c r="E106" t="s">
         <v>435</v>
       </c>
-      <c r="E106" t="s">
+      <c r="F106" t="s">
+        <v>7</v>
+      </c>
+      <c r="G106" t="s">
         <v>436</v>
-      </c>
-      <c r="F106" t="s">
-        <v>7</v>
-      </c>
-      <c r="G106" t="s">
-        <v>437</v>
       </c>
       <c r="H106" t="s">
         <v>11</v>
@@ -4986,22 +4980,22 @@
     </row>
     <row r="107" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A107" t="s">
-        <v>438</v>
+        <v>437</v>
       </c>
       <c r="C107" t="s">
         <v>20</v>
       </c>
       <c r="D107" t="s">
+        <v>438</v>
+      </c>
+      <c r="E107" t="s">
         <v>439</v>
       </c>
-      <c r="E107" t="s">
+      <c r="F107" t="s">
         <v>440</v>
       </c>
-      <c r="F107" t="s">
+      <c r="G107" t="s">
         <v>441</v>
-      </c>
-      <c r="G107" t="s">
-        <v>442</v>
       </c>
       <c r="H107" t="s">
         <v>11</v>
@@ -5009,22 +5003,22 @@
     </row>
     <row r="108" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A108" t="s">
-        <v>443</v>
+        <v>442</v>
       </c>
       <c r="C108" t="s">
         <v>19</v>
       </c>
       <c r="D108" t="s">
+        <v>443</v>
+      </c>
+      <c r="E108" t="s">
         <v>444</v>
       </c>
-      <c r="E108" t="s">
+      <c r="F108" t="s">
         <v>445</v>
       </c>
-      <c r="F108" t="s">
+      <c r="G108" t="s">
         <v>446</v>
-      </c>
-      <c r="G108" t="s">
-        <v>447</v>
       </c>
       <c r="H108" t="s">
         <v>11</v>
@@ -5032,19 +5026,19 @@
     </row>
     <row r="109" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A109" t="s">
-        <v>448</v>
+        <v>447</v>
       </c>
       <c r="C109" t="s">
         <v>19</v>
       </c>
       <c r="D109" t="s">
-        <v>449</v>
+        <v>448</v>
       </c>
       <c r="E109" t="s">
+        <v>444</v>
+      </c>
+      <c r="F109" t="s">
         <v>445</v>
-      </c>
-      <c r="F109" t="s">
-        <v>446</v>
       </c>
       <c r="G109" t="s">
         <v>59</v>
@@ -5055,22 +5049,22 @@
     </row>
     <row r="110" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A110" t="s">
-        <v>450</v>
+        <v>449</v>
       </c>
       <c r="C110" t="s">
         <v>18</v>
       </c>
       <c r="D110" t="s">
+        <v>450</v>
+      </c>
+      <c r="E110" t="s">
         <v>451</v>
       </c>
-      <c r="E110" t="s">
+      <c r="F110" t="s">
+        <v>415</v>
+      </c>
+      <c r="G110" t="s">
         <v>452</v>
-      </c>
-      <c r="F110" t="s">
-        <v>416</v>
-      </c>
-      <c r="G110" t="s">
-        <v>453</v>
       </c>
       <c r="H110" t="s">
         <v>11</v>
@@ -5078,13 +5072,13 @@
     </row>
     <row r="111" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A111" t="s">
-        <v>454</v>
+        <v>453</v>
       </c>
       <c r="C111" t="s">
         <v>50</v>
       </c>
       <c r="D111" t="s">
-        <v>455</v>
+        <v>454</v>
       </c>
       <c r="E111" t="s">
         <v>81</v>
@@ -5093,7 +5087,7 @@
         <v>82</v>
       </c>
       <c r="G111" t="s">
-        <v>456</v>
+        <v>455</v>
       </c>
       <c r="H111" t="s">
         <v>11</v>
@@ -5101,16 +5095,16 @@
     </row>
     <row r="112" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A112" t="s">
-        <v>457</v>
+        <v>456</v>
       </c>
       <c r="C112" t="s">
         <v>16</v>
       </c>
       <c r="D112" t="s">
+        <v>457</v>
+      </c>
+      <c r="E112" t="s">
         <v>458</v>
-      </c>
-      <c r="E112" t="s">
-        <v>459</v>
       </c>
       <c r="F112" t="s">
         <v>7</v>
@@ -5124,22 +5118,22 @@
     </row>
     <row r="113" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A113" t="s">
-        <v>460</v>
+        <v>459</v>
       </c>
       <c r="C113" t="s">
         <v>33</v>
       </c>
       <c r="D113" t="s">
+        <v>460</v>
+      </c>
+      <c r="E113" t="s">
         <v>461</v>
       </c>
-      <c r="E113" t="s">
+      <c r="F113" t="s">
+        <v>7</v>
+      </c>
+      <c r="G113" t="s">
         <v>462</v>
-      </c>
-      <c r="F113" t="s">
-        <v>7</v>
-      </c>
-      <c r="G113" t="s">
-        <v>463</v>
       </c>
       <c r="H113" t="s">
         <v>11</v>
@@ -5147,13 +5141,13 @@
     </row>
     <row r="114" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A114" t="s">
-        <v>464</v>
+        <v>463</v>
       </c>
       <c r="C114" t="s">
         <v>9</v>
       </c>
       <c r="D114" t="s">
-        <v>465</v>
+        <v>464</v>
       </c>
       <c r="E114" t="s">
         <v>26</v>
@@ -5162,7 +5156,7 @@
         <v>27</v>
       </c>
       <c r="G114" t="s">
-        <v>466</v>
+        <v>465</v>
       </c>
       <c r="H114" t="s">
         <v>11</v>
@@ -5170,22 +5164,22 @@
     </row>
     <row r="115" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A115" t="s">
-        <v>467</v>
+        <v>466</v>
       </c>
       <c r="C115" t="s">
         <v>43</v>
       </c>
       <c r="D115" t="s">
+        <v>467</v>
+      </c>
+      <c r="E115" t="s">
+        <v>358</v>
+      </c>
+      <c r="F115" t="s">
+        <v>7</v>
+      </c>
+      <c r="G115" t="s">
         <v>468</v>
-      </c>
-      <c r="E115" t="s">
-        <v>359</v>
-      </c>
-      <c r="F115" t="s">
-        <v>7</v>
-      </c>
-      <c r="G115" t="s">
-        <v>469</v>
       </c>
       <c r="H115" t="s">
         <v>11</v>
@@ -5193,22 +5187,22 @@
     </row>
     <row r="116" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A116" t="s">
+        <v>469</v>
+      </c>
+      <c r="C116" t="s">
+        <v>408</v>
+      </c>
+      <c r="D116" t="s">
         <v>470</v>
       </c>
-      <c r="C116" t="s">
-        <v>409</v>
-      </c>
-      <c r="D116" t="s">
+      <c r="E116" t="s">
+        <v>410</v>
+      </c>
+      <c r="F116" t="s">
+        <v>7</v>
+      </c>
+      <c r="G116" t="s">
         <v>471</v>
-      </c>
-      <c r="E116" t="s">
-        <v>411</v>
-      </c>
-      <c r="F116" t="s">
-        <v>7</v>
-      </c>
-      <c r="G116" t="s">
-        <v>472</v>
       </c>
       <c r="H116" t="s">
         <v>11</v>
@@ -5216,13 +5210,13 @@
     </row>
     <row r="117" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A117" t="s">
-        <v>473</v>
+        <v>472</v>
       </c>
       <c r="C117" t="s">
         <v>17</v>
       </c>
       <c r="D117" t="s">
-        <v>474</v>
+        <v>473</v>
       </c>
       <c r="E117" t="s">
         <v>60</v>
@@ -5231,7 +5225,7 @@
         <v>61</v>
       </c>
       <c r="G117" t="s">
-        <v>475</v>
+        <v>474</v>
       </c>
       <c r="H117" t="s">
         <v>11</v>
@@ -5239,22 +5233,22 @@
     </row>
     <row r="118" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A118" t="s">
-        <v>476</v>
+        <v>475</v>
       </c>
       <c r="C118" t="s">
         <v>17</v>
       </c>
       <c r="D118" t="s">
+        <v>476</v>
+      </c>
+      <c r="E118" t="s">
         <v>477</v>
       </c>
-      <c r="E118" t="s">
+      <c r="F118" t="s">
         <v>478</v>
       </c>
-      <c r="F118" t="s">
+      <c r="G118" t="s">
         <v>479</v>
-      </c>
-      <c r="G118" t="s">
-        <v>480</v>
       </c>
       <c r="H118" t="s">
         <v>11</v>
@@ -5262,22 +5256,22 @@
     </row>
     <row r="119" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A119" t="s">
-        <v>481</v>
+        <v>480</v>
       </c>
       <c r="C119" t="s">
         <v>17</v>
       </c>
       <c r="D119" t="s">
+        <v>476</v>
+      </c>
+      <c r="E119" t="s">
         <v>477</v>
       </c>
-      <c r="E119" t="s">
+      <c r="F119" t="s">
         <v>478</v>
       </c>
-      <c r="F119" t="s">
+      <c r="G119" t="s">
         <v>479</v>
-      </c>
-      <c r="G119" t="s">
-        <v>480</v>
       </c>
       <c r="H119" t="s">
         <v>11</v>
@@ -5285,22 +5279,22 @@
     </row>
     <row r="120" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A120" t="s">
-        <v>482</v>
+        <v>481</v>
       </c>
       <c r="C120" t="s">
         <v>17</v>
       </c>
       <c r="D120" t="s">
+        <v>476</v>
+      </c>
+      <c r="E120" t="s">
         <v>477</v>
       </c>
-      <c r="E120" t="s">
+      <c r="F120" t="s">
         <v>478</v>
       </c>
-      <c r="F120" t="s">
+      <c r="G120" t="s">
         <v>479</v>
-      </c>
-      <c r="G120" t="s">
-        <v>480</v>
       </c>
       <c r="H120" t="s">
         <v>11</v>
@@ -5308,22 +5302,22 @@
     </row>
     <row r="121" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A121" t="s">
-        <v>483</v>
+        <v>482</v>
       </c>
       <c r="C121" t="s">
         <v>25</v>
       </c>
       <c r="D121" t="s">
+        <v>483</v>
+      </c>
+      <c r="E121" t="s">
+        <v>169</v>
+      </c>
+      <c r="F121" t="s">
+        <v>7</v>
+      </c>
+      <c r="G121" t="s">
         <v>484</v>
-      </c>
-      <c r="E121" t="s">
-        <v>170</v>
-      </c>
-      <c r="F121" t="s">
-        <v>7</v>
-      </c>
-      <c r="G121" t="s">
-        <v>485</v>
       </c>
       <c r="H121" t="s">
         <v>11</v>
@@ -5331,13 +5325,13 @@
     </row>
     <row r="122" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A122" t="s">
-        <v>486</v>
+        <v>485</v>
       </c>
       <c r="C122" t="s">
         <v>18</v>
       </c>
       <c r="D122" t="s">
-        <v>487</v>
+        <v>486</v>
       </c>
       <c r="E122" t="s">
         <v>14</v>
@@ -5346,7 +5340,7 @@
         <v>15</v>
       </c>
       <c r="G122" t="s">
-        <v>488</v>
+        <v>487</v>
       </c>
       <c r="H122" t="s">
         <v>11</v>
@@ -5354,22 +5348,22 @@
     </row>
     <row r="123" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A123" t="s">
-        <v>489</v>
+        <v>488</v>
       </c>
       <c r="C123" t="s">
         <v>72</v>
       </c>
       <c r="D123" t="s">
+        <v>489</v>
+      </c>
+      <c r="E123" t="s">
         <v>490</v>
       </c>
-      <c r="E123" t="s">
+      <c r="F123" t="s">
+        <v>7</v>
+      </c>
+      <c r="G123" t="s">
         <v>491</v>
-      </c>
-      <c r="F123" t="s">
-        <v>7</v>
-      </c>
-      <c r="G123" t="s">
-        <v>492</v>
       </c>
       <c r="H123" t="s">
         <v>11</v>
@@ -5377,19 +5371,19 @@
     </row>
     <row r="124" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A124" t="s">
-        <v>493</v>
+        <v>492</v>
       </c>
       <c r="C124" t="s">
         <v>17</v>
       </c>
       <c r="D124" t="s">
+        <v>493</v>
+      </c>
+      <c r="E124" t="s">
         <v>494</v>
       </c>
-      <c r="E124" t="s">
+      <c r="F124" t="s">
         <v>495</v>
-      </c>
-      <c r="F124" t="s">
-        <v>496</v>
       </c>
       <c r="G124" t="s">
         <v>89</v>
@@ -5400,22 +5394,22 @@
     </row>
     <row r="125" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A125" t="s">
-        <v>497</v>
+        <v>496</v>
       </c>
       <c r="C125" t="s">
         <v>17</v>
       </c>
       <c r="D125" t="s">
+        <v>497</v>
+      </c>
+      <c r="E125" t="s">
         <v>498</v>
       </c>
-      <c r="E125" t="s">
+      <c r="F125" t="s">
         <v>499</v>
       </c>
-      <c r="F125" t="s">
+      <c r="G125" t="s">
         <v>500</v>
-      </c>
-      <c r="G125" t="s">
-        <v>501</v>
       </c>
       <c r="H125" t="s">
         <v>11</v>
@@ -5423,22 +5417,22 @@
     </row>
     <row r="126" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A126" t="s">
-        <v>502</v>
+        <v>501</v>
       </c>
       <c r="C126" t="s">
         <v>17</v>
       </c>
       <c r="D126" t="s">
+        <v>497</v>
+      </c>
+      <c r="E126" t="s">
         <v>498</v>
       </c>
-      <c r="E126" t="s">
+      <c r="F126" t="s">
         <v>499</v>
       </c>
-      <c r="F126" t="s">
+      <c r="G126" t="s">
         <v>500</v>
-      </c>
-      <c r="G126" t="s">
-        <v>501</v>
       </c>
       <c r="H126" t="s">
         <v>11</v>
@@ -5446,22 +5440,22 @@
     </row>
     <row r="127" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A127" t="s">
-        <v>503</v>
+        <v>502</v>
       </c>
       <c r="C127" t="s">
         <v>19</v>
       </c>
       <c r="D127" t="s">
+        <v>503</v>
+      </c>
+      <c r="E127" t="s">
         <v>504</v>
       </c>
-      <c r="E127" t="s">
+      <c r="F127" t="s">
+        <v>7</v>
+      </c>
+      <c r="G127" t="s">
         <v>505</v>
-      </c>
-      <c r="F127" t="s">
-        <v>7</v>
-      </c>
-      <c r="G127" t="s">
-        <v>506</v>
       </c>
       <c r="H127" t="s">
         <v>11</v>
@@ -5469,13 +5463,13 @@
     </row>
     <row r="128" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A128" t="s">
+        <v>506</v>
+      </c>
+      <c r="C128" t="s">
+        <v>393</v>
+      </c>
+      <c r="D128" t="s">
         <v>507</v>
-      </c>
-      <c r="C128" t="s">
-        <v>394</v>
-      </c>
-      <c r="D128" t="s">
-        <v>508</v>
       </c>
       <c r="E128" t="s">
         <v>36</v>
@@ -5484,7 +5478,7 @@
         <v>7</v>
       </c>
       <c r="G128" t="s">
-        <v>509</v>
+        <v>508</v>
       </c>
       <c r="H128" t="s">
         <v>11</v>
@@ -5492,22 +5486,22 @@
     </row>
     <row r="129" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A129" t="s">
-        <v>510</v>
+        <v>509</v>
       </c>
       <c r="C129" t="s">
         <v>72</v>
       </c>
       <c r="D129" t="s">
+        <v>510</v>
+      </c>
+      <c r="E129" t="s">
         <v>511</v>
       </c>
-      <c r="E129" t="s">
+      <c r="F129" t="s">
         <v>512</v>
       </c>
-      <c r="F129" t="s">
+      <c r="G129" t="s">
         <v>513</v>
-      </c>
-      <c r="G129" t="s">
-        <v>514</v>
       </c>
       <c r="H129" t="s">
         <v>11</v>
@@ -5515,22 +5509,22 @@
     </row>
     <row r="130" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A130" t="s">
-        <v>515</v>
+        <v>514</v>
       </c>
       <c r="C130" t="s">
         <v>17</v>
       </c>
       <c r="D130" t="s">
+        <v>515</v>
+      </c>
+      <c r="E130" t="s">
         <v>516</v>
       </c>
-      <c r="E130" t="s">
+      <c r="F130" t="s">
         <v>517</v>
       </c>
-      <c r="F130" t="s">
+      <c r="G130" t="s">
         <v>518</v>
-      </c>
-      <c r="G130" t="s">
-        <v>519</v>
       </c>
       <c r="H130" t="s">
         <v>11</v>
@@ -5538,22 +5532,22 @@
     </row>
     <row r="131" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A131" t="s">
-        <v>520</v>
+        <v>519</v>
       </c>
       <c r="C131" t="s">
         <v>20</v>
       </c>
       <c r="D131" t="s">
+        <v>520</v>
+      </c>
+      <c r="E131" t="s">
         <v>521</v>
       </c>
-      <c r="E131" t="s">
+      <c r="F131" t="s">
+        <v>7</v>
+      </c>
+      <c r="G131" t="s">
         <v>522</v>
-      </c>
-      <c r="F131" t="s">
-        <v>7</v>
-      </c>
-      <c r="G131" t="s">
-        <v>523</v>
       </c>
       <c r="H131" t="s">
         <v>11</v>
@@ -5561,22 +5555,22 @@
     </row>
     <row r="132" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A132" t="s">
+        <v>523</v>
+      </c>
+      <c r="C132" t="s">
+        <v>408</v>
+      </c>
+      <c r="D132" t="s">
         <v>524</v>
       </c>
-      <c r="C132" t="s">
-        <v>409</v>
-      </c>
-      <c r="D132" t="s">
+      <c r="E132" t="s">
         <v>525</v>
       </c>
-      <c r="E132" t="s">
+      <c r="F132" t="s">
+        <v>7</v>
+      </c>
+      <c r="G132" t="s">
         <v>526</v>
-      </c>
-      <c r="F132" t="s">
-        <v>7</v>
-      </c>
-      <c r="G132" t="s">
-        <v>527</v>
       </c>
       <c r="H132" t="s">
         <v>11</v>
@@ -5584,22 +5578,22 @@
     </row>
     <row r="133" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A133" t="s">
+        <v>527</v>
+      </c>
+      <c r="C133" t="s">
+        <v>393</v>
+      </c>
+      <c r="D133" t="s">
         <v>528</v>
       </c>
-      <c r="C133" t="s">
-        <v>394</v>
-      </c>
-      <c r="D133" t="s">
+      <c r="E133" t="s">
+        <v>395</v>
+      </c>
+      <c r="F133" t="s">
+        <v>7</v>
+      </c>
+      <c r="G133" t="s">
         <v>529</v>
-      </c>
-      <c r="E133" t="s">
-        <v>396</v>
-      </c>
-      <c r="F133" t="s">
-        <v>7</v>
-      </c>
-      <c r="G133" t="s">
-        <v>530</v>
       </c>
       <c r="H133" t="s">
         <v>11</v>
@@ -5607,13 +5601,13 @@
     </row>
     <row r="134" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A134" t="s">
-        <v>531</v>
+        <v>530</v>
       </c>
       <c r="C134" t="s">
         <v>20</v>
       </c>
       <c r="D134" t="s">
-        <v>532</v>
+        <v>531</v>
       </c>
       <c r="E134" t="s">
         <v>49</v>
@@ -5622,7 +5616,7 @@
         <v>7</v>
       </c>
       <c r="G134" t="s">
-        <v>533</v>
+        <v>532</v>
       </c>
       <c r="H134" t="s">
         <v>11</v>
@@ -5630,22 +5624,22 @@
     </row>
     <row r="135" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A135" t="s">
+        <v>533</v>
+      </c>
+      <c r="C135" t="s">
+        <v>408</v>
+      </c>
+      <c r="D135" t="s">
         <v>534</v>
       </c>
-      <c r="C135" t="s">
-        <v>409</v>
-      </c>
-      <c r="D135" t="s">
+      <c r="E135" t="s">
         <v>535</v>
       </c>
-      <c r="E135" t="s">
+      <c r="F135" t="s">
+        <v>7</v>
+      </c>
+      <c r="G135" t="s">
         <v>536</v>
-      </c>
-      <c r="F135" t="s">
-        <v>7</v>
-      </c>
-      <c r="G135" t="s">
-        <v>537</v>
       </c>
       <c r="H135" t="s">
         <v>11</v>
@@ -5653,22 +5647,22 @@
     </row>
     <row r="136" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A136" t="s">
-        <v>538</v>
+        <v>537</v>
       </c>
       <c r="C136" t="s">
         <v>50</v>
       </c>
       <c r="D136" t="s">
+        <v>538</v>
+      </c>
+      <c r="E136" t="s">
         <v>539</v>
       </c>
-      <c r="E136" t="s">
+      <c r="F136" t="s">
         <v>540</v>
       </c>
-      <c r="F136" t="s">
-        <v>541</v>
-      </c>
       <c r="G136" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="H136" t="s">
         <v>11</v>
@@ -5676,13 +5670,13 @@
     </row>
     <row r="137" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A137" t="s">
-        <v>542</v>
+        <v>541</v>
       </c>
       <c r="C137" t="s">
         <v>72</v>
       </c>
       <c r="D137" t="s">
-        <v>543</v>
+        <v>542</v>
       </c>
       <c r="E137" t="s">
         <v>73</v>
@@ -5691,7 +5685,7 @@
         <v>7</v>
       </c>
       <c r="G137" t="s">
-        <v>544</v>
+        <v>543</v>
       </c>
       <c r="H137" t="s">
         <v>11</v>
@@ -5699,13 +5693,13 @@
     </row>
     <row r="138" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A138" t="s">
+        <v>544</v>
+      </c>
+      <c r="C138" t="s">
+        <v>135</v>
+      </c>
+      <c r="D138" t="s">
         <v>545</v>
-      </c>
-      <c r="C138" t="s">
-        <v>136</v>
-      </c>
-      <c r="D138" t="s">
-        <v>546</v>
       </c>
       <c r="E138" t="s">
         <v>57</v>
@@ -5714,7 +5708,7 @@
         <v>58</v>
       </c>
       <c r="G138" t="s">
-        <v>547</v>
+        <v>546</v>
       </c>
       <c r="H138" t="s">
         <v>11</v>
@@ -5722,22 +5716,22 @@
     </row>
     <row r="139" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A139" t="s">
-        <v>548</v>
+        <v>547</v>
       </c>
       <c r="C139" t="s">
         <v>13</v>
       </c>
       <c r="D139" t="s">
+        <v>548</v>
+      </c>
+      <c r="E139" t="s">
         <v>549</v>
       </c>
-      <c r="E139" t="s">
+      <c r="F139" t="s">
+        <v>7</v>
+      </c>
+      <c r="G139" t="s">
         <v>550</v>
-      </c>
-      <c r="F139" t="s">
-        <v>7</v>
-      </c>
-      <c r="G139" t="s">
-        <v>551</v>
       </c>
       <c r="H139" t="s">
         <v>11</v>
@@ -5745,13 +5739,13 @@
     </row>
     <row r="140" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A140" t="s">
-        <v>552</v>
+        <v>551</v>
       </c>
       <c r="C140" t="s">
         <v>17</v>
       </c>
       <c r="D140" t="s">
-        <v>553</v>
+        <v>552</v>
       </c>
       <c r="E140" t="s">
         <v>60</v>
@@ -5760,7 +5754,7 @@
         <v>61</v>
       </c>
       <c r="G140" t="s">
-        <v>554</v>
+        <v>553</v>
       </c>
       <c r="H140" t="s">
         <v>11</v>
@@ -5768,13 +5762,13 @@
     </row>
     <row r="141" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A141" t="s">
-        <v>555</v>
+        <v>554</v>
       </c>
       <c r="C141" t="s">
         <v>33</v>
       </c>
       <c r="D141" t="s">
-        <v>556</v>
+        <v>555</v>
       </c>
       <c r="E141" t="s">
         <v>37</v>
@@ -5783,7 +5777,7 @@
         <v>38</v>
       </c>
       <c r="G141" t="s">
-        <v>557</v>
+        <v>556</v>
       </c>
       <c r="H141" t="s">
         <v>11</v>
@@ -5791,13 +5785,13 @@
     </row>
     <row r="142" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A142" t="s">
-        <v>558</v>
+        <v>557</v>
       </c>
       <c r="C142" t="s">
         <v>50</v>
       </c>
       <c r="D142" t="s">
-        <v>559</v>
+        <v>558</v>
       </c>
       <c r="E142" t="s">
         <v>78</v>
@@ -5806,7 +5800,7 @@
         <v>79</v>
       </c>
       <c r="G142" t="s">
-        <v>560</v>
+        <v>559</v>
       </c>
       <c r="H142" t="s">
         <v>11</v>
@@ -5814,22 +5808,22 @@
     </row>
     <row r="143" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A143" t="s">
+        <v>560</v>
+      </c>
+      <c r="C143" t="s">
+        <v>135</v>
+      </c>
+      <c r="D143" t="s">
         <v>561</v>
       </c>
-      <c r="C143" t="s">
-        <v>136</v>
-      </c>
-      <c r="D143" t="s">
+      <c r="E143" t="s">
+        <v>353</v>
+      </c>
+      <c r="F143" t="s">
+        <v>354</v>
+      </c>
+      <c r="G143" t="s">
         <v>562</v>
-      </c>
-      <c r="E143" t="s">
-        <v>354</v>
-      </c>
-      <c r="F143" t="s">
-        <v>355</v>
-      </c>
-      <c r="G143" t="s">
-        <v>563</v>
       </c>
       <c r="H143" t="s">
         <v>12</v>
@@ -5837,13 +5831,13 @@
     </row>
     <row r="144" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A144" t="s">
+        <v>563</v>
+      </c>
+      <c r="C144" t="s">
+        <v>135</v>
+      </c>
+      <c r="D144" t="s">
         <v>564</v>
-      </c>
-      <c r="C144" t="s">
-        <v>136</v>
-      </c>
-      <c r="D144" t="s">
-        <v>565</v>
       </c>
       <c r="E144" t="s">
         <v>57</v>
@@ -5860,22 +5854,22 @@
     </row>
     <row r="145" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A145" t="s">
-        <v>566</v>
+        <v>565</v>
       </c>
       <c r="C145" t="s">
         <v>19</v>
       </c>
       <c r="D145" t="s">
+        <v>566</v>
+      </c>
+      <c r="E145" t="s">
         <v>567</v>
       </c>
-      <c r="E145" t="s">
+      <c r="F145" t="s">
+        <v>7</v>
+      </c>
+      <c r="G145" t="s">
         <v>568</v>
-      </c>
-      <c r="F145" t="s">
-        <v>7</v>
-      </c>
-      <c r="G145" t="s">
-        <v>569</v>
       </c>
       <c r="H145" t="s">
         <v>12</v>
@@ -5883,22 +5877,22 @@
     </row>
     <row r="146" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A146" t="s">
-        <v>570</v>
+        <v>569</v>
       </c>
       <c r="C146" t="s">
         <v>17</v>
       </c>
       <c r="D146" t="s">
+        <v>570</v>
+      </c>
+      <c r="E146" t="s">
         <v>571</v>
       </c>
-      <c r="E146" t="s">
+      <c r="F146" t="s">
         <v>572</v>
       </c>
-      <c r="F146" t="s">
+      <c r="G146" t="s">
         <v>573</v>
-      </c>
-      <c r="G146" t="s">
-        <v>574</v>
       </c>
       <c r="H146" t="s">
         <v>12</v>
@@ -5906,22 +5900,22 @@
     </row>
     <row r="147" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A147" t="s">
-        <v>575</v>
+        <v>574</v>
       </c>
       <c r="C147" t="s">
         <v>16</v>
       </c>
       <c r="D147" t="s">
+        <v>575</v>
+      </c>
+      <c r="E147" t="s">
         <v>576</v>
       </c>
-      <c r="E147" t="s">
+      <c r="F147" t="s">
+        <v>7</v>
+      </c>
+      <c r="G147" t="s">
         <v>577</v>
-      </c>
-      <c r="F147" t="s">
-        <v>7</v>
-      </c>
-      <c r="G147" t="s">
-        <v>578</v>
       </c>
       <c r="H147" t="s">
         <v>12</v>
@@ -5929,22 +5923,22 @@
     </row>
     <row r="148" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A148" t="s">
-        <v>579</v>
+        <v>578</v>
       </c>
       <c r="C148" t="s">
         <v>22</v>
       </c>
       <c r="D148" t="s">
+        <v>579</v>
+      </c>
+      <c r="E148" t="s">
         <v>580</v>
       </c>
-      <c r="E148" t="s">
+      <c r="F148" t="s">
+        <v>7</v>
+      </c>
+      <c r="G148" t="s">
         <v>581</v>
-      </c>
-      <c r="F148" t="s">
-        <v>7</v>
-      </c>
-      <c r="G148" t="s">
-        <v>582</v>
       </c>
       <c r="H148" t="s">
         <v>12</v>
@@ -5952,22 +5946,22 @@
     </row>
     <row r="149" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A149" t="s">
+        <v>582</v>
+      </c>
+      <c r="C149" t="s">
+        <v>393</v>
+      </c>
+      <c r="D149" t="s">
         <v>583</v>
       </c>
-      <c r="C149" t="s">
-        <v>394</v>
-      </c>
-      <c r="D149" t="s">
+      <c r="E149" t="s">
         <v>584</v>
       </c>
-      <c r="E149" t="s">
+      <c r="F149" t="s">
+        <v>7</v>
+      </c>
+      <c r="G149" t="s">
         <v>585</v>
-      </c>
-      <c r="F149" t="s">
-        <v>7</v>
-      </c>
-      <c r="G149" t="s">
-        <v>586</v>
       </c>
       <c r="H149" t="s">
         <v>12</v>
@@ -5975,22 +5969,22 @@
     </row>
     <row r="150" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A150" t="s">
-        <v>587</v>
+        <v>586</v>
       </c>
       <c r="C150" t="s">
         <v>33</v>
       </c>
       <c r="D150" t="s">
+        <v>587</v>
+      </c>
+      <c r="E150" t="s">
         <v>588</v>
       </c>
-      <c r="E150" t="s">
+      <c r="F150" t="s">
+        <v>7</v>
+      </c>
+      <c r="G150" t="s">
         <v>589</v>
-      </c>
-      <c r="F150" t="s">
-        <v>7</v>
-      </c>
-      <c r="G150" t="s">
-        <v>590</v>
       </c>
       <c r="H150" t="s">
         <v>12</v>
@@ -5998,22 +5992,22 @@
     </row>
     <row r="151" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A151" t="s">
-        <v>591</v>
+        <v>590</v>
       </c>
       <c r="C151" t="s">
         <v>33</v>
       </c>
       <c r="D151" t="s">
+        <v>587</v>
+      </c>
+      <c r="E151" t="s">
         <v>588</v>
       </c>
-      <c r="E151" t="s">
+      <c r="F151" t="s">
+        <v>7</v>
+      </c>
+      <c r="G151" t="s">
         <v>589</v>
-      </c>
-      <c r="F151" t="s">
-        <v>7</v>
-      </c>
-      <c r="G151" t="s">
-        <v>590</v>
       </c>
       <c r="H151" t="s">
         <v>12</v>
@@ -6021,22 +6015,22 @@
     </row>
     <row r="152" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A152" t="s">
-        <v>592</v>
+        <v>591</v>
       </c>
       <c r="C152" t="s">
         <v>23</v>
       </c>
       <c r="D152" t="s">
+        <v>592</v>
+      </c>
+      <c r="E152" t="s">
         <v>593</v>
       </c>
-      <c r="E152" t="s">
-        <v>594</v>
-      </c>
       <c r="F152" t="s">
         <v>7</v>
       </c>
       <c r="G152" t="s">
-        <v>229</v>
+        <v>228</v>
       </c>
       <c r="H152" t="s">
         <v>12</v>
@@ -6044,22 +6038,22 @@
     </row>
     <row r="153" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A153" t="s">
-        <v>595</v>
+        <v>594</v>
       </c>
       <c r="C153" t="s">
         <v>72</v>
       </c>
       <c r="D153" t="s">
+        <v>595</v>
+      </c>
+      <c r="E153" t="s">
         <v>596</v>
       </c>
-      <c r="E153" t="s">
+      <c r="F153" t="s">
+        <v>7</v>
+      </c>
+      <c r="G153" t="s">
         <v>597</v>
-      </c>
-      <c r="F153" t="s">
-        <v>7</v>
-      </c>
-      <c r="G153" t="s">
-        <v>598</v>
       </c>
       <c r="H153" t="s">
         <v>12</v>
@@ -6067,22 +6061,22 @@
     </row>
     <row r="154" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A154" t="s">
-        <v>599</v>
+        <v>598</v>
       </c>
       <c r="C154" t="s">
         <v>64</v>
       </c>
       <c r="D154" t="s">
+        <v>599</v>
+      </c>
+      <c r="E154" t="s">
+        <v>203</v>
+      </c>
+      <c r="F154" t="s">
+        <v>7</v>
+      </c>
+      <c r="G154" t="s">
         <v>600</v>
-      </c>
-      <c r="E154" t="s">
-        <v>204</v>
-      </c>
-      <c r="F154" t="s">
-        <v>7</v>
-      </c>
-      <c r="G154" t="s">
-        <v>601</v>
       </c>
       <c r="H154" t="s">
         <v>12</v>
@@ -6090,22 +6084,22 @@
     </row>
     <row r="155" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A155" t="s">
-        <v>602</v>
+        <v>601</v>
       </c>
       <c r="C155" t="s">
         <v>25</v>
       </c>
       <c r="D155" t="s">
+        <v>602</v>
+      </c>
+      <c r="E155" t="s">
+        <v>169</v>
+      </c>
+      <c r="F155" t="s">
+        <v>7</v>
+      </c>
+      <c r="G155" t="s">
         <v>603</v>
-      </c>
-      <c r="E155" t="s">
-        <v>170</v>
-      </c>
-      <c r="F155" t="s">
-        <v>7</v>
-      </c>
-      <c r="G155" t="s">
-        <v>604</v>
       </c>
       <c r="H155" t="s">
         <v>12</v>
@@ -6113,22 +6107,22 @@
     </row>
     <row r="156" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A156" t="s">
-        <v>605</v>
+        <v>604</v>
       </c>
       <c r="C156" t="s">
         <v>25</v>
       </c>
       <c r="D156" t="s">
+        <v>602</v>
+      </c>
+      <c r="E156" t="s">
+        <v>169</v>
+      </c>
+      <c r="F156" t="s">
+        <v>7</v>
+      </c>
+      <c r="G156" t="s">
         <v>603</v>
-      </c>
-      <c r="E156" t="s">
-        <v>170</v>
-      </c>
-      <c r="F156" t="s">
-        <v>7</v>
-      </c>
-      <c r="G156" t="s">
-        <v>604</v>
       </c>
       <c r="H156" t="s">
         <v>12</v>
@@ -6136,13 +6130,13 @@
     </row>
     <row r="157" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A157" t="s">
-        <v>606</v>
+        <v>605</v>
       </c>
       <c r="C157" t="s">
         <v>18</v>
       </c>
       <c r="D157" t="s">
-        <v>607</v>
+        <v>606</v>
       </c>
       <c r="E157" t="s">
         <v>14</v>
@@ -6151,7 +6145,7 @@
         <v>15</v>
       </c>
       <c r="G157" t="s">
-        <v>608</v>
+        <v>607</v>
       </c>
       <c r="H157" t="s">
         <v>12</v>
@@ -6159,13 +6153,13 @@
     </row>
     <row r="158" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A158" t="s">
-        <v>609</v>
+        <v>608</v>
       </c>
       <c r="C158" t="s">
         <v>18</v>
       </c>
       <c r="D158" t="s">
-        <v>610</v>
+        <v>609</v>
       </c>
       <c r="E158" t="s">
         <v>14</v>
@@ -6174,7 +6168,7 @@
         <v>15</v>
       </c>
       <c r="G158" t="s">
-        <v>611</v>
+        <v>610</v>
       </c>
       <c r="H158" t="s">
         <v>12</v>
@@ -6182,22 +6176,22 @@
     </row>
     <row r="159" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A159" t="s">
+        <v>611</v>
+      </c>
+      <c r="C159" t="s">
+        <v>408</v>
+      </c>
+      <c r="D159" t="s">
         <v>612</v>
       </c>
-      <c r="C159" t="s">
-        <v>409</v>
-      </c>
-      <c r="D159" t="s">
+      <c r="E159" t="s">
+        <v>525</v>
+      </c>
+      <c r="F159" t="s">
+        <v>7</v>
+      </c>
+      <c r="G159" t="s">
         <v>613</v>
-      </c>
-      <c r="E159" t="s">
-        <v>526</v>
-      </c>
-      <c r="F159" t="s">
-        <v>7</v>
-      </c>
-      <c r="G159" t="s">
-        <v>614</v>
       </c>
       <c r="H159" t="s">
         <v>12</v>
@@ -6205,22 +6199,22 @@
     </row>
     <row r="160" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A160" t="s">
-        <v>615</v>
+        <v>614</v>
       </c>
       <c r="C160" t="s">
         <v>18</v>
       </c>
       <c r="D160" t="s">
+        <v>615</v>
+      </c>
+      <c r="E160" t="s">
+        <v>326</v>
+      </c>
+      <c r="F160" t="s">
+        <v>7</v>
+      </c>
+      <c r="G160" t="s">
         <v>616</v>
-      </c>
-      <c r="E160" t="s">
-        <v>327</v>
-      </c>
-      <c r="F160" t="s">
-        <v>7</v>
-      </c>
-      <c r="G160" t="s">
-        <v>617</v>
       </c>
       <c r="H160" t="s">
         <v>12</v>
@@ -6228,22 +6222,22 @@
     </row>
     <row r="161" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A161" t="s">
-        <v>618</v>
+        <v>617</v>
       </c>
       <c r="C161" t="s">
         <v>50</v>
       </c>
       <c r="D161" t="s">
+        <v>618</v>
+      </c>
+      <c r="E161" t="s">
         <v>619</v>
       </c>
-      <c r="E161" t="s">
+      <c r="F161" t="s">
         <v>620</v>
       </c>
-      <c r="F161" t="s">
+      <c r="G161" t="s">
         <v>621</v>
-      </c>
-      <c r="G161" t="s">
-        <v>622</v>
       </c>
       <c r="H161" t="s">
         <v>12</v>
@@ -6251,13 +6245,13 @@
     </row>
     <row r="162" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A162" t="s">
+        <v>622</v>
+      </c>
+      <c r="C162" t="s">
+        <v>135</v>
+      </c>
+      <c r="D162" t="s">
         <v>623</v>
-      </c>
-      <c r="C162" t="s">
-        <v>136</v>
-      </c>
-      <c r="D162" t="s">
-        <v>624</v>
       </c>
       <c r="E162" t="s">
         <v>30</v>
@@ -6266,7 +6260,7 @@
         <v>31</v>
       </c>
       <c r="G162" t="s">
-        <v>625</v>
+        <v>624</v>
       </c>
       <c r="H162" t="s">
         <v>12</v>
@@ -6274,22 +6268,22 @@
     </row>
     <row r="163" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A163" t="s">
-        <v>626</v>
+        <v>625</v>
       </c>
       <c r="C163" t="s">
         <v>13</v>
       </c>
       <c r="D163" t="s">
+        <v>626</v>
+      </c>
+      <c r="E163" t="s">
         <v>627</v>
       </c>
-      <c r="E163" t="s">
+      <c r="F163" t="s">
         <v>628</v>
       </c>
-      <c r="F163" t="s">
-        <v>629</v>
-      </c>
       <c r="G163" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="H163" t="s">
         <v>12</v>
@@ -6297,22 +6291,22 @@
     </row>
     <row r="164" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A164" t="s">
-        <v>630</v>
+        <v>629</v>
       </c>
       <c r="C164" t="s">
         <v>50</v>
       </c>
       <c r="D164" t="s">
+        <v>630</v>
+      </c>
+      <c r="E164" t="s">
         <v>631</v>
       </c>
-      <c r="E164" t="s">
+      <c r="F164" t="s">
         <v>632</v>
       </c>
-      <c r="F164" t="s">
-        <v>633</v>
-      </c>
       <c r="G164" t="s">
-        <v>378</v>
+        <v>377</v>
       </c>
       <c r="H164" t="s">
         <v>12</v>
@@ -6320,22 +6314,22 @@
     </row>
     <row r="165" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A165" t="s">
-        <v>634</v>
+        <v>633</v>
       </c>
       <c r="C165" t="s">
         <v>18</v>
       </c>
       <c r="D165" t="s">
+        <v>634</v>
+      </c>
+      <c r="E165" t="s">
+        <v>326</v>
+      </c>
+      <c r="F165" t="s">
+        <v>7</v>
+      </c>
+      <c r="G165" t="s">
         <v>635</v>
-      </c>
-      <c r="E165" t="s">
-        <v>327</v>
-      </c>
-      <c r="F165" t="s">
-        <v>7</v>
-      </c>
-      <c r="G165" t="s">
-        <v>636</v>
       </c>
       <c r="H165" t="s">
         <v>12</v>
@@ -6343,22 +6337,22 @@
     </row>
     <row r="166" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A166" t="s">
+        <v>636</v>
+      </c>
+      <c r="C166" t="s">
+        <v>147</v>
+      </c>
+      <c r="D166" t="s">
         <v>637</v>
       </c>
-      <c r="C166" t="s">
-        <v>148</v>
-      </c>
-      <c r="D166" t="s">
+      <c r="E166" t="s">
+        <v>276</v>
+      </c>
+      <c r="F166" t="s">
+        <v>7</v>
+      </c>
+      <c r="G166" t="s">
         <v>638</v>
-      </c>
-      <c r="E166" t="s">
-        <v>277</v>
-      </c>
-      <c r="F166" t="s">
-        <v>7</v>
-      </c>
-      <c r="G166" t="s">
-        <v>639</v>
       </c>
       <c r="H166" t="s">
         <v>12</v>
@@ -6366,22 +6360,22 @@
     </row>
     <row r="167" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A167" t="s">
+        <v>639</v>
+      </c>
+      <c r="C167" t="s">
+        <v>135</v>
+      </c>
+      <c r="D167" t="s">
         <v>640</v>
       </c>
-      <c r="C167" t="s">
-        <v>136</v>
-      </c>
-      <c r="D167" t="s">
-        <v>641</v>
-      </c>
       <c r="E167" t="s">
+        <v>353</v>
+      </c>
+      <c r="F167" t="s">
         <v>354</v>
       </c>
-      <c r="F167" t="s">
-        <v>355</v>
-      </c>
       <c r="G167" t="s">
-        <v>488</v>
+        <v>487</v>
       </c>
       <c r="H167" t="s">
         <v>12</v>
@@ -6389,22 +6383,22 @@
     </row>
     <row r="168" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A168" t="s">
-        <v>642</v>
+        <v>641</v>
       </c>
       <c r="C168" t="s">
         <v>25</v>
       </c>
       <c r="D168" t="s">
+        <v>642</v>
+      </c>
+      <c r="E168" t="s">
+        <v>169</v>
+      </c>
+      <c r="F168" t="s">
+        <v>7</v>
+      </c>
+      <c r="G168" t="s">
         <v>643</v>
-      </c>
-      <c r="E168" t="s">
-        <v>170</v>
-      </c>
-      <c r="F168" t="s">
-        <v>7</v>
-      </c>
-      <c r="G168" t="s">
-        <v>644</v>
       </c>
       <c r="H168" t="s">
         <v>12</v>
@@ -6412,22 +6406,22 @@
     </row>
     <row r="169" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A169" t="s">
-        <v>645</v>
+        <v>644</v>
       </c>
       <c r="C169" t="s">
         <v>25</v>
       </c>
       <c r="D169" t="s">
+        <v>642</v>
+      </c>
+      <c r="E169" t="s">
+        <v>169</v>
+      </c>
+      <c r="F169" t="s">
+        <v>7</v>
+      </c>
+      <c r="G169" t="s">
         <v>643</v>
-      </c>
-      <c r="E169" t="s">
-        <v>170</v>
-      </c>
-      <c r="F169" t="s">
-        <v>7</v>
-      </c>
-      <c r="G169" t="s">
-        <v>644</v>
       </c>
       <c r="H169" t="s">
         <v>12</v>
@@ -6435,22 +6429,22 @@
     </row>
     <row r="170" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A170" t="s">
+        <v>645</v>
+      </c>
+      <c r="C170" t="s">
+        <v>135</v>
+      </c>
+      <c r="D170" t="s">
         <v>646</v>
       </c>
-      <c r="C170" t="s">
-        <v>136</v>
-      </c>
-      <c r="D170" t="s">
+      <c r="E170" t="s">
         <v>647</v>
       </c>
-      <c r="E170" t="s">
+      <c r="F170" t="s">
         <v>648</v>
       </c>
-      <c r="F170" t="s">
+      <c r="G170" t="s">
         <v>649</v>
-      </c>
-      <c r="G170" t="s">
-        <v>650</v>
       </c>
       <c r="H170" t="s">
         <v>12</v>
@@ -6458,22 +6452,22 @@
     </row>
     <row r="171" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A171" t="s">
+        <v>650</v>
+      </c>
+      <c r="C171" t="s">
+        <v>43</v>
+      </c>
+      <c r="D171" t="s">
         <v>651</v>
       </c>
-      <c r="C171" t="s">
-        <v>13</v>
-      </c>
-      <c r="D171" t="s">
+      <c r="E171" t="s">
+        <v>28</v>
+      </c>
+      <c r="F171" t="s">
+        <v>7</v>
+      </c>
+      <c r="G171" t="s">
         <v>652</v>
-      </c>
-      <c r="E171" t="s">
-        <v>36</v>
-      </c>
-      <c r="F171" t="s">
-        <v>7</v>
-      </c>
-      <c r="G171" t="s">
-        <v>95</v>
       </c>
       <c r="H171" t="s">
         <v>12</v>
@@ -6484,19 +6478,19 @@
         <v>653</v>
       </c>
       <c r="C172" t="s">
-        <v>43</v>
+        <v>64</v>
       </c>
       <c r="D172" t="s">
         <v>654</v>
       </c>
       <c r="E172" t="s">
-        <v>28</v>
+        <v>655</v>
       </c>
       <c r="F172" t="s">
         <v>7</v>
       </c>
       <c r="G172" t="s">
-        <v>655</v>
+        <v>656</v>
       </c>
       <c r="H172" t="s">
         <v>12</v>
@@ -6504,22 +6498,22 @@
     </row>
     <row r="173" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A173" t="s">
-        <v>656</v>
+        <v>657</v>
       </c>
       <c r="C173" t="s">
-        <v>64</v>
+        <v>147</v>
       </c>
       <c r="D173" t="s">
-        <v>657</v>
+        <v>658</v>
       </c>
       <c r="E173" t="s">
-        <v>658</v>
+        <v>659</v>
       </c>
       <c r="F173" t="s">
-        <v>7</v>
+        <v>660</v>
       </c>
       <c r="G173" t="s">
-        <v>659</v>
+        <v>661</v>
       </c>
       <c r="H173" t="s">
         <v>12</v>
@@ -6527,22 +6521,22 @@
     </row>
     <row r="174" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A174" t="s">
+        <v>662</v>
+      </c>
+      <c r="C174" t="s">
+        <v>147</v>
+      </c>
+      <c r="D174" t="s">
+        <v>658</v>
+      </c>
+      <c r="E174" t="s">
+        <v>659</v>
+      </c>
+      <c r="F174" t="s">
         <v>660</v>
       </c>
-      <c r="C174" t="s">
-        <v>148</v>
-      </c>
-      <c r="D174" t="s">
+      <c r="G174" t="s">
         <v>661</v>
-      </c>
-      <c r="E174" t="s">
-        <v>662</v>
-      </c>
-      <c r="F174" t="s">
-        <v>663</v>
-      </c>
-      <c r="G174" t="s">
-        <v>664</v>
       </c>
       <c r="H174" t="s">
         <v>12</v>
@@ -6550,22 +6544,22 @@
     </row>
     <row r="175" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A175" t="s">
+        <v>663</v>
+      </c>
+      <c r="C175" t="s">
+        <v>43</v>
+      </c>
+      <c r="D175" t="s">
+        <v>664</v>
+      </c>
+      <c r="E175" t="s">
         <v>665</v>
       </c>
-      <c r="C175" t="s">
-        <v>148</v>
-      </c>
-      <c r="D175" t="s">
-        <v>661</v>
-      </c>
-      <c r="E175" t="s">
-        <v>662</v>
-      </c>
       <c r="F175" t="s">
-        <v>663</v>
+        <v>367</v>
       </c>
       <c r="G175" t="s">
-        <v>664</v>
+        <v>666</v>
       </c>
       <c r="H175" t="s">
         <v>12</v>
@@ -6573,22 +6567,22 @@
     </row>
     <row r="176" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A176" t="s">
-        <v>666</v>
+        <v>667</v>
       </c>
       <c r="C176" t="s">
-        <v>43</v>
+        <v>72</v>
       </c>
       <c r="D176" t="s">
-        <v>667</v>
+        <v>668</v>
       </c>
       <c r="E176" t="s">
-        <v>668</v>
+        <v>669</v>
       </c>
       <c r="F176" t="s">
-        <v>368</v>
+        <v>7</v>
       </c>
       <c r="G176" t="s">
-        <v>669</v>
+        <v>87</v>
       </c>
       <c r="H176" t="s">
         <v>12</v>
@@ -6599,19 +6593,19 @@
         <v>670</v>
       </c>
       <c r="C177" t="s">
-        <v>72</v>
+        <v>43</v>
       </c>
       <c r="D177" t="s">
         <v>671</v>
       </c>
       <c r="E177" t="s">
-        <v>672</v>
+        <v>65</v>
       </c>
       <c r="F177" t="s">
-        <v>7</v>
+        <v>66</v>
       </c>
       <c r="G177" t="s">
-        <v>87</v>
+        <v>67</v>
       </c>
       <c r="H177" t="s">
         <v>12</v>
@@ -6619,13 +6613,13 @@
     </row>
     <row r="178" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A178" t="s">
-        <v>673</v>
+        <v>672</v>
       </c>
       <c r="C178" t="s">
         <v>43</v>
       </c>
       <c r="D178" t="s">
-        <v>674</v>
+        <v>671</v>
       </c>
       <c r="E178" t="s">
         <v>65</v>
@@ -6642,22 +6636,22 @@
     </row>
     <row r="179" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A179" t="s">
-        <v>675</v>
+        <v>673</v>
       </c>
       <c r="C179" t="s">
-        <v>43</v>
+        <v>39</v>
       </c>
       <c r="D179" t="s">
         <v>674</v>
       </c>
       <c r="E179" t="s">
-        <v>65</v>
+        <v>675</v>
       </c>
       <c r="F179" t="s">
-        <v>66</v>
+        <v>7</v>
       </c>
       <c r="G179" t="s">
-        <v>67</v>
+        <v>676</v>
       </c>
       <c r="H179" t="s">
         <v>12</v>
@@ -6665,19 +6659,19 @@
     </row>
     <row r="180" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A180" t="s">
-        <v>676</v>
+        <v>677</v>
       </c>
       <c r="C180" t="s">
-        <v>39</v>
+        <v>17</v>
       </c>
       <c r="D180" t="s">
-        <v>677</v>
+        <v>678</v>
       </c>
       <c r="E180" t="s">
-        <v>678</v>
+        <v>60</v>
       </c>
       <c r="F180" t="s">
-        <v>7</v>
+        <v>61</v>
       </c>
       <c r="G180" t="s">
         <v>679</v>
@@ -6694,7 +6688,7 @@
         <v>17</v>
       </c>
       <c r="D181" t="s">
-        <v>681</v>
+        <v>678</v>
       </c>
       <c r="E181" t="s">
         <v>60</v>
@@ -6703,7 +6697,7 @@
         <v>61</v>
       </c>
       <c r="G181" t="s">
-        <v>682</v>
+        <v>679</v>
       </c>
       <c r="H181" t="s">
         <v>12</v>
@@ -6711,22 +6705,22 @@
     </row>
     <row r="182" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A182" t="s">
+        <v>681</v>
+      </c>
+      <c r="C182" t="s">
+        <v>135</v>
+      </c>
+      <c r="D182" t="s">
+        <v>682</v>
+      </c>
+      <c r="E182" t="s">
         <v>683</v>
       </c>
-      <c r="C182" t="s">
-        <v>17</v>
-      </c>
-      <c r="D182" t="s">
-        <v>681</v>
-      </c>
-      <c r="E182" t="s">
-        <v>60</v>
-      </c>
       <c r="F182" t="s">
-        <v>61</v>
+        <v>684</v>
       </c>
       <c r="G182" t="s">
-        <v>682</v>
+        <v>679</v>
       </c>
       <c r="H182" t="s">
         <v>12</v>
@@ -6734,22 +6728,22 @@
     </row>
     <row r="183" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A183" t="s">
+        <v>685</v>
+      </c>
+      <c r="C183" t="s">
+        <v>135</v>
+      </c>
+      <c r="D183" t="s">
+        <v>682</v>
+      </c>
+      <c r="E183" t="s">
+        <v>683</v>
+      </c>
+      <c r="F183" t="s">
         <v>684</v>
       </c>
-      <c r="C183" t="s">
-        <v>136</v>
-      </c>
-      <c r="D183" t="s">
-        <v>685</v>
-      </c>
-      <c r="E183" t="s">
-        <v>686</v>
-      </c>
-      <c r="F183" t="s">
-        <v>687</v>
-      </c>
       <c r="G183" t="s">
-        <v>682</v>
+        <v>679</v>
       </c>
       <c r="H183" t="s">
         <v>12</v>
@@ -6757,22 +6751,22 @@
     </row>
     <row r="184" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A184" t="s">
+        <v>686</v>
+      </c>
+      <c r="C184" t="s">
+        <v>9</v>
+      </c>
+      <c r="D184" t="s">
+        <v>687</v>
+      </c>
+      <c r="E184" t="s">
+        <v>69</v>
+      </c>
+      <c r="F184" t="s">
+        <v>70</v>
+      </c>
+      <c r="G184" t="s">
         <v>688</v>
-      </c>
-      <c r="C184" t="s">
-        <v>136</v>
-      </c>
-      <c r="D184" t="s">
-        <v>685</v>
-      </c>
-      <c r="E184" t="s">
-        <v>686</v>
-      </c>
-      <c r="F184" t="s">
-        <v>687</v>
-      </c>
-      <c r="G184" t="s">
-        <v>682</v>
       </c>
       <c r="H184" t="s">
         <v>12</v>
@@ -6786,7 +6780,7 @@
         <v>9</v>
       </c>
       <c r="D185" t="s">
-        <v>690</v>
+        <v>687</v>
       </c>
       <c r="E185" t="s">
         <v>69</v>
@@ -6795,7 +6789,7 @@
         <v>70</v>
       </c>
       <c r="G185" t="s">
-        <v>691</v>
+        <v>688</v>
       </c>
       <c r="H185" t="s">
         <v>12</v>
@@ -6803,22 +6797,22 @@
     </row>
     <row r="186" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A186" t="s">
+        <v>690</v>
+      </c>
+      <c r="C186" t="s">
+        <v>50</v>
+      </c>
+      <c r="D186" t="s">
+        <v>691</v>
+      </c>
+      <c r="E186" t="s">
+        <v>47</v>
+      </c>
+      <c r="F186" t="s">
+        <v>48</v>
+      </c>
+      <c r="G186" t="s">
         <v>692</v>
-      </c>
-      <c r="C186" t="s">
-        <v>9</v>
-      </c>
-      <c r="D186" t="s">
-        <v>690</v>
-      </c>
-      <c r="E186" t="s">
-        <v>69</v>
-      </c>
-      <c r="F186" t="s">
-        <v>70</v>
-      </c>
-      <c r="G186" t="s">
-        <v>691</v>
       </c>
       <c r="H186" t="s">
         <v>12</v>
@@ -6829,19 +6823,19 @@
         <v>693</v>
       </c>
       <c r="C187" t="s">
-        <v>50</v>
+        <v>23</v>
       </c>
       <c r="D187" t="s">
         <v>694</v>
       </c>
       <c r="E187" t="s">
-        <v>47</v>
+        <v>695</v>
       </c>
       <c r="F187" t="s">
-        <v>48</v>
+        <v>696</v>
       </c>
       <c r="G187" t="s">
-        <v>695</v>
+        <v>697</v>
       </c>
       <c r="H187" t="s">
         <v>12</v>
@@ -6849,19 +6843,19 @@
     </row>
     <row r="188" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A188" t="s">
-        <v>696</v>
+        <v>698</v>
       </c>
       <c r="C188" t="s">
-        <v>23</v>
+        <v>20</v>
       </c>
       <c r="D188" t="s">
-        <v>697</v>
+        <v>699</v>
       </c>
       <c r="E188" t="s">
-        <v>698</v>
+        <v>45</v>
       </c>
       <c r="F188" t="s">
-        <v>699</v>
+        <v>46</v>
       </c>
       <c r="G188" t="s">
         <v>700</v>
@@ -6875,19 +6869,19 @@
         <v>701</v>
       </c>
       <c r="C189" t="s">
-        <v>20</v>
+        <v>33</v>
       </c>
       <c r="D189" t="s">
         <v>702</v>
       </c>
       <c r="E189" t="s">
-        <v>45</v>
+        <v>37</v>
       </c>
       <c r="F189" t="s">
-        <v>46</v>
+        <v>38</v>
       </c>
       <c r="G189" t="s">
-        <v>703</v>
+        <v>559</v>
       </c>
       <c r="H189" t="s">
         <v>12</v>
@@ -6895,13 +6889,13 @@
     </row>
     <row r="190" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A190" t="s">
-        <v>704</v>
+        <v>703</v>
       </c>
       <c r="C190" t="s">
         <v>33</v>
       </c>
       <c r="D190" t="s">
-        <v>705</v>
+        <v>702</v>
       </c>
       <c r="E190" t="s">
         <v>37</v>
@@ -6910,7 +6904,7 @@
         <v>38</v>
       </c>
       <c r="G190" t="s">
-        <v>560</v>
+        <v>559</v>
       </c>
       <c r="H190" t="s">
         <v>12</v>
@@ -6918,22 +6912,22 @@
     </row>
     <row r="191" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A191" t="s">
-        <v>706</v>
+        <v>704</v>
       </c>
       <c r="C191" t="s">
-        <v>33</v>
+        <v>24</v>
       </c>
       <c r="D191" t="s">
         <v>705</v>
       </c>
       <c r="E191" t="s">
-        <v>37</v>
+        <v>68</v>
       </c>
       <c r="F191" t="s">
-        <v>38</v>
+        <v>7</v>
       </c>
       <c r="G191" t="s">
-        <v>560</v>
+        <v>706</v>
       </c>
       <c r="H191" t="s">
         <v>12</v>
@@ -6944,19 +6938,19 @@
         <v>707</v>
       </c>
       <c r="C192" t="s">
-        <v>24</v>
+        <v>50</v>
       </c>
       <c r="D192" t="s">
         <v>708</v>
       </c>
       <c r="E192" t="s">
-        <v>68</v>
+        <v>81</v>
       </c>
       <c r="F192" t="s">
-        <v>7</v>
+        <v>82</v>
       </c>
       <c r="G192" t="s">
-        <v>709</v>
+        <v>89</v>
       </c>
       <c r="H192" t="s">
         <v>12</v>
@@ -6964,13 +6958,13 @@
     </row>
     <row r="193" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A193" t="s">
-        <v>710</v>
+        <v>709</v>
       </c>
       <c r="C193" t="s">
         <v>50</v>
       </c>
       <c r="D193" t="s">
-        <v>711</v>
+        <v>708</v>
       </c>
       <c r="E193" t="s">
         <v>81</v>
@@ -6987,13 +6981,13 @@
     </row>
     <row r="194" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A194" t="s">
-        <v>712</v>
+        <v>710</v>
       </c>
       <c r="C194" t="s">
         <v>50</v>
       </c>
       <c r="D194" t="s">
-        <v>711</v>
+        <v>708</v>
       </c>
       <c r="E194" t="s">
         <v>81</v>
@@ -7010,13 +7004,13 @@
     </row>
     <row r="195" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A195" t="s">
-        <v>713</v>
+        <v>711</v>
       </c>
       <c r="C195" t="s">
         <v>50</v>
       </c>
       <c r="D195" t="s">
-        <v>711</v>
+        <v>708</v>
       </c>
       <c r="E195" t="s">
         <v>81</v>
@@ -7033,13 +7027,13 @@
     </row>
     <row r="196" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A196" t="s">
-        <v>714</v>
+        <v>712</v>
       </c>
       <c r="C196" t="s">
         <v>50</v>
       </c>
       <c r="D196" t="s">
-        <v>711</v>
+        <v>708</v>
       </c>
       <c r="E196" t="s">
         <v>81</v>
@@ -7056,13 +7050,13 @@
     </row>
     <row r="197" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A197" t="s">
-        <v>715</v>
+        <v>713</v>
       </c>
       <c r="C197" t="s">
         <v>50</v>
       </c>
       <c r="D197" t="s">
-        <v>711</v>
+        <v>708</v>
       </c>
       <c r="E197" t="s">
         <v>81</v>
@@ -7079,45 +7073,45 @@
     </row>
     <row r="198" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A198" t="s">
+        <v>714</v>
+      </c>
+      <c r="C198" t="s">
+        <v>20</v>
+      </c>
+      <c r="D198" t="s">
+        <v>715</v>
+      </c>
+      <c r="E198" t="s">
         <v>716</v>
       </c>
-      <c r="C198" t="s">
-        <v>50</v>
-      </c>
-      <c r="D198" t="s">
-        <v>711</v>
-      </c>
-      <c r="E198" t="s">
-        <v>81</v>
-      </c>
       <c r="F198" t="s">
-        <v>82</v>
+        <v>7</v>
       </c>
       <c r="G198" t="s">
-        <v>89</v>
+        <v>717</v>
       </c>
       <c r="H198" t="s">
-        <v>12</v>
+        <v>21</v>
       </c>
     </row>
     <row r="199" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A199" t="s">
-        <v>717</v>
+        <v>718</v>
       </c>
       <c r="C199" t="s">
         <v>20</v>
       </c>
       <c r="D199" t="s">
-        <v>718</v>
+        <v>715</v>
       </c>
       <c r="E199" t="s">
-        <v>719</v>
+        <v>716</v>
       </c>
       <c r="F199" t="s">
         <v>7</v>
       </c>
       <c r="G199" t="s">
-        <v>720</v>
+        <v>717</v>
       </c>
       <c r="H199" t="s">
         <v>21</v>
@@ -7125,22 +7119,22 @@
     </row>
     <row r="200" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A200" t="s">
+        <v>719</v>
+      </c>
+      <c r="C200" t="s">
+        <v>72</v>
+      </c>
+      <c r="D200" t="s">
+        <v>720</v>
+      </c>
+      <c r="E200" t="s">
         <v>721</v>
       </c>
-      <c r="C200" t="s">
-        <v>20</v>
-      </c>
-      <c r="D200" t="s">
-        <v>718</v>
-      </c>
-      <c r="E200" t="s">
-        <v>719</v>
-      </c>
       <c r="F200" t="s">
-        <v>7</v>
+        <v>722</v>
       </c>
       <c r="G200" t="s">
-        <v>720</v>
+        <v>723</v>
       </c>
       <c r="H200" t="s">
         <v>21</v>
@@ -7148,45 +7142,30 @@
     </row>
     <row r="201" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A201" t="s">
-        <v>722</v>
+        <v>724</v>
       </c>
       <c r="C201" t="s">
-        <v>72</v>
+        <v>19</v>
       </c>
       <c r="D201" t="s">
-        <v>723</v>
-      </c>
-      <c r="E201" t="s">
         <v>724</v>
       </c>
-      <c r="F201" t="s">
+      <c r="H201" t="s">
         <v>725</v>
       </c>
-      <c r="G201" t="s">
+    </row>
+    <row r="202" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A202" t="s">
         <v>726</v>
       </c>
-      <c r="H201" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="202" spans="1:8" x14ac:dyDescent="0.3">
       <c r="C202" t="s">
-        <v>409</v>
+        <v>19</v>
       </c>
       <c r="D202" t="s">
-        <v>727</v>
-      </c>
-      <c r="E202" t="s">
-        <v>526</v>
-      </c>
-      <c r="F202" t="s">
-        <v>7</v>
-      </c>
-      <c r="G202" t="s">
-        <v>728</v>
+        <v>726</v>
       </c>
       <c r="H202" t="s">
-        <v>32</v>
+        <v>725</v>
       </c>
     </row>
   </sheetData>

--- a/1.xlsx
+++ b/1.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="\\wh.local\fs\UserProfile_TSSWH19\_TSSWH19_redirected_folders\HunyaCs1\Desktop\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0FE54FB4-251A-41B8-A547-16102869D3A6}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{70A96B83-17DB-4A19-9C4F-2B6561EAB240}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="0" windowWidth="22260" windowHeight="12648" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1554" uniqueCount="745">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1567" uniqueCount="746">
   <si>
     <t>BUDAPEST</t>
   </si>
@@ -342,9 +342,6 @@
     <t>Vadász utca</t>
   </si>
   <si>
-    <t>1033</t>
-  </si>
-  <si>
     <t>Huba utca</t>
   </si>
   <si>
@@ -2112,15 +2109,6 @@
     <t>NFD6-03-23-Y783</t>
   </si>
   <si>
-    <t>NFD6-03-24-TKJE-1</t>
-  </si>
-  <si>
-    <t>NFD6-03-24-TKJE</t>
-  </si>
-  <si>
-    <t>Harang utca</t>
-  </si>
-  <si>
     <t>202603242600661501</t>
   </si>
   <si>
@@ -2263,6 +2251,21 @@
   </si>
   <si>
     <t>159995579538415715</t>
+  </si>
+  <si>
+    <t>NFD6-03-22-MURP</t>
+  </si>
+  <si>
+    <t>AUCHAN_ÁRUHÁZI</t>
+  </si>
+  <si>
+    <t>NFD6-03-17-8SMR</t>
+  </si>
+  <si>
+    <t>NFD6-03-21-YREW</t>
+  </si>
+  <si>
+    <t>NFD6-03-21-PBAK</t>
   </si>
 </sst>
 </file>
@@ -2581,7 +2584,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <sheetPr codeName="Munka1"/>
-  <dimension ref="A1:H222"/>
+  <dimension ref="A2:H227"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="24.88671875" bestFit="1" customWidth="1"/>
@@ -2594,70 +2597,47 @@
     <col min="8" max="8" width="19.88671875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A1" t="s">
-        <v>123</v>
-      </c>
-      <c r="C1" t="s">
-        <v>12</v>
-      </c>
-      <c r="D1" t="s">
-        <v>124</v>
-      </c>
-      <c r="E1" t="s">
-        <v>78</v>
-      </c>
-      <c r="F1" t="s">
-        <v>0</v>
-      </c>
-      <c r="G1" t="s">
-        <v>125</v>
-      </c>
-      <c r="H1" t="s">
-        <v>4</v>
-      </c>
-    </row>
     <row r="2" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
-        <v>126</v>
+        <v>122</v>
       </c>
       <c r="C2" t="s">
-        <v>31</v>
+        <v>12</v>
       </c>
       <c r="D2" t="s">
-        <v>127</v>
+        <v>123</v>
       </c>
       <c r="E2" t="s">
-        <v>109</v>
+        <v>78</v>
       </c>
       <c r="F2" t="s">
         <v>0</v>
       </c>
       <c r="G2" t="s">
-        <v>128</v>
+        <v>124</v>
       </c>
       <c r="H2" t="s">
-        <v>1</v>
+        <v>4</v>
       </c>
     </row>
     <row r="3" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
-        <v>129</v>
+        <v>125</v>
       </c>
       <c r="C3" t="s">
-        <v>10</v>
+        <v>31</v>
       </c>
       <c r="D3" t="s">
-        <v>130</v>
+        <v>126</v>
       </c>
       <c r="E3" t="s">
-        <v>20</v>
+        <v>108</v>
       </c>
       <c r="F3" t="s">
         <v>0</v>
       </c>
       <c r="G3" t="s">
-        <v>131</v>
+        <v>127</v>
       </c>
       <c r="H3" t="s">
         <v>1</v>
@@ -2665,22 +2645,22 @@
     </row>
     <row r="4" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
-        <v>132</v>
+        <v>128</v>
       </c>
       <c r="C4" t="s">
-        <v>133</v>
+        <v>10</v>
       </c>
       <c r="D4" t="s">
-        <v>134</v>
+        <v>129</v>
       </c>
       <c r="E4" t="s">
-        <v>135</v>
+        <v>20</v>
       </c>
       <c r="F4" t="s">
-        <v>136</v>
+        <v>0</v>
       </c>
       <c r="G4" t="s">
-        <v>137</v>
+        <v>130</v>
       </c>
       <c r="H4" t="s">
         <v>1</v>
@@ -2688,22 +2668,22 @@
     </row>
     <row r="5" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
-        <v>138</v>
+        <v>131</v>
       </c>
       <c r="C5" t="s">
-        <v>6</v>
+        <v>132</v>
       </c>
       <c r="D5" t="s">
-        <v>139</v>
+        <v>133</v>
       </c>
       <c r="E5" t="s">
-        <v>140</v>
+        <v>134</v>
       </c>
       <c r="F5" t="s">
-        <v>141</v>
+        <v>135</v>
       </c>
       <c r="G5" t="s">
-        <v>46</v>
+        <v>136</v>
       </c>
       <c r="H5" t="s">
         <v>1</v>
@@ -2711,22 +2691,22 @@
     </row>
     <row r="6" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
-        <v>142</v>
+        <v>137</v>
       </c>
       <c r="C6" t="s">
-        <v>41</v>
+        <v>6</v>
       </c>
       <c r="D6" t="s">
-        <v>143</v>
+        <v>138</v>
       </c>
       <c r="E6" t="s">
-        <v>7</v>
+        <v>139</v>
       </c>
       <c r="F6" t="s">
-        <v>8</v>
+        <v>140</v>
       </c>
       <c r="G6" t="s">
-        <v>144</v>
+        <v>46</v>
       </c>
       <c r="H6" t="s">
         <v>1</v>
@@ -2734,22 +2714,22 @@
     </row>
     <row r="7" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
-        <v>145</v>
+        <v>141</v>
       </c>
       <c r="C7" t="s">
-        <v>11</v>
+        <v>41</v>
       </c>
       <c r="D7" t="s">
-        <v>146</v>
+        <v>142</v>
       </c>
       <c r="E7" t="s">
-        <v>147</v>
+        <v>7</v>
       </c>
       <c r="F7" t="s">
-        <v>148</v>
+        <v>8</v>
       </c>
       <c r="G7" t="s">
-        <v>149</v>
+        <v>143</v>
       </c>
       <c r="H7" t="s">
         <v>1</v>
@@ -2757,22 +2737,22 @@
     </row>
     <row r="8" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
-        <v>150</v>
+        <v>144</v>
       </c>
       <c r="C8" t="s">
-        <v>17</v>
+        <v>11</v>
       </c>
       <c r="D8" t="s">
-        <v>151</v>
+        <v>145</v>
       </c>
       <c r="E8" t="s">
-        <v>152</v>
+        <v>146</v>
       </c>
       <c r="F8" t="s">
-        <v>0</v>
+        <v>147</v>
       </c>
       <c r="G8" t="s">
-        <v>153</v>
+        <v>148</v>
       </c>
       <c r="H8" t="s">
         <v>1</v>
@@ -2780,22 +2760,22 @@
     </row>
     <row r="9" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
-        <v>50</v>
+        <v>149</v>
       </c>
       <c r="C9" t="s">
-        <v>9</v>
+        <v>17</v>
       </c>
       <c r="D9" t="s">
-        <v>51</v>
+        <v>150</v>
       </c>
       <c r="E9" t="s">
-        <v>36</v>
+        <v>151</v>
       </c>
       <c r="F9" t="s">
         <v>0</v>
       </c>
       <c r="G9" t="s">
-        <v>52</v>
+        <v>152</v>
       </c>
       <c r="H9" t="s">
         <v>1</v>
@@ -2803,22 +2783,22 @@
     </row>
     <row r="10" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
-        <v>154</v>
+        <v>50</v>
       </c>
       <c r="C10" t="s">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="D10" t="s">
-        <v>155</v>
+        <v>51</v>
       </c>
       <c r="E10" t="s">
-        <v>156</v>
+        <v>36</v>
       </c>
       <c r="F10" t="s">
         <v>0</v>
       </c>
       <c r="G10" t="s">
-        <v>157</v>
+        <v>52</v>
       </c>
       <c r="H10" t="s">
         <v>1</v>
@@ -2826,22 +2806,22 @@
     </row>
     <row r="11" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A11" t="s">
-        <v>158</v>
+        <v>153</v>
       </c>
       <c r="C11" t="s">
-        <v>55</v>
+        <v>3</v>
       </c>
       <c r="D11" t="s">
-        <v>159</v>
+        <v>154</v>
       </c>
       <c r="E11" t="s">
-        <v>160</v>
+        <v>155</v>
       </c>
       <c r="F11" t="s">
         <v>0</v>
       </c>
       <c r="G11" t="s">
-        <v>85</v>
+        <v>156</v>
       </c>
       <c r="H11" t="s">
         <v>1</v>
@@ -2849,22 +2829,22 @@
     </row>
     <row r="12" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A12" t="s">
-        <v>161</v>
+        <v>157</v>
       </c>
       <c r="C12" t="s">
-        <v>9</v>
+        <v>55</v>
       </c>
       <c r="D12" t="s">
-        <v>162</v>
+        <v>158</v>
       </c>
       <c r="E12" t="s">
-        <v>25</v>
+        <v>159</v>
       </c>
       <c r="F12" t="s">
         <v>0</v>
       </c>
       <c r="G12" t="s">
-        <v>163</v>
+        <v>85</v>
       </c>
       <c r="H12" t="s">
         <v>1</v>
@@ -2872,22 +2852,22 @@
     </row>
     <row r="13" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A13" t="s">
-        <v>164</v>
+        <v>160</v>
       </c>
       <c r="C13" t="s">
-        <v>2</v>
+        <v>9</v>
       </c>
       <c r="D13" t="s">
-        <v>165</v>
+        <v>161</v>
       </c>
       <c r="E13" t="s">
-        <v>74</v>
+        <v>25</v>
       </c>
       <c r="F13" t="s">
         <v>0</v>
       </c>
       <c r="G13" t="s">
-        <v>166</v>
+        <v>162</v>
       </c>
       <c r="H13" t="s">
         <v>1</v>
@@ -2895,22 +2875,22 @@
     </row>
     <row r="14" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A14" t="s">
-        <v>167</v>
+        <v>163</v>
       </c>
       <c r="C14" t="s">
-        <v>10</v>
+        <v>2</v>
       </c>
       <c r="D14" t="s">
-        <v>168</v>
+        <v>164</v>
       </c>
       <c r="E14" t="s">
-        <v>169</v>
+        <v>74</v>
       </c>
       <c r="F14" t="s">
         <v>0</v>
       </c>
       <c r="G14" t="s">
-        <v>170</v>
+        <v>165</v>
       </c>
       <c r="H14" t="s">
         <v>1</v>
@@ -2918,22 +2898,22 @@
     </row>
     <row r="15" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A15" t="s">
-        <v>171</v>
+        <v>166</v>
       </c>
       <c r="C15" t="s">
         <v>10</v>
       </c>
       <c r="D15" t="s">
+        <v>167</v>
+      </c>
+      <c r="E15" t="s">
         <v>168</v>
       </c>
-      <c r="E15" t="s">
+      <c r="F15" t="s">
+        <v>0</v>
+      </c>
+      <c r="G15" t="s">
         <v>169</v>
-      </c>
-      <c r="F15" t="s">
-        <v>0</v>
-      </c>
-      <c r="G15" t="s">
-        <v>170</v>
       </c>
       <c r="H15" t="s">
         <v>1</v>
@@ -2941,22 +2921,22 @@
     </row>
     <row r="16" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A16" t="s">
-        <v>172</v>
+        <v>170</v>
       </c>
       <c r="C16" t="s">
-        <v>31</v>
+        <v>10</v>
       </c>
       <c r="D16" t="s">
-        <v>173</v>
+        <v>167</v>
       </c>
       <c r="E16" t="s">
-        <v>29</v>
+        <v>168</v>
       </c>
       <c r="F16" t="s">
-        <v>30</v>
+        <v>0</v>
       </c>
       <c r="G16" t="s">
-        <v>174</v>
+        <v>169</v>
       </c>
       <c r="H16" t="s">
         <v>1</v>
@@ -2964,13 +2944,13 @@
     </row>
     <row r="17" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A17" t="s">
-        <v>175</v>
+        <v>171</v>
       </c>
       <c r="C17" t="s">
         <v>31</v>
       </c>
       <c r="D17" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="E17" t="s">
         <v>29</v>
@@ -2979,7 +2959,7 @@
         <v>30</v>
       </c>
       <c r="G17" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="H17" t="s">
         <v>1</v>
@@ -2987,22 +2967,22 @@
     </row>
     <row r="18" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A18" t="s">
-        <v>176</v>
+        <v>174</v>
       </c>
       <c r="C18" t="s">
-        <v>14</v>
+        <v>31</v>
       </c>
       <c r="D18" t="s">
-        <v>177</v>
+        <v>172</v>
       </c>
       <c r="E18" t="s">
-        <v>178</v>
+        <v>29</v>
       </c>
       <c r="F18" t="s">
-        <v>179</v>
+        <v>30</v>
       </c>
       <c r="G18" t="s">
-        <v>96</v>
+        <v>173</v>
       </c>
       <c r="H18" t="s">
         <v>1</v>
@@ -3010,19 +2990,19 @@
     </row>
     <row r="19" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A19" t="s">
-        <v>180</v>
+        <v>175</v>
       </c>
       <c r="C19" t="s">
         <v>14</v>
       </c>
       <c r="D19" t="s">
+        <v>176</v>
+      </c>
+      <c r="E19" t="s">
         <v>177</v>
       </c>
-      <c r="E19" t="s">
+      <c r="F19" t="s">
         <v>178</v>
-      </c>
-      <c r="F19" t="s">
-        <v>179</v>
       </c>
       <c r="G19" t="s">
         <v>96</v>
@@ -3033,22 +3013,22 @@
     </row>
     <row r="20" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A20" t="s">
-        <v>181</v>
+        <v>179</v>
       </c>
       <c r="C20" t="s">
-        <v>2</v>
+        <v>14</v>
       </c>
       <c r="D20" t="s">
-        <v>182</v>
+        <v>176</v>
       </c>
       <c r="E20" t="s">
-        <v>183</v>
+        <v>177</v>
       </c>
       <c r="F20" t="s">
-        <v>184</v>
+        <v>178</v>
       </c>
       <c r="G20" t="s">
-        <v>185</v>
+        <v>96</v>
       </c>
       <c r="H20" t="s">
         <v>1</v>
@@ -3056,22 +3036,22 @@
     </row>
     <row r="21" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A21" t="s">
-        <v>59</v>
+        <v>180</v>
       </c>
       <c r="C21" t="s">
-        <v>9</v>
+        <v>2</v>
       </c>
       <c r="D21" t="s">
-        <v>60</v>
+        <v>181</v>
       </c>
       <c r="E21" t="s">
-        <v>61</v>
+        <v>182</v>
       </c>
       <c r="F21" t="s">
-        <v>0</v>
+        <v>183</v>
       </c>
       <c r="G21" t="s">
-        <v>62</v>
+        <v>184</v>
       </c>
       <c r="H21" t="s">
         <v>1</v>
@@ -3079,7 +3059,7 @@
     </row>
     <row r="22" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A22" t="s">
-        <v>63</v>
+        <v>59</v>
       </c>
       <c r="C22" t="s">
         <v>9</v>
@@ -3102,22 +3082,22 @@
     </row>
     <row r="23" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A23" t="s">
-        <v>186</v>
+        <v>63</v>
       </c>
       <c r="C23" t="s">
-        <v>133</v>
+        <v>9</v>
       </c>
       <c r="D23" t="s">
-        <v>187</v>
+        <v>60</v>
       </c>
       <c r="E23" t="s">
-        <v>188</v>
+        <v>61</v>
       </c>
       <c r="F23" t="s">
-        <v>189</v>
+        <v>0</v>
       </c>
       <c r="G23" t="s">
-        <v>190</v>
+        <v>62</v>
       </c>
       <c r="H23" t="s">
         <v>1</v>
@@ -3125,22 +3105,22 @@
     </row>
     <row r="24" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A24" t="s">
-        <v>191</v>
+        <v>185</v>
       </c>
       <c r="C24" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="D24" t="s">
-        <v>192</v>
+        <v>186</v>
       </c>
       <c r="E24" t="s">
-        <v>193</v>
+        <v>187</v>
       </c>
       <c r="F24" t="s">
-        <v>0</v>
+        <v>188</v>
       </c>
       <c r="G24" t="s">
-        <v>194</v>
+        <v>189</v>
       </c>
       <c r="H24" t="s">
         <v>1</v>
@@ -3148,22 +3128,22 @@
     </row>
     <row r="25" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A25" t="s">
-        <v>64</v>
+        <v>190</v>
       </c>
       <c r="C25" t="s">
-        <v>41</v>
+        <v>132</v>
       </c>
       <c r="D25" t="s">
-        <v>65</v>
+        <v>191</v>
       </c>
       <c r="E25" t="s">
-        <v>66</v>
+        <v>192</v>
       </c>
       <c r="F25" t="s">
-        <v>67</v>
+        <v>0</v>
       </c>
       <c r="G25" t="s">
-        <v>68</v>
+        <v>193</v>
       </c>
       <c r="H25" t="s">
         <v>1</v>
@@ -3171,22 +3151,22 @@
     </row>
     <row r="26" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A26" t="s">
-        <v>195</v>
+        <v>64</v>
       </c>
       <c r="C26" t="s">
-        <v>54</v>
+        <v>41</v>
       </c>
       <c r="D26" t="s">
-        <v>196</v>
+        <v>65</v>
       </c>
       <c r="E26" t="s">
-        <v>197</v>
+        <v>66</v>
       </c>
       <c r="F26" t="s">
-        <v>198</v>
+        <v>67</v>
       </c>
       <c r="G26" t="s">
-        <v>199</v>
+        <v>68</v>
       </c>
       <c r="H26" t="s">
         <v>1</v>
@@ -3194,22 +3174,22 @@
     </row>
     <row r="27" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A27" t="s">
-        <v>200</v>
+        <v>194</v>
       </c>
       <c r="C27" t="s">
-        <v>24</v>
+        <v>54</v>
       </c>
       <c r="D27" t="s">
-        <v>201</v>
+        <v>195</v>
       </c>
       <c r="E27" t="s">
-        <v>202</v>
+        <v>196</v>
       </c>
       <c r="F27" t="s">
-        <v>203</v>
+        <v>197</v>
       </c>
       <c r="G27" t="s">
-        <v>204</v>
+        <v>198</v>
       </c>
       <c r="H27" t="s">
         <v>1</v>
@@ -3217,22 +3197,22 @@
     </row>
     <row r="28" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A28" t="s">
-        <v>205</v>
+        <v>199</v>
       </c>
       <c r="C28" t="s">
-        <v>14</v>
+        <v>24</v>
       </c>
       <c r="D28" t="s">
-        <v>206</v>
+        <v>200</v>
       </c>
       <c r="E28" t="s">
-        <v>207</v>
+        <v>201</v>
       </c>
       <c r="F28" t="s">
-        <v>208</v>
+        <v>202</v>
       </c>
       <c r="G28" t="s">
-        <v>209</v>
+        <v>203</v>
       </c>
       <c r="H28" t="s">
         <v>1</v>
@@ -3240,22 +3220,22 @@
     </row>
     <row r="29" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A29" t="s">
-        <v>210</v>
+        <v>204</v>
       </c>
       <c r="C29" t="s">
         <v>14</v>
       </c>
       <c r="D29" t="s">
+        <v>205</v>
+      </c>
+      <c r="E29" t="s">
         <v>206</v>
       </c>
-      <c r="E29" t="s">
+      <c r="F29" t="s">
         <v>207</v>
       </c>
-      <c r="F29" t="s">
+      <c r="G29" t="s">
         <v>208</v>
-      </c>
-      <c r="G29" t="s">
-        <v>209</v>
       </c>
       <c r="H29" t="s">
         <v>1</v>
@@ -3263,22 +3243,22 @@
     </row>
     <row r="30" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A30" t="s">
-        <v>211</v>
+        <v>209</v>
       </c>
       <c r="C30" t="s">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="D30" t="s">
-        <v>212</v>
+        <v>205</v>
       </c>
       <c r="E30" t="s">
-        <v>213</v>
+        <v>206</v>
       </c>
       <c r="F30" t="s">
-        <v>214</v>
+        <v>207</v>
       </c>
       <c r="G30" t="s">
-        <v>106</v>
+        <v>208</v>
       </c>
       <c r="H30" t="s">
         <v>1</v>
@@ -3286,22 +3266,22 @@
     </row>
     <row r="31" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A31" t="s">
-        <v>215</v>
+        <v>210</v>
       </c>
       <c r="C31" t="s">
         <v>11</v>
       </c>
       <c r="D31" t="s">
+        <v>211</v>
+      </c>
+      <c r="E31" t="s">
         <v>212</v>
       </c>
-      <c r="E31" t="s">
+      <c r="F31" t="s">
         <v>213</v>
       </c>
-      <c r="F31" t="s">
-        <v>214</v>
-      </c>
       <c r="G31" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="H31" t="s">
         <v>1</v>
@@ -3309,22 +3289,22 @@
     </row>
     <row r="32" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A32" t="s">
-        <v>216</v>
+        <v>214</v>
       </c>
       <c r="C32" t="s">
-        <v>133</v>
+        <v>11</v>
       </c>
       <c r="D32" t="s">
-        <v>217</v>
+        <v>211</v>
       </c>
       <c r="E32" t="s">
-        <v>56</v>
+        <v>212</v>
       </c>
       <c r="F32" t="s">
-        <v>57</v>
+        <v>213</v>
       </c>
       <c r="G32" t="s">
-        <v>218</v>
+        <v>105</v>
       </c>
       <c r="H32" t="s">
         <v>1</v>
@@ -3332,22 +3312,22 @@
     </row>
     <row r="33" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A33" t="s">
-        <v>219</v>
+        <v>215</v>
       </c>
       <c r="C33" t="s">
-        <v>14</v>
+        <v>132</v>
       </c>
       <c r="D33" t="s">
-        <v>220</v>
+        <v>216</v>
       </c>
       <c r="E33" t="s">
-        <v>26</v>
+        <v>56</v>
       </c>
       <c r="F33" t="s">
-        <v>27</v>
+        <v>57</v>
       </c>
       <c r="G33" t="s">
-        <v>221</v>
+        <v>217</v>
       </c>
       <c r="H33" t="s">
         <v>1</v>
@@ -3355,22 +3335,22 @@
     </row>
     <row r="34" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A34" t="s">
-        <v>222</v>
+        <v>218</v>
       </c>
       <c r="C34" t="s">
-        <v>41</v>
+        <v>14</v>
       </c>
       <c r="D34" t="s">
-        <v>223</v>
+        <v>219</v>
       </c>
       <c r="E34" t="s">
-        <v>66</v>
+        <v>26</v>
       </c>
       <c r="F34" t="s">
-        <v>67</v>
+        <v>27</v>
       </c>
       <c r="G34" t="s">
-        <v>79</v>
+        <v>220</v>
       </c>
       <c r="H34" t="s">
         <v>1</v>
@@ -3378,22 +3358,22 @@
     </row>
     <row r="35" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A35" t="s">
-        <v>224</v>
+        <v>221</v>
       </c>
       <c r="C35" t="s">
-        <v>6</v>
+        <v>41</v>
       </c>
       <c r="D35" t="s">
-        <v>225</v>
+        <v>222</v>
       </c>
       <c r="E35" t="s">
-        <v>98</v>
+        <v>66</v>
       </c>
       <c r="F35" t="s">
-        <v>99</v>
+        <v>67</v>
       </c>
       <c r="G35" t="s">
-        <v>112</v>
+        <v>79</v>
       </c>
       <c r="H35" t="s">
         <v>1</v>
@@ -3401,22 +3381,22 @@
     </row>
     <row r="36" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A36" t="s">
-        <v>226</v>
+        <v>223</v>
       </c>
       <c r="C36" t="s">
-        <v>24</v>
+        <v>6</v>
       </c>
       <c r="D36" t="s">
-        <v>227</v>
+        <v>224</v>
       </c>
       <c r="E36" t="s">
-        <v>120</v>
+        <v>98</v>
       </c>
       <c r="F36" t="s">
-        <v>121</v>
+        <v>99</v>
       </c>
       <c r="G36" t="s">
-        <v>122</v>
+        <v>111</v>
       </c>
       <c r="H36" t="s">
         <v>1</v>
@@ -3424,22 +3404,22 @@
     </row>
     <row r="37" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A37" t="s">
-        <v>228</v>
+        <v>225</v>
       </c>
       <c r="C37" t="s">
-        <v>14</v>
+        <v>24</v>
       </c>
       <c r="D37" t="s">
-        <v>229</v>
+        <v>226</v>
       </c>
       <c r="E37" t="s">
-        <v>113</v>
+        <v>119</v>
       </c>
       <c r="F37" t="s">
-        <v>114</v>
+        <v>120</v>
       </c>
       <c r="G37" t="s">
-        <v>230</v>
+        <v>121</v>
       </c>
       <c r="H37" t="s">
         <v>1</v>
@@ -3447,22 +3427,22 @@
     </row>
     <row r="38" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A38" t="s">
-        <v>231</v>
+        <v>227</v>
       </c>
       <c r="C38" t="s">
-        <v>9</v>
+        <v>14</v>
       </c>
       <c r="D38" t="s">
-        <v>232</v>
+        <v>228</v>
       </c>
       <c r="E38" t="s">
-        <v>233</v>
+        <v>112</v>
       </c>
       <c r="F38" t="s">
-        <v>0</v>
+        <v>113</v>
       </c>
       <c r="G38" t="s">
-        <v>234</v>
+        <v>229</v>
       </c>
       <c r="H38" t="s">
         <v>1</v>
@@ -3470,22 +3450,22 @@
     </row>
     <row r="39" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A39" t="s">
-        <v>235</v>
+        <v>230</v>
       </c>
       <c r="C39" t="s">
         <v>9</v>
       </c>
       <c r="D39" t="s">
+        <v>231</v>
+      </c>
+      <c r="E39" t="s">
         <v>232</v>
       </c>
-      <c r="E39" t="s">
+      <c r="F39" t="s">
+        <v>0</v>
+      </c>
+      <c r="G39" t="s">
         <v>233</v>
-      </c>
-      <c r="F39" t="s">
-        <v>0</v>
-      </c>
-      <c r="G39" t="s">
-        <v>234</v>
       </c>
       <c r="H39" t="s">
         <v>1</v>
@@ -3493,22 +3473,22 @@
     </row>
     <row r="40" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A40" t="s">
-        <v>236</v>
+        <v>234</v>
       </c>
       <c r="C40" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="D40" t="s">
-        <v>237</v>
+        <v>231</v>
       </c>
       <c r="E40" t="s">
-        <v>213</v>
+        <v>232</v>
       </c>
       <c r="F40" t="s">
-        <v>214</v>
+        <v>0</v>
       </c>
       <c r="G40" t="s">
-        <v>238</v>
+        <v>233</v>
       </c>
       <c r="H40" t="s">
         <v>1</v>
@@ -3516,22 +3496,22 @@
     </row>
     <row r="41" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A41" t="s">
-        <v>239</v>
+        <v>235</v>
       </c>
       <c r="C41" t="s">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="D41" t="s">
-        <v>240</v>
+        <v>236</v>
       </c>
       <c r="E41" t="s">
-        <v>26</v>
+        <v>212</v>
       </c>
       <c r="F41" t="s">
-        <v>27</v>
+        <v>213</v>
       </c>
       <c r="G41" t="s">
-        <v>241</v>
+        <v>237</v>
       </c>
       <c r="H41" t="s">
         <v>1</v>
@@ -3539,13 +3519,13 @@
     </row>
     <row r="42" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A42" t="s">
-        <v>242</v>
+        <v>238</v>
       </c>
       <c r="C42" t="s">
         <v>14</v>
       </c>
       <c r="D42" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
       <c r="E42" t="s">
         <v>26</v>
@@ -3554,7 +3534,7 @@
         <v>27</v>
       </c>
       <c r="G42" t="s">
-        <v>241</v>
+        <v>240</v>
       </c>
       <c r="H42" t="s">
         <v>1</v>
@@ -3562,22 +3542,22 @@
     </row>
     <row r="43" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A43" t="s">
-        <v>243</v>
+        <v>241</v>
       </c>
       <c r="C43" t="s">
-        <v>35</v>
+        <v>14</v>
       </c>
       <c r="D43" t="s">
-        <v>244</v>
+        <v>239</v>
       </c>
       <c r="E43" t="s">
-        <v>245</v>
+        <v>26</v>
       </c>
       <c r="F43" t="s">
-        <v>0</v>
+        <v>27</v>
       </c>
       <c r="G43" t="s">
-        <v>246</v>
+        <v>240</v>
       </c>
       <c r="H43" t="s">
         <v>1</v>
@@ -3585,22 +3565,22 @@
     </row>
     <row r="44" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A44" t="s">
-        <v>247</v>
+        <v>242</v>
       </c>
       <c r="C44" t="s">
-        <v>28</v>
+        <v>35</v>
       </c>
       <c r="D44" t="s">
-        <v>248</v>
+        <v>243</v>
       </c>
       <c r="E44" t="s">
-        <v>71</v>
+        <v>244</v>
       </c>
       <c r="F44" t="s">
         <v>0</v>
       </c>
       <c r="G44" t="s">
-        <v>249</v>
+        <v>245</v>
       </c>
       <c r="H44" t="s">
         <v>1</v>
@@ -3608,22 +3588,22 @@
     </row>
     <row r="45" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A45" t="s">
-        <v>250</v>
+        <v>246</v>
       </c>
       <c r="C45" t="s">
-        <v>6</v>
+        <v>28</v>
       </c>
       <c r="D45" t="s">
-        <v>251</v>
+        <v>247</v>
       </c>
       <c r="E45" t="s">
-        <v>252</v>
+        <v>71</v>
       </c>
       <c r="F45" t="s">
-        <v>253</v>
+        <v>0</v>
       </c>
       <c r="G45" t="s">
-        <v>254</v>
+        <v>248</v>
       </c>
       <c r="H45" t="s">
         <v>1</v>
@@ -3631,22 +3611,22 @@
     </row>
     <row r="46" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A46" t="s">
-        <v>255</v>
+        <v>249</v>
       </c>
       <c r="C46" t="s">
-        <v>11</v>
+        <v>6</v>
       </c>
       <c r="D46" t="s">
-        <v>256</v>
+        <v>250</v>
       </c>
       <c r="E46" t="s">
-        <v>147</v>
+        <v>251</v>
       </c>
       <c r="F46" t="s">
-        <v>148</v>
+        <v>252</v>
       </c>
       <c r="G46" t="s">
-        <v>257</v>
+        <v>253</v>
       </c>
       <c r="H46" t="s">
         <v>1</v>
@@ -3654,22 +3634,22 @@
     </row>
     <row r="47" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A47" t="s">
-        <v>258</v>
+        <v>254</v>
       </c>
       <c r="C47" t="s">
         <v>11</v>
       </c>
       <c r="D47" t="s">
+        <v>255</v>
+      </c>
+      <c r="E47" t="s">
+        <v>146</v>
+      </c>
+      <c r="F47" t="s">
+        <v>147</v>
+      </c>
+      <c r="G47" t="s">
         <v>256</v>
-      </c>
-      <c r="E47" t="s">
-        <v>147</v>
-      </c>
-      <c r="F47" t="s">
-        <v>148</v>
-      </c>
-      <c r="G47" t="s">
-        <v>257</v>
       </c>
       <c r="H47" t="s">
         <v>1</v>
@@ -3677,22 +3657,22 @@
     </row>
     <row r="48" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A48" t="s">
-        <v>259</v>
+        <v>257</v>
       </c>
       <c r="C48" t="s">
-        <v>17</v>
+        <v>11</v>
       </c>
       <c r="D48" t="s">
-        <v>260</v>
+        <v>255</v>
       </c>
       <c r="E48" t="s">
-        <v>261</v>
+        <v>146</v>
       </c>
       <c r="F48" t="s">
-        <v>0</v>
+        <v>147</v>
       </c>
       <c r="G48" t="s">
-        <v>262</v>
+        <v>256</v>
       </c>
       <c r="H48" t="s">
         <v>1</v>
@@ -3700,22 +3680,22 @@
     </row>
     <row r="49" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A49" t="s">
-        <v>263</v>
+        <v>258</v>
       </c>
       <c r="C49" t="s">
-        <v>6</v>
+        <v>17</v>
       </c>
       <c r="D49" t="s">
-        <v>264</v>
+        <v>259</v>
       </c>
       <c r="E49" t="s">
-        <v>140</v>
+        <v>260</v>
       </c>
       <c r="F49" t="s">
-        <v>141</v>
+        <v>0</v>
       </c>
       <c r="G49" t="s">
-        <v>265</v>
+        <v>261</v>
       </c>
       <c r="H49" t="s">
         <v>1</v>
@@ -3723,22 +3703,22 @@
     </row>
     <row r="50" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A50" t="s">
-        <v>266</v>
+        <v>262</v>
       </c>
       <c r="C50" t="s">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="D50" t="s">
-        <v>267</v>
+        <v>263</v>
       </c>
       <c r="E50" t="s">
-        <v>268</v>
+        <v>139</v>
       </c>
       <c r="F50" t="s">
-        <v>0</v>
+        <v>140</v>
       </c>
       <c r="G50" t="s">
-        <v>269</v>
+        <v>264</v>
       </c>
       <c r="H50" t="s">
         <v>1</v>
@@ -3746,22 +3726,22 @@
     </row>
     <row r="51" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A51" t="s">
-        <v>270</v>
+        <v>265</v>
       </c>
       <c r="C51" t="s">
         <v>2</v>
       </c>
       <c r="D51" t="s">
+        <v>266</v>
+      </c>
+      <c r="E51" t="s">
         <v>267</v>
       </c>
-      <c r="E51" t="s">
+      <c r="F51" t="s">
+        <v>0</v>
+      </c>
+      <c r="G51" t="s">
         <v>268</v>
-      </c>
-      <c r="F51" t="s">
-        <v>0</v>
-      </c>
-      <c r="G51" t="s">
-        <v>269</v>
       </c>
       <c r="H51" t="s">
         <v>1</v>
@@ -3769,22 +3749,22 @@
     </row>
     <row r="52" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A52" t="s">
-        <v>271</v>
+        <v>269</v>
       </c>
       <c r="C52" t="s">
         <v>2</v>
       </c>
       <c r="D52" t="s">
-        <v>272</v>
+        <v>266</v>
       </c>
       <c r="E52" t="s">
-        <v>18</v>
+        <v>267</v>
       </c>
       <c r="F52" t="s">
-        <v>19</v>
+        <v>0</v>
       </c>
       <c r="G52" t="s">
-        <v>105</v>
+        <v>268</v>
       </c>
       <c r="H52" t="s">
         <v>1</v>
@@ -3792,22 +3772,22 @@
     </row>
     <row r="53" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A53" t="s">
-        <v>273</v>
+        <v>270</v>
       </c>
       <c r="C53" t="s">
-        <v>41</v>
+        <v>2</v>
       </c>
       <c r="D53" t="s">
-        <v>274</v>
+        <v>271</v>
       </c>
       <c r="E53" t="s">
-        <v>7</v>
+        <v>18</v>
       </c>
       <c r="F53" t="s">
-        <v>8</v>
+        <v>19</v>
       </c>
       <c r="G53" t="s">
-        <v>275</v>
+        <v>104</v>
       </c>
       <c r="H53" t="s">
         <v>1</v>
@@ -3815,22 +3795,22 @@
     </row>
     <row r="54" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A54" t="s">
-        <v>276</v>
+        <v>272</v>
       </c>
       <c r="C54" t="s">
-        <v>28</v>
+        <v>41</v>
       </c>
       <c r="D54" t="s">
-        <v>277</v>
+        <v>273</v>
       </c>
       <c r="E54" t="s">
-        <v>71</v>
+        <v>7</v>
       </c>
       <c r="F54" t="s">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="G54" t="s">
-        <v>278</v>
+        <v>274</v>
       </c>
       <c r="H54" t="s">
         <v>1</v>
@@ -3838,22 +3818,22 @@
     </row>
     <row r="55" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A55" t="s">
-        <v>279</v>
+        <v>275</v>
       </c>
       <c r="C55" t="s">
-        <v>133</v>
+        <v>28</v>
       </c>
       <c r="D55" t="s">
-        <v>280</v>
+        <v>276</v>
       </c>
       <c r="E55" t="s">
-        <v>193</v>
+        <v>71</v>
       </c>
       <c r="F55" t="s">
         <v>0</v>
       </c>
       <c r="G55" t="s">
-        <v>128</v>
+        <v>277</v>
       </c>
       <c r="H55" t="s">
         <v>1</v>
@@ -3861,22 +3841,22 @@
     </row>
     <row r="56" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A56" t="s">
-        <v>281</v>
+        <v>278</v>
       </c>
       <c r="C56" t="s">
-        <v>55</v>
+        <v>132</v>
       </c>
       <c r="D56" t="s">
-        <v>282</v>
+        <v>279</v>
       </c>
       <c r="E56" t="s">
-        <v>110</v>
+        <v>192</v>
       </c>
       <c r="F56" t="s">
         <v>0</v>
       </c>
       <c r="G56" t="s">
-        <v>283</v>
+        <v>127</v>
       </c>
       <c r="H56" t="s">
         <v>1</v>
@@ -3884,22 +3864,22 @@
     </row>
     <row r="57" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A57" t="s">
-        <v>284</v>
+        <v>280</v>
       </c>
       <c r="C57" t="s">
-        <v>12</v>
+        <v>55</v>
       </c>
       <c r="D57" t="s">
-        <v>285</v>
+        <v>281</v>
       </c>
       <c r="E57" t="s">
-        <v>286</v>
+        <v>109</v>
       </c>
       <c r="F57" t="s">
         <v>0</v>
       </c>
       <c r="G57" t="s">
-        <v>287</v>
+        <v>282</v>
       </c>
       <c r="H57" t="s">
         <v>1</v>
@@ -3907,22 +3887,22 @@
     </row>
     <row r="58" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A58" t="s">
-        <v>288</v>
+        <v>283</v>
       </c>
       <c r="C58" t="s">
-        <v>55</v>
+        <v>12</v>
       </c>
       <c r="D58" t="s">
-        <v>289</v>
+        <v>284</v>
       </c>
       <c r="E58" t="s">
-        <v>290</v>
+        <v>285</v>
       </c>
       <c r="F58" t="s">
         <v>0</v>
       </c>
       <c r="G58" t="s">
-        <v>291</v>
+        <v>286</v>
       </c>
       <c r="H58" t="s">
         <v>1</v>
@@ -3930,22 +3910,22 @@
     </row>
     <row r="59" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A59" t="s">
-        <v>292</v>
+        <v>287</v>
       </c>
       <c r="C59" t="s">
-        <v>31</v>
+        <v>55</v>
       </c>
       <c r="D59" t="s">
-        <v>293</v>
+        <v>288</v>
       </c>
       <c r="E59" t="s">
-        <v>95</v>
+        <v>289</v>
       </c>
       <c r="F59" t="s">
         <v>0</v>
       </c>
       <c r="G59" t="s">
-        <v>294</v>
+        <v>290</v>
       </c>
       <c r="H59" t="s">
         <v>1</v>
@@ -3953,22 +3933,22 @@
     </row>
     <row r="60" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A60" t="s">
-        <v>295</v>
+        <v>291</v>
       </c>
       <c r="C60" t="s">
-        <v>2</v>
+        <v>31</v>
       </c>
       <c r="D60" t="s">
-        <v>296</v>
+        <v>292</v>
       </c>
       <c r="E60" t="s">
-        <v>297</v>
+        <v>95</v>
       </c>
       <c r="F60" t="s">
         <v>0</v>
       </c>
       <c r="G60" t="s">
-        <v>298</v>
+        <v>293</v>
       </c>
       <c r="H60" t="s">
         <v>1</v>
@@ -3976,68 +3956,68 @@
     </row>
     <row r="61" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A61" t="s">
-        <v>299</v>
+        <v>294</v>
       </c>
       <c r="C61" t="s">
-        <v>24</v>
+        <v>2</v>
       </c>
       <c r="D61" t="s">
-        <v>300</v>
+        <v>295</v>
       </c>
       <c r="E61" t="s">
-        <v>301</v>
+        <v>296</v>
       </c>
       <c r="F61" t="s">
         <v>0</v>
       </c>
       <c r="G61" t="s">
-        <v>302</v>
+        <v>297</v>
       </c>
       <c r="H61" t="s">
-        <v>303</v>
+        <v>1</v>
       </c>
     </row>
     <row r="62" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A62" t="s">
-        <v>304</v>
+        <v>298</v>
       </c>
       <c r="C62" t="s">
-        <v>10</v>
+        <v>24</v>
       </c>
       <c r="D62" t="s">
-        <v>305</v>
+        <v>299</v>
       </c>
       <c r="E62" t="s">
-        <v>169</v>
+        <v>300</v>
       </c>
       <c r="F62" t="s">
         <v>0</v>
       </c>
       <c r="G62" t="s">
-        <v>306</v>
+        <v>301</v>
       </c>
       <c r="H62" t="s">
-        <v>4</v>
+        <v>302</v>
       </c>
     </row>
     <row r="63" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A63" t="s">
-        <v>307</v>
+        <v>303</v>
       </c>
       <c r="C63" t="s">
-        <v>16</v>
+        <v>10</v>
       </c>
       <c r="D63" t="s">
-        <v>308</v>
+        <v>304</v>
       </c>
       <c r="E63" t="s">
-        <v>309</v>
+        <v>168</v>
       </c>
       <c r="F63" t="s">
         <v>0</v>
       </c>
       <c r="G63" t="s">
-        <v>310</v>
+        <v>305</v>
       </c>
       <c r="H63" t="s">
         <v>4</v>
@@ -4045,22 +4025,22 @@
     </row>
     <row r="64" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A64" t="s">
-        <v>311</v>
+        <v>306</v>
       </c>
       <c r="C64" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="D64" t="s">
-        <v>312</v>
+        <v>307</v>
       </c>
       <c r="E64" t="s">
-        <v>313</v>
+        <v>308</v>
       </c>
       <c r="F64" t="s">
         <v>0</v>
       </c>
       <c r="G64" t="s">
-        <v>314</v>
+        <v>309</v>
       </c>
       <c r="H64" t="s">
         <v>4</v>
@@ -4068,22 +4048,22 @@
     </row>
     <row r="65" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A65" t="s">
-        <v>315</v>
+        <v>310</v>
       </c>
       <c r="C65" t="s">
         <v>17</v>
       </c>
       <c r="D65" t="s">
+        <v>311</v>
+      </c>
+      <c r="E65" t="s">
         <v>312</v>
       </c>
-      <c r="E65" t="s">
+      <c r="F65" t="s">
+        <v>0</v>
+      </c>
+      <c r="G65" t="s">
         <v>313</v>
-      </c>
-      <c r="F65" t="s">
-        <v>0</v>
-      </c>
-      <c r="G65" t="s">
-        <v>314</v>
       </c>
       <c r="H65" t="s">
         <v>4</v>
@@ -4091,22 +4071,22 @@
     </row>
     <row r="66" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A66" t="s">
-        <v>316</v>
+        <v>314</v>
       </c>
       <c r="C66" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="D66" t="s">
-        <v>317</v>
+        <v>311</v>
       </c>
       <c r="E66" t="s">
-        <v>309</v>
+        <v>312</v>
       </c>
       <c r="F66" t="s">
         <v>0</v>
       </c>
       <c r="G66" t="s">
-        <v>318</v>
+        <v>313</v>
       </c>
       <c r="H66" t="s">
         <v>4</v>
@@ -4114,22 +4094,22 @@
     </row>
     <row r="67" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A67" t="s">
-        <v>319</v>
+        <v>315</v>
       </c>
       <c r="C67" t="s">
-        <v>39</v>
+        <v>16</v>
       </c>
       <c r="D67" t="s">
-        <v>320</v>
+        <v>316</v>
       </c>
       <c r="E67" t="s">
-        <v>321</v>
+        <v>308</v>
       </c>
       <c r="F67" t="s">
-        <v>38</v>
+        <v>0</v>
       </c>
       <c r="G67" t="s">
-        <v>322</v>
+        <v>317</v>
       </c>
       <c r="H67" t="s">
         <v>4</v>
@@ -4137,22 +4117,22 @@
     </row>
     <row r="68" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A68" t="s">
-        <v>323</v>
+        <v>318</v>
       </c>
       <c r="C68" t="s">
-        <v>35</v>
+        <v>39</v>
       </c>
       <c r="D68" t="s">
-        <v>324</v>
+        <v>319</v>
       </c>
       <c r="E68" t="s">
-        <v>325</v>
+        <v>320</v>
       </c>
       <c r="F68" t="s">
-        <v>0</v>
+        <v>38</v>
       </c>
       <c r="G68" t="s">
-        <v>326</v>
+        <v>321</v>
       </c>
       <c r="H68" t="s">
         <v>4</v>
@@ -4160,22 +4140,22 @@
     </row>
     <row r="69" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A69" t="s">
-        <v>327</v>
+        <v>322</v>
       </c>
       <c r="C69" t="s">
-        <v>2</v>
+        <v>35</v>
       </c>
       <c r="D69" t="s">
-        <v>328</v>
+        <v>323</v>
       </c>
       <c r="E69" t="s">
-        <v>74</v>
+        <v>324</v>
       </c>
       <c r="F69" t="s">
         <v>0</v>
       </c>
       <c r="G69" t="s">
-        <v>329</v>
+        <v>325</v>
       </c>
       <c r="H69" t="s">
         <v>4</v>
@@ -4183,22 +4163,22 @@
     </row>
     <row r="70" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A70" t="s">
-        <v>330</v>
+        <v>326</v>
       </c>
       <c r="C70" t="s">
         <v>2</v>
       </c>
       <c r="D70" t="s">
-        <v>331</v>
+        <v>327</v>
       </c>
       <c r="E70" t="s">
-        <v>183</v>
+        <v>74</v>
       </c>
       <c r="F70" t="s">
-        <v>184</v>
+        <v>0</v>
       </c>
       <c r="G70" t="s">
-        <v>332</v>
+        <v>328</v>
       </c>
       <c r="H70" t="s">
         <v>4</v>
@@ -4206,22 +4186,22 @@
     </row>
     <row r="71" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A71" t="s">
-        <v>333</v>
+        <v>329</v>
       </c>
       <c r="C71" t="s">
         <v>2</v>
       </c>
       <c r="D71" t="s">
+        <v>330</v>
+      </c>
+      <c r="E71" t="s">
+        <v>182</v>
+      </c>
+      <c r="F71" t="s">
+        <v>183</v>
+      </c>
+      <c r="G71" t="s">
         <v>331</v>
-      </c>
-      <c r="E71" t="s">
-        <v>183</v>
-      </c>
-      <c r="F71" t="s">
-        <v>184</v>
-      </c>
-      <c r="G71" t="s">
-        <v>332</v>
       </c>
       <c r="H71" t="s">
         <v>4</v>
@@ -4229,22 +4209,22 @@
     </row>
     <row r="72" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A72" t="s">
-        <v>334</v>
+        <v>332</v>
       </c>
       <c r="C72" t="s">
-        <v>41</v>
+        <v>2</v>
       </c>
       <c r="D72" t="s">
-        <v>335</v>
+        <v>330</v>
       </c>
       <c r="E72" t="s">
-        <v>336</v>
+        <v>182</v>
       </c>
       <c r="F72" t="s">
-        <v>337</v>
+        <v>183</v>
       </c>
       <c r="G72" t="s">
-        <v>37</v>
+        <v>331</v>
       </c>
       <c r="H72" t="s">
         <v>4</v>
@@ -4252,22 +4232,22 @@
     </row>
     <row r="73" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A73" t="s">
-        <v>338</v>
+        <v>333</v>
       </c>
       <c r="C73" t="s">
-        <v>15</v>
+        <v>41</v>
       </c>
       <c r="D73" t="s">
-        <v>339</v>
+        <v>334</v>
       </c>
       <c r="E73" t="s">
-        <v>340</v>
+        <v>335</v>
       </c>
       <c r="F73" t="s">
-        <v>0</v>
+        <v>336</v>
       </c>
       <c r="G73" t="s">
-        <v>341</v>
+        <v>37</v>
       </c>
       <c r="H73" t="s">
         <v>4</v>
@@ -4275,22 +4255,22 @@
     </row>
     <row r="74" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A74" t="s">
-        <v>342</v>
+        <v>337</v>
       </c>
       <c r="C74" t="s">
-        <v>28</v>
+        <v>15</v>
       </c>
       <c r="D74" t="s">
-        <v>343</v>
+        <v>338</v>
       </c>
       <c r="E74" t="s">
-        <v>119</v>
+        <v>339</v>
       </c>
       <c r="F74" t="s">
         <v>0</v>
       </c>
       <c r="G74" t="s">
-        <v>344</v>
+        <v>340</v>
       </c>
       <c r="H74" t="s">
         <v>4</v>
@@ -4298,22 +4278,22 @@
     </row>
     <row r="75" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A75" t="s">
-        <v>72</v>
+        <v>341</v>
       </c>
       <c r="C75" t="s">
-        <v>2</v>
+        <v>28</v>
       </c>
       <c r="D75" t="s">
-        <v>73</v>
+        <v>342</v>
       </c>
       <c r="E75" t="s">
-        <v>74</v>
+        <v>118</v>
       </c>
       <c r="F75" t="s">
         <v>0</v>
       </c>
       <c r="G75" t="s">
-        <v>75</v>
+        <v>343</v>
       </c>
       <c r="H75" t="s">
         <v>4</v>
@@ -4321,22 +4301,22 @@
     </row>
     <row r="76" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A76" t="s">
-        <v>345</v>
+        <v>72</v>
       </c>
       <c r="C76" t="s">
-        <v>14</v>
+        <v>2</v>
       </c>
       <c r="D76" t="s">
-        <v>346</v>
+        <v>73</v>
       </c>
       <c r="E76" t="s">
-        <v>26</v>
+        <v>74</v>
       </c>
       <c r="F76" t="s">
-        <v>27</v>
+        <v>0</v>
       </c>
       <c r="G76" t="s">
-        <v>347</v>
+        <v>75</v>
       </c>
       <c r="H76" t="s">
         <v>4</v>
@@ -4344,22 +4324,22 @@
     </row>
     <row r="77" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A77" t="s">
-        <v>348</v>
+        <v>344</v>
       </c>
       <c r="C77" t="s">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="D77" t="s">
-        <v>349</v>
+        <v>345</v>
       </c>
       <c r="E77" t="s">
-        <v>101</v>
+        <v>26</v>
       </c>
       <c r="F77" t="s">
-        <v>0</v>
+        <v>27</v>
       </c>
       <c r="G77" t="s">
-        <v>350</v>
+        <v>346</v>
       </c>
       <c r="H77" t="s">
         <v>4</v>
@@ -4367,13 +4347,13 @@
     </row>
     <row r="78" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A78" t="s">
-        <v>351</v>
+        <v>347</v>
       </c>
       <c r="C78" t="s">
         <v>17</v>
       </c>
       <c r="D78" t="s">
-        <v>349</v>
+        <v>348</v>
       </c>
       <c r="E78" t="s">
         <v>101</v>
@@ -4382,7 +4362,7 @@
         <v>0</v>
       </c>
       <c r="G78" t="s">
-        <v>350</v>
+        <v>349</v>
       </c>
       <c r="H78" t="s">
         <v>4</v>
@@ -4390,13 +4370,13 @@
     </row>
     <row r="79" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A79" t="s">
-        <v>352</v>
+        <v>350</v>
       </c>
       <c r="C79" t="s">
         <v>17</v>
       </c>
       <c r="D79" t="s">
-        <v>349</v>
+        <v>348</v>
       </c>
       <c r="E79" t="s">
         <v>101</v>
@@ -4405,7 +4385,7 @@
         <v>0</v>
       </c>
       <c r="G79" t="s">
-        <v>350</v>
+        <v>349</v>
       </c>
       <c r="H79" t="s">
         <v>4</v>
@@ -4413,22 +4393,22 @@
     </row>
     <row r="80" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A80" t="s">
-        <v>353</v>
+        <v>351</v>
       </c>
       <c r="C80" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="D80" t="s">
-        <v>354</v>
+        <v>348</v>
       </c>
       <c r="E80" t="s">
-        <v>32</v>
+        <v>101</v>
       </c>
       <c r="F80" t="s">
         <v>0</v>
       </c>
       <c r="G80" t="s">
-        <v>355</v>
+        <v>349</v>
       </c>
       <c r="H80" t="s">
         <v>4</v>
@@ -4436,22 +4416,22 @@
     </row>
     <row r="81" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A81" t="s">
-        <v>356</v>
+        <v>352</v>
       </c>
       <c r="C81" t="s">
-        <v>6</v>
+        <v>15</v>
       </c>
       <c r="D81" t="s">
-        <v>357</v>
+        <v>353</v>
       </c>
       <c r="E81" t="s">
-        <v>98</v>
+        <v>32</v>
       </c>
       <c r="F81" t="s">
-        <v>99</v>
+        <v>0</v>
       </c>
       <c r="G81" t="s">
-        <v>358</v>
+        <v>354</v>
       </c>
       <c r="H81" t="s">
         <v>4</v>
@@ -4459,13 +4439,13 @@
     </row>
     <row r="82" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A82" t="s">
-        <v>359</v>
+        <v>355</v>
       </c>
       <c r="C82" t="s">
         <v>6</v>
       </c>
       <c r="D82" t="s">
-        <v>357</v>
+        <v>356</v>
       </c>
       <c r="E82" t="s">
         <v>98</v>
@@ -4474,7 +4454,7 @@
         <v>99</v>
       </c>
       <c r="G82" t="s">
-        <v>358</v>
+        <v>357</v>
       </c>
       <c r="H82" t="s">
         <v>4</v>
@@ -4482,22 +4462,22 @@
     </row>
     <row r="83" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A83" t="s">
-        <v>360</v>
+        <v>358</v>
       </c>
       <c r="C83" t="s">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="D83" t="s">
-        <v>361</v>
+        <v>356</v>
       </c>
       <c r="E83" t="s">
-        <v>21</v>
+        <v>98</v>
       </c>
       <c r="F83" t="s">
-        <v>0</v>
+        <v>99</v>
       </c>
       <c r="G83" t="s">
-        <v>118</v>
+        <v>357</v>
       </c>
       <c r="H83" t="s">
         <v>4</v>
@@ -4505,13 +4485,13 @@
     </row>
     <row r="84" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A84" t="s">
-        <v>362</v>
+        <v>359</v>
       </c>
       <c r="C84" t="s">
         <v>12</v>
       </c>
       <c r="D84" t="s">
-        <v>361</v>
+        <v>360</v>
       </c>
       <c r="E84" t="s">
         <v>21</v>
@@ -4520,7 +4500,7 @@
         <v>0</v>
       </c>
       <c r="G84" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="H84" t="s">
         <v>4</v>
@@ -4528,22 +4508,22 @@
     </row>
     <row r="85" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A85" t="s">
-        <v>363</v>
+        <v>361</v>
       </c>
       <c r="C85" t="s">
-        <v>16</v>
+        <v>12</v>
       </c>
       <c r="D85" t="s">
-        <v>364</v>
+        <v>360</v>
       </c>
       <c r="E85" t="s">
-        <v>365</v>
+        <v>21</v>
       </c>
       <c r="F85" t="s">
         <v>0</v>
       </c>
       <c r="G85" t="s">
-        <v>366</v>
+        <v>117</v>
       </c>
       <c r="H85" t="s">
         <v>4</v>
@@ -4551,22 +4531,22 @@
     </row>
     <row r="86" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A86" t="s">
-        <v>367</v>
+        <v>362</v>
       </c>
       <c r="C86" t="s">
         <v>16</v>
       </c>
       <c r="D86" t="s">
+        <v>363</v>
+      </c>
+      <c r="E86" t="s">
         <v>364</v>
       </c>
-      <c r="E86" t="s">
+      <c r="F86" t="s">
+        <v>0</v>
+      </c>
+      <c r="G86" t="s">
         <v>365</v>
-      </c>
-      <c r="F86" t="s">
-        <v>0</v>
-      </c>
-      <c r="G86" t="s">
-        <v>366</v>
       </c>
       <c r="H86" t="s">
         <v>4</v>
@@ -4574,22 +4554,22 @@
     </row>
     <row r="87" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A87" t="s">
-        <v>368</v>
+        <v>366</v>
       </c>
       <c r="C87" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="D87" t="s">
-        <v>369</v>
+        <v>363</v>
       </c>
       <c r="E87" t="s">
-        <v>370</v>
+        <v>364</v>
       </c>
       <c r="F87" t="s">
         <v>0</v>
       </c>
       <c r="G87" t="s">
-        <v>371</v>
+        <v>365</v>
       </c>
       <c r="H87" t="s">
         <v>4</v>
@@ -4597,22 +4577,22 @@
     </row>
     <row r="88" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A88" t="s">
-        <v>372</v>
+        <v>367</v>
       </c>
       <c r="C88" t="s">
         <v>17</v>
       </c>
       <c r="D88" t="s">
+        <v>368</v>
+      </c>
+      <c r="E88" t="s">
         <v>369</v>
       </c>
-      <c r="E88" t="s">
+      <c r="F88" t="s">
+        <v>0</v>
+      </c>
+      <c r="G88" t="s">
         <v>370</v>
-      </c>
-      <c r="F88" t="s">
-        <v>0</v>
-      </c>
-      <c r="G88" t="s">
-        <v>371</v>
       </c>
       <c r="H88" t="s">
         <v>4</v>
@@ -4620,22 +4600,22 @@
     </row>
     <row r="89" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A89" t="s">
-        <v>373</v>
+        <v>371</v>
       </c>
       <c r="C89" t="s">
-        <v>133</v>
+        <v>17</v>
       </c>
       <c r="D89" t="s">
-        <v>374</v>
+        <v>368</v>
       </c>
       <c r="E89" t="s">
-        <v>375</v>
+        <v>369</v>
       </c>
       <c r="F89" t="s">
-        <v>376</v>
+        <v>0</v>
       </c>
       <c r="G89" t="s">
-        <v>377</v>
+        <v>370</v>
       </c>
       <c r="H89" t="s">
         <v>4</v>
@@ -4643,22 +4623,22 @@
     </row>
     <row r="90" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A90" t="s">
-        <v>378</v>
+        <v>372</v>
       </c>
       <c r="C90" t="s">
-        <v>35</v>
+        <v>132</v>
       </c>
       <c r="D90" t="s">
-        <v>379</v>
+        <v>373</v>
       </c>
       <c r="E90" t="s">
-        <v>380</v>
+        <v>374</v>
       </c>
       <c r="F90" t="s">
-        <v>0</v>
+        <v>375</v>
       </c>
       <c r="G90" t="s">
-        <v>381</v>
+        <v>376</v>
       </c>
       <c r="H90" t="s">
         <v>4</v>
@@ -4666,22 +4646,22 @@
     </row>
     <row r="91" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A91" t="s">
-        <v>382</v>
+        <v>377</v>
       </c>
       <c r="C91" t="s">
         <v>35</v>
       </c>
       <c r="D91" t="s">
+        <v>378</v>
+      </c>
+      <c r="E91" t="s">
         <v>379</v>
       </c>
-      <c r="E91" t="s">
+      <c r="F91" t="s">
+        <v>0</v>
+      </c>
+      <c r="G91" t="s">
         <v>380</v>
-      </c>
-      <c r="F91" t="s">
-        <v>0</v>
-      </c>
-      <c r="G91" t="s">
-        <v>381</v>
       </c>
       <c r="H91" t="s">
         <v>4</v>
@@ -4689,22 +4669,22 @@
     </row>
     <row r="92" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A92" t="s">
-        <v>383</v>
+        <v>381</v>
       </c>
       <c r="C92" t="s">
-        <v>86</v>
+        <v>35</v>
       </c>
       <c r="D92" t="s">
-        <v>384</v>
+        <v>378</v>
       </c>
       <c r="E92" t="s">
-        <v>385</v>
+        <v>379</v>
       </c>
       <c r="F92" t="s">
-        <v>386</v>
+        <v>0</v>
       </c>
       <c r="G92" t="s">
-        <v>387</v>
+        <v>380</v>
       </c>
       <c r="H92" t="s">
         <v>4</v>
@@ -4712,22 +4692,22 @@
     </row>
     <row r="93" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A93" t="s">
-        <v>388</v>
+        <v>382</v>
       </c>
       <c r="C93" t="s">
         <v>86</v>
       </c>
       <c r="D93" t="s">
+        <v>383</v>
+      </c>
+      <c r="E93" t="s">
         <v>384</v>
       </c>
-      <c r="E93" t="s">
+      <c r="F93" t="s">
         <v>385</v>
       </c>
-      <c r="F93" t="s">
+      <c r="G93" t="s">
         <v>386</v>
-      </c>
-      <c r="G93" t="s">
-        <v>387</v>
       </c>
       <c r="H93" t="s">
         <v>4</v>
@@ -4735,22 +4715,22 @@
     </row>
     <row r="94" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A94" t="s">
-        <v>389</v>
+        <v>387</v>
       </c>
       <c r="C94" t="s">
-        <v>16</v>
+        <v>86</v>
       </c>
       <c r="D94" t="s">
-        <v>390</v>
+        <v>383</v>
       </c>
       <c r="E94" t="s">
-        <v>53</v>
+        <v>384</v>
       </c>
       <c r="F94" t="s">
-        <v>0</v>
+        <v>385</v>
       </c>
       <c r="G94" t="s">
-        <v>391</v>
+        <v>386</v>
       </c>
       <c r="H94" t="s">
         <v>4</v>
@@ -4758,22 +4738,22 @@
     </row>
     <row r="95" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A95" t="s">
-        <v>392</v>
+        <v>388</v>
       </c>
       <c r="C95" t="s">
-        <v>41</v>
+        <v>16</v>
       </c>
       <c r="D95" t="s">
-        <v>393</v>
+        <v>389</v>
       </c>
       <c r="E95" t="s">
-        <v>394</v>
+        <v>53</v>
       </c>
       <c r="F95" t="s">
-        <v>395</v>
+        <v>0</v>
       </c>
       <c r="G95" t="s">
-        <v>396</v>
+        <v>390</v>
       </c>
       <c r="H95" t="s">
         <v>4</v>
@@ -4781,22 +4761,22 @@
     </row>
     <row r="96" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A96" t="s">
-        <v>397</v>
+        <v>391</v>
       </c>
       <c r="C96" t="s">
-        <v>398</v>
+        <v>41</v>
       </c>
       <c r="D96" t="s">
-        <v>399</v>
+        <v>392</v>
       </c>
       <c r="E96" t="s">
-        <v>84</v>
+        <v>393</v>
       </c>
       <c r="F96" t="s">
-        <v>0</v>
+        <v>394</v>
       </c>
       <c r="G96" t="s">
-        <v>400</v>
+        <v>395</v>
       </c>
       <c r="H96" t="s">
         <v>4</v>
@@ -4804,22 +4784,22 @@
     </row>
     <row r="97" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A97" t="s">
-        <v>401</v>
+        <v>396</v>
       </c>
       <c r="C97" t="s">
-        <v>14</v>
+        <v>397</v>
       </c>
       <c r="D97" t="s">
-        <v>402</v>
+        <v>398</v>
       </c>
       <c r="E97" t="s">
-        <v>26</v>
+        <v>84</v>
       </c>
       <c r="F97" t="s">
-        <v>27</v>
+        <v>0</v>
       </c>
       <c r="G97" t="s">
-        <v>403</v>
+        <v>399</v>
       </c>
       <c r="H97" t="s">
         <v>4</v>
@@ -4827,13 +4807,13 @@
     </row>
     <row r="98" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A98" t="s">
-        <v>404</v>
+        <v>400</v>
       </c>
       <c r="C98" t="s">
         <v>14</v>
       </c>
       <c r="D98" t="s">
-        <v>402</v>
+        <v>401</v>
       </c>
       <c r="E98" t="s">
         <v>26</v>
@@ -4842,7 +4822,7 @@
         <v>27</v>
       </c>
       <c r="G98" t="s">
-        <v>403</v>
+        <v>402</v>
       </c>
       <c r="H98" t="s">
         <v>4</v>
@@ -4850,13 +4830,13 @@
     </row>
     <row r="99" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A99" t="s">
-        <v>405</v>
+        <v>403</v>
       </c>
       <c r="C99" t="s">
         <v>14</v>
       </c>
       <c r="D99" t="s">
-        <v>402</v>
+        <v>401</v>
       </c>
       <c r="E99" t="s">
         <v>26</v>
@@ -4865,7 +4845,7 @@
         <v>27</v>
       </c>
       <c r="G99" t="s">
-        <v>403</v>
+        <v>402</v>
       </c>
       <c r="H99" t="s">
         <v>4</v>
@@ -4873,22 +4853,22 @@
     </row>
     <row r="100" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A100" t="s">
-        <v>406</v>
+        <v>404</v>
       </c>
       <c r="C100" t="s">
         <v>14</v>
       </c>
       <c r="D100" t="s">
-        <v>407</v>
+        <v>401</v>
       </c>
       <c r="E100" t="s">
-        <v>408</v>
+        <v>26</v>
       </c>
       <c r="F100" t="s">
-        <v>409</v>
+        <v>27</v>
       </c>
       <c r="G100" t="s">
-        <v>410</v>
+        <v>402</v>
       </c>
       <c r="H100" t="s">
         <v>4</v>
@@ -4896,22 +4876,22 @@
     </row>
     <row r="101" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A101" t="s">
-        <v>411</v>
+        <v>405</v>
       </c>
       <c r="C101" t="s">
         <v>14</v>
       </c>
       <c r="D101" t="s">
-        <v>412</v>
+        <v>406</v>
       </c>
       <c r="E101" t="s">
-        <v>178</v>
+        <v>407</v>
       </c>
       <c r="F101" t="s">
-        <v>179</v>
+        <v>408</v>
       </c>
       <c r="G101" t="s">
-        <v>413</v>
+        <v>409</v>
       </c>
       <c r="H101" t="s">
         <v>4</v>
@@ -4919,22 +4899,22 @@
     </row>
     <row r="102" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A102" t="s">
-        <v>414</v>
+        <v>410</v>
       </c>
       <c r="C102" t="s">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="D102" t="s">
-        <v>415</v>
+        <v>411</v>
       </c>
       <c r="E102" t="s">
-        <v>76</v>
+        <v>177</v>
       </c>
       <c r="F102" t="s">
-        <v>77</v>
+        <v>178</v>
       </c>
       <c r="G102" t="s">
-        <v>416</v>
+        <v>412</v>
       </c>
       <c r="H102" t="s">
         <v>4</v>
@@ -4942,22 +4922,22 @@
     </row>
     <row r="103" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A103" t="s">
-        <v>417</v>
+        <v>413</v>
       </c>
       <c r="C103" t="s">
-        <v>133</v>
+        <v>10</v>
       </c>
       <c r="D103" t="s">
-        <v>418</v>
+        <v>414</v>
       </c>
       <c r="E103" t="s">
-        <v>419</v>
+        <v>76</v>
       </c>
       <c r="F103" t="s">
-        <v>0</v>
+        <v>77</v>
       </c>
       <c r="G103" t="s">
-        <v>420</v>
+        <v>415</v>
       </c>
       <c r="H103" t="s">
         <v>4</v>
@@ -4965,22 +4945,22 @@
     </row>
     <row r="104" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A104" t="s">
-        <v>421</v>
+        <v>416</v>
       </c>
       <c r="C104" t="s">
-        <v>6</v>
+        <v>132</v>
       </c>
       <c r="D104" t="s">
-        <v>422</v>
+        <v>417</v>
       </c>
       <c r="E104" t="s">
-        <v>423</v>
+        <v>418</v>
       </c>
       <c r="F104" t="s">
-        <v>424</v>
+        <v>0</v>
       </c>
       <c r="G104" t="s">
-        <v>425</v>
+        <v>419</v>
       </c>
       <c r="H104" t="s">
         <v>4</v>
@@ -4988,22 +4968,22 @@
     </row>
     <row r="105" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A105" t="s">
-        <v>426</v>
+        <v>420</v>
       </c>
       <c r="C105" t="s">
-        <v>133</v>
+        <v>6</v>
       </c>
       <c r="D105" t="s">
-        <v>427</v>
+        <v>421</v>
       </c>
       <c r="E105" t="s">
-        <v>419</v>
+        <v>422</v>
       </c>
       <c r="F105" t="s">
-        <v>0</v>
+        <v>423</v>
       </c>
       <c r="G105" t="s">
-        <v>428</v>
+        <v>424</v>
       </c>
       <c r="H105" t="s">
         <v>4</v>
@@ -5011,22 +4991,22 @@
     </row>
     <row r="106" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A106" t="s">
-        <v>429</v>
+        <v>425</v>
       </c>
       <c r="C106" t="s">
-        <v>11</v>
+        <v>132</v>
       </c>
       <c r="D106" t="s">
-        <v>430</v>
+        <v>426</v>
       </c>
       <c r="E106" t="s">
-        <v>213</v>
+        <v>418</v>
       </c>
       <c r="F106" t="s">
-        <v>214</v>
+        <v>0</v>
       </c>
       <c r="G106" t="s">
-        <v>431</v>
+        <v>427</v>
       </c>
       <c r="H106" t="s">
         <v>4</v>
@@ -5034,22 +5014,22 @@
     </row>
     <row r="107" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A107" t="s">
-        <v>432</v>
+        <v>428</v>
       </c>
       <c r="C107" t="s">
-        <v>28</v>
+        <v>11</v>
       </c>
       <c r="D107" t="s">
-        <v>433</v>
+        <v>429</v>
       </c>
       <c r="E107" t="s">
-        <v>434</v>
+        <v>212</v>
       </c>
       <c r="F107" t="s">
-        <v>0</v>
+        <v>213</v>
       </c>
       <c r="G107" t="s">
-        <v>435</v>
+        <v>430</v>
       </c>
       <c r="H107" t="s">
         <v>4</v>
@@ -5057,22 +5037,22 @@
     </row>
     <row r="108" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A108" t="s">
-        <v>436</v>
+        <v>431</v>
       </c>
       <c r="C108" t="s">
-        <v>12</v>
+        <v>28</v>
       </c>
       <c r="D108" t="s">
-        <v>437</v>
+        <v>432</v>
       </c>
       <c r="E108" t="s">
-        <v>438</v>
+        <v>433</v>
       </c>
       <c r="F108" t="s">
         <v>0</v>
       </c>
       <c r="G108" t="s">
-        <v>96</v>
+        <v>434</v>
       </c>
       <c r="H108" t="s">
         <v>4</v>
@@ -5080,22 +5060,22 @@
     </row>
     <row r="109" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A109" t="s">
-        <v>439</v>
+        <v>435</v>
       </c>
       <c r="C109" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="D109" t="s">
-        <v>440</v>
+        <v>436</v>
       </c>
       <c r="E109" t="s">
-        <v>80</v>
+        <v>437</v>
       </c>
       <c r="F109" t="s">
         <v>0</v>
       </c>
       <c r="G109" t="s">
-        <v>441</v>
+        <v>96</v>
       </c>
       <c r="H109" t="s">
         <v>4</v>
@@ -5103,22 +5083,22 @@
     </row>
     <row r="110" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A110" t="s">
-        <v>442</v>
+        <v>438</v>
       </c>
       <c r="C110" t="s">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="D110" t="s">
-        <v>443</v>
+        <v>439</v>
       </c>
       <c r="E110" t="s">
-        <v>32</v>
+        <v>80</v>
       </c>
       <c r="F110" t="s">
         <v>0</v>
       </c>
       <c r="G110" t="s">
-        <v>444</v>
+        <v>440</v>
       </c>
       <c r="H110" t="s">
         <v>4</v>
@@ -5126,22 +5106,22 @@
     </row>
     <row r="111" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A111" t="s">
-        <v>445</v>
+        <v>441</v>
       </c>
       <c r="C111" t="s">
-        <v>35</v>
+        <v>15</v>
       </c>
       <c r="D111" t="s">
-        <v>446</v>
+        <v>442</v>
       </c>
       <c r="E111" t="s">
-        <v>44</v>
+        <v>32</v>
       </c>
       <c r="F111" t="s">
         <v>0</v>
       </c>
       <c r="G111" t="s">
-        <v>447</v>
+        <v>443</v>
       </c>
       <c r="H111" t="s">
         <v>4</v>
@@ -5149,22 +5129,22 @@
     </row>
     <row r="112" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A112" t="s">
-        <v>448</v>
+        <v>444</v>
       </c>
       <c r="C112" t="s">
-        <v>6</v>
+        <v>35</v>
       </c>
       <c r="D112" t="s">
-        <v>449</v>
+        <v>445</v>
       </c>
       <c r="E112" t="s">
-        <v>423</v>
+        <v>44</v>
       </c>
       <c r="F112" t="s">
-        <v>424</v>
+        <v>0</v>
       </c>
       <c r="G112" t="s">
-        <v>450</v>
+        <v>446</v>
       </c>
       <c r="H112" t="s">
         <v>4</v>
@@ -5172,22 +5152,22 @@
     </row>
     <row r="113" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A113" t="s">
-        <v>451</v>
+        <v>447</v>
       </c>
       <c r="C113" t="s">
-        <v>86</v>
+        <v>6</v>
       </c>
       <c r="D113" t="s">
-        <v>452</v>
+        <v>448</v>
       </c>
       <c r="E113" t="s">
-        <v>453</v>
+        <v>422</v>
       </c>
       <c r="F113" t="s">
-        <v>0</v>
+        <v>423</v>
       </c>
       <c r="G113" t="s">
-        <v>454</v>
+        <v>449</v>
       </c>
       <c r="H113" t="s">
         <v>4</v>
@@ -5195,22 +5175,22 @@
     </row>
     <row r="114" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A114" t="s">
-        <v>92</v>
+        <v>450</v>
       </c>
       <c r="C114" t="s">
-        <v>15</v>
+        <v>86</v>
       </c>
       <c r="D114" t="s">
-        <v>93</v>
+        <v>451</v>
       </c>
       <c r="E114" t="s">
-        <v>94</v>
+        <v>452</v>
       </c>
       <c r="F114" t="s">
         <v>0</v>
       </c>
       <c r="G114" t="s">
-        <v>48</v>
+        <v>453</v>
       </c>
       <c r="H114" t="s">
         <v>4</v>
@@ -5218,22 +5198,22 @@
     </row>
     <row r="115" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A115" t="s">
-        <v>455</v>
+        <v>92</v>
       </c>
       <c r="C115" t="s">
-        <v>28</v>
+        <v>15</v>
       </c>
       <c r="D115" t="s">
-        <v>456</v>
+        <v>93</v>
       </c>
       <c r="E115" t="s">
-        <v>457</v>
+        <v>94</v>
       </c>
       <c r="F115" t="s">
         <v>0</v>
       </c>
       <c r="G115" t="s">
-        <v>458</v>
+        <v>48</v>
       </c>
       <c r="H115" t="s">
         <v>4</v>
@@ -5241,22 +5221,22 @@
     </row>
     <row r="116" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A116" t="s">
-        <v>459</v>
+        <v>454</v>
       </c>
       <c r="C116" t="s">
         <v>28</v>
       </c>
       <c r="D116" t="s">
-        <v>460</v>
+        <v>455</v>
       </c>
       <c r="E116" t="s">
-        <v>40</v>
+        <v>456</v>
       </c>
       <c r="F116" t="s">
         <v>0</v>
       </c>
       <c r="G116" t="s">
-        <v>49</v>
+        <v>457</v>
       </c>
       <c r="H116" t="s">
         <v>4</v>
@@ -5264,22 +5244,22 @@
     </row>
     <row r="117" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A117" t="s">
-        <v>461</v>
+        <v>458</v>
       </c>
       <c r="C117" t="s">
-        <v>3</v>
+        <v>28</v>
       </c>
       <c r="D117" t="s">
-        <v>462</v>
+        <v>459</v>
       </c>
       <c r="E117" t="s">
-        <v>45</v>
+        <v>40</v>
       </c>
       <c r="F117" t="s">
         <v>0</v>
       </c>
       <c r="G117" t="s">
-        <v>463</v>
+        <v>49</v>
       </c>
       <c r="H117" t="s">
         <v>4</v>
@@ -5287,22 +5267,22 @@
     </row>
     <row r="118" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A118" t="s">
-        <v>464</v>
+        <v>460</v>
       </c>
       <c r="C118" t="s">
-        <v>17</v>
+        <v>3</v>
       </c>
       <c r="D118" t="s">
-        <v>465</v>
+        <v>461</v>
       </c>
       <c r="E118" t="s">
-        <v>466</v>
+        <v>45</v>
       </c>
       <c r="F118" t="s">
         <v>0</v>
       </c>
       <c r="G118" t="s">
-        <v>467</v>
+        <v>462</v>
       </c>
       <c r="H118" t="s">
         <v>4</v>
@@ -5310,22 +5290,22 @@
     </row>
     <row r="119" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A119" t="s">
-        <v>468</v>
+        <v>463</v>
       </c>
       <c r="C119" t="s">
-        <v>10</v>
+        <v>17</v>
       </c>
       <c r="D119" t="s">
-        <v>469</v>
+        <v>464</v>
       </c>
       <c r="E119" t="s">
-        <v>80</v>
+        <v>465</v>
       </c>
       <c r="F119" t="s">
         <v>0</v>
       </c>
       <c r="G119" t="s">
-        <v>470</v>
+        <v>466</v>
       </c>
       <c r="H119" t="s">
         <v>4</v>
@@ -5333,22 +5313,22 @@
     </row>
     <row r="120" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A120" t="s">
-        <v>471</v>
+        <v>467</v>
       </c>
       <c r="C120" t="s">
-        <v>28</v>
+        <v>10</v>
       </c>
       <c r="D120" t="s">
-        <v>472</v>
+        <v>468</v>
       </c>
       <c r="E120" t="s">
-        <v>71</v>
+        <v>80</v>
       </c>
       <c r="F120" t="s">
         <v>0</v>
       </c>
       <c r="G120" t="s">
-        <v>473</v>
+        <v>469</v>
       </c>
       <c r="H120" t="s">
         <v>4</v>
@@ -5356,22 +5336,22 @@
     </row>
     <row r="121" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A121" t="s">
-        <v>474</v>
+        <v>470</v>
       </c>
       <c r="C121" t="s">
-        <v>11</v>
+        <v>28</v>
       </c>
       <c r="D121" t="s">
-        <v>475</v>
+        <v>471</v>
       </c>
       <c r="E121" t="s">
-        <v>147</v>
+        <v>71</v>
       </c>
       <c r="F121" t="s">
-        <v>148</v>
+        <v>0</v>
       </c>
       <c r="G121" t="s">
-        <v>476</v>
+        <v>472</v>
       </c>
       <c r="H121" t="s">
         <v>4</v>
@@ -5379,22 +5359,22 @@
     </row>
     <row r="122" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A122" t="s">
-        <v>477</v>
+        <v>473</v>
       </c>
       <c r="C122" t="s">
-        <v>41</v>
+        <v>11</v>
       </c>
       <c r="D122" t="s">
-        <v>478</v>
+        <v>474</v>
       </c>
       <c r="E122" t="s">
-        <v>7</v>
+        <v>146</v>
       </c>
       <c r="F122" t="s">
-        <v>8</v>
+        <v>147</v>
       </c>
       <c r="G122" t="s">
-        <v>479</v>
+        <v>475</v>
       </c>
       <c r="H122" t="s">
         <v>4</v>
@@ -5402,13 +5382,13 @@
     </row>
     <row r="123" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A123" t="s">
-        <v>480</v>
+        <v>476</v>
       </c>
       <c r="C123" t="s">
         <v>41</v>
       </c>
       <c r="D123" t="s">
-        <v>478</v>
+        <v>477</v>
       </c>
       <c r="E123" t="s">
         <v>7</v>
@@ -5417,7 +5397,7 @@
         <v>8</v>
       </c>
       <c r="G123" t="s">
-        <v>479</v>
+        <v>478</v>
       </c>
       <c r="H123" t="s">
         <v>4</v>
@@ -5425,22 +5405,22 @@
     </row>
     <row r="124" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A124" t="s">
-        <v>481</v>
+        <v>479</v>
       </c>
       <c r="C124" t="s">
-        <v>11</v>
+        <v>41</v>
       </c>
       <c r="D124" t="s">
-        <v>482</v>
+        <v>477</v>
       </c>
       <c r="E124" t="s">
-        <v>213</v>
+        <v>7</v>
       </c>
       <c r="F124" t="s">
-        <v>214</v>
+        <v>8</v>
       </c>
       <c r="G124" t="s">
-        <v>381</v>
+        <v>478</v>
       </c>
       <c r="H124" t="s">
         <v>4</v>
@@ -5448,22 +5428,22 @@
     </row>
     <row r="125" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A125" t="s">
-        <v>483</v>
+        <v>480</v>
       </c>
       <c r="C125" t="s">
         <v>11</v>
       </c>
       <c r="D125" t="s">
-        <v>482</v>
+        <v>481</v>
       </c>
       <c r="E125" t="s">
+        <v>212</v>
+      </c>
+      <c r="F125" t="s">
         <v>213</v>
       </c>
-      <c r="F125" t="s">
-        <v>214</v>
-      </c>
       <c r="G125" t="s">
-        <v>381</v>
+        <v>380</v>
       </c>
       <c r="H125" t="s">
         <v>4</v>
@@ -5471,22 +5451,22 @@
     </row>
     <row r="126" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A126" t="s">
-        <v>484</v>
+        <v>482</v>
       </c>
       <c r="C126" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="D126" t="s">
-        <v>485</v>
+        <v>481</v>
       </c>
       <c r="E126" t="s">
-        <v>117</v>
+        <v>212</v>
       </c>
       <c r="F126" t="s">
-        <v>0</v>
+        <v>213</v>
       </c>
       <c r="G126" t="s">
-        <v>486</v>
+        <v>380</v>
       </c>
       <c r="H126" t="s">
         <v>4</v>
@@ -5494,22 +5474,22 @@
     </row>
     <row r="127" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A127" t="s">
-        <v>487</v>
+        <v>483</v>
       </c>
       <c r="C127" t="s">
-        <v>28</v>
+        <v>12</v>
       </c>
       <c r="D127" t="s">
-        <v>488</v>
+        <v>484</v>
       </c>
       <c r="E127" t="s">
-        <v>489</v>
+        <v>116</v>
       </c>
       <c r="F127" t="s">
         <v>0</v>
       </c>
       <c r="G127" t="s">
-        <v>490</v>
+        <v>485</v>
       </c>
       <c r="H127" t="s">
         <v>4</v>
@@ -5517,22 +5497,22 @@
     </row>
     <row r="128" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A128" t="s">
-        <v>491</v>
+        <v>486</v>
       </c>
       <c r="C128" t="s">
         <v>28</v>
       </c>
       <c r="D128" t="s">
+        <v>487</v>
+      </c>
+      <c r="E128" t="s">
         <v>488</v>
       </c>
-      <c r="E128" t="s">
+      <c r="F128" t="s">
+        <v>0</v>
+      </c>
+      <c r="G128" t="s">
         <v>489</v>
-      </c>
-      <c r="F128" t="s">
-        <v>0</v>
-      </c>
-      <c r="G128" t="s">
-        <v>490</v>
       </c>
       <c r="H128" t="s">
         <v>4</v>
@@ -5540,22 +5520,22 @@
     </row>
     <row r="129" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A129" t="s">
-        <v>492</v>
+        <v>490</v>
       </c>
       <c r="C129" t="s">
-        <v>9</v>
+        <v>28</v>
       </c>
       <c r="D129" t="s">
-        <v>493</v>
+        <v>487</v>
       </c>
       <c r="E129" t="s">
-        <v>61</v>
+        <v>488</v>
       </c>
       <c r="F129" t="s">
         <v>0</v>
       </c>
       <c r="G129" t="s">
-        <v>494</v>
+        <v>489</v>
       </c>
       <c r="H129" t="s">
         <v>4</v>
@@ -5563,13 +5543,13 @@
     </row>
     <row r="130" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A130" t="s">
-        <v>495</v>
+        <v>491</v>
       </c>
       <c r="C130" t="s">
         <v>9</v>
       </c>
       <c r="D130" t="s">
-        <v>493</v>
+        <v>492</v>
       </c>
       <c r="E130" t="s">
         <v>61</v>
@@ -5578,7 +5558,7 @@
         <v>0</v>
       </c>
       <c r="G130" t="s">
-        <v>494</v>
+        <v>493</v>
       </c>
       <c r="H130" t="s">
         <v>4</v>
@@ -5586,22 +5566,22 @@
     </row>
     <row r="131" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A131" t="s">
-        <v>496</v>
+        <v>494</v>
       </c>
       <c r="C131" t="s">
-        <v>31</v>
+        <v>9</v>
       </c>
       <c r="D131" t="s">
-        <v>497</v>
+        <v>492</v>
       </c>
       <c r="E131" t="s">
-        <v>109</v>
+        <v>61</v>
       </c>
       <c r="F131" t="s">
         <v>0</v>
       </c>
       <c r="G131" t="s">
-        <v>498</v>
+        <v>493</v>
       </c>
       <c r="H131" t="s">
         <v>4</v>
@@ -5609,22 +5589,22 @@
     </row>
     <row r="132" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A132" t="s">
-        <v>499</v>
+        <v>495</v>
       </c>
       <c r="C132" t="s">
         <v>31</v>
       </c>
       <c r="D132" t="s">
+        <v>496</v>
+      </c>
+      <c r="E132" t="s">
+        <v>108</v>
+      </c>
+      <c r="F132" t="s">
+        <v>0</v>
+      </c>
+      <c r="G132" t="s">
         <v>497</v>
-      </c>
-      <c r="E132" t="s">
-        <v>109</v>
-      </c>
-      <c r="F132" t="s">
-        <v>0</v>
-      </c>
-      <c r="G132" t="s">
-        <v>498</v>
       </c>
       <c r="H132" t="s">
         <v>4</v>
@@ -5632,22 +5612,22 @@
     </row>
     <row r="133" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A133" t="s">
-        <v>500</v>
+        <v>498</v>
       </c>
       <c r="C133" t="s">
-        <v>54</v>
+        <v>31</v>
       </c>
       <c r="D133" t="s">
-        <v>501</v>
+        <v>496</v>
       </c>
       <c r="E133" t="s">
-        <v>115</v>
+        <v>108</v>
       </c>
       <c r="F133" t="s">
-        <v>116</v>
+        <v>0</v>
       </c>
       <c r="G133" t="s">
-        <v>502</v>
+        <v>497</v>
       </c>
       <c r="H133" t="s">
         <v>4</v>
@@ -5655,22 +5635,22 @@
     </row>
     <row r="134" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A134" t="s">
-        <v>503</v>
+        <v>499</v>
       </c>
       <c r="C134" t="s">
-        <v>12</v>
+        <v>54</v>
       </c>
       <c r="D134" t="s">
-        <v>504</v>
+        <v>500</v>
       </c>
       <c r="E134" t="s">
-        <v>21</v>
+        <v>114</v>
       </c>
       <c r="F134" t="s">
-        <v>0</v>
+        <v>115</v>
       </c>
       <c r="G134" t="s">
-        <v>46</v>
+        <v>501</v>
       </c>
       <c r="H134" t="s">
         <v>4</v>
@@ -5678,22 +5658,22 @@
     </row>
     <row r="135" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A135" t="s">
-        <v>505</v>
+        <v>502</v>
       </c>
       <c r="C135" t="s">
-        <v>86</v>
+        <v>12</v>
       </c>
       <c r="D135" t="s">
-        <v>506</v>
+        <v>503</v>
       </c>
       <c r="E135" t="s">
-        <v>507</v>
+        <v>21</v>
       </c>
       <c r="F135" t="s">
-        <v>508</v>
+        <v>0</v>
       </c>
       <c r="G135" t="s">
-        <v>509</v>
+        <v>46</v>
       </c>
       <c r="H135" t="s">
         <v>4</v>
@@ -5701,22 +5681,22 @@
     </row>
     <row r="136" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A136" t="s">
-        <v>510</v>
+        <v>504</v>
       </c>
       <c r="C136" t="s">
-        <v>3</v>
+        <v>86</v>
       </c>
       <c r="D136" t="s">
-        <v>511</v>
+        <v>505</v>
       </c>
       <c r="E136" t="s">
-        <v>45</v>
+        <v>506</v>
       </c>
       <c r="F136" t="s">
-        <v>0</v>
+        <v>507</v>
       </c>
       <c r="G136" t="s">
-        <v>512</v>
+        <v>508</v>
       </c>
       <c r="H136" t="s">
         <v>4</v>
@@ -5724,22 +5704,22 @@
     </row>
     <row r="137" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A137" t="s">
-        <v>513</v>
+        <v>509</v>
       </c>
       <c r="C137" t="s">
-        <v>14</v>
+        <v>3</v>
       </c>
       <c r="D137" t="s">
-        <v>514</v>
+        <v>510</v>
       </c>
       <c r="E137" t="s">
-        <v>42</v>
+        <v>45</v>
       </c>
       <c r="F137" t="s">
-        <v>43</v>
+        <v>0</v>
       </c>
       <c r="G137" t="s">
-        <v>515</v>
+        <v>511</v>
       </c>
       <c r="H137" t="s">
         <v>4</v>
@@ -5747,13 +5727,13 @@
     </row>
     <row r="138" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A138" t="s">
-        <v>516</v>
+        <v>512</v>
       </c>
       <c r="C138" t="s">
         <v>14</v>
       </c>
       <c r="D138" t="s">
-        <v>514</v>
+        <v>513</v>
       </c>
       <c r="E138" t="s">
         <v>42</v>
@@ -5762,7 +5742,7 @@
         <v>43</v>
       </c>
       <c r="G138" t="s">
-        <v>515</v>
+        <v>514</v>
       </c>
       <c r="H138" t="s">
         <v>4</v>
@@ -5770,13 +5750,13 @@
     </row>
     <row r="139" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A139" t="s">
-        <v>517</v>
+        <v>515</v>
       </c>
       <c r="C139" t="s">
         <v>14</v>
       </c>
       <c r="D139" t="s">
-        <v>514</v>
+        <v>513</v>
       </c>
       <c r="E139" t="s">
         <v>42</v>
@@ -5785,7 +5765,7 @@
         <v>43</v>
       </c>
       <c r="G139" t="s">
-        <v>515</v>
+        <v>514</v>
       </c>
       <c r="H139" t="s">
         <v>4</v>
@@ -5793,22 +5773,22 @@
     </row>
     <row r="140" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A140" t="s">
-        <v>518</v>
+        <v>516</v>
       </c>
       <c r="C140" t="s">
         <v>14</v>
       </c>
       <c r="D140" t="s">
-        <v>519</v>
+        <v>513</v>
       </c>
       <c r="E140" t="s">
-        <v>33</v>
+        <v>42</v>
       </c>
       <c r="F140" t="s">
-        <v>34</v>
+        <v>43</v>
       </c>
       <c r="G140" t="s">
-        <v>520</v>
+        <v>514</v>
       </c>
       <c r="H140" t="s">
         <v>4</v>
@@ -5816,13 +5796,13 @@
     </row>
     <row r="141" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A141" t="s">
-        <v>521</v>
+        <v>517</v>
       </c>
       <c r="C141" t="s">
         <v>14</v>
       </c>
       <c r="D141" t="s">
-        <v>519</v>
+        <v>518</v>
       </c>
       <c r="E141" t="s">
         <v>33</v>
@@ -5831,7 +5811,7 @@
         <v>34</v>
       </c>
       <c r="G141" t="s">
-        <v>520</v>
+        <v>519</v>
       </c>
       <c r="H141" t="s">
         <v>4</v>
@@ -5839,22 +5819,22 @@
     </row>
     <row r="142" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A142" t="s">
-        <v>522</v>
+        <v>520</v>
       </c>
       <c r="C142" t="s">
-        <v>31</v>
+        <v>14</v>
       </c>
       <c r="D142" t="s">
-        <v>523</v>
+        <v>518</v>
       </c>
       <c r="E142" t="s">
-        <v>26</v>
+        <v>33</v>
       </c>
       <c r="F142" t="s">
-        <v>27</v>
+        <v>34</v>
       </c>
       <c r="G142" t="s">
-        <v>524</v>
+        <v>519</v>
       </c>
       <c r="H142" t="s">
         <v>4</v>
@@ -5862,13 +5842,13 @@
     </row>
     <row r="143" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A143" t="s">
-        <v>525</v>
+        <v>521</v>
       </c>
       <c r="C143" t="s">
         <v>31</v>
       </c>
       <c r="D143" t="s">
-        <v>523</v>
+        <v>522</v>
       </c>
       <c r="E143" t="s">
         <v>26</v>
@@ -5877,7 +5857,7 @@
         <v>27</v>
       </c>
       <c r="G143" t="s">
-        <v>524</v>
+        <v>523</v>
       </c>
       <c r="H143" t="s">
         <v>4</v>
@@ -5885,13 +5865,13 @@
     </row>
     <row r="144" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A144" t="s">
-        <v>526</v>
+        <v>524</v>
       </c>
       <c r="C144" t="s">
         <v>31</v>
       </c>
       <c r="D144" t="s">
-        <v>523</v>
+        <v>522</v>
       </c>
       <c r="E144" t="s">
         <v>26</v>
@@ -5900,7 +5880,7 @@
         <v>27</v>
       </c>
       <c r="G144" t="s">
-        <v>524</v>
+        <v>523</v>
       </c>
       <c r="H144" t="s">
         <v>4</v>
@@ -5908,22 +5888,22 @@
     </row>
     <row r="145" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A145" t="s">
-        <v>527</v>
+        <v>525</v>
       </c>
       <c r="C145" t="s">
-        <v>28</v>
+        <v>31</v>
       </c>
       <c r="D145" t="s">
-        <v>528</v>
+        <v>522</v>
       </c>
       <c r="E145" t="s">
-        <v>457</v>
+        <v>26</v>
       </c>
       <c r="F145" t="s">
-        <v>0</v>
+        <v>27</v>
       </c>
       <c r="G145" t="s">
-        <v>529</v>
+        <v>523</v>
       </c>
       <c r="H145" t="s">
         <v>4</v>
@@ -5931,22 +5911,22 @@
     </row>
     <row r="146" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A146" t="s">
-        <v>530</v>
+        <v>526</v>
       </c>
       <c r="C146" t="s">
-        <v>398</v>
+        <v>28</v>
       </c>
       <c r="D146" t="s">
-        <v>531</v>
+        <v>527</v>
       </c>
       <c r="E146" t="s">
-        <v>84</v>
+        <v>456</v>
       </c>
       <c r="F146" t="s">
         <v>0</v>
       </c>
       <c r="G146" t="s">
-        <v>532</v>
+        <v>528</v>
       </c>
       <c r="H146" t="s">
         <v>4</v>
@@ -5954,13 +5934,13 @@
     </row>
     <row r="147" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A147" t="s">
-        <v>533</v>
+        <v>529</v>
       </c>
       <c r="C147" t="s">
-        <v>398</v>
+        <v>397</v>
       </c>
       <c r="D147" t="s">
-        <v>531</v>
+        <v>530</v>
       </c>
       <c r="E147" t="s">
         <v>84</v>
@@ -5969,7 +5949,7 @@
         <v>0</v>
       </c>
       <c r="G147" t="s">
-        <v>532</v>
+        <v>531</v>
       </c>
       <c r="H147" t="s">
         <v>4</v>
@@ -5977,13 +5957,13 @@
     </row>
     <row r="148" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A148" t="s">
-        <v>534</v>
+        <v>532</v>
       </c>
       <c r="C148" t="s">
-        <v>398</v>
+        <v>397</v>
       </c>
       <c r="D148" t="s">
-        <v>531</v>
+        <v>530</v>
       </c>
       <c r="E148" t="s">
         <v>84</v>
@@ -5992,7 +5972,7 @@
         <v>0</v>
       </c>
       <c r="G148" t="s">
-        <v>532</v>
+        <v>531</v>
       </c>
       <c r="H148" t="s">
         <v>4</v>
@@ -6000,22 +5980,22 @@
     </row>
     <row r="149" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A149" t="s">
-        <v>535</v>
+        <v>533</v>
       </c>
       <c r="C149" t="s">
-        <v>14</v>
+        <v>397</v>
       </c>
       <c r="D149" t="s">
-        <v>536</v>
+        <v>530</v>
       </c>
       <c r="E149" t="s">
-        <v>33</v>
+        <v>84</v>
       </c>
       <c r="F149" t="s">
-        <v>34</v>
+        <v>0</v>
       </c>
       <c r="G149" t="s">
-        <v>58</v>
+        <v>531</v>
       </c>
       <c r="H149" t="s">
         <v>4</v>
@@ -6023,22 +6003,22 @@
     </row>
     <row r="150" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A150" t="s">
-        <v>537</v>
+        <v>534</v>
       </c>
       <c r="C150" t="s">
-        <v>31</v>
+        <v>14</v>
       </c>
       <c r="D150" t="s">
-        <v>538</v>
+        <v>535</v>
       </c>
       <c r="E150" t="s">
-        <v>539</v>
+        <v>33</v>
       </c>
       <c r="F150" t="s">
-        <v>0</v>
+        <v>34</v>
       </c>
       <c r="G150" t="s">
-        <v>540</v>
+        <v>58</v>
       </c>
       <c r="H150" t="s">
         <v>4</v>
@@ -6046,22 +6026,22 @@
     </row>
     <row r="151" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A151" t="s">
-        <v>541</v>
+        <v>536</v>
       </c>
       <c r="C151" t="s">
-        <v>9</v>
+        <v>31</v>
       </c>
       <c r="D151" t="s">
-        <v>542</v>
+        <v>537</v>
       </c>
       <c r="E151" t="s">
-        <v>543</v>
+        <v>538</v>
       </c>
       <c r="F151" t="s">
         <v>0</v>
       </c>
       <c r="G151" t="s">
-        <v>544</v>
+        <v>539</v>
       </c>
       <c r="H151" t="s">
         <v>4</v>
@@ -6069,22 +6049,22 @@
     </row>
     <row r="152" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A152" t="s">
-        <v>545</v>
+        <v>540</v>
       </c>
       <c r="C152" t="s">
-        <v>86</v>
+        <v>9</v>
       </c>
       <c r="D152" t="s">
-        <v>546</v>
+        <v>541</v>
       </c>
       <c r="E152" t="s">
-        <v>90</v>
+        <v>542</v>
       </c>
       <c r="F152" t="s">
-        <v>91</v>
+        <v>0</v>
       </c>
       <c r="G152" t="s">
-        <v>547</v>
+        <v>543</v>
       </c>
       <c r="H152" t="s">
         <v>4</v>
@@ -6092,22 +6072,22 @@
     </row>
     <row r="153" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A153" t="s">
-        <v>548</v>
+        <v>544</v>
       </c>
       <c r="C153" t="s">
-        <v>16</v>
+        <v>86</v>
       </c>
       <c r="D153" t="s">
-        <v>549</v>
+        <v>545</v>
       </c>
       <c r="E153" t="s">
-        <v>365</v>
+        <v>90</v>
       </c>
       <c r="F153" t="s">
-        <v>0</v>
+        <v>91</v>
       </c>
       <c r="G153" t="s">
-        <v>550</v>
+        <v>546</v>
       </c>
       <c r="H153" t="s">
         <v>4</v>
@@ -6115,22 +6095,22 @@
     </row>
     <row r="154" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A154" t="s">
-        <v>551</v>
+        <v>547</v>
       </c>
       <c r="C154" t="s">
-        <v>86</v>
+        <v>16</v>
       </c>
       <c r="D154" t="s">
-        <v>552</v>
+        <v>548</v>
       </c>
       <c r="E154" t="s">
-        <v>553</v>
+        <v>364</v>
       </c>
       <c r="F154" t="s">
         <v>0</v>
       </c>
       <c r="G154" t="s">
-        <v>554</v>
+        <v>549</v>
       </c>
       <c r="H154" t="s">
         <v>4</v>
@@ -6138,22 +6118,22 @@
     </row>
     <row r="155" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A155" t="s">
-        <v>555</v>
+        <v>550</v>
       </c>
       <c r="C155" t="s">
         <v>86</v>
       </c>
       <c r="D155" t="s">
+        <v>551</v>
+      </c>
+      <c r="E155" t="s">
         <v>552</v>
       </c>
-      <c r="E155" t="s">
+      <c r="F155" t="s">
+        <v>0</v>
+      </c>
+      <c r="G155" t="s">
         <v>553</v>
-      </c>
-      <c r="F155" t="s">
-        <v>0</v>
-      </c>
-      <c r="G155" t="s">
-        <v>554</v>
       </c>
       <c r="H155" t="s">
         <v>4</v>
@@ -6161,22 +6141,22 @@
     </row>
     <row r="156" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A156" t="s">
-        <v>556</v>
+        <v>554</v>
       </c>
       <c r="C156" t="s">
-        <v>55</v>
+        <v>86</v>
       </c>
       <c r="D156" t="s">
-        <v>557</v>
+        <v>551</v>
       </c>
       <c r="E156" t="s">
-        <v>69</v>
+        <v>552</v>
       </c>
       <c r="F156" t="s">
         <v>0</v>
       </c>
       <c r="G156" t="s">
-        <v>558</v>
+        <v>553</v>
       </c>
       <c r="H156" t="s">
         <v>4</v>
@@ -6184,13 +6164,13 @@
     </row>
     <row r="157" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A157" t="s">
-        <v>559</v>
+        <v>555</v>
       </c>
       <c r="C157" t="s">
         <v>55</v>
       </c>
       <c r="D157" t="s">
-        <v>557</v>
+        <v>556</v>
       </c>
       <c r="E157" t="s">
         <v>69</v>
@@ -6199,7 +6179,7 @@
         <v>0</v>
       </c>
       <c r="G157" t="s">
-        <v>558</v>
+        <v>557</v>
       </c>
       <c r="H157" t="s">
         <v>4</v>
@@ -6207,22 +6187,22 @@
     </row>
     <row r="158" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A158" t="s">
-        <v>560</v>
+        <v>558</v>
       </c>
       <c r="C158" t="s">
-        <v>12</v>
+        <v>55</v>
       </c>
       <c r="D158" t="s">
-        <v>561</v>
+        <v>556</v>
       </c>
       <c r="E158" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="F158" t="s">
         <v>0</v>
       </c>
       <c r="G158" t="s">
-        <v>562</v>
+        <v>557</v>
       </c>
       <c r="H158" t="s">
         <v>4</v>
@@ -6230,22 +6210,22 @@
     </row>
     <row r="159" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A159" t="s">
-        <v>563</v>
+        <v>559</v>
       </c>
       <c r="C159" t="s">
-        <v>3</v>
+        <v>12</v>
       </c>
       <c r="D159" t="s">
-        <v>564</v>
+        <v>560</v>
       </c>
       <c r="E159" t="s">
-        <v>565</v>
+        <v>70</v>
       </c>
       <c r="F159" t="s">
         <v>0</v>
       </c>
       <c r="G159" t="s">
-        <v>566</v>
+        <v>561</v>
       </c>
       <c r="H159" t="s">
         <v>4</v>
@@ -6253,22 +6233,22 @@
     </row>
     <row r="160" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A160" t="s">
-        <v>567</v>
+        <v>562</v>
       </c>
       <c r="C160" t="s">
-        <v>133</v>
+        <v>3</v>
       </c>
       <c r="D160" t="s">
-        <v>568</v>
+        <v>563</v>
       </c>
       <c r="E160" t="s">
-        <v>569</v>
+        <v>564</v>
       </c>
       <c r="F160" t="s">
-        <v>570</v>
+        <v>0</v>
       </c>
       <c r="G160" t="s">
-        <v>571</v>
+        <v>565</v>
       </c>
       <c r="H160" t="s">
         <v>4</v>
@@ -6276,22 +6256,22 @@
     </row>
     <row r="161" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A161" t="s">
-        <v>572</v>
+        <v>566</v>
       </c>
       <c r="C161" t="s">
-        <v>86</v>
+        <v>132</v>
       </c>
       <c r="D161" t="s">
-        <v>573</v>
+        <v>567</v>
       </c>
       <c r="E161" t="s">
-        <v>574</v>
+        <v>568</v>
       </c>
       <c r="F161" t="s">
-        <v>0</v>
+        <v>569</v>
       </c>
       <c r="G161" t="s">
-        <v>575</v>
+        <v>570</v>
       </c>
       <c r="H161" t="s">
         <v>4</v>
@@ -6299,22 +6279,22 @@
     </row>
     <row r="162" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A162" t="s">
-        <v>576</v>
+        <v>571</v>
       </c>
       <c r="C162" t="s">
-        <v>17</v>
+        <v>86</v>
       </c>
       <c r="D162" t="s">
-        <v>577</v>
+        <v>572</v>
       </c>
       <c r="E162" t="s">
-        <v>102</v>
+        <v>573</v>
       </c>
       <c r="F162" t="s">
         <v>0</v>
       </c>
       <c r="G162" t="s">
-        <v>578</v>
+        <v>574</v>
       </c>
       <c r="H162" t="s">
         <v>4</v>
@@ -6322,13 +6302,13 @@
     </row>
     <row r="163" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A163" t="s">
-        <v>579</v>
+        <v>575</v>
       </c>
       <c r="C163" t="s">
         <v>17</v>
       </c>
       <c r="D163" t="s">
-        <v>577</v>
+        <v>576</v>
       </c>
       <c r="E163" t="s">
         <v>102</v>
@@ -6337,7 +6317,7 @@
         <v>0</v>
       </c>
       <c r="G163" t="s">
-        <v>578</v>
+        <v>577</v>
       </c>
       <c r="H163" t="s">
         <v>4</v>
@@ -6345,22 +6325,22 @@
     </row>
     <row r="164" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A164" t="s">
-        <v>580</v>
+        <v>578</v>
       </c>
       <c r="C164" t="s">
-        <v>31</v>
+        <v>17</v>
       </c>
       <c r="D164" t="s">
-        <v>581</v>
+        <v>576</v>
       </c>
       <c r="E164" t="s">
-        <v>109</v>
+        <v>102</v>
       </c>
       <c r="F164" t="s">
         <v>0</v>
       </c>
       <c r="G164" t="s">
-        <v>582</v>
+        <v>577</v>
       </c>
       <c r="H164" t="s">
         <v>4</v>
@@ -6368,22 +6348,22 @@
     </row>
     <row r="165" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A165" t="s">
-        <v>583</v>
+        <v>579</v>
       </c>
       <c r="C165" t="s">
-        <v>54</v>
+        <v>31</v>
       </c>
       <c r="D165" t="s">
-        <v>584</v>
+        <v>580</v>
       </c>
       <c r="E165" t="s">
-        <v>585</v>
+        <v>108</v>
       </c>
       <c r="F165" t="s">
-        <v>586</v>
+        <v>0</v>
       </c>
       <c r="G165" t="s">
-        <v>587</v>
+        <v>581</v>
       </c>
       <c r="H165" t="s">
         <v>4</v>
@@ -6391,22 +6371,22 @@
     </row>
     <row r="166" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A166" t="s">
-        <v>588</v>
+        <v>582</v>
       </c>
       <c r="C166" t="s">
-        <v>39</v>
+        <v>54</v>
       </c>
       <c r="D166" t="s">
-        <v>589</v>
+        <v>583</v>
       </c>
       <c r="E166" t="s">
-        <v>84</v>
+        <v>584</v>
       </c>
       <c r="F166" t="s">
-        <v>0</v>
+        <v>585</v>
       </c>
       <c r="G166" t="s">
-        <v>590</v>
+        <v>586</v>
       </c>
       <c r="H166" t="s">
         <v>4</v>
@@ -6414,22 +6394,22 @@
     </row>
     <row r="167" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A167" t="s">
-        <v>591</v>
+        <v>587</v>
       </c>
       <c r="C167" t="s">
-        <v>12</v>
+        <v>39</v>
       </c>
       <c r="D167" t="s">
-        <v>592</v>
+        <v>588</v>
       </c>
       <c r="E167" t="s">
-        <v>593</v>
+        <v>84</v>
       </c>
       <c r="F167" t="s">
         <v>0</v>
       </c>
       <c r="G167" t="s">
-        <v>594</v>
+        <v>589</v>
       </c>
       <c r="H167" t="s">
         <v>4</v>
@@ -6437,22 +6417,22 @@
     </row>
     <row r="168" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A168" t="s">
-        <v>595</v>
+        <v>590</v>
       </c>
       <c r="C168" t="s">
         <v>12</v>
       </c>
       <c r="D168" t="s">
-        <v>596</v>
+        <v>591</v>
       </c>
       <c r="E168" t="s">
-        <v>70</v>
+        <v>592</v>
       </c>
       <c r="F168" t="s">
         <v>0</v>
       </c>
       <c r="G168" t="s">
-        <v>597</v>
+        <v>593</v>
       </c>
       <c r="H168" t="s">
         <v>4</v>
@@ -6460,22 +6440,22 @@
     </row>
     <row r="169" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A169" t="s">
-        <v>598</v>
+        <v>594</v>
       </c>
       <c r="C169" t="s">
         <v>12</v>
       </c>
       <c r="D169" t="s">
-        <v>599</v>
+        <v>595</v>
       </c>
       <c r="E169" t="s">
-        <v>600</v>
+        <v>70</v>
       </c>
       <c r="F169" t="s">
         <v>0</v>
       </c>
       <c r="G169" t="s">
-        <v>190</v>
+        <v>596</v>
       </c>
       <c r="H169" t="s">
         <v>4</v>
@@ -6483,22 +6463,22 @@
     </row>
     <row r="170" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A170" t="s">
-        <v>601</v>
+        <v>597</v>
       </c>
       <c r="C170" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="D170" t="s">
-        <v>602</v>
+        <v>598</v>
       </c>
       <c r="E170" t="s">
-        <v>25</v>
+        <v>599</v>
       </c>
       <c r="F170" t="s">
         <v>0</v>
       </c>
       <c r="G170" t="s">
-        <v>603</v>
+        <v>189</v>
       </c>
       <c r="H170" t="s">
         <v>4</v>
@@ -6506,22 +6486,22 @@
     </row>
     <row r="171" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A171" t="s">
-        <v>604</v>
+        <v>600</v>
       </c>
       <c r="C171" t="s">
-        <v>24</v>
+        <v>10</v>
       </c>
       <c r="D171" t="s">
-        <v>605</v>
+        <v>601</v>
       </c>
       <c r="E171" t="s">
-        <v>606</v>
+        <v>25</v>
       </c>
       <c r="F171" t="s">
         <v>0</v>
       </c>
       <c r="G171" t="s">
-        <v>607</v>
+        <v>602</v>
       </c>
       <c r="H171" t="s">
         <v>4</v>
@@ -6529,22 +6509,22 @@
     </row>
     <row r="172" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A172" t="s">
-        <v>608</v>
+        <v>603</v>
       </c>
       <c r="C172" t="s">
-        <v>86</v>
+        <v>24</v>
       </c>
       <c r="D172" t="s">
-        <v>609</v>
+        <v>604</v>
       </c>
       <c r="E172" t="s">
-        <v>100</v>
+        <v>605</v>
       </c>
       <c r="F172" t="s">
         <v>0</v>
       </c>
       <c r="G172" t="s">
-        <v>610</v>
+        <v>606</v>
       </c>
       <c r="H172" t="s">
         <v>4</v>
@@ -6552,22 +6532,22 @@
     </row>
     <row r="173" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A173" t="s">
-        <v>611</v>
+        <v>607</v>
       </c>
       <c r="C173" t="s">
-        <v>39</v>
+        <v>86</v>
       </c>
       <c r="D173" t="s">
-        <v>612</v>
+        <v>608</v>
       </c>
       <c r="E173" t="s">
-        <v>108</v>
+        <v>100</v>
       </c>
       <c r="F173" t="s">
         <v>0</v>
       </c>
       <c r="G173" t="s">
-        <v>613</v>
+        <v>609</v>
       </c>
       <c r="H173" t="s">
         <v>4</v>
@@ -6575,22 +6555,22 @@
     </row>
     <row r="174" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A174" t="s">
-        <v>614</v>
+        <v>610</v>
       </c>
       <c r="C174" t="s">
         <v>39</v>
       </c>
       <c r="D174" t="s">
+        <v>611</v>
+      </c>
+      <c r="E174" t="s">
+        <v>107</v>
+      </c>
+      <c r="F174" t="s">
+        <v>0</v>
+      </c>
+      <c r="G174" t="s">
         <v>612</v>
-      </c>
-      <c r="E174" t="s">
-        <v>108</v>
-      </c>
-      <c r="F174" t="s">
-        <v>0</v>
-      </c>
-      <c r="G174" t="s">
-        <v>613</v>
       </c>
       <c r="H174" t="s">
         <v>4</v>
@@ -6598,22 +6578,22 @@
     </row>
     <row r="175" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A175" t="s">
-        <v>615</v>
+        <v>613</v>
       </c>
       <c r="C175" t="s">
-        <v>15</v>
+        <v>39</v>
       </c>
       <c r="D175" t="s">
-        <v>616</v>
+        <v>611</v>
       </c>
       <c r="E175" t="s">
-        <v>617</v>
+        <v>107</v>
       </c>
       <c r="F175" t="s">
         <v>0</v>
       </c>
       <c r="G175" t="s">
-        <v>618</v>
+        <v>612</v>
       </c>
       <c r="H175" t="s">
         <v>4</v>
@@ -6621,22 +6601,22 @@
     </row>
     <row r="176" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A176" t="s">
-        <v>619</v>
+        <v>614</v>
       </c>
       <c r="C176" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="D176" t="s">
-        <v>620</v>
+        <v>615</v>
       </c>
       <c r="E176" t="s">
-        <v>621</v>
+        <v>616</v>
       </c>
       <c r="F176" t="s">
         <v>0</v>
       </c>
       <c r="G176" t="s">
-        <v>622</v>
+        <v>617</v>
       </c>
       <c r="H176" t="s">
         <v>4</v>
@@ -6644,22 +6624,22 @@
     </row>
     <row r="177" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A177" t="s">
-        <v>623</v>
+        <v>618</v>
       </c>
       <c r="C177" t="s">
-        <v>39</v>
+        <v>17</v>
       </c>
       <c r="D177" t="s">
-        <v>624</v>
+        <v>619</v>
       </c>
       <c r="E177" t="s">
-        <v>625</v>
+        <v>620</v>
       </c>
       <c r="F177" t="s">
         <v>0</v>
       </c>
       <c r="G177" t="s">
-        <v>626</v>
+        <v>621</v>
       </c>
       <c r="H177" t="s">
         <v>4</v>
@@ -6667,22 +6647,22 @@
     </row>
     <row r="178" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A178" t="s">
-        <v>627</v>
+        <v>622</v>
       </c>
       <c r="C178" t="s">
         <v>39</v>
       </c>
       <c r="D178" t="s">
+        <v>623</v>
+      </c>
+      <c r="E178" t="s">
         <v>624</v>
       </c>
-      <c r="E178" t="s">
+      <c r="F178" t="s">
+        <v>0</v>
+      </c>
+      <c r="G178" t="s">
         <v>625</v>
-      </c>
-      <c r="F178" t="s">
-        <v>0</v>
-      </c>
-      <c r="G178" t="s">
-        <v>626</v>
       </c>
       <c r="H178" t="s">
         <v>4</v>
@@ -6690,22 +6670,22 @@
     </row>
     <row r="179" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A179" t="s">
-        <v>628</v>
+        <v>626</v>
       </c>
       <c r="C179" t="s">
-        <v>24</v>
+        <v>39</v>
       </c>
       <c r="D179" t="s">
-        <v>629</v>
+        <v>623</v>
       </c>
       <c r="E179" t="s">
-        <v>97</v>
+        <v>624</v>
       </c>
       <c r="F179" t="s">
         <v>0</v>
       </c>
       <c r="G179" t="s">
-        <v>630</v>
+        <v>625</v>
       </c>
       <c r="H179" t="s">
         <v>4</v>
@@ -6713,22 +6693,22 @@
     </row>
     <row r="180" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A180" t="s">
-        <v>631</v>
+        <v>627</v>
       </c>
       <c r="C180" t="s">
-        <v>35</v>
+        <v>24</v>
       </c>
       <c r="D180" t="s">
-        <v>632</v>
+        <v>628</v>
       </c>
       <c r="E180" t="s">
-        <v>89</v>
+        <v>97</v>
       </c>
       <c r="F180" t="s">
         <v>0</v>
       </c>
       <c r="G180" t="s">
-        <v>633</v>
+        <v>629</v>
       </c>
       <c r="H180" t="s">
         <v>4</v>
@@ -6736,22 +6716,22 @@
     </row>
     <row r="181" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A181" t="s">
-        <v>634</v>
+        <v>630</v>
       </c>
       <c r="C181" t="s">
-        <v>133</v>
+        <v>35</v>
       </c>
       <c r="D181" t="s">
-        <v>635</v>
+        <v>631</v>
       </c>
       <c r="E181" t="s">
-        <v>193</v>
+        <v>89</v>
       </c>
       <c r="F181" t="s">
         <v>0</v>
       </c>
       <c r="G181" t="s">
-        <v>509</v>
+        <v>632</v>
       </c>
       <c r="H181" t="s">
         <v>4</v>
@@ -6759,22 +6739,22 @@
     </row>
     <row r="182" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A182" t="s">
-        <v>636</v>
+        <v>633</v>
       </c>
       <c r="C182" t="s">
-        <v>41</v>
+        <v>132</v>
       </c>
       <c r="D182" t="s">
-        <v>637</v>
+        <v>634</v>
       </c>
       <c r="E182" t="s">
-        <v>66</v>
+        <v>192</v>
       </c>
       <c r="F182" t="s">
-        <v>67</v>
+        <v>0</v>
       </c>
       <c r="G182" t="s">
-        <v>638</v>
+        <v>508</v>
       </c>
       <c r="H182" t="s">
         <v>4</v>
@@ -6782,13 +6762,13 @@
     </row>
     <row r="183" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A183" t="s">
-        <v>639</v>
+        <v>635</v>
       </c>
       <c r="C183" t="s">
         <v>41</v>
       </c>
       <c r="D183" t="s">
-        <v>640</v>
+        <v>636</v>
       </c>
       <c r="E183" t="s">
         <v>66</v>
@@ -6797,7 +6777,7 @@
         <v>67</v>
       </c>
       <c r="G183" t="s">
-        <v>641</v>
+        <v>637</v>
       </c>
       <c r="H183" t="s">
         <v>4</v>
@@ -6805,22 +6785,22 @@
     </row>
     <row r="184" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A184" t="s">
-        <v>642</v>
+        <v>638</v>
       </c>
       <c r="C184" t="s">
-        <v>12</v>
+        <v>41</v>
       </c>
       <c r="D184" t="s">
-        <v>643</v>
+        <v>639</v>
       </c>
       <c r="E184" t="s">
-        <v>70</v>
+        <v>66</v>
       </c>
       <c r="F184" t="s">
-        <v>0</v>
+        <v>67</v>
       </c>
       <c r="G184" t="s">
-        <v>644</v>
+        <v>640</v>
       </c>
       <c r="H184" t="s">
         <v>4</v>
@@ -6828,22 +6808,22 @@
     </row>
     <row r="185" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A185" t="s">
-        <v>645</v>
+        <v>641</v>
       </c>
       <c r="C185" t="s">
-        <v>133</v>
+        <v>12</v>
       </c>
       <c r="D185" t="s">
-        <v>646</v>
+        <v>642</v>
       </c>
       <c r="E185" t="s">
-        <v>647</v>
+        <v>70</v>
       </c>
       <c r="F185" t="s">
         <v>0</v>
       </c>
       <c r="G185" t="s">
-        <v>648</v>
+        <v>643</v>
       </c>
       <c r="H185" t="s">
         <v>4</v>
@@ -6851,22 +6831,22 @@
     </row>
     <row r="186" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A186" t="s">
-        <v>649</v>
+        <v>644</v>
       </c>
       <c r="C186" t="s">
-        <v>3</v>
+        <v>132</v>
       </c>
       <c r="D186" t="s">
-        <v>650</v>
+        <v>645</v>
       </c>
       <c r="E186" t="s">
-        <v>81</v>
+        <v>646</v>
       </c>
       <c r="F186" t="s">
         <v>0</v>
       </c>
       <c r="G186" t="s">
-        <v>651</v>
+        <v>647</v>
       </c>
       <c r="H186" t="s">
         <v>4</v>
@@ -6874,22 +6854,22 @@
     </row>
     <row r="187" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A187" t="s">
-        <v>652</v>
+        <v>648</v>
       </c>
       <c r="C187" t="s">
-        <v>41</v>
+        <v>3</v>
       </c>
       <c r="D187" t="s">
-        <v>653</v>
+        <v>649</v>
       </c>
       <c r="E187" t="s">
-        <v>66</v>
+        <v>81</v>
       </c>
       <c r="F187" t="s">
-        <v>67</v>
+        <v>0</v>
       </c>
       <c r="G187" t="s">
-        <v>654</v>
+        <v>650</v>
       </c>
       <c r="H187" t="s">
         <v>4</v>
@@ -6897,45 +6877,45 @@
     </row>
     <row r="188" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A188" t="s">
-        <v>655</v>
+        <v>651</v>
       </c>
       <c r="C188" t="s">
-        <v>10</v>
+        <v>41</v>
       </c>
       <c r="D188" t="s">
-        <v>656</v>
+        <v>652</v>
       </c>
       <c r="E188" t="s">
-        <v>82</v>
+        <v>66</v>
       </c>
       <c r="F188" t="s">
-        <v>83</v>
+        <v>67</v>
       </c>
       <c r="G188" t="s">
-        <v>657</v>
+        <v>653</v>
       </c>
       <c r="H188" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="189" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A189" t="s">
-        <v>658</v>
+        <v>654</v>
       </c>
       <c r="C189" t="s">
-        <v>55</v>
+        <v>10</v>
       </c>
       <c r="D189" t="s">
-        <v>659</v>
+        <v>655</v>
       </c>
       <c r="E189" t="s">
-        <v>660</v>
+        <v>82</v>
       </c>
       <c r="F189" t="s">
-        <v>0</v>
+        <v>83</v>
       </c>
       <c r="G189" t="s">
-        <v>661</v>
+        <v>656</v>
       </c>
       <c r="H189" t="s">
         <v>5</v>
@@ -6943,22 +6923,22 @@
     </row>
     <row r="190" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A190" t="s">
-        <v>662</v>
+        <v>657</v>
       </c>
       <c r="C190" t="s">
-        <v>86</v>
+        <v>55</v>
       </c>
       <c r="D190" t="s">
-        <v>663</v>
+        <v>658</v>
       </c>
       <c r="E190" t="s">
-        <v>664</v>
+        <v>659</v>
       </c>
       <c r="F190" t="s">
-        <v>665</v>
+        <v>0</v>
       </c>
       <c r="G190" t="s">
-        <v>666</v>
+        <v>660</v>
       </c>
       <c r="H190" t="s">
         <v>5</v>
@@ -6966,22 +6946,22 @@
     </row>
     <row r="191" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A191" t="s">
-        <v>667</v>
+        <v>661</v>
       </c>
       <c r="C191" t="s">
-        <v>41</v>
+        <v>86</v>
       </c>
       <c r="D191" t="s">
-        <v>668</v>
+        <v>662</v>
       </c>
       <c r="E191" t="s">
-        <v>7</v>
+        <v>663</v>
       </c>
       <c r="F191" t="s">
-        <v>8</v>
+        <v>664</v>
       </c>
       <c r="G191" t="s">
-        <v>669</v>
+        <v>665</v>
       </c>
       <c r="H191" t="s">
         <v>5</v>
@@ -6989,22 +6969,22 @@
     </row>
     <row r="192" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A192" t="s">
-        <v>670</v>
+        <v>666</v>
       </c>
       <c r="C192" t="s">
         <v>41</v>
       </c>
       <c r="D192" t="s">
-        <v>671</v>
+        <v>667</v>
       </c>
       <c r="E192" t="s">
-        <v>87</v>
+        <v>7</v>
       </c>
       <c r="F192" t="s">
-        <v>88</v>
+        <v>8</v>
       </c>
       <c r="G192" t="s">
-        <v>672</v>
+        <v>668</v>
       </c>
       <c r="H192" t="s">
         <v>5</v>
@@ -7012,22 +6992,22 @@
     </row>
     <row r="193" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A193" t="s">
-        <v>673</v>
+        <v>669</v>
       </c>
       <c r="C193" t="s">
-        <v>55</v>
+        <v>41</v>
       </c>
       <c r="D193" t="s">
-        <v>674</v>
+        <v>670</v>
       </c>
       <c r="E193" t="s">
-        <v>69</v>
+        <v>87</v>
       </c>
       <c r="F193" t="s">
-        <v>0</v>
+        <v>88</v>
       </c>
       <c r="G193" t="s">
-        <v>675</v>
+        <v>671</v>
       </c>
       <c r="H193" t="s">
         <v>5</v>
@@ -7035,22 +7015,22 @@
     </row>
     <row r="194" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A194" t="s">
-        <v>676</v>
+        <v>672</v>
       </c>
       <c r="C194" t="s">
-        <v>41</v>
+        <v>55</v>
       </c>
       <c r="D194" t="s">
-        <v>677</v>
+        <v>673</v>
       </c>
       <c r="E194" t="s">
-        <v>7</v>
+        <v>69</v>
       </c>
       <c r="F194" t="s">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="G194" t="s">
-        <v>103</v>
+        <v>674</v>
       </c>
       <c r="H194" t="s">
         <v>5</v>
@@ -7058,13 +7038,13 @@
     </row>
     <row r="195" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A195" t="s">
-        <v>678</v>
+        <v>675</v>
       </c>
       <c r="C195" t="s">
         <v>41</v>
       </c>
       <c r="D195" t="s">
-        <v>677</v>
+        <v>676</v>
       </c>
       <c r="E195" t="s">
         <v>7</v>
@@ -7081,13 +7061,13 @@
     </row>
     <row r="196" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A196" t="s">
-        <v>679</v>
+        <v>677</v>
       </c>
       <c r="C196" t="s">
         <v>41</v>
       </c>
       <c r="D196" t="s">
-        <v>677</v>
+        <v>676</v>
       </c>
       <c r="E196" t="s">
         <v>7</v>
@@ -7104,13 +7084,13 @@
     </row>
     <row r="197" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A197" t="s">
-        <v>680</v>
+        <v>678</v>
       </c>
       <c r="C197" t="s">
         <v>41</v>
       </c>
       <c r="D197" t="s">
-        <v>677</v>
+        <v>676</v>
       </c>
       <c r="E197" t="s">
         <v>7</v>
@@ -7127,22 +7107,22 @@
     </row>
     <row r="198" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A198" t="s">
-        <v>681</v>
+        <v>679</v>
       </c>
       <c r="C198" t="s">
-        <v>24</v>
+        <v>41</v>
       </c>
       <c r="D198" t="s">
-        <v>682</v>
+        <v>676</v>
       </c>
       <c r="E198" t="s">
-        <v>111</v>
+        <v>7</v>
       </c>
       <c r="F198" t="s">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="G198" t="s">
-        <v>683</v>
+        <v>103</v>
       </c>
       <c r="H198" t="s">
         <v>5</v>
@@ -7150,22 +7130,22 @@
     </row>
     <row r="199" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A199" t="s">
-        <v>684</v>
+        <v>680</v>
       </c>
       <c r="C199" t="s">
-        <v>31</v>
+        <v>24</v>
       </c>
       <c r="D199" t="s">
-        <v>685</v>
+        <v>681</v>
       </c>
       <c r="E199" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="F199" t="s">
         <v>0</v>
       </c>
       <c r="G199" t="s">
-        <v>686</v>
+        <v>682</v>
       </c>
       <c r="H199" t="s">
         <v>5</v>
@@ -7173,22 +7153,22 @@
     </row>
     <row r="200" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A200" t="s">
-        <v>687</v>
+        <v>683</v>
       </c>
       <c r="C200" t="s">
-        <v>15</v>
+        <v>31</v>
       </c>
       <c r="D200" t="s">
-        <v>688</v>
+        <v>684</v>
       </c>
       <c r="E200" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="F200" t="s">
         <v>0</v>
       </c>
       <c r="G200" t="s">
-        <v>46</v>
+        <v>685</v>
       </c>
       <c r="H200" t="s">
         <v>5</v>
@@ -7196,22 +7176,22 @@
     </row>
     <row r="201" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A201" t="s">
-        <v>689</v>
+        <v>686</v>
       </c>
       <c r="C201" t="s">
-        <v>31</v>
+        <v>15</v>
       </c>
       <c r="D201" t="s">
-        <v>690</v>
+        <v>687</v>
       </c>
       <c r="E201" t="s">
-        <v>95</v>
+        <v>106</v>
       </c>
       <c r="F201" t="s">
         <v>0</v>
       </c>
       <c r="G201" t="s">
-        <v>691</v>
+        <v>46</v>
       </c>
       <c r="H201" t="s">
         <v>5</v>
@@ -7219,22 +7199,22 @@
     </row>
     <row r="202" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A202" t="s">
-        <v>692</v>
+        <v>688</v>
       </c>
       <c r="C202" t="s">
         <v>31</v>
       </c>
       <c r="D202" t="s">
-        <v>693</v>
+        <v>689</v>
       </c>
       <c r="E202" t="s">
-        <v>109</v>
+        <v>95</v>
       </c>
       <c r="F202" t="s">
         <v>0</v>
       </c>
       <c r="G202" t="s">
-        <v>686</v>
+        <v>690</v>
       </c>
       <c r="H202" t="s">
         <v>5</v>
@@ -7242,22 +7222,22 @@
     </row>
     <row r="203" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A203" t="s">
-        <v>694</v>
+        <v>691</v>
       </c>
       <c r="C203" t="s">
-        <v>39</v>
+        <v>31</v>
       </c>
       <c r="D203" t="s">
-        <v>695</v>
+        <v>692</v>
       </c>
       <c r="E203" t="s">
-        <v>104</v>
+        <v>108</v>
       </c>
       <c r="F203" t="s">
         <v>0</v>
       </c>
       <c r="G203" t="s">
-        <v>696</v>
+        <v>685</v>
       </c>
       <c r="H203" t="s">
         <v>5</v>
@@ -7265,19 +7245,19 @@
     </row>
     <row r="204" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A204" t="s">
-        <v>697</v>
+        <v>693</v>
       </c>
       <c r="C204" t="s">
         <v>54</v>
       </c>
       <c r="D204" t="s">
-        <v>698</v>
+        <v>694</v>
       </c>
       <c r="E204" t="s">
-        <v>699</v>
+        <v>695</v>
       </c>
       <c r="F204" t="s">
-        <v>700</v>
+        <v>696</v>
       </c>
       <c r="G204" t="s">
         <v>37</v>
@@ -7288,13 +7268,13 @@
     </row>
     <row r="205" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A205" t="s">
-        <v>701</v>
+        <v>697</v>
       </c>
       <c r="C205" t="s">
         <v>31</v>
       </c>
       <c r="D205" t="s">
-        <v>702</v>
+        <v>698</v>
       </c>
       <c r="E205" t="s">
         <v>47</v>
@@ -7303,7 +7283,7 @@
         <v>0</v>
       </c>
       <c r="G205" t="s">
-        <v>703</v>
+        <v>699</v>
       </c>
       <c r="H205" t="s">
         <v>5</v>
@@ -7311,13 +7291,13 @@
     </row>
     <row r="206" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A206" t="s">
-        <v>704</v>
+        <v>700</v>
       </c>
       <c r="C206" t="s">
         <v>31</v>
       </c>
       <c r="D206" t="s">
-        <v>702</v>
+        <v>698</v>
       </c>
       <c r="E206" t="s">
         <v>47</v>
@@ -7326,7 +7306,7 @@
         <v>0</v>
       </c>
       <c r="G206" t="s">
-        <v>703</v>
+        <v>699</v>
       </c>
       <c r="H206" t="s">
         <v>5</v>
@@ -7334,22 +7314,22 @@
     </row>
     <row r="207" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A207" t="s">
-        <v>705</v>
+        <v>701</v>
       </c>
       <c r="C207" t="s">
         <v>15</v>
       </c>
       <c r="D207" t="s">
-        <v>706</v>
+        <v>702</v>
       </c>
       <c r="E207" t="s">
-        <v>707</v>
+        <v>703</v>
       </c>
       <c r="F207" t="s">
         <v>0</v>
       </c>
       <c r="G207" t="s">
-        <v>708</v>
+        <v>704</v>
       </c>
       <c r="H207" t="s">
         <v>5</v>
@@ -7357,22 +7337,22 @@
     </row>
     <row r="208" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A208" t="s">
-        <v>709</v>
+        <v>705</v>
       </c>
       <c r="C208" t="s">
         <v>15</v>
       </c>
       <c r="D208" t="s">
-        <v>706</v>
+        <v>702</v>
       </c>
       <c r="E208" t="s">
-        <v>707</v>
+        <v>703</v>
       </c>
       <c r="F208" t="s">
         <v>0</v>
       </c>
       <c r="G208" t="s">
-        <v>708</v>
+        <v>704</v>
       </c>
       <c r="H208" t="s">
         <v>5</v>
@@ -7380,22 +7360,22 @@
     </row>
     <row r="209" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A209" t="s">
-        <v>710</v>
+        <v>706</v>
       </c>
       <c r="C209" t="s">
         <v>15</v>
       </c>
       <c r="D209" t="s">
-        <v>706</v>
+        <v>702</v>
       </c>
       <c r="E209" t="s">
-        <v>707</v>
+        <v>703</v>
       </c>
       <c r="F209" t="s">
         <v>0</v>
       </c>
       <c r="G209" t="s">
-        <v>708</v>
+        <v>704</v>
       </c>
       <c r="H209" t="s">
         <v>5</v>
@@ -7403,22 +7383,22 @@
     </row>
     <row r="210" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A210" t="s">
-        <v>711</v>
+        <v>707</v>
       </c>
       <c r="C210" t="s">
         <v>15</v>
       </c>
       <c r="D210" t="s">
-        <v>706</v>
+        <v>702</v>
       </c>
       <c r="E210" t="s">
-        <v>707</v>
+        <v>703</v>
       </c>
       <c r="F210" t="s">
         <v>0</v>
       </c>
       <c r="G210" t="s">
-        <v>708</v>
+        <v>704</v>
       </c>
       <c r="H210" t="s">
         <v>5</v>
@@ -7426,22 +7406,22 @@
     </row>
     <row r="211" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A211" t="s">
-        <v>712</v>
+        <v>708</v>
       </c>
       <c r="C211" t="s">
         <v>39</v>
       </c>
       <c r="D211" t="s">
-        <v>713</v>
+        <v>709</v>
       </c>
       <c r="E211" t="s">
-        <v>714</v>
+        <v>710</v>
       </c>
       <c r="F211" t="s">
-        <v>715</v>
+        <v>711</v>
       </c>
       <c r="G211" t="s">
-        <v>716</v>
+        <v>712</v>
       </c>
       <c r="H211" t="s">
         <v>5</v>
@@ -7449,22 +7429,22 @@
     </row>
     <row r="212" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A212" t="s">
-        <v>717</v>
+        <v>713</v>
       </c>
       <c r="C212" t="s">
         <v>39</v>
       </c>
       <c r="D212" t="s">
-        <v>713</v>
+        <v>709</v>
       </c>
       <c r="E212" t="s">
-        <v>714</v>
+        <v>710</v>
       </c>
       <c r="F212" t="s">
-        <v>715</v>
+        <v>711</v>
       </c>
       <c r="G212" t="s">
-        <v>716</v>
+        <v>712</v>
       </c>
       <c r="H212" t="s">
         <v>5</v>
@@ -7472,22 +7452,22 @@
     </row>
     <row r="213" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A213" t="s">
-        <v>718</v>
+        <v>714</v>
       </c>
       <c r="C213" t="s">
         <v>6</v>
       </c>
       <c r="D213" t="s">
-        <v>719</v>
+        <v>715</v>
       </c>
       <c r="E213" t="s">
+        <v>251</v>
+      </c>
+      <c r="F213" t="s">
         <v>252</v>
       </c>
-      <c r="F213" t="s">
-        <v>253</v>
-      </c>
       <c r="G213" t="s">
-        <v>720</v>
+        <v>716</v>
       </c>
       <c r="H213" t="s">
         <v>5</v>
@@ -7495,22 +7475,22 @@
     </row>
     <row r="214" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A214" t="s">
-        <v>721</v>
+        <v>717</v>
       </c>
       <c r="C214" t="s">
         <v>6</v>
       </c>
       <c r="D214" t="s">
-        <v>719</v>
+        <v>715</v>
       </c>
       <c r="E214" t="s">
+        <v>251</v>
+      </c>
+      <c r="F214" t="s">
         <v>252</v>
       </c>
-      <c r="F214" t="s">
-        <v>253</v>
-      </c>
       <c r="G214" t="s">
-        <v>720</v>
+        <v>716</v>
       </c>
       <c r="H214" t="s">
         <v>5</v>
@@ -7518,22 +7498,22 @@
     </row>
     <row r="215" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A215" t="s">
-        <v>722</v>
+        <v>718</v>
       </c>
       <c r="C215" t="s">
         <v>6</v>
       </c>
       <c r="D215" t="s">
-        <v>723</v>
+        <v>719</v>
       </c>
       <c r="E215" t="s">
-        <v>724</v>
+        <v>720</v>
       </c>
       <c r="F215" t="s">
-        <v>725</v>
+        <v>721</v>
       </c>
       <c r="G215" t="s">
-        <v>726</v>
+        <v>722</v>
       </c>
       <c r="H215" t="s">
         <v>5</v>
@@ -7541,22 +7521,22 @@
     </row>
     <row r="216" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A216" t="s">
-        <v>727</v>
+        <v>723</v>
       </c>
       <c r="C216" t="s">
         <v>6</v>
       </c>
       <c r="D216" t="s">
-        <v>723</v>
+        <v>719</v>
       </c>
       <c r="E216" t="s">
-        <v>724</v>
+        <v>720</v>
       </c>
       <c r="F216" t="s">
-        <v>725</v>
+        <v>721</v>
       </c>
       <c r="G216" t="s">
-        <v>726</v>
+        <v>722</v>
       </c>
       <c r="H216" t="s">
         <v>5</v>
@@ -7564,22 +7544,22 @@
     </row>
     <row r="217" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A217" t="s">
-        <v>728</v>
+        <v>724</v>
       </c>
       <c r="C217" t="s">
         <v>11</v>
       </c>
       <c r="D217" t="s">
-        <v>729</v>
+        <v>725</v>
       </c>
       <c r="E217" t="s">
-        <v>730</v>
+        <v>726</v>
       </c>
       <c r="F217" t="s">
-        <v>731</v>
+        <v>727</v>
       </c>
       <c r="G217" t="s">
-        <v>732</v>
+        <v>728</v>
       </c>
       <c r="H217" t="s">
         <v>5</v>
@@ -7587,22 +7567,22 @@
     </row>
     <row r="218" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A218" t="s">
-        <v>733</v>
+        <v>729</v>
       </c>
       <c r="C218" t="s">
         <v>11</v>
       </c>
       <c r="D218" t="s">
-        <v>729</v>
+        <v>725</v>
       </c>
       <c r="E218" t="s">
-        <v>730</v>
+        <v>726</v>
       </c>
       <c r="F218" t="s">
-        <v>731</v>
+        <v>727</v>
       </c>
       <c r="G218" t="s">
-        <v>732</v>
+        <v>728</v>
       </c>
       <c r="H218" t="s">
         <v>5</v>
@@ -7610,13 +7590,13 @@
     </row>
     <row r="219" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A219" t="s">
-        <v>734</v>
+        <v>730</v>
       </c>
       <c r="C219" t="s">
         <v>54</v>
       </c>
       <c r="D219" t="s">
-        <v>735</v>
+        <v>731</v>
       </c>
       <c r="E219" t="s">
         <v>22</v>
@@ -7625,7 +7605,7 @@
         <v>23</v>
       </c>
       <c r="G219" t="s">
-        <v>736</v>
+        <v>732</v>
       </c>
       <c r="H219" t="s">
         <v>5</v>
@@ -7633,22 +7613,22 @@
     </row>
     <row r="220" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A220" t="s">
-        <v>737</v>
+        <v>733</v>
       </c>
       <c r="C220" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="D220" t="s">
-        <v>738</v>
+        <v>734</v>
       </c>
       <c r="E220" t="s">
+        <v>568</v>
+      </c>
+      <c r="F220" t="s">
         <v>569</v>
       </c>
-      <c r="F220" t="s">
-        <v>570</v>
-      </c>
       <c r="G220" t="s">
-        <v>739</v>
+        <v>735</v>
       </c>
       <c r="H220" t="s">
         <v>13</v>
@@ -7656,13 +7636,13 @@
     </row>
     <row r="221" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A221" t="s">
-        <v>740</v>
+        <v>736</v>
       </c>
       <c r="C221" t="s">
         <v>41</v>
       </c>
       <c r="D221" t="s">
-        <v>741</v>
+        <v>737</v>
       </c>
       <c r="E221" t="s">
         <v>7</v>
@@ -7671,21 +7651,21 @@
         <v>8</v>
       </c>
       <c r="G221" t="s">
-        <v>742</v>
+        <v>738</v>
       </c>
       <c r="H221" t="s">
-        <v>743</v>
+        <v>739</v>
       </c>
     </row>
     <row r="222" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A222" t="s">
-        <v>744</v>
+        <v>740</v>
       </c>
       <c r="C222" t="s">
         <v>41</v>
       </c>
       <c r="D222" t="s">
-        <v>741</v>
+        <v>737</v>
       </c>
       <c r="E222" t="s">
         <v>7</v>
@@ -7694,10 +7674,80 @@
         <v>8</v>
       </c>
       <c r="G222" t="s">
+        <v>738</v>
+      </c>
+      <c r="H222" t="s">
+        <v>739</v>
+      </c>
+    </row>
+    <row r="223" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A223" t="s">
+        <v>741</v>
+      </c>
+      <c r="C223" t="s">
+        <v>17</v>
+      </c>
+      <c r="D223" t="s">
+        <v>741</v>
+      </c>
+      <c r="H223" t="s">
         <v>742</v>
       </c>
-      <c r="H222" t="s">
+    </row>
+    <row r="224" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A224" t="s">
+        <v>741</v>
+      </c>
+      <c r="C224" t="s">
+        <v>17</v>
+      </c>
+      <c r="D224" t="s">
+        <v>741</v>
+      </c>
+      <c r="H224" t="s">
+        <v>742</v>
+      </c>
+    </row>
+    <row r="225" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A225" t="s">
         <v>743</v>
+      </c>
+      <c r="C225" t="s">
+        <v>14</v>
+      </c>
+      <c r="D225" t="s">
+        <v>743</v>
+      </c>
+      <c r="H225" t="s">
+        <v>742</v>
+      </c>
+    </row>
+    <row r="226" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A226" t="s">
+        <v>744</v>
+      </c>
+      <c r="C226" t="s">
+        <v>14</v>
+      </c>
+      <c r="D226" t="s">
+        <v>744</v>
+      </c>
+      <c r="H226" t="s">
+        <v>742</v>
+      </c>
+    </row>
+    <row r="227" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A227" t="s">
+        <v>745</v>
+      </c>
+      <c r="C227" t="s">
+        <v>6</v>
+      </c>
+      <c r="D227" t="s">
+        <v>745</v>
+      </c>
+      <c r="H227" t="s">
+        <v>742</v>
       </c>
     </row>
   </sheetData>

--- a/1.xlsx
+++ b/1.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="\\wh.local\fs\UserProfile_TSSWH19\_TSSWH19_redirected_folders\HunyaCs1\Desktop\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{30037DDE-A003-48D2-921C-E4BF20801272}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EDDC5EC4-6337-4647-99CF-080402CBEFF0}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="0" windowWidth="22260" windowHeight="12648" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1210" uniqueCount="619">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1205" uniqueCount="611">
   <si>
     <t>BUDAPEST</t>
   </si>
@@ -246,9 +246,6 @@
     <t>Rákóczi utca</t>
   </si>
   <si>
-    <t>1097</t>
-  </si>
-  <si>
     <t>1157</t>
   </si>
   <si>
@@ -1719,36 +1716,6 @@
     <t>Fürdő utca</t>
   </si>
   <si>
-    <t>NFD6-03-25-DHWP-1</t>
-  </si>
-  <si>
-    <t>NFD6-03-25-DHWP</t>
-  </si>
-  <si>
-    <t>1223</t>
-  </si>
-  <si>
-    <t>Csöngő utca</t>
-  </si>
-  <si>
-    <t>NFD6-03-26-AZ9W-1</t>
-  </si>
-  <si>
-    <t>NFD6-03-26-AZ9W</t>
-  </si>
-  <si>
-    <t>Táblás köz</t>
-  </si>
-  <si>
-    <t>NFD6-03-26-JYUS-1</t>
-  </si>
-  <si>
-    <t>NFD6-03-26-JYUS</t>
-  </si>
-  <si>
-    <t>Köztársaság tér</t>
-  </si>
-  <si>
     <t>202603232600682501</t>
   </si>
   <si>
@@ -1885,6 +1852,15 @@
   </si>
   <si>
     <t>159995579538525568</t>
+  </si>
+  <si>
+    <t>NFD6-03-21-7Y85</t>
+  </si>
+  <si>
+    <t>NFD6-03-22-MCTT</t>
+  </si>
+  <si>
+    <t>AUCHAN_ÁRUHÁZI</t>
   </si>
 </sst>
 </file>
@@ -2218,45 +2194,45 @@
   <sheetData>
     <row r="1" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
+        <v>118</v>
+      </c>
+      <c r="C1" t="s">
         <v>119</v>
       </c>
-      <c r="C1" t="s">
+      <c r="D1" t="s">
         <v>120</v>
       </c>
-      <c r="D1" t="s">
+      <c r="E1" t="s">
         <v>121</v>
       </c>
-      <c r="E1" t="s">
+      <c r="F1" t="s">
         <v>122</v>
       </c>
-      <c r="F1" t="s">
+      <c r="G1" t="s">
         <v>123</v>
       </c>
-      <c r="G1" t="s">
+      <c r="H1" t="s">
         <v>124</v>
-      </c>
-      <c r="H1" t="s">
-        <v>125</v>
       </c>
     </row>
     <row r="2" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="C2" t="s">
         <v>34</v>
       </c>
       <c r="D2" t="s">
+        <v>126</v>
+      </c>
+      <c r="E2" t="s">
         <v>127</v>
       </c>
-      <c r="E2" t="s">
+      <c r="F2" t="s">
         <v>128</v>
       </c>
-      <c r="F2" t="s">
+      <c r="G2" t="s">
         <v>129</v>
-      </c>
-      <c r="G2" t="s">
-        <v>130</v>
       </c>
       <c r="H2" t="s">
         <v>1</v>
@@ -2264,22 +2240,22 @@
     </row>
     <row r="3" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="C3" t="s">
         <v>29</v>
       </c>
       <c r="D3" t="s">
+        <v>131</v>
+      </c>
+      <c r="E3" t="s">
         <v>132</v>
       </c>
-      <c r="E3" t="s">
+      <c r="F3" t="s">
+        <v>0</v>
+      </c>
+      <c r="G3" t="s">
         <v>133</v>
-      </c>
-      <c r="F3" t="s">
-        <v>0</v>
-      </c>
-      <c r="G3" t="s">
-        <v>134</v>
       </c>
       <c r="H3" t="s">
         <v>1</v>
@@ -2287,22 +2263,22 @@
     </row>
     <row r="4" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="C4" t="s">
         <v>13</v>
       </c>
       <c r="D4" t="s">
+        <v>135</v>
+      </c>
+      <c r="E4" t="s">
+        <v>90</v>
+      </c>
+      <c r="F4" t="s">
+        <v>91</v>
+      </c>
+      <c r="G4" t="s">
         <v>136</v>
-      </c>
-      <c r="E4" t="s">
-        <v>91</v>
-      </c>
-      <c r="F4" t="s">
-        <v>92</v>
-      </c>
-      <c r="G4" t="s">
-        <v>137</v>
       </c>
       <c r="H4" t="s">
         <v>1</v>
@@ -2310,13 +2286,13 @@
     </row>
     <row r="5" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="C5" t="s">
         <v>13</v>
       </c>
       <c r="D5" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="E5" t="s">
         <v>48</v>
@@ -2325,7 +2301,7 @@
         <v>49</v>
       </c>
       <c r="G5" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="H5" t="s">
         <v>1</v>
@@ -2333,22 +2309,22 @@
     </row>
     <row r="6" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="C6" t="s">
         <v>11</v>
       </c>
       <c r="D6" t="s">
+        <v>141</v>
+      </c>
+      <c r="E6" t="s">
+        <v>73</v>
+      </c>
+      <c r="F6" t="s">
+        <v>0</v>
+      </c>
+      <c r="G6" t="s">
         <v>142</v>
-      </c>
-      <c r="E6" t="s">
-        <v>74</v>
-      </c>
-      <c r="F6" t="s">
-        <v>0</v>
-      </c>
-      <c r="G6" t="s">
-        <v>143</v>
       </c>
       <c r="H6" t="s">
         <v>1</v>
@@ -2356,22 +2332,22 @@
     </row>
     <row r="7" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="C7" t="s">
         <v>2</v>
       </c>
       <c r="D7" t="s">
+        <v>144</v>
+      </c>
+      <c r="E7" t="s">
+        <v>103</v>
+      </c>
+      <c r="F7" t="s">
+        <v>0</v>
+      </c>
+      <c r="G7" t="s">
         <v>145</v>
-      </c>
-      <c r="E7" t="s">
-        <v>104</v>
-      </c>
-      <c r="F7" t="s">
-        <v>0</v>
-      </c>
-      <c r="G7" t="s">
-        <v>146</v>
       </c>
       <c r="H7" t="s">
         <v>1</v>
@@ -2379,22 +2355,22 @@
     </row>
     <row r="8" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="C8" t="s">
         <v>3</v>
       </c>
       <c r="D8" t="s">
+        <v>147</v>
+      </c>
+      <c r="E8" t="s">
         <v>148</v>
       </c>
-      <c r="E8" t="s">
+      <c r="F8" t="s">
+        <v>0</v>
+      </c>
+      <c r="G8" t="s">
         <v>149</v>
-      </c>
-      <c r="F8" t="s">
-        <v>0</v>
-      </c>
-      <c r="G8" t="s">
-        <v>150</v>
       </c>
       <c r="H8" t="s">
         <v>1</v>
@@ -2402,22 +2378,22 @@
     </row>
     <row r="9" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="C9" t="s">
         <v>11</v>
       </c>
       <c r="D9" t="s">
+        <v>151</v>
+      </c>
+      <c r="E9" t="s">
         <v>152</v>
       </c>
-      <c r="E9" t="s">
+      <c r="F9" t="s">
+        <v>0</v>
+      </c>
+      <c r="G9" t="s">
         <v>153</v>
-      </c>
-      <c r="F9" t="s">
-        <v>0</v>
-      </c>
-      <c r="G9" t="s">
-        <v>154</v>
       </c>
       <c r="H9" t="s">
         <v>1</v>
@@ -2425,13 +2401,13 @@
     </row>
     <row r="10" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
+        <v>154</v>
+      </c>
+      <c r="C10" t="s">
         <v>155</v>
       </c>
-      <c r="C10" t="s">
+      <c r="D10" t="s">
         <v>156</v>
-      </c>
-      <c r="D10" t="s">
-        <v>157</v>
       </c>
       <c r="E10" t="s">
         <v>20</v>
@@ -2440,7 +2416,7 @@
         <v>21</v>
       </c>
       <c r="G10" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="H10" t="s">
         <v>1</v>
@@ -2448,22 +2424,22 @@
     </row>
     <row r="11" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A11" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="C11" t="s">
         <v>22</v>
       </c>
       <c r="D11" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="E11" t="s">
+        <v>95</v>
+      </c>
+      <c r="F11" t="s">
+        <v>0</v>
+      </c>
+      <c r="G11" t="s">
         <v>96</v>
-      </c>
-      <c r="F11" t="s">
-        <v>0</v>
-      </c>
-      <c r="G11" t="s">
-        <v>97</v>
       </c>
       <c r="H11" t="s">
         <v>1</v>
@@ -2471,22 +2447,22 @@
     </row>
     <row r="12" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A12" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="C12" t="s">
         <v>22</v>
       </c>
       <c r="D12" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="E12" t="s">
+        <v>95</v>
+      </c>
+      <c r="F12" t="s">
+        <v>0</v>
+      </c>
+      <c r="G12" t="s">
         <v>96</v>
-      </c>
-      <c r="F12" t="s">
-        <v>0</v>
-      </c>
-      <c r="G12" t="s">
-        <v>97</v>
       </c>
       <c r="H12" t="s">
         <v>1</v>
@@ -2494,22 +2470,22 @@
     </row>
     <row r="13" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A13" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="C13" t="s">
         <v>13</v>
       </c>
       <c r="D13" t="s">
+        <v>162</v>
+      </c>
+      <c r="E13" t="s">
+        <v>114</v>
+      </c>
+      <c r="F13" t="s">
+        <v>115</v>
+      </c>
+      <c r="G13" t="s">
         <v>163</v>
-      </c>
-      <c r="E13" t="s">
-        <v>115</v>
-      </c>
-      <c r="F13" t="s">
-        <v>116</v>
-      </c>
-      <c r="G13" t="s">
-        <v>164</v>
       </c>
       <c r="H13" t="s">
         <v>1</v>
@@ -2517,13 +2493,13 @@
     </row>
     <row r="14" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A14" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="C14" t="s">
         <v>35</v>
       </c>
       <c r="D14" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="E14" t="s">
         <v>65</v>
@@ -2532,7 +2508,7 @@
         <v>66</v>
       </c>
       <c r="G14" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="H14" t="s">
         <v>1</v>
@@ -2540,22 +2516,22 @@
     </row>
     <row r="15" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A15" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="C15" t="s">
         <v>29</v>
       </c>
       <c r="D15" t="s">
+        <v>168</v>
+      </c>
+      <c r="E15" t="s">
         <v>169</v>
       </c>
-      <c r="E15" t="s">
+      <c r="F15" t="s">
         <v>170</v>
       </c>
-      <c r="F15" t="s">
-        <v>171</v>
-      </c>
       <c r="G15" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="H15" t="s">
         <v>1</v>
@@ -2563,22 +2539,22 @@
     </row>
     <row r="16" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A16" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="C16" t="s">
         <v>3</v>
       </c>
       <c r="D16" t="s">
+        <v>172</v>
+      </c>
+      <c r="E16" t="s">
+        <v>148</v>
+      </c>
+      <c r="F16" t="s">
+        <v>0</v>
+      </c>
+      <c r="G16" t="s">
         <v>173</v>
-      </c>
-      <c r="E16" t="s">
-        <v>149</v>
-      </c>
-      <c r="F16" t="s">
-        <v>0</v>
-      </c>
-      <c r="G16" t="s">
-        <v>174</v>
       </c>
       <c r="H16" t="s">
         <v>1</v>
@@ -2586,22 +2562,22 @@
     </row>
     <row r="17" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A17" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="C17" t="s">
         <v>13</v>
       </c>
       <c r="D17" t="s">
+        <v>175</v>
+      </c>
+      <c r="E17" t="s">
         <v>176</v>
       </c>
-      <c r="E17" t="s">
+      <c r="F17" t="s">
         <v>177</v>
       </c>
-      <c r="F17" t="s">
+      <c r="G17" t="s">
         <v>178</v>
-      </c>
-      <c r="G17" t="s">
-        <v>179</v>
       </c>
       <c r="H17" t="s">
         <v>1</v>
@@ -2609,22 +2585,22 @@
     </row>
     <row r="18" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A18" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="C18" t="s">
         <v>13</v>
       </c>
       <c r="D18" t="s">
+        <v>175</v>
+      </c>
+      <c r="E18" t="s">
         <v>176</v>
       </c>
-      <c r="E18" t="s">
+      <c r="F18" t="s">
         <v>177</v>
       </c>
-      <c r="F18" t="s">
+      <c r="G18" t="s">
         <v>178</v>
-      </c>
-      <c r="G18" t="s">
-        <v>179</v>
       </c>
       <c r="H18" t="s">
         <v>1</v>
@@ -2632,22 +2608,22 @@
     </row>
     <row r="19" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A19" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="C19" t="s">
         <v>14</v>
       </c>
       <c r="D19" t="s">
+        <v>181</v>
+      </c>
+      <c r="E19" t="s">
+        <v>77</v>
+      </c>
+      <c r="F19" t="s">
+        <v>0</v>
+      </c>
+      <c r="G19" t="s">
         <v>182</v>
-      </c>
-      <c r="E19" t="s">
-        <v>78</v>
-      </c>
-      <c r="F19" t="s">
-        <v>0</v>
-      </c>
-      <c r="G19" t="s">
-        <v>183</v>
       </c>
       <c r="H19" t="s">
         <v>1</v>
@@ -2655,13 +2631,13 @@
     </row>
     <row r="20" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A20" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="C20" t="s">
         <v>25</v>
       </c>
       <c r="D20" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="E20" t="s">
         <v>16</v>
@@ -2670,7 +2646,7 @@
         <v>17</v>
       </c>
       <c r="G20" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="H20" t="s">
         <v>1</v>
@@ -2678,13 +2654,13 @@
     </row>
     <row r="21" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A21" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="C21" t="s">
         <v>9</v>
       </c>
       <c r="D21" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="E21" t="s">
         <v>36</v>
@@ -2693,7 +2669,7 @@
         <v>37</v>
       </c>
       <c r="G21" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="H21" t="s">
         <v>1</v>
@@ -2701,13 +2677,13 @@
     </row>
     <row r="22" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A22" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="C22" t="s">
         <v>9</v>
       </c>
       <c r="D22" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="E22" t="s">
         <v>7</v>
@@ -2716,7 +2692,7 @@
         <v>8</v>
       </c>
       <c r="G22" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="H22" t="s">
         <v>1</v>
@@ -2724,22 +2700,22 @@
     </row>
     <row r="23" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A23" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="C23" t="s">
         <v>9</v>
       </c>
       <c r="D23" t="s">
+        <v>193</v>
+      </c>
+      <c r="E23" t="s">
+        <v>93</v>
+      </c>
+      <c r="F23" t="s">
+        <v>0</v>
+      </c>
+      <c r="G23" t="s">
         <v>194</v>
-      </c>
-      <c r="E23" t="s">
-        <v>94</v>
-      </c>
-      <c r="F23" t="s">
-        <v>0</v>
-      </c>
-      <c r="G23" t="s">
-        <v>195</v>
       </c>
       <c r="H23" t="s">
         <v>1</v>
@@ -2747,22 +2723,22 @@
     </row>
     <row r="24" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A24" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="C24" t="s">
         <v>3</v>
       </c>
       <c r="D24" t="s">
+        <v>196</v>
+      </c>
+      <c r="E24" t="s">
+        <v>80</v>
+      </c>
+      <c r="F24" t="s">
+        <v>0</v>
+      </c>
+      <c r="G24" t="s">
         <v>197</v>
-      </c>
-      <c r="E24" t="s">
-        <v>81</v>
-      </c>
-      <c r="F24" t="s">
-        <v>0</v>
-      </c>
-      <c r="G24" t="s">
-        <v>198</v>
       </c>
       <c r="H24" t="s">
         <v>1</v>
@@ -2770,13 +2746,13 @@
     </row>
     <row r="25" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A25" t="s">
+        <v>198</v>
+      </c>
+      <c r="C25" t="s">
+        <v>155</v>
+      </c>
+      <c r="D25" t="s">
         <v>199</v>
-      </c>
-      <c r="C25" t="s">
-        <v>156</v>
-      </c>
-      <c r="D25" t="s">
-        <v>200</v>
       </c>
       <c r="E25" t="s">
         <v>23</v>
@@ -2785,7 +2761,7 @@
         <v>24</v>
       </c>
       <c r="G25" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="H25" t="s">
         <v>1</v>
@@ -2793,22 +2769,22 @@
     </row>
     <row r="26" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A26" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c r="C26" t="s">
         <v>13</v>
       </c>
       <c r="D26" t="s">
+        <v>202</v>
+      </c>
+      <c r="E26" t="s">
         <v>203</v>
       </c>
-      <c r="E26" t="s">
+      <c r="F26" t="s">
         <v>204</v>
       </c>
-      <c r="F26" t="s">
+      <c r="G26" t="s">
         <v>205</v>
-      </c>
-      <c r="G26" t="s">
-        <v>206</v>
       </c>
       <c r="H26" t="s">
         <v>1</v>
@@ -2816,22 +2792,22 @@
     </row>
     <row r="27" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A27" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="C27" t="s">
         <v>13</v>
       </c>
       <c r="D27" t="s">
+        <v>202</v>
+      </c>
+      <c r="E27" t="s">
         <v>203</v>
       </c>
-      <c r="E27" t="s">
+      <c r="F27" t="s">
         <v>204</v>
       </c>
-      <c r="F27" t="s">
+      <c r="G27" t="s">
         <v>205</v>
-      </c>
-      <c r="G27" t="s">
-        <v>206</v>
       </c>
       <c r="H27" t="s">
         <v>1</v>
@@ -2839,13 +2815,13 @@
     </row>
     <row r="28" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A28" t="s">
+        <v>207</v>
+      </c>
+      <c r="C28" t="s">
+        <v>155</v>
+      </c>
+      <c r="D28" t="s">
         <v>208</v>
-      </c>
-      <c r="C28" t="s">
-        <v>156</v>
-      </c>
-      <c r="D28" t="s">
-        <v>209</v>
       </c>
       <c r="E28" t="s">
         <v>27</v>
@@ -2854,7 +2830,7 @@
         <v>28</v>
       </c>
       <c r="G28" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="H28" t="s">
         <v>1</v>
@@ -2862,13 +2838,13 @@
     </row>
     <row r="29" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A29" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="C29" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="D29" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="E29" t="s">
         <v>27</v>
@@ -2877,7 +2853,7 @@
         <v>28</v>
       </c>
       <c r="G29" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="H29" t="s">
         <v>1</v>
@@ -2885,22 +2861,22 @@
     </row>
     <row r="30" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A30" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="C30" t="s">
         <v>35</v>
       </c>
       <c r="D30" t="s">
+        <v>212</v>
+      </c>
+      <c r="E30" t="s">
         <v>213</v>
       </c>
-      <c r="E30" t="s">
+      <c r="F30" t="s">
         <v>214</v>
       </c>
-      <c r="F30" t="s">
+      <c r="G30" t="s">
         <v>215</v>
-      </c>
-      <c r="G30" t="s">
-        <v>216</v>
       </c>
       <c r="H30" t="s">
         <v>1</v>
@@ -2908,19 +2884,19 @@
     </row>
     <row r="31" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A31" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="C31" t="s">
         <v>13</v>
       </c>
       <c r="D31" t="s">
+        <v>217</v>
+      </c>
+      <c r="E31" t="s">
         <v>218</v>
       </c>
-      <c r="E31" t="s">
+      <c r="F31" t="s">
         <v>219</v>
-      </c>
-      <c r="F31" t="s">
-        <v>220</v>
       </c>
       <c r="G31" t="s">
         <v>58</v>
@@ -2931,22 +2907,22 @@
     </row>
     <row r="32" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A32" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
       <c r="C32" t="s">
         <v>6</v>
       </c>
       <c r="D32" t="s">
+        <v>221</v>
+      </c>
+      <c r="E32" t="s">
         <v>222</v>
       </c>
-      <c r="E32" t="s">
+      <c r="F32" t="s">
         <v>223</v>
       </c>
-      <c r="F32" t="s">
+      <c r="G32" t="s">
         <v>224</v>
-      </c>
-      <c r="G32" t="s">
-        <v>225</v>
       </c>
       <c r="H32" t="s">
         <v>1</v>
@@ -2954,22 +2930,22 @@
     </row>
     <row r="33" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A33" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="C33" t="s">
         <v>6</v>
       </c>
       <c r="D33" t="s">
+        <v>221</v>
+      </c>
+      <c r="E33" t="s">
         <v>222</v>
       </c>
-      <c r="E33" t="s">
+      <c r="F33" t="s">
         <v>223</v>
       </c>
-      <c r="F33" t="s">
+      <c r="G33" t="s">
         <v>224</v>
-      </c>
-      <c r="G33" t="s">
-        <v>225</v>
       </c>
       <c r="H33" t="s">
         <v>1</v>
@@ -2977,22 +2953,22 @@
     </row>
     <row r="34" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A34" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
       <c r="C34" t="s">
         <v>6</v>
       </c>
       <c r="D34" t="s">
+        <v>227</v>
+      </c>
+      <c r="E34" t="s">
         <v>228</v>
       </c>
-      <c r="E34" t="s">
+      <c r="F34" t="s">
         <v>229</v>
       </c>
-      <c r="F34" t="s">
+      <c r="G34" t="s">
         <v>230</v>
-      </c>
-      <c r="G34" t="s">
-        <v>231</v>
       </c>
       <c r="H34" t="s">
         <v>1</v>
@@ -3000,22 +2976,22 @@
     </row>
     <row r="35" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A35" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="C35" t="s">
         <v>13</v>
       </c>
       <c r="D35" t="s">
+        <v>232</v>
+      </c>
+      <c r="E35" t="s">
         <v>233</v>
       </c>
-      <c r="E35" t="s">
+      <c r="F35" t="s">
         <v>234</v>
       </c>
-      <c r="F35" t="s">
+      <c r="G35" t="s">
         <v>235</v>
-      </c>
-      <c r="G35" t="s">
-        <v>236</v>
       </c>
       <c r="H35" t="s">
         <v>1</v>
@@ -3023,22 +2999,22 @@
     </row>
     <row r="36" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A36" t="s">
-        <v>237</v>
+        <v>236</v>
       </c>
       <c r="C36" t="s">
         <v>34</v>
       </c>
       <c r="D36" t="s">
+        <v>237</v>
+      </c>
+      <c r="E36" t="s">
         <v>238</v>
       </c>
-      <c r="E36" t="s">
+      <c r="F36" t="s">
         <v>239</v>
       </c>
-      <c r="F36" t="s">
+      <c r="G36" t="s">
         <v>240</v>
-      </c>
-      <c r="G36" t="s">
-        <v>241</v>
       </c>
       <c r="H36" t="s">
         <v>1</v>
@@ -3046,13 +3022,13 @@
     </row>
     <row r="37" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A37" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
       <c r="C37" t="s">
         <v>12</v>
       </c>
       <c r="D37" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
       <c r="E37" t="s">
         <v>26</v>
@@ -3061,7 +3037,7 @@
         <v>0</v>
       </c>
       <c r="G37" t="s">
-        <v>244</v>
+        <v>243</v>
       </c>
       <c r="H37" t="s">
         <v>1</v>
@@ -3069,22 +3045,22 @@
     </row>
     <row r="38" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A38" t="s">
-        <v>245</v>
+        <v>244</v>
       </c>
       <c r="C38" t="s">
         <v>43</v>
       </c>
       <c r="D38" t="s">
+        <v>245</v>
+      </c>
+      <c r="E38" t="s">
         <v>246</v>
       </c>
-      <c r="E38" t="s">
+      <c r="F38" t="s">
+        <v>0</v>
+      </c>
+      <c r="G38" t="s">
         <v>247</v>
-      </c>
-      <c r="F38" t="s">
-        <v>0</v>
-      </c>
-      <c r="G38" t="s">
-        <v>248</v>
       </c>
       <c r="H38" t="s">
         <v>1</v>
@@ -3092,22 +3068,22 @@
     </row>
     <row r="39" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A39" t="s">
-        <v>249</v>
+        <v>248</v>
       </c>
       <c r="C39" t="s">
         <v>43</v>
       </c>
       <c r="D39" t="s">
+        <v>245</v>
+      </c>
+      <c r="E39" t="s">
         <v>246</v>
       </c>
-      <c r="E39" t="s">
+      <c r="F39" t="s">
+        <v>0</v>
+      </c>
+      <c r="G39" t="s">
         <v>247</v>
-      </c>
-      <c r="F39" t="s">
-        <v>0</v>
-      </c>
-      <c r="G39" t="s">
-        <v>248</v>
       </c>
       <c r="H39" t="s">
         <v>1</v>
@@ -3115,16 +3091,16 @@
     </row>
     <row r="40" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A40" t="s">
-        <v>250</v>
+        <v>249</v>
       </c>
       <c r="C40" t="s">
         <v>11</v>
       </c>
       <c r="D40" t="s">
-        <v>251</v>
+        <v>250</v>
       </c>
       <c r="E40" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="F40" t="s">
         <v>0</v>
@@ -3138,22 +3114,22 @@
     </row>
     <row r="41" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A41" t="s">
-        <v>252</v>
+        <v>251</v>
       </c>
       <c r="C41" t="s">
         <v>9</v>
       </c>
       <c r="D41" t="s">
+        <v>252</v>
+      </c>
+      <c r="E41" t="s">
         <v>253</v>
       </c>
-      <c r="E41" t="s">
+      <c r="F41" t="s">
         <v>254</v>
       </c>
-      <c r="F41" t="s">
+      <c r="G41" t="s">
         <v>255</v>
-      </c>
-      <c r="G41" t="s">
-        <v>256</v>
       </c>
       <c r="H41" t="s">
         <v>1</v>
@@ -3161,13 +3137,13 @@
     </row>
     <row r="42" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A42" t="s">
-        <v>257</v>
+        <v>256</v>
       </c>
       <c r="C42" t="s">
         <v>43</v>
       </c>
       <c r="D42" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="E42" t="s">
         <v>41</v>
@@ -3184,13 +3160,13 @@
     </row>
     <row r="43" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A43" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
       <c r="C43" t="s">
         <v>43</v>
       </c>
       <c r="D43" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="E43" t="s">
         <v>41</v>
@@ -3207,13 +3183,13 @@
     </row>
     <row r="44" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A44" t="s">
-        <v>260</v>
+        <v>259</v>
       </c>
       <c r="C44" t="s">
         <v>3</v>
       </c>
       <c r="D44" t="s">
-        <v>261</v>
+        <v>260</v>
       </c>
       <c r="E44" t="s">
         <v>46</v>
@@ -3222,7 +3198,7 @@
         <v>0</v>
       </c>
       <c r="G44" t="s">
-        <v>262</v>
+        <v>261</v>
       </c>
       <c r="H44" t="s">
         <v>1</v>
@@ -3230,22 +3206,22 @@
     </row>
     <row r="45" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A45" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="C45" t="s">
         <v>14</v>
       </c>
       <c r="D45" t="s">
+        <v>263</v>
+      </c>
+      <c r="E45" t="s">
+        <v>92</v>
+      </c>
+      <c r="F45" t="s">
+        <v>0</v>
+      </c>
+      <c r="G45" t="s">
         <v>264</v>
-      </c>
-      <c r="E45" t="s">
-        <v>93</v>
-      </c>
-      <c r="F45" t="s">
-        <v>0</v>
-      </c>
-      <c r="G45" t="s">
-        <v>265</v>
       </c>
       <c r="H45" t="s">
         <v>1</v>
@@ -3253,22 +3229,22 @@
     </row>
     <row r="46" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A46" t="s">
-        <v>266</v>
+        <v>265</v>
       </c>
       <c r="C46" t="s">
         <v>29</v>
       </c>
       <c r="D46" t="s">
+        <v>266</v>
+      </c>
+      <c r="E46" t="s">
+        <v>132</v>
+      </c>
+      <c r="F46" t="s">
+        <v>0</v>
+      </c>
+      <c r="G46" t="s">
         <v>267</v>
-      </c>
-      <c r="E46" t="s">
-        <v>133</v>
-      </c>
-      <c r="F46" t="s">
-        <v>0</v>
-      </c>
-      <c r="G46" t="s">
-        <v>268</v>
       </c>
       <c r="H46" t="s">
         <v>1</v>
@@ -3276,22 +3252,22 @@
     </row>
     <row r="47" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A47" t="s">
-        <v>269</v>
+        <v>268</v>
       </c>
       <c r="C47" t="s">
         <v>29</v>
       </c>
       <c r="D47" t="s">
+        <v>269</v>
+      </c>
+      <c r="E47" t="s">
         <v>270</v>
       </c>
-      <c r="E47" t="s">
+      <c r="F47" t="s">
+        <v>0</v>
+      </c>
+      <c r="G47" t="s">
         <v>271</v>
-      </c>
-      <c r="F47" t="s">
-        <v>0</v>
-      </c>
-      <c r="G47" t="s">
-        <v>272</v>
       </c>
       <c r="H47" t="s">
         <v>1</v>
@@ -3299,13 +3275,13 @@
     </row>
     <row r="48" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A48" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="C48" t="s">
         <v>32</v>
       </c>
       <c r="D48" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
       <c r="E48" t="s">
         <v>42</v>
@@ -3314,7 +3290,7 @@
         <v>0</v>
       </c>
       <c r="G48" t="s">
-        <v>275</v>
+        <v>274</v>
       </c>
       <c r="H48" t="s">
         <v>1</v>
@@ -3322,13 +3298,13 @@
     </row>
     <row r="49" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A49" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="C49" t="s">
         <v>32</v>
       </c>
       <c r="D49" t="s">
-        <v>277</v>
+        <v>276</v>
       </c>
       <c r="E49" t="s">
         <v>64</v>
@@ -3337,7 +3313,7 @@
         <v>0</v>
       </c>
       <c r="G49" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="H49" t="s">
         <v>1</v>
@@ -3345,13 +3321,13 @@
     </row>
     <row r="50" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A50" t="s">
-        <v>279</v>
+        <v>278</v>
       </c>
       <c r="C50" t="s">
         <v>32</v>
       </c>
       <c r="D50" t="s">
-        <v>277</v>
+        <v>276</v>
       </c>
       <c r="E50" t="s">
         <v>64</v>
@@ -3360,7 +3336,7 @@
         <v>0</v>
       </c>
       <c r="G50" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="H50" t="s">
         <v>1</v>
@@ -3368,13 +3344,13 @@
     </row>
     <row r="51" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A51" t="s">
-        <v>280</v>
+        <v>279</v>
       </c>
       <c r="C51" t="s">
         <v>34</v>
       </c>
       <c r="D51" t="s">
-        <v>281</v>
+        <v>280</v>
       </c>
       <c r="E51" t="s">
         <v>70</v>
@@ -3383,7 +3359,7 @@
         <v>0</v>
       </c>
       <c r="G51" t="s">
-        <v>282</v>
+        <v>281</v>
       </c>
       <c r="H51" t="s">
         <v>1</v>
@@ -3391,13 +3367,13 @@
     </row>
     <row r="52" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A52" t="s">
-        <v>283</v>
+        <v>282</v>
       </c>
       <c r="C52" t="s">
         <v>34</v>
       </c>
       <c r="D52" t="s">
-        <v>281</v>
+        <v>280</v>
       </c>
       <c r="E52" t="s">
         <v>70</v>
@@ -3406,7 +3382,7 @@
         <v>0</v>
       </c>
       <c r="G52" t="s">
-        <v>282</v>
+        <v>281</v>
       </c>
       <c r="H52" t="s">
         <v>1</v>
@@ -3414,13 +3390,13 @@
     </row>
     <row r="53" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A53" t="s">
-        <v>284</v>
+        <v>283</v>
       </c>
       <c r="C53" t="s">
         <v>22</v>
       </c>
       <c r="D53" t="s">
-        <v>285</v>
+        <v>284</v>
       </c>
       <c r="E53" t="s">
         <v>40</v>
@@ -3429,21 +3405,21 @@
         <v>0</v>
       </c>
       <c r="G53" t="s">
+        <v>285</v>
+      </c>
+      <c r="H53" t="s">
         <v>286</v>
-      </c>
-      <c r="H53" t="s">
-        <v>287</v>
       </c>
     </row>
     <row r="54" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A54" t="s">
-        <v>288</v>
+        <v>287</v>
       </c>
       <c r="C54" t="s">
         <v>9</v>
       </c>
       <c r="D54" t="s">
-        <v>289</v>
+        <v>288</v>
       </c>
       <c r="E54" t="s">
         <v>7</v>
@@ -3452,7 +3428,7 @@
         <v>8</v>
       </c>
       <c r="G54" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c r="H54" t="s">
         <v>4</v>
@@ -3460,22 +3436,22 @@
     </row>
     <row r="55" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A55" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="C55" t="s">
         <v>14</v>
       </c>
       <c r="D55" t="s">
+        <v>76</v>
+      </c>
+      <c r="E55" t="s">
         <v>77</v>
       </c>
-      <c r="E55" t="s">
+      <c r="F55" t="s">
+        <v>0</v>
+      </c>
+      <c r="G55" t="s">
         <v>78</v>
-      </c>
-      <c r="F55" t="s">
-        <v>0</v>
-      </c>
-      <c r="G55" t="s">
-        <v>79</v>
       </c>
       <c r="H55" t="s">
         <v>4</v>
@@ -3483,22 +3459,22 @@
     </row>
     <row r="56" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A56" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
       <c r="C56" t="s">
         <v>34</v>
       </c>
       <c r="D56" t="s">
+        <v>291</v>
+      </c>
+      <c r="E56" t="s">
         <v>292</v>
       </c>
-      <c r="E56" t="s">
+      <c r="F56" t="s">
         <v>293</v>
       </c>
-      <c r="F56" t="s">
+      <c r="G56" t="s">
         <v>294</v>
-      </c>
-      <c r="G56" t="s">
-        <v>295</v>
       </c>
       <c r="H56" t="s">
         <v>4</v>
@@ -3506,22 +3482,22 @@
     </row>
     <row r="57" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A57" t="s">
-        <v>296</v>
+        <v>295</v>
       </c>
       <c r="C57" t="s">
         <v>10</v>
       </c>
       <c r="D57" t="s">
+        <v>296</v>
+      </c>
+      <c r="E57" t="s">
         <v>297</v>
       </c>
-      <c r="E57" t="s">
+      <c r="F57" t="s">
         <v>298</v>
       </c>
-      <c r="F57" t="s">
+      <c r="G57" t="s">
         <v>299</v>
-      </c>
-      <c r="G57" t="s">
-        <v>300</v>
       </c>
       <c r="H57" t="s">
         <v>4</v>
@@ -3529,22 +3505,22 @@
     </row>
     <row r="58" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A58" t="s">
-        <v>301</v>
+        <v>300</v>
       </c>
       <c r="C58" t="s">
         <v>2</v>
       </c>
       <c r="D58" t="s">
+        <v>301</v>
+      </c>
+      <c r="E58" t="s">
+        <v>94</v>
+      </c>
+      <c r="F58" t="s">
+        <v>0</v>
+      </c>
+      <c r="G58" t="s">
         <v>302</v>
-      </c>
-      <c r="E58" t="s">
-        <v>95</v>
-      </c>
-      <c r="F58" t="s">
-        <v>0</v>
-      </c>
-      <c r="G58" t="s">
-        <v>303</v>
       </c>
       <c r="H58" t="s">
         <v>4</v>
@@ -3552,22 +3528,22 @@
     </row>
     <row r="59" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A59" t="s">
-        <v>304</v>
+        <v>303</v>
       </c>
       <c r="C59" t="s">
         <v>31</v>
       </c>
       <c r="D59" t="s">
+        <v>304</v>
+      </c>
+      <c r="E59" t="s">
         <v>305</v>
       </c>
-      <c r="E59" t="s">
+      <c r="F59" t="s">
+        <v>0</v>
+      </c>
+      <c r="G59" t="s">
         <v>306</v>
-      </c>
-      <c r="F59" t="s">
-        <v>0</v>
-      </c>
-      <c r="G59" t="s">
-        <v>307</v>
       </c>
       <c r="H59" t="s">
         <v>4</v>
@@ -3575,22 +3551,22 @@
     </row>
     <row r="60" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A60" t="s">
-        <v>308</v>
+        <v>307</v>
       </c>
       <c r="C60" t="s">
         <v>31</v>
       </c>
       <c r="D60" t="s">
+        <v>304</v>
+      </c>
+      <c r="E60" t="s">
         <v>305</v>
       </c>
-      <c r="E60" t="s">
+      <c r="F60" t="s">
+        <v>0</v>
+      </c>
+      <c r="G60" t="s">
         <v>306</v>
-      </c>
-      <c r="F60" t="s">
-        <v>0</v>
-      </c>
-      <c r="G60" t="s">
-        <v>307</v>
       </c>
       <c r="H60" t="s">
         <v>4</v>
@@ -3598,16 +3574,16 @@
     </row>
     <row r="61" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A61" t="s">
-        <v>309</v>
+        <v>308</v>
       </c>
       <c r="C61" t="s">
         <v>11</v>
       </c>
       <c r="D61" t="s">
-        <v>310</v>
+        <v>309</v>
       </c>
       <c r="E61" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="F61" t="s">
         <v>0</v>
@@ -3621,22 +3597,22 @@
     </row>
     <row r="62" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A62" t="s">
-        <v>311</v>
+        <v>310</v>
       </c>
       <c r="C62" t="s">
         <v>22</v>
       </c>
       <c r="D62" t="s">
+        <v>311</v>
+      </c>
+      <c r="E62" t="s">
         <v>312</v>
       </c>
-      <c r="E62" t="s">
-        <v>313</v>
-      </c>
       <c r="F62" t="s">
         <v>0</v>
       </c>
       <c r="G62" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="H62" t="s">
         <v>4</v>
@@ -3644,13 +3620,13 @@
     </row>
     <row r="63" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A63" t="s">
-        <v>314</v>
+        <v>313</v>
       </c>
       <c r="C63" t="s">
         <v>34</v>
       </c>
       <c r="D63" t="s">
-        <v>315</v>
+        <v>314</v>
       </c>
       <c r="E63" t="s">
         <v>70</v>
@@ -3659,7 +3635,7 @@
         <v>0</v>
       </c>
       <c r="G63" t="s">
-        <v>282</v>
+        <v>281</v>
       </c>
       <c r="H63" t="s">
         <v>4</v>
@@ -3667,13 +3643,13 @@
     </row>
     <row r="64" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A64" t="s">
-        <v>316</v>
+        <v>315</v>
       </c>
       <c r="C64" t="s">
         <v>34</v>
       </c>
       <c r="D64" t="s">
-        <v>315</v>
+        <v>314</v>
       </c>
       <c r="E64" t="s">
         <v>70</v>
@@ -3682,7 +3658,7 @@
         <v>0</v>
       </c>
       <c r="G64" t="s">
-        <v>282</v>
+        <v>281</v>
       </c>
       <c r="H64" t="s">
         <v>4</v>
@@ -3690,13 +3666,13 @@
     </row>
     <row r="65" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A65" t="s">
-        <v>317</v>
+        <v>316</v>
       </c>
       <c r="C65" t="s">
         <v>34</v>
       </c>
       <c r="D65" t="s">
-        <v>315</v>
+        <v>314</v>
       </c>
       <c r="E65" t="s">
         <v>70</v>
@@ -3705,7 +3681,7 @@
         <v>0</v>
       </c>
       <c r="G65" t="s">
-        <v>282</v>
+        <v>281</v>
       </c>
       <c r="H65" t="s">
         <v>4</v>
@@ -3713,22 +3689,22 @@
     </row>
     <row r="66" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A66" t="s">
-        <v>318</v>
+        <v>317</v>
       </c>
       <c r="C66" t="s">
         <v>15</v>
       </c>
       <c r="D66" t="s">
+        <v>318</v>
+      </c>
+      <c r="E66" t="s">
         <v>319</v>
       </c>
-      <c r="E66" t="s">
+      <c r="F66" t="s">
+        <v>0</v>
+      </c>
+      <c r="G66" t="s">
         <v>320</v>
-      </c>
-      <c r="F66" t="s">
-        <v>0</v>
-      </c>
-      <c r="G66" t="s">
-        <v>321</v>
       </c>
       <c r="H66" t="s">
         <v>4</v>
@@ -3736,22 +3712,22 @@
     </row>
     <row r="67" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A67" t="s">
-        <v>322</v>
+        <v>321</v>
       </c>
       <c r="C67" t="s">
         <v>15</v>
       </c>
       <c r="D67" t="s">
+        <v>318</v>
+      </c>
+      <c r="E67" t="s">
         <v>319</v>
       </c>
-      <c r="E67" t="s">
+      <c r="F67" t="s">
+        <v>0</v>
+      </c>
+      <c r="G67" t="s">
         <v>320</v>
-      </c>
-      <c r="F67" t="s">
-        <v>0</v>
-      </c>
-      <c r="G67" t="s">
-        <v>321</v>
       </c>
       <c r="H67" t="s">
         <v>4</v>
@@ -3759,22 +3735,22 @@
     </row>
     <row r="68" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A68" t="s">
-        <v>323</v>
+        <v>322</v>
       </c>
       <c r="C68" t="s">
         <v>15</v>
       </c>
       <c r="D68" t="s">
+        <v>318</v>
+      </c>
+      <c r="E68" t="s">
         <v>319</v>
       </c>
-      <c r="E68" t="s">
+      <c r="F68" t="s">
+        <v>0</v>
+      </c>
+      <c r="G68" t="s">
         <v>320</v>
-      </c>
-      <c r="F68" t="s">
-        <v>0</v>
-      </c>
-      <c r="G68" t="s">
-        <v>321</v>
       </c>
       <c r="H68" t="s">
         <v>4</v>
@@ -3782,22 +3758,22 @@
     </row>
     <row r="69" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A69" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="C69" t="s">
         <v>35</v>
       </c>
       <c r="D69" t="s">
+        <v>84</v>
+      </c>
+      <c r="E69" t="s">
         <v>85</v>
       </c>
-      <c r="E69" t="s">
+      <c r="F69" t="s">
         <v>86</v>
       </c>
-      <c r="F69" t="s">
+      <c r="G69" t="s">
         <v>87</v>
-      </c>
-      <c r="G69" t="s">
-        <v>88</v>
       </c>
       <c r="H69" t="s">
         <v>4</v>
@@ -3805,22 +3781,22 @@
     </row>
     <row r="70" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A70" t="s">
-        <v>324</v>
+        <v>323</v>
       </c>
       <c r="C70" t="s">
         <v>34</v>
       </c>
       <c r="D70" t="s">
+        <v>324</v>
+      </c>
+      <c r="E70" t="s">
         <v>325</v>
       </c>
-      <c r="E70" t="s">
+      <c r="F70" t="s">
         <v>326</v>
       </c>
-      <c r="F70" t="s">
+      <c r="G70" t="s">
         <v>327</v>
-      </c>
-      <c r="G70" t="s">
-        <v>328</v>
       </c>
       <c r="H70" t="s">
         <v>4</v>
@@ -3828,13 +3804,13 @@
     </row>
     <row r="71" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A71" t="s">
-        <v>329</v>
+        <v>328</v>
       </c>
       <c r="C71" t="s">
         <v>12</v>
       </c>
       <c r="D71" t="s">
-        <v>330</v>
+        <v>329</v>
       </c>
       <c r="E71" t="s">
         <v>60</v>
@@ -3843,7 +3819,7 @@
         <v>61</v>
       </c>
       <c r="G71" t="s">
-        <v>331</v>
+        <v>330</v>
       </c>
       <c r="H71" t="s">
         <v>4</v>
@@ -3851,13 +3827,13 @@
     </row>
     <row r="72" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A72" t="s">
-        <v>332</v>
+        <v>331</v>
       </c>
       <c r="C72" t="s">
         <v>12</v>
       </c>
       <c r="D72" t="s">
-        <v>333</v>
+        <v>332</v>
       </c>
       <c r="E72" t="s">
         <v>47</v>
@@ -3866,7 +3842,7 @@
         <v>0</v>
       </c>
       <c r="G72" t="s">
-        <v>334</v>
+        <v>333</v>
       </c>
       <c r="H72" t="s">
         <v>4</v>
@@ -3874,13 +3850,13 @@
     </row>
     <row r="73" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A73" t="s">
-        <v>335</v>
+        <v>334</v>
       </c>
       <c r="C73" t="s">
         <v>2</v>
       </c>
       <c r="D73" t="s">
-        <v>336</v>
+        <v>335</v>
       </c>
       <c r="E73" t="s">
         <v>50</v>
@@ -3889,7 +3865,7 @@
         <v>0</v>
       </c>
       <c r="G73" t="s">
-        <v>337</v>
+        <v>336</v>
       </c>
       <c r="H73" t="s">
         <v>4</v>
@@ -3897,22 +3873,22 @@
     </row>
     <row r="74" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A74" t="s">
-        <v>338</v>
+        <v>337</v>
       </c>
       <c r="C74" t="s">
         <v>11</v>
       </c>
       <c r="D74" t="s">
-        <v>339</v>
+        <v>338</v>
       </c>
       <c r="E74" t="s">
+        <v>152</v>
+      </c>
+      <c r="F74" t="s">
+        <v>0</v>
+      </c>
+      <c r="G74" t="s">
         <v>153</v>
-      </c>
-      <c r="F74" t="s">
-        <v>0</v>
-      </c>
-      <c r="G74" t="s">
-        <v>154</v>
       </c>
       <c r="H74" t="s">
         <v>4</v>
@@ -3920,13 +3896,13 @@
     </row>
     <row r="75" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A75" t="s">
-        <v>340</v>
+        <v>339</v>
       </c>
       <c r="C75" t="s">
         <v>31</v>
       </c>
       <c r="D75" t="s">
-        <v>341</v>
+        <v>340</v>
       </c>
       <c r="E75" t="s">
         <v>38</v>
@@ -3935,7 +3911,7 @@
         <v>0</v>
       </c>
       <c r="G75" t="s">
-        <v>342</v>
+        <v>341</v>
       </c>
       <c r="H75" t="s">
         <v>4</v>
@@ -3943,13 +3919,13 @@
     </row>
     <row r="76" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A76" t="s">
-        <v>343</v>
+        <v>342</v>
       </c>
       <c r="C76" t="s">
         <v>35</v>
       </c>
       <c r="D76" t="s">
-        <v>344</v>
+        <v>343</v>
       </c>
       <c r="E76" t="s">
         <v>65</v>
@@ -3958,7 +3934,7 @@
         <v>66</v>
       </c>
       <c r="G76" t="s">
-        <v>345</v>
+        <v>344</v>
       </c>
       <c r="H76" t="s">
         <v>4</v>
@@ -3966,13 +3942,13 @@
     </row>
     <row r="77" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A77" t="s">
-        <v>346</v>
+        <v>345</v>
       </c>
       <c r="C77" t="s">
         <v>35</v>
       </c>
       <c r="D77" t="s">
-        <v>344</v>
+        <v>343</v>
       </c>
       <c r="E77" t="s">
         <v>65</v>
@@ -3981,7 +3957,7 @@
         <v>66</v>
       </c>
       <c r="G77" t="s">
-        <v>345</v>
+        <v>344</v>
       </c>
       <c r="H77" t="s">
         <v>4</v>
@@ -3989,13 +3965,13 @@
     </row>
     <row r="78" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A78" t="s">
-        <v>347</v>
+        <v>346</v>
       </c>
       <c r="C78" t="s">
         <v>13</v>
       </c>
       <c r="D78" t="s">
-        <v>348</v>
+        <v>347</v>
       </c>
       <c r="E78" t="s">
         <v>48</v>
@@ -4004,7 +3980,7 @@
         <v>49</v>
       </c>
       <c r="G78" t="s">
-        <v>349</v>
+        <v>348</v>
       </c>
       <c r="H78" t="s">
         <v>4</v>
@@ -4012,22 +3988,22 @@
     </row>
     <row r="79" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A79" t="s">
-        <v>350</v>
+        <v>349</v>
       </c>
       <c r="C79" t="s">
         <v>34</v>
       </c>
       <c r="D79" t="s">
+        <v>350</v>
+      </c>
+      <c r="E79" t="s">
+        <v>325</v>
+      </c>
+      <c r="F79" t="s">
+        <v>326</v>
+      </c>
+      <c r="G79" t="s">
         <v>351</v>
-      </c>
-      <c r="E79" t="s">
-        <v>326</v>
-      </c>
-      <c r="F79" t="s">
-        <v>327</v>
-      </c>
-      <c r="G79" t="s">
-        <v>352</v>
       </c>
       <c r="H79" t="s">
         <v>4</v>
@@ -4035,22 +4011,22 @@
     </row>
     <row r="80" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A80" t="s">
-        <v>353</v>
+        <v>352</v>
       </c>
       <c r="C80" t="s">
         <v>2</v>
       </c>
       <c r="D80" t="s">
+        <v>353</v>
+      </c>
+      <c r="E80" t="s">
+        <v>97</v>
+      </c>
+      <c r="F80" t="s">
+        <v>0</v>
+      </c>
+      <c r="G80" t="s">
         <v>354</v>
-      </c>
-      <c r="E80" t="s">
-        <v>98</v>
-      </c>
-      <c r="F80" t="s">
-        <v>0</v>
-      </c>
-      <c r="G80" t="s">
-        <v>355</v>
       </c>
       <c r="H80" t="s">
         <v>4</v>
@@ -4058,13 +4034,13 @@
     </row>
     <row r="81" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A81" t="s">
-        <v>356</v>
+        <v>355</v>
       </c>
       <c r="C81" t="s">
         <v>10</v>
       </c>
       <c r="D81" t="s">
-        <v>357</v>
+        <v>356</v>
       </c>
       <c r="E81" t="s">
         <v>68</v>
@@ -4073,7 +4049,7 @@
         <v>69</v>
       </c>
       <c r="G81" t="s">
-        <v>358</v>
+        <v>357</v>
       </c>
       <c r="H81" t="s">
         <v>4</v>
@@ -4081,22 +4057,22 @@
     </row>
     <row r="82" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A82" t="s">
-        <v>359</v>
+        <v>358</v>
       </c>
       <c r="C82" t="s">
         <v>9</v>
       </c>
       <c r="D82" t="s">
+        <v>359</v>
+      </c>
+      <c r="E82" t="s">
         <v>360</v>
       </c>
-      <c r="E82" t="s">
+      <c r="F82" t="s">
         <v>361</v>
       </c>
-      <c r="F82" t="s">
+      <c r="G82" t="s">
         <v>362</v>
-      </c>
-      <c r="G82" t="s">
-        <v>363</v>
       </c>
       <c r="H82" t="s">
         <v>4</v>
@@ -4104,22 +4080,22 @@
     </row>
     <row r="83" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A83" t="s">
-        <v>364</v>
+        <v>363</v>
       </c>
       <c r="C83" t="s">
         <v>10</v>
       </c>
       <c r="D83" t="s">
+        <v>364</v>
+      </c>
+      <c r="E83" t="s">
         <v>365</v>
       </c>
-      <c r="E83" t="s">
+      <c r="F83" t="s">
         <v>366</v>
       </c>
-      <c r="F83" t="s">
-        <v>367</v>
-      </c>
       <c r="G83" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="H83" t="s">
         <v>4</v>
@@ -4127,22 +4103,22 @@
     </row>
     <row r="84" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A84" t="s">
-        <v>368</v>
+        <v>367</v>
       </c>
       <c r="C84" t="s">
         <v>10</v>
       </c>
       <c r="D84" t="s">
+        <v>364</v>
+      </c>
+      <c r="E84" t="s">
         <v>365</v>
       </c>
-      <c r="E84" t="s">
+      <c r="F84" t="s">
         <v>366</v>
       </c>
-      <c r="F84" t="s">
-        <v>367</v>
-      </c>
       <c r="G84" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="H84" t="s">
         <v>4</v>
@@ -4150,22 +4126,22 @@
     </row>
     <row r="85" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A85" t="s">
-        <v>369</v>
+        <v>368</v>
       </c>
       <c r="C85" t="s">
         <v>31</v>
       </c>
       <c r="D85" t="s">
+        <v>369</v>
+      </c>
+      <c r="E85" t="s">
+        <v>74</v>
+      </c>
+      <c r="F85" t="s">
+        <v>0</v>
+      </c>
+      <c r="G85" t="s">
         <v>370</v>
-      </c>
-      <c r="E85" t="s">
-        <v>75</v>
-      </c>
-      <c r="F85" t="s">
-        <v>0</v>
-      </c>
-      <c r="G85" t="s">
-        <v>371</v>
       </c>
       <c r="H85" t="s">
         <v>4</v>
@@ -4173,22 +4149,22 @@
     </row>
     <row r="86" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A86" t="s">
-        <v>372</v>
+        <v>371</v>
       </c>
       <c r="C86" t="s">
         <v>10</v>
       </c>
       <c r="D86" t="s">
+        <v>372</v>
+      </c>
+      <c r="E86" t="s">
         <v>373</v>
       </c>
-      <c r="E86" t="s">
+      <c r="F86" t="s">
         <v>374</v>
       </c>
-      <c r="F86" t="s">
+      <c r="G86" t="s">
         <v>375</v>
-      </c>
-      <c r="G86" t="s">
-        <v>376</v>
       </c>
       <c r="H86" t="s">
         <v>4</v>
@@ -4196,22 +4172,22 @@
     </row>
     <row r="87" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A87" t="s">
-        <v>377</v>
+        <v>376</v>
       </c>
       <c r="C87" t="s">
         <v>10</v>
       </c>
       <c r="D87" t="s">
+        <v>377</v>
+      </c>
+      <c r="E87" t="s">
+        <v>365</v>
+      </c>
+      <c r="F87" t="s">
+        <v>366</v>
+      </c>
+      <c r="G87" t="s">
         <v>378</v>
-      </c>
-      <c r="E87" t="s">
-        <v>366</v>
-      </c>
-      <c r="F87" t="s">
-        <v>367</v>
-      </c>
-      <c r="G87" t="s">
-        <v>379</v>
       </c>
       <c r="H87" t="s">
         <v>4</v>
@@ -4219,13 +4195,13 @@
     </row>
     <row r="88" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A88" t="s">
-        <v>380</v>
+        <v>379</v>
       </c>
       <c r="C88" t="s">
         <v>12</v>
       </c>
       <c r="D88" t="s">
-        <v>381</v>
+        <v>380</v>
       </c>
       <c r="E88" t="s">
         <v>51</v>
@@ -4234,7 +4210,7 @@
         <v>0</v>
       </c>
       <c r="G88" t="s">
-        <v>382</v>
+        <v>381</v>
       </c>
       <c r="H88" t="s">
         <v>4</v>
@@ -4242,22 +4218,22 @@
     </row>
     <row r="89" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A89" t="s">
-        <v>383</v>
+        <v>382</v>
       </c>
       <c r="C89" t="s">
         <v>59</v>
       </c>
       <c r="D89" t="s">
-        <v>384</v>
+        <v>383</v>
       </c>
       <c r="E89" t="s">
+        <v>81</v>
+      </c>
+      <c r="F89" t="s">
+        <v>0</v>
+      </c>
+      <c r="G89" t="s">
         <v>82</v>
-      </c>
-      <c r="F89" t="s">
-        <v>0</v>
-      </c>
-      <c r="G89" t="s">
-        <v>83</v>
       </c>
       <c r="H89" t="s">
         <v>4</v>
@@ -4265,22 +4241,22 @@
     </row>
     <row r="90" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A90" t="s">
-        <v>385</v>
+        <v>384</v>
       </c>
       <c r="C90" t="s">
         <v>59</v>
       </c>
       <c r="D90" t="s">
-        <v>384</v>
+        <v>383</v>
       </c>
       <c r="E90" t="s">
+        <v>81</v>
+      </c>
+      <c r="F90" t="s">
+        <v>0</v>
+      </c>
+      <c r="G90" t="s">
         <v>82</v>
-      </c>
-      <c r="F90" t="s">
-        <v>0</v>
-      </c>
-      <c r="G90" t="s">
-        <v>83</v>
       </c>
       <c r="H90" t="s">
         <v>4</v>
@@ -4288,13 +4264,13 @@
     </row>
     <row r="91" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A91" t="s">
+        <v>385</v>
+      </c>
+      <c r="C91" t="s">
+        <v>155</v>
+      </c>
+      <c r="D91" t="s">
         <v>386</v>
-      </c>
-      <c r="C91" t="s">
-        <v>156</v>
-      </c>
-      <c r="D91" t="s">
-        <v>387</v>
       </c>
       <c r="E91" t="s">
         <v>52</v>
@@ -4311,22 +4287,22 @@
     </row>
     <row r="92" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A92" t="s">
-        <v>388</v>
+        <v>387</v>
       </c>
       <c r="C92" t="s">
         <v>35</v>
       </c>
       <c r="D92" t="s">
+        <v>388</v>
+      </c>
+      <c r="E92" t="s">
         <v>389</v>
       </c>
-      <c r="E92" t="s">
+      <c r="F92" t="s">
+        <v>0</v>
+      </c>
+      <c r="G92" t="s">
         <v>390</v>
-      </c>
-      <c r="F92" t="s">
-        <v>0</v>
-      </c>
-      <c r="G92" t="s">
-        <v>391</v>
       </c>
       <c r="H92" t="s">
         <v>4</v>
@@ -4334,22 +4310,22 @@
     </row>
     <row r="93" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A93" t="s">
-        <v>392</v>
+        <v>391</v>
       </c>
       <c r="C93" t="s">
         <v>6</v>
       </c>
       <c r="D93" t="s">
+        <v>392</v>
+      </c>
+      <c r="E93" t="s">
         <v>393</v>
       </c>
-      <c r="E93" t="s">
+      <c r="F93" t="s">
         <v>394</v>
       </c>
-      <c r="F93" t="s">
+      <c r="G93" t="s">
         <v>395</v>
-      </c>
-      <c r="G93" t="s">
-        <v>396</v>
       </c>
       <c r="H93" t="s">
         <v>4</v>
@@ -4357,13 +4333,13 @@
     </row>
     <row r="94" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A94" t="s">
+        <v>98</v>
+      </c>
+      <c r="C94" t="s">
+        <v>155</v>
+      </c>
+      <c r="D94" t="s">
         <v>99</v>
-      </c>
-      <c r="C94" t="s">
-        <v>156</v>
-      </c>
-      <c r="D94" t="s">
-        <v>100</v>
       </c>
       <c r="E94" t="s">
         <v>52</v>
@@ -4372,7 +4348,7 @@
         <v>0</v>
       </c>
       <c r="G94" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="H94" t="s">
         <v>4</v>
@@ -4380,22 +4356,22 @@
     </row>
     <row r="95" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A95" t="s">
-        <v>397</v>
+        <v>396</v>
       </c>
       <c r="C95" t="s">
         <v>31</v>
       </c>
       <c r="D95" t="s">
+        <v>397</v>
+      </c>
+      <c r="E95" t="s">
         <v>398</v>
       </c>
-      <c r="E95" t="s">
+      <c r="F95" t="s">
+        <v>0</v>
+      </c>
+      <c r="G95" t="s">
         <v>399</v>
-      </c>
-      <c r="F95" t="s">
-        <v>0</v>
-      </c>
-      <c r="G95" t="s">
-        <v>400</v>
       </c>
       <c r="H95" t="s">
         <v>4</v>
@@ -4403,22 +4379,22 @@
     </row>
     <row r="96" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A96" t="s">
-        <v>401</v>
+        <v>400</v>
       </c>
       <c r="C96" t="s">
         <v>14</v>
       </c>
       <c r="D96" t="s">
+        <v>401</v>
+      </c>
+      <c r="E96" t="s">
         <v>402</v>
       </c>
-      <c r="E96" t="s">
+      <c r="F96" t="s">
+        <v>0</v>
+      </c>
+      <c r="G96" t="s">
         <v>403</v>
-      </c>
-      <c r="F96" t="s">
-        <v>0</v>
-      </c>
-      <c r="G96" t="s">
-        <v>404</v>
       </c>
       <c r="H96" t="s">
         <v>4</v>
@@ -4426,22 +4402,22 @@
     </row>
     <row r="97" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A97" t="s">
-        <v>405</v>
+        <v>404</v>
       </c>
       <c r="C97" t="s">
         <v>22</v>
       </c>
       <c r="D97" t="s">
+        <v>405</v>
+      </c>
+      <c r="E97" t="s">
         <v>406</v>
       </c>
-      <c r="E97" t="s">
+      <c r="F97" t="s">
+        <v>0</v>
+      </c>
+      <c r="G97" t="s">
         <v>407</v>
-      </c>
-      <c r="F97" t="s">
-        <v>0</v>
-      </c>
-      <c r="G97" t="s">
-        <v>408</v>
       </c>
       <c r="H97" t="s">
         <v>4</v>
@@ -4449,22 +4425,22 @@
     </row>
     <row r="98" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A98" t="s">
-        <v>409</v>
+        <v>408</v>
       </c>
       <c r="C98" t="s">
         <v>29</v>
       </c>
       <c r="D98" t="s">
+        <v>409</v>
+      </c>
+      <c r="E98" t="s">
         <v>410</v>
       </c>
-      <c r="E98" t="s">
+      <c r="F98" t="s">
+        <v>0</v>
+      </c>
+      <c r="G98" t="s">
         <v>411</v>
-      </c>
-      <c r="F98" t="s">
-        <v>0</v>
-      </c>
-      <c r="G98" t="s">
-        <v>412</v>
       </c>
       <c r="H98" t="s">
         <v>4</v>
@@ -4472,13 +4448,13 @@
     </row>
     <row r="99" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A99" t="s">
-        <v>413</v>
+        <v>412</v>
       </c>
       <c r="C99" t="s">
         <v>32</v>
       </c>
       <c r="D99" t="s">
-        <v>414</v>
+        <v>413</v>
       </c>
       <c r="E99" t="s">
         <v>19</v>
@@ -4487,7 +4463,7 @@
         <v>0</v>
       </c>
       <c r="G99" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="H99" t="s">
         <v>4</v>
@@ -4495,22 +4471,22 @@
     </row>
     <row r="100" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A100" t="s">
-        <v>415</v>
+        <v>414</v>
       </c>
       <c r="C100" t="s">
         <v>31</v>
       </c>
       <c r="D100" t="s">
+        <v>415</v>
+      </c>
+      <c r="E100" t="s">
         <v>416</v>
       </c>
-      <c r="E100" t="s">
+      <c r="F100" t="s">
+        <v>0</v>
+      </c>
+      <c r="G100" t="s">
         <v>417</v>
-      </c>
-      <c r="F100" t="s">
-        <v>0</v>
-      </c>
-      <c r="G100" t="s">
-        <v>418</v>
       </c>
       <c r="H100" t="s">
         <v>4</v>
@@ -4518,22 +4494,22 @@
     </row>
     <row r="101" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A101" t="s">
-        <v>419</v>
+        <v>418</v>
       </c>
       <c r="C101" t="s">
         <v>43</v>
       </c>
       <c r="D101" t="s">
+        <v>419</v>
+      </c>
+      <c r="E101" t="s">
+        <v>246</v>
+      </c>
+      <c r="F101" t="s">
+        <v>0</v>
+      </c>
+      <c r="G101" t="s">
         <v>420</v>
-      </c>
-      <c r="E101" t="s">
-        <v>247</v>
-      </c>
-      <c r="F101" t="s">
-        <v>0</v>
-      </c>
-      <c r="G101" t="s">
-        <v>421</v>
       </c>
       <c r="H101" t="s">
         <v>4</v>
@@ -4541,22 +4517,22 @@
     </row>
     <row r="102" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A102" t="s">
-        <v>422</v>
+        <v>421</v>
       </c>
       <c r="C102" t="s">
         <v>43</v>
       </c>
       <c r="D102" t="s">
+        <v>419</v>
+      </c>
+      <c r="E102" t="s">
+        <v>246</v>
+      </c>
+      <c r="F102" t="s">
+        <v>0</v>
+      </c>
+      <c r="G102" t="s">
         <v>420</v>
-      </c>
-      <c r="E102" t="s">
-        <v>247</v>
-      </c>
-      <c r="F102" t="s">
-        <v>0</v>
-      </c>
-      <c r="G102" t="s">
-        <v>421</v>
       </c>
       <c r="H102" t="s">
         <v>4</v>
@@ -4564,22 +4540,22 @@
     </row>
     <row r="103" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A103" t="s">
-        <v>423</v>
+        <v>422</v>
       </c>
       <c r="C103" t="s">
         <v>14</v>
       </c>
       <c r="D103" t="s">
+        <v>423</v>
+      </c>
+      <c r="E103" t="s">
         <v>424</v>
       </c>
-      <c r="E103" t="s">
+      <c r="F103" t="s">
+        <v>0</v>
+      </c>
+      <c r="G103" t="s">
         <v>425</v>
-      </c>
-      <c r="F103" t="s">
-        <v>0</v>
-      </c>
-      <c r="G103" t="s">
-        <v>426</v>
       </c>
       <c r="H103" t="s">
         <v>4</v>
@@ -4587,22 +4563,22 @@
     </row>
     <row r="104" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A104" t="s">
-        <v>427</v>
+        <v>426</v>
       </c>
       <c r="C104" t="s">
         <v>35</v>
       </c>
       <c r="D104" t="s">
+        <v>427</v>
+      </c>
+      <c r="E104" t="s">
+        <v>85</v>
+      </c>
+      <c r="F104" t="s">
+        <v>86</v>
+      </c>
+      <c r="G104" t="s">
         <v>428</v>
-      </c>
-      <c r="E104" t="s">
-        <v>86</v>
-      </c>
-      <c r="F104" t="s">
-        <v>87</v>
-      </c>
-      <c r="G104" t="s">
-        <v>429</v>
       </c>
       <c r="H104" t="s">
         <v>4</v>
@@ -4610,22 +4586,22 @@
     </row>
     <row r="105" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A105" t="s">
-        <v>430</v>
+        <v>429</v>
       </c>
       <c r="C105" t="s">
         <v>2</v>
       </c>
       <c r="D105" t="s">
+        <v>430</v>
+      </c>
+      <c r="E105" t="s">
         <v>431</v>
       </c>
-      <c r="E105" t="s">
+      <c r="F105" t="s">
+        <v>0</v>
+      </c>
+      <c r="G105" t="s">
         <v>432</v>
-      </c>
-      <c r="F105" t="s">
-        <v>0</v>
-      </c>
-      <c r="G105" t="s">
-        <v>433</v>
       </c>
       <c r="H105" t="s">
         <v>4</v>
@@ -4633,22 +4609,22 @@
     </row>
     <row r="106" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A106" t="s">
-        <v>434</v>
+        <v>433</v>
       </c>
       <c r="C106" t="s">
         <v>59</v>
       </c>
       <c r="D106" t="s">
+        <v>434</v>
+      </c>
+      <c r="E106" t="s">
         <v>435</v>
       </c>
-      <c r="E106" t="s">
+      <c r="F106" t="s">
+        <v>0</v>
+      </c>
+      <c r="G106" t="s">
         <v>436</v>
-      </c>
-      <c r="F106" t="s">
-        <v>0</v>
-      </c>
-      <c r="G106" t="s">
-        <v>437</v>
       </c>
       <c r="H106" t="s">
         <v>4</v>
@@ -4656,22 +4632,22 @@
     </row>
     <row r="107" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A107" t="s">
-        <v>438</v>
+        <v>437</v>
       </c>
       <c r="C107" t="s">
         <v>35</v>
       </c>
       <c r="D107" t="s">
+        <v>438</v>
+      </c>
+      <c r="E107" t="s">
         <v>439</v>
       </c>
-      <c r="E107" t="s">
+      <c r="F107" t="s">
         <v>440</v>
       </c>
-      <c r="F107" t="s">
+      <c r="G107" t="s">
         <v>441</v>
-      </c>
-      <c r="G107" t="s">
-        <v>442</v>
       </c>
       <c r="H107" t="s">
         <v>4</v>
@@ -4679,13 +4655,13 @@
     </row>
     <row r="108" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A108" t="s">
-        <v>443</v>
+        <v>442</v>
       </c>
       <c r="C108" t="s">
         <v>32</v>
       </c>
       <c r="D108" t="s">
-        <v>444</v>
+        <v>443</v>
       </c>
       <c r="E108" t="s">
         <v>18</v>
@@ -4694,7 +4670,7 @@
         <v>0</v>
       </c>
       <c r="G108" t="s">
-        <v>445</v>
+        <v>444</v>
       </c>
       <c r="H108" t="s">
         <v>4</v>
@@ -4702,13 +4678,13 @@
     </row>
     <row r="109" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A109" t="s">
-        <v>446</v>
+        <v>445</v>
       </c>
       <c r="C109" t="s">
         <v>12</v>
       </c>
       <c r="D109" t="s">
-        <v>447</v>
+        <v>446</v>
       </c>
       <c r="E109" t="s">
         <v>26</v>
@@ -4717,7 +4693,7 @@
         <v>0</v>
       </c>
       <c r="G109" t="s">
-        <v>448</v>
+        <v>447</v>
       </c>
       <c r="H109" t="s">
         <v>4</v>
@@ -4725,22 +4701,22 @@
     </row>
     <row r="110" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A110" t="s">
-        <v>449</v>
+        <v>448</v>
       </c>
       <c r="C110" t="s">
         <v>43</v>
       </c>
       <c r="D110" t="s">
+        <v>449</v>
+      </c>
+      <c r="E110" t="s">
+        <v>72</v>
+      </c>
+      <c r="F110" t="s">
+        <v>0</v>
+      </c>
+      <c r="G110" t="s">
         <v>450</v>
-      </c>
-      <c r="E110" t="s">
-        <v>73</v>
-      </c>
-      <c r="F110" t="s">
-        <v>0</v>
-      </c>
-      <c r="G110" t="s">
-        <v>451</v>
       </c>
       <c r="H110" t="s">
         <v>4</v>
@@ -4748,22 +4724,22 @@
     </row>
     <row r="111" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A111" t="s">
-        <v>452</v>
+        <v>451</v>
       </c>
       <c r="C111" t="s">
         <v>59</v>
       </c>
       <c r="D111" t="s">
+        <v>452</v>
+      </c>
+      <c r="E111" t="s">
         <v>453</v>
       </c>
-      <c r="E111" t="s">
+      <c r="F111" t="s">
+        <v>0</v>
+      </c>
+      <c r="G111" t="s">
         <v>454</v>
-      </c>
-      <c r="F111" t="s">
-        <v>0</v>
-      </c>
-      <c r="G111" t="s">
-        <v>455</v>
       </c>
       <c r="H111" t="s">
         <v>4</v>
@@ -4771,22 +4747,22 @@
     </row>
     <row r="112" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A112" t="s">
-        <v>456</v>
+        <v>455</v>
       </c>
       <c r="C112" t="s">
         <v>35</v>
       </c>
       <c r="D112" t="s">
+        <v>456</v>
+      </c>
+      <c r="E112" t="s">
         <v>457</v>
       </c>
-      <c r="E112" t="s">
+      <c r="F112" t="s">
+        <v>0</v>
+      </c>
+      <c r="G112" t="s">
         <v>458</v>
-      </c>
-      <c r="F112" t="s">
-        <v>0</v>
-      </c>
-      <c r="G112" t="s">
-        <v>459</v>
       </c>
       <c r="H112" t="s">
         <v>4</v>
@@ -4794,22 +4770,22 @@
     </row>
     <row r="113" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A113" t="s">
-        <v>460</v>
+        <v>459</v>
       </c>
       <c r="C113" t="s">
         <v>43</v>
       </c>
       <c r="D113" t="s">
+        <v>460</v>
+      </c>
+      <c r="E113" t="s">
         <v>461</v>
       </c>
-      <c r="E113" t="s">
+      <c r="F113" t="s">
+        <v>0</v>
+      </c>
+      <c r="G113" t="s">
         <v>462</v>
-      </c>
-      <c r="F113" t="s">
-        <v>0</v>
-      </c>
-      <c r="G113" t="s">
-        <v>463</v>
       </c>
       <c r="H113" t="s">
         <v>4</v>
@@ -4817,22 +4793,22 @@
     </row>
     <row r="114" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A114" t="s">
-        <v>464</v>
+        <v>463</v>
       </c>
       <c r="C114" t="s">
         <v>31</v>
       </c>
       <c r="D114" t="s">
+        <v>464</v>
+      </c>
+      <c r="E114" t="s">
+        <v>305</v>
+      </c>
+      <c r="F114" t="s">
+        <v>0</v>
+      </c>
+      <c r="G114" t="s">
         <v>465</v>
-      </c>
-      <c r="E114" t="s">
-        <v>306</v>
-      </c>
-      <c r="F114" t="s">
-        <v>0</v>
-      </c>
-      <c r="G114" t="s">
-        <v>466</v>
       </c>
       <c r="H114" t="s">
         <v>4</v>
@@ -4840,22 +4816,22 @@
     </row>
     <row r="115" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A115" t="s">
-        <v>467</v>
+        <v>466</v>
       </c>
       <c r="C115" t="s">
         <v>15</v>
       </c>
       <c r="D115" t="s">
+        <v>467</v>
+      </c>
+      <c r="E115" t="s">
         <v>468</v>
       </c>
-      <c r="E115" t="s">
+      <c r="F115" t="s">
+        <v>0</v>
+      </c>
+      <c r="G115" t="s">
         <v>469</v>
-      </c>
-      <c r="F115" t="s">
-        <v>0</v>
-      </c>
-      <c r="G115" t="s">
-        <v>470</v>
       </c>
       <c r="H115" t="s">
         <v>4</v>
@@ -4863,22 +4839,22 @@
     </row>
     <row r="116" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A116" t="s">
-        <v>471</v>
+        <v>470</v>
       </c>
       <c r="C116" t="s">
         <v>35</v>
       </c>
       <c r="D116" t="s">
+        <v>471</v>
+      </c>
+      <c r="E116" t="s">
         <v>472</v>
       </c>
-      <c r="E116" t="s">
+      <c r="F116" t="s">
+        <v>0</v>
+      </c>
+      <c r="G116" t="s">
         <v>473</v>
-      </c>
-      <c r="F116" t="s">
-        <v>0</v>
-      </c>
-      <c r="G116" t="s">
-        <v>474</v>
       </c>
       <c r="H116" t="s">
         <v>4</v>
@@ -4886,13 +4862,13 @@
     </row>
     <row r="117" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A117" t="s">
-        <v>475</v>
+        <v>474</v>
       </c>
       <c r="C117" t="s">
         <v>12</v>
       </c>
       <c r="D117" t="s">
-        <v>476</v>
+        <v>475</v>
       </c>
       <c r="E117" t="s">
         <v>51</v>
@@ -4901,7 +4877,7 @@
         <v>0</v>
       </c>
       <c r="G117" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="H117" t="s">
         <v>4</v>
@@ -4909,22 +4885,22 @@
     </row>
     <row r="118" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A118" t="s">
-        <v>477</v>
+        <v>476</v>
       </c>
       <c r="C118" t="s">
         <v>2</v>
       </c>
       <c r="D118" t="s">
+        <v>477</v>
+      </c>
+      <c r="E118" t="s">
         <v>478</v>
       </c>
-      <c r="E118" t="s">
+      <c r="F118" t="s">
+        <v>0</v>
+      </c>
+      <c r="G118" t="s">
         <v>479</v>
-      </c>
-      <c r="F118" t="s">
-        <v>0</v>
-      </c>
-      <c r="G118" t="s">
-        <v>480</v>
       </c>
       <c r="H118" t="s">
         <v>4</v>
@@ -4932,22 +4908,22 @@
     </row>
     <row r="119" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A119" t="s">
-        <v>481</v>
+        <v>480</v>
       </c>
       <c r="C119" t="s">
         <v>6</v>
       </c>
       <c r="D119" t="s">
+        <v>481</v>
+      </c>
+      <c r="E119" t="s">
+        <v>228</v>
+      </c>
+      <c r="F119" t="s">
+        <v>229</v>
+      </c>
+      <c r="G119" t="s">
         <v>482</v>
-      </c>
-      <c r="E119" t="s">
-        <v>229</v>
-      </c>
-      <c r="F119" t="s">
-        <v>230</v>
-      </c>
-      <c r="G119" t="s">
-        <v>483</v>
       </c>
       <c r="H119" t="s">
         <v>4</v>
@@ -4955,22 +4931,22 @@
     </row>
     <row r="120" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A120" t="s">
-        <v>484</v>
+        <v>483</v>
       </c>
       <c r="C120" t="s">
         <v>6</v>
       </c>
       <c r="D120" t="s">
+        <v>481</v>
+      </c>
+      <c r="E120" t="s">
+        <v>228</v>
+      </c>
+      <c r="F120" t="s">
+        <v>229</v>
+      </c>
+      <c r="G120" t="s">
         <v>482</v>
-      </c>
-      <c r="E120" t="s">
-        <v>229</v>
-      </c>
-      <c r="F120" t="s">
-        <v>230</v>
-      </c>
-      <c r="G120" t="s">
-        <v>483</v>
       </c>
       <c r="H120" t="s">
         <v>4</v>
@@ -4978,22 +4954,22 @@
     </row>
     <row r="121" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A121" t="s">
-        <v>485</v>
+        <v>484</v>
       </c>
       <c r="C121" t="s">
         <v>6</v>
       </c>
       <c r="D121" t="s">
+        <v>481</v>
+      </c>
+      <c r="E121" t="s">
+        <v>228</v>
+      </c>
+      <c r="F121" t="s">
+        <v>229</v>
+      </c>
+      <c r="G121" t="s">
         <v>482</v>
-      </c>
-      <c r="E121" t="s">
-        <v>229</v>
-      </c>
-      <c r="F121" t="s">
-        <v>230</v>
-      </c>
-      <c r="G121" t="s">
-        <v>483</v>
       </c>
       <c r="H121" t="s">
         <v>4</v>
@@ -5001,13 +4977,13 @@
     </row>
     <row r="122" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A122" t="s">
-        <v>486</v>
+        <v>485</v>
       </c>
       <c r="C122" t="s">
         <v>43</v>
       </c>
       <c r="D122" t="s">
-        <v>487</v>
+        <v>486</v>
       </c>
       <c r="E122" t="s">
         <v>41</v>
@@ -5016,7 +4992,7 @@
         <v>0</v>
       </c>
       <c r="G122" t="s">
-        <v>488</v>
+        <v>487</v>
       </c>
       <c r="H122" t="s">
         <v>4</v>
@@ -5024,22 +5000,22 @@
     </row>
     <row r="123" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A123" t="s">
-        <v>489</v>
+        <v>488</v>
       </c>
       <c r="C123" t="s">
         <v>29</v>
       </c>
       <c r="D123" t="s">
+        <v>489</v>
+      </c>
+      <c r="E123" t="s">
         <v>490</v>
       </c>
-      <c r="E123" t="s">
+      <c r="F123" t="s">
+        <v>0</v>
+      </c>
+      <c r="G123" t="s">
         <v>491</v>
-      </c>
-      <c r="F123" t="s">
-        <v>0</v>
-      </c>
-      <c r="G123" t="s">
-        <v>492</v>
       </c>
       <c r="H123" t="s">
         <v>4</v>
@@ -5047,13 +5023,13 @@
     </row>
     <row r="124" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A124" t="s">
-        <v>493</v>
+        <v>492</v>
       </c>
       <c r="C124" t="s">
         <v>9</v>
       </c>
       <c r="D124" t="s">
-        <v>494</v>
+        <v>493</v>
       </c>
       <c r="E124" t="s">
         <v>39</v>
@@ -5062,7 +5038,7 @@
         <v>0</v>
       </c>
       <c r="G124" t="s">
-        <v>495</v>
+        <v>494</v>
       </c>
       <c r="H124" t="s">
         <v>4</v>
@@ -5070,22 +5046,22 @@
     </row>
     <row r="125" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A125" t="s">
-        <v>496</v>
+        <v>495</v>
       </c>
       <c r="C125" t="s">
         <v>6</v>
       </c>
       <c r="D125" t="s">
+        <v>496</v>
+      </c>
+      <c r="E125" t="s">
         <v>497</v>
       </c>
-      <c r="E125" t="s">
+      <c r="F125" t="s">
         <v>498</v>
       </c>
-      <c r="F125" t="s">
+      <c r="G125" t="s">
         <v>499</v>
-      </c>
-      <c r="G125" t="s">
-        <v>500</v>
       </c>
       <c r="H125" t="s">
         <v>5</v>
@@ -5093,33 +5069,36 @@
     </row>
     <row r="126" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A126" t="s">
-        <v>501</v>
+        <v>500</v>
       </c>
       <c r="C126" t="s">
         <v>2</v>
       </c>
       <c r="D126" t="s">
+        <v>501</v>
+      </c>
+      <c r="E126" t="s">
         <v>502</v>
       </c>
-      <c r="E126" t="s">
+      <c r="F126" t="s">
         <v>503</v>
       </c>
-      <c r="F126" t="s">
+      <c r="G126" t="s">
         <v>504</v>
-      </c>
-      <c r="G126" t="s">
-        <v>505</v>
       </c>
       <c r="H126" t="s">
         <v>5</v>
       </c>
     </row>
     <row r="127" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A127" t="s">
+        <v>505</v>
+      </c>
       <c r="C127" t="s">
         <v>32</v>
       </c>
       <c r="D127" t="s">
-        <v>506</v>
+        <v>505</v>
       </c>
       <c r="E127" t="s">
         <v>18</v>
@@ -5128,7 +5107,7 @@
         <v>0</v>
       </c>
       <c r="G127" t="s">
-        <v>507</v>
+        <v>506</v>
       </c>
       <c r="H127" t="s">
         <v>5</v>
@@ -5136,22 +5115,22 @@
     </row>
     <row r="128" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A128" t="s">
+        <v>507</v>
+      </c>
+      <c r="C128" t="s">
+        <v>155</v>
+      </c>
+      <c r="D128" t="s">
         <v>508</v>
       </c>
-      <c r="C128" t="s">
-        <v>156</v>
-      </c>
-      <c r="D128" t="s">
+      <c r="E128" t="s">
         <v>509</v>
       </c>
-      <c r="E128" t="s">
+      <c r="F128" t="s">
         <v>510</v>
       </c>
-      <c r="F128" t="s">
+      <c r="G128" t="s">
         <v>511</v>
-      </c>
-      <c r="G128" t="s">
-        <v>512</v>
       </c>
       <c r="H128" t="s">
         <v>5</v>
@@ -5159,22 +5138,22 @@
     </row>
     <row r="129" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A129" t="s">
-        <v>513</v>
+        <v>512</v>
       </c>
       <c r="C129" t="s">
         <v>31</v>
       </c>
       <c r="D129" t="s">
+        <v>513</v>
+      </c>
+      <c r="E129" t="s">
+        <v>106</v>
+      </c>
+      <c r="F129" t="s">
+        <v>0</v>
+      </c>
+      <c r="G129" t="s">
         <v>514</v>
-      </c>
-      <c r="E129" t="s">
-        <v>107</v>
-      </c>
-      <c r="F129" t="s">
-        <v>0</v>
-      </c>
-      <c r="G129" t="s">
-        <v>515</v>
       </c>
       <c r="H129" t="s">
         <v>5</v>
@@ -5182,13 +5161,13 @@
     </row>
     <row r="130" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A130" t="s">
-        <v>516</v>
+        <v>515</v>
       </c>
       <c r="C130" t="s">
         <v>12</v>
       </c>
       <c r="D130" t="s">
-        <v>517</v>
+        <v>516</v>
       </c>
       <c r="E130" t="s">
         <v>26</v>
@@ -5197,7 +5176,7 @@
         <v>0</v>
       </c>
       <c r="G130" t="s">
-        <v>518</v>
+        <v>517</v>
       </c>
       <c r="H130" t="s">
         <v>5</v>
@@ -5205,22 +5184,22 @@
     </row>
     <row r="131" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A131" t="s">
-        <v>519</v>
+        <v>518</v>
       </c>
       <c r="C131" t="s">
         <v>29</v>
       </c>
       <c r="D131" t="s">
-        <v>520</v>
+        <v>519</v>
       </c>
       <c r="E131" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="F131" t="s">
         <v>0</v>
       </c>
       <c r="G131" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
       <c r="H131" t="s">
         <v>5</v>
@@ -5228,13 +5207,13 @@
     </row>
     <row r="132" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A132" t="s">
-        <v>521</v>
+        <v>520</v>
       </c>
       <c r="C132" t="s">
         <v>31</v>
       </c>
       <c r="D132" t="s">
-        <v>522</v>
+        <v>521</v>
       </c>
       <c r="E132" t="s">
         <v>53</v>
@@ -5243,7 +5222,7 @@
         <v>0</v>
       </c>
       <c r="G132" t="s">
-        <v>523</v>
+        <v>522</v>
       </c>
       <c r="H132" t="s">
         <v>5</v>
@@ -5251,13 +5230,13 @@
     </row>
     <row r="133" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A133" t="s">
-        <v>524</v>
+        <v>523</v>
       </c>
       <c r="C133" t="s">
         <v>35</v>
       </c>
       <c r="D133" t="s">
-        <v>525</v>
+        <v>524</v>
       </c>
       <c r="E133" t="s">
         <v>67</v>
@@ -5266,7 +5245,7 @@
         <v>0</v>
       </c>
       <c r="G133" t="s">
-        <v>526</v>
+        <v>525</v>
       </c>
       <c r="H133" t="s">
         <v>5</v>
@@ -5274,13 +5253,13 @@
     </row>
     <row r="134" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A134" t="s">
-        <v>527</v>
+        <v>526</v>
       </c>
       <c r="C134" t="s">
         <v>35</v>
       </c>
       <c r="D134" t="s">
-        <v>525</v>
+        <v>524</v>
       </c>
       <c r="E134" t="s">
         <v>67</v>
@@ -5289,7 +5268,7 @@
         <v>0</v>
       </c>
       <c r="G134" t="s">
-        <v>526</v>
+        <v>525</v>
       </c>
       <c r="H134" t="s">
         <v>5</v>
@@ -5297,13 +5276,13 @@
     </row>
     <row r="135" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A135" t="s">
-        <v>528</v>
+        <v>527</v>
       </c>
       <c r="C135" t="s">
         <v>9</v>
       </c>
       <c r="D135" t="s">
-        <v>529</v>
+        <v>528</v>
       </c>
       <c r="E135" t="s">
         <v>39</v>
@@ -5312,7 +5291,7 @@
         <v>0</v>
       </c>
       <c r="G135" t="s">
-        <v>530</v>
+        <v>529</v>
       </c>
       <c r="H135" t="s">
         <v>5</v>
@@ -5320,13 +5299,13 @@
     </row>
     <row r="136" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A136" t="s">
-        <v>531</v>
+        <v>530</v>
       </c>
       <c r="C136" t="s">
         <v>15</v>
       </c>
       <c r="D136" t="s">
-        <v>532</v>
+        <v>531</v>
       </c>
       <c r="E136" t="s">
         <v>55</v>
@@ -5343,13 +5322,13 @@
     </row>
     <row r="137" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A137" t="s">
-        <v>533</v>
+        <v>532</v>
       </c>
       <c r="C137" t="s">
         <v>14</v>
       </c>
       <c r="D137" t="s">
-        <v>534</v>
+        <v>533</v>
       </c>
       <c r="E137" t="s">
         <v>33</v>
@@ -5358,7 +5337,7 @@
         <v>0</v>
       </c>
       <c r="G137" t="s">
-        <v>535</v>
+        <v>534</v>
       </c>
       <c r="H137" t="s">
         <v>5</v>
@@ -5366,22 +5345,22 @@
     </row>
     <row r="138" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A138" t="s">
-        <v>536</v>
+        <v>535</v>
       </c>
       <c r="C138" t="s">
         <v>15</v>
       </c>
       <c r="D138" t="s">
+        <v>536</v>
+      </c>
+      <c r="E138" t="s">
         <v>537</v>
       </c>
-      <c r="E138" t="s">
+      <c r="F138" t="s">
         <v>538</v>
       </c>
-      <c r="F138" t="s">
+      <c r="G138" t="s">
         <v>539</v>
-      </c>
-      <c r="G138" t="s">
-        <v>540</v>
       </c>
       <c r="H138" t="s">
         <v>5</v>
@@ -5389,22 +5368,22 @@
     </row>
     <row r="139" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A139" t="s">
-        <v>541</v>
+        <v>540</v>
       </c>
       <c r="C139" t="s">
         <v>15</v>
       </c>
       <c r="D139" t="s">
+        <v>536</v>
+      </c>
+      <c r="E139" t="s">
         <v>537</v>
       </c>
-      <c r="E139" t="s">
+      <c r="F139" t="s">
         <v>538</v>
       </c>
-      <c r="F139" t="s">
+      <c r="G139" t="s">
         <v>539</v>
-      </c>
-      <c r="G139" t="s">
-        <v>540</v>
       </c>
       <c r="H139" t="s">
         <v>5</v>
@@ -5412,13 +5391,13 @@
     </row>
     <row r="140" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A140" t="s">
-        <v>542</v>
+        <v>541</v>
       </c>
       <c r="C140" t="s">
         <v>32</v>
       </c>
       <c r="D140" t="s">
-        <v>543</v>
+        <v>542</v>
       </c>
       <c r="E140" t="s">
         <v>19</v>
@@ -5427,7 +5406,7 @@
         <v>0</v>
       </c>
       <c r="G140" t="s">
-        <v>544</v>
+        <v>543</v>
       </c>
       <c r="H140" t="s">
         <v>5</v>
@@ -5435,22 +5414,22 @@
     </row>
     <row r="141" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A141" t="s">
-        <v>545</v>
+        <v>544</v>
       </c>
       <c r="C141" t="s">
         <v>43</v>
       </c>
       <c r="D141" t="s">
+        <v>545</v>
+      </c>
+      <c r="E141" t="s">
         <v>546</v>
       </c>
-      <c r="E141" t="s">
-        <v>547</v>
-      </c>
       <c r="F141" t="s">
         <v>0</v>
       </c>
       <c r="G141" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="H141" t="s">
         <v>5</v>
@@ -5458,13 +5437,13 @@
     </row>
     <row r="142" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A142" t="s">
-        <v>548</v>
+        <v>547</v>
       </c>
       <c r="C142" t="s">
         <v>32</v>
       </c>
       <c r="D142" t="s">
-        <v>549</v>
+        <v>548</v>
       </c>
       <c r="E142" t="s">
         <v>64</v>
@@ -5473,7 +5452,7 @@
         <v>0</v>
       </c>
       <c r="G142" t="s">
-        <v>550</v>
+        <v>549</v>
       </c>
       <c r="H142" t="s">
         <v>5</v>
@@ -5481,13 +5460,13 @@
     </row>
     <row r="143" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A143" t="s">
-        <v>551</v>
+        <v>550</v>
       </c>
       <c r="C143" t="s">
         <v>12</v>
       </c>
       <c r="D143" t="s">
-        <v>552</v>
+        <v>551</v>
       </c>
       <c r="E143" t="s">
         <v>68</v>
@@ -5496,7 +5475,7 @@
         <v>69</v>
       </c>
       <c r="G143" t="s">
-        <v>553</v>
+        <v>552</v>
       </c>
       <c r="H143" t="s">
         <v>5</v>
@@ -5504,13 +5483,13 @@
     </row>
     <row r="144" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A144" t="s">
-        <v>554</v>
+        <v>553</v>
       </c>
       <c r="C144" t="s">
         <v>12</v>
       </c>
       <c r="D144" t="s">
-        <v>552</v>
+        <v>551</v>
       </c>
       <c r="E144" t="s">
         <v>68</v>
@@ -5519,7 +5498,7 @@
         <v>69</v>
       </c>
       <c r="G144" t="s">
-        <v>553</v>
+        <v>552</v>
       </c>
       <c r="H144" t="s">
         <v>5</v>
@@ -5527,22 +5506,22 @@
     </row>
     <row r="145" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A145" t="s">
-        <v>555</v>
+        <v>554</v>
       </c>
       <c r="C145" t="s">
         <v>2</v>
       </c>
       <c r="D145" t="s">
+        <v>555</v>
+      </c>
+      <c r="E145" t="s">
         <v>556</v>
       </c>
-      <c r="E145" t="s">
+      <c r="F145" t="s">
         <v>557</v>
       </c>
-      <c r="F145" t="s">
+      <c r="G145" t="s">
         <v>558</v>
-      </c>
-      <c r="G145" t="s">
-        <v>559</v>
       </c>
       <c r="H145" t="s">
         <v>5</v>
@@ -5550,13 +5529,13 @@
     </row>
     <row r="146" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A146" t="s">
-        <v>560</v>
+        <v>559</v>
       </c>
       <c r="C146" t="s">
         <v>9</v>
       </c>
       <c r="D146" t="s">
-        <v>561</v>
+        <v>560</v>
       </c>
       <c r="E146" t="s">
         <v>44</v>
@@ -5565,7 +5544,7 @@
         <v>45</v>
       </c>
       <c r="G146" t="s">
-        <v>562</v>
+        <v>561</v>
       </c>
       <c r="H146" t="s">
         <v>5</v>
@@ -5573,22 +5552,22 @@
     </row>
     <row r="147" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A147" t="s">
+        <v>562</v>
+      </c>
+      <c r="C147" t="s">
+        <v>10</v>
+      </c>
+      <c r="D147" t="s">
         <v>563</v>
       </c>
-      <c r="C147" t="s">
-        <v>12</v>
-      </c>
-      <c r="D147" t="s">
+      <c r="E147" t="s">
         <v>564</v>
       </c>
-      <c r="E147" t="s">
+      <c r="F147" t="s">
         <v>565</v>
       </c>
-      <c r="F147" t="s">
-        <v>0</v>
-      </c>
       <c r="G147" t="s">
-        <v>566</v>
+        <v>71</v>
       </c>
       <c r="H147" t="s">
         <v>5</v>
@@ -5596,22 +5575,22 @@
     </row>
     <row r="148" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A148" t="s">
-        <v>567</v>
+        <v>107</v>
       </c>
       <c r="C148" t="s">
-        <v>156</v>
+        <v>12</v>
       </c>
       <c r="D148" t="s">
-        <v>568</v>
+        <v>108</v>
       </c>
       <c r="E148" t="s">
-        <v>72</v>
+        <v>109</v>
       </c>
       <c r="F148" t="s">
         <v>0</v>
       </c>
       <c r="G148" t="s">
-        <v>569</v>
+        <v>110</v>
       </c>
       <c r="H148" t="s">
         <v>5</v>
@@ -5619,22 +5598,22 @@
     </row>
     <row r="149" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A149" t="s">
-        <v>570</v>
+        <v>111</v>
       </c>
       <c r="C149" t="s">
-        <v>35</v>
+        <v>12</v>
       </c>
       <c r="D149" t="s">
-        <v>571</v>
+        <v>108</v>
       </c>
       <c r="E149" t="s">
-        <v>214</v>
+        <v>109</v>
       </c>
       <c r="F149" t="s">
-        <v>215</v>
+        <v>0</v>
       </c>
       <c r="G149" t="s">
-        <v>572</v>
+        <v>110</v>
       </c>
       <c r="H149" t="s">
         <v>5</v>
@@ -5642,22 +5621,22 @@
     </row>
     <row r="150" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A150" t="s">
-        <v>573</v>
+        <v>112</v>
       </c>
       <c r="C150" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="D150" t="s">
-        <v>574</v>
+        <v>108</v>
       </c>
       <c r="E150" t="s">
-        <v>575</v>
+        <v>109</v>
       </c>
       <c r="F150" t="s">
-        <v>576</v>
+        <v>0</v>
       </c>
       <c r="G150" t="s">
-        <v>71</v>
+        <v>110</v>
       </c>
       <c r="H150" t="s">
         <v>5</v>
@@ -5665,22 +5644,22 @@
     </row>
     <row r="151" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A151" t="s">
-        <v>108</v>
+        <v>113</v>
       </c>
       <c r="C151" t="s">
         <v>12</v>
       </c>
       <c r="D151" t="s">
+        <v>108</v>
+      </c>
+      <c r="E151" t="s">
         <v>109</v>
       </c>
-      <c r="E151" t="s">
+      <c r="F151" t="s">
+        <v>0</v>
+      </c>
+      <c r="G151" t="s">
         <v>110</v>
-      </c>
-      <c r="F151" t="s">
-        <v>0</v>
-      </c>
-      <c r="G151" t="s">
-        <v>111</v>
       </c>
       <c r="H151" t="s">
         <v>5</v>
@@ -5688,22 +5667,22 @@
     </row>
     <row r="152" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A152" t="s">
-        <v>112</v>
+        <v>566</v>
       </c>
       <c r="C152" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="D152" t="s">
-        <v>109</v>
+        <v>567</v>
       </c>
       <c r="E152" t="s">
-        <v>110</v>
+        <v>233</v>
       </c>
       <c r="F152" t="s">
-        <v>0</v>
+        <v>234</v>
       </c>
       <c r="G152" t="s">
-        <v>111</v>
+        <v>568</v>
       </c>
       <c r="H152" t="s">
         <v>5</v>
@@ -5711,22 +5690,22 @@
     </row>
     <row r="153" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A153" t="s">
-        <v>113</v>
+        <v>569</v>
       </c>
       <c r="C153" t="s">
-        <v>12</v>
+        <v>2</v>
       </c>
       <c r="D153" t="s">
-        <v>109</v>
+        <v>570</v>
       </c>
       <c r="E153" t="s">
-        <v>110</v>
+        <v>88</v>
       </c>
       <c r="F153" t="s">
-        <v>0</v>
+        <v>89</v>
       </c>
       <c r="G153" t="s">
-        <v>111</v>
+        <v>571</v>
       </c>
       <c r="H153" t="s">
         <v>5</v>
@@ -5734,22 +5713,22 @@
     </row>
     <row r="154" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A154" t="s">
-        <v>114</v>
+        <v>572</v>
       </c>
       <c r="C154" t="s">
-        <v>12</v>
+        <v>2</v>
       </c>
       <c r="D154" t="s">
-        <v>109</v>
+        <v>570</v>
       </c>
       <c r="E154" t="s">
-        <v>110</v>
+        <v>88</v>
       </c>
       <c r="F154" t="s">
-        <v>0</v>
+        <v>89</v>
       </c>
       <c r="G154" t="s">
-        <v>111</v>
+        <v>571</v>
       </c>
       <c r="H154" t="s">
         <v>5</v>
@@ -5757,22 +5736,22 @@
     </row>
     <row r="155" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A155" t="s">
-        <v>577</v>
+        <v>573</v>
       </c>
       <c r="C155" t="s">
-        <v>13</v>
+        <v>2</v>
       </c>
       <c r="D155" t="s">
-        <v>578</v>
+        <v>570</v>
       </c>
       <c r="E155" t="s">
-        <v>234</v>
+        <v>88</v>
       </c>
       <c r="F155" t="s">
-        <v>235</v>
+        <v>89</v>
       </c>
       <c r="G155" t="s">
-        <v>579</v>
+        <v>571</v>
       </c>
       <c r="H155" t="s">
         <v>5</v>
@@ -5780,22 +5759,22 @@
     </row>
     <row r="156" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A156" t="s">
-        <v>580</v>
+        <v>574</v>
       </c>
       <c r="C156" t="s">
         <v>2</v>
       </c>
       <c r="D156" t="s">
-        <v>581</v>
+        <v>570</v>
       </c>
       <c r="E156" t="s">
+        <v>88</v>
+      </c>
+      <c r="F156" t="s">
         <v>89</v>
       </c>
-      <c r="F156" t="s">
-        <v>90</v>
-      </c>
       <c r="G156" t="s">
-        <v>582</v>
+        <v>571</v>
       </c>
       <c r="H156" t="s">
         <v>5</v>
@@ -5803,22 +5782,22 @@
     </row>
     <row r="157" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A157" t="s">
-        <v>583</v>
+        <v>575</v>
       </c>
       <c r="C157" t="s">
-        <v>2</v>
+        <v>9</v>
       </c>
       <c r="D157" t="s">
-        <v>581</v>
+        <v>576</v>
       </c>
       <c r="E157" t="s">
-        <v>89</v>
+        <v>44</v>
       </c>
       <c r="F157" t="s">
-        <v>90</v>
+        <v>45</v>
       </c>
       <c r="G157" t="s">
-        <v>582</v>
+        <v>166</v>
       </c>
       <c r="H157" t="s">
         <v>5</v>
@@ -5826,22 +5805,22 @@
     </row>
     <row r="158" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A158" t="s">
-        <v>584</v>
+        <v>577</v>
       </c>
       <c r="C158" t="s">
-        <v>2</v>
+        <v>9</v>
       </c>
       <c r="D158" t="s">
-        <v>581</v>
+        <v>576</v>
       </c>
       <c r="E158" t="s">
-        <v>89</v>
+        <v>44</v>
       </c>
       <c r="F158" t="s">
-        <v>90</v>
+        <v>45</v>
       </c>
       <c r="G158" t="s">
-        <v>582</v>
+        <v>166</v>
       </c>
       <c r="H158" t="s">
         <v>5</v>
@@ -5849,19 +5828,19 @@
     </row>
     <row r="159" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A159" t="s">
-        <v>585</v>
+        <v>578</v>
       </c>
       <c r="C159" t="s">
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="D159" t="s">
+        <v>579</v>
+      </c>
+      <c r="E159" t="s">
+        <v>580</v>
+      </c>
+      <c r="F159" t="s">
         <v>581</v>
-      </c>
-      <c r="E159" t="s">
-        <v>89</v>
-      </c>
-      <c r="F159" t="s">
-        <v>90</v>
       </c>
       <c r="G159" t="s">
         <v>582</v>
@@ -5872,22 +5851,22 @@
     </row>
     <row r="160" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A160" t="s">
+        <v>583</v>
+      </c>
+      <c r="C160" t="s">
+        <v>2</v>
+      </c>
+      <c r="D160" t="s">
+        <v>584</v>
+      </c>
+      <c r="E160" t="s">
+        <v>585</v>
+      </c>
+      <c r="F160" t="s">
         <v>586</v>
       </c>
-      <c r="C160" t="s">
-        <v>9</v>
-      </c>
-      <c r="D160" t="s">
+      <c r="G160" t="s">
         <v>587</v>
-      </c>
-      <c r="E160" t="s">
-        <v>44</v>
-      </c>
-      <c r="F160" t="s">
-        <v>45</v>
-      </c>
-      <c r="G160" t="s">
-        <v>167</v>
       </c>
       <c r="H160" t="s">
         <v>5</v>
@@ -5898,19 +5877,19 @@
         <v>588</v>
       </c>
       <c r="C161" t="s">
-        <v>9</v>
+        <v>2</v>
       </c>
       <c r="D161" t="s">
+        <v>584</v>
+      </c>
+      <c r="E161" t="s">
+        <v>585</v>
+      </c>
+      <c r="F161" t="s">
+        <v>586</v>
+      </c>
+      <c r="G161" t="s">
         <v>587</v>
-      </c>
-      <c r="E161" t="s">
-        <v>44</v>
-      </c>
-      <c r="F161" t="s">
-        <v>45</v>
-      </c>
-      <c r="G161" t="s">
-        <v>167</v>
       </c>
       <c r="H161" t="s">
         <v>5</v>
@@ -5921,19 +5900,19 @@
         <v>589</v>
       </c>
       <c r="C162" t="s">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="D162" t="s">
         <v>590</v>
       </c>
       <c r="E162" t="s">
+        <v>203</v>
+      </c>
+      <c r="F162" t="s">
+        <v>204</v>
+      </c>
+      <c r="G162" t="s">
         <v>591</v>
-      </c>
-      <c r="F162" t="s">
-        <v>592</v>
-      </c>
-      <c r="G162" t="s">
-        <v>593</v>
       </c>
       <c r="H162" t="s">
         <v>5</v>
@@ -5941,22 +5920,22 @@
     </row>
     <row r="163" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A163" t="s">
-        <v>594</v>
+        <v>592</v>
       </c>
       <c r="C163" t="s">
-        <v>2</v>
+        <v>13</v>
       </c>
       <c r="D163" t="s">
-        <v>595</v>
+        <v>590</v>
       </c>
       <c r="E163" t="s">
-        <v>596</v>
+        <v>203</v>
       </c>
       <c r="F163" t="s">
-        <v>597</v>
+        <v>204</v>
       </c>
       <c r="G163" t="s">
-        <v>598</v>
+        <v>591</v>
       </c>
       <c r="H163" t="s">
         <v>5</v>
@@ -5964,22 +5943,22 @@
     </row>
     <row r="164" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A164" t="s">
-        <v>599</v>
+        <v>593</v>
       </c>
       <c r="C164" t="s">
-        <v>2</v>
+        <v>34</v>
       </c>
       <c r="D164" t="s">
-        <v>595</v>
+        <v>594</v>
       </c>
       <c r="E164" t="s">
-        <v>596</v>
+        <v>238</v>
       </c>
       <c r="F164" t="s">
-        <v>597</v>
+        <v>239</v>
       </c>
       <c r="G164" t="s">
-        <v>598</v>
+        <v>306</v>
       </c>
       <c r="H164" t="s">
         <v>5</v>
@@ -5987,22 +5966,22 @@
     </row>
     <row r="165" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A165" t="s">
-        <v>600</v>
+        <v>595</v>
       </c>
       <c r="C165" t="s">
-        <v>13</v>
+        <v>34</v>
       </c>
       <c r="D165" t="s">
-        <v>601</v>
+        <v>594</v>
       </c>
       <c r="E165" t="s">
-        <v>204</v>
+        <v>238</v>
       </c>
       <c r="F165" t="s">
-        <v>205</v>
+        <v>239</v>
       </c>
       <c r="G165" t="s">
-        <v>602</v>
+        <v>306</v>
       </c>
       <c r="H165" t="s">
         <v>5</v>
@@ -6010,186 +5989,168 @@
     </row>
     <row r="166" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A166" t="s">
-        <v>603</v>
+        <v>596</v>
       </c>
       <c r="C166" t="s">
-        <v>13</v>
+        <v>29</v>
       </c>
       <c r="D166" t="s">
-        <v>601</v>
+        <v>597</v>
       </c>
       <c r="E166" t="s">
-        <v>204</v>
+        <v>79</v>
       </c>
       <c r="F166" t="s">
-        <v>205</v>
+        <v>30</v>
       </c>
       <c r="G166" t="s">
-        <v>602</v>
+        <v>62</v>
       </c>
       <c r="H166" t="s">
-        <v>5</v>
+        <v>117</v>
       </c>
     </row>
     <row r="167" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A167" t="s">
-        <v>604</v>
+        <v>598</v>
       </c>
       <c r="C167" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="D167" t="s">
-        <v>605</v>
+        <v>599</v>
       </c>
       <c r="E167" t="s">
-        <v>239</v>
+        <v>104</v>
       </c>
       <c r="F167" t="s">
-        <v>240</v>
+        <v>0</v>
       </c>
       <c r="G167" t="s">
-        <v>307</v>
+        <v>600</v>
       </c>
       <c r="H167" t="s">
-        <v>5</v>
+        <v>601</v>
       </c>
     </row>
     <row r="168" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A168" t="s">
-        <v>606</v>
+        <v>602</v>
       </c>
       <c r="C168" t="s">
-        <v>34</v>
+        <v>59</v>
       </c>
       <c r="D168" t="s">
+        <v>603</v>
+      </c>
+      <c r="E168" t="s">
+        <v>604</v>
+      </c>
+      <c r="F168" t="s">
+        <v>0</v>
+      </c>
+      <c r="G168" t="s">
         <v>605</v>
       </c>
-      <c r="E168" t="s">
-        <v>239</v>
-      </c>
-      <c r="F168" t="s">
-        <v>240</v>
-      </c>
-      <c r="G168" t="s">
-        <v>307</v>
-      </c>
       <c r="H168" t="s">
-        <v>5</v>
+        <v>601</v>
       </c>
     </row>
     <row r="169" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A169" t="s">
-        <v>607</v>
+        <v>606</v>
       </c>
       <c r="C169" t="s">
-        <v>29</v>
+        <v>59</v>
       </c>
       <c r="D169" t="s">
-        <v>608</v>
+        <v>603</v>
       </c>
       <c r="E169" t="s">
-        <v>80</v>
+        <v>604</v>
       </c>
       <c r="F169" t="s">
-        <v>30</v>
+        <v>0</v>
       </c>
       <c r="G169" t="s">
-        <v>62</v>
+        <v>605</v>
       </c>
       <c r="H169" t="s">
-        <v>118</v>
+        <v>601</v>
       </c>
     </row>
     <row r="170" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A170" t="s">
-        <v>609</v>
+        <v>607</v>
       </c>
       <c r="C170" t="s">
-        <v>35</v>
+        <v>59</v>
       </c>
       <c r="D170" t="s">
-        <v>610</v>
+        <v>603</v>
       </c>
       <c r="E170" t="s">
-        <v>105</v>
+        <v>604</v>
       </c>
       <c r="F170" t="s">
         <v>0</v>
       </c>
       <c r="G170" t="s">
-        <v>611</v>
+        <v>605</v>
       </c>
       <c r="H170" t="s">
-        <v>612</v>
+        <v>601</v>
       </c>
     </row>
     <row r="171" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A171" t="s">
-        <v>613</v>
+        <v>608</v>
       </c>
       <c r="C171" t="s">
-        <v>59</v>
+        <v>13</v>
       </c>
       <c r="D171" t="s">
-        <v>614</v>
-      </c>
-      <c r="E171" t="s">
-        <v>615</v>
-      </c>
-      <c r="F171" t="s">
-        <v>0</v>
-      </c>
-      <c r="G171" t="s">
-        <v>616</v>
+        <v>608</v>
       </c>
       <c r="H171" t="s">
-        <v>612</v>
+        <v>610</v>
       </c>
     </row>
     <row r="172" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A172" t="s">
-        <v>617</v>
+        <v>609</v>
       </c>
       <c r="C172" t="s">
-        <v>59</v>
+        <v>3</v>
       </c>
       <c r="D172" t="s">
-        <v>614</v>
-      </c>
-      <c r="E172" t="s">
-        <v>615</v>
-      </c>
-      <c r="F172" t="s">
-        <v>0</v>
-      </c>
-      <c r="G172" t="s">
-        <v>616</v>
+        <v>609</v>
       </c>
       <c r="H172" t="s">
-        <v>612</v>
+        <v>610</v>
       </c>
     </row>
     <row r="173" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A173" t="s">
-        <v>618</v>
+        <v>505</v>
       </c>
       <c r="C173" t="s">
-        <v>59</v>
+        <v>32</v>
       </c>
       <c r="D173" t="s">
-        <v>614</v>
+        <v>505</v>
       </c>
       <c r="E173" t="s">
-        <v>615</v>
+        <v>18</v>
       </c>
       <c r="F173" t="s">
         <v>0</v>
       </c>
       <c r="G173" t="s">
-        <v>616</v>
+        <v>506</v>
       </c>
       <c r="H173" t="s">
-        <v>612</v>
+        <v>5</v>
       </c>
     </row>
   </sheetData>

--- a/1.xlsx
+++ b/1.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="\\wh.local\fs\UserProfile_TSSWH19\_TSSWH19_redirected_folders\HunyaCs1\Desktop\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EDDC5EC4-6337-4647-99CF-080402CBEFF0}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{83595A58-D015-4B9D-9A08-8DD44CFD316E}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="0" windowWidth="22260" windowHeight="12648" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1205" uniqueCount="611">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1050" uniqueCount="506">
   <si>
     <t>BUDAPEST</t>
   </si>
@@ -48,18 +48,12 @@
     <t>AUCHAN</t>
   </si>
   <si>
-    <t>SZ-840</t>
-  </si>
-  <si>
     <t>2120</t>
   </si>
   <si>
     <t>DUNAKESZI</t>
   </si>
   <si>
-    <t>SZ-828</t>
-  </si>
-  <si>
     <t>SZ-822</t>
   </si>
   <si>
@@ -84,9 +78,6 @@
     <t>VERESEGYHÁZ</t>
   </si>
   <si>
-    <t>1162</t>
-  </si>
-  <si>
     <t>1165</t>
   </si>
   <si>
@@ -108,21 +99,6 @@
     <t>SZ-836</t>
   </si>
   <si>
-    <t>1116</t>
-  </si>
-  <si>
-    <t>2316</t>
-  </si>
-  <si>
-    <t>TÖKÖL</t>
-  </si>
-  <si>
-    <t>SZ-818</t>
-  </si>
-  <si>
-    <t>TAHITÓTFALU</t>
-  </si>
-  <si>
     <t>SZ-801</t>
   </si>
   <si>
@@ -132,9 +108,6 @@
     <t>1134</t>
   </si>
   <si>
-    <t>SZ-827</t>
-  </si>
-  <si>
     <t>SZ-820</t>
   </si>
   <si>
@@ -147,18 +120,9 @@
     <t>1183</t>
   </si>
   <si>
-    <t>1048</t>
-  </si>
-  <si>
     <t>1144</t>
   </si>
   <si>
-    <t>1156</t>
-  </si>
-  <si>
-    <t>1163</t>
-  </si>
-  <si>
     <t>SZ-829</t>
   </si>
   <si>
@@ -168,9 +132,6 @@
     <t>GÖD</t>
   </si>
   <si>
-    <t>1105</t>
-  </si>
-  <si>
     <t>1119</t>
   </si>
   <si>
@@ -180,33 +141,9 @@
     <t>NAGYKŐRÖS</t>
   </si>
   <si>
-    <t>1021</t>
-  </si>
-  <si>
-    <t>1222</t>
-  </si>
-  <si>
-    <t>1214</t>
-  </si>
-  <si>
     <t>1181</t>
   </si>
   <si>
-    <t>Rózsa utca</t>
-  </si>
-  <si>
-    <t>2071</t>
-  </si>
-  <si>
-    <t>PÁTY</t>
-  </si>
-  <si>
-    <t>Váci út</t>
-  </si>
-  <si>
-    <t>Szabadság utca</t>
-  </si>
-  <si>
     <t>SZ-823</t>
   </si>
   <si>
@@ -219,18 +156,9 @@
     <t>Szabadság út</t>
   </si>
   <si>
-    <t>Páskomliget utca</t>
-  </si>
-  <si>
     <t>1161</t>
   </si>
   <si>
-    <t>2360</t>
-  </si>
-  <si>
-    <t>GYÁL</t>
-  </si>
-  <si>
     <t>1204</t>
   </si>
   <si>
@@ -240,138 +168,21 @@
     <t>ÉRD</t>
   </si>
   <si>
-    <t>1173</t>
-  </si>
-  <si>
     <t>Rákóczi utca</t>
   </si>
   <si>
-    <t>1157</t>
-  </si>
-  <si>
     <t>1043</t>
   </si>
   <si>
     <t>1188</t>
   </si>
   <si>
-    <t>304013244/1</t>
-  </si>
-  <si>
-    <t>304013244</t>
-  </si>
-  <si>
-    <t>1137</t>
-  </si>
-  <si>
-    <t>Szent István park</t>
-  </si>
-  <si>
-    <t>2021</t>
-  </si>
-  <si>
-    <t>1104</t>
-  </si>
-  <si>
-    <t>1093</t>
-  </si>
-  <si>
-    <t>Közraktár utca</t>
-  </si>
-  <si>
-    <t>305007380/1</t>
-  </si>
-  <si>
-    <t>305007380</t>
-  </si>
-  <si>
-    <t>2377</t>
-  </si>
-  <si>
-    <t>ÖRKÉNY</t>
-  </si>
-  <si>
-    <t>Bartók Béla utca</t>
-  </si>
-  <si>
-    <t>2081</t>
-  </si>
-  <si>
-    <t>PILISCSABA</t>
-  </si>
-  <si>
-    <t>2200</t>
-  </si>
-  <si>
-    <t>MONOR</t>
-  </si>
-  <si>
-    <t>1141</t>
-  </si>
-  <si>
     <t>1047</t>
   </si>
   <si>
-    <t>1025</t>
-  </si>
-  <si>
-    <t>1145</t>
-  </si>
-  <si>
-    <t>Újvidék tér</t>
-  </si>
-  <si>
-    <t>1022</t>
-  </si>
-  <si>
-    <t>305368169/1</t>
-  </si>
-  <si>
-    <t>305368169</t>
-  </si>
-  <si>
-    <t>Mars utca</t>
-  </si>
-  <si>
-    <t>1041</t>
-  </si>
-  <si>
-    <t>Újszász utca</t>
-  </si>
-  <si>
-    <t>1015</t>
-  </si>
-  <si>
-    <t>1237</t>
-  </si>
-  <si>
-    <t>Március .</t>
-  </si>
-  <si>
-    <t>1194</t>
-  </si>
-  <si>
-    <t>202603232600685901</t>
-  </si>
-  <si>
-    <t>NFE6-03-21-D5ZS</t>
-  </si>
-  <si>
     <t>1221</t>
   </si>
   <si>
-    <t>Gerinc utca</t>
-  </si>
-  <si>
-    <t>202603232600685902</t>
-  </si>
-  <si>
-    <t>202603232600685903</t>
-  </si>
-  <si>
-    <t>202603232600685904</t>
-  </si>
-  <si>
     <t>2225</t>
   </si>
   <si>
@@ -381,9 +192,6 @@
     <t>Dózsa György út</t>
   </si>
   <si>
-    <t>PICIGURMAN</t>
-  </si>
-  <si>
     <t>CSOMAGSZAM</t>
   </si>
   <si>
@@ -405,51 +213,9 @@
     <t>MEGBIZO_ROVIDKOD</t>
   </si>
   <si>
-    <t>69b580396967eb2a8b5cea90</t>
-  </si>
-  <si>
-    <t>260314-F00005356</t>
-  </si>
-  <si>
-    <t>2768</t>
-  </si>
-  <si>
-    <t>ÚJSZILVÁS</t>
-  </si>
-  <si>
-    <t>Nyárfa utca</t>
-  </si>
-  <si>
-    <t>69b5a6e26967eb2a8b5cec41</t>
-  </si>
-  <si>
-    <t>260314-F00006424</t>
-  </si>
-  <si>
     <t>1033</t>
   </si>
   <si>
-    <t>Hévízi út</t>
-  </si>
-  <si>
-    <t>69bad57cd96b4f4a2437ee37</t>
-  </si>
-  <si>
-    <t>260318-F00012735</t>
-  </si>
-  <si>
-    <t>Irányi utca</t>
-  </si>
-  <si>
-    <t>69bea567d96b4f4a2438242c</t>
-  </si>
-  <si>
-    <t>260318-W00006907</t>
-  </si>
-  <si>
-    <t>Baracsi utca</t>
-  </si>
-  <si>
     <t>69c39f76d96b4f4a24386478</t>
   </si>
   <si>
@@ -459,27 +225,6 @@
     <t>Virág utca</t>
   </si>
   <si>
-    <t>69c3ce70d96b4f4a24386bab</t>
-  </si>
-  <si>
-    <t>260320-F00007483</t>
-  </si>
-  <si>
-    <t>Hattyú utca</t>
-  </si>
-  <si>
-    <t>69bd8c65d96b4f4a24381a4c</t>
-  </si>
-  <si>
-    <t>260320-F00013067</t>
-  </si>
-  <si>
-    <t>1108</t>
-  </si>
-  <si>
-    <t>Harmat utca</t>
-  </si>
-  <si>
     <t>69c3a917d96b4f4a243865fa</t>
   </si>
   <si>
@@ -492,102 +237,18 @@
     <t>Cserhalom utca</t>
   </si>
   <si>
-    <t>69becea7d96b4f4a2438269f</t>
-  </si>
-  <si>
-    <t>SZ-809</t>
-  </si>
-  <si>
-    <t>260321-F00005989</t>
-  </si>
-  <si>
-    <t>Csokonai utca</t>
-  </si>
-  <si>
-    <t>69beadd2d96b4f4a243824b7</t>
-  </si>
-  <si>
-    <t>260321-W00006278</t>
-  </si>
-  <si>
-    <t>69beadd2d96b4f4a243824b9</t>
-  </si>
-  <si>
-    <t>69c27be7d96b4f4a2438557e</t>
-  </si>
-  <si>
-    <t>260322-F00000834</t>
-  </si>
-  <si>
-    <t>Kisfaludy utca</t>
-  </si>
-  <si>
-    <t>69c164b7d96b4f4a24384720</t>
-  </si>
-  <si>
-    <t>260322-F00001395</t>
-  </si>
-  <si>
-    <t>Tóth Árpád utca</t>
-  </si>
-  <si>
-    <t>69bfcd22d96b4f4a24382b96</t>
-  </si>
-  <si>
-    <t>260322-F00001689</t>
-  </si>
-  <si>
     <t>2000</t>
   </si>
   <si>
     <t>SZENTENDRE</t>
   </si>
   <si>
-    <t>69c39779d96b4f4a2438637d</t>
-  </si>
-  <si>
-    <t>260322-F00002242</t>
-  </si>
-  <si>
-    <t>Gőzmozdony utca</t>
-  </si>
-  <si>
-    <t>69bf94b4d96b4f4a24382904</t>
-  </si>
-  <si>
-    <t>260322-W00000963</t>
-  </si>
-  <si>
     <t>2700</t>
   </si>
   <si>
     <t>CEGLÉD</t>
   </si>
   <si>
-    <t>Szélmalom zug</t>
-  </si>
-  <si>
-    <t>69bf94b4d96b4f4a24382905</t>
-  </si>
-  <si>
-    <t>69bfd072d96b4f4a24382bc4</t>
-  </si>
-  <si>
-    <t>260322-W00003861</t>
-  </si>
-  <si>
-    <t>Radnóti Miklós utca</t>
-  </si>
-  <si>
-    <t>69c2695dd96b4f4a24385337</t>
-  </si>
-  <si>
-    <t>260322-W00005052</t>
-  </si>
-  <si>
-    <t>Tinódi Lantos Sebestyén utca</t>
-  </si>
-  <si>
     <t>69c0434bd96b4f4a24383167</t>
   </si>
   <si>
@@ -597,234 +258,6 @@
     <t>Bácska utca</t>
   </si>
   <si>
-    <t>69c103d7d96b4f4a24383617</t>
-  </si>
-  <si>
-    <t>260323-F00001981</t>
-  </si>
-  <si>
-    <t>Barátság útja</t>
-  </si>
-  <si>
-    <t>69c13836d96b4f4a24383f69</t>
-  </si>
-  <si>
-    <t>260323-F00008157-3</t>
-  </si>
-  <si>
-    <t>Báthory utca</t>
-  </si>
-  <si>
-    <t>69c3a6cdd96b4f4a24386592</t>
-  </si>
-  <si>
-    <t>260323-F00011492</t>
-  </si>
-  <si>
-    <t>Lavotta utca</t>
-  </si>
-  <si>
-    <t>69c15db9d96b4f4a24384624</t>
-  </si>
-  <si>
-    <t>260323-F00012616</t>
-  </si>
-  <si>
-    <t>Somogyváry Gyula utca</t>
-  </si>
-  <si>
-    <t>69c105d9d96b4f4a2438366c</t>
-  </si>
-  <si>
-    <t>260323-W00002399</t>
-  </si>
-  <si>
-    <t>2721</t>
-  </si>
-  <si>
-    <t>PILIS</t>
-  </si>
-  <si>
-    <t>Árpád utca</t>
-  </si>
-  <si>
-    <t>69c105d9d96b4f4a2438366e</t>
-  </si>
-  <si>
-    <t>69c134b7d96b4f4a24383ee1</t>
-  </si>
-  <si>
-    <t>260323-W00004775</t>
-  </si>
-  <si>
-    <t>Akácos út</t>
-  </si>
-  <si>
-    <t>69c134b7d96b4f4a24383ee2</t>
-  </si>
-  <si>
-    <t>69c14e82d96b4f4a24384368</t>
-  </si>
-  <si>
-    <t>260323-W00006151</t>
-  </si>
-  <si>
-    <t>2364</t>
-  </si>
-  <si>
-    <t>ÓCSA</t>
-  </si>
-  <si>
-    <t>Némedi utca</t>
-  </si>
-  <si>
-    <t>69c15204d96b4f4a24384419</t>
-  </si>
-  <si>
-    <t>260323-W00006636</t>
-  </si>
-  <si>
-    <t>2755</t>
-  </si>
-  <si>
-    <t>KOCSÉR</t>
-  </si>
-  <si>
-    <t>69c1696ed96b4f4a243847ab</t>
-  </si>
-  <si>
-    <t>260323-W00008239</t>
-  </si>
-  <si>
-    <t>2115</t>
-  </si>
-  <si>
-    <t>VÁCSZENTLÁSZLÓ</t>
-  </si>
-  <si>
-    <t>Kossuth utca</t>
-  </si>
-  <si>
-    <t>69c1696ed96b4f4a243847ac</t>
-  </si>
-  <si>
-    <t>69c1c857d96b4f4a24384c0c</t>
-  </si>
-  <si>
-    <t>260323-W00012553</t>
-  </si>
-  <si>
-    <t>2142</t>
-  </si>
-  <si>
-    <t>NAGYTARCSA</t>
-  </si>
-  <si>
-    <t>Cinkotai út</t>
-  </si>
-  <si>
-    <t>69c268f2d96b4f4a2438531f</t>
-  </si>
-  <si>
-    <t>260324-F00004532</t>
-  </si>
-  <si>
-    <t>2213</t>
-  </si>
-  <si>
-    <t>MONORIERDŐ</t>
-  </si>
-  <si>
-    <t>Bokor utca</t>
-  </si>
-  <si>
-    <t>69c2771ad96b4f4a24385516</t>
-  </si>
-  <si>
-    <t>260324-F00005752</t>
-  </si>
-  <si>
-    <t>2760</t>
-  </si>
-  <si>
-    <t>NAGYKÁTA</t>
-  </si>
-  <si>
-    <t>Kadarka utca</t>
-  </si>
-  <si>
-    <t>69c2931fd96b4f4a243858d5</t>
-  </si>
-  <si>
-    <t>260324-F00009104</t>
-  </si>
-  <si>
-    <t>Barázda utca</t>
-  </si>
-  <si>
-    <t>69c29939d96b4f4a243859de</t>
-  </si>
-  <si>
-    <t>260324-F00009731</t>
-  </si>
-  <si>
-    <t>1155</t>
-  </si>
-  <si>
-    <t>Kolozsvár utca</t>
-  </si>
-  <si>
-    <t>69c29939d96b4f4a243859e0</t>
-  </si>
-  <si>
-    <t>69c2cc85d96b4f4a24385f82</t>
-  </si>
-  <si>
-    <t>260324-F00013751</t>
-  </si>
-  <si>
-    <t>69c27cdbd96b4f4a2438558d</t>
-  </si>
-  <si>
-    <t>260324-W00004469</t>
-  </si>
-  <si>
-    <t>2623</t>
-  </si>
-  <si>
-    <t>KISMAROS</t>
-  </si>
-  <si>
-    <t>Harkály utca</t>
-  </si>
-  <si>
-    <t>69c290bdd96b4f4a2438584d</t>
-  </si>
-  <si>
-    <t>260324-W00005091</t>
-  </si>
-  <si>
-    <t>69c290bdd96b4f4a2438584e</t>
-  </si>
-  <si>
-    <t>69c2bfa1d96b4f4a24385e80</t>
-  </si>
-  <si>
-    <t>260324-W00007539</t>
-  </si>
-  <si>
-    <t>Havas Ignác utca</t>
-  </si>
-  <si>
-    <t>69c2c450d96b4f4a24385ee7</t>
-  </si>
-  <si>
-    <t>260324-W00007718</t>
-  </si>
-  <si>
-    <t>Fogarasi út</t>
-  </si>
-  <si>
     <t>69c312d7d96b4f4a243861f2</t>
   </si>
   <si>
@@ -834,132 +267,12 @@
     <t>Folyamőr utca</t>
   </si>
   <si>
-    <t>69c3a7dfd96b4f4a243865be</t>
-  </si>
-  <si>
-    <t>260325-F00002326</t>
-  </si>
-  <si>
-    <t>1032</t>
-  </si>
-  <si>
-    <t>Szőlő utca</t>
-  </si>
-  <si>
-    <t>69c3b815d96b4f4a24386878</t>
-  </si>
-  <si>
-    <t>260325-F00003965</t>
-  </si>
-  <si>
-    <t>Szérű utca</t>
-  </si>
-  <si>
-    <t>69c3c748d96b4f4a24386ac5</t>
-  </si>
-  <si>
-    <t>260325-F00005377</t>
-  </si>
-  <si>
-    <t>Thököly utca</t>
-  </si>
-  <si>
-    <t>69c3c748d96b4f4a24386ac6</t>
-  </si>
-  <si>
-    <t>69c3bcc9d96b4f4a24386935</t>
-  </si>
-  <si>
-    <t>260325-W00003345</t>
-  </si>
-  <si>
     <t>Pesti út</t>
   </si>
   <si>
-    <t>69c3bcc9d96b4f4a24386936</t>
-  </si>
-  <si>
-    <t>FIZZ-1000840042</t>
-  </si>
-  <si>
-    <t>267004357</t>
-  </si>
-  <si>
-    <t>Rákosfalva park</t>
-  </si>
-  <si>
     <t>SELEX</t>
   </si>
   <si>
-    <t>300160042/1</t>
-  </si>
-  <si>
-    <t>300160042</t>
-  </si>
-  <si>
-    <t>Kosztolányi Dezső utca</t>
-  </si>
-  <si>
-    <t>304487516/1</t>
-  </si>
-  <si>
-    <t>304487516</t>
-  </si>
-  <si>
-    <t>2119</t>
-  </si>
-  <si>
-    <t>PÉCEL</t>
-  </si>
-  <si>
-    <t>Szent Erzsébet körút</t>
-  </si>
-  <si>
-    <t>304727197/1</t>
-  </si>
-  <si>
-    <t>304727197</t>
-  </si>
-  <si>
-    <t>2072</t>
-  </si>
-  <si>
-    <t>ZSÁMBÉK</t>
-  </si>
-  <si>
-    <t>Gagarin utca</t>
-  </si>
-  <si>
-    <t>304781271/1</t>
-  </si>
-  <si>
-    <t>304781271</t>
-  </si>
-  <si>
-    <t>Törökvész út</t>
-  </si>
-  <si>
-    <t>304826527/1</t>
-  </si>
-  <si>
-    <t>304826527</t>
-  </si>
-  <si>
-    <t>1191</t>
-  </si>
-  <si>
-    <t>Széchenyi utca</t>
-  </si>
-  <si>
-    <t>304826527/2</t>
-  </si>
-  <si>
-    <t>304875107/1</t>
-  </si>
-  <si>
-    <t>304875107</t>
-  </si>
-  <si>
     <t>304875165/1</t>
   </si>
   <si>
@@ -969,898 +282,1270 @@
     <t>1146</t>
   </si>
   <si>
-    <t>305007060/1</t>
-  </si>
-  <si>
-    <t>305007060</t>
-  </si>
-  <si>
-    <t>305007060/2</t>
-  </si>
-  <si>
-    <t>305007060/3</t>
-  </si>
-  <si>
-    <t>305007364/1</t>
-  </si>
-  <si>
-    <t>305007364</t>
-  </si>
-  <si>
-    <t>1012</t>
-  </si>
-  <si>
-    <t>Lovas út</t>
-  </si>
-  <si>
-    <t>305007364/2</t>
-  </si>
-  <si>
-    <t>305007364/3</t>
-  </si>
-  <si>
-    <t>305007671/1</t>
-  </si>
-  <si>
-    <t>305007671</t>
-  </si>
-  <si>
     <t>2234</t>
   </si>
   <si>
     <t>MAGLÓD</t>
   </si>
   <si>
-    <t>Horváth Mihály utca</t>
-  </si>
-  <si>
-    <t>305007702/1</t>
-  </si>
-  <si>
-    <t>305007702</t>
-  </si>
-  <si>
-    <t>Darázs utca</t>
-  </si>
-  <si>
-    <t>305113625/1</t>
-  </si>
-  <si>
-    <t>305113625</t>
-  </si>
-  <si>
-    <t>Etele út</t>
-  </si>
-  <si>
-    <t>305113775/1</t>
-  </si>
-  <si>
-    <t>305113775</t>
-  </si>
-  <si>
-    <t>Furulya utca</t>
-  </si>
-  <si>
-    <t>305170101/1</t>
-  </si>
-  <si>
-    <t>305170101</t>
-  </si>
-  <si>
-    <t>305170126/1</t>
-  </si>
-  <si>
-    <t>305170126</t>
-  </si>
-  <si>
-    <t>Ráday Gedeon utca</t>
-  </si>
-  <si>
-    <t>305170285/1</t>
-  </si>
-  <si>
-    <t>305170285</t>
-  </si>
-  <si>
-    <t>Határ út</t>
-  </si>
-  <si>
-    <t>305170285/2</t>
-  </si>
-  <si>
-    <t>305225869/1</t>
-  </si>
-  <si>
-    <t>305225869</t>
-  </si>
-  <si>
     <t>Ceglédi út</t>
   </si>
   <si>
-    <t>305225881/1</t>
-  </si>
-  <si>
-    <t>305225881</t>
-  </si>
-  <si>
-    <t>Aradi vértanúk</t>
-  </si>
-  <si>
-    <t>305226110/1</t>
-  </si>
-  <si>
-    <t>305226110</t>
-  </si>
-  <si>
-    <t>Bimbó út</t>
-  </si>
-  <si>
-    <t>305226138/1</t>
-  </si>
-  <si>
-    <t>305226138</t>
-  </si>
-  <si>
-    <t>Rekettye utca</t>
-  </si>
-  <si>
-    <t>305272645/1</t>
-  </si>
-  <si>
-    <t>305272645</t>
-  </si>
-  <si>
-    <t>2634</t>
-  </si>
-  <si>
-    <t>NAGYBÖRZSÖNY</t>
-  </si>
-  <si>
     <t>Petőfi utca</t>
   </si>
   <si>
-    <t>305315280/1</t>
-  </si>
-  <si>
-    <t>305315280</t>
-  </si>
-  <si>
-    <t>2440</t>
-  </si>
-  <si>
-    <t>SZÁZHALOMBATTA</t>
-  </si>
-  <si>
-    <t>305315280/2</t>
-  </si>
-  <si>
-    <t>305315496/1</t>
-  </si>
-  <si>
-    <t>305315496</t>
-  </si>
-  <si>
-    <t>Kispesti utca</t>
-  </si>
-  <si>
-    <t>305315598/1</t>
-  </si>
-  <si>
-    <t>305315598</t>
-  </si>
-  <si>
     <t>2461</t>
   </si>
   <si>
     <t>TÁRNOK</t>
   </si>
   <si>
-    <t>Rákóczi Ferenc Út</t>
-  </si>
-  <si>
-    <t>305315690/1</t>
-  </si>
-  <si>
-    <t>305315690</t>
-  </si>
-  <si>
-    <t>Mérnök utca</t>
-  </si>
-  <si>
-    <t>305316154/1</t>
-  </si>
-  <si>
-    <t>305316154</t>
-  </si>
-  <si>
-    <t>Háros utca</t>
-  </si>
-  <si>
-    <t>305367871/1</t>
-  </si>
-  <si>
-    <t>305367871</t>
-  </si>
-  <si>
-    <t>305367871/2</t>
-  </si>
-  <si>
-    <t>305368015/1</t>
-  </si>
-  <si>
-    <t>305368015</t>
-  </si>
-  <si>
-    <t>305368059/1</t>
-  </si>
-  <si>
-    <t>305368059</t>
-  </si>
-  <si>
-    <t>1239</t>
-  </si>
-  <si>
-    <t>Vetés utca</t>
-  </si>
-  <si>
-    <t>305368127/1</t>
-  </si>
-  <si>
-    <t>305368127</t>
-  </si>
-  <si>
-    <t>2194</t>
-  </si>
-  <si>
-    <t>TURA</t>
-  </si>
-  <si>
-    <t>Bartók Béla Utca</t>
-  </si>
-  <si>
-    <t>305368412/1</t>
-  </si>
-  <si>
-    <t>305368412</t>
-  </si>
-  <si>
-    <t>1192</t>
-  </si>
-  <si>
-    <t>Álmos utca</t>
-  </si>
-  <si>
-    <t>305368556/1</t>
-  </si>
-  <si>
-    <t>305368556</t>
-  </si>
-  <si>
-    <t>1133</t>
-  </si>
-  <si>
-    <t>Visegrádi utca</t>
-  </si>
-  <si>
-    <t>305368607/1</t>
-  </si>
-  <si>
-    <t>305368607</t>
-  </si>
-  <si>
-    <t>1147</t>
-  </si>
-  <si>
-    <t>Telepes utca</t>
-  </si>
-  <si>
-    <t>305411587/1</t>
-  </si>
-  <si>
-    <t>305411587</t>
-  </si>
-  <si>
-    <t>1031</t>
-  </si>
-  <si>
-    <t>Víznyelő utca</t>
-  </si>
-  <si>
-    <t>305412004/1</t>
-  </si>
-  <si>
-    <t>305412004</t>
-  </si>
-  <si>
-    <t>305412281/1</t>
-  </si>
-  <si>
-    <t>305412281</t>
-  </si>
-  <si>
-    <t>1193</t>
-  </si>
-  <si>
-    <t>Szigligeti utca</t>
-  </si>
-  <si>
-    <t>305412301/1</t>
-  </si>
-  <si>
-    <t>305412301</t>
-  </si>
-  <si>
-    <t>Mozdonyvezető utca</t>
-  </si>
-  <si>
-    <t>305412301/2</t>
-  </si>
-  <si>
-    <t>305412349/1</t>
-  </si>
-  <si>
-    <t>305412349</t>
-  </si>
-  <si>
-    <t>1139</t>
-  </si>
-  <si>
-    <t>Teve utca</t>
-  </si>
-  <si>
-    <t>305461579/1</t>
-  </si>
-  <si>
-    <t>305461579</t>
-  </si>
-  <si>
-    <t>Vörösmarty Utca</t>
-  </si>
-  <si>
-    <t>305461614/1</t>
-  </si>
-  <si>
-    <t>305461614</t>
-  </si>
-  <si>
     <t>1028</t>
   </si>
   <si>
     <t>Hidegkúti út</t>
   </si>
   <si>
-    <t>305461692/1</t>
-  </si>
-  <si>
-    <t>305461692</t>
-  </si>
-  <si>
     <t>1087</t>
   </si>
   <si>
-    <t>Osztály utca</t>
-  </si>
-  <si>
-    <t>305461718/1</t>
-  </si>
-  <si>
-    <t>305461718</t>
-  </si>
-  <si>
-    <t>2365</t>
-  </si>
-  <si>
-    <t>INÁRCS</t>
-  </si>
-  <si>
-    <t>Rákóczi Út</t>
-  </si>
-  <si>
-    <t>305461748/1</t>
-  </si>
-  <si>
-    <t>305461748</t>
-  </si>
-  <si>
-    <t>Akácfa Utca</t>
-  </si>
-  <si>
-    <t>305461903/1</t>
-  </si>
-  <si>
-    <t>305461903</t>
-  </si>
-  <si>
-    <t>Mezőkövesd út</t>
-  </si>
-  <si>
-    <t>305462032/1</t>
-  </si>
-  <si>
-    <t>305462032</t>
-  </si>
-  <si>
-    <t>Nyírpalota utca utca</t>
-  </si>
-  <si>
-    <t>305462274/1</t>
-  </si>
-  <si>
-    <t>305462274</t>
-  </si>
-  <si>
-    <t>1075</t>
-  </si>
-  <si>
-    <t>Rumbach Sebestyén utca</t>
-  </si>
-  <si>
-    <t>305462349/1</t>
-  </si>
-  <si>
-    <t>305462349</t>
-  </si>
-  <si>
-    <t>1201</t>
-  </si>
-  <si>
     <t>Vörösmarty utca</t>
   </si>
   <si>
-    <t>305514209/1</t>
-  </si>
-  <si>
-    <t>305514209</t>
-  </si>
-  <si>
-    <t>1154</t>
-  </si>
-  <si>
-    <t>Pörge utca</t>
-  </si>
-  <si>
-    <t>305514281/1</t>
-  </si>
-  <si>
-    <t>305514281</t>
-  </si>
-  <si>
-    <t>Arany János</t>
-  </si>
-  <si>
-    <t>305514387/1</t>
-  </si>
-  <si>
-    <t>305514387</t>
-  </si>
-  <si>
-    <t>1011</t>
-  </si>
-  <si>
-    <t>Jégverem Utca</t>
-  </si>
-  <si>
-    <t>305514420/1</t>
-  </si>
-  <si>
-    <t>305514420</t>
-  </si>
-  <si>
-    <t>1202</t>
-  </si>
-  <si>
-    <t>Szakolca utca</t>
-  </si>
-  <si>
-    <t>305514685/1</t>
-  </si>
-  <si>
-    <t>305514685</t>
-  </si>
-  <si>
-    <t>305514728/1</t>
-  </si>
-  <si>
-    <t>305514728</t>
-  </si>
-  <si>
-    <t>1024</t>
-  </si>
-  <si>
-    <t>Kút utca</t>
-  </si>
-  <si>
-    <t>305514841/1</t>
-  </si>
-  <si>
-    <t>305514841</t>
-  </si>
-  <si>
-    <t>Ganz Ábrahám utca</t>
-  </si>
-  <si>
-    <t>305514841/2</t>
-  </si>
-  <si>
-    <t>305514841/3</t>
-  </si>
-  <si>
-    <t>305514873/1</t>
-  </si>
-  <si>
-    <t>305514873</t>
-  </si>
-  <si>
-    <t>Nyírpalota Utca</t>
-  </si>
-  <si>
-    <t>99002253/1</t>
-  </si>
-  <si>
-    <t>99002253</t>
-  </si>
-  <si>
-    <t>1038</t>
-  </si>
-  <si>
-    <t>Ezüsthegy utca</t>
-  </si>
-  <si>
-    <t>99002261/1</t>
-  </si>
-  <si>
-    <t>99002261</t>
-  </si>
-  <si>
-    <t>Külső Szilágyi Út</t>
-  </si>
-  <si>
-    <t>202603162600591601</t>
-  </si>
-  <si>
-    <t>NFD6-03-11-VHBG</t>
-  </si>
-  <si>
-    <t>2117</t>
-  </si>
-  <si>
-    <t>ISASZEG</t>
-  </si>
-  <si>
-    <t>Liget utca</t>
-  </si>
-  <si>
-    <t>159995579538520518</t>
-  </si>
-  <si>
-    <t>NFD6-03-14-8H4W/CSXD</t>
-  </si>
-  <si>
-    <t>2095</t>
-  </si>
-  <si>
-    <t>PILISSZÁNTÓ</t>
-  </si>
-  <si>
-    <t>Zahrada utca</t>
-  </si>
-  <si>
-    <t>NFD6-03-14-B3WN/XD</t>
-  </si>
-  <si>
-    <t>Viola utca</t>
-  </si>
-  <si>
-    <t>202603252600662901</t>
-  </si>
-  <si>
-    <t>NFD6-03-18-2D67</t>
-  </si>
-  <si>
-    <t>2321</t>
-  </si>
-  <si>
-    <t>SZIGETBECSE</t>
-  </si>
-  <si>
-    <t>Kiss utca</t>
-  </si>
-  <si>
-    <t>202603252600669701</t>
-  </si>
-  <si>
-    <t>NFD6-03-19-AFQA</t>
-  </si>
-  <si>
-    <t>Mészáros Lőrinc utca</t>
-  </si>
-  <si>
-    <t>202603202600672501</t>
-  </si>
-  <si>
-    <t>NFD6-03-19-PHF7</t>
-  </si>
-  <si>
-    <t>Rátz László utca</t>
-  </si>
-  <si>
-    <t>202603232600680301</t>
-  </si>
-  <si>
-    <t>NFD6-03-20-C6JG</t>
-  </si>
-  <si>
-    <t>202603232600676901</t>
-  </si>
-  <si>
-    <t>NFD6-03-20-XTR7</t>
-  </si>
-  <si>
-    <t>Batthyány Lajos utca</t>
-  </si>
-  <si>
-    <t>202603232600687301</t>
-  </si>
-  <si>
-    <t>NFD6-03-21-4FX2</t>
-  </si>
-  <si>
-    <t>Komárom utca</t>
-  </si>
-  <si>
-    <t>202603232600687302</t>
-  </si>
-  <si>
-    <t>202603232600691901</t>
-  </si>
-  <si>
-    <t>NFD6-03-21-8HG2</t>
-  </si>
-  <si>
-    <t>Bőröndös utca</t>
-  </si>
-  <si>
-    <t>202603232600686801</t>
-  </si>
-  <si>
-    <t>NFD6-03-21-HN5S</t>
-  </si>
-  <si>
-    <t>NFD6-03-22-HYML-1</t>
-  </si>
-  <si>
-    <t>NFD6-03-22-HYML</t>
-  </si>
-  <si>
-    <t>Rózsafa utca</t>
-  </si>
-  <si>
-    <t>202603242600711101</t>
-  </si>
-  <si>
-    <t>NFD6-03-23-6X2B</t>
-  </si>
-  <si>
-    <t>2092</t>
-  </si>
-  <si>
-    <t>BUDAKESZI</t>
-  </si>
-  <si>
-    <t>Eszter utca</t>
-  </si>
-  <si>
-    <t>202603242600711102</t>
-  </si>
-  <si>
-    <t>202603242600707501</t>
-  </si>
-  <si>
-    <t>NFD6-03-23-MRJQ</t>
-  </si>
-  <si>
-    <t>Futórózsa utca</t>
-  </si>
-  <si>
-    <t>202603252600720801</t>
-  </si>
-  <si>
-    <t>NFD6-03-24-AQ3L</t>
-  </si>
-  <si>
     <t>1151</t>
   </si>
   <si>
-    <t>202603252600720901</t>
-  </si>
-  <si>
-    <t>NFD6-03-24-DL5D</t>
-  </si>
-  <si>
-    <t>Pálya utca</t>
-  </si>
-  <si>
-    <t>202603252600718601</t>
-  </si>
-  <si>
-    <t>NFD6-03-24-F9FQ</t>
-  </si>
-  <si>
-    <t>Radnai utca</t>
-  </si>
-  <si>
-    <t>202603252600718602</t>
-  </si>
-  <si>
-    <t>202603252600722701</t>
-  </si>
-  <si>
-    <t>NFD6-03-24-KAC2</t>
-  </si>
-  <si>
-    <t>2094</t>
-  </si>
-  <si>
-    <t>NAGYKOVÁCSI</t>
-  </si>
-  <si>
-    <t>Szamos utca</t>
-  </si>
-  <si>
-    <t>202603252600719801</t>
-  </si>
-  <si>
-    <t>NFD6-03-24-UQH8</t>
-  </si>
-  <si>
-    <t>Fürdő utca</t>
-  </si>
-  <si>
-    <t>202603232600682501</t>
-  </si>
-  <si>
-    <t>NFE6-03-20-4R5P</t>
-  </si>
-  <si>
-    <t>2051</t>
-  </si>
-  <si>
-    <t>BIATORBÁGY</t>
-  </si>
-  <si>
-    <t>202603232600702001</t>
-  </si>
-  <si>
-    <t>NFE6-03-22-CQ2S</t>
-  </si>
-  <si>
-    <t>Barátság köz</t>
-  </si>
-  <si>
-    <t>202603232600700201</t>
-  </si>
-  <si>
-    <t>NFE6-03-22-PZZA</t>
-  </si>
-  <si>
-    <t>Szent István király útja</t>
-  </si>
-  <si>
-    <t>202603232600700202</t>
-  </si>
-  <si>
-    <t>202603232600700203</t>
-  </si>
-  <si>
-    <t>202603232600700204</t>
-  </si>
-  <si>
-    <t>202603242600705301</t>
-  </si>
-  <si>
-    <t>NFE6-03-23-9TB8</t>
-  </si>
-  <si>
-    <t>202603242600705302</t>
-  </si>
-  <si>
-    <t>202603252600718001</t>
-  </si>
-  <si>
-    <t>NFE6-03-24-84YE</t>
-  </si>
-  <si>
-    <t>2045</t>
-  </si>
-  <si>
-    <t>TÖRÖKBÁLINT</t>
-  </si>
-  <si>
-    <t>Őszibarack utca</t>
-  </si>
-  <si>
-    <t>202603252600720001</t>
-  </si>
-  <si>
-    <t>NFE6-03-24-JUVR</t>
-  </si>
-  <si>
-    <t>2085</t>
-  </si>
-  <si>
-    <t>PILISVÖRÖSVÁR</t>
-  </si>
-  <si>
-    <t>Béke utca</t>
-  </si>
-  <si>
-    <t>202603252600720002</t>
-  </si>
-  <si>
-    <t>202603252600715901</t>
-  </si>
-  <si>
-    <t>NFE6-03-24-QXCS</t>
-  </si>
-  <si>
-    <t>Vatyai út</t>
-  </si>
-  <si>
-    <t>202603252600715902</t>
-  </si>
-  <si>
-    <t>202603252600716101</t>
-  </si>
-  <si>
-    <t>NFE6-03-24-RQLN</t>
-  </si>
-  <si>
-    <t>202603252600716102</t>
-  </si>
-  <si>
-    <t>159995579538573309</t>
-  </si>
-  <si>
-    <t>VA26/001323</t>
-  </si>
-  <si>
-    <t>159995579538520617</t>
-  </si>
-  <si>
-    <t>vsi-2026/03919</t>
-  </si>
-  <si>
-    <t>Köves utca</t>
-  </si>
-  <si>
-    <t>DRENCO</t>
-  </si>
-  <si>
-    <t>159995579538525544</t>
-  </si>
-  <si>
-    <t>vsi-2026/03954</t>
-  </si>
-  <si>
-    <t>1055</t>
-  </si>
-  <si>
-    <t>Kossuth Tér</t>
-  </si>
-  <si>
-    <t>159995579538525551</t>
-  </si>
-  <si>
-    <t>159995579538525568</t>
-  </si>
-  <si>
-    <t>NFD6-03-21-7Y85</t>
-  </si>
-  <si>
-    <t>NFD6-03-22-MCTT</t>
-  </si>
-  <si>
-    <t>AUCHAN_ÁRUHÁZI</t>
+    <t>248744972/1</t>
+  </si>
+  <si>
+    <t>248744972</t>
+  </si>
+  <si>
+    <t>1113</t>
+  </si>
+  <si>
+    <t>Bocskai út</t>
+  </si>
+  <si>
+    <t>69b13adf51e7020fc80cccc4</t>
+  </si>
+  <si>
+    <t>260311-F00003619</t>
+  </si>
+  <si>
+    <t>2114</t>
+  </si>
+  <si>
+    <t>VALKÓ</t>
+  </si>
+  <si>
+    <t>69c24e64d96b4f4a24384f09</t>
+  </si>
+  <si>
+    <t>SZ-814</t>
+  </si>
+  <si>
+    <t>260317-F00004392</t>
+  </si>
+  <si>
+    <t>1086</t>
+  </si>
+  <si>
+    <t>Szerdahelyi utca</t>
+  </si>
+  <si>
+    <t>69b9506ad96b4f4a2437cfb2</t>
+  </si>
+  <si>
+    <t>260317-F00008559</t>
+  </si>
+  <si>
+    <t>2113</t>
+  </si>
+  <si>
+    <t>ERDŐKERTES</t>
+  </si>
+  <si>
+    <t>Katona József utca</t>
+  </si>
+  <si>
+    <t>69c3c301d96b4f4a24386a3c</t>
+  </si>
+  <si>
+    <t>260320-F00001288-1</t>
+  </si>
+  <si>
+    <t>Arany János utca</t>
+  </si>
+  <si>
+    <t>69c3b690d96b4f4a24386839</t>
+  </si>
+  <si>
+    <t>260320-F00007295-1</t>
+  </si>
+  <si>
+    <t>2132</t>
+  </si>
+  <si>
+    <t>Turista utca</t>
+  </si>
+  <si>
+    <t>69c29331d96b4f4a243858db</t>
+  </si>
+  <si>
+    <t>260320-F00010459</t>
+  </si>
+  <si>
+    <t>Deákvári főút</t>
+  </si>
+  <si>
+    <t>69bd1d58d96b4f4a24380db3</t>
+  </si>
+  <si>
+    <t>260320-W00003345</t>
+  </si>
+  <si>
+    <t>2336</t>
+  </si>
+  <si>
+    <t>DUNAVARSÁNY</t>
+  </si>
+  <si>
+    <t>69bd9114d96b4f4a24381a9a</t>
+  </si>
+  <si>
+    <t>260320-W00009564</t>
+  </si>
+  <si>
+    <t>1131</t>
+  </si>
+  <si>
+    <t>Keszkenő utca</t>
+  </si>
+  <si>
+    <t>69c26760d96b4f4a243852e1</t>
+  </si>
+  <si>
+    <t>260323-F00002502</t>
+  </si>
+  <si>
+    <t>1097</t>
+  </si>
+  <si>
+    <t>Vágóhíd utca</t>
+  </si>
+  <si>
+    <t>69c10e5fd96b4f4a24383804</t>
+  </si>
+  <si>
+    <t>260323-F00003631</t>
+  </si>
+  <si>
+    <t>2713</t>
+  </si>
+  <si>
+    <t>CSEMŐ</t>
+  </si>
+  <si>
+    <t>69c10e5fd96b4f4a24383805</t>
+  </si>
+  <si>
+    <t>69c12eefd96b4f4a24383dc1</t>
+  </si>
+  <si>
+    <t>260323-F00007335</t>
+  </si>
+  <si>
+    <t>Pannónia utca</t>
+  </si>
+  <si>
+    <t>69c283e4d96b4f4a24385678</t>
+  </si>
+  <si>
+    <t>260324-F00006893</t>
+  </si>
+  <si>
+    <t>Nagymező utca</t>
+  </si>
+  <si>
+    <t>69c283e4d96b4f4a24385679</t>
+  </si>
+  <si>
+    <t>69c28e68d96b4f4a243857fb</t>
+  </si>
+  <si>
+    <t>260324-F00008154</t>
+  </si>
+  <si>
+    <t>Géza utca</t>
+  </si>
+  <si>
+    <t>69c290bdd96b4f4a2438584a</t>
+  </si>
+  <si>
+    <t>260324-F00008791</t>
+  </si>
+  <si>
+    <t>2730</t>
+  </si>
+  <si>
+    <t>ALBERTIRSA</t>
+  </si>
+  <si>
+    <t>Pacsirta utca</t>
+  </si>
+  <si>
+    <t>69c28f96d96b4f4a24385815</t>
+  </si>
+  <si>
+    <t>260324-W00005290</t>
+  </si>
+  <si>
+    <t>2366</t>
+  </si>
+  <si>
+    <t>KAKUCS</t>
+  </si>
+  <si>
+    <t>69c28f96d96b4f4a24385818</t>
+  </si>
+  <si>
+    <t>69c28f96d96b4f4a2438581a</t>
+  </si>
+  <si>
+    <t>69c2d979d96b4f4a2438608b</t>
+  </si>
+  <si>
+    <t>260324-W00009019</t>
+  </si>
+  <si>
+    <t>1037</t>
+  </si>
+  <si>
+    <t>Kolostor út</t>
+  </si>
+  <si>
+    <t>69c2d979d96b4f4a2438608c</t>
+  </si>
+  <si>
+    <t>69c3b6e3d96b4f4a2438683f</t>
+  </si>
+  <si>
+    <t>260325-F00004204</t>
+  </si>
+  <si>
+    <t>Harangvirág utca</t>
+  </si>
+  <si>
+    <t>69c3dce7d96b4f4a24386da8</t>
+  </si>
+  <si>
+    <t>260325-F00007874</t>
+  </si>
+  <si>
+    <t>Barcsay utca</t>
+  </si>
+  <si>
+    <t>69c3db40d96b4f4a24386d5f</t>
+  </si>
+  <si>
+    <t>260325-F00007942</t>
+  </si>
+  <si>
+    <t>Wesselényi utca</t>
+  </si>
+  <si>
+    <t>69c3ef8bd96b4f4a24387068</t>
+  </si>
+  <si>
+    <t>260325-F00009953-2</t>
+  </si>
+  <si>
+    <t>Kőérberki út</t>
+  </si>
+  <si>
+    <t>69c408f5d96b4f4a243873a2</t>
+  </si>
+  <si>
+    <t>260325-F00012188</t>
+  </si>
+  <si>
+    <t>Lehel utca</t>
+  </si>
+  <si>
+    <t>69c42f99d96b4f4a24387654</t>
+  </si>
+  <si>
+    <t>260325-F00013344</t>
+  </si>
+  <si>
+    <t>Hunyadi utca</t>
+  </si>
+  <si>
+    <t>69c42f9ad96b4f4a24387657</t>
+  </si>
+  <si>
+    <t>SZ-835</t>
+  </si>
+  <si>
+    <t>260325-F00013551</t>
+  </si>
+  <si>
+    <t>1067</t>
+  </si>
+  <si>
+    <t>Teréz körút</t>
+  </si>
+  <si>
+    <t>69c3d560d96b4f4a24386c9b</t>
+  </si>
+  <si>
+    <t>260325-W00004201</t>
+  </si>
+  <si>
+    <t>1107</t>
+  </si>
+  <si>
+    <t>Gém utca</t>
+  </si>
+  <si>
+    <t>69c3e162d96b4f4a24386e8b</t>
+  </si>
+  <si>
+    <t>260325-W00005253</t>
+  </si>
+  <si>
+    <t>Gyógyszergyár utca</t>
+  </si>
+  <si>
+    <t>69c43eeed96b4f4a243876f2</t>
+  </si>
+  <si>
+    <t>260325-W00009456</t>
+  </si>
+  <si>
+    <t>Égerfa utca</t>
+  </si>
+  <si>
+    <t>69c4fde1d96b4f4a24387c6c</t>
+  </si>
+  <si>
+    <t>260326-F00002610</t>
+  </si>
+  <si>
+    <t>Róbert Károly körút</t>
+  </si>
+  <si>
+    <t>FIZZ-1000849314</t>
+  </si>
+  <si>
+    <t>267004465</t>
+  </si>
+  <si>
+    <t>2315</t>
+  </si>
+  <si>
+    <t>SZIGETHALOM</t>
+  </si>
+  <si>
+    <t>Mű út</t>
+  </si>
+  <si>
+    <t>1449-948833</t>
+  </si>
+  <si>
+    <t>267004466</t>
+  </si>
+  <si>
+    <t>1213</t>
+  </si>
+  <si>
+    <t>Tancsics Mihaly Utca</t>
+  </si>
+  <si>
+    <t>26MPE0003293/1</t>
+  </si>
+  <si>
+    <t>26MPE0003293</t>
+  </si>
+  <si>
+    <t>Kossuth Lajos út</t>
+  </si>
+  <si>
+    <t>MEGAPLACE</t>
+  </si>
+  <si>
+    <t>26MPE0003300/1</t>
+  </si>
+  <si>
+    <t>26MPE0003300</t>
+  </si>
+  <si>
+    <t>1112</t>
+  </si>
+  <si>
+    <t>FACSEMETE UTCA</t>
+  </si>
+  <si>
+    <t>304576536/1</t>
+  </si>
+  <si>
+    <t>304576536</t>
+  </si>
+  <si>
+    <t>füredi utca</t>
+  </si>
+  <si>
+    <t>304826661/1</t>
+  </si>
+  <si>
+    <t>304826661</t>
+  </si>
+  <si>
+    <t>1182</t>
+  </si>
+  <si>
+    <t>Halomi út</t>
+  </si>
+  <si>
+    <t>304826661/2</t>
+  </si>
+  <si>
+    <t>304826661/3</t>
+  </si>
+  <si>
+    <t>304875527/1</t>
+  </si>
+  <si>
+    <t>304875527</t>
+  </si>
+  <si>
+    <t>1148</t>
+  </si>
+  <si>
+    <t>Nagy Lajos király útja</t>
+  </si>
+  <si>
+    <t>304925187/1</t>
+  </si>
+  <si>
+    <t>304925187</t>
+  </si>
+  <si>
+    <t>Népfürdő utca</t>
+  </si>
+  <si>
+    <t>304963429/1</t>
+  </si>
+  <si>
+    <t>304963429</t>
+  </si>
+  <si>
+    <t>Folyamőr Utca</t>
+  </si>
+  <si>
+    <t>304963429/2</t>
+  </si>
+  <si>
+    <t>305169860/2/1</t>
+  </si>
+  <si>
+    <t>305169860/2</t>
+  </si>
+  <si>
+    <t>2351</t>
+  </si>
+  <si>
+    <t>ALSÓNÉMEDI</t>
+  </si>
+  <si>
+    <t>Halászy Károly Utca</t>
+  </si>
+  <si>
+    <t>305169860/2/2</t>
+  </si>
+  <si>
+    <t>305169860/2/3</t>
+  </si>
+  <si>
+    <t>305225419/1</t>
+  </si>
+  <si>
+    <t>305225419</t>
+  </si>
+  <si>
+    <t>Mátyás király utca</t>
+  </si>
+  <si>
+    <t>305225419/2</t>
+  </si>
+  <si>
+    <t>305272678/1</t>
+  </si>
+  <si>
+    <t>305272678</t>
+  </si>
+  <si>
+    <t>Hadak útja</t>
+  </si>
+  <si>
+    <t>305273127/1</t>
+  </si>
+  <si>
+    <t>305273127</t>
+  </si>
+  <si>
+    <t>Komp utca</t>
+  </si>
+  <si>
+    <t>305273127/2</t>
+  </si>
+  <si>
+    <t>305273127/3</t>
+  </si>
+  <si>
+    <t>305273217/1</t>
+  </si>
+  <si>
+    <t>305273217</t>
+  </si>
+  <si>
+    <t>305273217/2</t>
+  </si>
+  <si>
+    <t>305316045/1</t>
+  </si>
+  <si>
+    <t>305316045</t>
+  </si>
+  <si>
+    <t>Kalapács utca</t>
+  </si>
+  <si>
+    <t>305367873/1</t>
+  </si>
+  <si>
+    <t>305367873</t>
+  </si>
+  <si>
+    <t>Montevideo utca</t>
+  </si>
+  <si>
+    <t>305367873/2</t>
+  </si>
+  <si>
+    <t>305368467/1</t>
+  </si>
+  <si>
+    <t>305368467</t>
+  </si>
+  <si>
+    <t>Lenvirág utca</t>
+  </si>
+  <si>
+    <t>305411534/1</t>
+  </si>
+  <si>
+    <t>305411534</t>
+  </si>
+  <si>
+    <t>305411534/2</t>
+  </si>
+  <si>
+    <t>305411632/1</t>
+  </si>
+  <si>
+    <t>305411632</t>
+  </si>
+  <si>
+    <t>Kossuth Lajos utca</t>
+  </si>
+  <si>
+    <t>305411632/2</t>
+  </si>
+  <si>
+    <t>305411632/3</t>
+  </si>
+  <si>
+    <t>305412274/1</t>
+  </si>
+  <si>
+    <t>305412274</t>
+  </si>
+  <si>
+    <t>Károlyi István utca</t>
+  </si>
+  <si>
+    <t>305461509/1</t>
+  </si>
+  <si>
+    <t>305461509</t>
+  </si>
+  <si>
+    <t>305461509/2</t>
+  </si>
+  <si>
+    <t>305461526/1</t>
+  </si>
+  <si>
+    <t>305461526</t>
+  </si>
+  <si>
+    <t>Dr. Lengyel Lajos utca</t>
+  </si>
+  <si>
+    <t>305461661/1</t>
+  </si>
+  <si>
+    <t>305461661</t>
+  </si>
+  <si>
+    <t>1061</t>
+  </si>
+  <si>
+    <t>Káldy Gyula utca</t>
+  </si>
+  <si>
+    <t>305461842/1</t>
+  </si>
+  <si>
+    <t>305461842</t>
+  </si>
+  <si>
+    <t>1094</t>
+  </si>
+  <si>
+    <t>Ferenc körút</t>
+  </si>
+  <si>
+    <t>305461842/2</t>
+  </si>
+  <si>
+    <t>305462350/1</t>
+  </si>
+  <si>
+    <t>305462350</t>
+  </si>
+  <si>
+    <t>Gyáli Út</t>
+  </si>
+  <si>
+    <t>305514164/1</t>
+  </si>
+  <si>
+    <t>305514164</t>
+  </si>
+  <si>
+    <t>1142</t>
+  </si>
+  <si>
+    <t>Sárrét park</t>
+  </si>
+  <si>
+    <t>305514179/1</t>
+  </si>
+  <si>
+    <t>305514179</t>
+  </si>
+  <si>
+    <t>1172</t>
+  </si>
+  <si>
+    <t>Hidasnémeti utca</t>
+  </si>
+  <si>
+    <t>305514421/1</t>
+  </si>
+  <si>
+    <t>305514421</t>
+  </si>
+  <si>
+    <t>Cziffra György utca</t>
+  </si>
+  <si>
+    <t>305514421/2</t>
+  </si>
+  <si>
+    <t>305514421/3</t>
+  </si>
+  <si>
+    <t>305514425/1</t>
+  </si>
+  <si>
+    <t>305514425</t>
+  </si>
+  <si>
+    <t>Márton utca</t>
+  </si>
+  <si>
+    <t>305514520/1</t>
+  </si>
+  <si>
+    <t>305514520</t>
+  </si>
+  <si>
+    <t>Batthyány utca</t>
+  </si>
+  <si>
+    <t>305514591/1</t>
+  </si>
+  <si>
+    <t>305514591</t>
+  </si>
+  <si>
+    <t>2241</t>
+  </si>
+  <si>
+    <t>SÜLYSÁP</t>
+  </si>
+  <si>
+    <t>Vak Bottyán Utca</t>
+  </si>
+  <si>
+    <t>305556937/1</t>
+  </si>
+  <si>
+    <t>305556937</t>
+  </si>
+  <si>
+    <t>Fészekrakó utca</t>
+  </si>
+  <si>
+    <t>305557043/1</t>
+  </si>
+  <si>
+    <t>305557043</t>
+  </si>
+  <si>
+    <t>2740</t>
+  </si>
+  <si>
+    <t>ABONY</t>
+  </si>
+  <si>
+    <t>Nép út</t>
+  </si>
+  <si>
+    <t>305557043/2</t>
+  </si>
+  <si>
+    <t>305557076/1</t>
+  </si>
+  <si>
+    <t>305557076</t>
+  </si>
+  <si>
+    <t>1135</t>
+  </si>
+  <si>
+    <t>Frangepán utca</t>
+  </si>
+  <si>
+    <t>305557116/1</t>
+  </si>
+  <si>
+    <t>305557116</t>
+  </si>
+  <si>
+    <t>Ciprus utca</t>
+  </si>
+  <si>
+    <t>305557116/2</t>
+  </si>
+  <si>
+    <t>305557116/3</t>
+  </si>
+  <si>
+    <t>305557127/1</t>
+  </si>
+  <si>
+    <t>305557127</t>
+  </si>
+  <si>
+    <t>Thaly Kálmán utca</t>
+  </si>
+  <si>
+    <t>305557206/1</t>
+  </si>
+  <si>
+    <t>305557206</t>
+  </si>
+  <si>
+    <t>1036</t>
+  </si>
+  <si>
+    <t>Pacsirtamező utca</t>
+  </si>
+  <si>
+    <t>305557206/2</t>
+  </si>
+  <si>
+    <t>305557240/1</t>
+  </si>
+  <si>
+    <t>305557240</t>
+  </si>
+  <si>
+    <t>305557457/1</t>
+  </si>
+  <si>
+    <t>305557457</t>
+  </si>
+  <si>
+    <t>Huszka Jenő utca</t>
+  </si>
+  <si>
+    <t>305557485/1</t>
+  </si>
+  <si>
+    <t>305557485</t>
+  </si>
+  <si>
+    <t>Kolozsvári Utca</t>
+  </si>
+  <si>
+    <t>305557510/1</t>
+  </si>
+  <si>
+    <t>305557510</t>
+  </si>
+  <si>
+    <t>2335</t>
+  </si>
+  <si>
+    <t>TAKSONY</t>
+  </si>
+  <si>
+    <t>Bugyi út</t>
+  </si>
+  <si>
+    <t>305557510/2</t>
+  </si>
+  <si>
+    <t>305557607/1</t>
+  </si>
+  <si>
+    <t>305557607</t>
+  </si>
+  <si>
+    <t>2084</t>
+  </si>
+  <si>
+    <t>PILISSZENTIVÁN</t>
+  </si>
+  <si>
+    <t>305557607/2</t>
+  </si>
+  <si>
+    <t>305557633/1</t>
+  </si>
+  <si>
+    <t>305557633</t>
+  </si>
+  <si>
+    <t>1046</t>
+  </si>
+  <si>
+    <t>Klauzál utca</t>
+  </si>
+  <si>
+    <t>305557678/1</t>
+  </si>
+  <si>
+    <t>305557678</t>
+  </si>
+  <si>
+    <t>Egressy Béni utca</t>
+  </si>
+  <si>
+    <t>305557697/1</t>
+  </si>
+  <si>
+    <t>305557697</t>
+  </si>
+  <si>
+    <t>1029</t>
+  </si>
+  <si>
+    <t>Zerind vezér utca</t>
+  </si>
+  <si>
+    <t>305557707/1</t>
+  </si>
+  <si>
+    <t>305557707</t>
+  </si>
+  <si>
+    <t>2217</t>
+  </si>
+  <si>
+    <t>GOMBA</t>
+  </si>
+  <si>
+    <t>Külterület kültelek</t>
+  </si>
+  <si>
+    <t>305627959/1</t>
+  </si>
+  <si>
+    <t>305627959</t>
+  </si>
+  <si>
+    <t>Vasvári Pál utca</t>
+  </si>
+  <si>
+    <t>305627959/2</t>
+  </si>
+  <si>
+    <t>305628104/1</t>
+  </si>
+  <si>
+    <t>305628104</t>
+  </si>
+  <si>
+    <t>305628296/1</t>
+  </si>
+  <si>
+    <t>305628296</t>
+  </si>
+  <si>
+    <t>1132</t>
+  </si>
+  <si>
+    <t>Gyöngyház utca</t>
+  </si>
+  <si>
+    <t>305628296/2</t>
+  </si>
+  <si>
+    <t>305628358/1</t>
+  </si>
+  <si>
+    <t>305628358</t>
+  </si>
+  <si>
+    <t>2209</t>
+  </si>
+  <si>
+    <t>PÉTERI</t>
+  </si>
+  <si>
+    <t>Ady Endre utca</t>
+  </si>
+  <si>
+    <t>305628390/1</t>
+  </si>
+  <si>
+    <t>305628390</t>
+  </si>
+  <si>
+    <t>Havanna utca</t>
+  </si>
+  <si>
+    <t>305628560/1</t>
+  </si>
+  <si>
+    <t>305628560</t>
+  </si>
+  <si>
+    <t>1088</t>
+  </si>
+  <si>
+    <t>Krúdy Gyula utca</t>
+  </si>
+  <si>
+    <t>305628668/1</t>
+  </si>
+  <si>
+    <t>305628668</t>
+  </si>
+  <si>
+    <t>Diósy Lajos Utca</t>
+  </si>
+  <si>
+    <t>305628708/1</t>
+  </si>
+  <si>
+    <t>305628708</t>
+  </si>
+  <si>
+    <t>1205</t>
+  </si>
+  <si>
+    <t>Bádogos utca</t>
+  </si>
+  <si>
+    <t>305628716/1</t>
+  </si>
+  <si>
+    <t>305628716</t>
+  </si>
+  <si>
+    <t>József Attila útja</t>
+  </si>
+  <si>
+    <t>305628794/1</t>
+  </si>
+  <si>
+    <t>305628794</t>
+  </si>
+  <si>
+    <t>1054</t>
+  </si>
+  <si>
+    <t>Vadász utca</t>
+  </si>
+  <si>
+    <t>305666953/1</t>
+  </si>
+  <si>
+    <t>305666953</t>
+  </si>
+  <si>
+    <t>1195</t>
+  </si>
+  <si>
+    <t>Zrínyi utca</t>
+  </si>
+  <si>
+    <t>305666958/1</t>
+  </si>
+  <si>
+    <t>305666958</t>
+  </si>
+  <si>
+    <t>2191</t>
+  </si>
+  <si>
+    <t>BAG</t>
+  </si>
+  <si>
+    <t>Malom utca</t>
+  </si>
+  <si>
+    <t>305666958/2</t>
+  </si>
+  <si>
+    <t>305667035/1</t>
+  </si>
+  <si>
+    <t>305667035</t>
+  </si>
+  <si>
+    <t>Zólyomi út</t>
+  </si>
+  <si>
+    <t>305667035/2</t>
+  </si>
+  <si>
+    <t>305667066/1</t>
+  </si>
+  <si>
+    <t>305667066</t>
+  </si>
+  <si>
+    <t>305667140/1</t>
+  </si>
+  <si>
+    <t>305667140</t>
+  </si>
+  <si>
+    <t>2083</t>
+  </si>
+  <si>
+    <t>SOLYMÁR</t>
+  </si>
+  <si>
+    <t>Hóvirág utca</t>
+  </si>
+  <si>
+    <t>305667140/2</t>
+  </si>
+  <si>
+    <t>305667140/3</t>
+  </si>
+  <si>
+    <t>305667163/1</t>
+  </si>
+  <si>
+    <t>305667163</t>
+  </si>
+  <si>
+    <t>1027</t>
+  </si>
+  <si>
+    <t>Frankel Leó út</t>
+  </si>
+  <si>
+    <t>305667360/1</t>
+  </si>
+  <si>
+    <t>305667360</t>
+  </si>
+  <si>
+    <t>2337</t>
+  </si>
+  <si>
+    <t>DÉLEGYHÁZA</t>
+  </si>
+  <si>
+    <t>Dózsa György utca</t>
+  </si>
+  <si>
+    <t>202603262600668601</t>
+  </si>
+  <si>
+    <t>NFD6-03-19-Z3KA</t>
+  </si>
+  <si>
+    <t>Üllői út</t>
+  </si>
+  <si>
+    <t>202603262600677301</t>
+  </si>
+  <si>
+    <t>NFD6-03-20-Q6RK</t>
+  </si>
+  <si>
+    <t>Vihorlát út</t>
+  </si>
+  <si>
+    <t>202603242600707601</t>
+  </si>
+  <si>
+    <t>NFD6-03-23-PHCH</t>
+  </si>
+  <si>
+    <t>202603252600719101</t>
+  </si>
+  <si>
+    <t>NFD6-03-24-JSVU</t>
+  </si>
+  <si>
+    <t>1164</t>
+  </si>
+  <si>
+    <t>Lucernás utca</t>
+  </si>
+  <si>
+    <t>202603262600724901</t>
+  </si>
+  <si>
+    <t>NFD6-03-25-485U</t>
+  </si>
+  <si>
+    <t>Eperjes utca</t>
+  </si>
+  <si>
+    <t>202603262600725601</t>
+  </si>
+  <si>
+    <t>NFD6-03-25-4UM4</t>
+  </si>
+  <si>
+    <t>2011</t>
+  </si>
+  <si>
+    <t>BUDAKALÁSZ</t>
+  </si>
+  <si>
+    <t>Jókai Mór utca</t>
+  </si>
+  <si>
+    <t>202603262600725602</t>
+  </si>
+  <si>
+    <t>202603262600725301</t>
+  </si>
+  <si>
+    <t>NFD6-03-25-988N</t>
+  </si>
+  <si>
+    <t>Kerektó utca</t>
+  </si>
+  <si>
+    <t>202603262600730601</t>
+  </si>
+  <si>
+    <t>NFD6-03-25-R44V</t>
+  </si>
+  <si>
+    <t>202603232600686301</t>
+  </si>
+  <si>
+    <t>NFE6-03-21-2C5Z</t>
+  </si>
+  <si>
+    <t>1211</t>
+  </si>
+  <si>
+    <t>II. Rákóczi Ferenc út</t>
+  </si>
+  <si>
+    <t>202603232600686302</t>
+  </si>
+  <si>
+    <t>202603252600718501</t>
+  </si>
+  <si>
+    <t>NFE6-03-24-DK5Y</t>
+  </si>
+  <si>
+    <t>202603262600724401</t>
+  </si>
+  <si>
+    <t>NFE6-03-25-2DQ7</t>
+  </si>
+  <si>
+    <t>Balaton utca</t>
+  </si>
+  <si>
+    <t>202603262600730901</t>
+  </si>
+  <si>
+    <t>NFE6-03-25-BG7K</t>
+  </si>
+  <si>
+    <t>2013</t>
+  </si>
+  <si>
+    <t>POMÁZ</t>
+  </si>
+  <si>
+    <t>Szentendrei út</t>
+  </si>
+  <si>
+    <t>202603262600730902</t>
+  </si>
+  <si>
+    <t>159995579538580253</t>
+  </si>
+  <si>
+    <t>R414292</t>
+  </si>
+  <si>
+    <t>Ba-Ko köz</t>
+  </si>
+  <si>
+    <t>INSPORT</t>
+  </si>
+  <si>
+    <t>159995579538580260</t>
+  </si>
+  <si>
+    <t>159995579538580314</t>
+  </si>
+  <si>
+    <t>SZ 2026 137593</t>
+  </si>
+  <si>
+    <t>1084</t>
+  </si>
+  <si>
+    <t>Rákóczi tér</t>
+  </si>
+  <si>
+    <t>159995579538580321</t>
   </si>
 </sst>
 </file>
@@ -2179,83 +1864,83 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <sheetPr codeName="Munka1"/>
-  <dimension ref="A1:H173"/>
+  <dimension ref="A1:H150"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="25.44140625" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="24.88671875" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="9.109375"/>
     <col min="3" max="3" width="6.88671875" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="22.77734375" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="20.109375" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="5" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="20" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="34.6640625" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="34.109375" bestFit="1" customWidth="1"/>
     <col min="8" max="8" width="19.88671875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
-        <v>118</v>
+        <v>54</v>
       </c>
       <c r="C1" t="s">
-        <v>119</v>
+        <v>55</v>
       </c>
       <c r="D1" t="s">
-        <v>120</v>
+        <v>56</v>
       </c>
       <c r="E1" t="s">
-        <v>121</v>
+        <v>57</v>
       </c>
       <c r="F1" t="s">
-        <v>122</v>
+        <v>58</v>
       </c>
       <c r="G1" t="s">
-        <v>123</v>
+        <v>59</v>
       </c>
       <c r="H1" t="s">
-        <v>124</v>
+        <v>60</v>
       </c>
     </row>
     <row r="2" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
-        <v>125</v>
+        <v>95</v>
       </c>
       <c r="C2" t="s">
-        <v>34</v>
+        <v>10</v>
       </c>
       <c r="D2" t="s">
-        <v>126</v>
+        <v>96</v>
       </c>
       <c r="E2" t="s">
-        <v>127</v>
+        <v>97</v>
       </c>
       <c r="F2" t="s">
-        <v>128</v>
+        <v>0</v>
       </c>
       <c r="G2" t="s">
-        <v>129</v>
+        <v>98</v>
       </c>
       <c r="H2" t="s">
-        <v>1</v>
+        <v>4</v>
       </c>
     </row>
     <row r="3" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
-        <v>130</v>
+        <v>99</v>
       </c>
       <c r="C3" t="s">
-        <v>29</v>
+        <v>3</v>
       </c>
       <c r="D3" t="s">
-        <v>131</v>
+        <v>100</v>
       </c>
       <c r="E3" t="s">
-        <v>132</v>
+        <v>101</v>
       </c>
       <c r="F3" t="s">
-        <v>0</v>
+        <v>102</v>
       </c>
       <c r="G3" t="s">
-        <v>133</v>
+        <v>87</v>
       </c>
       <c r="H3" t="s">
         <v>1</v>
@@ -2263,22 +1948,22 @@
     </row>
     <row r="4" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
-        <v>134</v>
+        <v>103</v>
       </c>
       <c r="C4" t="s">
-        <v>13</v>
+        <v>104</v>
       </c>
       <c r="D4" t="s">
-        <v>135</v>
+        <v>105</v>
       </c>
       <c r="E4" t="s">
-        <v>90</v>
+        <v>106</v>
       </c>
       <c r="F4" t="s">
-        <v>91</v>
+        <v>0</v>
       </c>
       <c r="G4" t="s">
-        <v>136</v>
+        <v>107</v>
       </c>
       <c r="H4" t="s">
         <v>1</v>
@@ -2286,22 +1971,22 @@
     </row>
     <row r="5" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
-        <v>137</v>
+        <v>108</v>
       </c>
       <c r="C5" t="s">
-        <v>13</v>
+        <v>2</v>
       </c>
       <c r="D5" t="s">
-        <v>138</v>
+        <v>109</v>
       </c>
       <c r="E5" t="s">
-        <v>48</v>
+        <v>110</v>
       </c>
       <c r="F5" t="s">
-        <v>49</v>
+        <v>111</v>
       </c>
       <c r="G5" t="s">
-        <v>139</v>
+        <v>112</v>
       </c>
       <c r="H5" t="s">
         <v>1</v>
@@ -2309,22 +1994,22 @@
     </row>
     <row r="6" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
-        <v>140</v>
+        <v>62</v>
       </c>
       <c r="C6" t="s">
-        <v>11</v>
+        <v>24</v>
       </c>
       <c r="D6" t="s">
-        <v>141</v>
+        <v>63</v>
       </c>
       <c r="E6" t="s">
-        <v>73</v>
+        <v>47</v>
       </c>
       <c r="F6" t="s">
         <v>0</v>
       </c>
       <c r="G6" t="s">
-        <v>142</v>
+        <v>64</v>
       </c>
       <c r="H6" t="s">
         <v>1</v>
@@ -2332,22 +2017,22 @@
     </row>
     <row r="7" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
-        <v>143</v>
+        <v>113</v>
       </c>
       <c r="C7" t="s">
-        <v>2</v>
+        <v>24</v>
       </c>
       <c r="D7" t="s">
-        <v>144</v>
+        <v>114</v>
       </c>
       <c r="E7" t="s">
-        <v>103</v>
+        <v>6</v>
       </c>
       <c r="F7" t="s">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="G7" t="s">
-        <v>145</v>
+        <v>115</v>
       </c>
       <c r="H7" t="s">
         <v>1</v>
@@ -2355,22 +2040,22 @@
     </row>
     <row r="8" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
-        <v>146</v>
+        <v>116</v>
       </c>
       <c r="C8" t="s">
-        <v>3</v>
+        <v>24</v>
       </c>
       <c r="D8" t="s">
-        <v>147</v>
+        <v>117</v>
       </c>
       <c r="E8" t="s">
-        <v>148</v>
+        <v>118</v>
       </c>
       <c r="F8" t="s">
-        <v>0</v>
+        <v>33</v>
       </c>
       <c r="G8" t="s">
-        <v>149</v>
+        <v>119</v>
       </c>
       <c r="H8" t="s">
         <v>1</v>
@@ -2378,22 +2063,22 @@
     </row>
     <row r="9" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
-        <v>150</v>
+        <v>120</v>
       </c>
       <c r="C9" t="s">
-        <v>11</v>
+        <v>24</v>
       </c>
       <c r="D9" t="s">
-        <v>151</v>
+        <v>121</v>
       </c>
       <c r="E9" t="s">
-        <v>152</v>
+        <v>27</v>
       </c>
       <c r="F9" t="s">
-        <v>0</v>
+        <v>28</v>
       </c>
       <c r="G9" t="s">
-        <v>153</v>
+        <v>122</v>
       </c>
       <c r="H9" t="s">
         <v>1</v>
@@ -2401,22 +2086,22 @@
     </row>
     <row r="10" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
-        <v>154</v>
+        <v>123</v>
       </c>
       <c r="C10" t="s">
-        <v>155</v>
+        <v>23</v>
       </c>
       <c r="D10" t="s">
-        <v>156</v>
+        <v>124</v>
       </c>
       <c r="E10" t="s">
-        <v>20</v>
+        <v>125</v>
       </c>
       <c r="F10" t="s">
-        <v>21</v>
+        <v>126</v>
       </c>
       <c r="G10" t="s">
-        <v>157</v>
+        <v>115</v>
       </c>
       <c r="H10" t="s">
         <v>1</v>
@@ -2424,22 +2109,22 @@
     </row>
     <row r="11" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A11" t="s">
-        <v>158</v>
+        <v>127</v>
       </c>
       <c r="C11" t="s">
-        <v>22</v>
+        <v>12</v>
       </c>
       <c r="D11" t="s">
-        <v>159</v>
+        <v>128</v>
       </c>
       <c r="E11" t="s">
-        <v>95</v>
+        <v>129</v>
       </c>
       <c r="F11" t="s">
         <v>0</v>
       </c>
       <c r="G11" t="s">
-        <v>96</v>
+        <v>130</v>
       </c>
       <c r="H11" t="s">
         <v>1</v>
@@ -2447,22 +2132,22 @@
     </row>
     <row r="12" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A12" t="s">
-        <v>160</v>
+        <v>65</v>
       </c>
       <c r="C12" t="s">
-        <v>22</v>
+        <v>12</v>
       </c>
       <c r="D12" t="s">
-        <v>159</v>
+        <v>66</v>
       </c>
       <c r="E12" t="s">
-        <v>95</v>
+        <v>67</v>
       </c>
       <c r="F12" t="s">
         <v>0</v>
       </c>
       <c r="G12" t="s">
-        <v>96</v>
+        <v>68</v>
       </c>
       <c r="H12" t="s">
         <v>1</v>
@@ -2470,22 +2155,22 @@
     </row>
     <row r="13" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A13" t="s">
-        <v>161</v>
+        <v>73</v>
       </c>
       <c r="C13" t="s">
-        <v>13</v>
+        <v>24</v>
       </c>
       <c r="D13" t="s">
-        <v>162</v>
+        <v>74</v>
       </c>
       <c r="E13" t="s">
-        <v>114</v>
+        <v>27</v>
       </c>
       <c r="F13" t="s">
-        <v>115</v>
+        <v>28</v>
       </c>
       <c r="G13" t="s">
-        <v>163</v>
+        <v>75</v>
       </c>
       <c r="H13" t="s">
         <v>1</v>
@@ -2493,22 +2178,22 @@
     </row>
     <row r="14" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A14" t="s">
-        <v>164</v>
+        <v>131</v>
       </c>
       <c r="C14" t="s">
-        <v>35</v>
+        <v>104</v>
       </c>
       <c r="D14" t="s">
-        <v>165</v>
+        <v>132</v>
       </c>
       <c r="E14" t="s">
-        <v>65</v>
+        <v>133</v>
       </c>
       <c r="F14" t="s">
-        <v>66</v>
+        <v>0</v>
       </c>
       <c r="G14" t="s">
-        <v>166</v>
+        <v>134</v>
       </c>
       <c r="H14" t="s">
         <v>1</v>
@@ -2516,22 +2201,22 @@
     </row>
     <row r="15" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A15" t="s">
-        <v>167</v>
+        <v>135</v>
       </c>
       <c r="C15" t="s">
-        <v>29</v>
+        <v>26</v>
       </c>
       <c r="D15" t="s">
-        <v>168</v>
+        <v>136</v>
       </c>
       <c r="E15" t="s">
-        <v>169</v>
+        <v>137</v>
       </c>
       <c r="F15" t="s">
-        <v>170</v>
+        <v>138</v>
       </c>
       <c r="G15" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="H15" t="s">
         <v>1</v>
@@ -2539,22 +2224,22 @@
     </row>
     <row r="16" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A16" t="s">
-        <v>171</v>
+        <v>139</v>
       </c>
       <c r="C16" t="s">
-        <v>3</v>
+        <v>26</v>
       </c>
       <c r="D16" t="s">
-        <v>172</v>
+        <v>136</v>
       </c>
       <c r="E16" t="s">
-        <v>148</v>
+        <v>137</v>
       </c>
       <c r="F16" t="s">
-        <v>0</v>
+        <v>138</v>
       </c>
       <c r="G16" t="s">
-        <v>173</v>
+        <v>115</v>
       </c>
       <c r="H16" t="s">
         <v>1</v>
@@ -2562,22 +2247,22 @@
     </row>
     <row r="17" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A17" t="s">
-        <v>174</v>
+        <v>140</v>
       </c>
       <c r="C17" t="s">
-        <v>13</v>
+        <v>24</v>
       </c>
       <c r="D17" t="s">
-        <v>175</v>
+        <v>141</v>
       </c>
       <c r="E17" t="s">
-        <v>176</v>
+        <v>118</v>
       </c>
       <c r="F17" t="s">
-        <v>177</v>
+        <v>33</v>
       </c>
       <c r="G17" t="s">
-        <v>178</v>
+        <v>142</v>
       </c>
       <c r="H17" t="s">
         <v>1</v>
@@ -2585,22 +2270,22 @@
     </row>
     <row r="18" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A18" t="s">
-        <v>179</v>
+        <v>143</v>
       </c>
       <c r="C18" t="s">
-        <v>13</v>
+        <v>24</v>
       </c>
       <c r="D18" t="s">
-        <v>175</v>
+        <v>144</v>
       </c>
       <c r="E18" t="s">
-        <v>176</v>
+        <v>27</v>
       </c>
       <c r="F18" t="s">
-        <v>177</v>
+        <v>28</v>
       </c>
       <c r="G18" t="s">
-        <v>178</v>
+        <v>145</v>
       </c>
       <c r="H18" t="s">
         <v>1</v>
@@ -2608,22 +2293,22 @@
     </row>
     <row r="19" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A19" t="s">
-        <v>180</v>
+        <v>146</v>
       </c>
       <c r="C19" t="s">
-        <v>14</v>
+        <v>24</v>
       </c>
       <c r="D19" t="s">
-        <v>181</v>
+        <v>144</v>
       </c>
       <c r="E19" t="s">
-        <v>77</v>
+        <v>27</v>
       </c>
       <c r="F19" t="s">
-        <v>0</v>
+        <v>28</v>
       </c>
       <c r="G19" t="s">
-        <v>182</v>
+        <v>145</v>
       </c>
       <c r="H19" t="s">
         <v>1</v>
@@ -2631,22 +2316,22 @@
     </row>
     <row r="20" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A20" t="s">
-        <v>183</v>
+        <v>147</v>
       </c>
       <c r="C20" t="s">
-        <v>25</v>
+        <v>8</v>
       </c>
       <c r="D20" t="s">
-        <v>184</v>
+        <v>148</v>
       </c>
       <c r="E20" t="s">
-        <v>16</v>
+        <v>88</v>
       </c>
       <c r="F20" t="s">
-        <v>17</v>
+        <v>89</v>
       </c>
       <c r="G20" t="s">
-        <v>185</v>
+        <v>149</v>
       </c>
       <c r="H20" t="s">
         <v>1</v>
@@ -2654,22 +2339,22 @@
     </row>
     <row r="21" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A21" t="s">
-        <v>186</v>
+        <v>150</v>
       </c>
       <c r="C21" t="s">
-        <v>9</v>
+        <v>26</v>
       </c>
       <c r="D21" t="s">
-        <v>187</v>
+        <v>151</v>
       </c>
       <c r="E21" t="s">
-        <v>36</v>
+        <v>152</v>
       </c>
       <c r="F21" t="s">
-        <v>37</v>
+        <v>153</v>
       </c>
       <c r="G21" t="s">
-        <v>188</v>
+        <v>154</v>
       </c>
       <c r="H21" t="s">
         <v>1</v>
@@ -2677,22 +2362,22 @@
     </row>
     <row r="22" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A22" t="s">
-        <v>189</v>
+        <v>155</v>
       </c>
       <c r="C22" t="s">
-        <v>9</v>
+        <v>38</v>
       </c>
       <c r="D22" t="s">
-        <v>190</v>
+        <v>156</v>
       </c>
       <c r="E22" t="s">
-        <v>7</v>
+        <v>157</v>
       </c>
       <c r="F22" t="s">
-        <v>8</v>
+        <v>158</v>
       </c>
       <c r="G22" t="s">
-        <v>191</v>
+        <v>46</v>
       </c>
       <c r="H22" t="s">
         <v>1</v>
@@ -2700,22 +2385,22 @@
     </row>
     <row r="23" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A23" t="s">
-        <v>192</v>
+        <v>159</v>
       </c>
       <c r="C23" t="s">
-        <v>9</v>
+        <v>38</v>
       </c>
       <c r="D23" t="s">
-        <v>193</v>
+        <v>156</v>
       </c>
       <c r="E23" t="s">
-        <v>93</v>
+        <v>157</v>
       </c>
       <c r="F23" t="s">
-        <v>0</v>
+        <v>158</v>
       </c>
       <c r="G23" t="s">
-        <v>194</v>
+        <v>46</v>
       </c>
       <c r="H23" t="s">
         <v>1</v>
@@ -2723,22 +2408,22 @@
     </row>
     <row r="24" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A24" t="s">
-        <v>195</v>
+        <v>160</v>
       </c>
       <c r="C24" t="s">
-        <v>3</v>
+        <v>38</v>
       </c>
       <c r="D24" t="s">
-        <v>196</v>
+        <v>156</v>
       </c>
       <c r="E24" t="s">
-        <v>80</v>
+        <v>157</v>
       </c>
       <c r="F24" t="s">
-        <v>0</v>
+        <v>158</v>
       </c>
       <c r="G24" t="s">
-        <v>197</v>
+        <v>46</v>
       </c>
       <c r="H24" t="s">
         <v>1</v>
@@ -2746,22 +2431,22 @@
     </row>
     <row r="25" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A25" t="s">
-        <v>198</v>
+        <v>161</v>
       </c>
       <c r="C25" t="s">
-        <v>155</v>
+        <v>19</v>
       </c>
       <c r="D25" t="s">
-        <v>199</v>
+        <v>162</v>
       </c>
       <c r="E25" t="s">
-        <v>23</v>
+        <v>163</v>
       </c>
       <c r="F25" t="s">
-        <v>24</v>
+        <v>0</v>
       </c>
       <c r="G25" t="s">
-        <v>200</v>
+        <v>164</v>
       </c>
       <c r="H25" t="s">
         <v>1</v>
@@ -2769,22 +2454,22 @@
     </row>
     <row r="26" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A26" t="s">
-        <v>201</v>
+        <v>165</v>
       </c>
       <c r="C26" t="s">
-        <v>13</v>
+        <v>19</v>
       </c>
       <c r="D26" t="s">
-        <v>202</v>
+        <v>162</v>
       </c>
       <c r="E26" t="s">
-        <v>203</v>
+        <v>163</v>
       </c>
       <c r="F26" t="s">
-        <v>204</v>
+        <v>0</v>
       </c>
       <c r="G26" t="s">
-        <v>205</v>
+        <v>164</v>
       </c>
       <c r="H26" t="s">
         <v>1</v>
@@ -2792,22 +2477,22 @@
     </row>
     <row r="27" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A27" t="s">
-        <v>206</v>
+        <v>76</v>
       </c>
       <c r="C27" t="s">
-        <v>13</v>
+        <v>19</v>
       </c>
       <c r="D27" t="s">
-        <v>202</v>
+        <v>77</v>
       </c>
       <c r="E27" t="s">
-        <v>203</v>
+        <v>61</v>
       </c>
       <c r="F27" t="s">
-        <v>204</v>
+        <v>0</v>
       </c>
       <c r="G27" t="s">
-        <v>205</v>
+        <v>78</v>
       </c>
       <c r="H27" t="s">
         <v>1</v>
@@ -2815,22 +2500,22 @@
     </row>
     <row r="28" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A28" t="s">
-        <v>207</v>
+        <v>166</v>
       </c>
       <c r="C28" t="s">
-        <v>155</v>
+        <v>8</v>
       </c>
       <c r="D28" t="s">
-        <v>208</v>
+        <v>167</v>
       </c>
       <c r="E28" t="s">
-        <v>27</v>
+        <v>44</v>
       </c>
       <c r="F28" t="s">
-        <v>28</v>
+        <v>45</v>
       </c>
       <c r="G28" t="s">
-        <v>209</v>
+        <v>168</v>
       </c>
       <c r="H28" t="s">
         <v>1</v>
@@ -2838,22 +2523,22 @@
     </row>
     <row r="29" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A29" t="s">
-        <v>210</v>
+        <v>169</v>
       </c>
       <c r="C29" t="s">
-        <v>155</v>
+        <v>22</v>
       </c>
       <c r="D29" t="s">
-        <v>208</v>
+        <v>170</v>
       </c>
       <c r="E29" t="s">
-        <v>27</v>
+        <v>37</v>
       </c>
       <c r="F29" t="s">
-        <v>28</v>
+        <v>0</v>
       </c>
       <c r="G29" t="s">
-        <v>209</v>
+        <v>171</v>
       </c>
       <c r="H29" t="s">
         <v>1</v>
@@ -2861,22 +2546,22 @@
     </row>
     <row r="30" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A30" t="s">
-        <v>211</v>
+        <v>172</v>
       </c>
       <c r="C30" t="s">
-        <v>35</v>
+        <v>38</v>
       </c>
       <c r="D30" t="s">
-        <v>212</v>
+        <v>173</v>
       </c>
       <c r="E30" t="s">
-        <v>213</v>
+        <v>43</v>
       </c>
       <c r="F30" t="s">
-        <v>214</v>
+        <v>0</v>
       </c>
       <c r="G30" t="s">
-        <v>215</v>
+        <v>174</v>
       </c>
       <c r="H30" t="s">
         <v>1</v>
@@ -2884,22 +2569,22 @@
     </row>
     <row r="31" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A31" t="s">
-        <v>216</v>
+        <v>175</v>
       </c>
       <c r="C31" t="s">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="D31" t="s">
-        <v>217</v>
+        <v>176</v>
       </c>
       <c r="E31" t="s">
-        <v>218</v>
+        <v>50</v>
       </c>
       <c r="F31" t="s">
-        <v>219</v>
+        <v>0</v>
       </c>
       <c r="G31" t="s">
-        <v>58</v>
+        <v>177</v>
       </c>
       <c r="H31" t="s">
         <v>1</v>
@@ -2907,22 +2592,22 @@
     </row>
     <row r="32" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A32" t="s">
-        <v>220</v>
+        <v>178</v>
       </c>
       <c r="C32" t="s">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="D32" t="s">
-        <v>221</v>
+        <v>179</v>
       </c>
       <c r="E32" t="s">
-        <v>222</v>
+        <v>25</v>
       </c>
       <c r="F32" t="s">
-        <v>223</v>
+        <v>0</v>
       </c>
       <c r="G32" t="s">
-        <v>224</v>
+        <v>180</v>
       </c>
       <c r="H32" t="s">
         <v>1</v>
@@ -2930,22 +2615,22 @@
     </row>
     <row r="33" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A33" t="s">
-        <v>225</v>
+        <v>181</v>
       </c>
       <c r="C33" t="s">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="D33" t="s">
-        <v>221</v>
+        <v>182</v>
       </c>
       <c r="E33" t="s">
-        <v>222</v>
+        <v>42</v>
       </c>
       <c r="F33" t="s">
-        <v>223</v>
+        <v>0</v>
       </c>
       <c r="G33" t="s">
-        <v>224</v>
+        <v>183</v>
       </c>
       <c r="H33" t="s">
         <v>1</v>
@@ -2953,22 +2638,22 @@
     </row>
     <row r="34" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A34" t="s">
-        <v>226</v>
+        <v>184</v>
       </c>
       <c r="C34" t="s">
-        <v>6</v>
+        <v>185</v>
       </c>
       <c r="D34" t="s">
-        <v>227</v>
+        <v>186</v>
       </c>
       <c r="E34" t="s">
-        <v>228</v>
+        <v>187</v>
       </c>
       <c r="F34" t="s">
-        <v>229</v>
+        <v>0</v>
       </c>
       <c r="G34" t="s">
-        <v>230</v>
+        <v>188</v>
       </c>
       <c r="H34" t="s">
         <v>1</v>
@@ -2976,22 +2661,22 @@
     </row>
     <row r="35" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A35" t="s">
-        <v>231</v>
+        <v>189</v>
       </c>
       <c r="C35" t="s">
-        <v>13</v>
+        <v>3</v>
       </c>
       <c r="D35" t="s">
-        <v>232</v>
+        <v>190</v>
       </c>
       <c r="E35" t="s">
-        <v>233</v>
+        <v>191</v>
       </c>
       <c r="F35" t="s">
-        <v>234</v>
+        <v>0</v>
       </c>
       <c r="G35" t="s">
-        <v>235</v>
+        <v>192</v>
       </c>
       <c r="H35" t="s">
         <v>1</v>
@@ -2999,22 +2684,22 @@
     </row>
     <row r="36" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A36" t="s">
-        <v>236</v>
+        <v>193</v>
       </c>
       <c r="C36" t="s">
-        <v>34</v>
+        <v>19</v>
       </c>
       <c r="D36" t="s">
-        <v>237</v>
+        <v>194</v>
       </c>
       <c r="E36" t="s">
-        <v>238</v>
+        <v>163</v>
       </c>
       <c r="F36" t="s">
-        <v>239</v>
+        <v>0</v>
       </c>
       <c r="G36" t="s">
-        <v>240</v>
+        <v>195</v>
       </c>
       <c r="H36" t="s">
         <v>1</v>
@@ -3022,22 +2707,22 @@
     </row>
     <row r="37" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A37" t="s">
-        <v>241</v>
+        <v>196</v>
       </c>
       <c r="C37" t="s">
-        <v>12</v>
+        <v>22</v>
       </c>
       <c r="D37" t="s">
-        <v>242</v>
+        <v>197</v>
       </c>
       <c r="E37" t="s">
-        <v>26</v>
+        <v>48</v>
       </c>
       <c r="F37" t="s">
         <v>0</v>
       </c>
       <c r="G37" t="s">
-        <v>243</v>
+        <v>198</v>
       </c>
       <c r="H37" t="s">
         <v>1</v>
@@ -3045,22 +2730,22 @@
     </row>
     <row r="38" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A38" t="s">
-        <v>244</v>
+        <v>199</v>
       </c>
       <c r="C38" t="s">
-        <v>43</v>
+        <v>12</v>
       </c>
       <c r="D38" t="s">
-        <v>245</v>
+        <v>200</v>
       </c>
       <c r="E38" t="s">
-        <v>246</v>
+        <v>67</v>
       </c>
       <c r="F38" t="s">
         <v>0</v>
       </c>
       <c r="G38" t="s">
-        <v>247</v>
+        <v>201</v>
       </c>
       <c r="H38" t="s">
         <v>1</v>
@@ -3068,367 +2753,367 @@
     </row>
     <row r="39" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A39" t="s">
-        <v>248</v>
+        <v>202</v>
       </c>
       <c r="C39" t="s">
-        <v>43</v>
+        <v>23</v>
       </c>
       <c r="D39" t="s">
-        <v>245</v>
+        <v>203</v>
       </c>
       <c r="E39" t="s">
-        <v>246</v>
+        <v>204</v>
       </c>
       <c r="F39" t="s">
-        <v>0</v>
+        <v>205</v>
       </c>
       <c r="G39" t="s">
-        <v>247</v>
+        <v>206</v>
       </c>
       <c r="H39" t="s">
-        <v>1</v>
+        <v>80</v>
       </c>
     </row>
     <row r="40" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A40" t="s">
-        <v>249</v>
+        <v>207</v>
       </c>
       <c r="C40" t="s">
-        <v>11</v>
+        <v>23</v>
       </c>
       <c r="D40" t="s">
-        <v>250</v>
+        <v>208</v>
       </c>
       <c r="E40" t="s">
-        <v>101</v>
+        <v>209</v>
       </c>
       <c r="F40" t="s">
         <v>0</v>
       </c>
       <c r="G40" t="s">
-        <v>54</v>
+        <v>210</v>
       </c>
       <c r="H40" t="s">
-        <v>1</v>
+        <v>80</v>
       </c>
     </row>
     <row r="41" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A41" t="s">
-        <v>251</v>
+        <v>211</v>
       </c>
       <c r="C41" t="s">
-        <v>9</v>
+        <v>26</v>
       </c>
       <c r="D41" t="s">
-        <v>252</v>
+        <v>212</v>
       </c>
       <c r="E41" t="s">
-        <v>253</v>
+        <v>35</v>
       </c>
       <c r="F41" t="s">
-        <v>254</v>
+        <v>36</v>
       </c>
       <c r="G41" t="s">
-        <v>255</v>
+        <v>213</v>
       </c>
       <c r="H41" t="s">
-        <v>1</v>
+        <v>214</v>
       </c>
     </row>
     <row r="42" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A42" t="s">
-        <v>256</v>
+        <v>215</v>
       </c>
       <c r="C42" t="s">
-        <v>43</v>
+        <v>10</v>
       </c>
       <c r="D42" t="s">
-        <v>257</v>
+        <v>216</v>
       </c>
       <c r="E42" t="s">
-        <v>41</v>
+        <v>217</v>
       </c>
       <c r="F42" t="s">
         <v>0</v>
       </c>
       <c r="G42" t="s">
-        <v>63</v>
+        <v>218</v>
       </c>
       <c r="H42" t="s">
-        <v>1</v>
+        <v>214</v>
       </c>
     </row>
     <row r="43" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A43" t="s">
-        <v>258</v>
+        <v>219</v>
       </c>
       <c r="C43" t="s">
-        <v>43</v>
+        <v>31</v>
       </c>
       <c r="D43" t="s">
-        <v>257</v>
+        <v>220</v>
       </c>
       <c r="E43" t="s">
-        <v>41</v>
+        <v>30</v>
       </c>
       <c r="F43" t="s">
         <v>0</v>
       </c>
       <c r="G43" t="s">
-        <v>63</v>
+        <v>221</v>
       </c>
       <c r="H43" t="s">
-        <v>1</v>
+        <v>4</v>
       </c>
     </row>
     <row r="44" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A44" t="s">
-        <v>259</v>
+        <v>222</v>
       </c>
       <c r="C44" t="s">
-        <v>3</v>
+        <v>22</v>
       </c>
       <c r="D44" t="s">
-        <v>260</v>
+        <v>223</v>
       </c>
       <c r="E44" t="s">
-        <v>46</v>
+        <v>224</v>
       </c>
       <c r="F44" t="s">
         <v>0</v>
       </c>
       <c r="G44" t="s">
-        <v>261</v>
+        <v>225</v>
       </c>
       <c r="H44" t="s">
-        <v>1</v>
+        <v>4</v>
       </c>
     </row>
     <row r="45" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A45" t="s">
-        <v>262</v>
+        <v>226</v>
       </c>
       <c r="C45" t="s">
-        <v>14</v>
+        <v>22</v>
       </c>
       <c r="D45" t="s">
-        <v>263</v>
+        <v>223</v>
       </c>
       <c r="E45" t="s">
-        <v>92</v>
+        <v>224</v>
       </c>
       <c r="F45" t="s">
         <v>0</v>
       </c>
       <c r="G45" t="s">
-        <v>264</v>
+        <v>225</v>
       </c>
       <c r="H45" t="s">
-        <v>1</v>
+        <v>4</v>
       </c>
     </row>
     <row r="46" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A46" t="s">
-        <v>265</v>
+        <v>227</v>
       </c>
       <c r="C46" t="s">
-        <v>29</v>
+        <v>22</v>
       </c>
       <c r="D46" t="s">
-        <v>266</v>
+        <v>223</v>
       </c>
       <c r="E46" t="s">
-        <v>132</v>
+        <v>224</v>
       </c>
       <c r="F46" t="s">
         <v>0</v>
       </c>
       <c r="G46" t="s">
-        <v>267</v>
+        <v>225</v>
       </c>
       <c r="H46" t="s">
-        <v>1</v>
+        <v>4</v>
       </c>
     </row>
     <row r="47" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A47" t="s">
-        <v>268</v>
+        <v>81</v>
       </c>
       <c r="C47" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="D47" t="s">
-        <v>269</v>
+        <v>82</v>
       </c>
       <c r="E47" t="s">
-        <v>270</v>
+        <v>83</v>
       </c>
       <c r="F47" t="s">
         <v>0</v>
       </c>
       <c r="G47" t="s">
-        <v>271</v>
+        <v>53</v>
       </c>
       <c r="H47" t="s">
-        <v>1</v>
+        <v>4</v>
       </c>
     </row>
     <row r="48" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A48" t="s">
-        <v>272</v>
+        <v>228</v>
       </c>
       <c r="C48" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="D48" t="s">
-        <v>273</v>
+        <v>229</v>
       </c>
       <c r="E48" t="s">
-        <v>42</v>
+        <v>230</v>
       </c>
       <c r="F48" t="s">
         <v>0</v>
       </c>
       <c r="G48" t="s">
-        <v>274</v>
+        <v>231</v>
       </c>
       <c r="H48" t="s">
-        <v>1</v>
+        <v>4</v>
       </c>
     </row>
     <row r="49" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A49" t="s">
-        <v>275</v>
+        <v>232</v>
       </c>
       <c r="C49" t="s">
-        <v>32</v>
+        <v>12</v>
       </c>
       <c r="D49" t="s">
-        <v>276</v>
+        <v>233</v>
       </c>
       <c r="E49" t="s">
-        <v>64</v>
+        <v>67</v>
       </c>
       <c r="F49" t="s">
         <v>0</v>
       </c>
       <c r="G49" t="s">
-        <v>277</v>
+        <v>234</v>
       </c>
       <c r="H49" t="s">
-        <v>1</v>
+        <v>4</v>
       </c>
     </row>
     <row r="50" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A50" t="s">
-        <v>278</v>
+        <v>235</v>
       </c>
       <c r="C50" t="s">
-        <v>32</v>
+        <v>19</v>
       </c>
       <c r="D50" t="s">
-        <v>276</v>
+        <v>236</v>
       </c>
       <c r="E50" t="s">
-        <v>64</v>
+        <v>61</v>
       </c>
       <c r="F50" t="s">
         <v>0</v>
       </c>
       <c r="G50" t="s">
-        <v>277</v>
+        <v>237</v>
       </c>
       <c r="H50" t="s">
-        <v>1</v>
+        <v>4</v>
       </c>
     </row>
     <row r="51" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A51" t="s">
-        <v>279</v>
+        <v>238</v>
       </c>
       <c r="C51" t="s">
-        <v>34</v>
+        <v>19</v>
       </c>
       <c r="D51" t="s">
-        <v>280</v>
+        <v>236</v>
       </c>
       <c r="E51" t="s">
-        <v>70</v>
+        <v>61</v>
       </c>
       <c r="F51" t="s">
         <v>0</v>
       </c>
       <c r="G51" t="s">
-        <v>281</v>
+        <v>237</v>
       </c>
       <c r="H51" t="s">
-        <v>1</v>
+        <v>4</v>
       </c>
     </row>
     <row r="52" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A52" t="s">
-        <v>282</v>
+        <v>239</v>
       </c>
       <c r="C52" t="s">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="D52" t="s">
-        <v>280</v>
+        <v>240</v>
       </c>
       <c r="E52" t="s">
-        <v>70</v>
+        <v>241</v>
       </c>
       <c r="F52" t="s">
-        <v>0</v>
+        <v>242</v>
       </c>
       <c r="G52" t="s">
-        <v>281</v>
+        <v>243</v>
       </c>
       <c r="H52" t="s">
-        <v>1</v>
+        <v>4</v>
       </c>
     </row>
     <row r="53" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A53" t="s">
-        <v>283</v>
+        <v>244</v>
       </c>
       <c r="C53" t="s">
-        <v>22</v>
+        <v>38</v>
       </c>
       <c r="D53" t="s">
-        <v>284</v>
+        <v>240</v>
       </c>
       <c r="E53" t="s">
-        <v>40</v>
+        <v>241</v>
       </c>
       <c r="F53" t="s">
-        <v>0</v>
+        <v>242</v>
       </c>
       <c r="G53" t="s">
-        <v>285</v>
+        <v>243</v>
       </c>
       <c r="H53" t="s">
-        <v>286</v>
+        <v>4</v>
       </c>
     </row>
     <row r="54" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A54" t="s">
-        <v>287</v>
+        <v>245</v>
       </c>
       <c r="C54" t="s">
-        <v>9</v>
+        <v>38</v>
       </c>
       <c r="D54" t="s">
-        <v>288</v>
+        <v>240</v>
       </c>
       <c r="E54" t="s">
-        <v>7</v>
+        <v>241</v>
       </c>
       <c r="F54" t="s">
-        <v>8</v>
+        <v>242</v>
       </c>
       <c r="G54" t="s">
-        <v>289</v>
+        <v>243</v>
       </c>
       <c r="H54" t="s">
         <v>4</v>
@@ -3436,22 +3121,22 @@
     </row>
     <row r="55" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A55" t="s">
-        <v>75</v>
+        <v>246</v>
       </c>
       <c r="C55" t="s">
-        <v>14</v>
+        <v>23</v>
       </c>
       <c r="D55" t="s">
-        <v>76</v>
+        <v>247</v>
       </c>
       <c r="E55" t="s">
-        <v>77</v>
+        <v>20</v>
       </c>
       <c r="F55" t="s">
-        <v>0</v>
+        <v>21</v>
       </c>
       <c r="G55" t="s">
-        <v>78</v>
+        <v>248</v>
       </c>
       <c r="H55" t="s">
         <v>4</v>
@@ -3459,22 +3144,22 @@
     </row>
     <row r="56" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A56" t="s">
-        <v>290</v>
+        <v>249</v>
       </c>
       <c r="C56" t="s">
-        <v>34</v>
+        <v>23</v>
       </c>
       <c r="D56" t="s">
-        <v>291</v>
+        <v>247</v>
       </c>
       <c r="E56" t="s">
-        <v>292</v>
+        <v>20</v>
       </c>
       <c r="F56" t="s">
-        <v>293</v>
+        <v>21</v>
       </c>
       <c r="G56" t="s">
-        <v>294</v>
+        <v>248</v>
       </c>
       <c r="H56" t="s">
         <v>4</v>
@@ -3482,22 +3167,22 @@
     </row>
     <row r="57" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A57" t="s">
-        <v>295</v>
+        <v>250</v>
       </c>
       <c r="C57" t="s">
         <v>10</v>
       </c>
       <c r="D57" t="s">
-        <v>296</v>
+        <v>251</v>
       </c>
       <c r="E57" t="s">
-        <v>297</v>
+        <v>34</v>
       </c>
       <c r="F57" t="s">
-        <v>298</v>
+        <v>0</v>
       </c>
       <c r="G57" t="s">
-        <v>299</v>
+        <v>252</v>
       </c>
       <c r="H57" t="s">
         <v>4</v>
@@ -3505,22 +3190,22 @@
     </row>
     <row r="58" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A58" t="s">
-        <v>300</v>
+        <v>253</v>
       </c>
       <c r="C58" t="s">
-        <v>2</v>
+        <v>23</v>
       </c>
       <c r="D58" t="s">
-        <v>301</v>
+        <v>254</v>
       </c>
       <c r="E58" t="s">
-        <v>94</v>
+        <v>17</v>
       </c>
       <c r="F58" t="s">
-        <v>0</v>
+        <v>18</v>
       </c>
       <c r="G58" t="s">
-        <v>302</v>
+        <v>255</v>
       </c>
       <c r="H58" t="s">
         <v>4</v>
@@ -3528,22 +3213,22 @@
     </row>
     <row r="59" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A59" t="s">
-        <v>303</v>
+        <v>256</v>
       </c>
       <c r="C59" t="s">
-        <v>31</v>
+        <v>23</v>
       </c>
       <c r="D59" t="s">
-        <v>304</v>
+        <v>254</v>
       </c>
       <c r="E59" t="s">
-        <v>305</v>
+        <v>17</v>
       </c>
       <c r="F59" t="s">
-        <v>0</v>
+        <v>18</v>
       </c>
       <c r="G59" t="s">
-        <v>306</v>
+        <v>255</v>
       </c>
       <c r="H59" t="s">
         <v>4</v>
@@ -3551,22 +3236,22 @@
     </row>
     <row r="60" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A60" t="s">
-        <v>307</v>
+        <v>257</v>
       </c>
       <c r="C60" t="s">
-        <v>31</v>
+        <v>23</v>
       </c>
       <c r="D60" t="s">
-        <v>304</v>
+        <v>254</v>
       </c>
       <c r="E60" t="s">
-        <v>305</v>
+        <v>17</v>
       </c>
       <c r="F60" t="s">
-        <v>0</v>
+        <v>18</v>
       </c>
       <c r="G60" t="s">
-        <v>306</v>
+        <v>255</v>
       </c>
       <c r="H60" t="s">
         <v>4</v>
@@ -3574,22 +3259,22 @@
     </row>
     <row r="61" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A61" t="s">
-        <v>308</v>
+        <v>258</v>
       </c>
       <c r="C61" t="s">
-        <v>11</v>
+        <v>26</v>
       </c>
       <c r="D61" t="s">
-        <v>309</v>
+        <v>259</v>
       </c>
       <c r="E61" t="s">
-        <v>152</v>
+        <v>51</v>
       </c>
       <c r="F61" t="s">
-        <v>0</v>
+        <v>52</v>
       </c>
       <c r="G61" t="s">
-        <v>57</v>
+        <v>93</v>
       </c>
       <c r="H61" t="s">
         <v>4</v>
@@ -3597,22 +3282,22 @@
     </row>
     <row r="62" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A62" t="s">
-        <v>310</v>
+        <v>260</v>
       </c>
       <c r="C62" t="s">
-        <v>22</v>
+        <v>26</v>
       </c>
       <c r="D62" t="s">
-        <v>311</v>
+        <v>259</v>
       </c>
       <c r="E62" t="s">
-        <v>312</v>
+        <v>51</v>
       </c>
       <c r="F62" t="s">
-        <v>0</v>
+        <v>52</v>
       </c>
       <c r="G62" t="s">
-        <v>116</v>
+        <v>93</v>
       </c>
       <c r="H62" t="s">
         <v>4</v>
@@ -3620,22 +3305,22 @@
     </row>
     <row r="63" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A63" t="s">
-        <v>313</v>
+        <v>261</v>
       </c>
       <c r="C63" t="s">
-        <v>34</v>
+        <v>31</v>
       </c>
       <c r="D63" t="s">
-        <v>314</v>
+        <v>262</v>
       </c>
       <c r="E63" t="s">
-        <v>70</v>
+        <v>230</v>
       </c>
       <c r="F63" t="s">
         <v>0</v>
       </c>
       <c r="G63" t="s">
-        <v>281</v>
+        <v>263</v>
       </c>
       <c r="H63" t="s">
         <v>4</v>
@@ -3643,22 +3328,22 @@
     </row>
     <row r="64" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A64" t="s">
-        <v>315</v>
+        <v>264</v>
       </c>
       <c r="C64" t="s">
-        <v>34</v>
+        <v>19</v>
       </c>
       <c r="D64" t="s">
-        <v>314</v>
+        <v>265</v>
       </c>
       <c r="E64" t="s">
-        <v>70</v>
+        <v>163</v>
       </c>
       <c r="F64" t="s">
         <v>0</v>
       </c>
       <c r="G64" t="s">
-        <v>281</v>
+        <v>266</v>
       </c>
       <c r="H64" t="s">
         <v>4</v>
@@ -3666,22 +3351,22 @@
     </row>
     <row r="65" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A65" t="s">
-        <v>316</v>
+        <v>267</v>
       </c>
       <c r="C65" t="s">
-        <v>34</v>
+        <v>19</v>
       </c>
       <c r="D65" t="s">
-        <v>314</v>
+        <v>265</v>
       </c>
       <c r="E65" t="s">
-        <v>70</v>
+        <v>163</v>
       </c>
       <c r="F65" t="s">
         <v>0</v>
       </c>
       <c r="G65" t="s">
-        <v>281</v>
+        <v>266</v>
       </c>
       <c r="H65" t="s">
         <v>4</v>
@@ -3689,22 +3374,22 @@
     </row>
     <row r="66" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A66" t="s">
-        <v>317</v>
+        <v>268</v>
       </c>
       <c r="C66" t="s">
-        <v>15</v>
+        <v>2</v>
       </c>
       <c r="D66" t="s">
-        <v>318</v>
+        <v>269</v>
       </c>
       <c r="E66" t="s">
-        <v>319</v>
+        <v>94</v>
       </c>
       <c r="F66" t="s">
         <v>0</v>
       </c>
       <c r="G66" t="s">
-        <v>320</v>
+        <v>270</v>
       </c>
       <c r="H66" t="s">
         <v>4</v>
@@ -3712,22 +3397,22 @@
     </row>
     <row r="67" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A67" t="s">
-        <v>321</v>
+        <v>271</v>
       </c>
       <c r="C67" t="s">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="D67" t="s">
-        <v>318</v>
+        <v>272</v>
       </c>
       <c r="E67" t="s">
-        <v>319</v>
+        <v>133</v>
       </c>
       <c r="F67" t="s">
         <v>0</v>
       </c>
       <c r="G67" t="s">
-        <v>320</v>
+        <v>134</v>
       </c>
       <c r="H67" t="s">
         <v>4</v>
@@ -3735,22 +3420,22 @@
     </row>
     <row r="68" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A68" t="s">
-        <v>322</v>
+        <v>273</v>
       </c>
       <c r="C68" t="s">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="D68" t="s">
-        <v>318</v>
+        <v>272</v>
       </c>
       <c r="E68" t="s">
-        <v>319</v>
+        <v>133</v>
       </c>
       <c r="F68" t="s">
         <v>0</v>
       </c>
       <c r="G68" t="s">
-        <v>320</v>
+        <v>134</v>
       </c>
       <c r="H68" t="s">
         <v>4</v>
@@ -3758,22 +3443,22 @@
     </row>
     <row r="69" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A69" t="s">
-        <v>83</v>
+        <v>274</v>
       </c>
       <c r="C69" t="s">
-        <v>35</v>
+        <v>24</v>
       </c>
       <c r="D69" t="s">
-        <v>84</v>
+        <v>275</v>
       </c>
       <c r="E69" t="s">
-        <v>85</v>
+        <v>6</v>
       </c>
       <c r="F69" t="s">
-        <v>86</v>
+        <v>7</v>
       </c>
       <c r="G69" t="s">
-        <v>87</v>
+        <v>276</v>
       </c>
       <c r="H69" t="s">
         <v>4</v>
@@ -3781,22 +3466,22 @@
     </row>
     <row r="70" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A70" t="s">
-        <v>323</v>
+        <v>277</v>
       </c>
       <c r="C70" t="s">
-        <v>34</v>
+        <v>24</v>
       </c>
       <c r="D70" t="s">
-        <v>324</v>
+        <v>275</v>
       </c>
       <c r="E70" t="s">
-        <v>325</v>
+        <v>6</v>
       </c>
       <c r="F70" t="s">
-        <v>326</v>
+        <v>7</v>
       </c>
       <c r="G70" t="s">
-        <v>327</v>
+        <v>276</v>
       </c>
       <c r="H70" t="s">
         <v>4</v>
@@ -3804,22 +3489,22 @@
     </row>
     <row r="71" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A71" t="s">
-        <v>328</v>
+        <v>278</v>
       </c>
       <c r="C71" t="s">
-        <v>12</v>
+        <v>24</v>
       </c>
       <c r="D71" t="s">
-        <v>329</v>
+        <v>275</v>
       </c>
       <c r="E71" t="s">
-        <v>60</v>
+        <v>6</v>
       </c>
       <c r="F71" t="s">
-        <v>61</v>
+        <v>7</v>
       </c>
       <c r="G71" t="s">
-        <v>330</v>
+        <v>276</v>
       </c>
       <c r="H71" t="s">
         <v>4</v>
@@ -3827,22 +3512,22 @@
     </row>
     <row r="72" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A72" t="s">
-        <v>331</v>
+        <v>279</v>
       </c>
       <c r="C72" t="s">
-        <v>12</v>
+        <v>24</v>
       </c>
       <c r="D72" t="s">
-        <v>332</v>
+        <v>280</v>
       </c>
       <c r="E72" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="F72" t="s">
         <v>0</v>
       </c>
       <c r="G72" t="s">
-        <v>333</v>
+        <v>281</v>
       </c>
       <c r="H72" t="s">
         <v>4</v>
@@ -3850,22 +3535,22 @@
     </row>
     <row r="73" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A73" t="s">
-        <v>334</v>
+        <v>282</v>
       </c>
       <c r="C73" t="s">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="D73" t="s">
-        <v>335</v>
+        <v>283</v>
       </c>
       <c r="E73" t="s">
-        <v>50</v>
+        <v>39</v>
       </c>
       <c r="F73" t="s">
-        <v>0</v>
+        <v>40</v>
       </c>
       <c r="G73" t="s">
-        <v>336</v>
+        <v>41</v>
       </c>
       <c r="H73" t="s">
         <v>4</v>
@@ -3873,22 +3558,22 @@
     </row>
     <row r="74" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A74" t="s">
-        <v>337</v>
+        <v>284</v>
       </c>
       <c r="C74" t="s">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="D74" t="s">
-        <v>338</v>
+        <v>283</v>
       </c>
       <c r="E74" t="s">
-        <v>152</v>
+        <v>39</v>
       </c>
       <c r="F74" t="s">
-        <v>0</v>
+        <v>40</v>
       </c>
       <c r="G74" t="s">
-        <v>153</v>
+        <v>41</v>
       </c>
       <c r="H74" t="s">
         <v>4</v>
@@ -3896,22 +3581,22 @@
     </row>
     <row r="75" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A75" t="s">
-        <v>339</v>
+        <v>285</v>
       </c>
       <c r="C75" t="s">
-        <v>31</v>
+        <v>23</v>
       </c>
       <c r="D75" t="s">
-        <v>340</v>
+        <v>286</v>
       </c>
       <c r="E75" t="s">
-        <v>38</v>
+        <v>17</v>
       </c>
       <c r="F75" t="s">
-        <v>0</v>
+        <v>18</v>
       </c>
       <c r="G75" t="s">
-        <v>341</v>
+        <v>287</v>
       </c>
       <c r="H75" t="s">
         <v>4</v>
@@ -3919,22 +3604,22 @@
     </row>
     <row r="76" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A76" t="s">
-        <v>342</v>
+        <v>288</v>
       </c>
       <c r="C76" t="s">
-        <v>35</v>
+        <v>185</v>
       </c>
       <c r="D76" t="s">
-        <v>343</v>
+        <v>289</v>
       </c>
       <c r="E76" t="s">
-        <v>65</v>
+        <v>290</v>
       </c>
       <c r="F76" t="s">
-        <v>66</v>
+        <v>0</v>
       </c>
       <c r="G76" t="s">
-        <v>344</v>
+        <v>291</v>
       </c>
       <c r="H76" t="s">
         <v>4</v>
@@ -3942,22 +3627,22 @@
     </row>
     <row r="77" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A77" t="s">
-        <v>345</v>
+        <v>292</v>
       </c>
       <c r="C77" t="s">
-        <v>35</v>
+        <v>104</v>
       </c>
       <c r="D77" t="s">
-        <v>343</v>
+        <v>293</v>
       </c>
       <c r="E77" t="s">
-        <v>65</v>
+        <v>294</v>
       </c>
       <c r="F77" t="s">
-        <v>66</v>
+        <v>0</v>
       </c>
       <c r="G77" t="s">
-        <v>344</v>
+        <v>295</v>
       </c>
       <c r="H77" t="s">
         <v>4</v>
@@ -3965,22 +3650,22 @@
     </row>
     <row r="78" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A78" t="s">
-        <v>346</v>
+        <v>296</v>
       </c>
       <c r="C78" t="s">
-        <v>13</v>
+        <v>104</v>
       </c>
       <c r="D78" t="s">
-        <v>347</v>
+        <v>293</v>
       </c>
       <c r="E78" t="s">
-        <v>48</v>
+        <v>294</v>
       </c>
       <c r="F78" t="s">
-        <v>49</v>
+        <v>0</v>
       </c>
       <c r="G78" t="s">
-        <v>348</v>
+        <v>295</v>
       </c>
       <c r="H78" t="s">
         <v>4</v>
@@ -3988,22 +3673,22 @@
     </row>
     <row r="79" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A79" t="s">
-        <v>349</v>
+        <v>297</v>
       </c>
       <c r="C79" t="s">
-        <v>34</v>
+        <v>104</v>
       </c>
       <c r="D79" t="s">
-        <v>350</v>
+        <v>298</v>
       </c>
       <c r="E79" t="s">
-        <v>325</v>
+        <v>133</v>
       </c>
       <c r="F79" t="s">
-        <v>326</v>
+        <v>0</v>
       </c>
       <c r="G79" t="s">
-        <v>351</v>
+        <v>299</v>
       </c>
       <c r="H79" t="s">
         <v>4</v>
@@ -4011,22 +3696,22 @@
     </row>
     <row r="80" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A80" t="s">
-        <v>352</v>
+        <v>300</v>
       </c>
       <c r="C80" t="s">
-        <v>2</v>
+        <v>31</v>
       </c>
       <c r="D80" t="s">
-        <v>353</v>
+        <v>301</v>
       </c>
       <c r="E80" t="s">
-        <v>97</v>
+        <v>302</v>
       </c>
       <c r="F80" t="s">
         <v>0</v>
       </c>
       <c r="G80" t="s">
-        <v>354</v>
+        <v>303</v>
       </c>
       <c r="H80" t="s">
         <v>4</v>
@@ -4034,22 +3719,22 @@
     </row>
     <row r="81" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A81" t="s">
-        <v>355</v>
+        <v>304</v>
       </c>
       <c r="C81" t="s">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="D81" t="s">
-        <v>356</v>
+        <v>305</v>
       </c>
       <c r="E81" t="s">
-        <v>68</v>
+        <v>306</v>
       </c>
       <c r="F81" t="s">
-        <v>69</v>
+        <v>0</v>
       </c>
       <c r="G81" t="s">
-        <v>357</v>
+        <v>307</v>
       </c>
       <c r="H81" t="s">
         <v>4</v>
@@ -4057,22 +3742,22 @@
     </row>
     <row r="82" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A82" t="s">
-        <v>358</v>
+        <v>308</v>
       </c>
       <c r="C82" t="s">
-        <v>9</v>
+        <v>22</v>
       </c>
       <c r="D82" t="s">
-        <v>359</v>
+        <v>309</v>
       </c>
       <c r="E82" t="s">
-        <v>360</v>
+        <v>224</v>
       </c>
       <c r="F82" t="s">
-        <v>361</v>
+        <v>0</v>
       </c>
       <c r="G82" t="s">
-        <v>362</v>
+        <v>310</v>
       </c>
       <c r="H82" t="s">
         <v>4</v>
@@ -4080,22 +3765,22 @@
     </row>
     <row r="83" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A83" t="s">
-        <v>363</v>
+        <v>311</v>
       </c>
       <c r="C83" t="s">
-        <v>10</v>
+        <v>22</v>
       </c>
       <c r="D83" t="s">
-        <v>364</v>
+        <v>309</v>
       </c>
       <c r="E83" t="s">
-        <v>365</v>
+        <v>224</v>
       </c>
       <c r="F83" t="s">
-        <v>366</v>
+        <v>0</v>
       </c>
       <c r="G83" t="s">
-        <v>105</v>
+        <v>310</v>
       </c>
       <c r="H83" t="s">
         <v>4</v>
@@ -4103,22 +3788,22 @@
     </row>
     <row r="84" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A84" t="s">
-        <v>367</v>
+        <v>312</v>
       </c>
       <c r="C84" t="s">
-        <v>10</v>
+        <v>22</v>
       </c>
       <c r="D84" t="s">
-        <v>364</v>
+        <v>309</v>
       </c>
       <c r="E84" t="s">
-        <v>365</v>
+        <v>224</v>
       </c>
       <c r="F84" t="s">
-        <v>366</v>
+        <v>0</v>
       </c>
       <c r="G84" t="s">
-        <v>105</v>
+        <v>310</v>
       </c>
       <c r="H84" t="s">
         <v>4</v>
@@ -4126,22 +3811,22 @@
     </row>
     <row r="85" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A85" t="s">
-        <v>368</v>
+        <v>313</v>
       </c>
       <c r="C85" t="s">
-        <v>31</v>
+        <v>104</v>
       </c>
       <c r="D85" t="s">
-        <v>369</v>
+        <v>314</v>
       </c>
       <c r="E85" t="s">
-        <v>74</v>
+        <v>294</v>
       </c>
       <c r="F85" t="s">
         <v>0</v>
       </c>
       <c r="G85" t="s">
-        <v>370</v>
+        <v>315</v>
       </c>
       <c r="H85" t="s">
         <v>4</v>
@@ -4149,22 +3834,22 @@
     </row>
     <row r="86" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A86" t="s">
-        <v>371</v>
+        <v>316</v>
       </c>
       <c r="C86" t="s">
-        <v>10</v>
+        <v>23</v>
       </c>
       <c r="D86" t="s">
-        <v>372</v>
+        <v>317</v>
       </c>
       <c r="E86" t="s">
-        <v>373</v>
+        <v>20</v>
       </c>
       <c r="F86" t="s">
-        <v>374</v>
+        <v>21</v>
       </c>
       <c r="G86" t="s">
-        <v>375</v>
+        <v>318</v>
       </c>
       <c r="H86" t="s">
         <v>4</v>
@@ -4172,22 +3857,22 @@
     </row>
     <row r="87" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A87" t="s">
-        <v>376</v>
+        <v>319</v>
       </c>
       <c r="C87" t="s">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="D87" t="s">
-        <v>377</v>
+        <v>320</v>
       </c>
       <c r="E87" t="s">
-        <v>365</v>
+        <v>321</v>
       </c>
       <c r="F87" t="s">
-        <v>366</v>
+        <v>322</v>
       </c>
       <c r="G87" t="s">
-        <v>378</v>
+        <v>323</v>
       </c>
       <c r="H87" t="s">
         <v>4</v>
@@ -4195,22 +3880,22 @@
     </row>
     <row r="88" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A88" t="s">
-        <v>379</v>
+        <v>324</v>
       </c>
       <c r="C88" t="s">
-        <v>12</v>
+        <v>38</v>
       </c>
       <c r="D88" t="s">
-        <v>380</v>
+        <v>325</v>
       </c>
       <c r="E88" t="s">
-        <v>51</v>
+        <v>43</v>
       </c>
       <c r="F88" t="s">
         <v>0</v>
       </c>
       <c r="G88" t="s">
-        <v>381</v>
+        <v>326</v>
       </c>
       <c r="H88" t="s">
         <v>4</v>
@@ -4218,22 +3903,22 @@
     </row>
     <row r="89" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A89" t="s">
-        <v>382</v>
+        <v>327</v>
       </c>
       <c r="C89" t="s">
-        <v>59</v>
+        <v>26</v>
       </c>
       <c r="D89" t="s">
-        <v>383</v>
+        <v>328</v>
       </c>
       <c r="E89" t="s">
-        <v>81</v>
+        <v>329</v>
       </c>
       <c r="F89" t="s">
-        <v>0</v>
+        <v>330</v>
       </c>
       <c r="G89" t="s">
-        <v>82</v>
+        <v>331</v>
       </c>
       <c r="H89" t="s">
         <v>4</v>
@@ -4241,22 +3926,22 @@
     </row>
     <row r="90" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A90" t="s">
-        <v>384</v>
+        <v>332</v>
       </c>
       <c r="C90" t="s">
-        <v>59</v>
+        <v>26</v>
       </c>
       <c r="D90" t="s">
-        <v>383</v>
+        <v>328</v>
       </c>
       <c r="E90" t="s">
-        <v>81</v>
+        <v>329</v>
       </c>
       <c r="F90" t="s">
-        <v>0</v>
+        <v>330</v>
       </c>
       <c r="G90" t="s">
-        <v>82</v>
+        <v>331</v>
       </c>
       <c r="H90" t="s">
         <v>4</v>
@@ -4264,22 +3949,22 @@
     </row>
     <row r="91" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A91" t="s">
-        <v>385</v>
+        <v>333</v>
       </c>
       <c r="C91" t="s">
-        <v>155</v>
+        <v>12</v>
       </c>
       <c r="D91" t="s">
-        <v>386</v>
+        <v>334</v>
       </c>
       <c r="E91" t="s">
-        <v>52</v>
+        <v>335</v>
       </c>
       <c r="F91" t="s">
         <v>0</v>
       </c>
       <c r="G91" t="s">
-        <v>58</v>
+        <v>336</v>
       </c>
       <c r="H91" t="s">
         <v>4</v>
@@ -4287,22 +3972,22 @@
     </row>
     <row r="92" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A92" t="s">
-        <v>387</v>
+        <v>337</v>
       </c>
       <c r="C92" t="s">
-        <v>35</v>
+        <v>104</v>
       </c>
       <c r="D92" t="s">
-        <v>388</v>
+        <v>338</v>
       </c>
       <c r="E92" t="s">
-        <v>389</v>
+        <v>92</v>
       </c>
       <c r="F92" t="s">
         <v>0</v>
       </c>
       <c r="G92" t="s">
-        <v>390</v>
+        <v>339</v>
       </c>
       <c r="H92" t="s">
         <v>4</v>
@@ -4310,22 +3995,22 @@
     </row>
     <row r="93" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A93" t="s">
-        <v>391</v>
+        <v>340</v>
       </c>
       <c r="C93" t="s">
-        <v>6</v>
+        <v>104</v>
       </c>
       <c r="D93" t="s">
-        <v>392</v>
+        <v>338</v>
       </c>
       <c r="E93" t="s">
-        <v>393</v>
+        <v>92</v>
       </c>
       <c r="F93" t="s">
-        <v>394</v>
+        <v>0</v>
       </c>
       <c r="G93" t="s">
-        <v>395</v>
+        <v>339</v>
       </c>
       <c r="H93" t="s">
         <v>4</v>
@@ -4333,22 +4018,22 @@
     </row>
     <row r="94" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A94" t="s">
-        <v>98</v>
+        <v>341</v>
       </c>
       <c r="C94" t="s">
-        <v>155</v>
+        <v>104</v>
       </c>
       <c r="D94" t="s">
-        <v>99</v>
+        <v>338</v>
       </c>
       <c r="E94" t="s">
-        <v>52</v>
+        <v>92</v>
       </c>
       <c r="F94" t="s">
         <v>0</v>
       </c>
       <c r="G94" t="s">
-        <v>100</v>
+        <v>339</v>
       </c>
       <c r="H94" t="s">
         <v>4</v>
@@ -4356,22 +4041,22 @@
     </row>
     <row r="95" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A95" t="s">
-        <v>396</v>
+        <v>342</v>
       </c>
       <c r="C95" t="s">
-        <v>31</v>
+        <v>24</v>
       </c>
       <c r="D95" t="s">
-        <v>397</v>
+        <v>343</v>
       </c>
       <c r="E95" t="s">
-        <v>398</v>
+        <v>49</v>
       </c>
       <c r="F95" t="s">
         <v>0</v>
       </c>
       <c r="G95" t="s">
-        <v>399</v>
+        <v>344</v>
       </c>
       <c r="H95" t="s">
         <v>4</v>
@@ -4379,22 +4064,22 @@
     </row>
     <row r="96" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A96" t="s">
-        <v>400</v>
+        <v>345</v>
       </c>
       <c r="C96" t="s">
-        <v>14</v>
+        <v>19</v>
       </c>
       <c r="D96" t="s">
-        <v>401</v>
+        <v>346</v>
       </c>
       <c r="E96" t="s">
-        <v>402</v>
+        <v>347</v>
       </c>
       <c r="F96" t="s">
         <v>0</v>
       </c>
       <c r="G96" t="s">
-        <v>403</v>
+        <v>348</v>
       </c>
       <c r="H96" t="s">
         <v>4</v>
@@ -4402,22 +4087,22 @@
     </row>
     <row r="97" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A97" t="s">
-        <v>404</v>
+        <v>349</v>
       </c>
       <c r="C97" t="s">
-        <v>22</v>
+        <v>19</v>
       </c>
       <c r="D97" t="s">
-        <v>405</v>
+        <v>346</v>
       </c>
       <c r="E97" t="s">
-        <v>406</v>
+        <v>347</v>
       </c>
       <c r="F97" t="s">
         <v>0</v>
       </c>
       <c r="G97" t="s">
-        <v>407</v>
+        <v>348</v>
       </c>
       <c r="H97" t="s">
         <v>4</v>
@@ -4425,22 +4110,22 @@
     </row>
     <row r="98" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A98" t="s">
-        <v>408</v>
+        <v>350</v>
       </c>
       <c r="C98" t="s">
-        <v>29</v>
+        <v>26</v>
       </c>
       <c r="D98" t="s">
-        <v>409</v>
+        <v>351</v>
       </c>
       <c r="E98" t="s">
-        <v>410</v>
+        <v>71</v>
       </c>
       <c r="F98" t="s">
-        <v>0</v>
+        <v>72</v>
       </c>
       <c r="G98" t="s">
-        <v>411</v>
+        <v>79</v>
       </c>
       <c r="H98" t="s">
         <v>4</v>
@@ -4448,22 +4133,22 @@
     </row>
     <row r="99" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A99" t="s">
-        <v>412</v>
+        <v>352</v>
       </c>
       <c r="C99" t="s">
-        <v>32</v>
+        <v>24</v>
       </c>
       <c r="D99" t="s">
-        <v>413</v>
+        <v>353</v>
       </c>
       <c r="E99" t="s">
-        <v>19</v>
+        <v>6</v>
       </c>
       <c r="F99" t="s">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="G99" t="s">
-        <v>102</v>
+        <v>354</v>
       </c>
       <c r="H99" t="s">
         <v>4</v>
@@ -4471,22 +4156,22 @@
     </row>
     <row r="100" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A100" t="s">
-        <v>414</v>
+        <v>355</v>
       </c>
       <c r="C100" t="s">
-        <v>31</v>
+        <v>26</v>
       </c>
       <c r="D100" t="s">
-        <v>415</v>
+        <v>356</v>
       </c>
       <c r="E100" t="s">
-        <v>416</v>
+        <v>35</v>
       </c>
       <c r="F100" t="s">
-        <v>0</v>
+        <v>36</v>
       </c>
       <c r="G100" t="s">
-        <v>417</v>
+        <v>357</v>
       </c>
       <c r="H100" t="s">
         <v>4</v>
@@ -4494,22 +4179,22 @@
     </row>
     <row r="101" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A101" t="s">
-        <v>418</v>
+        <v>358</v>
       </c>
       <c r="C101" t="s">
-        <v>43</v>
+        <v>23</v>
       </c>
       <c r="D101" t="s">
-        <v>419</v>
+        <v>359</v>
       </c>
       <c r="E101" t="s">
-        <v>246</v>
+        <v>360</v>
       </c>
       <c r="F101" t="s">
-        <v>0</v>
+        <v>361</v>
       </c>
       <c r="G101" t="s">
-        <v>420</v>
+        <v>362</v>
       </c>
       <c r="H101" t="s">
         <v>4</v>
@@ -4517,22 +4202,22 @@
     </row>
     <row r="102" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A102" t="s">
-        <v>421</v>
+        <v>363</v>
       </c>
       <c r="C102" t="s">
-        <v>43</v>
+        <v>23</v>
       </c>
       <c r="D102" t="s">
-        <v>419</v>
+        <v>359</v>
       </c>
       <c r="E102" t="s">
-        <v>246</v>
+        <v>360</v>
       </c>
       <c r="F102" t="s">
-        <v>0</v>
+        <v>361</v>
       </c>
       <c r="G102" t="s">
-        <v>420</v>
+        <v>362</v>
       </c>
       <c r="H102" t="s">
         <v>4</v>
@@ -4540,22 +4225,22 @@
     </row>
     <row r="103" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A103" t="s">
-        <v>422</v>
+        <v>364</v>
       </c>
       <c r="C103" t="s">
-        <v>14</v>
+        <v>9</v>
       </c>
       <c r="D103" t="s">
-        <v>423</v>
+        <v>365</v>
       </c>
       <c r="E103" t="s">
-        <v>424</v>
+        <v>366</v>
       </c>
       <c r="F103" t="s">
-        <v>0</v>
+        <v>367</v>
       </c>
       <c r="G103" t="s">
-        <v>425</v>
+        <v>41</v>
       </c>
       <c r="H103" t="s">
         <v>4</v>
@@ -4563,22 +4248,22 @@
     </row>
     <row r="104" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A104" t="s">
-        <v>426</v>
+        <v>368</v>
       </c>
       <c r="C104" t="s">
-        <v>35</v>
+        <v>9</v>
       </c>
       <c r="D104" t="s">
-        <v>427</v>
+        <v>365</v>
       </c>
       <c r="E104" t="s">
-        <v>85</v>
+        <v>366</v>
       </c>
       <c r="F104" t="s">
-        <v>86</v>
+        <v>367</v>
       </c>
       <c r="G104" t="s">
-        <v>428</v>
+        <v>41</v>
       </c>
       <c r="H104" t="s">
         <v>4</v>
@@ -4586,22 +4271,22 @@
     </row>
     <row r="105" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A105" t="s">
-        <v>429</v>
+        <v>369</v>
       </c>
       <c r="C105" t="s">
-        <v>2</v>
+        <v>24</v>
       </c>
       <c r="D105" t="s">
-        <v>430</v>
+        <v>370</v>
       </c>
       <c r="E105" t="s">
-        <v>431</v>
+        <v>371</v>
       </c>
       <c r="F105" t="s">
         <v>0</v>
       </c>
       <c r="G105" t="s">
-        <v>432</v>
+        <v>372</v>
       </c>
       <c r="H105" t="s">
         <v>4</v>
@@ -4609,22 +4294,22 @@
     </row>
     <row r="106" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A106" t="s">
-        <v>433</v>
+        <v>373</v>
       </c>
       <c r="C106" t="s">
-        <v>59</v>
+        <v>2</v>
       </c>
       <c r="D106" t="s">
-        <v>434</v>
+        <v>374</v>
       </c>
       <c r="E106" t="s">
-        <v>435</v>
+        <v>14</v>
       </c>
       <c r="F106" t="s">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="G106" t="s">
-        <v>436</v>
+        <v>375</v>
       </c>
       <c r="H106" t="s">
         <v>4</v>
@@ -4632,22 +4317,22 @@
     </row>
     <row r="107" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A107" t="s">
-        <v>437</v>
+        <v>376</v>
       </c>
       <c r="C107" t="s">
-        <v>35</v>
+        <v>9</v>
       </c>
       <c r="D107" t="s">
-        <v>438</v>
+        <v>377</v>
       </c>
       <c r="E107" t="s">
-        <v>439</v>
+        <v>378</v>
       </c>
       <c r="F107" t="s">
-        <v>440</v>
+        <v>0</v>
       </c>
       <c r="G107" t="s">
-        <v>441</v>
+        <v>379</v>
       </c>
       <c r="H107" t="s">
         <v>4</v>
@@ -4655,22 +4340,22 @@
     </row>
     <row r="108" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A108" t="s">
-        <v>442</v>
+        <v>380</v>
       </c>
       <c r="C108" t="s">
-        <v>32</v>
+        <v>26</v>
       </c>
       <c r="D108" t="s">
-        <v>443</v>
+        <v>381</v>
       </c>
       <c r="E108" t="s">
-        <v>18</v>
+        <v>382</v>
       </c>
       <c r="F108" t="s">
-        <v>0</v>
+        <v>383</v>
       </c>
       <c r="G108" t="s">
-        <v>444</v>
+        <v>384</v>
       </c>
       <c r="H108" t="s">
         <v>4</v>
@@ -4678,22 +4363,22 @@
     </row>
     <row r="109" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A109" t="s">
-        <v>445</v>
+        <v>385</v>
       </c>
       <c r="C109" t="s">
-        <v>12</v>
+        <v>19</v>
       </c>
       <c r="D109" t="s">
-        <v>446</v>
+        <v>386</v>
       </c>
       <c r="E109" t="s">
-        <v>26</v>
+        <v>69</v>
       </c>
       <c r="F109" t="s">
-        <v>0</v>
+        <v>70</v>
       </c>
       <c r="G109" t="s">
-        <v>447</v>
+        <v>387</v>
       </c>
       <c r="H109" t="s">
         <v>4</v>
@@ -4701,22 +4386,22 @@
     </row>
     <row r="110" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A110" t="s">
-        <v>448</v>
+        <v>388</v>
       </c>
       <c r="C110" t="s">
-        <v>43</v>
+        <v>19</v>
       </c>
       <c r="D110" t="s">
-        <v>449</v>
+        <v>386</v>
       </c>
       <c r="E110" t="s">
-        <v>72</v>
+        <v>69</v>
       </c>
       <c r="F110" t="s">
-        <v>0</v>
+        <v>70</v>
       </c>
       <c r="G110" t="s">
-        <v>450</v>
+        <v>387</v>
       </c>
       <c r="H110" t="s">
         <v>4</v>
@@ -4724,22 +4409,22 @@
     </row>
     <row r="111" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A111" t="s">
-        <v>451</v>
+        <v>389</v>
       </c>
       <c r="C111" t="s">
-        <v>59</v>
+        <v>26</v>
       </c>
       <c r="D111" t="s">
-        <v>452</v>
+        <v>390</v>
       </c>
       <c r="E111" t="s">
-        <v>453</v>
+        <v>329</v>
       </c>
       <c r="F111" t="s">
-        <v>0</v>
+        <v>330</v>
       </c>
       <c r="G111" t="s">
-        <v>454</v>
+        <v>86</v>
       </c>
       <c r="H111" t="s">
         <v>4</v>
@@ -4747,22 +4432,22 @@
     </row>
     <row r="112" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A112" t="s">
-        <v>455</v>
+        <v>391</v>
       </c>
       <c r="C112" t="s">
-        <v>35</v>
+        <v>12</v>
       </c>
       <c r="D112" t="s">
-        <v>456</v>
+        <v>392</v>
       </c>
       <c r="E112" t="s">
-        <v>457</v>
+        <v>393</v>
       </c>
       <c r="F112" t="s">
         <v>0</v>
       </c>
       <c r="G112" t="s">
-        <v>458</v>
+        <v>394</v>
       </c>
       <c r="H112" t="s">
         <v>4</v>
@@ -4770,22 +4455,22 @@
     </row>
     <row r="113" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A113" t="s">
-        <v>459</v>
+        <v>395</v>
       </c>
       <c r="C113" t="s">
-        <v>43</v>
+        <v>12</v>
       </c>
       <c r="D113" t="s">
-        <v>460</v>
+        <v>392</v>
       </c>
       <c r="E113" t="s">
-        <v>461</v>
+        <v>393</v>
       </c>
       <c r="F113" t="s">
         <v>0</v>
       </c>
       <c r="G113" t="s">
-        <v>462</v>
+        <v>394</v>
       </c>
       <c r="H113" t="s">
         <v>4</v>
@@ -4793,22 +4478,22 @@
     </row>
     <row r="114" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A114" t="s">
-        <v>463</v>
+        <v>396</v>
       </c>
       <c r="C114" t="s">
-        <v>31</v>
+        <v>26</v>
       </c>
       <c r="D114" t="s">
-        <v>464</v>
+        <v>397</v>
       </c>
       <c r="E114" t="s">
-        <v>305</v>
+        <v>398</v>
       </c>
       <c r="F114" t="s">
-        <v>0</v>
+        <v>399</v>
       </c>
       <c r="G114" t="s">
-        <v>465</v>
+        <v>400</v>
       </c>
       <c r="H114" t="s">
         <v>4</v>
@@ -4816,22 +4501,22 @@
     </row>
     <row r="115" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A115" t="s">
-        <v>466</v>
+        <v>401</v>
       </c>
       <c r="C115" t="s">
-        <v>15</v>
+        <v>22</v>
       </c>
       <c r="D115" t="s">
-        <v>467</v>
+        <v>402</v>
       </c>
       <c r="E115" t="s">
-        <v>468</v>
+        <v>37</v>
       </c>
       <c r="F115" t="s">
         <v>0</v>
       </c>
       <c r="G115" t="s">
-        <v>469</v>
+        <v>403</v>
       </c>
       <c r="H115" t="s">
         <v>4</v>
@@ -4839,22 +4524,22 @@
     </row>
     <row r="116" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A116" t="s">
-        <v>470</v>
+        <v>404</v>
       </c>
       <c r="C116" t="s">
-        <v>35</v>
+        <v>104</v>
       </c>
       <c r="D116" t="s">
-        <v>471</v>
+        <v>405</v>
       </c>
       <c r="E116" t="s">
-        <v>472</v>
+        <v>406</v>
       </c>
       <c r="F116" t="s">
         <v>0</v>
       </c>
       <c r="G116" t="s">
-        <v>473</v>
+        <v>407</v>
       </c>
       <c r="H116" t="s">
         <v>4</v>
@@ -4862,22 +4547,22 @@
     </row>
     <row r="117" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A117" t="s">
-        <v>474</v>
+        <v>408</v>
       </c>
       <c r="C117" t="s">
-        <v>12</v>
+        <v>3</v>
       </c>
       <c r="D117" t="s">
-        <v>475</v>
+        <v>409</v>
       </c>
       <c r="E117" t="s">
-        <v>51</v>
+        <v>16</v>
       </c>
       <c r="F117" t="s">
         <v>0</v>
       </c>
       <c r="G117" t="s">
-        <v>205</v>
+        <v>410</v>
       </c>
       <c r="H117" t="s">
         <v>4</v>
@@ -4885,22 +4570,22 @@
     </row>
     <row r="118" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A118" t="s">
-        <v>476</v>
+        <v>411</v>
       </c>
       <c r="C118" t="s">
-        <v>2</v>
+        <v>38</v>
       </c>
       <c r="D118" t="s">
-        <v>477</v>
+        <v>412</v>
       </c>
       <c r="E118" t="s">
-        <v>478</v>
+        <v>413</v>
       </c>
       <c r="F118" t="s">
         <v>0</v>
       </c>
       <c r="G118" t="s">
-        <v>479</v>
+        <v>414</v>
       </c>
       <c r="H118" t="s">
         <v>4</v>
@@ -4908,22 +4593,22 @@
     </row>
     <row r="119" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A119" t="s">
-        <v>480</v>
+        <v>415</v>
       </c>
       <c r="C119" t="s">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="D119" t="s">
-        <v>481</v>
+        <v>416</v>
       </c>
       <c r="E119" t="s">
-        <v>228</v>
+        <v>378</v>
       </c>
       <c r="F119" t="s">
-        <v>229</v>
+        <v>0</v>
       </c>
       <c r="G119" t="s">
-        <v>482</v>
+        <v>417</v>
       </c>
       <c r="H119" t="s">
         <v>4</v>
@@ -4931,22 +4616,22 @@
     </row>
     <row r="120" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A120" t="s">
-        <v>483</v>
+        <v>418</v>
       </c>
       <c r="C120" t="s">
-        <v>6</v>
+        <v>185</v>
       </c>
       <c r="D120" t="s">
-        <v>481</v>
+        <v>419</v>
       </c>
       <c r="E120" t="s">
-        <v>228</v>
+        <v>420</v>
       </c>
       <c r="F120" t="s">
-        <v>229</v>
+        <v>0</v>
       </c>
       <c r="G120" t="s">
-        <v>482</v>
+        <v>421</v>
       </c>
       <c r="H120" t="s">
         <v>4</v>
@@ -4954,22 +4639,22 @@
     </row>
     <row r="121" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A121" t="s">
-        <v>484</v>
+        <v>422</v>
       </c>
       <c r="C121" t="s">
-        <v>6</v>
+        <v>38</v>
       </c>
       <c r="D121" t="s">
-        <v>481</v>
+        <v>423</v>
       </c>
       <c r="E121" t="s">
-        <v>228</v>
+        <v>424</v>
       </c>
       <c r="F121" t="s">
-        <v>229</v>
+        <v>0</v>
       </c>
       <c r="G121" t="s">
-        <v>482</v>
+        <v>425</v>
       </c>
       <c r="H121" t="s">
         <v>4</v>
@@ -4977,22 +4662,22 @@
     </row>
     <row r="122" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A122" t="s">
-        <v>485</v>
+        <v>426</v>
       </c>
       <c r="C122" t="s">
-        <v>43</v>
+        <v>3</v>
       </c>
       <c r="D122" t="s">
-        <v>486</v>
+        <v>427</v>
       </c>
       <c r="E122" t="s">
-        <v>41</v>
+        <v>428</v>
       </c>
       <c r="F122" t="s">
-        <v>0</v>
+        <v>429</v>
       </c>
       <c r="G122" t="s">
-        <v>487</v>
+        <v>430</v>
       </c>
       <c r="H122" t="s">
         <v>4</v>
@@ -5000,22 +4685,22 @@
     </row>
     <row r="123" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A123" t="s">
-        <v>488</v>
+        <v>431</v>
       </c>
       <c r="C123" t="s">
-        <v>29</v>
+        <v>3</v>
       </c>
       <c r="D123" t="s">
-        <v>489</v>
+        <v>427</v>
       </c>
       <c r="E123" t="s">
-        <v>490</v>
+        <v>428</v>
       </c>
       <c r="F123" t="s">
-        <v>0</v>
+        <v>429</v>
       </c>
       <c r="G123" t="s">
-        <v>491</v>
+        <v>430</v>
       </c>
       <c r="H123" t="s">
         <v>4</v>
@@ -5023,22 +4708,22 @@
     </row>
     <row r="124" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A124" t="s">
-        <v>492</v>
+        <v>432</v>
       </c>
       <c r="C124" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="D124" t="s">
-        <v>493</v>
+        <v>433</v>
       </c>
       <c r="E124" t="s">
-        <v>39</v>
+        <v>217</v>
       </c>
       <c r="F124" t="s">
         <v>0</v>
       </c>
       <c r="G124" t="s">
-        <v>494</v>
+        <v>434</v>
       </c>
       <c r="H124" t="s">
         <v>4</v>
@@ -5046,183 +4731,183 @@
     </row>
     <row r="125" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A125" t="s">
-        <v>495</v>
+        <v>435</v>
       </c>
       <c r="C125" t="s">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="D125" t="s">
-        <v>496</v>
+        <v>433</v>
       </c>
       <c r="E125" t="s">
-        <v>497</v>
+        <v>217</v>
       </c>
       <c r="F125" t="s">
-        <v>498</v>
+        <v>0</v>
       </c>
       <c r="G125" t="s">
-        <v>499</v>
+        <v>434</v>
       </c>
       <c r="H125" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="126" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A126" t="s">
-        <v>500</v>
+        <v>436</v>
       </c>
       <c r="C126" t="s">
-        <v>2</v>
+        <v>185</v>
       </c>
       <c r="D126" t="s">
-        <v>501</v>
+        <v>437</v>
       </c>
       <c r="E126" t="s">
-        <v>502</v>
+        <v>290</v>
       </c>
       <c r="F126" t="s">
-        <v>503</v>
+        <v>0</v>
       </c>
       <c r="G126" t="s">
-        <v>504</v>
+        <v>387</v>
       </c>
       <c r="H126" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="127" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A127" t="s">
-        <v>505</v>
+        <v>438</v>
       </c>
       <c r="C127" t="s">
-        <v>32</v>
+        <v>9</v>
       </c>
       <c r="D127" t="s">
-        <v>505</v>
+        <v>439</v>
       </c>
       <c r="E127" t="s">
-        <v>18</v>
+        <v>440</v>
       </c>
       <c r="F127" t="s">
-        <v>0</v>
+        <v>441</v>
       </c>
       <c r="G127" t="s">
-        <v>506</v>
+        <v>442</v>
       </c>
       <c r="H127" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="128" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A128" t="s">
-        <v>507</v>
+        <v>443</v>
       </c>
       <c r="C128" t="s">
-        <v>155</v>
+        <v>9</v>
       </c>
       <c r="D128" t="s">
-        <v>508</v>
+        <v>439</v>
       </c>
       <c r="E128" t="s">
-        <v>509</v>
+        <v>440</v>
       </c>
       <c r="F128" t="s">
-        <v>510</v>
+        <v>441</v>
       </c>
       <c r="G128" t="s">
-        <v>511</v>
+        <v>442</v>
       </c>
       <c r="H128" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="129" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A129" t="s">
-        <v>512</v>
+        <v>444</v>
       </c>
       <c r="C129" t="s">
-        <v>31</v>
+        <v>9</v>
       </c>
       <c r="D129" t="s">
-        <v>513</v>
+        <v>439</v>
       </c>
       <c r="E129" t="s">
-        <v>106</v>
+        <v>440</v>
       </c>
       <c r="F129" t="s">
-        <v>0</v>
+        <v>441</v>
       </c>
       <c r="G129" t="s">
-        <v>514</v>
+        <v>442</v>
       </c>
       <c r="H129" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="130" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A130" t="s">
-        <v>515</v>
+        <v>445</v>
       </c>
       <c r="C130" t="s">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="D130" t="s">
-        <v>516</v>
+        <v>446</v>
       </c>
       <c r="E130" t="s">
-        <v>26</v>
+        <v>447</v>
       </c>
       <c r="F130" t="s">
         <v>0</v>
       </c>
       <c r="G130" t="s">
-        <v>517</v>
+        <v>448</v>
       </c>
       <c r="H130" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="131" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A131" t="s">
-        <v>518</v>
+        <v>449</v>
       </c>
       <c r="C131" t="s">
-        <v>29</v>
+        <v>23</v>
       </c>
       <c r="D131" t="s">
-        <v>519</v>
+        <v>450</v>
       </c>
       <c r="E131" t="s">
-        <v>132</v>
+        <v>451</v>
       </c>
       <c r="F131" t="s">
-        <v>0</v>
+        <v>452</v>
       </c>
       <c r="G131" t="s">
-        <v>267</v>
+        <v>453</v>
       </c>
       <c r="H131" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="132" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A132" t="s">
-        <v>520</v>
+        <v>454</v>
       </c>
       <c r="C132" t="s">
-        <v>31</v>
+        <v>22</v>
       </c>
       <c r="D132" t="s">
-        <v>521</v>
+        <v>455</v>
       </c>
       <c r="E132" t="s">
-        <v>53</v>
+        <v>29</v>
       </c>
       <c r="F132" t="s">
         <v>0</v>
       </c>
       <c r="G132" t="s">
-        <v>522</v>
+        <v>456</v>
       </c>
       <c r="H132" t="s">
         <v>5</v>
@@ -5230,22 +4915,22 @@
     </row>
     <row r="133" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A133" t="s">
-        <v>523</v>
+        <v>457</v>
       </c>
       <c r="C133" t="s">
-        <v>35</v>
+        <v>23</v>
       </c>
       <c r="D133" t="s">
-        <v>524</v>
+        <v>458</v>
       </c>
       <c r="E133" t="s">
-        <v>67</v>
+        <v>209</v>
       </c>
       <c r="F133" t="s">
         <v>0</v>
       </c>
       <c r="G133" t="s">
-        <v>525</v>
+        <v>459</v>
       </c>
       <c r="H133" t="s">
         <v>5</v>
@@ -5253,22 +4938,22 @@
     </row>
     <row r="134" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A134" t="s">
-        <v>526</v>
+        <v>460</v>
       </c>
       <c r="C134" t="s">
-        <v>35</v>
+        <v>9</v>
       </c>
       <c r="D134" t="s">
-        <v>524</v>
+        <v>461</v>
       </c>
       <c r="E134" t="s">
-        <v>67</v>
+        <v>90</v>
       </c>
       <c r="F134" t="s">
         <v>0</v>
       </c>
       <c r="G134" t="s">
-        <v>525</v>
+        <v>91</v>
       </c>
       <c r="H134" t="s">
         <v>5</v>
@@ -5276,22 +4961,22 @@
     </row>
     <row r="135" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A135" t="s">
-        <v>527</v>
+        <v>462</v>
       </c>
       <c r="C135" t="s">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="D135" t="s">
-        <v>528</v>
+        <v>463</v>
       </c>
       <c r="E135" t="s">
-        <v>39</v>
+        <v>464</v>
       </c>
       <c r="F135" t="s">
         <v>0</v>
       </c>
       <c r="G135" t="s">
-        <v>529</v>
+        <v>465</v>
       </c>
       <c r="H135" t="s">
         <v>5</v>
@@ -5299,22 +4984,22 @@
     </row>
     <row r="136" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A136" t="s">
-        <v>530</v>
+        <v>466</v>
       </c>
       <c r="C136" t="s">
-        <v>15</v>
+        <v>38</v>
       </c>
       <c r="D136" t="s">
-        <v>531</v>
+        <v>467</v>
       </c>
       <c r="E136" t="s">
-        <v>55</v>
+        <v>43</v>
       </c>
       <c r="F136" t="s">
-        <v>56</v>
+        <v>0</v>
       </c>
       <c r="G136" t="s">
-        <v>71</v>
+        <v>468</v>
       </c>
       <c r="H136" t="s">
         <v>5</v>
@@ -5322,22 +5007,22 @@
     </row>
     <row r="137" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A137" t="s">
-        <v>532</v>
+        <v>469</v>
       </c>
       <c r="C137" t="s">
-        <v>14</v>
+        <v>19</v>
       </c>
       <c r="D137" t="s">
-        <v>533</v>
+        <v>470</v>
       </c>
       <c r="E137" t="s">
-        <v>33</v>
+        <v>471</v>
       </c>
       <c r="F137" t="s">
-        <v>0</v>
+        <v>472</v>
       </c>
       <c r="G137" t="s">
-        <v>534</v>
+        <v>473</v>
       </c>
       <c r="H137" t="s">
         <v>5</v>
@@ -5345,22 +5030,22 @@
     </row>
     <row r="138" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A138" t="s">
-        <v>535</v>
+        <v>474</v>
       </c>
       <c r="C138" t="s">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="D138" t="s">
-        <v>536</v>
+        <v>470</v>
       </c>
       <c r="E138" t="s">
-        <v>537</v>
+        <v>471</v>
       </c>
       <c r="F138" t="s">
-        <v>538</v>
+        <v>472</v>
       </c>
       <c r="G138" t="s">
-        <v>539</v>
+        <v>473</v>
       </c>
       <c r="H138" t="s">
         <v>5</v>
@@ -5368,22 +5053,22 @@
     </row>
     <row r="139" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A139" t="s">
-        <v>540</v>
+        <v>475</v>
       </c>
       <c r="C139" t="s">
-        <v>15</v>
+        <v>23</v>
       </c>
       <c r="D139" t="s">
-        <v>536</v>
+        <v>476</v>
       </c>
       <c r="E139" t="s">
-        <v>537</v>
+        <v>17</v>
       </c>
       <c r="F139" t="s">
-        <v>538</v>
+        <v>18</v>
       </c>
       <c r="G139" t="s">
-        <v>539</v>
+        <v>477</v>
       </c>
       <c r="H139" t="s">
         <v>5</v>
@@ -5391,22 +5076,22 @@
     </row>
     <row r="140" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A140" t="s">
-        <v>541</v>
+        <v>478</v>
       </c>
       <c r="C140" t="s">
-        <v>32</v>
+        <v>13</v>
       </c>
       <c r="D140" t="s">
-        <v>542</v>
+        <v>479</v>
       </c>
       <c r="E140" t="s">
-        <v>19</v>
+        <v>84</v>
       </c>
       <c r="F140" t="s">
-        <v>0</v>
+        <v>85</v>
       </c>
       <c r="G140" t="s">
-        <v>543</v>
+        <v>112</v>
       </c>
       <c r="H140" t="s">
         <v>5</v>
@@ -5414,22 +5099,22 @@
     </row>
     <row r="141" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A141" t="s">
-        <v>544</v>
+        <v>480</v>
       </c>
       <c r="C141" t="s">
-        <v>43</v>
+        <v>23</v>
       </c>
       <c r="D141" t="s">
-        <v>545</v>
+        <v>481</v>
       </c>
       <c r="E141" t="s">
-        <v>546</v>
+        <v>482</v>
       </c>
       <c r="F141" t="s">
         <v>0</v>
       </c>
       <c r="G141" t="s">
-        <v>224</v>
+        <v>483</v>
       </c>
       <c r="H141" t="s">
         <v>5</v>
@@ -5437,22 +5122,22 @@
     </row>
     <row r="142" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A142" t="s">
-        <v>547</v>
+        <v>484</v>
       </c>
       <c r="C142" t="s">
-        <v>32</v>
+        <v>23</v>
       </c>
       <c r="D142" t="s">
-        <v>548</v>
+        <v>481</v>
       </c>
       <c r="E142" t="s">
-        <v>64</v>
+        <v>482</v>
       </c>
       <c r="F142" t="s">
         <v>0</v>
       </c>
       <c r="G142" t="s">
-        <v>549</v>
+        <v>483</v>
       </c>
       <c r="H142" t="s">
         <v>5</v>
@@ -5460,22 +5145,22 @@
     </row>
     <row r="143" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A143" t="s">
-        <v>550</v>
+        <v>485</v>
       </c>
       <c r="C143" t="s">
-        <v>12</v>
+        <v>24</v>
       </c>
       <c r="D143" t="s">
-        <v>551</v>
+        <v>486</v>
       </c>
       <c r="E143" t="s">
-        <v>68</v>
+        <v>32</v>
       </c>
       <c r="F143" t="s">
-        <v>69</v>
+        <v>33</v>
       </c>
       <c r="G143" t="s">
-        <v>552</v>
+        <v>387</v>
       </c>
       <c r="H143" t="s">
         <v>5</v>
@@ -5483,22 +5168,22 @@
     </row>
     <row r="144" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A144" t="s">
-        <v>553</v>
+        <v>487</v>
       </c>
       <c r="C144" t="s">
-        <v>12</v>
+        <v>26</v>
       </c>
       <c r="D144" t="s">
-        <v>551</v>
+        <v>488</v>
       </c>
       <c r="E144" t="s">
-        <v>68</v>
+        <v>35</v>
       </c>
       <c r="F144" t="s">
-        <v>69</v>
+        <v>36</v>
       </c>
       <c r="G144" t="s">
-        <v>552</v>
+        <v>489</v>
       </c>
       <c r="H144" t="s">
         <v>5</v>
@@ -5506,22 +5191,22 @@
     </row>
     <row r="145" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A145" t="s">
-        <v>554</v>
+        <v>490</v>
       </c>
       <c r="C145" t="s">
-        <v>2</v>
+        <v>19</v>
       </c>
       <c r="D145" t="s">
-        <v>555</v>
+        <v>491</v>
       </c>
       <c r="E145" t="s">
-        <v>556</v>
+        <v>492</v>
       </c>
       <c r="F145" t="s">
-        <v>557</v>
+        <v>493</v>
       </c>
       <c r="G145" t="s">
-        <v>558</v>
+        <v>494</v>
       </c>
       <c r="H145" t="s">
         <v>5</v>
@@ -5529,22 +5214,22 @@
     </row>
     <row r="146" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A146" t="s">
-        <v>559</v>
+        <v>495</v>
       </c>
       <c r="C146" t="s">
-        <v>9</v>
+        <v>19</v>
       </c>
       <c r="D146" t="s">
-        <v>560</v>
+        <v>491</v>
       </c>
       <c r="E146" t="s">
-        <v>44</v>
+        <v>492</v>
       </c>
       <c r="F146" t="s">
-        <v>45</v>
+        <v>493</v>
       </c>
       <c r="G146" t="s">
-        <v>561</v>
+        <v>494</v>
       </c>
       <c r="H146" t="s">
         <v>5</v>
@@ -5552,605 +5237,94 @@
     </row>
     <row r="147" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A147" t="s">
-        <v>562</v>
+        <v>496</v>
       </c>
       <c r="C147" t="s">
-        <v>10</v>
+        <v>26</v>
       </c>
       <c r="D147" t="s">
-        <v>563</v>
+        <v>497</v>
       </c>
       <c r="E147" t="s">
-        <v>564</v>
+        <v>152</v>
       </c>
       <c r="F147" t="s">
-        <v>565</v>
+        <v>153</v>
       </c>
       <c r="G147" t="s">
-        <v>71</v>
+        <v>498</v>
       </c>
       <c r="H147" t="s">
-        <v>5</v>
+        <v>499</v>
       </c>
     </row>
     <row r="148" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A148" t="s">
-        <v>107</v>
+        <v>500</v>
       </c>
       <c r="C148" t="s">
-        <v>12</v>
+        <v>26</v>
       </c>
       <c r="D148" t="s">
-        <v>108</v>
+        <v>497</v>
       </c>
       <c r="E148" t="s">
-        <v>109</v>
+        <v>152</v>
       </c>
       <c r="F148" t="s">
-        <v>0</v>
+        <v>153</v>
       </c>
       <c r="G148" t="s">
-        <v>110</v>
+        <v>498</v>
       </c>
       <c r="H148" t="s">
-        <v>5</v>
+        <v>499</v>
       </c>
     </row>
     <row r="149" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A149" t="s">
-        <v>111</v>
+        <v>501</v>
       </c>
       <c r="C149" t="s">
-        <v>12</v>
+        <v>104</v>
       </c>
       <c r="D149" t="s">
-        <v>108</v>
+        <v>502</v>
       </c>
       <c r="E149" t="s">
-        <v>109</v>
+        <v>503</v>
       </c>
       <c r="F149" t="s">
         <v>0</v>
       </c>
       <c r="G149" t="s">
-        <v>110</v>
+        <v>504</v>
       </c>
       <c r="H149" t="s">
-        <v>5</v>
+        <v>499</v>
       </c>
     </row>
     <row r="150" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A150" t="s">
-        <v>112</v>
+        <v>505</v>
       </c>
       <c r="C150" t="s">
-        <v>12</v>
+        <v>104</v>
       </c>
       <c r="D150" t="s">
-        <v>108</v>
+        <v>502</v>
       </c>
       <c r="E150" t="s">
-        <v>109</v>
+        <v>503</v>
       </c>
       <c r="F150" t="s">
         <v>0</v>
       </c>
       <c r="G150" t="s">
-        <v>110</v>
+        <v>504</v>
       </c>
       <c r="H150" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="151" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A151" t="s">
-        <v>113</v>
-      </c>
-      <c r="C151" t="s">
-        <v>12</v>
-      </c>
-      <c r="D151" t="s">
-        <v>108</v>
-      </c>
-      <c r="E151" t="s">
-        <v>109</v>
-      </c>
-      <c r="F151" t="s">
-        <v>0</v>
-      </c>
-      <c r="G151" t="s">
-        <v>110</v>
-      </c>
-      <c r="H151" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="152" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A152" t="s">
-        <v>566</v>
-      </c>
-      <c r="C152" t="s">
-        <v>13</v>
-      </c>
-      <c r="D152" t="s">
-        <v>567</v>
-      </c>
-      <c r="E152" t="s">
-        <v>233</v>
-      </c>
-      <c r="F152" t="s">
-        <v>234</v>
-      </c>
-      <c r="G152" t="s">
-        <v>568</v>
-      </c>
-      <c r="H152" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="153" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A153" t="s">
-        <v>569</v>
-      </c>
-      <c r="C153" t="s">
-        <v>2</v>
-      </c>
-      <c r="D153" t="s">
-        <v>570</v>
-      </c>
-      <c r="E153" t="s">
-        <v>88</v>
-      </c>
-      <c r="F153" t="s">
-        <v>89</v>
-      </c>
-      <c r="G153" t="s">
-        <v>571</v>
-      </c>
-      <c r="H153" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="154" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A154" t="s">
-        <v>572</v>
-      </c>
-      <c r="C154" t="s">
-        <v>2</v>
-      </c>
-      <c r="D154" t="s">
-        <v>570</v>
-      </c>
-      <c r="E154" t="s">
-        <v>88</v>
-      </c>
-      <c r="F154" t="s">
-        <v>89</v>
-      </c>
-      <c r="G154" t="s">
-        <v>571</v>
-      </c>
-      <c r="H154" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="155" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A155" t="s">
-        <v>573</v>
-      </c>
-      <c r="C155" t="s">
-        <v>2</v>
-      </c>
-      <c r="D155" t="s">
-        <v>570</v>
-      </c>
-      <c r="E155" t="s">
-        <v>88</v>
-      </c>
-      <c r="F155" t="s">
-        <v>89</v>
-      </c>
-      <c r="G155" t="s">
-        <v>571</v>
-      </c>
-      <c r="H155" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="156" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A156" t="s">
-        <v>574</v>
-      </c>
-      <c r="C156" t="s">
-        <v>2</v>
-      </c>
-      <c r="D156" t="s">
-        <v>570</v>
-      </c>
-      <c r="E156" t="s">
-        <v>88</v>
-      </c>
-      <c r="F156" t="s">
-        <v>89</v>
-      </c>
-      <c r="G156" t="s">
-        <v>571</v>
-      </c>
-      <c r="H156" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="157" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A157" t="s">
-        <v>575</v>
-      </c>
-      <c r="C157" t="s">
-        <v>9</v>
-      </c>
-      <c r="D157" t="s">
-        <v>576</v>
-      </c>
-      <c r="E157" t="s">
-        <v>44</v>
-      </c>
-      <c r="F157" t="s">
-        <v>45</v>
-      </c>
-      <c r="G157" t="s">
-        <v>166</v>
-      </c>
-      <c r="H157" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="158" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A158" t="s">
-        <v>577</v>
-      </c>
-      <c r="C158" t="s">
-        <v>9</v>
-      </c>
-      <c r="D158" t="s">
-        <v>576</v>
-      </c>
-      <c r="E158" t="s">
-        <v>44</v>
-      </c>
-      <c r="F158" t="s">
-        <v>45</v>
-      </c>
-      <c r="G158" t="s">
-        <v>166</v>
-      </c>
-      <c r="H158" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="159" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A159" t="s">
-        <v>578</v>
-      </c>
-      <c r="C159" t="s">
-        <v>10</v>
-      </c>
-      <c r="D159" t="s">
-        <v>579</v>
-      </c>
-      <c r="E159" t="s">
-        <v>580</v>
-      </c>
-      <c r="F159" t="s">
-        <v>581</v>
-      </c>
-      <c r="G159" t="s">
-        <v>582</v>
-      </c>
-      <c r="H159" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="160" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A160" t="s">
-        <v>583</v>
-      </c>
-      <c r="C160" t="s">
-        <v>2</v>
-      </c>
-      <c r="D160" t="s">
-        <v>584</v>
-      </c>
-      <c r="E160" t="s">
-        <v>585</v>
-      </c>
-      <c r="F160" t="s">
-        <v>586</v>
-      </c>
-      <c r="G160" t="s">
-        <v>587</v>
-      </c>
-      <c r="H160" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="161" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A161" t="s">
-        <v>588</v>
-      </c>
-      <c r="C161" t="s">
-        <v>2</v>
-      </c>
-      <c r="D161" t="s">
-        <v>584</v>
-      </c>
-      <c r="E161" t="s">
-        <v>585</v>
-      </c>
-      <c r="F161" t="s">
-        <v>586</v>
-      </c>
-      <c r="G161" t="s">
-        <v>587</v>
-      </c>
-      <c r="H161" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="162" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A162" t="s">
-        <v>589</v>
-      </c>
-      <c r="C162" t="s">
-        <v>13</v>
-      </c>
-      <c r="D162" t="s">
-        <v>590</v>
-      </c>
-      <c r="E162" t="s">
-        <v>203</v>
-      </c>
-      <c r="F162" t="s">
-        <v>204</v>
-      </c>
-      <c r="G162" t="s">
-        <v>591</v>
-      </c>
-      <c r="H162" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="163" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A163" t="s">
-        <v>592</v>
-      </c>
-      <c r="C163" t="s">
-        <v>13</v>
-      </c>
-      <c r="D163" t="s">
-        <v>590</v>
-      </c>
-      <c r="E163" t="s">
-        <v>203</v>
-      </c>
-      <c r="F163" t="s">
-        <v>204</v>
-      </c>
-      <c r="G163" t="s">
-        <v>591</v>
-      </c>
-      <c r="H163" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="164" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A164" t="s">
-        <v>593</v>
-      </c>
-      <c r="C164" t="s">
-        <v>34</v>
-      </c>
-      <c r="D164" t="s">
-        <v>594</v>
-      </c>
-      <c r="E164" t="s">
-        <v>238</v>
-      </c>
-      <c r="F164" t="s">
-        <v>239</v>
-      </c>
-      <c r="G164" t="s">
-        <v>306</v>
-      </c>
-      <c r="H164" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="165" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A165" t="s">
-        <v>595</v>
-      </c>
-      <c r="C165" t="s">
-        <v>34</v>
-      </c>
-      <c r="D165" t="s">
-        <v>594</v>
-      </c>
-      <c r="E165" t="s">
-        <v>238</v>
-      </c>
-      <c r="F165" t="s">
-        <v>239</v>
-      </c>
-      <c r="G165" t="s">
-        <v>306</v>
-      </c>
-      <c r="H165" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="166" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A166" t="s">
-        <v>596</v>
-      </c>
-      <c r="C166" t="s">
-        <v>29</v>
-      </c>
-      <c r="D166" t="s">
-        <v>597</v>
-      </c>
-      <c r="E166" t="s">
-        <v>79</v>
-      </c>
-      <c r="F166" t="s">
-        <v>30</v>
-      </c>
-      <c r="G166" t="s">
-        <v>62</v>
-      </c>
-      <c r="H166" t="s">
-        <v>117</v>
-      </c>
-    </row>
-    <row r="167" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A167" t="s">
-        <v>598</v>
-      </c>
-      <c r="C167" t="s">
-        <v>35</v>
-      </c>
-      <c r="D167" t="s">
-        <v>599</v>
-      </c>
-      <c r="E167" t="s">
-        <v>104</v>
-      </c>
-      <c r="F167" t="s">
-        <v>0</v>
-      </c>
-      <c r="G167" t="s">
-        <v>600</v>
-      </c>
-      <c r="H167" t="s">
-        <v>601</v>
-      </c>
-    </row>
-    <row r="168" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A168" t="s">
-        <v>602</v>
-      </c>
-      <c r="C168" t="s">
-        <v>59</v>
-      </c>
-      <c r="D168" t="s">
-        <v>603</v>
-      </c>
-      <c r="E168" t="s">
-        <v>604</v>
-      </c>
-      <c r="F168" t="s">
-        <v>0</v>
-      </c>
-      <c r="G168" t="s">
-        <v>605</v>
-      </c>
-      <c r="H168" t="s">
-        <v>601</v>
-      </c>
-    </row>
-    <row r="169" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A169" t="s">
-        <v>606</v>
-      </c>
-      <c r="C169" t="s">
-        <v>59</v>
-      </c>
-      <c r="D169" t="s">
-        <v>603</v>
-      </c>
-      <c r="E169" t="s">
-        <v>604</v>
-      </c>
-      <c r="F169" t="s">
-        <v>0</v>
-      </c>
-      <c r="G169" t="s">
-        <v>605</v>
-      </c>
-      <c r="H169" t="s">
-        <v>601</v>
-      </c>
-    </row>
-    <row r="170" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A170" t="s">
-        <v>607</v>
-      </c>
-      <c r="C170" t="s">
-        <v>59</v>
-      </c>
-      <c r="D170" t="s">
-        <v>603</v>
-      </c>
-      <c r="E170" t="s">
-        <v>604</v>
-      </c>
-      <c r="F170" t="s">
-        <v>0</v>
-      </c>
-      <c r="G170" t="s">
-        <v>605</v>
-      </c>
-      <c r="H170" t="s">
-        <v>601</v>
-      </c>
-    </row>
-    <row r="171" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A171" t="s">
-        <v>608</v>
-      </c>
-      <c r="C171" t="s">
-        <v>13</v>
-      </c>
-      <c r="D171" t="s">
-        <v>608</v>
-      </c>
-      <c r="H171" t="s">
-        <v>610</v>
-      </c>
-    </row>
-    <row r="172" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A172" t="s">
-        <v>609</v>
-      </c>
-      <c r="C172" t="s">
-        <v>3</v>
-      </c>
-      <c r="D172" t="s">
-        <v>609</v>
-      </c>
-      <c r="H172" t="s">
-        <v>610</v>
-      </c>
-    </row>
-    <row r="173" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A173" t="s">
-        <v>505</v>
-      </c>
-      <c r="C173" t="s">
-        <v>32</v>
-      </c>
-      <c r="D173" t="s">
-        <v>505</v>
-      </c>
-      <c r="E173" t="s">
-        <v>18</v>
-      </c>
-      <c r="F173" t="s">
-        <v>0</v>
-      </c>
-      <c r="G173" t="s">
-        <v>506</v>
-      </c>
-      <c r="H173" t="s">
-        <v>5</v>
+        <v>499</v>
       </c>
     </row>
   </sheetData>

--- a/1.xlsx
+++ b/1.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="\\wh.local\fs\UserProfile_TSSWH19\_TSSWH19_redirected_folders\HunyaCs1\Desktop\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{83595A58-D015-4B9D-9A08-8DD44CFD316E}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{226108C0-93EB-4C9A-9B42-6535D0E3DA34}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="0" windowWidth="22260" windowHeight="12648" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1050" uniqueCount="506">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1043" uniqueCount="520">
   <si>
     <t>BUDAPEST</t>
   </si>
@@ -72,12 +72,6 @@
     <t>SZ-832</t>
   </si>
   <si>
-    <t>2112</t>
-  </si>
-  <si>
-    <t>VERESEGYHÁZ</t>
-  </si>
-  <si>
     <t>1165</t>
   </si>
   <si>
@@ -87,9 +81,6 @@
     <t>SZIGETSZENTMIKLÓS</t>
   </si>
   <si>
-    <t>SZ-815</t>
-  </si>
-  <si>
     <t>2330</t>
   </si>
   <si>
@@ -105,9 +96,6 @@
     <t>SZ-830</t>
   </si>
   <si>
-    <t>1134</t>
-  </si>
-  <si>
     <t>SZ-820</t>
   </si>
   <si>
@@ -120,45 +108,18 @@
     <t>1183</t>
   </si>
   <si>
-    <t>1144</t>
-  </si>
-  <si>
-    <t>SZ-829</t>
-  </si>
-  <si>
     <t>2131</t>
   </si>
   <si>
     <t>GÖD</t>
   </si>
   <si>
-    <t>1119</t>
-  </si>
-  <si>
-    <t>2750</t>
-  </si>
-  <si>
-    <t>NAGYKŐRÖS</t>
-  </si>
-  <si>
-    <t>1181</t>
-  </si>
-  <si>
-    <t>SZ-823</t>
-  </si>
-  <si>
     <t>2040</t>
   </si>
   <si>
     <t>BUDAÖRS</t>
   </si>
   <si>
-    <t>Szabadság út</t>
-  </si>
-  <si>
-    <t>1161</t>
-  </si>
-  <si>
     <t>1204</t>
   </si>
   <si>
@@ -168,27 +129,12 @@
     <t>ÉRD</t>
   </si>
   <si>
-    <t>Rákóczi utca</t>
-  </si>
-  <si>
-    <t>1043</t>
-  </si>
-  <si>
-    <t>1188</t>
-  </si>
-  <si>
     <t>1047</t>
   </si>
   <si>
     <t>1221</t>
   </si>
   <si>
-    <t>2225</t>
-  </si>
-  <si>
-    <t>ÜLLŐ</t>
-  </si>
-  <si>
     <t>Dózsa György út</t>
   </si>
   <si>
@@ -216,48 +162,12 @@
     <t>1033</t>
   </si>
   <si>
-    <t>69c39f76d96b4f4a24386478</t>
-  </si>
-  <si>
-    <t>260319-F00012082</t>
-  </si>
-  <si>
-    <t>Virág utca</t>
-  </si>
-  <si>
-    <t>69c3a917d96b4f4a243865fa</t>
-  </si>
-  <si>
-    <t>260321-F00004248</t>
-  </si>
-  <si>
-    <t>1138</t>
-  </si>
-  <si>
-    <t>Cserhalom utca</t>
-  </si>
-  <si>
-    <t>2000</t>
-  </si>
-  <si>
-    <t>SZENTENDRE</t>
-  </si>
-  <si>
     <t>2700</t>
   </si>
   <si>
     <t>CEGLÉD</t>
   </si>
   <si>
-    <t>69c0434bd96b4f4a24383167</t>
-  </si>
-  <si>
-    <t>260322-W00008003</t>
-  </si>
-  <si>
-    <t>Bácska utca</t>
-  </si>
-  <si>
     <t>69c312d7d96b4f4a243861f2</t>
   </si>
   <si>
@@ -267,528 +177,51 @@
     <t>Folyamőr utca</t>
   </si>
   <si>
-    <t>Pesti út</t>
-  </si>
-  <si>
     <t>SELEX</t>
   </si>
   <si>
-    <t>304875165/1</t>
-  </si>
-  <si>
-    <t>304875165</t>
-  </si>
-  <si>
     <t>1146</t>
   </si>
   <si>
-    <t>2234</t>
-  </si>
-  <si>
-    <t>MAGLÓD</t>
-  </si>
-  <si>
-    <t>Ceglédi út</t>
-  </si>
-  <si>
-    <t>Petőfi utca</t>
-  </si>
-  <si>
-    <t>2461</t>
-  </si>
-  <si>
-    <t>TÁRNOK</t>
-  </si>
-  <si>
     <t>1028</t>
   </si>
   <si>
-    <t>Hidegkúti út</t>
-  </si>
-  <si>
-    <t>1087</t>
-  </si>
-  <si>
-    <t>Vörösmarty utca</t>
-  </si>
-  <si>
     <t>1151</t>
   </si>
   <si>
-    <t>248744972/1</t>
-  </si>
-  <si>
-    <t>248744972</t>
-  </si>
-  <si>
-    <t>1113</t>
-  </si>
-  <si>
-    <t>Bocskai út</t>
-  </si>
-  <si>
-    <t>69b13adf51e7020fc80cccc4</t>
-  </si>
-  <si>
-    <t>260311-F00003619</t>
-  </si>
-  <si>
-    <t>2114</t>
-  </si>
-  <si>
-    <t>VALKÓ</t>
-  </si>
-  <si>
-    <t>69c24e64d96b4f4a24384f09</t>
-  </si>
-  <si>
     <t>SZ-814</t>
   </si>
   <si>
-    <t>260317-F00004392</t>
-  </si>
-  <si>
-    <t>1086</t>
-  </si>
-  <si>
-    <t>Szerdahelyi utca</t>
-  </si>
-  <si>
-    <t>69b9506ad96b4f4a2437cfb2</t>
-  </si>
-  <si>
-    <t>260317-F00008559</t>
-  </si>
-  <si>
-    <t>2113</t>
-  </si>
-  <si>
-    <t>ERDŐKERTES</t>
-  </si>
-  <si>
-    <t>Katona József utca</t>
-  </si>
-  <si>
-    <t>69c3c301d96b4f4a24386a3c</t>
-  </si>
-  <si>
-    <t>260320-F00001288-1</t>
-  </si>
-  <si>
-    <t>Arany János utca</t>
-  </si>
-  <si>
-    <t>69c3b690d96b4f4a24386839</t>
-  </si>
-  <si>
-    <t>260320-F00007295-1</t>
-  </si>
-  <si>
-    <t>2132</t>
-  </si>
-  <si>
-    <t>Turista utca</t>
-  </si>
-  <si>
-    <t>69c29331d96b4f4a243858db</t>
-  </si>
-  <si>
-    <t>260320-F00010459</t>
-  </si>
-  <si>
-    <t>Deákvári főút</t>
-  </si>
-  <si>
-    <t>69bd1d58d96b4f4a24380db3</t>
-  </si>
-  <si>
-    <t>260320-W00003345</t>
-  </si>
-  <si>
-    <t>2336</t>
-  </si>
-  <si>
-    <t>DUNAVARSÁNY</t>
-  </si>
-  <si>
-    <t>69bd9114d96b4f4a24381a9a</t>
-  </si>
-  <si>
-    <t>260320-W00009564</t>
-  </si>
-  <si>
     <t>1131</t>
   </si>
   <si>
-    <t>Keszkenő utca</t>
-  </si>
-  <si>
-    <t>69c26760d96b4f4a243852e1</t>
-  </si>
-  <si>
-    <t>260323-F00002502</t>
-  </si>
-  <si>
-    <t>1097</t>
-  </si>
-  <si>
-    <t>Vágóhíd utca</t>
-  </si>
-  <si>
-    <t>69c10e5fd96b4f4a24383804</t>
-  </si>
-  <si>
-    <t>260323-F00003631</t>
-  </si>
-  <si>
-    <t>2713</t>
-  </si>
-  <si>
-    <t>CSEMŐ</t>
-  </si>
-  <si>
-    <t>69c10e5fd96b4f4a24383805</t>
-  </si>
-  <si>
-    <t>69c12eefd96b4f4a24383dc1</t>
-  </si>
-  <si>
-    <t>260323-F00007335</t>
-  </si>
-  <si>
-    <t>Pannónia utca</t>
-  </si>
-  <si>
-    <t>69c283e4d96b4f4a24385678</t>
-  </si>
-  <si>
-    <t>260324-F00006893</t>
-  </si>
-  <si>
-    <t>Nagymező utca</t>
-  </si>
-  <si>
-    <t>69c283e4d96b4f4a24385679</t>
-  </si>
-  <si>
-    <t>69c28e68d96b4f4a243857fb</t>
-  </si>
-  <si>
-    <t>260324-F00008154</t>
-  </si>
-  <si>
-    <t>Géza utca</t>
-  </si>
-  <si>
-    <t>69c290bdd96b4f4a2438584a</t>
-  </si>
-  <si>
-    <t>260324-F00008791</t>
-  </si>
-  <si>
     <t>2730</t>
   </si>
   <si>
     <t>ALBERTIRSA</t>
   </si>
   <si>
-    <t>Pacsirta utca</t>
-  </si>
-  <si>
-    <t>69c28f96d96b4f4a24385815</t>
-  </si>
-  <si>
-    <t>260324-W00005290</t>
-  </si>
-  <si>
-    <t>2366</t>
-  </si>
-  <si>
-    <t>KAKUCS</t>
-  </si>
-  <si>
-    <t>69c28f96d96b4f4a24385818</t>
-  </si>
-  <si>
-    <t>69c28f96d96b4f4a2438581a</t>
-  </si>
-  <si>
-    <t>69c2d979d96b4f4a2438608b</t>
-  </si>
-  <si>
-    <t>260324-W00009019</t>
-  </si>
-  <si>
     <t>1037</t>
   </si>
   <si>
-    <t>Kolostor út</t>
-  </si>
-  <si>
-    <t>69c2d979d96b4f4a2438608c</t>
-  </si>
-  <si>
-    <t>69c3b6e3d96b4f4a2438683f</t>
-  </si>
-  <si>
-    <t>260325-F00004204</t>
-  </si>
-  <si>
-    <t>Harangvirág utca</t>
-  </si>
-  <si>
-    <t>69c3dce7d96b4f4a24386da8</t>
-  </si>
-  <si>
-    <t>260325-F00007874</t>
-  </si>
-  <si>
-    <t>Barcsay utca</t>
-  </si>
-  <si>
-    <t>69c3db40d96b4f4a24386d5f</t>
-  </si>
-  <si>
-    <t>260325-F00007942</t>
-  </si>
-  <si>
-    <t>Wesselényi utca</t>
-  </si>
-  <si>
-    <t>69c3ef8bd96b4f4a24387068</t>
-  </si>
-  <si>
-    <t>260325-F00009953-2</t>
-  </si>
-  <si>
-    <t>Kőérberki út</t>
-  </si>
-  <si>
-    <t>69c408f5d96b4f4a243873a2</t>
-  </si>
-  <si>
-    <t>260325-F00012188</t>
-  </si>
-  <si>
-    <t>Lehel utca</t>
-  </si>
-  <si>
-    <t>69c42f99d96b4f4a24387654</t>
-  </si>
-  <si>
-    <t>260325-F00013344</t>
-  </si>
-  <si>
-    <t>Hunyadi utca</t>
-  </si>
-  <si>
-    <t>69c42f9ad96b4f4a24387657</t>
-  </si>
-  <si>
     <t>SZ-835</t>
   </si>
   <si>
-    <t>260325-F00013551</t>
-  </si>
-  <si>
-    <t>1067</t>
-  </si>
-  <si>
-    <t>Teréz körút</t>
-  </si>
-  <si>
-    <t>69c3d560d96b4f4a24386c9b</t>
-  </si>
-  <si>
-    <t>260325-W00004201</t>
-  </si>
-  <si>
     <t>1107</t>
   </si>
   <si>
-    <t>Gém utca</t>
-  </si>
-  <si>
-    <t>69c3e162d96b4f4a24386e8b</t>
-  </si>
-  <si>
-    <t>260325-W00005253</t>
-  </si>
-  <si>
-    <t>Gyógyszergyár utca</t>
-  </si>
-  <si>
-    <t>69c43eeed96b4f4a243876f2</t>
-  </si>
-  <si>
-    <t>260325-W00009456</t>
-  </si>
-  <si>
-    <t>Égerfa utca</t>
-  </si>
-  <si>
-    <t>69c4fde1d96b4f4a24387c6c</t>
-  </si>
-  <si>
-    <t>260326-F00002610</t>
-  </si>
-  <si>
-    <t>Róbert Károly körút</t>
-  </si>
-  <si>
-    <t>FIZZ-1000849314</t>
-  </si>
-  <si>
-    <t>267004465</t>
-  </si>
-  <si>
     <t>2315</t>
   </si>
   <si>
     <t>SZIGETHALOM</t>
   </si>
   <si>
-    <t>Mű út</t>
-  </si>
-  <si>
-    <t>1449-948833</t>
-  </si>
-  <si>
-    <t>267004466</t>
-  </si>
-  <si>
-    <t>1213</t>
-  </si>
-  <si>
-    <t>Tancsics Mihaly Utca</t>
-  </si>
-  <si>
-    <t>26MPE0003293/1</t>
-  </si>
-  <si>
-    <t>26MPE0003293</t>
-  </si>
-  <si>
-    <t>Kossuth Lajos út</t>
-  </si>
-  <si>
     <t>MEGAPLACE</t>
   </si>
   <si>
-    <t>26MPE0003300/1</t>
-  </si>
-  <si>
-    <t>26MPE0003300</t>
-  </si>
-  <si>
     <t>1112</t>
   </si>
   <si>
-    <t>FACSEMETE UTCA</t>
-  </si>
-  <si>
-    <t>304576536/1</t>
-  </si>
-  <si>
-    <t>304576536</t>
-  </si>
-  <si>
-    <t>füredi utca</t>
-  </si>
-  <si>
-    <t>304826661/1</t>
-  </si>
-  <si>
-    <t>304826661</t>
-  </si>
-  <si>
-    <t>1182</t>
-  </si>
-  <si>
-    <t>Halomi út</t>
-  </si>
-  <si>
-    <t>304826661/2</t>
-  </si>
-  <si>
-    <t>304826661/3</t>
-  </si>
-  <si>
-    <t>304875527/1</t>
-  </si>
-  <si>
-    <t>304875527</t>
-  </si>
-  <si>
-    <t>1148</t>
-  </si>
-  <si>
-    <t>Nagy Lajos király útja</t>
-  </si>
-  <si>
-    <t>304925187/1</t>
-  </si>
-  <si>
-    <t>304925187</t>
-  </si>
-  <si>
-    <t>Népfürdő utca</t>
-  </si>
-  <si>
-    <t>304963429/1</t>
-  </si>
-  <si>
-    <t>304963429</t>
-  </si>
-  <si>
-    <t>Folyamőr Utca</t>
-  </si>
-  <si>
-    <t>304963429/2</t>
-  </si>
-  <si>
-    <t>305169860/2/1</t>
-  </si>
-  <si>
-    <t>305169860/2</t>
-  </si>
-  <si>
-    <t>2351</t>
-  </si>
-  <si>
-    <t>ALSÓNÉMEDI</t>
-  </si>
-  <si>
-    <t>Halászy Károly Utca</t>
-  </si>
-  <si>
-    <t>305169860/2/2</t>
-  </si>
-  <si>
-    <t>305169860/2/3</t>
-  </si>
-  <si>
-    <t>305225419/1</t>
-  </si>
-  <si>
-    <t>305225419</t>
-  </si>
-  <si>
-    <t>Mátyás király utca</t>
-  </si>
-  <si>
-    <t>305225419/2</t>
-  </si>
-  <si>
-    <t>305272678/1</t>
-  </si>
-  <si>
-    <t>305272678</t>
-  </si>
-  <si>
-    <t>Hadak útja</t>
-  </si>
-  <si>
     <t>305273127/1</t>
   </si>
   <si>
@@ -804,748 +237,1357 @@
     <t>305273127/3</t>
   </si>
   <si>
-    <t>305273217/1</t>
-  </si>
-  <si>
-    <t>305273217</t>
-  </si>
-  <si>
-    <t>305273217/2</t>
-  </si>
-  <si>
-    <t>305316045/1</t>
-  </si>
-  <si>
-    <t>305316045</t>
-  </si>
-  <si>
-    <t>Kalapács utca</t>
-  </si>
-  <si>
-    <t>305367873/1</t>
-  </si>
-  <si>
-    <t>305367873</t>
-  </si>
-  <si>
-    <t>Montevideo utca</t>
-  </si>
-  <si>
-    <t>305367873/2</t>
-  </si>
-  <si>
-    <t>305368467/1</t>
-  </si>
-  <si>
-    <t>305368467</t>
-  </si>
-  <si>
-    <t>Lenvirág utca</t>
-  </si>
-  <si>
-    <t>305411534/1</t>
-  </si>
-  <si>
-    <t>305411534</t>
-  </si>
-  <si>
-    <t>305411534/2</t>
-  </si>
-  <si>
-    <t>305411632/1</t>
-  </si>
-  <si>
-    <t>305411632</t>
-  </si>
-  <si>
     <t>Kossuth Lajos utca</t>
   </si>
   <si>
-    <t>305411632/2</t>
-  </si>
-  <si>
-    <t>305411632/3</t>
-  </si>
-  <si>
-    <t>305412274/1</t>
-  </si>
-  <si>
-    <t>305412274</t>
-  </si>
-  <si>
-    <t>Károlyi István utca</t>
-  </si>
-  <si>
-    <t>305461509/1</t>
-  </si>
-  <si>
-    <t>305461509</t>
-  </si>
-  <si>
-    <t>305461509/2</t>
-  </si>
-  <si>
-    <t>305461526/1</t>
-  </si>
-  <si>
-    <t>305461526</t>
-  </si>
-  <si>
-    <t>Dr. Lengyel Lajos utca</t>
-  </si>
-  <si>
-    <t>305461661/1</t>
-  </si>
-  <si>
-    <t>305461661</t>
-  </si>
-  <si>
-    <t>1061</t>
-  </si>
-  <si>
-    <t>Káldy Gyula utca</t>
-  </si>
-  <si>
-    <t>305461842/1</t>
-  </si>
-  <si>
-    <t>305461842</t>
-  </si>
-  <si>
-    <t>1094</t>
-  </si>
-  <si>
-    <t>Ferenc körút</t>
-  </si>
-  <si>
-    <t>305461842/2</t>
-  </si>
-  <si>
-    <t>305462350/1</t>
-  </si>
-  <si>
-    <t>305462350</t>
-  </si>
-  <si>
-    <t>Gyáli Út</t>
-  </si>
-  <si>
-    <t>305514164/1</t>
-  </si>
-  <si>
-    <t>305514164</t>
-  </si>
-  <si>
     <t>1142</t>
   </si>
   <si>
-    <t>Sárrét park</t>
-  </si>
-  <si>
-    <t>305514179/1</t>
-  </si>
-  <si>
-    <t>305514179</t>
-  </si>
-  <si>
     <t>1172</t>
   </si>
   <si>
     <t>Hidasnémeti utca</t>
   </si>
   <si>
-    <t>305514421/1</t>
-  </si>
-  <si>
-    <t>305514421</t>
-  </si>
-  <si>
-    <t>Cziffra György utca</t>
-  </si>
-  <si>
-    <t>305514421/2</t>
-  </si>
-  <si>
-    <t>305514421/3</t>
-  </si>
-  <si>
-    <t>305514425/1</t>
-  </si>
-  <si>
-    <t>305514425</t>
-  </si>
-  <si>
-    <t>Márton utca</t>
-  </si>
-  <si>
-    <t>305514520/1</t>
-  </si>
-  <si>
-    <t>305514520</t>
-  </si>
-  <si>
-    <t>Batthyány utca</t>
-  </si>
-  <si>
-    <t>305514591/1</t>
-  </si>
-  <si>
-    <t>305514591</t>
-  </si>
-  <si>
-    <t>2241</t>
-  </si>
-  <si>
-    <t>SÜLYSÁP</t>
-  </si>
-  <si>
-    <t>Vak Bottyán Utca</t>
-  </si>
-  <si>
-    <t>305556937/1</t>
-  </si>
-  <si>
-    <t>305556937</t>
-  </si>
-  <si>
-    <t>Fészekrakó utca</t>
-  </si>
-  <si>
-    <t>305557043/1</t>
-  </si>
-  <si>
-    <t>305557043</t>
-  </si>
-  <si>
-    <t>2740</t>
-  </si>
-  <si>
-    <t>ABONY</t>
-  </si>
-  <si>
-    <t>Nép út</t>
-  </si>
-  <si>
-    <t>305557043/2</t>
-  </si>
-  <si>
-    <t>305557076/1</t>
-  </si>
-  <si>
-    <t>305557076</t>
-  </si>
-  <si>
     <t>1135</t>
   </si>
   <si>
-    <t>Frangepán utca</t>
-  </si>
-  <si>
-    <t>305557116/1</t>
-  </si>
-  <si>
-    <t>305557116</t>
-  </si>
-  <si>
-    <t>Ciprus utca</t>
-  </si>
-  <si>
-    <t>305557116/2</t>
-  </si>
-  <si>
-    <t>305557116/3</t>
-  </si>
-  <si>
-    <t>305557127/1</t>
-  </si>
-  <si>
-    <t>305557127</t>
-  </si>
-  <si>
-    <t>Thaly Kálmán utca</t>
-  </si>
-  <si>
-    <t>305557206/1</t>
-  </si>
-  <si>
-    <t>305557206</t>
-  </si>
-  <si>
-    <t>1036</t>
-  </si>
-  <si>
-    <t>Pacsirtamező utca</t>
-  </si>
-  <si>
-    <t>305557206/2</t>
-  </si>
-  <si>
-    <t>305557240/1</t>
-  </si>
-  <si>
-    <t>305557240</t>
-  </si>
-  <si>
-    <t>305557457/1</t>
-  </si>
-  <si>
-    <t>305557457</t>
-  </si>
-  <si>
-    <t>Huszka Jenő utca</t>
-  </si>
-  <si>
-    <t>305557485/1</t>
-  </si>
-  <si>
-    <t>305557485</t>
-  </si>
-  <si>
-    <t>Kolozsvári Utca</t>
-  </si>
-  <si>
-    <t>305557510/1</t>
-  </si>
-  <si>
-    <t>305557510</t>
-  </si>
-  <si>
-    <t>2335</t>
-  </si>
-  <si>
-    <t>TAKSONY</t>
-  </si>
-  <si>
-    <t>Bugyi út</t>
-  </si>
-  <si>
-    <t>305557510/2</t>
-  </si>
-  <si>
-    <t>305557607/1</t>
-  </si>
-  <si>
-    <t>305557607</t>
-  </si>
-  <si>
-    <t>2084</t>
-  </si>
-  <si>
-    <t>PILISSZENTIVÁN</t>
-  </si>
-  <si>
-    <t>305557607/2</t>
-  </si>
-  <si>
-    <t>305557633/1</t>
-  </si>
-  <si>
-    <t>305557633</t>
-  </si>
-  <si>
     <t>1046</t>
   </si>
   <si>
-    <t>Klauzál utca</t>
-  </si>
-  <si>
-    <t>305557678/1</t>
-  </si>
-  <si>
-    <t>305557678</t>
-  </si>
-  <si>
-    <t>Egressy Béni utca</t>
-  </si>
-  <si>
-    <t>305557697/1</t>
-  </si>
-  <si>
-    <t>305557697</t>
-  </si>
-  <si>
-    <t>1029</t>
-  </si>
-  <si>
-    <t>Zerind vezér utca</t>
-  </si>
-  <si>
-    <t>305557707/1</t>
-  </si>
-  <si>
-    <t>305557707</t>
-  </si>
-  <si>
-    <t>2217</t>
-  </si>
-  <si>
-    <t>GOMBA</t>
-  </si>
-  <si>
-    <t>Külterület kültelek</t>
-  </si>
-  <si>
-    <t>305627959/1</t>
-  </si>
-  <si>
-    <t>305627959</t>
-  </si>
-  <si>
-    <t>Vasvári Pál utca</t>
-  </si>
-  <si>
-    <t>305627959/2</t>
-  </si>
-  <si>
-    <t>305628104/1</t>
-  </si>
-  <si>
-    <t>305628104</t>
-  </si>
-  <si>
-    <t>305628296/1</t>
-  </si>
-  <si>
-    <t>305628296</t>
-  </si>
-  <si>
-    <t>1132</t>
-  </si>
-  <si>
-    <t>Gyöngyház utca</t>
-  </si>
-  <si>
-    <t>305628296/2</t>
-  </si>
-  <si>
-    <t>305628358/1</t>
-  </si>
-  <si>
-    <t>305628358</t>
-  </si>
-  <si>
-    <t>2209</t>
-  </si>
-  <si>
-    <t>PÉTERI</t>
-  </si>
-  <si>
-    <t>Ady Endre utca</t>
-  </si>
-  <si>
-    <t>305628390/1</t>
-  </si>
-  <si>
-    <t>305628390</t>
-  </si>
-  <si>
-    <t>Havanna utca</t>
-  </si>
-  <si>
-    <t>305628560/1</t>
-  </si>
-  <si>
-    <t>305628560</t>
-  </si>
-  <si>
-    <t>1088</t>
-  </si>
-  <si>
-    <t>Krúdy Gyula utca</t>
-  </si>
-  <si>
-    <t>305628668/1</t>
-  </si>
-  <si>
-    <t>305628668</t>
-  </si>
-  <si>
-    <t>Diósy Lajos Utca</t>
-  </si>
-  <si>
-    <t>305628708/1</t>
-  </si>
-  <si>
-    <t>305628708</t>
-  </si>
-  <si>
     <t>1205</t>
   </si>
   <si>
-    <t>Bádogos utca</t>
-  </si>
-  <si>
-    <t>305628716/1</t>
-  </si>
-  <si>
-    <t>305628716</t>
-  </si>
-  <si>
-    <t>József Attila útja</t>
-  </si>
-  <si>
-    <t>305628794/1</t>
-  </si>
-  <si>
-    <t>305628794</t>
-  </si>
-  <si>
     <t>1054</t>
   </si>
   <si>
-    <t>Vadász utca</t>
-  </si>
-  <si>
-    <t>305666953/1</t>
-  </si>
-  <si>
-    <t>305666953</t>
-  </si>
-  <si>
-    <t>1195</t>
-  </si>
-  <si>
-    <t>Zrínyi utca</t>
-  </si>
-  <si>
-    <t>305666958/1</t>
-  </si>
-  <si>
-    <t>305666958</t>
-  </si>
-  <si>
-    <t>2191</t>
-  </si>
-  <si>
-    <t>BAG</t>
-  </si>
-  <si>
-    <t>Malom utca</t>
-  </si>
-  <si>
-    <t>305666958/2</t>
-  </si>
-  <si>
-    <t>305667035/1</t>
-  </si>
-  <si>
-    <t>305667035</t>
-  </si>
-  <si>
-    <t>Zólyomi út</t>
-  </si>
-  <si>
-    <t>305667035/2</t>
-  </si>
-  <si>
-    <t>305667066/1</t>
-  </si>
-  <si>
-    <t>305667066</t>
-  </si>
-  <si>
-    <t>305667140/1</t>
-  </si>
-  <si>
-    <t>305667140</t>
-  </si>
-  <si>
     <t>2083</t>
   </si>
   <si>
     <t>SOLYMÁR</t>
   </si>
   <si>
-    <t>Hóvirág utca</t>
-  </si>
-  <si>
-    <t>305667140/2</t>
-  </si>
-  <si>
-    <t>305667140/3</t>
-  </si>
-  <si>
-    <t>305667163/1</t>
-  </si>
-  <si>
-    <t>305667163</t>
-  </si>
-  <si>
-    <t>1027</t>
-  </si>
-  <si>
-    <t>Frankel Leó út</t>
-  </si>
-  <si>
-    <t>305667360/1</t>
-  </si>
-  <si>
-    <t>305667360</t>
-  </si>
-  <si>
     <t>2337</t>
   </si>
   <si>
     <t>DÉLEGYHÁZA</t>
   </si>
   <si>
-    <t>Dózsa György utca</t>
-  </si>
-  <si>
-    <t>202603262600668601</t>
-  </si>
-  <si>
-    <t>NFD6-03-19-Z3KA</t>
-  </si>
-  <si>
-    <t>Üllői út</t>
-  </si>
-  <si>
-    <t>202603262600677301</t>
-  </si>
-  <si>
-    <t>NFD6-03-20-Q6RK</t>
-  </si>
-  <si>
-    <t>Vihorlát út</t>
-  </si>
-  <si>
-    <t>202603242600707601</t>
-  </si>
-  <si>
-    <t>NFD6-03-23-PHCH</t>
-  </si>
-  <si>
-    <t>202603252600719101</t>
-  </si>
-  <si>
-    <t>NFD6-03-24-JSVU</t>
-  </si>
-  <si>
     <t>1164</t>
   </si>
   <si>
-    <t>Lucernás utca</t>
-  </si>
-  <si>
-    <t>202603262600724901</t>
-  </si>
-  <si>
-    <t>NFD6-03-25-485U</t>
-  </si>
-  <si>
-    <t>Eperjes utca</t>
-  </si>
-  <si>
-    <t>202603262600725601</t>
-  </si>
-  <si>
-    <t>NFD6-03-25-4UM4</t>
-  </si>
-  <si>
-    <t>2011</t>
-  </si>
-  <si>
-    <t>BUDAKALÁSZ</t>
-  </si>
-  <si>
     <t>Jókai Mór utca</t>
   </si>
   <si>
-    <t>202603262600725602</t>
-  </si>
-  <si>
-    <t>202603262600725301</t>
-  </si>
-  <si>
-    <t>NFD6-03-25-988N</t>
-  </si>
-  <si>
-    <t>Kerektó utca</t>
-  </si>
-  <si>
-    <t>202603262600730601</t>
-  </si>
-  <si>
-    <t>NFD6-03-25-R44V</t>
-  </si>
-  <si>
-    <t>202603232600686301</t>
-  </si>
-  <si>
-    <t>NFE6-03-21-2C5Z</t>
-  </si>
-  <si>
-    <t>1211</t>
-  </si>
-  <si>
-    <t>II. Rákóczi Ferenc út</t>
-  </si>
-  <si>
-    <t>202603232600686302</t>
-  </si>
-  <si>
-    <t>202603252600718501</t>
-  </si>
-  <si>
-    <t>NFE6-03-24-DK5Y</t>
-  </si>
-  <si>
-    <t>202603262600724401</t>
-  </si>
-  <si>
-    <t>NFE6-03-25-2DQ7</t>
-  </si>
-  <si>
-    <t>Balaton utca</t>
-  </si>
-  <si>
-    <t>202603262600730901</t>
-  </si>
-  <si>
-    <t>NFE6-03-25-BG7K</t>
-  </si>
-  <si>
     <t>2013</t>
   </si>
   <si>
     <t>POMÁZ</t>
   </si>
   <si>
-    <t>Szentendrei út</t>
-  </si>
-  <si>
-    <t>202603262600730902</t>
-  </si>
-  <si>
-    <t>159995579538580253</t>
-  </si>
-  <si>
-    <t>R414292</t>
-  </si>
-  <si>
-    <t>Ba-Ko köz</t>
-  </si>
-  <si>
-    <t>INSPORT</t>
-  </si>
-  <si>
-    <t>159995579538580260</t>
-  </si>
-  <si>
-    <t>159995579538580314</t>
-  </si>
-  <si>
-    <t>SZ 2026 137593</t>
-  </si>
-  <si>
     <t>1084</t>
   </si>
   <si>
-    <t>Rákóczi tér</t>
-  </si>
-  <si>
-    <t>159995579538580321</t>
+    <t>248745137/1</t>
+  </si>
+  <si>
+    <t>248745137</t>
+  </si>
+  <si>
+    <t>Laky Adolf utca</t>
+  </si>
+  <si>
+    <t>248745137/2</t>
+  </si>
+  <si>
+    <t>248745137/3</t>
+  </si>
+  <si>
+    <t>69c51fe2d96b4f4a243880e3</t>
+  </si>
+  <si>
+    <t>SZ-828</t>
+  </si>
+  <si>
+    <t>260305-F00013849-1</t>
+  </si>
+  <si>
+    <t>Varsa köz</t>
+  </si>
+  <si>
+    <t>69c10f9dd96b4f4a2438383b</t>
+  </si>
+  <si>
+    <t>260316-F00010130</t>
+  </si>
+  <si>
+    <t>1034</t>
+  </si>
+  <si>
+    <t>Bécsi út</t>
+  </si>
+  <si>
+    <t>69bac3ecd96b4f4a2437ec51</t>
+  </si>
+  <si>
+    <t>SZ-809</t>
+  </si>
+  <si>
+    <t>260318-F00011706</t>
+  </si>
+  <si>
+    <t>2253</t>
+  </si>
+  <si>
+    <t>TÁPIÓSÁG</t>
+  </si>
+  <si>
+    <t>Forgács utca</t>
+  </si>
+  <si>
+    <t>69c2ba7ed96b4f4a24385de2</t>
+  </si>
+  <si>
+    <t>260320-F00012558</t>
+  </si>
+  <si>
+    <t>1214</t>
+  </si>
+  <si>
+    <t>Szent István út</t>
+  </si>
+  <si>
+    <t>69c63d28d96b4f4a24388da2</t>
+  </si>
+  <si>
+    <t>260323-F00011559</t>
+  </si>
+  <si>
+    <t>1203</t>
+  </si>
+  <si>
+    <t>Baross utca</t>
+  </si>
+  <si>
+    <t>69c3fe6bd96b4f4a2438728b</t>
+  </si>
+  <si>
+    <t>260325-F00011314</t>
+  </si>
+  <si>
+    <t>Patkó utca</t>
+  </si>
+  <si>
+    <t>69c40317d96b4f4a24387301</t>
+  </si>
+  <si>
+    <t>260325-F00011584</t>
+  </si>
+  <si>
+    <t>Völgy utca</t>
+  </si>
+  <si>
+    <t>69c40317d96b4f4a24387304</t>
+  </si>
+  <si>
+    <t>69c3fb18d96b4f4a2438722b</t>
+  </si>
+  <si>
+    <t>260325-W00006456</t>
+  </si>
+  <si>
+    <t>Rákóczi út</t>
+  </si>
+  <si>
+    <t>69c40d6bd96b4f4a243873ff</t>
+  </si>
+  <si>
+    <t>260325-W00006951</t>
+  </si>
+  <si>
+    <t>Diófa utca</t>
+  </si>
+  <si>
+    <t>69c40d6bd96b4f4a24387401</t>
+  </si>
+  <si>
+    <t>69c4069ad96b4f4a2438735b</t>
+  </si>
+  <si>
+    <t>260325-W00007033</t>
+  </si>
+  <si>
+    <t>2135</t>
+  </si>
+  <si>
+    <t>CSÖRÖG</t>
+  </si>
+  <si>
+    <t>Komáromi utca</t>
+  </si>
+  <si>
+    <t>69c4ea28d96b4f4a2438794c</t>
+  </si>
+  <si>
+    <t>260326-F00000925</t>
+  </si>
+  <si>
+    <t>2711</t>
+  </si>
+  <si>
+    <t>TÁPIÓSZENTMÁRTON</t>
+  </si>
+  <si>
+    <t>Szelei út</t>
+  </si>
+  <si>
+    <t>69c5015fd96b4f4a24387d1c</t>
+  </si>
+  <si>
+    <t>260326-F00002900</t>
+  </si>
+  <si>
+    <t>2360</t>
+  </si>
+  <si>
+    <t>GYÁL</t>
+  </si>
+  <si>
+    <t>Csontos József utca</t>
+  </si>
+  <si>
+    <t>69c517f7d96b4f4a24388022</t>
+  </si>
+  <si>
+    <t>260326-F00005629</t>
+  </si>
+  <si>
+    <t>2115</t>
+  </si>
+  <si>
+    <t>VÁCSZENTLÁSZLÓ</t>
+  </si>
+  <si>
+    <t>Kossuth utca</t>
+  </si>
+  <si>
+    <t>69c54813d96b4f4a2438865f</t>
+  </si>
+  <si>
+    <t>260326-F00009741</t>
+  </si>
+  <si>
+    <t>1184</t>
+  </si>
+  <si>
+    <t>Rezeda utca</t>
+  </si>
+  <si>
+    <t>69c564fdd96b4f4a2438891f</t>
+  </si>
+  <si>
+    <t>SZ-840</t>
+  </si>
+  <si>
+    <t>260326-F00011628</t>
+  </si>
+  <si>
+    <t>1115</t>
+  </si>
+  <si>
+    <t>Fraknó utca</t>
+  </si>
+  <si>
+    <t>69c564fdd96b4f4a24388920</t>
+  </si>
+  <si>
+    <t>69c4f95dd96b4f4a24387bbe</t>
+  </si>
+  <si>
+    <t>260326-W00002321</t>
+  </si>
+  <si>
+    <t>2371</t>
+  </si>
+  <si>
+    <t>DABAS</t>
+  </si>
+  <si>
+    <t>Madách Imre utca</t>
+  </si>
+  <si>
+    <t>69c5399ed96b4f4a24388479</t>
+  </si>
+  <si>
+    <t>260326-W00005763</t>
+  </si>
+  <si>
+    <t>69c53e4cd96b4f4a2438851a</t>
+  </si>
+  <si>
+    <t>SZ-827</t>
+  </si>
+  <si>
+    <t>260326-W00005973</t>
+  </si>
+  <si>
+    <t>1015</t>
+  </si>
+  <si>
+    <t>Csalogány utca</t>
+  </si>
+  <si>
+    <t>69c53e54d96b4f4a2438852f</t>
+  </si>
+  <si>
+    <t>260326-W00006020</t>
+  </si>
+  <si>
+    <t>1026</t>
+  </si>
+  <si>
+    <t>Pasaréti út</t>
+  </si>
+  <si>
+    <t>69c65c43d96b4f4a24389233</t>
+  </si>
+  <si>
+    <t>260327-F00003672</t>
+  </si>
+  <si>
+    <t>Felsőmalom utca</t>
+  </si>
+  <si>
+    <t>69c665c7d96b4f4a24389385</t>
+  </si>
+  <si>
+    <t>260327-W00002647</t>
+  </si>
+  <si>
+    <t>1239</t>
+  </si>
+  <si>
+    <t>Péter Apostol utca</t>
+  </si>
+  <si>
+    <t>69c665c7d96b4f4a24389386</t>
+  </si>
+  <si>
+    <t>69c665c7d96b4f4a2438938a</t>
+  </si>
+  <si>
+    <t>69c65d6cd96b4f4a24389253</t>
+  </si>
+  <si>
+    <t>260327-W00002989</t>
+  </si>
+  <si>
+    <t>1126</t>
+  </si>
+  <si>
+    <t>Böszörményi út</t>
+  </si>
+  <si>
+    <t>FIZZ-1000849440</t>
+  </si>
+  <si>
+    <t>267004499</t>
+  </si>
+  <si>
+    <t>Kalman Imre utca</t>
+  </si>
+  <si>
+    <t>FIZZ-1000850493</t>
+  </si>
+  <si>
+    <t>SZ-818</t>
+  </si>
+  <si>
+    <t>267004502</t>
+  </si>
+  <si>
+    <t>1044</t>
+  </si>
+  <si>
+    <t>Megyeri út</t>
+  </si>
+  <si>
+    <t>26MPE0003367/1</t>
+  </si>
+  <si>
+    <t>26MPE0003367</t>
+  </si>
+  <si>
+    <t>Ady Endre tér</t>
+  </si>
+  <si>
+    <t>26MPE0003369/1</t>
+  </si>
+  <si>
+    <t>26MPE0003369</t>
+  </si>
+  <si>
+    <t>1096</t>
+  </si>
+  <si>
+    <t>Sobieski János utca</t>
+  </si>
+  <si>
+    <t>26MPE0003399/1</t>
+  </si>
+  <si>
+    <t>26MPE0003399</t>
+  </si>
+  <si>
+    <t>303005689/1</t>
+  </si>
+  <si>
+    <t>303005689</t>
+  </si>
+  <si>
+    <t>Termálfürdő körút</t>
+  </si>
+  <si>
+    <t>304362671/1</t>
+  </si>
+  <si>
+    <t>304362671</t>
+  </si>
+  <si>
+    <t>1089</t>
+  </si>
+  <si>
+    <t>Delej utca</t>
+  </si>
+  <si>
+    <t>304362671/2</t>
+  </si>
+  <si>
+    <t>304826827/1</t>
+  </si>
+  <si>
+    <t>304826827</t>
+  </si>
+  <si>
+    <t>1153</t>
+  </si>
+  <si>
+    <t>Bocskai Utca</t>
+  </si>
+  <si>
+    <t>304826827/2</t>
+  </si>
+  <si>
+    <t>305170764/1</t>
+  </si>
+  <si>
+    <t>305170764</t>
+  </si>
+  <si>
+    <t>2045</t>
+  </si>
+  <si>
+    <t>TÖRÖKBÁLINT</t>
+  </si>
+  <si>
+    <t>Kinizsi Pál</t>
+  </si>
+  <si>
+    <t>305273366/1</t>
+  </si>
+  <si>
+    <t>305273366</t>
+  </si>
+  <si>
+    <t>Fecske utca</t>
+  </si>
+  <si>
+    <t>305315270/1</t>
+  </si>
+  <si>
+    <t>305315270</t>
+  </si>
+  <si>
+    <t>2100</t>
+  </si>
+  <si>
+    <t>GÖDÖLLŐ</t>
+  </si>
+  <si>
+    <t>Szív utca</t>
+  </si>
+  <si>
+    <t>305368730/1</t>
+  </si>
+  <si>
+    <t>305368730</t>
+  </si>
+  <si>
+    <t>1143</t>
+  </si>
+  <si>
+    <t>Zászlós utca</t>
+  </si>
+  <si>
+    <t>305412140/1</t>
+  </si>
+  <si>
+    <t>305412140</t>
+  </si>
+  <si>
+    <t>1149</t>
+  </si>
+  <si>
+    <t>Bosnyák tér</t>
+  </si>
+  <si>
+    <t>305412442/1</t>
+  </si>
+  <si>
+    <t>305412442</t>
+  </si>
+  <si>
+    <t>305412442/2</t>
+  </si>
+  <si>
+    <t>305412442/3</t>
+  </si>
+  <si>
+    <t>305557165/1</t>
+  </si>
+  <si>
+    <t>305557165</t>
+  </si>
+  <si>
+    <t>2230</t>
+  </si>
+  <si>
+    <t>GYÖMRŐ</t>
+  </si>
+  <si>
+    <t>305557165/2</t>
+  </si>
+  <si>
+    <t>305557165/3</t>
+  </si>
+  <si>
+    <t>305557278/1</t>
+  </si>
+  <si>
+    <t>305557278</t>
+  </si>
+  <si>
+    <t>Rodostó utca</t>
+  </si>
+  <si>
+    <t>305557328/1</t>
+  </si>
+  <si>
+    <t>305557328</t>
+  </si>
+  <si>
+    <t>1215</t>
+  </si>
+  <si>
+    <t>Árpád utca</t>
+  </si>
+  <si>
+    <t>305557328/2</t>
+  </si>
+  <si>
+    <t>305557362/1</t>
+  </si>
+  <si>
+    <t>305557362</t>
+  </si>
+  <si>
+    <t>Panoráma utca</t>
+  </si>
+  <si>
+    <t>305557428/1</t>
+  </si>
+  <si>
+    <t>305557428</t>
+  </si>
+  <si>
+    <t>Munkácsy Mihály utca</t>
+  </si>
+  <si>
+    <t>305557555/1</t>
+  </si>
+  <si>
+    <t>305557555</t>
+  </si>
+  <si>
+    <t>Huszti út</t>
+  </si>
+  <si>
+    <t>305557595/1</t>
+  </si>
+  <si>
+    <t>305557595</t>
+  </si>
+  <si>
+    <t>Szendrő utca</t>
+  </si>
+  <si>
+    <t>305557799/1</t>
+  </si>
+  <si>
+    <t>305557799</t>
+  </si>
+  <si>
+    <t>1025</t>
+  </si>
+  <si>
+    <t>Csévi utca</t>
+  </si>
+  <si>
+    <t>305557863/1</t>
+  </si>
+  <si>
+    <t>305557863</t>
+  </si>
+  <si>
+    <t>1077</t>
+  </si>
+  <si>
+    <t>Wesselényi Utca</t>
+  </si>
+  <si>
+    <t>305557863/2</t>
+  </si>
+  <si>
+    <t>305628078/1</t>
+  </si>
+  <si>
+    <t>305628078</t>
+  </si>
+  <si>
+    <t>1117</t>
+  </si>
+  <si>
+    <t>Bercsényi utca</t>
+  </si>
+  <si>
+    <t>305667060/1</t>
+  </si>
+  <si>
+    <t>305667060</t>
+  </si>
+  <si>
+    <t>305667073/1</t>
+  </si>
+  <si>
+    <t>305667073</t>
+  </si>
+  <si>
+    <t>1021</t>
+  </si>
+  <si>
+    <t>Széher út</t>
+  </si>
+  <si>
+    <t>305667073/2</t>
+  </si>
+  <si>
+    <t>305667073/3</t>
+  </si>
+  <si>
+    <t>305667629/1</t>
+  </si>
+  <si>
+    <t>305667629</t>
+  </si>
+  <si>
+    <t>2612</t>
+  </si>
+  <si>
+    <t>KOSD</t>
+  </si>
+  <si>
+    <t>Bocskai utca</t>
+  </si>
+  <si>
+    <t>305667629/2</t>
+  </si>
+  <si>
+    <t>305667629/3</t>
+  </si>
+  <si>
+    <t>305667736/1</t>
+  </si>
+  <si>
+    <t>305667736</t>
+  </si>
+  <si>
+    <t>1141</t>
+  </si>
+  <si>
+    <t>Csernyus utca</t>
+  </si>
+  <si>
+    <t>305667736/2</t>
+  </si>
+  <si>
+    <t>305667790/1</t>
+  </si>
+  <si>
+    <t>305667790</t>
+  </si>
+  <si>
+    <t>2009</t>
+  </si>
+  <si>
+    <t>PILISSZENTLÁSZLÓ</t>
+  </si>
+  <si>
+    <t>Rózsahegy utca</t>
+  </si>
+  <si>
+    <t>305725457/1</t>
+  </si>
+  <si>
+    <t>305725457</t>
+  </si>
+  <si>
+    <t>1039</t>
+  </si>
+  <si>
+    <t>Víziorgona utca</t>
+  </si>
+  <si>
+    <t>305725479/1</t>
+  </si>
+  <si>
+    <t>305725479</t>
+  </si>
+  <si>
+    <t>Csepeli .</t>
+  </si>
+  <si>
+    <t>305725539/1</t>
+  </si>
+  <si>
+    <t>305725539</t>
+  </si>
+  <si>
+    <t>Bláthy Ottó utca</t>
+  </si>
+  <si>
+    <t>305725744/1</t>
+  </si>
+  <si>
+    <t>305725744</t>
+  </si>
+  <si>
+    <t>Rózsa utca</t>
+  </si>
+  <si>
+    <t>305725906/1</t>
+  </si>
+  <si>
+    <t>305725906</t>
+  </si>
+  <si>
+    <t>Viola Utca</t>
+  </si>
+  <si>
+    <t>305725937/1</t>
+  </si>
+  <si>
+    <t>305725937</t>
+  </si>
+  <si>
+    <t>1156</t>
+  </si>
+  <si>
+    <t>Nyírpalota út</t>
+  </si>
+  <si>
+    <t>305725937/2</t>
+  </si>
+  <si>
+    <t>305726018/1</t>
+  </si>
+  <si>
+    <t>305726018</t>
+  </si>
+  <si>
+    <t>Szövetség utca</t>
+  </si>
+  <si>
+    <t>305726025/1</t>
+  </si>
+  <si>
+    <t>305726025</t>
+  </si>
+  <si>
+    <t>Gárdonyi Géza utca</t>
+  </si>
+  <si>
+    <t>305726046/1</t>
+  </si>
+  <si>
+    <t>305726046</t>
+  </si>
+  <si>
+    <t>1155</t>
+  </si>
+  <si>
+    <t>Alkotmány utca</t>
+  </si>
+  <si>
+    <t>305726061/1</t>
+  </si>
+  <si>
+    <t>305726061</t>
+  </si>
+  <si>
+    <t>1052</t>
+  </si>
+  <si>
+    <t>Váci utca</t>
+  </si>
+  <si>
+    <t>305726199/1</t>
+  </si>
+  <si>
+    <t>305726199</t>
+  </si>
+  <si>
+    <t>Bethlen Gábor utca</t>
+  </si>
+  <si>
+    <t>305726274/1</t>
+  </si>
+  <si>
+    <t>305726274</t>
+  </si>
+  <si>
+    <t>2097</t>
+  </si>
+  <si>
+    <t>PILISBOROSJENŐ</t>
+  </si>
+  <si>
+    <t>Fő utca</t>
+  </si>
+  <si>
+    <t>305726314/1</t>
+  </si>
+  <si>
+    <t>305726314</t>
+  </si>
+  <si>
+    <t>Eperjesi utca</t>
+  </si>
+  <si>
+    <t>305726314/2</t>
+  </si>
+  <si>
+    <t>305781061/1</t>
+  </si>
+  <si>
+    <t>305781061</t>
+  </si>
+  <si>
+    <t>Lakat utca</t>
+  </si>
+  <si>
+    <t>305781098/1</t>
+  </si>
+  <si>
+    <t>305781098</t>
+  </si>
+  <si>
+    <t>Gyöngyvirág utca</t>
+  </si>
+  <si>
+    <t>305781165/1</t>
+  </si>
+  <si>
+    <t>305781165</t>
+  </si>
+  <si>
+    <t>Thököly út</t>
+  </si>
+  <si>
+    <t>305781182/1</t>
+  </si>
+  <si>
+    <t>305781182</t>
+  </si>
+  <si>
+    <t>2373</t>
+  </si>
+  <si>
+    <t>Vacsi utca</t>
+  </si>
+  <si>
+    <t>305781233/1</t>
+  </si>
+  <si>
+    <t>305781233</t>
+  </si>
+  <si>
+    <t>2144</t>
+  </si>
+  <si>
+    <t>KEREPES</t>
+  </si>
+  <si>
+    <t>Szőlő utca</t>
+  </si>
+  <si>
+    <t>305781305/1</t>
+  </si>
+  <si>
+    <t>305781305</t>
+  </si>
+  <si>
+    <t>Jegenye utca</t>
+  </si>
+  <si>
+    <t>305781359/1</t>
+  </si>
+  <si>
+    <t>305781359</t>
+  </si>
+  <si>
+    <t>Szent Korona útja</t>
+  </si>
+  <si>
+    <t>305781364/1</t>
+  </si>
+  <si>
+    <t>305781364</t>
+  </si>
+  <si>
+    <t>Szent László út</t>
+  </si>
+  <si>
+    <t>305781415/1</t>
+  </si>
+  <si>
+    <t>305781415</t>
+  </si>
+  <si>
+    <t>1222</t>
+  </si>
+  <si>
+    <t>Sörház utca</t>
+  </si>
+  <si>
+    <t>305781653/1</t>
+  </si>
+  <si>
+    <t>305781653</t>
+  </si>
+  <si>
+    <t>1116</t>
+  </si>
+  <si>
+    <t>Kalotaszeg utca</t>
+  </si>
+  <si>
+    <t>305781761/1</t>
+  </si>
+  <si>
+    <t>305781761</t>
+  </si>
+  <si>
+    <t>1201</t>
+  </si>
+  <si>
+    <t>Nagy Győry István köz</t>
+  </si>
+  <si>
+    <t>305781761/2</t>
+  </si>
+  <si>
+    <t>305830800/1</t>
+  </si>
+  <si>
+    <t>SZ-860</t>
+  </si>
+  <si>
+    <t>305830800</t>
+  </si>
+  <si>
+    <t>Árok utca</t>
+  </si>
+  <si>
+    <t>305831416/1</t>
+  </si>
+  <si>
+    <t>305831416</t>
+  </si>
+  <si>
+    <t>2096</t>
+  </si>
+  <si>
+    <t>ÜRÖM</t>
+  </si>
+  <si>
+    <t>Doktor utca</t>
+  </si>
+  <si>
+    <t>305901506/1</t>
+  </si>
+  <si>
+    <t>305901506</t>
+  </si>
+  <si>
+    <t>Sasadi út</t>
+  </si>
+  <si>
+    <t>305901895/1</t>
+  </si>
+  <si>
+    <t>305901895</t>
+  </si>
+  <si>
+    <t>1022</t>
+  </si>
+  <si>
+    <t>Hankóczy Jenő utca</t>
+  </si>
+  <si>
+    <t>305901980/1</t>
+  </si>
+  <si>
+    <t>305901980</t>
+  </si>
+  <si>
+    <t>306026162/1</t>
+  </si>
+  <si>
+    <t>306026162</t>
+  </si>
+  <si>
+    <t>Csillagszem utca</t>
+  </si>
+  <si>
+    <t>306078479/1</t>
+  </si>
+  <si>
+    <t>306078479</t>
+  </si>
+  <si>
+    <t>1101</t>
+  </si>
+  <si>
+    <t>Salgótarjáni utca</t>
+  </si>
+  <si>
+    <t>306078571/1</t>
+  </si>
+  <si>
+    <t>306078571</t>
+  </si>
+  <si>
+    <t>1038</t>
+  </si>
+  <si>
+    <t>Zemplén Győző utca</t>
+  </si>
+  <si>
+    <t>306078571/2</t>
+  </si>
+  <si>
+    <t>306079098/1</t>
+  </si>
+  <si>
+    <t>306079098</t>
+  </si>
+  <si>
+    <t>1103</t>
+  </si>
+  <si>
+    <t>Kis Gergely utca</t>
+  </si>
+  <si>
+    <t>306147203/1</t>
+  </si>
+  <si>
+    <t>306147203</t>
+  </si>
+  <si>
+    <t>Munkás utca</t>
+  </si>
+  <si>
+    <t>306180874/1</t>
+  </si>
+  <si>
+    <t>306180874</t>
+  </si>
+  <si>
+    <t>Cirmos utca</t>
+  </si>
+  <si>
+    <t>306181130/1</t>
+  </si>
+  <si>
+    <t>306181130</t>
+  </si>
+  <si>
+    <t>Fóti utca</t>
+  </si>
+  <si>
+    <t>99002274/1</t>
+  </si>
+  <si>
+    <t>99002274</t>
+  </si>
+  <si>
+    <t>Béke utca</t>
+  </si>
+  <si>
+    <t>202603272600689501</t>
+  </si>
+  <si>
+    <t>NFD6-03-21-4HP6</t>
+  </si>
+  <si>
+    <t>Deák Ferenc utca</t>
+  </si>
+  <si>
+    <t>202603272600696101</t>
+  </si>
+  <si>
+    <t>NFD6-03-22-MBHS</t>
+  </si>
+  <si>
+    <t>Csendes utca</t>
+  </si>
+  <si>
+    <t>202603272600696102</t>
+  </si>
+  <si>
+    <t>202603272600710001</t>
+  </si>
+  <si>
+    <t>NFD6-03-23-2X6M</t>
+  </si>
+  <si>
+    <t>1121</t>
+  </si>
+  <si>
+    <t>Mártonfa utca</t>
+  </si>
+  <si>
+    <t>202603242600710401</t>
+  </si>
+  <si>
+    <t>NFD6-03-23-5RVM</t>
+  </si>
+  <si>
+    <t>1125</t>
+  </si>
+  <si>
+    <t>Zirzen Janka utca</t>
+  </si>
+  <si>
+    <t>202603272600706101</t>
+  </si>
+  <si>
+    <t>NFD6-03-23-FF8R</t>
+  </si>
+  <si>
+    <t>Felsőcsatári út</t>
+  </si>
+  <si>
+    <t>202603262600728101</t>
+  </si>
+  <si>
+    <t>NFD6-03-25-BC8J</t>
+  </si>
+  <si>
+    <t>Koronafürt utca</t>
+  </si>
+  <si>
+    <t>202603262600726901</t>
+  </si>
+  <si>
+    <t>NFD6-03-25-F8NA</t>
+  </si>
+  <si>
+    <t>Móricz Zsigmond utca</t>
+  </si>
+  <si>
+    <t>202603272600735901</t>
+  </si>
+  <si>
+    <t>NFD6-03-26-224N</t>
+  </si>
+  <si>
+    <t>Kuruclesi út</t>
+  </si>
+  <si>
+    <t>202603272600737401</t>
+  </si>
+  <si>
+    <t>NFD6-03-26-34YD</t>
+  </si>
+  <si>
+    <t>1162</t>
+  </si>
+  <si>
+    <t>János utca</t>
+  </si>
+  <si>
+    <t>202603272600735201</t>
+  </si>
+  <si>
+    <t>NFD6-03-26-BFCV</t>
+  </si>
+  <si>
+    <t>Hunyadi János utca</t>
+  </si>
+  <si>
+    <t>202603272600736201</t>
+  </si>
+  <si>
+    <t>NFD6-03-26-GMEV</t>
+  </si>
+  <si>
+    <t>Franciska utca</t>
+  </si>
+  <si>
+    <t>202603272600736001</t>
+  </si>
+  <si>
+    <t>NFD6-03-26-KUET</t>
+  </si>
+  <si>
+    <t>Tomaj utca</t>
+  </si>
+  <si>
+    <t>202603272600736002</t>
+  </si>
+  <si>
+    <t>202603272600734601</t>
+  </si>
+  <si>
+    <t>NFD6-03-26-SBWU</t>
+  </si>
+  <si>
+    <t>Lukács György utca</t>
+  </si>
+  <si>
+    <t>202603272600736501</t>
+  </si>
+  <si>
+    <t>NFD6-03-26-U97V</t>
+  </si>
+  <si>
+    <t>Márton út</t>
+  </si>
+  <si>
+    <t>202603272600736901</t>
+  </si>
+  <si>
+    <t>NFD6-03-26-YCBA</t>
+  </si>
+  <si>
+    <t>Somfa utca</t>
+  </si>
+  <si>
+    <t>NFD6-03-29-CG8Y-1</t>
+  </si>
+  <si>
+    <t>NFD6-03-29-CG8Y</t>
+  </si>
+  <si>
+    <t>Bányász utca</t>
+  </si>
+  <si>
+    <t>202603262600731001</t>
+  </si>
+  <si>
+    <t>NFE6-03-25-E869</t>
+  </si>
+  <si>
+    <t>Radnóti Miklós köz</t>
+  </si>
+  <si>
+    <t>202603262600731002</t>
+  </si>
+  <si>
+    <t>202603272600738801</t>
+  </si>
+  <si>
+    <t>NFE6-03-26-5CSG</t>
+  </si>
+  <si>
+    <t>Paprika utca</t>
+  </si>
+  <si>
+    <t>202603272600738802</t>
+  </si>
+  <si>
+    <t>202603272600738803</t>
+  </si>
+  <si>
+    <t>202603272600738804</t>
+  </si>
+  <si>
+    <t>202603272600738805</t>
+  </si>
+  <si>
+    <t>202603272600732101</t>
+  </si>
+  <si>
+    <t>NFE6-03-26-EZ58</t>
+  </si>
+  <si>
+    <t>Fő út</t>
+  </si>
+  <si>
+    <t>202603272600734901</t>
+  </si>
+  <si>
+    <t>NFE6-03-26-MTVN</t>
+  </si>
+  <si>
+    <t>2133</t>
+  </si>
+  <si>
+    <t>SZŐDLIGET</t>
+  </si>
+  <si>
+    <t>202603272600739601</t>
+  </si>
+  <si>
+    <t>NFE6-03-26-XL5L</t>
+  </si>
+  <si>
+    <t>Bártfai utca</t>
+  </si>
+  <si>
+    <t>159995579538654671</t>
+  </si>
+  <si>
+    <t>SA26/H001449</t>
+  </si>
+  <si>
+    <t>2314</t>
+  </si>
+  <si>
+    <t>HALÁSZTELEK</t>
+  </si>
+  <si>
+    <t>Biró László utca</t>
+  </si>
+  <si>
+    <t>PICIGURMAN</t>
+  </si>
+  <si>
+    <t>159995579538654688</t>
+  </si>
+  <si>
+    <t>159995579538654695</t>
   </si>
 </sst>
 </file>
@@ -1864,7 +1906,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <sheetPr codeName="Munka1"/>
-  <dimension ref="A1:H150"/>
+  <dimension ref="A1:H149"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="24.88671875" bestFit="1" customWidth="1"/>
@@ -1873,51 +1915,51 @@
     <col min="4" max="4" width="20.109375" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="5" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="20" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="34.109375" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="35.5546875" bestFit="1" customWidth="1"/>
     <col min="8" max="8" width="19.88671875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
-        <v>54</v>
+        <v>36</v>
       </c>
       <c r="C1" t="s">
-        <v>55</v>
+        <v>37</v>
       </c>
       <c r="D1" t="s">
-        <v>56</v>
+        <v>38</v>
       </c>
       <c r="E1" t="s">
-        <v>57</v>
+        <v>39</v>
       </c>
       <c r="F1" t="s">
-        <v>58</v>
+        <v>40</v>
       </c>
       <c r="G1" t="s">
-        <v>59</v>
+        <v>41</v>
       </c>
       <c r="H1" t="s">
-        <v>60</v>
+        <v>42</v>
       </c>
     </row>
     <row r="2" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
-        <v>95</v>
+        <v>86</v>
       </c>
       <c r="C2" t="s">
-        <v>10</v>
+        <v>21</v>
       </c>
       <c r="D2" t="s">
-        <v>96</v>
+        <v>87</v>
       </c>
       <c r="E2" t="s">
-        <v>97</v>
+        <v>70</v>
       </c>
       <c r="F2" t="s">
         <v>0</v>
       </c>
       <c r="G2" t="s">
-        <v>98</v>
+        <v>88</v>
       </c>
       <c r="H2" t="s">
         <v>4</v>
@@ -1925,68 +1967,68 @@
     </row>
     <row r="3" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
-        <v>99</v>
+        <v>89</v>
       </c>
       <c r="C3" t="s">
-        <v>3</v>
+        <v>21</v>
       </c>
       <c r="D3" t="s">
-        <v>100</v>
+        <v>87</v>
       </c>
       <c r="E3" t="s">
-        <v>101</v>
+        <v>70</v>
       </c>
       <c r="F3" t="s">
-        <v>102</v>
+        <v>0</v>
       </c>
       <c r="G3" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="H3" t="s">
-        <v>1</v>
+        <v>4</v>
       </c>
     </row>
     <row r="4" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
-        <v>103</v>
+        <v>90</v>
       </c>
       <c r="C4" t="s">
-        <v>104</v>
+        <v>21</v>
       </c>
       <c r="D4" t="s">
-        <v>105</v>
+        <v>87</v>
       </c>
       <c r="E4" t="s">
-        <v>106</v>
+        <v>70</v>
       </c>
       <c r="F4" t="s">
         <v>0</v>
       </c>
       <c r="G4" t="s">
-        <v>107</v>
+        <v>88</v>
       </c>
       <c r="H4" t="s">
-        <v>1</v>
+        <v>4</v>
       </c>
     </row>
     <row r="5" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
-        <v>108</v>
+        <v>91</v>
       </c>
       <c r="C5" t="s">
-        <v>2</v>
+        <v>92</v>
       </c>
       <c r="D5" t="s">
-        <v>109</v>
+        <v>93</v>
       </c>
       <c r="E5" t="s">
-        <v>110</v>
+        <v>23</v>
       </c>
       <c r="F5" t="s">
-        <v>111</v>
+        <v>24</v>
       </c>
       <c r="G5" t="s">
-        <v>112</v>
+        <v>94</v>
       </c>
       <c r="H5" t="s">
         <v>1</v>
@@ -1994,22 +2036,22 @@
     </row>
     <row r="6" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
-        <v>62</v>
+        <v>95</v>
       </c>
       <c r="C6" t="s">
-        <v>24</v>
+        <v>3</v>
       </c>
       <c r="D6" t="s">
-        <v>63</v>
+        <v>96</v>
       </c>
       <c r="E6" t="s">
-        <v>47</v>
+        <v>97</v>
       </c>
       <c r="F6" t="s">
         <v>0</v>
       </c>
       <c r="G6" t="s">
-        <v>64</v>
+        <v>98</v>
       </c>
       <c r="H6" t="s">
         <v>1</v>
@@ -2017,22 +2059,22 @@
     </row>
     <row r="7" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
-        <v>113</v>
+        <v>99</v>
       </c>
       <c r="C7" t="s">
-        <v>24</v>
+        <v>100</v>
       </c>
       <c r="D7" t="s">
-        <v>114</v>
+        <v>101</v>
       </c>
       <c r="E7" t="s">
-        <v>6</v>
+        <v>102</v>
       </c>
       <c r="F7" t="s">
-        <v>7</v>
+        <v>103</v>
       </c>
       <c r="G7" t="s">
-        <v>115</v>
+        <v>104</v>
       </c>
       <c r="H7" t="s">
         <v>1</v>
@@ -2040,22 +2082,22 @@
     </row>
     <row r="8" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
-        <v>116</v>
+        <v>105</v>
       </c>
       <c r="C8" t="s">
-        <v>24</v>
+        <v>10</v>
       </c>
       <c r="D8" t="s">
-        <v>117</v>
+        <v>106</v>
       </c>
       <c r="E8" t="s">
-        <v>118</v>
+        <v>107</v>
       </c>
       <c r="F8" t="s">
-        <v>33</v>
+        <v>0</v>
       </c>
       <c r="G8" t="s">
-        <v>119</v>
+        <v>108</v>
       </c>
       <c r="H8" t="s">
         <v>1</v>
@@ -2063,22 +2105,22 @@
     </row>
     <row r="9" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
-        <v>120</v>
+        <v>109</v>
       </c>
       <c r="C9" t="s">
-        <v>24</v>
+        <v>10</v>
       </c>
       <c r="D9" t="s">
-        <v>121</v>
+        <v>110</v>
       </c>
       <c r="E9" t="s">
-        <v>27</v>
+        <v>111</v>
       </c>
       <c r="F9" t="s">
-        <v>28</v>
+        <v>0</v>
       </c>
       <c r="G9" t="s">
-        <v>122</v>
+        <v>112</v>
       </c>
       <c r="H9" t="s">
         <v>1</v>
@@ -2086,22 +2128,22 @@
     </row>
     <row r="10" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
-        <v>123</v>
+        <v>46</v>
       </c>
       <c r="C10" t="s">
-        <v>23</v>
+        <v>3</v>
       </c>
       <c r="D10" t="s">
-        <v>124</v>
+        <v>47</v>
       </c>
       <c r="E10" t="s">
-        <v>125</v>
+        <v>43</v>
       </c>
       <c r="F10" t="s">
-        <v>126</v>
+        <v>0</v>
       </c>
       <c r="G10" t="s">
-        <v>115</v>
+        <v>48</v>
       </c>
       <c r="H10" t="s">
         <v>1</v>
@@ -2109,22 +2151,22 @@
     </row>
     <row r="11" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A11" t="s">
-        <v>127</v>
+        <v>113</v>
       </c>
       <c r="C11" t="s">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="D11" t="s">
-        <v>128</v>
+        <v>114</v>
       </c>
       <c r="E11" t="s">
-        <v>129</v>
+        <v>28</v>
       </c>
       <c r="F11" t="s">
-        <v>0</v>
+        <v>29</v>
       </c>
       <c r="G11" t="s">
-        <v>130</v>
+        <v>115</v>
       </c>
       <c r="H11" t="s">
         <v>1</v>
@@ -2132,22 +2174,22 @@
     </row>
     <row r="12" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A12" t="s">
-        <v>65</v>
+        <v>116</v>
       </c>
       <c r="C12" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="D12" t="s">
-        <v>66</v>
+        <v>117</v>
       </c>
       <c r="E12" t="s">
-        <v>67</v>
+        <v>107</v>
       </c>
       <c r="F12" t="s">
         <v>0</v>
       </c>
       <c r="G12" t="s">
-        <v>68</v>
+        <v>118</v>
       </c>
       <c r="H12" t="s">
         <v>1</v>
@@ -2155,22 +2197,22 @@
     </row>
     <row r="13" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A13" t="s">
-        <v>73</v>
+        <v>119</v>
       </c>
       <c r="C13" t="s">
-        <v>24</v>
+        <v>10</v>
       </c>
       <c r="D13" t="s">
-        <v>74</v>
+        <v>117</v>
       </c>
       <c r="E13" t="s">
-        <v>27</v>
+        <v>107</v>
       </c>
       <c r="F13" t="s">
-        <v>28</v>
+        <v>0</v>
       </c>
       <c r="G13" t="s">
-        <v>75</v>
+        <v>118</v>
       </c>
       <c r="H13" t="s">
         <v>1</v>
@@ -2178,22 +2220,22 @@
     </row>
     <row r="14" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A14" t="s">
-        <v>131</v>
+        <v>120</v>
       </c>
       <c r="C14" t="s">
-        <v>104</v>
+        <v>53</v>
       </c>
       <c r="D14" t="s">
-        <v>132</v>
+        <v>121</v>
       </c>
       <c r="E14" t="s">
-        <v>133</v>
+        <v>44</v>
       </c>
       <c r="F14" t="s">
-        <v>0</v>
+        <v>45</v>
       </c>
       <c r="G14" t="s">
-        <v>134</v>
+        <v>122</v>
       </c>
       <c r="H14" t="s">
         <v>1</v>
@@ -2201,22 +2243,22 @@
     </row>
     <row r="15" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A15" t="s">
-        <v>135</v>
+        <v>123</v>
       </c>
       <c r="C15" t="s">
-        <v>26</v>
+        <v>8</v>
       </c>
       <c r="D15" t="s">
-        <v>136</v>
+        <v>124</v>
       </c>
       <c r="E15" t="s">
-        <v>137</v>
+        <v>31</v>
       </c>
       <c r="F15" t="s">
-        <v>138</v>
+        <v>32</v>
       </c>
       <c r="G15" t="s">
-        <v>115</v>
+        <v>125</v>
       </c>
       <c r="H15" t="s">
         <v>1</v>
@@ -2224,22 +2266,22 @@
     </row>
     <row r="16" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A16" t="s">
-        <v>139</v>
+        <v>126</v>
       </c>
       <c r="C16" t="s">
-        <v>26</v>
+        <v>8</v>
       </c>
       <c r="D16" t="s">
-        <v>136</v>
+        <v>124</v>
       </c>
       <c r="E16" t="s">
-        <v>137</v>
+        <v>31</v>
       </c>
       <c r="F16" t="s">
-        <v>138</v>
+        <v>32</v>
       </c>
       <c r="G16" t="s">
-        <v>115</v>
+        <v>125</v>
       </c>
       <c r="H16" t="s">
         <v>1</v>
@@ -2247,22 +2289,22 @@
     </row>
     <row r="17" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A17" t="s">
-        <v>140</v>
+        <v>127</v>
       </c>
       <c r="C17" t="s">
-        <v>24</v>
+        <v>92</v>
       </c>
       <c r="D17" t="s">
-        <v>141</v>
+        <v>128</v>
       </c>
       <c r="E17" t="s">
-        <v>118</v>
+        <v>129</v>
       </c>
       <c r="F17" t="s">
-        <v>33</v>
+        <v>130</v>
       </c>
       <c r="G17" t="s">
-        <v>142</v>
+        <v>131</v>
       </c>
       <c r="H17" t="s">
         <v>1</v>
@@ -2270,22 +2312,22 @@
     </row>
     <row r="18" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A18" t="s">
-        <v>143</v>
+        <v>132</v>
       </c>
       <c r="C18" t="s">
-        <v>24</v>
+        <v>100</v>
       </c>
       <c r="D18" t="s">
-        <v>144</v>
+        <v>133</v>
       </c>
       <c r="E18" t="s">
-        <v>27</v>
+        <v>134</v>
       </c>
       <c r="F18" t="s">
-        <v>28</v>
+        <v>135</v>
       </c>
       <c r="G18" t="s">
-        <v>145</v>
+        <v>136</v>
       </c>
       <c r="H18" t="s">
         <v>1</v>
@@ -2293,22 +2335,22 @@
     </row>
     <row r="19" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A19" t="s">
-        <v>146</v>
+        <v>137</v>
       </c>
       <c r="C19" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="D19" t="s">
-        <v>144</v>
+        <v>138</v>
       </c>
       <c r="E19" t="s">
-        <v>27</v>
+        <v>139</v>
       </c>
       <c r="F19" t="s">
-        <v>28</v>
+        <v>140</v>
       </c>
       <c r="G19" t="s">
-        <v>145</v>
+        <v>141</v>
       </c>
       <c r="H19" t="s">
         <v>1</v>
@@ -2316,22 +2358,22 @@
     </row>
     <row r="20" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A20" t="s">
-        <v>147</v>
+        <v>142</v>
       </c>
       <c r="C20" t="s">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="D20" t="s">
-        <v>148</v>
+        <v>143</v>
       </c>
       <c r="E20" t="s">
-        <v>88</v>
+        <v>144</v>
       </c>
       <c r="F20" t="s">
-        <v>89</v>
+        <v>145</v>
       </c>
       <c r="G20" t="s">
-        <v>149</v>
+        <v>146</v>
       </c>
       <c r="H20" t="s">
         <v>1</v>
@@ -2339,22 +2381,22 @@
     </row>
     <row r="21" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A21" t="s">
+        <v>147</v>
+      </c>
+      <c r="C21" t="s">
+        <v>53</v>
+      </c>
+      <c r="D21" t="s">
+        <v>148</v>
+      </c>
+      <c r="E21" t="s">
+        <v>149</v>
+      </c>
+      <c r="F21" t="s">
+        <v>0</v>
+      </c>
+      <c r="G21" t="s">
         <v>150</v>
-      </c>
-      <c r="C21" t="s">
-        <v>26</v>
-      </c>
-      <c r="D21" t="s">
-        <v>151</v>
-      </c>
-      <c r="E21" t="s">
-        <v>152</v>
-      </c>
-      <c r="F21" t="s">
-        <v>153</v>
-      </c>
-      <c r="G21" t="s">
-        <v>154</v>
       </c>
       <c r="H21" t="s">
         <v>1</v>
@@ -2362,22 +2404,22 @@
     </row>
     <row r="22" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A22" t="s">
+        <v>151</v>
+      </c>
+      <c r="C22" t="s">
+        <v>152</v>
+      </c>
+      <c r="D22" t="s">
+        <v>153</v>
+      </c>
+      <c r="E22" t="s">
+        <v>154</v>
+      </c>
+      <c r="F22" t="s">
+        <v>0</v>
+      </c>
+      <c r="G22" t="s">
         <v>155</v>
-      </c>
-      <c r="C22" t="s">
-        <v>38</v>
-      </c>
-      <c r="D22" t="s">
-        <v>156</v>
-      </c>
-      <c r="E22" t="s">
-        <v>157</v>
-      </c>
-      <c r="F22" t="s">
-        <v>158</v>
-      </c>
-      <c r="G22" t="s">
-        <v>46</v>
       </c>
       <c r="H22" t="s">
         <v>1</v>
@@ -2385,22 +2427,22 @@
     </row>
     <row r="23" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A23" t="s">
-        <v>159</v>
+        <v>156</v>
       </c>
       <c r="C23" t="s">
-        <v>38</v>
+        <v>152</v>
       </c>
       <c r="D23" t="s">
-        <v>156</v>
+        <v>153</v>
       </c>
       <c r="E23" t="s">
-        <v>157</v>
+        <v>154</v>
       </c>
       <c r="F23" t="s">
-        <v>158</v>
+        <v>0</v>
       </c>
       <c r="G23" t="s">
-        <v>46</v>
+        <v>155</v>
       </c>
       <c r="H23" t="s">
         <v>1</v>
@@ -2408,22 +2450,22 @@
     </row>
     <row r="24" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A24" t="s">
+        <v>157</v>
+      </c>
+      <c r="C24" t="s">
+        <v>22</v>
+      </c>
+      <c r="D24" t="s">
+        <v>158</v>
+      </c>
+      <c r="E24" t="s">
+        <v>159</v>
+      </c>
+      <c r="F24" t="s">
         <v>160</v>
       </c>
-      <c r="C24" t="s">
-        <v>38</v>
-      </c>
-      <c r="D24" t="s">
-        <v>156</v>
-      </c>
-      <c r="E24" t="s">
-        <v>157</v>
-      </c>
-      <c r="F24" t="s">
-        <v>158</v>
-      </c>
       <c r="G24" t="s">
-        <v>46</v>
+        <v>161</v>
       </c>
       <c r="H24" t="s">
         <v>1</v>
@@ -2431,22 +2473,22 @@
     </row>
     <row r="25" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A25" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="C25" t="s">
-        <v>19</v>
+        <v>152</v>
       </c>
       <c r="D25" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="E25" t="s">
-        <v>163</v>
+        <v>34</v>
       </c>
       <c r="F25" t="s">
         <v>0</v>
       </c>
       <c r="G25" t="s">
-        <v>164</v>
+        <v>69</v>
       </c>
       <c r="H25" t="s">
         <v>1</v>
@@ -2454,22 +2496,22 @@
     </row>
     <row r="26" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A26" t="s">
+        <v>164</v>
+      </c>
+      <c r="C26" t="s">
         <v>165</v>
       </c>
-      <c r="C26" t="s">
-        <v>19</v>
-      </c>
       <c r="D26" t="s">
-        <v>162</v>
+        <v>166</v>
       </c>
       <c r="E26" t="s">
-        <v>163</v>
+        <v>167</v>
       </c>
       <c r="F26" t="s">
         <v>0</v>
       </c>
       <c r="G26" t="s">
-        <v>164</v>
+        <v>168</v>
       </c>
       <c r="H26" t="s">
         <v>1</v>
@@ -2477,22 +2519,22 @@
     </row>
     <row r="27" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A27" t="s">
-        <v>76</v>
+        <v>169</v>
       </c>
       <c r="C27" t="s">
-        <v>19</v>
+        <v>9</v>
       </c>
       <c r="D27" t="s">
-        <v>77</v>
+        <v>170</v>
       </c>
       <c r="E27" t="s">
-        <v>61</v>
+        <v>171</v>
       </c>
       <c r="F27" t="s">
         <v>0</v>
       </c>
       <c r="G27" t="s">
-        <v>78</v>
+        <v>172</v>
       </c>
       <c r="H27" t="s">
         <v>1</v>
@@ -2500,22 +2542,22 @@
     </row>
     <row r="28" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A28" t="s">
-        <v>166</v>
+        <v>173</v>
       </c>
       <c r="C28" t="s">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="D28" t="s">
-        <v>167</v>
+        <v>174</v>
       </c>
       <c r="E28" t="s">
-        <v>44</v>
+        <v>81</v>
       </c>
       <c r="F28" t="s">
-        <v>45</v>
+        <v>0</v>
       </c>
       <c r="G28" t="s">
-        <v>168</v>
+        <v>175</v>
       </c>
       <c r="H28" t="s">
         <v>1</v>
@@ -2523,22 +2565,22 @@
     </row>
     <row r="29" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A29" t="s">
-        <v>169</v>
+        <v>176</v>
       </c>
       <c r="C29" t="s">
         <v>22</v>
       </c>
       <c r="D29" t="s">
-        <v>170</v>
+        <v>177</v>
       </c>
       <c r="E29" t="s">
-        <v>37</v>
+        <v>178</v>
       </c>
       <c r="F29" t="s">
         <v>0</v>
       </c>
       <c r="G29" t="s">
-        <v>171</v>
+        <v>179</v>
       </c>
       <c r="H29" t="s">
         <v>1</v>
@@ -2546,22 +2588,22 @@
     </row>
     <row r="30" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A30" t="s">
-        <v>172</v>
+        <v>180</v>
       </c>
       <c r="C30" t="s">
-        <v>38</v>
+        <v>22</v>
       </c>
       <c r="D30" t="s">
-        <v>173</v>
+        <v>177</v>
       </c>
       <c r="E30" t="s">
-        <v>43</v>
+        <v>178</v>
       </c>
       <c r="F30" t="s">
         <v>0</v>
       </c>
       <c r="G30" t="s">
-        <v>174</v>
+        <v>179</v>
       </c>
       <c r="H30" t="s">
         <v>1</v>
@@ -2569,22 +2611,22 @@
     </row>
     <row r="31" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A31" t="s">
-        <v>175</v>
+        <v>181</v>
       </c>
       <c r="C31" t="s">
-        <v>10</v>
+        <v>22</v>
       </c>
       <c r="D31" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="E31" t="s">
-        <v>50</v>
+        <v>178</v>
       </c>
       <c r="F31" t="s">
         <v>0</v>
       </c>
       <c r="G31" t="s">
-        <v>177</v>
+        <v>179</v>
       </c>
       <c r="H31" t="s">
         <v>1</v>
@@ -2592,22 +2634,22 @@
     </row>
     <row r="32" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A32" t="s">
-        <v>178</v>
+        <v>182</v>
       </c>
       <c r="C32" t="s">
-        <v>12</v>
+        <v>165</v>
       </c>
       <c r="D32" t="s">
-        <v>179</v>
+        <v>183</v>
       </c>
       <c r="E32" t="s">
-        <v>25</v>
+        <v>184</v>
       </c>
       <c r="F32" t="s">
         <v>0</v>
       </c>
       <c r="G32" t="s">
-        <v>180</v>
+        <v>185</v>
       </c>
       <c r="H32" t="s">
         <v>1</v>
@@ -2615,186 +2657,186 @@
     </row>
     <row r="33" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A33" t="s">
-        <v>181</v>
+        <v>186</v>
       </c>
       <c r="C33" t="s">
-        <v>3</v>
+        <v>19</v>
       </c>
       <c r="D33" t="s">
-        <v>182</v>
+        <v>187</v>
       </c>
       <c r="E33" t="s">
-        <v>42</v>
+        <v>76</v>
       </c>
       <c r="F33" t="s">
         <v>0</v>
       </c>
       <c r="G33" t="s">
-        <v>183</v>
+        <v>188</v>
       </c>
       <c r="H33" t="s">
-        <v>1</v>
+        <v>49</v>
       </c>
     </row>
     <row r="34" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A34" t="s">
-        <v>184</v>
+        <v>189</v>
       </c>
       <c r="C34" t="s">
-        <v>185</v>
+        <v>190</v>
       </c>
       <c r="D34" t="s">
-        <v>186</v>
+        <v>191</v>
       </c>
       <c r="E34" t="s">
-        <v>187</v>
+        <v>192</v>
       </c>
       <c r="F34" t="s">
         <v>0</v>
       </c>
       <c r="G34" t="s">
-        <v>188</v>
+        <v>193</v>
       </c>
       <c r="H34" t="s">
-        <v>1</v>
+        <v>49</v>
       </c>
     </row>
     <row r="35" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A35" t="s">
-        <v>189</v>
+        <v>194</v>
       </c>
       <c r="C35" t="s">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="D35" t="s">
-        <v>190</v>
+        <v>195</v>
       </c>
       <c r="E35" t="s">
-        <v>191</v>
+        <v>30</v>
       </c>
       <c r="F35" t="s">
         <v>0</v>
       </c>
       <c r="G35" t="s">
-        <v>192</v>
+        <v>196</v>
       </c>
       <c r="H35" t="s">
-        <v>1</v>
+        <v>62</v>
       </c>
     </row>
     <row r="36" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A36" t="s">
-        <v>193</v>
+        <v>197</v>
       </c>
       <c r="C36" t="s">
-        <v>19</v>
+        <v>10</v>
       </c>
       <c r="D36" t="s">
-        <v>194</v>
+        <v>198</v>
       </c>
       <c r="E36" t="s">
-        <v>163</v>
+        <v>199</v>
       </c>
       <c r="F36" t="s">
         <v>0</v>
       </c>
       <c r="G36" t="s">
-        <v>195</v>
+        <v>200</v>
       </c>
       <c r="H36" t="s">
-        <v>1</v>
+        <v>62</v>
       </c>
     </row>
     <row r="37" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A37" t="s">
-        <v>196</v>
+        <v>201</v>
       </c>
       <c r="C37" t="s">
-        <v>22</v>
+        <v>9</v>
       </c>
       <c r="D37" t="s">
-        <v>197</v>
+        <v>202</v>
       </c>
       <c r="E37" t="s">
-        <v>48</v>
+        <v>77</v>
       </c>
       <c r="F37" t="s">
-        <v>0</v>
+        <v>78</v>
       </c>
       <c r="G37" t="s">
-        <v>198</v>
+        <v>82</v>
       </c>
       <c r="H37" t="s">
-        <v>1</v>
+        <v>62</v>
       </c>
     </row>
     <row r="38" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A38" t="s">
-        <v>199</v>
+        <v>203</v>
       </c>
       <c r="C38" t="s">
-        <v>12</v>
+        <v>92</v>
       </c>
       <c r="D38" t="s">
-        <v>200</v>
+        <v>204</v>
       </c>
       <c r="E38" t="s">
-        <v>67</v>
+        <v>26</v>
       </c>
       <c r="F38" t="s">
-        <v>0</v>
+        <v>27</v>
       </c>
       <c r="G38" t="s">
-        <v>201</v>
+        <v>205</v>
       </c>
       <c r="H38" t="s">
-        <v>1</v>
+        <v>4</v>
       </c>
     </row>
     <row r="39" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A39" t="s">
-        <v>202</v>
+        <v>206</v>
       </c>
       <c r="C39" t="s">
-        <v>23</v>
+        <v>19</v>
       </c>
       <c r="D39" t="s">
-        <v>203</v>
+        <v>207</v>
       </c>
       <c r="E39" t="s">
-        <v>204</v>
+        <v>208</v>
       </c>
       <c r="F39" t="s">
-        <v>205</v>
+        <v>0</v>
       </c>
       <c r="G39" t="s">
-        <v>206</v>
+        <v>209</v>
       </c>
       <c r="H39" t="s">
-        <v>80</v>
+        <v>4</v>
       </c>
     </row>
     <row r="40" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A40" t="s">
+        <v>210</v>
+      </c>
+      <c r="C40" t="s">
+        <v>19</v>
+      </c>
+      <c r="D40" t="s">
         <v>207</v>
       </c>
-      <c r="C40" t="s">
-        <v>23</v>
-      </c>
-      <c r="D40" t="s">
+      <c r="E40" t="s">
         <v>208</v>
       </c>
-      <c r="E40" t="s">
+      <c r="F40" t="s">
+        <v>0</v>
+      </c>
+      <c r="G40" t="s">
         <v>209</v>
       </c>
-      <c r="F40" t="s">
-        <v>0</v>
-      </c>
-      <c r="G40" t="s">
-        <v>210</v>
-      </c>
       <c r="H40" t="s">
-        <v>80</v>
+        <v>4</v>
       </c>
     </row>
     <row r="41" spans="1:8" x14ac:dyDescent="0.3">
@@ -2802,22 +2844,22 @@
         <v>211</v>
       </c>
       <c r="C41" t="s">
-        <v>26</v>
+        <v>190</v>
       </c>
       <c r="D41" t="s">
         <v>212</v>
       </c>
       <c r="E41" t="s">
-        <v>35</v>
+        <v>213</v>
       </c>
       <c r="F41" t="s">
-        <v>36</v>
+        <v>0</v>
       </c>
       <c r="G41" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="H41" t="s">
-        <v>214</v>
+        <v>4</v>
       </c>
     </row>
     <row r="42" spans="1:8" x14ac:dyDescent="0.3">
@@ -2825,42 +2867,42 @@
         <v>215</v>
       </c>
       <c r="C42" t="s">
-        <v>10</v>
+        <v>190</v>
       </c>
       <c r="D42" t="s">
-        <v>216</v>
+        <v>212</v>
       </c>
       <c r="E42" t="s">
-        <v>217</v>
+        <v>213</v>
       </c>
       <c r="F42" t="s">
         <v>0</v>
       </c>
       <c r="G42" t="s">
-        <v>218</v>
+        <v>214</v>
       </c>
       <c r="H42" t="s">
-        <v>214</v>
+        <v>4</v>
       </c>
     </row>
     <row r="43" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A43" t="s">
+        <v>216</v>
+      </c>
+      <c r="C43" t="s">
+        <v>8</v>
+      </c>
+      <c r="D43" t="s">
+        <v>217</v>
+      </c>
+      <c r="E43" t="s">
+        <v>218</v>
+      </c>
+      <c r="F43" t="s">
         <v>219</v>
       </c>
-      <c r="C43" t="s">
-        <v>31</v>
-      </c>
-      <c r="D43" t="s">
+      <c r="G43" t="s">
         <v>220</v>
-      </c>
-      <c r="E43" t="s">
-        <v>30</v>
-      </c>
-      <c r="F43" t="s">
-        <v>0</v>
-      </c>
-      <c r="G43" t="s">
-        <v>221</v>
       </c>
       <c r="H43" t="s">
         <v>4</v>
@@ -2868,22 +2910,22 @@
     </row>
     <row r="44" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A44" t="s">
-        <v>222</v>
+        <v>64</v>
       </c>
       <c r="C44" t="s">
-        <v>22</v>
+        <v>13</v>
       </c>
       <c r="D44" t="s">
-        <v>223</v>
+        <v>65</v>
       </c>
       <c r="E44" t="s">
-        <v>224</v>
+        <v>15</v>
       </c>
       <c r="F44" t="s">
-        <v>0</v>
+        <v>16</v>
       </c>
       <c r="G44" t="s">
-        <v>225</v>
+        <v>66</v>
       </c>
       <c r="H44" t="s">
         <v>4</v>
@@ -2891,22 +2933,22 @@
     </row>
     <row r="45" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A45" t="s">
-        <v>226</v>
+        <v>67</v>
       </c>
       <c r="C45" t="s">
-        <v>22</v>
+        <v>13</v>
       </c>
       <c r="D45" t="s">
-        <v>223</v>
+        <v>65</v>
       </c>
       <c r="E45" t="s">
-        <v>224</v>
+        <v>15</v>
       </c>
       <c r="F45" t="s">
-        <v>0</v>
+        <v>16</v>
       </c>
       <c r="G45" t="s">
-        <v>225</v>
+        <v>66</v>
       </c>
       <c r="H45" t="s">
         <v>4</v>
@@ -2914,22 +2956,22 @@
     </row>
     <row r="46" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A46" t="s">
-        <v>227</v>
+        <v>68</v>
       </c>
       <c r="C46" t="s">
-        <v>22</v>
+        <v>13</v>
       </c>
       <c r="D46" t="s">
-        <v>223</v>
+        <v>65</v>
       </c>
       <c r="E46" t="s">
-        <v>224</v>
+        <v>15</v>
       </c>
       <c r="F46" t="s">
-        <v>0</v>
+        <v>16</v>
       </c>
       <c r="G46" t="s">
-        <v>225</v>
+        <v>66</v>
       </c>
       <c r="H46" t="s">
         <v>4</v>
@@ -2937,22 +2979,22 @@
     </row>
     <row r="47" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A47" t="s">
-        <v>81</v>
+        <v>221</v>
       </c>
       <c r="C47" t="s">
-        <v>31</v>
+        <v>19</v>
       </c>
       <c r="D47" t="s">
-        <v>82</v>
+        <v>222</v>
       </c>
       <c r="E47" t="s">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="F47" t="s">
         <v>0</v>
       </c>
       <c r="G47" t="s">
-        <v>53</v>
+        <v>223</v>
       </c>
       <c r="H47" t="s">
         <v>4</v>
@@ -2960,22 +3002,22 @@
     </row>
     <row r="48" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A48" t="s">
+        <v>224</v>
+      </c>
+      <c r="C48" t="s">
+        <v>2</v>
+      </c>
+      <c r="D48" t="s">
+        <v>225</v>
+      </c>
+      <c r="E48" t="s">
+        <v>226</v>
+      </c>
+      <c r="F48" t="s">
+        <v>227</v>
+      </c>
+      <c r="G48" t="s">
         <v>228</v>
-      </c>
-      <c r="C48" t="s">
-        <v>31</v>
-      </c>
-      <c r="D48" t="s">
-        <v>229</v>
-      </c>
-      <c r="E48" t="s">
-        <v>230</v>
-      </c>
-      <c r="F48" t="s">
-        <v>0</v>
-      </c>
-      <c r="G48" t="s">
-        <v>231</v>
       </c>
       <c r="H48" t="s">
         <v>4</v>
@@ -2983,22 +3025,22 @@
     </row>
     <row r="49" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A49" t="s">
+        <v>229</v>
+      </c>
+      <c r="C49" t="s">
+        <v>11</v>
+      </c>
+      <c r="D49" t="s">
+        <v>230</v>
+      </c>
+      <c r="E49" t="s">
+        <v>231</v>
+      </c>
+      <c r="F49" t="s">
+        <v>0</v>
+      </c>
+      <c r="G49" t="s">
         <v>232</v>
-      </c>
-      <c r="C49" t="s">
-        <v>12</v>
-      </c>
-      <c r="D49" t="s">
-        <v>233</v>
-      </c>
-      <c r="E49" t="s">
-        <v>67</v>
-      </c>
-      <c r="F49" t="s">
-        <v>0</v>
-      </c>
-      <c r="G49" t="s">
-        <v>234</v>
       </c>
       <c r="H49" t="s">
         <v>4</v>
@@ -3006,22 +3048,22 @@
     </row>
     <row r="50" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A50" t="s">
+        <v>233</v>
+      </c>
+      <c r="C50" t="s">
+        <v>11</v>
+      </c>
+      <c r="D50" t="s">
+        <v>234</v>
+      </c>
+      <c r="E50" t="s">
         <v>235</v>
       </c>
-      <c r="C50" t="s">
-        <v>19</v>
-      </c>
-      <c r="D50" t="s">
+      <c r="F50" t="s">
+        <v>0</v>
+      </c>
+      <c r="G50" t="s">
         <v>236</v>
-      </c>
-      <c r="E50" t="s">
-        <v>61</v>
-      </c>
-      <c r="F50" t="s">
-        <v>0</v>
-      </c>
-      <c r="G50" t="s">
-        <v>237</v>
       </c>
       <c r="H50" t="s">
         <v>4</v>
@@ -3029,22 +3071,22 @@
     </row>
     <row r="51" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A51" t="s">
+        <v>237</v>
+      </c>
+      <c r="C51" t="s">
+        <v>190</v>
+      </c>
+      <c r="D51" t="s">
         <v>238</v>
       </c>
-      <c r="C51" t="s">
-        <v>19</v>
-      </c>
-      <c r="D51" t="s">
-        <v>236</v>
-      </c>
       <c r="E51" t="s">
-        <v>61</v>
+        <v>33</v>
       </c>
       <c r="F51" t="s">
         <v>0</v>
       </c>
       <c r="G51" t="s">
-        <v>237</v>
+        <v>112</v>
       </c>
       <c r="H51" t="s">
         <v>4</v>
@@ -3055,19 +3097,19 @@
         <v>239</v>
       </c>
       <c r="C52" t="s">
-        <v>38</v>
+        <v>190</v>
       </c>
       <c r="D52" t="s">
-        <v>240</v>
+        <v>238</v>
       </c>
       <c r="E52" t="s">
-        <v>241</v>
+        <v>33</v>
       </c>
       <c r="F52" t="s">
-        <v>242</v>
+        <v>0</v>
       </c>
       <c r="G52" t="s">
-        <v>243</v>
+        <v>112</v>
       </c>
       <c r="H52" t="s">
         <v>4</v>
@@ -3075,22 +3117,22 @@
     </row>
     <row r="53" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A53" t="s">
-        <v>244</v>
+        <v>240</v>
       </c>
       <c r="C53" t="s">
-        <v>38</v>
+        <v>190</v>
       </c>
       <c r="D53" t="s">
-        <v>240</v>
+        <v>238</v>
       </c>
       <c r="E53" t="s">
-        <v>241</v>
+        <v>33</v>
       </c>
       <c r="F53" t="s">
-        <v>242</v>
+        <v>0</v>
       </c>
       <c r="G53" t="s">
-        <v>243</v>
+        <v>112</v>
       </c>
       <c r="H53" t="s">
         <v>4</v>
@@ -3098,22 +3140,22 @@
     </row>
     <row r="54" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A54" t="s">
-        <v>245</v>
+        <v>241</v>
       </c>
       <c r="C54" t="s">
-        <v>38</v>
+        <v>100</v>
       </c>
       <c r="D54" t="s">
-        <v>240</v>
+        <v>242</v>
       </c>
       <c r="E54" t="s">
-        <v>241</v>
+        <v>243</v>
       </c>
       <c r="F54" t="s">
-        <v>242</v>
+        <v>244</v>
       </c>
       <c r="G54" t="s">
-        <v>243</v>
+        <v>35</v>
       </c>
       <c r="H54" t="s">
         <v>4</v>
@@ -3121,22 +3163,22 @@
     </row>
     <row r="55" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A55" t="s">
-        <v>246</v>
+        <v>245</v>
       </c>
       <c r="C55" t="s">
-        <v>23</v>
+        <v>100</v>
       </c>
       <c r="D55" t="s">
-        <v>247</v>
+        <v>242</v>
       </c>
       <c r="E55" t="s">
-        <v>20</v>
+        <v>243</v>
       </c>
       <c r="F55" t="s">
-        <v>21</v>
+        <v>244</v>
       </c>
       <c r="G55" t="s">
-        <v>248</v>
+        <v>35</v>
       </c>
       <c r="H55" t="s">
         <v>4</v>
@@ -3144,22 +3186,22 @@
     </row>
     <row r="56" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A56" t="s">
-        <v>249</v>
+        <v>246</v>
       </c>
       <c r="C56" t="s">
-        <v>23</v>
+        <v>100</v>
       </c>
       <c r="D56" t="s">
-        <v>247</v>
+        <v>242</v>
       </c>
       <c r="E56" t="s">
-        <v>20</v>
+        <v>243</v>
       </c>
       <c r="F56" t="s">
-        <v>21</v>
+        <v>244</v>
       </c>
       <c r="G56" t="s">
-        <v>248</v>
+        <v>35</v>
       </c>
       <c r="H56" t="s">
         <v>4</v>
@@ -3167,22 +3209,22 @@
     </row>
     <row r="57" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A57" t="s">
-        <v>250</v>
+        <v>247</v>
       </c>
       <c r="C57" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="D57" t="s">
-        <v>251</v>
+        <v>248</v>
       </c>
       <c r="E57" t="s">
-        <v>34</v>
+        <v>51</v>
       </c>
       <c r="F57" t="s">
         <v>0</v>
       </c>
       <c r="G57" t="s">
-        <v>252</v>
+        <v>249</v>
       </c>
       <c r="H57" t="s">
         <v>4</v>
@@ -3190,22 +3232,22 @@
     </row>
     <row r="58" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A58" t="s">
+        <v>250</v>
+      </c>
+      <c r="C58" t="s">
+        <v>10</v>
+      </c>
+      <c r="D58" t="s">
+        <v>251</v>
+      </c>
+      <c r="E58" t="s">
+        <v>252</v>
+      </c>
+      <c r="F58" t="s">
+        <v>0</v>
+      </c>
+      <c r="G58" t="s">
         <v>253</v>
-      </c>
-      <c r="C58" t="s">
-        <v>23</v>
-      </c>
-      <c r="D58" t="s">
-        <v>254</v>
-      </c>
-      <c r="E58" t="s">
-        <v>17</v>
-      </c>
-      <c r="F58" t="s">
-        <v>18</v>
-      </c>
-      <c r="G58" t="s">
-        <v>255</v>
       </c>
       <c r="H58" t="s">
         <v>4</v>
@@ -3213,22 +3255,22 @@
     </row>
     <row r="59" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A59" t="s">
-        <v>256</v>
+        <v>254</v>
       </c>
       <c r="C59" t="s">
-        <v>23</v>
+        <v>10</v>
       </c>
       <c r="D59" t="s">
-        <v>254</v>
+        <v>251</v>
       </c>
       <c r="E59" t="s">
-        <v>17</v>
+        <v>252</v>
       </c>
       <c r="F59" t="s">
-        <v>18</v>
+        <v>0</v>
       </c>
       <c r="G59" t="s">
-        <v>255</v>
+        <v>253</v>
       </c>
       <c r="H59" t="s">
         <v>4</v>
@@ -3236,22 +3278,22 @@
     </row>
     <row r="60" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A60" t="s">
+        <v>255</v>
+      </c>
+      <c r="C60" t="s">
+        <v>9</v>
+      </c>
+      <c r="D60" t="s">
+        <v>256</v>
+      </c>
+      <c r="E60" t="s">
+        <v>77</v>
+      </c>
+      <c r="F60" t="s">
+        <v>78</v>
+      </c>
+      <c r="G60" t="s">
         <v>257</v>
-      </c>
-      <c r="C60" t="s">
-        <v>23</v>
-      </c>
-      <c r="D60" t="s">
-        <v>254</v>
-      </c>
-      <c r="E60" t="s">
-        <v>17</v>
-      </c>
-      <c r="F60" t="s">
-        <v>18</v>
-      </c>
-      <c r="G60" t="s">
-        <v>255</v>
       </c>
       <c r="H60" t="s">
         <v>4</v>
@@ -3262,19 +3304,19 @@
         <v>258</v>
       </c>
       <c r="C61" t="s">
-        <v>26</v>
+        <v>92</v>
       </c>
       <c r="D61" t="s">
         <v>259</v>
       </c>
       <c r="E61" t="s">
-        <v>51</v>
+        <v>6</v>
       </c>
       <c r="F61" t="s">
-        <v>52</v>
+        <v>7</v>
       </c>
       <c r="G61" t="s">
-        <v>93</v>
+        <v>260</v>
       </c>
       <c r="H61" t="s">
         <v>4</v>
@@ -3282,22 +3324,22 @@
     </row>
     <row r="62" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A62" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="C62" t="s">
-        <v>26</v>
+        <v>3</v>
       </c>
       <c r="D62" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="E62" t="s">
-        <v>51</v>
+        <v>43</v>
       </c>
       <c r="F62" t="s">
-        <v>52</v>
+        <v>0</v>
       </c>
       <c r="G62" t="s">
-        <v>93</v>
+        <v>263</v>
       </c>
       <c r="H62" t="s">
         <v>4</v>
@@ -3305,22 +3347,22 @@
     </row>
     <row r="63" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A63" t="s">
-        <v>261</v>
+        <v>264</v>
       </c>
       <c r="C63" t="s">
-        <v>31</v>
+        <v>165</v>
       </c>
       <c r="D63" t="s">
-        <v>262</v>
+        <v>265</v>
       </c>
       <c r="E63" t="s">
-        <v>230</v>
+        <v>184</v>
       </c>
       <c r="F63" t="s">
         <v>0</v>
       </c>
       <c r="G63" t="s">
-        <v>263</v>
+        <v>266</v>
       </c>
       <c r="H63" t="s">
         <v>4</v>
@@ -3328,22 +3370,22 @@
     </row>
     <row r="64" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A64" t="s">
-        <v>264</v>
+        <v>267</v>
       </c>
       <c r="C64" t="s">
-        <v>19</v>
+        <v>9</v>
       </c>
       <c r="D64" t="s">
-        <v>265</v>
+        <v>268</v>
       </c>
       <c r="E64" t="s">
-        <v>163</v>
+        <v>269</v>
       </c>
       <c r="F64" t="s">
         <v>0</v>
       </c>
       <c r="G64" t="s">
-        <v>266</v>
+        <v>270</v>
       </c>
       <c r="H64" t="s">
         <v>4</v>
@@ -3351,22 +3393,22 @@
     </row>
     <row r="65" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A65" t="s">
-        <v>267</v>
+        <v>271</v>
       </c>
       <c r="C65" t="s">
-        <v>19</v>
+        <v>11</v>
       </c>
       <c r="D65" t="s">
-        <v>265</v>
+        <v>272</v>
       </c>
       <c r="E65" t="s">
-        <v>163</v>
+        <v>273</v>
       </c>
       <c r="F65" t="s">
         <v>0</v>
       </c>
       <c r="G65" t="s">
-        <v>266</v>
+        <v>274</v>
       </c>
       <c r="H65" t="s">
         <v>4</v>
@@ -3374,22 +3416,22 @@
     </row>
     <row r="66" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A66" t="s">
-        <v>268</v>
+        <v>275</v>
       </c>
       <c r="C66" t="s">
-        <v>2</v>
+        <v>11</v>
       </c>
       <c r="D66" t="s">
-        <v>269</v>
+        <v>272</v>
       </c>
       <c r="E66" t="s">
-        <v>94</v>
+        <v>273</v>
       </c>
       <c r="F66" t="s">
         <v>0</v>
       </c>
       <c r="G66" t="s">
-        <v>270</v>
+        <v>274</v>
       </c>
       <c r="H66" t="s">
         <v>4</v>
@@ -3397,22 +3439,22 @@
     </row>
     <row r="67" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A67" t="s">
-        <v>271</v>
+        <v>276</v>
       </c>
       <c r="C67" t="s">
-        <v>11</v>
+        <v>152</v>
       </c>
       <c r="D67" t="s">
-        <v>272</v>
+        <v>277</v>
       </c>
       <c r="E67" t="s">
-        <v>133</v>
+        <v>278</v>
       </c>
       <c r="F67" t="s">
         <v>0</v>
       </c>
       <c r="G67" t="s">
-        <v>134</v>
+        <v>279</v>
       </c>
       <c r="H67" t="s">
         <v>4</v>
@@ -3420,22 +3462,22 @@
     </row>
     <row r="68" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A68" t="s">
-        <v>273</v>
+        <v>280</v>
       </c>
       <c r="C68" t="s">
-        <v>11</v>
+        <v>100</v>
       </c>
       <c r="D68" t="s">
-        <v>272</v>
+        <v>281</v>
       </c>
       <c r="E68" t="s">
-        <v>133</v>
+        <v>71</v>
       </c>
       <c r="F68" t="s">
         <v>0</v>
       </c>
       <c r="G68" t="s">
-        <v>134</v>
+        <v>72</v>
       </c>
       <c r="H68" t="s">
         <v>4</v>
@@ -3443,22 +3485,22 @@
     </row>
     <row r="69" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A69" t="s">
-        <v>274</v>
+        <v>282</v>
       </c>
       <c r="C69" t="s">
-        <v>24</v>
+        <v>9</v>
       </c>
       <c r="D69" t="s">
-        <v>275</v>
+        <v>283</v>
       </c>
       <c r="E69" t="s">
-        <v>6</v>
+        <v>284</v>
       </c>
       <c r="F69" t="s">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="G69" t="s">
-        <v>276</v>
+        <v>285</v>
       </c>
       <c r="H69" t="s">
         <v>4</v>
@@ -3466,22 +3508,22 @@
     </row>
     <row r="70" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A70" t="s">
-        <v>277</v>
+        <v>286</v>
       </c>
       <c r="C70" t="s">
-        <v>24</v>
+        <v>9</v>
       </c>
       <c r="D70" t="s">
-        <v>275</v>
+        <v>283</v>
       </c>
       <c r="E70" t="s">
-        <v>6</v>
+        <v>284</v>
       </c>
       <c r="F70" t="s">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="G70" t="s">
-        <v>276</v>
+        <v>285</v>
       </c>
       <c r="H70" t="s">
         <v>4</v>
@@ -3489,22 +3531,22 @@
     </row>
     <row r="71" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A71" t="s">
-        <v>278</v>
+        <v>287</v>
       </c>
       <c r="C71" t="s">
-        <v>24</v>
+        <v>9</v>
       </c>
       <c r="D71" t="s">
-        <v>275</v>
+        <v>283</v>
       </c>
       <c r="E71" t="s">
-        <v>6</v>
+        <v>284</v>
       </c>
       <c r="F71" t="s">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="G71" t="s">
-        <v>276</v>
+        <v>285</v>
       </c>
       <c r="H71" t="s">
         <v>4</v>
@@ -3512,22 +3554,22 @@
     </row>
     <row r="72" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A72" t="s">
-        <v>279</v>
+        <v>288</v>
       </c>
       <c r="C72" t="s">
-        <v>24</v>
+        <v>92</v>
       </c>
       <c r="D72" t="s">
-        <v>280</v>
+        <v>289</v>
       </c>
       <c r="E72" t="s">
-        <v>49</v>
+        <v>290</v>
       </c>
       <c r="F72" t="s">
-        <v>0</v>
+        <v>291</v>
       </c>
       <c r="G72" t="s">
-        <v>281</v>
+        <v>292</v>
       </c>
       <c r="H72" t="s">
         <v>4</v>
@@ -3535,22 +3577,22 @@
     </row>
     <row r="73" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A73" t="s">
-        <v>282</v>
+        <v>293</v>
       </c>
       <c r="C73" t="s">
-        <v>8</v>
+        <v>92</v>
       </c>
       <c r="D73" t="s">
-        <v>283</v>
+        <v>289</v>
       </c>
       <c r="E73" t="s">
-        <v>39</v>
+        <v>290</v>
       </c>
       <c r="F73" t="s">
-        <v>40</v>
+        <v>291</v>
       </c>
       <c r="G73" t="s">
-        <v>41</v>
+        <v>292</v>
       </c>
       <c r="H73" t="s">
         <v>4</v>
@@ -3558,22 +3600,22 @@
     </row>
     <row r="74" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A74" t="s">
-        <v>284</v>
+        <v>294</v>
       </c>
       <c r="C74" t="s">
-        <v>8</v>
+        <v>92</v>
       </c>
       <c r="D74" t="s">
-        <v>283</v>
+        <v>289</v>
       </c>
       <c r="E74" t="s">
-        <v>39</v>
+        <v>290</v>
       </c>
       <c r="F74" t="s">
-        <v>40</v>
+        <v>291</v>
       </c>
       <c r="G74" t="s">
-        <v>41</v>
+        <v>292</v>
       </c>
       <c r="H74" t="s">
         <v>4</v>
@@ -3581,22 +3623,22 @@
     </row>
     <row r="75" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A75" t="s">
-        <v>285</v>
+        <v>295</v>
       </c>
       <c r="C75" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="D75" t="s">
-        <v>286</v>
+        <v>296</v>
       </c>
       <c r="E75" t="s">
-        <v>17</v>
+        <v>297</v>
       </c>
       <c r="F75" t="s">
-        <v>18</v>
+        <v>0</v>
       </c>
       <c r="G75" t="s">
-        <v>287</v>
+        <v>298</v>
       </c>
       <c r="H75" t="s">
         <v>4</v>
@@ -3604,22 +3646,22 @@
     </row>
     <row r="76" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A76" t="s">
-        <v>288</v>
+        <v>299</v>
       </c>
       <c r="C76" t="s">
-        <v>185</v>
+        <v>21</v>
       </c>
       <c r="D76" t="s">
-        <v>289</v>
+        <v>296</v>
       </c>
       <c r="E76" t="s">
-        <v>290</v>
+        <v>297</v>
       </c>
       <c r="F76" t="s">
         <v>0</v>
       </c>
       <c r="G76" t="s">
-        <v>291</v>
+        <v>298</v>
       </c>
       <c r="H76" t="s">
         <v>4</v>
@@ -3627,22 +3669,22 @@
     </row>
     <row r="77" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A77" t="s">
-        <v>292</v>
+        <v>300</v>
       </c>
       <c r="C77" t="s">
-        <v>104</v>
+        <v>58</v>
       </c>
       <c r="D77" t="s">
-        <v>293</v>
+        <v>301</v>
       </c>
       <c r="E77" t="s">
-        <v>294</v>
+        <v>302</v>
       </c>
       <c r="F77" t="s">
-        <v>0</v>
+        <v>303</v>
       </c>
       <c r="G77" t="s">
-        <v>295</v>
+        <v>304</v>
       </c>
       <c r="H77" t="s">
         <v>4</v>
@@ -3650,22 +3692,22 @@
     </row>
     <row r="78" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A78" t="s">
-        <v>296</v>
+        <v>305</v>
       </c>
       <c r="C78" t="s">
-        <v>104</v>
+        <v>58</v>
       </c>
       <c r="D78" t="s">
-        <v>293</v>
+        <v>306</v>
       </c>
       <c r="E78" t="s">
-        <v>294</v>
+        <v>307</v>
       </c>
       <c r="F78" t="s">
         <v>0</v>
       </c>
       <c r="G78" t="s">
-        <v>295</v>
+        <v>308</v>
       </c>
       <c r="H78" t="s">
         <v>4</v>
@@ -3673,22 +3715,22 @@
     </row>
     <row r="79" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A79" t="s">
-        <v>297</v>
+        <v>309</v>
       </c>
       <c r="C79" t="s">
-        <v>104</v>
+        <v>13</v>
       </c>
       <c r="D79" t="s">
-        <v>298</v>
+        <v>310</v>
       </c>
       <c r="E79" t="s">
-        <v>133</v>
+        <v>15</v>
       </c>
       <c r="F79" t="s">
-        <v>0</v>
+        <v>16</v>
       </c>
       <c r="G79" t="s">
-        <v>299</v>
+        <v>311</v>
       </c>
       <c r="H79" t="s">
         <v>4</v>
@@ -3696,22 +3738,22 @@
     </row>
     <row r="80" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A80" t="s">
-        <v>300</v>
+        <v>312</v>
       </c>
       <c r="C80" t="s">
-        <v>31</v>
+        <v>19</v>
       </c>
       <c r="D80" t="s">
-        <v>301</v>
+        <v>313</v>
       </c>
       <c r="E80" t="s">
-        <v>302</v>
+        <v>208</v>
       </c>
       <c r="F80" t="s">
         <v>0</v>
       </c>
       <c r="G80" t="s">
-        <v>303</v>
+        <v>314</v>
       </c>
       <c r="H80" t="s">
         <v>4</v>
@@ -3719,22 +3761,22 @@
     </row>
     <row r="81" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A81" t="s">
-        <v>304</v>
+        <v>315</v>
       </c>
       <c r="C81" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="D81" t="s">
-        <v>305</v>
+        <v>316</v>
       </c>
       <c r="E81" t="s">
-        <v>306</v>
+        <v>273</v>
       </c>
       <c r="F81" t="s">
         <v>0</v>
       </c>
       <c r="G81" t="s">
-        <v>307</v>
+        <v>317</v>
       </c>
       <c r="H81" t="s">
         <v>4</v>
@@ -3742,22 +3784,22 @@
     </row>
     <row r="82" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A82" t="s">
-        <v>308</v>
+        <v>318</v>
       </c>
       <c r="C82" t="s">
-        <v>22</v>
+        <v>53</v>
       </c>
       <c r="D82" t="s">
-        <v>309</v>
+        <v>319</v>
       </c>
       <c r="E82" t="s">
-        <v>224</v>
+        <v>55</v>
       </c>
       <c r="F82" t="s">
-        <v>0</v>
+        <v>56</v>
       </c>
       <c r="G82" t="s">
-        <v>310</v>
+        <v>320</v>
       </c>
       <c r="H82" t="s">
         <v>4</v>
@@ -3765,22 +3807,22 @@
     </row>
     <row r="83" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A83" t="s">
-        <v>311</v>
+        <v>321</v>
       </c>
       <c r="C83" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="D83" t="s">
-        <v>309</v>
+        <v>322</v>
       </c>
       <c r="E83" t="s">
-        <v>224</v>
+        <v>323</v>
       </c>
       <c r="F83" t="s">
         <v>0</v>
       </c>
       <c r="G83" t="s">
-        <v>310</v>
+        <v>324</v>
       </c>
       <c r="H83" t="s">
         <v>4</v>
@@ -3788,22 +3830,22 @@
     </row>
     <row r="84" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A84" t="s">
-        <v>312</v>
+        <v>325</v>
       </c>
       <c r="C84" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="D84" t="s">
-        <v>309</v>
+        <v>322</v>
       </c>
       <c r="E84" t="s">
-        <v>224</v>
+        <v>323</v>
       </c>
       <c r="F84" t="s">
         <v>0</v>
       </c>
       <c r="G84" t="s">
-        <v>310</v>
+        <v>324</v>
       </c>
       <c r="H84" t="s">
         <v>4</v>
@@ -3811,22 +3853,22 @@
     </row>
     <row r="85" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A85" t="s">
-        <v>313</v>
+        <v>326</v>
       </c>
       <c r="C85" t="s">
-        <v>104</v>
+        <v>53</v>
       </c>
       <c r="D85" t="s">
-        <v>314</v>
+        <v>327</v>
       </c>
       <c r="E85" t="s">
-        <v>294</v>
+        <v>55</v>
       </c>
       <c r="F85" t="s">
-        <v>0</v>
+        <v>56</v>
       </c>
       <c r="G85" t="s">
-        <v>315</v>
+        <v>328</v>
       </c>
       <c r="H85" t="s">
         <v>4</v>
@@ -3834,22 +3876,22 @@
     </row>
     <row r="86" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A86" t="s">
-        <v>316</v>
+        <v>329</v>
       </c>
       <c r="C86" t="s">
-        <v>23</v>
+        <v>13</v>
       </c>
       <c r="D86" t="s">
-        <v>317</v>
+        <v>330</v>
       </c>
       <c r="E86" t="s">
-        <v>20</v>
+        <v>60</v>
       </c>
       <c r="F86" t="s">
-        <v>21</v>
+        <v>61</v>
       </c>
       <c r="G86" t="s">
-        <v>318</v>
+        <v>331</v>
       </c>
       <c r="H86" t="s">
         <v>4</v>
@@ -3857,22 +3899,22 @@
     </row>
     <row r="87" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A87" t="s">
-        <v>319</v>
+        <v>332</v>
       </c>
       <c r="C87" t="s">
-        <v>13</v>
+        <v>21</v>
       </c>
       <c r="D87" t="s">
-        <v>320</v>
+        <v>333</v>
       </c>
       <c r="E87" t="s">
-        <v>321</v>
+        <v>334</v>
       </c>
       <c r="F87" t="s">
-        <v>322</v>
+        <v>0</v>
       </c>
       <c r="G87" t="s">
-        <v>323</v>
+        <v>335</v>
       </c>
       <c r="H87" t="s">
         <v>4</v>
@@ -3880,22 +3922,22 @@
     </row>
     <row r="88" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A88" t="s">
-        <v>324</v>
+        <v>336</v>
       </c>
       <c r="C88" t="s">
-        <v>38</v>
+        <v>19</v>
       </c>
       <c r="D88" t="s">
-        <v>325</v>
+        <v>337</v>
       </c>
       <c r="E88" t="s">
-        <v>43</v>
+        <v>338</v>
       </c>
       <c r="F88" t="s">
         <v>0</v>
       </c>
       <c r="G88" t="s">
-        <v>326</v>
+        <v>339</v>
       </c>
       <c r="H88" t="s">
         <v>4</v>
@@ -3903,22 +3945,22 @@
     </row>
     <row r="89" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A89" t="s">
-        <v>327</v>
+        <v>340</v>
       </c>
       <c r="C89" t="s">
-        <v>26</v>
+        <v>13</v>
       </c>
       <c r="D89" t="s">
-        <v>328</v>
+        <v>341</v>
       </c>
       <c r="E89" t="s">
-        <v>329</v>
+        <v>17</v>
       </c>
       <c r="F89" t="s">
-        <v>330</v>
+        <v>18</v>
       </c>
       <c r="G89" t="s">
-        <v>331</v>
+        <v>342</v>
       </c>
       <c r="H89" t="s">
         <v>4</v>
@@ -3926,22 +3968,22 @@
     </row>
     <row r="90" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A90" t="s">
-        <v>332</v>
+        <v>343</v>
       </c>
       <c r="C90" t="s">
-        <v>26</v>
+        <v>58</v>
       </c>
       <c r="D90" t="s">
-        <v>328</v>
+        <v>344</v>
       </c>
       <c r="E90" t="s">
-        <v>329</v>
+        <v>345</v>
       </c>
       <c r="F90" t="s">
-        <v>330</v>
+        <v>346</v>
       </c>
       <c r="G90" t="s">
-        <v>331</v>
+        <v>347</v>
       </c>
       <c r="H90" t="s">
         <v>4</v>
@@ -3949,22 +3991,22 @@
     </row>
     <row r="91" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A91" t="s">
-        <v>333</v>
+        <v>348</v>
       </c>
       <c r="C91" t="s">
-        <v>12</v>
+        <v>190</v>
       </c>
       <c r="D91" t="s">
-        <v>334</v>
+        <v>349</v>
       </c>
       <c r="E91" t="s">
-        <v>335</v>
+        <v>74</v>
       </c>
       <c r="F91" t="s">
         <v>0</v>
       </c>
       <c r="G91" t="s">
-        <v>336</v>
+        <v>350</v>
       </c>
       <c r="H91" t="s">
         <v>4</v>
@@ -3972,22 +4014,22 @@
     </row>
     <row r="92" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A92" t="s">
-        <v>337</v>
+        <v>351</v>
       </c>
       <c r="C92" t="s">
-        <v>104</v>
+        <v>190</v>
       </c>
       <c r="D92" t="s">
-        <v>338</v>
+        <v>349</v>
       </c>
       <c r="E92" t="s">
-        <v>92</v>
+        <v>74</v>
       </c>
       <c r="F92" t="s">
         <v>0</v>
       </c>
       <c r="G92" t="s">
-        <v>339</v>
+        <v>350</v>
       </c>
       <c r="H92" t="s">
         <v>4</v>
@@ -3995,22 +4037,22 @@
     </row>
     <row r="93" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A93" t="s">
-        <v>340</v>
+        <v>352</v>
       </c>
       <c r="C93" t="s">
-        <v>104</v>
+        <v>2</v>
       </c>
       <c r="D93" t="s">
-        <v>338</v>
+        <v>353</v>
       </c>
       <c r="E93" t="s">
-        <v>92</v>
+        <v>14</v>
       </c>
       <c r="F93" t="s">
         <v>0</v>
       </c>
       <c r="G93" t="s">
-        <v>339</v>
+        <v>354</v>
       </c>
       <c r="H93" t="s">
         <v>4</v>
@@ -4018,22 +4060,22 @@
     </row>
     <row r="94" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A94" t="s">
-        <v>341</v>
+        <v>355</v>
       </c>
       <c r="C94" t="s">
-        <v>104</v>
+        <v>53</v>
       </c>
       <c r="D94" t="s">
-        <v>338</v>
+        <v>356</v>
       </c>
       <c r="E94" t="s">
-        <v>92</v>
+        <v>149</v>
       </c>
       <c r="F94" t="s">
         <v>0</v>
       </c>
       <c r="G94" t="s">
-        <v>339</v>
+        <v>357</v>
       </c>
       <c r="H94" t="s">
         <v>4</v>
@@ -4041,22 +4083,22 @@
     </row>
     <row r="95" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A95" t="s">
-        <v>342</v>
+        <v>358</v>
       </c>
       <c r="C95" t="s">
-        <v>24</v>
+        <v>11</v>
       </c>
       <c r="D95" t="s">
-        <v>343</v>
+        <v>359</v>
       </c>
       <c r="E95" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="F95" t="s">
         <v>0</v>
       </c>
       <c r="G95" t="s">
-        <v>344</v>
+        <v>360</v>
       </c>
       <c r="H95" t="s">
         <v>4</v>
@@ -4064,22 +4106,22 @@
     </row>
     <row r="96" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A96" t="s">
-        <v>345</v>
+        <v>361</v>
       </c>
       <c r="C96" t="s">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="D96" t="s">
-        <v>346</v>
+        <v>362</v>
       </c>
       <c r="E96" t="s">
-        <v>347</v>
+        <v>363</v>
       </c>
       <c r="F96" t="s">
-        <v>0</v>
+        <v>160</v>
       </c>
       <c r="G96" t="s">
-        <v>348</v>
+        <v>364</v>
       </c>
       <c r="H96" t="s">
         <v>4</v>
@@ -4087,22 +4129,22 @@
     </row>
     <row r="97" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A97" t="s">
-        <v>349</v>
+        <v>365</v>
       </c>
       <c r="C97" t="s">
-        <v>19</v>
+        <v>2</v>
       </c>
       <c r="D97" t="s">
-        <v>346</v>
+        <v>366</v>
       </c>
       <c r="E97" t="s">
-        <v>347</v>
+        <v>367</v>
       </c>
       <c r="F97" t="s">
-        <v>0</v>
+        <v>368</v>
       </c>
       <c r="G97" t="s">
-        <v>348</v>
+        <v>369</v>
       </c>
       <c r="H97" t="s">
         <v>4</v>
@@ -4110,22 +4152,22 @@
     </row>
     <row r="98" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A98" t="s">
-        <v>350</v>
+        <v>370</v>
       </c>
       <c r="C98" t="s">
-        <v>26</v>
+        <v>20</v>
       </c>
       <c r="D98" t="s">
-        <v>351</v>
+        <v>371</v>
       </c>
       <c r="E98" t="s">
-        <v>71</v>
+        <v>59</v>
       </c>
       <c r="F98" t="s">
-        <v>72</v>
+        <v>0</v>
       </c>
       <c r="G98" t="s">
-        <v>79</v>
+        <v>372</v>
       </c>
       <c r="H98" t="s">
         <v>4</v>
@@ -4133,22 +4175,22 @@
     </row>
     <row r="99" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A99" t="s">
-        <v>352</v>
+        <v>373</v>
       </c>
       <c r="C99" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="D99" t="s">
-        <v>353</v>
+        <v>374</v>
       </c>
       <c r="E99" t="s">
-        <v>6</v>
+        <v>334</v>
       </c>
       <c r="F99" t="s">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="G99" t="s">
-        <v>354</v>
+        <v>375</v>
       </c>
       <c r="H99" t="s">
         <v>4</v>
@@ -4156,22 +4198,22 @@
     </row>
     <row r="100" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A100" t="s">
-        <v>355</v>
+        <v>376</v>
       </c>
       <c r="C100" t="s">
-        <v>26</v>
+        <v>12</v>
       </c>
       <c r="D100" t="s">
-        <v>356</v>
+        <v>377</v>
       </c>
       <c r="E100" t="s">
-        <v>35</v>
+        <v>54</v>
       </c>
       <c r="F100" t="s">
-        <v>36</v>
+        <v>0</v>
       </c>
       <c r="G100" t="s">
-        <v>357</v>
+        <v>378</v>
       </c>
       <c r="H100" t="s">
         <v>4</v>
@@ -4179,22 +4221,22 @@
     </row>
     <row r="101" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A101" t="s">
-        <v>358</v>
+        <v>379</v>
       </c>
       <c r="C101" t="s">
-        <v>23</v>
+        <v>8</v>
       </c>
       <c r="D101" t="s">
-        <v>359</v>
+        <v>380</v>
       </c>
       <c r="E101" t="s">
-        <v>360</v>
+        <v>381</v>
       </c>
       <c r="F101" t="s">
-        <v>361</v>
+        <v>0</v>
       </c>
       <c r="G101" t="s">
-        <v>362</v>
+        <v>382</v>
       </c>
       <c r="H101" t="s">
         <v>4</v>
@@ -4202,22 +4244,22 @@
     </row>
     <row r="102" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A102" t="s">
-        <v>363</v>
+        <v>383</v>
       </c>
       <c r="C102" t="s">
-        <v>23</v>
+        <v>152</v>
       </c>
       <c r="D102" t="s">
-        <v>359</v>
+        <v>384</v>
       </c>
       <c r="E102" t="s">
-        <v>360</v>
+        <v>385</v>
       </c>
       <c r="F102" t="s">
-        <v>361</v>
+        <v>0</v>
       </c>
       <c r="G102" t="s">
-        <v>362</v>
+        <v>386</v>
       </c>
       <c r="H102" t="s">
         <v>4</v>
@@ -4225,22 +4267,22 @@
     </row>
     <row r="103" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A103" t="s">
-        <v>364</v>
+        <v>387</v>
       </c>
       <c r="C103" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="D103" t="s">
-        <v>365</v>
+        <v>388</v>
       </c>
       <c r="E103" t="s">
-        <v>366</v>
+        <v>389</v>
       </c>
       <c r="F103" t="s">
-        <v>367</v>
+        <v>0</v>
       </c>
       <c r="G103" t="s">
-        <v>41</v>
+        <v>390</v>
       </c>
       <c r="H103" t="s">
         <v>4</v>
@@ -4248,22 +4290,22 @@
     </row>
     <row r="104" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A104" t="s">
-        <v>368</v>
+        <v>391</v>
       </c>
       <c r="C104" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="D104" t="s">
-        <v>365</v>
+        <v>388</v>
       </c>
       <c r="E104" t="s">
-        <v>366</v>
+        <v>389</v>
       </c>
       <c r="F104" t="s">
-        <v>367</v>
+        <v>0</v>
       </c>
       <c r="G104" t="s">
-        <v>41</v>
+        <v>390</v>
       </c>
       <c r="H104" t="s">
         <v>4</v>
@@ -4271,22 +4313,22 @@
     </row>
     <row r="105" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A105" t="s">
-        <v>369</v>
+        <v>392</v>
       </c>
       <c r="C105" t="s">
-        <v>24</v>
+        <v>393</v>
       </c>
       <c r="D105" t="s">
-        <v>370</v>
+        <v>394</v>
       </c>
       <c r="E105" t="s">
-        <v>371</v>
+        <v>77</v>
       </c>
       <c r="F105" t="s">
-        <v>0</v>
+        <v>78</v>
       </c>
       <c r="G105" t="s">
-        <v>372</v>
+        <v>395</v>
       </c>
       <c r="H105" t="s">
         <v>4</v>
@@ -4294,22 +4336,22 @@
     </row>
     <row r="106" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A106" t="s">
-        <v>373</v>
+        <v>396</v>
       </c>
       <c r="C106" t="s">
-        <v>2</v>
+        <v>58</v>
       </c>
       <c r="D106" t="s">
-        <v>374</v>
+        <v>397</v>
       </c>
       <c r="E106" t="s">
-        <v>14</v>
+        <v>398</v>
       </c>
       <c r="F106" t="s">
-        <v>15</v>
+        <v>399</v>
       </c>
       <c r="G106" t="s">
-        <v>375</v>
+        <v>400</v>
       </c>
       <c r="H106" t="s">
         <v>4</v>
@@ -4317,22 +4359,22 @@
     </row>
     <row r="107" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A107" t="s">
-        <v>376</v>
+        <v>401</v>
       </c>
       <c r="C107" t="s">
-        <v>9</v>
+        <v>152</v>
       </c>
       <c r="D107" t="s">
-        <v>377</v>
+        <v>402</v>
       </c>
       <c r="E107" t="s">
-        <v>378</v>
+        <v>63</v>
       </c>
       <c r="F107" t="s">
         <v>0</v>
       </c>
       <c r="G107" t="s">
-        <v>379</v>
+        <v>403</v>
       </c>
       <c r="H107" t="s">
         <v>4</v>
@@ -4340,22 +4382,22 @@
     </row>
     <row r="108" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A108" t="s">
-        <v>380</v>
+        <v>404</v>
       </c>
       <c r="C108" t="s">
-        <v>26</v>
+        <v>9</v>
       </c>
       <c r="D108" t="s">
-        <v>381</v>
+        <v>405</v>
       </c>
       <c r="E108" t="s">
-        <v>382</v>
+        <v>406</v>
       </c>
       <c r="F108" t="s">
-        <v>383</v>
+        <v>0</v>
       </c>
       <c r="G108" t="s">
-        <v>384</v>
+        <v>407</v>
       </c>
       <c r="H108" t="s">
         <v>4</v>
@@ -4363,22 +4405,22 @@
     </row>
     <row r="109" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A109" t="s">
-        <v>385</v>
+        <v>408</v>
       </c>
       <c r="C109" t="s">
-        <v>19</v>
+        <v>3</v>
       </c>
       <c r="D109" t="s">
-        <v>386</v>
+        <v>409</v>
       </c>
       <c r="E109" t="s">
-        <v>69</v>
+        <v>43</v>
       </c>
       <c r="F109" t="s">
-        <v>70</v>
+        <v>0</v>
       </c>
       <c r="G109" t="s">
-        <v>387</v>
+        <v>48</v>
       </c>
       <c r="H109" t="s">
         <v>4</v>
@@ -4386,22 +4428,22 @@
     </row>
     <row r="110" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A110" t="s">
-        <v>388</v>
+        <v>410</v>
       </c>
       <c r="C110" t="s">
-        <v>19</v>
+        <v>3</v>
       </c>
       <c r="D110" t="s">
-        <v>386</v>
+        <v>411</v>
       </c>
       <c r="E110" t="s">
-        <v>69</v>
+        <v>57</v>
       </c>
       <c r="F110" t="s">
-        <v>70</v>
+        <v>0</v>
       </c>
       <c r="G110" t="s">
-        <v>387</v>
+        <v>412</v>
       </c>
       <c r="H110" t="s">
         <v>4</v>
@@ -4409,22 +4451,22 @@
     </row>
     <row r="111" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A111" t="s">
-        <v>389</v>
+        <v>413</v>
       </c>
       <c r="C111" t="s">
-        <v>26</v>
+        <v>20</v>
       </c>
       <c r="D111" t="s">
-        <v>390</v>
+        <v>414</v>
       </c>
       <c r="E111" t="s">
-        <v>329</v>
+        <v>415</v>
       </c>
       <c r="F111" t="s">
-        <v>330</v>
+        <v>0</v>
       </c>
       <c r="G111" t="s">
-        <v>86</v>
+        <v>416</v>
       </c>
       <c r="H111" t="s">
         <v>4</v>
@@ -4432,22 +4474,22 @@
     </row>
     <row r="112" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A112" t="s">
-        <v>391</v>
+        <v>417</v>
       </c>
       <c r="C112" t="s">
-        <v>12</v>
+        <v>58</v>
       </c>
       <c r="D112" t="s">
-        <v>392</v>
+        <v>418</v>
       </c>
       <c r="E112" t="s">
-        <v>393</v>
+        <v>419</v>
       </c>
       <c r="F112" t="s">
         <v>0</v>
       </c>
       <c r="G112" t="s">
-        <v>394</v>
+        <v>420</v>
       </c>
       <c r="H112" t="s">
         <v>4</v>
@@ -4455,22 +4497,22 @@
     </row>
     <row r="113" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A113" t="s">
-        <v>395</v>
+        <v>421</v>
       </c>
       <c r="C113" t="s">
-        <v>12</v>
+        <v>58</v>
       </c>
       <c r="D113" t="s">
-        <v>392</v>
+        <v>418</v>
       </c>
       <c r="E113" t="s">
-        <v>393</v>
+        <v>419</v>
       </c>
       <c r="F113" t="s">
         <v>0</v>
       </c>
       <c r="G113" t="s">
-        <v>394</v>
+        <v>420</v>
       </c>
       <c r="H113" t="s">
         <v>4</v>
@@ -4478,22 +4520,22 @@
     </row>
     <row r="114" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A114" t="s">
-        <v>396</v>
+        <v>422</v>
       </c>
       <c r="C114" t="s">
-        <v>26</v>
+        <v>20</v>
       </c>
       <c r="D114" t="s">
-        <v>397</v>
+        <v>423</v>
       </c>
       <c r="E114" t="s">
-        <v>398</v>
+        <v>424</v>
       </c>
       <c r="F114" t="s">
-        <v>399</v>
+        <v>0</v>
       </c>
       <c r="G114" t="s">
-        <v>400</v>
+        <v>425</v>
       </c>
       <c r="H114" t="s">
         <v>4</v>
@@ -4501,22 +4543,22 @@
     </row>
     <row r="115" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A115" t="s">
-        <v>401</v>
+        <v>426</v>
       </c>
       <c r="C115" t="s">
-        <v>22</v>
+        <v>92</v>
       </c>
       <c r="D115" t="s">
-        <v>402</v>
+        <v>427</v>
       </c>
       <c r="E115" t="s">
-        <v>37</v>
+        <v>6</v>
       </c>
       <c r="F115" t="s">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="G115" t="s">
-        <v>403</v>
+        <v>428</v>
       </c>
       <c r="H115" t="s">
         <v>4</v>
@@ -4524,22 +4566,22 @@
     </row>
     <row r="116" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A116" t="s">
-        <v>404</v>
+        <v>429</v>
       </c>
       <c r="C116" t="s">
-        <v>104</v>
+        <v>152</v>
       </c>
       <c r="D116" t="s">
-        <v>405</v>
+        <v>430</v>
       </c>
       <c r="E116" t="s">
-        <v>406</v>
+        <v>63</v>
       </c>
       <c r="F116" t="s">
         <v>0</v>
       </c>
       <c r="G116" t="s">
-        <v>407</v>
+        <v>431</v>
       </c>
       <c r="H116" t="s">
         <v>4</v>
@@ -4547,22 +4589,22 @@
     </row>
     <row r="117" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A117" t="s">
-        <v>408</v>
+        <v>432</v>
       </c>
       <c r="C117" t="s">
-        <v>3</v>
+        <v>92</v>
       </c>
       <c r="D117" t="s">
-        <v>409</v>
+        <v>433</v>
       </c>
       <c r="E117" t="s">
-        <v>16</v>
+        <v>26</v>
       </c>
       <c r="F117" t="s">
-        <v>0</v>
+        <v>27</v>
       </c>
       <c r="G117" t="s">
-        <v>410</v>
+        <v>434</v>
       </c>
       <c r="H117" t="s">
         <v>4</v>
@@ -4570,22 +4612,22 @@
     </row>
     <row r="118" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A118" t="s">
-        <v>411</v>
+        <v>435</v>
       </c>
       <c r="C118" t="s">
-        <v>38</v>
+        <v>12</v>
       </c>
       <c r="D118" t="s">
-        <v>412</v>
+        <v>436</v>
       </c>
       <c r="E118" t="s">
-        <v>413</v>
+        <v>73</v>
       </c>
       <c r="F118" t="s">
         <v>0</v>
       </c>
       <c r="G118" t="s">
-        <v>414</v>
+        <v>437</v>
       </c>
       <c r="H118" t="s">
         <v>4</v>
@@ -4593,321 +4635,321 @@
     </row>
     <row r="119" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A119" t="s">
-        <v>415</v>
+        <v>438</v>
       </c>
       <c r="C119" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="D119" t="s">
-        <v>416</v>
+        <v>439</v>
       </c>
       <c r="E119" t="s">
-        <v>378</v>
+        <v>218</v>
       </c>
       <c r="F119" t="s">
-        <v>0</v>
+        <v>219</v>
       </c>
       <c r="G119" t="s">
-        <v>417</v>
+        <v>440</v>
       </c>
       <c r="H119" t="s">
-        <v>4</v>
+        <v>5</v>
       </c>
     </row>
     <row r="120" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A120" t="s">
-        <v>418</v>
+        <v>441</v>
       </c>
       <c r="C120" t="s">
-        <v>185</v>
+        <v>13</v>
       </c>
       <c r="D120" t="s">
-        <v>419</v>
+        <v>442</v>
       </c>
       <c r="E120" t="s">
-        <v>420</v>
+        <v>79</v>
       </c>
       <c r="F120" t="s">
-        <v>0</v>
+        <v>80</v>
       </c>
       <c r="G120" t="s">
-        <v>421</v>
+        <v>443</v>
       </c>
       <c r="H120" t="s">
-        <v>4</v>
+        <v>5</v>
       </c>
     </row>
     <row r="121" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A121" t="s">
-        <v>422</v>
+        <v>444</v>
       </c>
       <c r="C121" t="s">
-        <v>38</v>
+        <v>13</v>
       </c>
       <c r="D121" t="s">
-        <v>423</v>
+        <v>442</v>
       </c>
       <c r="E121" t="s">
-        <v>424</v>
+        <v>79</v>
       </c>
       <c r="F121" t="s">
-        <v>0</v>
+        <v>80</v>
       </c>
       <c r="G121" t="s">
-        <v>425</v>
+        <v>443</v>
       </c>
       <c r="H121" t="s">
-        <v>4</v>
+        <v>5</v>
       </c>
     </row>
     <row r="122" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A122" t="s">
-        <v>426</v>
+        <v>445</v>
       </c>
       <c r="C122" t="s">
-        <v>3</v>
+        <v>165</v>
       </c>
       <c r="D122" t="s">
-        <v>427</v>
+        <v>446</v>
       </c>
       <c r="E122" t="s">
-        <v>428</v>
+        <v>447</v>
       </c>
       <c r="F122" t="s">
-        <v>429</v>
+        <v>0</v>
       </c>
       <c r="G122" t="s">
-        <v>430</v>
+        <v>448</v>
       </c>
       <c r="H122" t="s">
-        <v>4</v>
+        <v>5</v>
       </c>
     </row>
     <row r="123" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A123" t="s">
-        <v>431</v>
+        <v>449</v>
       </c>
       <c r="C123" t="s">
-        <v>3</v>
+        <v>165</v>
       </c>
       <c r="D123" t="s">
-        <v>427</v>
+        <v>450</v>
       </c>
       <c r="E123" t="s">
-        <v>428</v>
+        <v>451</v>
       </c>
       <c r="F123" t="s">
-        <v>429</v>
+        <v>0</v>
       </c>
       <c r="G123" t="s">
-        <v>430</v>
+        <v>452</v>
       </c>
       <c r="H123" t="s">
-        <v>4</v>
+        <v>5</v>
       </c>
     </row>
     <row r="124" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A124" t="s">
-        <v>432</v>
+        <v>453</v>
       </c>
       <c r="C124" t="s">
-        <v>10</v>
+        <v>53</v>
       </c>
       <c r="D124" t="s">
-        <v>433</v>
+        <v>454</v>
       </c>
       <c r="E124" t="s">
-        <v>217</v>
+        <v>25</v>
       </c>
       <c r="F124" t="s">
         <v>0</v>
       </c>
       <c r="G124" t="s">
-        <v>434</v>
+        <v>455</v>
       </c>
       <c r="H124" t="s">
-        <v>4</v>
+        <v>5</v>
       </c>
     </row>
     <row r="125" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A125" t="s">
-        <v>435</v>
+        <v>456</v>
       </c>
       <c r="C125" t="s">
-        <v>10</v>
+        <v>2</v>
       </c>
       <c r="D125" t="s">
-        <v>433</v>
+        <v>457</v>
       </c>
       <c r="E125" t="s">
-        <v>217</v>
+        <v>14</v>
       </c>
       <c r="F125" t="s">
         <v>0</v>
       </c>
       <c r="G125" t="s">
-        <v>434</v>
+        <v>458</v>
       </c>
       <c r="H125" t="s">
-        <v>4</v>
+        <v>5</v>
       </c>
     </row>
     <row r="126" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A126" t="s">
-        <v>436</v>
+        <v>459</v>
       </c>
       <c r="C126" t="s">
-        <v>185</v>
+        <v>58</v>
       </c>
       <c r="D126" t="s">
-        <v>437</v>
+        <v>460</v>
       </c>
       <c r="E126" t="s">
-        <v>290</v>
+        <v>83</v>
       </c>
       <c r="F126" t="s">
-        <v>0</v>
+        <v>84</v>
       </c>
       <c r="G126" t="s">
-        <v>387</v>
+        <v>461</v>
       </c>
       <c r="H126" t="s">
-        <v>4</v>
+        <v>5</v>
       </c>
     </row>
     <row r="127" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A127" t="s">
-        <v>438</v>
+        <v>462</v>
       </c>
       <c r="C127" t="s">
         <v>9</v>
       </c>
       <c r="D127" t="s">
-        <v>439</v>
+        <v>463</v>
       </c>
       <c r="E127" t="s">
-        <v>440</v>
+        <v>284</v>
       </c>
       <c r="F127" t="s">
-        <v>441</v>
+        <v>0</v>
       </c>
       <c r="G127" t="s">
-        <v>442</v>
+        <v>464</v>
       </c>
       <c r="H127" t="s">
-        <v>4</v>
+        <v>5</v>
       </c>
     </row>
     <row r="128" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A128" t="s">
-        <v>443</v>
+        <v>465</v>
       </c>
       <c r="C128" t="s">
-        <v>9</v>
+        <v>2</v>
       </c>
       <c r="D128" t="s">
-        <v>439</v>
+        <v>466</v>
       </c>
       <c r="E128" t="s">
-        <v>440</v>
+        <v>467</v>
       </c>
       <c r="F128" t="s">
-        <v>441</v>
+        <v>0</v>
       </c>
       <c r="G128" t="s">
-        <v>442</v>
+        <v>468</v>
       </c>
       <c r="H128" t="s">
-        <v>4</v>
+        <v>5</v>
       </c>
     </row>
     <row r="129" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A129" t="s">
-        <v>444</v>
+        <v>469</v>
       </c>
       <c r="C129" t="s">
-        <v>9</v>
+        <v>393</v>
       </c>
       <c r="D129" t="s">
-        <v>439</v>
+        <v>470</v>
       </c>
       <c r="E129" t="s">
-        <v>440</v>
+        <v>51</v>
       </c>
       <c r="F129" t="s">
-        <v>441</v>
+        <v>0</v>
       </c>
       <c r="G129" t="s">
-        <v>442</v>
+        <v>471</v>
       </c>
       <c r="H129" t="s">
-        <v>4</v>
+        <v>5</v>
       </c>
     </row>
     <row r="130" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A130" t="s">
-        <v>445</v>
+        <v>472</v>
       </c>
       <c r="C130" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="D130" t="s">
-        <v>446</v>
+        <v>473</v>
       </c>
       <c r="E130" t="s">
-        <v>447</v>
+        <v>381</v>
       </c>
       <c r="F130" t="s">
         <v>0</v>
       </c>
       <c r="G130" t="s">
-        <v>448</v>
+        <v>474</v>
       </c>
       <c r="H130" t="s">
-        <v>4</v>
+        <v>5</v>
       </c>
     </row>
     <row r="131" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A131" t="s">
-        <v>449</v>
+        <v>475</v>
       </c>
       <c r="C131" t="s">
-        <v>23</v>
+        <v>152</v>
       </c>
       <c r="D131" t="s">
-        <v>450</v>
+        <v>476</v>
       </c>
       <c r="E131" t="s">
-        <v>451</v>
+        <v>385</v>
       </c>
       <c r="F131" t="s">
-        <v>452</v>
+        <v>0</v>
       </c>
       <c r="G131" t="s">
-        <v>453</v>
+        <v>477</v>
       </c>
       <c r="H131" t="s">
-        <v>4</v>
+        <v>5</v>
       </c>
     </row>
     <row r="132" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A132" t="s">
-        <v>454</v>
+        <v>478</v>
       </c>
       <c r="C132" t="s">
-        <v>22</v>
+        <v>152</v>
       </c>
       <c r="D132" t="s">
-        <v>455</v>
+        <v>476</v>
       </c>
       <c r="E132" t="s">
-        <v>29</v>
+        <v>385</v>
       </c>
       <c r="F132" t="s">
         <v>0</v>
       </c>
       <c r="G132" t="s">
-        <v>456</v>
+        <v>477</v>
       </c>
       <c r="H132" t="s">
         <v>5</v>
@@ -4915,22 +4957,22 @@
     </row>
     <row r="133" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A133" t="s">
-        <v>457</v>
+        <v>479</v>
       </c>
       <c r="C133" t="s">
-        <v>23</v>
+        <v>58</v>
       </c>
       <c r="D133" t="s">
-        <v>458</v>
+        <v>480</v>
       </c>
       <c r="E133" t="s">
-        <v>209</v>
+        <v>307</v>
       </c>
       <c r="F133" t="s">
         <v>0</v>
       </c>
       <c r="G133" t="s">
-        <v>459</v>
+        <v>481</v>
       </c>
       <c r="H133" t="s">
         <v>5</v>
@@ -4938,22 +4980,22 @@
     </row>
     <row r="134" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A134" t="s">
-        <v>460</v>
+        <v>482</v>
       </c>
       <c r="C134" t="s">
-        <v>9</v>
+        <v>58</v>
       </c>
       <c r="D134" t="s">
-        <v>461</v>
+        <v>483</v>
       </c>
       <c r="E134" t="s">
-        <v>90</v>
+        <v>419</v>
       </c>
       <c r="F134" t="s">
         <v>0</v>
       </c>
       <c r="G134" t="s">
-        <v>91</v>
+        <v>484</v>
       </c>
       <c r="H134" t="s">
         <v>5</v>
@@ -4961,22 +5003,22 @@
     </row>
     <row r="135" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A135" t="s">
-        <v>462</v>
+        <v>485</v>
       </c>
       <c r="C135" t="s">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="D135" t="s">
-        <v>463</v>
+        <v>486</v>
       </c>
       <c r="E135" t="s">
-        <v>464</v>
+        <v>31</v>
       </c>
       <c r="F135" t="s">
-        <v>0</v>
+        <v>32</v>
       </c>
       <c r="G135" t="s">
-        <v>465</v>
+        <v>487</v>
       </c>
       <c r="H135" t="s">
         <v>5</v>
@@ -4984,22 +5026,22 @@
     </row>
     <row r="136" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A136" t="s">
-        <v>466</v>
+        <v>488</v>
       </c>
       <c r="C136" t="s">
-        <v>38</v>
+        <v>10</v>
       </c>
       <c r="D136" t="s">
-        <v>467</v>
+        <v>489</v>
       </c>
       <c r="E136" t="s">
-        <v>43</v>
+        <v>75</v>
       </c>
       <c r="F136" t="s">
         <v>0</v>
       </c>
       <c r="G136" t="s">
-        <v>468</v>
+        <v>490</v>
       </c>
       <c r="H136" t="s">
         <v>5</v>
@@ -5007,22 +5049,22 @@
     </row>
     <row r="137" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A137" t="s">
-        <v>469</v>
+        <v>491</v>
       </c>
       <c r="C137" t="s">
-        <v>19</v>
+        <v>13</v>
       </c>
       <c r="D137" t="s">
-        <v>470</v>
+        <v>492</v>
       </c>
       <c r="E137" t="s">
-        <v>471</v>
+        <v>60</v>
       </c>
       <c r="F137" t="s">
-        <v>472</v>
+        <v>61</v>
       </c>
       <c r="G137" t="s">
-        <v>473</v>
+        <v>493</v>
       </c>
       <c r="H137" t="s">
         <v>5</v>
@@ -5030,22 +5072,22 @@
     </row>
     <row r="138" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A138" t="s">
-        <v>474</v>
+        <v>494</v>
       </c>
       <c r="C138" t="s">
-        <v>19</v>
+        <v>13</v>
       </c>
       <c r="D138" t="s">
-        <v>470</v>
+        <v>492</v>
       </c>
       <c r="E138" t="s">
-        <v>471</v>
+        <v>60</v>
       </c>
       <c r="F138" t="s">
-        <v>472</v>
+        <v>61</v>
       </c>
       <c r="G138" t="s">
-        <v>473</v>
+        <v>493</v>
       </c>
       <c r="H138" t="s">
         <v>5</v>
@@ -5053,22 +5095,22 @@
     </row>
     <row r="139" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A139" t="s">
-        <v>475</v>
+        <v>495</v>
       </c>
       <c r="C139" t="s">
-        <v>23</v>
+        <v>13</v>
       </c>
       <c r="D139" t="s">
-        <v>476</v>
+        <v>496</v>
       </c>
       <c r="E139" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="F139" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="G139" t="s">
-        <v>477</v>
+        <v>497</v>
       </c>
       <c r="H139" t="s">
         <v>5</v>
@@ -5076,22 +5118,22 @@
     </row>
     <row r="140" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A140" t="s">
-        <v>478</v>
+        <v>498</v>
       </c>
       <c r="C140" t="s">
         <v>13</v>
       </c>
       <c r="D140" t="s">
-        <v>479</v>
+        <v>496</v>
       </c>
       <c r="E140" t="s">
-        <v>84</v>
+        <v>15</v>
       </c>
       <c r="F140" t="s">
-        <v>85</v>
+        <v>16</v>
       </c>
       <c r="G140" t="s">
-        <v>112</v>
+        <v>497</v>
       </c>
       <c r="H140" t="s">
         <v>5</v>
@@ -5099,22 +5141,22 @@
     </row>
     <row r="141" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A141" t="s">
-        <v>480</v>
+        <v>499</v>
       </c>
       <c r="C141" t="s">
-        <v>23</v>
+        <v>13</v>
       </c>
       <c r="D141" t="s">
-        <v>481</v>
+        <v>496</v>
       </c>
       <c r="E141" t="s">
-        <v>482</v>
+        <v>15</v>
       </c>
       <c r="F141" t="s">
-        <v>0</v>
+        <v>16</v>
       </c>
       <c r="G141" t="s">
-        <v>483</v>
+        <v>497</v>
       </c>
       <c r="H141" t="s">
         <v>5</v>
@@ -5122,22 +5164,22 @@
     </row>
     <row r="142" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A142" t="s">
-        <v>484</v>
+        <v>500</v>
       </c>
       <c r="C142" t="s">
-        <v>23</v>
+        <v>13</v>
       </c>
       <c r="D142" t="s">
-        <v>481</v>
+        <v>496</v>
       </c>
       <c r="E142" t="s">
-        <v>482</v>
+        <v>15</v>
       </c>
       <c r="F142" t="s">
-        <v>0</v>
+        <v>16</v>
       </c>
       <c r="G142" t="s">
-        <v>483</v>
+        <v>497</v>
       </c>
       <c r="H142" t="s">
         <v>5</v>
@@ -5145,22 +5187,22 @@
     </row>
     <row r="143" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A143" t="s">
-        <v>485</v>
+        <v>501</v>
       </c>
       <c r="C143" t="s">
-        <v>24</v>
+        <v>13</v>
       </c>
       <c r="D143" t="s">
-        <v>486</v>
+        <v>496</v>
       </c>
       <c r="E143" t="s">
-        <v>32</v>
+        <v>15</v>
       </c>
       <c r="F143" t="s">
-        <v>33</v>
+        <v>16</v>
       </c>
       <c r="G143" t="s">
-        <v>387</v>
+        <v>497</v>
       </c>
       <c r="H143" t="s">
         <v>5</v>
@@ -5168,22 +5210,22 @@
     </row>
     <row r="144" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A144" t="s">
-        <v>487</v>
+        <v>502</v>
       </c>
       <c r="C144" t="s">
-        <v>26</v>
+        <v>190</v>
       </c>
       <c r="D144" t="s">
-        <v>488</v>
+        <v>503</v>
       </c>
       <c r="E144" t="s">
-        <v>35</v>
+        <v>52</v>
       </c>
       <c r="F144" t="s">
-        <v>36</v>
+        <v>0</v>
       </c>
       <c r="G144" t="s">
-        <v>489</v>
+        <v>504</v>
       </c>
       <c r="H144" t="s">
         <v>5</v>
@@ -5191,22 +5233,22 @@
     </row>
     <row r="145" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A145" t="s">
-        <v>490</v>
+        <v>505</v>
       </c>
       <c r="C145" t="s">
-        <v>19</v>
+        <v>92</v>
       </c>
       <c r="D145" t="s">
-        <v>491</v>
+        <v>506</v>
       </c>
       <c r="E145" t="s">
-        <v>492</v>
+        <v>507</v>
       </c>
       <c r="F145" t="s">
-        <v>493</v>
+        <v>508</v>
       </c>
       <c r="G145" t="s">
-        <v>494</v>
+        <v>150</v>
       </c>
       <c r="H145" t="s">
         <v>5</v>
@@ -5214,22 +5256,22 @@
     </row>
     <row r="146" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A146" t="s">
-        <v>495</v>
+        <v>509</v>
       </c>
       <c r="C146" t="s">
-        <v>19</v>
+        <v>152</v>
       </c>
       <c r="D146" t="s">
-        <v>491</v>
+        <v>510</v>
       </c>
       <c r="E146" t="s">
-        <v>492</v>
+        <v>154</v>
       </c>
       <c r="F146" t="s">
-        <v>493</v>
+        <v>0</v>
       </c>
       <c r="G146" t="s">
-        <v>494</v>
+        <v>511</v>
       </c>
       <c r="H146" t="s">
         <v>5</v>
@@ -5237,94 +5279,71 @@
     </row>
     <row r="147" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A147" t="s">
-        <v>496</v>
+        <v>512</v>
       </c>
       <c r="C147" t="s">
-        <v>26</v>
+        <v>13</v>
       </c>
       <c r="D147" t="s">
-        <v>497</v>
+        <v>513</v>
       </c>
       <c r="E147" t="s">
-        <v>152</v>
+        <v>514</v>
       </c>
       <c r="F147" t="s">
-        <v>153</v>
+        <v>515</v>
       </c>
       <c r="G147" t="s">
-        <v>498</v>
+        <v>516</v>
       </c>
       <c r="H147" t="s">
-        <v>499</v>
+        <v>517</v>
       </c>
     </row>
     <row r="148" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A148" t="s">
-        <v>500</v>
+        <v>518</v>
       </c>
       <c r="C148" t="s">
-        <v>26</v>
+        <v>13</v>
       </c>
       <c r="D148" t="s">
-        <v>497</v>
+        <v>513</v>
       </c>
       <c r="E148" t="s">
-        <v>152</v>
+        <v>514</v>
       </c>
       <c r="F148" t="s">
-        <v>153</v>
+        <v>515</v>
       </c>
       <c r="G148" t="s">
-        <v>498</v>
+        <v>516</v>
       </c>
       <c r="H148" t="s">
-        <v>499</v>
+        <v>517</v>
       </c>
     </row>
     <row r="149" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A149" t="s">
-        <v>501</v>
+        <v>519</v>
       </c>
       <c r="C149" t="s">
-        <v>104</v>
+        <v>13</v>
       </c>
       <c r="D149" t="s">
-        <v>502</v>
+        <v>513</v>
       </c>
       <c r="E149" t="s">
-        <v>503</v>
+        <v>514</v>
       </c>
       <c r="F149" t="s">
-        <v>0</v>
+        <v>515</v>
       </c>
       <c r="G149" t="s">
-        <v>504</v>
+        <v>516</v>
       </c>
       <c r="H149" t="s">
-        <v>499</v>
-      </c>
-    </row>
-    <row r="150" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A150" t="s">
-        <v>505</v>
-      </c>
-      <c r="C150" t="s">
-        <v>104</v>
-      </c>
-      <c r="D150" t="s">
-        <v>502</v>
-      </c>
-      <c r="E150" t="s">
-        <v>503</v>
-      </c>
-      <c r="F150" t="s">
-        <v>0</v>
-      </c>
-      <c r="G150" t="s">
-        <v>504</v>
-      </c>
-      <c r="H150" t="s">
-        <v>499</v>
+        <v>517</v>
       </c>
     </row>
   </sheetData>

--- a/1.xlsx
+++ b/1.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="\\wh.local\fs\UserProfile_TSSWH19\_TSSWH19_redirected_folders\HunyaCs1\Desktop\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{226108C0-93EB-4C9A-9B42-6535D0E3DA34}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A6AEC489-0282-4478-B520-2C53E328996D}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="0" windowWidth="22260" windowHeight="12648" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1043" uniqueCount="520">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1040" uniqueCount="518">
   <si>
     <t>BUDAPEST</t>
   </si>
@@ -255,9 +255,6 @@
     <t>1046</t>
   </si>
   <si>
-    <t>1205</t>
-  </si>
-  <si>
     <t>1054</t>
   </si>
   <si>
@@ -1494,15 +1491,6 @@
     <t>Somfa utca</t>
   </si>
   <si>
-    <t>NFD6-03-29-CG8Y-1</t>
-  </si>
-  <si>
-    <t>NFD6-03-29-CG8Y</t>
-  </si>
-  <si>
-    <t>Bányász utca</t>
-  </si>
-  <si>
     <t>202603262600731001</t>
   </si>
   <si>
@@ -1588,6 +1576,12 @@
   </si>
   <si>
     <t>159995579538654695</t>
+  </si>
+  <si>
+    <t>NFD6-03-24-L76B</t>
+  </si>
+  <si>
+    <t>AUCHAN_ÁRUHÁZI</t>
   </si>
 </sst>
 </file>
@@ -1944,13 +1938,13 @@
     </row>
     <row r="2" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="C2" t="s">
         <v>21</v>
       </c>
       <c r="D2" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="E2" t="s">
         <v>70</v>
@@ -1959,7 +1953,7 @@
         <v>0</v>
       </c>
       <c r="G2" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="H2" t="s">
         <v>4</v>
@@ -1967,13 +1961,13 @@
     </row>
     <row r="3" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="C3" t="s">
         <v>21</v>
       </c>
       <c r="D3" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="E3" t="s">
         <v>70</v>
@@ -1982,7 +1976,7 @@
         <v>0</v>
       </c>
       <c r="G3" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="H3" t="s">
         <v>4</v>
@@ -1990,13 +1984,13 @@
     </row>
     <row r="4" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="C4" t="s">
         <v>21</v>
       </c>
       <c r="D4" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="E4" t="s">
         <v>70</v>
@@ -2005,7 +1999,7 @@
         <v>0</v>
       </c>
       <c r="G4" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="H4" t="s">
         <v>4</v>
@@ -2013,13 +2007,13 @@
     </row>
     <row r="5" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
+        <v>90</v>
+      </c>
+      <c r="C5" t="s">
         <v>91</v>
       </c>
-      <c r="C5" t="s">
+      <c r="D5" t="s">
         <v>92</v>
-      </c>
-      <c r="D5" t="s">
-        <v>93</v>
       </c>
       <c r="E5" t="s">
         <v>23</v>
@@ -2028,7 +2022,7 @@
         <v>24</v>
       </c>
       <c r="G5" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="H5" t="s">
         <v>1</v>
@@ -2036,22 +2030,22 @@
     </row>
     <row r="6" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="C6" t="s">
         <v>3</v>
       </c>
       <c r="D6" t="s">
+        <v>95</v>
+      </c>
+      <c r="E6" t="s">
         <v>96</v>
       </c>
-      <c r="E6" t="s">
+      <c r="F6" t="s">
+        <v>0</v>
+      </c>
+      <c r="G6" t="s">
         <v>97</v>
-      </c>
-      <c r="F6" t="s">
-        <v>0</v>
-      </c>
-      <c r="G6" t="s">
-        <v>98</v>
       </c>
       <c r="H6" t="s">
         <v>1</v>
@@ -2059,22 +2053,22 @@
     </row>
     <row r="7" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
+        <v>98</v>
+      </c>
+      <c r="C7" t="s">
         <v>99</v>
       </c>
-      <c r="C7" t="s">
+      <c r="D7" t="s">
         <v>100</v>
       </c>
-      <c r="D7" t="s">
+      <c r="E7" t="s">
         <v>101</v>
       </c>
-      <c r="E7" t="s">
+      <c r="F7" t="s">
         <v>102</v>
       </c>
-      <c r="F7" t="s">
+      <c r="G7" t="s">
         <v>103</v>
-      </c>
-      <c r="G7" t="s">
-        <v>104</v>
       </c>
       <c r="H7" t="s">
         <v>1</v>
@@ -2082,22 +2076,22 @@
     </row>
     <row r="8" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="C8" t="s">
         <v>10</v>
       </c>
       <c r="D8" t="s">
+        <v>105</v>
+      </c>
+      <c r="E8" t="s">
         <v>106</v>
       </c>
-      <c r="E8" t="s">
+      <c r="F8" t="s">
+        <v>0</v>
+      </c>
+      <c r="G8" t="s">
         <v>107</v>
-      </c>
-      <c r="F8" t="s">
-        <v>0</v>
-      </c>
-      <c r="G8" t="s">
-        <v>108</v>
       </c>
       <c r="H8" t="s">
         <v>1</v>
@@ -2105,22 +2099,22 @@
     </row>
     <row r="9" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="C9" t="s">
         <v>10</v>
       </c>
       <c r="D9" t="s">
+        <v>109</v>
+      </c>
+      <c r="E9" t="s">
         <v>110</v>
       </c>
-      <c r="E9" t="s">
+      <c r="F9" t="s">
+        <v>0</v>
+      </c>
+      <c r="G9" t="s">
         <v>111</v>
-      </c>
-      <c r="F9" t="s">
-        <v>0</v>
-      </c>
-      <c r="G9" t="s">
-        <v>112</v>
       </c>
       <c r="H9" t="s">
         <v>1</v>
@@ -2151,13 +2145,13 @@
     </row>
     <row r="11" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A11" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="C11" t="s">
         <v>8</v>
       </c>
       <c r="D11" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="E11" t="s">
         <v>28</v>
@@ -2166,7 +2160,7 @@
         <v>29</v>
       </c>
       <c r="G11" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="H11" t="s">
         <v>1</v>
@@ -2174,22 +2168,22 @@
     </row>
     <row r="12" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A12" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="C12" t="s">
         <v>10</v>
       </c>
       <c r="D12" t="s">
+        <v>116</v>
+      </c>
+      <c r="E12" t="s">
+        <v>106</v>
+      </c>
+      <c r="F12" t="s">
+        <v>0</v>
+      </c>
+      <c r="G12" t="s">
         <v>117</v>
-      </c>
-      <c r="E12" t="s">
-        <v>107</v>
-      </c>
-      <c r="F12" t="s">
-        <v>0</v>
-      </c>
-      <c r="G12" t="s">
-        <v>118</v>
       </c>
       <c r="H12" t="s">
         <v>1</v>
@@ -2197,22 +2191,22 @@
     </row>
     <row r="13" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A13" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="C13" t="s">
         <v>10</v>
       </c>
       <c r="D13" t="s">
+        <v>116</v>
+      </c>
+      <c r="E13" t="s">
+        <v>106</v>
+      </c>
+      <c r="F13" t="s">
+        <v>0</v>
+      </c>
+      <c r="G13" t="s">
         <v>117</v>
-      </c>
-      <c r="E13" t="s">
-        <v>107</v>
-      </c>
-      <c r="F13" t="s">
-        <v>0</v>
-      </c>
-      <c r="G13" t="s">
-        <v>118</v>
       </c>
       <c r="H13" t="s">
         <v>1</v>
@@ -2220,13 +2214,13 @@
     </row>
     <row r="14" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A14" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="C14" t="s">
         <v>53</v>
       </c>
       <c r="D14" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="E14" t="s">
         <v>44</v>
@@ -2235,7 +2229,7 @@
         <v>45</v>
       </c>
       <c r="G14" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="H14" t="s">
         <v>1</v>
@@ -2243,13 +2237,13 @@
     </row>
     <row r="15" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A15" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="C15" t="s">
         <v>8</v>
       </c>
       <c r="D15" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="E15" t="s">
         <v>31</v>
@@ -2258,7 +2252,7 @@
         <v>32</v>
       </c>
       <c r="G15" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="H15" t="s">
         <v>1</v>
@@ -2266,13 +2260,13 @@
     </row>
     <row r="16" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A16" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="C16" t="s">
         <v>8</v>
       </c>
       <c r="D16" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="E16" t="s">
         <v>31</v>
@@ -2281,7 +2275,7 @@
         <v>32</v>
       </c>
       <c r="G16" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="H16" t="s">
         <v>1</v>
@@ -2289,22 +2283,22 @@
     </row>
     <row r="17" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A17" t="s">
+        <v>126</v>
+      </c>
+      <c r="C17" t="s">
+        <v>91</v>
+      </c>
+      <c r="D17" t="s">
         <v>127</v>
       </c>
-      <c r="C17" t="s">
-        <v>92</v>
-      </c>
-      <c r="D17" t="s">
+      <c r="E17" t="s">
         <v>128</v>
       </c>
-      <c r="E17" t="s">
+      <c r="F17" t="s">
         <v>129</v>
       </c>
-      <c r="F17" t="s">
+      <c r="G17" t="s">
         <v>130</v>
-      </c>
-      <c r="G17" t="s">
-        <v>131</v>
       </c>
       <c r="H17" t="s">
         <v>1</v>
@@ -2312,22 +2306,22 @@
     </row>
     <row r="18" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A18" t="s">
+        <v>131</v>
+      </c>
+      <c r="C18" t="s">
+        <v>99</v>
+      </c>
+      <c r="D18" t="s">
         <v>132</v>
       </c>
-      <c r="C18" t="s">
-        <v>100</v>
-      </c>
-      <c r="D18" t="s">
+      <c r="E18" t="s">
         <v>133</v>
       </c>
-      <c r="E18" t="s">
+      <c r="F18" t="s">
         <v>134</v>
       </c>
-      <c r="F18" t="s">
+      <c r="G18" t="s">
         <v>135</v>
-      </c>
-      <c r="G18" t="s">
-        <v>136</v>
       </c>
       <c r="H18" t="s">
         <v>1</v>
@@ -2335,22 +2329,22 @@
     </row>
     <row r="19" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A19" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="C19" t="s">
         <v>22</v>
       </c>
       <c r="D19" t="s">
+        <v>137</v>
+      </c>
+      <c r="E19" t="s">
         <v>138</v>
       </c>
-      <c r="E19" t="s">
+      <c r="F19" t="s">
         <v>139</v>
       </c>
-      <c r="F19" t="s">
+      <c r="G19" t="s">
         <v>140</v>
-      </c>
-      <c r="G19" t="s">
-        <v>141</v>
       </c>
       <c r="H19" t="s">
         <v>1</v>
@@ -2358,22 +2352,22 @@
     </row>
     <row r="20" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A20" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="C20" t="s">
         <v>2</v>
       </c>
       <c r="D20" t="s">
+        <v>142</v>
+      </c>
+      <c r="E20" t="s">
         <v>143</v>
       </c>
-      <c r="E20" t="s">
+      <c r="F20" t="s">
         <v>144</v>
       </c>
-      <c r="F20" t="s">
+      <c r="G20" t="s">
         <v>145</v>
-      </c>
-      <c r="G20" t="s">
-        <v>146</v>
       </c>
       <c r="H20" t="s">
         <v>1</v>
@@ -2381,22 +2375,22 @@
     </row>
     <row r="21" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A21" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="C21" t="s">
         <v>53</v>
       </c>
       <c r="D21" t="s">
+        <v>147</v>
+      </c>
+      <c r="E21" t="s">
         <v>148</v>
       </c>
-      <c r="E21" t="s">
+      <c r="F21" t="s">
+        <v>0</v>
+      </c>
+      <c r="G21" t="s">
         <v>149</v>
-      </c>
-      <c r="F21" t="s">
-        <v>0</v>
-      </c>
-      <c r="G21" t="s">
-        <v>150</v>
       </c>
       <c r="H21" t="s">
         <v>1</v>
@@ -2404,22 +2398,22 @@
     </row>
     <row r="22" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A22" t="s">
+        <v>150</v>
+      </c>
+      <c r="C22" t="s">
         <v>151</v>
       </c>
-      <c r="C22" t="s">
+      <c r="D22" t="s">
         <v>152</v>
       </c>
-      <c r="D22" t="s">
+      <c r="E22" t="s">
         <v>153</v>
       </c>
-      <c r="E22" t="s">
+      <c r="F22" t="s">
+        <v>0</v>
+      </c>
+      <c r="G22" t="s">
         <v>154</v>
-      </c>
-      <c r="F22" t="s">
-        <v>0</v>
-      </c>
-      <c r="G22" t="s">
-        <v>155</v>
       </c>
       <c r="H22" t="s">
         <v>1</v>
@@ -2427,22 +2421,22 @@
     </row>
     <row r="23" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A23" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="C23" t="s">
+        <v>151</v>
+      </c>
+      <c r="D23" t="s">
         <v>152</v>
       </c>
-      <c r="D23" t="s">
+      <c r="E23" t="s">
         <v>153</v>
       </c>
-      <c r="E23" t="s">
+      <c r="F23" t="s">
+        <v>0</v>
+      </c>
+      <c r="G23" t="s">
         <v>154</v>
-      </c>
-      <c r="F23" t="s">
-        <v>0</v>
-      </c>
-      <c r="G23" t="s">
-        <v>155</v>
       </c>
       <c r="H23" t="s">
         <v>1</v>
@@ -2450,22 +2444,22 @@
     </row>
     <row r="24" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A24" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="C24" t="s">
         <v>22</v>
       </c>
       <c r="D24" t="s">
+        <v>157</v>
+      </c>
+      <c r="E24" t="s">
         <v>158</v>
       </c>
-      <c r="E24" t="s">
+      <c r="F24" t="s">
         <v>159</v>
       </c>
-      <c r="F24" t="s">
+      <c r="G24" t="s">
         <v>160</v>
-      </c>
-      <c r="G24" t="s">
-        <v>161</v>
       </c>
       <c r="H24" t="s">
         <v>1</v>
@@ -2473,13 +2467,13 @@
     </row>
     <row r="25" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A25" t="s">
+        <v>161</v>
+      </c>
+      <c r="C25" t="s">
+        <v>151</v>
+      </c>
+      <c r="D25" t="s">
         <v>162</v>
-      </c>
-      <c r="C25" t="s">
-        <v>152</v>
-      </c>
-      <c r="D25" t="s">
-        <v>163</v>
       </c>
       <c r="E25" t="s">
         <v>34</v>
@@ -2496,22 +2490,22 @@
     </row>
     <row r="26" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A26" t="s">
+        <v>163</v>
+      </c>
+      <c r="C26" t="s">
         <v>164</v>
       </c>
-      <c r="C26" t="s">
+      <c r="D26" t="s">
         <v>165</v>
       </c>
-      <c r="D26" t="s">
+      <c r="E26" t="s">
         <v>166</v>
       </c>
-      <c r="E26" t="s">
+      <c r="F26" t="s">
+        <v>0</v>
+      </c>
+      <c r="G26" t="s">
         <v>167</v>
-      </c>
-      <c r="F26" t="s">
-        <v>0</v>
-      </c>
-      <c r="G26" t="s">
-        <v>168</v>
       </c>
       <c r="H26" t="s">
         <v>1</v>
@@ -2519,22 +2513,22 @@
     </row>
     <row r="27" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A27" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="C27" t="s">
         <v>9</v>
       </c>
       <c r="D27" t="s">
+        <v>169</v>
+      </c>
+      <c r="E27" t="s">
         <v>170</v>
       </c>
-      <c r="E27" t="s">
+      <c r="F27" t="s">
+        <v>0</v>
+      </c>
+      <c r="G27" t="s">
         <v>171</v>
-      </c>
-      <c r="F27" t="s">
-        <v>0</v>
-      </c>
-      <c r="G27" t="s">
-        <v>172</v>
       </c>
       <c r="H27" t="s">
         <v>1</v>
@@ -2542,22 +2536,22 @@
     </row>
     <row r="28" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A28" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="C28" t="s">
         <v>2</v>
       </c>
       <c r="D28" t="s">
+        <v>173</v>
+      </c>
+      <c r="E28" t="s">
+        <v>80</v>
+      </c>
+      <c r="F28" t="s">
+        <v>0</v>
+      </c>
+      <c r="G28" t="s">
         <v>174</v>
-      </c>
-      <c r="E28" t="s">
-        <v>81</v>
-      </c>
-      <c r="F28" t="s">
-        <v>0</v>
-      </c>
-      <c r="G28" t="s">
-        <v>175</v>
       </c>
       <c r="H28" t="s">
         <v>1</v>
@@ -2565,22 +2559,22 @@
     </row>
     <row r="29" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A29" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="C29" t="s">
         <v>22</v>
       </c>
       <c r="D29" t="s">
+        <v>176</v>
+      </c>
+      <c r="E29" t="s">
         <v>177</v>
       </c>
-      <c r="E29" t="s">
+      <c r="F29" t="s">
+        <v>0</v>
+      </c>
+      <c r="G29" t="s">
         <v>178</v>
-      </c>
-      <c r="F29" t="s">
-        <v>0</v>
-      </c>
-      <c r="G29" t="s">
-        <v>179</v>
       </c>
       <c r="H29" t="s">
         <v>1</v>
@@ -2588,22 +2582,22 @@
     </row>
     <row r="30" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A30" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="C30" t="s">
         <v>22</v>
       </c>
       <c r="D30" t="s">
+        <v>176</v>
+      </c>
+      <c r="E30" t="s">
         <v>177</v>
       </c>
-      <c r="E30" t="s">
+      <c r="F30" t="s">
+        <v>0</v>
+      </c>
+      <c r="G30" t="s">
         <v>178</v>
-      </c>
-      <c r="F30" t="s">
-        <v>0</v>
-      </c>
-      <c r="G30" t="s">
-        <v>179</v>
       </c>
       <c r="H30" t="s">
         <v>1</v>
@@ -2611,22 +2605,22 @@
     </row>
     <row r="31" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A31" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="C31" t="s">
         <v>22</v>
       </c>
       <c r="D31" t="s">
+        <v>176</v>
+      </c>
+      <c r="E31" t="s">
         <v>177</v>
       </c>
-      <c r="E31" t="s">
+      <c r="F31" t="s">
+        <v>0</v>
+      </c>
+      <c r="G31" t="s">
         <v>178</v>
-      </c>
-      <c r="F31" t="s">
-        <v>0</v>
-      </c>
-      <c r="G31" t="s">
-        <v>179</v>
       </c>
       <c r="H31" t="s">
         <v>1</v>
@@ -2634,22 +2628,22 @@
     </row>
     <row r="32" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A32" t="s">
+        <v>181</v>
+      </c>
+      <c r="C32" t="s">
+        <v>164</v>
+      </c>
+      <c r="D32" t="s">
         <v>182</v>
       </c>
-      <c r="C32" t="s">
-        <v>165</v>
-      </c>
-      <c r="D32" t="s">
+      <c r="E32" t="s">
         <v>183</v>
       </c>
-      <c r="E32" t="s">
+      <c r="F32" t="s">
+        <v>0</v>
+      </c>
+      <c r="G32" t="s">
         <v>184</v>
-      </c>
-      <c r="F32" t="s">
-        <v>0</v>
-      </c>
-      <c r="G32" t="s">
-        <v>185</v>
       </c>
       <c r="H32" t="s">
         <v>1</v>
@@ -2657,22 +2651,22 @@
     </row>
     <row r="33" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A33" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="C33" t="s">
         <v>19</v>
       </c>
       <c r="D33" t="s">
+        <v>186</v>
+      </c>
+      <c r="E33" t="s">
+        <v>75</v>
+      </c>
+      <c r="F33" t="s">
+        <v>0</v>
+      </c>
+      <c r="G33" t="s">
         <v>187</v>
-      </c>
-      <c r="E33" t="s">
-        <v>76</v>
-      </c>
-      <c r="F33" t="s">
-        <v>0</v>
-      </c>
-      <c r="G33" t="s">
-        <v>188</v>
       </c>
       <c r="H33" t="s">
         <v>49</v>
@@ -2680,22 +2674,22 @@
     </row>
     <row r="34" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A34" t="s">
+        <v>188</v>
+      </c>
+      <c r="C34" t="s">
         <v>189</v>
       </c>
-      <c r="C34" t="s">
+      <c r="D34" t="s">
         <v>190</v>
       </c>
-      <c r="D34" t="s">
+      <c r="E34" t="s">
         <v>191</v>
       </c>
-      <c r="E34" t="s">
+      <c r="F34" t="s">
+        <v>0</v>
+      </c>
+      <c r="G34" t="s">
         <v>192</v>
-      </c>
-      <c r="F34" t="s">
-        <v>0</v>
-      </c>
-      <c r="G34" t="s">
-        <v>193</v>
       </c>
       <c r="H34" t="s">
         <v>49</v>
@@ -2703,13 +2697,13 @@
     </row>
     <row r="35" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A35" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="C35" t="s">
         <v>10</v>
       </c>
       <c r="D35" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="E35" t="s">
         <v>30</v>
@@ -2718,7 +2712,7 @@
         <v>0</v>
       </c>
       <c r="G35" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="H35" t="s">
         <v>62</v>
@@ -2726,22 +2720,22 @@
     </row>
     <row r="36" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A36" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="C36" t="s">
         <v>10</v>
       </c>
       <c r="D36" t="s">
+        <v>197</v>
+      </c>
+      <c r="E36" t="s">
         <v>198</v>
       </c>
-      <c r="E36" t="s">
+      <c r="F36" t="s">
+        <v>0</v>
+      </c>
+      <c r="G36" t="s">
         <v>199</v>
-      </c>
-      <c r="F36" t="s">
-        <v>0</v>
-      </c>
-      <c r="G36" t="s">
-        <v>200</v>
       </c>
       <c r="H36" t="s">
         <v>62</v>
@@ -2749,22 +2743,22 @@
     </row>
     <row r="37" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A37" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="C37" t="s">
         <v>9</v>
       </c>
       <c r="D37" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c r="E37" t="s">
+        <v>76</v>
+      </c>
+      <c r="F37" t="s">
         <v>77</v>
       </c>
-      <c r="F37" t="s">
-        <v>78</v>
-      </c>
       <c r="G37" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="H37" t="s">
         <v>62</v>
@@ -2772,13 +2766,13 @@
     </row>
     <row r="38" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A38" t="s">
+        <v>202</v>
+      </c>
+      <c r="C38" t="s">
+        <v>91</v>
+      </c>
+      <c r="D38" t="s">
         <v>203</v>
-      </c>
-      <c r="C38" t="s">
-        <v>92</v>
-      </c>
-      <c r="D38" t="s">
-        <v>204</v>
       </c>
       <c r="E38" t="s">
         <v>26</v>
@@ -2787,7 +2781,7 @@
         <v>27</v>
       </c>
       <c r="G38" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="H38" t="s">
         <v>4</v>
@@ -2795,22 +2789,22 @@
     </row>
     <row r="39" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A39" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="C39" t="s">
         <v>19</v>
       </c>
       <c r="D39" t="s">
+        <v>206</v>
+      </c>
+      <c r="E39" t="s">
         <v>207</v>
       </c>
-      <c r="E39" t="s">
+      <c r="F39" t="s">
+        <v>0</v>
+      </c>
+      <c r="G39" t="s">
         <v>208</v>
-      </c>
-      <c r="F39" t="s">
-        <v>0</v>
-      </c>
-      <c r="G39" t="s">
-        <v>209</v>
       </c>
       <c r="H39" t="s">
         <v>4</v>
@@ -2818,22 +2812,22 @@
     </row>
     <row r="40" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A40" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="C40" t="s">
         <v>19</v>
       </c>
       <c r="D40" t="s">
+        <v>206</v>
+      </c>
+      <c r="E40" t="s">
         <v>207</v>
       </c>
-      <c r="E40" t="s">
+      <c r="F40" t="s">
+        <v>0</v>
+      </c>
+      <c r="G40" t="s">
         <v>208</v>
-      </c>
-      <c r="F40" t="s">
-        <v>0</v>
-      </c>
-      <c r="G40" t="s">
-        <v>209</v>
       </c>
       <c r="H40" t="s">
         <v>4</v>
@@ -2841,22 +2835,22 @@
     </row>
     <row r="41" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A41" t="s">
+        <v>210</v>
+      </c>
+      <c r="C41" t="s">
+        <v>189</v>
+      </c>
+      <c r="D41" t="s">
         <v>211</v>
       </c>
-      <c r="C41" t="s">
-        <v>190</v>
-      </c>
-      <c r="D41" t="s">
+      <c r="E41" t="s">
         <v>212</v>
       </c>
-      <c r="E41" t="s">
+      <c r="F41" t="s">
+        <v>0</v>
+      </c>
+      <c r="G41" t="s">
         <v>213</v>
-      </c>
-      <c r="F41" t="s">
-        <v>0</v>
-      </c>
-      <c r="G41" t="s">
-        <v>214</v>
       </c>
       <c r="H41" t="s">
         <v>4</v>
@@ -2864,22 +2858,22 @@
     </row>
     <row r="42" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A42" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="C42" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="D42" t="s">
+        <v>211</v>
+      </c>
+      <c r="E42" t="s">
         <v>212</v>
       </c>
-      <c r="E42" t="s">
+      <c r="F42" t="s">
+        <v>0</v>
+      </c>
+      <c r="G42" t="s">
         <v>213</v>
-      </c>
-      <c r="F42" t="s">
-        <v>0</v>
-      </c>
-      <c r="G42" t="s">
-        <v>214</v>
       </c>
       <c r="H42" t="s">
         <v>4</v>
@@ -2887,22 +2881,22 @@
     </row>
     <row r="43" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A43" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="C43" t="s">
         <v>8</v>
       </c>
       <c r="D43" t="s">
+        <v>216</v>
+      </c>
+      <c r="E43" t="s">
         <v>217</v>
       </c>
-      <c r="E43" t="s">
+      <c r="F43" t="s">
         <v>218</v>
       </c>
-      <c r="F43" t="s">
+      <c r="G43" t="s">
         <v>219</v>
-      </c>
-      <c r="G43" t="s">
-        <v>220</v>
       </c>
       <c r="H43" t="s">
         <v>4</v>
@@ -2979,22 +2973,22 @@
     </row>
     <row r="47" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A47" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
       <c r="C47" t="s">
         <v>19</v>
       </c>
       <c r="D47" t="s">
+        <v>221</v>
+      </c>
+      <c r="E47" t="s">
+        <v>84</v>
+      </c>
+      <c r="F47" t="s">
+        <v>0</v>
+      </c>
+      <c r="G47" t="s">
         <v>222</v>
-      </c>
-      <c r="E47" t="s">
-        <v>85</v>
-      </c>
-      <c r="F47" t="s">
-        <v>0</v>
-      </c>
-      <c r="G47" t="s">
-        <v>223</v>
       </c>
       <c r="H47" t="s">
         <v>4</v>
@@ -3002,22 +2996,22 @@
     </row>
     <row r="48" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A48" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="C48" t="s">
         <v>2</v>
       </c>
       <c r="D48" t="s">
+        <v>224</v>
+      </c>
+      <c r="E48" t="s">
         <v>225</v>
       </c>
-      <c r="E48" t="s">
+      <c r="F48" t="s">
         <v>226</v>
       </c>
-      <c r="F48" t="s">
+      <c r="G48" t="s">
         <v>227</v>
-      </c>
-      <c r="G48" t="s">
-        <v>228</v>
       </c>
       <c r="H48" t="s">
         <v>4</v>
@@ -3025,22 +3019,22 @@
     </row>
     <row r="49" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A49" t="s">
-        <v>229</v>
+        <v>228</v>
       </c>
       <c r="C49" t="s">
         <v>11</v>
       </c>
       <c r="D49" t="s">
+        <v>229</v>
+      </c>
+      <c r="E49" t="s">
         <v>230</v>
       </c>
-      <c r="E49" t="s">
+      <c r="F49" t="s">
+        <v>0</v>
+      </c>
+      <c r="G49" t="s">
         <v>231</v>
-      </c>
-      <c r="F49" t="s">
-        <v>0</v>
-      </c>
-      <c r="G49" t="s">
-        <v>232</v>
       </c>
       <c r="H49" t="s">
         <v>4</v>
@@ -3048,22 +3042,22 @@
     </row>
     <row r="50" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A50" t="s">
-        <v>233</v>
+        <v>232</v>
       </c>
       <c r="C50" t="s">
         <v>11</v>
       </c>
       <c r="D50" t="s">
+        <v>233</v>
+      </c>
+      <c r="E50" t="s">
         <v>234</v>
       </c>
-      <c r="E50" t="s">
+      <c r="F50" t="s">
+        <v>0</v>
+      </c>
+      <c r="G50" t="s">
         <v>235</v>
-      </c>
-      <c r="F50" t="s">
-        <v>0</v>
-      </c>
-      <c r="G50" t="s">
-        <v>236</v>
       </c>
       <c r="H50" t="s">
         <v>4</v>
@@ -3071,13 +3065,13 @@
     </row>
     <row r="51" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A51" t="s">
+        <v>236</v>
+      </c>
+      <c r="C51" t="s">
+        <v>189</v>
+      </c>
+      <c r="D51" t="s">
         <v>237</v>
-      </c>
-      <c r="C51" t="s">
-        <v>190</v>
-      </c>
-      <c r="D51" t="s">
-        <v>238</v>
       </c>
       <c r="E51" t="s">
         <v>33</v>
@@ -3086,7 +3080,7 @@
         <v>0</v>
       </c>
       <c r="G51" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="H51" t="s">
         <v>4</v>
@@ -3094,13 +3088,13 @@
     </row>
     <row r="52" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A52" t="s">
-        <v>239</v>
+        <v>238</v>
       </c>
       <c r="C52" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="D52" t="s">
-        <v>238</v>
+        <v>237</v>
       </c>
       <c r="E52" t="s">
         <v>33</v>
@@ -3109,7 +3103,7 @@
         <v>0</v>
       </c>
       <c r="G52" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="H52" t="s">
         <v>4</v>
@@ -3117,13 +3111,13 @@
     </row>
     <row r="53" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A53" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
       <c r="C53" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="D53" t="s">
-        <v>238</v>
+        <v>237</v>
       </c>
       <c r="E53" t="s">
         <v>33</v>
@@ -3132,7 +3126,7 @@
         <v>0</v>
       </c>
       <c r="G53" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="H53" t="s">
         <v>4</v>
@@ -3140,19 +3134,19 @@
     </row>
     <row r="54" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A54" t="s">
+        <v>240</v>
+      </c>
+      <c r="C54" t="s">
+        <v>99</v>
+      </c>
+      <c r="D54" t="s">
         <v>241</v>
       </c>
-      <c r="C54" t="s">
-        <v>100</v>
-      </c>
-      <c r="D54" t="s">
+      <c r="E54" t="s">
         <v>242</v>
       </c>
-      <c r="E54" t="s">
+      <c r="F54" t="s">
         <v>243</v>
-      </c>
-      <c r="F54" t="s">
-        <v>244</v>
       </c>
       <c r="G54" t="s">
         <v>35</v>
@@ -3163,19 +3157,19 @@
     </row>
     <row r="55" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A55" t="s">
-        <v>245</v>
+        <v>244</v>
       </c>
       <c r="C55" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="D55" t="s">
+        <v>241</v>
+      </c>
+      <c r="E55" t="s">
         <v>242</v>
       </c>
-      <c r="E55" t="s">
+      <c r="F55" t="s">
         <v>243</v>
-      </c>
-      <c r="F55" t="s">
-        <v>244</v>
       </c>
       <c r="G55" t="s">
         <v>35</v>
@@ -3186,19 +3180,19 @@
     </row>
     <row r="56" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A56" t="s">
-        <v>246</v>
+        <v>245</v>
       </c>
       <c r="C56" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="D56" t="s">
+        <v>241</v>
+      </c>
+      <c r="E56" t="s">
         <v>242</v>
       </c>
-      <c r="E56" t="s">
+      <c r="F56" t="s">
         <v>243</v>
-      </c>
-      <c r="F56" t="s">
-        <v>244</v>
       </c>
       <c r="G56" t="s">
         <v>35</v>
@@ -3209,13 +3203,13 @@
     </row>
     <row r="57" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A57" t="s">
-        <v>247</v>
+        <v>246</v>
       </c>
       <c r="C57" t="s">
         <v>9</v>
       </c>
       <c r="D57" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="E57" t="s">
         <v>51</v>
@@ -3224,7 +3218,7 @@
         <v>0</v>
       </c>
       <c r="G57" t="s">
-        <v>249</v>
+        <v>248</v>
       </c>
       <c r="H57" t="s">
         <v>4</v>
@@ -3232,22 +3226,22 @@
     </row>
     <row r="58" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A58" t="s">
-        <v>250</v>
+        <v>249</v>
       </c>
       <c r="C58" t="s">
         <v>10</v>
       </c>
       <c r="D58" t="s">
+        <v>250</v>
+      </c>
+      <c r="E58" t="s">
         <v>251</v>
       </c>
-      <c r="E58" t="s">
+      <c r="F58" t="s">
+        <v>0</v>
+      </c>
+      <c r="G58" t="s">
         <v>252</v>
-      </c>
-      <c r="F58" t="s">
-        <v>0</v>
-      </c>
-      <c r="G58" t="s">
-        <v>253</v>
       </c>
       <c r="H58" t="s">
         <v>4</v>
@@ -3255,22 +3249,22 @@
     </row>
     <row r="59" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A59" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="C59" t="s">
         <v>10</v>
       </c>
       <c r="D59" t="s">
+        <v>250</v>
+      </c>
+      <c r="E59" t="s">
         <v>251</v>
       </c>
-      <c r="E59" t="s">
+      <c r="F59" t="s">
+        <v>0</v>
+      </c>
+      <c r="G59" t="s">
         <v>252</v>
-      </c>
-      <c r="F59" t="s">
-        <v>0</v>
-      </c>
-      <c r="G59" t="s">
-        <v>253</v>
       </c>
       <c r="H59" t="s">
         <v>4</v>
@@ -3278,22 +3272,22 @@
     </row>
     <row r="60" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A60" t="s">
-        <v>255</v>
+        <v>254</v>
       </c>
       <c r="C60" t="s">
         <v>9</v>
       </c>
       <c r="D60" t="s">
+        <v>255</v>
+      </c>
+      <c r="E60" t="s">
+        <v>76</v>
+      </c>
+      <c r="F60" t="s">
+        <v>77</v>
+      </c>
+      <c r="G60" t="s">
         <v>256</v>
-      </c>
-      <c r="E60" t="s">
-        <v>77</v>
-      </c>
-      <c r="F60" t="s">
-        <v>78</v>
-      </c>
-      <c r="G60" t="s">
-        <v>257</v>
       </c>
       <c r="H60" t="s">
         <v>4</v>
@@ -3301,13 +3295,13 @@
     </row>
     <row r="61" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A61" t="s">
+        <v>257</v>
+      </c>
+      <c r="C61" t="s">
+        <v>91</v>
+      </c>
+      <c r="D61" t="s">
         <v>258</v>
-      </c>
-      <c r="C61" t="s">
-        <v>92</v>
-      </c>
-      <c r="D61" t="s">
-        <v>259</v>
       </c>
       <c r="E61" t="s">
         <v>6</v>
@@ -3316,7 +3310,7 @@
         <v>7</v>
       </c>
       <c r="G61" t="s">
-        <v>260</v>
+        <v>259</v>
       </c>
       <c r="H61" t="s">
         <v>4</v>
@@ -3324,13 +3318,13 @@
     </row>
     <row r="62" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A62" t="s">
-        <v>261</v>
+        <v>260</v>
       </c>
       <c r="C62" t="s">
         <v>3</v>
       </c>
       <c r="D62" t="s">
-        <v>262</v>
+        <v>261</v>
       </c>
       <c r="E62" t="s">
         <v>43</v>
@@ -3339,7 +3333,7 @@
         <v>0</v>
       </c>
       <c r="G62" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="H62" t="s">
         <v>4</v>
@@ -3347,22 +3341,22 @@
     </row>
     <row r="63" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A63" t="s">
+        <v>263</v>
+      </c>
+      <c r="C63" t="s">
+        <v>164</v>
+      </c>
+      <c r="D63" t="s">
         <v>264</v>
       </c>
-      <c r="C63" t="s">
-        <v>165</v>
-      </c>
-      <c r="D63" t="s">
+      <c r="E63" t="s">
+        <v>183</v>
+      </c>
+      <c r="F63" t="s">
+        <v>0</v>
+      </c>
+      <c r="G63" t="s">
         <v>265</v>
-      </c>
-      <c r="E63" t="s">
-        <v>184</v>
-      </c>
-      <c r="F63" t="s">
-        <v>0</v>
-      </c>
-      <c r="G63" t="s">
-        <v>266</v>
       </c>
       <c r="H63" t="s">
         <v>4</v>
@@ -3370,22 +3364,22 @@
     </row>
     <row r="64" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A64" t="s">
-        <v>267</v>
+        <v>266</v>
       </c>
       <c r="C64" t="s">
         <v>9</v>
       </c>
       <c r="D64" t="s">
+        <v>267</v>
+      </c>
+      <c r="E64" t="s">
         <v>268</v>
       </c>
-      <c r="E64" t="s">
+      <c r="F64" t="s">
+        <v>0</v>
+      </c>
+      <c r="G64" t="s">
         <v>269</v>
-      </c>
-      <c r="F64" t="s">
-        <v>0</v>
-      </c>
-      <c r="G64" t="s">
-        <v>270</v>
       </c>
       <c r="H64" t="s">
         <v>4</v>
@@ -3393,22 +3387,22 @@
     </row>
     <row r="65" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A65" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
       <c r="C65" t="s">
         <v>11</v>
       </c>
       <c r="D65" t="s">
+        <v>271</v>
+      </c>
+      <c r="E65" t="s">
         <v>272</v>
       </c>
-      <c r="E65" t="s">
+      <c r="F65" t="s">
+        <v>0</v>
+      </c>
+      <c r="G65" t="s">
         <v>273</v>
-      </c>
-      <c r="F65" t="s">
-        <v>0</v>
-      </c>
-      <c r="G65" t="s">
-        <v>274</v>
       </c>
       <c r="H65" t="s">
         <v>4</v>
@@ -3416,22 +3410,22 @@
     </row>
     <row r="66" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A66" t="s">
-        <v>275</v>
+        <v>274</v>
       </c>
       <c r="C66" t="s">
         <v>11</v>
       </c>
       <c r="D66" t="s">
+        <v>271</v>
+      </c>
+      <c r="E66" t="s">
         <v>272</v>
       </c>
-      <c r="E66" t="s">
+      <c r="F66" t="s">
+        <v>0</v>
+      </c>
+      <c r="G66" t="s">
         <v>273</v>
-      </c>
-      <c r="F66" t="s">
-        <v>0</v>
-      </c>
-      <c r="G66" t="s">
-        <v>274</v>
       </c>
       <c r="H66" t="s">
         <v>4</v>
@@ -3439,22 +3433,22 @@
     </row>
     <row r="67" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A67" t="s">
+        <v>275</v>
+      </c>
+      <c r="C67" t="s">
+        <v>151</v>
+      </c>
+      <c r="D67" t="s">
         <v>276</v>
       </c>
-      <c r="C67" t="s">
-        <v>152</v>
-      </c>
-      <c r="D67" t="s">
+      <c r="E67" t="s">
         <v>277</v>
       </c>
-      <c r="E67" t="s">
+      <c r="F67" t="s">
+        <v>0</v>
+      </c>
+      <c r="G67" t="s">
         <v>278</v>
-      </c>
-      <c r="F67" t="s">
-        <v>0</v>
-      </c>
-      <c r="G67" t="s">
-        <v>279</v>
       </c>
       <c r="H67" t="s">
         <v>4</v>
@@ -3462,13 +3456,13 @@
     </row>
     <row r="68" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A68" t="s">
+        <v>279</v>
+      </c>
+      <c r="C68" t="s">
+        <v>99</v>
+      </c>
+      <c r="D68" t="s">
         <v>280</v>
-      </c>
-      <c r="C68" t="s">
-        <v>100</v>
-      </c>
-      <c r="D68" t="s">
-        <v>281</v>
       </c>
       <c r="E68" t="s">
         <v>71</v>
@@ -3485,22 +3479,22 @@
     </row>
     <row r="69" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A69" t="s">
-        <v>282</v>
+        <v>281</v>
       </c>
       <c r="C69" t="s">
         <v>9</v>
       </c>
       <c r="D69" t="s">
+        <v>282</v>
+      </c>
+      <c r="E69" t="s">
         <v>283</v>
       </c>
-      <c r="E69" t="s">
+      <c r="F69" t="s">
+        <v>0</v>
+      </c>
+      <c r="G69" t="s">
         <v>284</v>
-      </c>
-      <c r="F69" t="s">
-        <v>0</v>
-      </c>
-      <c r="G69" t="s">
-        <v>285</v>
       </c>
       <c r="H69" t="s">
         <v>4</v>
@@ -3508,22 +3502,22 @@
     </row>
     <row r="70" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A70" t="s">
-        <v>286</v>
+        <v>285</v>
       </c>
       <c r="C70" t="s">
         <v>9</v>
       </c>
       <c r="D70" t="s">
+        <v>282</v>
+      </c>
+      <c r="E70" t="s">
         <v>283</v>
       </c>
-      <c r="E70" t="s">
+      <c r="F70" t="s">
+        <v>0</v>
+      </c>
+      <c r="G70" t="s">
         <v>284</v>
-      </c>
-      <c r="F70" t="s">
-        <v>0</v>
-      </c>
-      <c r="G70" t="s">
-        <v>285</v>
       </c>
       <c r="H70" t="s">
         <v>4</v>
@@ -3531,22 +3525,22 @@
     </row>
     <row r="71" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A71" t="s">
-        <v>287</v>
+        <v>286</v>
       </c>
       <c r="C71" t="s">
         <v>9</v>
       </c>
       <c r="D71" t="s">
+        <v>282</v>
+      </c>
+      <c r="E71" t="s">
         <v>283</v>
       </c>
-      <c r="E71" t="s">
+      <c r="F71" t="s">
+        <v>0</v>
+      </c>
+      <c r="G71" t="s">
         <v>284</v>
-      </c>
-      <c r="F71" t="s">
-        <v>0</v>
-      </c>
-      <c r="G71" t="s">
-        <v>285</v>
       </c>
       <c r="H71" t="s">
         <v>4</v>
@@ -3554,22 +3548,22 @@
     </row>
     <row r="72" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A72" t="s">
+        <v>287</v>
+      </c>
+      <c r="C72" t="s">
+        <v>91</v>
+      </c>
+      <c r="D72" t="s">
         <v>288</v>
       </c>
-      <c r="C72" t="s">
-        <v>92</v>
-      </c>
-      <c r="D72" t="s">
+      <c r="E72" t="s">
         <v>289</v>
       </c>
-      <c r="E72" t="s">
+      <c r="F72" t="s">
         <v>290</v>
       </c>
-      <c r="F72" t="s">
+      <c r="G72" t="s">
         <v>291</v>
-      </c>
-      <c r="G72" t="s">
-        <v>292</v>
       </c>
       <c r="H72" t="s">
         <v>4</v>
@@ -3577,22 +3571,22 @@
     </row>
     <row r="73" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A73" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="C73" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="D73" t="s">
+        <v>288</v>
+      </c>
+      <c r="E73" t="s">
         <v>289</v>
       </c>
-      <c r="E73" t="s">
+      <c r="F73" t="s">
         <v>290</v>
       </c>
-      <c r="F73" t="s">
+      <c r="G73" t="s">
         <v>291</v>
-      </c>
-      <c r="G73" t="s">
-        <v>292</v>
       </c>
       <c r="H73" t="s">
         <v>4</v>
@@ -3600,22 +3594,22 @@
     </row>
     <row r="74" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A74" t="s">
-        <v>294</v>
+        <v>293</v>
       </c>
       <c r="C74" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="D74" t="s">
+        <v>288</v>
+      </c>
+      <c r="E74" t="s">
         <v>289</v>
       </c>
-      <c r="E74" t="s">
+      <c r="F74" t="s">
         <v>290</v>
       </c>
-      <c r="F74" t="s">
+      <c r="G74" t="s">
         <v>291</v>
-      </c>
-      <c r="G74" t="s">
-        <v>292</v>
       </c>
       <c r="H74" t="s">
         <v>4</v>
@@ -3623,22 +3617,22 @@
     </row>
     <row r="75" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A75" t="s">
-        <v>295</v>
+        <v>294</v>
       </c>
       <c r="C75" t="s">
         <v>21</v>
       </c>
       <c r="D75" t="s">
+        <v>295</v>
+      </c>
+      <c r="E75" t="s">
         <v>296</v>
       </c>
-      <c r="E75" t="s">
+      <c r="F75" t="s">
+        <v>0</v>
+      </c>
+      <c r="G75" t="s">
         <v>297</v>
-      </c>
-      <c r="F75" t="s">
-        <v>0</v>
-      </c>
-      <c r="G75" t="s">
-        <v>298</v>
       </c>
       <c r="H75" t="s">
         <v>4</v>
@@ -3646,22 +3640,22 @@
     </row>
     <row r="76" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A76" t="s">
-        <v>299</v>
+        <v>298</v>
       </c>
       <c r="C76" t="s">
         <v>21</v>
       </c>
       <c r="D76" t="s">
+        <v>295</v>
+      </c>
+      <c r="E76" t="s">
         <v>296</v>
       </c>
-      <c r="E76" t="s">
+      <c r="F76" t="s">
+        <v>0</v>
+      </c>
+      <c r="G76" t="s">
         <v>297</v>
-      </c>
-      <c r="F76" t="s">
-        <v>0</v>
-      </c>
-      <c r="G76" t="s">
-        <v>298</v>
       </c>
       <c r="H76" t="s">
         <v>4</v>
@@ -3669,22 +3663,22 @@
     </row>
     <row r="77" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A77" t="s">
-        <v>300</v>
+        <v>299</v>
       </c>
       <c r="C77" t="s">
         <v>58</v>
       </c>
       <c r="D77" t="s">
+        <v>300</v>
+      </c>
+      <c r="E77" t="s">
         <v>301</v>
       </c>
-      <c r="E77" t="s">
+      <c r="F77" t="s">
         <v>302</v>
       </c>
-      <c r="F77" t="s">
+      <c r="G77" t="s">
         <v>303</v>
-      </c>
-      <c r="G77" t="s">
-        <v>304</v>
       </c>
       <c r="H77" t="s">
         <v>4</v>
@@ -3692,22 +3686,22 @@
     </row>
     <row r="78" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A78" t="s">
-        <v>305</v>
+        <v>304</v>
       </c>
       <c r="C78" t="s">
         <v>58</v>
       </c>
       <c r="D78" t="s">
+        <v>305</v>
+      </c>
+      <c r="E78" t="s">
         <v>306</v>
       </c>
-      <c r="E78" t="s">
+      <c r="F78" t="s">
+        <v>0</v>
+      </c>
+      <c r="G78" t="s">
         <v>307</v>
-      </c>
-      <c r="F78" t="s">
-        <v>0</v>
-      </c>
-      <c r="G78" t="s">
-        <v>308</v>
       </c>
       <c r="H78" t="s">
         <v>4</v>
@@ -3715,13 +3709,13 @@
     </row>
     <row r="79" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A79" t="s">
-        <v>309</v>
+        <v>308</v>
       </c>
       <c r="C79" t="s">
         <v>13</v>
       </c>
       <c r="D79" t="s">
-        <v>310</v>
+        <v>309</v>
       </c>
       <c r="E79" t="s">
         <v>15</v>
@@ -3730,7 +3724,7 @@
         <v>16</v>
       </c>
       <c r="G79" t="s">
-        <v>311</v>
+        <v>310</v>
       </c>
       <c r="H79" t="s">
         <v>4</v>
@@ -3738,22 +3732,22 @@
     </row>
     <row r="80" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A80" t="s">
-        <v>312</v>
+        <v>311</v>
       </c>
       <c r="C80" t="s">
         <v>19</v>
       </c>
       <c r="D80" t="s">
+        <v>312</v>
+      </c>
+      <c r="E80" t="s">
+        <v>207</v>
+      </c>
+      <c r="F80" t="s">
+        <v>0</v>
+      </c>
+      <c r="G80" t="s">
         <v>313</v>
-      </c>
-      <c r="E80" t="s">
-        <v>208</v>
-      </c>
-      <c r="F80" t="s">
-        <v>0</v>
-      </c>
-      <c r="G80" t="s">
-        <v>314</v>
       </c>
       <c r="H80" t="s">
         <v>4</v>
@@ -3761,22 +3755,22 @@
     </row>
     <row r="81" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A81" t="s">
-        <v>315</v>
+        <v>314</v>
       </c>
       <c r="C81" t="s">
         <v>11</v>
       </c>
       <c r="D81" t="s">
+        <v>315</v>
+      </c>
+      <c r="E81" t="s">
+        <v>272</v>
+      </c>
+      <c r="F81" t="s">
+        <v>0</v>
+      </c>
+      <c r="G81" t="s">
         <v>316</v>
-      </c>
-      <c r="E81" t="s">
-        <v>273</v>
-      </c>
-      <c r="F81" t="s">
-        <v>0</v>
-      </c>
-      <c r="G81" t="s">
-        <v>317</v>
       </c>
       <c r="H81" t="s">
         <v>4</v>
@@ -3784,13 +3778,13 @@
     </row>
     <row r="82" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A82" t="s">
-        <v>318</v>
+        <v>317</v>
       </c>
       <c r="C82" t="s">
         <v>53</v>
       </c>
       <c r="D82" t="s">
-        <v>319</v>
+        <v>318</v>
       </c>
       <c r="E82" t="s">
         <v>55</v>
@@ -3799,7 +3793,7 @@
         <v>56</v>
       </c>
       <c r="G82" t="s">
-        <v>320</v>
+        <v>319</v>
       </c>
       <c r="H82" t="s">
         <v>4</v>
@@ -3807,22 +3801,22 @@
     </row>
     <row r="83" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A83" t="s">
-        <v>321</v>
+        <v>320</v>
       </c>
       <c r="C83" t="s">
         <v>21</v>
       </c>
       <c r="D83" t="s">
+        <v>321</v>
+      </c>
+      <c r="E83" t="s">
         <v>322</v>
       </c>
-      <c r="E83" t="s">
+      <c r="F83" t="s">
+        <v>0</v>
+      </c>
+      <c r="G83" t="s">
         <v>323</v>
-      </c>
-      <c r="F83" t="s">
-        <v>0</v>
-      </c>
-      <c r="G83" t="s">
-        <v>324</v>
       </c>
       <c r="H83" t="s">
         <v>4</v>
@@ -3830,22 +3824,22 @@
     </row>
     <row r="84" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A84" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
       <c r="C84" t="s">
         <v>21</v>
       </c>
       <c r="D84" t="s">
+        <v>321</v>
+      </c>
+      <c r="E84" t="s">
         <v>322</v>
       </c>
-      <c r="E84" t="s">
+      <c r="F84" t="s">
+        <v>0</v>
+      </c>
+      <c r="G84" t="s">
         <v>323</v>
-      </c>
-      <c r="F84" t="s">
-        <v>0</v>
-      </c>
-      <c r="G84" t="s">
-        <v>324</v>
       </c>
       <c r="H84" t="s">
         <v>4</v>
@@ -3853,13 +3847,13 @@
     </row>
     <row r="85" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A85" t="s">
-        <v>326</v>
+        <v>325</v>
       </c>
       <c r="C85" t="s">
         <v>53</v>
       </c>
       <c r="D85" t="s">
-        <v>327</v>
+        <v>326</v>
       </c>
       <c r="E85" t="s">
         <v>55</v>
@@ -3868,7 +3862,7 @@
         <v>56</v>
       </c>
       <c r="G85" t="s">
-        <v>328</v>
+        <v>327</v>
       </c>
       <c r="H85" t="s">
         <v>4</v>
@@ -3876,13 +3870,13 @@
     </row>
     <row r="86" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A86" t="s">
-        <v>329</v>
+        <v>328</v>
       </c>
       <c r="C86" t="s">
         <v>13</v>
       </c>
       <c r="D86" t="s">
-        <v>330</v>
+        <v>329</v>
       </c>
       <c r="E86" t="s">
         <v>60</v>
@@ -3891,7 +3885,7 @@
         <v>61</v>
       </c>
       <c r="G86" t="s">
-        <v>331</v>
+        <v>330</v>
       </c>
       <c r="H86" t="s">
         <v>4</v>
@@ -3899,22 +3893,22 @@
     </row>
     <row r="87" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A87" t="s">
-        <v>332</v>
+        <v>331</v>
       </c>
       <c r="C87" t="s">
         <v>21</v>
       </c>
       <c r="D87" t="s">
+        <v>332</v>
+      </c>
+      <c r="E87" t="s">
         <v>333</v>
       </c>
-      <c r="E87" t="s">
+      <c r="F87" t="s">
+        <v>0</v>
+      </c>
+      <c r="G87" t="s">
         <v>334</v>
-      </c>
-      <c r="F87" t="s">
-        <v>0</v>
-      </c>
-      <c r="G87" t="s">
-        <v>335</v>
       </c>
       <c r="H87" t="s">
         <v>4</v>
@@ -3922,22 +3916,22 @@
     </row>
     <row r="88" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A88" t="s">
-        <v>336</v>
+        <v>335</v>
       </c>
       <c r="C88" t="s">
         <v>19</v>
       </c>
       <c r="D88" t="s">
+        <v>336</v>
+      </c>
+      <c r="E88" t="s">
         <v>337</v>
       </c>
-      <c r="E88" t="s">
+      <c r="F88" t="s">
+        <v>0</v>
+      </c>
+      <c r="G88" t="s">
         <v>338</v>
-      </c>
-      <c r="F88" t="s">
-        <v>0</v>
-      </c>
-      <c r="G88" t="s">
-        <v>339</v>
       </c>
       <c r="H88" t="s">
         <v>4</v>
@@ -3945,13 +3939,13 @@
     </row>
     <row r="89" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A89" t="s">
-        <v>340</v>
+        <v>339</v>
       </c>
       <c r="C89" t="s">
         <v>13</v>
       </c>
       <c r="D89" t="s">
-        <v>341</v>
+        <v>340</v>
       </c>
       <c r="E89" t="s">
         <v>17</v>
@@ -3960,7 +3954,7 @@
         <v>18</v>
       </c>
       <c r="G89" t="s">
-        <v>342</v>
+        <v>341</v>
       </c>
       <c r="H89" t="s">
         <v>4</v>
@@ -3968,22 +3962,22 @@
     </row>
     <row r="90" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A90" t="s">
-        <v>343</v>
+        <v>342</v>
       </c>
       <c r="C90" t="s">
         <v>58</v>
       </c>
       <c r="D90" t="s">
+        <v>343</v>
+      </c>
+      <c r="E90" t="s">
         <v>344</v>
       </c>
-      <c r="E90" t="s">
+      <c r="F90" t="s">
         <v>345</v>
       </c>
-      <c r="F90" t="s">
+      <c r="G90" t="s">
         <v>346</v>
-      </c>
-      <c r="G90" t="s">
-        <v>347</v>
       </c>
       <c r="H90" t="s">
         <v>4</v>
@@ -3991,13 +3985,13 @@
     </row>
     <row r="91" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A91" t="s">
+        <v>347</v>
+      </c>
+      <c r="C91" t="s">
+        <v>189</v>
+      </c>
+      <c r="D91" t="s">
         <v>348</v>
-      </c>
-      <c r="C91" t="s">
-        <v>190</v>
-      </c>
-      <c r="D91" t="s">
-        <v>349</v>
       </c>
       <c r="E91" t="s">
         <v>74</v>
@@ -4006,7 +4000,7 @@
         <v>0</v>
       </c>
       <c r="G91" t="s">
-        <v>350</v>
+        <v>349</v>
       </c>
       <c r="H91" t="s">
         <v>4</v>
@@ -4014,13 +4008,13 @@
     </row>
     <row r="92" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A92" t="s">
-        <v>351</v>
+        <v>350</v>
       </c>
       <c r="C92" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="D92" t="s">
-        <v>349</v>
+        <v>348</v>
       </c>
       <c r="E92" t="s">
         <v>74</v>
@@ -4029,7 +4023,7 @@
         <v>0</v>
       </c>
       <c r="G92" t="s">
-        <v>350</v>
+        <v>349</v>
       </c>
       <c r="H92" t="s">
         <v>4</v>
@@ -4037,13 +4031,13 @@
     </row>
     <row r="93" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A93" t="s">
-        <v>352</v>
+        <v>351</v>
       </c>
       <c r="C93" t="s">
         <v>2</v>
       </c>
       <c r="D93" t="s">
-        <v>353</v>
+        <v>352</v>
       </c>
       <c r="E93" t="s">
         <v>14</v>
@@ -4052,7 +4046,7 @@
         <v>0</v>
       </c>
       <c r="G93" t="s">
-        <v>354</v>
+        <v>353</v>
       </c>
       <c r="H93" t="s">
         <v>4</v>
@@ -4060,22 +4054,22 @@
     </row>
     <row r="94" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A94" t="s">
-        <v>355</v>
+        <v>354</v>
       </c>
       <c r="C94" t="s">
         <v>53</v>
       </c>
       <c r="D94" t="s">
+        <v>355</v>
+      </c>
+      <c r="E94" t="s">
+        <v>148</v>
+      </c>
+      <c r="F94" t="s">
+        <v>0</v>
+      </c>
+      <c r="G94" t="s">
         <v>356</v>
-      </c>
-      <c r="E94" t="s">
-        <v>149</v>
-      </c>
-      <c r="F94" t="s">
-        <v>0</v>
-      </c>
-      <c r="G94" t="s">
-        <v>357</v>
       </c>
       <c r="H94" t="s">
         <v>4</v>
@@ -4083,13 +4077,13 @@
     </row>
     <row r="95" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A95" t="s">
-        <v>358</v>
+        <v>357</v>
       </c>
       <c r="C95" t="s">
         <v>11</v>
       </c>
       <c r="D95" t="s">
-        <v>359</v>
+        <v>358</v>
       </c>
       <c r="E95" t="s">
         <v>50</v>
@@ -4098,7 +4092,7 @@
         <v>0</v>
       </c>
       <c r="G95" t="s">
-        <v>360</v>
+        <v>359</v>
       </c>
       <c r="H95" t="s">
         <v>4</v>
@@ -4106,22 +4100,22 @@
     </row>
     <row r="96" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A96" t="s">
-        <v>361</v>
+        <v>360</v>
       </c>
       <c r="C96" t="s">
         <v>22</v>
       </c>
       <c r="D96" t="s">
+        <v>361</v>
+      </c>
+      <c r="E96" t="s">
         <v>362</v>
       </c>
-      <c r="E96" t="s">
+      <c r="F96" t="s">
+        <v>159</v>
+      </c>
+      <c r="G96" t="s">
         <v>363</v>
-      </c>
-      <c r="F96" t="s">
-        <v>160</v>
-      </c>
-      <c r="G96" t="s">
-        <v>364</v>
       </c>
       <c r="H96" t="s">
         <v>4</v>
@@ -4129,22 +4123,22 @@
     </row>
     <row r="97" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A97" t="s">
-        <v>365</v>
+        <v>364</v>
       </c>
       <c r="C97" t="s">
         <v>2</v>
       </c>
       <c r="D97" t="s">
+        <v>365</v>
+      </c>
+      <c r="E97" t="s">
         <v>366</v>
       </c>
-      <c r="E97" t="s">
+      <c r="F97" t="s">
         <v>367</v>
       </c>
-      <c r="F97" t="s">
+      <c r="G97" t="s">
         <v>368</v>
-      </c>
-      <c r="G97" t="s">
-        <v>369</v>
       </c>
       <c r="H97" t="s">
         <v>4</v>
@@ -4152,13 +4146,13 @@
     </row>
     <row r="98" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A98" t="s">
-        <v>370</v>
+        <v>369</v>
       </c>
       <c r="C98" t="s">
         <v>20</v>
       </c>
       <c r="D98" t="s">
-        <v>371</v>
+        <v>370</v>
       </c>
       <c r="E98" t="s">
         <v>59</v>
@@ -4167,7 +4161,7 @@
         <v>0</v>
       </c>
       <c r="G98" t="s">
-        <v>372</v>
+        <v>371</v>
       </c>
       <c r="H98" t="s">
         <v>4</v>
@@ -4175,22 +4169,22 @@
     </row>
     <row r="99" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A99" t="s">
-        <v>373</v>
+        <v>372</v>
       </c>
       <c r="C99" t="s">
         <v>21</v>
       </c>
       <c r="D99" t="s">
+        <v>373</v>
+      </c>
+      <c r="E99" t="s">
+        <v>333</v>
+      </c>
+      <c r="F99" t="s">
+        <v>0</v>
+      </c>
+      <c r="G99" t="s">
         <v>374</v>
-      </c>
-      <c r="E99" t="s">
-        <v>334</v>
-      </c>
-      <c r="F99" t="s">
-        <v>0</v>
-      </c>
-      <c r="G99" t="s">
-        <v>375</v>
       </c>
       <c r="H99" t="s">
         <v>4</v>
@@ -4198,13 +4192,13 @@
     </row>
     <row r="100" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A100" t="s">
-        <v>376</v>
+        <v>375</v>
       </c>
       <c r="C100" t="s">
         <v>12</v>
       </c>
       <c r="D100" t="s">
-        <v>377</v>
+        <v>376</v>
       </c>
       <c r="E100" t="s">
         <v>54</v>
@@ -4213,7 +4207,7 @@
         <v>0</v>
       </c>
       <c r="G100" t="s">
-        <v>378</v>
+        <v>377</v>
       </c>
       <c r="H100" t="s">
         <v>4</v>
@@ -4221,22 +4215,22 @@
     </row>
     <row r="101" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A101" t="s">
-        <v>379</v>
+        <v>378</v>
       </c>
       <c r="C101" t="s">
         <v>8</v>
       </c>
       <c r="D101" t="s">
+        <v>379</v>
+      </c>
+      <c r="E101" t="s">
         <v>380</v>
       </c>
-      <c r="E101" t="s">
+      <c r="F101" t="s">
+        <v>0</v>
+      </c>
+      <c r="G101" t="s">
         <v>381</v>
-      </c>
-      <c r="F101" t="s">
-        <v>0</v>
-      </c>
-      <c r="G101" t="s">
-        <v>382</v>
       </c>
       <c r="H101" t="s">
         <v>4</v>
@@ -4244,22 +4238,22 @@
     </row>
     <row r="102" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A102" t="s">
+        <v>382</v>
+      </c>
+      <c r="C102" t="s">
+        <v>151</v>
+      </c>
+      <c r="D102" t="s">
         <v>383</v>
       </c>
-      <c r="C102" t="s">
-        <v>152</v>
-      </c>
-      <c r="D102" t="s">
+      <c r="E102" t="s">
         <v>384</v>
       </c>
-      <c r="E102" t="s">
+      <c r="F102" t="s">
+        <v>0</v>
+      </c>
+      <c r="G102" t="s">
         <v>385</v>
-      </c>
-      <c r="F102" t="s">
-        <v>0</v>
-      </c>
-      <c r="G102" t="s">
-        <v>386</v>
       </c>
       <c r="H102" t="s">
         <v>4</v>
@@ -4267,22 +4261,22 @@
     </row>
     <row r="103" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A103" t="s">
-        <v>387</v>
+        <v>386</v>
       </c>
       <c r="C103" t="s">
         <v>10</v>
       </c>
       <c r="D103" t="s">
+        <v>387</v>
+      </c>
+      <c r="E103" t="s">
         <v>388</v>
       </c>
-      <c r="E103" t="s">
+      <c r="F103" t="s">
+        <v>0</v>
+      </c>
+      <c r="G103" t="s">
         <v>389</v>
-      </c>
-      <c r="F103" t="s">
-        <v>0</v>
-      </c>
-      <c r="G103" t="s">
-        <v>390</v>
       </c>
       <c r="H103" t="s">
         <v>4</v>
@@ -4290,22 +4284,22 @@
     </row>
     <row r="104" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A104" t="s">
-        <v>391</v>
+        <v>390</v>
       </c>
       <c r="C104" t="s">
         <v>10</v>
       </c>
       <c r="D104" t="s">
+        <v>387</v>
+      </c>
+      <c r="E104" t="s">
         <v>388</v>
       </c>
-      <c r="E104" t="s">
+      <c r="F104" t="s">
+        <v>0</v>
+      </c>
+      <c r="G104" t="s">
         <v>389</v>
-      </c>
-      <c r="F104" t="s">
-        <v>0</v>
-      </c>
-      <c r="G104" t="s">
-        <v>390</v>
       </c>
       <c r="H104" t="s">
         <v>4</v>
@@ -4313,22 +4307,22 @@
     </row>
     <row r="105" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A105" t="s">
+        <v>391</v>
+      </c>
+      <c r="C105" t="s">
         <v>392</v>
       </c>
-      <c r="C105" t="s">
+      <c r="D105" t="s">
         <v>393</v>
       </c>
-      <c r="D105" t="s">
+      <c r="E105" t="s">
+        <v>76</v>
+      </c>
+      <c r="F105" t="s">
+        <v>77</v>
+      </c>
+      <c r="G105" t="s">
         <v>394</v>
-      </c>
-      <c r="E105" t="s">
-        <v>77</v>
-      </c>
-      <c r="F105" t="s">
-        <v>78</v>
-      </c>
-      <c r="G105" t="s">
-        <v>395</v>
       </c>
       <c r="H105" t="s">
         <v>4</v>
@@ -4336,22 +4330,22 @@
     </row>
     <row r="106" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A106" t="s">
-        <v>396</v>
+        <v>395</v>
       </c>
       <c r="C106" t="s">
         <v>58</v>
       </c>
       <c r="D106" t="s">
+        <v>396</v>
+      </c>
+      <c r="E106" t="s">
         <v>397</v>
       </c>
-      <c r="E106" t="s">
+      <c r="F106" t="s">
         <v>398</v>
       </c>
-      <c r="F106" t="s">
+      <c r="G106" t="s">
         <v>399</v>
-      </c>
-      <c r="G106" t="s">
-        <v>400</v>
       </c>
       <c r="H106" t="s">
         <v>4</v>
@@ -4359,13 +4353,13 @@
     </row>
     <row r="107" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A107" t="s">
+        <v>400</v>
+      </c>
+      <c r="C107" t="s">
+        <v>151</v>
+      </c>
+      <c r="D107" t="s">
         <v>401</v>
-      </c>
-      <c r="C107" t="s">
-        <v>152</v>
-      </c>
-      <c r="D107" t="s">
-        <v>402</v>
       </c>
       <c r="E107" t="s">
         <v>63</v>
@@ -4374,7 +4368,7 @@
         <v>0</v>
       </c>
       <c r="G107" t="s">
-        <v>403</v>
+        <v>402</v>
       </c>
       <c r="H107" t="s">
         <v>4</v>
@@ -4382,22 +4376,22 @@
     </row>
     <row r="108" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A108" t="s">
-        <v>404</v>
+        <v>403</v>
       </c>
       <c r="C108" t="s">
         <v>9</v>
       </c>
       <c r="D108" t="s">
+        <v>404</v>
+      </c>
+      <c r="E108" t="s">
         <v>405</v>
       </c>
-      <c r="E108" t="s">
+      <c r="F108" t="s">
+        <v>0</v>
+      </c>
+      <c r="G108" t="s">
         <v>406</v>
-      </c>
-      <c r="F108" t="s">
-        <v>0</v>
-      </c>
-      <c r="G108" t="s">
-        <v>407</v>
       </c>
       <c r="H108" t="s">
         <v>4</v>
@@ -4405,13 +4399,13 @@
     </row>
     <row r="109" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A109" t="s">
-        <v>408</v>
+        <v>407</v>
       </c>
       <c r="C109" t="s">
         <v>3</v>
       </c>
       <c r="D109" t="s">
-        <v>409</v>
+        <v>408</v>
       </c>
       <c r="E109" t="s">
         <v>43</v>
@@ -4428,13 +4422,13 @@
     </row>
     <row r="110" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A110" t="s">
-        <v>410</v>
+        <v>409</v>
       </c>
       <c r="C110" t="s">
         <v>3</v>
       </c>
       <c r="D110" t="s">
-        <v>411</v>
+        <v>410</v>
       </c>
       <c r="E110" t="s">
         <v>57</v>
@@ -4443,7 +4437,7 @@
         <v>0</v>
       </c>
       <c r="G110" t="s">
-        <v>412</v>
+        <v>411</v>
       </c>
       <c r="H110" t="s">
         <v>4</v>
@@ -4451,22 +4445,22 @@
     </row>
     <row r="111" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A111" t="s">
-        <v>413</v>
+        <v>412</v>
       </c>
       <c r="C111" t="s">
         <v>20</v>
       </c>
       <c r="D111" t="s">
+        <v>413</v>
+      </c>
+      <c r="E111" t="s">
         <v>414</v>
       </c>
-      <c r="E111" t="s">
+      <c r="F111" t="s">
+        <v>0</v>
+      </c>
+      <c r="G111" t="s">
         <v>415</v>
-      </c>
-      <c r="F111" t="s">
-        <v>0</v>
-      </c>
-      <c r="G111" t="s">
-        <v>416</v>
       </c>
       <c r="H111" t="s">
         <v>4</v>
@@ -4474,22 +4468,22 @@
     </row>
     <row r="112" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A112" t="s">
-        <v>417</v>
+        <v>416</v>
       </c>
       <c r="C112" t="s">
         <v>58</v>
       </c>
       <c r="D112" t="s">
+        <v>417</v>
+      </c>
+      <c r="E112" t="s">
         <v>418</v>
       </c>
-      <c r="E112" t="s">
+      <c r="F112" t="s">
+        <v>0</v>
+      </c>
+      <c r="G112" t="s">
         <v>419</v>
-      </c>
-      <c r="F112" t="s">
-        <v>0</v>
-      </c>
-      <c r="G112" t="s">
-        <v>420</v>
       </c>
       <c r="H112" t="s">
         <v>4</v>
@@ -4497,22 +4491,22 @@
     </row>
     <row r="113" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A113" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="C113" t="s">
         <v>58</v>
       </c>
       <c r="D113" t="s">
+        <v>417</v>
+      </c>
+      <c r="E113" t="s">
         <v>418</v>
       </c>
-      <c r="E113" t="s">
+      <c r="F113" t="s">
+        <v>0</v>
+      </c>
+      <c r="G113" t="s">
         <v>419</v>
-      </c>
-      <c r="F113" t="s">
-        <v>0</v>
-      </c>
-      <c r="G113" t="s">
-        <v>420</v>
       </c>
       <c r="H113" t="s">
         <v>4</v>
@@ -4520,22 +4514,22 @@
     </row>
     <row r="114" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A114" t="s">
-        <v>422</v>
+        <v>421</v>
       </c>
       <c r="C114" t="s">
         <v>20</v>
       </c>
       <c r="D114" t="s">
+        <v>422</v>
+      </c>
+      <c r="E114" t="s">
         <v>423</v>
       </c>
-      <c r="E114" t="s">
+      <c r="F114" t="s">
+        <v>0</v>
+      </c>
+      <c r="G114" t="s">
         <v>424</v>
-      </c>
-      <c r="F114" t="s">
-        <v>0</v>
-      </c>
-      <c r="G114" t="s">
-        <v>425</v>
       </c>
       <c r="H114" t="s">
         <v>4</v>
@@ -4543,13 +4537,13 @@
     </row>
     <row r="115" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A115" t="s">
+        <v>425</v>
+      </c>
+      <c r="C115" t="s">
+        <v>91</v>
+      </c>
+      <c r="D115" t="s">
         <v>426</v>
-      </c>
-      <c r="C115" t="s">
-        <v>92</v>
-      </c>
-      <c r="D115" t="s">
-        <v>427</v>
       </c>
       <c r="E115" t="s">
         <v>6</v>
@@ -4558,7 +4552,7 @@
         <v>7</v>
       </c>
       <c r="G115" t="s">
-        <v>428</v>
+        <v>427</v>
       </c>
       <c r="H115" t="s">
         <v>4</v>
@@ -4566,13 +4560,13 @@
     </row>
     <row r="116" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A116" t="s">
+        <v>428</v>
+      </c>
+      <c r="C116" t="s">
+        <v>151</v>
+      </c>
+      <c r="D116" t="s">
         <v>429</v>
-      </c>
-      <c r="C116" t="s">
-        <v>152</v>
-      </c>
-      <c r="D116" t="s">
-        <v>430</v>
       </c>
       <c r="E116" t="s">
         <v>63</v>
@@ -4581,7 +4575,7 @@
         <v>0</v>
       </c>
       <c r="G116" t="s">
-        <v>431</v>
+        <v>430</v>
       </c>
       <c r="H116" t="s">
         <v>4</v>
@@ -4589,13 +4583,13 @@
     </row>
     <row r="117" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A117" t="s">
+        <v>431</v>
+      </c>
+      <c r="C117" t="s">
+        <v>91</v>
+      </c>
+      <c r="D117" t="s">
         <v>432</v>
-      </c>
-      <c r="C117" t="s">
-        <v>92</v>
-      </c>
-      <c r="D117" t="s">
-        <v>433</v>
       </c>
       <c r="E117" t="s">
         <v>26</v>
@@ -4604,7 +4598,7 @@
         <v>27</v>
       </c>
       <c r="G117" t="s">
-        <v>434</v>
+        <v>433</v>
       </c>
       <c r="H117" t="s">
         <v>4</v>
@@ -4612,13 +4606,13 @@
     </row>
     <row r="118" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A118" t="s">
-        <v>435</v>
+        <v>434</v>
       </c>
       <c r="C118" t="s">
         <v>12</v>
       </c>
       <c r="D118" t="s">
-        <v>436</v>
+        <v>435</v>
       </c>
       <c r="E118" t="s">
         <v>73</v>
@@ -4627,7 +4621,7 @@
         <v>0</v>
       </c>
       <c r="G118" t="s">
-        <v>437</v>
+        <v>436</v>
       </c>
       <c r="H118" t="s">
         <v>4</v>
@@ -4635,22 +4629,22 @@
     </row>
     <row r="119" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A119" t="s">
-        <v>438</v>
+        <v>437</v>
       </c>
       <c r="C119" t="s">
         <v>8</v>
       </c>
       <c r="D119" t="s">
+        <v>438</v>
+      </c>
+      <c r="E119" t="s">
+        <v>217</v>
+      </c>
+      <c r="F119" t="s">
+        <v>218</v>
+      </c>
+      <c r="G119" t="s">
         <v>439</v>
-      </c>
-      <c r="E119" t="s">
-        <v>218</v>
-      </c>
-      <c r="F119" t="s">
-        <v>219</v>
-      </c>
-      <c r="G119" t="s">
-        <v>440</v>
       </c>
       <c r="H119" t="s">
         <v>5</v>
@@ -4658,22 +4652,22 @@
     </row>
     <row r="120" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A120" t="s">
-        <v>441</v>
+        <v>440</v>
       </c>
       <c r="C120" t="s">
         <v>13</v>
       </c>
       <c r="D120" t="s">
+        <v>441</v>
+      </c>
+      <c r="E120" t="s">
+        <v>78</v>
+      </c>
+      <c r="F120" t="s">
+        <v>79</v>
+      </c>
+      <c r="G120" t="s">
         <v>442</v>
-      </c>
-      <c r="E120" t="s">
-        <v>79</v>
-      </c>
-      <c r="F120" t="s">
-        <v>80</v>
-      </c>
-      <c r="G120" t="s">
-        <v>443</v>
       </c>
       <c r="H120" t="s">
         <v>5</v>
@@ -4681,22 +4675,22 @@
     </row>
     <row r="121" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A121" t="s">
-        <v>444</v>
+        <v>443</v>
       </c>
       <c r="C121" t="s">
         <v>13</v>
       </c>
       <c r="D121" t="s">
+        <v>441</v>
+      </c>
+      <c r="E121" t="s">
+        <v>78</v>
+      </c>
+      <c r="F121" t="s">
+        <v>79</v>
+      </c>
+      <c r="G121" t="s">
         <v>442</v>
-      </c>
-      <c r="E121" t="s">
-        <v>79</v>
-      </c>
-      <c r="F121" t="s">
-        <v>80</v>
-      </c>
-      <c r="G121" t="s">
-        <v>443</v>
       </c>
       <c r="H121" t="s">
         <v>5</v>
@@ -4704,22 +4698,22 @@
     </row>
     <row r="122" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A122" t="s">
+        <v>444</v>
+      </c>
+      <c r="C122" t="s">
+        <v>164</v>
+      </c>
+      <c r="D122" t="s">
         <v>445</v>
       </c>
-      <c r="C122" t="s">
-        <v>165</v>
-      </c>
-      <c r="D122" t="s">
+      <c r="E122" t="s">
         <v>446</v>
       </c>
-      <c r="E122" t="s">
+      <c r="F122" t="s">
+        <v>0</v>
+      </c>
+      <c r="G122" t="s">
         <v>447</v>
-      </c>
-      <c r="F122" t="s">
-        <v>0</v>
-      </c>
-      <c r="G122" t="s">
-        <v>448</v>
       </c>
       <c r="H122" t="s">
         <v>5</v>
@@ -4727,22 +4721,22 @@
     </row>
     <row r="123" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A123" t="s">
+        <v>448</v>
+      </c>
+      <c r="C123" t="s">
+        <v>164</v>
+      </c>
+      <c r="D123" t="s">
         <v>449</v>
       </c>
-      <c r="C123" t="s">
-        <v>165</v>
-      </c>
-      <c r="D123" t="s">
+      <c r="E123" t="s">
         <v>450</v>
       </c>
-      <c r="E123" t="s">
+      <c r="F123" t="s">
+        <v>0</v>
+      </c>
+      <c r="G123" t="s">
         <v>451</v>
-      </c>
-      <c r="F123" t="s">
-        <v>0</v>
-      </c>
-      <c r="G123" t="s">
-        <v>452</v>
       </c>
       <c r="H123" t="s">
         <v>5</v>
@@ -4750,13 +4744,13 @@
     </row>
     <row r="124" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A124" t="s">
-        <v>453</v>
+        <v>452</v>
       </c>
       <c r="C124" t="s">
         <v>53</v>
       </c>
       <c r="D124" t="s">
-        <v>454</v>
+        <v>453</v>
       </c>
       <c r="E124" t="s">
         <v>25</v>
@@ -4765,7 +4759,7 @@
         <v>0</v>
       </c>
       <c r="G124" t="s">
-        <v>455</v>
+        <v>454</v>
       </c>
       <c r="H124" t="s">
         <v>5</v>
@@ -4773,13 +4767,13 @@
     </row>
     <row r="125" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A125" t="s">
-        <v>456</v>
+        <v>455</v>
       </c>
       <c r="C125" t="s">
         <v>2</v>
       </c>
       <c r="D125" t="s">
-        <v>457</v>
+        <v>456</v>
       </c>
       <c r="E125" t="s">
         <v>14</v>
@@ -4788,7 +4782,7 @@
         <v>0</v>
       </c>
       <c r="G125" t="s">
-        <v>458</v>
+        <v>457</v>
       </c>
       <c r="H125" t="s">
         <v>5</v>
@@ -4796,22 +4790,22 @@
     </row>
     <row r="126" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A126" t="s">
-        <v>459</v>
+        <v>458</v>
       </c>
       <c r="C126" t="s">
         <v>58</v>
       </c>
       <c r="D126" t="s">
+        <v>459</v>
+      </c>
+      <c r="E126" t="s">
+        <v>82</v>
+      </c>
+      <c r="F126" t="s">
+        <v>83</v>
+      </c>
+      <c r="G126" t="s">
         <v>460</v>
-      </c>
-      <c r="E126" t="s">
-        <v>83</v>
-      </c>
-      <c r="F126" t="s">
-        <v>84</v>
-      </c>
-      <c r="G126" t="s">
-        <v>461</v>
       </c>
       <c r="H126" t="s">
         <v>5</v>
@@ -4819,22 +4813,22 @@
     </row>
     <row r="127" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A127" t="s">
-        <v>462</v>
+        <v>461</v>
       </c>
       <c r="C127" t="s">
         <v>9</v>
       </c>
       <c r="D127" t="s">
+        <v>462</v>
+      </c>
+      <c r="E127" t="s">
+        <v>283</v>
+      </c>
+      <c r="F127" t="s">
+        <v>0</v>
+      </c>
+      <c r="G127" t="s">
         <v>463</v>
-      </c>
-      <c r="E127" t="s">
-        <v>284</v>
-      </c>
-      <c r="F127" t="s">
-        <v>0</v>
-      </c>
-      <c r="G127" t="s">
-        <v>464</v>
       </c>
       <c r="H127" t="s">
         <v>5</v>
@@ -4842,22 +4836,22 @@
     </row>
     <row r="128" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A128" t="s">
-        <v>465</v>
+        <v>464</v>
       </c>
       <c r="C128" t="s">
         <v>2</v>
       </c>
       <c r="D128" t="s">
+        <v>465</v>
+      </c>
+      <c r="E128" t="s">
         <v>466</v>
       </c>
-      <c r="E128" t="s">
+      <c r="F128" t="s">
+        <v>0</v>
+      </c>
+      <c r="G128" t="s">
         <v>467</v>
-      </c>
-      <c r="F128" t="s">
-        <v>0</v>
-      </c>
-      <c r="G128" t="s">
-        <v>468</v>
       </c>
       <c r="H128" t="s">
         <v>5</v>
@@ -4865,13 +4859,13 @@
     </row>
     <row r="129" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A129" t="s">
+        <v>468</v>
+      </c>
+      <c r="C129" t="s">
+        <v>392</v>
+      </c>
+      <c r="D129" t="s">
         <v>469</v>
-      </c>
-      <c r="C129" t="s">
-        <v>393</v>
-      </c>
-      <c r="D129" t="s">
-        <v>470</v>
       </c>
       <c r="E129" t="s">
         <v>51</v>
@@ -4880,7 +4874,7 @@
         <v>0</v>
       </c>
       <c r="G129" t="s">
-        <v>471</v>
+        <v>470</v>
       </c>
       <c r="H129" t="s">
         <v>5</v>
@@ -4888,22 +4882,22 @@
     </row>
     <row r="130" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A130" t="s">
-        <v>472</v>
+        <v>471</v>
       </c>
       <c r="C130" t="s">
         <v>8</v>
       </c>
       <c r="D130" t="s">
+        <v>472</v>
+      </c>
+      <c r="E130" t="s">
+        <v>380</v>
+      </c>
+      <c r="F130" t="s">
+        <v>0</v>
+      </c>
+      <c r="G130" t="s">
         <v>473</v>
-      </c>
-      <c r="E130" t="s">
-        <v>381</v>
-      </c>
-      <c r="F130" t="s">
-        <v>0</v>
-      </c>
-      <c r="G130" t="s">
-        <v>474</v>
       </c>
       <c r="H130" t="s">
         <v>5</v>
@@ -4911,22 +4905,22 @@
     </row>
     <row r="131" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A131" t="s">
+        <v>474</v>
+      </c>
+      <c r="C131" t="s">
+        <v>151</v>
+      </c>
+      <c r="D131" t="s">
         <v>475</v>
       </c>
-      <c r="C131" t="s">
-        <v>152</v>
-      </c>
-      <c r="D131" t="s">
+      <c r="E131" t="s">
+        <v>384</v>
+      </c>
+      <c r="F131" t="s">
+        <v>0</v>
+      </c>
+      <c r="G131" t="s">
         <v>476</v>
-      </c>
-      <c r="E131" t="s">
-        <v>385</v>
-      </c>
-      <c r="F131" t="s">
-        <v>0</v>
-      </c>
-      <c r="G131" t="s">
-        <v>477</v>
       </c>
       <c r="H131" t="s">
         <v>5</v>
@@ -4934,22 +4928,22 @@
     </row>
     <row r="132" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A132" t="s">
-        <v>478</v>
+        <v>477</v>
       </c>
       <c r="C132" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="D132" t="s">
+        <v>475</v>
+      </c>
+      <c r="E132" t="s">
+        <v>384</v>
+      </c>
+      <c r="F132" t="s">
+        <v>0</v>
+      </c>
+      <c r="G132" t="s">
         <v>476</v>
-      </c>
-      <c r="E132" t="s">
-        <v>385</v>
-      </c>
-      <c r="F132" t="s">
-        <v>0</v>
-      </c>
-      <c r="G132" t="s">
-        <v>477</v>
       </c>
       <c r="H132" t="s">
         <v>5</v>
@@ -4957,22 +4951,22 @@
     </row>
     <row r="133" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A133" t="s">
-        <v>479</v>
+        <v>478</v>
       </c>
       <c r="C133" t="s">
         <v>58</v>
       </c>
       <c r="D133" t="s">
+        <v>479</v>
+      </c>
+      <c r="E133" t="s">
+        <v>306</v>
+      </c>
+      <c r="F133" t="s">
+        <v>0</v>
+      </c>
+      <c r="G133" t="s">
         <v>480</v>
-      </c>
-      <c r="E133" t="s">
-        <v>307</v>
-      </c>
-      <c r="F133" t="s">
-        <v>0</v>
-      </c>
-      <c r="G133" t="s">
-        <v>481</v>
       </c>
       <c r="H133" t="s">
         <v>5</v>
@@ -4980,22 +4974,22 @@
     </row>
     <row r="134" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A134" t="s">
-        <v>482</v>
+        <v>481</v>
       </c>
       <c r="C134" t="s">
         <v>58</v>
       </c>
       <c r="D134" t="s">
+        <v>482</v>
+      </c>
+      <c r="E134" t="s">
+        <v>418</v>
+      </c>
+      <c r="F134" t="s">
+        <v>0</v>
+      </c>
+      <c r="G134" t="s">
         <v>483</v>
-      </c>
-      <c r="E134" t="s">
-        <v>419</v>
-      </c>
-      <c r="F134" t="s">
-        <v>0</v>
-      </c>
-      <c r="G134" t="s">
-        <v>484</v>
       </c>
       <c r="H134" t="s">
         <v>5</v>
@@ -5003,13 +4997,13 @@
     </row>
     <row r="135" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A135" t="s">
-        <v>485</v>
+        <v>484</v>
       </c>
       <c r="C135" t="s">
         <v>8</v>
       </c>
       <c r="D135" t="s">
-        <v>486</v>
+        <v>485</v>
       </c>
       <c r="E135" t="s">
         <v>31</v>
@@ -5018,7 +5012,7 @@
         <v>32</v>
       </c>
       <c r="G135" t="s">
-        <v>487</v>
+        <v>486</v>
       </c>
       <c r="H135" t="s">
         <v>5</v>
@@ -5026,22 +5020,22 @@
     </row>
     <row r="136" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A136" t="s">
+        <v>487</v>
+      </c>
+      <c r="C136" t="s">
+        <v>13</v>
+      </c>
+      <c r="D136" t="s">
         <v>488</v>
       </c>
-      <c r="C136" t="s">
-        <v>10</v>
-      </c>
-      <c r="D136" t="s">
+      <c r="E136" t="s">
+        <v>60</v>
+      </c>
+      <c r="F136" t="s">
+        <v>61</v>
+      </c>
+      <c r="G136" t="s">
         <v>489</v>
-      </c>
-      <c r="E136" t="s">
-        <v>75</v>
-      </c>
-      <c r="F136" t="s">
-        <v>0</v>
-      </c>
-      <c r="G136" t="s">
-        <v>490</v>
       </c>
       <c r="H136" t="s">
         <v>5</v>
@@ -5049,13 +5043,13 @@
     </row>
     <row r="137" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A137" t="s">
-        <v>491</v>
+        <v>490</v>
       </c>
       <c r="C137" t="s">
         <v>13</v>
       </c>
       <c r="D137" t="s">
-        <v>492</v>
+        <v>488</v>
       </c>
       <c r="E137" t="s">
         <v>60</v>
@@ -5064,7 +5058,7 @@
         <v>61</v>
       </c>
       <c r="G137" t="s">
-        <v>493</v>
+        <v>489</v>
       </c>
       <c r="H137" t="s">
         <v>5</v>
@@ -5072,7 +5066,7 @@
     </row>
     <row r="138" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A138" t="s">
-        <v>494</v>
+        <v>491</v>
       </c>
       <c r="C138" t="s">
         <v>13</v>
@@ -5081,10 +5075,10 @@
         <v>492</v>
       </c>
       <c r="E138" t="s">
-        <v>60</v>
+        <v>15</v>
       </c>
       <c r="F138" t="s">
-        <v>61</v>
+        <v>16</v>
       </c>
       <c r="G138" t="s">
         <v>493</v>
@@ -5095,13 +5089,13 @@
     </row>
     <row r="139" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A139" t="s">
-        <v>495</v>
+        <v>494</v>
       </c>
       <c r="C139" t="s">
         <v>13</v>
       </c>
       <c r="D139" t="s">
-        <v>496</v>
+        <v>492</v>
       </c>
       <c r="E139" t="s">
         <v>15</v>
@@ -5110,7 +5104,7 @@
         <v>16</v>
       </c>
       <c r="G139" t="s">
-        <v>497</v>
+        <v>493</v>
       </c>
       <c r="H139" t="s">
         <v>5</v>
@@ -5118,13 +5112,13 @@
     </row>
     <row r="140" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A140" t="s">
-        <v>498</v>
+        <v>495</v>
       </c>
       <c r="C140" t="s">
         <v>13</v>
       </c>
       <c r="D140" t="s">
-        <v>496</v>
+        <v>492</v>
       </c>
       <c r="E140" t="s">
         <v>15</v>
@@ -5133,7 +5127,7 @@
         <v>16</v>
       </c>
       <c r="G140" t="s">
-        <v>497</v>
+        <v>493</v>
       </c>
       <c r="H140" t="s">
         <v>5</v>
@@ -5141,13 +5135,13 @@
     </row>
     <row r="141" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A141" t="s">
-        <v>499</v>
+        <v>496</v>
       </c>
       <c r="C141" t="s">
         <v>13</v>
       </c>
       <c r="D141" t="s">
-        <v>496</v>
+        <v>492</v>
       </c>
       <c r="E141" t="s">
         <v>15</v>
@@ -5156,7 +5150,7 @@
         <v>16</v>
       </c>
       <c r="G141" t="s">
-        <v>497</v>
+        <v>493</v>
       </c>
       <c r="H141" t="s">
         <v>5</v>
@@ -5164,13 +5158,13 @@
     </row>
     <row r="142" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A142" t="s">
-        <v>500</v>
+        <v>497</v>
       </c>
       <c r="C142" t="s">
         <v>13</v>
       </c>
       <c r="D142" t="s">
-        <v>496</v>
+        <v>492</v>
       </c>
       <c r="E142" t="s">
         <v>15</v>
@@ -5179,7 +5173,7 @@
         <v>16</v>
       </c>
       <c r="G142" t="s">
-        <v>497</v>
+        <v>493</v>
       </c>
       <c r="H142" t="s">
         <v>5</v>
@@ -5187,22 +5181,22 @@
     </row>
     <row r="143" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A143" t="s">
-        <v>501</v>
+        <v>498</v>
       </c>
       <c r="C143" t="s">
-        <v>13</v>
+        <v>189</v>
       </c>
       <c r="D143" t="s">
-        <v>496</v>
+        <v>499</v>
       </c>
       <c r="E143" t="s">
-        <v>15</v>
+        <v>52</v>
       </c>
       <c r="F143" t="s">
-        <v>16</v>
+        <v>0</v>
       </c>
       <c r="G143" t="s">
-        <v>497</v>
+        <v>500</v>
       </c>
       <c r="H143" t="s">
         <v>5</v>
@@ -5210,22 +5204,22 @@
     </row>
     <row r="144" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A144" t="s">
+        <v>501</v>
+      </c>
+      <c r="C144" t="s">
+        <v>91</v>
+      </c>
+      <c r="D144" t="s">
         <v>502</v>
       </c>
-      <c r="C144" t="s">
-        <v>190</v>
-      </c>
-      <c r="D144" t="s">
+      <c r="E144" t="s">
         <v>503</v>
       </c>
-      <c r="E144" t="s">
-        <v>52</v>
-      </c>
       <c r="F144" t="s">
-        <v>0</v>
+        <v>504</v>
       </c>
       <c r="G144" t="s">
-        <v>504</v>
+        <v>149</v>
       </c>
       <c r="H144" t="s">
         <v>5</v>
@@ -5236,19 +5230,19 @@
         <v>505</v>
       </c>
       <c r="C145" t="s">
-        <v>92</v>
+        <v>151</v>
       </c>
       <c r="D145" t="s">
         <v>506</v>
       </c>
       <c r="E145" t="s">
+        <v>153</v>
+      </c>
+      <c r="F145" t="s">
+        <v>0</v>
+      </c>
+      <c r="G145" t="s">
         <v>507</v>
-      </c>
-      <c r="F145" t="s">
-        <v>508</v>
-      </c>
-      <c r="G145" t="s">
-        <v>150</v>
       </c>
       <c r="H145" t="s">
         <v>5</v>
@@ -5256,90 +5250,81 @@
     </row>
     <row r="146" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A146" t="s">
+        <v>508</v>
+      </c>
+      <c r="C146" t="s">
+        <v>13</v>
+      </c>
+      <c r="D146" t="s">
         <v>509</v>
       </c>
-      <c r="C146" t="s">
-        <v>152</v>
-      </c>
-      <c r="D146" t="s">
+      <c r="E146" t="s">
         <v>510</v>
       </c>
-      <c r="E146" t="s">
-        <v>154</v>
-      </c>
       <c r="F146" t="s">
-        <v>0</v>
+        <v>511</v>
       </c>
       <c r="G146" t="s">
-        <v>511</v>
+        <v>512</v>
       </c>
       <c r="H146" t="s">
-        <v>5</v>
+        <v>513</v>
       </c>
     </row>
     <row r="147" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A147" t="s">
-        <v>512</v>
+        <v>514</v>
       </c>
       <c r="C147" t="s">
         <v>13</v>
       </c>
       <c r="D147" t="s">
+        <v>509</v>
+      </c>
+      <c r="E147" t="s">
+        <v>510</v>
+      </c>
+      <c r="F147" t="s">
+        <v>511</v>
+      </c>
+      <c r="G147" t="s">
+        <v>512</v>
+      </c>
+      <c r="H147" t="s">
         <v>513</v>
-      </c>
-      <c r="E147" t="s">
-        <v>514</v>
-      </c>
-      <c r="F147" t="s">
-        <v>515</v>
-      </c>
-      <c r="G147" t="s">
-        <v>516</v>
-      </c>
-      <c r="H147" t="s">
-        <v>517</v>
       </c>
     </row>
     <row r="148" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A148" t="s">
-        <v>518</v>
+        <v>515</v>
       </c>
       <c r="C148" t="s">
         <v>13</v>
       </c>
       <c r="D148" t="s">
+        <v>509</v>
+      </c>
+      <c r="E148" t="s">
+        <v>510</v>
+      </c>
+      <c r="F148" t="s">
+        <v>511</v>
+      </c>
+      <c r="G148" t="s">
+        <v>512</v>
+      </c>
+      <c r="H148" t="s">
         <v>513</v>
-      </c>
-      <c r="E148" t="s">
-        <v>514</v>
-      </c>
-      <c r="F148" t="s">
-        <v>515</v>
-      </c>
-      <c r="G148" t="s">
-        <v>516</v>
-      </c>
-      <c r="H148" t="s">
-        <v>517</v>
       </c>
     </row>
     <row r="149" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A149" t="s">
-        <v>519</v>
+        <v>516</v>
       </c>
       <c r="C149" t="s">
-        <v>13</v>
+        <v>99</v>
       </c>
       <c r="D149" t="s">
-        <v>513</v>
-      </c>
-      <c r="E149" t="s">
-        <v>514</v>
-      </c>
-      <c r="F149" t="s">
-        <v>515</v>
-      </c>
-      <c r="G149" t="s">
         <v>516</v>
       </c>
       <c r="H149" t="s">

--- a/1.xlsx
+++ b/1.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="\\wh.local\fs\UserProfile_TSSWH19\_TSSWH19_redirected_folders\HunyaCs1\Desktop\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A6AEC489-0282-4478-B520-2C53E328996D}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B0CD7A01-8044-4800-87D0-7EF5121E50F1}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="0" windowWidth="22260" windowHeight="12648" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1040" uniqueCount="518">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1469" uniqueCount="729">
   <si>
     <t>BUDAPEST</t>
   </si>
@@ -72,30 +72,18 @@
     <t>SZ-832</t>
   </si>
   <si>
-    <t>1165</t>
-  </si>
-  <si>
     <t>2310</t>
   </si>
   <si>
     <t>SZIGETSZENTMIKLÓS</t>
   </si>
   <si>
-    <t>2330</t>
-  </si>
-  <si>
-    <t>DUNAHARASZTI</t>
-  </si>
-  <si>
     <t>SZ-836</t>
   </si>
   <si>
     <t>SZ-801</t>
   </si>
   <si>
-    <t>SZ-830</t>
-  </si>
-  <si>
     <t>SZ-820</t>
   </si>
   <si>
@@ -105,9 +93,6 @@
     <t>VÁC</t>
   </si>
   <si>
-    <t>1183</t>
-  </si>
-  <si>
     <t>2131</t>
   </si>
   <si>
@@ -120,9 +105,6 @@
     <t>BUDAÖRS</t>
   </si>
   <si>
-    <t>1204</t>
-  </si>
-  <si>
     <t>2030</t>
   </si>
   <si>
@@ -135,9 +117,6 @@
     <t>1221</t>
   </si>
   <si>
-    <t>Dózsa György út</t>
-  </si>
-  <si>
     <t>CSOMAGSZAM</t>
   </si>
   <si>
@@ -159,42 +138,24 @@
     <t>MEGBIZO_ROVIDKOD</t>
   </si>
   <si>
-    <t>1033</t>
-  </si>
-  <si>
     <t>2700</t>
   </si>
   <si>
     <t>CEGLÉD</t>
   </si>
   <si>
-    <t>69c312d7d96b4f4a243861f2</t>
-  </si>
-  <si>
-    <t>260324-W00011106</t>
-  </si>
-  <si>
-    <t>Folyamőr utca</t>
-  </si>
-  <si>
     <t>SELEX</t>
   </si>
   <si>
     <t>1146</t>
   </si>
   <si>
-    <t>1028</t>
-  </si>
-  <si>
     <t>1151</t>
   </si>
   <si>
     <t>SZ-814</t>
   </si>
   <si>
-    <t>1131</t>
-  </si>
-  <si>
     <t>2730</t>
   </si>
   <si>
@@ -204,9 +165,6 @@
     <t>1037</t>
   </si>
   <si>
-    <t>SZ-835</t>
-  </si>
-  <si>
     <t>1107</t>
   </si>
   <si>
@@ -216,66 +174,15 @@
     <t>SZIGETHALOM</t>
   </si>
   <si>
-    <t>MEGAPLACE</t>
-  </si>
-  <si>
-    <t>1112</t>
-  </si>
-  <si>
-    <t>305273127/1</t>
-  </si>
-  <si>
-    <t>305273127</t>
-  </si>
-  <si>
-    <t>Komp utca</t>
-  </si>
-  <si>
-    <t>305273127/2</t>
-  </si>
-  <si>
-    <t>305273127/3</t>
-  </si>
-  <si>
-    <t>Kossuth Lajos utca</t>
-  </si>
-  <si>
-    <t>1142</t>
-  </si>
-  <si>
-    <t>1172</t>
-  </si>
-  <si>
-    <t>Hidasnémeti utca</t>
-  </si>
-  <si>
-    <t>1135</t>
-  </si>
-  <si>
-    <t>1046</t>
-  </si>
-  <si>
-    <t>1054</t>
-  </si>
-  <si>
     <t>2083</t>
   </si>
   <si>
     <t>SOLYMÁR</t>
   </si>
   <si>
-    <t>2337</t>
-  </si>
-  <si>
-    <t>DÉLEGYHÁZA</t>
-  </si>
-  <si>
     <t>1164</t>
   </si>
   <si>
-    <t>Jókai Mór utca</t>
-  </si>
-  <si>
     <t>2013</t>
   </si>
   <si>
@@ -285,240 +192,33 @@
     <t>1084</t>
   </si>
   <si>
-    <t>248745137/1</t>
-  </si>
-  <si>
-    <t>248745137</t>
-  </si>
-  <si>
-    <t>Laky Adolf utca</t>
-  </si>
-  <si>
-    <t>248745137/2</t>
-  </si>
-  <si>
-    <t>248745137/3</t>
-  </si>
-  <si>
-    <t>69c51fe2d96b4f4a243880e3</t>
-  </si>
-  <si>
     <t>SZ-828</t>
   </si>
   <si>
-    <t>260305-F00013849-1</t>
-  </si>
-  <si>
-    <t>Varsa köz</t>
-  </si>
-  <si>
-    <t>69c10f9dd96b4f4a2438383b</t>
-  </si>
-  <si>
-    <t>260316-F00010130</t>
-  </si>
-  <si>
-    <t>1034</t>
-  </si>
-  <si>
-    <t>Bécsi út</t>
-  </si>
-  <si>
-    <t>69bac3ecd96b4f4a2437ec51</t>
-  </si>
-  <si>
-    <t>SZ-809</t>
-  </si>
-  <si>
-    <t>260318-F00011706</t>
-  </si>
-  <si>
-    <t>2253</t>
-  </si>
-  <si>
-    <t>TÁPIÓSÁG</t>
-  </si>
-  <si>
-    <t>Forgács utca</t>
-  </si>
-  <si>
-    <t>69c2ba7ed96b4f4a24385de2</t>
-  </si>
-  <si>
-    <t>260320-F00012558</t>
-  </si>
-  <si>
     <t>1214</t>
   </si>
   <si>
-    <t>Szent István út</t>
-  </si>
-  <si>
-    <t>69c63d28d96b4f4a24388da2</t>
-  </si>
-  <si>
-    <t>260323-F00011559</t>
-  </si>
-  <si>
     <t>1203</t>
   </si>
   <si>
-    <t>Baross utca</t>
-  </si>
-  <si>
-    <t>69c3fe6bd96b4f4a2438728b</t>
-  </si>
-  <si>
-    <t>260325-F00011314</t>
-  </si>
-  <si>
-    <t>Patkó utca</t>
-  </si>
-  <si>
-    <t>69c40317d96b4f4a24387301</t>
-  </si>
-  <si>
-    <t>260325-F00011584</t>
-  </si>
-  <si>
-    <t>Völgy utca</t>
-  </si>
-  <si>
-    <t>69c40317d96b4f4a24387304</t>
-  </si>
-  <si>
-    <t>69c3fb18d96b4f4a2438722b</t>
-  </si>
-  <si>
-    <t>260325-W00006456</t>
-  </si>
-  <si>
-    <t>Rákóczi út</t>
-  </si>
-  <si>
-    <t>69c40d6bd96b4f4a243873ff</t>
-  </si>
-  <si>
-    <t>260325-W00006951</t>
-  </si>
-  <si>
-    <t>Diófa utca</t>
-  </si>
-  <si>
-    <t>69c40d6bd96b4f4a24387401</t>
-  </si>
-  <si>
-    <t>69c4069ad96b4f4a2438735b</t>
-  </si>
-  <si>
-    <t>260325-W00007033</t>
-  </si>
-  <si>
-    <t>2135</t>
-  </si>
-  <si>
-    <t>CSÖRÖG</t>
-  </si>
-  <si>
-    <t>Komáromi utca</t>
-  </si>
-  <si>
-    <t>69c4ea28d96b4f4a2438794c</t>
-  </si>
-  <si>
-    <t>260326-F00000925</t>
-  </si>
-  <si>
-    <t>2711</t>
-  </si>
-  <si>
-    <t>TÁPIÓSZENTMÁRTON</t>
-  </si>
-  <si>
-    <t>Szelei út</t>
-  </si>
-  <si>
-    <t>69c5015fd96b4f4a24387d1c</t>
-  </si>
-  <si>
-    <t>260326-F00002900</t>
-  </si>
-  <si>
     <t>2360</t>
   </si>
   <si>
     <t>GYÁL</t>
   </si>
   <si>
-    <t>Csontos József utca</t>
-  </si>
-  <si>
-    <t>69c517f7d96b4f4a24388022</t>
-  </si>
-  <si>
-    <t>260326-F00005629</t>
-  </si>
-  <si>
-    <t>2115</t>
-  </si>
-  <si>
-    <t>VÁCSZENTLÁSZLÓ</t>
-  </si>
-  <si>
-    <t>Kossuth utca</t>
-  </si>
-  <si>
-    <t>69c54813d96b4f4a2438865f</t>
-  </si>
-  <si>
-    <t>260326-F00009741</t>
-  </si>
-  <si>
     <t>1184</t>
   </si>
   <si>
-    <t>Rezeda utca</t>
-  </si>
-  <si>
-    <t>69c564fdd96b4f4a2438891f</t>
-  </si>
-  <si>
     <t>SZ-840</t>
   </si>
   <si>
-    <t>260326-F00011628</t>
-  </si>
-  <si>
     <t>1115</t>
   </si>
   <si>
-    <t>Fraknó utca</t>
-  </si>
-  <si>
-    <t>69c564fdd96b4f4a24388920</t>
-  </si>
-  <si>
-    <t>69c4f95dd96b4f4a24387bbe</t>
-  </si>
-  <si>
-    <t>260326-W00002321</t>
-  </si>
-  <si>
-    <t>2371</t>
-  </si>
-  <si>
     <t>DABAS</t>
   </si>
   <si>
-    <t>Madách Imre utca</t>
-  </si>
-  <si>
-    <t>69c5399ed96b4f4a24388479</t>
-  </si>
-  <si>
-    <t>260326-W00005763</t>
-  </si>
-  <si>
     <t>69c53e4cd96b4f4a2438851a</t>
   </si>
   <si>
@@ -534,198 +234,30 @@
     <t>Csalogány utca</t>
   </si>
   <si>
-    <t>69c53e54d96b4f4a2438852f</t>
-  </si>
-  <si>
-    <t>260326-W00006020</t>
-  </si>
-  <si>
-    <t>1026</t>
-  </si>
-  <si>
-    <t>Pasaréti út</t>
-  </si>
-  <si>
-    <t>69c65c43d96b4f4a24389233</t>
-  </si>
-  <si>
-    <t>260327-F00003672</t>
-  </si>
-  <si>
-    <t>Felsőmalom utca</t>
-  </si>
-  <si>
-    <t>69c665c7d96b4f4a24389385</t>
-  </si>
-  <si>
-    <t>260327-W00002647</t>
-  </si>
-  <si>
-    <t>1239</t>
-  </si>
-  <si>
-    <t>Péter Apostol utca</t>
-  </si>
-  <si>
-    <t>69c665c7d96b4f4a24389386</t>
-  </si>
-  <si>
-    <t>69c665c7d96b4f4a2438938a</t>
-  </si>
-  <si>
-    <t>69c65d6cd96b4f4a24389253</t>
-  </si>
-  <si>
-    <t>260327-W00002989</t>
-  </si>
-  <si>
     <t>1126</t>
   </si>
   <si>
-    <t>Böszörményi út</t>
-  </si>
-  <si>
-    <t>FIZZ-1000849440</t>
-  </si>
-  <si>
-    <t>267004499</t>
-  </si>
-  <si>
-    <t>Kalman Imre utca</t>
-  </si>
-  <si>
-    <t>FIZZ-1000850493</t>
-  </si>
-  <si>
     <t>SZ-818</t>
   </si>
   <si>
-    <t>267004502</t>
-  </si>
-  <si>
     <t>1044</t>
   </si>
   <si>
     <t>Megyeri út</t>
   </si>
   <si>
-    <t>26MPE0003367/1</t>
-  </si>
-  <si>
-    <t>26MPE0003367</t>
-  </si>
-  <si>
-    <t>Ady Endre tér</t>
-  </si>
-  <si>
-    <t>26MPE0003369/1</t>
-  </si>
-  <si>
-    <t>26MPE0003369</t>
-  </si>
-  <si>
     <t>1096</t>
   </si>
   <si>
-    <t>Sobieski János utca</t>
-  </si>
-  <si>
-    <t>26MPE0003399/1</t>
-  </si>
-  <si>
-    <t>26MPE0003399</t>
-  </si>
-  <si>
-    <t>303005689/1</t>
-  </si>
-  <si>
-    <t>303005689</t>
-  </si>
-  <si>
-    <t>Termálfürdő körút</t>
-  </si>
-  <si>
-    <t>304362671/1</t>
-  </si>
-  <si>
-    <t>304362671</t>
-  </si>
-  <si>
     <t>1089</t>
   </si>
   <si>
-    <t>Delej utca</t>
-  </si>
-  <si>
-    <t>304362671/2</t>
-  </si>
-  <si>
-    <t>304826827/1</t>
-  </si>
-  <si>
-    <t>304826827</t>
-  </si>
-  <si>
-    <t>1153</t>
-  </si>
-  <si>
-    <t>Bocskai Utca</t>
-  </si>
-  <si>
-    <t>304826827/2</t>
-  </si>
-  <si>
-    <t>305170764/1</t>
-  </si>
-  <si>
-    <t>305170764</t>
-  </si>
-  <si>
-    <t>2045</t>
-  </si>
-  <si>
-    <t>TÖRÖKBÁLINT</t>
-  </si>
-  <si>
-    <t>Kinizsi Pál</t>
-  </si>
-  <si>
-    <t>305273366/1</t>
-  </si>
-  <si>
-    <t>305273366</t>
-  </si>
-  <si>
-    <t>Fecske utca</t>
-  </si>
-  <si>
-    <t>305315270/1</t>
-  </si>
-  <si>
-    <t>305315270</t>
-  </si>
-  <si>
     <t>2100</t>
   </si>
   <si>
     <t>GÖDÖLLŐ</t>
   </si>
   <si>
-    <t>Szív utca</t>
-  </si>
-  <si>
-    <t>305368730/1</t>
-  </si>
-  <si>
-    <t>305368730</t>
-  </si>
-  <si>
-    <t>1143</t>
-  </si>
-  <si>
-    <t>Zászlós utca</t>
-  </si>
-  <si>
     <t>305412140/1</t>
   </si>
   <si>
@@ -738,330 +270,42 @@
     <t>Bosnyák tér</t>
   </si>
   <si>
-    <t>305412442/1</t>
-  </si>
-  <si>
-    <t>305412442</t>
-  </si>
-  <si>
-    <t>305412442/2</t>
-  </si>
-  <si>
-    <t>305412442/3</t>
-  </si>
-  <si>
-    <t>305557165/1</t>
-  </si>
-  <si>
-    <t>305557165</t>
-  </si>
-  <si>
     <t>2230</t>
   </si>
   <si>
     <t>GYÖMRŐ</t>
   </si>
   <si>
-    <t>305557165/2</t>
-  </si>
-  <si>
-    <t>305557165/3</t>
-  </si>
-  <si>
-    <t>305557278/1</t>
-  </si>
-  <si>
-    <t>305557278</t>
-  </si>
-  <si>
-    <t>Rodostó utca</t>
-  </si>
-  <si>
-    <t>305557328/1</t>
-  </si>
-  <si>
-    <t>305557328</t>
-  </si>
-  <si>
     <t>1215</t>
   </si>
   <si>
     <t>Árpád utca</t>
   </si>
   <si>
-    <t>305557328/2</t>
-  </si>
-  <si>
-    <t>305557362/1</t>
-  </si>
-  <si>
-    <t>305557362</t>
-  </si>
-  <si>
-    <t>Panoráma utca</t>
-  </si>
-  <si>
-    <t>305557428/1</t>
-  </si>
-  <si>
-    <t>305557428</t>
-  </si>
-  <si>
-    <t>Munkácsy Mihály utca</t>
-  </si>
-  <si>
-    <t>305557555/1</t>
-  </si>
-  <si>
-    <t>305557555</t>
-  </si>
-  <si>
-    <t>Huszti út</t>
-  </si>
-  <si>
-    <t>305557595/1</t>
-  </si>
-  <si>
-    <t>305557595</t>
-  </si>
-  <si>
-    <t>Szendrő utca</t>
-  </si>
-  <si>
-    <t>305557799/1</t>
-  </si>
-  <si>
-    <t>305557799</t>
-  </si>
-  <si>
     <t>1025</t>
   </si>
   <si>
-    <t>Csévi utca</t>
-  </si>
-  <si>
-    <t>305557863/1</t>
-  </si>
-  <si>
-    <t>305557863</t>
-  </si>
-  <si>
-    <t>1077</t>
-  </si>
-  <si>
-    <t>Wesselényi Utca</t>
-  </si>
-  <si>
-    <t>305557863/2</t>
-  </si>
-  <si>
-    <t>305628078/1</t>
-  </si>
-  <si>
-    <t>305628078</t>
-  </si>
-  <si>
     <t>1117</t>
   </si>
   <si>
-    <t>Bercsényi utca</t>
-  </si>
-  <si>
-    <t>305667060/1</t>
-  </si>
-  <si>
-    <t>305667060</t>
-  </si>
-  <si>
-    <t>305667073/1</t>
-  </si>
-  <si>
-    <t>305667073</t>
-  </si>
-  <si>
     <t>1021</t>
   </si>
   <si>
-    <t>Széher út</t>
-  </si>
-  <si>
-    <t>305667073/2</t>
-  </si>
-  <si>
-    <t>305667073/3</t>
-  </si>
-  <si>
-    <t>305667629/1</t>
-  </si>
-  <si>
-    <t>305667629</t>
-  </si>
-  <si>
-    <t>2612</t>
-  </si>
-  <si>
-    <t>KOSD</t>
-  </si>
-  <si>
     <t>Bocskai utca</t>
   </si>
   <si>
-    <t>305667629/2</t>
-  </si>
-  <si>
-    <t>305667629/3</t>
-  </si>
-  <si>
-    <t>305667736/1</t>
-  </si>
-  <si>
-    <t>305667736</t>
-  </si>
-  <si>
     <t>1141</t>
   </si>
   <si>
-    <t>Csernyus utca</t>
-  </si>
-  <si>
-    <t>305667736/2</t>
-  </si>
-  <si>
-    <t>305667790/1</t>
-  </si>
-  <si>
-    <t>305667790</t>
-  </si>
-  <si>
-    <t>2009</t>
-  </si>
-  <si>
-    <t>PILISSZENTLÁSZLÓ</t>
-  </si>
-  <si>
-    <t>Rózsahegy utca</t>
-  </si>
-  <si>
-    <t>305725457/1</t>
-  </si>
-  <si>
-    <t>305725457</t>
-  </si>
-  <si>
     <t>1039</t>
   </si>
   <si>
-    <t>Víziorgona utca</t>
-  </si>
-  <si>
-    <t>305725479/1</t>
-  </si>
-  <si>
-    <t>305725479</t>
-  </si>
-  <si>
-    <t>Csepeli .</t>
-  </si>
-  <si>
-    <t>305725539/1</t>
-  </si>
-  <si>
-    <t>305725539</t>
-  </si>
-  <si>
-    <t>Bláthy Ottó utca</t>
-  </si>
-  <si>
-    <t>305725744/1</t>
-  </si>
-  <si>
-    <t>305725744</t>
-  </si>
-  <si>
     <t>Rózsa utca</t>
   </si>
   <si>
-    <t>305725906/1</t>
-  </si>
-  <si>
-    <t>305725906</t>
-  </si>
-  <si>
-    <t>Viola Utca</t>
-  </si>
-  <si>
-    <t>305725937/1</t>
-  </si>
-  <si>
-    <t>305725937</t>
-  </si>
-  <si>
-    <t>1156</t>
-  </si>
-  <si>
-    <t>Nyírpalota út</t>
-  </si>
-  <si>
-    <t>305725937/2</t>
-  </si>
-  <si>
-    <t>305726018/1</t>
-  </si>
-  <si>
-    <t>305726018</t>
-  </si>
-  <si>
     <t>Szövetség utca</t>
   </si>
   <si>
-    <t>305726025/1</t>
-  </si>
-  <si>
-    <t>305726025</t>
-  </si>
-  <si>
-    <t>Gárdonyi Géza utca</t>
-  </si>
-  <si>
-    <t>305726046/1</t>
-  </si>
-  <si>
-    <t>305726046</t>
-  </si>
-  <si>
-    <t>1155</t>
-  </si>
-  <si>
-    <t>Alkotmány utca</t>
-  </si>
-  <si>
-    <t>305726061/1</t>
-  </si>
-  <si>
-    <t>305726061</t>
-  </si>
-  <si>
-    <t>1052</t>
-  </si>
-  <si>
-    <t>Váci utca</t>
-  </si>
-  <si>
-    <t>305726199/1</t>
-  </si>
-  <si>
-    <t>305726199</t>
-  </si>
-  <si>
-    <t>Bethlen Gábor utca</t>
-  </si>
-  <si>
-    <t>305726274/1</t>
-  </si>
-  <si>
-    <t>305726274</t>
-  </si>
-  <si>
     <t>2097</t>
   </si>
   <si>
@@ -1071,517 +315,1906 @@
     <t>Fő utca</t>
   </si>
   <si>
-    <t>305726314/1</t>
-  </si>
-  <si>
-    <t>305726314</t>
-  </si>
-  <si>
-    <t>Eperjesi utca</t>
-  </si>
-  <si>
-    <t>305726314/2</t>
-  </si>
-  <si>
-    <t>305781061/1</t>
-  </si>
-  <si>
-    <t>305781061</t>
-  </si>
-  <si>
-    <t>Lakat utca</t>
-  </si>
-  <si>
-    <t>305781098/1</t>
-  </si>
-  <si>
-    <t>305781098</t>
-  </si>
-  <si>
     <t>Gyöngyvirág utca</t>
   </si>
   <si>
-    <t>305781165/1</t>
-  </si>
-  <si>
-    <t>305781165</t>
-  </si>
-  <si>
-    <t>Thököly út</t>
-  </si>
-  <si>
-    <t>305781182/1</t>
-  </si>
-  <si>
-    <t>305781182</t>
-  </si>
-  <si>
-    <t>2373</t>
-  </si>
-  <si>
-    <t>Vacsi utca</t>
-  </si>
-  <si>
-    <t>305781233/1</t>
-  </si>
-  <si>
-    <t>305781233</t>
-  </si>
-  <si>
     <t>2144</t>
   </si>
   <si>
     <t>KEREPES</t>
   </si>
   <si>
-    <t>Szőlő utca</t>
-  </si>
-  <si>
-    <t>305781305/1</t>
-  </si>
-  <si>
-    <t>305781305</t>
-  </si>
-  <si>
-    <t>Jegenye utca</t>
-  </si>
-  <si>
-    <t>305781359/1</t>
-  </si>
-  <si>
-    <t>305781359</t>
-  </si>
-  <si>
-    <t>Szent Korona útja</t>
-  </si>
-  <si>
-    <t>305781364/1</t>
-  </si>
-  <si>
-    <t>305781364</t>
-  </si>
-  <si>
     <t>Szent László út</t>
   </si>
   <si>
-    <t>305781415/1</t>
-  </si>
-  <si>
-    <t>305781415</t>
-  </si>
-  <si>
     <t>1222</t>
   </si>
   <si>
-    <t>Sörház utca</t>
-  </si>
-  <si>
-    <t>305781653/1</t>
-  </si>
-  <si>
-    <t>305781653</t>
-  </si>
-  <si>
     <t>1116</t>
   </si>
   <si>
-    <t>Kalotaszeg utca</t>
-  </si>
-  <si>
-    <t>305781761/1</t>
-  </si>
-  <si>
-    <t>305781761</t>
-  </si>
-  <si>
-    <t>1201</t>
-  </si>
-  <si>
-    <t>Nagy Győry István köz</t>
-  </si>
-  <si>
-    <t>305781761/2</t>
-  </si>
-  <si>
-    <t>305830800/1</t>
-  </si>
-  <si>
-    <t>SZ-860</t>
-  </si>
-  <si>
-    <t>305830800</t>
-  </si>
-  <si>
-    <t>Árok utca</t>
-  </si>
-  <si>
-    <t>305831416/1</t>
-  </si>
-  <si>
-    <t>305831416</t>
-  </si>
-  <si>
-    <t>2096</t>
-  </si>
-  <si>
-    <t>ÜRÖM</t>
-  </si>
-  <si>
-    <t>Doktor utca</t>
-  </si>
-  <si>
-    <t>305901506/1</t>
-  </si>
-  <si>
-    <t>305901506</t>
-  </si>
-  <si>
-    <t>Sasadi út</t>
-  </si>
-  <si>
-    <t>305901895/1</t>
-  </si>
-  <si>
-    <t>305901895</t>
-  </si>
-  <si>
-    <t>1022</t>
-  </si>
-  <si>
-    <t>Hankóczy Jenő utca</t>
-  </si>
-  <si>
-    <t>305901980/1</t>
-  </si>
-  <si>
-    <t>305901980</t>
-  </si>
-  <si>
-    <t>306026162/1</t>
-  </si>
-  <si>
-    <t>306026162</t>
-  </si>
-  <si>
-    <t>Csillagszem utca</t>
-  </si>
-  <si>
-    <t>306078479/1</t>
-  </si>
-  <si>
-    <t>306078479</t>
-  </si>
-  <si>
-    <t>1101</t>
-  </si>
-  <si>
-    <t>Salgótarjáni utca</t>
-  </si>
-  <si>
-    <t>306078571/1</t>
-  </si>
-  <si>
-    <t>306078571</t>
-  </si>
-  <si>
     <t>1038</t>
   </si>
   <si>
-    <t>Zemplén Győző utca</t>
-  </si>
-  <si>
-    <t>306078571/2</t>
-  </si>
-  <si>
-    <t>306079098/1</t>
-  </si>
-  <si>
-    <t>306079098</t>
-  </si>
-  <si>
-    <t>1103</t>
-  </si>
-  <si>
-    <t>Kis Gergely utca</t>
-  </si>
-  <si>
-    <t>306147203/1</t>
-  </si>
-  <si>
-    <t>306147203</t>
-  </si>
-  <si>
-    <t>Munkás utca</t>
-  </si>
-  <si>
-    <t>306180874/1</t>
-  </si>
-  <si>
-    <t>306180874</t>
-  </si>
-  <si>
-    <t>Cirmos utca</t>
-  </si>
-  <si>
-    <t>306181130/1</t>
-  </si>
-  <si>
-    <t>306181130</t>
-  </si>
-  <si>
-    <t>Fóti utca</t>
-  </si>
-  <si>
-    <t>99002274/1</t>
-  </si>
-  <si>
-    <t>99002274</t>
-  </si>
-  <si>
-    <t>Béke utca</t>
-  </si>
-  <si>
-    <t>202603272600689501</t>
-  </si>
-  <si>
-    <t>NFD6-03-21-4HP6</t>
-  </si>
-  <si>
-    <t>Deák Ferenc utca</t>
-  </si>
-  <si>
-    <t>202603272600696101</t>
-  </si>
-  <si>
-    <t>NFD6-03-22-MBHS</t>
-  </si>
-  <si>
-    <t>Csendes utca</t>
-  </si>
-  <si>
-    <t>202603272600696102</t>
-  </si>
-  <si>
-    <t>202603272600710001</t>
-  </si>
-  <si>
-    <t>NFD6-03-23-2X6M</t>
-  </si>
-  <si>
     <t>1121</t>
   </si>
   <si>
-    <t>Mártonfa utca</t>
-  </si>
-  <si>
-    <t>202603242600710401</t>
-  </si>
-  <si>
-    <t>NFD6-03-23-5RVM</t>
-  </si>
-  <si>
-    <t>1125</t>
-  </si>
-  <si>
-    <t>Zirzen Janka utca</t>
-  </si>
-  <si>
-    <t>202603272600706101</t>
-  </si>
-  <si>
-    <t>NFD6-03-23-FF8R</t>
-  </si>
-  <si>
-    <t>Felsőcsatári út</t>
-  </si>
-  <si>
-    <t>202603262600728101</t>
-  </si>
-  <si>
-    <t>NFD6-03-25-BC8J</t>
-  </si>
-  <si>
-    <t>Koronafürt utca</t>
-  </si>
-  <si>
-    <t>202603262600726901</t>
-  </si>
-  <si>
-    <t>NFD6-03-25-F8NA</t>
-  </si>
-  <si>
-    <t>Móricz Zsigmond utca</t>
-  </si>
-  <si>
-    <t>202603272600735901</t>
-  </si>
-  <si>
-    <t>NFD6-03-26-224N</t>
-  </si>
-  <si>
-    <t>Kuruclesi út</t>
-  </si>
-  <si>
-    <t>202603272600737401</t>
-  </si>
-  <si>
-    <t>NFD6-03-26-34YD</t>
-  </si>
-  <si>
-    <t>1162</t>
-  </si>
-  <si>
-    <t>János utca</t>
-  </si>
-  <si>
-    <t>202603272600735201</t>
-  </si>
-  <si>
-    <t>NFD6-03-26-BFCV</t>
-  </si>
-  <si>
-    <t>Hunyadi János utca</t>
-  </si>
-  <si>
-    <t>202603272600736201</t>
-  </si>
-  <si>
-    <t>NFD6-03-26-GMEV</t>
-  </si>
-  <si>
-    <t>Franciska utca</t>
-  </si>
-  <si>
-    <t>202603272600736001</t>
-  </si>
-  <si>
-    <t>NFD6-03-26-KUET</t>
-  </si>
-  <si>
-    <t>Tomaj utca</t>
-  </si>
-  <si>
-    <t>202603272600736002</t>
-  </si>
-  <si>
-    <t>202603272600734601</t>
-  </si>
-  <si>
-    <t>NFD6-03-26-SBWU</t>
-  </si>
-  <si>
-    <t>Lukács György utca</t>
-  </si>
-  <si>
-    <t>202603272600736501</t>
-  </si>
-  <si>
-    <t>NFD6-03-26-U97V</t>
-  </si>
-  <si>
-    <t>Márton út</t>
-  </si>
-  <si>
-    <t>202603272600736901</t>
-  </si>
-  <si>
-    <t>NFD6-03-26-YCBA</t>
-  </si>
-  <si>
-    <t>Somfa utca</t>
-  </si>
-  <si>
-    <t>202603262600731001</t>
-  </si>
-  <si>
-    <t>NFE6-03-25-E869</t>
-  </si>
-  <si>
-    <t>Radnóti Miklós köz</t>
-  </si>
-  <si>
-    <t>202603262600731002</t>
-  </si>
-  <si>
-    <t>202603272600738801</t>
-  </si>
-  <si>
-    <t>NFE6-03-26-5CSG</t>
-  </si>
-  <si>
-    <t>Paprika utca</t>
-  </si>
-  <si>
-    <t>202603272600738802</t>
-  </si>
-  <si>
-    <t>202603272600738803</t>
-  </si>
-  <si>
-    <t>202603272600738804</t>
-  </si>
-  <si>
-    <t>202603272600738805</t>
-  </si>
-  <si>
-    <t>202603272600732101</t>
-  </si>
-  <si>
-    <t>NFE6-03-26-EZ58</t>
-  </si>
-  <si>
     <t>Fő út</t>
   </si>
   <si>
-    <t>202603272600734901</t>
-  </si>
-  <si>
-    <t>NFE6-03-26-MTVN</t>
-  </si>
-  <si>
-    <t>2133</t>
-  </si>
-  <si>
-    <t>SZŐDLIGET</t>
-  </si>
-  <si>
-    <t>202603272600739601</t>
-  </si>
-  <si>
-    <t>NFE6-03-26-XL5L</t>
-  </si>
-  <si>
-    <t>Bártfai utca</t>
-  </si>
-  <si>
-    <t>159995579538654671</t>
-  </si>
-  <si>
-    <t>SA26/H001449</t>
-  </si>
-  <si>
     <t>2314</t>
   </si>
   <si>
     <t>HALÁSZTELEK</t>
   </si>
   <si>
-    <t>Biró László utca</t>
-  </si>
-  <si>
     <t>PICIGURMAN</t>
   </si>
   <si>
-    <t>159995579538654688</t>
-  </si>
-  <si>
-    <t>159995579538654695</t>
-  </si>
-  <si>
-    <t>NFD6-03-24-L76B</t>
-  </si>
-  <si>
-    <t>AUCHAN_ÁRUHÁZI</t>
+    <t>159995579538704314</t>
+  </si>
+  <si>
+    <t>1-2650/2026</t>
+  </si>
+  <si>
+    <t>2092</t>
+  </si>
+  <si>
+    <t>BUDAKESZI</t>
+  </si>
+  <si>
+    <t>Barackvirág utca</t>
+  </si>
+  <si>
+    <t>EUROTRESOR</t>
+  </si>
+  <si>
+    <t>248745052/1</t>
+  </si>
+  <si>
+    <t>248745052</t>
+  </si>
+  <si>
+    <t>2220</t>
+  </si>
+  <si>
+    <t>VECSÉS</t>
+  </si>
+  <si>
+    <t>Széchenyi utca</t>
+  </si>
+  <si>
+    <t>69b538f86967eb2a8b5ce608</t>
+  </si>
+  <si>
+    <t>SZ-815</t>
+  </si>
+  <si>
+    <t>260310-F00003841</t>
+  </si>
+  <si>
+    <t>Istvánmezei út</t>
+  </si>
+  <si>
+    <t>69c69d04d96b4f4a24389a65</t>
+  </si>
+  <si>
+    <t>260319-F00005275</t>
+  </si>
+  <si>
+    <t>1073</t>
+  </si>
+  <si>
+    <t>Erzsébet körút</t>
+  </si>
+  <si>
+    <t>69c29206d96b4f4a2438588e</t>
+  </si>
+  <si>
+    <t>260320-F00006265</t>
+  </si>
+  <si>
+    <t>Nap utca</t>
+  </si>
+  <si>
+    <t>69c24cffd96b4f4a24384ed2</t>
+  </si>
+  <si>
+    <t>260324-F00001104</t>
+  </si>
+  <si>
+    <t>2254</t>
+  </si>
+  <si>
+    <t>SZENTMÁRTONKÁTA</t>
+  </si>
+  <si>
+    <t>Szecsői út</t>
+  </si>
+  <si>
+    <t>69c24cffd96b4f4a24384ed3</t>
+  </si>
+  <si>
+    <t>69c6760ad96b4f4a2438954a</t>
+  </si>
+  <si>
+    <t>260324-F00007301-2</t>
+  </si>
+  <si>
+    <t>2440</t>
+  </si>
+  <si>
+    <t>SZÁZHALOMBATTA</t>
+  </si>
+  <si>
+    <t>Erőmű út</t>
+  </si>
+  <si>
+    <t>69c55217d96b4f4a2438876d</t>
+  </si>
+  <si>
+    <t>260325-F00002425</t>
+  </si>
+  <si>
+    <t>2011</t>
+  </si>
+  <si>
+    <t>BUDAKALÁSZ</t>
+  </si>
+  <si>
+    <t>Budai út</t>
+  </si>
+  <si>
+    <t>69c55217d96b4f4a2438876f</t>
+  </si>
+  <si>
+    <t>69c3d582d96b4f4a24386cb2</t>
+  </si>
+  <si>
+    <t>260325-F00007218</t>
+  </si>
+  <si>
+    <t>2712</t>
+  </si>
+  <si>
+    <t>NYÁRSAPÁT</t>
+  </si>
+  <si>
+    <t>Arany János utca</t>
+  </si>
+  <si>
+    <t>69ca44650ed4809420f49ad4</t>
+  </si>
+  <si>
+    <t>260325-F00009865</t>
+  </si>
+  <si>
+    <t>1092</t>
+  </si>
+  <si>
+    <t>Kinizsi utca</t>
+  </si>
+  <si>
+    <t>69c54304d96b4f4a243885de</t>
+  </si>
+  <si>
+    <t>260326-F00009388</t>
+  </si>
+  <si>
+    <t>2750</t>
+  </si>
+  <si>
+    <t>NAGYKŐRÖS</t>
+  </si>
+  <si>
+    <t>Temetőhegy dűlő</t>
+  </si>
+  <si>
+    <t>69c54304d96b4f4a243885e0</t>
+  </si>
+  <si>
+    <t>69c5376cd96b4f4a24388417</t>
+  </si>
+  <si>
+    <t>260326-W00003327</t>
+  </si>
+  <si>
+    <t>2623</t>
+  </si>
+  <si>
+    <t>KISMAROS</t>
+  </si>
+  <si>
+    <t>Szokolyai út</t>
+  </si>
+  <si>
+    <t>69c52b8dd96b4f4a24388248</t>
+  </si>
+  <si>
+    <t>260326-W00004974</t>
+  </si>
+  <si>
+    <t>BA-KO utca</t>
+  </si>
+  <si>
+    <t>69c52b8dd96b4f4a2438824a</t>
+  </si>
+  <si>
+    <t>69c65b16d96b4f4a243891de</t>
+  </si>
+  <si>
+    <t>SZ-823</t>
+  </si>
+  <si>
+    <t>260327-W00002992</t>
+  </si>
+  <si>
+    <t>2377</t>
+  </si>
+  <si>
+    <t>ÖRKÉNY</t>
+  </si>
+  <si>
+    <t>Mester utca</t>
+  </si>
+  <si>
+    <t>69c67f6bd96b4f4a243896a9</t>
+  </si>
+  <si>
+    <t>260327-W00004793</t>
+  </si>
+  <si>
+    <t>1144</t>
+  </si>
+  <si>
+    <t>Ond vezér útja</t>
+  </si>
+  <si>
+    <t>69c67f6bd96b4f4a243896aa</t>
+  </si>
+  <si>
+    <t>69c6b9fcd96b4f4a24389cb4</t>
+  </si>
+  <si>
+    <t>260327-W00008038</t>
+  </si>
+  <si>
+    <t>Farkastorki lejtő</t>
+  </si>
+  <si>
+    <t>69c78bc00ed4809420f47cf0</t>
+  </si>
+  <si>
+    <t>260328-W00001506</t>
+  </si>
+  <si>
+    <t>Komócsy utca</t>
+  </si>
+  <si>
+    <t>69c7b4d10ed4809420f48163</t>
+  </si>
+  <si>
+    <t>260328-W00003392</t>
+  </si>
+  <si>
+    <t>Szentmihályi út</t>
+  </si>
+  <si>
+    <t>69c7b4d10ed4809420f48164</t>
+  </si>
+  <si>
+    <t>69c806cd0ed4809420f486f5</t>
+  </si>
+  <si>
+    <t>260328-W00007033</t>
+  </si>
+  <si>
+    <t>1118</t>
+  </si>
+  <si>
+    <t>Regős utca</t>
+  </si>
+  <si>
+    <t>69c806cd0ed4809420f486f6</t>
+  </si>
+  <si>
+    <t>69c81ab90ed4809420f487ee</t>
+  </si>
+  <si>
+    <t>260328-W00008247</t>
+  </si>
+  <si>
+    <t>Fehérvári út</t>
+  </si>
+  <si>
+    <t>69c8d2b70ed4809420f4899f</t>
+  </si>
+  <si>
+    <t>260329-F00000332</t>
+  </si>
+  <si>
+    <t>Toldi Miklós utca</t>
+  </si>
+  <si>
+    <t>69c8d2b70ed4809420f489a1</t>
+  </si>
+  <si>
+    <t>69c9076e0ed4809420f48cb5</t>
+  </si>
+  <si>
+    <t>260329-F00001566</t>
+  </si>
+  <si>
+    <t>1042</t>
+  </si>
+  <si>
+    <t>69c9076e0ed4809420f48cb6</t>
+  </si>
+  <si>
+    <t>69c911fd0ed4809420f48d37</t>
+  </si>
+  <si>
+    <t>260329-W00004456</t>
+  </si>
+  <si>
+    <t>1114</t>
+  </si>
+  <si>
+    <t>Bartók Béla út</t>
+  </si>
+  <si>
+    <t>69c96b100ed4809420f49262</t>
+  </si>
+  <si>
+    <t>260329-W00009427</t>
+  </si>
+  <si>
+    <t>Szerenád utca</t>
+  </si>
+  <si>
+    <t>69c981550ed4809420f49313</t>
+  </si>
+  <si>
+    <t>260329-W00010655</t>
+  </si>
+  <si>
+    <t>1136</t>
+  </si>
+  <si>
+    <t>Pannónia utca</t>
+  </si>
+  <si>
+    <t>69c9a0f80ed4809420f49383</t>
+  </si>
+  <si>
+    <t>260329-W00011511</t>
+  </si>
+  <si>
+    <t>1082</t>
+  </si>
+  <si>
+    <t>Kisfaludy utca</t>
+  </si>
+  <si>
+    <t>69ca42aa0ed4809420f49a6e</t>
+  </si>
+  <si>
+    <t>260330-W00003245</t>
+  </si>
+  <si>
+    <t>1097</t>
+  </si>
+  <si>
+    <t>Tóth Kálmán utca</t>
+  </si>
+  <si>
+    <t>69ca5a1f0ed4809420f49e3c</t>
+  </si>
+  <si>
+    <t>260330-W00004336</t>
+  </si>
+  <si>
+    <t>1106</t>
+  </si>
+  <si>
+    <t>Tárna utca</t>
+  </si>
+  <si>
+    <t>FIZZ-1000851362</t>
+  </si>
+  <si>
+    <t>267004537</t>
+  </si>
+  <si>
+    <t>2235</t>
+  </si>
+  <si>
+    <t>MENDE</t>
+  </si>
+  <si>
+    <t>Rét u.</t>
+  </si>
+  <si>
+    <t>FIZZ-1000851624</t>
+  </si>
+  <si>
+    <t>267004553</t>
+  </si>
+  <si>
+    <t>Elnök Utca</t>
+  </si>
+  <si>
+    <t>FIZZ-1000855521</t>
+  </si>
+  <si>
+    <t>SZ-829</t>
+  </si>
+  <si>
+    <t>267004633</t>
+  </si>
+  <si>
+    <t>Antalhegyi utca</t>
+  </si>
+  <si>
+    <t>1449-352092</t>
+  </si>
+  <si>
+    <t>267004642</t>
+  </si>
+  <si>
+    <t>2039</t>
+  </si>
+  <si>
+    <t>PUSZTAZÁMOR</t>
+  </si>
+  <si>
+    <t>Petőfi Sándor utca</t>
+  </si>
+  <si>
+    <t>304676066/1/1</t>
+  </si>
+  <si>
+    <t>304676066/1</t>
+  </si>
+  <si>
+    <t>1181</t>
+  </si>
+  <si>
+    <t>Csontváry Kosztka Tivadar utca</t>
+  </si>
+  <si>
+    <t>305368079/1</t>
+  </si>
+  <si>
+    <t>305368079</t>
+  </si>
+  <si>
+    <t>1148</t>
+  </si>
+  <si>
+    <t>Vezér utca</t>
+  </si>
+  <si>
+    <t>305368497/1</t>
+  </si>
+  <si>
+    <t>305368497</t>
+  </si>
+  <si>
+    <t>1124</t>
+  </si>
+  <si>
+    <t>Fodor utca</t>
+  </si>
+  <si>
+    <t>305461585/1</t>
+  </si>
+  <si>
+    <t>305461585</t>
+  </si>
+  <si>
+    <t>Salgói utca</t>
+  </si>
+  <si>
+    <t>305462193/1</t>
+  </si>
+  <si>
+    <t>305462193</t>
+  </si>
+  <si>
+    <t>Boglárka utca</t>
+  </si>
+  <si>
+    <t>305462193/2</t>
+  </si>
+  <si>
+    <t>305462193/3</t>
+  </si>
+  <si>
+    <t>305462293/1</t>
+  </si>
+  <si>
+    <t>305462293</t>
+  </si>
+  <si>
+    <t>1134</t>
+  </si>
+  <si>
+    <t>Kassák Lajos utca</t>
+  </si>
+  <si>
+    <t>305462293/2</t>
+  </si>
+  <si>
+    <t>305557677/1</t>
+  </si>
+  <si>
+    <t>305557677</t>
+  </si>
+  <si>
+    <t>XV. utca</t>
+  </si>
+  <si>
+    <t>305557715/1</t>
+  </si>
+  <si>
+    <t>305557715</t>
+  </si>
+  <si>
+    <t>Kodály Zoltán sétány</t>
+  </si>
+  <si>
+    <t>305557715/2</t>
+  </si>
+  <si>
+    <t>305666948/1</t>
+  </si>
+  <si>
+    <t>305666948</t>
+  </si>
+  <si>
+    <t>Bodza utca</t>
+  </si>
+  <si>
+    <t>305667898/1</t>
+  </si>
+  <si>
+    <t>305667898</t>
+  </si>
+  <si>
+    <t>Kápolna utca</t>
+  </si>
+  <si>
+    <t>305725639/1</t>
+  </si>
+  <si>
+    <t>305725639</t>
+  </si>
+  <si>
+    <t>Törökugrató utca</t>
+  </si>
+  <si>
+    <t>305725639/2</t>
+  </si>
+  <si>
+    <t>305725853/1</t>
+  </si>
+  <si>
+    <t>305725853</t>
+  </si>
+  <si>
+    <t>Kert utca</t>
+  </si>
+  <si>
+    <t>305725898/1</t>
+  </si>
+  <si>
+    <t>305725898</t>
+  </si>
+  <si>
+    <t>1123</t>
+  </si>
+  <si>
+    <t>Táltos utca</t>
+  </si>
+  <si>
+    <t>305726246/1</t>
+  </si>
+  <si>
+    <t>305726246</t>
+  </si>
+  <si>
+    <t>2113</t>
+  </si>
+  <si>
+    <t>ERDŐKERTES</t>
+  </si>
+  <si>
+    <t>Kalauz utca</t>
+  </si>
+  <si>
+    <t>305781064/1</t>
+  </si>
+  <si>
+    <t>305781064</t>
+  </si>
+  <si>
+    <t>2132</t>
+  </si>
+  <si>
+    <t>Nyár utca</t>
+  </si>
+  <si>
+    <t>305781147/1</t>
+  </si>
+  <si>
+    <t>305781147</t>
+  </si>
+  <si>
+    <t>1074</t>
+  </si>
+  <si>
+    <t>Szövetség Utca</t>
+  </si>
+  <si>
+    <t>305781454/1</t>
+  </si>
+  <si>
+    <t>305781454</t>
+  </si>
+  <si>
+    <t>2745</t>
+  </si>
+  <si>
+    <t>KŐRÖSTETÉTLEN</t>
+  </si>
+  <si>
+    <t>Dózsa György utca</t>
+  </si>
+  <si>
+    <t>305782022/1</t>
+  </si>
+  <si>
+    <t>305782022</t>
+  </si>
+  <si>
+    <t>2252</t>
+  </si>
+  <si>
+    <t>TÓALMÁS</t>
+  </si>
+  <si>
+    <t>305782022/2</t>
+  </si>
+  <si>
+    <t>305830650/1</t>
+  </si>
+  <si>
+    <t>305830650</t>
+  </si>
+  <si>
+    <t>1078</t>
+  </si>
+  <si>
+    <t>Cserhát utca</t>
+  </si>
+  <si>
+    <t>305830650/2</t>
+  </si>
+  <si>
+    <t>305830650/3</t>
+  </si>
+  <si>
+    <t>305830674/1</t>
+  </si>
+  <si>
+    <t>305830674</t>
+  </si>
+  <si>
+    <t>Bercsényi .</t>
+  </si>
+  <si>
+    <t>305830746/1</t>
+  </si>
+  <si>
+    <t>305830746</t>
+  </si>
+  <si>
+    <t>Kék Golyó utca</t>
+  </si>
+  <si>
+    <t>305831048/1</t>
+  </si>
+  <si>
+    <t>305831048</t>
+  </si>
+  <si>
+    <t>Barázda utca</t>
+  </si>
+  <si>
+    <t>305831070/1</t>
+  </si>
+  <si>
+    <t>305831070</t>
+  </si>
+  <si>
+    <t>1105</t>
+  </si>
+  <si>
+    <t>Mongol utca</t>
+  </si>
+  <si>
+    <t>305831163/1</t>
+  </si>
+  <si>
+    <t>305831163</t>
+  </si>
+  <si>
+    <t>Lajtha László Utca</t>
+  </si>
+  <si>
+    <t>305831186/1</t>
+  </si>
+  <si>
+    <t>305831186</t>
+  </si>
+  <si>
+    <t>1192</t>
+  </si>
+  <si>
+    <t>Botond utca</t>
+  </si>
+  <si>
+    <t>305831241/1</t>
+  </si>
+  <si>
+    <t>305831241</t>
+  </si>
+  <si>
+    <t>1083</t>
+  </si>
+  <si>
+    <t>Szigony utca</t>
+  </si>
+  <si>
+    <t>305831241/2</t>
+  </si>
+  <si>
+    <t>305831241/3</t>
+  </si>
+  <si>
+    <t>305831285/1</t>
+  </si>
+  <si>
+    <t>305831285</t>
+  </si>
+  <si>
+    <t>Tárház utca</t>
+  </si>
+  <si>
+    <t>305901369/1</t>
+  </si>
+  <si>
+    <t>305901369</t>
+  </si>
+  <si>
+    <t>2316</t>
+  </si>
+  <si>
+    <t>TÖKÖL</t>
+  </si>
+  <si>
+    <t>Kolozsvári utca</t>
+  </si>
+  <si>
+    <t>305901427/1</t>
+  </si>
+  <si>
+    <t>305901427</t>
+  </si>
+  <si>
+    <t>Mikszáth Kálmán utca</t>
+  </si>
+  <si>
+    <t>305901427/2</t>
+  </si>
+  <si>
+    <t>305901483/1</t>
+  </si>
+  <si>
+    <t>305901483</t>
+  </si>
+  <si>
+    <t>Széchenyi István utca</t>
+  </si>
+  <si>
+    <t>305901533/1</t>
+  </si>
+  <si>
+    <t>305901533</t>
+  </si>
+  <si>
+    <t>2723</t>
+  </si>
+  <si>
+    <t>NYÁREGYHÁZA</t>
+  </si>
+  <si>
+    <t>József Attila út</t>
+  </si>
+  <si>
+    <t>305901619/1</t>
+  </si>
+  <si>
+    <t>305901619</t>
+  </si>
+  <si>
+    <t>2194</t>
+  </si>
+  <si>
+    <t>TURA</t>
+  </si>
+  <si>
+    <t>Köztársaság utca</t>
+  </si>
+  <si>
+    <t>305901665/1</t>
+  </si>
+  <si>
+    <t>305901665</t>
+  </si>
+  <si>
+    <t>Dugonics utca</t>
+  </si>
+  <si>
+    <t>305901665/2</t>
+  </si>
+  <si>
+    <t>305901792/1</t>
+  </si>
+  <si>
+    <t>305901792</t>
+  </si>
+  <si>
+    <t>305901845/1</t>
+  </si>
+  <si>
+    <t>305901845</t>
+  </si>
+  <si>
+    <t>1064</t>
+  </si>
+  <si>
+    <t>Izabella utca</t>
+  </si>
+  <si>
+    <t>305901864/1</t>
+  </si>
+  <si>
+    <t>305901864</t>
+  </si>
+  <si>
+    <t>1188</t>
+  </si>
+  <si>
+    <t>Nagykőrösi út</t>
+  </si>
+  <si>
+    <t>305901933/1</t>
+  </si>
+  <si>
+    <t>305901933</t>
+  </si>
+  <si>
+    <t>1191</t>
+  </si>
+  <si>
+    <t>Ady Endre Út</t>
+  </si>
+  <si>
+    <t>305902119/1</t>
+  </si>
+  <si>
+    <t>305902119</t>
+  </si>
+  <si>
+    <t>Pesti Út</t>
+  </si>
+  <si>
+    <t>305902266/1</t>
+  </si>
+  <si>
+    <t>305902266</t>
+  </si>
+  <si>
+    <t>1045</t>
+  </si>
+  <si>
+    <t>305954219/1</t>
+  </si>
+  <si>
+    <t>305954219</t>
+  </si>
+  <si>
+    <t>Vég Mese Köz</t>
+  </si>
+  <si>
+    <t>305954497/1</t>
+  </si>
+  <si>
+    <t>305954497</t>
+  </si>
+  <si>
+    <t>Gyepes utca</t>
+  </si>
+  <si>
+    <t>305954776/1</t>
+  </si>
+  <si>
+    <t>305954776</t>
+  </si>
+  <si>
+    <t>1032</t>
+  </si>
+  <si>
+    <t>Zápor utca</t>
+  </si>
+  <si>
+    <t>305954940/1</t>
+  </si>
+  <si>
+    <t>305954940</t>
+  </si>
+  <si>
+    <t>2737</t>
+  </si>
+  <si>
+    <t>CEGLÉDBERCEL</t>
+  </si>
+  <si>
+    <t>Bajcsy-Zsilinszky Utca</t>
+  </si>
+  <si>
+    <t>305955001/1</t>
+  </si>
+  <si>
+    <t>305955001</t>
+  </si>
+  <si>
+    <t>Szent László utca</t>
+  </si>
+  <si>
+    <t>305955144/1</t>
+  </si>
+  <si>
+    <t>305955144</t>
+  </si>
+  <si>
+    <t>305955144/2</t>
+  </si>
+  <si>
+    <t>305955144/3</t>
+  </si>
+  <si>
+    <t>306025753/1</t>
+  </si>
+  <si>
+    <t>306025753</t>
+  </si>
+  <si>
+    <t>2225</t>
+  </si>
+  <si>
+    <t>ÜLLŐ</t>
+  </si>
+  <si>
+    <t>306025921/1</t>
+  </si>
+  <si>
+    <t>306025921</t>
+  </si>
+  <si>
+    <t>306025992/1</t>
+  </si>
+  <si>
+    <t>306025992</t>
+  </si>
+  <si>
+    <t>2214</t>
+  </si>
+  <si>
+    <t>PÁND</t>
+  </si>
+  <si>
+    <t>306026079/1</t>
+  </si>
+  <si>
+    <t>306026079</t>
+  </si>
+  <si>
+    <t>2721</t>
+  </si>
+  <si>
+    <t>PILIS</t>
+  </si>
+  <si>
+    <t>Táncsics Mihály utca</t>
+  </si>
+  <si>
+    <t>306026203/1</t>
+  </si>
+  <si>
+    <t>306026203</t>
+  </si>
+  <si>
+    <t>306026622/1</t>
+  </si>
+  <si>
+    <t>306026622</t>
+  </si>
+  <si>
+    <t>306078394/1</t>
+  </si>
+  <si>
+    <t>306078394</t>
+  </si>
+  <si>
+    <t>1012</t>
+  </si>
+  <si>
+    <t>Alkotás utca</t>
+  </si>
+  <si>
+    <t>306078523/1</t>
+  </si>
+  <si>
+    <t>306078523</t>
+  </si>
+  <si>
+    <t>1147</t>
+  </si>
+  <si>
+    <t>Kerékgyártó utca</t>
+  </si>
+  <si>
+    <t>306078528/1</t>
+  </si>
+  <si>
+    <t>306078528</t>
+  </si>
+  <si>
+    <t>2713</t>
+  </si>
+  <si>
+    <t>CSEMŐ</t>
+  </si>
+  <si>
+    <t>Várkonyi István utca</t>
+  </si>
+  <si>
+    <t>306078848/1</t>
+  </si>
+  <si>
+    <t>306078848</t>
+  </si>
+  <si>
+    <t>1157</t>
+  </si>
+  <si>
+    <t>Kőrakás park</t>
+  </si>
+  <si>
+    <t>306078884/1</t>
+  </si>
+  <si>
+    <t>306078884</t>
+  </si>
+  <si>
+    <t>Margó Tivadar utca</t>
+  </si>
+  <si>
+    <t>306078931/1</t>
+  </si>
+  <si>
+    <t>306078931</t>
+  </si>
+  <si>
+    <t>Jós utca</t>
+  </si>
+  <si>
+    <t>306078952/1</t>
+  </si>
+  <si>
+    <t>306078952</t>
+  </si>
+  <si>
+    <t>2365</t>
+  </si>
+  <si>
+    <t>INÁRCS</t>
+  </si>
+  <si>
+    <t>Hársfa utca</t>
+  </si>
+  <si>
+    <t>306078975/1</t>
+  </si>
+  <si>
+    <t>306078975</t>
+  </si>
+  <si>
+    <t>Attila utca</t>
+  </si>
+  <si>
+    <t>306079051/1</t>
+  </si>
+  <si>
+    <t>306079051</t>
+  </si>
+  <si>
+    <t>Homok dűlő</t>
+  </si>
+  <si>
+    <t>306079074/1</t>
+  </si>
+  <si>
+    <t>306079074</t>
+  </si>
+  <si>
+    <t>2142</t>
+  </si>
+  <si>
+    <t>NAGYTARCSA</t>
+  </si>
+  <si>
+    <t>306079088/1</t>
+  </si>
+  <si>
+    <t>306079088</t>
+  </si>
+  <si>
+    <t>1193</t>
+  </si>
+  <si>
+    <t>Szigligeti utca</t>
+  </si>
+  <si>
+    <t>306079088/2</t>
+  </si>
+  <si>
+    <t>306079129/1</t>
+  </si>
+  <si>
+    <t>306079129</t>
+  </si>
+  <si>
+    <t>1211</t>
+  </si>
+  <si>
+    <t>II. Rákóczi Ferenc</t>
+  </si>
+  <si>
+    <t>306079129/2</t>
+  </si>
+  <si>
+    <t>306079202/1</t>
+  </si>
+  <si>
+    <t>306079202</t>
+  </si>
+  <si>
+    <t>Budakeszi út</t>
+  </si>
+  <si>
+    <t>306079202/2</t>
+  </si>
+  <si>
+    <t>306146401/1</t>
+  </si>
+  <si>
+    <t>306146401</t>
+  </si>
+  <si>
+    <t>Ráday utca</t>
+  </si>
+  <si>
+    <t>306146401/2</t>
+  </si>
+  <si>
+    <t>306146604/1</t>
+  </si>
+  <si>
+    <t>306146604</t>
+  </si>
+  <si>
+    <t>Gémeskút utca</t>
+  </si>
+  <si>
+    <t>306146732/1</t>
+  </si>
+  <si>
+    <t>306146732</t>
+  </si>
+  <si>
+    <t>2084</t>
+  </si>
+  <si>
+    <t>PILISSZENTIVÁN</t>
+  </si>
+  <si>
+    <t>Szabadság út</t>
+  </si>
+  <si>
+    <t>306146793/1</t>
+  </si>
+  <si>
+    <t>306146793</t>
+  </si>
+  <si>
+    <t>Telepy utca</t>
+  </si>
+  <si>
+    <t>306146843/1</t>
+  </si>
+  <si>
+    <t>306146843</t>
+  </si>
+  <si>
+    <t>306146997/1</t>
+  </si>
+  <si>
+    <t>306146997</t>
+  </si>
+  <si>
+    <t>1043</t>
+  </si>
+  <si>
+    <t>Munkásotthon utca</t>
+  </si>
+  <si>
+    <t>306147012/1</t>
+  </si>
+  <si>
+    <t>306147012</t>
+  </si>
+  <si>
+    <t>1098</t>
+  </si>
+  <si>
+    <t>Távíró utca</t>
+  </si>
+  <si>
+    <t>306147075/1</t>
+  </si>
+  <si>
+    <t>306147075</t>
+  </si>
+  <si>
+    <t>2071</t>
+  </si>
+  <si>
+    <t>PÁTY</t>
+  </si>
+  <si>
+    <t>Liget utca</t>
+  </si>
+  <si>
+    <t>306180969/1</t>
+  </si>
+  <si>
+    <t>306180969</t>
+  </si>
+  <si>
+    <t>1094</t>
+  </si>
+  <si>
+    <t>Liliom utca</t>
+  </si>
+  <si>
+    <t>306181305/1</t>
+  </si>
+  <si>
+    <t>306181305</t>
+  </si>
+  <si>
+    <t>Üllői út</t>
+  </si>
+  <si>
+    <t>306181461/1</t>
+  </si>
+  <si>
+    <t>306181461</t>
+  </si>
+  <si>
+    <t>Hegyalja utca</t>
+  </si>
+  <si>
+    <t>306226714/1</t>
+  </si>
+  <si>
+    <t>306226714</t>
+  </si>
+  <si>
+    <t>1196</t>
+  </si>
+  <si>
+    <t>Áchim András utca</t>
+  </si>
+  <si>
+    <t>306277511/1</t>
+  </si>
+  <si>
+    <t>306277511</t>
+  </si>
+  <si>
+    <t>2119</t>
+  </si>
+  <si>
+    <t>PÉCEL</t>
+  </si>
+  <si>
+    <t>Búzavirág utca</t>
+  </si>
+  <si>
+    <t>306277639/1</t>
+  </si>
+  <si>
+    <t>306277639</t>
+  </si>
+  <si>
+    <t>1048</t>
+  </si>
+  <si>
+    <t>Szíjgyártó utca</t>
+  </si>
+  <si>
+    <t>306334250/1</t>
+  </si>
+  <si>
+    <t>306334250</t>
+  </si>
+  <si>
+    <t>Márvány utca</t>
+  </si>
+  <si>
+    <t>306334375/1</t>
+  </si>
+  <si>
+    <t>306334375</t>
+  </si>
+  <si>
+    <t>Ady Endre út</t>
+  </si>
+  <si>
+    <t>159995579538714764</t>
+  </si>
+  <si>
+    <t>NFD6-03-20-ZZ2L/XD</t>
+  </si>
+  <si>
+    <t>Napsugár sétány</t>
+  </si>
+  <si>
+    <t>202603272600688901</t>
+  </si>
+  <si>
+    <t>NFD6-03-21-MZ5H</t>
+  </si>
+  <si>
+    <t>2081</t>
+  </si>
+  <si>
+    <t>PILISCSABA</t>
+  </si>
+  <si>
+    <t>Károlyi Mihály utca</t>
+  </si>
+  <si>
+    <t>202603232600698901</t>
+  </si>
+  <si>
+    <t>NFD6-03-22-KW7W</t>
+  </si>
+  <si>
+    <t>Sügér</t>
+  </si>
+  <si>
+    <t>202603232600698902</t>
+  </si>
+  <si>
+    <t>202603272600724301</t>
+  </si>
+  <si>
+    <t>NFD6-03-25-CX4V</t>
+  </si>
+  <si>
+    <t>Malom dűlő HR</t>
+  </si>
+  <si>
+    <t>202603272600739001</t>
+  </si>
+  <si>
+    <t>NFD6-03-26-GAT8</t>
+  </si>
+  <si>
+    <t>2085</t>
+  </si>
+  <si>
+    <t>PILISVÖRÖSVÁR</t>
+  </si>
+  <si>
+    <t>202603272600732401</t>
+  </si>
+  <si>
+    <t>NFD6-03-26-PWPR</t>
+  </si>
+  <si>
+    <t>2146</t>
+  </si>
+  <si>
+    <t>MOGYORÓD</t>
+  </si>
+  <si>
+    <t>Gödöllői út</t>
+  </si>
+  <si>
+    <t>202603302600749401</t>
+  </si>
+  <si>
+    <t>NFD6-03-28-2ME3</t>
+  </si>
+  <si>
+    <t>Solymárvölgyi út</t>
+  </si>
+  <si>
+    <t>202603302600749301</t>
+  </si>
+  <si>
+    <t>NFD6-03-28-8TEL</t>
+  </si>
+  <si>
+    <t>1174</t>
+  </si>
+  <si>
+    <t>Kutassy Ágoston utca</t>
+  </si>
+  <si>
+    <t>202603302600749302</t>
+  </si>
+  <si>
+    <t>202603302600749303</t>
+  </si>
+  <si>
+    <t>202603302600749304</t>
+  </si>
+  <si>
+    <t>202603302600752401</t>
+  </si>
+  <si>
+    <t>NFD6-03-28-DTTW</t>
+  </si>
+  <si>
+    <t>2143</t>
+  </si>
+  <si>
+    <t>KISTARCSA</t>
+  </si>
+  <si>
+    <t>Mikszáth utca</t>
+  </si>
+  <si>
+    <t>202603302600749501</t>
+  </si>
+  <si>
+    <t>NFD6-03-28-GJFH</t>
+  </si>
+  <si>
+    <t>József Attila utca</t>
+  </si>
+  <si>
+    <t>202603302600752201</t>
+  </si>
+  <si>
+    <t>NFD6-03-28-HXCH</t>
+  </si>
+  <si>
+    <t>2182</t>
+  </si>
+  <si>
+    <t>DOMONY</t>
+  </si>
+  <si>
+    <t>Akác utca</t>
+  </si>
+  <si>
+    <t>202603302600752701</t>
+  </si>
+  <si>
+    <t>NFD6-03-28-LFWS</t>
+  </si>
+  <si>
+    <t>2234</t>
+  </si>
+  <si>
+    <t>MAGLÓD</t>
+  </si>
+  <si>
+    <t>Ady Endre utca</t>
+  </si>
+  <si>
+    <t>202603302600752001</t>
+  </si>
+  <si>
+    <t>NFD6-03-28-LNRR</t>
+  </si>
+  <si>
+    <t>2200</t>
+  </si>
+  <si>
+    <t>MONOR</t>
+  </si>
+  <si>
+    <t>Avar utca</t>
+  </si>
+  <si>
+    <t>202603302600747301</t>
+  </si>
+  <si>
+    <t>NFD6-03-28-T6X9</t>
+  </si>
+  <si>
+    <t>Törökkút utca</t>
+  </si>
+  <si>
+    <t>202603302600746701</t>
+  </si>
+  <si>
+    <t>NFD6-03-28-TAJV</t>
+  </si>
+  <si>
+    <t>Nefelejcs utca</t>
+  </si>
+  <si>
+    <t>202603302600746201</t>
+  </si>
+  <si>
+    <t>NFD6-03-28-U6YY</t>
+  </si>
+  <si>
+    <t>1182</t>
+  </si>
+  <si>
+    <t>Tömb utca</t>
+  </si>
+  <si>
+    <t>202603302600750201</t>
+  </si>
+  <si>
+    <t>NFD6-03-28-YEYP</t>
+  </si>
+  <si>
+    <t>Tóth József utca</t>
+  </si>
+  <si>
+    <t>202603302600750202</t>
+  </si>
+  <si>
+    <t>202603302600750203</t>
+  </si>
+  <si>
+    <t>202603302600750204</t>
+  </si>
+  <si>
+    <t>202603302600750205</t>
+  </si>
+  <si>
+    <t>202603302600756701</t>
+  </si>
+  <si>
+    <t>NFD6-03-29-2QQ6</t>
+  </si>
+  <si>
+    <t>202603302600757501</t>
+  </si>
+  <si>
+    <t>NFD6-03-29-8F7Y</t>
+  </si>
+  <si>
+    <t>Dobó István utca</t>
+  </si>
+  <si>
+    <t>202603302600757701</t>
+  </si>
+  <si>
+    <t>NFD6-03-29-8RQD</t>
+  </si>
+  <si>
+    <t>2162</t>
+  </si>
+  <si>
+    <t>ŐRBOTTYÁN</t>
+  </si>
+  <si>
+    <t>202603302600757702</t>
+  </si>
+  <si>
+    <t>202603302600757703</t>
+  </si>
+  <si>
+    <t>202603302600757704</t>
+  </si>
+  <si>
+    <t>202603302600761001</t>
+  </si>
+  <si>
+    <t>NFD6-03-29-8XC2</t>
+  </si>
+  <si>
+    <t>Szivárvány utca</t>
+  </si>
+  <si>
+    <t>202603302600759301</t>
+  </si>
+  <si>
+    <t>NFD6-03-29-DEVD</t>
+  </si>
+  <si>
+    <t>Kárpitos utca</t>
+  </si>
+  <si>
+    <t>202603302600759302</t>
+  </si>
+  <si>
+    <t>202603302600757201</t>
+  </si>
+  <si>
+    <t>NFD6-03-29-NA2F</t>
+  </si>
+  <si>
+    <t>Hímző utca</t>
+  </si>
+  <si>
+    <t>202603302600754901</t>
+  </si>
+  <si>
+    <t>NFD6-03-29-S294</t>
+  </si>
+  <si>
+    <t>202603302600756801</t>
+  </si>
+  <si>
+    <t>NFD6-03-29-V9JX</t>
+  </si>
+  <si>
+    <t>Kiránduló utca</t>
+  </si>
+  <si>
+    <t>202603302600755701</t>
+  </si>
+  <si>
+    <t>NFD6-03-29-WV3M</t>
+  </si>
+  <si>
+    <t>202603302600757601</t>
+  </si>
+  <si>
+    <t>NFD6-03-29-ZXGK</t>
+  </si>
+  <si>
+    <t>Pácoló utca</t>
+  </si>
+  <si>
+    <t>202603232600695401</t>
+  </si>
+  <si>
+    <t>NFE6-03-22-W92M</t>
+  </si>
+  <si>
+    <t>2376</t>
+  </si>
+  <si>
+    <t>HERNÁD</t>
+  </si>
+  <si>
+    <t>Temesvári út</t>
+  </si>
+  <si>
+    <t>202603262600725501</t>
+  </si>
+  <si>
+    <t>NFE6-03-25-ZVXU</t>
+  </si>
+  <si>
+    <t>Karinthy Frigyes utca</t>
+  </si>
+  <si>
+    <t>202603262600725502</t>
+  </si>
+  <si>
+    <t>202603302600742301</t>
+  </si>
+  <si>
+    <t>NFE6-03-27-TF48</t>
+  </si>
+  <si>
+    <t>1122</t>
+  </si>
+  <si>
+    <t>Ráth György utca</t>
+  </si>
+  <si>
+    <t>202603302600742302</t>
+  </si>
+  <si>
+    <t>202603302600742303</t>
+  </si>
+  <si>
+    <t>202603302600742304</t>
+  </si>
+  <si>
+    <t>202603302600753601</t>
+  </si>
+  <si>
+    <t>NFE6-03-28-9QGF</t>
+  </si>
+  <si>
+    <t>Cinke utca</t>
+  </si>
+  <si>
+    <t>202603302600753602</t>
+  </si>
+  <si>
+    <t>202603302600745701</t>
+  </si>
+  <si>
+    <t>NFE6-03-28-DXUP</t>
+  </si>
+  <si>
+    <t>202603302600750701</t>
+  </si>
+  <si>
+    <t>NFE6-03-28-WASB</t>
+  </si>
+  <si>
+    <t>Lázár Ervin utca</t>
+  </si>
+  <si>
+    <t>202603302600750702</t>
+  </si>
+  <si>
+    <t>202603302600763401</t>
+  </si>
+  <si>
+    <t>NFE6-03-29-2FKK</t>
+  </si>
+  <si>
+    <t>Auróra utca</t>
+  </si>
+  <si>
+    <t>202603302600761801</t>
+  </si>
+  <si>
+    <t>NFE6-03-29-F33V</t>
+  </si>
+  <si>
+    <t>2381</t>
+  </si>
+  <si>
+    <t>TÁBORFALVA</t>
+  </si>
+  <si>
+    <t>Iskola utca</t>
+  </si>
+  <si>
+    <t>202603302600758901</t>
+  </si>
+  <si>
+    <t>NFE6-03-29-HQ5U</t>
+  </si>
+  <si>
+    <t>Batthyány utca</t>
+  </si>
+  <si>
+    <t>159995579538714986</t>
+  </si>
+  <si>
+    <t>R413857</t>
+  </si>
+  <si>
+    <t>Lehel út</t>
+  </si>
+  <si>
+    <t>INSPORT</t>
+  </si>
+  <si>
+    <t>159995579538716119</t>
+  </si>
+  <si>
+    <t>R414280</t>
+  </si>
+  <si>
+    <t>1171</t>
+  </si>
+  <si>
+    <t>Mezőőr utca</t>
+  </si>
+  <si>
+    <t>159995579538655180</t>
+  </si>
+  <si>
+    <t>R414431</t>
+  </si>
+  <si>
+    <t>2112</t>
+  </si>
+  <si>
+    <t>VERESEGYHÁZ</t>
+  </si>
+  <si>
+    <t>Somkóró u</t>
+  </si>
+  <si>
+    <t>159995579538714887</t>
+  </si>
+  <si>
+    <t>R414687</t>
+  </si>
+  <si>
+    <t>Vereckei út</t>
+  </si>
+  <si>
+    <t>159995579538714894</t>
+  </si>
+  <si>
+    <t>159995579538717161</t>
+  </si>
+  <si>
+    <t>R414723</t>
+  </si>
+  <si>
+    <t>159995579538717178</t>
+  </si>
+  <si>
+    <t>159995579538717185</t>
+  </si>
+  <si>
+    <t>159995579538717192</t>
+  </si>
+  <si>
+    <t>159995579538717208</t>
+  </si>
+  <si>
+    <t>159995579538652448</t>
+  </si>
+  <si>
+    <t>SA26/H001444</t>
+  </si>
+  <si>
+    <t>2370</t>
+  </si>
+  <si>
+    <t>Klapka utca</t>
+  </si>
+  <si>
+    <t>159995579538652455</t>
+  </si>
+  <si>
+    <t>159995579538702426</t>
+  </si>
+  <si>
+    <t>SA26/H001481</t>
+  </si>
+  <si>
+    <t>2023</t>
+  </si>
+  <si>
+    <t>DUNABOGDÁNY</t>
+  </si>
+  <si>
+    <t>Sólyom utca</t>
+  </si>
+  <si>
+    <t>159995579538702433</t>
   </si>
 </sst>
 </file>
@@ -1900,7 +2533,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <sheetPr codeName="Munka1"/>
-  <dimension ref="A1:H149"/>
+  <dimension ref="A1:H210"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="24.88671875" bestFit="1" customWidth="1"/>
@@ -1909,74 +2542,74 @@
     <col min="4" max="4" width="20.109375" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="5" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="20" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="35.5546875" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="33.44140625" bestFit="1" customWidth="1"/>
     <col min="8" max="8" width="19.88671875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
-        <v>36</v>
+        <v>29</v>
       </c>
       <c r="C1" t="s">
-        <v>37</v>
+        <v>30</v>
       </c>
       <c r="D1" t="s">
-        <v>38</v>
+        <v>31</v>
       </c>
       <c r="E1" t="s">
-        <v>39</v>
+        <v>32</v>
       </c>
       <c r="F1" t="s">
-        <v>40</v>
+        <v>33</v>
       </c>
       <c r="G1" t="s">
-        <v>41</v>
+        <v>34</v>
       </c>
       <c r="H1" t="s">
-        <v>42</v>
+        <v>35</v>
       </c>
     </row>
     <row r="2" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
-        <v>85</v>
+        <v>107</v>
       </c>
       <c r="C2" t="s">
-        <v>21</v>
+        <v>16</v>
       </c>
       <c r="D2" t="s">
-        <v>86</v>
+        <v>108</v>
       </c>
       <c r="E2" t="s">
-        <v>70</v>
+        <v>109</v>
       </c>
       <c r="F2" t="s">
-        <v>0</v>
+        <v>110</v>
       </c>
       <c r="G2" t="s">
-        <v>87</v>
+        <v>111</v>
       </c>
       <c r="H2" t="s">
-        <v>4</v>
+        <v>112</v>
       </c>
     </row>
     <row r="3" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
-        <v>88</v>
+        <v>113</v>
       </c>
       <c r="C3" t="s">
-        <v>21</v>
+        <v>11</v>
       </c>
       <c r="D3" t="s">
-        <v>86</v>
+        <v>114</v>
       </c>
       <c r="E3" t="s">
-        <v>70</v>
+        <v>115</v>
       </c>
       <c r="F3" t="s">
-        <v>0</v>
+        <v>116</v>
       </c>
       <c r="G3" t="s">
-        <v>87</v>
+        <v>117</v>
       </c>
       <c r="H3" t="s">
         <v>4</v>
@@ -1984,45 +2617,45 @@
     </row>
     <row r="4" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
-        <v>89</v>
+        <v>118</v>
       </c>
       <c r="C4" t="s">
-        <v>21</v>
+        <v>119</v>
       </c>
       <c r="D4" t="s">
-        <v>86</v>
+        <v>120</v>
       </c>
       <c r="E4" t="s">
-        <v>70</v>
+        <v>39</v>
       </c>
       <c r="F4" t="s">
         <v>0</v>
       </c>
       <c r="G4" t="s">
-        <v>87</v>
+        <v>121</v>
       </c>
       <c r="H4" t="s">
-        <v>4</v>
+        <v>1</v>
       </c>
     </row>
     <row r="5" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
-        <v>90</v>
+        <v>122</v>
       </c>
       <c r="C5" t="s">
-        <v>91</v>
+        <v>2</v>
       </c>
       <c r="D5" t="s">
-        <v>92</v>
+        <v>123</v>
       </c>
       <c r="E5" t="s">
-        <v>23</v>
+        <v>124</v>
       </c>
       <c r="F5" t="s">
-        <v>24</v>
+        <v>0</v>
       </c>
       <c r="G5" t="s">
-        <v>93</v>
+        <v>125</v>
       </c>
       <c r="H5" t="s">
         <v>1</v>
@@ -2030,22 +2663,22 @@
     </row>
     <row r="6" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
-        <v>94</v>
+        <v>126</v>
       </c>
       <c r="C6" t="s">
-        <v>3</v>
+        <v>41</v>
       </c>
       <c r="D6" t="s">
-        <v>95</v>
+        <v>127</v>
       </c>
       <c r="E6" t="s">
-        <v>96</v>
+        <v>14</v>
       </c>
       <c r="F6" t="s">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="G6" t="s">
-        <v>97</v>
+        <v>128</v>
       </c>
       <c r="H6" t="s">
         <v>1</v>
@@ -2053,22 +2686,22 @@
     </row>
     <row r="7" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
-        <v>98</v>
+        <v>129</v>
       </c>
       <c r="C7" t="s">
-        <v>99</v>
+        <v>60</v>
       </c>
       <c r="D7" t="s">
-        <v>100</v>
+        <v>130</v>
       </c>
       <c r="E7" t="s">
-        <v>101</v>
+        <v>131</v>
       </c>
       <c r="F7" t="s">
-        <v>102</v>
+        <v>132</v>
       </c>
       <c r="G7" t="s">
-        <v>103</v>
+        <v>133</v>
       </c>
       <c r="H7" t="s">
         <v>1</v>
@@ -2076,22 +2709,22 @@
     </row>
     <row r="8" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
-        <v>104</v>
+        <v>134</v>
       </c>
       <c r="C8" t="s">
-        <v>10</v>
+        <v>60</v>
       </c>
       <c r="D8" t="s">
-        <v>105</v>
+        <v>130</v>
       </c>
       <c r="E8" t="s">
-        <v>106</v>
+        <v>131</v>
       </c>
       <c r="F8" t="s">
-        <v>0</v>
+        <v>132</v>
       </c>
       <c r="G8" t="s">
-        <v>107</v>
+        <v>133</v>
       </c>
       <c r="H8" t="s">
         <v>1</v>
@@ -2099,22 +2732,22 @@
     </row>
     <row r="9" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
-        <v>108</v>
+        <v>135</v>
       </c>
       <c r="C9" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="D9" t="s">
-        <v>109</v>
+        <v>136</v>
       </c>
       <c r="E9" t="s">
-        <v>110</v>
+        <v>137</v>
       </c>
       <c r="F9" t="s">
-        <v>0</v>
+        <v>138</v>
       </c>
       <c r="G9" t="s">
-        <v>111</v>
+        <v>139</v>
       </c>
       <c r="H9" t="s">
         <v>1</v>
@@ -2122,22 +2755,22 @@
     </row>
     <row r="10" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
-        <v>46</v>
+        <v>140</v>
       </c>
       <c r="C10" t="s">
-        <v>3</v>
+        <v>17</v>
       </c>
       <c r="D10" t="s">
-        <v>47</v>
+        <v>141</v>
       </c>
       <c r="E10" t="s">
-        <v>43</v>
+        <v>142</v>
       </c>
       <c r="F10" t="s">
-        <v>0</v>
+        <v>143</v>
       </c>
       <c r="G10" t="s">
-        <v>48</v>
+        <v>144</v>
       </c>
       <c r="H10" t="s">
         <v>1</v>
@@ -2145,22 +2778,22 @@
     </row>
     <row r="11" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A11" t="s">
-        <v>112</v>
+        <v>145</v>
       </c>
       <c r="C11" t="s">
-        <v>8</v>
+        <v>17</v>
       </c>
       <c r="D11" t="s">
-        <v>113</v>
+        <v>141</v>
       </c>
       <c r="E11" t="s">
-        <v>28</v>
+        <v>142</v>
       </c>
       <c r="F11" t="s">
-        <v>29</v>
+        <v>143</v>
       </c>
       <c r="G11" t="s">
-        <v>114</v>
+        <v>144</v>
       </c>
       <c r="H11" t="s">
         <v>1</v>
@@ -2168,22 +2801,22 @@
     </row>
     <row r="12" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A12" t="s">
-        <v>115</v>
+        <v>146</v>
       </c>
       <c r="C12" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="D12" t="s">
-        <v>116</v>
+        <v>147</v>
       </c>
       <c r="E12" t="s">
-        <v>106</v>
+        <v>148</v>
       </c>
       <c r="F12" t="s">
-        <v>0</v>
+        <v>149</v>
       </c>
       <c r="G12" t="s">
-        <v>117</v>
+        <v>150</v>
       </c>
       <c r="H12" t="s">
         <v>1</v>
@@ -2191,22 +2824,22 @@
     </row>
     <row r="13" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A13" t="s">
-        <v>118</v>
+        <v>151</v>
       </c>
       <c r="C13" t="s">
         <v>10</v>
       </c>
       <c r="D13" t="s">
-        <v>116</v>
+        <v>152</v>
       </c>
       <c r="E13" t="s">
-        <v>106</v>
+        <v>153</v>
       </c>
       <c r="F13" t="s">
         <v>0</v>
       </c>
       <c r="G13" t="s">
-        <v>117</v>
+        <v>154</v>
       </c>
       <c r="H13" t="s">
         <v>1</v>
@@ -2214,22 +2847,22 @@
     </row>
     <row r="14" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A14" t="s">
-        <v>119</v>
+        <v>155</v>
       </c>
       <c r="C14" t="s">
-        <v>53</v>
+        <v>11</v>
       </c>
       <c r="D14" t="s">
-        <v>120</v>
+        <v>156</v>
       </c>
       <c r="E14" t="s">
-        <v>44</v>
+        <v>157</v>
       </c>
       <c r="F14" t="s">
-        <v>45</v>
+        <v>158</v>
       </c>
       <c r="G14" t="s">
-        <v>121</v>
+        <v>159</v>
       </c>
       <c r="H14" t="s">
         <v>1</v>
@@ -2237,22 +2870,22 @@
     </row>
     <row r="15" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A15" t="s">
-        <v>122</v>
+        <v>160</v>
       </c>
       <c r="C15" t="s">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="D15" t="s">
-        <v>123</v>
+        <v>156</v>
       </c>
       <c r="E15" t="s">
-        <v>31</v>
+        <v>157</v>
       </c>
       <c r="F15" t="s">
-        <v>32</v>
+        <v>158</v>
       </c>
       <c r="G15" t="s">
-        <v>124</v>
+        <v>159</v>
       </c>
       <c r="H15" t="s">
         <v>1</v>
@@ -2260,22 +2893,22 @@
     </row>
     <row r="16" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A16" t="s">
-        <v>125</v>
+        <v>161</v>
       </c>
       <c r="C16" t="s">
-        <v>8</v>
+        <v>54</v>
       </c>
       <c r="D16" t="s">
-        <v>123</v>
+        <v>162</v>
       </c>
       <c r="E16" t="s">
-        <v>31</v>
+        <v>163</v>
       </c>
       <c r="F16" t="s">
-        <v>32</v>
+        <v>164</v>
       </c>
       <c r="G16" t="s">
-        <v>124</v>
+        <v>165</v>
       </c>
       <c r="H16" t="s">
         <v>1</v>
@@ -2283,22 +2916,22 @@
     </row>
     <row r="17" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A17" t="s">
-        <v>126</v>
+        <v>166</v>
       </c>
       <c r="C17" t="s">
-        <v>91</v>
+        <v>11</v>
       </c>
       <c r="D17" t="s">
-        <v>127</v>
+        <v>167</v>
       </c>
       <c r="E17" t="s">
-        <v>128</v>
+        <v>42</v>
       </c>
       <c r="F17" t="s">
-        <v>129</v>
+        <v>43</v>
       </c>
       <c r="G17" t="s">
-        <v>130</v>
+        <v>168</v>
       </c>
       <c r="H17" t="s">
         <v>1</v>
@@ -2306,22 +2939,22 @@
     </row>
     <row r="18" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A18" t="s">
-        <v>131</v>
+        <v>169</v>
       </c>
       <c r="C18" t="s">
-        <v>99</v>
+        <v>11</v>
       </c>
       <c r="D18" t="s">
-        <v>132</v>
+        <v>167</v>
       </c>
       <c r="E18" t="s">
-        <v>133</v>
+        <v>42</v>
       </c>
       <c r="F18" t="s">
-        <v>134</v>
+        <v>43</v>
       </c>
       <c r="G18" t="s">
-        <v>135</v>
+        <v>168</v>
       </c>
       <c r="H18" t="s">
         <v>1</v>
@@ -2329,22 +2962,22 @@
     </row>
     <row r="19" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A19" t="s">
-        <v>136</v>
+        <v>63</v>
       </c>
       <c r="C19" t="s">
-        <v>22</v>
+        <v>16</v>
       </c>
       <c r="D19" t="s">
-        <v>137</v>
+        <v>65</v>
       </c>
       <c r="E19" t="s">
-        <v>138</v>
+        <v>66</v>
       </c>
       <c r="F19" t="s">
-        <v>139</v>
+        <v>0</v>
       </c>
       <c r="G19" t="s">
-        <v>140</v>
+        <v>67</v>
       </c>
       <c r="H19" t="s">
         <v>1</v>
@@ -2352,22 +2985,22 @@
     </row>
     <row r="20" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A20" t="s">
-        <v>141</v>
+        <v>170</v>
       </c>
       <c r="C20" t="s">
-        <v>2</v>
+        <v>171</v>
       </c>
       <c r="D20" t="s">
-        <v>142</v>
+        <v>172</v>
       </c>
       <c r="E20" t="s">
-        <v>143</v>
+        <v>173</v>
       </c>
       <c r="F20" t="s">
-        <v>144</v>
+        <v>174</v>
       </c>
       <c r="G20" t="s">
-        <v>145</v>
+        <v>175</v>
       </c>
       <c r="H20" t="s">
         <v>1</v>
@@ -2375,22 +3008,22 @@
     </row>
     <row r="21" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A21" t="s">
-        <v>146</v>
+        <v>176</v>
       </c>
       <c r="C21" t="s">
-        <v>53</v>
+        <v>119</v>
       </c>
       <c r="D21" t="s">
-        <v>147</v>
+        <v>177</v>
       </c>
       <c r="E21" t="s">
-        <v>148</v>
+        <v>178</v>
       </c>
       <c r="F21" t="s">
         <v>0</v>
       </c>
       <c r="G21" t="s">
-        <v>149</v>
+        <v>179</v>
       </c>
       <c r="H21" t="s">
         <v>1</v>
@@ -2398,22 +3031,22 @@
     </row>
     <row r="22" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A22" t="s">
-        <v>150</v>
+        <v>180</v>
       </c>
       <c r="C22" t="s">
-        <v>151</v>
+        <v>119</v>
       </c>
       <c r="D22" t="s">
-        <v>152</v>
+        <v>177</v>
       </c>
       <c r="E22" t="s">
-        <v>153</v>
+        <v>178</v>
       </c>
       <c r="F22" t="s">
         <v>0</v>
       </c>
       <c r="G22" t="s">
-        <v>154</v>
+        <v>179</v>
       </c>
       <c r="H22" t="s">
         <v>1</v>
@@ -2421,22 +3054,22 @@
     </row>
     <row r="23" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A23" t="s">
-        <v>155</v>
+        <v>181</v>
       </c>
       <c r="C23" t="s">
-        <v>151</v>
+        <v>9</v>
       </c>
       <c r="D23" t="s">
-        <v>152</v>
+        <v>182</v>
       </c>
       <c r="E23" t="s">
-        <v>153</v>
+        <v>44</v>
       </c>
       <c r="F23" t="s">
         <v>0</v>
       </c>
       <c r="G23" t="s">
-        <v>154</v>
+        <v>183</v>
       </c>
       <c r="H23" t="s">
         <v>1</v>
@@ -2444,22 +3077,22 @@
     </row>
     <row r="24" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A24" t="s">
-        <v>156</v>
+        <v>184</v>
       </c>
       <c r="C24" t="s">
-        <v>22</v>
+        <v>119</v>
       </c>
       <c r="D24" t="s">
-        <v>157</v>
+        <v>185</v>
       </c>
       <c r="E24" t="s">
-        <v>158</v>
+        <v>88</v>
       </c>
       <c r="F24" t="s">
-        <v>159</v>
+        <v>0</v>
       </c>
       <c r="G24" t="s">
-        <v>160</v>
+        <v>186</v>
       </c>
       <c r="H24" t="s">
         <v>1</v>
@@ -2467,22 +3100,22 @@
     </row>
     <row r="25" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A25" t="s">
-        <v>161</v>
+        <v>187</v>
       </c>
       <c r="C25" t="s">
-        <v>151</v>
+        <v>119</v>
       </c>
       <c r="D25" t="s">
-        <v>162</v>
+        <v>188</v>
       </c>
       <c r="E25" t="s">
-        <v>34</v>
+        <v>178</v>
       </c>
       <c r="F25" t="s">
         <v>0</v>
       </c>
       <c r="G25" t="s">
-        <v>69</v>
+        <v>189</v>
       </c>
       <c r="H25" t="s">
         <v>1</v>
@@ -2490,22 +3123,22 @@
     </row>
     <row r="26" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A26" t="s">
-        <v>163</v>
+        <v>190</v>
       </c>
       <c r="C26" t="s">
-        <v>164</v>
+        <v>119</v>
       </c>
       <c r="D26" t="s">
-        <v>165</v>
+        <v>188</v>
       </c>
       <c r="E26" t="s">
-        <v>166</v>
+        <v>178</v>
       </c>
       <c r="F26" t="s">
         <v>0</v>
       </c>
       <c r="G26" t="s">
-        <v>167</v>
+        <v>189</v>
       </c>
       <c r="H26" t="s">
         <v>1</v>
@@ -2513,22 +3146,22 @@
     </row>
     <row r="27" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A27" t="s">
-        <v>168</v>
+        <v>191</v>
       </c>
       <c r="C27" t="s">
-        <v>9</v>
+        <v>69</v>
       </c>
       <c r="D27" t="s">
-        <v>169</v>
+        <v>192</v>
       </c>
       <c r="E27" t="s">
-        <v>170</v>
+        <v>193</v>
       </c>
       <c r="F27" t="s">
         <v>0</v>
       </c>
       <c r="G27" t="s">
-        <v>171</v>
+        <v>194</v>
       </c>
       <c r="H27" t="s">
         <v>1</v>
@@ -2536,22 +3169,22 @@
     </row>
     <row r="28" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A28" t="s">
-        <v>172</v>
+        <v>195</v>
       </c>
       <c r="C28" t="s">
-        <v>2</v>
+        <v>69</v>
       </c>
       <c r="D28" t="s">
-        <v>173</v>
+        <v>192</v>
       </c>
       <c r="E28" t="s">
-        <v>80</v>
+        <v>193</v>
       </c>
       <c r="F28" t="s">
         <v>0</v>
       </c>
       <c r="G28" t="s">
-        <v>174</v>
+        <v>194</v>
       </c>
       <c r="H28" t="s">
         <v>1</v>
@@ -2559,22 +3192,22 @@
     </row>
     <row r="29" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A29" t="s">
-        <v>175</v>
+        <v>196</v>
       </c>
       <c r="C29" t="s">
-        <v>22</v>
+        <v>69</v>
       </c>
       <c r="D29" t="s">
-        <v>176</v>
+        <v>197</v>
       </c>
       <c r="E29" t="s">
-        <v>177</v>
+        <v>85</v>
       </c>
       <c r="F29" t="s">
         <v>0</v>
       </c>
       <c r="G29" t="s">
-        <v>178</v>
+        <v>198</v>
       </c>
       <c r="H29" t="s">
         <v>1</v>
@@ -2582,22 +3215,22 @@
     </row>
     <row r="30" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A30" t="s">
-        <v>179</v>
+        <v>199</v>
       </c>
       <c r="C30" t="s">
-        <v>22</v>
+        <v>8</v>
       </c>
       <c r="D30" t="s">
-        <v>176</v>
+        <v>200</v>
       </c>
       <c r="E30" t="s">
-        <v>177</v>
+        <v>99</v>
       </c>
       <c r="F30" t="s">
         <v>0</v>
       </c>
       <c r="G30" t="s">
-        <v>178</v>
+        <v>201</v>
       </c>
       <c r="H30" t="s">
         <v>1</v>
@@ -2605,22 +3238,22 @@
     </row>
     <row r="31" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A31" t="s">
-        <v>180</v>
+        <v>202</v>
       </c>
       <c r="C31" t="s">
-        <v>22</v>
+        <v>8</v>
       </c>
       <c r="D31" t="s">
-        <v>176</v>
+        <v>200</v>
       </c>
       <c r="E31" t="s">
-        <v>177</v>
+        <v>99</v>
       </c>
       <c r="F31" t="s">
         <v>0</v>
       </c>
       <c r="G31" t="s">
-        <v>178</v>
+        <v>201</v>
       </c>
       <c r="H31" t="s">
         <v>1</v>
@@ -2628,22 +3261,22 @@
     </row>
     <row r="32" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A32" t="s">
-        <v>181</v>
+        <v>203</v>
       </c>
       <c r="C32" t="s">
-        <v>164</v>
+        <v>60</v>
       </c>
       <c r="D32" t="s">
-        <v>182</v>
+        <v>204</v>
       </c>
       <c r="E32" t="s">
-        <v>183</v>
+        <v>205</v>
       </c>
       <c r="F32" t="s">
         <v>0</v>
       </c>
       <c r="G32" t="s">
-        <v>184</v>
+        <v>90</v>
       </c>
       <c r="H32" t="s">
         <v>1</v>
@@ -2651,275 +3284,275 @@
     </row>
     <row r="33" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A33" t="s">
-        <v>185</v>
+        <v>206</v>
       </c>
       <c r="C33" t="s">
-        <v>19</v>
+        <v>60</v>
       </c>
       <c r="D33" t="s">
-        <v>186</v>
+        <v>204</v>
       </c>
       <c r="E33" t="s">
-        <v>75</v>
+        <v>205</v>
       </c>
       <c r="F33" t="s">
         <v>0</v>
       </c>
       <c r="G33" t="s">
-        <v>187</v>
+        <v>90</v>
       </c>
       <c r="H33" t="s">
-        <v>49</v>
+        <v>1</v>
       </c>
     </row>
     <row r="34" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A34" t="s">
-        <v>188</v>
+        <v>207</v>
       </c>
       <c r="C34" t="s">
-        <v>189</v>
+        <v>69</v>
       </c>
       <c r="D34" t="s">
-        <v>190</v>
+        <v>208</v>
       </c>
       <c r="E34" t="s">
-        <v>191</v>
+        <v>209</v>
       </c>
       <c r="F34" t="s">
         <v>0</v>
       </c>
       <c r="G34" t="s">
-        <v>192</v>
+        <v>210</v>
       </c>
       <c r="H34" t="s">
-        <v>49</v>
+        <v>1</v>
       </c>
     </row>
     <row r="35" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A35" t="s">
-        <v>193</v>
+        <v>211</v>
       </c>
       <c r="C35" t="s">
-        <v>10</v>
+        <v>69</v>
       </c>
       <c r="D35" t="s">
-        <v>194</v>
+        <v>212</v>
       </c>
       <c r="E35" t="s">
-        <v>30</v>
+        <v>85</v>
       </c>
       <c r="F35" t="s">
         <v>0</v>
       </c>
       <c r="G35" t="s">
-        <v>195</v>
+        <v>213</v>
       </c>
       <c r="H35" t="s">
-        <v>62</v>
+        <v>1</v>
       </c>
     </row>
     <row r="36" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A36" t="s">
-        <v>196</v>
+        <v>214</v>
       </c>
       <c r="C36" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="D36" t="s">
-        <v>197</v>
+        <v>215</v>
       </c>
       <c r="E36" t="s">
-        <v>198</v>
+        <v>216</v>
       </c>
       <c r="F36" t="s">
         <v>0</v>
       </c>
       <c r="G36" t="s">
-        <v>199</v>
+        <v>217</v>
       </c>
       <c r="H36" t="s">
-        <v>62</v>
+        <v>1</v>
       </c>
     </row>
     <row r="37" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A37" t="s">
-        <v>200</v>
+        <v>218</v>
       </c>
       <c r="C37" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="D37" t="s">
-        <v>201</v>
+        <v>219</v>
       </c>
       <c r="E37" t="s">
-        <v>76</v>
+        <v>220</v>
       </c>
       <c r="F37" t="s">
-        <v>77</v>
+        <v>0</v>
       </c>
       <c r="G37" t="s">
-        <v>81</v>
+        <v>221</v>
       </c>
       <c r="H37" t="s">
-        <v>62</v>
+        <v>1</v>
       </c>
     </row>
     <row r="38" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A38" t="s">
-        <v>202</v>
+        <v>222</v>
       </c>
       <c r="C38" t="s">
-        <v>91</v>
+        <v>41</v>
       </c>
       <c r="D38" t="s">
-        <v>203</v>
+        <v>223</v>
       </c>
       <c r="E38" t="s">
-        <v>26</v>
+        <v>224</v>
       </c>
       <c r="F38" t="s">
-        <v>27</v>
+        <v>0</v>
       </c>
       <c r="G38" t="s">
-        <v>204</v>
+        <v>225</v>
       </c>
       <c r="H38" t="s">
-        <v>4</v>
+        <v>1</v>
       </c>
     </row>
     <row r="39" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A39" t="s">
-        <v>205</v>
+        <v>226</v>
       </c>
       <c r="C39" t="s">
-        <v>19</v>
+        <v>3</v>
       </c>
       <c r="D39" t="s">
-        <v>206</v>
+        <v>227</v>
       </c>
       <c r="E39" t="s">
-        <v>207</v>
+        <v>228</v>
       </c>
       <c r="F39" t="s">
         <v>0</v>
       </c>
       <c r="G39" t="s">
-        <v>208</v>
+        <v>229</v>
       </c>
       <c r="H39" t="s">
-        <v>4</v>
+        <v>1</v>
       </c>
     </row>
     <row r="40" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A40" t="s">
-        <v>209</v>
+        <v>230</v>
       </c>
       <c r="C40" t="s">
-        <v>19</v>
+        <v>60</v>
       </c>
       <c r="D40" t="s">
-        <v>206</v>
+        <v>231</v>
       </c>
       <c r="E40" t="s">
-        <v>207</v>
+        <v>232</v>
       </c>
       <c r="F40" t="s">
-        <v>0</v>
+        <v>233</v>
       </c>
       <c r="G40" t="s">
-        <v>208</v>
+        <v>234</v>
       </c>
       <c r="H40" t="s">
-        <v>4</v>
+        <v>38</v>
       </c>
     </row>
     <row r="41" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A41" t="s">
-        <v>210</v>
+        <v>235</v>
       </c>
       <c r="C41" t="s">
-        <v>189</v>
+        <v>10</v>
       </c>
       <c r="D41" t="s">
-        <v>211</v>
+        <v>236</v>
       </c>
       <c r="E41" t="s">
-        <v>212</v>
+        <v>73</v>
       </c>
       <c r="F41" t="s">
         <v>0</v>
       </c>
       <c r="G41" t="s">
-        <v>213</v>
+        <v>237</v>
       </c>
       <c r="H41" t="s">
-        <v>4</v>
+        <v>38</v>
       </c>
     </row>
     <row r="42" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A42" t="s">
-        <v>214</v>
+        <v>238</v>
       </c>
       <c r="C42" t="s">
-        <v>189</v>
+        <v>239</v>
       </c>
       <c r="D42" t="s">
-        <v>211</v>
+        <v>240</v>
       </c>
       <c r="E42" t="s">
-        <v>212</v>
+        <v>74</v>
       </c>
       <c r="F42" t="s">
-        <v>0</v>
+        <v>75</v>
       </c>
       <c r="G42" t="s">
-        <v>213</v>
+        <v>241</v>
       </c>
       <c r="H42" t="s">
-        <v>4</v>
+        <v>38</v>
       </c>
     </row>
     <row r="43" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A43" t="s">
-        <v>215</v>
+        <v>242</v>
       </c>
       <c r="C43" t="s">
         <v>8</v>
       </c>
       <c r="D43" t="s">
-        <v>216</v>
+        <v>243</v>
       </c>
       <c r="E43" t="s">
-        <v>217</v>
+        <v>244</v>
       </c>
       <c r="F43" t="s">
-        <v>218</v>
+        <v>245</v>
       </c>
       <c r="G43" t="s">
-        <v>219</v>
+        <v>246</v>
       </c>
       <c r="H43" t="s">
-        <v>4</v>
+        <v>38</v>
       </c>
     </row>
     <row r="44" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A44" t="s">
-        <v>64</v>
+        <v>247</v>
       </c>
       <c r="C44" t="s">
-        <v>13</v>
+        <v>18</v>
       </c>
       <c r="D44" t="s">
-        <v>65</v>
+        <v>248</v>
       </c>
       <c r="E44" t="s">
-        <v>15</v>
+        <v>249</v>
       </c>
       <c r="F44" t="s">
-        <v>16</v>
+        <v>0</v>
       </c>
       <c r="G44" t="s">
-        <v>66</v>
+        <v>250</v>
       </c>
       <c r="H44" t="s">
         <v>4</v>
@@ -2927,22 +3560,22 @@
     </row>
     <row r="45" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A45" t="s">
-        <v>67</v>
+        <v>251</v>
       </c>
       <c r="C45" t="s">
-        <v>13</v>
+        <v>119</v>
       </c>
       <c r="D45" t="s">
-        <v>65</v>
+        <v>252</v>
       </c>
       <c r="E45" t="s">
-        <v>15</v>
+        <v>253</v>
       </c>
       <c r="F45" t="s">
-        <v>16</v>
+        <v>0</v>
       </c>
       <c r="G45" t="s">
-        <v>66</v>
+        <v>254</v>
       </c>
       <c r="H45" t="s">
         <v>4</v>
@@ -2950,22 +3583,22 @@
     </row>
     <row r="46" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A46" t="s">
-        <v>68</v>
+        <v>255</v>
       </c>
       <c r="C46" t="s">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="D46" t="s">
-        <v>65</v>
+        <v>256</v>
       </c>
       <c r="E46" t="s">
-        <v>15</v>
+        <v>257</v>
       </c>
       <c r="F46" t="s">
-        <v>16</v>
+        <v>0</v>
       </c>
       <c r="G46" t="s">
-        <v>66</v>
+        <v>258</v>
       </c>
       <c r="H46" t="s">
         <v>4</v>
@@ -2973,22 +3606,22 @@
     </row>
     <row r="47" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A47" t="s">
-        <v>220</v>
+        <v>76</v>
       </c>
       <c r="C47" t="s">
-        <v>19</v>
+        <v>119</v>
       </c>
       <c r="D47" t="s">
-        <v>221</v>
+        <v>77</v>
       </c>
       <c r="E47" t="s">
-        <v>84</v>
+        <v>78</v>
       </c>
       <c r="F47" t="s">
         <v>0</v>
       </c>
       <c r="G47" t="s">
-        <v>222</v>
+        <v>79</v>
       </c>
       <c r="H47" t="s">
         <v>4</v>
@@ -2996,22 +3629,22 @@
     </row>
     <row r="48" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A48" t="s">
-        <v>223</v>
+        <v>259</v>
       </c>
       <c r="C48" t="s">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="D48" t="s">
-        <v>224</v>
+        <v>260</v>
       </c>
       <c r="E48" t="s">
-        <v>225</v>
+        <v>25</v>
       </c>
       <c r="F48" t="s">
-        <v>226</v>
+        <v>26</v>
       </c>
       <c r="G48" t="s">
-        <v>227</v>
+        <v>261</v>
       </c>
       <c r="H48" t="s">
         <v>4</v>
@@ -3019,22 +3652,22 @@
     </row>
     <row r="49" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A49" t="s">
-        <v>228</v>
+        <v>262</v>
       </c>
       <c r="C49" t="s">
-        <v>11</v>
+        <v>239</v>
       </c>
       <c r="D49" t="s">
-        <v>229</v>
+        <v>263</v>
       </c>
       <c r="E49" t="s">
-        <v>230</v>
+        <v>74</v>
       </c>
       <c r="F49" t="s">
-        <v>0</v>
+        <v>75</v>
       </c>
       <c r="G49" t="s">
-        <v>231</v>
+        <v>264</v>
       </c>
       <c r="H49" t="s">
         <v>4</v>
@@ -3042,22 +3675,22 @@
     </row>
     <row r="50" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A50" t="s">
-        <v>232</v>
+        <v>265</v>
       </c>
       <c r="C50" t="s">
-        <v>11</v>
+        <v>239</v>
       </c>
       <c r="D50" t="s">
-        <v>233</v>
+        <v>263</v>
       </c>
       <c r="E50" t="s">
-        <v>234</v>
+        <v>74</v>
       </c>
       <c r="F50" t="s">
-        <v>0</v>
+        <v>75</v>
       </c>
       <c r="G50" t="s">
-        <v>235</v>
+        <v>264</v>
       </c>
       <c r="H50" t="s">
         <v>4</v>
@@ -3065,22 +3698,22 @@
     </row>
     <row r="51" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A51" t="s">
-        <v>236</v>
+        <v>266</v>
       </c>
       <c r="C51" t="s">
-        <v>189</v>
+        <v>239</v>
       </c>
       <c r="D51" t="s">
-        <v>237</v>
+        <v>263</v>
       </c>
       <c r="E51" t="s">
-        <v>33</v>
+        <v>74</v>
       </c>
       <c r="F51" t="s">
-        <v>0</v>
+        <v>75</v>
       </c>
       <c r="G51" t="s">
-        <v>111</v>
+        <v>264</v>
       </c>
       <c r="H51" t="s">
         <v>4</v>
@@ -3088,22 +3721,22 @@
     </row>
     <row r="52" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A52" t="s">
-        <v>238</v>
+        <v>267</v>
       </c>
       <c r="C52" t="s">
-        <v>189</v>
+        <v>12</v>
       </c>
       <c r="D52" t="s">
-        <v>237</v>
+        <v>268</v>
       </c>
       <c r="E52" t="s">
-        <v>33</v>
+        <v>269</v>
       </c>
       <c r="F52" t="s">
         <v>0</v>
       </c>
       <c r="G52" t="s">
-        <v>111</v>
+        <v>270</v>
       </c>
       <c r="H52" t="s">
         <v>4</v>
@@ -3111,22 +3744,22 @@
     </row>
     <row r="53" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A53" t="s">
-        <v>239</v>
+        <v>271</v>
       </c>
       <c r="C53" t="s">
-        <v>189</v>
+        <v>12</v>
       </c>
       <c r="D53" t="s">
-        <v>237</v>
+        <v>268</v>
       </c>
       <c r="E53" t="s">
-        <v>33</v>
+        <v>269</v>
       </c>
       <c r="F53" t="s">
         <v>0</v>
       </c>
       <c r="G53" t="s">
-        <v>111</v>
+        <v>270</v>
       </c>
       <c r="H53" t="s">
         <v>4</v>
@@ -3134,22 +3767,22 @@
     </row>
     <row r="54" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A54" t="s">
-        <v>240</v>
+        <v>272</v>
       </c>
       <c r="C54" t="s">
-        <v>99</v>
+        <v>41</v>
       </c>
       <c r="D54" t="s">
-        <v>241</v>
+        <v>273</v>
       </c>
       <c r="E54" t="s">
-        <v>242</v>
+        <v>46</v>
       </c>
       <c r="F54" t="s">
-        <v>243</v>
+        <v>47</v>
       </c>
       <c r="G54" t="s">
-        <v>35</v>
+        <v>274</v>
       </c>
       <c r="H54" t="s">
         <v>4</v>
@@ -3157,22 +3790,22 @@
     </row>
     <row r="55" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A55" t="s">
-        <v>244</v>
+        <v>275</v>
       </c>
       <c r="C55" t="s">
-        <v>99</v>
+        <v>8</v>
       </c>
       <c r="D55" t="s">
-        <v>241</v>
+        <v>276</v>
       </c>
       <c r="E55" t="s">
-        <v>242</v>
+        <v>137</v>
       </c>
       <c r="F55" t="s">
-        <v>243</v>
+        <v>138</v>
       </c>
       <c r="G55" t="s">
-        <v>35</v>
+        <v>277</v>
       </c>
       <c r="H55" t="s">
         <v>4</v>
@@ -3180,22 +3813,22 @@
     </row>
     <row r="56" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A56" t="s">
-        <v>245</v>
+        <v>278</v>
       </c>
       <c r="C56" t="s">
-        <v>99</v>
+        <v>8</v>
       </c>
       <c r="D56" t="s">
-        <v>241</v>
+        <v>276</v>
       </c>
       <c r="E56" t="s">
-        <v>242</v>
+        <v>137</v>
       </c>
       <c r="F56" t="s">
-        <v>243</v>
+        <v>138</v>
       </c>
       <c r="G56" t="s">
-        <v>35</v>
+        <v>277</v>
       </c>
       <c r="H56" t="s">
         <v>4</v>
@@ -3203,22 +3836,22 @@
     </row>
     <row r="57" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A57" t="s">
-        <v>246</v>
+        <v>279</v>
       </c>
       <c r="C57" t="s">
-        <v>9</v>
+        <v>239</v>
       </c>
       <c r="D57" t="s">
-        <v>247</v>
+        <v>280</v>
       </c>
       <c r="E57" t="s">
-        <v>51</v>
+        <v>96</v>
       </c>
       <c r="F57" t="s">
-        <v>0</v>
+        <v>97</v>
       </c>
       <c r="G57" t="s">
-        <v>248</v>
+        <v>281</v>
       </c>
       <c r="H57" t="s">
         <v>4</v>
@@ -3226,22 +3859,22 @@
     </row>
     <row r="58" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A58" t="s">
-        <v>249</v>
+        <v>282</v>
       </c>
       <c r="C58" t="s">
-        <v>10</v>
+        <v>54</v>
       </c>
       <c r="D58" t="s">
-        <v>250</v>
+        <v>283</v>
       </c>
       <c r="E58" t="s">
-        <v>251</v>
+        <v>6</v>
       </c>
       <c r="F58" t="s">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="G58" t="s">
-        <v>252</v>
+        <v>284</v>
       </c>
       <c r="H58" t="s">
         <v>4</v>
@@ -3249,22 +3882,22 @@
     </row>
     <row r="59" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A59" t="s">
-        <v>253</v>
+        <v>285</v>
       </c>
       <c r="C59" t="s">
-        <v>10</v>
+        <v>69</v>
       </c>
       <c r="D59" t="s">
-        <v>250</v>
+        <v>286</v>
       </c>
       <c r="E59" t="s">
-        <v>251</v>
+        <v>193</v>
       </c>
       <c r="F59" t="s">
         <v>0</v>
       </c>
       <c r="G59" t="s">
-        <v>252</v>
+        <v>287</v>
       </c>
       <c r="H59" t="s">
         <v>4</v>
@@ -3272,22 +3905,22 @@
     </row>
     <row r="60" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A60" t="s">
-        <v>254</v>
+        <v>288</v>
       </c>
       <c r="C60" t="s">
-        <v>9</v>
+        <v>69</v>
       </c>
       <c r="D60" t="s">
-        <v>255</v>
+        <v>286</v>
       </c>
       <c r="E60" t="s">
-        <v>76</v>
+        <v>193</v>
       </c>
       <c r="F60" t="s">
-        <v>77</v>
+        <v>0</v>
       </c>
       <c r="G60" t="s">
-        <v>256</v>
+        <v>287</v>
       </c>
       <c r="H60" t="s">
         <v>4</v>
@@ -3295,22 +3928,22 @@
     </row>
     <row r="61" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A61" t="s">
-        <v>257</v>
+        <v>289</v>
       </c>
       <c r="C61" t="s">
-        <v>91</v>
+        <v>16</v>
       </c>
       <c r="D61" t="s">
-        <v>258</v>
+        <v>290</v>
       </c>
       <c r="E61" t="s">
-        <v>6</v>
+        <v>109</v>
       </c>
       <c r="F61" t="s">
-        <v>7</v>
+        <v>110</v>
       </c>
       <c r="G61" t="s">
-        <v>259</v>
+        <v>291</v>
       </c>
       <c r="H61" t="s">
         <v>4</v>
@@ -3318,22 +3951,22 @@
     </row>
     <row r="62" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A62" t="s">
-        <v>260</v>
+        <v>292</v>
       </c>
       <c r="C62" t="s">
-        <v>3</v>
+        <v>16</v>
       </c>
       <c r="D62" t="s">
-        <v>261</v>
+        <v>293</v>
       </c>
       <c r="E62" t="s">
-        <v>43</v>
+        <v>294</v>
       </c>
       <c r="F62" t="s">
         <v>0</v>
       </c>
       <c r="G62" t="s">
-        <v>262</v>
+        <v>295</v>
       </c>
       <c r="H62" t="s">
         <v>4</v>
@@ -3341,22 +3974,22 @@
     </row>
     <row r="63" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A63" t="s">
-        <v>263</v>
+        <v>296</v>
       </c>
       <c r="C63" t="s">
-        <v>164</v>
+        <v>64</v>
       </c>
       <c r="D63" t="s">
-        <v>264</v>
+        <v>297</v>
       </c>
       <c r="E63" t="s">
-        <v>183</v>
+        <v>298</v>
       </c>
       <c r="F63" t="s">
-        <v>0</v>
+        <v>299</v>
       </c>
       <c r="G63" t="s">
-        <v>265</v>
+        <v>300</v>
       </c>
       <c r="H63" t="s">
         <v>4</v>
@@ -3364,22 +3997,22 @@
     </row>
     <row r="64" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A64" t="s">
-        <v>266</v>
+        <v>301</v>
       </c>
       <c r="C64" t="s">
-        <v>9</v>
+        <v>54</v>
       </c>
       <c r="D64" t="s">
-        <v>267</v>
+        <v>302</v>
       </c>
       <c r="E64" t="s">
-        <v>268</v>
+        <v>303</v>
       </c>
       <c r="F64" t="s">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="G64" t="s">
-        <v>269</v>
+        <v>304</v>
       </c>
       <c r="H64" t="s">
         <v>4</v>
@@ -3387,22 +4020,22 @@
     </row>
     <row r="65" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A65" t="s">
-        <v>270</v>
+        <v>305</v>
       </c>
       <c r="C65" t="s">
-        <v>11</v>
+        <v>2</v>
       </c>
       <c r="D65" t="s">
-        <v>271</v>
+        <v>306</v>
       </c>
       <c r="E65" t="s">
-        <v>272</v>
+        <v>307</v>
       </c>
       <c r="F65" t="s">
         <v>0</v>
       </c>
       <c r="G65" t="s">
-        <v>273</v>
+        <v>308</v>
       </c>
       <c r="H65" t="s">
         <v>4</v>
@@ -3410,22 +4043,22 @@
     </row>
     <row r="66" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A66" t="s">
-        <v>274</v>
+        <v>309</v>
       </c>
       <c r="C66" t="s">
         <v>11</v>
       </c>
       <c r="D66" t="s">
-        <v>271</v>
+        <v>310</v>
       </c>
       <c r="E66" t="s">
-        <v>272</v>
+        <v>311</v>
       </c>
       <c r="F66" t="s">
-        <v>0</v>
+        <v>312</v>
       </c>
       <c r="G66" t="s">
-        <v>273</v>
+        <v>313</v>
       </c>
       <c r="H66" t="s">
         <v>4</v>
@@ -3433,22 +4066,22 @@
     </row>
     <row r="67" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A67" t="s">
-        <v>275</v>
+        <v>314</v>
       </c>
       <c r="C67" t="s">
-        <v>151</v>
+        <v>60</v>
       </c>
       <c r="D67" t="s">
-        <v>276</v>
+        <v>315</v>
       </c>
       <c r="E67" t="s">
-        <v>277</v>
+        <v>316</v>
       </c>
       <c r="F67" t="s">
-        <v>0</v>
+        <v>317</v>
       </c>
       <c r="G67" t="s">
-        <v>278</v>
+        <v>150</v>
       </c>
       <c r="H67" t="s">
         <v>4</v>
@@ -3456,22 +4089,22 @@
     </row>
     <row r="68" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A68" t="s">
-        <v>279</v>
+        <v>318</v>
       </c>
       <c r="C68" t="s">
-        <v>99</v>
+        <v>60</v>
       </c>
       <c r="D68" t="s">
-        <v>280</v>
+        <v>315</v>
       </c>
       <c r="E68" t="s">
-        <v>71</v>
+        <v>316</v>
       </c>
       <c r="F68" t="s">
-        <v>0</v>
+        <v>317</v>
       </c>
       <c r="G68" t="s">
-        <v>72</v>
+        <v>150</v>
       </c>
       <c r="H68" t="s">
         <v>4</v>
@@ -3479,22 +4112,22 @@
     </row>
     <row r="69" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A69" t="s">
-        <v>281</v>
+        <v>319</v>
       </c>
       <c r="C69" t="s">
-        <v>9</v>
+        <v>2</v>
       </c>
       <c r="D69" t="s">
-        <v>282</v>
+        <v>320</v>
       </c>
       <c r="E69" t="s">
-        <v>283</v>
+        <v>321</v>
       </c>
       <c r="F69" t="s">
         <v>0</v>
       </c>
       <c r="G69" t="s">
-        <v>284</v>
+        <v>322</v>
       </c>
       <c r="H69" t="s">
         <v>4</v>
@@ -3502,22 +4135,22 @@
     </row>
     <row r="70" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A70" t="s">
-        <v>285</v>
+        <v>323</v>
       </c>
       <c r="C70" t="s">
-        <v>9</v>
+        <v>2</v>
       </c>
       <c r="D70" t="s">
-        <v>282</v>
+        <v>320</v>
       </c>
       <c r="E70" t="s">
-        <v>283</v>
+        <v>321</v>
       </c>
       <c r="F70" t="s">
         <v>0</v>
       </c>
       <c r="G70" t="s">
-        <v>284</v>
+        <v>322</v>
       </c>
       <c r="H70" t="s">
         <v>4</v>
@@ -3525,22 +4158,22 @@
     </row>
     <row r="71" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A71" t="s">
-        <v>286</v>
+        <v>324</v>
       </c>
       <c r="C71" t="s">
-        <v>9</v>
+        <v>2</v>
       </c>
       <c r="D71" t="s">
-        <v>282</v>
+        <v>320</v>
       </c>
       <c r="E71" t="s">
-        <v>283</v>
+        <v>321</v>
       </c>
       <c r="F71" t="s">
         <v>0</v>
       </c>
       <c r="G71" t="s">
-        <v>284</v>
+        <v>322</v>
       </c>
       <c r="H71" t="s">
         <v>4</v>
@@ -3548,22 +4181,22 @@
     </row>
     <row r="72" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A72" t="s">
-        <v>287</v>
+        <v>325</v>
       </c>
       <c r="C72" t="s">
-        <v>91</v>
+        <v>69</v>
       </c>
       <c r="D72" t="s">
-        <v>288</v>
+        <v>326</v>
       </c>
       <c r="E72" t="s">
-        <v>289</v>
+        <v>85</v>
       </c>
       <c r="F72" t="s">
-        <v>290</v>
+        <v>0</v>
       </c>
       <c r="G72" t="s">
-        <v>291</v>
+        <v>327</v>
       </c>
       <c r="H72" t="s">
         <v>4</v>
@@ -3571,22 +4204,22 @@
     </row>
     <row r="73" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A73" t="s">
-        <v>292</v>
+        <v>328</v>
       </c>
       <c r="C73" t="s">
-        <v>91</v>
+        <v>16</v>
       </c>
       <c r="D73" t="s">
-        <v>288</v>
+        <v>329</v>
       </c>
       <c r="E73" t="s">
-        <v>289</v>
+        <v>294</v>
       </c>
       <c r="F73" t="s">
-        <v>290</v>
+        <v>0</v>
       </c>
       <c r="G73" t="s">
-        <v>291</v>
+        <v>330</v>
       </c>
       <c r="H73" t="s">
         <v>4</v>
@@ -3594,22 +4227,22 @@
     </row>
     <row r="74" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A74" t="s">
-        <v>293</v>
+        <v>331</v>
       </c>
       <c r="C74" t="s">
-        <v>91</v>
+        <v>69</v>
       </c>
       <c r="D74" t="s">
-        <v>288</v>
+        <v>332</v>
       </c>
       <c r="E74" t="s">
-        <v>289</v>
+        <v>100</v>
       </c>
       <c r="F74" t="s">
-        <v>290</v>
+        <v>0</v>
       </c>
       <c r="G74" t="s">
-        <v>291</v>
+        <v>333</v>
       </c>
       <c r="H74" t="s">
         <v>4</v>
@@ -3617,22 +4250,22 @@
     </row>
     <row r="75" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A75" t="s">
-        <v>294</v>
+        <v>334</v>
       </c>
       <c r="C75" t="s">
-        <v>21</v>
+        <v>3</v>
       </c>
       <c r="D75" t="s">
-        <v>295</v>
+        <v>335</v>
       </c>
       <c r="E75" t="s">
-        <v>296</v>
+        <v>336</v>
       </c>
       <c r="F75" t="s">
         <v>0</v>
       </c>
       <c r="G75" t="s">
-        <v>297</v>
+        <v>337</v>
       </c>
       <c r="H75" t="s">
         <v>4</v>
@@ -3640,22 +4273,22 @@
     </row>
     <row r="76" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A76" t="s">
-        <v>298</v>
+        <v>338</v>
       </c>
       <c r="C76" t="s">
-        <v>21</v>
+        <v>13</v>
       </c>
       <c r="D76" t="s">
-        <v>295</v>
+        <v>339</v>
       </c>
       <c r="E76" t="s">
-        <v>296</v>
+        <v>56</v>
       </c>
       <c r="F76" t="s">
         <v>0</v>
       </c>
       <c r="G76" t="s">
-        <v>297</v>
+        <v>340</v>
       </c>
       <c r="H76" t="s">
         <v>4</v>
@@ -3663,22 +4296,22 @@
     </row>
     <row r="77" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A77" t="s">
-        <v>299</v>
+        <v>341</v>
       </c>
       <c r="C77" t="s">
-        <v>58</v>
+        <v>13</v>
       </c>
       <c r="D77" t="s">
-        <v>300</v>
+        <v>342</v>
       </c>
       <c r="E77" t="s">
-        <v>301</v>
+        <v>343</v>
       </c>
       <c r="F77" t="s">
-        <v>302</v>
+        <v>0</v>
       </c>
       <c r="G77" t="s">
-        <v>303</v>
+        <v>344</v>
       </c>
       <c r="H77" t="s">
         <v>4</v>
@@ -3686,22 +4319,22 @@
     </row>
     <row r="78" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A78" t="s">
-        <v>304</v>
+        <v>345</v>
       </c>
       <c r="C78" t="s">
-        <v>58</v>
+        <v>10</v>
       </c>
       <c r="D78" t="s">
-        <v>305</v>
+        <v>346</v>
       </c>
       <c r="E78" t="s">
-        <v>306</v>
+        <v>347</v>
       </c>
       <c r="F78" t="s">
         <v>0</v>
       </c>
       <c r="G78" t="s">
-        <v>307</v>
+        <v>348</v>
       </c>
       <c r="H78" t="s">
         <v>4</v>
@@ -3709,22 +4342,22 @@
     </row>
     <row r="79" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A79" t="s">
-        <v>308</v>
+        <v>349</v>
       </c>
       <c r="C79" t="s">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="D79" t="s">
-        <v>309</v>
+        <v>346</v>
       </c>
       <c r="E79" t="s">
-        <v>15</v>
+        <v>347</v>
       </c>
       <c r="F79" t="s">
-        <v>16</v>
+        <v>0</v>
       </c>
       <c r="G79" t="s">
-        <v>310</v>
+        <v>348</v>
       </c>
       <c r="H79" t="s">
         <v>4</v>
@@ -3732,22 +4365,22 @@
     </row>
     <row r="80" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A80" t="s">
-        <v>311</v>
+        <v>350</v>
       </c>
       <c r="C80" t="s">
-        <v>19</v>
+        <v>10</v>
       </c>
       <c r="D80" t="s">
-        <v>312</v>
+        <v>346</v>
       </c>
       <c r="E80" t="s">
-        <v>207</v>
+        <v>347</v>
       </c>
       <c r="F80" t="s">
         <v>0</v>
       </c>
       <c r="G80" t="s">
-        <v>313</v>
+        <v>348</v>
       </c>
       <c r="H80" t="s">
         <v>4</v>
@@ -3755,22 +4388,22 @@
     </row>
     <row r="81" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A81" t="s">
-        <v>314</v>
+        <v>351</v>
       </c>
       <c r="C81" t="s">
-        <v>11</v>
+        <v>41</v>
       </c>
       <c r="D81" t="s">
-        <v>315</v>
+        <v>352</v>
       </c>
       <c r="E81" t="s">
-        <v>272</v>
+        <v>55</v>
       </c>
       <c r="F81" t="s">
         <v>0</v>
       </c>
       <c r="G81" t="s">
-        <v>316</v>
+        <v>353</v>
       </c>
       <c r="H81" t="s">
         <v>4</v>
@@ -3778,22 +4411,22 @@
     </row>
     <row r="82" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A82" t="s">
-        <v>317</v>
+        <v>354</v>
       </c>
       <c r="C82" t="s">
-        <v>53</v>
+        <v>41</v>
       </c>
       <c r="D82" t="s">
-        <v>318</v>
+        <v>355</v>
       </c>
       <c r="E82" t="s">
-        <v>55</v>
+        <v>356</v>
       </c>
       <c r="F82" t="s">
-        <v>56</v>
+        <v>357</v>
       </c>
       <c r="G82" t="s">
-        <v>319</v>
+        <v>358</v>
       </c>
       <c r="H82" t="s">
         <v>4</v>
@@ -3801,22 +4434,22 @@
     </row>
     <row r="83" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A83" t="s">
-        <v>320</v>
+        <v>359</v>
       </c>
       <c r="C83" t="s">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="D83" t="s">
-        <v>321</v>
+        <v>360</v>
       </c>
       <c r="E83" t="s">
-        <v>322</v>
+        <v>59</v>
       </c>
       <c r="F83" t="s">
         <v>0</v>
       </c>
       <c r="G83" t="s">
-        <v>323</v>
+        <v>361</v>
       </c>
       <c r="H83" t="s">
         <v>4</v>
@@ -3824,22 +4457,22 @@
     </row>
     <row r="84" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A84" t="s">
-        <v>324</v>
+        <v>362</v>
       </c>
       <c r="C84" t="s">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="D84" t="s">
-        <v>321</v>
+        <v>360</v>
       </c>
       <c r="E84" t="s">
-        <v>322</v>
+        <v>59</v>
       </c>
       <c r="F84" t="s">
         <v>0</v>
       </c>
       <c r="G84" t="s">
-        <v>323</v>
+        <v>361</v>
       </c>
       <c r="H84" t="s">
         <v>4</v>
@@ -3847,22 +4480,22 @@
     </row>
     <row r="85" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A85" t="s">
-        <v>325</v>
+        <v>363</v>
       </c>
       <c r="C85" t="s">
-        <v>53</v>
+        <v>18</v>
       </c>
       <c r="D85" t="s">
-        <v>326</v>
+        <v>364</v>
       </c>
       <c r="E85" t="s">
-        <v>55</v>
+        <v>59</v>
       </c>
       <c r="F85" t="s">
-        <v>56</v>
+        <v>0</v>
       </c>
       <c r="G85" t="s">
-        <v>327</v>
+        <v>365</v>
       </c>
       <c r="H85" t="s">
         <v>4</v>
@@ -3870,22 +4503,22 @@
     </row>
     <row r="86" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A86" t="s">
-        <v>328</v>
+        <v>366</v>
       </c>
       <c r="C86" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="D86" t="s">
-        <v>329</v>
+        <v>367</v>
       </c>
       <c r="E86" t="s">
-        <v>60</v>
+        <v>368</v>
       </c>
       <c r="F86" t="s">
-        <v>61</v>
+        <v>369</v>
       </c>
       <c r="G86" t="s">
-        <v>330</v>
+        <v>370</v>
       </c>
       <c r="H86" t="s">
         <v>4</v>
@@ -3893,22 +4526,22 @@
     </row>
     <row r="87" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A87" t="s">
-        <v>331</v>
+        <v>371</v>
       </c>
       <c r="C87" t="s">
-        <v>21</v>
+        <v>239</v>
       </c>
       <c r="D87" t="s">
-        <v>332</v>
+        <v>372</v>
       </c>
       <c r="E87" t="s">
-        <v>333</v>
+        <v>373</v>
       </c>
       <c r="F87" t="s">
-        <v>0</v>
+        <v>374</v>
       </c>
       <c r="G87" t="s">
-        <v>334</v>
+        <v>375</v>
       </c>
       <c r="H87" t="s">
         <v>4</v>
@@ -3916,22 +4549,22 @@
     </row>
     <row r="88" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A88" t="s">
-        <v>335</v>
+        <v>376</v>
       </c>
       <c r="C88" t="s">
-        <v>19</v>
+        <v>54</v>
       </c>
       <c r="D88" t="s">
-        <v>336</v>
+        <v>377</v>
       </c>
       <c r="E88" t="s">
-        <v>337</v>
+        <v>6</v>
       </c>
       <c r="F88" t="s">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="G88" t="s">
-        <v>338</v>
+        <v>378</v>
       </c>
       <c r="H88" t="s">
         <v>4</v>
@@ -3939,22 +4572,22 @@
     </row>
     <row r="89" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A89" t="s">
-        <v>339</v>
+        <v>379</v>
       </c>
       <c r="C89" t="s">
-        <v>13</v>
+        <v>54</v>
       </c>
       <c r="D89" t="s">
-        <v>340</v>
+        <v>377</v>
       </c>
       <c r="E89" t="s">
-        <v>17</v>
+        <v>6</v>
       </c>
       <c r="F89" t="s">
-        <v>18</v>
+        <v>7</v>
       </c>
       <c r="G89" t="s">
-        <v>341</v>
+        <v>378</v>
       </c>
       <c r="H89" t="s">
         <v>4</v>
@@ -3962,22 +4595,22 @@
     </row>
     <row r="90" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A90" t="s">
-        <v>342</v>
+        <v>380</v>
       </c>
       <c r="C90" t="s">
-        <v>58</v>
+        <v>2</v>
       </c>
       <c r="D90" t="s">
-        <v>343</v>
+        <v>381</v>
       </c>
       <c r="E90" t="s">
-        <v>344</v>
+        <v>307</v>
       </c>
       <c r="F90" t="s">
-        <v>345</v>
+        <v>0</v>
       </c>
       <c r="G90" t="s">
-        <v>346</v>
+        <v>91</v>
       </c>
       <c r="H90" t="s">
         <v>4</v>
@@ -3985,22 +4618,22 @@
     </row>
     <row r="91" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A91" t="s">
-        <v>347</v>
+        <v>382</v>
       </c>
       <c r="C91" t="s">
-        <v>189</v>
+        <v>2</v>
       </c>
       <c r="D91" t="s">
-        <v>348</v>
+        <v>383</v>
       </c>
       <c r="E91" t="s">
-        <v>74</v>
+        <v>384</v>
       </c>
       <c r="F91" t="s">
         <v>0</v>
       </c>
       <c r="G91" t="s">
-        <v>349</v>
+        <v>385</v>
       </c>
       <c r="H91" t="s">
         <v>4</v>
@@ -4008,22 +4641,22 @@
     </row>
     <row r="92" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A92" t="s">
-        <v>350</v>
+        <v>386</v>
       </c>
       <c r="C92" t="s">
-        <v>189</v>
+        <v>18</v>
       </c>
       <c r="D92" t="s">
-        <v>348</v>
+        <v>387</v>
       </c>
       <c r="E92" t="s">
-        <v>74</v>
+        <v>388</v>
       </c>
       <c r="F92" t="s">
         <v>0</v>
       </c>
       <c r="G92" t="s">
-        <v>349</v>
+        <v>389</v>
       </c>
       <c r="H92" t="s">
         <v>4</v>
@@ -4031,22 +4664,22 @@
     </row>
     <row r="93" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A93" t="s">
-        <v>351</v>
+        <v>390</v>
       </c>
       <c r="C93" t="s">
-        <v>2</v>
+        <v>13</v>
       </c>
       <c r="D93" t="s">
-        <v>352</v>
+        <v>391</v>
       </c>
       <c r="E93" t="s">
-        <v>14</v>
+        <v>392</v>
       </c>
       <c r="F93" t="s">
         <v>0</v>
       </c>
       <c r="G93" t="s">
-        <v>353</v>
+        <v>393</v>
       </c>
       <c r="H93" t="s">
         <v>4</v>
@@ -4054,22 +4687,22 @@
     </row>
     <row r="94" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A94" t="s">
-        <v>354</v>
+        <v>394</v>
       </c>
       <c r="C94" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="D94" t="s">
-        <v>355</v>
+        <v>395</v>
       </c>
       <c r="E94" t="s">
-        <v>148</v>
+        <v>21</v>
       </c>
       <c r="F94" t="s">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="G94" t="s">
-        <v>356</v>
+        <v>396</v>
       </c>
       <c r="H94" t="s">
         <v>4</v>
@@ -4077,22 +4710,22 @@
     </row>
     <row r="95" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A95" t="s">
-        <v>357</v>
+        <v>397</v>
       </c>
       <c r="C95" t="s">
-        <v>11</v>
+        <v>60</v>
       </c>
       <c r="D95" t="s">
-        <v>358</v>
+        <v>398</v>
       </c>
       <c r="E95" t="s">
-        <v>50</v>
+        <v>399</v>
       </c>
       <c r="F95" t="s">
         <v>0</v>
       </c>
       <c r="G95" t="s">
-        <v>359</v>
+        <v>90</v>
       </c>
       <c r="H95" t="s">
         <v>4</v>
@@ -4100,22 +4733,22 @@
     </row>
     <row r="96" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A96" t="s">
-        <v>360</v>
+        <v>400</v>
       </c>
       <c r="C96" t="s">
-        <v>22</v>
+        <v>16</v>
       </c>
       <c r="D96" t="s">
-        <v>361</v>
+        <v>401</v>
       </c>
       <c r="E96" t="s">
-        <v>362</v>
+        <v>102</v>
       </c>
       <c r="F96" t="s">
-        <v>159</v>
+        <v>0</v>
       </c>
       <c r="G96" t="s">
-        <v>363</v>
+        <v>402</v>
       </c>
       <c r="H96" t="s">
         <v>4</v>
@@ -4123,22 +4756,22 @@
     </row>
     <row r="97" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A97" t="s">
-        <v>364</v>
+        <v>403</v>
       </c>
       <c r="C97" t="s">
-        <v>2</v>
+        <v>17</v>
       </c>
       <c r="D97" t="s">
-        <v>365</v>
+        <v>404</v>
       </c>
       <c r="E97" t="s">
-        <v>366</v>
+        <v>101</v>
       </c>
       <c r="F97" t="s">
-        <v>367</v>
+        <v>0</v>
       </c>
       <c r="G97" t="s">
-        <v>368</v>
+        <v>405</v>
       </c>
       <c r="H97" t="s">
         <v>4</v>
@@ -4146,22 +4779,22 @@
     </row>
     <row r="98" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A98" t="s">
-        <v>369</v>
+        <v>406</v>
       </c>
       <c r="C98" t="s">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="D98" t="s">
-        <v>370</v>
+        <v>407</v>
       </c>
       <c r="E98" t="s">
-        <v>59</v>
+        <v>408</v>
       </c>
       <c r="F98" t="s">
         <v>0</v>
       </c>
       <c r="G98" t="s">
-        <v>371</v>
+        <v>409</v>
       </c>
       <c r="H98" t="s">
         <v>4</v>
@@ -4169,22 +4802,22 @@
     </row>
     <row r="99" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A99" t="s">
-        <v>372</v>
+        <v>410</v>
       </c>
       <c r="C99" t="s">
-        <v>21</v>
+        <v>11</v>
       </c>
       <c r="D99" t="s">
-        <v>373</v>
+        <v>411</v>
       </c>
       <c r="E99" t="s">
-        <v>333</v>
+        <v>412</v>
       </c>
       <c r="F99" t="s">
-        <v>0</v>
+        <v>413</v>
       </c>
       <c r="G99" t="s">
-        <v>374</v>
+        <v>414</v>
       </c>
       <c r="H99" t="s">
         <v>4</v>
@@ -4192,22 +4825,22 @@
     </row>
     <row r="100" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A100" t="s">
-        <v>375</v>
+        <v>415</v>
       </c>
       <c r="C100" t="s">
-        <v>12</v>
+        <v>54</v>
       </c>
       <c r="D100" t="s">
-        <v>376</v>
+        <v>416</v>
       </c>
       <c r="E100" t="s">
-        <v>54</v>
+        <v>21</v>
       </c>
       <c r="F100" t="s">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="G100" t="s">
-        <v>377</v>
+        <v>417</v>
       </c>
       <c r="H100" t="s">
         <v>4</v>
@@ -4215,22 +4848,22 @@
     </row>
     <row r="101" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A101" t="s">
-        <v>378</v>
+        <v>418</v>
       </c>
       <c r="C101" t="s">
-        <v>8</v>
+        <v>60</v>
       </c>
       <c r="D101" t="s">
-        <v>379</v>
+        <v>419</v>
       </c>
       <c r="E101" t="s">
-        <v>380</v>
+        <v>70</v>
       </c>
       <c r="F101" t="s">
         <v>0</v>
       </c>
       <c r="G101" t="s">
-        <v>381</v>
+        <v>71</v>
       </c>
       <c r="H101" t="s">
         <v>4</v>
@@ -4238,22 +4871,22 @@
     </row>
     <row r="102" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A102" t="s">
-        <v>382</v>
+        <v>420</v>
       </c>
       <c r="C102" t="s">
-        <v>151</v>
+        <v>60</v>
       </c>
       <c r="D102" t="s">
-        <v>383</v>
+        <v>419</v>
       </c>
       <c r="E102" t="s">
-        <v>384</v>
+        <v>70</v>
       </c>
       <c r="F102" t="s">
         <v>0</v>
       </c>
       <c r="G102" t="s">
-        <v>385</v>
+        <v>71</v>
       </c>
       <c r="H102" t="s">
         <v>4</v>
@@ -4261,22 +4894,22 @@
     </row>
     <row r="103" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A103" t="s">
-        <v>386</v>
+        <v>421</v>
       </c>
       <c r="C103" t="s">
-        <v>10</v>
+        <v>60</v>
       </c>
       <c r="D103" t="s">
-        <v>387</v>
+        <v>419</v>
       </c>
       <c r="E103" t="s">
-        <v>388</v>
+        <v>70</v>
       </c>
       <c r="F103" t="s">
         <v>0</v>
       </c>
       <c r="G103" t="s">
-        <v>389</v>
+        <v>71</v>
       </c>
       <c r="H103" t="s">
         <v>4</v>
@@ -4284,22 +4917,19 @@
     </row>
     <row r="104" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A104" t="s">
-        <v>390</v>
+        <v>422</v>
       </c>
       <c r="C104" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="D104" t="s">
-        <v>387</v>
+        <v>423</v>
       </c>
       <c r="E104" t="s">
-        <v>388</v>
+        <v>424</v>
       </c>
       <c r="F104" t="s">
-        <v>0</v>
-      </c>
-      <c r="G104" t="s">
-        <v>389</v>
+        <v>425</v>
       </c>
       <c r="H104" t="s">
         <v>4</v>
@@ -4307,22 +4937,22 @@
     </row>
     <row r="105" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A105" t="s">
-        <v>391</v>
+        <v>426</v>
       </c>
       <c r="C105" t="s">
-        <v>392</v>
+        <v>8</v>
       </c>
       <c r="D105" t="s">
-        <v>393</v>
+        <v>427</v>
       </c>
       <c r="E105" t="s">
-        <v>76</v>
+        <v>25</v>
       </c>
       <c r="F105" t="s">
-        <v>77</v>
+        <v>26</v>
       </c>
       <c r="G105" t="s">
-        <v>394</v>
+        <v>198</v>
       </c>
       <c r="H105" t="s">
         <v>4</v>
@@ -4330,22 +4960,22 @@
     </row>
     <row r="106" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A106" t="s">
-        <v>395</v>
+        <v>428</v>
       </c>
       <c r="C106" t="s">
-        <v>58</v>
+        <v>11</v>
       </c>
       <c r="D106" t="s">
-        <v>396</v>
+        <v>429</v>
       </c>
       <c r="E106" t="s">
-        <v>397</v>
+        <v>430</v>
       </c>
       <c r="F106" t="s">
-        <v>398</v>
+        <v>431</v>
       </c>
       <c r="G106" t="s">
-        <v>399</v>
+        <v>117</v>
       </c>
       <c r="H106" t="s">
         <v>4</v>
@@ -4353,22 +4983,22 @@
     </row>
     <row r="107" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A107" t="s">
-        <v>400</v>
+        <v>432</v>
       </c>
       <c r="C107" t="s">
-        <v>151</v>
+        <v>11</v>
       </c>
       <c r="D107" t="s">
-        <v>401</v>
+        <v>433</v>
       </c>
       <c r="E107" t="s">
-        <v>63</v>
+        <v>434</v>
       </c>
       <c r="F107" t="s">
-        <v>0</v>
+        <v>435</v>
       </c>
       <c r="G107" t="s">
-        <v>402</v>
+        <v>436</v>
       </c>
       <c r="H107" t="s">
         <v>4</v>
@@ -4376,22 +5006,22 @@
     </row>
     <row r="108" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A108" t="s">
-        <v>403</v>
+        <v>437</v>
       </c>
       <c r="C108" t="s">
-        <v>9</v>
+        <v>41</v>
       </c>
       <c r="D108" t="s">
-        <v>404</v>
+        <v>438</v>
       </c>
       <c r="E108" t="s">
-        <v>405</v>
+        <v>104</v>
       </c>
       <c r="F108" t="s">
-        <v>0</v>
+        <v>105</v>
       </c>
       <c r="G108" t="s">
-        <v>406</v>
+        <v>83</v>
       </c>
       <c r="H108" t="s">
         <v>4</v>
@@ -4399,22 +5029,22 @@
     </row>
     <row r="109" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A109" t="s">
-        <v>407</v>
+        <v>439</v>
       </c>
       <c r="C109" t="s">
-        <v>3</v>
+        <v>69</v>
       </c>
       <c r="D109" t="s">
-        <v>408</v>
+        <v>440</v>
       </c>
       <c r="E109" t="s">
-        <v>43</v>
+        <v>100</v>
       </c>
       <c r="F109" t="s">
         <v>0</v>
       </c>
       <c r="G109" t="s">
-        <v>48</v>
+        <v>198</v>
       </c>
       <c r="H109" t="s">
         <v>4</v>
@@ -4422,22 +5052,22 @@
     </row>
     <row r="110" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A110" t="s">
-        <v>409</v>
+        <v>441</v>
       </c>
       <c r="C110" t="s">
-        <v>3</v>
+        <v>16</v>
       </c>
       <c r="D110" t="s">
-        <v>410</v>
+        <v>442</v>
       </c>
       <c r="E110" t="s">
-        <v>57</v>
+        <v>443</v>
       </c>
       <c r="F110" t="s">
         <v>0</v>
       </c>
       <c r="G110" t="s">
-        <v>411</v>
+        <v>444</v>
       </c>
       <c r="H110" t="s">
         <v>4</v>
@@ -4445,22 +5075,22 @@
     </row>
     <row r="111" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A111" t="s">
-        <v>412</v>
+        <v>445</v>
       </c>
       <c r="C111" t="s">
-        <v>20</v>
+        <v>119</v>
       </c>
       <c r="D111" t="s">
-        <v>413</v>
+        <v>446</v>
       </c>
       <c r="E111" t="s">
-        <v>414</v>
+        <v>447</v>
       </c>
       <c r="F111" t="s">
         <v>0</v>
       </c>
       <c r="G111" t="s">
-        <v>415</v>
+        <v>448</v>
       </c>
       <c r="H111" t="s">
         <v>4</v>
@@ -4468,22 +5098,22 @@
     </row>
     <row r="112" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A112" t="s">
-        <v>416</v>
+        <v>449</v>
       </c>
       <c r="C112" t="s">
-        <v>58</v>
+        <v>11</v>
       </c>
       <c r="D112" t="s">
-        <v>417</v>
+        <v>450</v>
       </c>
       <c r="E112" t="s">
-        <v>418</v>
+        <v>451</v>
       </c>
       <c r="F112" t="s">
-        <v>0</v>
+        <v>452</v>
       </c>
       <c r="G112" t="s">
-        <v>419</v>
+        <v>453</v>
       </c>
       <c r="H112" t="s">
         <v>4</v>
@@ -4491,22 +5121,22 @@
     </row>
     <row r="113" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A113" t="s">
-        <v>420</v>
+        <v>454</v>
       </c>
       <c r="C113" t="s">
-        <v>58</v>
+        <v>64</v>
       </c>
       <c r="D113" t="s">
-        <v>417</v>
+        <v>455</v>
       </c>
       <c r="E113" t="s">
-        <v>418</v>
+        <v>456</v>
       </c>
       <c r="F113" t="s">
         <v>0</v>
       </c>
       <c r="G113" t="s">
-        <v>419</v>
+        <v>457</v>
       </c>
       <c r="H113" t="s">
         <v>4</v>
@@ -4514,22 +5144,22 @@
     </row>
     <row r="114" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A114" t="s">
-        <v>421</v>
+        <v>458</v>
       </c>
       <c r="C114" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="D114" t="s">
-        <v>422</v>
+        <v>459</v>
       </c>
       <c r="E114" t="s">
-        <v>423</v>
+        <v>249</v>
       </c>
       <c r="F114" t="s">
         <v>0</v>
       </c>
       <c r="G114" t="s">
-        <v>424</v>
+        <v>460</v>
       </c>
       <c r="H114" t="s">
         <v>4</v>
@@ -4537,22 +5167,22 @@
     </row>
     <row r="115" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A115" t="s">
-        <v>425</v>
+        <v>461</v>
       </c>
       <c r="C115" t="s">
-        <v>91</v>
+        <v>17</v>
       </c>
       <c r="D115" t="s">
-        <v>426</v>
+        <v>462</v>
       </c>
       <c r="E115" t="s">
-        <v>6</v>
+        <v>89</v>
       </c>
       <c r="F115" t="s">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="G115" t="s">
-        <v>427</v>
+        <v>463</v>
       </c>
       <c r="H115" t="s">
         <v>4</v>
@@ -4560,22 +5190,22 @@
     </row>
     <row r="116" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A116" t="s">
-        <v>428</v>
+        <v>464</v>
       </c>
       <c r="C116" t="s">
-        <v>151</v>
+        <v>171</v>
       </c>
       <c r="D116" t="s">
-        <v>429</v>
+        <v>465</v>
       </c>
       <c r="E116" t="s">
-        <v>63</v>
+        <v>466</v>
       </c>
       <c r="F116" t="s">
-        <v>0</v>
+        <v>467</v>
       </c>
       <c r="G116" t="s">
-        <v>430</v>
+        <v>468</v>
       </c>
       <c r="H116" t="s">
         <v>4</v>
@@ -4583,22 +5213,22 @@
     </row>
     <row r="117" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A117" t="s">
-        <v>431</v>
+        <v>469</v>
       </c>
       <c r="C117" t="s">
-        <v>91</v>
+        <v>60</v>
       </c>
       <c r="D117" t="s">
-        <v>432</v>
+        <v>470</v>
       </c>
       <c r="E117" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="F117" t="s">
-        <v>27</v>
+        <v>0</v>
       </c>
       <c r="G117" t="s">
-        <v>433</v>
+        <v>471</v>
       </c>
       <c r="H117" t="s">
         <v>4</v>
@@ -4606,22 +5236,22 @@
     </row>
     <row r="118" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A118" t="s">
-        <v>434</v>
+        <v>472</v>
       </c>
       <c r="C118" t="s">
-        <v>12</v>
+        <v>54</v>
       </c>
       <c r="D118" t="s">
-        <v>435</v>
+        <v>473</v>
       </c>
       <c r="E118" t="s">
-        <v>73</v>
+        <v>19</v>
       </c>
       <c r="F118" t="s">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="G118" t="s">
-        <v>436</v>
+        <v>474</v>
       </c>
       <c r="H118" t="s">
         <v>4</v>
@@ -4629,574 +5259,574 @@
     </row>
     <row r="119" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A119" t="s">
-        <v>437</v>
+        <v>475</v>
       </c>
       <c r="C119" t="s">
-        <v>8</v>
+        <v>239</v>
       </c>
       <c r="D119" t="s">
-        <v>438</v>
+        <v>476</v>
       </c>
       <c r="E119" t="s">
-        <v>217</v>
+        <v>477</v>
       </c>
       <c r="F119" t="s">
-        <v>218</v>
+        <v>478</v>
       </c>
       <c r="G119" t="s">
-        <v>439</v>
+        <v>117</v>
       </c>
       <c r="H119" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="120" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A120" t="s">
-        <v>440</v>
+        <v>479</v>
       </c>
       <c r="C120" t="s">
         <v>13</v>
       </c>
       <c r="D120" t="s">
-        <v>441</v>
+        <v>480</v>
       </c>
       <c r="E120" t="s">
-        <v>78</v>
+        <v>481</v>
       </c>
       <c r="F120" t="s">
-        <v>79</v>
+        <v>0</v>
       </c>
       <c r="G120" t="s">
-        <v>442</v>
+        <v>482</v>
       </c>
       <c r="H120" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="121" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A121" t="s">
-        <v>443</v>
+        <v>483</v>
       </c>
       <c r="C121" t="s">
         <v>13</v>
       </c>
       <c r="D121" t="s">
-        <v>441</v>
+        <v>480</v>
       </c>
       <c r="E121" t="s">
-        <v>78</v>
+        <v>481</v>
       </c>
       <c r="F121" t="s">
-        <v>79</v>
+        <v>0</v>
       </c>
       <c r="G121" t="s">
-        <v>442</v>
+        <v>482</v>
       </c>
       <c r="H121" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="122" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A122" t="s">
-        <v>444</v>
+        <v>484</v>
       </c>
       <c r="C122" t="s">
-        <v>164</v>
+        <v>41</v>
       </c>
       <c r="D122" t="s">
-        <v>445</v>
+        <v>485</v>
       </c>
       <c r="E122" t="s">
-        <v>446</v>
+        <v>486</v>
       </c>
       <c r="F122" t="s">
         <v>0</v>
       </c>
       <c r="G122" t="s">
-        <v>447</v>
+        <v>487</v>
       </c>
       <c r="H122" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="123" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A123" t="s">
-        <v>448</v>
+        <v>488</v>
       </c>
       <c r="C123" t="s">
-        <v>164</v>
+        <v>41</v>
       </c>
       <c r="D123" t="s">
-        <v>449</v>
+        <v>485</v>
       </c>
       <c r="E123" t="s">
-        <v>450</v>
+        <v>486</v>
       </c>
       <c r="F123" t="s">
         <v>0</v>
       </c>
       <c r="G123" t="s">
-        <v>451</v>
+        <v>487</v>
       </c>
       <c r="H123" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="124" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A124" t="s">
-        <v>452</v>
+        <v>489</v>
       </c>
       <c r="C124" t="s">
-        <v>53</v>
+        <v>9</v>
       </c>
       <c r="D124" t="s">
-        <v>453</v>
+        <v>490</v>
       </c>
       <c r="E124" t="s">
-        <v>25</v>
+        <v>86</v>
       </c>
       <c r="F124" t="s">
         <v>0</v>
       </c>
       <c r="G124" t="s">
-        <v>454</v>
+        <v>491</v>
       </c>
       <c r="H124" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="125" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A125" t="s">
-        <v>455</v>
+        <v>492</v>
       </c>
       <c r="C125" t="s">
-        <v>2</v>
+        <v>9</v>
       </c>
       <c r="D125" t="s">
-        <v>456</v>
+        <v>490</v>
       </c>
       <c r="E125" t="s">
-        <v>14</v>
+        <v>86</v>
       </c>
       <c r="F125" t="s">
         <v>0</v>
       </c>
       <c r="G125" t="s">
-        <v>457</v>
+        <v>491</v>
       </c>
       <c r="H125" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="126" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A126" t="s">
-        <v>458</v>
+        <v>493</v>
       </c>
       <c r="C126" t="s">
-        <v>58</v>
+        <v>10</v>
       </c>
       <c r="D126" t="s">
-        <v>459</v>
+        <v>494</v>
       </c>
       <c r="E126" t="s">
-        <v>82</v>
+        <v>153</v>
       </c>
       <c r="F126" t="s">
-        <v>83</v>
+        <v>0</v>
       </c>
       <c r="G126" t="s">
-        <v>460</v>
+        <v>495</v>
       </c>
       <c r="H126" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="127" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A127" t="s">
-        <v>461</v>
+        <v>496</v>
       </c>
       <c r="C127" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="D127" t="s">
-        <v>462</v>
+        <v>494</v>
       </c>
       <c r="E127" t="s">
-        <v>283</v>
+        <v>153</v>
       </c>
       <c r="F127" t="s">
         <v>0</v>
       </c>
       <c r="G127" t="s">
-        <v>463</v>
+        <v>495</v>
       </c>
       <c r="H127" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="128" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A128" t="s">
-        <v>464</v>
+        <v>497</v>
       </c>
       <c r="C128" t="s">
-        <v>2</v>
+        <v>11</v>
       </c>
       <c r="D128" t="s">
-        <v>465</v>
+        <v>498</v>
       </c>
       <c r="E128" t="s">
-        <v>466</v>
+        <v>36</v>
       </c>
       <c r="F128" t="s">
-        <v>0</v>
+        <v>37</v>
       </c>
       <c r="G128" t="s">
-        <v>467</v>
+        <v>499</v>
       </c>
       <c r="H128" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="129" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A129" t="s">
-        <v>468</v>
+        <v>500</v>
       </c>
       <c r="C129" t="s">
-        <v>392</v>
+        <v>9</v>
       </c>
       <c r="D129" t="s">
-        <v>469</v>
+        <v>501</v>
       </c>
       <c r="E129" t="s">
-        <v>51</v>
+        <v>502</v>
       </c>
       <c r="F129" t="s">
-        <v>0</v>
+        <v>503</v>
       </c>
       <c r="G129" t="s">
-        <v>470</v>
+        <v>504</v>
       </c>
       <c r="H129" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="130" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A130" t="s">
-        <v>471</v>
+        <v>505</v>
       </c>
       <c r="C130" t="s">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="D130" t="s">
-        <v>472</v>
+        <v>506</v>
       </c>
       <c r="E130" t="s">
-        <v>380</v>
+        <v>72</v>
       </c>
       <c r="F130" t="s">
         <v>0</v>
       </c>
       <c r="G130" t="s">
-        <v>473</v>
+        <v>507</v>
       </c>
       <c r="H130" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="131" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A131" t="s">
-        <v>474</v>
+        <v>508</v>
       </c>
       <c r="C131" t="s">
-        <v>151</v>
+        <v>16</v>
       </c>
       <c r="D131" t="s">
-        <v>475</v>
+        <v>509</v>
       </c>
       <c r="E131" t="s">
-        <v>384</v>
+        <v>109</v>
       </c>
       <c r="F131" t="s">
-        <v>0</v>
+        <v>110</v>
       </c>
       <c r="G131" t="s">
-        <v>476</v>
+        <v>94</v>
       </c>
       <c r="H131" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="132" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A132" t="s">
-        <v>477</v>
+        <v>510</v>
       </c>
       <c r="C132" t="s">
-        <v>151</v>
+        <v>60</v>
       </c>
       <c r="D132" t="s">
-        <v>475</v>
+        <v>511</v>
       </c>
       <c r="E132" t="s">
-        <v>384</v>
+        <v>512</v>
       </c>
       <c r="F132" t="s">
         <v>0</v>
       </c>
       <c r="G132" t="s">
-        <v>476</v>
+        <v>513</v>
       </c>
       <c r="H132" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="133" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A133" t="s">
-        <v>478</v>
+        <v>514</v>
       </c>
       <c r="C133" t="s">
-        <v>58</v>
+        <v>13</v>
       </c>
       <c r="D133" t="s">
-        <v>479</v>
+        <v>515</v>
       </c>
       <c r="E133" t="s">
-        <v>306</v>
+        <v>516</v>
       </c>
       <c r="F133" t="s">
         <v>0</v>
       </c>
       <c r="G133" t="s">
-        <v>480</v>
+        <v>517</v>
       </c>
       <c r="H133" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="134" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A134" t="s">
-        <v>481</v>
+        <v>518</v>
       </c>
       <c r="C134" t="s">
-        <v>58</v>
+        <v>16</v>
       </c>
       <c r="D134" t="s">
-        <v>482</v>
+        <v>519</v>
       </c>
       <c r="E134" t="s">
-        <v>418</v>
+        <v>520</v>
       </c>
       <c r="F134" t="s">
-        <v>0</v>
+        <v>521</v>
       </c>
       <c r="G134" t="s">
-        <v>483</v>
+        <v>522</v>
       </c>
       <c r="H134" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="135" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A135" t="s">
-        <v>484</v>
+        <v>523</v>
       </c>
       <c r="C135" t="s">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="D135" t="s">
-        <v>485</v>
+        <v>524</v>
       </c>
       <c r="E135" t="s">
-        <v>31</v>
+        <v>525</v>
       </c>
       <c r="F135" t="s">
-        <v>32</v>
+        <v>0</v>
       </c>
       <c r="G135" t="s">
-        <v>486</v>
+        <v>526</v>
       </c>
       <c r="H135" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="136" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A136" t="s">
-        <v>487</v>
+        <v>527</v>
       </c>
       <c r="C136" t="s">
-        <v>13</v>
+        <v>3</v>
       </c>
       <c r="D136" t="s">
-        <v>488</v>
+        <v>528</v>
       </c>
       <c r="E136" t="s">
-        <v>60</v>
+        <v>45</v>
       </c>
       <c r="F136" t="s">
-        <v>61</v>
+        <v>0</v>
       </c>
       <c r="G136" t="s">
-        <v>489</v>
+        <v>529</v>
       </c>
       <c r="H136" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="137" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A137" t="s">
-        <v>490</v>
+        <v>530</v>
       </c>
       <c r="C137" t="s">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="D137" t="s">
-        <v>488</v>
+        <v>531</v>
       </c>
       <c r="E137" t="s">
-        <v>60</v>
+        <v>23</v>
       </c>
       <c r="F137" t="s">
-        <v>61</v>
+        <v>24</v>
       </c>
       <c r="G137" t="s">
-        <v>489</v>
+        <v>532</v>
       </c>
       <c r="H137" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="138" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A138" t="s">
-        <v>491</v>
+        <v>533</v>
       </c>
       <c r="C138" t="s">
         <v>13</v>
       </c>
       <c r="D138" t="s">
-        <v>492</v>
+        <v>534</v>
       </c>
       <c r="E138" t="s">
-        <v>15</v>
+        <v>535</v>
       </c>
       <c r="F138" t="s">
-        <v>16</v>
+        <v>0</v>
       </c>
       <c r="G138" t="s">
-        <v>493</v>
+        <v>536</v>
       </c>
       <c r="H138" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="139" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A139" t="s">
-        <v>494</v>
+        <v>537</v>
       </c>
       <c r="C139" t="s">
-        <v>13</v>
+        <v>60</v>
       </c>
       <c r="D139" t="s">
-        <v>492</v>
+        <v>538</v>
       </c>
       <c r="E139" t="s">
-        <v>15</v>
+        <v>539</v>
       </c>
       <c r="F139" t="s">
-        <v>16</v>
+        <v>540</v>
       </c>
       <c r="G139" t="s">
-        <v>493</v>
+        <v>541</v>
       </c>
       <c r="H139" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="140" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A140" t="s">
-        <v>495</v>
+        <v>542</v>
       </c>
       <c r="C140" t="s">
-        <v>13</v>
+        <v>60</v>
       </c>
       <c r="D140" t="s">
-        <v>492</v>
+        <v>543</v>
       </c>
       <c r="E140" t="s">
-        <v>15</v>
+        <v>544</v>
       </c>
       <c r="F140" t="s">
-        <v>16</v>
+        <v>0</v>
       </c>
       <c r="G140" t="s">
-        <v>493</v>
+        <v>545</v>
       </c>
       <c r="H140" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="141" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A141" t="s">
-        <v>496</v>
+        <v>546</v>
       </c>
       <c r="C141" t="s">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="D141" t="s">
-        <v>492</v>
+        <v>547</v>
       </c>
       <c r="E141" t="s">
-        <v>15</v>
+        <v>68</v>
       </c>
       <c r="F141" t="s">
-        <v>16</v>
+        <v>0</v>
       </c>
       <c r="G141" t="s">
-        <v>493</v>
+        <v>548</v>
       </c>
       <c r="H141" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="142" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A142" t="s">
-        <v>497</v>
+        <v>549</v>
       </c>
       <c r="C142" t="s">
-        <v>13</v>
+        <v>41</v>
       </c>
       <c r="D142" t="s">
-        <v>492</v>
+        <v>550</v>
       </c>
       <c r="E142" t="s">
-        <v>15</v>
+        <v>82</v>
       </c>
       <c r="F142" t="s">
-        <v>16</v>
+        <v>0</v>
       </c>
       <c r="G142" t="s">
-        <v>493</v>
+        <v>551</v>
       </c>
       <c r="H142" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="143" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A143" t="s">
-        <v>498</v>
+        <v>552</v>
       </c>
       <c r="C143" t="s">
-        <v>189</v>
+        <v>8</v>
       </c>
       <c r="D143" t="s">
-        <v>499</v>
+        <v>553</v>
       </c>
       <c r="E143" t="s">
-        <v>52</v>
+        <v>23</v>
       </c>
       <c r="F143" t="s">
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="G143" t="s">
-        <v>500</v>
+        <v>554</v>
       </c>
       <c r="H143" t="s">
         <v>5</v>
@@ -5204,22 +5834,22 @@
     </row>
     <row r="144" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A144" t="s">
-        <v>501</v>
+        <v>555</v>
       </c>
       <c r="C144" t="s">
-        <v>91</v>
+        <v>9</v>
       </c>
       <c r="D144" t="s">
-        <v>502</v>
+        <v>556</v>
       </c>
       <c r="E144" t="s">
-        <v>503</v>
+        <v>557</v>
       </c>
       <c r="F144" t="s">
-        <v>504</v>
+        <v>558</v>
       </c>
       <c r="G144" t="s">
-        <v>149</v>
+        <v>559</v>
       </c>
       <c r="H144" t="s">
         <v>5</v>
@@ -5227,22 +5857,22 @@
     </row>
     <row r="145" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A145" t="s">
-        <v>505</v>
+        <v>560</v>
       </c>
       <c r="C145" t="s">
-        <v>151</v>
+        <v>54</v>
       </c>
       <c r="D145" t="s">
-        <v>506</v>
+        <v>561</v>
       </c>
       <c r="E145" t="s">
-        <v>153</v>
+        <v>163</v>
       </c>
       <c r="F145" t="s">
-        <v>0</v>
+        <v>164</v>
       </c>
       <c r="G145" t="s">
-        <v>507</v>
+        <v>562</v>
       </c>
       <c r="H145" t="s">
         <v>5</v>
@@ -5250,85 +5880,1497 @@
     </row>
     <row r="146" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A146" t="s">
-        <v>508</v>
+        <v>563</v>
       </c>
       <c r="C146" t="s">
-        <v>13</v>
+        <v>54</v>
       </c>
       <c r="D146" t="s">
-        <v>509</v>
+        <v>561</v>
       </c>
       <c r="E146" t="s">
-        <v>510</v>
+        <v>163</v>
       </c>
       <c r="F146" t="s">
-        <v>511</v>
+        <v>164</v>
       </c>
       <c r="G146" t="s">
-        <v>512</v>
+        <v>562</v>
       </c>
       <c r="H146" t="s">
-        <v>513</v>
+        <v>5</v>
       </c>
     </row>
     <row r="147" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A147" t="s">
-        <v>514</v>
+        <v>564</v>
       </c>
       <c r="C147" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="D147" t="s">
-        <v>509</v>
+        <v>565</v>
       </c>
       <c r="E147" t="s">
-        <v>510</v>
+        <v>92</v>
       </c>
       <c r="F147" t="s">
-        <v>511</v>
+        <v>93</v>
       </c>
       <c r="G147" t="s">
-        <v>512</v>
+        <v>566</v>
       </c>
       <c r="H147" t="s">
-        <v>513</v>
+        <v>5</v>
       </c>
     </row>
     <row r="148" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A148" t="s">
-        <v>515</v>
+        <v>567</v>
       </c>
       <c r="C148" t="s">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="D148" t="s">
-        <v>509</v>
+        <v>568</v>
       </c>
       <c r="E148" t="s">
-        <v>510</v>
+        <v>569</v>
       </c>
       <c r="F148" t="s">
-        <v>511</v>
+        <v>570</v>
       </c>
       <c r="G148" t="s">
-        <v>512</v>
+        <v>87</v>
       </c>
       <c r="H148" t="s">
-        <v>513</v>
+        <v>5</v>
       </c>
     </row>
     <row r="149" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A149" t="s">
-        <v>516</v>
+        <v>571</v>
       </c>
       <c r="C149" t="s">
-        <v>99</v>
+        <v>64</v>
       </c>
       <c r="D149" t="s">
-        <v>516</v>
+        <v>572</v>
+      </c>
+      <c r="E149" t="s">
+        <v>573</v>
+      </c>
+      <c r="F149" t="s">
+        <v>574</v>
+      </c>
+      <c r="G149" t="s">
+        <v>575</v>
       </c>
       <c r="H149" t="s">
-        <v>517</v>
+        <v>5</v>
+      </c>
+    </row>
+    <row r="150" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A150" t="s">
+        <v>576</v>
+      </c>
+      <c r="C150" t="s">
+        <v>9</v>
+      </c>
+      <c r="D150" t="s">
+        <v>577</v>
+      </c>
+      <c r="E150" t="s">
+        <v>44</v>
+      </c>
+      <c r="F150" t="s">
+        <v>0</v>
+      </c>
+      <c r="G150" t="s">
+        <v>578</v>
+      </c>
+      <c r="H150" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="151" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A151" t="s">
+        <v>579</v>
+      </c>
+      <c r="C151" t="s">
+        <v>60</v>
+      </c>
+      <c r="D151" t="s">
+        <v>580</v>
+      </c>
+      <c r="E151" t="s">
+        <v>581</v>
+      </c>
+      <c r="F151" t="s">
+        <v>0</v>
+      </c>
+      <c r="G151" t="s">
+        <v>582</v>
+      </c>
+      <c r="H151" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="152" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A152" t="s">
+        <v>583</v>
+      </c>
+      <c r="C152" t="s">
+        <v>60</v>
+      </c>
+      <c r="D152" t="s">
+        <v>580</v>
+      </c>
+      <c r="E152" t="s">
+        <v>581</v>
+      </c>
+      <c r="F152" t="s">
+        <v>0</v>
+      </c>
+      <c r="G152" t="s">
+        <v>582</v>
+      </c>
+      <c r="H152" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="153" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A153" t="s">
+        <v>584</v>
+      </c>
+      <c r="C153" t="s">
+        <v>60</v>
+      </c>
+      <c r="D153" t="s">
+        <v>580</v>
+      </c>
+      <c r="E153" t="s">
+        <v>581</v>
+      </c>
+      <c r="F153" t="s">
+        <v>0</v>
+      </c>
+      <c r="G153" t="s">
+        <v>582</v>
+      </c>
+      <c r="H153" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="154" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A154" t="s">
+        <v>585</v>
+      </c>
+      <c r="C154" t="s">
+        <v>60</v>
+      </c>
+      <c r="D154" t="s">
+        <v>580</v>
+      </c>
+      <c r="E154" t="s">
+        <v>581</v>
+      </c>
+      <c r="F154" t="s">
+        <v>0</v>
+      </c>
+      <c r="G154" t="s">
+        <v>582</v>
+      </c>
+      <c r="H154" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="155" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A155" t="s">
+        <v>586</v>
+      </c>
+      <c r="C155" t="s">
+        <v>239</v>
+      </c>
+      <c r="D155" t="s">
+        <v>587</v>
+      </c>
+      <c r="E155" t="s">
+        <v>588</v>
+      </c>
+      <c r="F155" t="s">
+        <v>589</v>
+      </c>
+      <c r="G155" t="s">
+        <v>590</v>
+      </c>
+      <c r="H155" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="156" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A156" t="s">
+        <v>591</v>
+      </c>
+      <c r="C156" t="s">
+        <v>60</v>
+      </c>
+      <c r="D156" t="s">
+        <v>592</v>
+      </c>
+      <c r="E156" t="s">
+        <v>539</v>
+      </c>
+      <c r="F156" t="s">
+        <v>540</v>
+      </c>
+      <c r="G156" t="s">
+        <v>593</v>
+      </c>
+      <c r="H156" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="157" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A157" t="s">
+        <v>594</v>
+      </c>
+      <c r="C157" t="s">
+        <v>64</v>
+      </c>
+      <c r="D157" t="s">
+        <v>595</v>
+      </c>
+      <c r="E157" t="s">
+        <v>596</v>
+      </c>
+      <c r="F157" t="s">
+        <v>597</v>
+      </c>
+      <c r="G157" t="s">
+        <v>598</v>
+      </c>
+      <c r="H157" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="158" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A158" t="s">
+        <v>599</v>
+      </c>
+      <c r="C158" t="s">
+        <v>60</v>
+      </c>
+      <c r="D158" t="s">
+        <v>600</v>
+      </c>
+      <c r="E158" t="s">
+        <v>601</v>
+      </c>
+      <c r="F158" t="s">
+        <v>602</v>
+      </c>
+      <c r="G158" t="s">
+        <v>603</v>
+      </c>
+      <c r="H158" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="159" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A159" t="s">
+        <v>604</v>
+      </c>
+      <c r="C159" t="s">
+        <v>11</v>
+      </c>
+      <c r="D159" t="s">
+        <v>605</v>
+      </c>
+      <c r="E159" t="s">
+        <v>606</v>
+      </c>
+      <c r="F159" t="s">
+        <v>607</v>
+      </c>
+      <c r="G159" t="s">
+        <v>608</v>
+      </c>
+      <c r="H159" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="160" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A160" t="s">
+        <v>609</v>
+      </c>
+      <c r="C160" t="s">
+        <v>9</v>
+      </c>
+      <c r="D160" t="s">
+        <v>610</v>
+      </c>
+      <c r="E160" t="s">
+        <v>48</v>
+      </c>
+      <c r="F160" t="s">
+        <v>49</v>
+      </c>
+      <c r="G160" t="s">
+        <v>611</v>
+      </c>
+      <c r="H160" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="161" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A161" t="s">
+        <v>612</v>
+      </c>
+      <c r="C161" t="s">
+        <v>60</v>
+      </c>
+      <c r="D161" t="s">
+        <v>613</v>
+      </c>
+      <c r="E161" t="s">
+        <v>131</v>
+      </c>
+      <c r="F161" t="s">
+        <v>132</v>
+      </c>
+      <c r="G161" t="s">
+        <v>614</v>
+      </c>
+      <c r="H161" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="162" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A162" t="s">
+        <v>615</v>
+      </c>
+      <c r="C162" t="s">
+        <v>18</v>
+      </c>
+      <c r="D162" t="s">
+        <v>616</v>
+      </c>
+      <c r="E162" t="s">
+        <v>617</v>
+      </c>
+      <c r="F162" t="s">
+        <v>0</v>
+      </c>
+      <c r="G162" t="s">
+        <v>618</v>
+      </c>
+      <c r="H162" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="163" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A163" t="s">
+        <v>619</v>
+      </c>
+      <c r="C163" t="s">
+        <v>60</v>
+      </c>
+      <c r="D163" t="s">
+        <v>620</v>
+      </c>
+      <c r="E163" t="s">
+        <v>80</v>
+      </c>
+      <c r="F163" t="s">
+        <v>81</v>
+      </c>
+      <c r="G163" t="s">
+        <v>621</v>
+      </c>
+      <c r="H163" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="164" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A164" t="s">
+        <v>622</v>
+      </c>
+      <c r="C164" t="s">
+        <v>60</v>
+      </c>
+      <c r="D164" t="s">
+        <v>620</v>
+      </c>
+      <c r="E164" t="s">
+        <v>80</v>
+      </c>
+      <c r="F164" t="s">
+        <v>81</v>
+      </c>
+      <c r="G164" t="s">
+        <v>621</v>
+      </c>
+      <c r="H164" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="165" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A165" t="s">
+        <v>623</v>
+      </c>
+      <c r="C165" t="s">
+        <v>60</v>
+      </c>
+      <c r="D165" t="s">
+        <v>620</v>
+      </c>
+      <c r="E165" t="s">
+        <v>80</v>
+      </c>
+      <c r="F165" t="s">
+        <v>81</v>
+      </c>
+      <c r="G165" t="s">
+        <v>621</v>
+      </c>
+      <c r="H165" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="166" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A166" t="s">
+        <v>624</v>
+      </c>
+      <c r="C166" t="s">
+        <v>60</v>
+      </c>
+      <c r="D166" t="s">
+        <v>620</v>
+      </c>
+      <c r="E166" t="s">
+        <v>80</v>
+      </c>
+      <c r="F166" t="s">
+        <v>81</v>
+      </c>
+      <c r="G166" t="s">
+        <v>621</v>
+      </c>
+      <c r="H166" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="167" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A167" t="s">
+        <v>625</v>
+      </c>
+      <c r="C167" t="s">
+        <v>60</v>
+      </c>
+      <c r="D167" t="s">
+        <v>620</v>
+      </c>
+      <c r="E167" t="s">
+        <v>80</v>
+      </c>
+      <c r="F167" t="s">
+        <v>81</v>
+      </c>
+      <c r="G167" t="s">
+        <v>621</v>
+      </c>
+      <c r="H167" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="168" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A168" t="s">
+        <v>626</v>
+      </c>
+      <c r="C168" t="s">
+        <v>17</v>
+      </c>
+      <c r="D168" t="s">
+        <v>627</v>
+      </c>
+      <c r="E168" t="s">
+        <v>51</v>
+      </c>
+      <c r="F168" t="s">
+        <v>52</v>
+      </c>
+      <c r="G168" t="s">
+        <v>95</v>
+      </c>
+      <c r="H168" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="169" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A169" t="s">
+        <v>628</v>
+      </c>
+      <c r="C169" t="s">
+        <v>41</v>
+      </c>
+      <c r="D169" t="s">
+        <v>629</v>
+      </c>
+      <c r="E169" t="s">
+        <v>46</v>
+      </c>
+      <c r="F169" t="s">
+        <v>47</v>
+      </c>
+      <c r="G169" t="s">
+        <v>630</v>
+      </c>
+      <c r="H169" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="170" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A170" t="s">
+        <v>631</v>
+      </c>
+      <c r="C170" t="s">
+        <v>64</v>
+      </c>
+      <c r="D170" t="s">
+        <v>632</v>
+      </c>
+      <c r="E170" t="s">
+        <v>633</v>
+      </c>
+      <c r="F170" t="s">
+        <v>634</v>
+      </c>
+      <c r="G170" t="s">
+        <v>103</v>
+      </c>
+      <c r="H170" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="171" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A171" t="s">
+        <v>635</v>
+      </c>
+      <c r="C171" t="s">
+        <v>64</v>
+      </c>
+      <c r="D171" t="s">
+        <v>632</v>
+      </c>
+      <c r="E171" t="s">
+        <v>633</v>
+      </c>
+      <c r="F171" t="s">
+        <v>634</v>
+      </c>
+      <c r="G171" t="s">
+        <v>103</v>
+      </c>
+      <c r="H171" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="172" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A172" t="s">
+        <v>636</v>
+      </c>
+      <c r="C172" t="s">
+        <v>64</v>
+      </c>
+      <c r="D172" t="s">
+        <v>632</v>
+      </c>
+      <c r="E172" t="s">
+        <v>633</v>
+      </c>
+      <c r="F172" t="s">
+        <v>634</v>
+      </c>
+      <c r="G172" t="s">
+        <v>103</v>
+      </c>
+      <c r="H172" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="173" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A173" t="s">
+        <v>637</v>
+      </c>
+      <c r="C173" t="s">
+        <v>64</v>
+      </c>
+      <c r="D173" t="s">
+        <v>632</v>
+      </c>
+      <c r="E173" t="s">
+        <v>633</v>
+      </c>
+      <c r="F173" t="s">
+        <v>634</v>
+      </c>
+      <c r="G173" t="s">
+        <v>103</v>
+      </c>
+      <c r="H173" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="174" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A174" t="s">
+        <v>638</v>
+      </c>
+      <c r="C174" t="s">
+        <v>8</v>
+      </c>
+      <c r="D174" t="s">
+        <v>639</v>
+      </c>
+      <c r="E174" t="s">
+        <v>23</v>
+      </c>
+      <c r="F174" t="s">
+        <v>24</v>
+      </c>
+      <c r="G174" t="s">
+        <v>640</v>
+      </c>
+      <c r="H174" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="175" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A175" t="s">
+        <v>641</v>
+      </c>
+      <c r="C175" t="s">
+        <v>8</v>
+      </c>
+      <c r="D175" t="s">
+        <v>642</v>
+      </c>
+      <c r="E175" t="s">
+        <v>25</v>
+      </c>
+      <c r="F175" t="s">
+        <v>26</v>
+      </c>
+      <c r="G175" t="s">
+        <v>643</v>
+      </c>
+      <c r="H175" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="176" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A176" t="s">
+        <v>644</v>
+      </c>
+      <c r="C176" t="s">
+        <v>8</v>
+      </c>
+      <c r="D176" t="s">
+        <v>642</v>
+      </c>
+      <c r="E176" t="s">
+        <v>25</v>
+      </c>
+      <c r="F176" t="s">
+        <v>26</v>
+      </c>
+      <c r="G176" t="s">
+        <v>643</v>
+      </c>
+      <c r="H176" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="177" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A177" t="s">
+        <v>645</v>
+      </c>
+      <c r="C177" t="s">
+        <v>17</v>
+      </c>
+      <c r="D177" t="s">
+        <v>646</v>
+      </c>
+      <c r="E177" t="s">
+        <v>89</v>
+      </c>
+      <c r="F177" t="s">
+        <v>0</v>
+      </c>
+      <c r="G177" t="s">
+        <v>647</v>
+      </c>
+      <c r="H177" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="178" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A178" t="s">
+        <v>648</v>
+      </c>
+      <c r="C178" t="s">
+        <v>239</v>
+      </c>
+      <c r="D178" t="s">
+        <v>649</v>
+      </c>
+      <c r="E178" t="s">
+        <v>588</v>
+      </c>
+      <c r="F178" t="s">
+        <v>589</v>
+      </c>
+      <c r="G178" t="s">
+        <v>98</v>
+      </c>
+      <c r="H178" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="179" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A179" t="s">
+        <v>650</v>
+      </c>
+      <c r="C179" t="s">
+        <v>8</v>
+      </c>
+      <c r="D179" t="s">
+        <v>651</v>
+      </c>
+      <c r="E179" t="s">
+        <v>28</v>
+      </c>
+      <c r="F179" t="s">
+        <v>0</v>
+      </c>
+      <c r="G179" t="s">
+        <v>652</v>
+      </c>
+      <c r="H179" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="180" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A180" t="s">
+        <v>653</v>
+      </c>
+      <c r="C180" t="s">
+        <v>69</v>
+      </c>
+      <c r="D180" t="s">
+        <v>654</v>
+      </c>
+      <c r="E180" t="s">
+        <v>61</v>
+      </c>
+      <c r="F180" t="s">
+        <v>0</v>
+      </c>
+      <c r="G180" t="s">
+        <v>210</v>
+      </c>
+      <c r="H180" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="181" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A181" t="s">
+        <v>655</v>
+      </c>
+      <c r="C181" t="s">
+        <v>60</v>
+      </c>
+      <c r="D181" t="s">
+        <v>656</v>
+      </c>
+      <c r="E181" t="s">
+        <v>544</v>
+      </c>
+      <c r="F181" t="s">
+        <v>0</v>
+      </c>
+      <c r="G181" t="s">
+        <v>657</v>
+      </c>
+      <c r="H181" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="182" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A182" t="s">
+        <v>658</v>
+      </c>
+      <c r="C182" t="s">
+        <v>171</v>
+      </c>
+      <c r="D182" t="s">
+        <v>659</v>
+      </c>
+      <c r="E182" t="s">
+        <v>660</v>
+      </c>
+      <c r="F182" t="s">
+        <v>661</v>
+      </c>
+      <c r="G182" t="s">
+        <v>662</v>
+      </c>
+      <c r="H182" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="183" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A183" t="s">
+        <v>663</v>
+      </c>
+      <c r="C183" t="s">
+        <v>171</v>
+      </c>
+      <c r="D183" t="s">
+        <v>664</v>
+      </c>
+      <c r="E183" t="s">
+        <v>57</v>
+      </c>
+      <c r="F183" t="s">
+        <v>58</v>
+      </c>
+      <c r="G183" t="s">
+        <v>665</v>
+      </c>
+      <c r="H183" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="184" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A184" t="s">
+        <v>666</v>
+      </c>
+      <c r="C184" t="s">
+        <v>171</v>
+      </c>
+      <c r="D184" t="s">
+        <v>664</v>
+      </c>
+      <c r="E184" t="s">
+        <v>57</v>
+      </c>
+      <c r="F184" t="s">
+        <v>58</v>
+      </c>
+      <c r="G184" t="s">
+        <v>665</v>
+      </c>
+      <c r="H184" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="185" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A185" t="s">
+        <v>667</v>
+      </c>
+      <c r="C185" t="s">
+        <v>16</v>
+      </c>
+      <c r="D185" t="s">
+        <v>668</v>
+      </c>
+      <c r="E185" t="s">
+        <v>669</v>
+      </c>
+      <c r="F185" t="s">
+        <v>0</v>
+      </c>
+      <c r="G185" t="s">
+        <v>670</v>
+      </c>
+      <c r="H185" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="186" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A186" t="s">
+        <v>671</v>
+      </c>
+      <c r="C186" t="s">
+        <v>16</v>
+      </c>
+      <c r="D186" t="s">
+        <v>668</v>
+      </c>
+      <c r="E186" t="s">
+        <v>669</v>
+      </c>
+      <c r="F186" t="s">
+        <v>0</v>
+      </c>
+      <c r="G186" t="s">
+        <v>670</v>
+      </c>
+      <c r="H186" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="187" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A187" t="s">
+        <v>672</v>
+      </c>
+      <c r="C187" t="s">
+        <v>16</v>
+      </c>
+      <c r="D187" t="s">
+        <v>668</v>
+      </c>
+      <c r="E187" t="s">
+        <v>669</v>
+      </c>
+      <c r="F187" t="s">
+        <v>0</v>
+      </c>
+      <c r="G187" t="s">
+        <v>670</v>
+      </c>
+      <c r="H187" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="188" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A188" t="s">
+        <v>673</v>
+      </c>
+      <c r="C188" t="s">
+        <v>16</v>
+      </c>
+      <c r="D188" t="s">
+        <v>668</v>
+      </c>
+      <c r="E188" t="s">
+        <v>669</v>
+      </c>
+      <c r="F188" t="s">
+        <v>0</v>
+      </c>
+      <c r="G188" t="s">
+        <v>670</v>
+      </c>
+      <c r="H188" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="189" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A189" t="s">
+        <v>674</v>
+      </c>
+      <c r="C189" t="s">
+        <v>239</v>
+      </c>
+      <c r="D189" t="s">
+        <v>675</v>
+      </c>
+      <c r="E189" t="s">
+        <v>50</v>
+      </c>
+      <c r="F189" t="s">
+        <v>0</v>
+      </c>
+      <c r="G189" t="s">
+        <v>676</v>
+      </c>
+      <c r="H189" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="190" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A190" t="s">
+        <v>677</v>
+      </c>
+      <c r="C190" t="s">
+        <v>239</v>
+      </c>
+      <c r="D190" t="s">
+        <v>675</v>
+      </c>
+      <c r="E190" t="s">
+        <v>50</v>
+      </c>
+      <c r="F190" t="s">
+        <v>0</v>
+      </c>
+      <c r="G190" t="s">
+        <v>676</v>
+      </c>
+      <c r="H190" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="191" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A191" t="s">
+        <v>678</v>
+      </c>
+      <c r="C191" t="s">
+        <v>171</v>
+      </c>
+      <c r="D191" t="s">
+        <v>679</v>
+      </c>
+      <c r="E191" t="s">
+        <v>57</v>
+      </c>
+      <c r="F191" t="s">
+        <v>58</v>
+      </c>
+      <c r="G191" t="s">
+        <v>221</v>
+      </c>
+      <c r="H191" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="192" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A192" t="s">
+        <v>680</v>
+      </c>
+      <c r="C192" t="s">
+        <v>60</v>
+      </c>
+      <c r="D192" t="s">
+        <v>681</v>
+      </c>
+      <c r="E192" t="s">
+        <v>539</v>
+      </c>
+      <c r="F192" t="s">
+        <v>540</v>
+      </c>
+      <c r="G192" t="s">
+        <v>682</v>
+      </c>
+      <c r="H192" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="193" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A193" t="s">
+        <v>683</v>
+      </c>
+      <c r="C193" t="s">
+        <v>60</v>
+      </c>
+      <c r="D193" t="s">
+        <v>681</v>
+      </c>
+      <c r="E193" t="s">
+        <v>539</v>
+      </c>
+      <c r="F193" t="s">
+        <v>540</v>
+      </c>
+      <c r="G193" t="s">
+        <v>682</v>
+      </c>
+      <c r="H193" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="194" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A194" t="s">
+        <v>684</v>
+      </c>
+      <c r="C194" t="s">
+        <v>10</v>
+      </c>
+      <c r="D194" t="s">
+        <v>685</v>
+      </c>
+      <c r="E194" t="s">
+        <v>53</v>
+      </c>
+      <c r="F194" t="s">
+        <v>0</v>
+      </c>
+      <c r="G194" t="s">
+        <v>686</v>
+      </c>
+      <c r="H194" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="195" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A195" t="s">
+        <v>687</v>
+      </c>
+      <c r="C195" t="s">
+        <v>171</v>
+      </c>
+      <c r="D195" t="s">
+        <v>688</v>
+      </c>
+      <c r="E195" t="s">
+        <v>689</v>
+      </c>
+      <c r="F195" t="s">
+        <v>690</v>
+      </c>
+      <c r="G195" t="s">
+        <v>691</v>
+      </c>
+      <c r="H195" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="196" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A196" t="s">
+        <v>692</v>
+      </c>
+      <c r="C196" t="s">
+        <v>60</v>
+      </c>
+      <c r="D196" t="s">
+        <v>693</v>
+      </c>
+      <c r="E196" t="s">
+        <v>40</v>
+      </c>
+      <c r="F196" t="s">
+        <v>0</v>
+      </c>
+      <c r="G196" t="s">
+        <v>694</v>
+      </c>
+      <c r="H196" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="197" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A197" t="s">
+        <v>695</v>
+      </c>
+      <c r="C197" t="s">
+        <v>12</v>
+      </c>
+      <c r="D197" t="s">
+        <v>696</v>
+      </c>
+      <c r="E197" t="s">
+        <v>269</v>
+      </c>
+      <c r="F197" t="s">
+        <v>0</v>
+      </c>
+      <c r="G197" t="s">
+        <v>697</v>
+      </c>
+      <c r="H197" t="s">
+        <v>698</v>
+      </c>
+    </row>
+    <row r="198" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A198" t="s">
+        <v>699</v>
+      </c>
+      <c r="C198" t="s">
+        <v>60</v>
+      </c>
+      <c r="D198" t="s">
+        <v>700</v>
+      </c>
+      <c r="E198" t="s">
+        <v>701</v>
+      </c>
+      <c r="F198" t="s">
+        <v>0</v>
+      </c>
+      <c r="G198" t="s">
+        <v>702</v>
+      </c>
+      <c r="H198" t="s">
+        <v>698</v>
+      </c>
+    </row>
+    <row r="199" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A199" t="s">
+        <v>703</v>
+      </c>
+      <c r="C199" t="s">
+        <v>64</v>
+      </c>
+      <c r="D199" t="s">
+        <v>704</v>
+      </c>
+      <c r="E199" t="s">
+        <v>705</v>
+      </c>
+      <c r="F199" t="s">
+        <v>706</v>
+      </c>
+      <c r="G199" t="s">
+        <v>707</v>
+      </c>
+      <c r="H199" t="s">
+        <v>698</v>
+      </c>
+    </row>
+    <row r="200" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A200" t="s">
+        <v>708</v>
+      </c>
+      <c r="C200" t="s">
+        <v>9</v>
+      </c>
+      <c r="D200" t="s">
+        <v>709</v>
+      </c>
+      <c r="E200" t="s">
+        <v>84</v>
+      </c>
+      <c r="F200" t="s">
+        <v>0</v>
+      </c>
+      <c r="G200" t="s">
+        <v>710</v>
+      </c>
+      <c r="H200" t="s">
+        <v>698</v>
+      </c>
+    </row>
+    <row r="201" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A201" t="s">
+        <v>711</v>
+      </c>
+      <c r="C201" t="s">
+        <v>9</v>
+      </c>
+      <c r="D201" t="s">
+        <v>709</v>
+      </c>
+      <c r="E201" t="s">
+        <v>84</v>
+      </c>
+      <c r="F201" t="s">
+        <v>0</v>
+      </c>
+      <c r="G201" t="s">
+        <v>710</v>
+      </c>
+      <c r="H201" t="s">
+        <v>698</v>
+      </c>
+    </row>
+    <row r="202" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A202" t="s">
+        <v>712</v>
+      </c>
+      <c r="C202" t="s">
+        <v>54</v>
+      </c>
+      <c r="D202" t="s">
+        <v>713</v>
+      </c>
+      <c r="E202" t="s">
+        <v>21</v>
+      </c>
+      <c r="F202" t="s">
+        <v>22</v>
+      </c>
+      <c r="G202" t="s">
+        <v>468</v>
+      </c>
+      <c r="H202" t="s">
+        <v>698</v>
+      </c>
+    </row>
+    <row r="203" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A203" t="s">
+        <v>714</v>
+      </c>
+      <c r="C203" t="s">
+        <v>54</v>
+      </c>
+      <c r="D203" t="s">
+        <v>713</v>
+      </c>
+      <c r="E203" t="s">
+        <v>21</v>
+      </c>
+      <c r="F203" t="s">
+        <v>22</v>
+      </c>
+      <c r="G203" t="s">
+        <v>468</v>
+      </c>
+      <c r="H203" t="s">
+        <v>698</v>
+      </c>
+    </row>
+    <row r="204" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A204" t="s">
+        <v>715</v>
+      </c>
+      <c r="C204" t="s">
+        <v>54</v>
+      </c>
+      <c r="D204" t="s">
+        <v>713</v>
+      </c>
+      <c r="E204" t="s">
+        <v>21</v>
+      </c>
+      <c r="F204" t="s">
+        <v>22</v>
+      </c>
+      <c r="G204" t="s">
+        <v>468</v>
+      </c>
+      <c r="H204" t="s">
+        <v>698</v>
+      </c>
+    </row>
+    <row r="205" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A205" t="s">
+        <v>716</v>
+      </c>
+      <c r="C205" t="s">
+        <v>54</v>
+      </c>
+      <c r="D205" t="s">
+        <v>713</v>
+      </c>
+      <c r="E205" t="s">
+        <v>21</v>
+      </c>
+      <c r="F205" t="s">
+        <v>22</v>
+      </c>
+      <c r="G205" t="s">
+        <v>468</v>
+      </c>
+      <c r="H205" t="s">
+        <v>698</v>
+      </c>
+    </row>
+    <row r="206" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A206" t="s">
+        <v>717</v>
+      </c>
+      <c r="C206" t="s">
+        <v>54</v>
+      </c>
+      <c r="D206" t="s">
+        <v>713</v>
+      </c>
+      <c r="E206" t="s">
+        <v>21</v>
+      </c>
+      <c r="F206" t="s">
+        <v>22</v>
+      </c>
+      <c r="G206" t="s">
+        <v>468</v>
+      </c>
+      <c r="H206" t="s">
+        <v>698</v>
+      </c>
+    </row>
+    <row r="207" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A207" t="s">
+        <v>718</v>
+      </c>
+      <c r="C207" t="s">
+        <v>171</v>
+      </c>
+      <c r="D207" t="s">
+        <v>719</v>
+      </c>
+      <c r="E207" t="s">
+        <v>720</v>
+      </c>
+      <c r="F207" t="s">
+        <v>62</v>
+      </c>
+      <c r="G207" t="s">
+        <v>721</v>
+      </c>
+      <c r="H207" t="s">
+        <v>106</v>
+      </c>
+    </row>
+    <row r="208" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A208" t="s">
+        <v>722</v>
+      </c>
+      <c r="C208" t="s">
+        <v>171</v>
+      </c>
+      <c r="D208" t="s">
+        <v>719</v>
+      </c>
+      <c r="E208" t="s">
+        <v>720</v>
+      </c>
+      <c r="F208" t="s">
+        <v>62</v>
+      </c>
+      <c r="G208" t="s">
+        <v>721</v>
+      </c>
+      <c r="H208" t="s">
+        <v>106</v>
+      </c>
+    </row>
+    <row r="209" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A209" t="s">
+        <v>723</v>
+      </c>
+      <c r="C209" t="s">
+        <v>17</v>
+      </c>
+      <c r="D209" t="s">
+        <v>724</v>
+      </c>
+      <c r="E209" t="s">
+        <v>725</v>
+      </c>
+      <c r="F209" t="s">
+        <v>726</v>
+      </c>
+      <c r="G209" t="s">
+        <v>727</v>
+      </c>
+      <c r="H209" t="s">
+        <v>106</v>
+      </c>
+    </row>
+    <row r="210" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A210" t="s">
+        <v>728</v>
+      </c>
+      <c r="C210" t="s">
+        <v>17</v>
+      </c>
+      <c r="D210" t="s">
+        <v>724</v>
+      </c>
+      <c r="E210" t="s">
+        <v>725</v>
+      </c>
+      <c r="F210" t="s">
+        <v>726</v>
+      </c>
+      <c r="G210" t="s">
+        <v>727</v>
+      </c>
+      <c r="H210" t="s">
+        <v>106</v>
       </c>
     </row>
   </sheetData>

--- a/1.xlsx
+++ b/1.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="\\wh.local\fs\UserProfile_TSSWH19\_TSSWH19_redirected_folders\HunyaCs1\Desktop\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B0CD7A01-8044-4800-87D0-7EF5121E50F1}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{94D68E4E-0ACB-498C-AF25-4623F68B0134}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="0" windowWidth="22260" windowHeight="12648" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1469" uniqueCount="729">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1473" uniqueCount="732">
   <si>
     <t>BUDAPEST</t>
   </si>
@@ -2215,6 +2215,15 @@
   </si>
   <si>
     <t>159995579538702433</t>
+  </si>
+  <si>
+    <t>NFD6-03-28-QWR4</t>
+  </si>
+  <si>
+    <t>AUCHAN_ÁRUHÁZI</t>
+  </si>
+  <si>
+    <t>SZ-854</t>
   </si>
 </sst>
 </file>
@@ -2533,7 +2542,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <sheetPr codeName="Munka1"/>
-  <dimension ref="A1:H210"/>
+  <dimension ref="A1:H211"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="24.88671875" bestFit="1" customWidth="1"/>
@@ -2689,7 +2698,7 @@
         <v>129</v>
       </c>
       <c r="C7" t="s">
-        <v>60</v>
+        <v>731</v>
       </c>
       <c r="D7" t="s">
         <v>130</v>
@@ -2712,7 +2721,7 @@
         <v>134</v>
       </c>
       <c r="C8" t="s">
-        <v>60</v>
+        <v>731</v>
       </c>
       <c r="D8" t="s">
         <v>130</v>
@@ -3448,7 +3457,7 @@
         <v>230</v>
       </c>
       <c r="C40" t="s">
-        <v>60</v>
+        <v>731</v>
       </c>
       <c r="D40" t="s">
         <v>231</v>
@@ -4069,7 +4078,7 @@
         <v>314</v>
       </c>
       <c r="C67" t="s">
-        <v>60</v>
+        <v>731</v>
       </c>
       <c r="D67" t="s">
         <v>315</v>
@@ -4092,7 +4101,7 @@
         <v>318</v>
       </c>
       <c r="C68" t="s">
-        <v>60</v>
+        <v>731</v>
       </c>
       <c r="D68" t="s">
         <v>315</v>
@@ -5722,7 +5731,7 @@
         <v>537</v>
       </c>
       <c r="C139" t="s">
-        <v>60</v>
+        <v>731</v>
       </c>
       <c r="D139" t="s">
         <v>538</v>
@@ -5998,7 +6007,7 @@
         <v>579</v>
       </c>
       <c r="C151" t="s">
-        <v>60</v>
+        <v>731</v>
       </c>
       <c r="D151" t="s">
         <v>580</v>
@@ -6021,7 +6030,7 @@
         <v>583</v>
       </c>
       <c r="C152" t="s">
-        <v>60</v>
+        <v>731</v>
       </c>
       <c r="D152" t="s">
         <v>580</v>
@@ -6044,7 +6053,7 @@
         <v>584</v>
       </c>
       <c r="C153" t="s">
-        <v>60</v>
+        <v>731</v>
       </c>
       <c r="D153" t="s">
         <v>580</v>
@@ -6067,7 +6076,7 @@
         <v>585</v>
       </c>
       <c r="C154" t="s">
-        <v>60</v>
+        <v>731</v>
       </c>
       <c r="D154" t="s">
         <v>580</v>
@@ -6113,7 +6122,7 @@
         <v>591</v>
       </c>
       <c r="C156" t="s">
-        <v>60</v>
+        <v>731</v>
       </c>
       <c r="D156" t="s">
         <v>592</v>
@@ -6159,7 +6168,7 @@
         <v>599</v>
       </c>
       <c r="C158" t="s">
-        <v>60</v>
+        <v>731</v>
       </c>
       <c r="D158" t="s">
         <v>600</v>
@@ -6228,7 +6237,7 @@
         <v>612</v>
       </c>
       <c r="C161" t="s">
-        <v>60</v>
+        <v>731</v>
       </c>
       <c r="D161" t="s">
         <v>613</v>
@@ -6274,7 +6283,7 @@
         <v>619</v>
       </c>
       <c r="C163" t="s">
-        <v>60</v>
+        <v>731</v>
       </c>
       <c r="D163" t="s">
         <v>620</v>
@@ -6297,7 +6306,7 @@
         <v>622</v>
       </c>
       <c r="C164" t="s">
-        <v>60</v>
+        <v>731</v>
       </c>
       <c r="D164" t="s">
         <v>620</v>
@@ -6320,7 +6329,7 @@
         <v>623</v>
       </c>
       <c r="C165" t="s">
-        <v>60</v>
+        <v>731</v>
       </c>
       <c r="D165" t="s">
         <v>620</v>
@@ -6343,7 +6352,7 @@
         <v>624</v>
       </c>
       <c r="C166" t="s">
-        <v>60</v>
+        <v>731</v>
       </c>
       <c r="D166" t="s">
         <v>620</v>
@@ -6366,7 +6375,7 @@
         <v>625</v>
       </c>
       <c r="C167" t="s">
-        <v>60</v>
+        <v>731</v>
       </c>
       <c r="D167" t="s">
         <v>620</v>
@@ -6941,7 +6950,7 @@
         <v>680</v>
       </c>
       <c r="C192" t="s">
-        <v>60</v>
+        <v>731</v>
       </c>
       <c r="D192" t="s">
         <v>681</v>
@@ -6964,7 +6973,7 @@
         <v>683</v>
       </c>
       <c r="C193" t="s">
-        <v>60</v>
+        <v>731</v>
       </c>
       <c r="D193" t="s">
         <v>681</v>
@@ -7079,7 +7088,7 @@
         <v>699</v>
       </c>
       <c r="C198" t="s">
-        <v>60</v>
+        <v>731</v>
       </c>
       <c r="D198" t="s">
         <v>700</v>
@@ -7371,6 +7380,20 @@
       </c>
       <c r="H210" t="s">
         <v>106</v>
+      </c>
+    </row>
+    <row r="211" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A211" t="s">
+        <v>729</v>
+      </c>
+      <c r="C211" t="s">
+        <v>64</v>
+      </c>
+      <c r="D211" t="s">
+        <v>729</v>
+      </c>
+      <c r="H211" t="s">
+        <v>730</v>
       </c>
     </row>
   </sheetData>

--- a/1.xlsx
+++ b/1.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="\\wh.local\fs\UserProfile_TSSWH19\_TSSWH19_redirected_folders\HunyaCs1\Desktop\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E62DA29A-8483-477F-BA26-7D5F5773D703}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{93041527-90E8-4EBC-AE38-D81F4EFDBD8F}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="0" windowWidth="22260" windowHeight="12648" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1526" uniqueCount="732">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1530" uniqueCount="734">
   <si>
     <t>BUDAPEST</t>
   </si>
@@ -2224,6 +2224,12 @@
   </si>
   <si>
     <t>R414514</t>
+  </si>
+  <si>
+    <t>NFD6-03-30-44D4</t>
+  </si>
+  <si>
+    <t>AUCHAN_ÁRUHÁZI</t>
   </si>
 </sst>
 </file>
@@ -2542,7 +2548,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <sheetPr codeName="Munka1"/>
-  <dimension ref="A1:H218"/>
+  <dimension ref="A1:H219"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="25.44140625" bestFit="1" customWidth="1"/>
@@ -7569,6 +7575,20 @@
         <v>136</v>
       </c>
     </row>
+    <row r="219" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A219" t="s">
+        <v>732</v>
+      </c>
+      <c r="C219" t="s">
+        <v>47</v>
+      </c>
+      <c r="D219" t="s">
+        <v>732</v>
+      </c>
+      <c r="H219" t="s">
+        <v>733</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>

--- a/1.xlsx
+++ b/1.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="\\wh.local\fs\UserProfile_TSSWH19\_TSSWH19_redirected_folders\HunyaCs1\Desktop\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A22B9C73-7981-44DD-874D-AFB38A69BED0}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{585CA4F4-B43A-4AF1-A85E-E210C3ABC4BB}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="0" windowWidth="22260" windowHeight="12648" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="966" uniqueCount="506">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="945" uniqueCount="489">
   <si>
     <t>BUDAPEST</t>
   </si>
@@ -60,15 +60,6 @@
     <t>SZ-820</t>
   </si>
   <si>
-    <t>2600</t>
-  </si>
-  <si>
-    <t>VÁC</t>
-  </si>
-  <si>
-    <t>2131</t>
-  </si>
-  <si>
     <t>GÖD</t>
   </si>
   <si>
@@ -84,9 +75,6 @@
     <t>ÉRD</t>
   </si>
   <si>
-    <t>1221</t>
-  </si>
-  <si>
     <t>CSOMAGSZAM</t>
   </si>
   <si>
@@ -108,15 +96,6 @@
     <t>MEGBIZO_ROVIDKOD</t>
   </si>
   <si>
-    <t>SELEX</t>
-  </si>
-  <si>
-    <t>2730</t>
-  </si>
-  <si>
-    <t>ALBERTIRSA</t>
-  </si>
-  <si>
     <t>SZ-828</t>
   </si>
   <si>
@@ -138,192 +117,54 @@
     <t>1096</t>
   </si>
   <si>
-    <t>2100</t>
-  </si>
-  <si>
-    <t>GÖDÖLLŐ</t>
-  </si>
-  <si>
     <t>1117</t>
   </si>
   <si>
     <t>1039</t>
   </si>
   <si>
-    <t>Széchenyi utca</t>
-  </si>
-  <si>
     <t>SZ-815</t>
   </si>
   <si>
     <t>SZ-823</t>
   </si>
   <si>
-    <t>1118</t>
-  </si>
-  <si>
-    <t>1181</t>
-  </si>
-  <si>
-    <t>1045</t>
-  </si>
-  <si>
     <t>1032</t>
   </si>
   <si>
     <t>1157</t>
   </si>
   <si>
-    <t>1094</t>
-  </si>
-  <si>
-    <t>Liliom utca</t>
-  </si>
-  <si>
-    <t>Hegyalja utca</t>
-  </si>
-  <si>
-    <t>2081</t>
-  </si>
-  <si>
-    <t>PILISCSABA</t>
-  </si>
-  <si>
     <t>2200</t>
   </si>
   <si>
     <t>MONOR</t>
   </si>
   <si>
-    <t>INSPORT</t>
-  </si>
-  <si>
     <t>2112</t>
   </si>
   <si>
     <t>VERESEGYHÁZ</t>
   </si>
   <si>
-    <t>69cb7f790ed4809420f4adea</t>
-  </si>
-  <si>
-    <t>260317-F00014200-1</t>
-  </si>
-  <si>
     <t>1036</t>
   </si>
   <si>
-    <t>Lajos utca</t>
-  </si>
-  <si>
-    <t>Harmat utca</t>
-  </si>
-  <si>
-    <t>2045</t>
-  </si>
-  <si>
-    <t>TÖRÖKBÁLINT</t>
-  </si>
-  <si>
-    <t>2051</t>
-  </si>
-  <si>
-    <t>BIATORBÁGY</t>
-  </si>
-  <si>
-    <t>Csokonai utca</t>
-  </si>
-  <si>
-    <t>Kossuth Lajos utca</t>
-  </si>
-  <si>
     <t>Vörösmarty utca</t>
   </si>
   <si>
-    <t>1223</t>
-  </si>
-  <si>
-    <t>SZ-835</t>
-  </si>
-  <si>
     <t>1086</t>
   </si>
   <si>
-    <t>1194</t>
-  </si>
-  <si>
-    <t>69cbadfa0ed4809420f4b461</t>
-  </si>
-  <si>
-    <t>260331-F00006683</t>
-  </si>
-  <si>
     <t>1142</t>
   </si>
   <si>
-    <t>Nezsider park</t>
-  </si>
-  <si>
     <t>SZ-830</t>
   </si>
   <si>
-    <t>1071</t>
-  </si>
-  <si>
-    <t>MEGAPLACE</t>
-  </si>
-  <si>
-    <t>1172</t>
-  </si>
-  <si>
-    <t>305557116/1</t>
-  </si>
-  <si>
-    <t>305557116</t>
-  </si>
-  <si>
-    <t>1087</t>
-  </si>
-  <si>
-    <t>Ciprus utca</t>
-  </si>
-  <si>
-    <t>305557116/2</t>
-  </si>
-  <si>
-    <t>305557116/3</t>
-  </si>
-  <si>
-    <t>2024</t>
-  </si>
-  <si>
-    <t>KISOROSZI</t>
-  </si>
-  <si>
-    <t>1139</t>
-  </si>
-  <si>
-    <t>1112</t>
-  </si>
-  <si>
     <t>1165</t>
   </si>
   <si>
-    <t>2760</t>
-  </si>
-  <si>
-    <t>NAGYKÁTA</t>
-  </si>
-  <si>
-    <t>1016</t>
-  </si>
-  <si>
-    <t>2117</t>
-  </si>
-  <si>
-    <t>ISASZEG</t>
-  </si>
-  <si>
     <t>1163</t>
   </si>
   <si>
@@ -333,1219 +174,1327 @@
     <t>FÓT</t>
   </si>
   <si>
-    <t>1013</t>
-  </si>
-  <si>
-    <t>Attila út</t>
-  </si>
-  <si>
-    <t>Kárász utca</t>
-  </si>
-  <si>
-    <t>Magyar utca</t>
-  </si>
-  <si>
-    <t>2364</t>
-  </si>
-  <si>
-    <t>ÓCSA</t>
-  </si>
-  <si>
-    <t>SZ-800</t>
-  </si>
-  <si>
-    <t>2000</t>
-  </si>
-  <si>
-    <t>SZENTENDRE</t>
-  </si>
-  <si>
-    <t>69c3ef4bd96b4f4a24387065</t>
-  </si>
-  <si>
-    <t>260320-F00011317</t>
-  </si>
-  <si>
     <t>2767</t>
   </si>
   <si>
     <t>TÁPIÓGYÖRGYE</t>
   </si>
   <si>
-    <t>69c55215d96b4f4a2438876a</t>
-  </si>
-  <si>
-    <t>260321-F00005875</t>
-  </si>
-  <si>
-    <t>Erdőkerülő utca</t>
-  </si>
-  <si>
-    <t>69c290bdd96b4f4a2438584a</t>
-  </si>
-  <si>
-    <t>SZ-809</t>
-  </si>
-  <si>
-    <t>260324-F00008791</t>
-  </si>
-  <si>
     <t>Pacsirta utca</t>
   </si>
   <si>
-    <t>69c3fe6bd96b4f4a2438728b</t>
-  </si>
-  <si>
-    <t>260325-F00011314</t>
-  </si>
-  <si>
-    <t>Patkó utca</t>
-  </si>
-  <si>
-    <t>69cbb3ba0ed4809420f4b500</t>
-  </si>
-  <si>
-    <t>260327-F00001238</t>
-  </si>
-  <si>
-    <t>1031</t>
-  </si>
-  <si>
-    <t>Vitorla utca</t>
-  </si>
-  <si>
-    <t>69c6d298d96b4f4a24389e1f</t>
-  </si>
-  <si>
-    <t>260327-W00009216</t>
-  </si>
-  <si>
-    <t>Arató utca</t>
-  </si>
-  <si>
-    <t>69c92bc40ed4809420f48f30</t>
-  </si>
-  <si>
-    <t>260329-W00005809</t>
-  </si>
-  <si>
-    <t>Nagyváradi utca</t>
-  </si>
-  <si>
-    <t>69ca21200ed4809420f494c0</t>
-  </si>
-  <si>
-    <t>260330-F00000873</t>
-  </si>
-  <si>
     <t>1239</t>
   </si>
   <si>
-    <t>Szikes utca</t>
-  </si>
-  <si>
-    <t>69ca81fb0ed4809420f4a402</t>
-  </si>
-  <si>
-    <t>260330-F00011022-2</t>
-  </si>
-  <si>
-    <t>2209</t>
-  </si>
-  <si>
-    <t>PÉTERI</t>
-  </si>
-  <si>
     <t>Petőfi Sándor utca</t>
   </si>
   <si>
-    <t>69ca8a870ed4809420f4a55e</t>
-  </si>
-  <si>
-    <t>260330-F00012030-1</t>
-  </si>
-  <si>
-    <t>2638</t>
-  </si>
-  <si>
-    <t>KEMENCE</t>
-  </si>
-  <si>
-    <t>Belterület</t>
-  </si>
-  <si>
-    <t>69ca72c00ed4809420f4a1d6</t>
-  </si>
-  <si>
-    <t>260330-W00005897</t>
-  </si>
-  <si>
-    <t>István király út</t>
-  </si>
-  <si>
-    <t>69ca72c00ed4809420f4a1dc</t>
-  </si>
-  <si>
-    <t>69ca95db0ed4809420f4a6b5</t>
-  </si>
-  <si>
-    <t>260330-W00007879</t>
-  </si>
-  <si>
     <t>Erdősor utca</t>
   </si>
   <si>
-    <t>69cab90a0ed4809420f4a9a4</t>
-  </si>
-  <si>
-    <t>260330-W00008758</t>
-  </si>
-  <si>
-    <t>Virág köz</t>
-  </si>
-  <si>
-    <t>69cad07d0ed4809420f4aa8c</t>
-  </si>
-  <si>
-    <t>260330-W00009381</t>
-  </si>
-  <si>
-    <t>2071</t>
-  </si>
-  <si>
-    <t>PÁTY</t>
-  </si>
-  <si>
-    <t>Somogyi Béla út</t>
-  </si>
-  <si>
-    <t>69cabf1e0ed4809420f4a9fe</t>
-  </si>
-  <si>
-    <t>260330-W00009812</t>
-  </si>
-  <si>
-    <t>2735</t>
-  </si>
-  <si>
-    <t>DÁNSZENTMIKLÓS</t>
-  </si>
-  <si>
-    <t>69cbfb4a0ed4809420f4be21</t>
-  </si>
-  <si>
-    <t>260331-F00012772-2</t>
-  </si>
-  <si>
-    <t>1061</t>
-  </si>
-  <si>
-    <t>Andrássy út</t>
-  </si>
-  <si>
-    <t>69cbb3cf0ed4809420f4b514</t>
-  </si>
-  <si>
-    <t>260331-W00004384</t>
-  </si>
-  <si>
-    <t>1081</t>
-  </si>
-  <si>
-    <t>Alföldi utca</t>
-  </si>
-  <si>
-    <t>69cbd6f70ed4809420f4ba3c</t>
-  </si>
-  <si>
-    <t>260331-W00006246</t>
-  </si>
-  <si>
     <t>1024</t>
   </si>
   <si>
-    <t>Retek utca</t>
-  </si>
-  <si>
-    <t>69cbf1ee0ed4809420f4bd64</t>
-  </si>
-  <si>
-    <t>260331-W00007687</t>
-  </si>
-  <si>
-    <t>Pablo Neruda utca</t>
-  </si>
-  <si>
-    <t>69cce22d5cef447acab8516b</t>
-  </si>
-  <si>
-    <t>260401-F00003760</t>
-  </si>
-  <si>
     <t>1048</t>
   </si>
   <si>
-    <t>Intarzia utca</t>
-  </si>
-  <si>
-    <t>69cce22d5cef447acab8516c</t>
-  </si>
-  <si>
-    <t>69cce80b5cef447acab85235</t>
-  </si>
-  <si>
-    <t>260401-F00004087</t>
-  </si>
-  <si>
-    <t>Karácsony Sándor utca</t>
-  </si>
-  <si>
-    <t>69ccdb585cef447acab85043</t>
-  </si>
-  <si>
-    <t>260401-W00002577</t>
-  </si>
-  <si>
-    <t>1136</t>
-  </si>
-  <si>
-    <t>Balzac utca</t>
-  </si>
-  <si>
-    <t>69cd009f5cef447acab8553f</t>
-  </si>
-  <si>
-    <t>260401-W00003832</t>
-  </si>
-  <si>
-    <t>Endresz György utca</t>
-  </si>
-  <si>
-    <t>69ccf87c5cef447acab85436</t>
-  </si>
-  <si>
-    <t>260401-W00003939</t>
-  </si>
-  <si>
-    <t>Ágoston utca</t>
-  </si>
-  <si>
-    <t>FIZZ-1000856683</t>
-  </si>
-  <si>
-    <t>267004683</t>
-  </si>
-  <si>
-    <t>1089</t>
-  </si>
-  <si>
-    <t>Diószegi Sámuel utca</t>
-  </si>
-  <si>
-    <t>FIZZ-1000857417</t>
-  </si>
-  <si>
-    <t>267004704</t>
-  </si>
-  <si>
-    <t>1073</t>
-  </si>
-  <si>
-    <t>Erzsébet körút</t>
-  </si>
-  <si>
-    <t>FIZZ-1000856632</t>
-  </si>
-  <si>
-    <t>267004708</t>
-  </si>
-  <si>
     <t>Újszász utca</t>
   </si>
   <si>
-    <t>FIZZ-1000857575</t>
-  </si>
-  <si>
-    <t>267004710</t>
-  </si>
-  <si>
-    <t>Erkel Ferenc utca</t>
-  </si>
-  <si>
-    <t>FIZZ-1000853889</t>
-  </si>
-  <si>
-    <t>267004720</t>
-  </si>
-  <si>
-    <t>Népszínház utca</t>
-  </si>
-  <si>
-    <t>FIZZ-1000858247</t>
-  </si>
-  <si>
-    <t>267004733</t>
-  </si>
-  <si>
-    <t>Ady Endre út.</t>
-  </si>
-  <si>
-    <t>26MPE0003567/1</t>
-  </si>
-  <si>
-    <t>26MPE0003567</t>
-  </si>
-  <si>
-    <t>Akó utca</t>
-  </si>
-  <si>
-    <t>26MPE0003577/1</t>
-  </si>
-  <si>
-    <t>26MPE0003577</t>
-  </si>
-  <si>
-    <t>Leányka utca</t>
-  </si>
-  <si>
-    <t>304308992/1</t>
-  </si>
-  <si>
-    <t>304308992</t>
-  </si>
-  <si>
-    <t>Termálfürdő körút</t>
-  </si>
-  <si>
-    <t>305170407/1</t>
-  </si>
-  <si>
-    <t>305170407</t>
-  </si>
-  <si>
     <t>2144</t>
   </si>
   <si>
     <t>KEREPES</t>
   </si>
   <si>
-    <t>Harangvirág utca</t>
-  </si>
-  <si>
-    <t>305170764/1</t>
-  </si>
-  <si>
     <t>SZ-860</t>
   </si>
   <si>
-    <t>305170764</t>
-  </si>
-  <si>
-    <t>Kinizsi Pál</t>
-  </si>
-  <si>
-    <t>305225507/1</t>
-  </si>
-  <si>
-    <t>305225507</t>
-  </si>
-  <si>
-    <t>Csap utca</t>
-  </si>
-  <si>
-    <t>305628569/1</t>
-  </si>
-  <si>
-    <t>305628569</t>
-  </si>
-  <si>
-    <t>1044</t>
-  </si>
-  <si>
-    <t>Székesdűlő sor</t>
-  </si>
-  <si>
-    <t>305628569/2</t>
-  </si>
-  <si>
-    <t>305628569/3</t>
-  </si>
-  <si>
-    <t>305726062/1</t>
-  </si>
-  <si>
-    <t>305726062</t>
-  </si>
-  <si>
-    <t>Kolozs utca</t>
-  </si>
-  <si>
-    <t>305781979/1</t>
-  </si>
-  <si>
-    <t>305781979</t>
-  </si>
-  <si>
-    <t>Diófa utca</t>
-  </si>
-  <si>
-    <t>305831157/1</t>
-  </si>
-  <si>
-    <t>305831157</t>
-  </si>
-  <si>
-    <t>305831157/2</t>
-  </si>
-  <si>
-    <t>305954413/1</t>
-  </si>
-  <si>
-    <t>305954413</t>
-  </si>
-  <si>
     <t>2440</t>
   </si>
   <si>
     <t>SZÁZHALOMBATTA</t>
   </si>
   <si>
-    <t>305954413/2</t>
-  </si>
-  <si>
-    <t>305954413/3</t>
-  </si>
-  <si>
-    <t>305954566/1</t>
-  </si>
-  <si>
-    <t>305954566</t>
-  </si>
-  <si>
-    <t>Levendula utca</t>
-  </si>
-  <si>
-    <t>306025754/1</t>
-  </si>
-  <si>
-    <t>306025754</t>
-  </si>
-  <si>
-    <t>1237</t>
-  </si>
-  <si>
-    <t>Mezőlak utca</t>
-  </si>
-  <si>
-    <t>306026031/1</t>
-  </si>
-  <si>
-    <t>306026031</t>
-  </si>
-  <si>
     <t>1025</t>
   </si>
   <si>
-    <t>Boróka utca</t>
-  </si>
-  <si>
-    <t>306026031/2</t>
-  </si>
-  <si>
-    <t>306078924/1</t>
-  </si>
-  <si>
-    <t>306078924</t>
-  </si>
-  <si>
-    <t>Enikő utca</t>
-  </si>
-  <si>
-    <t>306146515/1</t>
-  </si>
-  <si>
-    <t>306146515</t>
-  </si>
-  <si>
-    <t>Árpád fejedelem útja</t>
-  </si>
-  <si>
-    <t>306146820/1</t>
-  </si>
-  <si>
-    <t>306146820</t>
-  </si>
-  <si>
-    <t>Csíkihegyek utca</t>
-  </si>
-  <si>
-    <t>306180812/1</t>
-  </si>
-  <si>
-    <t>306180812</t>
-  </si>
-  <si>
     <t>1115</t>
   </si>
   <si>
-    <t>Keveháza u</t>
-  </si>
-  <si>
-    <t>306181153/1</t>
-  </si>
-  <si>
-    <t>306181153</t>
-  </si>
-  <si>
-    <t>1195</t>
-  </si>
-  <si>
-    <t>Batthyány utca</t>
-  </si>
-  <si>
-    <t>306181153/2</t>
-  </si>
-  <si>
-    <t>306181399/1</t>
-  </si>
-  <si>
-    <t>306181399</t>
-  </si>
-  <si>
-    <t>1064</t>
-  </si>
-  <si>
-    <t>Izabella utca</t>
-  </si>
-  <si>
-    <t>306181517/1</t>
-  </si>
-  <si>
-    <t>306181517</t>
-  </si>
-  <si>
-    <t>1113</t>
-  </si>
-  <si>
-    <t>Villányi út</t>
-  </si>
-  <si>
-    <t>306181628/1</t>
-  </si>
-  <si>
-    <t>306181628</t>
-  </si>
-  <si>
-    <t>306181628/2</t>
-  </si>
-  <si>
-    <t>306226429/1</t>
-  </si>
-  <si>
-    <t>306226429</t>
-  </si>
-  <si>
     <t>1097</t>
   </si>
   <si>
     <t>Vágóhíd utca</t>
   </si>
   <si>
-    <t>306226429/2</t>
-  </si>
-  <si>
-    <t>306226637/1</t>
-  </si>
-  <si>
-    <t>306226637</t>
-  </si>
-  <si>
-    <t>Mátyás király utca</t>
-  </si>
-  <si>
-    <t>306226647/1</t>
-  </si>
-  <si>
-    <t>306226647</t>
-  </si>
-  <si>
-    <t>Damjanich utca</t>
-  </si>
-  <si>
-    <t>306276869/1</t>
-  </si>
-  <si>
-    <t>306276869</t>
-  </si>
-  <si>
-    <t>Jókai Mór utca</t>
-  </si>
-  <si>
-    <t>306277239/1</t>
-  </si>
-  <si>
-    <t>306277239</t>
-  </si>
-  <si>
-    <t>Haller utca</t>
-  </si>
-  <si>
-    <t>306277569/1</t>
-  </si>
-  <si>
-    <t>306277569</t>
-  </si>
-  <si>
-    <t>306277692/1</t>
-  </si>
-  <si>
-    <t>306277692</t>
-  </si>
-  <si>
-    <t>Somogyi Béla utca</t>
-  </si>
-  <si>
-    <t>306277692/2</t>
-  </si>
-  <si>
-    <t>306277692/3</t>
-  </si>
-  <si>
-    <t>306334202/1</t>
-  </si>
-  <si>
-    <t>306334202</t>
-  </si>
-  <si>
-    <t>Balogh Ádám utca</t>
-  </si>
-  <si>
-    <t>306334355/1</t>
-  </si>
-  <si>
-    <t>306334355</t>
-  </si>
-  <si>
     <t>1107</t>
   </si>
   <si>
-    <t>Zágrábi utca</t>
-  </si>
-  <si>
-    <t>306334355/2</t>
-  </si>
-  <si>
-    <t>306334392/1</t>
-  </si>
-  <si>
-    <t>306334392</t>
-  </si>
-  <si>
-    <t>1148</t>
-  </si>
-  <si>
-    <t>Nagy Lajos király útja</t>
-  </si>
-  <si>
-    <t>306334872/1</t>
-  </si>
-  <si>
-    <t>306334872</t>
-  </si>
-  <si>
-    <t>1035</t>
-  </si>
-  <si>
-    <t>Szentendrei út</t>
-  </si>
-  <si>
-    <t>306335021/1</t>
-  </si>
-  <si>
-    <t>306335021</t>
-  </si>
-  <si>
-    <t>1095</t>
-  </si>
-  <si>
-    <t>Lechner Ödön fasor</t>
-  </si>
-  <si>
-    <t>306335021/2</t>
-  </si>
-  <si>
-    <t>306335037/1</t>
-  </si>
-  <si>
-    <t>306335037</t>
-  </si>
-  <si>
-    <t>Tormásrét utca</t>
-  </si>
-  <si>
-    <t>306335108/1</t>
-  </si>
-  <si>
-    <t>306335108</t>
-  </si>
-  <si>
-    <t>Vérhalom tér</t>
-  </si>
-  <si>
-    <t>306399247/1</t>
-  </si>
-  <si>
-    <t>306399247</t>
-  </si>
-  <si>
-    <t>1133</t>
-  </si>
-  <si>
-    <t>Hegedűs Gyula utca</t>
-  </si>
-  <si>
-    <t>306399487/1</t>
-  </si>
-  <si>
-    <t>306399487</t>
-  </si>
-  <si>
-    <t>Bagoly utca</t>
-  </si>
-  <si>
-    <t>306399599/1</t>
-  </si>
-  <si>
-    <t>306399599</t>
-  </si>
-  <si>
-    <t>Váci út</t>
-  </si>
-  <si>
-    <t>306399710/1</t>
-  </si>
-  <si>
-    <t>306399710</t>
-  </si>
-  <si>
-    <t>Kelet utca</t>
-  </si>
-  <si>
-    <t>306399710/2</t>
-  </si>
-  <si>
-    <t>306399710/3</t>
-  </si>
-  <si>
-    <t>306399869/1</t>
-  </si>
-  <si>
-    <t>306399869</t>
-  </si>
-  <si>
-    <t>1156</t>
-  </si>
-  <si>
-    <t>Nádastó park</t>
-  </si>
-  <si>
-    <t>306399967/1</t>
-  </si>
-  <si>
-    <t>306399967</t>
-  </si>
-  <si>
-    <t>1074</t>
-  </si>
-  <si>
-    <t>306400053/1</t>
-  </si>
-  <si>
-    <t>306400053</t>
-  </si>
-  <si>
-    <t>306457009/1</t>
-  </si>
-  <si>
-    <t>306457009</t>
-  </si>
-  <si>
-    <t>Szegedi út</t>
-  </si>
-  <si>
-    <t>306457287/1</t>
-  </si>
-  <si>
     <t>SZ-832</t>
   </si>
   <si>
-    <t>306457287</t>
-  </si>
-  <si>
-    <t>2330</t>
-  </si>
-  <si>
-    <t>DUNAHARASZTI</t>
-  </si>
-  <si>
-    <t>306457354/1</t>
-  </si>
-  <si>
-    <t>306457354</t>
-  </si>
-  <si>
     <t>1135</t>
   </si>
   <si>
-    <t>Szent László út</t>
-  </si>
-  <si>
-    <t>306457354/2</t>
-  </si>
-  <si>
-    <t>306457588/1</t>
-  </si>
-  <si>
-    <t>306457588</t>
-  </si>
-  <si>
-    <t>Hősök tere</t>
-  </si>
-  <si>
-    <t>306457666/1</t>
-  </si>
-  <si>
-    <t>306457666</t>
-  </si>
-  <si>
-    <t>Istvántelki út</t>
-  </si>
-  <si>
-    <t>306457758/1</t>
-  </si>
-  <si>
-    <t>306457758</t>
-  </si>
-  <si>
-    <t>1137</t>
-  </si>
-  <si>
-    <t>Katona József utca</t>
-  </si>
-  <si>
-    <t>306457898/1</t>
-  </si>
-  <si>
-    <t>306457898</t>
-  </si>
-  <si>
-    <t>1029</t>
-  </si>
-  <si>
-    <t>Ördögárok utca</t>
-  </si>
-  <si>
-    <t>306457957/1</t>
-  </si>
-  <si>
-    <t>306457957</t>
-  </si>
-  <si>
-    <t>1078</t>
-  </si>
-  <si>
-    <t>Hernád utca</t>
-  </si>
-  <si>
-    <t>306516744/1</t>
-  </si>
-  <si>
-    <t>306516744</t>
-  </si>
-  <si>
-    <t>Csáktornya Park</t>
-  </si>
-  <si>
-    <t>306570937/1</t>
-  </si>
-  <si>
-    <t>306570937</t>
-  </si>
-  <si>
-    <t>Eötvös utca</t>
-  </si>
-  <si>
-    <t>306571158/1</t>
-  </si>
-  <si>
-    <t>306571158</t>
-  </si>
-  <si>
-    <t>Erzsébet királyné útja útja</t>
-  </si>
-  <si>
-    <t>306621126/1</t>
-  </si>
-  <si>
-    <t>306621126</t>
-  </si>
-  <si>
-    <t>1212</t>
-  </si>
-  <si>
-    <t>Táncsics Mihály utca</t>
-  </si>
-  <si>
-    <t>306621794/1</t>
-  </si>
-  <si>
-    <t>306621794</t>
-  </si>
-  <si>
-    <t>2317</t>
-  </si>
-  <si>
-    <t>SZIGETCSÉP</t>
-  </si>
-  <si>
-    <t>Duna sor</t>
-  </si>
-  <si>
-    <t>306621895/1</t>
-  </si>
-  <si>
-    <t>306621895</t>
-  </si>
-  <si>
     <t>1144</t>
   </si>
   <si>
-    <t>Gvadányi utca</t>
-  </si>
-  <si>
-    <t>159995579538795732</t>
-  </si>
-  <si>
-    <t>73676-106667</t>
-  </si>
-  <si>
-    <t>Budafoki út.</t>
-  </si>
-  <si>
     <t>EZTOOLS</t>
   </si>
   <si>
-    <t>159995579538795749</t>
-  </si>
-  <si>
-    <t>99002299/1</t>
-  </si>
-  <si>
-    <t>99002299</t>
-  </si>
-  <si>
-    <t>1204</t>
-  </si>
-  <si>
-    <t>Orsolya utca</t>
-  </si>
-  <si>
-    <t>99002300/1</t>
-  </si>
-  <si>
-    <t>99002300</t>
-  </si>
-  <si>
     <t>2011</t>
   </si>
   <si>
     <t>BUDAKALÁSZ</t>
   </si>
   <si>
-    <t>202604012600675801</t>
-  </si>
-  <si>
-    <t>NFD6-03-20-ZZ2L</t>
-  </si>
-  <si>
-    <t>Napsugár sétány</t>
-  </si>
-  <si>
-    <t>202604012600675802</t>
-  </si>
-  <si>
-    <t>202603312600765701</t>
-  </si>
-  <si>
-    <t>NFD6-03-30-PMK5</t>
-  </si>
-  <si>
     <t>1033</t>
   </si>
   <si>
-    <t>Szérűskert utca</t>
-  </si>
-  <si>
-    <t>202604012600772201</t>
-  </si>
-  <si>
-    <t>NFD6-03-30-YNRL</t>
-  </si>
-  <si>
-    <t>József Attila útja</t>
-  </si>
-  <si>
-    <t>202604012600774901</t>
-  </si>
-  <si>
-    <t>NFD6-03-31-4WTG</t>
-  </si>
-  <si>
     <t>Napsugár utca</t>
   </si>
   <si>
-    <t>202604012600774902</t>
-  </si>
-  <si>
-    <t>202604012600772601</t>
-  </si>
-  <si>
-    <t>NFD6-03-31-ME8T</t>
-  </si>
-  <si>
-    <t>Keve utca</t>
-  </si>
-  <si>
-    <t>202604012600774301</t>
-  </si>
-  <si>
-    <t>NFD6-03-31-VM72</t>
-  </si>
-  <si>
-    <t>2310</t>
-  </si>
-  <si>
-    <t>SZIGETSZENTMIKLÓS</t>
-  </si>
-  <si>
-    <t>Esze Tamás köz</t>
-  </si>
-  <si>
-    <t>202604012600774302</t>
-  </si>
-  <si>
-    <t>202604012600774303</t>
-  </si>
-  <si>
-    <t>202604022600782201</t>
-  </si>
-  <si>
-    <t>NFD6-04-01-43LN</t>
-  </si>
-  <si>
-    <t>1213</t>
-  </si>
-  <si>
-    <t>Szilfás utca</t>
-  </si>
-  <si>
-    <t>202604022600778801</t>
-  </si>
-  <si>
-    <t>NFD6-04-01-49QY</t>
-  </si>
-  <si>
-    <t>Golgota utca</t>
-  </si>
-  <si>
-    <t>202604022600778802</t>
-  </si>
-  <si>
-    <t>202604022600779701</t>
-  </si>
-  <si>
-    <t>NFD6-04-01-UMAB</t>
-  </si>
-  <si>
-    <t>Kövező utca</t>
-  </si>
-  <si>
-    <t>202604012600729501</t>
-  </si>
-  <si>
-    <t>NFE6-03-25-ZGJP</t>
-  </si>
-  <si>
-    <t>Palota-kert -</t>
-  </si>
-  <si>
-    <t>202603302600751901</t>
-  </si>
-  <si>
-    <t>NFE6-03-28-YTGU</t>
-  </si>
-  <si>
-    <t>202603302600751902</t>
-  </si>
-  <si>
-    <t>202604012600772401</t>
-  </si>
-  <si>
-    <t>NFE6-03-31-D6UK</t>
-  </si>
-  <si>
     <t>2230</t>
   </si>
   <si>
     <t>GYÖMRŐ</t>
   </si>
   <si>
-    <t>Kossuth köz</t>
-  </si>
-  <si>
-    <t>202604012600775201</t>
-  </si>
-  <si>
-    <t>NFE6-03-31-ZNUJ</t>
-  </si>
-  <si>
-    <t>2093</t>
-  </si>
-  <si>
-    <t>BUDAJENŐ</t>
-  </si>
-  <si>
-    <t>202604012600775202</t>
-  </si>
-  <si>
-    <t>159995579538655227</t>
-  </si>
-  <si>
-    <t>R414493</t>
-  </si>
-  <si>
-    <t>Ördögorom lejtő</t>
-  </si>
-  <si>
-    <t>159995579538655234</t>
-  </si>
-  <si>
-    <t>159995579538786426</t>
-  </si>
-  <si>
-    <t>SA26/H001449_csere</t>
-  </si>
-  <si>
-    <t>2314</t>
-  </si>
-  <si>
-    <t>HALÁSZTELEK</t>
-  </si>
-  <si>
-    <t>Biró László utca</t>
-  </si>
-  <si>
     <t>PICIGURMAN</t>
+  </si>
+  <si>
+    <t>69cd28da5cef447acab85b43</t>
+  </si>
+  <si>
+    <t>SZ-819</t>
+  </si>
+  <si>
+    <t>260320-F00008570</t>
+  </si>
+  <si>
+    <t>1122</t>
+  </si>
+  <si>
+    <t>Székács utca</t>
+  </si>
+  <si>
+    <t>69cd09085cef447acab8568b</t>
+  </si>
+  <si>
+    <t>260326-W00002768</t>
+  </si>
+  <si>
+    <t>1201</t>
+  </si>
+  <si>
+    <t>Alsó határút</t>
+  </si>
+  <si>
+    <t>69cce7115cef447acab8522c</t>
+  </si>
+  <si>
+    <t>260327-F00009863</t>
+  </si>
+  <si>
+    <t>Irinyi János utca</t>
+  </si>
+  <si>
+    <t>69ce25d45cef447acab8637c</t>
+  </si>
+  <si>
+    <t>260327-F00012241</t>
+  </si>
+  <si>
+    <t>1149</t>
+  </si>
+  <si>
+    <t>Egressy út</t>
+  </si>
+  <si>
+    <t>69ccc6665cef447acab84d77</t>
+  </si>
+  <si>
+    <t>260328-F00002417</t>
+  </si>
+  <si>
+    <t>Béke sétány</t>
+  </si>
+  <si>
+    <t>69cbb6840ed4809420f4b5a8</t>
+  </si>
+  <si>
+    <t>260329-F00000276</t>
+  </si>
+  <si>
+    <t>2750</t>
+  </si>
+  <si>
+    <t>NAGYKŐRÖS</t>
+  </si>
+  <si>
+    <t>Lázár Vilmos utca</t>
+  </si>
+  <si>
+    <t>69c8cbb10ed4809420f48981</t>
+  </si>
+  <si>
+    <t>SZ-814</t>
+  </si>
+  <si>
+    <t>260329-W00000897</t>
+  </si>
+  <si>
+    <t>2344</t>
+  </si>
+  <si>
+    <t>DÖMSÖD</t>
+  </si>
+  <si>
+    <t>Tassi út</t>
+  </si>
+  <si>
+    <t>69ca6bb80ed4809420f4a0bc</t>
+  </si>
+  <si>
+    <t>260330-F00008887</t>
+  </si>
+  <si>
+    <t>2711</t>
+  </si>
+  <si>
+    <t>TÁPIÓSZENTMÁRTON</t>
+  </si>
+  <si>
+    <t>Szelei út</t>
+  </si>
+  <si>
+    <t>69ca6bb80ed4809420f4a0bd</t>
+  </si>
+  <si>
+    <t>69ca6bb80ed4809420f4a0c0</t>
+  </si>
+  <si>
+    <t>69cd07165cef447acab8562c</t>
+  </si>
+  <si>
+    <t>260331-F00009332</t>
+  </si>
+  <si>
+    <t>Mohács utca</t>
+  </si>
+  <si>
+    <t>69cbc8f20ed4809420f4b838</t>
+  </si>
+  <si>
+    <t>260331-F00009720</t>
+  </si>
+  <si>
+    <t>2132</t>
+  </si>
+  <si>
+    <t>Ady Endre út</t>
+  </si>
+  <si>
+    <t>69cbfffb0ed4809420f4bea7</t>
+  </si>
+  <si>
+    <t>260331-F00013345</t>
+  </si>
+  <si>
+    <t>69cba3b10ed4809420f4b328</t>
+  </si>
+  <si>
+    <t>260331-W00003690</t>
+  </si>
+  <si>
+    <t>Futórózsa utca</t>
+  </si>
+  <si>
+    <t>69cbec0c0ed4809420f4bca2</t>
+  </si>
+  <si>
+    <t>260331-W00006880</t>
+  </si>
+  <si>
+    <t>Vadrózsa utca</t>
+  </si>
+  <si>
+    <t>69cbeae90ed4809420f4bc87</t>
+  </si>
+  <si>
+    <t>260331-W00007287</t>
+  </si>
+  <si>
+    <t>2337</t>
+  </si>
+  <si>
+    <t>DÉLEGYHÁZA</t>
+  </si>
+  <si>
+    <t>69cbeae90ed4809420f4bc88</t>
+  </si>
+  <si>
+    <t>69cbf31f0ed4809420f4bd8d</t>
+  </si>
+  <si>
+    <t>260331-W00007694</t>
+  </si>
+  <si>
+    <t>Kancsó dűlő</t>
+  </si>
+  <si>
+    <t>69cc0a870ed4809420f4bf46</t>
+  </si>
+  <si>
+    <t>260331-W00008718</t>
+  </si>
+  <si>
+    <t>Eperfasor utca</t>
+  </si>
+  <si>
+    <t>69ccddbc5cef447acab850bb</t>
+  </si>
+  <si>
+    <t>260401-F00002977</t>
+  </si>
+  <si>
+    <t>2212</t>
+  </si>
+  <si>
+    <t>CSÉVHARASZT</t>
+  </si>
+  <si>
+    <t>Ady Endre utca</t>
+  </si>
+  <si>
+    <t>69cd12345cef447acab857ce</t>
+  </si>
+  <si>
+    <t>260401-F00007846</t>
+  </si>
+  <si>
+    <t>1126</t>
+  </si>
+  <si>
+    <t>Böszörményi út</t>
+  </si>
+  <si>
+    <t>69cd13695cef447acab85806</t>
+  </si>
+  <si>
+    <t>260401-F00008298</t>
+  </si>
+  <si>
+    <t>Fraknó utca</t>
+  </si>
+  <si>
+    <t>69cd0b2f5cef447acab856e6</t>
+  </si>
+  <si>
+    <t>SZ-801</t>
+  </si>
+  <si>
+    <t>260401-W00004850</t>
+  </si>
+  <si>
+    <t>1051</t>
+  </si>
+  <si>
+    <t>Október</t>
+  </si>
+  <si>
+    <t>69cd73725cef447acab85ff4</t>
+  </si>
+  <si>
+    <t>260401-W00009922</t>
+  </si>
+  <si>
+    <t>1171</t>
+  </si>
+  <si>
+    <t>Lajosház utca</t>
+  </si>
+  <si>
+    <t>69cda5e75cef447acab8606a</t>
+  </si>
+  <si>
+    <t>260401-W00011153</t>
+  </si>
+  <si>
+    <t>1103</t>
+  </si>
+  <si>
+    <t>Salamon utca</t>
+  </si>
+  <si>
+    <t>69ce30255cef447acab86488</t>
+  </si>
+  <si>
+    <t>260402-F00003734</t>
+  </si>
+  <si>
+    <t>1185</t>
+  </si>
+  <si>
+    <t>Jeges utca</t>
+  </si>
+  <si>
+    <t>69ce42eb5cef447acab86775</t>
+  </si>
+  <si>
+    <t>260402-F00005695</t>
+  </si>
+  <si>
+    <t>Virágvölgy utca</t>
+  </si>
+  <si>
+    <t>69ce385b5cef447acab865ea</t>
+  </si>
+  <si>
+    <t>260402-W00003803</t>
+  </si>
+  <si>
+    <t>Nándorfejérvári út</t>
+  </si>
+  <si>
+    <t>305666975/1</t>
+  </si>
+  <si>
+    <t>305666975</t>
+  </si>
+  <si>
+    <t>1123</t>
+  </si>
+  <si>
+    <t>Ráth György utca</t>
+  </si>
+  <si>
+    <t>305725691/1</t>
+  </si>
+  <si>
+    <t>305725691</t>
+  </si>
+  <si>
+    <t>Malomvíz utca</t>
+  </si>
+  <si>
+    <t>306026504/1</t>
+  </si>
+  <si>
+    <t>306026504</t>
+  </si>
+  <si>
+    <t>Vecsési út</t>
+  </si>
+  <si>
+    <t>306078782/1</t>
+  </si>
+  <si>
+    <t>306078782</t>
+  </si>
+  <si>
+    <t>Jókai Mór Utca</t>
+  </si>
+  <si>
+    <t>306181486/1</t>
+  </si>
+  <si>
+    <t>306181486</t>
+  </si>
+  <si>
+    <t>Lenhossék utca</t>
+  </si>
+  <si>
+    <t>306181745/1</t>
+  </si>
+  <si>
+    <t>306181745</t>
+  </si>
+  <si>
+    <t>1052</t>
+  </si>
+  <si>
+    <t>Apáczai Csere János Utca</t>
+  </si>
+  <si>
+    <t>306226090/1</t>
+  </si>
+  <si>
+    <t>306226090</t>
+  </si>
+  <si>
+    <t>2615</t>
+  </si>
+  <si>
+    <t>CSŐVÁR</t>
+  </si>
+  <si>
+    <t>Kinizsi út</t>
+  </si>
+  <si>
+    <t>306226090/2</t>
+  </si>
+  <si>
+    <t>306226153/1</t>
+  </si>
+  <si>
+    <t>306226153</t>
+  </si>
+  <si>
+    <t>2234</t>
+  </si>
+  <si>
+    <t>MAGLÓD</t>
+  </si>
+  <si>
+    <t>Sorompó utca</t>
+  </si>
+  <si>
+    <t>306226287/1</t>
+  </si>
+  <si>
+    <t>306226287</t>
+  </si>
+  <si>
+    <t>306277495/1</t>
+  </si>
+  <si>
+    <t>306277495</t>
+  </si>
+  <si>
+    <t>Berky Lili utca</t>
+  </si>
+  <si>
+    <t>306277495/2</t>
+  </si>
+  <si>
+    <t>306334215/1</t>
+  </si>
+  <si>
+    <t>306334215</t>
+  </si>
+  <si>
+    <t>Bábos Utca</t>
+  </si>
+  <si>
+    <t>306334542/1</t>
+  </si>
+  <si>
+    <t>306334542</t>
+  </si>
+  <si>
+    <t>306334789/1</t>
+  </si>
+  <si>
+    <t>306334789</t>
+  </si>
+  <si>
+    <t>2162</t>
+  </si>
+  <si>
+    <t>ŐRBOTTYÁN</t>
+  </si>
+  <si>
+    <t>Ősz utca</t>
+  </si>
+  <si>
+    <t>306334789/2</t>
+  </si>
+  <si>
+    <t>306335042/1</t>
+  </si>
+  <si>
+    <t>306335042</t>
+  </si>
+  <si>
+    <t>Galagonya utca</t>
+  </si>
+  <si>
+    <t>306399389/1</t>
+  </si>
+  <si>
+    <t>306399389</t>
+  </si>
+  <si>
+    <t>1101</t>
+  </si>
+  <si>
+    <t>Gép utca</t>
+  </si>
+  <si>
+    <t>306457171/1</t>
+  </si>
+  <si>
+    <t>306457171</t>
+  </si>
+  <si>
+    <t>Zsókavár utca</t>
+  </si>
+  <si>
+    <t>306457641/1</t>
+  </si>
+  <si>
+    <t>306457641</t>
+  </si>
+  <si>
+    <t>1088</t>
+  </si>
+  <si>
+    <t>Szentkirályi utca</t>
+  </si>
+  <si>
+    <t>306457823/1</t>
+  </si>
+  <si>
+    <t>306457823</t>
+  </si>
+  <si>
+    <t>1111</t>
+  </si>
+  <si>
+    <t>Karinthy Frigyes út</t>
+  </si>
+  <si>
+    <t>306516572/1</t>
+  </si>
+  <si>
+    <t>306516572</t>
+  </si>
+  <si>
+    <t>Erzsébet királyné utca</t>
+  </si>
+  <si>
+    <t>306516691/1</t>
+  </si>
+  <si>
+    <t>306516691</t>
+  </si>
+  <si>
+    <t>2315</t>
+  </si>
+  <si>
+    <t>SZIGETHALOM</t>
+  </si>
+  <si>
+    <t>Nyár utca</t>
+  </si>
+  <si>
+    <t>306516770/1</t>
+  </si>
+  <si>
+    <t>306516770</t>
+  </si>
+  <si>
+    <t>2017</t>
+  </si>
+  <si>
+    <t>PÓCSMEGYER</t>
+  </si>
+  <si>
+    <t>Leander utca</t>
+  </si>
+  <si>
+    <t>306516770/2</t>
+  </si>
+  <si>
+    <t>306516870/1</t>
+  </si>
+  <si>
+    <t>306516870</t>
+  </si>
+  <si>
+    <t>Ond Vezér útja</t>
+  </si>
+  <si>
+    <t>306516900/1</t>
+  </si>
+  <si>
+    <t>306516900</t>
+  </si>
+  <si>
+    <t>Szánkózó utca</t>
+  </si>
+  <si>
+    <t>306516905/1</t>
+  </si>
+  <si>
+    <t>306516905</t>
+  </si>
+  <si>
+    <t>1037</t>
+  </si>
+  <si>
+    <t>Remete köz</t>
+  </si>
+  <si>
+    <t>306570862/1</t>
+  </si>
+  <si>
+    <t>306570862</t>
+  </si>
+  <si>
+    <t>2217</t>
+  </si>
+  <si>
+    <t>GOMBA</t>
+  </si>
+  <si>
+    <t>Felsőfarkasd utca</t>
+  </si>
+  <si>
+    <t>306571058/1</t>
+  </si>
+  <si>
+    <t>306571058</t>
+  </si>
+  <si>
+    <t>1138</t>
+  </si>
+  <si>
+    <t>Szekszárdi utca</t>
+  </si>
+  <si>
+    <t>306571117/1</t>
+  </si>
+  <si>
+    <t>306571117</t>
+  </si>
+  <si>
+    <t>Kék Duna</t>
+  </si>
+  <si>
+    <t>306571168/1</t>
+  </si>
+  <si>
+    <t>306571168</t>
+  </si>
+  <si>
+    <t>2146</t>
+  </si>
+  <si>
+    <t>MOGYORÓD</t>
+  </si>
+  <si>
+    <t>306571168/2</t>
+  </si>
+  <si>
+    <t>306571205/1</t>
+  </si>
+  <si>
+    <t>306571205</t>
+  </si>
+  <si>
+    <t>Fráter Lóránd Utca</t>
+  </si>
+  <si>
+    <t>306571205/2</t>
+  </si>
+  <si>
+    <t>306571205/3</t>
+  </si>
+  <si>
+    <t>306571244/1</t>
+  </si>
+  <si>
+    <t>306571244</t>
+  </si>
+  <si>
+    <t>Fillér utca</t>
+  </si>
+  <si>
+    <t>306571279/1</t>
+  </si>
+  <si>
+    <t>306571279</t>
+  </si>
+  <si>
+    <t>Becő utca</t>
+  </si>
+  <si>
+    <t>306571350/1</t>
+  </si>
+  <si>
+    <t>306571350</t>
+  </si>
+  <si>
+    <t>Kiscelli utca</t>
+  </si>
+  <si>
+    <t>306571366/1</t>
+  </si>
+  <si>
+    <t>306571366</t>
+  </si>
+  <si>
+    <t>1027</t>
+  </si>
+  <si>
+    <t>Varsányi Irén utca</t>
+  </si>
+  <si>
+    <t>306621084/1</t>
+  </si>
+  <si>
+    <t>306621084</t>
+  </si>
+  <si>
+    <t>1066</t>
+  </si>
+  <si>
+    <t>Ó utca</t>
+  </si>
+  <si>
+    <t>306621084/2</t>
+  </si>
+  <si>
+    <t>306621224/1</t>
+  </si>
+  <si>
+    <t>306621224</t>
+  </si>
+  <si>
+    <t>2381</t>
+  </si>
+  <si>
+    <t>TÁBORFALVA</t>
+  </si>
+  <si>
+    <t>Posta sor</t>
+  </si>
+  <si>
+    <t>306621254/1</t>
+  </si>
+  <si>
+    <t>306621254</t>
+  </si>
+  <si>
+    <t>Hímző Utca</t>
+  </si>
+  <si>
+    <t>306621254/2</t>
+  </si>
+  <si>
+    <t>306621372/1</t>
+  </si>
+  <si>
+    <t>306621372</t>
+  </si>
+  <si>
+    <t>Tóth Árpád utca</t>
+  </si>
+  <si>
+    <t>306621384/1</t>
+  </si>
+  <si>
+    <t>306621384</t>
+  </si>
+  <si>
+    <t>1225</t>
+  </si>
+  <si>
+    <t>306621487/1</t>
+  </si>
+  <si>
+    <t>306621487</t>
+  </si>
+  <si>
+    <t>Toldy Ferenc utca</t>
+  </si>
+  <si>
+    <t>306621605/1</t>
+  </si>
+  <si>
+    <t>306621605</t>
+  </si>
+  <si>
+    <t>1191</t>
+  </si>
+  <si>
+    <t>Arany János utca</t>
+  </si>
+  <si>
+    <t>306621675/1</t>
+  </si>
+  <si>
+    <t>306621675</t>
+  </si>
+  <si>
+    <t>Puskás Tivadar Út</t>
+  </si>
+  <si>
+    <t>306621754/1</t>
+  </si>
+  <si>
+    <t>306621754</t>
+  </si>
+  <si>
+    <t>Pannónia utca</t>
+  </si>
+  <si>
+    <t>306621977/1</t>
+  </si>
+  <si>
+    <t>306621977</t>
+  </si>
+  <si>
+    <t>Pomázi ÚT</t>
+  </si>
+  <si>
+    <t>306622077/1</t>
+  </si>
+  <si>
+    <t>306622077</t>
+  </si>
+  <si>
+    <t>2083</t>
+  </si>
+  <si>
+    <t>SOLYMÁR</t>
+  </si>
+  <si>
+    <t>Csősz utca</t>
+  </si>
+  <si>
+    <t>306668667/1</t>
+  </si>
+  <si>
+    <t>306668667</t>
+  </si>
+  <si>
+    <t>2628</t>
+  </si>
+  <si>
+    <t>SZOB</t>
+  </si>
+  <si>
+    <t>Szent László utca</t>
+  </si>
+  <si>
+    <t>306668686/1</t>
+  </si>
+  <si>
+    <t>306668686</t>
+  </si>
+  <si>
+    <t>Róbert Károly körút</t>
+  </si>
+  <si>
+    <t>306668686/2</t>
+  </si>
+  <si>
+    <t>306668686/3</t>
+  </si>
+  <si>
+    <t>306668720/1</t>
+  </si>
+  <si>
+    <t>306668720</t>
+  </si>
+  <si>
+    <t>Folyamőr utca</t>
+  </si>
+  <si>
+    <t>306668857/1</t>
+  </si>
+  <si>
+    <t>306668857</t>
+  </si>
+  <si>
+    <t>1067</t>
+  </si>
+  <si>
+    <t>Teréz körút</t>
+  </si>
+  <si>
+    <t>306668857/2</t>
+  </si>
+  <si>
+    <t>306668925/1</t>
+  </si>
+  <si>
+    <t>306668925</t>
+  </si>
+  <si>
+    <t>1203</t>
+  </si>
+  <si>
+    <t>306669012/1</t>
+  </si>
+  <si>
+    <t>306669012</t>
+  </si>
+  <si>
+    <t>1046</t>
+  </si>
+  <si>
+    <t>Nádor utca</t>
+  </si>
+  <si>
+    <t>306669135/1</t>
+  </si>
+  <si>
+    <t>306669135</t>
+  </si>
+  <si>
+    <t>1182</t>
+  </si>
+  <si>
+    <t>Torda utca</t>
+  </si>
+  <si>
+    <t>306669170/1</t>
+  </si>
+  <si>
+    <t>306669170</t>
+  </si>
+  <si>
+    <t>2080</t>
+  </si>
+  <si>
+    <t>PILISJÁSZFALU</t>
+  </si>
+  <si>
+    <t>Búzavirág utca</t>
+  </si>
+  <si>
+    <t>306669170/2</t>
+  </si>
+  <si>
+    <t>306669238/1</t>
+  </si>
+  <si>
+    <t>306669238</t>
+  </si>
+  <si>
+    <t>2097</t>
+  </si>
+  <si>
+    <t>PILISBOROSJENŐ</t>
+  </si>
+  <si>
+    <t>Ezüsthegyi utca</t>
+  </si>
+  <si>
+    <t>306669358/1</t>
+  </si>
+  <si>
+    <t>306669358</t>
+  </si>
+  <si>
+    <t>Törökvész út</t>
+  </si>
+  <si>
+    <t>306669441/1</t>
+  </si>
+  <si>
+    <t>306669441</t>
+  </si>
+  <si>
+    <t>1116</t>
+  </si>
+  <si>
+    <t>Gyapot utca</t>
+  </si>
+  <si>
+    <t>306721338/1</t>
+  </si>
+  <si>
+    <t>306721338</t>
+  </si>
+  <si>
+    <t>Lujza utca</t>
+  </si>
+  <si>
+    <t>306766217/1</t>
+  </si>
+  <si>
+    <t>306766217</t>
+  </si>
+  <si>
+    <t>1146</t>
+  </si>
+  <si>
+    <t>Cházár András utca</t>
+  </si>
+  <si>
+    <t>306766293/1</t>
+  </si>
+  <si>
+    <t>306766293</t>
+  </si>
+  <si>
+    <t>Szatmár utca</t>
+  </si>
+  <si>
+    <t>306766468/1</t>
+  </si>
+  <si>
+    <t>306766468</t>
+  </si>
+  <si>
+    <t>Balkán utca</t>
+  </si>
+  <si>
+    <t>306823789/1</t>
+  </si>
+  <si>
+    <t>306823789</t>
+  </si>
+  <si>
+    <t>Szállás utca</t>
+  </si>
+  <si>
+    <t>306823789/2</t>
+  </si>
+  <si>
+    <t>306824401/1</t>
+  </si>
+  <si>
+    <t>306824401</t>
+  </si>
+  <si>
+    <t>2316</t>
+  </si>
+  <si>
+    <t>TÖKÖL</t>
+  </si>
+  <si>
+    <t>Gyöngyvirág utca</t>
+  </si>
+  <si>
+    <t>306891292/1</t>
+  </si>
+  <si>
+    <t>306891292</t>
+  </si>
+  <si>
+    <t>Magdolna utca</t>
+  </si>
+  <si>
+    <t>306891353/1</t>
+  </si>
+  <si>
+    <t>306891353</t>
+  </si>
+  <si>
+    <t>Teleki László tér</t>
+  </si>
+  <si>
+    <t>306949039/1</t>
+  </si>
+  <si>
+    <t>306949039</t>
+  </si>
+  <si>
+    <t>2194</t>
+  </si>
+  <si>
+    <t>TURA</t>
+  </si>
+  <si>
+    <t>Mária utca</t>
+  </si>
+  <si>
+    <t>307015528/1</t>
+  </si>
+  <si>
+    <t>307015528</t>
+  </si>
+  <si>
+    <t>2766</t>
+  </si>
+  <si>
+    <t>TÁPIÓSZELE</t>
+  </si>
+  <si>
+    <t>Temető út</t>
+  </si>
+  <si>
+    <t>307015567/1</t>
+  </si>
+  <si>
+    <t>307015567</t>
+  </si>
+  <si>
+    <t>Bihari út</t>
+  </si>
+  <si>
+    <t>307016077/1</t>
+  </si>
+  <si>
+    <t>307016077</t>
+  </si>
+  <si>
+    <t>Búza Utca</t>
+  </si>
+  <si>
+    <t>307016104/1</t>
+  </si>
+  <si>
+    <t>307016104</t>
+  </si>
+  <si>
+    <t>Bécsi út</t>
+  </si>
+  <si>
+    <t>307080841/1</t>
+  </si>
+  <si>
+    <t>307080841</t>
+  </si>
+  <si>
+    <t>2764</t>
+  </si>
+  <si>
+    <t>TÁPIÓBICSKE</t>
+  </si>
+  <si>
+    <t>Rákóczi Út</t>
+  </si>
+  <si>
+    <t>307081455/1</t>
+  </si>
+  <si>
+    <t>307081455</t>
+  </si>
+  <si>
+    <t>Rákóczi út</t>
+  </si>
+  <si>
+    <t>202604022600737801</t>
+  </si>
+  <si>
+    <t>NFD6-03-26-YKZ5</t>
+  </si>
+  <si>
+    <t>2225</t>
+  </si>
+  <si>
+    <t>ÜLLŐ</t>
+  </si>
+  <si>
+    <t>Maglódi út</t>
+  </si>
+  <si>
+    <t>202604022600737802</t>
+  </si>
+  <si>
+    <t>202604022600737803</t>
+  </si>
+  <si>
+    <t>202604022600737804</t>
+  </si>
+  <si>
+    <t>202604022600737805</t>
+  </si>
+  <si>
+    <t>202603312600766001</t>
+  </si>
+  <si>
+    <t>NFD6-03-30-2KJS</t>
+  </si>
+  <si>
+    <t>Búza utca</t>
+  </si>
+  <si>
+    <t>202604012600775101</t>
+  </si>
+  <si>
+    <t>NFD6-03-31-54XF</t>
+  </si>
+  <si>
+    <t>202604022600778901</t>
+  </si>
+  <si>
+    <t>NFD6-04-01-KCZU</t>
+  </si>
+  <si>
+    <t>202604022600778902</t>
+  </si>
+  <si>
+    <t>202604022600778903</t>
+  </si>
+  <si>
+    <t>202604022600778904</t>
+  </si>
+  <si>
+    <t>202604022600782301</t>
+  </si>
+  <si>
+    <t>NFD6-04-01-KFEG</t>
+  </si>
+  <si>
+    <t>1114</t>
+  </si>
+  <si>
+    <t>Fadrusz utca</t>
+  </si>
+  <si>
+    <t>202604022600778701</t>
+  </si>
+  <si>
+    <t>NFD6-04-01-MS5Z</t>
+  </si>
+  <si>
+    <t>Latorca utca</t>
+  </si>
+  <si>
+    <t>202604022600780101</t>
+  </si>
+  <si>
+    <t>NFD6-04-01-YLYE</t>
+  </si>
+  <si>
+    <t>1205</t>
+  </si>
+  <si>
+    <t>Köteles utca</t>
+  </si>
+  <si>
+    <t>NFD6-04-04-35PG-1</t>
+  </si>
+  <si>
+    <t>NFD6-04-04-35PG</t>
+  </si>
+  <si>
+    <t>Vadvirág utca</t>
+  </si>
+  <si>
+    <t>159995579538787997</t>
+  </si>
+  <si>
+    <t>SA26/H001588</t>
+  </si>
+  <si>
+    <t>1188</t>
+  </si>
+  <si>
+    <t>Szentgyörgyi Dezső u.</t>
+  </si>
+  <si>
+    <t>159995579538788000</t>
+  </si>
+  <si>
+    <t>159995579538788017</t>
+  </si>
+  <si>
+    <t>159995579538793998</t>
+  </si>
+  <si>
+    <t>SZL20260323/01</t>
+  </si>
+  <si>
+    <t>Kelenföldi u.</t>
+  </si>
+  <si>
+    <t>159995579538794001</t>
+  </si>
+  <si>
+    <t>159995579538794018</t>
+  </si>
+  <si>
+    <t>159995579538794025</t>
   </si>
 </sst>
 </file>
@@ -1864,7 +1813,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <sheetPr codeName="Munka1"/>
-  <dimension ref="A1:H138"/>
+  <dimension ref="A1:H135"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="24.88671875" bestFit="1" customWidth="1"/>
@@ -1872,52 +1821,52 @@
     <col min="3" max="3" width="6.88671875" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="20.109375" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="5" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="20" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="34.77734375" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="19.6640625" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="29" bestFit="1" customWidth="1"/>
     <col min="8" max="8" width="19.88671875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
+        <v>15</v>
+      </c>
+      <c r="C1" t="s">
+        <v>16</v>
+      </c>
+      <c r="D1" t="s">
+        <v>17</v>
+      </c>
+      <c r="E1" t="s">
+        <v>18</v>
+      </c>
+      <c r="F1" t="s">
         <v>19</v>
       </c>
-      <c r="C1" t="s">
+      <c r="G1" t="s">
         <v>20</v>
       </c>
-      <c r="D1" t="s">
+      <c r="H1" t="s">
         <v>21</v>
-      </c>
-      <c r="E1" t="s">
-        <v>22</v>
-      </c>
-      <c r="F1" t="s">
-        <v>23</v>
-      </c>
-      <c r="G1" t="s">
-        <v>24</v>
-      </c>
-      <c r="H1" t="s">
-        <v>25</v>
       </c>
     </row>
     <row r="2" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
-        <v>58</v>
+        <v>78</v>
       </c>
       <c r="C2" t="s">
-        <v>41</v>
+        <v>79</v>
       </c>
       <c r="D2" t="s">
-        <v>59</v>
+        <v>80</v>
       </c>
       <c r="E2" t="s">
-        <v>60</v>
+        <v>81</v>
       </c>
       <c r="F2" t="s">
         <v>0</v>
       </c>
       <c r="G2" t="s">
-        <v>61</v>
+        <v>82</v>
       </c>
       <c r="H2" t="s">
         <v>1</v>
@@ -1925,22 +1874,22 @@
     </row>
     <row r="3" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
-        <v>110</v>
+        <v>83</v>
       </c>
       <c r="C3" t="s">
-        <v>71</v>
+        <v>32</v>
       </c>
       <c r="D3" t="s">
-        <v>111</v>
+        <v>84</v>
       </c>
       <c r="E3" t="s">
-        <v>112</v>
+        <v>85</v>
       </c>
       <c r="F3" t="s">
-        <v>113</v>
+        <v>0</v>
       </c>
       <c r="G3" t="s">
-        <v>67</v>
+        <v>86</v>
       </c>
       <c r="H3" t="s">
         <v>1</v>
@@ -1948,22 +1897,22 @@
     </row>
     <row r="4" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
-        <v>114</v>
+        <v>87</v>
       </c>
       <c r="C4" t="s">
-        <v>29</v>
+        <v>5</v>
       </c>
       <c r="D4" t="s">
-        <v>115</v>
+        <v>88</v>
       </c>
       <c r="E4" t="s">
-        <v>47</v>
+        <v>60</v>
       </c>
       <c r="F4" t="s">
-        <v>0</v>
+        <v>61</v>
       </c>
       <c r="G4" t="s">
-        <v>116</v>
+        <v>89</v>
       </c>
       <c r="H4" t="s">
         <v>1</v>
@@ -1971,22 +1920,22 @@
     </row>
     <row r="5" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
-        <v>117</v>
+        <v>90</v>
       </c>
       <c r="C5" t="s">
-        <v>118</v>
+        <v>31</v>
       </c>
       <c r="D5" t="s">
-        <v>119</v>
+        <v>91</v>
       </c>
       <c r="E5" t="s">
-        <v>27</v>
+        <v>92</v>
       </c>
       <c r="F5" t="s">
-        <v>28</v>
+        <v>0</v>
       </c>
       <c r="G5" t="s">
-        <v>120</v>
+        <v>93</v>
       </c>
       <c r="H5" t="s">
         <v>1</v>
@@ -1994,22 +1943,22 @@
     </row>
     <row r="6" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
-        <v>121</v>
+        <v>94</v>
       </c>
       <c r="C6" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="D6" t="s">
-        <v>122</v>
+        <v>95</v>
       </c>
       <c r="E6" t="s">
-        <v>14</v>
+        <v>71</v>
       </c>
       <c r="F6" t="s">
-        <v>15</v>
+        <v>72</v>
       </c>
       <c r="G6" t="s">
-        <v>123</v>
+        <v>96</v>
       </c>
       <c r="H6" t="s">
         <v>1</v>
@@ -2017,22 +1966,22 @@
     </row>
     <row r="7" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
-        <v>124</v>
+        <v>97</v>
       </c>
       <c r="C7" t="s">
-        <v>41</v>
+        <v>9</v>
       </c>
       <c r="D7" t="s">
-        <v>125</v>
+        <v>98</v>
       </c>
       <c r="E7" t="s">
-        <v>126</v>
+        <v>99</v>
       </c>
       <c r="F7" t="s">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="G7" t="s">
-        <v>127</v>
+        <v>101</v>
       </c>
       <c r="H7" t="s">
         <v>1</v>
@@ -2040,22 +1989,22 @@
     </row>
     <row r="8" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
-        <v>128</v>
+        <v>102</v>
       </c>
       <c r="C8" t="s">
-        <v>29</v>
+        <v>103</v>
       </c>
       <c r="D8" t="s">
-        <v>129</v>
+        <v>104</v>
       </c>
       <c r="E8" t="s">
-        <v>56</v>
+        <v>105</v>
       </c>
       <c r="F8" t="s">
-        <v>57</v>
+        <v>106</v>
       </c>
       <c r="G8" t="s">
-        <v>130</v>
+        <v>107</v>
       </c>
       <c r="H8" t="s">
         <v>1</v>
@@ -2063,22 +2012,22 @@
     </row>
     <row r="9" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
-        <v>131</v>
+        <v>108</v>
       </c>
       <c r="C9" t="s">
-        <v>2</v>
+        <v>26</v>
       </c>
       <c r="D9" t="s">
-        <v>132</v>
+        <v>109</v>
       </c>
       <c r="E9" t="s">
-        <v>96</v>
+        <v>110</v>
       </c>
       <c r="F9" t="s">
-        <v>97</v>
+        <v>111</v>
       </c>
       <c r="G9" t="s">
-        <v>133</v>
+        <v>112</v>
       </c>
       <c r="H9" t="s">
         <v>1</v>
@@ -2086,22 +2035,22 @@
     </row>
     <row r="10" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
-        <v>134</v>
+        <v>113</v>
       </c>
       <c r="C10" t="s">
-        <v>42</v>
+        <v>26</v>
       </c>
       <c r="D10" t="s">
-        <v>135</v>
+        <v>109</v>
       </c>
       <c r="E10" t="s">
-        <v>136</v>
+        <v>110</v>
       </c>
       <c r="F10" t="s">
-        <v>0</v>
+        <v>111</v>
       </c>
       <c r="G10" t="s">
-        <v>137</v>
+        <v>112</v>
       </c>
       <c r="H10" t="s">
         <v>1</v>
@@ -2109,22 +2058,22 @@
     </row>
     <row r="11" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A11" t="s">
-        <v>138</v>
+        <v>114</v>
       </c>
       <c r="C11" t="s">
-        <v>118</v>
+        <v>26</v>
       </c>
       <c r="D11" t="s">
-        <v>139</v>
+        <v>109</v>
       </c>
       <c r="E11" t="s">
-        <v>140</v>
+        <v>110</v>
       </c>
       <c r="F11" t="s">
-        <v>141</v>
+        <v>111</v>
       </c>
       <c r="G11" t="s">
-        <v>142</v>
+        <v>112</v>
       </c>
       <c r="H11" t="s">
         <v>1</v>
@@ -2132,22 +2081,22 @@
     </row>
     <row r="12" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A12" t="s">
-        <v>143</v>
+        <v>115</v>
       </c>
       <c r="C12" t="s">
-        <v>78</v>
+        <v>7</v>
       </c>
       <c r="D12" t="s">
-        <v>144</v>
+        <v>116</v>
       </c>
       <c r="E12" t="s">
-        <v>145</v>
+        <v>68</v>
       </c>
       <c r="F12" t="s">
-        <v>146</v>
+        <v>0</v>
       </c>
       <c r="G12" t="s">
-        <v>147</v>
+        <v>117</v>
       </c>
       <c r="H12" t="s">
         <v>1</v>
@@ -2155,22 +2104,22 @@
     </row>
     <row r="13" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A13" t="s">
-        <v>148</v>
+        <v>118</v>
       </c>
       <c r="C13" t="s">
-        <v>71</v>
+        <v>43</v>
       </c>
       <c r="D13" t="s">
-        <v>149</v>
+        <v>119</v>
       </c>
       <c r="E13" t="s">
-        <v>93</v>
+        <v>120</v>
       </c>
       <c r="F13" t="s">
-        <v>94</v>
+        <v>10</v>
       </c>
       <c r="G13" t="s">
-        <v>150</v>
+        <v>121</v>
       </c>
       <c r="H13" t="s">
         <v>1</v>
@@ -2178,22 +2127,22 @@
     </row>
     <row r="14" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A14" t="s">
-        <v>151</v>
+        <v>122</v>
       </c>
       <c r="C14" t="s">
-        <v>71</v>
+        <v>103</v>
       </c>
       <c r="D14" t="s">
-        <v>149</v>
+        <v>123</v>
       </c>
       <c r="E14" t="s">
-        <v>93</v>
+        <v>105</v>
       </c>
       <c r="F14" t="s">
-        <v>94</v>
+        <v>106</v>
       </c>
       <c r="G14" t="s">
-        <v>150</v>
+        <v>107</v>
       </c>
       <c r="H14" t="s">
         <v>1</v>
@@ -2201,22 +2150,22 @@
     </row>
     <row r="15" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A15" t="s">
-        <v>152</v>
+        <v>124</v>
       </c>
       <c r="C15" t="s">
-        <v>42</v>
+        <v>2</v>
       </c>
       <c r="D15" t="s">
-        <v>153</v>
+        <v>125</v>
       </c>
       <c r="E15" t="s">
-        <v>105</v>
+        <v>44</v>
       </c>
       <c r="F15" t="s">
-        <v>106</v>
+        <v>0</v>
       </c>
       <c r="G15" t="s">
-        <v>154</v>
+        <v>126</v>
       </c>
       <c r="H15" t="s">
         <v>1</v>
@@ -2224,22 +2173,22 @@
     </row>
     <row r="16" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A16" t="s">
-        <v>155</v>
+        <v>127</v>
       </c>
       <c r="C16" t="s">
-        <v>71</v>
+        <v>2</v>
       </c>
       <c r="D16" t="s">
-        <v>156</v>
+        <v>128</v>
       </c>
       <c r="E16" t="s">
-        <v>93</v>
+        <v>57</v>
       </c>
       <c r="F16" t="s">
-        <v>94</v>
+        <v>58</v>
       </c>
       <c r="G16" t="s">
-        <v>157</v>
+        <v>129</v>
       </c>
       <c r="H16" t="s">
         <v>1</v>
@@ -2247,22 +2196,22 @@
     </row>
     <row r="17" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A17" t="s">
-        <v>158</v>
+        <v>130</v>
       </c>
       <c r="C17" t="s">
-        <v>34</v>
+        <v>103</v>
       </c>
       <c r="D17" t="s">
-        <v>159</v>
+        <v>131</v>
       </c>
       <c r="E17" t="s">
-        <v>160</v>
+        <v>132</v>
       </c>
       <c r="F17" t="s">
-        <v>161</v>
+        <v>133</v>
       </c>
       <c r="G17" t="s">
-        <v>162</v>
+        <v>40</v>
       </c>
       <c r="H17" t="s">
         <v>1</v>
@@ -2270,22 +2219,22 @@
     </row>
     <row r="18" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A18" t="s">
-        <v>163</v>
+        <v>134</v>
       </c>
       <c r="C18" t="s">
-        <v>118</v>
+        <v>103</v>
       </c>
       <c r="D18" t="s">
-        <v>164</v>
+        <v>131</v>
       </c>
       <c r="E18" t="s">
-        <v>165</v>
+        <v>132</v>
       </c>
       <c r="F18" t="s">
-        <v>166</v>
+        <v>133</v>
       </c>
       <c r="G18" t="s">
-        <v>68</v>
+        <v>40</v>
       </c>
       <c r="H18" t="s">
         <v>1</v>
@@ -2293,22 +2242,22 @@
     </row>
     <row r="19" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A19" t="s">
-        <v>74</v>
+        <v>135</v>
       </c>
       <c r="C19" t="s">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="D19" t="s">
-        <v>75</v>
+        <v>136</v>
       </c>
       <c r="E19" t="s">
-        <v>76</v>
+        <v>35</v>
       </c>
       <c r="F19" t="s">
-        <v>0</v>
+        <v>36</v>
       </c>
       <c r="G19" t="s">
-        <v>77</v>
+        <v>137</v>
       </c>
       <c r="H19" t="s">
         <v>1</v>
@@ -2316,22 +2265,22 @@
     </row>
     <row r="20" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A20" t="s">
-        <v>167</v>
+        <v>138</v>
       </c>
       <c r="C20" t="s">
-        <v>9</v>
+        <v>26</v>
       </c>
       <c r="D20" t="s">
-        <v>168</v>
+        <v>139</v>
       </c>
       <c r="E20" t="s">
-        <v>169</v>
+        <v>75</v>
       </c>
       <c r="F20" t="s">
-        <v>0</v>
+        <v>76</v>
       </c>
       <c r="G20" t="s">
-        <v>170</v>
+        <v>140</v>
       </c>
       <c r="H20" t="s">
         <v>1</v>
@@ -2339,22 +2288,22 @@
     </row>
     <row r="21" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A21" t="s">
-        <v>171</v>
+        <v>141</v>
       </c>
       <c r="C21" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D21" t="s">
-        <v>172</v>
+        <v>142</v>
       </c>
       <c r="E21" t="s">
-        <v>173</v>
+        <v>143</v>
       </c>
       <c r="F21" t="s">
-        <v>0</v>
+        <v>144</v>
       </c>
       <c r="G21" t="s">
-        <v>174</v>
+        <v>145</v>
       </c>
       <c r="H21" t="s">
         <v>1</v>
@@ -2362,22 +2311,22 @@
     </row>
     <row r="22" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A22" t="s">
-        <v>175</v>
+        <v>146</v>
       </c>
       <c r="C22" t="s">
-        <v>33</v>
+        <v>79</v>
       </c>
       <c r="D22" t="s">
-        <v>176</v>
+        <v>147</v>
       </c>
       <c r="E22" t="s">
-        <v>177</v>
+        <v>148</v>
       </c>
       <c r="F22" t="s">
         <v>0</v>
       </c>
       <c r="G22" t="s">
-        <v>178</v>
+        <v>149</v>
       </c>
       <c r="H22" t="s">
         <v>1</v>
@@ -2385,22 +2334,22 @@
     </row>
     <row r="23" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A23" t="s">
-        <v>179</v>
+        <v>150</v>
       </c>
       <c r="C23" t="s">
-        <v>41</v>
+        <v>79</v>
       </c>
       <c r="D23" t="s">
-        <v>180</v>
+        <v>151</v>
       </c>
       <c r="E23" t="s">
-        <v>39</v>
+        <v>63</v>
       </c>
       <c r="F23" t="s">
         <v>0</v>
       </c>
       <c r="G23" t="s">
-        <v>181</v>
+        <v>152</v>
       </c>
       <c r="H23" t="s">
         <v>1</v>
@@ -2408,22 +2357,22 @@
     </row>
     <row r="24" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A24" t="s">
-        <v>182</v>
+        <v>153</v>
       </c>
       <c r="C24" t="s">
-        <v>78</v>
+        <v>154</v>
       </c>
       <c r="D24" t="s">
-        <v>183</v>
+        <v>155</v>
       </c>
       <c r="E24" t="s">
-        <v>184</v>
+        <v>156</v>
       </c>
       <c r="F24" t="s">
         <v>0</v>
       </c>
       <c r="G24" t="s">
-        <v>185</v>
+        <v>157</v>
       </c>
       <c r="H24" t="s">
         <v>1</v>
@@ -2431,22 +2380,22 @@
     </row>
     <row r="25" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A25" t="s">
-        <v>186</v>
+        <v>158</v>
       </c>
       <c r="C25" t="s">
-        <v>78</v>
+        <v>26</v>
       </c>
       <c r="D25" t="s">
-        <v>183</v>
+        <v>159</v>
       </c>
       <c r="E25" t="s">
-        <v>184</v>
+        <v>160</v>
       </c>
       <c r="F25" t="s">
         <v>0</v>
       </c>
       <c r="G25" t="s">
-        <v>185</v>
+        <v>161</v>
       </c>
       <c r="H25" t="s">
         <v>1</v>
@@ -2454,22 +2403,22 @@
     </row>
     <row r="26" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A26" t="s">
-        <v>187</v>
+        <v>162</v>
       </c>
       <c r="C26" t="s">
-        <v>8</v>
+        <v>25</v>
       </c>
       <c r="D26" t="s">
-        <v>188</v>
+        <v>163</v>
       </c>
       <c r="E26" t="s">
-        <v>72</v>
+        <v>164</v>
       </c>
       <c r="F26" t="s">
         <v>0</v>
       </c>
       <c r="G26" t="s">
-        <v>189</v>
+        <v>165</v>
       </c>
       <c r="H26" t="s">
         <v>1</v>
@@ -2477,22 +2426,22 @@
     </row>
     <row r="27" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A27" t="s">
-        <v>190</v>
+        <v>166</v>
       </c>
       <c r="C27" t="s">
-        <v>7</v>
+        <v>59</v>
       </c>
       <c r="D27" t="s">
-        <v>191</v>
+        <v>167</v>
       </c>
       <c r="E27" t="s">
-        <v>192</v>
+        <v>168</v>
       </c>
       <c r="F27" t="s">
         <v>0</v>
       </c>
       <c r="G27" t="s">
-        <v>193</v>
+        <v>169</v>
       </c>
       <c r="H27" t="s">
         <v>1</v>
@@ -2500,22 +2449,22 @@
     </row>
     <row r="28" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A28" t="s">
-        <v>194</v>
+        <v>170</v>
       </c>
       <c r="C28" t="s">
-        <v>42</v>
+        <v>32</v>
       </c>
       <c r="D28" t="s">
-        <v>195</v>
+        <v>171</v>
       </c>
       <c r="E28" t="s">
-        <v>73</v>
+        <v>51</v>
       </c>
       <c r="F28" t="s">
         <v>0</v>
       </c>
       <c r="G28" t="s">
-        <v>196</v>
+        <v>172</v>
       </c>
       <c r="H28" t="s">
         <v>1</v>
@@ -2523,22 +2472,22 @@
     </row>
     <row r="29" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A29" t="s">
-        <v>197</v>
+        <v>173</v>
       </c>
       <c r="C29" t="s">
-        <v>41</v>
+        <v>79</v>
       </c>
       <c r="D29" t="s">
-        <v>198</v>
+        <v>174</v>
       </c>
       <c r="E29" t="s">
-        <v>46</v>
+        <v>29</v>
       </c>
       <c r="F29" t="s">
         <v>0</v>
       </c>
       <c r="G29" t="s">
-        <v>199</v>
+        <v>175</v>
       </c>
       <c r="H29" t="s">
         <v>1</v>
@@ -2546,206 +2495,206 @@
     </row>
     <row r="30" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A30" t="s">
-        <v>200</v>
+        <v>176</v>
       </c>
       <c r="C30" t="s">
-        <v>8</v>
+        <v>79</v>
       </c>
       <c r="D30" t="s">
-        <v>201</v>
+        <v>177</v>
       </c>
       <c r="E30" t="s">
-        <v>202</v>
+        <v>178</v>
       </c>
       <c r="F30" t="s">
         <v>0</v>
       </c>
       <c r="G30" t="s">
-        <v>203</v>
+        <v>179</v>
       </c>
       <c r="H30" t="s">
-        <v>26</v>
+        <v>3</v>
       </c>
     </row>
     <row r="31" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A31" t="s">
-        <v>204</v>
+        <v>180</v>
       </c>
       <c r="C31" t="s">
-        <v>9</v>
+        <v>43</v>
       </c>
       <c r="D31" t="s">
-        <v>205</v>
+        <v>181</v>
       </c>
       <c r="E31" t="s">
-        <v>206</v>
+        <v>55</v>
       </c>
       <c r="F31" t="s">
         <v>0</v>
       </c>
       <c r="G31" t="s">
-        <v>207</v>
+        <v>182</v>
       </c>
       <c r="H31" t="s">
-        <v>26</v>
+        <v>3</v>
       </c>
     </row>
     <row r="32" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A32" t="s">
-        <v>208</v>
+        <v>183</v>
       </c>
       <c r="C32" t="s">
-        <v>2</v>
+        <v>32</v>
       </c>
       <c r="D32" t="s">
-        <v>209</v>
+        <v>184</v>
       </c>
       <c r="E32" t="s">
-        <v>92</v>
+        <v>23</v>
       </c>
       <c r="F32" t="s">
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="G32" t="s">
-        <v>210</v>
+        <v>185</v>
       </c>
       <c r="H32" t="s">
-        <v>26</v>
+        <v>3</v>
       </c>
     </row>
     <row r="33" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A33" t="s">
-        <v>211</v>
+        <v>186</v>
       </c>
       <c r="C33" t="s">
-        <v>29</v>
+        <v>32</v>
       </c>
       <c r="D33" t="s">
-        <v>212</v>
+        <v>187</v>
       </c>
       <c r="E33" t="s">
-        <v>56</v>
+        <v>23</v>
       </c>
       <c r="F33" t="s">
-        <v>57</v>
+        <v>24</v>
       </c>
       <c r="G33" t="s">
-        <v>213</v>
+        <v>188</v>
       </c>
       <c r="H33" t="s">
-        <v>26</v>
+        <v>3</v>
       </c>
     </row>
     <row r="34" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A34" t="s">
-        <v>214</v>
+        <v>189</v>
       </c>
       <c r="C34" t="s">
         <v>8</v>
       </c>
       <c r="D34" t="s">
-        <v>215</v>
+        <v>190</v>
       </c>
       <c r="E34" t="s">
-        <v>173</v>
+        <v>28</v>
       </c>
       <c r="F34" t="s">
         <v>0</v>
       </c>
       <c r="G34" t="s">
-        <v>216</v>
+        <v>191</v>
       </c>
       <c r="H34" t="s">
-        <v>26</v>
+        <v>3</v>
       </c>
     </row>
     <row r="35" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A35" t="s">
-        <v>217</v>
+        <v>192</v>
       </c>
       <c r="C35" t="s">
-        <v>5</v>
+        <v>154</v>
       </c>
       <c r="D35" t="s">
-        <v>218</v>
+        <v>193</v>
       </c>
       <c r="E35" t="s">
-        <v>18</v>
+        <v>194</v>
       </c>
       <c r="F35" t="s">
         <v>0</v>
       </c>
       <c r="G35" t="s">
-        <v>219</v>
+        <v>195</v>
       </c>
       <c r="H35" t="s">
-        <v>26</v>
+        <v>3</v>
       </c>
     </row>
     <row r="36" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A36" t="s">
-        <v>220</v>
+        <v>196</v>
       </c>
       <c r="C36" t="s">
-        <v>78</v>
+        <v>22</v>
       </c>
       <c r="D36" t="s">
-        <v>221</v>
+        <v>197</v>
       </c>
       <c r="E36" t="s">
-        <v>10</v>
+        <v>198</v>
       </c>
       <c r="F36" t="s">
-        <v>11</v>
+        <v>199</v>
       </c>
       <c r="G36" t="s">
-        <v>222</v>
+        <v>200</v>
       </c>
       <c r="H36" t="s">
-        <v>80</v>
+        <v>3</v>
       </c>
     </row>
     <row r="37" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A37" t="s">
-        <v>223</v>
+        <v>201</v>
       </c>
       <c r="C37" t="s">
-        <v>5</v>
+        <v>22</v>
       </c>
       <c r="D37" t="s">
-        <v>224</v>
+        <v>197</v>
       </c>
       <c r="E37" t="s">
-        <v>18</v>
+        <v>198</v>
       </c>
       <c r="F37" t="s">
-        <v>0</v>
+        <v>199</v>
       </c>
       <c r="G37" t="s">
-        <v>225</v>
+        <v>200</v>
       </c>
       <c r="H37" t="s">
-        <v>80</v>
+        <v>3</v>
       </c>
     </row>
     <row r="38" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A38" t="s">
-        <v>226</v>
+        <v>202</v>
       </c>
       <c r="C38" t="s">
-        <v>78</v>
+        <v>26</v>
       </c>
       <c r="D38" t="s">
-        <v>227</v>
+        <v>203</v>
       </c>
       <c r="E38" t="s">
-        <v>12</v>
+        <v>204</v>
       </c>
       <c r="F38" t="s">
-        <v>13</v>
+        <v>205</v>
       </c>
       <c r="G38" t="s">
-        <v>228</v>
+        <v>206</v>
       </c>
       <c r="H38" t="s">
         <v>3</v>
@@ -2753,22 +2702,22 @@
     </row>
     <row r="39" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A39" t="s">
-        <v>229</v>
+        <v>207</v>
       </c>
       <c r="C39" t="s">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="D39" t="s">
-        <v>230</v>
+        <v>208</v>
       </c>
       <c r="E39" t="s">
-        <v>231</v>
+        <v>64</v>
       </c>
       <c r="F39" t="s">
-        <v>232</v>
+        <v>0</v>
       </c>
       <c r="G39" t="s">
-        <v>233</v>
+        <v>65</v>
       </c>
       <c r="H39" t="s">
         <v>3</v>
@@ -2776,22 +2725,22 @@
     </row>
     <row r="40" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A40" t="s">
-        <v>234</v>
+        <v>209</v>
       </c>
       <c r="C40" t="s">
-        <v>235</v>
+        <v>26</v>
       </c>
       <c r="D40" t="s">
-        <v>236</v>
+        <v>210</v>
       </c>
       <c r="E40" t="s">
-        <v>63</v>
+        <v>160</v>
       </c>
       <c r="F40" t="s">
-        <v>64</v>
+        <v>0</v>
       </c>
       <c r="G40" t="s">
-        <v>237</v>
+        <v>211</v>
       </c>
       <c r="H40" t="s">
         <v>3</v>
@@ -2799,22 +2748,22 @@
     </row>
     <row r="41" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A41" t="s">
-        <v>238</v>
+        <v>212</v>
       </c>
       <c r="C41" t="s">
-        <v>34</v>
+        <v>26</v>
       </c>
       <c r="D41" t="s">
-        <v>239</v>
+        <v>210</v>
       </c>
       <c r="E41" t="s">
-        <v>95</v>
+        <v>160</v>
       </c>
       <c r="F41" t="s">
         <v>0</v>
       </c>
       <c r="G41" t="s">
-        <v>240</v>
+        <v>211</v>
       </c>
       <c r="H41" t="s">
         <v>3</v>
@@ -2822,22 +2771,22 @@
     </row>
     <row r="42" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A42" t="s">
-        <v>82</v>
+        <v>213</v>
       </c>
       <c r="C42" t="s">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="D42" t="s">
-        <v>83</v>
+        <v>214</v>
       </c>
       <c r="E42" t="s">
-        <v>84</v>
+        <v>45</v>
       </c>
       <c r="F42" t="s">
         <v>0</v>
       </c>
       <c r="G42" t="s">
-        <v>85</v>
+        <v>215</v>
       </c>
       <c r="H42" t="s">
         <v>3</v>
@@ -2845,22 +2794,22 @@
     </row>
     <row r="43" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A43" t="s">
-        <v>86</v>
+        <v>216</v>
       </c>
       <c r="C43" t="s">
-        <v>8</v>
+        <v>103</v>
       </c>
       <c r="D43" t="s">
-        <v>83</v>
+        <v>217</v>
       </c>
       <c r="E43" t="s">
-        <v>84</v>
+        <v>132</v>
       </c>
       <c r="F43" t="s">
-        <v>0</v>
+        <v>133</v>
       </c>
       <c r="G43" t="s">
-        <v>85</v>
+        <v>74</v>
       </c>
       <c r="H43" t="s">
         <v>3</v>
@@ -2868,22 +2817,22 @@
     </row>
     <row r="44" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A44" t="s">
-        <v>87</v>
+        <v>218</v>
       </c>
       <c r="C44" t="s">
-        <v>8</v>
+        <v>22</v>
       </c>
       <c r="D44" t="s">
-        <v>83</v>
+        <v>219</v>
       </c>
       <c r="E44" t="s">
-        <v>84</v>
+        <v>220</v>
       </c>
       <c r="F44" t="s">
-        <v>0</v>
+        <v>221</v>
       </c>
       <c r="G44" t="s">
-        <v>85</v>
+        <v>222</v>
       </c>
       <c r="H44" t="s">
         <v>3</v>
@@ -2891,22 +2840,22 @@
     </row>
     <row r="45" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A45" t="s">
-        <v>241</v>
+        <v>223</v>
       </c>
       <c r="C45" t="s">
-        <v>78</v>
+        <v>22</v>
       </c>
       <c r="D45" t="s">
-        <v>242</v>
+        <v>219</v>
       </c>
       <c r="E45" t="s">
-        <v>243</v>
+        <v>220</v>
       </c>
       <c r="F45" t="s">
-        <v>0</v>
+        <v>221</v>
       </c>
       <c r="G45" t="s">
-        <v>244</v>
+        <v>222</v>
       </c>
       <c r="H45" t="s">
         <v>3</v>
@@ -2914,22 +2863,22 @@
     </row>
     <row r="46" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A46" t="s">
-        <v>245</v>
+        <v>224</v>
       </c>
       <c r="C46" t="s">
-        <v>78</v>
+        <v>27</v>
       </c>
       <c r="D46" t="s">
-        <v>242</v>
+        <v>225</v>
       </c>
       <c r="E46" t="s">
-        <v>243</v>
+        <v>39</v>
       </c>
       <c r="F46" t="s">
         <v>0</v>
       </c>
       <c r="G46" t="s">
-        <v>244</v>
+        <v>226</v>
       </c>
       <c r="H46" t="s">
         <v>3</v>
@@ -2937,22 +2886,22 @@
     </row>
     <row r="47" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A47" t="s">
-        <v>246</v>
+        <v>227</v>
       </c>
       <c r="C47" t="s">
-        <v>78</v>
+        <v>25</v>
       </c>
       <c r="D47" t="s">
-        <v>242</v>
+        <v>228</v>
       </c>
       <c r="E47" t="s">
-        <v>243</v>
+        <v>229</v>
       </c>
       <c r="F47" t="s">
         <v>0</v>
       </c>
       <c r="G47" t="s">
-        <v>244</v>
+        <v>230</v>
       </c>
       <c r="H47" t="s">
         <v>3</v>
@@ -2960,22 +2909,22 @@
     </row>
     <row r="48" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A48" t="s">
-        <v>247</v>
+        <v>231</v>
       </c>
       <c r="C48" t="s">
-        <v>2</v>
+        <v>22</v>
       </c>
       <c r="D48" t="s">
-        <v>248</v>
+        <v>232</v>
       </c>
       <c r="E48" t="s">
-        <v>98</v>
+        <v>34</v>
       </c>
       <c r="F48" t="s">
         <v>0</v>
       </c>
       <c r="G48" t="s">
-        <v>249</v>
+        <v>233</v>
       </c>
       <c r="H48" t="s">
         <v>3</v>
@@ -2983,22 +2932,22 @@
     </row>
     <row r="49" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A49" t="s">
-        <v>250</v>
+        <v>234</v>
       </c>
       <c r="C49" t="s">
-        <v>41</v>
+        <v>8</v>
       </c>
       <c r="D49" t="s">
-        <v>251</v>
+        <v>235</v>
       </c>
       <c r="E49" t="s">
-        <v>88</v>
+        <v>236</v>
       </c>
       <c r="F49" t="s">
-        <v>89</v>
+        <v>0</v>
       </c>
       <c r="G49" t="s">
-        <v>252</v>
+        <v>237</v>
       </c>
       <c r="H49" t="s">
         <v>3</v>
@@ -3006,22 +2955,22 @@
     </row>
     <row r="50" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A50" t="s">
-        <v>253</v>
+        <v>238</v>
       </c>
       <c r="C50" t="s">
-        <v>34</v>
+        <v>79</v>
       </c>
       <c r="D50" t="s">
-        <v>254</v>
+        <v>239</v>
       </c>
       <c r="E50" t="s">
-        <v>101</v>
+        <v>240</v>
       </c>
       <c r="F50" t="s">
         <v>0</v>
       </c>
       <c r="G50" t="s">
-        <v>102</v>
+        <v>241</v>
       </c>
       <c r="H50" t="s">
         <v>3</v>
@@ -3029,22 +2978,22 @@
     </row>
     <row r="51" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A51" t="s">
-        <v>255</v>
+        <v>242</v>
       </c>
       <c r="C51" t="s">
-        <v>34</v>
+        <v>22</v>
       </c>
       <c r="D51" t="s">
-        <v>254</v>
+        <v>243</v>
       </c>
       <c r="E51" t="s">
-        <v>101</v>
+        <v>46</v>
       </c>
       <c r="F51" t="s">
-        <v>0</v>
+        <v>47</v>
       </c>
       <c r="G51" t="s">
-        <v>102</v>
+        <v>244</v>
       </c>
       <c r="H51" t="s">
         <v>3</v>
@@ -3052,22 +3001,22 @@
     </row>
     <row r="52" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A52" t="s">
-        <v>256</v>
+        <v>245</v>
       </c>
       <c r="C52" t="s">
-        <v>5</v>
+        <v>103</v>
       </c>
       <c r="D52" t="s">
-        <v>257</v>
+        <v>246</v>
       </c>
       <c r="E52" t="s">
-        <v>258</v>
+        <v>247</v>
       </c>
       <c r="F52" t="s">
-        <v>259</v>
+        <v>248</v>
       </c>
       <c r="G52" t="s">
-        <v>103</v>
+        <v>249</v>
       </c>
       <c r="H52" t="s">
         <v>3</v>
@@ -3075,22 +3024,22 @@
     </row>
     <row r="53" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A53" t="s">
-        <v>260</v>
+        <v>250</v>
       </c>
       <c r="C53" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="D53" t="s">
-        <v>257</v>
+        <v>251</v>
       </c>
       <c r="E53" t="s">
-        <v>258</v>
+        <v>252</v>
       </c>
       <c r="F53" t="s">
-        <v>259</v>
+        <v>253</v>
       </c>
       <c r="G53" t="s">
-        <v>103</v>
+        <v>254</v>
       </c>
       <c r="H53" t="s">
         <v>3</v>
@@ -3098,22 +3047,22 @@
     </row>
     <row r="54" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A54" t="s">
-        <v>261</v>
+        <v>255</v>
       </c>
       <c r="C54" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="D54" t="s">
-        <v>257</v>
+        <v>251</v>
       </c>
       <c r="E54" t="s">
-        <v>258</v>
+        <v>252</v>
       </c>
       <c r="F54" t="s">
-        <v>259</v>
+        <v>253</v>
       </c>
       <c r="G54" t="s">
-        <v>103</v>
+        <v>254</v>
       </c>
       <c r="H54" t="s">
         <v>3</v>
@@ -3121,22 +3070,22 @@
     </row>
     <row r="55" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A55" t="s">
-        <v>262</v>
+        <v>256</v>
       </c>
       <c r="C55" t="s">
-        <v>118</v>
+        <v>31</v>
       </c>
       <c r="D55" t="s">
-        <v>263</v>
+        <v>257</v>
       </c>
       <c r="E55" t="s">
-        <v>27</v>
+        <v>69</v>
       </c>
       <c r="F55" t="s">
-        <v>28</v>
+        <v>0</v>
       </c>
       <c r="G55" t="s">
-        <v>264</v>
+        <v>258</v>
       </c>
       <c r="H55" t="s">
         <v>3</v>
@@ -3144,22 +3093,22 @@
     </row>
     <row r="56" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A56" t="s">
-        <v>265</v>
+        <v>259</v>
       </c>
       <c r="C56" t="s">
-        <v>42</v>
+        <v>22</v>
       </c>
       <c r="D56" t="s">
-        <v>266</v>
+        <v>260</v>
       </c>
       <c r="E56" t="s">
-        <v>267</v>
+        <v>37</v>
       </c>
       <c r="F56" t="s">
-        <v>0</v>
+        <v>38</v>
       </c>
       <c r="G56" t="s">
-        <v>268</v>
+        <v>261</v>
       </c>
       <c r="H56" t="s">
         <v>3</v>
@@ -3167,22 +3116,22 @@
     </row>
     <row r="57" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A57" t="s">
-        <v>269</v>
+        <v>262</v>
       </c>
       <c r="C57" t="s">
-        <v>33</v>
+        <v>27</v>
       </c>
       <c r="D57" t="s">
-        <v>270</v>
+        <v>263</v>
       </c>
       <c r="E57" t="s">
-        <v>271</v>
+        <v>264</v>
       </c>
       <c r="F57" t="s">
         <v>0</v>
       </c>
       <c r="G57" t="s">
-        <v>272</v>
+        <v>265</v>
       </c>
       <c r="H57" t="s">
         <v>3</v>
@@ -3190,22 +3139,22 @@
     </row>
     <row r="58" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A58" t="s">
-        <v>273</v>
+        <v>266</v>
       </c>
       <c r="C58" t="s">
-        <v>33</v>
+        <v>9</v>
       </c>
       <c r="D58" t="s">
+        <v>267</v>
+      </c>
+      <c r="E58" t="s">
+        <v>268</v>
+      </c>
+      <c r="F58" t="s">
+        <v>269</v>
+      </c>
+      <c r="G58" t="s">
         <v>270</v>
-      </c>
-      <c r="E58" t="s">
-        <v>271</v>
-      </c>
-      <c r="F58" t="s">
-        <v>0</v>
-      </c>
-      <c r="G58" t="s">
-        <v>272</v>
       </c>
       <c r="H58" t="s">
         <v>3</v>
@@ -3213,22 +3162,22 @@
     </row>
     <row r="59" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A59" t="s">
+        <v>271</v>
+      </c>
+      <c r="C59" t="s">
+        <v>7</v>
+      </c>
+      <c r="D59" t="s">
+        <v>272</v>
+      </c>
+      <c r="E59" t="s">
+        <v>273</v>
+      </c>
+      <c r="F59" t="s">
+        <v>0</v>
+      </c>
+      <c r="G59" t="s">
         <v>274</v>
-      </c>
-      <c r="C59" t="s">
-        <v>5</v>
-      </c>
-      <c r="D59" t="s">
-        <v>275</v>
-      </c>
-      <c r="E59" t="s">
-        <v>16</v>
-      </c>
-      <c r="F59" t="s">
-        <v>17</v>
-      </c>
-      <c r="G59" t="s">
-        <v>276</v>
       </c>
       <c r="H59" t="s">
         <v>3</v>
@@ -3236,22 +3185,22 @@
     </row>
     <row r="60" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A60" t="s">
+        <v>275</v>
+      </c>
+      <c r="C60" t="s">
+        <v>6</v>
+      </c>
+      <c r="D60" t="s">
+        <v>276</v>
+      </c>
+      <c r="E60" t="s">
+        <v>71</v>
+      </c>
+      <c r="F60" t="s">
+        <v>72</v>
+      </c>
+      <c r="G60" t="s">
         <v>277</v>
-      </c>
-      <c r="C60" t="s">
-        <v>41</v>
-      </c>
-      <c r="D60" t="s">
-        <v>278</v>
-      </c>
-      <c r="E60" t="s">
-        <v>60</v>
-      </c>
-      <c r="F60" t="s">
-        <v>0</v>
-      </c>
-      <c r="G60" t="s">
-        <v>279</v>
       </c>
       <c r="H60" t="s">
         <v>3</v>
@@ -3259,22 +3208,22 @@
     </row>
     <row r="61" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A61" t="s">
+        <v>278</v>
+      </c>
+      <c r="C61" t="s">
+        <v>22</v>
+      </c>
+      <c r="D61" t="s">
+        <v>279</v>
+      </c>
+      <c r="E61" t="s">
         <v>280</v>
       </c>
-      <c r="C61" t="s">
-        <v>32</v>
-      </c>
-      <c r="D61" t="s">
+      <c r="F61" t="s">
         <v>281</v>
       </c>
-      <c r="E61" t="s">
-        <v>43</v>
-      </c>
-      <c r="F61" t="s">
-        <v>0</v>
-      </c>
       <c r="G61" t="s">
-        <v>282</v>
+        <v>53</v>
       </c>
       <c r="H61" t="s">
         <v>3</v>
@@ -3282,22 +3231,22 @@
     </row>
     <row r="62" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A62" t="s">
-        <v>283</v>
+        <v>282</v>
       </c>
       <c r="C62" t="s">
-        <v>32</v>
+        <v>22</v>
       </c>
       <c r="D62" t="s">
-        <v>284</v>
+        <v>279</v>
       </c>
       <c r="E62" t="s">
-        <v>285</v>
+        <v>280</v>
       </c>
       <c r="F62" t="s">
-        <v>0</v>
+        <v>281</v>
       </c>
       <c r="G62" t="s">
-        <v>286</v>
+        <v>53</v>
       </c>
       <c r="H62" t="s">
         <v>3</v>
@@ -3305,22 +3254,22 @@
     </row>
     <row r="63" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A63" t="s">
-        <v>287</v>
+        <v>283</v>
       </c>
       <c r="C63" t="s">
-        <v>42</v>
+        <v>9</v>
       </c>
       <c r="D63" t="s">
-        <v>288</v>
+        <v>284</v>
       </c>
       <c r="E63" t="s">
-        <v>289</v>
+        <v>168</v>
       </c>
       <c r="F63" t="s">
         <v>0</v>
       </c>
       <c r="G63" t="s">
-        <v>290</v>
+        <v>285</v>
       </c>
       <c r="H63" t="s">
         <v>3</v>
@@ -3328,22 +3277,22 @@
     </row>
     <row r="64" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A64" t="s">
-        <v>291</v>
+        <v>286</v>
       </c>
       <c r="C64" t="s">
-        <v>42</v>
+        <v>9</v>
       </c>
       <c r="D64" t="s">
-        <v>288</v>
+        <v>284</v>
       </c>
       <c r="E64" t="s">
-        <v>289</v>
+        <v>168</v>
       </c>
       <c r="F64" t="s">
         <v>0</v>
       </c>
       <c r="G64" t="s">
-        <v>290</v>
+        <v>285</v>
       </c>
       <c r="H64" t="s">
         <v>3</v>
@@ -3351,22 +3300,22 @@
     </row>
     <row r="65" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A65" t="s">
-        <v>292</v>
+        <v>287</v>
       </c>
       <c r="C65" t="s">
         <v>9</v>
       </c>
       <c r="D65" t="s">
-        <v>293</v>
+        <v>284</v>
       </c>
       <c r="E65" t="s">
-        <v>294</v>
+        <v>168</v>
       </c>
       <c r="F65" t="s">
         <v>0</v>
       </c>
       <c r="G65" t="s">
-        <v>295</v>
+        <v>285</v>
       </c>
       <c r="H65" t="s">
         <v>3</v>
@@ -3374,22 +3323,22 @@
     </row>
     <row r="66" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A66" t="s">
-        <v>296</v>
+        <v>288</v>
       </c>
       <c r="C66" t="s">
-        <v>32</v>
+        <v>67</v>
       </c>
       <c r="D66" t="s">
-        <v>297</v>
+        <v>289</v>
       </c>
       <c r="E66" t="s">
-        <v>298</v>
+        <v>54</v>
       </c>
       <c r="F66" t="s">
         <v>0</v>
       </c>
       <c r="G66" t="s">
-        <v>299</v>
+        <v>290</v>
       </c>
       <c r="H66" t="s">
         <v>3</v>
@@ -3397,13 +3346,13 @@
     </row>
     <row r="67" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A67" t="s">
-        <v>300</v>
+        <v>291</v>
       </c>
       <c r="C67" t="s">
-        <v>107</v>
+        <v>2</v>
       </c>
       <c r="D67" t="s">
-        <v>301</v>
+        <v>292</v>
       </c>
       <c r="E67" t="s">
         <v>44</v>
@@ -3412,7 +3361,7 @@
         <v>0</v>
       </c>
       <c r="G67" t="s">
-        <v>68</v>
+        <v>293</v>
       </c>
       <c r="H67" t="s">
         <v>3</v>
@@ -3420,22 +3369,22 @@
     </row>
     <row r="68" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A68" t="s">
-        <v>302</v>
+        <v>294</v>
       </c>
       <c r="C68" t="s">
-        <v>107</v>
+        <v>27</v>
       </c>
       <c r="D68" t="s">
-        <v>301</v>
+        <v>295</v>
       </c>
       <c r="E68" t="s">
-        <v>44</v>
+        <v>33</v>
       </c>
       <c r="F68" t="s">
         <v>0</v>
       </c>
       <c r="G68" t="s">
-        <v>68</v>
+        <v>296</v>
       </c>
       <c r="H68" t="s">
         <v>3</v>
@@ -3443,22 +3392,22 @@
     </row>
     <row r="69" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A69" t="s">
-        <v>303</v>
+        <v>297</v>
       </c>
       <c r="C69" t="s">
-        <v>8</v>
+        <v>67</v>
       </c>
       <c r="D69" t="s">
-        <v>304</v>
+        <v>298</v>
       </c>
       <c r="E69" t="s">
-        <v>305</v>
+        <v>299</v>
       </c>
       <c r="F69" t="s">
         <v>0</v>
       </c>
       <c r="G69" t="s">
-        <v>306</v>
+        <v>300</v>
       </c>
       <c r="H69" t="s">
         <v>3</v>
@@ -3466,22 +3415,22 @@
     </row>
     <row r="70" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A70" t="s">
-        <v>307</v>
+        <v>301</v>
       </c>
       <c r="C70" t="s">
-        <v>8</v>
+        <v>154</v>
       </c>
       <c r="D70" t="s">
+        <v>302</v>
+      </c>
+      <c r="E70" t="s">
+        <v>303</v>
+      </c>
+      <c r="F70" t="s">
+        <v>0</v>
+      </c>
+      <c r="G70" t="s">
         <v>304</v>
-      </c>
-      <c r="E70" t="s">
-        <v>305</v>
-      </c>
-      <c r="F70" t="s">
-        <v>0</v>
-      </c>
-      <c r="G70" t="s">
-        <v>306</v>
       </c>
       <c r="H70" t="s">
         <v>3</v>
@@ -3489,22 +3438,22 @@
     </row>
     <row r="71" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A71" t="s">
-        <v>308</v>
+        <v>305</v>
       </c>
       <c r="C71" t="s">
-        <v>118</v>
+        <v>154</v>
       </c>
       <c r="D71" t="s">
-        <v>309</v>
+        <v>302</v>
       </c>
       <c r="E71" t="s">
-        <v>53</v>
+        <v>303</v>
       </c>
       <c r="F71" t="s">
-        <v>54</v>
+        <v>0</v>
       </c>
       <c r="G71" t="s">
-        <v>310</v>
+        <v>304</v>
       </c>
       <c r="H71" t="s">
         <v>3</v>
@@ -3512,22 +3461,22 @@
     </row>
     <row r="72" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A72" t="s">
-        <v>311</v>
+        <v>306</v>
       </c>
       <c r="C72" t="s">
-        <v>9</v>
+        <v>32</v>
       </c>
       <c r="D72" t="s">
-        <v>312</v>
+        <v>307</v>
       </c>
       <c r="E72" t="s">
-        <v>79</v>
+        <v>308</v>
       </c>
       <c r="F72" t="s">
-        <v>0</v>
+        <v>309</v>
       </c>
       <c r="G72" t="s">
-        <v>313</v>
+        <v>310</v>
       </c>
       <c r="H72" t="s">
         <v>3</v>
@@ -3535,22 +3484,22 @@
     </row>
     <row r="73" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A73" t="s">
-        <v>314</v>
+        <v>311</v>
       </c>
       <c r="C73" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="D73" t="s">
-        <v>315</v>
+        <v>312</v>
       </c>
       <c r="E73" t="s">
-        <v>70</v>
+        <v>30</v>
       </c>
       <c r="F73" t="s">
         <v>0</v>
       </c>
       <c r="G73" t="s">
-        <v>316</v>
+        <v>313</v>
       </c>
       <c r="H73" t="s">
         <v>3</v>
@@ -3558,22 +3507,22 @@
     </row>
     <row r="74" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A74" t="s">
-        <v>317</v>
+        <v>314</v>
       </c>
       <c r="C74" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="D74" t="s">
-        <v>318</v>
+        <v>312</v>
       </c>
       <c r="E74" t="s">
-        <v>35</v>
+        <v>30</v>
       </c>
       <c r="F74" t="s">
         <v>0</v>
       </c>
       <c r="G74" t="s">
-        <v>319</v>
+        <v>313</v>
       </c>
       <c r="H74" t="s">
         <v>3</v>
@@ -3581,22 +3530,22 @@
     </row>
     <row r="75" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A75" t="s">
-        <v>320</v>
+        <v>315</v>
       </c>
       <c r="C75" t="s">
-        <v>33</v>
+        <v>22</v>
       </c>
       <c r="D75" t="s">
-        <v>321</v>
+        <v>316</v>
       </c>
       <c r="E75" t="s">
-        <v>51</v>
+        <v>46</v>
       </c>
       <c r="F75" t="s">
-        <v>52</v>
+        <v>47</v>
       </c>
       <c r="G75" t="s">
-        <v>40</v>
+        <v>317</v>
       </c>
       <c r="H75" t="s">
         <v>3</v>
@@ -3604,22 +3553,22 @@
     </row>
     <row r="76" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A76" t="s">
-        <v>322</v>
+        <v>318</v>
       </c>
       <c r="C76" t="s">
-        <v>118</v>
+        <v>5</v>
       </c>
       <c r="D76" t="s">
-        <v>323</v>
+        <v>319</v>
       </c>
       <c r="E76" t="s">
-        <v>53</v>
+        <v>320</v>
       </c>
       <c r="F76" t="s">
-        <v>54</v>
+        <v>0</v>
       </c>
       <c r="G76" t="s">
-        <v>324</v>
+        <v>52</v>
       </c>
       <c r="H76" t="s">
         <v>3</v>
@@ -3627,22 +3576,22 @@
     </row>
     <row r="77" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A77" t="s">
-        <v>325</v>
+        <v>321</v>
       </c>
       <c r="C77" t="s">
-        <v>118</v>
+        <v>26</v>
       </c>
       <c r="D77" t="s">
+        <v>322</v>
+      </c>
+      <c r="E77" t="s">
+        <v>48</v>
+      </c>
+      <c r="F77" t="s">
+        <v>49</v>
+      </c>
+      <c r="G77" t="s">
         <v>323</v>
-      </c>
-      <c r="E77" t="s">
-        <v>53</v>
-      </c>
-      <c r="F77" t="s">
-        <v>54</v>
-      </c>
-      <c r="G77" t="s">
-        <v>324</v>
       </c>
       <c r="H77" t="s">
         <v>3</v>
@@ -3650,22 +3599,22 @@
     </row>
     <row r="78" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A78" t="s">
+        <v>324</v>
+      </c>
+      <c r="C78" t="s">
+        <v>25</v>
+      </c>
+      <c r="D78" t="s">
+        <v>325</v>
+      </c>
+      <c r="E78" t="s">
         <v>326</v>
       </c>
-      <c r="C78" t="s">
-        <v>118</v>
-      </c>
-      <c r="D78" t="s">
-        <v>323</v>
-      </c>
-      <c r="E78" t="s">
-        <v>53</v>
-      </c>
       <c r="F78" t="s">
-        <v>54</v>
+        <v>0</v>
       </c>
       <c r="G78" t="s">
-        <v>324</v>
+        <v>327</v>
       </c>
       <c r="H78" t="s">
         <v>3</v>
@@ -3673,22 +3622,22 @@
     </row>
     <row r="79" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A79" t="s">
-        <v>327</v>
+        <v>328</v>
       </c>
       <c r="C79" t="s">
-        <v>42</v>
+        <v>5</v>
       </c>
       <c r="D79" t="s">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c r="E79" t="s">
-        <v>30</v>
+        <v>11</v>
       </c>
       <c r="F79" t="s">
-        <v>31</v>
+        <v>12</v>
       </c>
       <c r="G79" t="s">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="H79" t="s">
         <v>3</v>
@@ -3696,19 +3645,19 @@
     </row>
     <row r="80" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A80" t="s">
-        <v>330</v>
+        <v>331</v>
       </c>
       <c r="C80" t="s">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="D80" t="s">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="E80" t="s">
-        <v>332</v>
+        <v>60</v>
       </c>
       <c r="F80" t="s">
-        <v>0</v>
+        <v>61</v>
       </c>
       <c r="G80" t="s">
         <v>333</v>
@@ -3722,19 +3671,19 @@
         <v>334</v>
       </c>
       <c r="C81" t="s">
-        <v>2</v>
+        <v>27</v>
       </c>
       <c r="D81" t="s">
-        <v>331</v>
+        <v>335</v>
       </c>
       <c r="E81" t="s">
-        <v>332</v>
+        <v>264</v>
       </c>
       <c r="F81" t="s">
         <v>0</v>
       </c>
       <c r="G81" t="s">
-        <v>333</v>
+        <v>336</v>
       </c>
       <c r="H81" t="s">
         <v>3</v>
@@ -3742,22 +3691,22 @@
     </row>
     <row r="82" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A82" t="s">
-        <v>335</v>
+        <v>337</v>
       </c>
       <c r="C82" t="s">
-        <v>6</v>
+        <v>67</v>
       </c>
       <c r="D82" t="s">
-        <v>336</v>
+        <v>338</v>
       </c>
       <c r="E82" t="s">
-        <v>337</v>
+        <v>339</v>
       </c>
       <c r="F82" t="s">
-        <v>0</v>
+        <v>340</v>
       </c>
       <c r="G82" t="s">
-        <v>338</v>
+        <v>341</v>
       </c>
       <c r="H82" t="s">
         <v>3</v>
@@ -3765,22 +3714,22 @@
     </row>
     <row r="83" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A83" t="s">
-        <v>339</v>
+        <v>342</v>
       </c>
       <c r="C83" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="D83" t="s">
-        <v>340</v>
+        <v>343</v>
       </c>
       <c r="E83" t="s">
-        <v>341</v>
+        <v>344</v>
       </c>
       <c r="F83" t="s">
-        <v>0</v>
+        <v>345</v>
       </c>
       <c r="G83" t="s">
-        <v>342</v>
+        <v>346</v>
       </c>
       <c r="H83" t="s">
         <v>3</v>
@@ -3788,22 +3737,22 @@
     </row>
     <row r="84" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A84" t="s">
-        <v>343</v>
+        <v>347</v>
       </c>
       <c r="C84" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="D84" t="s">
-        <v>344</v>
+        <v>348</v>
       </c>
       <c r="E84" t="s">
-        <v>345</v>
+        <v>273</v>
       </c>
       <c r="F84" t="s">
         <v>0</v>
       </c>
       <c r="G84" t="s">
-        <v>346</v>
+        <v>349</v>
       </c>
       <c r="H84" t="s">
         <v>3</v>
@@ -3811,22 +3760,22 @@
     </row>
     <row r="85" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A85" t="s">
-        <v>347</v>
+        <v>350</v>
       </c>
       <c r="C85" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="D85" t="s">
-        <v>344</v>
+        <v>348</v>
       </c>
       <c r="E85" t="s">
-        <v>345</v>
+        <v>273</v>
       </c>
       <c r="F85" t="s">
         <v>0</v>
       </c>
       <c r="G85" t="s">
-        <v>346</v>
+        <v>349</v>
       </c>
       <c r="H85" t="s">
         <v>3</v>
@@ -3834,22 +3783,22 @@
     </row>
     <row r="86" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A86" t="s">
+        <v>351</v>
+      </c>
+      <c r="C86" t="s">
+        <v>7</v>
+      </c>
+      <c r="D86" t="s">
         <v>348</v>
       </c>
-      <c r="C86" t="s">
-        <v>5</v>
-      </c>
-      <c r="D86" t="s">
+      <c r="E86" t="s">
+        <v>273</v>
+      </c>
+      <c r="F86" t="s">
+        <v>0</v>
+      </c>
+      <c r="G86" t="s">
         <v>349</v>
-      </c>
-      <c r="E86" t="s">
-        <v>65</v>
-      </c>
-      <c r="F86" t="s">
-        <v>66</v>
-      </c>
-      <c r="G86" t="s">
-        <v>350</v>
       </c>
       <c r="H86" t="s">
         <v>3</v>
@@ -3857,22 +3806,22 @@
     </row>
     <row r="87" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A87" t="s">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="C87" t="s">
-        <v>33</v>
+        <v>27</v>
       </c>
       <c r="D87" t="s">
-        <v>352</v>
+        <v>353</v>
       </c>
       <c r="E87" t="s">
-        <v>271</v>
+        <v>73</v>
       </c>
       <c r="F87" t="s">
         <v>0</v>
       </c>
       <c r="G87" t="s">
-        <v>353</v>
+        <v>354</v>
       </c>
       <c r="H87" t="s">
         <v>3</v>
@@ -3880,22 +3829,22 @@
     </row>
     <row r="88" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A88" t="s">
-        <v>354</v>
+        <v>355</v>
       </c>
       <c r="C88" t="s">
-        <v>7</v>
+        <v>154</v>
       </c>
       <c r="D88" t="s">
-        <v>355</v>
+        <v>356</v>
       </c>
       <c r="E88" t="s">
-        <v>356</v>
+        <v>357</v>
       </c>
       <c r="F88" t="s">
         <v>0</v>
       </c>
       <c r="G88" t="s">
-        <v>357</v>
+        <v>358</v>
       </c>
       <c r="H88" t="s">
         <v>3</v>
@@ -3903,22 +3852,22 @@
     </row>
     <row r="89" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A89" t="s">
+        <v>359</v>
+      </c>
+      <c r="C89" t="s">
+        <v>154</v>
+      </c>
+      <c r="D89" t="s">
+        <v>356</v>
+      </c>
+      <c r="E89" t="s">
+        <v>357</v>
+      </c>
+      <c r="F89" t="s">
+        <v>0</v>
+      </c>
+      <c r="G89" t="s">
         <v>358</v>
-      </c>
-      <c r="C89" t="s">
-        <v>41</v>
-      </c>
-      <c r="D89" t="s">
-        <v>359</v>
-      </c>
-      <c r="E89" t="s">
-        <v>108</v>
-      </c>
-      <c r="F89" t="s">
-        <v>109</v>
-      </c>
-      <c r="G89" t="s">
-        <v>360</v>
       </c>
       <c r="H89" t="s">
         <v>3</v>
@@ -3926,22 +3875,22 @@
     </row>
     <row r="90" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A90" t="s">
+        <v>360</v>
+      </c>
+      <c r="C90" t="s">
+        <v>32</v>
+      </c>
+      <c r="D90" t="s">
         <v>361</v>
       </c>
-      <c r="C90" t="s">
-        <v>78</v>
-      </c>
-      <c r="D90" t="s">
+      <c r="E90" t="s">
         <v>362</v>
       </c>
-      <c r="E90" t="s">
-        <v>243</v>
-      </c>
       <c r="F90" t="s">
         <v>0</v>
       </c>
       <c r="G90" t="s">
-        <v>363</v>
+        <v>222</v>
       </c>
       <c r="H90" t="s">
         <v>3</v>
@@ -3949,16 +3898,16 @@
     </row>
     <row r="91" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A91" t="s">
+        <v>363</v>
+      </c>
+      <c r="C91" t="s">
+        <v>43</v>
+      </c>
+      <c r="D91" t="s">
         <v>364</v>
       </c>
-      <c r="C91" t="s">
-        <v>42</v>
-      </c>
-      <c r="D91" t="s">
+      <c r="E91" t="s">
         <v>365</v>
-      </c>
-      <c r="E91" t="s">
-        <v>73</v>
       </c>
       <c r="F91" t="s">
         <v>0</v>
@@ -3975,19 +3924,19 @@
         <v>367</v>
       </c>
       <c r="C92" t="s">
-        <v>42</v>
+        <v>59</v>
       </c>
       <c r="D92" t="s">
-        <v>365</v>
+        <v>368</v>
       </c>
       <c r="E92" t="s">
-        <v>73</v>
+        <v>369</v>
       </c>
       <c r="F92" t="s">
         <v>0</v>
       </c>
       <c r="G92" t="s">
-        <v>366</v>
+        <v>370</v>
       </c>
       <c r="H92" t="s">
         <v>3</v>
@@ -3995,22 +3944,22 @@
     </row>
     <row r="93" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A93" t="s">
-        <v>368</v>
+        <v>371</v>
       </c>
       <c r="C93" t="s">
-        <v>42</v>
+        <v>67</v>
       </c>
       <c r="D93" t="s">
-        <v>365</v>
+        <v>372</v>
       </c>
       <c r="E93" t="s">
-        <v>73</v>
+        <v>373</v>
       </c>
       <c r="F93" t="s">
-        <v>0</v>
+        <v>374</v>
       </c>
       <c r="G93" t="s">
-        <v>366</v>
+        <v>375</v>
       </c>
       <c r="H93" t="s">
         <v>3</v>
@@ -4018,22 +3967,22 @@
     </row>
     <row r="94" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A94" t="s">
-        <v>369</v>
+        <v>376</v>
       </c>
       <c r="C94" t="s">
-        <v>29</v>
+        <v>67</v>
       </c>
       <c r="D94" t="s">
-        <v>370</v>
+        <v>372</v>
       </c>
       <c r="E94" t="s">
-        <v>371</v>
+        <v>373</v>
       </c>
       <c r="F94" t="s">
-        <v>0</v>
+        <v>374</v>
       </c>
       <c r="G94" t="s">
-        <v>372</v>
+        <v>375</v>
       </c>
       <c r="H94" t="s">
         <v>3</v>
@@ -4041,22 +3990,22 @@
     </row>
     <row r="95" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A95" t="s">
-        <v>373</v>
+        <v>377</v>
       </c>
       <c r="C95" t="s">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="D95" t="s">
-        <v>374</v>
+        <v>378</v>
       </c>
       <c r="E95" t="s">
-        <v>375</v>
+        <v>379</v>
       </c>
       <c r="F95" t="s">
-        <v>0</v>
+        <v>380</v>
       </c>
       <c r="G95" t="s">
-        <v>69</v>
+        <v>381</v>
       </c>
       <c r="H95" t="s">
         <v>3</v>
@@ -4064,22 +4013,22 @@
     </row>
     <row r="96" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A96" t="s">
-        <v>376</v>
+        <v>382</v>
       </c>
       <c r="C96" t="s">
-        <v>8</v>
+        <v>67</v>
       </c>
       <c r="D96" t="s">
-        <v>377</v>
+        <v>383</v>
       </c>
       <c r="E96" t="s">
-        <v>48</v>
+        <v>62</v>
       </c>
       <c r="F96" t="s">
         <v>0</v>
       </c>
       <c r="G96" t="s">
-        <v>49</v>
+        <v>384</v>
       </c>
       <c r="H96" t="s">
         <v>3</v>
@@ -4087,22 +4036,22 @@
     </row>
     <row r="97" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A97" t="s">
-        <v>378</v>
+        <v>385</v>
       </c>
       <c r="C97" t="s">
-        <v>7</v>
+        <v>79</v>
       </c>
       <c r="D97" t="s">
-        <v>379</v>
+        <v>386</v>
       </c>
       <c r="E97" t="s">
-        <v>90</v>
+        <v>387</v>
       </c>
       <c r="F97" t="s">
         <v>0</v>
       </c>
       <c r="G97" t="s">
-        <v>380</v>
+        <v>388</v>
       </c>
       <c r="H97" t="s">
         <v>3</v>
@@ -4110,22 +4059,22 @@
     </row>
     <row r="98" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A98" t="s">
-        <v>381</v>
+        <v>389</v>
       </c>
       <c r="C98" t="s">
-        <v>382</v>
+        <v>8</v>
       </c>
       <c r="D98" t="s">
-        <v>383</v>
+        <v>390</v>
       </c>
       <c r="E98" t="s">
-        <v>384</v>
+        <v>41</v>
       </c>
       <c r="F98" t="s">
-        <v>385</v>
+        <v>0</v>
       </c>
       <c r="G98" t="s">
-        <v>104</v>
+        <v>391</v>
       </c>
       <c r="H98" t="s">
         <v>3</v>
@@ -4133,22 +4082,22 @@
     </row>
     <row r="99" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A99" t="s">
-        <v>386</v>
+        <v>392</v>
       </c>
       <c r="C99" t="s">
-        <v>6</v>
+        <v>31</v>
       </c>
       <c r="D99" t="s">
-        <v>387</v>
+        <v>393</v>
       </c>
       <c r="E99" t="s">
-        <v>388</v>
+        <v>394</v>
       </c>
       <c r="F99" t="s">
         <v>0</v>
       </c>
       <c r="G99" t="s">
-        <v>389</v>
+        <v>395</v>
       </c>
       <c r="H99" t="s">
         <v>3</v>
@@ -4156,22 +4105,22 @@
     </row>
     <row r="100" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A100" t="s">
-        <v>390</v>
+        <v>396</v>
       </c>
       <c r="C100" t="s">
-        <v>6</v>
+        <v>31</v>
       </c>
       <c r="D100" t="s">
-        <v>387</v>
+        <v>397</v>
       </c>
       <c r="E100" t="s">
-        <v>388</v>
+        <v>42</v>
       </c>
       <c r="F100" t="s">
         <v>0</v>
       </c>
       <c r="G100" t="s">
-        <v>389</v>
+        <v>398</v>
       </c>
       <c r="H100" t="s">
         <v>3</v>
@@ -4179,22 +4128,22 @@
     </row>
     <row r="101" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A101" t="s">
-        <v>391</v>
+        <v>399</v>
       </c>
       <c r="C101" t="s">
-        <v>71</v>
+        <v>25</v>
       </c>
       <c r="D101" t="s">
-        <v>392</v>
+        <v>400</v>
       </c>
       <c r="E101" t="s">
-        <v>81</v>
+        <v>66</v>
       </c>
       <c r="F101" t="s">
         <v>0</v>
       </c>
       <c r="G101" t="s">
-        <v>393</v>
+        <v>401</v>
       </c>
       <c r="H101" t="s">
         <v>3</v>
@@ -4202,22 +4151,22 @@
     </row>
     <row r="102" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A102" t="s">
-        <v>394</v>
+        <v>402</v>
       </c>
       <c r="C102" t="s">
-        <v>78</v>
+        <v>25</v>
       </c>
       <c r="D102" t="s">
-        <v>395</v>
+        <v>403</v>
       </c>
       <c r="E102" t="s">
-        <v>45</v>
+        <v>66</v>
       </c>
       <c r="F102" t="s">
         <v>0</v>
       </c>
       <c r="G102" t="s">
-        <v>396</v>
+        <v>404</v>
       </c>
       <c r="H102" t="s">
         <v>3</v>
@@ -4225,22 +4174,22 @@
     </row>
     <row r="103" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A103" t="s">
-        <v>397</v>
+        <v>405</v>
       </c>
       <c r="C103" t="s">
-        <v>7</v>
+        <v>25</v>
       </c>
       <c r="D103" t="s">
-        <v>398</v>
+        <v>403</v>
       </c>
       <c r="E103" t="s">
-        <v>399</v>
+        <v>66</v>
       </c>
       <c r="F103" t="s">
         <v>0</v>
       </c>
       <c r="G103" t="s">
-        <v>400</v>
+        <v>404</v>
       </c>
       <c r="H103" t="s">
         <v>3</v>
@@ -4248,22 +4197,22 @@
     </row>
     <row r="104" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A104" t="s">
-        <v>401</v>
+        <v>406</v>
       </c>
       <c r="C104" t="s">
-        <v>33</v>
+        <v>103</v>
       </c>
       <c r="D104" t="s">
-        <v>402</v>
+        <v>407</v>
       </c>
       <c r="E104" t="s">
-        <v>403</v>
+        <v>408</v>
       </c>
       <c r="F104" t="s">
-        <v>0</v>
+        <v>409</v>
       </c>
       <c r="G104" t="s">
-        <v>404</v>
+        <v>410</v>
       </c>
       <c r="H104" t="s">
         <v>3</v>
@@ -4271,22 +4220,22 @@
     </row>
     <row r="105" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A105" t="s">
-        <v>405</v>
+        <v>411</v>
       </c>
       <c r="C105" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="D105" t="s">
-        <v>406</v>
+        <v>412</v>
       </c>
       <c r="E105" t="s">
-        <v>407</v>
+        <v>41</v>
       </c>
       <c r="F105" t="s">
         <v>0</v>
       </c>
       <c r="G105" t="s">
-        <v>408</v>
+        <v>413</v>
       </c>
       <c r="H105" t="s">
         <v>3</v>
@@ -4294,22 +4243,22 @@
     </row>
     <row r="106" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A106" t="s">
-        <v>409</v>
+        <v>414</v>
       </c>
       <c r="C106" t="s">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="D106" t="s">
-        <v>410</v>
+        <v>415</v>
       </c>
       <c r="E106" t="s">
-        <v>76</v>
+        <v>41</v>
       </c>
       <c r="F106" t="s">
         <v>0</v>
       </c>
       <c r="G106" t="s">
-        <v>411</v>
+        <v>416</v>
       </c>
       <c r="H106" t="s">
         <v>3</v>
@@ -4317,22 +4266,22 @@
     </row>
     <row r="107" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A107" t="s">
-        <v>412</v>
+        <v>417</v>
       </c>
       <c r="C107" t="s">
-        <v>382</v>
+        <v>2</v>
       </c>
       <c r="D107" t="s">
-        <v>413</v>
+        <v>418</v>
       </c>
       <c r="E107" t="s">
-        <v>384</v>
+        <v>419</v>
       </c>
       <c r="F107" t="s">
-        <v>385</v>
+        <v>420</v>
       </c>
       <c r="G107" t="s">
-        <v>414</v>
+        <v>421</v>
       </c>
       <c r="H107" t="s">
         <v>3</v>
@@ -4340,22 +4289,22 @@
     </row>
     <row r="108" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A108" t="s">
-        <v>415</v>
+        <v>422</v>
       </c>
       <c r="C108" t="s">
-        <v>6</v>
+        <v>26</v>
       </c>
       <c r="D108" t="s">
-        <v>416</v>
+        <v>423</v>
       </c>
       <c r="E108" t="s">
-        <v>76</v>
+        <v>424</v>
       </c>
       <c r="F108" t="s">
-        <v>0</v>
+        <v>425</v>
       </c>
       <c r="G108" t="s">
-        <v>417</v>
+        <v>426</v>
       </c>
       <c r="H108" t="s">
         <v>3</v>
@@ -4363,22 +4312,22 @@
     </row>
     <row r="109" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A109" t="s">
-        <v>418</v>
+        <v>427</v>
       </c>
       <c r="C109" t="s">
-        <v>107</v>
+        <v>25</v>
       </c>
       <c r="D109" t="s">
-        <v>419</v>
+        <v>428</v>
       </c>
       <c r="E109" t="s">
-        <v>420</v>
+        <v>66</v>
       </c>
       <c r="F109" t="s">
         <v>0</v>
       </c>
       <c r="G109" t="s">
-        <v>421</v>
+        <v>429</v>
       </c>
       <c r="H109" t="s">
         <v>3</v>
@@ -4386,22 +4335,22 @@
     </row>
     <row r="110" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A110" t="s">
-        <v>422</v>
+        <v>430</v>
       </c>
       <c r="C110" t="s">
-        <v>107</v>
+        <v>103</v>
       </c>
       <c r="D110" t="s">
-        <v>423</v>
+        <v>431</v>
       </c>
       <c r="E110" t="s">
-        <v>424</v>
+        <v>132</v>
       </c>
       <c r="F110" t="s">
-        <v>425</v>
+        <v>133</v>
       </c>
       <c r="G110" t="s">
-        <v>426</v>
+        <v>432</v>
       </c>
       <c r="H110" t="s">
         <v>3</v>
@@ -4409,22 +4358,22 @@
     </row>
     <row r="111" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A111" t="s">
-        <v>427</v>
+        <v>433</v>
       </c>
       <c r="C111" t="s">
-        <v>6</v>
+        <v>27</v>
       </c>
       <c r="D111" t="s">
-        <v>428</v>
+        <v>434</v>
       </c>
       <c r="E111" t="s">
-        <v>429</v>
+        <v>264</v>
       </c>
       <c r="F111" t="s">
         <v>0</v>
       </c>
       <c r="G111" t="s">
-        <v>430</v>
+        <v>435</v>
       </c>
       <c r="H111" t="s">
         <v>3</v>
@@ -4432,114 +4381,114 @@
     </row>
     <row r="112" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A112" t="s">
-        <v>431</v>
+        <v>436</v>
       </c>
       <c r="C112" t="s">
-        <v>32</v>
+        <v>26</v>
       </c>
       <c r="D112" t="s">
-        <v>432</v>
+        <v>437</v>
       </c>
       <c r="E112" t="s">
-        <v>38</v>
+        <v>438</v>
       </c>
       <c r="F112" t="s">
-        <v>0</v>
+        <v>439</v>
       </c>
       <c r="G112" t="s">
-        <v>433</v>
+        <v>440</v>
       </c>
       <c r="H112" t="s">
-        <v>434</v>
+        <v>3</v>
       </c>
     </row>
     <row r="113" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A113" t="s">
-        <v>435</v>
+        <v>441</v>
       </c>
       <c r="C113" t="s">
-        <v>32</v>
+        <v>26</v>
       </c>
       <c r="D113" t="s">
-        <v>432</v>
+        <v>442</v>
       </c>
       <c r="E113" t="s">
-        <v>38</v>
+        <v>438</v>
       </c>
       <c r="F113" t="s">
-        <v>0</v>
+        <v>439</v>
       </c>
       <c r="G113" t="s">
-        <v>433</v>
+        <v>443</v>
       </c>
       <c r="H113" t="s">
-        <v>434</v>
+        <v>3</v>
       </c>
     </row>
     <row r="114" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A114" t="s">
-        <v>436</v>
+        <v>444</v>
       </c>
       <c r="C114" t="s">
-        <v>42</v>
+        <v>9</v>
       </c>
       <c r="D114" t="s">
-        <v>437</v>
+        <v>445</v>
       </c>
       <c r="E114" t="s">
-        <v>438</v>
+        <v>446</v>
       </c>
       <c r="F114" t="s">
-        <v>0</v>
+        <v>447</v>
       </c>
       <c r="G114" t="s">
-        <v>439</v>
+        <v>448</v>
       </c>
       <c r="H114" t="s">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="115" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A115" t="s">
-        <v>440</v>
+        <v>449</v>
       </c>
       <c r="C115" t="s">
-        <v>41</v>
+        <v>9</v>
       </c>
       <c r="D115" t="s">
-        <v>441</v>
+        <v>445</v>
       </c>
       <c r="E115" t="s">
-        <v>442</v>
+        <v>446</v>
       </c>
       <c r="F115" t="s">
-        <v>443</v>
+        <v>447</v>
       </c>
       <c r="G115" t="s">
-        <v>252</v>
+        <v>448</v>
       </c>
       <c r="H115" t="s">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="116" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A116" t="s">
-        <v>444</v>
+        <v>450</v>
       </c>
       <c r="C116" t="s">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="D116" t="s">
         <v>445</v>
       </c>
       <c r="E116" t="s">
-        <v>14</v>
+        <v>446</v>
       </c>
       <c r="F116" t="s">
-        <v>15</v>
+        <v>447</v>
       </c>
       <c r="G116" t="s">
-        <v>446</v>
+        <v>448</v>
       </c>
       <c r="H116" t="s">
         <v>4</v>
@@ -4547,22 +4496,22 @@
     </row>
     <row r="117" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A117" t="s">
-        <v>447</v>
+        <v>451</v>
       </c>
       <c r="C117" t="s">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="D117" t="s">
         <v>445</v>
       </c>
       <c r="E117" t="s">
-        <v>14</v>
+        <v>446</v>
       </c>
       <c r="F117" t="s">
-        <v>15</v>
+        <v>447</v>
       </c>
       <c r="G117" t="s">
-        <v>446</v>
+        <v>448</v>
       </c>
       <c r="H117" t="s">
         <v>4</v>
@@ -4570,22 +4519,22 @@
     </row>
     <row r="118" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A118" t="s">
+        <v>452</v>
+      </c>
+      <c r="C118" t="s">
+        <v>9</v>
+      </c>
+      <c r="D118" t="s">
+        <v>445</v>
+      </c>
+      <c r="E118" t="s">
+        <v>446</v>
+      </c>
+      <c r="F118" t="s">
+        <v>447</v>
+      </c>
+      <c r="G118" t="s">
         <v>448</v>
-      </c>
-      <c r="C118" t="s">
-        <v>41</v>
-      </c>
-      <c r="D118" t="s">
-        <v>449</v>
-      </c>
-      <c r="E118" t="s">
-        <v>450</v>
-      </c>
-      <c r="F118" t="s">
-        <v>0</v>
-      </c>
-      <c r="G118" t="s">
-        <v>451</v>
       </c>
       <c r="H118" t="s">
         <v>4</v>
@@ -4593,22 +4542,22 @@
     </row>
     <row r="119" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A119" t="s">
-        <v>452</v>
+        <v>453</v>
       </c>
       <c r="C119" t="s">
-        <v>33</v>
+        <v>27</v>
       </c>
       <c r="D119" t="s">
-        <v>453</v>
+        <v>454</v>
       </c>
       <c r="E119" t="s">
-        <v>403</v>
+        <v>73</v>
       </c>
       <c r="F119" t="s">
         <v>0</v>
       </c>
       <c r="G119" t="s">
-        <v>454</v>
+        <v>455</v>
       </c>
       <c r="H119" t="s">
         <v>4</v>
@@ -4616,22 +4565,22 @@
     </row>
     <row r="120" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A120" t="s">
-        <v>455</v>
+        <v>456</v>
       </c>
       <c r="C120" t="s">
-        <v>33</v>
+        <v>2</v>
       </c>
       <c r="D120" t="s">
-        <v>456</v>
+        <v>457</v>
       </c>
       <c r="E120" t="s">
-        <v>271</v>
+        <v>44</v>
       </c>
       <c r="F120" t="s">
         <v>0</v>
       </c>
       <c r="G120" t="s">
-        <v>457</v>
+        <v>56</v>
       </c>
       <c r="H120" t="s">
         <v>4</v>
@@ -4642,19 +4591,19 @@
         <v>458</v>
       </c>
       <c r="C121" t="s">
-        <v>33</v>
+        <v>2</v>
       </c>
       <c r="D121" t="s">
-        <v>456</v>
+        <v>459</v>
       </c>
       <c r="E121" t="s">
-        <v>271</v>
+        <v>419</v>
       </c>
       <c r="F121" t="s">
-        <v>0</v>
+        <v>420</v>
       </c>
       <c r="G121" t="s">
-        <v>457</v>
+        <v>50</v>
       </c>
       <c r="H121" t="s">
         <v>4</v>
@@ -4662,22 +4611,22 @@
     </row>
     <row r="122" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A122" t="s">
+        <v>460</v>
+      </c>
+      <c r="C122" t="s">
+        <v>2</v>
+      </c>
+      <c r="D122" t="s">
         <v>459</v>
       </c>
-      <c r="C122" t="s">
-        <v>41</v>
-      </c>
-      <c r="D122" t="s">
-        <v>460</v>
-      </c>
       <c r="E122" t="s">
-        <v>126</v>
+        <v>419</v>
       </c>
       <c r="F122" t="s">
-        <v>0</v>
+        <v>420</v>
       </c>
       <c r="G122" t="s">
-        <v>461</v>
+        <v>50</v>
       </c>
       <c r="H122" t="s">
         <v>4</v>
@@ -4685,22 +4634,22 @@
     </row>
     <row r="123" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A123" t="s">
-        <v>462</v>
+        <v>461</v>
       </c>
       <c r="C123" t="s">
-        <v>382</v>
+        <v>2</v>
       </c>
       <c r="D123" t="s">
-        <v>463</v>
+        <v>459</v>
       </c>
       <c r="E123" t="s">
-        <v>464</v>
+        <v>419</v>
       </c>
       <c r="F123" t="s">
-        <v>465</v>
+        <v>420</v>
       </c>
       <c r="G123" t="s">
-        <v>466</v>
+        <v>50</v>
       </c>
       <c r="H123" t="s">
         <v>4</v>
@@ -4708,22 +4657,22 @@
     </row>
     <row r="124" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A124" t="s">
-        <v>467</v>
+        <v>462</v>
       </c>
       <c r="C124" t="s">
-        <v>382</v>
+        <v>2</v>
       </c>
       <c r="D124" t="s">
-        <v>463</v>
+        <v>459</v>
       </c>
       <c r="E124" t="s">
-        <v>464</v>
+        <v>419</v>
       </c>
       <c r="F124" t="s">
-        <v>465</v>
+        <v>420</v>
       </c>
       <c r="G124" t="s">
-        <v>466</v>
+        <v>50</v>
       </c>
       <c r="H124" t="s">
         <v>4</v>
@@ -4731,19 +4680,19 @@
     </row>
     <row r="125" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A125" t="s">
-        <v>468</v>
+        <v>463</v>
       </c>
       <c r="C125" t="s">
-        <v>382</v>
+        <v>79</v>
       </c>
       <c r="D125" t="s">
-        <v>463</v>
+        <v>464</v>
       </c>
       <c r="E125" t="s">
-        <v>464</v>
+        <v>465</v>
       </c>
       <c r="F125" t="s">
-        <v>465</v>
+        <v>0</v>
       </c>
       <c r="G125" t="s">
         <v>466</v>
@@ -4754,22 +4703,22 @@
     </row>
     <row r="126" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A126" t="s">
+        <v>467</v>
+      </c>
+      <c r="C126" t="s">
+        <v>5</v>
+      </c>
+      <c r="D126" t="s">
+        <v>468</v>
+      </c>
+      <c r="E126" t="s">
+        <v>13</v>
+      </c>
+      <c r="F126" t="s">
+        <v>14</v>
+      </c>
+      <c r="G126" t="s">
         <v>469</v>
-      </c>
-      <c r="C126" t="s">
-        <v>382</v>
-      </c>
-      <c r="D126" t="s">
-        <v>470</v>
-      </c>
-      <c r="E126" t="s">
-        <v>471</v>
-      </c>
-      <c r="F126" t="s">
-        <v>0</v>
-      </c>
-      <c r="G126" t="s">
-        <v>472</v>
       </c>
       <c r="H126" t="s">
         <v>4</v>
@@ -4777,22 +4726,22 @@
     </row>
     <row r="127" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A127" t="s">
+        <v>470</v>
+      </c>
+      <c r="C127" t="s">
+        <v>8</v>
+      </c>
+      <c r="D127" t="s">
+        <v>471</v>
+      </c>
+      <c r="E127" t="s">
+        <v>472</v>
+      </c>
+      <c r="F127" t="s">
+        <v>0</v>
+      </c>
+      <c r="G127" t="s">
         <v>473</v>
-      </c>
-      <c r="C127" t="s">
-        <v>382</v>
-      </c>
-      <c r="D127" t="s">
-        <v>474</v>
-      </c>
-      <c r="E127" t="s">
-        <v>384</v>
-      </c>
-      <c r="F127" t="s">
-        <v>385</v>
-      </c>
-      <c r="G127" t="s">
-        <v>475</v>
       </c>
       <c r="H127" t="s">
         <v>4</v>
@@ -4800,22 +4749,22 @@
     </row>
     <row r="128" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A128" t="s">
+        <v>474</v>
+      </c>
+      <c r="C128" t="s">
+        <v>9</v>
+      </c>
+      <c r="D128" t="s">
+        <v>475</v>
+      </c>
+      <c r="E128" t="s">
+        <v>446</v>
+      </c>
+      <c r="F128" t="s">
+        <v>447</v>
+      </c>
+      <c r="G128" t="s">
         <v>476</v>
-      </c>
-      <c r="C128" t="s">
-        <v>382</v>
-      </c>
-      <c r="D128" t="s">
-        <v>474</v>
-      </c>
-      <c r="E128" t="s">
-        <v>384</v>
-      </c>
-      <c r="F128" t="s">
-        <v>385</v>
-      </c>
-      <c r="G128" t="s">
-        <v>475</v>
       </c>
       <c r="H128" t="s">
         <v>4</v>
@@ -4826,91 +4775,91 @@
         <v>477</v>
       </c>
       <c r="C129" t="s">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="D129" t="s">
         <v>478</v>
       </c>
       <c r="E129" t="s">
-        <v>16</v>
+        <v>479</v>
       </c>
       <c r="F129" t="s">
-        <v>17</v>
+        <v>0</v>
       </c>
       <c r="G129" t="s">
-        <v>479</v>
+        <v>480</v>
       </c>
       <c r="H129" t="s">
-        <v>4</v>
+        <v>77</v>
       </c>
     </row>
     <row r="130" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A130" t="s">
+        <v>481</v>
+      </c>
+      <c r="C130" t="s">
+        <v>8</v>
+      </c>
+      <c r="D130" t="s">
+        <v>478</v>
+      </c>
+      <c r="E130" t="s">
+        <v>479</v>
+      </c>
+      <c r="F130" t="s">
+        <v>0</v>
+      </c>
+      <c r="G130" t="s">
         <v>480</v>
       </c>
-      <c r="C130" t="s">
-        <v>2</v>
-      </c>
-      <c r="D130" t="s">
-        <v>481</v>
-      </c>
-      <c r="E130" t="s">
-        <v>36</v>
-      </c>
-      <c r="F130" t="s">
-        <v>37</v>
-      </c>
-      <c r="G130" t="s">
-        <v>482</v>
-      </c>
       <c r="H130" t="s">
-        <v>4</v>
+        <v>77</v>
       </c>
     </row>
     <row r="131" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A131" t="s">
-        <v>483</v>
+        <v>482</v>
       </c>
       <c r="C131" t="s">
-        <v>29</v>
+        <v>8</v>
       </c>
       <c r="D131" t="s">
-        <v>484</v>
+        <v>478</v>
       </c>
       <c r="E131" t="s">
-        <v>99</v>
+        <v>479</v>
       </c>
       <c r="F131" t="s">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="G131" t="s">
-        <v>50</v>
+        <v>480</v>
       </c>
       <c r="H131" t="s">
-        <v>4</v>
+        <v>77</v>
       </c>
     </row>
     <row r="132" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A132" t="s">
-        <v>485</v>
+        <v>483</v>
       </c>
       <c r="C132" t="s">
-        <v>29</v>
+        <v>79</v>
       </c>
       <c r="D132" t="s">
         <v>484</v>
       </c>
       <c r="E132" t="s">
-        <v>99</v>
+        <v>63</v>
       </c>
       <c r="F132" t="s">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="G132" t="s">
-        <v>50</v>
+        <v>485</v>
       </c>
       <c r="H132" t="s">
-        <v>4</v>
+        <v>70</v>
       </c>
     </row>
     <row r="133" spans="1:8" x14ac:dyDescent="0.3">
@@ -4918,137 +4867,68 @@
         <v>486</v>
       </c>
       <c r="C133" t="s">
-        <v>71</v>
+        <v>79</v>
       </c>
       <c r="D133" t="s">
-        <v>487</v>
+        <v>484</v>
       </c>
       <c r="E133" t="s">
-        <v>488</v>
+        <v>63</v>
       </c>
       <c r="F133" t="s">
-        <v>489</v>
+        <v>0</v>
       </c>
       <c r="G133" t="s">
-        <v>490</v>
+        <v>485</v>
       </c>
       <c r="H133" t="s">
-        <v>4</v>
+        <v>70</v>
       </c>
     </row>
     <row r="134" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A134" t="s">
-        <v>491</v>
+        <v>487</v>
       </c>
       <c r="C134" t="s">
-        <v>34</v>
+        <v>79</v>
       </c>
       <c r="D134" t="s">
-        <v>492</v>
+        <v>484</v>
       </c>
       <c r="E134" t="s">
-        <v>493</v>
+        <v>63</v>
       </c>
       <c r="F134" t="s">
-        <v>494</v>
+        <v>0</v>
       </c>
       <c r="G134" t="s">
-        <v>62</v>
+        <v>485</v>
       </c>
       <c r="H134" t="s">
-        <v>4</v>
+        <v>70</v>
       </c>
     </row>
     <row r="135" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A135" t="s">
-        <v>495</v>
+        <v>488</v>
       </c>
       <c r="C135" t="s">
-        <v>34</v>
+        <v>79</v>
       </c>
       <c r="D135" t="s">
-        <v>492</v>
+        <v>484</v>
       </c>
       <c r="E135" t="s">
-        <v>493</v>
+        <v>63</v>
       </c>
       <c r="F135" t="s">
-        <v>494</v>
+        <v>0</v>
       </c>
       <c r="G135" t="s">
-        <v>62</v>
+        <v>485</v>
       </c>
       <c r="H135" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="136" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A136" t="s">
-        <v>496</v>
-      </c>
-      <c r="C136" t="s">
-        <v>32</v>
-      </c>
-      <c r="D136" t="s">
-        <v>497</v>
-      </c>
-      <c r="E136" t="s">
-        <v>91</v>
-      </c>
-      <c r="F136" t="s">
-        <v>0</v>
-      </c>
-      <c r="G136" t="s">
-        <v>498</v>
-      </c>
-      <c r="H136" t="s">
-        <v>55</v>
-      </c>
-    </row>
-    <row r="137" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A137" t="s">
-        <v>499</v>
-      </c>
-      <c r="C137" t="s">
-        <v>32</v>
-      </c>
-      <c r="D137" t="s">
-        <v>497</v>
-      </c>
-      <c r="E137" t="s">
-        <v>91</v>
-      </c>
-      <c r="F137" t="s">
-        <v>0</v>
-      </c>
-      <c r="G137" t="s">
-        <v>498</v>
-      </c>
-      <c r="H137" t="s">
-        <v>55</v>
-      </c>
-    </row>
-    <row r="138" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A138" t="s">
-        <v>500</v>
-      </c>
-      <c r="C138" t="s">
-        <v>382</v>
-      </c>
-      <c r="D138" t="s">
-        <v>501</v>
-      </c>
-      <c r="E138" t="s">
-        <v>502</v>
-      </c>
-      <c r="F138" t="s">
-        <v>503</v>
-      </c>
-      <c r="G138" t="s">
-        <v>504</v>
-      </c>
-      <c r="H138" t="s">
-        <v>505</v>
+        <v>70</v>
       </c>
     </row>
   </sheetData>

--- a/1.xlsx
+++ b/1.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="\\wh.local\fs\UserProfile_TSSWH19\_TSSWH19_redirected_folders\HunyaCs1\Desktop\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{585CA4F4-B43A-4AF1-A85E-E210C3ABC4BB}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6761AFD0-E45D-4621-810A-B19DED82F50B}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="0" windowWidth="22260" windowHeight="12648" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="945" uniqueCount="489">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="953" uniqueCount="490">
   <si>
     <t>BUDAPEST</t>
   </si>
@@ -1495,6 +1495,9 @@
   </si>
   <si>
     <t>159995579538794025</t>
+  </si>
+  <si>
+    <t>SELEX</t>
   </si>
 </sst>
 </file>
@@ -1530,8 +1533,9 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normál" xfId="0" builtinId="0"/>
@@ -1813,3122 +1817,3178 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <sheetPr codeName="Munka1"/>
-  <dimension ref="A1:H135"/>
+  <dimension ref="A1:H139"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="24.88671875" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="9.109375"/>
-    <col min="3" max="3" width="6.88671875" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="20.109375" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="5" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="19.6640625" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="29" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="19.88671875" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="24.88671875" style="1" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="9.109375" style="1"/>
+    <col min="3" max="3" width="6.88671875" style="1" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="20.109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="5" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="19.6640625" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="29" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="19.88671875" style="1" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A1" t="s">
+      <c r="A1" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="C1" t="s">
+      <c r="C1" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="D1" t="s">
+      <c r="D1" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="E1" t="s">
+      <c r="E1" s="1" t="s">
         <v>18</v>
       </c>
-      <c r="F1" t="s">
+      <c r="F1" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="G1" t="s">
+      <c r="G1" s="1" t="s">
         <v>20</v>
       </c>
-      <c r="H1" t="s">
+      <c r="H1" s="1" t="s">
         <v>21</v>
       </c>
     </row>
     <row r="2" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A2" t="s">
+      <c r="A2" s="1" t="s">
         <v>78</v>
       </c>
-      <c r="C2" t="s">
+      <c r="C2" s="1" t="s">
         <v>79</v>
       </c>
-      <c r="D2" t="s">
+      <c r="D2" s="1" t="s">
         <v>80</v>
       </c>
-      <c r="E2" t="s">
+      <c r="E2" s="1" t="s">
         <v>81</v>
       </c>
-      <c r="F2" t="s">
-        <v>0</v>
-      </c>
-      <c r="G2" t="s">
+      <c r="F2" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="G2" s="1" t="s">
         <v>82</v>
       </c>
-      <c r="H2" t="s">
+      <c r="H2" s="1" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="3" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A3" t="s">
+      <c r="A3" s="1" t="s">
         <v>83</v>
       </c>
-      <c r="C3" t="s">
+      <c r="C3" s="1" t="s">
         <v>32</v>
       </c>
-      <c r="D3" t="s">
+      <c r="D3" s="1" t="s">
         <v>84</v>
       </c>
-      <c r="E3" t="s">
+      <c r="E3" s="1" t="s">
         <v>85</v>
       </c>
-      <c r="F3" t="s">
-        <v>0</v>
-      </c>
-      <c r="G3" t="s">
+      <c r="F3" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="G3" s="1" t="s">
         <v>86</v>
       </c>
-      <c r="H3" t="s">
+      <c r="H3" s="1" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="4" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A4" t="s">
+      <c r="A4" s="1" t="s">
         <v>87</v>
       </c>
-      <c r="C4" t="s">
+      <c r="C4" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="D4" t="s">
+      <c r="D4" s="1" t="s">
         <v>88</v>
       </c>
-      <c r="E4" t="s">
+      <c r="E4" s="1" t="s">
         <v>60</v>
       </c>
-      <c r="F4" t="s">
+      <c r="F4" s="1" t="s">
         <v>61</v>
       </c>
-      <c r="G4" t="s">
+      <c r="G4" s="1" t="s">
         <v>89</v>
       </c>
-      <c r="H4" t="s">
+      <c r="H4" s="1" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="5" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A5" t="s">
+      <c r="A5" s="1" t="s">
         <v>90</v>
       </c>
-      <c r="C5" t="s">
+      <c r="C5" s="1" t="s">
         <v>31</v>
       </c>
-      <c r="D5" t="s">
+      <c r="D5" s="1" t="s">
         <v>91</v>
       </c>
-      <c r="E5" t="s">
+      <c r="E5" s="1" t="s">
         <v>92</v>
       </c>
-      <c r="F5" t="s">
-        <v>0</v>
-      </c>
-      <c r="G5" t="s">
+      <c r="F5" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="G5" s="1" t="s">
         <v>93</v>
       </c>
-      <c r="H5" t="s">
+      <c r="H5" s="1" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="6" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A6" t="s">
+      <c r="A6" s="1" t="s">
         <v>94</v>
       </c>
-      <c r="C6" t="s">
+      <c r="C6" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="D6" t="s">
+      <c r="D6" s="1" t="s">
         <v>95</v>
       </c>
-      <c r="E6" t="s">
+      <c r="E6" s="1" t="s">
         <v>71</v>
       </c>
-      <c r="F6" t="s">
+      <c r="F6" s="1" t="s">
         <v>72</v>
       </c>
-      <c r="G6" t="s">
+      <c r="G6" s="1" t="s">
         <v>96</v>
       </c>
-      <c r="H6" t="s">
+      <c r="H6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="7" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A7" t="s">
+      <c r="A7" s="1" t="s">
         <v>97</v>
       </c>
-      <c r="C7" t="s">
+      <c r="C7" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="D7" t="s">
+      <c r="D7" s="1" t="s">
         <v>98</v>
       </c>
-      <c r="E7" t="s">
+      <c r="E7" s="1" t="s">
         <v>99</v>
       </c>
-      <c r="F7" t="s">
+      <c r="F7" s="1" t="s">
         <v>100</v>
       </c>
-      <c r="G7" t="s">
+      <c r="G7" s="1" t="s">
         <v>101</v>
       </c>
-      <c r="H7" t="s">
+      <c r="H7" s="1" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="8" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A8" t="s">
+      <c r="A8" s="1" t="s">
         <v>102</v>
       </c>
-      <c r="C8" t="s">
+      <c r="C8" s="1" t="s">
         <v>103</v>
       </c>
-      <c r="D8" t="s">
+      <c r="D8" s="1" t="s">
         <v>104</v>
       </c>
-      <c r="E8" t="s">
+      <c r="E8" s="1" t="s">
         <v>105</v>
       </c>
-      <c r="F8" t="s">
+      <c r="F8" s="1" t="s">
         <v>106</v>
       </c>
-      <c r="G8" t="s">
+      <c r="G8" s="1" t="s">
         <v>107</v>
       </c>
-      <c r="H8" t="s">
+      <c r="H8" s="1" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="9" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A9" t="s">
+      <c r="A9" s="1" t="s">
         <v>108</v>
       </c>
-      <c r="C9" t="s">
+      <c r="C9" s="1" t="s">
         <v>26</v>
       </c>
-      <c r="D9" t="s">
+      <c r="D9" s="1" t="s">
         <v>109</v>
       </c>
-      <c r="E9" t="s">
+      <c r="E9" s="1" t="s">
         <v>110</v>
       </c>
-      <c r="F9" t="s">
+      <c r="F9" s="1" t="s">
         <v>111</v>
       </c>
-      <c r="G9" t="s">
+      <c r="G9" s="1" t="s">
         <v>112</v>
       </c>
-      <c r="H9" t="s">
+      <c r="H9" s="1" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="10" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A10" t="s">
+      <c r="A10" s="1" t="s">
         <v>113</v>
       </c>
-      <c r="C10" t="s">
+      <c r="C10" s="1" t="s">
         <v>26</v>
       </c>
-      <c r="D10" t="s">
+      <c r="D10" s="1" t="s">
         <v>109</v>
       </c>
-      <c r="E10" t="s">
+      <c r="E10" s="1" t="s">
         <v>110</v>
       </c>
-      <c r="F10" t="s">
+      <c r="F10" s="1" t="s">
         <v>111</v>
       </c>
-      <c r="G10" t="s">
+      <c r="G10" s="1" t="s">
         <v>112</v>
       </c>
-      <c r="H10" t="s">
+      <c r="H10" s="1" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="11" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A11" t="s">
+      <c r="A11" s="1" t="s">
         <v>114</v>
       </c>
-      <c r="C11" t="s">
+      <c r="C11" s="1" t="s">
         <v>26</v>
       </c>
-      <c r="D11" t="s">
+      <c r="D11" s="1" t="s">
         <v>109</v>
       </c>
-      <c r="E11" t="s">
+      <c r="E11" s="1" t="s">
         <v>110</v>
       </c>
-      <c r="F11" t="s">
+      <c r="F11" s="1" t="s">
         <v>111</v>
       </c>
-      <c r="G11" t="s">
+      <c r="G11" s="1" t="s">
         <v>112</v>
       </c>
-      <c r="H11" t="s">
+      <c r="H11" s="1" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="12" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A12" t="s">
+      <c r="A12" s="1" t="s">
         <v>115</v>
       </c>
-      <c r="C12" t="s">
+      <c r="C12" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="D12" t="s">
+      <c r="D12" s="1" t="s">
         <v>116</v>
       </c>
-      <c r="E12" t="s">
+      <c r="E12" s="1" t="s">
         <v>68</v>
       </c>
-      <c r="F12" t="s">
-        <v>0</v>
-      </c>
-      <c r="G12" t="s">
+      <c r="F12" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="G12" s="1" t="s">
         <v>117</v>
       </c>
-      <c r="H12" t="s">
+      <c r="H12" s="1" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="13" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A13" t="s">
+      <c r="A13" s="1" t="s">
         <v>118</v>
       </c>
-      <c r="C13" t="s">
+      <c r="C13" s="1" t="s">
         <v>43</v>
       </c>
-      <c r="D13" t="s">
+      <c r="D13" s="1" t="s">
         <v>119</v>
       </c>
-      <c r="E13" t="s">
+      <c r="E13" s="1" t="s">
         <v>120</v>
       </c>
-      <c r="F13" t="s">
+      <c r="F13" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="G13" t="s">
+      <c r="G13" s="1" t="s">
         <v>121</v>
       </c>
-      <c r="H13" t="s">
+      <c r="H13" s="1" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="14" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A14" t="s">
+      <c r="A14" s="1" t="s">
         <v>122</v>
       </c>
-      <c r="C14" t="s">
+      <c r="C14" s="1" t="s">
         <v>103</v>
       </c>
-      <c r="D14" t="s">
+      <c r="D14" s="1" t="s">
         <v>123</v>
       </c>
-      <c r="E14" t="s">
+      <c r="E14" s="1" t="s">
         <v>105</v>
       </c>
-      <c r="F14" t="s">
+      <c r="F14" s="1" t="s">
         <v>106</v>
       </c>
-      <c r="G14" t="s">
+      <c r="G14" s="1" t="s">
         <v>107</v>
       </c>
-      <c r="H14" t="s">
+      <c r="H14" s="1" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="15" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A15" t="s">
+      <c r="A15" s="1" t="s">
         <v>124</v>
       </c>
-      <c r="C15" t="s">
+      <c r="C15" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="D15" t="s">
+      <c r="D15" s="1" t="s">
         <v>125</v>
       </c>
-      <c r="E15" t="s">
+      <c r="E15" s="1" t="s">
         <v>44</v>
       </c>
-      <c r="F15" t="s">
-        <v>0</v>
-      </c>
-      <c r="G15" t="s">
+      <c r="F15" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="G15" s="1" t="s">
         <v>126</v>
       </c>
-      <c r="H15" t="s">
+      <c r="H15" s="1" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="16" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A16" t="s">
+      <c r="A16" s="1" t="s">
         <v>127</v>
       </c>
-      <c r="C16" t="s">
+      <c r="C16" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="D16" t="s">
+      <c r="D16" s="1" t="s">
         <v>128</v>
       </c>
-      <c r="E16" t="s">
+      <c r="E16" s="1" t="s">
         <v>57</v>
       </c>
-      <c r="F16" t="s">
+      <c r="F16" s="1" t="s">
         <v>58</v>
       </c>
-      <c r="G16" t="s">
+      <c r="G16" s="1" t="s">
         <v>129</v>
       </c>
-      <c r="H16" t="s">
+      <c r="H16" s="1" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="17" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A17" t="s">
+      <c r="A17" s="1" t="s">
         <v>130</v>
       </c>
-      <c r="C17" t="s">
+      <c r="C17" s="1" t="s">
         <v>103</v>
       </c>
-      <c r="D17" t="s">
+      <c r="D17" s="1" t="s">
         <v>131</v>
       </c>
-      <c r="E17" t="s">
+      <c r="E17" s="1" t="s">
         <v>132</v>
       </c>
-      <c r="F17" t="s">
+      <c r="F17" s="1" t="s">
         <v>133</v>
       </c>
-      <c r="G17" t="s">
+      <c r="G17" s="1" t="s">
         <v>40</v>
       </c>
-      <c r="H17" t="s">
+      <c r="H17" s="1" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="18" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A18" t="s">
+      <c r="A18" s="1" t="s">
         <v>134</v>
       </c>
-      <c r="C18" t="s">
+      <c r="C18" s="1" t="s">
         <v>103</v>
       </c>
-      <c r="D18" t="s">
+      <c r="D18" s="1" t="s">
         <v>131</v>
       </c>
-      <c r="E18" t="s">
+      <c r="E18" s="1" t="s">
         <v>132</v>
       </c>
-      <c r="F18" t="s">
+      <c r="F18" s="1" t="s">
         <v>133</v>
       </c>
-      <c r="G18" t="s">
+      <c r="G18" s="1" t="s">
         <v>40</v>
       </c>
-      <c r="H18" t="s">
+      <c r="H18" s="1" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="19" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A19" t="s">
+      <c r="A19" s="1" t="s">
         <v>135</v>
       </c>
-      <c r="C19" t="s">
+      <c r="C19" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="D19" t="s">
+      <c r="D19" s="1" t="s">
         <v>136</v>
       </c>
-      <c r="E19" t="s">
+      <c r="E19" s="1" t="s">
         <v>35</v>
       </c>
-      <c r="F19" t="s">
+      <c r="F19" s="1" t="s">
         <v>36</v>
       </c>
-      <c r="G19" t="s">
+      <c r="G19" s="1" t="s">
         <v>137</v>
       </c>
-      <c r="H19" t="s">
+      <c r="H19" s="1" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="20" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A20" t="s">
+      <c r="A20" s="1" t="s">
         <v>138</v>
       </c>
-      <c r="C20" t="s">
+      <c r="C20" s="1" t="s">
         <v>26</v>
       </c>
-      <c r="D20" t="s">
+      <c r="D20" s="1" t="s">
         <v>139</v>
       </c>
-      <c r="E20" t="s">
+      <c r="E20" s="1" t="s">
         <v>75</v>
       </c>
-      <c r="F20" t="s">
+      <c r="F20" s="1" t="s">
         <v>76</v>
       </c>
-      <c r="G20" t="s">
+      <c r="G20" s="1" t="s">
         <v>140</v>
       </c>
-      <c r="H20" t="s">
+      <c r="H20" s="1" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="21" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A21" t="s">
+      <c r="A21" s="1" t="s">
         <v>141</v>
       </c>
-      <c r="C21" t="s">
+      <c r="C21" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="D21" t="s">
+      <c r="D21" s="1" t="s">
         <v>142</v>
       </c>
-      <c r="E21" t="s">
+      <c r="E21" s="1" t="s">
         <v>143</v>
       </c>
-      <c r="F21" t="s">
+      <c r="F21" s="1" t="s">
         <v>144</v>
       </c>
-      <c r="G21" t="s">
+      <c r="G21" s="1" t="s">
         <v>145</v>
       </c>
-      <c r="H21" t="s">
+      <c r="H21" s="1" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="22" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A22" t="s">
+      <c r="A22" s="1" t="s">
         <v>146</v>
       </c>
-      <c r="C22" t="s">
+      <c r="C22" s="1" t="s">
         <v>79</v>
       </c>
-      <c r="D22" t="s">
+      <c r="D22" s="1" t="s">
         <v>147</v>
       </c>
-      <c r="E22" t="s">
+      <c r="E22" s="1" t="s">
         <v>148</v>
       </c>
-      <c r="F22" t="s">
-        <v>0</v>
-      </c>
-      <c r="G22" t="s">
+      <c r="F22" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="G22" s="1" t="s">
         <v>149</v>
       </c>
-      <c r="H22" t="s">
+      <c r="H22" s="1" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="23" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A23" t="s">
+      <c r="A23" s="1" t="s">
         <v>150</v>
       </c>
-      <c r="C23" t="s">
+      <c r="C23" s="1" t="s">
         <v>79</v>
       </c>
-      <c r="D23" t="s">
+      <c r="D23" s="1" t="s">
         <v>151</v>
       </c>
-      <c r="E23" t="s">
+      <c r="E23" s="1" t="s">
         <v>63</v>
       </c>
-      <c r="F23" t="s">
-        <v>0</v>
-      </c>
-      <c r="G23" t="s">
+      <c r="F23" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="G23" s="1" t="s">
         <v>152</v>
       </c>
-      <c r="H23" t="s">
+      <c r="H23" s="1" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="24" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A24" t="s">
+      <c r="A24" s="1" t="s">
         <v>153</v>
       </c>
-      <c r="C24" t="s">
+      <c r="C24" s="1" t="s">
         <v>154</v>
       </c>
-      <c r="D24" t="s">
+      <c r="D24" s="1" t="s">
         <v>155</v>
       </c>
-      <c r="E24" t="s">
+      <c r="E24" s="1" t="s">
         <v>156</v>
       </c>
-      <c r="F24" t="s">
-        <v>0</v>
-      </c>
-      <c r="G24" t="s">
+      <c r="F24" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="G24" s="1" t="s">
         <v>157</v>
       </c>
-      <c r="H24" t="s">
+      <c r="H24" s="1" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="25" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A25" t="s">
+      <c r="A25" s="1" t="s">
         <v>158</v>
       </c>
-      <c r="C25" t="s">
+      <c r="C25" s="1" t="s">
         <v>26</v>
       </c>
-      <c r="D25" t="s">
+      <c r="D25" s="1" t="s">
         <v>159</v>
       </c>
-      <c r="E25" t="s">
+      <c r="E25" s="1" t="s">
         <v>160</v>
       </c>
-      <c r="F25" t="s">
-        <v>0</v>
-      </c>
-      <c r="G25" t="s">
+      <c r="F25" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="G25" s="1" t="s">
         <v>161</v>
       </c>
-      <c r="H25" t="s">
+      <c r="H25" s="1" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="26" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A26" t="s">
+      <c r="A26" s="1" t="s">
         <v>162</v>
       </c>
-      <c r="C26" t="s">
+      <c r="C26" s="1" t="s">
         <v>25</v>
       </c>
-      <c r="D26" t="s">
+      <c r="D26" s="1" t="s">
         <v>163</v>
       </c>
-      <c r="E26" t="s">
+      <c r="E26" s="1" t="s">
         <v>164</v>
       </c>
-      <c r="F26" t="s">
-        <v>0</v>
-      </c>
-      <c r="G26" t="s">
+      <c r="F26" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="G26" s="1" t="s">
         <v>165</v>
       </c>
-      <c r="H26" t="s">
+      <c r="H26" s="1" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="27" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A27" t="s">
+      <c r="A27" s="1" t="s">
         <v>166</v>
       </c>
-      <c r="C27" t="s">
+      <c r="C27" s="1" t="s">
         <v>59</v>
       </c>
-      <c r="D27" t="s">
+      <c r="D27" s="1" t="s">
         <v>167</v>
       </c>
-      <c r="E27" t="s">
+      <c r="E27" s="1" t="s">
         <v>168</v>
       </c>
-      <c r="F27" t="s">
-        <v>0</v>
-      </c>
-      <c r="G27" t="s">
+      <c r="F27" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="G27" s="1" t="s">
         <v>169</v>
       </c>
-      <c r="H27" t="s">
+      <c r="H27" s="1" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="28" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A28" t="s">
+      <c r="A28" s="1" t="s">
         <v>170</v>
       </c>
-      <c r="C28" t="s">
+      <c r="C28" s="1" t="s">
         <v>32</v>
       </c>
-      <c r="D28" t="s">
+      <c r="D28" s="1" t="s">
         <v>171</v>
       </c>
-      <c r="E28" t="s">
+      <c r="E28" s="1" t="s">
         <v>51</v>
       </c>
-      <c r="F28" t="s">
-        <v>0</v>
-      </c>
-      <c r="G28" t="s">
+      <c r="F28" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="G28" s="1" t="s">
         <v>172</v>
       </c>
-      <c r="H28" t="s">
+      <c r="H28" s="1" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="29" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A29" t="s">
+      <c r="A29" s="1" t="s">
         <v>173</v>
       </c>
-      <c r="C29" t="s">
+      <c r="C29" s="1" t="s">
         <v>79</v>
       </c>
-      <c r="D29" t="s">
+      <c r="D29" s="1" t="s">
         <v>174</v>
       </c>
-      <c r="E29" t="s">
+      <c r="E29" s="1" t="s">
         <v>29</v>
       </c>
-      <c r="F29" t="s">
-        <v>0</v>
-      </c>
-      <c r="G29" t="s">
+      <c r="F29" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="G29" s="1" t="s">
         <v>175</v>
       </c>
-      <c r="H29" t="s">
+      <c r="H29" s="1" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="30" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A30" t="s">
+      <c r="A30" s="1" t="s">
         <v>176</v>
       </c>
-      <c r="C30" t="s">
+      <c r="C30" s="1" t="s">
         <v>79</v>
       </c>
-      <c r="D30" t="s">
+      <c r="D30" s="1" t="s">
         <v>177</v>
       </c>
-      <c r="E30" t="s">
+      <c r="E30" s="1" t="s">
         <v>178</v>
       </c>
-      <c r="F30" t="s">
-        <v>0</v>
-      </c>
-      <c r="G30" t="s">
+      <c r="F30" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="G30" s="1" t="s">
         <v>179</v>
       </c>
-      <c r="H30" t="s">
+      <c r="H30" s="1" t="s">
         <v>3</v>
       </c>
     </row>
     <row r="31" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A31" t="s">
+      <c r="A31" s="1" t="s">
         <v>180</v>
       </c>
-      <c r="C31" t="s">
+      <c r="C31" s="1" t="s">
         <v>43</v>
       </c>
-      <c r="D31" t="s">
+      <c r="D31" s="1" t="s">
         <v>181</v>
       </c>
-      <c r="E31" t="s">
+      <c r="E31" s="1" t="s">
         <v>55</v>
       </c>
-      <c r="F31" t="s">
-        <v>0</v>
-      </c>
-      <c r="G31" t="s">
+      <c r="F31" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="G31" s="1" t="s">
         <v>182</v>
       </c>
-      <c r="H31" t="s">
+      <c r="H31" s="1" t="s">
         <v>3</v>
       </c>
     </row>
     <row r="32" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A32" t="s">
+      <c r="A32" s="1" t="s">
         <v>183</v>
       </c>
-      <c r="C32" t="s">
+      <c r="C32" s="1" t="s">
         <v>32</v>
       </c>
-      <c r="D32" t="s">
+      <c r="D32" s="1" t="s">
         <v>184</v>
       </c>
-      <c r="E32" t="s">
+      <c r="E32" s="1" t="s">
         <v>23</v>
       </c>
-      <c r="F32" t="s">
+      <c r="F32" s="1" t="s">
         <v>24</v>
       </c>
-      <c r="G32" t="s">
+      <c r="G32" s="1" t="s">
         <v>185</v>
       </c>
-      <c r="H32" t="s">
+      <c r="H32" s="1" t="s">
         <v>3</v>
       </c>
     </row>
     <row r="33" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A33" t="s">
+      <c r="A33" s="1" t="s">
         <v>186</v>
       </c>
-      <c r="C33" t="s">
+      <c r="C33" s="1" t="s">
         <v>32</v>
       </c>
-      <c r="D33" t="s">
+      <c r="D33" s="1" t="s">
         <v>187</v>
       </c>
-      <c r="E33" t="s">
+      <c r="E33" s="1" t="s">
         <v>23</v>
       </c>
-      <c r="F33" t="s">
+      <c r="F33" s="1" t="s">
         <v>24</v>
       </c>
-      <c r="G33" t="s">
+      <c r="G33" s="1" t="s">
         <v>188</v>
       </c>
-      <c r="H33" t="s">
+      <c r="H33" s="1" t="s">
         <v>3</v>
       </c>
     </row>
     <row r="34" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A34" t="s">
+      <c r="A34" s="1" t="s">
         <v>189</v>
       </c>
-      <c r="C34" t="s">
+      <c r="C34" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="D34" t="s">
+      <c r="D34" s="1" t="s">
         <v>190</v>
       </c>
-      <c r="E34" t="s">
+      <c r="E34" s="1" t="s">
         <v>28</v>
       </c>
-      <c r="F34" t="s">
-        <v>0</v>
-      </c>
-      <c r="G34" t="s">
+      <c r="F34" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="G34" s="1" t="s">
         <v>191</v>
       </c>
-      <c r="H34" t="s">
+      <c r="H34" s="1" t="s">
         <v>3</v>
       </c>
     </row>
     <row r="35" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A35" t="s">
+      <c r="A35" s="1" t="s">
         <v>192</v>
       </c>
-      <c r="C35" t="s">
+      <c r="C35" s="1" t="s">
         <v>154</v>
       </c>
-      <c r="D35" t="s">
+      <c r="D35" s="1" t="s">
         <v>193</v>
       </c>
-      <c r="E35" t="s">
+      <c r="E35" s="1" t="s">
         <v>194</v>
       </c>
-      <c r="F35" t="s">
-        <v>0</v>
-      </c>
-      <c r="G35" t="s">
+      <c r="F35" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="G35" s="1" t="s">
         <v>195</v>
       </c>
-      <c r="H35" t="s">
+      <c r="H35" s="1" t="s">
         <v>3</v>
       </c>
     </row>
     <row r="36" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A36" t="s">
+      <c r="A36" s="1" t="s">
         <v>196</v>
       </c>
-      <c r="C36" t="s">
+      <c r="C36" s="1" t="s">
         <v>22</v>
       </c>
-      <c r="D36" t="s">
+      <c r="D36" s="1" t="s">
         <v>197</v>
       </c>
-      <c r="E36" t="s">
+      <c r="E36" s="1" t="s">
         <v>198</v>
       </c>
-      <c r="F36" t="s">
+      <c r="F36" s="1" t="s">
         <v>199</v>
       </c>
-      <c r="G36" t="s">
+      <c r="G36" s="1" t="s">
         <v>200</v>
       </c>
-      <c r="H36" t="s">
+      <c r="H36" s="1" t="s">
         <v>3</v>
       </c>
     </row>
     <row r="37" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A37" t="s">
+      <c r="A37" s="1" t="s">
         <v>201</v>
       </c>
-      <c r="C37" t="s">
+      <c r="C37" s="1" t="s">
         <v>22</v>
       </c>
-      <c r="D37" t="s">
+      <c r="D37" s="1" t="s">
         <v>197</v>
       </c>
-      <c r="E37" t="s">
+      <c r="E37" s="1" t="s">
         <v>198</v>
       </c>
-      <c r="F37" t="s">
+      <c r="F37" s="1" t="s">
         <v>199</v>
       </c>
-      <c r="G37" t="s">
+      <c r="G37" s="1" t="s">
         <v>200</v>
       </c>
-      <c r="H37" t="s">
+      <c r="H37" s="1" t="s">
         <v>3</v>
       </c>
     </row>
     <row r="38" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A38" t="s">
+      <c r="A38" s="1" t="s">
         <v>202</v>
       </c>
-      <c r="C38" t="s">
+      <c r="C38" s="1" t="s">
         <v>26</v>
       </c>
-      <c r="D38" t="s">
+      <c r="D38" s="1" t="s">
         <v>203</v>
       </c>
-      <c r="E38" t="s">
+      <c r="E38" s="1" t="s">
         <v>204</v>
       </c>
-      <c r="F38" t="s">
+      <c r="F38" s="1" t="s">
         <v>205</v>
       </c>
-      <c r="G38" t="s">
+      <c r="G38" s="1" t="s">
         <v>206</v>
       </c>
-      <c r="H38" t="s">
+      <c r="H38" s="1" t="s">
         <v>3</v>
       </c>
     </row>
     <row r="39" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A39" t="s">
+      <c r="A39" s="1" t="s">
         <v>207</v>
       </c>
-      <c r="C39" t="s">
+      <c r="C39" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="D39" t="s">
+      <c r="D39" s="1" t="s">
         <v>208</v>
       </c>
-      <c r="E39" t="s">
+      <c r="E39" s="1" t="s">
         <v>64</v>
       </c>
-      <c r="F39" t="s">
-        <v>0</v>
-      </c>
-      <c r="G39" t="s">
+      <c r="F39" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="G39" s="1" t="s">
         <v>65</v>
       </c>
-      <c r="H39" t="s">
+      <c r="H39" s="1" t="s">
         <v>3</v>
       </c>
     </row>
     <row r="40" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A40" t="s">
+      <c r="A40" s="1" t="s">
         <v>209</v>
       </c>
-      <c r="C40" t="s">
+      <c r="C40" s="1" t="s">
         <v>26</v>
       </c>
-      <c r="D40" t="s">
+      <c r="D40" s="1" t="s">
         <v>210</v>
       </c>
-      <c r="E40" t="s">
+      <c r="E40" s="1" t="s">
         <v>160</v>
       </c>
-      <c r="F40" t="s">
-        <v>0</v>
-      </c>
-      <c r="G40" t="s">
+      <c r="F40" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="G40" s="1" t="s">
         <v>211</v>
       </c>
-      <c r="H40" t="s">
+      <c r="H40" s="1" t="s">
         <v>3</v>
       </c>
     </row>
     <row r="41" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A41" t="s">
+      <c r="A41" s="1" t="s">
         <v>212</v>
       </c>
-      <c r="C41" t="s">
+      <c r="C41" s="1" t="s">
         <v>26</v>
       </c>
-      <c r="D41" t="s">
+      <c r="D41" s="1" t="s">
         <v>210</v>
       </c>
-      <c r="E41" t="s">
+      <c r="E41" s="1" t="s">
         <v>160</v>
       </c>
-      <c r="F41" t="s">
-        <v>0</v>
-      </c>
-      <c r="G41" t="s">
+      <c r="F41" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="G41" s="1" t="s">
         <v>211</v>
       </c>
-      <c r="H41" t="s">
+      <c r="H41" s="1" t="s">
         <v>3</v>
       </c>
     </row>
     <row r="42" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A42" t="s">
+      <c r="A42" s="1" t="s">
         <v>213</v>
       </c>
-      <c r="C42" t="s">
+      <c r="C42" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="D42" t="s">
+      <c r="D42" s="1" t="s">
         <v>214</v>
       </c>
-      <c r="E42" t="s">
+      <c r="E42" s="1" t="s">
         <v>45</v>
       </c>
-      <c r="F42" t="s">
-        <v>0</v>
-      </c>
-      <c r="G42" t="s">
+      <c r="F42" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="G42" s="1" t="s">
         <v>215</v>
       </c>
-      <c r="H42" t="s">
+      <c r="H42" s="1" t="s">
         <v>3</v>
       </c>
     </row>
     <row r="43" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A43" t="s">
+      <c r="A43" s="1" t="s">
         <v>216</v>
       </c>
-      <c r="C43" t="s">
+      <c r="C43" s="1" t="s">
         <v>103</v>
       </c>
-      <c r="D43" t="s">
+      <c r="D43" s="1" t="s">
         <v>217</v>
       </c>
-      <c r="E43" t="s">
+      <c r="E43" s="1" t="s">
         <v>132</v>
       </c>
-      <c r="F43" t="s">
+      <c r="F43" s="1" t="s">
         <v>133</v>
       </c>
-      <c r="G43" t="s">
+      <c r="G43" s="1" t="s">
         <v>74</v>
       </c>
-      <c r="H43" t="s">
+      <c r="H43" s="1" t="s">
         <v>3</v>
       </c>
     </row>
     <row r="44" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A44" t="s">
+      <c r="A44" s="1" t="s">
         <v>218</v>
       </c>
-      <c r="C44" t="s">
+      <c r="C44" s="1" t="s">
         <v>22</v>
       </c>
-      <c r="D44" t="s">
+      <c r="D44" s="1" t="s">
         <v>219</v>
       </c>
-      <c r="E44" t="s">
+      <c r="E44" s="1" t="s">
         <v>220</v>
       </c>
-      <c r="F44" t="s">
+      <c r="F44" s="1" t="s">
         <v>221</v>
       </c>
-      <c r="G44" t="s">
+      <c r="G44" s="1" t="s">
         <v>222</v>
       </c>
-      <c r="H44" t="s">
+      <c r="H44" s="1" t="s">
         <v>3</v>
       </c>
     </row>
     <row r="45" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A45" t="s">
+      <c r="A45" s="1" t="s">
         <v>223</v>
       </c>
-      <c r="C45" t="s">
+      <c r="C45" s="1" t="s">
         <v>22</v>
       </c>
-      <c r="D45" t="s">
+      <c r="D45" s="1" t="s">
         <v>219</v>
       </c>
-      <c r="E45" t="s">
+      <c r="E45" s="1" t="s">
         <v>220</v>
       </c>
-      <c r="F45" t="s">
+      <c r="F45" s="1" t="s">
         <v>221</v>
       </c>
-      <c r="G45" t="s">
+      <c r="G45" s="1" t="s">
         <v>222</v>
       </c>
-      <c r="H45" t="s">
+      <c r="H45" s="1" t="s">
         <v>3</v>
       </c>
     </row>
     <row r="46" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A46" t="s">
+      <c r="A46" s="1" t="s">
         <v>224</v>
       </c>
-      <c r="C46" t="s">
+      <c r="C46" s="1" t="s">
         <v>27</v>
       </c>
-      <c r="D46" t="s">
+      <c r="D46" s="1" t="s">
         <v>225</v>
       </c>
-      <c r="E46" t="s">
+      <c r="E46" s="1" t="s">
         <v>39</v>
       </c>
-      <c r="F46" t="s">
-        <v>0</v>
-      </c>
-      <c r="G46" t="s">
+      <c r="F46" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="G46" s="1" t="s">
         <v>226</v>
       </c>
-      <c r="H46" t="s">
+      <c r="H46" s="1" t="s">
         <v>3</v>
       </c>
     </row>
     <row r="47" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A47" t="s">
+      <c r="A47" s="1" t="s">
         <v>227</v>
       </c>
-      <c r="C47" t="s">
+      <c r="C47" s="1" t="s">
         <v>25</v>
       </c>
-      <c r="D47" t="s">
+      <c r="D47" s="1" t="s">
         <v>228</v>
       </c>
-      <c r="E47" t="s">
+      <c r="E47" s="1" t="s">
         <v>229</v>
       </c>
-      <c r="F47" t="s">
-        <v>0</v>
-      </c>
-      <c r="G47" t="s">
+      <c r="F47" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="G47" s="1" t="s">
         <v>230</v>
       </c>
-      <c r="H47" t="s">
+      <c r="H47" s="1" t="s">
         <v>3</v>
       </c>
     </row>
     <row r="48" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A48" t="s">
+      <c r="A48" s="1" t="s">
         <v>231</v>
       </c>
-      <c r="C48" t="s">
+      <c r="C48" s="1" t="s">
         <v>22</v>
       </c>
-      <c r="D48" t="s">
+      <c r="D48" s="1" t="s">
         <v>232</v>
       </c>
-      <c r="E48" t="s">
+      <c r="E48" s="1" t="s">
         <v>34</v>
       </c>
-      <c r="F48" t="s">
-        <v>0</v>
-      </c>
-      <c r="G48" t="s">
+      <c r="F48" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="G48" s="1" t="s">
         <v>233</v>
       </c>
-      <c r="H48" t="s">
+      <c r="H48" s="1" t="s">
         <v>3</v>
       </c>
     </row>
     <row r="49" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A49" t="s">
+      <c r="A49" s="1" t="s">
         <v>234</v>
       </c>
-      <c r="C49" t="s">
+      <c r="C49" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="D49" t="s">
+      <c r="D49" s="1" t="s">
         <v>235</v>
       </c>
-      <c r="E49" t="s">
+      <c r="E49" s="1" t="s">
         <v>236</v>
       </c>
-      <c r="F49" t="s">
-        <v>0</v>
-      </c>
-      <c r="G49" t="s">
+      <c r="F49" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="G49" s="1" t="s">
         <v>237</v>
       </c>
-      <c r="H49" t="s">
+      <c r="H49" s="1" t="s">
         <v>3</v>
       </c>
     </row>
     <row r="50" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A50" t="s">
+      <c r="A50" s="1" t="s">
         <v>238</v>
       </c>
-      <c r="C50" t="s">
+      <c r="C50" s="1" t="s">
         <v>79</v>
       </c>
-      <c r="D50" t="s">
+      <c r="D50" s="1" t="s">
         <v>239</v>
       </c>
-      <c r="E50" t="s">
+      <c r="E50" s="1" t="s">
         <v>240</v>
       </c>
-      <c r="F50" t="s">
-        <v>0</v>
-      </c>
-      <c r="G50" t="s">
+      <c r="F50" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="G50" s="1" t="s">
         <v>241</v>
       </c>
-      <c r="H50" t="s">
+      <c r="H50" s="1" t="s">
         <v>3</v>
       </c>
     </row>
     <row r="51" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A51" t="s">
+      <c r="A51" s="1" t="s">
         <v>242</v>
       </c>
-      <c r="C51" t="s">
+      <c r="C51" s="1" t="s">
         <v>22</v>
       </c>
-      <c r="D51" t="s">
+      <c r="D51" s="1" t="s">
         <v>243</v>
       </c>
-      <c r="E51" t="s">
+      <c r="E51" s="1" t="s">
         <v>46</v>
       </c>
-      <c r="F51" t="s">
+      <c r="F51" s="1" t="s">
         <v>47</v>
       </c>
-      <c r="G51" t="s">
+      <c r="G51" s="1" t="s">
         <v>244</v>
       </c>
-      <c r="H51" t="s">
+      <c r="H51" s="1" t="s">
         <v>3</v>
       </c>
     </row>
     <row r="52" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A52" t="s">
+      <c r="A52" s="1" t="s">
         <v>245</v>
       </c>
-      <c r="C52" t="s">
+      <c r="C52" s="1" t="s">
         <v>103</v>
       </c>
-      <c r="D52" t="s">
+      <c r="D52" s="1" t="s">
         <v>246</v>
       </c>
-      <c r="E52" t="s">
+      <c r="E52" s="1" t="s">
         <v>247</v>
       </c>
-      <c r="F52" t="s">
+      <c r="F52" s="1" t="s">
         <v>248</v>
       </c>
-      <c r="G52" t="s">
+      <c r="G52" s="1" t="s">
         <v>249</v>
       </c>
-      <c r="H52" t="s">
+      <c r="H52" s="1" t="s">
         <v>3</v>
       </c>
     </row>
     <row r="53" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A53" t="s">
+      <c r="A53" s="1" t="s">
         <v>250</v>
       </c>
-      <c r="C53" t="s">
+      <c r="C53" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="D53" t="s">
+      <c r="D53" s="1" t="s">
         <v>251</v>
       </c>
-      <c r="E53" t="s">
+      <c r="E53" s="1" t="s">
         <v>252</v>
       </c>
-      <c r="F53" t="s">
+      <c r="F53" s="1" t="s">
         <v>253</v>
       </c>
-      <c r="G53" t="s">
+      <c r="G53" s="1" t="s">
         <v>254</v>
       </c>
-      <c r="H53" t="s">
+      <c r="H53" s="1" t="s">
         <v>3</v>
       </c>
     </row>
     <row r="54" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A54" t="s">
+      <c r="A54" s="1" t="s">
         <v>255</v>
       </c>
-      <c r="C54" t="s">
+      <c r="C54" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="D54" t="s">
+      <c r="D54" s="1" t="s">
         <v>251</v>
       </c>
-      <c r="E54" t="s">
+      <c r="E54" s="1" t="s">
         <v>252</v>
       </c>
-      <c r="F54" t="s">
+      <c r="F54" s="1" t="s">
         <v>253</v>
       </c>
-      <c r="G54" t="s">
+      <c r="G54" s="1" t="s">
         <v>254</v>
       </c>
-      <c r="H54" t="s">
+      <c r="H54" s="1" t="s">
         <v>3</v>
       </c>
     </row>
     <row r="55" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A55" t="s">
+      <c r="A55" s="1" t="s">
         <v>256</v>
       </c>
-      <c r="C55" t="s">
+      <c r="C55" s="1" t="s">
         <v>31</v>
       </c>
-      <c r="D55" t="s">
+      <c r="D55" s="1" t="s">
         <v>257</v>
       </c>
-      <c r="E55" t="s">
+      <c r="E55" s="1" t="s">
         <v>69</v>
       </c>
-      <c r="F55" t="s">
-        <v>0</v>
-      </c>
-      <c r="G55" t="s">
+      <c r="F55" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="G55" s="1" t="s">
         <v>258</v>
       </c>
-      <c r="H55" t="s">
+      <c r="H55" s="1" t="s">
         <v>3</v>
       </c>
     </row>
     <row r="56" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A56" t="s">
+      <c r="A56" s="1" t="s">
         <v>259</v>
       </c>
-      <c r="C56" t="s">
+      <c r="C56" s="1" t="s">
         <v>22</v>
       </c>
-      <c r="D56" t="s">
+      <c r="D56" s="1" t="s">
         <v>260</v>
       </c>
-      <c r="E56" t="s">
+      <c r="E56" s="1" t="s">
         <v>37</v>
       </c>
-      <c r="F56" t="s">
+      <c r="F56" s="1" t="s">
         <v>38</v>
       </c>
-      <c r="G56" t="s">
+      <c r="G56" s="1" t="s">
         <v>261</v>
       </c>
-      <c r="H56" t="s">
+      <c r="H56" s="1" t="s">
         <v>3</v>
       </c>
     </row>
     <row r="57" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A57" t="s">
+      <c r="A57" s="1" t="s">
         <v>262</v>
       </c>
-      <c r="C57" t="s">
+      <c r="C57" s="1" t="s">
         <v>27</v>
       </c>
-      <c r="D57" t="s">
+      <c r="D57" s="1" t="s">
         <v>263</v>
       </c>
-      <c r="E57" t="s">
+      <c r="E57" s="1" t="s">
         <v>264</v>
       </c>
-      <c r="F57" t="s">
-        <v>0</v>
-      </c>
-      <c r="G57" t="s">
+      <c r="F57" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="G57" s="1" t="s">
         <v>265</v>
       </c>
-      <c r="H57" t="s">
+      <c r="H57" s="1" t="s">
         <v>3</v>
       </c>
     </row>
     <row r="58" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A58" t="s">
+      <c r="A58" s="1" t="s">
         <v>266</v>
       </c>
-      <c r="C58" t="s">
+      <c r="C58" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="D58" t="s">
+      <c r="D58" s="1" t="s">
         <v>267</v>
       </c>
-      <c r="E58" t="s">
+      <c r="E58" s="1" t="s">
         <v>268</v>
       </c>
-      <c r="F58" t="s">
+      <c r="F58" s="1" t="s">
         <v>269</v>
       </c>
-      <c r="G58" t="s">
+      <c r="G58" s="1" t="s">
         <v>270</v>
       </c>
-      <c r="H58" t="s">
+      <c r="H58" s="1" t="s">
         <v>3</v>
       </c>
     </row>
     <row r="59" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A59" t="s">
+      <c r="A59" s="1" t="s">
         <v>271</v>
       </c>
-      <c r="C59" t="s">
+      <c r="C59" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="D59" t="s">
+      <c r="D59" s="1" t="s">
         <v>272</v>
       </c>
-      <c r="E59" t="s">
+      <c r="E59" s="1" t="s">
         <v>273</v>
       </c>
-      <c r="F59" t="s">
-        <v>0</v>
-      </c>
-      <c r="G59" t="s">
+      <c r="F59" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="G59" s="1" t="s">
         <v>274</v>
       </c>
-      <c r="H59" t="s">
+      <c r="H59" s="1" t="s">
         <v>3</v>
       </c>
     </row>
     <row r="60" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A60" t="s">
+      <c r="A60" s="1" t="s">
         <v>275</v>
       </c>
-      <c r="C60" t="s">
+      <c r="C60" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="D60" t="s">
+      <c r="D60" s="1" t="s">
         <v>276</v>
       </c>
-      <c r="E60" t="s">
+      <c r="E60" s="1" t="s">
         <v>71</v>
       </c>
-      <c r="F60" t="s">
+      <c r="F60" s="1" t="s">
         <v>72</v>
       </c>
-      <c r="G60" t="s">
+      <c r="G60" s="1" t="s">
         <v>277</v>
       </c>
-      <c r="H60" t="s">
+      <c r="H60" s="1" t="s">
         <v>3</v>
       </c>
     </row>
     <row r="61" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A61" t="s">
+      <c r="A61" s="1" t="s">
         <v>278</v>
       </c>
-      <c r="C61" t="s">
+      <c r="C61" s="1" t="s">
         <v>22</v>
       </c>
-      <c r="D61" t="s">
+      <c r="D61" s="1" t="s">
         <v>279</v>
       </c>
-      <c r="E61" t="s">
+      <c r="E61" s="1" t="s">
         <v>280</v>
       </c>
-      <c r="F61" t="s">
+      <c r="F61" s="1" t="s">
         <v>281</v>
       </c>
-      <c r="G61" t="s">
+      <c r="G61" s="1" t="s">
         <v>53</v>
       </c>
-      <c r="H61" t="s">
+      <c r="H61" s="1" t="s">
         <v>3</v>
       </c>
     </row>
     <row r="62" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A62" t="s">
+      <c r="A62" s="1" t="s">
         <v>282</v>
       </c>
-      <c r="C62" t="s">
+      <c r="C62" s="1" t="s">
         <v>22</v>
       </c>
-      <c r="D62" t="s">
+      <c r="D62" s="1" t="s">
         <v>279</v>
       </c>
-      <c r="E62" t="s">
+      <c r="E62" s="1" t="s">
         <v>280</v>
       </c>
-      <c r="F62" t="s">
+      <c r="F62" s="1" t="s">
         <v>281</v>
       </c>
-      <c r="G62" t="s">
+      <c r="G62" s="1" t="s">
         <v>53</v>
       </c>
-      <c r="H62" t="s">
+      <c r="H62" s="1" t="s">
         <v>3</v>
       </c>
     </row>
     <row r="63" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A63" t="s">
+      <c r="A63" s="1" t="s">
         <v>283</v>
       </c>
-      <c r="C63" t="s">
+      <c r="C63" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="D63" t="s">
+      <c r="D63" s="1" t="s">
         <v>284</v>
       </c>
-      <c r="E63" t="s">
+      <c r="E63" s="1" t="s">
         <v>168</v>
       </c>
-      <c r="F63" t="s">
-        <v>0</v>
-      </c>
-      <c r="G63" t="s">
+      <c r="F63" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="G63" s="1" t="s">
         <v>285</v>
       </c>
-      <c r="H63" t="s">
+      <c r="H63" s="1" t="s">
         <v>3</v>
       </c>
     </row>
     <row r="64" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A64" t="s">
+      <c r="A64" s="1" t="s">
         <v>286</v>
       </c>
-      <c r="C64" t="s">
+      <c r="C64" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="D64" t="s">
+      <c r="D64" s="1" t="s">
         <v>284</v>
       </c>
-      <c r="E64" t="s">
+      <c r="E64" s="1" t="s">
         <v>168</v>
       </c>
-      <c r="F64" t="s">
-        <v>0</v>
-      </c>
-      <c r="G64" t="s">
+      <c r="F64" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="G64" s="1" t="s">
         <v>285</v>
       </c>
-      <c r="H64" t="s">
+      <c r="H64" s="1" t="s">
         <v>3</v>
       </c>
     </row>
     <row r="65" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A65" t="s">
+      <c r="A65" s="1" t="s">
         <v>287</v>
       </c>
-      <c r="C65" t="s">
+      <c r="C65" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="D65" t="s">
+      <c r="D65" s="1" t="s">
         <v>284</v>
       </c>
-      <c r="E65" t="s">
+      <c r="E65" s="1" t="s">
         <v>168</v>
       </c>
-      <c r="F65" t="s">
-        <v>0</v>
-      </c>
-      <c r="G65" t="s">
+      <c r="F65" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="G65" s="1" t="s">
         <v>285</v>
       </c>
-      <c r="H65" t="s">
+      <c r="H65" s="1" t="s">
         <v>3</v>
       </c>
     </row>
     <row r="66" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A66" t="s">
+      <c r="A66" s="1" t="s">
         <v>288</v>
       </c>
-      <c r="C66" t="s">
+      <c r="C66" s="1" t="s">
         <v>67</v>
       </c>
-      <c r="D66" t="s">
+      <c r="D66" s="1" t="s">
         <v>289</v>
       </c>
-      <c r="E66" t="s">
+      <c r="E66" s="1" t="s">
         <v>54</v>
       </c>
-      <c r="F66" t="s">
-        <v>0</v>
-      </c>
-      <c r="G66" t="s">
+      <c r="F66" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="G66" s="1" t="s">
         <v>290</v>
       </c>
-      <c r="H66" t="s">
+      <c r="H66" s="1" t="s">
         <v>3</v>
       </c>
     </row>
     <row r="67" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A67" t="s">
+      <c r="A67" s="1" t="s">
         <v>291</v>
       </c>
-      <c r="C67" t="s">
+      <c r="C67" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="D67" t="s">
+      <c r="D67" s="1" t="s">
         <v>292</v>
       </c>
-      <c r="E67" t="s">
+      <c r="E67" s="1" t="s">
         <v>44</v>
       </c>
-      <c r="F67" t="s">
-        <v>0</v>
-      </c>
-      <c r="G67" t="s">
+      <c r="F67" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="G67" s="1" t="s">
         <v>293</v>
       </c>
-      <c r="H67" t="s">
+      <c r="H67" s="1" t="s">
         <v>3</v>
       </c>
     </row>
     <row r="68" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A68" t="s">
+      <c r="A68" s="1" t="s">
         <v>294</v>
       </c>
-      <c r="C68" t="s">
+      <c r="C68" s="1" t="s">
         <v>27</v>
       </c>
-      <c r="D68" t="s">
+      <c r="D68" s="1" t="s">
         <v>295</v>
       </c>
-      <c r="E68" t="s">
+      <c r="E68" s="1" t="s">
         <v>33</v>
       </c>
-      <c r="F68" t="s">
-        <v>0</v>
-      </c>
-      <c r="G68" t="s">
+      <c r="F68" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="G68" s="1" t="s">
         <v>296</v>
       </c>
-      <c r="H68" t="s">
+      <c r="H68" s="1" t="s">
         <v>3</v>
       </c>
     </row>
     <row r="69" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A69" t="s">
+      <c r="A69" s="1" t="s">
         <v>297</v>
       </c>
-      <c r="C69" t="s">
+      <c r="C69" s="1" t="s">
         <v>67</v>
       </c>
-      <c r="D69" t="s">
+      <c r="D69" s="1" t="s">
         <v>298</v>
       </c>
-      <c r="E69" t="s">
+      <c r="E69" s="1" t="s">
         <v>299</v>
       </c>
-      <c r="F69" t="s">
-        <v>0</v>
-      </c>
-      <c r="G69" t="s">
+      <c r="F69" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="G69" s="1" t="s">
         <v>300</v>
       </c>
-      <c r="H69" t="s">
+      <c r="H69" s="1" t="s">
         <v>3</v>
       </c>
     </row>
     <row r="70" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A70" t="s">
+      <c r="A70" s="1" t="s">
         <v>301</v>
       </c>
-      <c r="C70" t="s">
+      <c r="C70" s="1" t="s">
         <v>154</v>
       </c>
-      <c r="D70" t="s">
+      <c r="D70" s="1" t="s">
         <v>302</v>
       </c>
-      <c r="E70" t="s">
+      <c r="E70" s="1" t="s">
         <v>303</v>
       </c>
-      <c r="F70" t="s">
-        <v>0</v>
-      </c>
-      <c r="G70" t="s">
+      <c r="F70" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="G70" s="1" t="s">
         <v>304</v>
       </c>
-      <c r="H70" t="s">
+      <c r="H70" s="1" t="s">
         <v>3</v>
       </c>
     </row>
     <row r="71" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A71" t="s">
+      <c r="A71" s="1" t="s">
         <v>305</v>
       </c>
-      <c r="C71" t="s">
+      <c r="C71" s="1" t="s">
         <v>154</v>
       </c>
-      <c r="D71" t="s">
+      <c r="D71" s="1" t="s">
         <v>302</v>
       </c>
-      <c r="E71" t="s">
+      <c r="E71" s="1" t="s">
         <v>303</v>
       </c>
-      <c r="F71" t="s">
-        <v>0</v>
-      </c>
-      <c r="G71" t="s">
+      <c r="F71" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="G71" s="1" t="s">
         <v>304</v>
       </c>
-      <c r="H71" t="s">
+      <c r="H71" s="1" t="s">
         <v>3</v>
       </c>
     </row>
     <row r="72" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A72" t="s">
+      <c r="A72" s="1" t="s">
         <v>306</v>
       </c>
-      <c r="C72" t="s">
+      <c r="C72" s="1" t="s">
         <v>32</v>
       </c>
-      <c r="D72" t="s">
+      <c r="D72" s="1" t="s">
         <v>307</v>
       </c>
-      <c r="E72" t="s">
+      <c r="E72" s="1" t="s">
         <v>308</v>
       </c>
-      <c r="F72" t="s">
+      <c r="F72" s="1" t="s">
         <v>309</v>
       </c>
-      <c r="G72" t="s">
+      <c r="G72" s="1" t="s">
         <v>310</v>
       </c>
-      <c r="H72" t="s">
+      <c r="H72" s="1" t="s">
         <v>3</v>
       </c>
     </row>
     <row r="73" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A73" t="s">
+      <c r="A73" s="1" t="s">
         <v>311</v>
       </c>
-      <c r="C73" t="s">
+      <c r="C73" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="D73" t="s">
+      <c r="D73" s="1" t="s">
         <v>312</v>
       </c>
-      <c r="E73" t="s">
+      <c r="E73" s="1" t="s">
         <v>30</v>
       </c>
-      <c r="F73" t="s">
-        <v>0</v>
-      </c>
-      <c r="G73" t="s">
+      <c r="F73" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="G73" s="1" t="s">
         <v>313</v>
       </c>
-      <c r="H73" t="s">
+      <c r="H73" s="1" t="s">
         <v>3</v>
       </c>
     </row>
     <row r="74" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A74" t="s">
+      <c r="A74" s="1" t="s">
         <v>314</v>
       </c>
-      <c r="C74" t="s">
+      <c r="C74" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="D74" t="s">
+      <c r="D74" s="1" t="s">
         <v>312</v>
       </c>
-      <c r="E74" t="s">
+      <c r="E74" s="1" t="s">
         <v>30</v>
       </c>
-      <c r="F74" t="s">
-        <v>0</v>
-      </c>
-      <c r="G74" t="s">
+      <c r="F74" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="G74" s="1" t="s">
         <v>313</v>
       </c>
-      <c r="H74" t="s">
+      <c r="H74" s="1" t="s">
         <v>3</v>
       </c>
     </row>
     <row r="75" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A75" t="s">
+      <c r="A75" s="1" t="s">
         <v>315</v>
       </c>
-      <c r="C75" t="s">
+      <c r="C75" s="1" t="s">
         <v>22</v>
       </c>
-      <c r="D75" t="s">
+      <c r="D75" s="1" t="s">
         <v>316</v>
       </c>
-      <c r="E75" t="s">
+      <c r="E75" s="1" t="s">
         <v>46</v>
       </c>
-      <c r="F75" t="s">
+      <c r="F75" s="1" t="s">
         <v>47</v>
       </c>
-      <c r="G75" t="s">
+      <c r="G75" s="1" t="s">
         <v>317</v>
       </c>
-      <c r="H75" t="s">
+      <c r="H75" s="1" t="s">
         <v>3</v>
       </c>
     </row>
     <row r="76" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A76" t="s">
+      <c r="A76" s="1" t="s">
         <v>318</v>
       </c>
-      <c r="C76" t="s">
+      <c r="C76" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="D76" t="s">
+      <c r="D76" s="1" t="s">
         <v>319</v>
       </c>
-      <c r="E76" t="s">
+      <c r="E76" s="1" t="s">
         <v>320</v>
       </c>
-      <c r="F76" t="s">
-        <v>0</v>
-      </c>
-      <c r="G76" t="s">
+      <c r="F76" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="G76" s="1" t="s">
         <v>52</v>
       </c>
-      <c r="H76" t="s">
+      <c r="H76" s="1" t="s">
         <v>3</v>
       </c>
     </row>
     <row r="77" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A77" t="s">
+      <c r="A77" s="1" t="s">
         <v>321</v>
       </c>
-      <c r="C77" t="s">
+      <c r="C77" s="1" t="s">
         <v>26</v>
       </c>
-      <c r="D77" t="s">
+      <c r="D77" s="1" t="s">
         <v>322</v>
       </c>
-      <c r="E77" t="s">
+      <c r="E77" s="1" t="s">
         <v>48</v>
       </c>
-      <c r="F77" t="s">
+      <c r="F77" s="1" t="s">
         <v>49</v>
       </c>
-      <c r="G77" t="s">
+      <c r="G77" s="1" t="s">
         <v>323</v>
       </c>
-      <c r="H77" t="s">
+      <c r="H77" s="1" t="s">
         <v>3</v>
       </c>
     </row>
     <row r="78" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A78" t="s">
+      <c r="A78" s="1" t="s">
         <v>324</v>
       </c>
-      <c r="C78" t="s">
+      <c r="C78" s="1" t="s">
         <v>25</v>
       </c>
-      <c r="D78" t="s">
+      <c r="D78" s="1" t="s">
         <v>325</v>
       </c>
-      <c r="E78" t="s">
+      <c r="E78" s="1" t="s">
         <v>326</v>
       </c>
-      <c r="F78" t="s">
-        <v>0</v>
-      </c>
-      <c r="G78" t="s">
+      <c r="F78" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="G78" s="1" t="s">
         <v>327</v>
       </c>
-      <c r="H78" t="s">
+      <c r="H78" s="1" t="s">
         <v>3</v>
       </c>
     </row>
     <row r="79" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A79" t="s">
+      <c r="A79" s="1" t="s">
         <v>328</v>
       </c>
-      <c r="C79" t="s">
+      <c r="C79" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="D79" t="s">
+      <c r="D79" s="1" t="s">
         <v>329</v>
       </c>
-      <c r="E79" t="s">
+      <c r="E79" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="F79" t="s">
+      <c r="F79" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="G79" t="s">
+      <c r="G79" s="1" t="s">
         <v>330</v>
       </c>
-      <c r="H79" t="s">
+      <c r="H79" s="1" t="s">
         <v>3</v>
       </c>
     </row>
     <row r="80" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A80" t="s">
+      <c r="A80" s="1" t="s">
         <v>331</v>
       </c>
-      <c r="C80" t="s">
+      <c r="C80" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="D80" t="s">
+      <c r="D80" s="1" t="s">
         <v>332</v>
       </c>
-      <c r="E80" t="s">
+      <c r="E80" s="1" t="s">
         <v>60</v>
       </c>
-      <c r="F80" t="s">
+      <c r="F80" s="1" t="s">
         <v>61</v>
       </c>
-      <c r="G80" t="s">
+      <c r="G80" s="1" t="s">
         <v>333</v>
       </c>
-      <c r="H80" t="s">
+      <c r="H80" s="1" t="s">
         <v>3</v>
       </c>
     </row>
     <row r="81" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A81" t="s">
+      <c r="A81" s="1" t="s">
         <v>334</v>
       </c>
-      <c r="C81" t="s">
+      <c r="C81" s="1" t="s">
         <v>27</v>
       </c>
-      <c r="D81" t="s">
+      <c r="D81" s="1" t="s">
         <v>335</v>
       </c>
-      <c r="E81" t="s">
+      <c r="E81" s="1" t="s">
         <v>264</v>
       </c>
-      <c r="F81" t="s">
-        <v>0</v>
-      </c>
-      <c r="G81" t="s">
+      <c r="F81" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="G81" s="1" t="s">
         <v>336</v>
       </c>
-      <c r="H81" t="s">
+      <c r="H81" s="1" t="s">
         <v>3</v>
       </c>
     </row>
     <row r="82" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A82" t="s">
+      <c r="A82" s="1" t="s">
         <v>337</v>
       </c>
-      <c r="C82" t="s">
+      <c r="C82" s="1" t="s">
         <v>67</v>
       </c>
-      <c r="D82" t="s">
+      <c r="D82" s="1" t="s">
         <v>338</v>
       </c>
-      <c r="E82" t="s">
+      <c r="E82" s="1" t="s">
         <v>339</v>
       </c>
-      <c r="F82" t="s">
+      <c r="F82" s="1" t="s">
         <v>340</v>
       </c>
-      <c r="G82" t="s">
+      <c r="G82" s="1" t="s">
         <v>341</v>
       </c>
-      <c r="H82" t="s">
+      <c r="H82" s="1" t="s">
         <v>3</v>
       </c>
     </row>
     <row r="83" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A83" t="s">
+      <c r="A83" s="1" t="s">
         <v>342</v>
       </c>
-      <c r="C83" t="s">
+      <c r="C83" s="1" t="s">
         <v>43</v>
       </c>
-      <c r="D83" t="s">
+      <c r="D83" s="1" t="s">
         <v>343</v>
       </c>
-      <c r="E83" t="s">
+      <c r="E83" s="1" t="s">
         <v>344</v>
       </c>
-      <c r="F83" t="s">
+      <c r="F83" s="1" t="s">
         <v>345</v>
       </c>
-      <c r="G83" t="s">
+      <c r="G83" s="1" t="s">
         <v>346</v>
       </c>
-      <c r="H83" t="s">
+      <c r="H83" s="1" t="s">
         <v>3</v>
       </c>
     </row>
     <row r="84" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A84" t="s">
+      <c r="A84" s="1" t="s">
         <v>347</v>
       </c>
-      <c r="C84" t="s">
+      <c r="C84" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="D84" t="s">
+      <c r="D84" s="1" t="s">
         <v>348</v>
       </c>
-      <c r="E84" t="s">
+      <c r="E84" s="1" t="s">
         <v>273</v>
       </c>
-      <c r="F84" t="s">
-        <v>0</v>
-      </c>
-      <c r="G84" t="s">
+      <c r="F84" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="G84" s="1" t="s">
         <v>349</v>
       </c>
-      <c r="H84" t="s">
+      <c r="H84" s="1" t="s">
         <v>3</v>
       </c>
     </row>
     <row r="85" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A85" t="s">
+      <c r="A85" s="1" t="s">
         <v>350</v>
       </c>
-      <c r="C85" t="s">
+      <c r="C85" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="D85" t="s">
+      <c r="D85" s="1" t="s">
         <v>348</v>
       </c>
-      <c r="E85" t="s">
+      <c r="E85" s="1" t="s">
         <v>273</v>
       </c>
-      <c r="F85" t="s">
-        <v>0</v>
-      </c>
-      <c r="G85" t="s">
+      <c r="F85" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="G85" s="1" t="s">
         <v>349</v>
       </c>
-      <c r="H85" t="s">
+      <c r="H85" s="1" t="s">
         <v>3</v>
       </c>
     </row>
     <row r="86" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A86" t="s">
+      <c r="A86" s="1" t="s">
         <v>351</v>
       </c>
-      <c r="C86" t="s">
+      <c r="C86" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="D86" t="s">
+      <c r="D86" s="1" t="s">
         <v>348</v>
       </c>
-      <c r="E86" t="s">
+      <c r="E86" s="1" t="s">
         <v>273</v>
       </c>
-      <c r="F86" t="s">
-        <v>0</v>
-      </c>
-      <c r="G86" t="s">
+      <c r="F86" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="G86" s="1" t="s">
         <v>349</v>
       </c>
-      <c r="H86" t="s">
+      <c r="H86" s="1" t="s">
         <v>3</v>
       </c>
     </row>
     <row r="87" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A87" t="s">
+      <c r="A87" s="1" t="s">
         <v>352</v>
       </c>
-      <c r="C87" t="s">
+      <c r="C87" s="1" t="s">
         <v>27</v>
       </c>
-      <c r="D87" t="s">
+      <c r="D87" s="1" t="s">
         <v>353</v>
       </c>
-      <c r="E87" t="s">
+      <c r="E87" s="1" t="s">
         <v>73</v>
       </c>
-      <c r="F87" t="s">
-        <v>0</v>
-      </c>
-      <c r="G87" t="s">
+      <c r="F87" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="G87" s="1" t="s">
         <v>354</v>
       </c>
-      <c r="H87" t="s">
+      <c r="H87" s="1" t="s">
         <v>3</v>
       </c>
     </row>
     <row r="88" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A88" t="s">
+      <c r="A88" s="1" t="s">
         <v>355</v>
       </c>
-      <c r="C88" t="s">
+      <c r="C88" s="1" t="s">
         <v>154</v>
       </c>
-      <c r="D88" t="s">
+      <c r="D88" s="1" t="s">
         <v>356</v>
       </c>
-      <c r="E88" t="s">
+      <c r="E88" s="1" t="s">
         <v>357</v>
       </c>
-      <c r="F88" t="s">
-        <v>0</v>
-      </c>
-      <c r="G88" t="s">
+      <c r="F88" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="G88" s="1" t="s">
         <v>358</v>
       </c>
-      <c r="H88" t="s">
+      <c r="H88" s="1" t="s">
         <v>3</v>
       </c>
     </row>
     <row r="89" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A89" t="s">
+      <c r="A89" s="1" t="s">
         <v>359</v>
       </c>
-      <c r="C89" t="s">
+      <c r="C89" s="1" t="s">
         <v>154</v>
       </c>
-      <c r="D89" t="s">
+      <c r="D89" s="1" t="s">
         <v>356</v>
       </c>
-      <c r="E89" t="s">
+      <c r="E89" s="1" t="s">
         <v>357</v>
       </c>
-      <c r="F89" t="s">
-        <v>0</v>
-      </c>
-      <c r="G89" t="s">
+      <c r="F89" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="G89" s="1" t="s">
         <v>358</v>
       </c>
-      <c r="H89" t="s">
+      <c r="H89" s="1" t="s">
         <v>3</v>
       </c>
     </row>
     <row r="90" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A90" t="s">
+      <c r="A90" s="1" t="s">
         <v>360</v>
       </c>
-      <c r="C90" t="s">
+      <c r="C90" s="1" t="s">
         <v>32</v>
       </c>
-      <c r="D90" t="s">
+      <c r="D90" s="1" t="s">
         <v>361</v>
       </c>
-      <c r="E90" t="s">
+      <c r="E90" s="1" t="s">
         <v>362</v>
       </c>
-      <c r="F90" t="s">
-        <v>0</v>
-      </c>
-      <c r="G90" t="s">
+      <c r="F90" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="G90" s="1" t="s">
         <v>222</v>
       </c>
-      <c r="H90" t="s">
+      <c r="H90" s="1" t="s">
         <v>3</v>
       </c>
     </row>
     <row r="91" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A91" t="s">
+      <c r="A91" s="1" t="s">
         <v>363</v>
       </c>
-      <c r="C91" t="s">
+      <c r="C91" s="1" t="s">
         <v>43</v>
       </c>
-      <c r="D91" t="s">
+      <c r="D91" s="1" t="s">
         <v>364</v>
       </c>
-      <c r="E91" t="s">
+      <c r="E91" s="1" t="s">
         <v>365</v>
       </c>
-      <c r="F91" t="s">
-        <v>0</v>
-      </c>
-      <c r="G91" t="s">
+      <c r="F91" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="G91" s="1" t="s">
         <v>366</v>
       </c>
-      <c r="H91" t="s">
+      <c r="H91" s="1" t="s">
         <v>3</v>
       </c>
     </row>
     <row r="92" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A92" t="s">
+      <c r="A92" s="1" t="s">
         <v>367</v>
       </c>
-      <c r="C92" t="s">
+      <c r="C92" s="1" t="s">
         <v>59</v>
       </c>
-      <c r="D92" t="s">
+      <c r="D92" s="1" t="s">
         <v>368</v>
       </c>
-      <c r="E92" t="s">
+      <c r="E92" s="1" t="s">
         <v>369</v>
       </c>
-      <c r="F92" t="s">
-        <v>0</v>
-      </c>
-      <c r="G92" t="s">
+      <c r="F92" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="G92" s="1" t="s">
         <v>370</v>
       </c>
-      <c r="H92" t="s">
+      <c r="H92" s="1" t="s">
         <v>3</v>
       </c>
     </row>
     <row r="93" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A93" t="s">
+      <c r="A93" s="1" t="s">
         <v>371</v>
       </c>
-      <c r="C93" t="s">
+      <c r="C93" s="1" t="s">
         <v>67</v>
       </c>
-      <c r="D93" t="s">
+      <c r="D93" s="1" t="s">
         <v>372</v>
       </c>
-      <c r="E93" t="s">
+      <c r="E93" s="1" t="s">
         <v>373</v>
       </c>
-      <c r="F93" t="s">
+      <c r="F93" s="1" t="s">
         <v>374</v>
       </c>
-      <c r="G93" t="s">
+      <c r="G93" s="1" t="s">
         <v>375</v>
       </c>
-      <c r="H93" t="s">
+      <c r="H93" s="1" t="s">
         <v>3</v>
       </c>
     </row>
     <row r="94" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A94" t="s">
+      <c r="A94" s="1" t="s">
         <v>376</v>
       </c>
-      <c r="C94" t="s">
+      <c r="C94" s="1" t="s">
         <v>67</v>
       </c>
-      <c r="D94" t="s">
+      <c r="D94" s="1" t="s">
         <v>372</v>
       </c>
-      <c r="E94" t="s">
+      <c r="E94" s="1" t="s">
         <v>373</v>
       </c>
-      <c r="F94" t="s">
+      <c r="F94" s="1" t="s">
         <v>374</v>
       </c>
-      <c r="G94" t="s">
+      <c r="G94" s="1" t="s">
         <v>375</v>
       </c>
-      <c r="H94" t="s">
+      <c r="H94" s="1" t="s">
         <v>3</v>
       </c>
     </row>
     <row r="95" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A95" t="s">
+      <c r="A95" s="1" t="s">
         <v>377</v>
       </c>
-      <c r="C95" t="s">
+      <c r="C95" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="D95" t="s">
+      <c r="D95" s="1" t="s">
         <v>378</v>
       </c>
-      <c r="E95" t="s">
+      <c r="E95" s="1" t="s">
         <v>379</v>
       </c>
-      <c r="F95" t="s">
+      <c r="F95" s="1" t="s">
         <v>380</v>
       </c>
-      <c r="G95" t="s">
+      <c r="G95" s="1" t="s">
         <v>381</v>
       </c>
-      <c r="H95" t="s">
+      <c r="H95" s="1" t="s">
         <v>3</v>
       </c>
     </row>
     <row r="96" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A96" t="s">
+      <c r="A96" s="1" t="s">
         <v>382</v>
       </c>
-      <c r="C96" t="s">
+      <c r="C96" s="1" t="s">
         <v>67</v>
       </c>
-      <c r="D96" t="s">
+      <c r="D96" s="1" t="s">
         <v>383</v>
       </c>
-      <c r="E96" t="s">
+      <c r="E96" s="1" t="s">
         <v>62</v>
       </c>
-      <c r="F96" t="s">
-        <v>0</v>
-      </c>
-      <c r="G96" t="s">
+      <c r="F96" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="G96" s="1" t="s">
         <v>384</v>
       </c>
-      <c r="H96" t="s">
+      <c r="H96" s="1" t="s">
         <v>3</v>
       </c>
     </row>
     <row r="97" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A97" t="s">
+      <c r="A97" s="1" t="s">
         <v>385</v>
       </c>
-      <c r="C97" t="s">
+      <c r="C97" s="1" t="s">
         <v>79</v>
       </c>
-      <c r="D97" t="s">
+      <c r="D97" s="1" t="s">
         <v>386</v>
       </c>
-      <c r="E97" t="s">
+      <c r="E97" s="1" t="s">
         <v>387</v>
       </c>
-      <c r="F97" t="s">
-        <v>0</v>
-      </c>
-      <c r="G97" t="s">
+      <c r="F97" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="G97" s="1" t="s">
         <v>388</v>
       </c>
-      <c r="H97" t="s">
+      <c r="H97" s="1" t="s">
         <v>3</v>
       </c>
     </row>
     <row r="98" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A98" t="s">
+      <c r="A98" s="1" t="s">
         <v>389</v>
       </c>
-      <c r="C98" t="s">
+      <c r="C98" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="D98" t="s">
+      <c r="D98" s="1" t="s">
         <v>390</v>
       </c>
-      <c r="E98" t="s">
+      <c r="E98" s="1" t="s">
         <v>41</v>
       </c>
-      <c r="F98" t="s">
-        <v>0</v>
-      </c>
-      <c r="G98" t="s">
+      <c r="F98" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="G98" s="1" t="s">
         <v>391</v>
       </c>
-      <c r="H98" t="s">
+      <c r="H98" s="1" t="s">
         <v>3</v>
       </c>
     </row>
     <row r="99" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A99" t="s">
+      <c r="A99" s="1" t="s">
         <v>392</v>
       </c>
-      <c r="C99" t="s">
+      <c r="C99" s="1" t="s">
         <v>31</v>
       </c>
-      <c r="D99" t="s">
+      <c r="D99" s="1" t="s">
         <v>393</v>
       </c>
-      <c r="E99" t="s">
+      <c r="E99" s="1" t="s">
         <v>394</v>
       </c>
-      <c r="F99" t="s">
-        <v>0</v>
-      </c>
-      <c r="G99" t="s">
+      <c r="F99" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="G99" s="1" t="s">
         <v>395</v>
       </c>
-      <c r="H99" t="s">
+      <c r="H99" s="1" t="s">
         <v>3</v>
       </c>
     </row>
     <row r="100" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A100" t="s">
+      <c r="A100" s="1" t="s">
         <v>396</v>
       </c>
-      <c r="C100" t="s">
+      <c r="C100" s="1" t="s">
         <v>31</v>
       </c>
-      <c r="D100" t="s">
+      <c r="D100" s="1" t="s">
         <v>397</v>
       </c>
-      <c r="E100" t="s">
+      <c r="E100" s="1" t="s">
         <v>42</v>
       </c>
-      <c r="F100" t="s">
-        <v>0</v>
-      </c>
-      <c r="G100" t="s">
+      <c r="F100" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="G100" s="1" t="s">
         <v>398</v>
       </c>
-      <c r="H100" t="s">
+      <c r="H100" s="1" t="s">
         <v>3</v>
       </c>
     </row>
     <row r="101" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A101" t="s">
+      <c r="A101" s="1" t="s">
         <v>399</v>
       </c>
-      <c r="C101" t="s">
+      <c r="C101" s="1" t="s">
         <v>25</v>
       </c>
-      <c r="D101" t="s">
+      <c r="D101" s="1" t="s">
         <v>400</v>
       </c>
-      <c r="E101" t="s">
+      <c r="E101" s="1" t="s">
         <v>66</v>
       </c>
-      <c r="F101" t="s">
-        <v>0</v>
-      </c>
-      <c r="G101" t="s">
+      <c r="F101" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="G101" s="1" t="s">
         <v>401</v>
       </c>
-      <c r="H101" t="s">
+      <c r="H101" s="1" t="s">
         <v>3</v>
       </c>
     </row>
     <row r="102" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A102" t="s">
+      <c r="A102" s="1" t="s">
         <v>402</v>
       </c>
-      <c r="C102" t="s">
+      <c r="C102" s="1" t="s">
         <v>25</v>
       </c>
-      <c r="D102" t="s">
+      <c r="D102" s="1" t="s">
         <v>403</v>
       </c>
-      <c r="E102" t="s">
+      <c r="E102" s="1" t="s">
         <v>66</v>
       </c>
-      <c r="F102" t="s">
-        <v>0</v>
-      </c>
-      <c r="G102" t="s">
+      <c r="F102" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="G102" s="1" t="s">
         <v>404</v>
       </c>
-      <c r="H102" t="s">
+      <c r="H102" s="1" t="s">
         <v>3</v>
       </c>
     </row>
     <row r="103" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A103" t="s">
+      <c r="A103" s="1" t="s">
         <v>405</v>
       </c>
-      <c r="C103" t="s">
+      <c r="C103" s="1" t="s">
         <v>25</v>
       </c>
-      <c r="D103" t="s">
+      <c r="D103" s="1" t="s">
         <v>403</v>
       </c>
-      <c r="E103" t="s">
+      <c r="E103" s="1" t="s">
         <v>66</v>
       </c>
-      <c r="F103" t="s">
-        <v>0</v>
-      </c>
-      <c r="G103" t="s">
+      <c r="F103" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="G103" s="1" t="s">
         <v>404</v>
       </c>
-      <c r="H103" t="s">
+      <c r="H103" s="1" t="s">
         <v>3</v>
       </c>
     </row>
     <row r="104" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A104" t="s">
+      <c r="A104" s="1" t="s">
         <v>406</v>
       </c>
-      <c r="C104" t="s">
+      <c r="C104" s="1" t="s">
         <v>103</v>
       </c>
-      <c r="D104" t="s">
+      <c r="D104" s="1" t="s">
         <v>407</v>
       </c>
-      <c r="E104" t="s">
+      <c r="E104" s="1" t="s">
         <v>408</v>
       </c>
-      <c r="F104" t="s">
+      <c r="F104" s="1" t="s">
         <v>409</v>
       </c>
-      <c r="G104" t="s">
+      <c r="G104" s="1" t="s">
         <v>410</v>
       </c>
-      <c r="H104" t="s">
+      <c r="H104" s="1" t="s">
         <v>3</v>
       </c>
     </row>
     <row r="105" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A105" t="s">
+      <c r="A105" s="1" t="s">
         <v>411</v>
       </c>
-      <c r="C105" t="s">
+      <c r="C105" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="D105" t="s">
+      <c r="D105" s="1" t="s">
         <v>412</v>
       </c>
-      <c r="E105" t="s">
+      <c r="E105" s="1" t="s">
         <v>41</v>
       </c>
-      <c r="F105" t="s">
-        <v>0</v>
-      </c>
-      <c r="G105" t="s">
+      <c r="F105" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="G105" s="1" t="s">
         <v>413</v>
       </c>
-      <c r="H105" t="s">
+      <c r="H105" s="1" t="s">
         <v>3</v>
       </c>
     </row>
     <row r="106" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A106" t="s">
+      <c r="A106" s="1" t="s">
         <v>414</v>
       </c>
-      <c r="C106" t="s">
+      <c r="C106" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="D106" t="s">
+      <c r="D106" s="1" t="s">
         <v>415</v>
       </c>
-      <c r="E106" t="s">
+      <c r="E106" s="1" t="s">
         <v>41</v>
       </c>
-      <c r="F106" t="s">
-        <v>0</v>
-      </c>
-      <c r="G106" t="s">
+      <c r="F106" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="G106" s="1" t="s">
         <v>416</v>
       </c>
-      <c r="H106" t="s">
+      <c r="H106" s="1" t="s">
         <v>3</v>
       </c>
     </row>
     <row r="107" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A107" t="s">
+      <c r="A107" s="1" t="s">
         <v>417</v>
       </c>
-      <c r="C107" t="s">
+      <c r="C107" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="D107" t="s">
+      <c r="D107" s="1" t="s">
         <v>418</v>
       </c>
-      <c r="E107" t="s">
+      <c r="E107" s="1" t="s">
         <v>419</v>
       </c>
-      <c r="F107" t="s">
+      <c r="F107" s="1" t="s">
         <v>420</v>
       </c>
-      <c r="G107" t="s">
+      <c r="G107" s="1" t="s">
         <v>421</v>
       </c>
-      <c r="H107" t="s">
+      <c r="H107" s="1" t="s">
         <v>3</v>
       </c>
     </row>
     <row r="108" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A108" t="s">
+      <c r="A108" s="1" t="s">
         <v>422</v>
       </c>
-      <c r="C108" t="s">
+      <c r="C108" s="1" t="s">
         <v>26</v>
       </c>
-      <c r="D108" t="s">
+      <c r="D108" s="1" t="s">
         <v>423</v>
       </c>
-      <c r="E108" t="s">
+      <c r="E108" s="1" t="s">
         <v>424</v>
       </c>
-      <c r="F108" t="s">
+      <c r="F108" s="1" t="s">
         <v>425</v>
       </c>
-      <c r="G108" t="s">
+      <c r="G108" s="1" t="s">
         <v>426</v>
       </c>
-      <c r="H108" t="s">
+      <c r="H108" s="1" t="s">
         <v>3</v>
       </c>
     </row>
     <row r="109" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A109" t="s">
+      <c r="A109" s="1" t="s">
         <v>427</v>
       </c>
-      <c r="C109" t="s">
+      <c r="C109" s="1" t="s">
         <v>25</v>
       </c>
-      <c r="D109" t="s">
+      <c r="D109" s="1" t="s">
         <v>428</v>
       </c>
-      <c r="E109" t="s">
+      <c r="E109" s="1" t="s">
         <v>66</v>
       </c>
-      <c r="F109" t="s">
-        <v>0</v>
-      </c>
-      <c r="G109" t="s">
+      <c r="F109" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="G109" s="1" t="s">
         <v>429</v>
       </c>
-      <c r="H109" t="s">
+      <c r="H109" s="1" t="s">
         <v>3</v>
       </c>
     </row>
     <row r="110" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A110" t="s">
+      <c r="A110" s="1" t="s">
         <v>430</v>
       </c>
-      <c r="C110" t="s">
+      <c r="C110" s="1" t="s">
         <v>103</v>
       </c>
-      <c r="D110" t="s">
+      <c r="D110" s="1" t="s">
         <v>431</v>
       </c>
-      <c r="E110" t="s">
+      <c r="E110" s="1" t="s">
         <v>132</v>
       </c>
-      <c r="F110" t="s">
+      <c r="F110" s="1" t="s">
         <v>133</v>
       </c>
-      <c r="G110" t="s">
+      <c r="G110" s="1" t="s">
         <v>432</v>
       </c>
-      <c r="H110" t="s">
+      <c r="H110" s="1" t="s">
         <v>3</v>
       </c>
     </row>
     <row r="111" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A111" t="s">
+      <c r="A111" s="1" t="s">
         <v>433</v>
       </c>
-      <c r="C111" t="s">
+      <c r="C111" s="1" t="s">
         <v>27</v>
       </c>
-      <c r="D111" t="s">
+      <c r="D111" s="1" t="s">
         <v>434</v>
       </c>
-      <c r="E111" t="s">
+      <c r="E111" s="1" t="s">
         <v>264</v>
       </c>
-      <c r="F111" t="s">
-        <v>0</v>
-      </c>
-      <c r="G111" t="s">
+      <c r="F111" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="G111" s="1" t="s">
         <v>435</v>
       </c>
-      <c r="H111" t="s">
+      <c r="H111" s="1" t="s">
         <v>3</v>
       </c>
     </row>
     <row r="112" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A112" t="s">
+      <c r="A112" s="1" t="s">
         <v>436</v>
       </c>
-      <c r="C112" t="s">
+      <c r="C112" s="1" t="s">
         <v>26</v>
       </c>
-      <c r="D112" t="s">
+      <c r="D112" s="1" t="s">
         <v>437</v>
       </c>
-      <c r="E112" t="s">
+      <c r="E112" s="1" t="s">
         <v>438</v>
       </c>
-      <c r="F112" t="s">
+      <c r="F112" s="1" t="s">
         <v>439</v>
       </c>
-      <c r="G112" t="s">
+      <c r="G112" s="1" t="s">
         <v>440</v>
       </c>
-      <c r="H112" t="s">
+      <c r="H112" s="1" t="s">
         <v>3</v>
       </c>
     </row>
     <row r="113" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A113" t="s">
+      <c r="A113" s="1" t="s">
         <v>441</v>
       </c>
-      <c r="C113" t="s">
+      <c r="C113" s="1" t="s">
         <v>26</v>
       </c>
-      <c r="D113" t="s">
+      <c r="D113" s="1" t="s">
         <v>442</v>
       </c>
-      <c r="E113" t="s">
+      <c r="E113" s="1" t="s">
         <v>438</v>
       </c>
-      <c r="F113" t="s">
+      <c r="F113" s="1" t="s">
         <v>439</v>
       </c>
-      <c r="G113" t="s">
+      <c r="G113" s="1" t="s">
         <v>443</v>
       </c>
-      <c r="H113" t="s">
+      <c r="H113" s="1" t="s">
         <v>3</v>
       </c>
     </row>
     <row r="114" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A114" t="s">
+      <c r="A114" s="1" t="s">
         <v>444</v>
       </c>
-      <c r="C114" t="s">
+      <c r="C114" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="D114" t="s">
+      <c r="D114" s="1" t="s">
         <v>445</v>
       </c>
-      <c r="E114" t="s">
+      <c r="E114" s="1" t="s">
         <v>446</v>
       </c>
-      <c r="F114" t="s">
+      <c r="F114" s="1" t="s">
         <v>447</v>
       </c>
-      <c r="G114" t="s">
+      <c r="G114" s="1" t="s">
         <v>448</v>
       </c>
-      <c r="H114" t="s">
+      <c r="H114" s="1" t="s">
         <v>4</v>
       </c>
     </row>
     <row r="115" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A115" t="s">
+      <c r="A115" s="1" t="s">
         <v>449</v>
       </c>
-      <c r="C115" t="s">
+      <c r="C115" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="D115" t="s">
+      <c r="D115" s="1" t="s">
         <v>445</v>
       </c>
-      <c r="E115" t="s">
+      <c r="E115" s="1" t="s">
         <v>446</v>
       </c>
-      <c r="F115" t="s">
+      <c r="F115" s="1" t="s">
         <v>447</v>
       </c>
-      <c r="G115" t="s">
+      <c r="G115" s="1" t="s">
         <v>448</v>
       </c>
-      <c r="H115" t="s">
+      <c r="H115" s="1" t="s">
         <v>4</v>
       </c>
     </row>
     <row r="116" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A116" t="s">
+      <c r="A116" s="1" t="s">
         <v>450</v>
       </c>
-      <c r="C116" t="s">
+      <c r="C116" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="D116" t="s">
+      <c r="D116" s="1" t="s">
         <v>445</v>
       </c>
-      <c r="E116" t="s">
+      <c r="E116" s="1" t="s">
         <v>446</v>
       </c>
-      <c r="F116" t="s">
+      <c r="F116" s="1" t="s">
         <v>447</v>
       </c>
-      <c r="G116" t="s">
+      <c r="G116" s="1" t="s">
         <v>448</v>
       </c>
-      <c r="H116" t="s">
+      <c r="H116" s="1" t="s">
         <v>4</v>
       </c>
     </row>
     <row r="117" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A117" t="s">
+      <c r="A117" s="1" t="s">
         <v>451</v>
       </c>
-      <c r="C117" t="s">
+      <c r="C117" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="D117" t="s">
+      <c r="D117" s="1" t="s">
         <v>445</v>
       </c>
-      <c r="E117" t="s">
+      <c r="E117" s="1" t="s">
         <v>446</v>
       </c>
-      <c r="F117" t="s">
+      <c r="F117" s="1" t="s">
         <v>447</v>
       </c>
-      <c r="G117" t="s">
+      <c r="G117" s="1" t="s">
         <v>448</v>
       </c>
-      <c r="H117" t="s">
+      <c r="H117" s="1" t="s">
         <v>4</v>
       </c>
     </row>
     <row r="118" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A118" t="s">
+      <c r="A118" s="1" t="s">
         <v>452</v>
       </c>
-      <c r="C118" t="s">
+      <c r="C118" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="D118" t="s">
+      <c r="D118" s="1" t="s">
         <v>445</v>
       </c>
-      <c r="E118" t="s">
+      <c r="E118" s="1" t="s">
         <v>446</v>
       </c>
-      <c r="F118" t="s">
+      <c r="F118" s="1" t="s">
         <v>447</v>
       </c>
-      <c r="G118" t="s">
+      <c r="G118" s="1" t="s">
         <v>448</v>
       </c>
-      <c r="H118" t="s">
+      <c r="H118" s="1" t="s">
         <v>4</v>
       </c>
     </row>
     <row r="119" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A119" t="s">
+      <c r="A119" s="1" t="s">
         <v>453</v>
       </c>
-      <c r="C119" t="s">
+      <c r="C119" s="1" t="s">
         <v>27</v>
       </c>
-      <c r="D119" t="s">
+      <c r="D119" s="1" t="s">
         <v>454</v>
       </c>
-      <c r="E119" t="s">
+      <c r="E119" s="1" t="s">
         <v>73</v>
       </c>
-      <c r="F119" t="s">
-        <v>0</v>
-      </c>
-      <c r="G119" t="s">
+      <c r="F119" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="G119" s="1" t="s">
         <v>455</v>
       </c>
-      <c r="H119" t="s">
+      <c r="H119" s="1" t="s">
         <v>4</v>
       </c>
     </row>
     <row r="120" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A120" t="s">
+      <c r="A120" s="1" t="s">
         <v>456</v>
       </c>
-      <c r="C120" t="s">
+      <c r="C120" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="D120" t="s">
+      <c r="D120" s="1" t="s">
         <v>457</v>
       </c>
-      <c r="E120" t="s">
+      <c r="E120" s="1" t="s">
         <v>44</v>
       </c>
-      <c r="F120" t="s">
-        <v>0</v>
-      </c>
-      <c r="G120" t="s">
+      <c r="F120" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="G120" s="1" t="s">
         <v>56</v>
       </c>
-      <c r="H120" t="s">
+      <c r="H120" s="1" t="s">
         <v>4</v>
       </c>
     </row>
     <row r="121" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A121" t="s">
+      <c r="A121" s="1" t="s">
         <v>458</v>
       </c>
-      <c r="C121" t="s">
+      <c r="C121" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="D121" t="s">
+      <c r="D121" s="1" t="s">
         <v>459</v>
       </c>
-      <c r="E121" t="s">
+      <c r="E121" s="1" t="s">
         <v>419</v>
       </c>
-      <c r="F121" t="s">
+      <c r="F121" s="1" t="s">
         <v>420</v>
       </c>
-      <c r="G121" t="s">
+      <c r="G121" s="1" t="s">
         <v>50</v>
       </c>
-      <c r="H121" t="s">
+      <c r="H121" s="1" t="s">
         <v>4</v>
       </c>
     </row>
     <row r="122" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A122" t="s">
+      <c r="A122" s="1" t="s">
         <v>460</v>
       </c>
-      <c r="C122" t="s">
+      <c r="C122" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="D122" t="s">
+      <c r="D122" s="1" t="s">
         <v>459</v>
       </c>
-      <c r="E122" t="s">
+      <c r="E122" s="1" t="s">
         <v>419</v>
       </c>
-      <c r="F122" t="s">
+      <c r="F122" s="1" t="s">
         <v>420</v>
       </c>
-      <c r="G122" t="s">
+      <c r="G122" s="1" t="s">
         <v>50</v>
       </c>
-      <c r="H122" t="s">
+      <c r="H122" s="1" t="s">
         <v>4</v>
       </c>
     </row>
     <row r="123" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A123" t="s">
+      <c r="A123" s="1" t="s">
         <v>461</v>
       </c>
-      <c r="C123" t="s">
+      <c r="C123" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="D123" t="s">
+      <c r="D123" s="1" t="s">
         <v>459</v>
       </c>
-      <c r="E123" t="s">
+      <c r="E123" s="1" t="s">
         <v>419</v>
       </c>
-      <c r="F123" t="s">
+      <c r="F123" s="1" t="s">
         <v>420</v>
       </c>
-      <c r="G123" t="s">
+      <c r="G123" s="1" t="s">
         <v>50</v>
       </c>
-      <c r="H123" t="s">
+      <c r="H123" s="1" t="s">
         <v>4</v>
       </c>
     </row>
     <row r="124" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A124" t="s">
+      <c r="A124" s="1" t="s">
         <v>462</v>
       </c>
-      <c r="C124" t="s">
+      <c r="C124" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="D124" t="s">
+      <c r="D124" s="1" t="s">
         <v>459</v>
       </c>
-      <c r="E124" t="s">
+      <c r="E124" s="1" t="s">
         <v>419</v>
       </c>
-      <c r="F124" t="s">
+      <c r="F124" s="1" t="s">
         <v>420</v>
       </c>
-      <c r="G124" t="s">
+      <c r="G124" s="1" t="s">
         <v>50</v>
       </c>
-      <c r="H124" t="s">
+      <c r="H124" s="1" t="s">
         <v>4</v>
       </c>
     </row>
     <row r="125" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A125" t="s">
+      <c r="A125" s="1" t="s">
         <v>463</v>
       </c>
-      <c r="C125" t="s">
+      <c r="C125" s="1" t="s">
         <v>79</v>
       </c>
-      <c r="D125" t="s">
+      <c r="D125" s="1" t="s">
         <v>464</v>
       </c>
-      <c r="E125" t="s">
+      <c r="E125" s="1" t="s">
         <v>465</v>
       </c>
-      <c r="F125" t="s">
-        <v>0</v>
-      </c>
-      <c r="G125" t="s">
+      <c r="F125" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="G125" s="1" t="s">
         <v>466</v>
       </c>
-      <c r="H125" t="s">
+      <c r="H125" s="1" t="s">
         <v>4</v>
       </c>
     </row>
     <row r="126" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A126" t="s">
+      <c r="A126" s="1" t="s">
         <v>467</v>
       </c>
-      <c r="C126" t="s">
+      <c r="C126" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="D126" t="s">
+      <c r="D126" s="1" t="s">
         <v>468</v>
       </c>
-      <c r="E126" t="s">
+      <c r="E126" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="F126" t="s">
+      <c r="F126" s="1" t="s">
         <v>14</v>
       </c>
-      <c r="G126" t="s">
+      <c r="G126" s="1" t="s">
         <v>469</v>
       </c>
-      <c r="H126" t="s">
+      <c r="H126" s="1" t="s">
         <v>4</v>
       </c>
     </row>
     <row r="127" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A127" t="s">
+      <c r="A127" s="1" t="s">
         <v>470</v>
       </c>
-      <c r="C127" t="s">
+      <c r="C127" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="D127" t="s">
+      <c r="D127" s="1" t="s">
         <v>471</v>
       </c>
-      <c r="E127" t="s">
+      <c r="E127" s="1" t="s">
         <v>472</v>
       </c>
-      <c r="F127" t="s">
-        <v>0</v>
-      </c>
-      <c r="G127" t="s">
+      <c r="F127" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="G127" s="1" t="s">
         <v>473</v>
       </c>
-      <c r="H127" t="s">
+      <c r="H127" s="1" t="s">
         <v>4</v>
       </c>
     </row>
     <row r="128" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A128" t="s">
+      <c r="A128" s="1" t="s">
         <v>474</v>
       </c>
-      <c r="C128" t="s">
+      <c r="C128" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="D128" t="s">
+      <c r="D128" s="1" t="s">
         <v>475</v>
       </c>
-      <c r="E128" t="s">
+      <c r="E128" s="1" t="s">
         <v>446</v>
       </c>
-      <c r="F128" t="s">
+      <c r="F128" s="1" t="s">
         <v>447</v>
       </c>
-      <c r="G128" t="s">
+      <c r="G128" s="1" t="s">
         <v>476</v>
       </c>
-      <c r="H128" t="s">
+      <c r="H128" s="1" t="s">
         <v>4</v>
       </c>
     </row>
     <row r="129" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A129" t="s">
+      <c r="A129" s="1" t="s">
         <v>477</v>
       </c>
-      <c r="C129" t="s">
+      <c r="C129" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="D129" t="s">
+      <c r="D129" s="1" t="s">
         <v>478</v>
       </c>
-      <c r="E129" t="s">
+      <c r="E129" s="1" t="s">
         <v>479</v>
       </c>
-      <c r="F129" t="s">
-        <v>0</v>
-      </c>
-      <c r="G129" t="s">
+      <c r="F129" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="G129" s="1" t="s">
         <v>480</v>
       </c>
-      <c r="H129" t="s">
+      <c r="H129" s="1" t="s">
         <v>77</v>
       </c>
     </row>
     <row r="130" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A130" t="s">
+      <c r="A130" s="1" t="s">
         <v>481</v>
       </c>
-      <c r="C130" t="s">
+      <c r="C130" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="D130" t="s">
+      <c r="D130" s="1" t="s">
         <v>478</v>
       </c>
-      <c r="E130" t="s">
+      <c r="E130" s="1" t="s">
         <v>479</v>
       </c>
-      <c r="F130" t="s">
-        <v>0</v>
-      </c>
-      <c r="G130" t="s">
+      <c r="F130" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="G130" s="1" t="s">
         <v>480</v>
       </c>
-      <c r="H130" t="s">
+      <c r="H130" s="1" t="s">
         <v>77</v>
       </c>
     </row>
     <row r="131" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A131" t="s">
+      <c r="A131" s="1" t="s">
         <v>482</v>
       </c>
-      <c r="C131" t="s">
+      <c r="C131" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="D131" t="s">
+      <c r="D131" s="1" t="s">
         <v>478</v>
       </c>
-      <c r="E131" t="s">
+      <c r="E131" s="1" t="s">
         <v>479</v>
       </c>
-      <c r="F131" t="s">
-        <v>0</v>
-      </c>
-      <c r="G131" t="s">
+      <c r="F131" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="G131" s="1" t="s">
         <v>480</v>
       </c>
-      <c r="H131" t="s">
+      <c r="H131" s="1" t="s">
         <v>77</v>
       </c>
     </row>
     <row r="132" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A132" t="s">
+      <c r="A132" s="1" t="s">
         <v>483</v>
       </c>
-      <c r="C132" t="s">
+      <c r="C132" s="1" t="s">
         <v>79</v>
       </c>
-      <c r="D132" t="s">
+      <c r="D132" s="1" t="s">
         <v>484</v>
       </c>
-      <c r="E132" t="s">
+      <c r="E132" s="1" t="s">
         <v>63</v>
       </c>
-      <c r="F132" t="s">
-        <v>0</v>
-      </c>
-      <c r="G132" t="s">
+      <c r="F132" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="G132" s="1" t="s">
         <v>485</v>
       </c>
-      <c r="H132" t="s">
+      <c r="H132" s="1" t="s">
         <v>70</v>
       </c>
     </row>
     <row r="133" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A133" t="s">
+      <c r="A133" s="1" t="s">
         <v>486</v>
       </c>
-      <c r="C133" t="s">
+      <c r="C133" s="1" t="s">
         <v>79</v>
       </c>
-      <c r="D133" t="s">
+      <c r="D133" s="1" t="s">
         <v>484</v>
       </c>
-      <c r="E133" t="s">
+      <c r="E133" s="1" t="s">
         <v>63</v>
       </c>
-      <c r="F133" t="s">
-        <v>0</v>
-      </c>
-      <c r="G133" t="s">
+      <c r="F133" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="G133" s="1" t="s">
         <v>485</v>
       </c>
-      <c r="H133" t="s">
+      <c r="H133" s="1" t="s">
         <v>70</v>
       </c>
     </row>
     <row r="134" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A134" t="s">
+      <c r="A134" s="1" t="s">
         <v>487</v>
       </c>
-      <c r="C134" t="s">
+      <c r="C134" s="1" t="s">
         <v>79</v>
       </c>
-      <c r="D134" t="s">
+      <c r="D134" s="1" t="s">
         <v>484</v>
       </c>
-      <c r="E134" t="s">
+      <c r="E134" s="1" t="s">
         <v>63</v>
       </c>
-      <c r="F134" t="s">
-        <v>0</v>
-      </c>
-      <c r="G134" t="s">
+      <c r="F134" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="G134" s="1" t="s">
         <v>485</v>
       </c>
-      <c r="H134" t="s">
+      <c r="H134" s="1" t="s">
         <v>70</v>
       </c>
     </row>
     <row r="135" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A135" t="s">
+      <c r="A135" s="1" t="s">
         <v>488</v>
       </c>
-      <c r="C135" t="s">
+      <c r="C135" s="1" t="s">
         <v>79</v>
       </c>
-      <c r="D135" t="s">
+      <c r="D135" s="1" t="s">
         <v>484</v>
       </c>
-      <c r="E135" t="s">
+      <c r="E135" s="1" t="s">
         <v>63</v>
       </c>
-      <c r="F135" t="s">
-        <v>0</v>
-      </c>
-      <c r="G135" t="s">
+      <c r="F135" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="G135" s="1" t="s">
         <v>485</v>
       </c>
-      <c r="H135" t="s">
+      <c r="H135" s="1" t="s">
         <v>70</v>
+      </c>
+    </row>
+    <row r="136" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A136" s="1">
+        <v>267004831</v>
+      </c>
+      <c r="C136" s="1" t="s">
+        <v>103</v>
+      </c>
+      <c r="D136" s="1">
+        <v>267004831</v>
+      </c>
+      <c r="H136" s="1" t="s">
+        <v>489</v>
+      </c>
+    </row>
+    <row r="137" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A137" s="1">
+        <v>267004842</v>
+      </c>
+      <c r="C137" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="D137" s="1">
+        <v>267004842</v>
+      </c>
+      <c r="H137" s="1" t="s">
+        <v>489</v>
+      </c>
+    </row>
+    <row r="138" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A138" s="1">
+        <v>267004847</v>
+      </c>
+      <c r="C138" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="D138" s="1">
+        <v>267004847</v>
+      </c>
+      <c r="H138" s="1" t="s">
+        <v>489</v>
+      </c>
+    </row>
+    <row r="139" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A139" s="1">
+        <v>267004845</v>
+      </c>
+      <c r="C139" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="D139" s="1">
+        <v>267004845</v>
+      </c>
+      <c r="H139" s="1" t="s">
+        <v>489</v>
       </c>
     </row>
   </sheetData>

--- a/1.xlsx
+++ b/1.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="\\wh.local\fs\UserProfile_TSSWH19\_TSSWH19_redirected_folders\HunyaCs1\Desktop\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7307698A-32A1-478D-97DB-F47AD4138434}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CAE5A61B-8D49-4279-8EEE-F65EE7D456C2}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="0" windowWidth="22260" windowHeight="12648" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1484" uniqueCount="743">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1463" uniqueCount="733">
   <si>
     <t>BUDAPEST</t>
   </si>
@@ -1752,12 +1752,6 @@
     <t>ÖRKÉNY</t>
   </si>
   <si>
-    <t>NFD6-03-28-VZP9-1</t>
-  </si>
-  <si>
-    <t>NFD6-03-28-VZP9</t>
-  </si>
-  <si>
     <t>202604072600755201</t>
   </si>
   <si>
@@ -1995,18 +1989,6 @@
     <t>NFD6-04-04-P3ZC</t>
   </si>
   <si>
-    <t>NFD6-04-04-PBDP-1</t>
-  </si>
-  <si>
-    <t>NFD6-04-04-PBDP</t>
-  </si>
-  <si>
-    <t>1183</t>
-  </si>
-  <si>
-    <t>Ráday Gedeon utca</t>
-  </si>
-  <si>
     <t>202604072600794401</t>
   </si>
   <si>
@@ -2053,18 +2035,6 @@
   </si>
   <si>
     <t>NFD6-04-04-Y2JK</t>
-  </si>
-  <si>
-    <t>NFD6-04-07-DY48-1</t>
-  </si>
-  <si>
-    <t>NFD6-04-07-DY48</t>
-  </si>
-  <si>
-    <t>1194</t>
-  </si>
-  <si>
-    <t>Hofherr Albert utca</t>
   </si>
   <si>
     <t>202603302600759401</t>
@@ -2575,7 +2545,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <sheetPr codeName="Munka1"/>
-  <dimension ref="A1:H212"/>
+  <dimension ref="A1:H209"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="24.88671875" bestFit="1" customWidth="1"/>
@@ -5974,19 +5944,19 @@
         <v>574</v>
       </c>
       <c r="C148" t="s">
-        <v>29</v>
+        <v>66</v>
       </c>
       <c r="D148" t="s">
         <v>575</v>
       </c>
       <c r="E148" t="s">
-        <v>456</v>
+        <v>576</v>
       </c>
       <c r="F148" t="s">
         <v>0</v>
       </c>
       <c r="G148" t="s">
-        <v>482</v>
+        <v>577</v>
       </c>
       <c r="H148" t="s">
         <v>4</v>
@@ -5994,22 +5964,22 @@
     </row>
     <row r="149" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A149" t="s">
-        <v>576</v>
+        <v>578</v>
       </c>
       <c r="C149" t="s">
-        <v>66</v>
+        <v>5</v>
       </c>
       <c r="D149" t="s">
-        <v>577</v>
+        <v>579</v>
       </c>
       <c r="E149" t="s">
-        <v>578</v>
+        <v>12</v>
       </c>
       <c r="F149" t="s">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="G149" t="s">
-        <v>579</v>
+        <v>580</v>
       </c>
       <c r="H149" t="s">
         <v>4</v>
@@ -6017,22 +5987,22 @@
     </row>
     <row r="150" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A150" t="s">
-        <v>580</v>
+        <v>581</v>
       </c>
       <c r="C150" t="s">
         <v>5</v>
       </c>
       <c r="D150" t="s">
-        <v>581</v>
+        <v>582</v>
       </c>
       <c r="E150" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="F150" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="G150" t="s">
-        <v>582</v>
+        <v>583</v>
       </c>
       <c r="H150" t="s">
         <v>4</v>
@@ -6040,22 +6010,22 @@
     </row>
     <row r="151" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A151" t="s">
-        <v>583</v>
+        <v>584</v>
       </c>
       <c r="C151" t="s">
-        <v>5</v>
+        <v>26</v>
       </c>
       <c r="D151" t="s">
-        <v>584</v>
+        <v>585</v>
       </c>
       <c r="E151" t="s">
-        <v>10</v>
+        <v>192</v>
       </c>
       <c r="F151" t="s">
-        <v>11</v>
+        <v>0</v>
       </c>
       <c r="G151" t="s">
-        <v>585</v>
+        <v>586</v>
       </c>
       <c r="H151" t="s">
         <v>4</v>
@@ -6063,22 +6033,22 @@
     </row>
     <row r="152" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A152" t="s">
-        <v>586</v>
+        <v>587</v>
       </c>
       <c r="C152" t="s">
-        <v>26</v>
+        <v>66</v>
       </c>
       <c r="D152" t="s">
-        <v>587</v>
+        <v>588</v>
       </c>
       <c r="E152" t="s">
-        <v>192</v>
+        <v>589</v>
       </c>
       <c r="F152" t="s">
-        <v>0</v>
+        <v>590</v>
       </c>
       <c r="G152" t="s">
-        <v>588</v>
+        <v>591</v>
       </c>
       <c r="H152" t="s">
         <v>4</v>
@@ -6086,22 +6056,22 @@
     </row>
     <row r="153" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A153" t="s">
-        <v>589</v>
+        <v>592</v>
       </c>
       <c r="C153" t="s">
         <v>66</v>
       </c>
       <c r="D153" t="s">
+        <v>588</v>
+      </c>
+      <c r="E153" t="s">
+        <v>589</v>
+      </c>
+      <c r="F153" t="s">
         <v>590</v>
       </c>
-      <c r="E153" t="s">
+      <c r="G153" t="s">
         <v>591</v>
-      </c>
-      <c r="F153" t="s">
-        <v>592</v>
-      </c>
-      <c r="G153" t="s">
-        <v>593</v>
       </c>
       <c r="H153" t="s">
         <v>4</v>
@@ -6109,22 +6079,22 @@
     </row>
     <row r="154" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A154" t="s">
+        <v>593</v>
+      </c>
+      <c r="C154" t="s">
+        <v>400</v>
+      </c>
+      <c r="D154" t="s">
         <v>594</v>
       </c>
-      <c r="C154" t="s">
-        <v>66</v>
-      </c>
-      <c r="D154" t="s">
-        <v>590</v>
-      </c>
       <c r="E154" t="s">
-        <v>591</v>
+        <v>595</v>
       </c>
       <c r="F154" t="s">
-        <v>592</v>
+        <v>596</v>
       </c>
       <c r="G154" t="s">
-        <v>593</v>
+        <v>597</v>
       </c>
       <c r="H154" t="s">
         <v>4</v>
@@ -6132,22 +6102,22 @@
     </row>
     <row r="155" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A155" t="s">
-        <v>595</v>
+        <v>598</v>
       </c>
       <c r="C155" t="s">
-        <v>400</v>
+        <v>24</v>
       </c>
       <c r="D155" t="s">
-        <v>596</v>
+        <v>599</v>
       </c>
       <c r="E155" t="s">
-        <v>597</v>
+        <v>533</v>
       </c>
       <c r="F155" t="s">
-        <v>598</v>
+        <v>534</v>
       </c>
       <c r="G155" t="s">
-        <v>599</v>
+        <v>600</v>
       </c>
       <c r="H155" t="s">
         <v>4</v>
@@ -6155,22 +6125,22 @@
     </row>
     <row r="156" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A156" t="s">
-        <v>600</v>
+        <v>601</v>
       </c>
       <c r="C156" t="s">
         <v>24</v>
       </c>
       <c r="D156" t="s">
-        <v>601</v>
+        <v>602</v>
       </c>
       <c r="E156" t="s">
-        <v>533</v>
+        <v>551</v>
       </c>
       <c r="F156" t="s">
-        <v>534</v>
+        <v>552</v>
       </c>
       <c r="G156" t="s">
-        <v>602</v>
+        <v>603</v>
       </c>
       <c r="H156" t="s">
         <v>4</v>
@@ -6178,22 +6148,22 @@
     </row>
     <row r="157" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A157" t="s">
-        <v>603</v>
+        <v>604</v>
       </c>
       <c r="C157" t="s">
-        <v>24</v>
+        <v>35</v>
       </c>
       <c r="D157" t="s">
-        <v>604</v>
+        <v>605</v>
       </c>
       <c r="E157" t="s">
-        <v>551</v>
+        <v>108</v>
       </c>
       <c r="F157" t="s">
-        <v>552</v>
+        <v>109</v>
       </c>
       <c r="G157" t="s">
-        <v>605</v>
+        <v>606</v>
       </c>
       <c r="H157" t="s">
         <v>4</v>
@@ -6201,22 +6171,22 @@
     </row>
     <row r="158" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A158" t="s">
-        <v>606</v>
+        <v>607</v>
       </c>
       <c r="C158" t="s">
-        <v>35</v>
+        <v>29</v>
       </c>
       <c r="D158" t="s">
-        <v>607</v>
+        <v>608</v>
       </c>
       <c r="E158" t="s">
-        <v>108</v>
+        <v>456</v>
       </c>
       <c r="F158" t="s">
-        <v>109</v>
+        <v>0</v>
       </c>
       <c r="G158" t="s">
-        <v>608</v>
+        <v>609</v>
       </c>
       <c r="H158" t="s">
         <v>4</v>
@@ -6224,22 +6194,22 @@
     </row>
     <row r="159" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A159" t="s">
-        <v>609</v>
+        <v>610</v>
       </c>
       <c r="C159" t="s">
-        <v>29</v>
+        <v>9</v>
       </c>
       <c r="D159" t="s">
-        <v>610</v>
+        <v>611</v>
       </c>
       <c r="E159" t="s">
-        <v>456</v>
+        <v>22</v>
       </c>
       <c r="F159" t="s">
-        <v>0</v>
+        <v>23</v>
       </c>
       <c r="G159" t="s">
-        <v>611</v>
+        <v>612</v>
       </c>
       <c r="H159" t="s">
         <v>4</v>
@@ -6247,13 +6217,13 @@
     </row>
     <row r="160" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A160" t="s">
-        <v>612</v>
+        <v>613</v>
       </c>
       <c r="C160" t="s">
         <v>9</v>
       </c>
       <c r="D160" t="s">
-        <v>613</v>
+        <v>611</v>
       </c>
       <c r="E160" t="s">
         <v>22</v>
@@ -6262,7 +6232,7 @@
         <v>23</v>
       </c>
       <c r="G160" t="s">
-        <v>614</v>
+        <v>612</v>
       </c>
       <c r="H160" t="s">
         <v>4</v>
@@ -6270,22 +6240,22 @@
     </row>
     <row r="161" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A161" t="s">
+        <v>614</v>
+      </c>
+      <c r="C161" t="s">
+        <v>25</v>
+      </c>
+      <c r="D161" t="s">
         <v>615</v>
       </c>
-      <c r="C161" t="s">
-        <v>9</v>
-      </c>
-      <c r="D161" t="s">
-        <v>613</v>
-      </c>
       <c r="E161" t="s">
-        <v>22</v>
+        <v>53</v>
       </c>
       <c r="F161" t="s">
-        <v>23</v>
+        <v>54</v>
       </c>
       <c r="G161" t="s">
-        <v>614</v>
+        <v>616</v>
       </c>
       <c r="H161" t="s">
         <v>4</v>
@@ -6293,22 +6263,22 @@
     </row>
     <row r="162" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A162" t="s">
-        <v>616</v>
+        <v>617</v>
       </c>
       <c r="C162" t="s">
-        <v>25</v>
+        <v>55</v>
       </c>
       <c r="D162" t="s">
-        <v>617</v>
+        <v>618</v>
       </c>
       <c r="E162" t="s">
-        <v>53</v>
+        <v>81</v>
       </c>
       <c r="F162" t="s">
-        <v>54</v>
+        <v>82</v>
       </c>
       <c r="G162" t="s">
-        <v>618</v>
+        <v>619</v>
       </c>
       <c r="H162" t="s">
         <v>4</v>
@@ -6316,22 +6286,22 @@
     </row>
     <row r="163" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A163" t="s">
-        <v>619</v>
+        <v>620</v>
       </c>
       <c r="C163" t="s">
-        <v>55</v>
+        <v>5</v>
       </c>
       <c r="D163" t="s">
-        <v>620</v>
+        <v>621</v>
       </c>
       <c r="E163" t="s">
-        <v>81</v>
+        <v>12</v>
       </c>
       <c r="F163" t="s">
-        <v>82</v>
+        <v>13</v>
       </c>
       <c r="G163" t="s">
-        <v>621</v>
+        <v>622</v>
       </c>
       <c r="H163" t="s">
         <v>4</v>
@@ -6339,22 +6309,22 @@
     </row>
     <row r="164" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A164" t="s">
-        <v>622</v>
+        <v>623</v>
       </c>
       <c r="C164" t="s">
-        <v>5</v>
+        <v>24</v>
       </c>
       <c r="D164" t="s">
-        <v>623</v>
+        <v>624</v>
       </c>
       <c r="E164" t="s">
-        <v>12</v>
+        <v>257</v>
       </c>
       <c r="F164" t="s">
-        <v>13</v>
+        <v>0</v>
       </c>
       <c r="G164" t="s">
-        <v>624</v>
+        <v>625</v>
       </c>
       <c r="H164" t="s">
         <v>4</v>
@@ -6362,22 +6332,22 @@
     </row>
     <row r="165" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A165" t="s">
-        <v>625</v>
+        <v>626</v>
       </c>
       <c r="C165" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="D165" t="s">
-        <v>626</v>
+        <v>627</v>
       </c>
       <c r="E165" t="s">
-        <v>257</v>
+        <v>71</v>
       </c>
       <c r="F165" t="s">
-        <v>0</v>
+        <v>72</v>
       </c>
       <c r="G165" t="s">
-        <v>627</v>
+        <v>628</v>
       </c>
       <c r="H165" t="s">
         <v>4</v>
@@ -6385,22 +6355,22 @@
     </row>
     <row r="166" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A166" t="s">
-        <v>628</v>
+        <v>629</v>
       </c>
       <c r="C166" t="s">
-        <v>25</v>
+        <v>66</v>
       </c>
       <c r="D166" t="s">
-        <v>629</v>
+        <v>630</v>
       </c>
       <c r="E166" t="s">
-        <v>71</v>
+        <v>89</v>
       </c>
       <c r="F166" t="s">
-        <v>72</v>
+        <v>90</v>
       </c>
       <c r="G166" t="s">
-        <v>630</v>
+        <v>631</v>
       </c>
       <c r="H166" t="s">
         <v>4</v>
@@ -6408,13 +6378,13 @@
     </row>
     <row r="167" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A167" t="s">
-        <v>631</v>
+        <v>632</v>
       </c>
       <c r="C167" t="s">
         <v>66</v>
       </c>
       <c r="D167" t="s">
-        <v>632</v>
+        <v>630</v>
       </c>
       <c r="E167" t="s">
         <v>89</v>
@@ -6423,7 +6393,7 @@
         <v>90</v>
       </c>
       <c r="G167" t="s">
-        <v>633</v>
+        <v>631</v>
       </c>
       <c r="H167" t="s">
         <v>4</v>
@@ -6431,22 +6401,22 @@
     </row>
     <row r="168" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A168" t="s">
+        <v>633</v>
+      </c>
+      <c r="C168" t="s">
+        <v>24</v>
+      </c>
+      <c r="D168" t="s">
         <v>634</v>
       </c>
-      <c r="C168" t="s">
-        <v>66</v>
-      </c>
-      <c r="D168" t="s">
-        <v>632</v>
-      </c>
       <c r="E168" t="s">
-        <v>89</v>
+        <v>635</v>
       </c>
       <c r="F168" t="s">
-        <v>90</v>
+        <v>636</v>
       </c>
       <c r="G168" t="s">
-        <v>633</v>
+        <v>134</v>
       </c>
       <c r="H168" t="s">
         <v>4</v>
@@ -6454,22 +6424,22 @@
     </row>
     <row r="169" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A169" t="s">
-        <v>635</v>
+        <v>637</v>
       </c>
       <c r="C169" t="s">
-        <v>24</v>
+        <v>2</v>
       </c>
       <c r="D169" t="s">
-        <v>636</v>
+        <v>638</v>
       </c>
       <c r="E169" t="s">
-        <v>637</v>
+        <v>36</v>
       </c>
       <c r="F169" t="s">
-        <v>638</v>
+        <v>0</v>
       </c>
       <c r="G169" t="s">
-        <v>134</v>
+        <v>77</v>
       </c>
       <c r="H169" t="s">
         <v>4</v>
@@ -6480,19 +6450,19 @@
         <v>639</v>
       </c>
       <c r="C170" t="s">
-        <v>2</v>
+        <v>9</v>
       </c>
       <c r="D170" t="s">
         <v>640</v>
       </c>
       <c r="E170" t="s">
-        <v>36</v>
+        <v>22</v>
       </c>
       <c r="F170" t="s">
-        <v>0</v>
+        <v>23</v>
       </c>
       <c r="G170" t="s">
-        <v>77</v>
+        <v>641</v>
       </c>
       <c r="H170" t="s">
         <v>4</v>
@@ -6500,13 +6470,13 @@
     </row>
     <row r="171" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A171" t="s">
-        <v>641</v>
+        <v>642</v>
       </c>
       <c r="C171" t="s">
         <v>9</v>
       </c>
       <c r="D171" t="s">
-        <v>642</v>
+        <v>640</v>
       </c>
       <c r="E171" t="s">
         <v>22</v>
@@ -6515,7 +6485,7 @@
         <v>23</v>
       </c>
       <c r="G171" t="s">
-        <v>643</v>
+        <v>641</v>
       </c>
       <c r="H171" t="s">
         <v>4</v>
@@ -6523,22 +6493,22 @@
     </row>
     <row r="172" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A172" t="s">
+        <v>643</v>
+      </c>
+      <c r="C172" t="s">
+        <v>6</v>
+      </c>
+      <c r="D172" t="s">
         <v>644</v>
       </c>
-      <c r="C172" t="s">
-        <v>9</v>
-      </c>
-      <c r="D172" t="s">
-        <v>642</v>
-      </c>
       <c r="E172" t="s">
-        <v>22</v>
+        <v>95</v>
       </c>
       <c r="F172" t="s">
-        <v>23</v>
+        <v>0</v>
       </c>
       <c r="G172" t="s">
-        <v>643</v>
+        <v>645</v>
       </c>
       <c r="H172" t="s">
         <v>4</v>
@@ -6546,13 +6516,13 @@
     </row>
     <row r="173" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A173" t="s">
-        <v>645</v>
+        <v>646</v>
       </c>
       <c r="C173" t="s">
         <v>6</v>
       </c>
       <c r="D173" t="s">
-        <v>646</v>
+        <v>644</v>
       </c>
       <c r="E173" t="s">
         <v>95</v>
@@ -6561,7 +6531,7 @@
         <v>0</v>
       </c>
       <c r="G173" t="s">
-        <v>647</v>
+        <v>645</v>
       </c>
       <c r="H173" t="s">
         <v>4</v>
@@ -6569,13 +6539,13 @@
     </row>
     <row r="174" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A174" t="s">
-        <v>648</v>
+        <v>647</v>
       </c>
       <c r="C174" t="s">
         <v>6</v>
       </c>
       <c r="D174" t="s">
-        <v>646</v>
+        <v>644</v>
       </c>
       <c r="E174" t="s">
         <v>95</v>
@@ -6584,7 +6554,7 @@
         <v>0</v>
       </c>
       <c r="G174" t="s">
-        <v>647</v>
+        <v>645</v>
       </c>
       <c r="H174" t="s">
         <v>4</v>
@@ -6592,13 +6562,13 @@
     </row>
     <row r="175" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A175" t="s">
-        <v>649</v>
+        <v>648</v>
       </c>
       <c r="C175" t="s">
         <v>6</v>
       </c>
       <c r="D175" t="s">
-        <v>646</v>
+        <v>644</v>
       </c>
       <c r="E175" t="s">
         <v>95</v>
@@ -6607,7 +6577,7 @@
         <v>0</v>
       </c>
       <c r="G175" t="s">
-        <v>647</v>
+        <v>645</v>
       </c>
       <c r="H175" t="s">
         <v>4</v>
@@ -6615,13 +6585,13 @@
     </row>
     <row r="176" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A176" t="s">
-        <v>650</v>
+        <v>649</v>
       </c>
       <c r="C176" t="s">
         <v>6</v>
       </c>
       <c r="D176" t="s">
-        <v>646</v>
+        <v>644</v>
       </c>
       <c r="E176" t="s">
         <v>95</v>
@@ -6630,7 +6600,7 @@
         <v>0</v>
       </c>
       <c r="G176" t="s">
-        <v>647</v>
+        <v>645</v>
       </c>
       <c r="H176" t="s">
         <v>4</v>
@@ -6638,13 +6608,13 @@
     </row>
     <row r="177" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A177" t="s">
-        <v>651</v>
+        <v>650</v>
       </c>
       <c r="C177" t="s">
         <v>6</v>
       </c>
       <c r="D177" t="s">
-        <v>646</v>
+        <v>644</v>
       </c>
       <c r="E177" t="s">
         <v>95</v>
@@ -6653,7 +6623,7 @@
         <v>0</v>
       </c>
       <c r="G177" t="s">
-        <v>647</v>
+        <v>645</v>
       </c>
       <c r="H177" t="s">
         <v>4</v>
@@ -6661,22 +6631,22 @@
     </row>
     <row r="178" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A178" t="s">
+        <v>651</v>
+      </c>
+      <c r="C178" t="s">
+        <v>35</v>
+      </c>
+      <c r="D178" t="s">
         <v>652</v>
       </c>
-      <c r="C178" t="s">
-        <v>6</v>
-      </c>
-      <c r="D178" t="s">
-        <v>646</v>
-      </c>
       <c r="E178" t="s">
-        <v>95</v>
+        <v>108</v>
       </c>
       <c r="F178" t="s">
-        <v>0</v>
+        <v>109</v>
       </c>
       <c r="G178" t="s">
-        <v>647</v>
+        <v>356</v>
       </c>
       <c r="H178" t="s">
         <v>4</v>
@@ -6687,19 +6657,19 @@
         <v>653</v>
       </c>
       <c r="C179" t="s">
-        <v>35</v>
+        <v>25</v>
       </c>
       <c r="D179" t="s">
         <v>654</v>
       </c>
       <c r="E179" t="s">
-        <v>108</v>
+        <v>71</v>
       </c>
       <c r="F179" t="s">
-        <v>109</v>
+        <v>72</v>
       </c>
       <c r="G179" t="s">
-        <v>356</v>
+        <v>501</v>
       </c>
       <c r="H179" t="s">
         <v>4</v>
@@ -6710,19 +6680,19 @@
         <v>655</v>
       </c>
       <c r="C180" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="D180" t="s">
         <v>656</v>
       </c>
       <c r="E180" t="s">
+        <v>381</v>
+      </c>
+      <c r="F180" t="s">
+        <v>0</v>
+      </c>
+      <c r="G180" t="s">
         <v>657</v>
-      </c>
-      <c r="F180" t="s">
-        <v>0</v>
-      </c>
-      <c r="G180" t="s">
-        <v>658</v>
       </c>
       <c r="H180" t="s">
         <v>4</v>
@@ -6730,22 +6700,22 @@
     </row>
     <row r="181" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A181" t="s">
+        <v>658</v>
+      </c>
+      <c r="C181" t="s">
+        <v>35</v>
+      </c>
+      <c r="D181" t="s">
         <v>659</v>
       </c>
-      <c r="C181" t="s">
-        <v>25</v>
-      </c>
-      <c r="D181" t="s">
+      <c r="E181" t="s">
         <v>660</v>
       </c>
-      <c r="E181" t="s">
-        <v>71</v>
-      </c>
       <c r="F181" t="s">
-        <v>72</v>
+        <v>661</v>
       </c>
       <c r="G181" t="s">
-        <v>501</v>
+        <v>662</v>
       </c>
       <c r="H181" t="s">
         <v>4</v>
@@ -6753,22 +6723,22 @@
     </row>
     <row r="182" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A182" t="s">
+        <v>663</v>
+      </c>
+      <c r="C182" t="s">
+        <v>35</v>
+      </c>
+      <c r="D182" t="s">
+        <v>659</v>
+      </c>
+      <c r="E182" t="s">
+        <v>660</v>
+      </c>
+      <c r="F182" t="s">
         <v>661</v>
       </c>
-      <c r="C182" t="s">
-        <v>5</v>
-      </c>
-      <c r="D182" t="s">
+      <c r="G182" t="s">
         <v>662</v>
-      </c>
-      <c r="E182" t="s">
-        <v>381</v>
-      </c>
-      <c r="F182" t="s">
-        <v>0</v>
-      </c>
-      <c r="G182" t="s">
-        <v>663</v>
       </c>
       <c r="H182" t="s">
         <v>4</v>
@@ -6779,19 +6749,19 @@
         <v>664</v>
       </c>
       <c r="C183" t="s">
-        <v>35</v>
+        <v>55</v>
       </c>
       <c r="D183" t="s">
         <v>665</v>
       </c>
       <c r="E183" t="s">
+        <v>564</v>
+      </c>
+      <c r="F183" t="s">
+        <v>565</v>
+      </c>
+      <c r="G183" t="s">
         <v>666</v>
-      </c>
-      <c r="F183" t="s">
-        <v>667</v>
-      </c>
-      <c r="G183" t="s">
-        <v>668</v>
       </c>
       <c r="H183" t="s">
         <v>4</v>
@@ -6799,22 +6769,22 @@
     </row>
     <row r="184" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A184" t="s">
-        <v>669</v>
+        <v>667</v>
       </c>
       <c r="C184" t="s">
-        <v>35</v>
+        <v>129</v>
       </c>
       <c r="D184" t="s">
-        <v>665</v>
+        <v>668</v>
       </c>
       <c r="E184" t="s">
-        <v>666</v>
+        <v>47</v>
       </c>
       <c r="F184" t="s">
-        <v>667</v>
+        <v>0</v>
       </c>
       <c r="G184" t="s">
-        <v>668</v>
+        <v>48</v>
       </c>
       <c r="H184" t="s">
         <v>4</v>
@@ -6822,22 +6792,22 @@
     </row>
     <row r="185" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A185" t="s">
+        <v>669</v>
+      </c>
+      <c r="C185" t="s">
+        <v>66</v>
+      </c>
+      <c r="D185" t="s">
         <v>670</v>
       </c>
-      <c r="C185" t="s">
-        <v>55</v>
-      </c>
-      <c r="D185" t="s">
+      <c r="E185" t="s">
         <v>671</v>
       </c>
-      <c r="E185" t="s">
-        <v>564</v>
-      </c>
       <c r="F185" t="s">
-        <v>565</v>
+        <v>672</v>
       </c>
       <c r="G185" t="s">
-        <v>672</v>
+        <v>673</v>
       </c>
       <c r="H185" t="s">
         <v>4</v>
@@ -6845,22 +6815,22 @@
     </row>
     <row r="186" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A186" t="s">
-        <v>673</v>
+        <v>674</v>
       </c>
       <c r="C186" t="s">
-        <v>129</v>
+        <v>66</v>
       </c>
       <c r="D186" t="s">
-        <v>674</v>
+        <v>675</v>
       </c>
       <c r="E186" t="s">
-        <v>47</v>
+        <v>179</v>
       </c>
       <c r="F186" t="s">
         <v>0</v>
       </c>
       <c r="G186" t="s">
-        <v>48</v>
+        <v>676</v>
       </c>
       <c r="H186" t="s">
         <v>4</v>
@@ -6868,22 +6838,22 @@
     </row>
     <row r="187" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A187" t="s">
-        <v>675</v>
+        <v>677</v>
       </c>
       <c r="C187" t="s">
-        <v>8</v>
+        <v>66</v>
       </c>
       <c r="D187" t="s">
-        <v>676</v>
+        <v>678</v>
       </c>
       <c r="E187" t="s">
-        <v>677</v>
+        <v>89</v>
       </c>
       <c r="F187" t="s">
-        <v>0</v>
+        <v>90</v>
       </c>
       <c r="G187" t="s">
-        <v>678</v>
+        <v>679</v>
       </c>
       <c r="H187" t="s">
         <v>4</v>
@@ -6891,22 +6861,22 @@
     </row>
     <row r="188" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A188" t="s">
-        <v>679</v>
+        <v>680</v>
       </c>
       <c r="C188" t="s">
         <v>66</v>
       </c>
       <c r="D188" t="s">
-        <v>680</v>
+        <v>678</v>
       </c>
       <c r="E188" t="s">
-        <v>681</v>
+        <v>89</v>
       </c>
       <c r="F188" t="s">
-        <v>682</v>
+        <v>90</v>
       </c>
       <c r="G188" t="s">
-        <v>683</v>
+        <v>679</v>
       </c>
       <c r="H188" t="s">
         <v>4</v>
@@ -6914,22 +6884,22 @@
     </row>
     <row r="189" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A189" t="s">
-        <v>684</v>
+        <v>681</v>
       </c>
       <c r="C189" t="s">
         <v>66</v>
       </c>
       <c r="D189" t="s">
-        <v>685</v>
+        <v>678</v>
       </c>
       <c r="E189" t="s">
-        <v>179</v>
+        <v>89</v>
       </c>
       <c r="F189" t="s">
-        <v>0</v>
+        <v>90</v>
       </c>
       <c r="G189" t="s">
-        <v>686</v>
+        <v>679</v>
       </c>
       <c r="H189" t="s">
         <v>4</v>
@@ -6937,13 +6907,13 @@
     </row>
     <row r="190" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A190" t="s">
-        <v>687</v>
+        <v>682</v>
       </c>
       <c r="C190" t="s">
         <v>66</v>
       </c>
       <c r="D190" t="s">
-        <v>688</v>
+        <v>678</v>
       </c>
       <c r="E190" t="s">
         <v>89</v>
@@ -6952,7 +6922,7 @@
         <v>90</v>
       </c>
       <c r="G190" t="s">
-        <v>689</v>
+        <v>679</v>
       </c>
       <c r="H190" t="s">
         <v>4</v>
@@ -6960,13 +6930,13 @@
     </row>
     <row r="191" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A191" t="s">
-        <v>690</v>
+        <v>683</v>
       </c>
       <c r="C191" t="s">
         <v>66</v>
       </c>
       <c r="D191" t="s">
-        <v>688</v>
+        <v>678</v>
       </c>
       <c r="E191" t="s">
         <v>89</v>
@@ -6975,7 +6945,7 @@
         <v>90</v>
       </c>
       <c r="G191" t="s">
-        <v>689</v>
+        <v>679</v>
       </c>
       <c r="H191" t="s">
         <v>4</v>
@@ -6983,13 +6953,13 @@
     </row>
     <row r="192" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A192" t="s">
-        <v>691</v>
+        <v>684</v>
       </c>
       <c r="C192" t="s">
         <v>66</v>
       </c>
       <c r="D192" t="s">
-        <v>688</v>
+        <v>678</v>
       </c>
       <c r="E192" t="s">
         <v>89</v>
@@ -6998,7 +6968,7 @@
         <v>90</v>
       </c>
       <c r="G192" t="s">
-        <v>689</v>
+        <v>679</v>
       </c>
       <c r="H192" t="s">
         <v>4</v>
@@ -7006,22 +6976,22 @@
     </row>
     <row r="193" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A193" t="s">
-        <v>692</v>
+        <v>685</v>
       </c>
       <c r="C193" t="s">
-        <v>66</v>
+        <v>25</v>
       </c>
       <c r="D193" t="s">
-        <v>688</v>
+        <v>686</v>
       </c>
       <c r="E193" t="s">
-        <v>89</v>
+        <v>67</v>
       </c>
       <c r="F193" t="s">
-        <v>90</v>
+        <v>0</v>
       </c>
       <c r="G193" t="s">
-        <v>689</v>
+        <v>687</v>
       </c>
       <c r="H193" t="s">
         <v>4</v>
@@ -7029,22 +6999,22 @@
     </row>
     <row r="194" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A194" t="s">
-        <v>693</v>
+        <v>688</v>
       </c>
       <c r="C194" t="s">
-        <v>66</v>
+        <v>55</v>
       </c>
       <c r="D194" t="s">
-        <v>688</v>
+        <v>689</v>
       </c>
       <c r="E194" t="s">
-        <v>89</v>
+        <v>85</v>
       </c>
       <c r="F194" t="s">
-        <v>90</v>
+        <v>86</v>
       </c>
       <c r="G194" t="s">
-        <v>689</v>
+        <v>167</v>
       </c>
       <c r="H194" t="s">
         <v>4</v>
@@ -7052,22 +7022,22 @@
     </row>
     <row r="195" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A195" t="s">
-        <v>694</v>
+        <v>690</v>
       </c>
       <c r="C195" t="s">
-        <v>66</v>
+        <v>55</v>
       </c>
       <c r="D195" t="s">
-        <v>688</v>
+        <v>689</v>
       </c>
       <c r="E195" t="s">
-        <v>89</v>
+        <v>85</v>
       </c>
       <c r="F195" t="s">
-        <v>90</v>
+        <v>86</v>
       </c>
       <c r="G195" t="s">
-        <v>689</v>
+        <v>167</v>
       </c>
       <c r="H195" t="s">
         <v>4</v>
@@ -7075,22 +7045,22 @@
     </row>
     <row r="196" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A196" t="s">
-        <v>695</v>
+        <v>691</v>
       </c>
       <c r="C196" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="D196" t="s">
-        <v>696</v>
+        <v>692</v>
       </c>
       <c r="E196" t="s">
-        <v>67</v>
+        <v>551</v>
       </c>
       <c r="F196" t="s">
-        <v>0</v>
+        <v>552</v>
       </c>
       <c r="G196" t="s">
-        <v>697</v>
+        <v>693</v>
       </c>
       <c r="H196" t="s">
         <v>4</v>
@@ -7098,22 +7068,22 @@
     </row>
     <row r="197" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A197" t="s">
-        <v>698</v>
+        <v>694</v>
       </c>
       <c r="C197" t="s">
-        <v>55</v>
+        <v>35</v>
       </c>
       <c r="D197" t="s">
-        <v>699</v>
+        <v>695</v>
       </c>
       <c r="E197" t="s">
-        <v>85</v>
+        <v>696</v>
       </c>
       <c r="F197" t="s">
-        <v>86</v>
+        <v>697</v>
       </c>
       <c r="G197" t="s">
-        <v>167</v>
+        <v>298</v>
       </c>
       <c r="H197" t="s">
         <v>4</v>
@@ -7121,22 +7091,22 @@
     </row>
     <row r="198" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A198" t="s">
-        <v>700</v>
+        <v>698</v>
       </c>
       <c r="C198" t="s">
-        <v>55</v>
+        <v>29</v>
       </c>
       <c r="D198" t="s">
         <v>699</v>
       </c>
       <c r="E198" t="s">
-        <v>85</v>
+        <v>104</v>
       </c>
       <c r="F198" t="s">
-        <v>86</v>
+        <v>0</v>
       </c>
       <c r="G198" t="s">
-        <v>167</v>
+        <v>700</v>
       </c>
       <c r="H198" t="s">
         <v>4</v>
@@ -7147,19 +7117,19 @@
         <v>701</v>
       </c>
       <c r="C199" t="s">
-        <v>24</v>
+        <v>66</v>
       </c>
       <c r="D199" t="s">
         <v>702</v>
       </c>
       <c r="E199" t="s">
-        <v>551</v>
+        <v>703</v>
       </c>
       <c r="F199" t="s">
-        <v>552</v>
+        <v>0</v>
       </c>
       <c r="G199" t="s">
-        <v>703</v>
+        <v>365</v>
       </c>
       <c r="H199" t="s">
         <v>4</v>
@@ -7170,19 +7140,19 @@
         <v>704</v>
       </c>
       <c r="C200" t="s">
-        <v>35</v>
+        <v>6</v>
       </c>
       <c r="D200" t="s">
         <v>705</v>
       </c>
       <c r="E200" t="s">
+        <v>84</v>
+      </c>
+      <c r="F200" t="s">
+        <v>0</v>
+      </c>
+      <c r="G200" t="s">
         <v>706</v>
-      </c>
-      <c r="F200" t="s">
-        <v>707</v>
-      </c>
-      <c r="G200" t="s">
-        <v>298</v>
       </c>
       <c r="H200" t="s">
         <v>4</v>
@@ -7190,22 +7160,22 @@
     </row>
     <row r="201" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A201" t="s">
-        <v>708</v>
+        <v>707</v>
       </c>
       <c r="C201" t="s">
         <v>29</v>
       </c>
       <c r="D201" t="s">
-        <v>709</v>
+        <v>708</v>
       </c>
       <c r="E201" t="s">
-        <v>104</v>
+        <v>30</v>
       </c>
       <c r="F201" t="s">
         <v>0</v>
       </c>
       <c r="G201" t="s">
-        <v>710</v>
+        <v>91</v>
       </c>
       <c r="H201" t="s">
         <v>4</v>
@@ -7213,22 +7183,22 @@
     </row>
     <row r="202" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A202" t="s">
+        <v>709</v>
+      </c>
+      <c r="C202" t="s">
+        <v>6</v>
+      </c>
+      <c r="D202" t="s">
+        <v>710</v>
+      </c>
+      <c r="E202" t="s">
+        <v>31</v>
+      </c>
+      <c r="F202" t="s">
+        <v>32</v>
+      </c>
+      <c r="G202" t="s">
         <v>711</v>
-      </c>
-      <c r="C202" t="s">
-        <v>66</v>
-      </c>
-      <c r="D202" t="s">
-        <v>712</v>
-      </c>
-      <c r="E202" t="s">
-        <v>713</v>
-      </c>
-      <c r="F202" t="s">
-        <v>0</v>
-      </c>
-      <c r="G202" t="s">
-        <v>365</v>
       </c>
       <c r="H202" t="s">
         <v>4</v>
@@ -7236,22 +7206,22 @@
     </row>
     <row r="203" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A203" t="s">
+        <v>712</v>
+      </c>
+      <c r="C203" t="s">
+        <v>400</v>
+      </c>
+      <c r="D203" t="s">
+        <v>713</v>
+      </c>
+      <c r="E203" t="s">
+        <v>402</v>
+      </c>
+      <c r="F203" t="s">
         <v>714</v>
       </c>
-      <c r="C203" t="s">
-        <v>6</v>
-      </c>
-      <c r="D203" t="s">
+      <c r="G203" t="s">
         <v>715</v>
-      </c>
-      <c r="E203" t="s">
-        <v>84</v>
-      </c>
-      <c r="F203" t="s">
-        <v>0</v>
-      </c>
-      <c r="G203" t="s">
-        <v>716</v>
       </c>
       <c r="H203" t="s">
         <v>4</v>
@@ -7259,22 +7229,22 @@
     </row>
     <row r="204" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A204" t="s">
+        <v>716</v>
+      </c>
+      <c r="C204" t="s">
+        <v>35</v>
+      </c>
+      <c r="D204" t="s">
         <v>717</v>
       </c>
-      <c r="C204" t="s">
-        <v>29</v>
-      </c>
-      <c r="D204" t="s">
+      <c r="E204" t="s">
+        <v>108</v>
+      </c>
+      <c r="F204" t="s">
+        <v>109</v>
+      </c>
+      <c r="G204" t="s">
         <v>718</v>
-      </c>
-      <c r="E204" t="s">
-        <v>30</v>
-      </c>
-      <c r="F204" t="s">
-        <v>0</v>
-      </c>
-      <c r="G204" t="s">
-        <v>91</v>
       </c>
       <c r="H204" t="s">
         <v>4</v>
@@ -7285,19 +7255,19 @@
         <v>719</v>
       </c>
       <c r="C205" t="s">
-        <v>6</v>
+        <v>98</v>
       </c>
       <c r="D205" t="s">
         <v>720</v>
       </c>
       <c r="E205" t="s">
-        <v>31</v>
+        <v>721</v>
       </c>
       <c r="F205" t="s">
-        <v>32</v>
+        <v>0</v>
       </c>
       <c r="G205" t="s">
-        <v>721</v>
+        <v>722</v>
       </c>
       <c r="H205" t="s">
         <v>4</v>
@@ -7305,19 +7275,19 @@
     </row>
     <row r="206" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A206" t="s">
-        <v>722</v>
+        <v>723</v>
       </c>
       <c r="C206" t="s">
         <v>400</v>
       </c>
       <c r="D206" t="s">
-        <v>723</v>
+        <v>724</v>
       </c>
       <c r="E206" t="s">
-        <v>402</v>
+        <v>415</v>
       </c>
       <c r="F206" t="s">
-        <v>724</v>
+        <v>416</v>
       </c>
       <c r="G206" t="s">
         <v>725</v>
@@ -7331,16 +7301,16 @@
         <v>726</v>
       </c>
       <c r="C207" t="s">
-        <v>35</v>
+        <v>8</v>
       </c>
       <c r="D207" t="s">
         <v>727</v>
       </c>
       <c r="E207" t="s">
-        <v>108</v>
+        <v>94</v>
       </c>
       <c r="F207" t="s">
-        <v>109</v>
+        <v>0</v>
       </c>
       <c r="G207" t="s">
         <v>728</v>
@@ -7354,19 +7324,19 @@
         <v>729</v>
       </c>
       <c r="C208" t="s">
-        <v>98</v>
+        <v>5</v>
       </c>
       <c r="D208" t="s">
         <v>730</v>
       </c>
       <c r="E208" t="s">
+        <v>163</v>
+      </c>
+      <c r="F208" t="s">
+        <v>0</v>
+      </c>
+      <c r="G208" t="s">
         <v>731</v>
-      </c>
-      <c r="F208" t="s">
-        <v>0</v>
-      </c>
-      <c r="G208" t="s">
-        <v>732</v>
       </c>
       <c r="H208" t="s">
         <v>4</v>
@@ -7374,93 +7344,24 @@
     </row>
     <row r="209" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A209" t="s">
-        <v>733</v>
+        <v>732</v>
       </c>
       <c r="C209" t="s">
-        <v>400</v>
+        <v>5</v>
       </c>
       <c r="D209" t="s">
-        <v>734</v>
+        <v>730</v>
       </c>
       <c r="E209" t="s">
-        <v>415</v>
+        <v>163</v>
       </c>
       <c r="F209" t="s">
-        <v>416</v>
+        <v>0</v>
       </c>
       <c r="G209" t="s">
-        <v>735</v>
+        <v>731</v>
       </c>
       <c r="H209" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="210" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A210" t="s">
-        <v>736</v>
-      </c>
-      <c r="C210" t="s">
-        <v>8</v>
-      </c>
-      <c r="D210" t="s">
-        <v>737</v>
-      </c>
-      <c r="E210" t="s">
-        <v>94</v>
-      </c>
-      <c r="F210" t="s">
-        <v>0</v>
-      </c>
-      <c r="G210" t="s">
-        <v>738</v>
-      </c>
-      <c r="H210" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="211" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A211" t="s">
-        <v>739</v>
-      </c>
-      <c r="C211" t="s">
-        <v>5</v>
-      </c>
-      <c r="D211" t="s">
-        <v>740</v>
-      </c>
-      <c r="E211" t="s">
-        <v>163</v>
-      </c>
-      <c r="F211" t="s">
-        <v>0</v>
-      </c>
-      <c r="G211" t="s">
-        <v>741</v>
-      </c>
-      <c r="H211" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="212" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A212" t="s">
-        <v>742</v>
-      </c>
-      <c r="C212" t="s">
-        <v>5</v>
-      </c>
-      <c r="D212" t="s">
-        <v>740</v>
-      </c>
-      <c r="E212" t="s">
-        <v>163</v>
-      </c>
-      <c r="F212" t="s">
-        <v>0</v>
-      </c>
-      <c r="G212" t="s">
-        <v>741</v>
-      </c>
-      <c r="H212" t="s">
         <v>4</v>
       </c>
     </row>

--- a/1.xlsx
+++ b/1.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="\\wh.local\fs\UserProfile_TSSWH19\_TSSWH19_redirected_folders\HunyaCs1\Desktop\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B5518AD2-EEC1-4EDE-AE9C-99B13CEC3D80}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8FB141C9-2047-4443-BDFD-FD9EC7B32E52}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="0" windowWidth="22260" windowHeight="12648" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1106" uniqueCount="583">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1118" uniqueCount="586">
   <si>
     <t>BUDAPEST</t>
   </si>
@@ -1777,6 +1777,15 @@
   </si>
   <si>
     <t>SZ2026138667/2</t>
+  </si>
+  <si>
+    <t>NFD6-03-31-ESM8/XD</t>
+  </si>
+  <si>
+    <t>NFD6-04-02-6HC5</t>
+  </si>
+  <si>
+    <t>AUCHAN_ÁRUHÁZI</t>
   </si>
 </sst>
 </file>
@@ -2095,7 +2104,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <sheetPr codeName="Munka1"/>
-  <dimension ref="A1:H158"/>
+  <dimension ref="A1:H161"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="24.88671875" bestFit="1" customWidth="1"/>
@@ -5742,6 +5751,48 @@
         <v>581</v>
       </c>
     </row>
+    <row r="159" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A159" t="s">
+        <v>583</v>
+      </c>
+      <c r="C159" t="s">
+        <v>21</v>
+      </c>
+      <c r="D159" t="s">
+        <v>583</v>
+      </c>
+      <c r="H159" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="160" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A160" t="s">
+        <v>583</v>
+      </c>
+      <c r="C160" t="s">
+        <v>21</v>
+      </c>
+      <c r="D160" t="s">
+        <v>583</v>
+      </c>
+      <c r="H160" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="161" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A161" t="s">
+        <v>584</v>
+      </c>
+      <c r="C161" t="s">
+        <v>2</v>
+      </c>
+      <c r="D161" t="s">
+        <v>584</v>
+      </c>
+      <c r="H161" t="s">
+        <v>585</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>

--- a/1.xlsx
+++ b/1.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="\\wh.local\fs\UserProfile_TSSWH19\_TSSWH19_redirected_folders\HunyaCs1\Desktop\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D0FFEF37-8BFF-4FB9-9032-FE634C957451}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5F516B4F-CF4C-4C4F-A22B-2B0F48BE181B}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="0" windowWidth="22260" windowHeight="12648" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="959" uniqueCount="485">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="952" uniqueCount="483">
   <si>
     <t>BUDAPEST</t>
   </si>
@@ -1453,12 +1453,6 @@
   </si>
   <si>
     <t>Kőrösi Sándor utca</t>
-  </si>
-  <si>
-    <t>NFD6-04-09-P36M-1</t>
-  </si>
-  <si>
-    <t>NFD6-04-09-P36M</t>
   </si>
   <si>
     <t>202604072600813302</t>
@@ -1801,7 +1795,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <sheetPr codeName="Munka1"/>
-  <dimension ref="A1:H137"/>
+  <dimension ref="A1:H136"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="24.88671875" bestFit="1" customWidth="1"/>
@@ -4832,19 +4826,19 @@
         <v>475</v>
       </c>
       <c r="C132" t="s">
-        <v>37</v>
+        <v>25</v>
       </c>
       <c r="D132" t="s">
         <v>476</v>
       </c>
       <c r="E132" t="s">
-        <v>47</v>
+        <v>57</v>
       </c>
       <c r="F132" t="s">
-        <v>0</v>
+        <v>58</v>
       </c>
       <c r="G132" t="s">
-        <v>138</v>
+        <v>477</v>
       </c>
       <c r="H132" t="s">
         <v>4</v>
@@ -4852,13 +4846,13 @@
     </row>
     <row r="133" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A133" t="s">
-        <v>477</v>
+        <v>478</v>
       </c>
       <c r="C133" t="s">
         <v>25</v>
       </c>
       <c r="D133" t="s">
-        <v>478</v>
+        <v>476</v>
       </c>
       <c r="E133" t="s">
         <v>57</v>
@@ -4867,7 +4861,7 @@
         <v>58</v>
       </c>
       <c r="G133" t="s">
-        <v>479</v>
+        <v>477</v>
       </c>
       <c r="H133" t="s">
         <v>4</v>
@@ -4875,22 +4869,22 @@
     </row>
     <row r="134" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A134" t="s">
-        <v>480</v>
+        <v>82</v>
       </c>
       <c r="C134" t="s">
-        <v>25</v>
+        <v>2</v>
       </c>
       <c r="D134" t="s">
-        <v>478</v>
+        <v>83</v>
       </c>
       <c r="E134" t="s">
-        <v>57</v>
+        <v>26</v>
       </c>
       <c r="F134" t="s">
-        <v>58</v>
+        <v>0</v>
       </c>
       <c r="G134" t="s">
-        <v>479</v>
+        <v>84</v>
       </c>
       <c r="H134" t="s">
         <v>4</v>
@@ -4898,22 +4892,22 @@
     </row>
     <row r="135" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A135" t="s">
-        <v>82</v>
+        <v>479</v>
       </c>
       <c r="C135" t="s">
-        <v>2</v>
+        <v>44</v>
       </c>
       <c r="D135" t="s">
-        <v>83</v>
+        <v>480</v>
       </c>
       <c r="E135" t="s">
-        <v>26</v>
+        <v>196</v>
       </c>
       <c r="F135" t="s">
         <v>0</v>
       </c>
       <c r="G135" t="s">
-        <v>84</v>
+        <v>481</v>
       </c>
       <c r="H135" t="s">
         <v>4</v>
@@ -4921,13 +4915,13 @@
     </row>
     <row r="136" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A136" t="s">
-        <v>481</v>
+        <v>482</v>
       </c>
       <c r="C136" t="s">
         <v>44</v>
       </c>
       <c r="D136" t="s">
-        <v>482</v>
+        <v>480</v>
       </c>
       <c r="E136" t="s">
         <v>196</v>
@@ -4936,32 +4930,9 @@
         <v>0</v>
       </c>
       <c r="G136" t="s">
-        <v>483</v>
+        <v>481</v>
       </c>
       <c r="H136" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="137" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A137" t="s">
-        <v>484</v>
-      </c>
-      <c r="C137" t="s">
-        <v>44</v>
-      </c>
-      <c r="D137" t="s">
-        <v>482</v>
-      </c>
-      <c r="E137" t="s">
-        <v>196</v>
-      </c>
-      <c r="F137" t="s">
-        <v>0</v>
-      </c>
-      <c r="G137" t="s">
-        <v>483</v>
-      </c>
-      <c r="H137" t="s">
         <v>4</v>
       </c>
     </row>

--- a/1.xlsx
+++ b/1.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="\\wh.local\fs\UserProfile_TSSWH19\_TSSWH19_redirected_folders\HunyaCs1\Desktop\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5F516B4F-CF4C-4C4F-A22B-2B0F48BE181B}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6FC01077-D8C0-4940-8BA2-795E770C9E9C}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="0" windowWidth="22260" windowHeight="12648" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="952" uniqueCount="483">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1008" uniqueCount="532">
   <si>
     <t>BUDAPEST</t>
   </si>
@@ -51,21 +51,12 @@
     <t>SZ-805</t>
   </si>
   <si>
-    <t>SZ-834</t>
-  </si>
-  <si>
     <t>SZ-836</t>
   </si>
   <si>
     <t>SZ-820</t>
   </si>
   <si>
-    <t>2040</t>
-  </si>
-  <si>
-    <t>BUDAÖRS</t>
-  </si>
-  <si>
     <t>2030</t>
   </si>
   <si>
@@ -108,9 +99,6 @@
     <t>SZ-830</t>
   </si>
   <si>
-    <t>1165</t>
-  </si>
-  <si>
     <t>2440</t>
   </si>
   <si>
@@ -132,24 +120,12 @@
     <t>SZ-801</t>
   </si>
   <si>
-    <t>1171</t>
-  </si>
-  <si>
-    <t>1138</t>
-  </si>
-  <si>
     <t>SELEX</t>
   </si>
   <si>
     <t>SZ-833</t>
   </si>
   <si>
-    <t>1172</t>
-  </si>
-  <si>
-    <t>1213</t>
-  </si>
-  <si>
     <t>1118</t>
   </si>
   <si>
@@ -159,27 +135,15 @@
     <t>1204</t>
   </si>
   <si>
-    <t>1156</t>
-  </si>
-  <si>
     <t>SZ-835</t>
   </si>
   <si>
-    <t>1045</t>
-  </si>
-  <si>
     <t>1145</t>
   </si>
   <si>
     <t>1221</t>
   </si>
   <si>
-    <t>2300</t>
-  </si>
-  <si>
-    <t>RÁCKEVE</t>
-  </si>
-  <si>
     <t>2100</t>
   </si>
   <si>
@@ -192,42 +156,12 @@
     <t>SZIGETSZENTMIKLÓS</t>
   </si>
   <si>
-    <t>Kölcsey utca</t>
-  </si>
-  <si>
-    <t>Mártírok útja</t>
-  </si>
-  <si>
-    <t>Pozsonyi utca</t>
-  </si>
-  <si>
-    <t>2132</t>
-  </si>
-  <si>
     <t>GÖD</t>
   </si>
   <si>
-    <t>2628</t>
-  </si>
-  <si>
-    <t>SZOB</t>
-  </si>
-  <si>
     <t>SZ-823</t>
   </si>
   <si>
-    <t>69d403fb5cef447acab88a4c</t>
-  </si>
-  <si>
-    <t>260406-W00006111</t>
-  </si>
-  <si>
-    <t>Dévényi utca</t>
-  </si>
-  <si>
-    <t>1046</t>
-  </si>
-  <si>
     <t>69d61ed15cef447acab8aca9</t>
   </si>
   <si>
@@ -240,33 +174,9 @@
     <t>Baross utca</t>
   </si>
   <si>
-    <t>Árpád utca</t>
-  </si>
-  <si>
-    <t>Ady Endre utca</t>
-  </si>
-  <si>
-    <t>1054</t>
-  </si>
-  <si>
-    <t>Attila utca</t>
-  </si>
-  <si>
-    <t>1192</t>
-  </si>
-  <si>
     <t>1135</t>
   </si>
   <si>
-    <t>1214</t>
-  </si>
-  <si>
-    <t>2244</t>
-  </si>
-  <si>
-    <t>ÚRI</t>
-  </si>
-  <si>
     <t>Akácfa utca</t>
   </si>
   <si>
@@ -276,1207 +186,1444 @@
     <t>1116</t>
   </si>
   <si>
-    <t>202604082600813901</t>
-  </si>
-  <si>
-    <t>NFE6-04-07-K4EQ</t>
-  </si>
-  <si>
-    <t>Diósy Lajos utca</t>
-  </si>
-  <si>
-    <t>2235</t>
-  </si>
-  <si>
-    <t>MENDE</t>
-  </si>
-  <si>
-    <t>1051</t>
-  </si>
-  <si>
     <t>2131</t>
   </si>
   <si>
-    <t>159995579538885747</t>
-  </si>
-  <si>
-    <t>1-2858/2026</t>
-  </si>
-  <si>
     <t>1139</t>
   </si>
   <si>
-    <t>Fáy utca</t>
-  </si>
-  <si>
-    <t>EUROTRESOR</t>
-  </si>
-  <si>
-    <t>159995579538943201</t>
-  </si>
-  <si>
-    <t>2026/04430</t>
-  </si>
-  <si>
-    <t>2045</t>
-  </si>
-  <si>
-    <t>TÖRÖKBÁLINT</t>
-  </si>
-  <si>
-    <t>Óvoda utca</t>
-  </si>
-  <si>
-    <t>DRENCO</t>
-  </si>
-  <si>
-    <t>159995579538943218</t>
-  </si>
-  <si>
-    <t>69d652975cef447acab8b52b</t>
-  </si>
-  <si>
-    <t>260331-F00002714-2</t>
-  </si>
-  <si>
-    <t>1022</t>
-  </si>
-  <si>
-    <t>Alvinci út</t>
-  </si>
-  <si>
-    <t>69cd3d8b5cef447acab85d32</t>
-  </si>
-  <si>
-    <t>260401-W00007395</t>
-  </si>
-  <si>
-    <t>Hajdú utca</t>
-  </si>
-  <si>
-    <t>69d610005cef447acab8aa15</t>
-  </si>
-  <si>
-    <t>260403-W00003962</t>
-  </si>
-  <si>
-    <t>Állomás utca</t>
-  </si>
-  <si>
-    <t>69d4b40c5cef447acab88d78</t>
-  </si>
-  <si>
-    <t>260403-W00006528</t>
-  </si>
-  <si>
-    <t>1162</t>
-  </si>
-  <si>
-    <t>Hermina út</t>
-  </si>
-  <si>
-    <t>69cfe1bd5cef447acab87746</t>
-  </si>
-  <si>
-    <t>260403-W00006547</t>
-  </si>
-  <si>
-    <t>2023</t>
-  </si>
-  <si>
-    <t>DUNABOGDÁNY</t>
-  </si>
-  <si>
-    <t>Petőfi Sándor utca</t>
-  </si>
-  <si>
-    <t>69cfe1bd5cef447acab87749</t>
-  </si>
-  <si>
-    <t>69d225d45cef447acab882dd</t>
-  </si>
-  <si>
-    <t>260405-F00000586</t>
-  </si>
-  <si>
-    <t>2255</t>
-  </si>
-  <si>
-    <t>SZENTLŐRINCKÁTA</t>
-  </si>
-  <si>
-    <t>Zöldmező utca</t>
-  </si>
-  <si>
-    <t>69d504c25cef447acab89c8f</t>
-  </si>
-  <si>
-    <t>260407-F00011764</t>
-  </si>
-  <si>
-    <t>2712</t>
-  </si>
-  <si>
-    <t>NYÁRSAPÁT</t>
-  </si>
-  <si>
-    <t>Jókai Mór utca</t>
-  </si>
-  <si>
-    <t>69d67da35cef447acab8bad0</t>
-  </si>
-  <si>
-    <t>SZ-827</t>
-  </si>
-  <si>
-    <t>260407-W00003224</t>
-  </si>
-  <si>
-    <t>1122</t>
-  </si>
-  <si>
-    <t>Maros utca</t>
-  </si>
-  <si>
-    <t>69d77b7f5cef447acab8c723</t>
-  </si>
-  <si>
-    <t>260407-W00005119</t>
-  </si>
-  <si>
-    <t>Leányka utca</t>
-  </si>
-  <si>
-    <t>69d512ad5cef447acab89f05</t>
-  </si>
-  <si>
-    <t>260407-W00007219</t>
-  </si>
-  <si>
-    <t>2344</t>
-  </si>
-  <si>
-    <t>DÖMSÖD</t>
-  </si>
-  <si>
-    <t>69d520b85cef447acab8a119</t>
-  </si>
-  <si>
-    <t>260407-W00007973</t>
-  </si>
-  <si>
-    <t>2096</t>
-  </si>
-  <si>
-    <t>ÜRÖM</t>
-  </si>
-  <si>
-    <t>Bécsi út</t>
-  </si>
-  <si>
-    <t>69d51af75cef447acab8a050</t>
-  </si>
-  <si>
-    <t>260407-W00008002</t>
-  </si>
-  <si>
     <t>2600</t>
   </si>
   <si>
     <t>VÁC</t>
   </si>
   <si>
-    <t>Althann Mihály Frigyes utca</t>
-  </si>
-  <si>
-    <t>69d526975cef447acab8a1e0</t>
-  </si>
-  <si>
-    <t>260407-W00008756</t>
-  </si>
-  <si>
-    <t>2085</t>
-  </si>
-  <si>
-    <t>PILISVÖRÖSVÁR</t>
-  </si>
-  <si>
-    <t>Szent Erzsébet utca</t>
-  </si>
-  <si>
-    <t>69d5316b5cef447acab8a30b</t>
-  </si>
-  <si>
-    <t>260407-W00009332</t>
-  </si>
-  <si>
-    <t>2252</t>
-  </si>
-  <si>
-    <t>TÓALMÁS</t>
-  </si>
-  <si>
-    <t>69d5316b5cef447acab8a30c</t>
-  </si>
-  <si>
-    <t>69d543e25cef447acab8a444</t>
-  </si>
-  <si>
-    <t>260407-W00009741</t>
-  </si>
-  <si>
     <t>2377</t>
   </si>
   <si>
     <t>ÖRKÉNY</t>
   </si>
   <si>
-    <t>69d548915cef447acab8a480</t>
-  </si>
-  <si>
-    <t>260407-W00010386</t>
-  </si>
-  <si>
-    <t>Meggyfa utca</t>
-  </si>
-  <si>
-    <t>69d553165cef447acab8a4f2</t>
-  </si>
-  <si>
-    <t>260407-W00011029</t>
-  </si>
-  <si>
-    <t>Petőfi Sándor tér</t>
-  </si>
-  <si>
-    <t>69d553165cef447acab8a4f3</t>
-  </si>
-  <si>
-    <t>69d578985cef447acab8a5a8</t>
-  </si>
-  <si>
-    <t>260407-W00012578</t>
-  </si>
-  <si>
-    <t>2051</t>
-  </si>
-  <si>
-    <t>BIATORBÁGY</t>
-  </si>
-  <si>
-    <t>Kandó Kálmán utca</t>
-  </si>
-  <si>
-    <t>69d604105cef447acab8a802</t>
-  </si>
-  <si>
-    <t>260408-F00001045</t>
-  </si>
-  <si>
-    <t>Szilva utca</t>
-  </si>
-  <si>
-    <t>69d64cb55cef447acab8b40d</t>
-  </si>
-  <si>
-    <t>260408-F00009345</t>
-  </si>
-  <si>
-    <t>Ménesi út</t>
-  </si>
-  <si>
-    <t>69d64cb55cef447acab8b40f</t>
-  </si>
-  <si>
-    <t>69d64cde5cef447acab8b431</t>
-  </si>
-  <si>
-    <t>260408-F00009537</t>
-  </si>
-  <si>
-    <t>1134</t>
-  </si>
-  <si>
-    <t>Gidófalvy Lajos utca</t>
-  </si>
-  <si>
-    <t>69d662f85cef447acab8b7c9</t>
-  </si>
-  <si>
-    <t>260408-F00011645</t>
-  </si>
-  <si>
-    <t>1225</t>
-  </si>
-  <si>
-    <t>Gyümölcs utca</t>
-  </si>
-  <si>
-    <t>69d66a015cef447acab8b8df</t>
-  </si>
-  <si>
-    <t>260408-F00012820-4</t>
-  </si>
-  <si>
     <t>1037</t>
   </si>
   <si>
-    <t>69d5b6c25cef447acab8a5d7</t>
-  </si>
-  <si>
-    <t>260408-W00000309</t>
-  </si>
-  <si>
-    <t>2335</t>
-  </si>
-  <si>
-    <t>TAKSONY</t>
-  </si>
-  <si>
     <t>Deák Ferenc utca</t>
   </si>
   <si>
-    <t>69d6599b5cef447acab8b667</t>
-  </si>
-  <si>
-    <t>260408-W00006104</t>
-  </si>
-  <si>
-    <t>1089</t>
-  </si>
-  <si>
-    <t>Orczy út</t>
-  </si>
-  <si>
-    <t>69d6599b5cef447acab8b668</t>
-  </si>
-  <si>
-    <t>69d6887e5cef447acab8bbcd</t>
-  </si>
-  <si>
-    <t>260408-W00009263</t>
-  </si>
-  <si>
     <t>1144</t>
   </si>
   <si>
     <t>Szentmihályi út</t>
   </si>
   <si>
-    <t>69d77b785cef447acab8c71e</t>
-  </si>
-  <si>
-    <t>260409-F00002764</t>
-  </si>
-  <si>
-    <t>Kisgazda utca</t>
-  </si>
-  <si>
-    <t>69d77b785cef447acab8c720</t>
-  </si>
-  <si>
-    <t>69d77bcc5cef447acab8c745</t>
-  </si>
-  <si>
-    <t>260409-F00003189-1</t>
-  </si>
-  <si>
-    <t>1191</t>
-  </si>
-  <si>
-    <t>Dobó Katica utca</t>
-  </si>
-  <si>
-    <t>69d77b6f5cef447acab8c71b</t>
-  </si>
-  <si>
-    <t>260409-F00003307</t>
-  </si>
-  <si>
-    <t>Sas utca</t>
-  </si>
-  <si>
-    <t>69d77b8e5cef447acab8c72a</t>
-  </si>
-  <si>
-    <t>260409-W00002963</t>
-  </si>
-  <si>
-    <t>Apály utca</t>
-  </si>
-  <si>
-    <t>69d77b995cef447acab8c72d</t>
-  </si>
-  <si>
-    <t>260409-W00003224</t>
-  </si>
-  <si>
-    <t>Nagybányai út</t>
-  </si>
-  <si>
-    <t>69d779e45cef447acab8c6c8</t>
-  </si>
-  <si>
-    <t>260409-W00004105</t>
-  </si>
-  <si>
-    <t>Üteg utca</t>
-  </si>
-  <si>
-    <t>FIZZ-1000865185</t>
-  </si>
-  <si>
-    <t>267004961</t>
-  </si>
-  <si>
-    <t>1102</t>
-  </si>
-  <si>
-    <t>Harmat utca</t>
-  </si>
-  <si>
-    <t>304065244/1</t>
-  </si>
-  <si>
-    <t>304065244</t>
-  </si>
-  <si>
-    <t>Szlovák út</t>
-  </si>
-  <si>
-    <t>305514971/1</t>
-  </si>
-  <si>
-    <t>305514971</t>
-  </si>
-  <si>
     <t>1188</t>
   </si>
   <si>
-    <t>305514971/2</t>
-  </si>
-  <si>
-    <t>305514971/3</t>
-  </si>
-  <si>
-    <t>306276867/1</t>
-  </si>
-  <si>
-    <t>306276867</t>
-  </si>
-  <si>
-    <t>Havanna Utca</t>
-  </si>
-  <si>
-    <t>306276867/2</t>
-  </si>
-  <si>
-    <t>306621355/1</t>
-  </si>
-  <si>
-    <t>306621355</t>
-  </si>
-  <si>
-    <t>2011</t>
-  </si>
-  <si>
-    <t>BUDAKALÁSZ</t>
-  </si>
-  <si>
-    <t>Szentendrei út</t>
-  </si>
-  <si>
-    <t>306721122/1</t>
-  </si>
-  <si>
-    <t>306721122</t>
-  </si>
-  <si>
-    <t>Botond utca</t>
-  </si>
-  <si>
-    <t>306721122/2</t>
-  </si>
-  <si>
-    <t>306721122/3</t>
-  </si>
-  <si>
-    <t>306721194/1</t>
-  </si>
-  <si>
-    <t>306721194</t>
-  </si>
-  <si>
-    <t>Vadász utca</t>
-  </si>
-  <si>
-    <t>306721577/1</t>
-  </si>
-  <si>
-    <t>306721577</t>
-  </si>
-  <si>
-    <t>1161</t>
-  </si>
-  <si>
-    <t>Csömöri út</t>
-  </si>
-  <si>
-    <t>306721577/2</t>
-  </si>
-  <si>
-    <t>306721577/3</t>
-  </si>
-  <si>
-    <t>306766315/1</t>
-  </si>
-  <si>
-    <t>306766315</t>
-  </si>
-  <si>
-    <t>Vörösmarty Mihály utca</t>
-  </si>
-  <si>
-    <t>306891106/1</t>
-  </si>
-  <si>
-    <t>306891106</t>
-  </si>
-  <si>
-    <t>Szitakötő Utca</t>
-  </si>
-  <si>
-    <t>306891106/2</t>
-  </si>
-  <si>
-    <t>306891149/1</t>
-  </si>
-  <si>
-    <t>306891149</t>
-  </si>
-  <si>
     <t>2365</t>
   </si>
   <si>
     <t>INÁRCS</t>
   </si>
   <si>
-    <t>Bajcsy-Zsilinszky út</t>
-  </si>
-  <si>
-    <t>306891149/2</t>
-  </si>
-  <si>
-    <t>306891149/3</t>
-  </si>
-  <si>
-    <t>306949074/1</t>
-  </si>
-  <si>
-    <t>306949074</t>
-  </si>
-  <si>
     <t>1067</t>
   </si>
   <si>
-    <t>Teréz körút</t>
-  </si>
-  <si>
-    <t>306949074/2</t>
-  </si>
-  <si>
-    <t>306949074/3</t>
-  </si>
-  <si>
-    <t>306949363/1</t>
-  </si>
-  <si>
-    <t>306949363</t>
-  </si>
-  <si>
-    <t>Rózsa utca</t>
-  </si>
-  <si>
-    <t>306949363/2</t>
-  </si>
-  <si>
-    <t>307015937/1</t>
-  </si>
-  <si>
-    <t>307015937</t>
-  </si>
-  <si>
-    <t>Pásztortűz Utca</t>
-  </si>
-  <si>
-    <t>307080919/1</t>
-  </si>
-  <si>
-    <t>307080919</t>
-  </si>
-  <si>
-    <t>1031</t>
-  </si>
-  <si>
-    <t>Prés utca</t>
-  </si>
-  <si>
-    <t>307081059/1</t>
-  </si>
-  <si>
-    <t>307081059</t>
-  </si>
-  <si>
-    <t>1052</t>
-  </si>
-  <si>
-    <t>Kígyó utca</t>
-  </si>
-  <si>
-    <t>307081059/2</t>
-  </si>
-  <si>
-    <t>307081059/3</t>
-  </si>
-  <si>
-    <t>307081532/1</t>
-  </si>
-  <si>
-    <t>307081532</t>
-  </si>
-  <si>
     <t>Havanna utca</t>
   </si>
   <si>
-    <t>307081532/2</t>
-  </si>
-  <si>
-    <t>307141490/1</t>
-  </si>
-  <si>
-    <t>307141490</t>
-  </si>
-  <si>
     <t>1048</t>
   </si>
   <si>
-    <t>Hajló utca</t>
-  </si>
-  <si>
-    <t>307141507/1</t>
-  </si>
-  <si>
-    <t>307141507</t>
-  </si>
-  <si>
-    <t>307141507/2</t>
-  </si>
-  <si>
-    <t>307141586/1</t>
-  </si>
-  <si>
-    <t>307141586</t>
-  </si>
-  <si>
-    <t>1151</t>
-  </si>
-  <si>
-    <t>Tarpai tér</t>
-  </si>
-  <si>
-    <t>307141586/2</t>
-  </si>
-  <si>
-    <t>307141586/3</t>
-  </si>
-  <si>
-    <t>307141716/1</t>
-  </si>
-  <si>
-    <t>307141716</t>
-  </si>
-  <si>
-    <t>307141716/2</t>
-  </si>
-  <si>
-    <t>307141891/1</t>
-  </si>
-  <si>
-    <t>307141891</t>
-  </si>
-  <si>
     <t>1131</t>
   </si>
   <si>
-    <t>Béke utca</t>
-  </si>
-  <si>
-    <t>307197669/1</t>
-  </si>
-  <si>
-    <t>307197669</t>
-  </si>
-  <si>
-    <t>Kis Köz</t>
-  </si>
-  <si>
-    <t>307197779/1</t>
-  </si>
-  <si>
-    <t>307197779</t>
-  </si>
-  <si>
-    <t>2181</t>
-  </si>
-  <si>
-    <t>IKLAD</t>
-  </si>
-  <si>
-    <t>Ságvári Utca</t>
-  </si>
-  <si>
-    <t>307197880/1</t>
-  </si>
-  <si>
-    <t>307197880</t>
-  </si>
-  <si>
-    <t>Zöldkő utca</t>
-  </si>
-  <si>
-    <t>307198088/1</t>
-  </si>
-  <si>
-    <t>307198088</t>
-  </si>
-  <si>
     <t>1027</t>
   </si>
   <si>
-    <t>Horvát utca</t>
-  </si>
-  <si>
-    <t>307237812/1</t>
-  </si>
-  <si>
-    <t>307237812</t>
-  </si>
-  <si>
-    <t>Istvántelki út</t>
-  </si>
-  <si>
-    <t>307237812/2</t>
-  </si>
-  <si>
-    <t>307237837/1</t>
-  </si>
-  <si>
-    <t>307237837</t>
-  </si>
-  <si>
-    <t>Jászkisér utca</t>
-  </si>
-  <si>
-    <t>307237999/1</t>
-  </si>
-  <si>
-    <t>307237999</t>
-  </si>
-  <si>
-    <t>2220</t>
-  </si>
-  <si>
-    <t>VECSÉS</t>
-  </si>
-  <si>
-    <t>Táncsics Mihály utca</t>
-  </si>
-  <si>
-    <t>307238407/1</t>
-  </si>
-  <si>
-    <t>307238407</t>
-  </si>
-  <si>
-    <t>Kerekes utca</t>
-  </si>
-  <si>
-    <t>307238455/1</t>
-  </si>
-  <si>
-    <t>307238455</t>
-  </si>
-  <si>
-    <t>1123</t>
-  </si>
-  <si>
-    <t>Alkotás utca</t>
-  </si>
-  <si>
-    <t>307278702/1</t>
-  </si>
-  <si>
-    <t>307278702</t>
-  </si>
-  <si>
-    <t>Ferenc utca</t>
-  </si>
-  <si>
-    <t>307278970/1</t>
-  </si>
-  <si>
-    <t>307278970</t>
-  </si>
-  <si>
-    <t>1098</t>
-  </si>
-  <si>
-    <t>Börzsöny utca</t>
-  </si>
-  <si>
-    <t>307279018/1</t>
-  </si>
-  <si>
-    <t>307279018</t>
-  </si>
-  <si>
-    <t>Dembinszky József Utca</t>
-  </si>
-  <si>
-    <t>307279166/1</t>
-  </si>
-  <si>
-    <t>307279166</t>
-  </si>
-  <si>
     <t>1126</t>
   </si>
   <si>
-    <t>Szoboszlai utca</t>
-  </si>
-  <si>
-    <t>307279464/1</t>
-  </si>
-  <si>
-    <t>307279464</t>
-  </si>
-  <si>
     <t>1072</t>
   </si>
   <si>
-    <t>307279511/1</t>
-  </si>
-  <si>
-    <t>307279511</t>
-  </si>
-  <si>
-    <t>2092</t>
-  </si>
-  <si>
-    <t>BUDAKESZI</t>
-  </si>
-  <si>
-    <t>Kert utca</t>
-  </si>
-  <si>
-    <t>307342887/1</t>
-  </si>
-  <si>
-    <t>307342887</t>
-  </si>
-  <si>
-    <t>Faludi Utca</t>
-  </si>
-  <si>
-    <t>307342965/1</t>
-  </si>
-  <si>
-    <t>307342965</t>
-  </si>
-  <si>
-    <t>FSD park</t>
-  </si>
-  <si>
-    <t>307343270/1</t>
-  </si>
-  <si>
-    <t>307343270</t>
-  </si>
-  <si>
-    <t>1157</t>
-  </si>
-  <si>
-    <t>Kőrakás park</t>
-  </si>
-  <si>
-    <t>307343363/1</t>
-  </si>
-  <si>
-    <t>307343363</t>
-  </si>
-  <si>
-    <t>Fegyvernek utca</t>
-  </si>
-  <si>
-    <t>307343487/1</t>
-  </si>
-  <si>
-    <t>307343487</t>
-  </si>
-  <si>
-    <t>2143</t>
-  </si>
-  <si>
-    <t>KISTARCSA</t>
-  </si>
-  <si>
-    <t>Eperjesi út</t>
-  </si>
-  <si>
-    <t>307343616/1</t>
-  </si>
-  <si>
-    <t>307343616</t>
-  </si>
-  <si>
-    <t>Táncsics Mihály Utca</t>
-  </si>
-  <si>
-    <t>307343670/1</t>
-  </si>
-  <si>
-    <t>307343670</t>
-  </si>
-  <si>
-    <t>Szent Imre utca</t>
-  </si>
-  <si>
-    <t>307343706/1</t>
-  </si>
-  <si>
-    <t>307343706</t>
-  </si>
-  <si>
-    <t>Béla utca</t>
-  </si>
-  <si>
-    <t>307378951/1</t>
-  </si>
-  <si>
-    <t>307378951</t>
-  </si>
-  <si>
-    <t>Hámory Imre utca</t>
-  </si>
-  <si>
-    <t>307379247/1</t>
-  </si>
-  <si>
-    <t>307379247</t>
-  </si>
-  <si>
-    <t>307379284/1</t>
-  </si>
-  <si>
-    <t>307379284</t>
-  </si>
-  <si>
-    <t>Hernád köz</t>
-  </si>
-  <si>
-    <t>307379364/1</t>
-  </si>
-  <si>
-    <t>307379364</t>
-  </si>
-  <si>
-    <t>Bartók Béla utca</t>
-  </si>
-  <si>
-    <t>307379471/1</t>
-  </si>
-  <si>
-    <t>307379471</t>
-  </si>
-  <si>
-    <t>Mezőkövesd út</t>
-  </si>
-  <si>
-    <t>307379557/1</t>
-  </si>
-  <si>
-    <t>307379557</t>
-  </si>
-  <si>
-    <t>1075</t>
-  </si>
-  <si>
-    <t>Dob utca</t>
-  </si>
-  <si>
-    <t>307426993/1</t>
-  </si>
-  <si>
-    <t>307426993</t>
-  </si>
-  <si>
-    <t>1158</t>
-  </si>
-  <si>
-    <t>Vasgolyó utca</t>
-  </si>
-  <si>
-    <t>99002333/1</t>
-  </si>
-  <si>
-    <t>99002333</t>
-  </si>
-  <si>
-    <t>Nádastó park</t>
-  </si>
-  <si>
-    <t>202604092600773501</t>
-  </si>
-  <si>
-    <t>NFD6-03-31-EEFN</t>
-  </si>
-  <si>
-    <t>Máriavölgy utca</t>
-  </si>
-  <si>
-    <t>202604082600806701</t>
-  </si>
-  <si>
-    <t>NFD6-04-07-5GR8</t>
-  </si>
-  <si>
     <t>2234</t>
   </si>
   <si>
     <t>MAGLÓD</t>
   </si>
   <si>
-    <t>Bajcsy-Zsilinszky utca</t>
-  </si>
-  <si>
-    <t>202604082600812301</t>
-  </si>
-  <si>
-    <t>NFD6-04-07-8F7R</t>
-  </si>
-  <si>
-    <t>Széchenyi utca</t>
-  </si>
-  <si>
-    <t>202604082600812302</t>
-  </si>
-  <si>
-    <t>202604082600807101</t>
-  </si>
-  <si>
-    <t>NFD6-04-07-GKGL</t>
-  </si>
-  <si>
-    <t>2217</t>
-  </si>
-  <si>
-    <t>GOMBA</t>
-  </si>
-  <si>
-    <t>Gombai út</t>
-  </si>
-  <si>
-    <t>202604082600807102</t>
-  </si>
-  <si>
-    <t>202604082600807701</t>
-  </si>
-  <si>
-    <t>NFD6-04-07-UNT7</t>
-  </si>
-  <si>
-    <t>1039</t>
-  </si>
-  <si>
     <t>Kinizsi utca</t>
   </si>
   <si>
-    <t>202604082600809101</t>
-  </si>
-  <si>
-    <t>NFD6-04-07-YB8U</t>
-  </si>
-  <si>
-    <t>202604092600821201</t>
-  </si>
-  <si>
-    <t>NFD6-04-08-7N88</t>
-  </si>
-  <si>
-    <t>Bánya utca</t>
-  </si>
-  <si>
-    <t>202604092600822501</t>
-  </si>
-  <si>
-    <t>NFD6-04-08-BV6F</t>
-  </si>
-  <si>
-    <t>Cirmos sétány</t>
-  </si>
-  <si>
-    <t>202604092600822901</t>
-  </si>
-  <si>
-    <t>NFD6-04-08-EX7U</t>
-  </si>
-  <si>
-    <t>Csút utca</t>
-  </si>
-  <si>
-    <t>202604092600823601</t>
-  </si>
-  <si>
-    <t>NFD6-04-08-LKEQ</t>
-  </si>
-  <si>
     <t>1119</t>
   </si>
   <si>
     <t>Fehérvári út</t>
   </si>
   <si>
-    <t>202604092600823201</t>
-  </si>
-  <si>
-    <t>NFD6-04-08-RX93</t>
-  </si>
-  <si>
-    <t>Kőrösi Sándor utca</t>
-  </si>
-  <si>
-    <t>202604072600813302</t>
-  </si>
-  <si>
-    <t>NFE6-04-07-3YQP</t>
-  </si>
-  <si>
-    <t>Ady Endre út</t>
-  </si>
-  <si>
-    <t>202604082600813301</t>
-  </si>
-  <si>
-    <t>202604092600823501</t>
-  </si>
-  <si>
-    <t>NFE6-04-08-36J8</t>
-  </si>
-  <si>
-    <t>Kocsis Sándor út</t>
-  </si>
-  <si>
-    <t>202604092600823502</t>
+    <t>248745386/1</t>
+  </si>
+  <si>
+    <t>248745386</t>
+  </si>
+  <si>
+    <t>1103</t>
+  </si>
+  <si>
+    <t>Gyömrői út</t>
+  </si>
+  <si>
+    <t>248745393/1</t>
+  </si>
+  <si>
+    <t>248745393</t>
+  </si>
+  <si>
+    <t>1097</t>
+  </si>
+  <si>
+    <t>Vágóhíd utca</t>
+  </si>
+  <si>
+    <t>69d78d8b5cef447acab8c9ee</t>
+  </si>
+  <si>
+    <t>260321-W00006372</t>
+  </si>
+  <si>
+    <t>Liszt Ferenc utca</t>
+  </si>
+  <si>
+    <t>69cc0a870ed4809420f4bf46</t>
+  </si>
+  <si>
+    <t>260331-W00008718</t>
+  </si>
+  <si>
+    <t>2230</t>
+  </si>
+  <si>
+    <t>GYÖMRŐ</t>
+  </si>
+  <si>
+    <t>Eperfasor utca</t>
+  </si>
+  <si>
+    <t>69d7acc05cef447acab8cf76</t>
+  </si>
+  <si>
+    <t>260401-F00012350</t>
+  </si>
+  <si>
+    <t>1114</t>
+  </si>
+  <si>
+    <t>Vásárhelyi Pál utca</t>
+  </si>
+  <si>
+    <t>69d89a0f5cef447acab8d91e</t>
+  </si>
+  <si>
+    <t>260401-W00007623</t>
+  </si>
+  <si>
+    <t>1125</t>
+  </si>
+  <si>
+    <t>Szilágyi Erzsébet fasor</t>
+  </si>
+  <si>
+    <t>69d8bdb85cef447acab8ddff</t>
+  </si>
+  <si>
+    <t>260402-F00006899</t>
+  </si>
+  <si>
+    <t>Tűzkő utca</t>
+  </si>
+  <si>
+    <t>69d661415cef447acab8b79a</t>
+  </si>
+  <si>
+    <t>SZ-828</t>
+  </si>
+  <si>
+    <t>260402-F00009433</t>
+  </si>
+  <si>
+    <t>Aranka utca</t>
+  </si>
+  <si>
+    <t>69ce33b05cef447acab8653d</t>
+  </si>
+  <si>
+    <t>260402-W00003563</t>
+  </si>
+  <si>
+    <t>2634</t>
+  </si>
+  <si>
+    <t>NAGYBÖRZSÖNY</t>
+  </si>
+  <si>
+    <t>Petőfi utca</t>
+  </si>
+  <si>
+    <t>69ce33b05cef447acab8653e</t>
+  </si>
+  <si>
+    <t>69ceaeba5cef447acab872a5</t>
+  </si>
+  <si>
+    <t>260402-W00010016</t>
+  </si>
+  <si>
+    <t>1152</t>
+  </si>
+  <si>
+    <t>Szilas park</t>
+  </si>
+  <si>
+    <t>69d8ce805cef447acab8e0b9</t>
+  </si>
+  <si>
+    <t>260404-F00005161-1</t>
+  </si>
+  <si>
+    <t>Kapás utca</t>
+  </si>
+  <si>
+    <t>69d89a715cef447acab8d930</t>
+  </si>
+  <si>
+    <t>260405-W00005445</t>
+  </si>
+  <si>
+    <t>69d4c42b5cef447acab890b6</t>
+  </si>
+  <si>
+    <t>SZ-809</t>
+  </si>
+  <si>
+    <t>260407-F00003638</t>
+  </si>
+  <si>
+    <t>69d57b135cef447acab8a5b1</t>
+  </si>
+  <si>
+    <t>260407-W00012558</t>
+  </si>
+  <si>
+    <t>2192</t>
+  </si>
+  <si>
+    <t>HÉVÍZGYÖRK</t>
+  </si>
+  <si>
+    <t>Ősz utca</t>
+  </si>
+  <si>
+    <t>69d7e8a45cef447acab8d68b</t>
+  </si>
+  <si>
+    <t>260408-F00014737</t>
+  </si>
+  <si>
+    <t>Rátz László utca</t>
+  </si>
+  <si>
+    <t>69d62bee5cef447acab8af26</t>
+  </si>
+  <si>
+    <t>260408-W00004264</t>
+  </si>
+  <si>
+    <t>69d62bee5cef447acab8af27</t>
+  </si>
+  <si>
+    <t>69d6447b5cef447acab8b2ae</t>
+  </si>
+  <si>
+    <t>SZ-860</t>
+  </si>
+  <si>
+    <t>260408-W00005531</t>
+  </si>
+  <si>
+    <t>Budafoki út</t>
+  </si>
+  <si>
+    <t>69d67a6d5cef447acab8ba89</t>
+  </si>
+  <si>
+    <t>SZ-818</t>
+  </si>
+  <si>
+    <t>260408-W00008388</t>
+  </si>
+  <si>
+    <t>1071</t>
+  </si>
+  <si>
+    <t>Dózsa György út</t>
+  </si>
+  <si>
+    <t>69d694485cef447acab8bcad</t>
+  </si>
+  <si>
+    <t>260408-W00009477</t>
+  </si>
+  <si>
+    <t>2769</t>
+  </si>
+  <si>
+    <t>TÁPIÓSZŐLŐS</t>
+  </si>
+  <si>
+    <t>69d77ab65cef447acab8c6dc</t>
+  </si>
+  <si>
+    <t>260409-F00003679</t>
+  </si>
+  <si>
+    <t>2213</t>
+  </si>
+  <si>
+    <t>MONORIERDŐ</t>
+  </si>
+  <si>
+    <t>Nyúl utca</t>
+  </si>
+  <si>
+    <t>69d7da325cef447acab8d56c</t>
+  </si>
+  <si>
+    <t>260409-F00014617</t>
+  </si>
+  <si>
+    <t>1086</t>
+  </si>
+  <si>
+    <t>Koszorú utca</t>
+  </si>
+  <si>
+    <t>69d76e2e5cef447acab8c498</t>
+  </si>
+  <si>
+    <t>260409-W00003332</t>
+  </si>
+  <si>
+    <t>Váci út</t>
+  </si>
+  <si>
+    <t>69d7ac575cef447acab8cf61</t>
+  </si>
+  <si>
+    <t>260409-W00006961</t>
+  </si>
+  <si>
+    <t>1082</t>
+  </si>
+  <si>
+    <t>Üllői út</t>
+  </si>
+  <si>
+    <t>69d7ac575cef447acab8cf62</t>
+  </si>
+  <si>
+    <t>69d7ad735cef447acab8cf98</t>
+  </si>
+  <si>
+    <t>260409-W00007253</t>
+  </si>
+  <si>
+    <t>Farkasalma utca</t>
+  </si>
+  <si>
+    <t>69d7ad735cef447acab8cf99</t>
+  </si>
+  <si>
+    <t>69d7bf0d5cef447acab8d2d5</t>
+  </si>
+  <si>
+    <t>260409-W00008389</t>
+  </si>
+  <si>
+    <t>1021</t>
+  </si>
+  <si>
+    <t>Hűvösvölgyi út</t>
+  </si>
+  <si>
+    <t>69d8b3f65cef447acab8dc1a</t>
+  </si>
+  <si>
+    <t>SZ-821</t>
+  </si>
+  <si>
+    <t>260410-F00002552</t>
+  </si>
+  <si>
+    <t>Török Flóris utca</t>
+  </si>
+  <si>
+    <t>69d8b3f65cef447acab8dc1b</t>
+  </si>
+  <si>
+    <t>69d8c32f5cef447acab8def3</t>
+  </si>
+  <si>
+    <t>260410-F00004400</t>
+  </si>
+  <si>
+    <t>1182</t>
+  </si>
+  <si>
+    <t>Nagyenyed utca</t>
+  </si>
+  <si>
+    <t>69d846f15cef447acab8d829</t>
+  </si>
+  <si>
+    <t>260410-W00000232</t>
+  </si>
+  <si>
+    <t>1121</t>
+  </si>
+  <si>
+    <t>Irhás árok</t>
+  </si>
+  <si>
+    <t>69d8c45e5cef447acab8df3a</t>
+  </si>
+  <si>
+    <t>260410-W00003790</t>
+  </si>
+  <si>
+    <t>Lehel utca</t>
+  </si>
+  <si>
+    <t>69d8d96e5cef447acab8e22e</t>
+  </si>
+  <si>
+    <t>260410-W00004936</t>
+  </si>
+  <si>
+    <t>1174</t>
+  </si>
+  <si>
+    <t>Berzsenyi Dániel utca</t>
+  </si>
+  <si>
+    <t>FIZZ-1000860285</t>
+  </si>
+  <si>
+    <t>267004973</t>
+  </si>
+  <si>
+    <t>2225</t>
+  </si>
+  <si>
+    <t>ÜLLŐ</t>
+  </si>
+  <si>
+    <t>Öregszőlő utca</t>
+  </si>
+  <si>
+    <t>FIZZ-1000862427</t>
+  </si>
+  <si>
+    <t>267004978</t>
+  </si>
+  <si>
+    <t>Kucsma utca</t>
+  </si>
+  <si>
+    <t>26MPE0003708/1</t>
+  </si>
+  <si>
+    <t>26MPE0003708</t>
+  </si>
+  <si>
+    <t>2022</t>
+  </si>
+  <si>
+    <t>TAHITÓTFALU</t>
+  </si>
+  <si>
+    <t>Szőlő utca</t>
+  </si>
+  <si>
+    <t>MEGAPLACE</t>
+  </si>
+  <si>
+    <t>26MPE0003710/1</t>
+  </si>
+  <si>
+    <t>26MPE0003710</t>
+  </si>
+  <si>
+    <t>2370</t>
+  </si>
+  <si>
+    <t>DABAS</t>
+  </si>
+  <si>
+    <t>Fő út</t>
+  </si>
+  <si>
+    <t>26MPE0003719/1</t>
+  </si>
+  <si>
+    <t>26MPE0003719</t>
+  </si>
+  <si>
+    <t>M</t>
+  </si>
+  <si>
+    <t>26MPE0003757/1</t>
+  </si>
+  <si>
+    <t>26MPE0003757</t>
+  </si>
+  <si>
+    <t>2049</t>
+  </si>
+  <si>
+    <t>DIÓSD</t>
+  </si>
+  <si>
+    <t>Jolán utca</t>
+  </si>
+  <si>
+    <t>26MPE0003826/1</t>
+  </si>
+  <si>
+    <t>26MPE0003826</t>
+  </si>
+  <si>
+    <t>2740</t>
+  </si>
+  <si>
+    <t>ABONY</t>
+  </si>
+  <si>
+    <t>Tabán utca</t>
+  </si>
+  <si>
+    <t>300523974/1</t>
+  </si>
+  <si>
+    <t>300523974</t>
+  </si>
+  <si>
+    <t>2315</t>
+  </si>
+  <si>
+    <t>SZIGETHALOM</t>
+  </si>
+  <si>
+    <t>Gyöngyvirág Utca</t>
+  </si>
+  <si>
+    <t>305557116/1</t>
+  </si>
+  <si>
+    <t>305557116</t>
+  </si>
+  <si>
+    <t>1087</t>
+  </si>
+  <si>
+    <t>Ciprus utca</t>
+  </si>
+  <si>
+    <t>305557116/2</t>
+  </si>
+  <si>
+    <t>305557116/3</t>
+  </si>
+  <si>
+    <t>305830892/1</t>
+  </si>
+  <si>
+    <t>305830892</t>
+  </si>
+  <si>
+    <t>Szent László út</t>
+  </si>
+  <si>
+    <t>305830892/2</t>
+  </si>
+  <si>
+    <t>306621232/1</t>
+  </si>
+  <si>
+    <t>306621232</t>
+  </si>
+  <si>
+    <t>Rege út</t>
+  </si>
+  <si>
+    <t>306669492/1</t>
+  </si>
+  <si>
+    <t>306669492</t>
+  </si>
+  <si>
+    <t>Tétényi utca</t>
+  </si>
+  <si>
+    <t>306669492/2</t>
+  </si>
+  <si>
+    <t>306766498/1</t>
+  </si>
+  <si>
+    <t>306766498</t>
+  </si>
+  <si>
+    <t>Iharos Sándor Utca</t>
+  </si>
+  <si>
+    <t>306823916/1</t>
+  </si>
+  <si>
+    <t>306823916</t>
+  </si>
+  <si>
+    <t>1201</t>
+  </si>
+  <si>
+    <t>Baba utca</t>
+  </si>
+  <si>
+    <t>306823916/2</t>
+  </si>
+  <si>
+    <t>306891294/1</t>
+  </si>
+  <si>
+    <t>306891294</t>
+  </si>
+  <si>
+    <t>2364</t>
+  </si>
+  <si>
+    <t>ÓCSA</t>
+  </si>
+  <si>
+    <t>Székes tanya nyúlfarm</t>
+  </si>
+  <si>
+    <t>306891294/2</t>
+  </si>
+  <si>
+    <t>307081008/1</t>
+  </si>
+  <si>
+    <t>307081008</t>
+  </si>
+  <si>
+    <t>2170</t>
+  </si>
+  <si>
+    <t>ASZÓD</t>
+  </si>
+  <si>
+    <t>Berek utca</t>
+  </si>
+  <si>
+    <t>307081249/1</t>
+  </si>
+  <si>
+    <t>307081249</t>
+  </si>
+  <si>
+    <t>2360</t>
+  </si>
+  <si>
+    <t>GYÁL</t>
+  </si>
+  <si>
+    <t>Bercsényi Miklós utca</t>
+  </si>
+  <si>
+    <t>307081249/2</t>
+  </si>
+  <si>
+    <t>307081249/3</t>
+  </si>
+  <si>
+    <t>307081428/1</t>
+  </si>
+  <si>
+    <t>307081428</t>
+  </si>
+  <si>
+    <t>1107</t>
+  </si>
+  <si>
+    <t>307141884/1</t>
+  </si>
+  <si>
+    <t>307141884</t>
+  </si>
+  <si>
+    <t>Szugló utca</t>
+  </si>
+  <si>
+    <t>307198140/1</t>
+  </si>
+  <si>
+    <t>307198140</t>
+  </si>
+  <si>
+    <t>Gyöngyvirág utca</t>
+  </si>
+  <si>
+    <t>307198140/2</t>
+  </si>
+  <si>
+    <t>307237760/1</t>
+  </si>
+  <si>
+    <t>307237760</t>
+  </si>
+  <si>
+    <t>Kazinczy Ferenc utca</t>
+  </si>
+  <si>
+    <t>307238085/1</t>
+  </si>
+  <si>
+    <t>307238085</t>
+  </si>
+  <si>
+    <t>2114</t>
+  </si>
+  <si>
+    <t>VALKÓ</t>
+  </si>
+  <si>
+    <t>Dányi út</t>
+  </si>
+  <si>
+    <t>307238509/1</t>
+  </si>
+  <si>
+    <t>307238509</t>
+  </si>
+  <si>
+    <t>Gerinc utca</t>
+  </si>
+  <si>
+    <t>307278644/1</t>
+  </si>
+  <si>
+    <t>307278644</t>
+  </si>
+  <si>
+    <t>1053</t>
+  </si>
+  <si>
+    <t>Múzeum Körút</t>
+  </si>
+  <si>
+    <t>307278768/1</t>
+  </si>
+  <si>
+    <t>SZ-800</t>
+  </si>
+  <si>
+    <t>307278768</t>
+  </si>
+  <si>
+    <t>Kékfestő utca</t>
+  </si>
+  <si>
+    <t>307278791/1</t>
+  </si>
+  <si>
+    <t>307278791</t>
+  </si>
+  <si>
+    <t>2112</t>
+  </si>
+  <si>
+    <t>VERESEGYHÁZ</t>
+  </si>
+  <si>
+    <t>Budapesti út</t>
+  </si>
+  <si>
+    <t>307279268/1</t>
+  </si>
+  <si>
+    <t>307279268</t>
+  </si>
+  <si>
+    <t>307279324/1</t>
+  </si>
+  <si>
+    <t>307279324</t>
+  </si>
+  <si>
+    <t>Rákóczi út</t>
+  </si>
+  <si>
+    <t>307279397/1</t>
+  </si>
+  <si>
+    <t>307279397</t>
+  </si>
+  <si>
+    <t>Szondi utca</t>
+  </si>
+  <si>
+    <t>307279479/1</t>
+  </si>
+  <si>
+    <t>307279479</t>
+  </si>
+  <si>
+    <t>2330</t>
+  </si>
+  <si>
+    <t>DUNAHARASZTI</t>
+  </si>
+  <si>
+    <t>Kossuth Lajos Utca</t>
+  </si>
+  <si>
+    <t>307342850/1</t>
+  </si>
+  <si>
+    <t>307342850</t>
+  </si>
+  <si>
+    <t>2339</t>
+  </si>
+  <si>
+    <t>MAJOSHÁZA</t>
+  </si>
+  <si>
+    <t>Zrínyi utca</t>
+  </si>
+  <si>
+    <t>307343263/1</t>
+  </si>
+  <si>
+    <t>307343263</t>
+  </si>
+  <si>
+    <t>Kupeczky utca</t>
+  </si>
+  <si>
+    <t>307379077/2/1</t>
+  </si>
+  <si>
+    <t>307379077/2</t>
+  </si>
+  <si>
+    <t>1155</t>
+  </si>
+  <si>
+    <t>Őrszem utca</t>
+  </si>
+  <si>
+    <t>307379439/1</t>
+  </si>
+  <si>
+    <t>307379439</t>
+  </si>
+  <si>
+    <t>1147</t>
+  </si>
+  <si>
+    <t>Kerékgyártó utca</t>
+  </si>
+  <si>
+    <t>307379439/2</t>
+  </si>
+  <si>
+    <t>307379669/1</t>
+  </si>
+  <si>
+    <t>307379669</t>
+  </si>
+  <si>
+    <t>2094</t>
+  </si>
+  <si>
+    <t>NAGYKOVÁCSI</t>
+  </si>
+  <si>
+    <t>Munkácsy Mihály utca</t>
+  </si>
+  <si>
+    <t>307379894/1</t>
+  </si>
+  <si>
+    <t>307379894</t>
+  </si>
+  <si>
+    <t>Bajcsy-Zsilinszky Endre Utca</t>
+  </si>
+  <si>
+    <t>307379931/1</t>
+  </si>
+  <si>
+    <t>307379931</t>
+  </si>
+  <si>
+    <t>Szlávy utca</t>
+  </si>
+  <si>
+    <t>307426389/1</t>
+  </si>
+  <si>
+    <t>307426389</t>
+  </si>
+  <si>
+    <t>Fehárvári út</t>
+  </si>
+  <si>
+    <t>307426557/1</t>
+  </si>
+  <si>
+    <t>307426557</t>
+  </si>
+  <si>
+    <t>1173</t>
+  </si>
+  <si>
+    <t>Tápió utca</t>
+  </si>
+  <si>
+    <t>307426610/1</t>
+  </si>
+  <si>
+    <t>307426610</t>
+  </si>
+  <si>
+    <t>2081</t>
+  </si>
+  <si>
+    <t>PILISCSABA</t>
+  </si>
+  <si>
+    <t>Kossuth Lajos köz</t>
+  </si>
+  <si>
+    <t>307426668/1</t>
+  </si>
+  <si>
+    <t>307426668</t>
+  </si>
+  <si>
+    <t>1011</t>
+  </si>
+  <si>
+    <t>Fő utca</t>
+  </si>
+  <si>
+    <t>307426710/1</t>
+  </si>
+  <si>
+    <t>307426710</t>
+  </si>
+  <si>
+    <t>Csermely Károly</t>
+  </si>
+  <si>
+    <t>307426887/1</t>
+  </si>
+  <si>
+    <t>307426887</t>
+  </si>
+  <si>
+    <t>1062</t>
+  </si>
+  <si>
+    <t>Andrássy út</t>
+  </si>
+  <si>
+    <t>307426936/1</t>
+  </si>
+  <si>
+    <t>307426936</t>
+  </si>
+  <si>
+    <t>307426936/2</t>
+  </si>
+  <si>
+    <t>307427078/1</t>
+  </si>
+  <si>
+    <t>307427078</t>
+  </si>
+  <si>
+    <t>307427165/1</t>
+  </si>
+  <si>
+    <t>307427165</t>
+  </si>
+  <si>
+    <t>Forrás Utca</t>
+  </si>
+  <si>
+    <t>307482401/1</t>
+  </si>
+  <si>
+    <t>307482401</t>
+  </si>
+  <si>
+    <t>Paál László köz</t>
+  </si>
+  <si>
+    <t>307482401/2</t>
+  </si>
+  <si>
+    <t>307482484/1</t>
+  </si>
+  <si>
+    <t>307482484</t>
+  </si>
+  <si>
+    <t>Márvány utca</t>
+  </si>
+  <si>
+    <t>307482627/1</t>
+  </si>
+  <si>
+    <t>307482627</t>
+  </si>
+  <si>
+    <t>Muhar utca</t>
+  </si>
+  <si>
+    <t>307482743/1</t>
+  </si>
+  <si>
+    <t>307482743</t>
+  </si>
+  <si>
+    <t>1106</t>
+  </si>
+  <si>
+    <t>Gyakorló utca</t>
+  </si>
+  <si>
+    <t>307482871/1</t>
+  </si>
+  <si>
+    <t>307482871</t>
+  </si>
+  <si>
+    <t>2120</t>
+  </si>
+  <si>
+    <t>DUNAKESZI</t>
+  </si>
+  <si>
+    <t>Faludi János utca</t>
+  </si>
+  <si>
+    <t>307482902/1</t>
+  </si>
+  <si>
+    <t>307482902</t>
+  </si>
+  <si>
+    <t>1117</t>
+  </si>
+  <si>
+    <t>307483072/1</t>
+  </si>
+  <si>
+    <t>307483072</t>
+  </si>
+  <si>
+    <t>1112</t>
+  </si>
+  <si>
+    <t>Hermánd utca</t>
+  </si>
+  <si>
+    <t>307483214/1</t>
+  </si>
+  <si>
+    <t>307483214</t>
+  </si>
+  <si>
+    <t>Párta köz</t>
+  </si>
+  <si>
+    <t>307483270/1</t>
+  </si>
+  <si>
+    <t>307483270</t>
+  </si>
+  <si>
+    <t>1023</t>
+  </si>
+  <si>
+    <t>Levél utca</t>
+  </si>
+  <si>
+    <t>307483270/2</t>
+  </si>
+  <si>
+    <t>307483270/3</t>
+  </si>
+  <si>
+    <t>307530336/1</t>
+  </si>
+  <si>
+    <t>307530336</t>
+  </si>
+  <si>
+    <t>2737</t>
+  </si>
+  <si>
+    <t>CEGLÉDBERCEL</t>
+  </si>
+  <si>
+    <t>Vörösmarty utca</t>
+  </si>
+  <si>
+    <t>307530358/1</t>
+  </si>
+  <si>
+    <t>307530358</t>
+  </si>
+  <si>
+    <t>2633</t>
+  </si>
+  <si>
+    <t>IPOLYTÖLGYES</t>
+  </si>
+  <si>
+    <t>Kossuth utca</t>
+  </si>
+  <si>
+    <t>307530520/1</t>
+  </si>
+  <si>
+    <t>307530520</t>
+  </si>
+  <si>
+    <t>Körösbánya Utca</t>
+  </si>
+  <si>
+    <t>307530564/1</t>
+  </si>
+  <si>
+    <t>307530564</t>
+  </si>
+  <si>
+    <t>Malomtó utca</t>
+  </si>
+  <si>
+    <t>307530620/1</t>
+  </si>
+  <si>
+    <t>307530620</t>
+  </si>
+  <si>
+    <t>1149</t>
+  </si>
+  <si>
+    <t>Kövér Lajos utca</t>
+  </si>
+  <si>
+    <t>307530962/1</t>
+  </si>
+  <si>
+    <t>307530962</t>
+  </si>
+  <si>
+    <t>1163</t>
+  </si>
+  <si>
+    <t>Lándzsa utca</t>
+  </si>
+  <si>
+    <t>307530981/1</t>
+  </si>
+  <si>
+    <t>307530981</t>
+  </si>
+  <si>
+    <t>1108</t>
+  </si>
+  <si>
+    <t>Lenfonó utca</t>
+  </si>
+  <si>
+    <t>307531024/1</t>
+  </si>
+  <si>
+    <t>307531024</t>
+  </si>
+  <si>
+    <t>Juhar utca</t>
+  </si>
+  <si>
+    <t>307579790/1</t>
+  </si>
+  <si>
+    <t>307579790</t>
+  </si>
+  <si>
+    <t>Hága László utca</t>
+  </si>
+  <si>
+    <t>307628153/1</t>
+  </si>
+  <si>
+    <t>307628153</t>
+  </si>
+  <si>
+    <t>1194</t>
+  </si>
+  <si>
+    <t>Kolozsvár utca</t>
+  </si>
+  <si>
+    <t>307628153/2</t>
+  </si>
+  <si>
+    <t>307628394/1</t>
+  </si>
+  <si>
+    <t>307628394</t>
+  </si>
+  <si>
+    <t>1101</t>
+  </si>
+  <si>
+    <t>Csilla utca</t>
+  </si>
+  <si>
+    <t>307689408/1</t>
+  </si>
+  <si>
+    <t>307689408</t>
+  </si>
+  <si>
+    <t>Háros utca</t>
+  </si>
+  <si>
+    <t>307741125/1</t>
+  </si>
+  <si>
+    <t>307741125</t>
+  </si>
+  <si>
+    <t>1203</t>
+  </si>
+  <si>
+    <t>307741256/1</t>
+  </si>
+  <si>
+    <t>307741256</t>
+  </si>
+  <si>
+    <t>2072</t>
+  </si>
+  <si>
+    <t>ZSÁMBÉK</t>
+  </si>
+  <si>
+    <t>307741380/1</t>
+  </si>
+  <si>
+    <t>307741380</t>
+  </si>
+  <si>
+    <t>Illyés Gyula utca</t>
+  </si>
+  <si>
+    <t>307741380/2</t>
+  </si>
+  <si>
+    <t>307806493/1</t>
+  </si>
+  <si>
+    <t>307806493</t>
+  </si>
+  <si>
+    <t>307806637/1</t>
+  </si>
+  <si>
+    <t>307806637</t>
+  </si>
+  <si>
+    <t>1164</t>
+  </si>
+  <si>
+    <t>Vízesés utca</t>
+  </si>
+  <si>
+    <t>99002327/1</t>
+  </si>
+  <si>
+    <t>99002327</t>
+  </si>
+  <si>
+    <t>Pesti út</t>
+  </si>
+  <si>
+    <t>99002335/1</t>
+  </si>
+  <si>
+    <t>99002335</t>
+  </si>
+  <si>
+    <t>Liszt Ferenc sétány</t>
+  </si>
+  <si>
+    <t>202604102600779201</t>
+  </si>
+  <si>
+    <t>NFD6-04-01-H7FC</t>
+  </si>
+  <si>
+    <t>202604102600786401</t>
+  </si>
+  <si>
+    <t>NFD6-04-02-SZQD</t>
+  </si>
+  <si>
+    <t>Zágrábi utca</t>
+  </si>
+  <si>
+    <t>202604102600786402</t>
+  </si>
+  <si>
+    <t>202604102600786403</t>
+  </si>
+  <si>
+    <t>202604082600809501</t>
+  </si>
+  <si>
+    <t>NFD6-04-07-J4DB</t>
+  </si>
+  <si>
+    <t>Gábor Áron utca</t>
+  </si>
+  <si>
+    <t>202604102600830601</t>
+  </si>
+  <si>
+    <t>NFD6-04-09-7QM7</t>
+  </si>
+  <si>
+    <t>Sugár út</t>
+  </si>
+  <si>
+    <t>202604102600831101</t>
+  </si>
+  <si>
+    <t>NFD6-04-09-B4MB</t>
+  </si>
+  <si>
+    <t>Szabadszó utca</t>
+  </si>
+  <si>
+    <t>202604102600827301</t>
+  </si>
+  <si>
+    <t>NFD6-04-09-KCU2</t>
+  </si>
+  <si>
+    <t>Szélmalom út</t>
+  </si>
+  <si>
+    <t>202604102600829201</t>
+  </si>
+  <si>
+    <t>NFD6-04-09-N5U2</t>
+  </si>
+  <si>
+    <t>Piszke utca</t>
+  </si>
+  <si>
+    <t>202604102600832201</t>
+  </si>
+  <si>
+    <t>NFD6-04-09-PL9X</t>
+  </si>
+  <si>
+    <t>Szemere Bertalan utca</t>
+  </si>
+  <si>
+    <t>202604102600827901</t>
+  </si>
+  <si>
+    <t>NFD6-04-09-TJEY</t>
+  </si>
+  <si>
+    <t>1035</t>
+  </si>
+  <si>
+    <t>Vörösvári út</t>
+  </si>
+  <si>
+    <t>NFD6-04-10-F58Q-1</t>
+  </si>
+  <si>
+    <t>NFD6-04-10-F58Q</t>
+  </si>
+  <si>
+    <t>Napsugár utca</t>
+  </si>
+  <si>
+    <t>202604102600833401</t>
+  </si>
+  <si>
+    <t>NFE6-04-09-LBAF</t>
+  </si>
+  <si>
+    <t>Ferihegyi út</t>
+  </si>
+  <si>
+    <t>202604102600828601</t>
+  </si>
+  <si>
+    <t>NFE6-04-09-MYLR</t>
+  </si>
+  <si>
+    <t>Iharos Sándor utca</t>
+  </si>
+  <si>
+    <t>202604102600834601</t>
+  </si>
+  <si>
+    <t>NFE6-04-09-SDP3</t>
+  </si>
+  <si>
+    <t>Kordován tér</t>
+  </si>
+  <si>
+    <t>202604102600832301</t>
+  </si>
+  <si>
+    <t>NFE6-04-09-Y5KC</t>
+  </si>
+  <si>
+    <t>Arany János utca</t>
+  </si>
+  <si>
+    <t>202604102600831001</t>
+  </si>
+  <si>
+    <t>NFE6-04-09-ZLLP</t>
+  </si>
+  <si>
+    <t>Sárd utca</t>
   </si>
 </sst>
 </file>
@@ -1795,7 +1942,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <sheetPr codeName="Munka1"/>
-  <dimension ref="A1:H136"/>
+  <dimension ref="A1:H144"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="24.88671875" bestFit="1" customWidth="1"/>
@@ -1804,120 +1951,120 @@
     <col min="4" max="4" width="20.109375" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="5" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="20" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="34.44140625" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="33.77734375" bestFit="1" customWidth="1"/>
     <col min="8" max="8" width="19.88671875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
+        <v>11</v>
+      </c>
+      <c r="C1" t="s">
+        <v>12</v>
+      </c>
+      <c r="D1" t="s">
+        <v>13</v>
+      </c>
+      <c r="E1" t="s">
         <v>14</v>
       </c>
-      <c r="C1" t="s">
+      <c r="F1" t="s">
         <v>15</v>
       </c>
-      <c r="D1" t="s">
+      <c r="G1" t="s">
         <v>16</v>
       </c>
-      <c r="E1" t="s">
+      <c r="H1" t="s">
         <v>17</v>
-      </c>
-      <c r="F1" t="s">
-        <v>18</v>
-      </c>
-      <c r="G1" t="s">
-        <v>19</v>
-      </c>
-      <c r="H1" t="s">
-        <v>20</v>
       </c>
     </row>
     <row r="2" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
-        <v>89</v>
+        <v>77</v>
       </c>
       <c r="C2" t="s">
-        <v>7</v>
+        <v>22</v>
       </c>
       <c r="D2" t="s">
-        <v>90</v>
+        <v>78</v>
       </c>
       <c r="E2" t="s">
-        <v>91</v>
+        <v>79</v>
       </c>
       <c r="F2" t="s">
         <v>0</v>
       </c>
       <c r="G2" t="s">
-        <v>92</v>
+        <v>80</v>
       </c>
       <c r="H2" t="s">
-        <v>93</v>
+        <v>3</v>
       </c>
     </row>
     <row r="3" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
-        <v>94</v>
+        <v>81</v>
       </c>
       <c r="C3" t="s">
-        <v>30</v>
+        <v>26</v>
       </c>
       <c r="D3" t="s">
-        <v>95</v>
+        <v>82</v>
       </c>
       <c r="E3" t="s">
-        <v>96</v>
+        <v>83</v>
       </c>
       <c r="F3" t="s">
-        <v>97</v>
+        <v>0</v>
       </c>
       <c r="G3" t="s">
-        <v>98</v>
+        <v>84</v>
       </c>
       <c r="H3" t="s">
-        <v>99</v>
+        <v>3</v>
       </c>
     </row>
     <row r="4" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
-        <v>100</v>
+        <v>85</v>
       </c>
       <c r="C4" t="s">
-        <v>30</v>
+        <v>7</v>
       </c>
       <c r="D4" t="s">
-        <v>95</v>
+        <v>86</v>
       </c>
       <c r="E4" t="s">
-        <v>96</v>
+        <v>72</v>
       </c>
       <c r="F4" t="s">
-        <v>97</v>
+        <v>73</v>
       </c>
       <c r="G4" t="s">
-        <v>98</v>
+        <v>87</v>
       </c>
       <c r="H4" t="s">
-        <v>99</v>
+        <v>1</v>
       </c>
     </row>
     <row r="5" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
-        <v>101</v>
+        <v>88</v>
       </c>
       <c r="C5" t="s">
-        <v>31</v>
+        <v>7</v>
       </c>
       <c r="D5" t="s">
-        <v>102</v>
+        <v>89</v>
       </c>
       <c r="E5" t="s">
-        <v>103</v>
+        <v>90</v>
       </c>
       <c r="F5" t="s">
-        <v>0</v>
+        <v>91</v>
       </c>
       <c r="G5" t="s">
-        <v>104</v>
+        <v>92</v>
       </c>
       <c r="H5" t="s">
         <v>1</v>
@@ -1925,22 +2072,22 @@
     </row>
     <row r="6" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
-        <v>105</v>
+        <v>93</v>
       </c>
       <c r="C6" t="s">
-        <v>7</v>
+        <v>31</v>
       </c>
       <c r="D6" t="s">
-        <v>106</v>
+        <v>94</v>
       </c>
       <c r="E6" t="s">
-        <v>91</v>
+        <v>95</v>
       </c>
       <c r="F6" t="s">
         <v>0</v>
       </c>
       <c r="G6" t="s">
-        <v>107</v>
+        <v>96</v>
       </c>
       <c r="H6" t="s">
         <v>1</v>
@@ -1948,22 +2095,22 @@
     </row>
     <row r="7" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
-        <v>108</v>
+        <v>97</v>
       </c>
       <c r="C7" t="s">
-        <v>6</v>
+        <v>28</v>
       </c>
       <c r="D7" t="s">
-        <v>109</v>
+        <v>98</v>
       </c>
       <c r="E7" t="s">
-        <v>85</v>
+        <v>99</v>
       </c>
       <c r="F7" t="s">
-        <v>86</v>
+        <v>0</v>
       </c>
       <c r="G7" t="s">
-        <v>110</v>
+        <v>100</v>
       </c>
       <c r="H7" t="s">
         <v>1</v>
@@ -1971,22 +2118,22 @@
     </row>
     <row r="8" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
-        <v>111</v>
+        <v>101</v>
       </c>
       <c r="C8" t="s">
-        <v>2</v>
+        <v>31</v>
       </c>
       <c r="D8" t="s">
-        <v>112</v>
+        <v>102</v>
       </c>
       <c r="E8" t="s">
-        <v>113</v>
+        <v>32</v>
       </c>
       <c r="F8" t="s">
         <v>0</v>
       </c>
       <c r="G8" t="s">
-        <v>114</v>
+        <v>103</v>
       </c>
       <c r="H8" t="s">
         <v>1</v>
@@ -1994,22 +2141,22 @@
     </row>
     <row r="9" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
-        <v>115</v>
+        <v>104</v>
       </c>
       <c r="C9" t="s">
-        <v>44</v>
+        <v>105</v>
       </c>
       <c r="D9" t="s">
-        <v>116</v>
+        <v>106</v>
       </c>
       <c r="E9" t="s">
-        <v>117</v>
+        <v>54</v>
       </c>
       <c r="F9" t="s">
-        <v>118</v>
+        <v>55</v>
       </c>
       <c r="G9" t="s">
-        <v>119</v>
+        <v>107</v>
       </c>
       <c r="H9" t="s">
         <v>1</v>
@@ -2017,22 +2164,22 @@
     </row>
     <row r="10" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
-        <v>120</v>
+        <v>108</v>
       </c>
       <c r="C10" t="s">
-        <v>44</v>
+        <v>105</v>
       </c>
       <c r="D10" t="s">
-        <v>116</v>
+        <v>109</v>
       </c>
       <c r="E10" t="s">
-        <v>117</v>
+        <v>110</v>
       </c>
       <c r="F10" t="s">
-        <v>118</v>
+        <v>111</v>
       </c>
       <c r="G10" t="s">
-        <v>119</v>
+        <v>112</v>
       </c>
       <c r="H10" t="s">
         <v>1</v>
@@ -2040,22 +2187,22 @@
     </row>
     <row r="11" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A11" t="s">
-        <v>121</v>
+        <v>113</v>
       </c>
       <c r="C11" t="s">
-        <v>6</v>
+        <v>105</v>
       </c>
       <c r="D11" t="s">
-        <v>122</v>
+        <v>109</v>
       </c>
       <c r="E11" t="s">
-        <v>123</v>
+        <v>110</v>
       </c>
       <c r="F11" t="s">
-        <v>124</v>
+        <v>111</v>
       </c>
       <c r="G11" t="s">
-        <v>125</v>
+        <v>112</v>
       </c>
       <c r="H11" t="s">
         <v>1</v>
@@ -2063,22 +2210,22 @@
     </row>
     <row r="12" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A12" t="s">
-        <v>62</v>
+        <v>114</v>
       </c>
       <c r="C12" t="s">
-        <v>30</v>
+        <v>2</v>
       </c>
       <c r="D12" t="s">
-        <v>63</v>
+        <v>115</v>
       </c>
       <c r="E12" t="s">
-        <v>12</v>
+        <v>116</v>
       </c>
       <c r="F12" t="s">
-        <v>13</v>
+        <v>0</v>
       </c>
       <c r="G12" t="s">
-        <v>64</v>
+        <v>117</v>
       </c>
       <c r="H12" t="s">
         <v>1</v>
@@ -2086,22 +2233,22 @@
     </row>
     <row r="13" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A13" t="s">
-        <v>126</v>
+        <v>118</v>
       </c>
       <c r="C13" t="s">
-        <v>9</v>
+        <v>27</v>
       </c>
       <c r="D13" t="s">
-        <v>127</v>
+        <v>119</v>
       </c>
       <c r="E13" t="s">
-        <v>128</v>
+        <v>69</v>
       </c>
       <c r="F13" t="s">
-        <v>129</v>
+        <v>0</v>
       </c>
       <c r="G13" t="s">
-        <v>130</v>
+        <v>120</v>
       </c>
       <c r="H13" t="s">
         <v>1</v>
@@ -2109,22 +2256,22 @@
     </row>
     <row r="14" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A14" t="s">
+        <v>121</v>
+      </c>
+      <c r="C14" t="s">
+        <v>8</v>
+      </c>
+      <c r="D14" t="s">
+        <v>122</v>
+      </c>
+      <c r="E14" t="s">
+        <v>33</v>
+      </c>
+      <c r="F14" t="s">
+        <v>0</v>
+      </c>
+      <c r="G14" t="s">
         <v>66</v>
-      </c>
-      <c r="C14" t="s">
-        <v>32</v>
-      </c>
-      <c r="D14" t="s">
-        <v>67</v>
-      </c>
-      <c r="E14" t="s">
-        <v>68</v>
-      </c>
-      <c r="F14" t="s">
-        <v>0</v>
-      </c>
-      <c r="G14" t="s">
-        <v>69</v>
       </c>
       <c r="H14" t="s">
         <v>1</v>
@@ -2132,22 +2279,22 @@
     </row>
     <row r="15" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A15" t="s">
-        <v>131</v>
+        <v>123</v>
       </c>
       <c r="C15" t="s">
-        <v>132</v>
+        <v>124</v>
       </c>
       <c r="D15" t="s">
-        <v>133</v>
+        <v>125</v>
       </c>
       <c r="E15" t="s">
-        <v>134</v>
+        <v>60</v>
       </c>
       <c r="F15" t="s">
         <v>0</v>
       </c>
       <c r="G15" t="s">
-        <v>135</v>
+        <v>61</v>
       </c>
       <c r="H15" t="s">
         <v>1</v>
@@ -2155,22 +2302,22 @@
     </row>
     <row r="16" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A16" t="s">
-        <v>136</v>
+        <v>44</v>
       </c>
       <c r="C16" t="s">
-        <v>37</v>
+        <v>26</v>
       </c>
       <c r="D16" t="s">
-        <v>137</v>
+        <v>45</v>
       </c>
       <c r="E16" t="s">
+        <v>46</v>
+      </c>
+      <c r="F16" t="s">
+        <v>0</v>
+      </c>
+      <c r="G16" t="s">
         <v>47</v>
-      </c>
-      <c r="F16" t="s">
-        <v>0</v>
-      </c>
-      <c r="G16" t="s">
-        <v>138</v>
       </c>
       <c r="H16" t="s">
         <v>1</v>
@@ -2178,22 +2325,22 @@
     </row>
     <row r="17" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A17" t="s">
-        <v>139</v>
+        <v>126</v>
       </c>
       <c r="C17" t="s">
-        <v>33</v>
+        <v>18</v>
       </c>
       <c r="D17" t="s">
-        <v>140</v>
+        <v>127</v>
       </c>
       <c r="E17" t="s">
-        <v>141</v>
+        <v>128</v>
       </c>
       <c r="F17" t="s">
-        <v>142</v>
+        <v>129</v>
       </c>
       <c r="G17" t="s">
-        <v>73</v>
+        <v>130</v>
       </c>
       <c r="H17" t="s">
         <v>1</v>
@@ -2201,22 +2348,22 @@
     </row>
     <row r="18" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A18" t="s">
-        <v>143</v>
+        <v>131</v>
       </c>
       <c r="C18" t="s">
-        <v>44</v>
+        <v>31</v>
       </c>
       <c r="D18" t="s">
-        <v>144</v>
+        <v>132</v>
       </c>
       <c r="E18" t="s">
-        <v>145</v>
+        <v>51</v>
       </c>
       <c r="F18" t="s">
-        <v>146</v>
+        <v>0</v>
       </c>
       <c r="G18" t="s">
-        <v>147</v>
+        <v>133</v>
       </c>
       <c r="H18" t="s">
         <v>1</v>
@@ -2224,22 +2371,22 @@
     </row>
     <row r="19" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A19" t="s">
-        <v>148</v>
+        <v>134</v>
       </c>
       <c r="C19" t="s">
-        <v>25</v>
+        <v>124</v>
       </c>
       <c r="D19" t="s">
-        <v>149</v>
+        <v>135</v>
       </c>
       <c r="E19" t="s">
-        <v>150</v>
+        <v>60</v>
       </c>
       <c r="F19" t="s">
-        <v>151</v>
+        <v>0</v>
       </c>
       <c r="G19" t="s">
-        <v>152</v>
+        <v>61</v>
       </c>
       <c r="H19" t="s">
         <v>1</v>
@@ -2247,22 +2394,22 @@
     </row>
     <row r="20" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A20" t="s">
-        <v>153</v>
+        <v>136</v>
       </c>
       <c r="C20" t="s">
-        <v>31</v>
+        <v>124</v>
       </c>
       <c r="D20" t="s">
-        <v>154</v>
+        <v>135</v>
       </c>
       <c r="E20" t="s">
-        <v>155</v>
+        <v>60</v>
       </c>
       <c r="F20" t="s">
-        <v>156</v>
+        <v>0</v>
       </c>
       <c r="G20" t="s">
-        <v>157</v>
+        <v>61</v>
       </c>
       <c r="H20" t="s">
         <v>1</v>
@@ -2270,22 +2417,22 @@
     </row>
     <row r="21" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A21" t="s">
-        <v>158</v>
+        <v>137</v>
       </c>
       <c r="C21" t="s">
-        <v>6</v>
+        <v>138</v>
       </c>
       <c r="D21" t="s">
-        <v>159</v>
+        <v>139</v>
       </c>
       <c r="E21" t="s">
-        <v>160</v>
+        <v>9</v>
       </c>
       <c r="F21" t="s">
-        <v>161</v>
+        <v>10</v>
       </c>
       <c r="G21" t="s">
-        <v>71</v>
+        <v>140</v>
       </c>
       <c r="H21" t="s">
         <v>1</v>
@@ -2293,22 +2440,22 @@
     </row>
     <row r="22" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A22" t="s">
-        <v>162</v>
+        <v>141</v>
       </c>
       <c r="C22" t="s">
-        <v>6</v>
+        <v>142</v>
       </c>
       <c r="D22" t="s">
-        <v>159</v>
+        <v>143</v>
       </c>
       <c r="E22" t="s">
-        <v>160</v>
+        <v>144</v>
       </c>
       <c r="F22" t="s">
-        <v>161</v>
+        <v>0</v>
       </c>
       <c r="G22" t="s">
-        <v>71</v>
+        <v>145</v>
       </c>
       <c r="H22" t="s">
         <v>1</v>
@@ -2316,22 +2463,22 @@
     </row>
     <row r="23" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A23" t="s">
-        <v>163</v>
+        <v>146</v>
       </c>
       <c r="C23" t="s">
-        <v>61</v>
+        <v>7</v>
       </c>
       <c r="D23" t="s">
-        <v>164</v>
+        <v>147</v>
       </c>
       <c r="E23" t="s">
-        <v>165</v>
+        <v>148</v>
       </c>
       <c r="F23" t="s">
-        <v>166</v>
+        <v>149</v>
       </c>
       <c r="G23" t="s">
-        <v>70</v>
+        <v>59</v>
       </c>
       <c r="H23" t="s">
         <v>1</v>
@@ -2339,22 +2486,22 @@
     </row>
     <row r="24" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A24" t="s">
-        <v>167</v>
+        <v>150</v>
       </c>
       <c r="C24" t="s">
-        <v>25</v>
+        <v>35</v>
       </c>
       <c r="D24" t="s">
-        <v>168</v>
+        <v>151</v>
       </c>
       <c r="E24" t="s">
-        <v>59</v>
+        <v>152</v>
       </c>
       <c r="F24" t="s">
-        <v>60</v>
+        <v>153</v>
       </c>
       <c r="G24" t="s">
-        <v>169</v>
+        <v>154</v>
       </c>
       <c r="H24" t="s">
         <v>1</v>
@@ -2362,22 +2509,22 @@
     </row>
     <row r="25" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A25" t="s">
-        <v>170</v>
+        <v>155</v>
       </c>
       <c r="C25" t="s">
-        <v>2</v>
+        <v>26</v>
       </c>
       <c r="D25" t="s">
-        <v>171</v>
+        <v>156</v>
       </c>
       <c r="E25" t="s">
-        <v>50</v>
+        <v>157</v>
       </c>
       <c r="F25" t="s">
-        <v>51</v>
+        <v>0</v>
       </c>
       <c r="G25" t="s">
-        <v>172</v>
+        <v>158</v>
       </c>
       <c r="H25" t="s">
         <v>1</v>
@@ -2385,22 +2532,22 @@
     </row>
     <row r="26" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A26" t="s">
-        <v>173</v>
+        <v>159</v>
       </c>
       <c r="C26" t="s">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="D26" t="s">
-        <v>171</v>
+        <v>160</v>
       </c>
       <c r="E26" t="s">
-        <v>50</v>
+        <v>53</v>
       </c>
       <c r="F26" t="s">
-        <v>51</v>
+        <v>0</v>
       </c>
       <c r="G26" t="s">
-        <v>172</v>
+        <v>161</v>
       </c>
       <c r="H26" t="s">
         <v>1</v>
@@ -2408,22 +2555,22 @@
     </row>
     <row r="27" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A27" t="s">
-        <v>174</v>
+        <v>162</v>
       </c>
       <c r="C27" t="s">
-        <v>30</v>
+        <v>26</v>
       </c>
       <c r="D27" t="s">
-        <v>175</v>
+        <v>163</v>
       </c>
       <c r="E27" t="s">
-        <v>176</v>
+        <v>164</v>
       </c>
       <c r="F27" t="s">
-        <v>177</v>
+        <v>0</v>
       </c>
       <c r="G27" t="s">
-        <v>178</v>
+        <v>165</v>
       </c>
       <c r="H27" t="s">
         <v>1</v>
@@ -2431,22 +2578,22 @@
     </row>
     <row r="28" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A28" t="s">
-        <v>179</v>
+        <v>166</v>
       </c>
       <c r="C28" t="s">
-        <v>33</v>
+        <v>26</v>
       </c>
       <c r="D28" t="s">
-        <v>180</v>
+        <v>163</v>
       </c>
       <c r="E28" t="s">
-        <v>48</v>
+        <v>164</v>
       </c>
       <c r="F28" t="s">
-        <v>49</v>
+        <v>0</v>
       </c>
       <c r="G28" t="s">
-        <v>181</v>
+        <v>165</v>
       </c>
       <c r="H28" t="s">
         <v>1</v>
@@ -2454,22 +2601,22 @@
     </row>
     <row r="29" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A29" t="s">
-        <v>182</v>
+        <v>167</v>
       </c>
       <c r="C29" t="s">
-        <v>37</v>
+        <v>22</v>
       </c>
       <c r="D29" t="s">
-        <v>183</v>
+        <v>168</v>
       </c>
       <c r="E29" t="s">
-        <v>40</v>
+        <v>79</v>
       </c>
       <c r="F29" t="s">
         <v>0</v>
       </c>
       <c r="G29" t="s">
-        <v>184</v>
+        <v>169</v>
       </c>
       <c r="H29" t="s">
         <v>1</v>
@@ -2477,22 +2624,22 @@
     </row>
     <row r="30" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A30" t="s">
-        <v>185</v>
+        <v>170</v>
       </c>
       <c r="C30" t="s">
-        <v>37</v>
+        <v>22</v>
       </c>
       <c r="D30" t="s">
-        <v>183</v>
+        <v>168</v>
       </c>
       <c r="E30" t="s">
-        <v>40</v>
+        <v>79</v>
       </c>
       <c r="F30" t="s">
         <v>0</v>
       </c>
       <c r="G30" t="s">
-        <v>184</v>
+        <v>169</v>
       </c>
       <c r="H30" t="s">
         <v>1</v>
@@ -2500,22 +2647,22 @@
     </row>
     <row r="31" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A31" t="s">
-        <v>186</v>
+        <v>171</v>
       </c>
       <c r="C31" t="s">
-        <v>7</v>
+        <v>27</v>
       </c>
       <c r="D31" t="s">
-        <v>187</v>
+        <v>172</v>
       </c>
       <c r="E31" t="s">
-        <v>188</v>
+        <v>173</v>
       </c>
       <c r="F31" t="s">
         <v>0</v>
       </c>
       <c r="G31" t="s">
-        <v>189</v>
+        <v>174</v>
       </c>
       <c r="H31" t="s">
         <v>1</v>
@@ -2523,22 +2670,22 @@
     </row>
     <row r="32" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A32" t="s">
-        <v>190</v>
+        <v>175</v>
       </c>
       <c r="C32" t="s">
-        <v>37</v>
+        <v>176</v>
       </c>
       <c r="D32" t="s">
-        <v>191</v>
+        <v>177</v>
       </c>
       <c r="E32" t="s">
-        <v>192</v>
+        <v>34</v>
       </c>
       <c r="F32" t="s">
         <v>0</v>
       </c>
       <c r="G32" t="s">
-        <v>193</v>
+        <v>178</v>
       </c>
       <c r="H32" t="s">
         <v>1</v>
@@ -2546,22 +2693,22 @@
     </row>
     <row r="33" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A33" t="s">
-        <v>194</v>
+        <v>179</v>
       </c>
       <c r="C33" t="s">
-        <v>44</v>
+        <v>176</v>
       </c>
       <c r="D33" t="s">
-        <v>195</v>
+        <v>177</v>
       </c>
       <c r="E33" t="s">
-        <v>196</v>
+        <v>34</v>
       </c>
       <c r="F33" t="s">
         <v>0</v>
       </c>
       <c r="G33" t="s">
-        <v>147</v>
+        <v>178</v>
       </c>
       <c r="H33" t="s">
         <v>1</v>
@@ -2569,22 +2716,22 @@
     </row>
     <row r="34" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A34" t="s">
-        <v>197</v>
+        <v>180</v>
       </c>
       <c r="C34" t="s">
-        <v>33</v>
+        <v>8</v>
       </c>
       <c r="D34" t="s">
-        <v>198</v>
+        <v>181</v>
       </c>
       <c r="E34" t="s">
-        <v>199</v>
+        <v>182</v>
       </c>
       <c r="F34" t="s">
-        <v>200</v>
+        <v>0</v>
       </c>
       <c r="G34" t="s">
-        <v>201</v>
+        <v>183</v>
       </c>
       <c r="H34" t="s">
         <v>1</v>
@@ -2592,22 +2739,22 @@
     </row>
     <row r="35" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A35" t="s">
-        <v>202</v>
+        <v>184</v>
       </c>
       <c r="C35" t="s">
-        <v>32</v>
+        <v>28</v>
       </c>
       <c r="D35" t="s">
-        <v>203</v>
+        <v>185</v>
       </c>
       <c r="E35" t="s">
-        <v>204</v>
+        <v>186</v>
       </c>
       <c r="F35" t="s">
         <v>0</v>
       </c>
       <c r="G35" t="s">
-        <v>205</v>
+        <v>187</v>
       </c>
       <c r="H35" t="s">
         <v>1</v>
@@ -2615,22 +2762,22 @@
     </row>
     <row r="36" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A36" t="s">
-        <v>206</v>
+        <v>188</v>
       </c>
       <c r="C36" t="s">
-        <v>32</v>
+        <v>6</v>
       </c>
       <c r="D36" t="s">
-        <v>203</v>
+        <v>189</v>
       </c>
       <c r="E36" t="s">
-        <v>204</v>
+        <v>48</v>
       </c>
       <c r="F36" t="s">
         <v>0</v>
       </c>
       <c r="G36" t="s">
-        <v>205</v>
+        <v>190</v>
       </c>
       <c r="H36" t="s">
         <v>1</v>
@@ -2638,22 +2785,22 @@
     </row>
     <row r="37" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A37" t="s">
-        <v>207</v>
+        <v>191</v>
       </c>
       <c r="C37" t="s">
         <v>22</v>
       </c>
       <c r="D37" t="s">
-        <v>208</v>
+        <v>192</v>
       </c>
       <c r="E37" t="s">
-        <v>209</v>
+        <v>193</v>
       </c>
       <c r="F37" t="s">
         <v>0</v>
       </c>
       <c r="G37" t="s">
-        <v>210</v>
+        <v>194</v>
       </c>
       <c r="H37" t="s">
         <v>1</v>
@@ -2661,206 +2808,206 @@
     </row>
     <row r="38" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A38" t="s">
-        <v>211</v>
+        <v>195</v>
       </c>
       <c r="C38" t="s">
-        <v>31</v>
+        <v>35</v>
       </c>
       <c r="D38" t="s">
-        <v>212</v>
+        <v>196</v>
       </c>
       <c r="E38" t="s">
-        <v>80</v>
+        <v>197</v>
       </c>
       <c r="F38" t="s">
-        <v>0</v>
+        <v>198</v>
       </c>
       <c r="G38" t="s">
-        <v>213</v>
+        <v>199</v>
       </c>
       <c r="H38" t="s">
-        <v>1</v>
+        <v>30</v>
       </c>
     </row>
     <row r="39" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A39" t="s">
-        <v>214</v>
+        <v>200</v>
       </c>
       <c r="C39" t="s">
-        <v>31</v>
+        <v>6</v>
       </c>
       <c r="D39" t="s">
-        <v>212</v>
+        <v>201</v>
       </c>
       <c r="E39" t="s">
-        <v>80</v>
+        <v>68</v>
       </c>
       <c r="F39" t="s">
         <v>0</v>
       </c>
       <c r="G39" t="s">
-        <v>213</v>
+        <v>202</v>
       </c>
       <c r="H39" t="s">
-        <v>1</v>
+        <v>30</v>
       </c>
     </row>
     <row r="40" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A40" t="s">
-        <v>215</v>
+        <v>203</v>
       </c>
       <c r="C40" t="s">
-        <v>61</v>
+        <v>19</v>
       </c>
       <c r="D40" t="s">
-        <v>216</v>
+        <v>204</v>
       </c>
       <c r="E40" t="s">
-        <v>217</v>
+        <v>205</v>
       </c>
       <c r="F40" t="s">
-        <v>0</v>
+        <v>206</v>
       </c>
       <c r="G40" t="s">
-        <v>218</v>
+        <v>207</v>
       </c>
       <c r="H40" t="s">
-        <v>1</v>
+        <v>208</v>
       </c>
     </row>
     <row r="41" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A41" t="s">
-        <v>219</v>
+        <v>209</v>
       </c>
       <c r="C41" t="s">
-        <v>5</v>
+        <v>43</v>
       </c>
       <c r="D41" t="s">
-        <v>220</v>
+        <v>210</v>
       </c>
       <c r="E41" t="s">
-        <v>87</v>
+        <v>211</v>
       </c>
       <c r="F41" t="s">
-        <v>0</v>
+        <v>212</v>
       </c>
       <c r="G41" t="s">
-        <v>221</v>
+        <v>213</v>
       </c>
       <c r="H41" t="s">
-        <v>1</v>
+        <v>208</v>
       </c>
     </row>
     <row r="42" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A42" t="s">
-        <v>222</v>
+        <v>214</v>
       </c>
       <c r="C42" t="s">
-        <v>7</v>
+        <v>43</v>
       </c>
       <c r="D42" t="s">
-        <v>223</v>
+        <v>215</v>
       </c>
       <c r="E42" t="s">
-        <v>188</v>
+        <v>63</v>
       </c>
       <c r="F42" t="s">
-        <v>0</v>
+        <v>64</v>
       </c>
       <c r="G42" t="s">
-        <v>224</v>
+        <v>216</v>
       </c>
       <c r="H42" t="s">
-        <v>1</v>
+        <v>208</v>
       </c>
     </row>
     <row r="43" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A43" t="s">
-        <v>225</v>
+        <v>217</v>
       </c>
       <c r="C43" t="s">
-        <v>31</v>
+        <v>5</v>
       </c>
       <c r="D43" t="s">
-        <v>226</v>
+        <v>218</v>
       </c>
       <c r="E43" t="s">
-        <v>29</v>
+        <v>219</v>
       </c>
       <c r="F43" t="s">
-        <v>0</v>
+        <v>220</v>
       </c>
       <c r="G43" t="s">
-        <v>227</v>
+        <v>221</v>
       </c>
       <c r="H43" t="s">
-        <v>1</v>
+        <v>208</v>
       </c>
     </row>
     <row r="44" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A44" t="s">
-        <v>228</v>
+        <v>222</v>
       </c>
       <c r="C44" t="s">
-        <v>7</v>
+        <v>35</v>
       </c>
       <c r="D44" t="s">
-        <v>229</v>
+        <v>223</v>
       </c>
       <c r="E44" t="s">
-        <v>91</v>
+        <v>224</v>
       </c>
       <c r="F44" t="s">
-        <v>0</v>
+        <v>225</v>
       </c>
       <c r="G44" t="s">
-        <v>230</v>
+        <v>226</v>
       </c>
       <c r="H44" t="s">
-        <v>1</v>
+        <v>208</v>
       </c>
     </row>
     <row r="45" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A45" t="s">
+        <v>227</v>
+      </c>
+      <c r="C45" t="s">
+        <v>29</v>
+      </c>
+      <c r="D45" t="s">
+        <v>228</v>
+      </c>
+      <c r="E45" t="s">
+        <v>229</v>
+      </c>
+      <c r="F45" t="s">
+        <v>230</v>
+      </c>
+      <c r="G45" t="s">
         <v>231</v>
       </c>
-      <c r="C45" t="s">
-        <v>8</v>
-      </c>
-      <c r="D45" t="s">
-        <v>232</v>
-      </c>
-      <c r="E45" t="s">
-        <v>233</v>
-      </c>
-      <c r="F45" t="s">
-        <v>0</v>
-      </c>
-      <c r="G45" t="s">
-        <v>234</v>
-      </c>
       <c r="H45" t="s">
-        <v>36</v>
+        <v>3</v>
       </c>
     </row>
     <row r="46" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A46" t="s">
+        <v>232</v>
+      </c>
+      <c r="C46" t="s">
+        <v>26</v>
+      </c>
+      <c r="D46" t="s">
+        <v>233</v>
+      </c>
+      <c r="E46" t="s">
+        <v>234</v>
+      </c>
+      <c r="F46" t="s">
+        <v>0</v>
+      </c>
+      <c r="G46" t="s">
         <v>235</v>
-      </c>
-      <c r="C46" t="s">
-        <v>2</v>
-      </c>
-      <c r="D46" t="s">
-        <v>236</v>
-      </c>
-      <c r="E46" t="s">
-        <v>113</v>
-      </c>
-      <c r="F46" t="s">
-        <v>0</v>
-      </c>
-      <c r="G46" t="s">
-        <v>237</v>
       </c>
       <c r="H46" t="s">
         <v>3</v>
@@ -2868,22 +3015,22 @@
     </row>
     <row r="47" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A47" t="s">
-        <v>238</v>
+        <v>236</v>
       </c>
       <c r="C47" t="s">
-        <v>9</v>
+        <v>26</v>
       </c>
       <c r="D47" t="s">
-        <v>239</v>
+        <v>233</v>
       </c>
       <c r="E47" t="s">
-        <v>240</v>
+        <v>234</v>
       </c>
       <c r="F47" t="s">
         <v>0</v>
       </c>
       <c r="G47" t="s">
-        <v>54</v>
+        <v>235</v>
       </c>
       <c r="H47" t="s">
         <v>3</v>
@@ -2891,22 +3038,22 @@
     </row>
     <row r="48" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A48" t="s">
-        <v>241</v>
+        <v>237</v>
       </c>
       <c r="C48" t="s">
-        <v>9</v>
+        <v>26</v>
       </c>
       <c r="D48" t="s">
-        <v>239</v>
+        <v>233</v>
       </c>
       <c r="E48" t="s">
-        <v>240</v>
+        <v>234</v>
       </c>
       <c r="F48" t="s">
         <v>0</v>
       </c>
       <c r="G48" t="s">
-        <v>54</v>
+        <v>235</v>
       </c>
       <c r="H48" t="s">
         <v>3</v>
@@ -2914,22 +3061,22 @@
     </row>
     <row r="49" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A49" t="s">
-        <v>242</v>
+        <v>238</v>
       </c>
       <c r="C49" t="s">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="D49" t="s">
         <v>239</v>
       </c>
       <c r="E49" t="s">
+        <v>48</v>
+      </c>
+      <c r="F49" t="s">
+        <v>0</v>
+      </c>
+      <c r="G49" t="s">
         <v>240</v>
-      </c>
-      <c r="F49" t="s">
-        <v>0</v>
-      </c>
-      <c r="G49" t="s">
-        <v>54</v>
       </c>
       <c r="H49" t="s">
         <v>3</v>
@@ -2937,22 +3084,22 @@
     </row>
     <row r="50" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A50" t="s">
-        <v>243</v>
+        <v>241</v>
       </c>
       <c r="C50" t="s">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="D50" t="s">
-        <v>244</v>
+        <v>239</v>
       </c>
       <c r="E50" t="s">
-        <v>41</v>
+        <v>48</v>
       </c>
       <c r="F50" t="s">
         <v>0</v>
       </c>
       <c r="G50" t="s">
-        <v>245</v>
+        <v>240</v>
       </c>
       <c r="H50" t="s">
         <v>3</v>
@@ -2960,22 +3107,22 @@
     </row>
     <row r="51" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A51" t="s">
-        <v>246</v>
+        <v>242</v>
       </c>
       <c r="C51" t="s">
-        <v>9</v>
+        <v>28</v>
       </c>
       <c r="D51" t="s">
+        <v>243</v>
+      </c>
+      <c r="E51" t="s">
+        <v>186</v>
+      </c>
+      <c r="F51" t="s">
+        <v>0</v>
+      </c>
+      <c r="G51" t="s">
         <v>244</v>
-      </c>
-      <c r="E51" t="s">
-        <v>41</v>
-      </c>
-      <c r="F51" t="s">
-        <v>0</v>
-      </c>
-      <c r="G51" t="s">
-        <v>245</v>
       </c>
       <c r="H51" t="s">
         <v>3</v>
@@ -2983,22 +3130,22 @@
     </row>
     <row r="52" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A52" t="s">
+        <v>245</v>
+      </c>
+      <c r="C52" t="s">
+        <v>5</v>
+      </c>
+      <c r="D52" t="s">
+        <v>246</v>
+      </c>
+      <c r="E52" t="s">
+        <v>219</v>
+      </c>
+      <c r="F52" t="s">
+        <v>220</v>
+      </c>
+      <c r="G52" t="s">
         <v>247</v>
-      </c>
-      <c r="C52" t="s">
-        <v>44</v>
-      </c>
-      <c r="D52" t="s">
-        <v>248</v>
-      </c>
-      <c r="E52" t="s">
-        <v>249</v>
-      </c>
-      <c r="F52" t="s">
-        <v>250</v>
-      </c>
-      <c r="G52" t="s">
-        <v>251</v>
       </c>
       <c r="H52" t="s">
         <v>3</v>
@@ -3006,22 +3153,22 @@
     </row>
     <row r="53" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A53" t="s">
-        <v>252</v>
+        <v>248</v>
       </c>
       <c r="C53" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="D53" t="s">
-        <v>253</v>
+        <v>246</v>
       </c>
       <c r="E53" t="s">
-        <v>188</v>
+        <v>219</v>
       </c>
       <c r="F53" t="s">
-        <v>0</v>
+        <v>220</v>
       </c>
       <c r="G53" t="s">
-        <v>254</v>
+        <v>247</v>
       </c>
       <c r="H53" t="s">
         <v>3</v>
@@ -3029,22 +3176,22 @@
     </row>
     <row r="54" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A54" t="s">
-        <v>255</v>
+        <v>249</v>
       </c>
       <c r="C54" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="D54" t="s">
-        <v>253</v>
+        <v>250</v>
       </c>
       <c r="E54" t="s">
-        <v>188</v>
+        <v>62</v>
       </c>
       <c r="F54" t="s">
         <v>0</v>
       </c>
       <c r="G54" t="s">
-        <v>254</v>
+        <v>251</v>
       </c>
       <c r="H54" t="s">
         <v>3</v>
@@ -3052,22 +3199,22 @@
     </row>
     <row r="55" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A55" t="s">
-        <v>256</v>
+        <v>252</v>
       </c>
       <c r="C55" t="s">
-        <v>7</v>
+        <v>176</v>
       </c>
       <c r="D55" t="s">
         <v>253</v>
       </c>
       <c r="E55" t="s">
-        <v>188</v>
+        <v>254</v>
       </c>
       <c r="F55" t="s">
         <v>0</v>
       </c>
       <c r="G55" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="H55" t="s">
         <v>3</v>
@@ -3075,22 +3222,22 @@
     </row>
     <row r="56" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A56" t="s">
-        <v>257</v>
+        <v>256</v>
       </c>
       <c r="C56" t="s">
-        <v>5</v>
+        <v>176</v>
       </c>
       <c r="D56" t="s">
-        <v>258</v>
+        <v>253</v>
       </c>
       <c r="E56" t="s">
-        <v>72</v>
+        <v>254</v>
       </c>
       <c r="F56" t="s">
         <v>0</v>
       </c>
       <c r="G56" t="s">
-        <v>259</v>
+        <v>255</v>
       </c>
       <c r="H56" t="s">
         <v>3</v>
@@ -3098,22 +3245,22 @@
     </row>
     <row r="57" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A57" t="s">
+        <v>257</v>
+      </c>
+      <c r="C57" t="s">
+        <v>43</v>
+      </c>
+      <c r="D57" t="s">
+        <v>258</v>
+      </c>
+      <c r="E57" t="s">
+        <v>259</v>
+      </c>
+      <c r="F57" t="s">
         <v>260</v>
       </c>
-      <c r="C57" t="s">
-        <v>2</v>
-      </c>
-      <c r="D57" t="s">
+      <c r="G57" t="s">
         <v>261</v>
-      </c>
-      <c r="E57" t="s">
-        <v>262</v>
-      </c>
-      <c r="F57" t="s">
-        <v>0</v>
-      </c>
-      <c r="G57" t="s">
-        <v>263</v>
       </c>
       <c r="H57" t="s">
         <v>3</v>
@@ -3121,22 +3268,22 @@
     </row>
     <row r="58" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A58" t="s">
-        <v>264</v>
+        <v>262</v>
       </c>
       <c r="C58" t="s">
-        <v>2</v>
+        <v>43</v>
       </c>
       <c r="D58" t="s">
+        <v>258</v>
+      </c>
+      <c r="E58" t="s">
+        <v>259</v>
+      </c>
+      <c r="F58" t="s">
+        <v>260</v>
+      </c>
+      <c r="G58" t="s">
         <v>261</v>
-      </c>
-      <c r="E58" t="s">
-        <v>262</v>
-      </c>
-      <c r="F58" t="s">
-        <v>0</v>
-      </c>
-      <c r="G58" t="s">
-        <v>263</v>
       </c>
       <c r="H58" t="s">
         <v>3</v>
@@ -3144,22 +3291,22 @@
     </row>
     <row r="59" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A59" t="s">
-        <v>265</v>
+        <v>263</v>
       </c>
       <c r="C59" t="s">
         <v>2</v>
       </c>
       <c r="D59" t="s">
-        <v>261</v>
+        <v>264</v>
       </c>
       <c r="E59" t="s">
-        <v>262</v>
+        <v>265</v>
       </c>
       <c r="F59" t="s">
-        <v>0</v>
+        <v>266</v>
       </c>
       <c r="G59" t="s">
-        <v>263</v>
+        <v>267</v>
       </c>
       <c r="H59" t="s">
         <v>3</v>
@@ -3167,22 +3314,22 @@
     </row>
     <row r="60" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A60" t="s">
-        <v>266</v>
+        <v>268</v>
       </c>
       <c r="C60" t="s">
-        <v>30</v>
+        <v>43</v>
       </c>
       <c r="D60" t="s">
-        <v>267</v>
+        <v>269</v>
       </c>
       <c r="E60" t="s">
-        <v>27</v>
+        <v>270</v>
       </c>
       <c r="F60" t="s">
-        <v>28</v>
+        <v>271</v>
       </c>
       <c r="G60" t="s">
-        <v>268</v>
+        <v>272</v>
       </c>
       <c r="H60" t="s">
         <v>3</v>
@@ -3190,22 +3337,22 @@
     </row>
     <row r="61" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A61" t="s">
+        <v>273</v>
+      </c>
+      <c r="C61" t="s">
+        <v>43</v>
+      </c>
+      <c r="D61" t="s">
         <v>269</v>
       </c>
-      <c r="C61" t="s">
-        <v>22</v>
-      </c>
-      <c r="D61" t="s">
+      <c r="E61" t="s">
         <v>270</v>
       </c>
-      <c r="E61" t="s">
-        <v>46</v>
-      </c>
       <c r="F61" t="s">
-        <v>0</v>
+        <v>271</v>
       </c>
       <c r="G61" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="H61" t="s">
         <v>3</v>
@@ -3213,22 +3360,22 @@
     </row>
     <row r="62" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A62" t="s">
+        <v>274</v>
+      </c>
+      <c r="C62" t="s">
+        <v>43</v>
+      </c>
+      <c r="D62" t="s">
+        <v>269</v>
+      </c>
+      <c r="E62" t="s">
+        <v>270</v>
+      </c>
+      <c r="F62" t="s">
+        <v>271</v>
+      </c>
+      <c r="G62" t="s">
         <v>272</v>
-      </c>
-      <c r="C62" t="s">
-        <v>22</v>
-      </c>
-      <c r="D62" t="s">
-        <v>270</v>
-      </c>
-      <c r="E62" t="s">
-        <v>46</v>
-      </c>
-      <c r="F62" t="s">
-        <v>0</v>
-      </c>
-      <c r="G62" t="s">
-        <v>271</v>
       </c>
       <c r="H62" t="s">
         <v>3</v>
@@ -3236,22 +3383,22 @@
     </row>
     <row r="63" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A63" t="s">
-        <v>273</v>
+        <v>275</v>
       </c>
       <c r="C63" t="s">
-        <v>61</v>
+        <v>22</v>
       </c>
       <c r="D63" t="s">
-        <v>274</v>
+        <v>276</v>
       </c>
       <c r="E63" t="s">
-        <v>275</v>
+        <v>277</v>
       </c>
       <c r="F63" t="s">
-        <v>276</v>
+        <v>0</v>
       </c>
       <c r="G63" t="s">
-        <v>277</v>
+        <v>165</v>
       </c>
       <c r="H63" t="s">
         <v>3</v>
@@ -3262,19 +3409,19 @@
         <v>278</v>
       </c>
       <c r="C64" t="s">
-        <v>61</v>
+        <v>124</v>
       </c>
       <c r="D64" t="s">
-        <v>274</v>
+        <v>279</v>
       </c>
       <c r="E64" t="s">
-        <v>275</v>
+        <v>36</v>
       </c>
       <c r="F64" t="s">
-        <v>276</v>
+        <v>0</v>
       </c>
       <c r="G64" t="s">
-        <v>277</v>
+        <v>280</v>
       </c>
       <c r="H64" t="s">
         <v>3</v>
@@ -3282,22 +3429,22 @@
     </row>
     <row r="65" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A65" t="s">
-        <v>279</v>
+        <v>281</v>
       </c>
       <c r="C65" t="s">
-        <v>61</v>
+        <v>43</v>
       </c>
       <c r="D65" t="s">
-        <v>274</v>
+        <v>282</v>
       </c>
       <c r="E65" t="s">
-        <v>275</v>
+        <v>259</v>
       </c>
       <c r="F65" t="s">
-        <v>276</v>
+        <v>260</v>
       </c>
       <c r="G65" t="s">
-        <v>277</v>
+        <v>283</v>
       </c>
       <c r="H65" t="s">
         <v>3</v>
@@ -3305,19 +3452,19 @@
     </row>
     <row r="66" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A66" t="s">
-        <v>280</v>
+        <v>284</v>
       </c>
       <c r="C66" t="s">
-        <v>5</v>
+        <v>43</v>
       </c>
       <c r="D66" t="s">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="E66" t="s">
-        <v>282</v>
+        <v>259</v>
       </c>
       <c r="F66" t="s">
-        <v>0</v>
+        <v>260</v>
       </c>
       <c r="G66" t="s">
         <v>283</v>
@@ -3328,22 +3475,22 @@
     </row>
     <row r="67" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A67" t="s">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="C67" t="s">
-        <v>5</v>
+        <v>105</v>
       </c>
       <c r="D67" t="s">
-        <v>281</v>
+        <v>286</v>
       </c>
       <c r="E67" t="s">
-        <v>282</v>
+        <v>52</v>
       </c>
       <c r="F67" t="s">
-        <v>0</v>
+        <v>42</v>
       </c>
       <c r="G67" t="s">
-        <v>283</v>
+        <v>287</v>
       </c>
       <c r="H67" t="s">
         <v>3</v>
@@ -3351,22 +3498,22 @@
     </row>
     <row r="68" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A68" t="s">
-        <v>285</v>
+        <v>288</v>
       </c>
       <c r="C68" t="s">
-        <v>5</v>
+        <v>18</v>
       </c>
       <c r="D68" t="s">
-        <v>281</v>
+        <v>289</v>
       </c>
       <c r="E68" t="s">
-        <v>282</v>
+        <v>290</v>
       </c>
       <c r="F68" t="s">
-        <v>0</v>
+        <v>291</v>
       </c>
       <c r="G68" t="s">
-        <v>283</v>
+        <v>292</v>
       </c>
       <c r="H68" t="s">
         <v>3</v>
@@ -3374,22 +3521,22 @@
     </row>
     <row r="69" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A69" t="s">
-        <v>286</v>
+        <v>293</v>
       </c>
       <c r="C69" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="D69" t="s">
-        <v>287</v>
+        <v>294</v>
       </c>
       <c r="E69" t="s">
-        <v>52</v>
+        <v>37</v>
       </c>
       <c r="F69" t="s">
-        <v>53</v>
+        <v>0</v>
       </c>
       <c r="G69" t="s">
-        <v>288</v>
+        <v>295</v>
       </c>
       <c r="H69" t="s">
         <v>3</v>
@@ -3397,22 +3544,22 @@
     </row>
     <row r="70" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A70" t="s">
-        <v>289</v>
+        <v>296</v>
       </c>
       <c r="C70" t="s">
-        <v>33</v>
+        <v>142</v>
       </c>
       <c r="D70" t="s">
-        <v>287</v>
+        <v>297</v>
       </c>
       <c r="E70" t="s">
-        <v>52</v>
+        <v>298</v>
       </c>
       <c r="F70" t="s">
-        <v>53</v>
+        <v>0</v>
       </c>
       <c r="G70" t="s">
-        <v>288</v>
+        <v>299</v>
       </c>
       <c r="H70" t="s">
         <v>3</v>
@@ -3420,22 +3567,22 @@
     </row>
     <row r="71" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A71" t="s">
-        <v>290</v>
+        <v>300</v>
       </c>
       <c r="C71" t="s">
-        <v>6</v>
+        <v>301</v>
       </c>
       <c r="D71" t="s">
-        <v>291</v>
+        <v>302</v>
       </c>
       <c r="E71" t="s">
-        <v>34</v>
+        <v>58</v>
       </c>
       <c r="F71" t="s">
         <v>0</v>
       </c>
       <c r="G71" t="s">
-        <v>292</v>
+        <v>303</v>
       </c>
       <c r="H71" t="s">
         <v>3</v>
@@ -3443,22 +3590,22 @@
     </row>
     <row r="72" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A72" t="s">
-        <v>293</v>
+        <v>304</v>
       </c>
       <c r="C72" t="s">
-        <v>44</v>
+        <v>2</v>
       </c>
       <c r="D72" t="s">
-        <v>294</v>
+        <v>305</v>
       </c>
       <c r="E72" t="s">
-        <v>295</v>
+        <v>306</v>
       </c>
       <c r="F72" t="s">
-        <v>0</v>
+        <v>307</v>
       </c>
       <c r="G72" t="s">
-        <v>296</v>
+        <v>308</v>
       </c>
       <c r="H72" t="s">
         <v>3</v>
@@ -3466,22 +3613,22 @@
     </row>
     <row r="73" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A73" t="s">
-        <v>297</v>
+        <v>309</v>
       </c>
       <c r="C73" t="s">
-        <v>5</v>
+        <v>43</v>
       </c>
       <c r="D73" t="s">
-        <v>298</v>
+        <v>310</v>
       </c>
       <c r="E73" t="s">
-        <v>299</v>
+        <v>211</v>
       </c>
       <c r="F73" t="s">
-        <v>0</v>
+        <v>212</v>
       </c>
       <c r="G73" t="s">
-        <v>300</v>
+        <v>74</v>
       </c>
       <c r="H73" t="s">
         <v>3</v>
@@ -3489,22 +3636,22 @@
     </row>
     <row r="74" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A74" t="s">
-        <v>301</v>
+        <v>311</v>
       </c>
       <c r="C74" t="s">
-        <v>5</v>
+        <v>43</v>
       </c>
       <c r="D74" t="s">
-        <v>298</v>
+        <v>312</v>
       </c>
       <c r="E74" t="s">
-        <v>299</v>
+        <v>63</v>
       </c>
       <c r="F74" t="s">
-        <v>0</v>
+        <v>64</v>
       </c>
       <c r="G74" t="s">
-        <v>300</v>
+        <v>313</v>
       </c>
       <c r="H74" t="s">
         <v>3</v>
@@ -3512,22 +3659,22 @@
     </row>
     <row r="75" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A75" t="s">
-        <v>302</v>
+        <v>314</v>
       </c>
       <c r="C75" t="s">
-        <v>5</v>
+        <v>142</v>
       </c>
       <c r="D75" t="s">
-        <v>298</v>
+        <v>315</v>
       </c>
       <c r="E75" t="s">
-        <v>299</v>
+        <v>65</v>
       </c>
       <c r="F75" t="s">
         <v>0</v>
       </c>
       <c r="G75" t="s">
-        <v>300</v>
+        <v>316</v>
       </c>
       <c r="H75" t="s">
         <v>3</v>
@@ -3535,22 +3682,22 @@
     </row>
     <row r="76" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A76" t="s">
-        <v>303</v>
+        <v>317</v>
       </c>
       <c r="C76" t="s">
-        <v>9</v>
+        <v>29</v>
       </c>
       <c r="D76" t="s">
-        <v>304</v>
+        <v>318</v>
       </c>
       <c r="E76" t="s">
-        <v>41</v>
+        <v>319</v>
       </c>
       <c r="F76" t="s">
-        <v>0</v>
+        <v>320</v>
       </c>
       <c r="G76" t="s">
-        <v>305</v>
+        <v>321</v>
       </c>
       <c r="H76" t="s">
         <v>3</v>
@@ -3558,22 +3705,22 @@
     </row>
     <row r="77" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A77" t="s">
-        <v>306</v>
+        <v>322</v>
       </c>
       <c r="C77" t="s">
-        <v>9</v>
+        <v>29</v>
       </c>
       <c r="D77" t="s">
-        <v>304</v>
+        <v>323</v>
       </c>
       <c r="E77" t="s">
-        <v>41</v>
+        <v>324</v>
       </c>
       <c r="F77" t="s">
-        <v>0</v>
+        <v>325</v>
       </c>
       <c r="G77" t="s">
-        <v>305</v>
+        <v>326</v>
       </c>
       <c r="H77" t="s">
         <v>3</v>
@@ -3581,22 +3728,22 @@
     </row>
     <row r="78" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A78" t="s">
-        <v>307</v>
+        <v>327</v>
       </c>
       <c r="C78" t="s">
+        <v>27</v>
+      </c>
+      <c r="D78" t="s">
+        <v>328</v>
+      </c>
+      <c r="E78" t="s">
         <v>25</v>
       </c>
-      <c r="D78" t="s">
-        <v>308</v>
-      </c>
-      <c r="E78" t="s">
-        <v>309</v>
-      </c>
       <c r="F78" t="s">
         <v>0</v>
       </c>
       <c r="G78" t="s">
-        <v>310</v>
+        <v>329</v>
       </c>
       <c r="H78" t="s">
         <v>3</v>
@@ -3604,22 +3751,22 @@
     </row>
     <row r="79" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A79" t="s">
-        <v>311</v>
+        <v>330</v>
       </c>
       <c r="C79" t="s">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="D79" t="s">
-        <v>312</v>
+        <v>331</v>
       </c>
       <c r="E79" t="s">
-        <v>77</v>
+        <v>332</v>
       </c>
       <c r="F79" t="s">
-        <v>78</v>
+        <v>0</v>
       </c>
       <c r="G79" t="s">
-        <v>71</v>
+        <v>333</v>
       </c>
       <c r="H79" t="s">
         <v>3</v>
@@ -3627,22 +3774,22 @@
     </row>
     <row r="80" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A80" t="s">
-        <v>313</v>
+        <v>334</v>
       </c>
       <c r="C80" t="s">
-        <v>6</v>
+        <v>124</v>
       </c>
       <c r="D80" t="s">
-        <v>312</v>
+        <v>335</v>
       </c>
       <c r="E80" t="s">
-        <v>77</v>
+        <v>336</v>
       </c>
       <c r="F80" t="s">
-        <v>78</v>
+        <v>0</v>
       </c>
       <c r="G80" t="s">
-        <v>71</v>
+        <v>337</v>
       </c>
       <c r="H80" t="s">
         <v>3</v>
@@ -3650,22 +3797,22 @@
     </row>
     <row r="81" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A81" t="s">
-        <v>314</v>
+        <v>338</v>
       </c>
       <c r="C81" t="s">
-        <v>21</v>
+        <v>124</v>
       </c>
       <c r="D81" t="s">
-        <v>315</v>
+        <v>335</v>
       </c>
       <c r="E81" t="s">
-        <v>316</v>
+        <v>336</v>
       </c>
       <c r="F81" t="s">
         <v>0</v>
       </c>
       <c r="G81" t="s">
-        <v>317</v>
+        <v>337</v>
       </c>
       <c r="H81" t="s">
         <v>3</v>
@@ -3673,22 +3820,22 @@
     </row>
     <row r="82" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A82" t="s">
-        <v>318</v>
+        <v>339</v>
       </c>
       <c r="C82" t="s">
-        <v>21</v>
+        <v>27</v>
       </c>
       <c r="D82" t="s">
-        <v>315</v>
+        <v>340</v>
       </c>
       <c r="E82" t="s">
-        <v>316</v>
+        <v>341</v>
       </c>
       <c r="F82" t="s">
-        <v>0</v>
+        <v>342</v>
       </c>
       <c r="G82" t="s">
-        <v>317</v>
+        <v>343</v>
       </c>
       <c r="H82" t="s">
         <v>3</v>
@@ -3696,22 +3843,22 @@
     </row>
     <row r="83" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A83" t="s">
-        <v>319</v>
+        <v>344</v>
       </c>
       <c r="C83" t="s">
-        <v>21</v>
+        <v>138</v>
       </c>
       <c r="D83" t="s">
-        <v>315</v>
+        <v>345</v>
       </c>
       <c r="E83" t="s">
-        <v>316</v>
+        <v>9</v>
       </c>
       <c r="F83" t="s">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="G83" t="s">
-        <v>317</v>
+        <v>346</v>
       </c>
       <c r="H83" t="s">
         <v>3</v>
@@ -3719,22 +3866,22 @@
     </row>
     <row r="84" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A84" t="s">
-        <v>320</v>
+        <v>347</v>
       </c>
       <c r="C84" t="s">
-        <v>61</v>
+        <v>22</v>
       </c>
       <c r="D84" t="s">
-        <v>321</v>
+        <v>348</v>
       </c>
       <c r="E84" t="s">
-        <v>42</v>
+        <v>79</v>
       </c>
       <c r="F84" t="s">
         <v>0</v>
       </c>
       <c r="G84" t="s">
-        <v>55</v>
+        <v>349</v>
       </c>
       <c r="H84" t="s">
         <v>3</v>
@@ -3742,22 +3889,22 @@
     </row>
     <row r="85" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A85" t="s">
-        <v>322</v>
+        <v>350</v>
       </c>
       <c r="C85" t="s">
-        <v>61</v>
+        <v>31</v>
       </c>
       <c r="D85" t="s">
-        <v>321</v>
+        <v>351</v>
       </c>
       <c r="E85" t="s">
-        <v>42</v>
+        <v>75</v>
       </c>
       <c r="F85" t="s">
         <v>0</v>
       </c>
       <c r="G85" t="s">
-        <v>55</v>
+        <v>352</v>
       </c>
       <c r="H85" t="s">
         <v>3</v>
@@ -3765,22 +3912,22 @@
     </row>
     <row r="86" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A86" t="s">
-        <v>323</v>
+        <v>353</v>
       </c>
       <c r="C86" t="s">
         <v>7</v>
       </c>
       <c r="D86" t="s">
-        <v>324</v>
+        <v>354</v>
       </c>
       <c r="E86" t="s">
-        <v>325</v>
+        <v>355</v>
       </c>
       <c r="F86" t="s">
         <v>0</v>
       </c>
       <c r="G86" t="s">
-        <v>326</v>
+        <v>356</v>
       </c>
       <c r="H86" t="s">
         <v>3</v>
@@ -3788,22 +3935,22 @@
     </row>
     <row r="87" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A87" t="s">
-        <v>327</v>
+        <v>357</v>
       </c>
       <c r="C87" t="s">
-        <v>61</v>
+        <v>27</v>
       </c>
       <c r="D87" t="s">
-        <v>328</v>
+        <v>358</v>
       </c>
       <c r="E87" t="s">
-        <v>74</v>
+        <v>359</v>
       </c>
       <c r="F87" t="s">
-        <v>0</v>
+        <v>360</v>
       </c>
       <c r="G87" t="s">
-        <v>329</v>
+        <v>361</v>
       </c>
       <c r="H87" t="s">
         <v>3</v>
@@ -3811,22 +3958,22 @@
     </row>
     <row r="88" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A88" t="s">
-        <v>330</v>
+        <v>362</v>
       </c>
       <c r="C88" t="s">
-        <v>21</v>
+        <v>28</v>
       </c>
       <c r="D88" t="s">
-        <v>331</v>
+        <v>363</v>
       </c>
       <c r="E88" t="s">
-        <v>332</v>
+        <v>364</v>
       </c>
       <c r="F88" t="s">
-        <v>333</v>
+        <v>0</v>
       </c>
       <c r="G88" t="s">
-        <v>334</v>
+        <v>365</v>
       </c>
       <c r="H88" t="s">
         <v>3</v>
@@ -3834,22 +3981,22 @@
     </row>
     <row r="89" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A89" t="s">
-        <v>335</v>
+        <v>366</v>
       </c>
       <c r="C89" t="s">
-        <v>31</v>
+        <v>22</v>
       </c>
       <c r="D89" t="s">
-        <v>336</v>
+        <v>367</v>
       </c>
       <c r="E89" t="s">
-        <v>29</v>
+        <v>193</v>
       </c>
       <c r="F89" t="s">
         <v>0</v>
       </c>
       <c r="G89" t="s">
-        <v>337</v>
+        <v>368</v>
       </c>
       <c r="H89" t="s">
         <v>3</v>
@@ -3857,22 +4004,22 @@
     </row>
     <row r="90" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A90" t="s">
-        <v>338</v>
+        <v>369</v>
       </c>
       <c r="C90" t="s">
-        <v>31</v>
+        <v>142</v>
       </c>
       <c r="D90" t="s">
-        <v>339</v>
+        <v>370</v>
       </c>
       <c r="E90" t="s">
-        <v>340</v>
+        <v>371</v>
       </c>
       <c r="F90" t="s">
         <v>0</v>
       </c>
       <c r="G90" t="s">
-        <v>341</v>
+        <v>372</v>
       </c>
       <c r="H90" t="s">
         <v>3</v>
@@ -3880,22 +4027,22 @@
     </row>
     <row r="91" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A91" t="s">
-        <v>342</v>
+        <v>373</v>
       </c>
       <c r="C91" t="s">
-        <v>25</v>
+        <v>124</v>
       </c>
       <c r="D91" t="s">
-        <v>343</v>
+        <v>374</v>
       </c>
       <c r="E91" t="s">
-        <v>45</v>
+        <v>36</v>
       </c>
       <c r="F91" t="s">
         <v>0</v>
       </c>
       <c r="G91" t="s">
-        <v>344</v>
+        <v>280</v>
       </c>
       <c r="H91" t="s">
         <v>3</v>
@@ -3903,22 +4050,22 @@
     </row>
     <row r="92" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A92" t="s">
-        <v>345</v>
+        <v>375</v>
       </c>
       <c r="C92" t="s">
-        <v>25</v>
+        <v>124</v>
       </c>
       <c r="D92" t="s">
-        <v>343</v>
+        <v>374</v>
       </c>
       <c r="E92" t="s">
-        <v>45</v>
+        <v>36</v>
       </c>
       <c r="F92" t="s">
         <v>0</v>
       </c>
       <c r="G92" t="s">
-        <v>344</v>
+        <v>280</v>
       </c>
       <c r="H92" t="s">
         <v>3</v>
@@ -3926,22 +4073,22 @@
     </row>
     <row r="93" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A93" t="s">
-        <v>346</v>
+        <v>376</v>
       </c>
       <c r="C93" t="s">
-        <v>6</v>
+        <v>142</v>
       </c>
       <c r="D93" t="s">
-        <v>347</v>
+        <v>377</v>
       </c>
       <c r="E93" t="s">
-        <v>38</v>
+        <v>71</v>
       </c>
       <c r="F93" t="s">
         <v>0</v>
       </c>
       <c r="G93" t="s">
-        <v>348</v>
+        <v>49</v>
       </c>
       <c r="H93" t="s">
         <v>3</v>
@@ -3949,22 +4096,22 @@
     </row>
     <row r="94" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A94" t="s">
-        <v>349</v>
+        <v>378</v>
       </c>
       <c r="C94" t="s">
-        <v>9</v>
+        <v>43</v>
       </c>
       <c r="D94" t="s">
-        <v>350</v>
+        <v>379</v>
       </c>
       <c r="E94" t="s">
-        <v>351</v>
+        <v>56</v>
       </c>
       <c r="F94" t="s">
-        <v>352</v>
+        <v>57</v>
       </c>
       <c r="G94" t="s">
-        <v>353</v>
+        <v>380</v>
       </c>
       <c r="H94" t="s">
         <v>3</v>
@@ -3972,22 +4119,22 @@
     </row>
     <row r="95" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A95" t="s">
-        <v>354</v>
+        <v>381</v>
       </c>
       <c r="C95" t="s">
-        <v>7</v>
+        <v>18</v>
       </c>
       <c r="D95" t="s">
-        <v>355</v>
+        <v>382</v>
       </c>
       <c r="E95" t="s">
-        <v>75</v>
+        <v>38</v>
       </c>
       <c r="F95" t="s">
-        <v>0</v>
+        <v>39</v>
       </c>
       <c r="G95" t="s">
-        <v>356</v>
+        <v>383</v>
       </c>
       <c r="H95" t="s">
         <v>3</v>
@@ -3995,22 +4142,22 @@
     </row>
     <row r="96" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A96" t="s">
-        <v>357</v>
+        <v>384</v>
       </c>
       <c r="C96" t="s">
-        <v>132</v>
+        <v>18</v>
       </c>
       <c r="D96" t="s">
-        <v>358</v>
+        <v>382</v>
       </c>
       <c r="E96" t="s">
-        <v>359</v>
+        <v>38</v>
       </c>
       <c r="F96" t="s">
-        <v>0</v>
+        <v>39</v>
       </c>
       <c r="G96" t="s">
-        <v>360</v>
+        <v>383</v>
       </c>
       <c r="H96" t="s">
         <v>3</v>
@@ -4018,22 +4165,22 @@
     </row>
     <row r="97" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A97" t="s">
-        <v>361</v>
+        <v>385</v>
       </c>
       <c r="C97" t="s">
-        <v>2</v>
+        <v>28</v>
       </c>
       <c r="D97" t="s">
-        <v>362</v>
+        <v>386</v>
       </c>
       <c r="E97" t="s">
-        <v>113</v>
+        <v>70</v>
       </c>
       <c r="F97" t="s">
         <v>0</v>
       </c>
       <c r="G97" t="s">
-        <v>363</v>
+        <v>387</v>
       </c>
       <c r="H97" t="s">
         <v>3</v>
@@ -4041,22 +4188,22 @@
     </row>
     <row r="98" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A98" t="s">
-        <v>364</v>
+        <v>388</v>
       </c>
       <c r="C98" t="s">
-        <v>32</v>
+        <v>27</v>
       </c>
       <c r="D98" t="s">
-        <v>365</v>
+        <v>389</v>
       </c>
       <c r="E98" t="s">
-        <v>366</v>
+        <v>50</v>
       </c>
       <c r="F98" t="s">
         <v>0</v>
       </c>
       <c r="G98" t="s">
-        <v>367</v>
+        <v>390</v>
       </c>
       <c r="H98" t="s">
         <v>3</v>
@@ -4064,22 +4211,22 @@
     </row>
     <row r="99" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A99" t="s">
-        <v>368</v>
+        <v>391</v>
       </c>
       <c r="C99" t="s">
-        <v>2</v>
+        <v>22</v>
       </c>
       <c r="D99" t="s">
-        <v>369</v>
+        <v>392</v>
       </c>
       <c r="E99" t="s">
-        <v>50</v>
+        <v>393</v>
       </c>
       <c r="F99" t="s">
-        <v>51</v>
+        <v>0</v>
       </c>
       <c r="G99" t="s">
-        <v>370</v>
+        <v>394</v>
       </c>
       <c r="H99" t="s">
         <v>3</v>
@@ -4087,22 +4234,22 @@
     </row>
     <row r="100" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A100" t="s">
-        <v>371</v>
+        <v>395</v>
       </c>
       <c r="C100" t="s">
-        <v>132</v>
+        <v>105</v>
       </c>
       <c r="D100" t="s">
-        <v>372</v>
+        <v>396</v>
       </c>
       <c r="E100" t="s">
-        <v>373</v>
+        <v>397</v>
       </c>
       <c r="F100" t="s">
-        <v>0</v>
+        <v>398</v>
       </c>
       <c r="G100" t="s">
-        <v>374</v>
+        <v>399</v>
       </c>
       <c r="H100" t="s">
         <v>3</v>
@@ -4110,22 +4257,22 @@
     </row>
     <row r="101" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A101" t="s">
-        <v>375</v>
+        <v>400</v>
       </c>
       <c r="C101" t="s">
-        <v>22</v>
+        <v>31</v>
       </c>
       <c r="D101" t="s">
-        <v>376</v>
+        <v>401</v>
       </c>
       <c r="E101" t="s">
-        <v>377</v>
+        <v>402</v>
       </c>
       <c r="F101" t="s">
         <v>0</v>
       </c>
       <c r="G101" t="s">
-        <v>79</v>
+        <v>76</v>
       </c>
       <c r="H101" t="s">
         <v>3</v>
@@ -4133,22 +4280,22 @@
     </row>
     <row r="102" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A102" t="s">
-        <v>378</v>
+        <v>403</v>
       </c>
       <c r="C102" t="s">
-        <v>132</v>
+        <v>31</v>
       </c>
       <c r="D102" t="s">
-        <v>379</v>
+        <v>404</v>
       </c>
       <c r="E102" t="s">
-        <v>380</v>
+        <v>405</v>
       </c>
       <c r="F102" t="s">
-        <v>381</v>
+        <v>0</v>
       </c>
       <c r="G102" t="s">
-        <v>382</v>
+        <v>406</v>
       </c>
       <c r="H102" t="s">
         <v>3</v>
@@ -4156,22 +4303,22 @@
     </row>
     <row r="103" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A103" t="s">
-        <v>383</v>
+        <v>407</v>
       </c>
       <c r="C103" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="D103" t="s">
-        <v>384</v>
+        <v>408</v>
       </c>
       <c r="E103" t="s">
-        <v>35</v>
+        <v>48</v>
       </c>
       <c r="F103" t="s">
         <v>0</v>
       </c>
       <c r="G103" t="s">
-        <v>385</v>
+        <v>409</v>
       </c>
       <c r="H103" t="s">
         <v>3</v>
@@ -4179,22 +4326,22 @@
     </row>
     <row r="104" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A104" t="s">
-        <v>386</v>
+        <v>410</v>
       </c>
       <c r="C104" t="s">
-        <v>30</v>
+        <v>27</v>
       </c>
       <c r="D104" t="s">
-        <v>387</v>
+        <v>411</v>
       </c>
       <c r="E104" t="s">
-        <v>96</v>
+        <v>412</v>
       </c>
       <c r="F104" t="s">
-        <v>97</v>
+        <v>0</v>
       </c>
       <c r="G104" t="s">
-        <v>388</v>
+        <v>413</v>
       </c>
       <c r="H104" t="s">
         <v>3</v>
@@ -4202,22 +4349,22 @@
     </row>
     <row r="105" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A105" t="s">
-        <v>389</v>
+        <v>414</v>
       </c>
       <c r="C105" t="s">
-        <v>21</v>
+        <v>27</v>
       </c>
       <c r="D105" t="s">
-        <v>390</v>
+        <v>411</v>
       </c>
       <c r="E105" t="s">
-        <v>391</v>
+        <v>412</v>
       </c>
       <c r="F105" t="s">
         <v>0</v>
       </c>
       <c r="G105" t="s">
-        <v>392</v>
+        <v>413</v>
       </c>
       <c r="H105" t="s">
         <v>3</v>
@@ -4225,22 +4372,22 @@
     </row>
     <row r="106" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A106" t="s">
-        <v>393</v>
+        <v>415</v>
       </c>
       <c r="C106" t="s">
-        <v>37</v>
+        <v>27</v>
       </c>
       <c r="D106" t="s">
-        <v>394</v>
+        <v>411</v>
       </c>
       <c r="E106" t="s">
-        <v>81</v>
+        <v>412</v>
       </c>
       <c r="F106" t="s">
         <v>0</v>
       </c>
       <c r="G106" t="s">
-        <v>395</v>
+        <v>413</v>
       </c>
       <c r="H106" t="s">
         <v>3</v>
@@ -4248,22 +4395,22 @@
     </row>
     <row r="107" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A107" t="s">
-        <v>396</v>
+        <v>416</v>
       </c>
       <c r="C107" t="s">
-        <v>2</v>
+        <v>35</v>
       </c>
       <c r="D107" t="s">
-        <v>397</v>
+        <v>417</v>
       </c>
       <c r="E107" t="s">
-        <v>398</v>
+        <v>418</v>
       </c>
       <c r="F107" t="s">
-        <v>399</v>
+        <v>419</v>
       </c>
       <c r="G107" t="s">
-        <v>400</v>
+        <v>420</v>
       </c>
       <c r="H107" t="s">
         <v>3</v>
@@ -4271,22 +4418,22 @@
     </row>
     <row r="108" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A108" t="s">
-        <v>401</v>
+        <v>421</v>
       </c>
       <c r="C108" t="s">
-        <v>9</v>
+        <v>105</v>
       </c>
       <c r="D108" t="s">
-        <v>402</v>
+        <v>422</v>
       </c>
       <c r="E108" t="s">
-        <v>240</v>
+        <v>423</v>
       </c>
       <c r="F108" t="s">
-        <v>0</v>
+        <v>424</v>
       </c>
       <c r="G108" t="s">
-        <v>403</v>
+        <v>425</v>
       </c>
       <c r="H108" t="s">
         <v>3</v>
@@ -4294,22 +4441,22 @@
     </row>
     <row r="109" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A109" t="s">
-        <v>404</v>
+        <v>426</v>
       </c>
       <c r="C109" t="s">
-        <v>25</v>
+        <v>105</v>
       </c>
       <c r="D109" t="s">
-        <v>405</v>
+        <v>427</v>
       </c>
       <c r="E109" t="s">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="F109" t="s">
         <v>0</v>
       </c>
       <c r="G109" t="s">
-        <v>406</v>
+        <v>428</v>
       </c>
       <c r="H109" t="s">
         <v>3</v>
@@ -4317,22 +4464,22 @@
     </row>
     <row r="110" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A110" t="s">
-        <v>407</v>
+        <v>429</v>
       </c>
       <c r="C110" t="s">
-        <v>2</v>
+        <v>18</v>
       </c>
       <c r="D110" t="s">
-        <v>408</v>
+        <v>430</v>
       </c>
       <c r="E110" t="s">
-        <v>262</v>
+        <v>38</v>
       </c>
       <c r="F110" t="s">
-        <v>0</v>
+        <v>39</v>
       </c>
       <c r="G110" t="s">
-        <v>409</v>
+        <v>431</v>
       </c>
       <c r="H110" t="s">
         <v>3</v>
@@ -4340,22 +4487,22 @@
     </row>
     <row r="111" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A111" t="s">
-        <v>410</v>
+        <v>432</v>
       </c>
       <c r="C111" t="s">
-        <v>30</v>
+        <v>124</v>
       </c>
       <c r="D111" t="s">
-        <v>411</v>
+        <v>433</v>
       </c>
       <c r="E111" t="s">
-        <v>176</v>
+        <v>434</v>
       </c>
       <c r="F111" t="s">
-        <v>177</v>
+        <v>0</v>
       </c>
       <c r="G111" t="s">
-        <v>412</v>
+        <v>435</v>
       </c>
       <c r="H111" t="s">
         <v>3</v>
@@ -4363,22 +4510,22 @@
     </row>
     <row r="112" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A112" t="s">
-        <v>413</v>
+        <v>436</v>
       </c>
       <c r="C112" t="s">
-        <v>9</v>
+        <v>18</v>
       </c>
       <c r="D112" t="s">
-        <v>414</v>
+        <v>437</v>
       </c>
       <c r="E112" t="s">
-        <v>23</v>
+        <v>438</v>
       </c>
       <c r="F112" t="s">
-        <v>24</v>
+        <v>0</v>
       </c>
       <c r="G112" t="s">
-        <v>201</v>
+        <v>439</v>
       </c>
       <c r="H112" t="s">
         <v>3</v>
@@ -4386,22 +4533,22 @@
     </row>
     <row r="113" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A113" t="s">
-        <v>415</v>
+        <v>440</v>
       </c>
       <c r="C113" t="s">
-        <v>25</v>
+        <v>22</v>
       </c>
       <c r="D113" t="s">
-        <v>416</v>
+        <v>441</v>
       </c>
       <c r="E113" t="s">
-        <v>88</v>
+        <v>442</v>
       </c>
       <c r="F113" t="s">
-        <v>58</v>
+        <v>0</v>
       </c>
       <c r="G113" t="s">
-        <v>417</v>
+        <v>443</v>
       </c>
       <c r="H113" t="s">
         <v>3</v>
@@ -4409,22 +4556,22 @@
     </row>
     <row r="114" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A114" t="s">
-        <v>418</v>
+        <v>444</v>
       </c>
       <c r="C114" t="s">
-        <v>25</v>
+        <v>22</v>
       </c>
       <c r="D114" t="s">
-        <v>419</v>
+        <v>445</v>
       </c>
       <c r="E114" t="s">
-        <v>88</v>
+        <v>442</v>
       </c>
       <c r="F114" t="s">
-        <v>58</v>
+        <v>0</v>
       </c>
       <c r="G114" t="s">
-        <v>420</v>
+        <v>446</v>
       </c>
       <c r="H114" t="s">
         <v>3</v>
@@ -4432,22 +4579,22 @@
     </row>
     <row r="115" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A115" t="s">
-        <v>421</v>
+        <v>447</v>
       </c>
       <c r="C115" t="s">
-        <v>37</v>
+        <v>5</v>
       </c>
       <c r="D115" t="s">
-        <v>422</v>
+        <v>448</v>
       </c>
       <c r="E115" t="s">
-        <v>81</v>
+        <v>23</v>
       </c>
       <c r="F115" t="s">
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="G115" t="s">
-        <v>423</v>
+        <v>449</v>
       </c>
       <c r="H115" t="s">
         <v>3</v>
@@ -4455,22 +4602,22 @@
     </row>
     <row r="116" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A116" t="s">
-        <v>424</v>
+        <v>450</v>
       </c>
       <c r="C116" t="s">
-        <v>22</v>
+        <v>176</v>
       </c>
       <c r="D116" t="s">
-        <v>425</v>
+        <v>451</v>
       </c>
       <c r="E116" t="s">
-        <v>426</v>
+        <v>452</v>
       </c>
       <c r="F116" t="s">
         <v>0</v>
       </c>
       <c r="G116" t="s">
-        <v>427</v>
+        <v>453</v>
       </c>
       <c r="H116" t="s">
         <v>3</v>
@@ -4478,22 +4625,22 @@
     </row>
     <row r="117" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A117" t="s">
-        <v>428</v>
+        <v>454</v>
       </c>
       <c r="C117" t="s">
-        <v>21</v>
+        <v>176</v>
       </c>
       <c r="D117" t="s">
-        <v>429</v>
+        <v>451</v>
       </c>
       <c r="E117" t="s">
-        <v>430</v>
+        <v>452</v>
       </c>
       <c r="F117" t="s">
         <v>0</v>
       </c>
       <c r="G117" t="s">
-        <v>431</v>
+        <v>453</v>
       </c>
       <c r="H117" t="s">
         <v>3</v>
@@ -4501,22 +4648,22 @@
     </row>
     <row r="118" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A118" t="s">
-        <v>432</v>
+        <v>455</v>
       </c>
       <c r="C118" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="D118" t="s">
-        <v>433</v>
+        <v>456</v>
       </c>
       <c r="E118" t="s">
-        <v>43</v>
+        <v>457</v>
       </c>
       <c r="F118" t="s">
         <v>0</v>
       </c>
       <c r="G118" t="s">
-        <v>434</v>
+        <v>458</v>
       </c>
       <c r="H118" t="s">
         <v>3</v>
@@ -4524,229 +4671,229 @@
     </row>
     <row r="119" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A119" t="s">
-        <v>435</v>
+        <v>459</v>
       </c>
       <c r="C119" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="D119" t="s">
-        <v>436</v>
+        <v>460</v>
       </c>
       <c r="E119" t="s">
-        <v>10</v>
+        <v>40</v>
       </c>
       <c r="F119" t="s">
-        <v>11</v>
+        <v>41</v>
       </c>
       <c r="G119" t="s">
-        <v>437</v>
+        <v>461</v>
       </c>
       <c r="H119" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="120" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A120" t="s">
-        <v>438</v>
+        <v>462</v>
       </c>
       <c r="C120" t="s">
-        <v>6</v>
+        <v>176</v>
       </c>
       <c r="D120" t="s">
-        <v>439</v>
+        <v>463</v>
       </c>
       <c r="E120" t="s">
-        <v>440</v>
+        <v>464</v>
       </c>
       <c r="F120" t="s">
-        <v>441</v>
+        <v>0</v>
       </c>
       <c r="G120" t="s">
-        <v>442</v>
+        <v>178</v>
       </c>
       <c r="H120" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="121" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A121" t="s">
-        <v>443</v>
+        <v>465</v>
       </c>
       <c r="C121" t="s">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="D121" t="s">
-        <v>444</v>
+        <v>466</v>
       </c>
       <c r="E121" t="s">
-        <v>398</v>
+        <v>467</v>
       </c>
       <c r="F121" t="s">
-        <v>399</v>
+        <v>468</v>
       </c>
       <c r="G121" t="s">
-        <v>445</v>
+        <v>313</v>
       </c>
       <c r="H121" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="122" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A122" t="s">
-        <v>446</v>
+        <v>469</v>
       </c>
       <c r="C122" t="s">
         <v>2</v>
       </c>
       <c r="D122" t="s">
-        <v>444</v>
+        <v>470</v>
       </c>
       <c r="E122" t="s">
-        <v>398</v>
+        <v>116</v>
       </c>
       <c r="F122" t="s">
-        <v>399</v>
+        <v>0</v>
       </c>
       <c r="G122" t="s">
-        <v>445</v>
+        <v>471</v>
       </c>
       <c r="H122" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="123" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A123" t="s">
-        <v>447</v>
+        <v>472</v>
       </c>
       <c r="C123" t="s">
-        <v>9</v>
+        <v>2</v>
       </c>
       <c r="D123" t="s">
-        <v>448</v>
+        <v>470</v>
       </c>
       <c r="E123" t="s">
-        <v>449</v>
+        <v>116</v>
       </c>
       <c r="F123" t="s">
-        <v>450</v>
+        <v>0</v>
       </c>
       <c r="G123" t="s">
-        <v>451</v>
+        <v>471</v>
       </c>
       <c r="H123" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="124" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A124" t="s">
-        <v>452</v>
+        <v>473</v>
       </c>
       <c r="C124" t="s">
-        <v>9</v>
+        <v>176</v>
       </c>
       <c r="D124" t="s">
-        <v>448</v>
+        <v>474</v>
       </c>
       <c r="E124" t="s">
-        <v>449</v>
+        <v>464</v>
       </c>
       <c r="F124" t="s">
-        <v>450</v>
+        <v>0</v>
       </c>
       <c r="G124" t="s">
-        <v>451</v>
+        <v>47</v>
       </c>
       <c r="H124" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="125" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A125" t="s">
-        <v>453</v>
+        <v>475</v>
       </c>
       <c r="C125" t="s">
-        <v>44</v>
+        <v>18</v>
       </c>
       <c r="D125" t="s">
-        <v>454</v>
+        <v>476</v>
       </c>
       <c r="E125" t="s">
-        <v>455</v>
+        <v>477</v>
       </c>
       <c r="F125" t="s">
         <v>0</v>
       </c>
       <c r="G125" t="s">
-        <v>456</v>
+        <v>478</v>
       </c>
       <c r="H125" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="126" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A126" t="s">
-        <v>457</v>
+        <v>479</v>
       </c>
       <c r="C126" t="s">
-        <v>25</v>
+        <v>7</v>
       </c>
       <c r="D126" t="s">
-        <v>458</v>
+        <v>480</v>
       </c>
       <c r="E126" t="s">
-        <v>57</v>
+        <v>355</v>
       </c>
       <c r="F126" t="s">
-        <v>58</v>
+        <v>0</v>
       </c>
       <c r="G126" t="s">
-        <v>56</v>
+        <v>481</v>
       </c>
       <c r="H126" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="127" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A127" t="s">
-        <v>459</v>
+        <v>482</v>
       </c>
       <c r="C127" t="s">
-        <v>33</v>
+        <v>5</v>
       </c>
       <c r="D127" t="s">
-        <v>460</v>
+        <v>483</v>
       </c>
       <c r="E127" t="s">
-        <v>76</v>
+        <v>23</v>
       </c>
       <c r="F127" t="s">
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="G127" t="s">
-        <v>461</v>
+        <v>484</v>
       </c>
       <c r="H127" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="128" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A128" t="s">
-        <v>462</v>
+        <v>485</v>
       </c>
       <c r="C128" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="D128" t="s">
-        <v>463</v>
+        <v>486</v>
       </c>
       <c r="E128" t="s">
-        <v>39</v>
+        <v>75</v>
       </c>
       <c r="F128" t="s">
         <v>0</v>
       </c>
       <c r="G128" t="s">
-        <v>464</v>
+        <v>76</v>
       </c>
       <c r="H128" t="s">
         <v>4</v>
@@ -4754,22 +4901,22 @@
     </row>
     <row r="129" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A129" t="s">
-        <v>465</v>
+        <v>487</v>
       </c>
       <c r="C129" t="s">
-        <v>37</v>
+        <v>22</v>
       </c>
       <c r="D129" t="s">
-        <v>466</v>
+        <v>488</v>
       </c>
       <c r="E129" t="s">
-        <v>192</v>
+        <v>277</v>
       </c>
       <c r="F129" t="s">
         <v>0</v>
       </c>
       <c r="G129" t="s">
-        <v>467</v>
+        <v>489</v>
       </c>
       <c r="H129" t="s">
         <v>4</v>
@@ -4777,22 +4924,22 @@
     </row>
     <row r="130" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A130" t="s">
-        <v>468</v>
+        <v>490</v>
       </c>
       <c r="C130" t="s">
-        <v>37</v>
+        <v>22</v>
       </c>
       <c r="D130" t="s">
-        <v>469</v>
+        <v>488</v>
       </c>
       <c r="E130" t="s">
-        <v>470</v>
+        <v>277</v>
       </c>
       <c r="F130" t="s">
         <v>0</v>
       </c>
       <c r="G130" t="s">
-        <v>471</v>
+        <v>489</v>
       </c>
       <c r="H130" t="s">
         <v>4</v>
@@ -4800,22 +4947,22 @@
     </row>
     <row r="131" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A131" t="s">
-        <v>472</v>
+        <v>491</v>
       </c>
       <c r="C131" t="s">
-        <v>33</v>
+        <v>22</v>
       </c>
       <c r="D131" t="s">
-        <v>473</v>
+        <v>488</v>
       </c>
       <c r="E131" t="s">
-        <v>39</v>
+        <v>277</v>
       </c>
       <c r="F131" t="s">
         <v>0</v>
       </c>
       <c r="G131" t="s">
-        <v>474</v>
+        <v>489</v>
       </c>
       <c r="H131" t="s">
         <v>4</v>
@@ -4823,22 +4970,22 @@
     </row>
     <row r="132" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A132" t="s">
-        <v>475</v>
+        <v>492</v>
       </c>
       <c r="C132" t="s">
-        <v>25</v>
+        <v>7</v>
       </c>
       <c r="D132" t="s">
-        <v>476</v>
+        <v>493</v>
       </c>
       <c r="E132" t="s">
-        <v>57</v>
+        <v>72</v>
       </c>
       <c r="F132" t="s">
-        <v>58</v>
+        <v>73</v>
       </c>
       <c r="G132" t="s">
-        <v>477</v>
+        <v>494</v>
       </c>
       <c r="H132" t="s">
         <v>4</v>
@@ -4846,22 +4993,22 @@
     </row>
     <row r="133" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A133" t="s">
-        <v>478</v>
+        <v>495</v>
       </c>
       <c r="C133" t="s">
-        <v>25</v>
+        <v>7</v>
       </c>
       <c r="D133" t="s">
-        <v>476</v>
+        <v>496</v>
       </c>
       <c r="E133" t="s">
-        <v>57</v>
+        <v>72</v>
       </c>
       <c r="F133" t="s">
-        <v>58</v>
+        <v>73</v>
       </c>
       <c r="G133" t="s">
-        <v>477</v>
+        <v>497</v>
       </c>
       <c r="H133" t="s">
         <v>4</v>
@@ -4869,22 +5016,22 @@
     </row>
     <row r="134" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A134" t="s">
-        <v>82</v>
+        <v>498</v>
       </c>
       <c r="C134" t="s">
-        <v>2</v>
+        <v>18</v>
       </c>
       <c r="D134" t="s">
-        <v>83</v>
+        <v>499</v>
       </c>
       <c r="E134" t="s">
-        <v>26</v>
+        <v>438</v>
       </c>
       <c r="F134" t="s">
         <v>0</v>
       </c>
       <c r="G134" t="s">
-        <v>84</v>
+        <v>500</v>
       </c>
       <c r="H134" t="s">
         <v>4</v>
@@ -4892,22 +5039,22 @@
     </row>
     <row r="135" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A135" t="s">
-        <v>479</v>
+        <v>501</v>
       </c>
       <c r="C135" t="s">
-        <v>44</v>
+        <v>35</v>
       </c>
       <c r="D135" t="s">
-        <v>480</v>
+        <v>502</v>
       </c>
       <c r="E135" t="s">
-        <v>196</v>
+        <v>20</v>
       </c>
       <c r="F135" t="s">
-        <v>0</v>
+        <v>21</v>
       </c>
       <c r="G135" t="s">
-        <v>481</v>
+        <v>503</v>
       </c>
       <c r="H135" t="s">
         <v>4</v>
@@ -4915,24 +5062,208 @@
     </row>
     <row r="136" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A136" t="s">
-        <v>482</v>
+        <v>504</v>
       </c>
       <c r="C136" t="s">
-        <v>44</v>
+        <v>27</v>
       </c>
       <c r="D136" t="s">
-        <v>480</v>
+        <v>505</v>
       </c>
       <c r="E136" t="s">
-        <v>196</v>
+        <v>50</v>
       </c>
       <c r="F136" t="s">
         <v>0</v>
       </c>
       <c r="G136" t="s">
-        <v>481</v>
+        <v>506</v>
       </c>
       <c r="H136" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="137" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A137" t="s">
+        <v>507</v>
+      </c>
+      <c r="C137" t="s">
+        <v>35</v>
+      </c>
+      <c r="D137" t="s">
+        <v>508</v>
+      </c>
+      <c r="E137" t="s">
+        <v>224</v>
+      </c>
+      <c r="F137" t="s">
+        <v>225</v>
+      </c>
+      <c r="G137" t="s">
+        <v>509</v>
+      </c>
+      <c r="H137" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="138" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A138" t="s">
+        <v>510</v>
+      </c>
+      <c r="C138" t="s">
+        <v>301</v>
+      </c>
+      <c r="D138" t="s">
+        <v>511</v>
+      </c>
+      <c r="E138" t="s">
+        <v>512</v>
+      </c>
+      <c r="F138" t="s">
+        <v>0</v>
+      </c>
+      <c r="G138" t="s">
+        <v>513</v>
+      </c>
+      <c r="H138" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="139" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A139" t="s">
+        <v>514</v>
+      </c>
+      <c r="C139" t="s">
+        <v>27</v>
+      </c>
+      <c r="D139" t="s">
+        <v>515</v>
+      </c>
+      <c r="E139" t="s">
+        <v>25</v>
+      </c>
+      <c r="F139" t="s">
+        <v>0</v>
+      </c>
+      <c r="G139" t="s">
+        <v>516</v>
+      </c>
+      <c r="H139" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="140" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A140" t="s">
+        <v>517</v>
+      </c>
+      <c r="C140" t="s">
+        <v>7</v>
+      </c>
+      <c r="D140" t="s">
+        <v>518</v>
+      </c>
+      <c r="E140" t="s">
+        <v>355</v>
+      </c>
+      <c r="F140" t="s">
+        <v>0</v>
+      </c>
+      <c r="G140" t="s">
+        <v>519</v>
+      </c>
+      <c r="H140" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="141" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A141" t="s">
+        <v>520</v>
+      </c>
+      <c r="C141" t="s">
+        <v>8</v>
+      </c>
+      <c r="D141" t="s">
+        <v>521</v>
+      </c>
+      <c r="E141" t="s">
+        <v>62</v>
+      </c>
+      <c r="F141" t="s">
+        <v>0</v>
+      </c>
+      <c r="G141" t="s">
+        <v>522</v>
+      </c>
+      <c r="H141" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="142" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A142" t="s">
+        <v>523</v>
+      </c>
+      <c r="C142" t="s">
+        <v>105</v>
+      </c>
+      <c r="D142" t="s">
+        <v>524</v>
+      </c>
+      <c r="E142" t="s">
+        <v>67</v>
+      </c>
+      <c r="F142" t="s">
+        <v>0</v>
+      </c>
+      <c r="G142" t="s">
+        <v>525</v>
+      </c>
+      <c r="H142" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="143" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A143" t="s">
+        <v>526</v>
+      </c>
+      <c r="C143" t="s">
+        <v>31</v>
+      </c>
+      <c r="D143" t="s">
+        <v>527</v>
+      </c>
+      <c r="E143" t="s">
+        <v>37</v>
+      </c>
+      <c r="F143" t="s">
+        <v>0</v>
+      </c>
+      <c r="G143" t="s">
+        <v>528</v>
+      </c>
+      <c r="H143" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="144" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A144" t="s">
+        <v>529</v>
+      </c>
+      <c r="C144" t="s">
+        <v>5</v>
+      </c>
+      <c r="D144" t="s">
+        <v>530</v>
+      </c>
+      <c r="E144" t="s">
+        <v>9</v>
+      </c>
+      <c r="F144" t="s">
+        <v>10</v>
+      </c>
+      <c r="G144" t="s">
+        <v>531</v>
+      </c>
+      <c r="H144" t="s">
         <v>4</v>
       </c>
     </row>

--- a/1.xlsx
+++ b/1.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="\\wh.local\fs\UserProfile_TSSWH19\_TSSWH19_redirected_folders\HunyaCs1\Desktop\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6FC01077-D8C0-4940-8BA2-795E770C9E9C}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6827B532-05EE-40C2-B87A-4B7E89A74172}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="0" windowWidth="22260" windowHeight="12648" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1008" uniqueCount="532">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1001" uniqueCount="529">
   <si>
     <t>BUDAPEST</t>
   </si>
@@ -1570,15 +1570,6 @@
   </si>
   <si>
     <t>Vörösvári út</t>
-  </si>
-  <si>
-    <t>NFD6-04-10-F58Q-1</t>
-  </si>
-  <si>
-    <t>NFD6-04-10-F58Q</t>
-  </si>
-  <si>
-    <t>Napsugár utca</t>
   </si>
   <si>
     <t>202604102600833401</t>
@@ -1942,7 +1933,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <sheetPr codeName="Munka1"/>
-  <dimension ref="A1:H144"/>
+  <dimension ref="A1:H143"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="24.88671875" bestFit="1" customWidth="1"/>
@@ -5134,13 +5125,13 @@
         <v>514</v>
       </c>
       <c r="C139" t="s">
-        <v>27</v>
+        <v>7</v>
       </c>
       <c r="D139" t="s">
         <v>515</v>
       </c>
       <c r="E139" t="s">
-        <v>25</v>
+        <v>355</v>
       </c>
       <c r="F139" t="s">
         <v>0</v>
@@ -5157,13 +5148,13 @@
         <v>517</v>
       </c>
       <c r="C140" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="D140" t="s">
         <v>518</v>
       </c>
       <c r="E140" t="s">
-        <v>355</v>
+        <v>62</v>
       </c>
       <c r="F140" t="s">
         <v>0</v>
@@ -5180,13 +5171,13 @@
         <v>520</v>
       </c>
       <c r="C141" t="s">
-        <v>8</v>
+        <v>105</v>
       </c>
       <c r="D141" t="s">
         <v>521</v>
       </c>
       <c r="E141" t="s">
-        <v>62</v>
+        <v>67</v>
       </c>
       <c r="F141" t="s">
         <v>0</v>
@@ -5203,13 +5194,13 @@
         <v>523</v>
       </c>
       <c r="C142" t="s">
-        <v>105</v>
+        <v>31</v>
       </c>
       <c r="D142" t="s">
         <v>524</v>
       </c>
       <c r="E142" t="s">
-        <v>67</v>
+        <v>37</v>
       </c>
       <c r="F142" t="s">
         <v>0</v>
@@ -5226,44 +5217,21 @@
         <v>526</v>
       </c>
       <c r="C143" t="s">
-        <v>31</v>
+        <v>5</v>
       </c>
       <c r="D143" t="s">
         <v>527</v>
       </c>
       <c r="E143" t="s">
-        <v>37</v>
+        <v>9</v>
       </c>
       <c r="F143" t="s">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="G143" t="s">
         <v>528</v>
       </c>
       <c r="H143" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="144" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A144" t="s">
-        <v>529</v>
-      </c>
-      <c r="C144" t="s">
-        <v>5</v>
-      </c>
-      <c r="D144" t="s">
-        <v>530</v>
-      </c>
-      <c r="E144" t="s">
-        <v>9</v>
-      </c>
-      <c r="F144" t="s">
-        <v>10</v>
-      </c>
-      <c r="G144" t="s">
-        <v>531</v>
-      </c>
-      <c r="H144" t="s">
         <v>4</v>
       </c>
     </row>

--- a/1.xlsx
+++ b/1.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="\\wh.local\fs\UserProfile_TSSWH19\_TSSWH19_redirected_folders\HunyaCs1\Desktop\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6827B532-05EE-40C2-B87A-4B7E89A74172}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{69AFBB93-F62C-40D9-8B07-81D021D7CEA8}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="0" windowWidth="22260" windowHeight="12648" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1001" uniqueCount="529">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1575" uniqueCount="771">
   <si>
     <t>BUDAPEST</t>
   </si>
@@ -51,9 +51,6 @@
     <t>SZ-805</t>
   </si>
   <si>
-    <t>SZ-836</t>
-  </si>
-  <si>
     <t>SZ-820</t>
   </si>
   <si>
@@ -105,9 +102,6 @@
     <t>SZÁZHALOMBATTA</t>
   </si>
   <si>
-    <t>1025</t>
-  </si>
-  <si>
     <t>SZ-832</t>
   </si>
   <si>
@@ -159,24 +153,12 @@
     <t>GÖD</t>
   </si>
   <si>
-    <t>SZ-823</t>
-  </si>
-  <si>
-    <t>69d61ed15cef447acab8aca9</t>
-  </si>
-  <si>
-    <t>260407-F00014466</t>
-  </si>
-  <si>
     <t>1085</t>
   </si>
   <si>
     <t>Baross utca</t>
   </si>
   <si>
-    <t>1135</t>
-  </si>
-  <si>
     <t>Akácfa utca</t>
   </si>
   <si>
@@ -189,9 +171,6 @@
     <t>2131</t>
   </si>
   <si>
-    <t>1139</t>
-  </si>
-  <si>
     <t>2600</t>
   </si>
   <si>
@@ -207,15 +186,9 @@
     <t>1037</t>
   </si>
   <si>
-    <t>Deák Ferenc utca</t>
-  </si>
-  <si>
     <t>1144</t>
   </si>
   <si>
-    <t>Szentmihályi út</t>
-  </si>
-  <si>
     <t>1188</t>
   </si>
   <si>
@@ -225,141 +198,42 @@
     <t>INÁRCS</t>
   </si>
   <si>
-    <t>1067</t>
-  </si>
-  <si>
     <t>Havanna utca</t>
   </si>
   <si>
-    <t>1048</t>
-  </si>
-  <si>
-    <t>1131</t>
-  </si>
-  <si>
     <t>1027</t>
   </si>
   <si>
-    <t>1126</t>
-  </si>
-  <si>
-    <t>1072</t>
-  </si>
-  <si>
     <t>2234</t>
   </si>
   <si>
     <t>MAGLÓD</t>
   </si>
   <si>
-    <t>Kinizsi utca</t>
-  </si>
-  <si>
     <t>1119</t>
   </si>
   <si>
     <t>Fehérvári út</t>
   </si>
   <si>
-    <t>248745386/1</t>
-  </si>
-  <si>
-    <t>248745386</t>
-  </si>
-  <si>
     <t>1103</t>
   </si>
   <si>
-    <t>Gyömrői út</t>
-  </si>
-  <si>
-    <t>248745393/1</t>
-  </si>
-  <si>
-    <t>248745393</t>
-  </si>
-  <si>
     <t>1097</t>
   </si>
   <si>
     <t>Vágóhíd utca</t>
   </si>
   <si>
-    <t>69d78d8b5cef447acab8c9ee</t>
-  </si>
-  <si>
-    <t>260321-W00006372</t>
-  </si>
-  <si>
-    <t>Liszt Ferenc utca</t>
-  </si>
-  <si>
-    <t>69cc0a870ed4809420f4bf46</t>
-  </si>
-  <si>
-    <t>260331-W00008718</t>
-  </si>
-  <si>
     <t>2230</t>
   </si>
   <si>
     <t>GYÖMRŐ</t>
   </si>
   <si>
-    <t>Eperfasor utca</t>
-  </si>
-  <si>
-    <t>69d7acc05cef447acab8cf76</t>
-  </si>
-  <si>
-    <t>260401-F00012350</t>
-  </si>
-  <si>
-    <t>1114</t>
-  </si>
-  <si>
-    <t>Vásárhelyi Pál utca</t>
-  </si>
-  <si>
-    <t>69d89a0f5cef447acab8d91e</t>
-  </si>
-  <si>
-    <t>260401-W00007623</t>
-  </si>
-  <si>
-    <t>1125</t>
-  </si>
-  <si>
-    <t>Szilágyi Erzsébet fasor</t>
-  </si>
-  <si>
-    <t>69d8bdb85cef447acab8ddff</t>
-  </si>
-  <si>
-    <t>260402-F00006899</t>
-  </si>
-  <si>
-    <t>Tűzkő utca</t>
-  </si>
-  <si>
-    <t>69d661415cef447acab8b79a</t>
-  </si>
-  <si>
     <t>SZ-828</t>
   </si>
   <si>
-    <t>260402-F00009433</t>
-  </si>
-  <si>
-    <t>Aranka utca</t>
-  </si>
-  <si>
-    <t>69ce33b05cef447acab8653d</t>
-  </si>
-  <si>
-    <t>260402-W00003563</t>
-  </si>
-  <si>
     <t>2634</t>
   </si>
   <si>
@@ -369,21 +243,6 @@
     <t>Petőfi utca</t>
   </si>
   <si>
-    <t>69ce33b05cef447acab8653e</t>
-  </si>
-  <si>
-    <t>69ceaeba5cef447acab872a5</t>
-  </si>
-  <si>
-    <t>260402-W00010016</t>
-  </si>
-  <si>
-    <t>1152</t>
-  </si>
-  <si>
-    <t>Szilas park</t>
-  </si>
-  <si>
     <t>69d8ce805cef447acab8e0b9</t>
   </si>
   <si>
@@ -393,477 +252,57 @@
     <t>Kapás utca</t>
   </si>
   <si>
-    <t>69d89a715cef447acab8d930</t>
-  </si>
-  <si>
-    <t>260405-W00005445</t>
-  </si>
-  <si>
-    <t>69d4c42b5cef447acab890b6</t>
-  </si>
-  <si>
     <t>SZ-809</t>
   </si>
   <si>
-    <t>260407-F00003638</t>
-  </si>
-  <si>
-    <t>69d57b135cef447acab8a5b1</t>
-  </si>
-  <si>
-    <t>260407-W00012558</t>
-  </si>
-  <si>
-    <t>2192</t>
-  </si>
-  <si>
-    <t>HÉVÍZGYÖRK</t>
-  </si>
-  <si>
-    <t>Ősz utca</t>
-  </si>
-  <si>
-    <t>69d7e8a45cef447acab8d68b</t>
-  </si>
-  <si>
-    <t>260408-F00014737</t>
-  </si>
-  <si>
     <t>Rátz László utca</t>
   </si>
   <si>
-    <t>69d62bee5cef447acab8af26</t>
-  </si>
-  <si>
-    <t>260408-W00004264</t>
-  </si>
-  <si>
-    <t>69d62bee5cef447acab8af27</t>
-  </si>
-  <si>
-    <t>69d6447b5cef447acab8b2ae</t>
-  </si>
-  <si>
     <t>SZ-860</t>
   </si>
   <si>
-    <t>260408-W00005531</t>
-  </si>
-  <si>
-    <t>Budafoki út</t>
-  </si>
-  <si>
-    <t>69d67a6d5cef447acab8ba89</t>
-  </si>
-  <si>
     <t>SZ-818</t>
   </si>
   <si>
-    <t>260408-W00008388</t>
-  </si>
-  <si>
-    <t>1071</t>
-  </si>
-  <si>
-    <t>Dózsa György út</t>
-  </si>
-  <si>
-    <t>69d694485cef447acab8bcad</t>
-  </si>
-  <si>
-    <t>260408-W00009477</t>
-  </si>
-  <si>
-    <t>2769</t>
-  </si>
-  <si>
-    <t>TÁPIÓSZŐLŐS</t>
-  </si>
-  <si>
-    <t>69d77ab65cef447acab8c6dc</t>
-  </si>
-  <si>
-    <t>260409-F00003679</t>
-  </si>
-  <si>
     <t>2213</t>
   </si>
   <si>
     <t>MONORIERDŐ</t>
   </si>
   <si>
-    <t>Nyúl utca</t>
-  </si>
-  <si>
-    <t>69d7da325cef447acab8d56c</t>
-  </si>
-  <si>
-    <t>260409-F00014617</t>
-  </si>
-  <si>
-    <t>1086</t>
-  </si>
-  <si>
-    <t>Koszorú utca</t>
-  </si>
-  <si>
-    <t>69d76e2e5cef447acab8c498</t>
-  </si>
-  <si>
-    <t>260409-W00003332</t>
-  </si>
-  <si>
-    <t>Váci út</t>
-  </si>
-  <si>
-    <t>69d7ac575cef447acab8cf61</t>
-  </si>
-  <si>
-    <t>260409-W00006961</t>
-  </si>
-  <si>
-    <t>1082</t>
-  </si>
-  <si>
-    <t>Üllői út</t>
-  </si>
-  <si>
-    <t>69d7ac575cef447acab8cf62</t>
-  </si>
-  <si>
-    <t>69d7ad735cef447acab8cf98</t>
-  </si>
-  <si>
-    <t>260409-W00007253</t>
-  </si>
-  <si>
-    <t>Farkasalma utca</t>
-  </si>
-  <si>
-    <t>69d7ad735cef447acab8cf99</t>
-  </si>
-  <si>
-    <t>69d7bf0d5cef447acab8d2d5</t>
-  </si>
-  <si>
-    <t>260409-W00008389</t>
-  </si>
-  <si>
     <t>1021</t>
   </si>
   <si>
-    <t>Hűvösvölgyi út</t>
-  </si>
-  <si>
-    <t>69d8b3f65cef447acab8dc1a</t>
-  </si>
-  <si>
     <t>SZ-821</t>
   </si>
   <si>
-    <t>260410-F00002552</t>
-  </si>
-  <si>
-    <t>Török Flóris utca</t>
-  </si>
-  <si>
-    <t>69d8b3f65cef447acab8dc1b</t>
-  </si>
-  <si>
-    <t>69d8c32f5cef447acab8def3</t>
-  </si>
-  <si>
-    <t>260410-F00004400</t>
-  </si>
-  <si>
     <t>1182</t>
   </si>
   <si>
-    <t>Nagyenyed utca</t>
-  </si>
-  <si>
-    <t>69d846f15cef447acab8d829</t>
-  </si>
-  <si>
-    <t>260410-W00000232</t>
-  </si>
-  <si>
-    <t>1121</t>
-  </si>
-  <si>
-    <t>Irhás árok</t>
-  </si>
-  <si>
-    <t>69d8c45e5cef447acab8df3a</t>
-  </si>
-  <si>
-    <t>260410-W00003790</t>
-  </si>
-  <si>
-    <t>Lehel utca</t>
-  </si>
-  <si>
-    <t>69d8d96e5cef447acab8e22e</t>
-  </si>
-  <si>
-    <t>260410-W00004936</t>
-  </si>
-  <si>
     <t>1174</t>
   </si>
   <si>
-    <t>Berzsenyi Dániel utca</t>
-  </si>
-  <si>
-    <t>FIZZ-1000860285</t>
-  </si>
-  <si>
-    <t>267004973</t>
-  </si>
-  <si>
-    <t>2225</t>
-  </si>
-  <si>
-    <t>ÜLLŐ</t>
-  </si>
-  <si>
-    <t>Öregszőlő utca</t>
-  </si>
-  <si>
-    <t>FIZZ-1000862427</t>
-  </si>
-  <si>
-    <t>267004978</t>
-  </si>
-  <si>
-    <t>Kucsma utca</t>
-  </si>
-  <si>
-    <t>26MPE0003708/1</t>
-  </si>
-  <si>
-    <t>26MPE0003708</t>
-  </si>
-  <si>
-    <t>2022</t>
-  </si>
-  <si>
-    <t>TAHITÓTFALU</t>
-  </si>
-  <si>
     <t>Szőlő utca</t>
   </si>
   <si>
-    <t>MEGAPLACE</t>
-  </si>
-  <si>
-    <t>26MPE0003710/1</t>
-  </si>
-  <si>
-    <t>26MPE0003710</t>
-  </si>
-  <si>
-    <t>2370</t>
-  </si>
-  <si>
-    <t>DABAS</t>
-  </si>
-  <si>
     <t>Fő út</t>
   </si>
   <si>
-    <t>26MPE0003719/1</t>
-  </si>
-  <si>
-    <t>26MPE0003719</t>
-  </si>
-  <si>
-    <t>M</t>
-  </si>
-  <si>
-    <t>26MPE0003757/1</t>
-  </si>
-  <si>
-    <t>26MPE0003757</t>
-  </si>
-  <si>
-    <t>2049</t>
-  </si>
-  <si>
-    <t>DIÓSD</t>
-  </si>
-  <si>
-    <t>Jolán utca</t>
-  </si>
-  <si>
-    <t>26MPE0003826/1</t>
-  </si>
-  <si>
-    <t>26MPE0003826</t>
-  </si>
-  <si>
-    <t>2740</t>
-  </si>
-  <si>
-    <t>ABONY</t>
-  </si>
-  <si>
-    <t>Tabán utca</t>
-  </si>
-  <si>
-    <t>300523974/1</t>
-  </si>
-  <si>
-    <t>300523974</t>
-  </si>
-  <si>
     <t>2315</t>
   </si>
   <si>
     <t>SZIGETHALOM</t>
   </si>
   <si>
-    <t>Gyöngyvirág Utca</t>
-  </si>
-  <si>
-    <t>305557116/1</t>
-  </si>
-  <si>
-    <t>305557116</t>
-  </si>
-  <si>
-    <t>1087</t>
-  </si>
-  <si>
-    <t>Ciprus utca</t>
-  </si>
-  <si>
-    <t>305557116/2</t>
-  </si>
-  <si>
-    <t>305557116/3</t>
-  </si>
-  <si>
-    <t>305830892/1</t>
-  </si>
-  <si>
-    <t>305830892</t>
-  </si>
-  <si>
-    <t>Szent László út</t>
-  </si>
-  <si>
-    <t>305830892/2</t>
-  </si>
-  <si>
-    <t>306621232/1</t>
-  </si>
-  <si>
-    <t>306621232</t>
-  </si>
-  <si>
-    <t>Rege út</t>
-  </si>
-  <si>
-    <t>306669492/1</t>
-  </si>
-  <si>
-    <t>306669492</t>
-  </si>
-  <si>
-    <t>Tétényi utca</t>
-  </si>
-  <si>
-    <t>306669492/2</t>
-  </si>
-  <si>
-    <t>306766498/1</t>
-  </si>
-  <si>
-    <t>306766498</t>
-  </si>
-  <si>
-    <t>Iharos Sándor Utca</t>
-  </si>
-  <si>
-    <t>306823916/1</t>
-  </si>
-  <si>
-    <t>306823916</t>
-  </si>
-  <si>
     <t>1201</t>
   </si>
   <si>
-    <t>Baba utca</t>
-  </si>
-  <si>
-    <t>306823916/2</t>
-  </si>
-  <si>
-    <t>306891294/1</t>
-  </si>
-  <si>
-    <t>306891294</t>
-  </si>
-  <si>
-    <t>2364</t>
-  </si>
-  <si>
-    <t>ÓCSA</t>
-  </si>
-  <si>
-    <t>Székes tanya nyúlfarm</t>
-  </si>
-  <si>
-    <t>306891294/2</t>
-  </si>
-  <si>
-    <t>307081008/1</t>
-  </si>
-  <si>
-    <t>307081008</t>
-  </si>
-  <si>
-    <t>2170</t>
-  </si>
-  <si>
-    <t>ASZÓD</t>
-  </si>
-  <si>
-    <t>Berek utca</t>
-  </si>
-  <si>
-    <t>307081249/1</t>
-  </si>
-  <si>
-    <t>307081249</t>
-  </si>
-  <si>
     <t>2360</t>
   </si>
   <si>
     <t>GYÁL</t>
   </si>
   <si>
-    <t>Bercsényi Miklós utca</t>
-  </si>
-  <si>
-    <t>307081249/2</t>
-  </si>
-  <si>
-    <t>307081249/3</t>
-  </si>
-  <si>
-    <t>307081428/1</t>
-  </si>
-  <si>
-    <t>307081428</t>
-  </si>
-  <si>
-    <t>1107</t>
-  </si>
-  <si>
     <t>307141884/1</t>
   </si>
   <si>
@@ -873,513 +312,51 @@
     <t>Szugló utca</t>
   </si>
   <si>
-    <t>307198140/1</t>
-  </si>
-  <si>
-    <t>307198140</t>
-  </si>
-  <si>
-    <t>Gyöngyvirág utca</t>
-  </si>
-  <si>
-    <t>307198140/2</t>
-  </si>
-  <si>
-    <t>307237760/1</t>
-  </si>
-  <si>
-    <t>307237760</t>
-  </si>
-  <si>
-    <t>Kazinczy Ferenc utca</t>
-  </si>
-  <si>
-    <t>307238085/1</t>
-  </si>
-  <si>
-    <t>307238085</t>
-  </si>
-  <si>
-    <t>2114</t>
-  </si>
-  <si>
-    <t>VALKÓ</t>
-  </si>
-  <si>
-    <t>Dányi út</t>
-  </si>
-  <si>
-    <t>307238509/1</t>
-  </si>
-  <si>
-    <t>307238509</t>
-  </si>
-  <si>
-    <t>Gerinc utca</t>
-  </si>
-  <si>
-    <t>307278644/1</t>
-  </si>
-  <si>
-    <t>307278644</t>
-  </si>
-  <si>
     <t>1053</t>
   </si>
   <si>
-    <t>Múzeum Körút</t>
-  </si>
-  <si>
-    <t>307278768/1</t>
-  </si>
-  <si>
-    <t>SZ-800</t>
-  </si>
-  <si>
-    <t>307278768</t>
-  </si>
-  <si>
-    <t>Kékfestő utca</t>
-  </si>
-  <si>
-    <t>307278791/1</t>
-  </si>
-  <si>
-    <t>307278791</t>
-  </si>
-  <si>
     <t>2112</t>
   </si>
   <si>
     <t>VERESEGYHÁZ</t>
   </si>
   <si>
-    <t>Budapesti út</t>
-  </si>
-  <si>
-    <t>307279268/1</t>
-  </si>
-  <si>
-    <t>307279268</t>
-  </si>
-  <si>
-    <t>307279324/1</t>
-  </si>
-  <si>
-    <t>307279324</t>
-  </si>
-  <si>
     <t>Rákóczi út</t>
   </si>
   <si>
-    <t>307279397/1</t>
-  </si>
-  <si>
-    <t>307279397</t>
-  </si>
-  <si>
-    <t>Szondi utca</t>
-  </si>
-  <si>
-    <t>307279479/1</t>
-  </si>
-  <si>
-    <t>307279479</t>
-  </si>
-  <si>
     <t>2330</t>
   </si>
   <si>
     <t>DUNAHARASZTI</t>
   </si>
   <si>
-    <t>Kossuth Lajos Utca</t>
-  </si>
-  <si>
-    <t>307342850/1</t>
-  </si>
-  <si>
-    <t>307342850</t>
-  </si>
-  <si>
-    <t>2339</t>
-  </si>
-  <si>
-    <t>MAJOSHÁZA</t>
-  </si>
-  <si>
-    <t>Zrínyi utca</t>
-  </si>
-  <si>
-    <t>307343263/1</t>
-  </si>
-  <si>
-    <t>307343263</t>
-  </si>
-  <si>
-    <t>Kupeczky utca</t>
-  </si>
-  <si>
-    <t>307379077/2/1</t>
-  </si>
-  <si>
-    <t>307379077/2</t>
-  </si>
-  <si>
-    <t>1155</t>
-  </si>
-  <si>
-    <t>Őrszem utca</t>
-  </si>
-  <si>
-    <t>307379439/1</t>
-  </si>
-  <si>
-    <t>307379439</t>
-  </si>
-  <si>
-    <t>1147</t>
-  </si>
-  <si>
-    <t>Kerékgyártó utca</t>
-  </si>
-  <si>
-    <t>307379439/2</t>
-  </si>
-  <si>
-    <t>307379669/1</t>
-  </si>
-  <si>
-    <t>307379669</t>
-  </si>
-  <si>
-    <t>2094</t>
-  </si>
-  <si>
-    <t>NAGYKOVÁCSI</t>
-  </si>
-  <si>
     <t>Munkácsy Mihály utca</t>
   </si>
   <si>
-    <t>307379894/1</t>
-  </si>
-  <si>
-    <t>307379894</t>
-  </si>
-  <si>
-    <t>Bajcsy-Zsilinszky Endre Utca</t>
-  </si>
-  <si>
-    <t>307379931/1</t>
-  </si>
-  <si>
-    <t>307379931</t>
-  </si>
-  <si>
-    <t>Szlávy utca</t>
-  </si>
-  <si>
-    <t>307426389/1</t>
-  </si>
-  <si>
-    <t>307426389</t>
-  </si>
-  <si>
-    <t>Fehárvári út</t>
-  </si>
-  <si>
-    <t>307426557/1</t>
-  </si>
-  <si>
-    <t>307426557</t>
-  </si>
-  <si>
     <t>1173</t>
   </si>
   <si>
-    <t>Tápió utca</t>
-  </si>
-  <si>
-    <t>307426610/1</t>
-  </si>
-  <si>
-    <t>307426610</t>
-  </si>
-  <si>
     <t>2081</t>
   </si>
   <si>
     <t>PILISCSABA</t>
   </si>
   <si>
-    <t>Kossuth Lajos köz</t>
-  </si>
-  <si>
-    <t>307426668/1</t>
-  </si>
-  <si>
-    <t>307426668</t>
-  </si>
-  <si>
-    <t>1011</t>
-  </si>
-  <si>
-    <t>Fő utca</t>
-  </si>
-  <si>
-    <t>307426710/1</t>
-  </si>
-  <si>
-    <t>307426710</t>
-  </si>
-  <si>
-    <t>Csermely Károly</t>
-  </si>
-  <si>
-    <t>307426887/1</t>
-  </si>
-  <si>
-    <t>307426887</t>
-  </si>
-  <si>
-    <t>1062</t>
-  </si>
-  <si>
-    <t>Andrássy út</t>
-  </si>
-  <si>
-    <t>307426936/1</t>
-  </si>
-  <si>
-    <t>307426936</t>
-  </si>
-  <si>
-    <t>307426936/2</t>
-  </si>
-  <si>
-    <t>307427078/1</t>
-  </si>
-  <si>
-    <t>307427078</t>
-  </si>
-  <si>
-    <t>307427165/1</t>
-  </si>
-  <si>
-    <t>307427165</t>
-  </si>
-  <si>
-    <t>Forrás Utca</t>
-  </si>
-  <si>
-    <t>307482401/1</t>
-  </si>
-  <si>
-    <t>307482401</t>
-  </si>
-  <si>
-    <t>Paál László köz</t>
-  </si>
-  <si>
-    <t>307482401/2</t>
-  </si>
-  <si>
-    <t>307482484/1</t>
-  </si>
-  <si>
-    <t>307482484</t>
-  </si>
-  <si>
-    <t>Márvány utca</t>
-  </si>
-  <si>
-    <t>307482627/1</t>
-  </si>
-  <si>
-    <t>307482627</t>
-  </si>
-  <si>
-    <t>Muhar utca</t>
-  </si>
-  <si>
-    <t>307482743/1</t>
-  </si>
-  <si>
-    <t>307482743</t>
-  </si>
-  <si>
-    <t>1106</t>
-  </si>
-  <si>
-    <t>Gyakorló utca</t>
-  </si>
-  <si>
-    <t>307482871/1</t>
-  </si>
-  <si>
-    <t>307482871</t>
-  </si>
-  <si>
     <t>2120</t>
   </si>
   <si>
     <t>DUNAKESZI</t>
   </si>
   <si>
-    <t>Faludi János utca</t>
-  </si>
-  <si>
-    <t>307482902/1</t>
-  </si>
-  <si>
-    <t>307482902</t>
-  </si>
-  <si>
     <t>1117</t>
   </si>
   <si>
-    <t>307483072/1</t>
-  </si>
-  <si>
-    <t>307483072</t>
-  </si>
-  <si>
     <t>1112</t>
   </si>
   <si>
-    <t>Hermánd utca</t>
-  </si>
-  <si>
-    <t>307483214/1</t>
-  </si>
-  <si>
-    <t>307483214</t>
-  </si>
-  <si>
-    <t>Párta köz</t>
-  </si>
-  <si>
-    <t>307483270/1</t>
-  </si>
-  <si>
-    <t>307483270</t>
-  </si>
-  <si>
-    <t>1023</t>
-  </si>
-  <si>
-    <t>Levél utca</t>
-  </si>
-  <si>
-    <t>307483270/2</t>
-  </si>
-  <si>
-    <t>307483270/3</t>
-  </si>
-  <si>
-    <t>307530336/1</t>
-  </si>
-  <si>
-    <t>307530336</t>
-  </si>
-  <si>
-    <t>2737</t>
-  </si>
-  <si>
-    <t>CEGLÉDBERCEL</t>
-  </si>
-  <si>
     <t>Vörösmarty utca</t>
   </si>
   <si>
-    <t>307530358/1</t>
-  </si>
-  <si>
-    <t>307530358</t>
-  </si>
-  <si>
-    <t>2633</t>
-  </si>
-  <si>
-    <t>IPOLYTÖLGYES</t>
-  </si>
-  <si>
-    <t>Kossuth utca</t>
-  </si>
-  <si>
-    <t>307530520/1</t>
-  </si>
-  <si>
-    <t>307530520</t>
-  </si>
-  <si>
-    <t>Körösbánya Utca</t>
-  </si>
-  <si>
-    <t>307530564/1</t>
-  </si>
-  <si>
-    <t>307530564</t>
-  </si>
-  <si>
-    <t>Malomtó utca</t>
-  </si>
-  <si>
-    <t>307530620/1</t>
-  </si>
-  <si>
-    <t>307530620</t>
-  </si>
-  <si>
-    <t>1149</t>
-  </si>
-  <si>
-    <t>Kövér Lajos utca</t>
-  </si>
-  <si>
-    <t>307530962/1</t>
-  </si>
-  <si>
-    <t>307530962</t>
-  </si>
-  <si>
-    <t>1163</t>
-  </si>
-  <si>
-    <t>Lándzsa utca</t>
-  </si>
-  <si>
-    <t>307530981/1</t>
-  </si>
-  <si>
-    <t>307530981</t>
-  </si>
-  <si>
-    <t>1108</t>
-  </si>
-  <si>
-    <t>Lenfonó utca</t>
-  </si>
-  <si>
-    <t>307531024/1</t>
-  </si>
-  <si>
-    <t>307531024</t>
-  </si>
-  <si>
-    <t>Juhar utca</t>
-  </si>
-  <si>
-    <t>307579790/1</t>
-  </si>
-  <si>
-    <t>307579790</t>
-  </si>
-  <si>
-    <t>Hága László utca</t>
-  </si>
-  <si>
     <t>307628153/1</t>
   </si>
   <si>
@@ -1395,226 +372,1975 @@
     <t>307628153/2</t>
   </si>
   <si>
-    <t>307628394/1</t>
-  </si>
-  <si>
-    <t>307628394</t>
-  </si>
-  <si>
-    <t>1101</t>
-  </si>
-  <si>
-    <t>Csilla utca</t>
-  </si>
-  <si>
-    <t>307689408/1</t>
-  </si>
-  <si>
-    <t>307689408</t>
-  </si>
-  <si>
-    <t>Háros utca</t>
-  </si>
-  <si>
-    <t>307741125/1</t>
-  </si>
-  <si>
-    <t>307741125</t>
-  </si>
-  <si>
-    <t>1203</t>
-  </si>
-  <si>
-    <t>307741256/1</t>
-  </si>
-  <si>
-    <t>307741256</t>
-  </si>
-  <si>
-    <t>2072</t>
-  </si>
-  <si>
-    <t>ZSÁMBÉK</t>
-  </si>
-  <si>
-    <t>307741380/1</t>
-  </si>
-  <si>
-    <t>307741380</t>
-  </si>
-  <si>
-    <t>Illyés Gyula utca</t>
-  </si>
-  <si>
-    <t>307741380/2</t>
-  </si>
-  <si>
-    <t>307806493/1</t>
-  </si>
-  <si>
-    <t>307806493</t>
-  </si>
-  <si>
-    <t>307806637/1</t>
-  </si>
-  <si>
-    <t>307806637</t>
-  </si>
-  <si>
     <t>1164</t>
   </si>
   <si>
-    <t>Vízesés utca</t>
-  </si>
-  <si>
-    <t>99002327/1</t>
-  </si>
-  <si>
-    <t>99002327</t>
-  </si>
-  <si>
-    <t>Pesti út</t>
-  </si>
-  <si>
-    <t>99002335/1</t>
-  </si>
-  <si>
-    <t>99002335</t>
-  </si>
-  <si>
-    <t>Liszt Ferenc sétány</t>
-  </si>
-  <si>
-    <t>202604102600779201</t>
-  </si>
-  <si>
-    <t>NFD6-04-01-H7FC</t>
-  </si>
-  <si>
-    <t>202604102600786401</t>
-  </si>
-  <si>
-    <t>NFD6-04-02-SZQD</t>
-  </si>
-  <si>
-    <t>Zágrábi utca</t>
-  </si>
-  <si>
-    <t>202604102600786402</t>
-  </si>
-  <si>
-    <t>202604102600786403</t>
-  </si>
-  <si>
-    <t>202604082600809501</t>
-  </si>
-  <si>
-    <t>NFD6-04-07-J4DB</t>
-  </si>
-  <si>
-    <t>Gábor Áron utca</t>
-  </si>
-  <si>
-    <t>202604102600830601</t>
-  </si>
-  <si>
-    <t>NFD6-04-09-7QM7</t>
-  </si>
-  <si>
-    <t>Sugár út</t>
-  </si>
-  <si>
-    <t>202604102600831101</t>
-  </si>
-  <si>
-    <t>NFD6-04-09-B4MB</t>
-  </si>
-  <si>
-    <t>Szabadszó utca</t>
-  </si>
-  <si>
-    <t>202604102600827301</t>
-  </si>
-  <si>
-    <t>NFD6-04-09-KCU2</t>
-  </si>
-  <si>
     <t>Szélmalom út</t>
   </si>
   <si>
-    <t>202604102600829201</t>
-  </si>
-  <si>
-    <t>NFD6-04-09-N5U2</t>
-  </si>
-  <si>
-    <t>Piszke utca</t>
-  </si>
-  <si>
-    <t>202604102600832201</t>
-  </si>
-  <si>
-    <t>NFD6-04-09-PL9X</t>
-  </si>
-  <si>
-    <t>Szemere Bertalan utca</t>
-  </si>
-  <si>
-    <t>202604102600827901</t>
-  </si>
-  <si>
-    <t>NFD6-04-09-TJEY</t>
-  </si>
-  <si>
     <t>1035</t>
   </si>
   <si>
-    <t>Vörösvári út</t>
-  </si>
-  <si>
-    <t>202604102600833401</t>
-  </si>
-  <si>
-    <t>NFE6-04-09-LBAF</t>
-  </si>
-  <si>
-    <t>Ferihegyi út</t>
-  </si>
-  <si>
-    <t>202604102600828601</t>
-  </si>
-  <si>
-    <t>NFE6-04-09-MYLR</t>
-  </si>
-  <si>
-    <t>Iharos Sándor utca</t>
-  </si>
-  <si>
-    <t>202604102600834601</t>
-  </si>
-  <si>
-    <t>NFE6-04-09-SDP3</t>
-  </si>
-  <si>
-    <t>Kordován tér</t>
-  </si>
-  <si>
-    <t>202604102600832301</t>
-  </si>
-  <si>
-    <t>NFE6-04-09-Y5KC</t>
-  </si>
-  <si>
     <t>Arany János utca</t>
   </si>
   <si>
-    <t>202604102600831001</t>
-  </si>
-  <si>
-    <t>NFE6-04-09-ZLLP</t>
-  </si>
-  <si>
-    <t>Sárd utca</t>
+    <t>159995579539097170</t>
+  </si>
+  <si>
+    <t>1-3059/2026</t>
+  </si>
+  <si>
+    <t>EUROTRESOR</t>
+  </si>
+  <si>
+    <t>248745408/1</t>
+  </si>
+  <si>
+    <t>248745408</t>
+  </si>
+  <si>
+    <t>2045</t>
+  </si>
+  <si>
+    <t>TÖRÖKBÁLINT</t>
+  </si>
+  <si>
+    <t>Torbágy utca</t>
+  </si>
+  <si>
+    <t>69d7a3255cef447acab8cdf1</t>
+  </si>
+  <si>
+    <t>260311-F00014104</t>
+  </si>
+  <si>
+    <t>2220</t>
+  </si>
+  <si>
+    <t>VECSÉS</t>
+  </si>
+  <si>
+    <t>Lázár Vilmos utca</t>
+  </si>
+  <si>
+    <t>69d63fc65cef447acab8b219</t>
+  </si>
+  <si>
+    <t>260317-F00006210</t>
+  </si>
+  <si>
+    <t>Füredi utca</t>
+  </si>
+  <si>
+    <t>69dcc0fa5cef447acab90da8</t>
+  </si>
+  <si>
+    <t>260329-W00010441</t>
+  </si>
+  <si>
+    <t>1184</t>
+  </si>
+  <si>
+    <t>Széchenyi István utca</t>
+  </si>
+  <si>
+    <t>69d8a15e5cef447acab8d9a6</t>
+  </si>
+  <si>
+    <t>260331-F00010842</t>
+  </si>
+  <si>
+    <t>2085</t>
+  </si>
+  <si>
+    <t>PILISVÖRÖSVÁR</t>
+  </si>
+  <si>
+    <t>Fecske utca</t>
+  </si>
+  <si>
+    <t>69d8a49c5cef447acab8d9fb</t>
+  </si>
+  <si>
+    <t>260401-W00010636</t>
+  </si>
+  <si>
+    <t>2760</t>
+  </si>
+  <si>
+    <t>NAGYKÁTA</t>
+  </si>
+  <si>
+    <t>Bartók Béla utca</t>
+  </si>
+  <si>
+    <t>69d125305cef447acab87ff1</t>
+  </si>
+  <si>
+    <t>SZ-850</t>
+  </si>
+  <si>
+    <t>260404-W00005064</t>
+  </si>
+  <si>
+    <t>2721</t>
+  </si>
+  <si>
+    <t>PILIS</t>
+  </si>
+  <si>
+    <t>Hernád köz</t>
+  </si>
+  <si>
+    <t>69d7b5b35cef447acab8d158</t>
+  </si>
+  <si>
+    <t>260407-F00006572</t>
+  </si>
+  <si>
+    <t>2750</t>
+  </si>
+  <si>
+    <t>NAGYKŐRÖS</t>
+  </si>
+  <si>
+    <t>Pásztor utca</t>
+  </si>
+  <si>
+    <t>69d7be7a5cef447acab8d2ae</t>
+  </si>
+  <si>
+    <t>260407-F00007186</t>
+  </si>
+  <si>
+    <t>2151</t>
+  </si>
+  <si>
+    <t>FÓT</t>
+  </si>
+  <si>
+    <t>Alagi utca</t>
+  </si>
+  <si>
+    <t>69d7be7a5cef447acab8d2af</t>
+  </si>
+  <si>
+    <t>69d7b9735cef447acab8d1e0</t>
+  </si>
+  <si>
+    <t>260407-W00002141</t>
+  </si>
+  <si>
+    <t>Kölcsey utca</t>
+  </si>
+  <si>
+    <t>69d545085cef447acab8a460</t>
+  </si>
+  <si>
+    <t>260407-W00010284</t>
+  </si>
+  <si>
+    <t>Cinke utca</t>
+  </si>
+  <si>
+    <t>69d643555cef447acab8b2a8</t>
+  </si>
+  <si>
+    <t>260408-W00005528</t>
+  </si>
+  <si>
+    <t>2626</t>
+  </si>
+  <si>
+    <t>NAGYMAROS</t>
+  </si>
+  <si>
+    <t>Kittenberger Kálmán utca</t>
+  </si>
+  <si>
+    <t>69d64b8f5cef447acab8b3cc</t>
+  </si>
+  <si>
+    <t>SZ-827</t>
+  </si>
+  <si>
+    <t>260408-W00005982</t>
+  </si>
+  <si>
+    <t>2074</t>
+  </si>
+  <si>
+    <t>PERBÁL</t>
+  </si>
+  <si>
+    <t>Hunyadi utca</t>
+  </si>
+  <si>
+    <t>69d64b8f5cef447acab8b3cd</t>
+  </si>
+  <si>
+    <t>69d64b8f5cef447acab8b3cf</t>
+  </si>
+  <si>
+    <t>69d759195cef447acab8c08d</t>
+  </si>
+  <si>
+    <t>260409-F00001952</t>
+  </si>
+  <si>
+    <t>1143</t>
+  </si>
+  <si>
+    <t>Ilka utca</t>
+  </si>
+  <si>
+    <t>69d74d895cef447acab8bee6</t>
+  </si>
+  <si>
+    <t>260409-W00001238</t>
+  </si>
+  <si>
+    <t>Dr. Gönczy Gyula utca</t>
+  </si>
+  <si>
+    <t>69d74d895cef447acab8bee7</t>
+  </si>
+  <si>
+    <t>69d749cf5cef447acab8be8a</t>
+  </si>
+  <si>
+    <t>260409-W00001351</t>
+  </si>
+  <si>
+    <t>1196</t>
+  </si>
+  <si>
+    <t>Esze Tamás utca</t>
+  </si>
+  <si>
+    <t>69d7b2225cef447acab8d096</t>
+  </si>
+  <si>
+    <t>260409-W00006945</t>
+  </si>
+  <si>
+    <t>2747</t>
+  </si>
+  <si>
+    <t>TÖRTEL</t>
+  </si>
+  <si>
+    <t>Ernyő dűlő</t>
+  </si>
+  <si>
+    <t>69d7b2225cef447acab8d097</t>
+  </si>
+  <si>
+    <t>69d7ad835cef447acab8cfc3</t>
+  </si>
+  <si>
+    <t>260409-W00007277</t>
+  </si>
+  <si>
+    <t>2730</t>
+  </si>
+  <si>
+    <t>ALBERTIRSA</t>
+  </si>
+  <si>
+    <t>József Attila utca</t>
+  </si>
+  <si>
+    <t>69d7c2865cef447acab8d32a</t>
+  </si>
+  <si>
+    <t>260409-W00008311</t>
+  </si>
+  <si>
+    <t>2144</t>
+  </si>
+  <si>
+    <t>KEREPES</t>
+  </si>
+  <si>
+    <t>69d7c4eb5cef447acab8d371</t>
+  </si>
+  <si>
+    <t>260409-W00008369</t>
+  </si>
+  <si>
+    <t>69d7c4eb5cef447acab8d372</t>
+  </si>
+  <si>
+    <t>69d90aa85cef447acab8ea34</t>
+  </si>
+  <si>
+    <t>260410-F00010871-3</t>
+  </si>
+  <si>
+    <t>Fejér György utca</t>
+  </si>
+  <si>
+    <t>69d9014f5cef447acab8e8bc</t>
+  </si>
+  <si>
+    <t>260410-F00011257</t>
+  </si>
+  <si>
+    <t>1038</t>
+  </si>
+  <si>
+    <t>Kőbánya utca</t>
+  </si>
+  <si>
+    <t>69d935ff5cef447acab8ede5</t>
+  </si>
+  <si>
+    <t>260410-F00014071</t>
+  </si>
+  <si>
+    <t>1032</t>
+  </si>
+  <si>
+    <t>69d89c805cef447acab8d947</t>
+  </si>
+  <si>
+    <t>260410-W00001725</t>
+  </si>
+  <si>
+    <t>69d8ae505cef447acab8db7e</t>
+  </si>
+  <si>
+    <t>260410-W00002683</t>
+  </si>
+  <si>
+    <t>Csodaszarvas utca</t>
+  </si>
+  <si>
+    <t>69d8ae505cef447acab8db80</t>
+  </si>
+  <si>
+    <t>69d8f9115cef447acab8e74e</t>
+  </si>
+  <si>
+    <t>260410-W00006839</t>
+  </si>
+  <si>
+    <t>1039</t>
+  </si>
+  <si>
+    <t>Hatvany Lajos utca</t>
+  </si>
+  <si>
+    <t>69d917905cef447acab8ebce</t>
+  </si>
+  <si>
+    <t>260410-W00008466</t>
+  </si>
+  <si>
+    <t>69dcb3755cef447acab90bc4</t>
+  </si>
+  <si>
+    <t>260411-F00001242</t>
+  </si>
+  <si>
+    <t>Lenke utca</t>
+  </si>
+  <si>
+    <t>69da49a15cef447acab8f857</t>
+  </si>
+  <si>
+    <t>260411-F00004932</t>
+  </si>
+  <si>
+    <t>Kelemen utca</t>
+  </si>
+  <si>
+    <t>69dbb01d5cef447acab90300</t>
+  </si>
+  <si>
+    <t>260412-F00003094</t>
+  </si>
+  <si>
+    <t>1113</t>
+  </si>
+  <si>
+    <t>Nagyszőlős utca</t>
+  </si>
+  <si>
+    <t>69dba31b5cef447acab9024a</t>
+  </si>
+  <si>
+    <t>260412-W00005130</t>
+  </si>
+  <si>
+    <t>1146</t>
+  </si>
+  <si>
+    <t>Cházár András utca</t>
+  </si>
+  <si>
+    <t>69dcc1cb5cef447acab90deb</t>
+  </si>
+  <si>
+    <t>260413-F00002564</t>
+  </si>
+  <si>
+    <t>1083</t>
+  </si>
+  <si>
+    <t>Práter utca</t>
+  </si>
+  <si>
+    <t>69dcb1e15cef447acab90b7a</t>
+  </si>
+  <si>
+    <t>260413-F00004022</t>
+  </si>
+  <si>
+    <t>69dcb1e15cef447acab90b7b</t>
+  </si>
+  <si>
+    <t>69dc95ba5cef447acab906e1</t>
+  </si>
+  <si>
+    <t>260413-W00001139</t>
+  </si>
+  <si>
+    <t>1045</t>
+  </si>
+  <si>
+    <t>Virág utca</t>
+  </si>
+  <si>
+    <t>69dcad275cef447acab90aa9</t>
+  </si>
+  <si>
+    <t>260413-W00002149</t>
+  </si>
+  <si>
+    <t>1239</t>
+  </si>
+  <si>
+    <t>Batthyány utca</t>
+  </si>
+  <si>
+    <t>1449-167564</t>
+  </si>
+  <si>
+    <t>267004770</t>
+  </si>
+  <si>
+    <t>Kinizsi ut</t>
+  </si>
+  <si>
+    <t>FIZZ-1000861023</t>
+  </si>
+  <si>
+    <t>267004888</t>
+  </si>
+  <si>
+    <t>Madách Imre</t>
+  </si>
+  <si>
+    <t>FIZZ-1000868812</t>
+  </si>
+  <si>
+    <t>267005103</t>
+  </si>
+  <si>
+    <t>2013</t>
+  </si>
+  <si>
+    <t>POMÁZ-KISKOVÁCSI</t>
+  </si>
+  <si>
+    <t>Tavasz U</t>
+  </si>
+  <si>
+    <t>FIZZ-1000869350</t>
+  </si>
+  <si>
+    <t>267005111</t>
+  </si>
+  <si>
+    <t>Csiki-hegyek utca</t>
+  </si>
+  <si>
+    <t>FIZZ-1000869999</t>
+  </si>
+  <si>
+    <t>267005156</t>
+  </si>
+  <si>
+    <t>Árok Utca</t>
+  </si>
+  <si>
+    <t>FIZZ-1000870832</t>
+  </si>
+  <si>
+    <t>267005161</t>
+  </si>
+  <si>
+    <t>2639</t>
+  </si>
+  <si>
+    <t>BERNECEBARÁTI</t>
+  </si>
+  <si>
+    <t>Mikes Kelemen utca</t>
+  </si>
+  <si>
+    <t>FIZZ-1000870939</t>
+  </si>
+  <si>
+    <t>267005164</t>
+  </si>
+  <si>
+    <t>1157</t>
+  </si>
+  <si>
+    <t>Erdőkerülő utca</t>
+  </si>
+  <si>
+    <t>301281314/1</t>
+  </si>
+  <si>
+    <t>301281314</t>
+  </si>
+  <si>
+    <t>Vegyész utca</t>
+  </si>
+  <si>
+    <t>304875752/1</t>
+  </si>
+  <si>
+    <t>304875752</t>
+  </si>
+  <si>
+    <t>Tó utca</t>
+  </si>
+  <si>
+    <t>304875752/2</t>
+  </si>
+  <si>
+    <t>306457853/1</t>
+  </si>
+  <si>
+    <t>306457853</t>
+  </si>
+  <si>
+    <t>1016</t>
+  </si>
+  <si>
+    <t>Bérc utca</t>
+  </si>
+  <si>
+    <t>306457853/2</t>
+  </si>
+  <si>
+    <t>306621355/1</t>
+  </si>
+  <si>
+    <t>306621355</t>
+  </si>
+  <si>
+    <t>2011</t>
+  </si>
+  <si>
+    <t>BUDAKALÁSZ</t>
+  </si>
+  <si>
+    <t>Szentendrei út</t>
+  </si>
+  <si>
+    <t>306721180/1</t>
+  </si>
+  <si>
+    <t>306721180</t>
+  </si>
+  <si>
+    <t>Füredi park</t>
+  </si>
+  <si>
+    <t>306823736/1</t>
+  </si>
+  <si>
+    <t>306823736</t>
+  </si>
+  <si>
+    <t>2700</t>
+  </si>
+  <si>
+    <t>CEGLÉD</t>
+  </si>
+  <si>
+    <t>Só utca</t>
+  </si>
+  <si>
+    <t>306890648/2/1</t>
+  </si>
+  <si>
+    <t>306890648/2</t>
+  </si>
+  <si>
+    <t>306890648/2/2</t>
+  </si>
+  <si>
+    <t>307081145/1</t>
+  </si>
+  <si>
+    <t>307081145</t>
+  </si>
+  <si>
+    <t>1214</t>
+  </si>
+  <si>
+    <t>Kossuth lajos utca</t>
+  </si>
+  <si>
+    <t>307081145/2</t>
+  </si>
+  <si>
+    <t>307141764/1</t>
+  </si>
+  <si>
+    <t>307141764</t>
+  </si>
+  <si>
+    <t>2768</t>
+  </si>
+  <si>
+    <t>ÚJSZILVÁS</t>
+  </si>
+  <si>
+    <t>Rózsa utca</t>
+  </si>
+  <si>
+    <t>307141764/2</t>
+  </si>
+  <si>
+    <t>307198032/1</t>
+  </si>
+  <si>
+    <t>307198032</t>
+  </si>
+  <si>
+    <t>Balogh Ádám utca</t>
+  </si>
+  <si>
+    <t>307198032/2</t>
+  </si>
+  <si>
+    <t>307198032/3</t>
+  </si>
+  <si>
+    <t>307238580/1</t>
+  </si>
+  <si>
+    <t>307238580</t>
+  </si>
+  <si>
+    <t>2336</t>
+  </si>
+  <si>
+    <t>DUNAVARSÁNY</t>
+  </si>
+  <si>
+    <t>Vörösmarty Mihály utca</t>
+  </si>
+  <si>
+    <t>307279136/1</t>
+  </si>
+  <si>
+    <t>307279136</t>
+  </si>
+  <si>
+    <t>307279136/2</t>
+  </si>
+  <si>
+    <t>307343085/1</t>
+  </si>
+  <si>
+    <t>307343085</t>
+  </si>
+  <si>
+    <t>1036</t>
+  </si>
+  <si>
+    <t>Uszály utca</t>
+  </si>
+  <si>
+    <t>307343452/1</t>
+  </si>
+  <si>
+    <t>307343452</t>
+  </si>
+  <si>
+    <t>Úrbéres utca</t>
+  </si>
+  <si>
+    <t>307343662/1</t>
+  </si>
+  <si>
+    <t>307343662</t>
+  </si>
+  <si>
+    <t>307378990/1</t>
+  </si>
+  <si>
+    <t>307378990</t>
+  </si>
+  <si>
+    <t>2614</t>
+  </si>
+  <si>
+    <t>PENC</t>
+  </si>
+  <si>
+    <t>Csővári út</t>
+  </si>
+  <si>
+    <t>307379683/1</t>
+  </si>
+  <si>
+    <t>307379683</t>
+  </si>
+  <si>
+    <t>Remsey Jenő körút</t>
+  </si>
+  <si>
+    <t>307379683/2</t>
+  </si>
+  <si>
+    <t>307426249/1</t>
+  </si>
+  <si>
+    <t>307426249</t>
+  </si>
+  <si>
+    <t>2461</t>
+  </si>
+  <si>
+    <t>TÁRNOK</t>
+  </si>
+  <si>
+    <t>Kárász utca</t>
+  </si>
+  <si>
+    <t>307426249/2</t>
+  </si>
+  <si>
+    <t>307426300/1</t>
+  </si>
+  <si>
+    <t>307426300</t>
+  </si>
+  <si>
+    <t>Ország út</t>
+  </si>
+  <si>
+    <t>307427054/1</t>
+  </si>
+  <si>
+    <t>307427054</t>
+  </si>
+  <si>
+    <t>1033</t>
+  </si>
+  <si>
+    <t>Szentendrei Út</t>
+  </si>
+  <si>
+    <t>307427054/2</t>
+  </si>
+  <si>
+    <t>307482603/1</t>
+  </si>
+  <si>
+    <t>307482603</t>
+  </si>
+  <si>
+    <t>Lajos utca</t>
+  </si>
+  <si>
+    <t>307482949/1</t>
+  </si>
+  <si>
+    <t>307482949</t>
+  </si>
+  <si>
+    <t>Pünkösdfürdő utca</t>
+  </si>
+  <si>
+    <t>307482966/1</t>
+  </si>
+  <si>
+    <t>307482966</t>
+  </si>
+  <si>
+    <t>Versec sor</t>
+  </si>
+  <si>
+    <t>307483162/1</t>
+  </si>
+  <si>
+    <t>307483162</t>
+  </si>
+  <si>
+    <t>2092</t>
+  </si>
+  <si>
+    <t>BUDAKESZI</t>
+  </si>
+  <si>
+    <t>Etheles park</t>
+  </si>
+  <si>
+    <t>307530057/1</t>
+  </si>
+  <si>
+    <t>307530057</t>
+  </si>
+  <si>
+    <t>Lövéte utca</t>
+  </si>
+  <si>
+    <t>307530383/1</t>
+  </si>
+  <si>
+    <t>307530383</t>
+  </si>
+  <si>
+    <t>1202</t>
+  </si>
+  <si>
+    <t>Felvidék utca</t>
+  </si>
+  <si>
+    <t>307530443/1</t>
+  </si>
+  <si>
+    <t>307530443</t>
+  </si>
+  <si>
+    <t>2711</t>
+  </si>
+  <si>
+    <t>TÁPIÓSZENTMÁRTON</t>
+  </si>
+  <si>
+    <t>Kubinyi Ágoston út</t>
+  </si>
+  <si>
+    <t>307530746/1</t>
+  </si>
+  <si>
+    <t>307530746</t>
+  </si>
+  <si>
+    <t>panoráma utca</t>
+  </si>
+  <si>
+    <t>307530770/1</t>
+  </si>
+  <si>
+    <t>307530770</t>
+  </si>
+  <si>
+    <t>307579435/1</t>
+  </si>
+  <si>
+    <t>307579435</t>
+  </si>
+  <si>
+    <t>Orion utca</t>
+  </si>
+  <si>
+    <t>307579464/1</t>
+  </si>
+  <si>
+    <t>307579464</t>
+  </si>
+  <si>
+    <t>1213</t>
+  </si>
+  <si>
+    <t>Damjanich János út</t>
+  </si>
+  <si>
+    <t>307579514/1</t>
+  </si>
+  <si>
+    <t>SZ-834</t>
+  </si>
+  <si>
+    <t>307579514</t>
+  </si>
+  <si>
+    <t>1132</t>
+  </si>
+  <si>
+    <t>Visegrádi utca</t>
+  </si>
+  <si>
+    <t>307579536/1</t>
+  </si>
+  <si>
+    <t>307579536</t>
+  </si>
+  <si>
+    <t>Dereglye utca</t>
+  </si>
+  <si>
+    <t>307579705/1</t>
+  </si>
+  <si>
+    <t>307579705</t>
+  </si>
+  <si>
+    <t>Wass Albert utca</t>
+  </si>
+  <si>
+    <t>307579705/2</t>
+  </si>
+  <si>
+    <t>307579813/1</t>
+  </si>
+  <si>
+    <t>307579813</t>
+  </si>
+  <si>
+    <t>2318</t>
+  </si>
+  <si>
+    <t>SZIGETSZENTMÁRTON</t>
+  </si>
+  <si>
+    <t>Petőfi Sándor Utca</t>
+  </si>
+  <si>
+    <t>307579813/2</t>
+  </si>
+  <si>
+    <t>307579992/1</t>
+  </si>
+  <si>
+    <t>307579992</t>
+  </si>
+  <si>
+    <t>Tarcali utca</t>
+  </si>
+  <si>
+    <t>307627776/1</t>
+  </si>
+  <si>
+    <t>307627776</t>
+  </si>
+  <si>
+    <t>307627826/1</t>
+  </si>
+  <si>
+    <t>307627826</t>
+  </si>
+  <si>
+    <t>307627906/1</t>
+  </si>
+  <si>
+    <t>307627906</t>
+  </si>
+  <si>
+    <t>Tippan utca</t>
+  </si>
+  <si>
+    <t>307628001/1</t>
+  </si>
+  <si>
+    <t>307628001</t>
+  </si>
+  <si>
+    <t>Hamzsabégi út</t>
+  </si>
+  <si>
+    <t>307628048/1</t>
+  </si>
+  <si>
+    <t>307628048</t>
+  </si>
+  <si>
+    <t>1123</t>
+  </si>
+  <si>
+    <t>Csörsz utca</t>
+  </si>
+  <si>
+    <t>307628223/1</t>
+  </si>
+  <si>
+    <t>307628223</t>
+  </si>
+  <si>
+    <t>307628548/1</t>
+  </si>
+  <si>
+    <t>307628548</t>
+  </si>
+  <si>
+    <t>Illés utca</t>
+  </si>
+  <si>
+    <t>307628658/1</t>
+  </si>
+  <si>
+    <t>307628658</t>
+  </si>
+  <si>
+    <t>1115</t>
+  </si>
+  <si>
+    <t>Bánk Bán</t>
+  </si>
+  <si>
+    <t>307628658/2</t>
+  </si>
+  <si>
+    <t>307688669/1</t>
+  </si>
+  <si>
+    <t>307688669</t>
+  </si>
+  <si>
+    <t>Csontváry Kosztka Tivadar utca</t>
+  </si>
+  <si>
+    <t>307688816/1</t>
+  </si>
+  <si>
+    <t>307688816</t>
+  </si>
+  <si>
+    <t>Nagymező utca</t>
+  </si>
+  <si>
+    <t>307688992/1</t>
+  </si>
+  <si>
+    <t>307688992</t>
+  </si>
+  <si>
+    <t>Nádor utca</t>
+  </si>
+  <si>
+    <t>307689103/1</t>
+  </si>
+  <si>
+    <t>307689103</t>
+  </si>
+  <si>
+    <t>Eötvös utca</t>
+  </si>
+  <si>
+    <t>307689158/1</t>
+  </si>
+  <si>
+    <t>307689158</t>
+  </si>
+  <si>
+    <t>Haránt köz</t>
+  </si>
+  <si>
+    <t>307689164/1</t>
+  </si>
+  <si>
+    <t>307689164</t>
+  </si>
+  <si>
+    <t>307689174/1</t>
+  </si>
+  <si>
+    <t>307689174</t>
+  </si>
+  <si>
+    <t>1046</t>
+  </si>
+  <si>
+    <t>Blaha Lujza utca</t>
+  </si>
+  <si>
+    <t>307689224/1</t>
+  </si>
+  <si>
+    <t>307689224</t>
+  </si>
+  <si>
+    <t>Erdősor út</t>
+  </si>
+  <si>
+    <t>307689459/1</t>
+  </si>
+  <si>
+    <t>307689459</t>
+  </si>
+  <si>
+    <t>2317</t>
+  </si>
+  <si>
+    <t>SZIGETCSÉP</t>
+  </si>
+  <si>
+    <t>Ady Endre utca</t>
+  </si>
+  <si>
+    <t>307689522/1</t>
+  </si>
+  <si>
+    <t>307689522</t>
+  </si>
+  <si>
+    <t>307689552/1</t>
+  </si>
+  <si>
+    <t>307689552</t>
+  </si>
+  <si>
+    <t>Fraknó utca</t>
+  </si>
+  <si>
+    <t>307740581/1</t>
+  </si>
+  <si>
+    <t>307740581</t>
+  </si>
+  <si>
+    <t>307740878/1</t>
+  </si>
+  <si>
+    <t>307740878</t>
+  </si>
+  <si>
+    <t>Torbágy Utca</t>
+  </si>
+  <si>
+    <t>307740887/1</t>
+  </si>
+  <si>
+    <t>307740887</t>
+  </si>
+  <si>
+    <t>Páskom utca</t>
+  </si>
+  <si>
+    <t>307741091/1</t>
+  </si>
+  <si>
+    <t>307741091</t>
+  </si>
+  <si>
+    <t>307741229/1</t>
+  </si>
+  <si>
+    <t>307741229</t>
+  </si>
+  <si>
+    <t>Zöldmező utca</t>
+  </si>
+  <si>
+    <t>307741234/1</t>
+  </si>
+  <si>
+    <t>307741234</t>
+  </si>
+  <si>
+    <t>Soroksári út</t>
+  </si>
+  <si>
+    <t>307741341/1</t>
+  </si>
+  <si>
+    <t>307741341</t>
+  </si>
+  <si>
+    <t>1078</t>
+  </si>
+  <si>
+    <t>Marek József utca</t>
+  </si>
+  <si>
+    <t>307806234/1</t>
+  </si>
+  <si>
+    <t>307806234</t>
+  </si>
+  <si>
+    <t>Levendula utca</t>
+  </si>
+  <si>
+    <t>307806234/2</t>
+  </si>
+  <si>
+    <t>307806310/1</t>
+  </si>
+  <si>
+    <t>307806310</t>
+  </si>
+  <si>
+    <t>1055</t>
+  </si>
+  <si>
+    <t>Szent István körút</t>
+  </si>
+  <si>
+    <t>307806404/1</t>
+  </si>
+  <si>
+    <t>307806404</t>
+  </si>
+  <si>
+    <t>Bem József utca</t>
+  </si>
+  <si>
+    <t>307806426/1</t>
+  </si>
+  <si>
+    <t>307806426</t>
+  </si>
+  <si>
+    <t>Nagykőrösi utca</t>
+  </si>
+  <si>
+    <t>307806470/1</t>
+  </si>
+  <si>
+    <t>307806470</t>
+  </si>
+  <si>
+    <t>2241</t>
+  </si>
+  <si>
+    <t>SÜLYSÁP</t>
+  </si>
+  <si>
+    <t>Rózsa Utca</t>
+  </si>
+  <si>
+    <t>307806535/1</t>
+  </si>
+  <si>
+    <t>307806535</t>
+  </si>
+  <si>
+    <t>Kossuth Lajos utca</t>
+  </si>
+  <si>
+    <t>307806552/1</t>
+  </si>
+  <si>
+    <t>307806552</t>
+  </si>
+  <si>
+    <t>1111</t>
+  </si>
+  <si>
+    <t>Bartók Béla</t>
+  </si>
+  <si>
+    <t>307806590/1</t>
+  </si>
+  <si>
+    <t>307806590</t>
+  </si>
+  <si>
+    <t>csertő utca</t>
+  </si>
+  <si>
+    <t>307806699/1</t>
+  </si>
+  <si>
+    <t>307806699</t>
+  </si>
+  <si>
+    <t>Kékperje Utca</t>
+  </si>
+  <si>
+    <t>307806757/1</t>
+  </si>
+  <si>
+    <t>307806757</t>
+  </si>
+  <si>
+    <t>Dráva utca</t>
+  </si>
+  <si>
+    <t>307806757/2</t>
+  </si>
+  <si>
+    <t>307806757/3</t>
+  </si>
+  <si>
+    <t>307806941/1</t>
+  </si>
+  <si>
+    <t>307806941</t>
+  </si>
+  <si>
+    <t>Abonyfalva utca</t>
+  </si>
+  <si>
+    <t>307806973/1</t>
+  </si>
+  <si>
+    <t>307806973</t>
+  </si>
+  <si>
+    <t>1089</t>
+  </si>
+  <si>
+    <t>Kálvária tér</t>
+  </si>
+  <si>
+    <t>307807008/1</t>
+  </si>
+  <si>
+    <t>307807008</t>
+  </si>
+  <si>
+    <t>2051</t>
+  </si>
+  <si>
+    <t>BIATORBÁGY</t>
+  </si>
+  <si>
+    <t>Karikó János utca</t>
+  </si>
+  <si>
+    <t>202604132600784501</t>
+  </si>
+  <si>
+    <t>NFD6-04-02-537V</t>
+  </si>
+  <si>
+    <t>2113</t>
+  </si>
+  <si>
+    <t>ERDŐKERTES</t>
+  </si>
+  <si>
+    <t>Sport utca</t>
+  </si>
+  <si>
+    <t>202604132600811501</t>
+  </si>
+  <si>
+    <t>NFD6-04-07-VGNX</t>
+  </si>
+  <si>
+    <t>2141</t>
+  </si>
+  <si>
+    <t>CSÖMÖR</t>
+  </si>
+  <si>
+    <t>Nagy Sándor utca</t>
+  </si>
+  <si>
+    <t>202604092600825401</t>
+  </si>
+  <si>
+    <t>NFD6-04-08-VQLD</t>
+  </si>
+  <si>
+    <t>Mecsek utca</t>
+  </si>
+  <si>
+    <t>202604102600830201</t>
+  </si>
+  <si>
+    <t>NFD6-04-09-GCSW</t>
+  </si>
+  <si>
+    <t>2314</t>
+  </si>
+  <si>
+    <t>HALÁSZTELEK</t>
+  </si>
+  <si>
+    <t>Hermina utca</t>
+  </si>
+  <si>
+    <t>202604102600829101</t>
+  </si>
+  <si>
+    <t>NFD6-04-09-WNFS</t>
+  </si>
+  <si>
+    <t>2117</t>
+  </si>
+  <si>
+    <t>ISASZEG</t>
+  </si>
+  <si>
+    <t>Thököly utca</t>
+  </si>
+  <si>
+    <t>202604102600829102</t>
+  </si>
+  <si>
+    <t>202604102600829103</t>
+  </si>
+  <si>
+    <t>202604102600829104</t>
+  </si>
+  <si>
+    <t>202604102600829105</t>
+  </si>
+  <si>
+    <t>202604102600829106</t>
+  </si>
+  <si>
+    <t>202604102600829107</t>
+  </si>
+  <si>
+    <t>202604132600837401</t>
+  </si>
+  <si>
+    <t>NFD6-04-10-2N8Q</t>
+  </si>
+  <si>
+    <t>Gödölye utca</t>
+  </si>
+  <si>
+    <t>202604132600840901</t>
+  </si>
+  <si>
+    <t>NFD6-04-10-37AR</t>
+  </si>
+  <si>
+    <t>1029</t>
+  </si>
+  <si>
+    <t>Feketerigó utca</t>
+  </si>
+  <si>
+    <t>202604132600843401</t>
+  </si>
+  <si>
+    <t>NFD6-04-10-5QWF</t>
+  </si>
+  <si>
+    <t>1183</t>
+  </si>
+  <si>
+    <t>Ráday Gedeon utca</t>
+  </si>
+  <si>
+    <t>202604132600836301</t>
+  </si>
+  <si>
+    <t>NFD6-04-10-5ZLZ</t>
+  </si>
+  <si>
+    <t>2233</t>
+  </si>
+  <si>
+    <t>ECSER</t>
+  </si>
+  <si>
+    <t>Szegfű utca</t>
+  </si>
+  <si>
+    <t>202604132600837301</t>
+  </si>
+  <si>
+    <t>NFD6-04-10-ABK2</t>
+  </si>
+  <si>
+    <t>Rév út</t>
+  </si>
+  <si>
+    <t>202604132600840101</t>
+  </si>
+  <si>
+    <t>NFD6-04-10-BS88</t>
+  </si>
+  <si>
+    <t>1081</t>
+  </si>
+  <si>
+    <t>Bezerédj utca</t>
+  </si>
+  <si>
+    <t>202604132600844401</t>
+  </si>
+  <si>
+    <t>NFD6-04-10-CH4X</t>
+  </si>
+  <si>
+    <t>202604132600841901</t>
+  </si>
+  <si>
+    <t>NFD6-04-10-CUEF</t>
+  </si>
+  <si>
+    <t>POMÁZ</t>
+  </si>
+  <si>
+    <t>Sicambria utca</t>
+  </si>
+  <si>
+    <t>202604132600841501</t>
+  </si>
+  <si>
+    <t>NFD6-04-10-DZ8P</t>
+  </si>
+  <si>
+    <t>Móricz Zsigmond utca</t>
+  </si>
+  <si>
+    <t>202604132600838501</t>
+  </si>
+  <si>
+    <t>NFD6-04-10-ERL8</t>
+  </si>
+  <si>
+    <t>Kóczán út</t>
+  </si>
+  <si>
+    <t>202604132600840401</t>
+  </si>
+  <si>
+    <t>NFD6-04-10-FEAT</t>
+  </si>
+  <si>
+    <t>202604132600840001</t>
+  </si>
+  <si>
+    <t>NFD6-04-10-GQGC</t>
+  </si>
+  <si>
+    <t>2000</t>
+  </si>
+  <si>
+    <t>SZENTENDRE</t>
+  </si>
+  <si>
+    <t>Vasvári Pál utca</t>
+  </si>
+  <si>
+    <t>202604132600840002</t>
+  </si>
+  <si>
+    <t>202604132600844101</t>
+  </si>
+  <si>
+    <t>NFD6-04-10-HPMX</t>
+  </si>
+  <si>
+    <t>Cirmos sétány</t>
+  </si>
+  <si>
+    <t>202604132600846401</t>
+  </si>
+  <si>
+    <t>NFD6-04-10-L3H6</t>
+  </si>
+  <si>
+    <t>202604132600837101</t>
+  </si>
+  <si>
+    <t>NFD6-04-10-L7L2</t>
+  </si>
+  <si>
+    <t>1153</t>
+  </si>
+  <si>
+    <t>Pázmány Péter utca</t>
+  </si>
+  <si>
+    <t>202604132600844501</t>
+  </si>
+  <si>
+    <t>NFD6-04-10-NASX</t>
+  </si>
+  <si>
+    <t>1124</t>
+  </si>
+  <si>
+    <t>Kiss János altábornagy utca</t>
+  </si>
+  <si>
+    <t>202604132600837201</t>
+  </si>
+  <si>
+    <t>NFD6-04-10-SC2K</t>
+  </si>
+  <si>
+    <t>Juhász Gyula utca</t>
+  </si>
+  <si>
+    <t>202604132600844001</t>
+  </si>
+  <si>
+    <t>NFD6-04-10-VE4L</t>
+  </si>
+  <si>
+    <t>1223</t>
+  </si>
+  <si>
+    <t>Kapu utca</t>
+  </si>
+  <si>
+    <t>202604132600838901</t>
+  </si>
+  <si>
+    <t>NFD6-04-10-XG52</t>
+  </si>
+  <si>
+    <t>Berkenye sétány</t>
+  </si>
+  <si>
+    <t>202604132600844601</t>
+  </si>
+  <si>
+    <t>NFD6-04-10-ZCW2</t>
+  </si>
+  <si>
+    <t>2340</t>
+  </si>
+  <si>
+    <t>KISKUNLACHÁZA</t>
+  </si>
+  <si>
+    <t>Sas utca</t>
+  </si>
+  <si>
+    <t>202604132600858301</t>
+  </si>
+  <si>
+    <t>NFD6-04-11-ANMF</t>
+  </si>
+  <si>
+    <t>1161</t>
+  </si>
+  <si>
+    <t>Csömöri út</t>
+  </si>
+  <si>
+    <t>202604132600858302</t>
+  </si>
+  <si>
+    <t>202604132600859501</t>
+  </si>
+  <si>
+    <t>NFD6-04-11-KK77</t>
+  </si>
+  <si>
+    <t>2084</t>
+  </si>
+  <si>
+    <t>PILISSZENTIVÁN</t>
+  </si>
+  <si>
+    <t>Bem utca</t>
+  </si>
+  <si>
+    <t>202604132600861201</t>
+  </si>
+  <si>
+    <t>NFD6-04-11-KQD9</t>
+  </si>
+  <si>
+    <t>1044</t>
+  </si>
+  <si>
+    <t>Ugró Gyula sor</t>
+  </si>
+  <si>
+    <t>202604132600857001</t>
+  </si>
+  <si>
+    <t>NFD6-04-11-KVJ9</t>
+  </si>
+  <si>
+    <t>1172</t>
+  </si>
+  <si>
+    <t>I. utca</t>
+  </si>
+  <si>
+    <t>202604132600854201</t>
+  </si>
+  <si>
+    <t>NFD6-04-11-LPP4</t>
+  </si>
+  <si>
+    <t>János utca</t>
+  </si>
+  <si>
+    <t>202604132600855401</t>
+  </si>
+  <si>
+    <t>NFD6-04-11-TZQR</t>
+  </si>
+  <si>
+    <t>202604132600857901</t>
+  </si>
+  <si>
+    <t>NFD6-04-11-W7RD</t>
+  </si>
+  <si>
+    <t>2300</t>
+  </si>
+  <si>
+    <t>RÁCKEVE</t>
+  </si>
+  <si>
+    <t>Marossy utca</t>
+  </si>
+  <si>
+    <t>202604132600858401</t>
+  </si>
+  <si>
+    <t>NFD6-04-11-WS9L</t>
+  </si>
+  <si>
+    <t>2083</t>
+  </si>
+  <si>
+    <t>SOLYMÁR</t>
+  </si>
+  <si>
+    <t>Terstyánszky Ödön utca</t>
+  </si>
+  <si>
+    <t>202604132600863001</t>
+  </si>
+  <si>
+    <t>NFD6-04-12-2E7D</t>
+  </si>
+  <si>
+    <t>2053</t>
+  </si>
+  <si>
+    <t>HERCEGHALOM</t>
+  </si>
+  <si>
+    <t>202604132600863801</t>
+  </si>
+  <si>
+    <t>NFD6-04-12-2RYP</t>
+  </si>
+  <si>
+    <t>2145</t>
+  </si>
+  <si>
+    <t>Sólyom utca</t>
+  </si>
+  <si>
+    <t>202604132600863802</t>
+  </si>
+  <si>
+    <t>202604132600866601</t>
+  </si>
+  <si>
+    <t>NFD6-04-12-2YG9</t>
+  </si>
+  <si>
+    <t>202604132600864301</t>
+  </si>
+  <si>
+    <t>NFD6-04-12-4ECA</t>
+  </si>
+  <si>
+    <t>Népszínház utca</t>
+  </si>
+  <si>
+    <t>202604132600862601</t>
+  </si>
+  <si>
+    <t>NFD6-04-12-55F4</t>
+  </si>
+  <si>
+    <t>Lukács György utca</t>
+  </si>
+  <si>
+    <t>202604132600865101</t>
+  </si>
+  <si>
+    <t>NFD6-04-12-6N7A</t>
+  </si>
+  <si>
+    <t>202604132600865102</t>
+  </si>
+  <si>
+    <t>202604132600865103</t>
+  </si>
+  <si>
+    <t>202604132600865104</t>
+  </si>
+  <si>
+    <t>202604132600865105</t>
+  </si>
+  <si>
+    <t>202604132600862001</t>
+  </si>
+  <si>
+    <t>NFD6-04-12-7CCY</t>
+  </si>
+  <si>
+    <t>Sátorfák utca</t>
+  </si>
+  <si>
+    <t>202604132600862002</t>
+  </si>
+  <si>
+    <t>202604132600862003</t>
+  </si>
+  <si>
+    <t>202604132600862004</t>
+  </si>
+  <si>
+    <t>202604132600864801</t>
+  </si>
+  <si>
+    <t>NFD6-04-12-GVVJ</t>
+  </si>
+  <si>
+    <t>Szacsvay Tibor utca</t>
+  </si>
+  <si>
+    <t>202604132600865201</t>
+  </si>
+  <si>
+    <t>NFD6-04-12-JVPH</t>
+  </si>
+  <si>
+    <t>Lévai utca</t>
+  </si>
+  <si>
+    <t>202604132600864401</t>
+  </si>
+  <si>
+    <t>NFD6-04-12-RD45</t>
+  </si>
+  <si>
+    <t>1156</t>
+  </si>
+  <si>
+    <t>Páskomliget utca</t>
+  </si>
+  <si>
+    <t>NFD6-04-13-YYWP-1</t>
+  </si>
+  <si>
+    <t>NFD6-04-13-YYWP</t>
+  </si>
+  <si>
+    <t>Kapisztrán utca</t>
+  </si>
+  <si>
+    <t>NFD6-04-14-8VL5-1</t>
+  </si>
+  <si>
+    <t>NFD6-04-14-8VL5</t>
+  </si>
+  <si>
+    <t>Tétényi út</t>
+  </si>
+  <si>
+    <t>NFD6-04-14-JTNX-1</t>
+  </si>
+  <si>
+    <t>NFD6-04-14-JTNX</t>
+  </si>
+  <si>
+    <t>Eperjes utca</t>
+  </si>
+  <si>
+    <t>202604102600830801</t>
+  </si>
+  <si>
+    <t>NFE6-04-09-7WKK</t>
+  </si>
+  <si>
+    <t>Köztársaság utca</t>
+  </si>
+  <si>
+    <t>202604132600859001</t>
+  </si>
+  <si>
+    <t>NFE6-04-11-P6L8</t>
+  </si>
+  <si>
+    <t>1193</t>
+  </si>
+  <si>
+    <t>Vécsey utca</t>
+  </si>
+  <si>
+    <t>202604132600859002</t>
+  </si>
+  <si>
+    <t>202604132600856001</t>
+  </si>
+  <si>
+    <t>NFE6-04-11-SUUL</t>
+  </si>
+  <si>
+    <t>202604132600856002</t>
+  </si>
+  <si>
+    <t>202604132600856003</t>
+  </si>
+  <si>
+    <t>202604132600856004</t>
+  </si>
+  <si>
+    <t>159995579539076359</t>
+  </si>
+  <si>
+    <t>R415499</t>
+  </si>
+  <si>
+    <t>Dobós István u.</t>
+  </si>
+  <si>
+    <t>INSPORT</t>
+  </si>
+  <si>
+    <t>159995579539076366</t>
+  </si>
+  <si>
+    <t>159995579539076373</t>
+  </si>
+  <si>
+    <t>159995579539076380</t>
+  </si>
+  <si>
+    <t>159995579539076397</t>
+  </si>
+  <si>
+    <t>159995579539076281</t>
+  </si>
+  <si>
+    <t>R416494</t>
+  </si>
+  <si>
+    <t>Bercsényi utca</t>
+  </si>
+  <si>
+    <t>159995579538917837</t>
+  </si>
+  <si>
+    <t>SA26/H001709</t>
+  </si>
+  <si>
+    <t>Fodormenta utca</t>
+  </si>
+  <si>
+    <t>PICIGURMAN</t>
+  </si>
+  <si>
+    <t>159995579538917844</t>
   </si>
 </sst>
 </file>
@@ -1933,7 +2659,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <sheetPr codeName="Munka1"/>
-  <dimension ref="A1:H143"/>
+  <dimension ref="A1:H225"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="24.88671875" bestFit="1" customWidth="1"/>
@@ -1941,75 +2667,75 @@
     <col min="3" max="3" width="6.88671875" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="20.109375" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="5" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="20" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="33.77734375" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="20.6640625" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="35.5546875" bestFit="1" customWidth="1"/>
     <col min="8" max="8" width="19.88671875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
+        <v>10</v>
+      </c>
+      <c r="C1" t="s">
         <v>11</v>
       </c>
-      <c r="C1" t="s">
+      <c r="D1" t="s">
         <v>12</v>
       </c>
-      <c r="D1" t="s">
+      <c r="E1" t="s">
         <v>13</v>
       </c>
-      <c r="E1" t="s">
+      <c r="F1" t="s">
         <v>14</v>
       </c>
-      <c r="F1" t="s">
+      <c r="G1" t="s">
         <v>15</v>
       </c>
-      <c r="G1" t="s">
+      <c r="H1" t="s">
         <v>16</v>
-      </c>
-      <c r="H1" t="s">
-        <v>17</v>
       </c>
     </row>
     <row r="2" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
-        <v>77</v>
+        <v>118</v>
       </c>
       <c r="C2" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="D2" t="s">
-        <v>78</v>
+        <v>119</v>
       </c>
       <c r="E2" t="s">
-        <v>79</v>
+        <v>104</v>
       </c>
       <c r="F2" t="s">
-        <v>0</v>
+        <v>105</v>
       </c>
       <c r="G2" t="s">
-        <v>80</v>
+        <v>85</v>
       </c>
       <c r="H2" t="s">
-        <v>3</v>
+        <v>120</v>
       </c>
     </row>
     <row r="3" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
-        <v>81</v>
+        <v>121</v>
       </c>
       <c r="C3" t="s">
-        <v>26</v>
+        <v>5</v>
       </c>
       <c r="D3" t="s">
-        <v>82</v>
+        <v>122</v>
       </c>
       <c r="E3" t="s">
-        <v>83</v>
+        <v>123</v>
       </c>
       <c r="F3" t="s">
-        <v>0</v>
+        <v>124</v>
       </c>
       <c r="G3" t="s">
-        <v>84</v>
+        <v>125</v>
       </c>
       <c r="H3" t="s">
         <v>3</v>
@@ -2017,22 +2743,22 @@
     </row>
     <row r="4" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
-        <v>85</v>
+        <v>126</v>
       </c>
       <c r="C4" t="s">
-        <v>7</v>
+        <v>27</v>
       </c>
       <c r="D4" t="s">
-        <v>86</v>
+        <v>127</v>
       </c>
       <c r="E4" t="s">
-        <v>72</v>
+        <v>128</v>
       </c>
       <c r="F4" t="s">
-        <v>73</v>
+        <v>129</v>
       </c>
       <c r="G4" t="s">
-        <v>87</v>
+        <v>130</v>
       </c>
       <c r="H4" t="s">
         <v>1</v>
@@ -2040,22 +2766,22 @@
     </row>
     <row r="5" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
-        <v>88</v>
+        <v>131</v>
       </c>
       <c r="C5" t="s">
-        <v>7</v>
+        <v>18</v>
       </c>
       <c r="D5" t="s">
-        <v>89</v>
+        <v>132</v>
       </c>
       <c r="E5" t="s">
-        <v>90</v>
+        <v>52</v>
       </c>
       <c r="F5" t="s">
-        <v>91</v>
+        <v>0</v>
       </c>
       <c r="G5" t="s">
-        <v>92</v>
+        <v>133</v>
       </c>
       <c r="H5" t="s">
         <v>1</v>
@@ -2063,22 +2789,22 @@
     </row>
     <row r="6" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
-        <v>93</v>
+        <v>134</v>
       </c>
       <c r="C6" t="s">
-        <v>31</v>
+        <v>27</v>
       </c>
       <c r="D6" t="s">
-        <v>94</v>
+        <v>135</v>
       </c>
       <c r="E6" t="s">
-        <v>95</v>
+        <v>136</v>
       </c>
       <c r="F6" t="s">
         <v>0</v>
       </c>
       <c r="G6" t="s">
-        <v>96</v>
+        <v>137</v>
       </c>
       <c r="H6" t="s">
         <v>1</v>
@@ -2086,22 +2812,22 @@
     </row>
     <row r="7" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
-        <v>97</v>
+        <v>138</v>
       </c>
       <c r="C7" t="s">
-        <v>28</v>
+        <v>25</v>
       </c>
       <c r="D7" t="s">
-        <v>98</v>
+        <v>139</v>
       </c>
       <c r="E7" t="s">
-        <v>99</v>
+        <v>140</v>
       </c>
       <c r="F7" t="s">
-        <v>0</v>
+        <v>141</v>
       </c>
       <c r="G7" t="s">
-        <v>100</v>
+        <v>142</v>
       </c>
       <c r="H7" t="s">
         <v>1</v>
@@ -2109,22 +2835,22 @@
     </row>
     <row r="8" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
-        <v>101</v>
+        <v>143</v>
       </c>
       <c r="C8" t="s">
-        <v>31</v>
+        <v>74</v>
       </c>
       <c r="D8" t="s">
-        <v>102</v>
+        <v>144</v>
       </c>
       <c r="E8" t="s">
-        <v>32</v>
+        <v>145</v>
       </c>
       <c r="F8" t="s">
-        <v>0</v>
+        <v>146</v>
       </c>
       <c r="G8" t="s">
-        <v>103</v>
+        <v>147</v>
       </c>
       <c r="H8" t="s">
         <v>1</v>
@@ -2132,22 +2858,22 @@
     </row>
     <row r="9" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
-        <v>104</v>
+        <v>71</v>
       </c>
       <c r="C9" t="s">
-        <v>105</v>
+        <v>25</v>
       </c>
       <c r="D9" t="s">
-        <v>106</v>
+        <v>72</v>
       </c>
       <c r="E9" t="s">
-        <v>54</v>
+        <v>57</v>
       </c>
       <c r="F9" t="s">
-        <v>55</v>
+        <v>0</v>
       </c>
       <c r="G9" t="s">
-        <v>107</v>
+        <v>73</v>
       </c>
       <c r="H9" t="s">
         <v>1</v>
@@ -2155,22 +2881,22 @@
     </row>
     <row r="10" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
-        <v>108</v>
+        <v>148</v>
       </c>
       <c r="C10" t="s">
-        <v>105</v>
+        <v>149</v>
       </c>
       <c r="D10" t="s">
-        <v>109</v>
+        <v>150</v>
       </c>
       <c r="E10" t="s">
-        <v>110</v>
+        <v>151</v>
       </c>
       <c r="F10" t="s">
-        <v>111</v>
+        <v>152</v>
       </c>
       <c r="G10" t="s">
-        <v>112</v>
+        <v>153</v>
       </c>
       <c r="H10" t="s">
         <v>1</v>
@@ -2178,22 +2904,22 @@
     </row>
     <row r="11" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A11" t="s">
-        <v>113</v>
+        <v>154</v>
       </c>
       <c r="C11" t="s">
-        <v>105</v>
+        <v>149</v>
       </c>
       <c r="D11" t="s">
-        <v>109</v>
+        <v>155</v>
       </c>
       <c r="E11" t="s">
-        <v>110</v>
+        <v>156</v>
       </c>
       <c r="F11" t="s">
-        <v>111</v>
+        <v>157</v>
       </c>
       <c r="G11" t="s">
-        <v>112</v>
+        <v>158</v>
       </c>
       <c r="H11" t="s">
         <v>1</v>
@@ -2201,22 +2927,22 @@
     </row>
     <row r="12" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A12" t="s">
-        <v>114</v>
+        <v>159</v>
       </c>
       <c r="C12" t="s">
         <v>2</v>
       </c>
       <c r="D12" t="s">
-        <v>115</v>
+        <v>160</v>
       </c>
       <c r="E12" t="s">
-        <v>116</v>
+        <v>161</v>
       </c>
       <c r="F12" t="s">
-        <v>0</v>
+        <v>162</v>
       </c>
       <c r="G12" t="s">
-        <v>117</v>
+        <v>163</v>
       </c>
       <c r="H12" t="s">
         <v>1</v>
@@ -2224,22 +2950,22 @@
     </row>
     <row r="13" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A13" t="s">
-        <v>118</v>
+        <v>164</v>
       </c>
       <c r="C13" t="s">
-        <v>27</v>
+        <v>2</v>
       </c>
       <c r="D13" t="s">
-        <v>119</v>
+        <v>160</v>
       </c>
       <c r="E13" t="s">
-        <v>69</v>
+        <v>161</v>
       </c>
       <c r="F13" t="s">
-        <v>0</v>
+        <v>162</v>
       </c>
       <c r="G13" t="s">
-        <v>120</v>
+        <v>163</v>
       </c>
       <c r="H13" t="s">
         <v>1</v>
@@ -2247,22 +2973,22 @@
     </row>
     <row r="14" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A14" t="s">
-        <v>121</v>
+        <v>165</v>
       </c>
       <c r="C14" t="s">
-        <v>8</v>
+        <v>149</v>
       </c>
       <c r="D14" t="s">
-        <v>122</v>
+        <v>166</v>
       </c>
       <c r="E14" t="s">
-        <v>33</v>
+        <v>156</v>
       </c>
       <c r="F14" t="s">
-        <v>0</v>
+        <v>157</v>
       </c>
       <c r="G14" t="s">
-        <v>66</v>
+        <v>167</v>
       </c>
       <c r="H14" t="s">
         <v>1</v>
@@ -2270,22 +2996,22 @@
     </row>
     <row r="15" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A15" t="s">
-        <v>123</v>
+        <v>168</v>
       </c>
       <c r="C15" t="s">
-        <v>124</v>
+        <v>5</v>
       </c>
       <c r="D15" t="s">
-        <v>125</v>
+        <v>169</v>
       </c>
       <c r="E15" t="s">
-        <v>60</v>
+        <v>8</v>
       </c>
       <c r="F15" t="s">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="G15" t="s">
-        <v>61</v>
+        <v>170</v>
       </c>
       <c r="H15" t="s">
         <v>1</v>
@@ -2293,22 +3019,22 @@
     </row>
     <row r="16" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A16" t="s">
-        <v>44</v>
+        <v>171</v>
       </c>
       <c r="C16" t="s">
-        <v>26</v>
+        <v>21</v>
       </c>
       <c r="D16" t="s">
-        <v>45</v>
+        <v>172</v>
       </c>
       <c r="E16" t="s">
-        <v>46</v>
+        <v>173</v>
       </c>
       <c r="F16" t="s">
-        <v>0</v>
+        <v>174</v>
       </c>
       <c r="G16" t="s">
-        <v>47</v>
+        <v>175</v>
       </c>
       <c r="H16" t="s">
         <v>1</v>
@@ -2316,22 +3042,22 @@
     </row>
     <row r="17" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A17" t="s">
-        <v>126</v>
+        <v>176</v>
       </c>
       <c r="C17" t="s">
-        <v>18</v>
+        <v>177</v>
       </c>
       <c r="D17" t="s">
-        <v>127</v>
+        <v>178</v>
       </c>
       <c r="E17" t="s">
-        <v>128</v>
+        <v>179</v>
       </c>
       <c r="F17" t="s">
-        <v>129</v>
+        <v>180</v>
       </c>
       <c r="G17" t="s">
-        <v>130</v>
+        <v>181</v>
       </c>
       <c r="H17" t="s">
         <v>1</v>
@@ -2339,22 +3065,22 @@
     </row>
     <row r="18" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A18" t="s">
-        <v>131</v>
+        <v>182</v>
       </c>
       <c r="C18" t="s">
-        <v>31</v>
+        <v>177</v>
       </c>
       <c r="D18" t="s">
-        <v>132</v>
+        <v>178</v>
       </c>
       <c r="E18" t="s">
-        <v>51</v>
+        <v>179</v>
       </c>
       <c r="F18" t="s">
-        <v>0</v>
+        <v>180</v>
       </c>
       <c r="G18" t="s">
-        <v>133</v>
+        <v>181</v>
       </c>
       <c r="H18" t="s">
         <v>1</v>
@@ -2362,22 +3088,22 @@
     </row>
     <row r="19" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A19" t="s">
-        <v>134</v>
+        <v>183</v>
       </c>
       <c r="C19" t="s">
-        <v>124</v>
+        <v>177</v>
       </c>
       <c r="D19" t="s">
-        <v>135</v>
+        <v>178</v>
       </c>
       <c r="E19" t="s">
-        <v>60</v>
+        <v>179</v>
       </c>
       <c r="F19" t="s">
-        <v>0</v>
+        <v>180</v>
       </c>
       <c r="G19" t="s">
-        <v>61</v>
+        <v>181</v>
       </c>
       <c r="H19" t="s">
         <v>1</v>
@@ -2385,22 +3111,22 @@
     </row>
     <row r="20" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A20" t="s">
-        <v>136</v>
+        <v>184</v>
       </c>
       <c r="C20" t="s">
-        <v>124</v>
+        <v>18</v>
       </c>
       <c r="D20" t="s">
-        <v>135</v>
+        <v>185</v>
       </c>
       <c r="E20" t="s">
-        <v>60</v>
+        <v>186</v>
       </c>
       <c r="F20" t="s">
         <v>0</v>
       </c>
       <c r="G20" t="s">
-        <v>61</v>
+        <v>187</v>
       </c>
       <c r="H20" t="s">
         <v>1</v>
@@ -2408,22 +3134,22 @@
     </row>
     <row r="21" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A21" t="s">
-        <v>137</v>
+        <v>188</v>
       </c>
       <c r="C21" t="s">
-        <v>138</v>
+        <v>21</v>
       </c>
       <c r="D21" t="s">
-        <v>139</v>
+        <v>189</v>
       </c>
       <c r="E21" t="s">
-        <v>9</v>
+        <v>46</v>
       </c>
       <c r="F21" t="s">
-        <v>10</v>
+        <v>40</v>
       </c>
       <c r="G21" t="s">
-        <v>140</v>
+        <v>190</v>
       </c>
       <c r="H21" t="s">
         <v>1</v>
@@ -2431,22 +3157,22 @@
     </row>
     <row r="22" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A22" t="s">
-        <v>141</v>
+        <v>191</v>
       </c>
       <c r="C22" t="s">
-        <v>142</v>
+        <v>21</v>
       </c>
       <c r="D22" t="s">
-        <v>143</v>
+        <v>189</v>
       </c>
       <c r="E22" t="s">
-        <v>144</v>
+        <v>46</v>
       </c>
       <c r="F22" t="s">
-        <v>0</v>
+        <v>40</v>
       </c>
       <c r="G22" t="s">
-        <v>145</v>
+        <v>190</v>
       </c>
       <c r="H22" t="s">
         <v>1</v>
@@ -2454,22 +3180,22 @@
     </row>
     <row r="23" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A23" t="s">
-        <v>146</v>
+        <v>192</v>
       </c>
       <c r="C23" t="s">
-        <v>7</v>
+        <v>76</v>
       </c>
       <c r="D23" t="s">
-        <v>147</v>
+        <v>193</v>
       </c>
       <c r="E23" t="s">
-        <v>148</v>
+        <v>194</v>
       </c>
       <c r="F23" t="s">
-        <v>149</v>
+        <v>0</v>
       </c>
       <c r="G23" t="s">
-        <v>59</v>
+        <v>195</v>
       </c>
       <c r="H23" t="s">
         <v>1</v>
@@ -2477,22 +3203,22 @@
     </row>
     <row r="24" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A24" t="s">
-        <v>150</v>
+        <v>196</v>
       </c>
       <c r="C24" t="s">
-        <v>35</v>
+        <v>149</v>
       </c>
       <c r="D24" t="s">
-        <v>151</v>
+        <v>197</v>
       </c>
       <c r="E24" t="s">
-        <v>152</v>
+        <v>198</v>
       </c>
       <c r="F24" t="s">
-        <v>153</v>
+        <v>199</v>
       </c>
       <c r="G24" t="s">
-        <v>154</v>
+        <v>200</v>
       </c>
       <c r="H24" t="s">
         <v>1</v>
@@ -2500,22 +3226,22 @@
     </row>
     <row r="25" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A25" t="s">
-        <v>155</v>
+        <v>201</v>
       </c>
       <c r="C25" t="s">
-        <v>26</v>
+        <v>149</v>
       </c>
       <c r="D25" t="s">
-        <v>156</v>
+        <v>197</v>
       </c>
       <c r="E25" t="s">
-        <v>157</v>
+        <v>198</v>
       </c>
       <c r="F25" t="s">
-        <v>0</v>
+        <v>199</v>
       </c>
       <c r="G25" t="s">
-        <v>158</v>
+        <v>200</v>
       </c>
       <c r="H25" t="s">
         <v>1</v>
@@ -2523,22 +3249,22 @@
     </row>
     <row r="26" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A26" t="s">
-        <v>159</v>
+        <v>202</v>
       </c>
       <c r="C26" t="s">
-        <v>6</v>
+        <v>149</v>
       </c>
       <c r="D26" t="s">
-        <v>160</v>
+        <v>203</v>
       </c>
       <c r="E26" t="s">
-        <v>53</v>
+        <v>204</v>
       </c>
       <c r="F26" t="s">
-        <v>0</v>
+        <v>205</v>
       </c>
       <c r="G26" t="s">
-        <v>161</v>
+        <v>206</v>
       </c>
       <c r="H26" t="s">
         <v>1</v>
@@ -2546,22 +3272,22 @@
     </row>
     <row r="27" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A27" t="s">
-        <v>162</v>
+        <v>207</v>
       </c>
       <c r="C27" t="s">
-        <v>26</v>
+        <v>17</v>
       </c>
       <c r="D27" t="s">
-        <v>163</v>
+        <v>208</v>
       </c>
       <c r="E27" t="s">
-        <v>164</v>
+        <v>209</v>
       </c>
       <c r="F27" t="s">
-        <v>0</v>
+        <v>210</v>
       </c>
       <c r="G27" t="s">
-        <v>165</v>
+        <v>43</v>
       </c>
       <c r="H27" t="s">
         <v>1</v>
@@ -2569,22 +3295,22 @@
     </row>
     <row r="28" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A28" t="s">
-        <v>166</v>
+        <v>211</v>
       </c>
       <c r="C28" t="s">
-        <v>26</v>
+        <v>7</v>
       </c>
       <c r="D28" t="s">
-        <v>163</v>
+        <v>212</v>
       </c>
       <c r="E28" t="s">
-        <v>164</v>
+        <v>54</v>
       </c>
       <c r="F28" t="s">
-        <v>0</v>
+        <v>55</v>
       </c>
       <c r="G28" t="s">
-        <v>165</v>
+        <v>97</v>
       </c>
       <c r="H28" t="s">
         <v>1</v>
@@ -2592,22 +3318,22 @@
     </row>
     <row r="29" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A29" t="s">
-        <v>167</v>
+        <v>213</v>
       </c>
       <c r="C29" t="s">
-        <v>22</v>
+        <v>7</v>
       </c>
       <c r="D29" t="s">
-        <v>168</v>
+        <v>212</v>
       </c>
       <c r="E29" t="s">
-        <v>79</v>
+        <v>54</v>
       </c>
       <c r="F29" t="s">
-        <v>0</v>
+        <v>55</v>
       </c>
       <c r="G29" t="s">
-        <v>169</v>
+        <v>97</v>
       </c>
       <c r="H29" t="s">
         <v>1</v>
@@ -2615,22 +3341,22 @@
     </row>
     <row r="30" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A30" t="s">
-        <v>170</v>
+        <v>214</v>
       </c>
       <c r="C30" t="s">
-        <v>22</v>
+        <v>6</v>
       </c>
       <c r="D30" t="s">
-        <v>168</v>
+        <v>215</v>
       </c>
       <c r="E30" t="s">
-        <v>79</v>
+        <v>94</v>
       </c>
       <c r="F30" t="s">
         <v>0</v>
       </c>
       <c r="G30" t="s">
-        <v>169</v>
+        <v>216</v>
       </c>
       <c r="H30" t="s">
         <v>1</v>
@@ -2638,22 +3364,22 @@
     </row>
     <row r="31" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A31" t="s">
-        <v>171</v>
+        <v>217</v>
       </c>
       <c r="C31" t="s">
-        <v>27</v>
+        <v>81</v>
       </c>
       <c r="D31" t="s">
-        <v>172</v>
+        <v>218</v>
       </c>
       <c r="E31" t="s">
-        <v>173</v>
+        <v>219</v>
       </c>
       <c r="F31" t="s">
         <v>0</v>
       </c>
       <c r="G31" t="s">
-        <v>174</v>
+        <v>220</v>
       </c>
       <c r="H31" t="s">
         <v>1</v>
@@ -2661,22 +3387,22 @@
     </row>
     <row r="32" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A32" t="s">
-        <v>175</v>
+        <v>221</v>
       </c>
       <c r="C32" t="s">
-        <v>176</v>
+        <v>67</v>
       </c>
       <c r="D32" t="s">
-        <v>177</v>
+        <v>222</v>
       </c>
       <c r="E32" t="s">
-        <v>34</v>
+        <v>223</v>
       </c>
       <c r="F32" t="s">
         <v>0</v>
       </c>
       <c r="G32" t="s">
-        <v>178</v>
+        <v>84</v>
       </c>
       <c r="H32" t="s">
         <v>1</v>
@@ -2684,22 +3410,22 @@
     </row>
     <row r="33" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A33" t="s">
-        <v>179</v>
+        <v>224</v>
       </c>
       <c r="C33" t="s">
-        <v>176</v>
+        <v>81</v>
       </c>
       <c r="D33" t="s">
-        <v>177</v>
+        <v>225</v>
       </c>
       <c r="E33" t="s">
-        <v>34</v>
+        <v>219</v>
       </c>
       <c r="F33" t="s">
         <v>0</v>
       </c>
       <c r="G33" t="s">
-        <v>178</v>
+        <v>220</v>
       </c>
       <c r="H33" t="s">
         <v>1</v>
@@ -2707,22 +3433,22 @@
     </row>
     <row r="34" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A34" t="s">
-        <v>180</v>
+        <v>226</v>
       </c>
       <c r="C34" t="s">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="D34" t="s">
-        <v>181</v>
+        <v>227</v>
       </c>
       <c r="E34" t="s">
-        <v>182</v>
+        <v>95</v>
       </c>
       <c r="F34" t="s">
-        <v>0</v>
+        <v>96</v>
       </c>
       <c r="G34" t="s">
-        <v>183</v>
+        <v>228</v>
       </c>
       <c r="H34" t="s">
         <v>1</v>
@@ -2730,22 +3456,22 @@
     </row>
     <row r="35" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A35" t="s">
-        <v>184</v>
+        <v>229</v>
       </c>
       <c r="C35" t="s">
-        <v>28</v>
+        <v>2</v>
       </c>
       <c r="D35" t="s">
-        <v>185</v>
+        <v>227</v>
       </c>
       <c r="E35" t="s">
-        <v>186</v>
+        <v>95</v>
       </c>
       <c r="F35" t="s">
-        <v>0</v>
+        <v>96</v>
       </c>
       <c r="G35" t="s">
-        <v>187</v>
+        <v>228</v>
       </c>
       <c r="H35" t="s">
         <v>1</v>
@@ -2753,22 +3479,22 @@
     </row>
     <row r="36" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A36" t="s">
-        <v>188</v>
+        <v>230</v>
       </c>
       <c r="C36" t="s">
-        <v>6</v>
+        <v>81</v>
       </c>
       <c r="D36" t="s">
-        <v>189</v>
+        <v>231</v>
       </c>
       <c r="E36" t="s">
-        <v>48</v>
+        <v>232</v>
       </c>
       <c r="F36" t="s">
         <v>0</v>
       </c>
       <c r="G36" t="s">
-        <v>190</v>
+        <v>233</v>
       </c>
       <c r="H36" t="s">
         <v>1</v>
@@ -2776,22 +3502,22 @@
     </row>
     <row r="37" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A37" t="s">
-        <v>191</v>
+        <v>234</v>
       </c>
       <c r="C37" t="s">
-        <v>22</v>
+        <v>18</v>
       </c>
       <c r="D37" t="s">
-        <v>192</v>
+        <v>235</v>
       </c>
       <c r="E37" t="s">
-        <v>193</v>
+        <v>52</v>
       </c>
       <c r="F37" t="s">
         <v>0</v>
       </c>
       <c r="G37" t="s">
-        <v>194</v>
+        <v>133</v>
       </c>
       <c r="H37" t="s">
         <v>1</v>
@@ -2799,390 +3525,390 @@
     </row>
     <row r="38" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A38" t="s">
-        <v>195</v>
+        <v>236</v>
       </c>
       <c r="C38" t="s">
-        <v>35</v>
+        <v>27</v>
       </c>
       <c r="D38" t="s">
-        <v>196</v>
+        <v>237</v>
       </c>
       <c r="E38" t="s">
-        <v>197</v>
+        <v>53</v>
       </c>
       <c r="F38" t="s">
-        <v>198</v>
+        <v>0</v>
       </c>
       <c r="G38" t="s">
-        <v>199</v>
+        <v>238</v>
       </c>
       <c r="H38" t="s">
-        <v>30</v>
+        <v>1</v>
       </c>
     </row>
     <row r="39" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A39" t="s">
-        <v>200</v>
+        <v>239</v>
       </c>
       <c r="C39" t="s">
-        <v>6</v>
+        <v>24</v>
       </c>
       <c r="D39" t="s">
-        <v>201</v>
+        <v>240</v>
       </c>
       <c r="E39" t="s">
-        <v>68</v>
+        <v>62</v>
       </c>
       <c r="F39" t="s">
         <v>0</v>
       </c>
       <c r="G39" t="s">
-        <v>202</v>
+        <v>241</v>
       </c>
       <c r="H39" t="s">
-        <v>30</v>
+        <v>1</v>
       </c>
     </row>
     <row r="40" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A40" t="s">
-        <v>203</v>
+        <v>242</v>
       </c>
       <c r="C40" t="s">
-        <v>19</v>
+        <v>29</v>
       </c>
       <c r="D40" t="s">
-        <v>204</v>
+        <v>243</v>
       </c>
       <c r="E40" t="s">
-        <v>205</v>
+        <v>244</v>
       </c>
       <c r="F40" t="s">
-        <v>206</v>
+        <v>0</v>
       </c>
       <c r="G40" t="s">
-        <v>207</v>
+        <v>245</v>
       </c>
       <c r="H40" t="s">
-        <v>208</v>
+        <v>1</v>
       </c>
     </row>
     <row r="41" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A41" t="s">
-        <v>209</v>
+        <v>246</v>
       </c>
       <c r="C41" t="s">
-        <v>43</v>
+        <v>18</v>
       </c>
       <c r="D41" t="s">
-        <v>210</v>
+        <v>247</v>
       </c>
       <c r="E41" t="s">
-        <v>211</v>
+        <v>248</v>
       </c>
       <c r="F41" t="s">
-        <v>212</v>
+        <v>0</v>
       </c>
       <c r="G41" t="s">
-        <v>213</v>
+        <v>249</v>
       </c>
       <c r="H41" t="s">
-        <v>208</v>
+        <v>1</v>
       </c>
     </row>
     <row r="42" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A42" t="s">
-        <v>214</v>
+        <v>250</v>
       </c>
       <c r="C42" t="s">
-        <v>43</v>
+        <v>33</v>
       </c>
       <c r="D42" t="s">
-        <v>215</v>
+        <v>251</v>
       </c>
       <c r="E42" t="s">
-        <v>63</v>
+        <v>252</v>
       </c>
       <c r="F42" t="s">
-        <v>64</v>
+        <v>0</v>
       </c>
       <c r="G42" t="s">
-        <v>216</v>
+        <v>253</v>
       </c>
       <c r="H42" t="s">
-        <v>208</v>
+        <v>1</v>
       </c>
     </row>
     <row r="43" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A43" t="s">
-        <v>217</v>
+        <v>254</v>
       </c>
       <c r="C43" t="s">
-        <v>5</v>
+        <v>27</v>
       </c>
       <c r="D43" t="s">
-        <v>218</v>
+        <v>255</v>
       </c>
       <c r="E43" t="s">
-        <v>219</v>
+        <v>31</v>
       </c>
       <c r="F43" t="s">
-        <v>220</v>
+        <v>0</v>
       </c>
       <c r="G43" t="s">
-        <v>221</v>
+        <v>56</v>
       </c>
       <c r="H43" t="s">
-        <v>208</v>
+        <v>1</v>
       </c>
     </row>
     <row r="44" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A44" t="s">
-        <v>222</v>
+        <v>256</v>
       </c>
       <c r="C44" t="s">
-        <v>35</v>
+        <v>27</v>
       </c>
       <c r="D44" t="s">
-        <v>223</v>
+        <v>255</v>
       </c>
       <c r="E44" t="s">
-        <v>224</v>
+        <v>31</v>
       </c>
       <c r="F44" t="s">
-        <v>225</v>
+        <v>0</v>
       </c>
       <c r="G44" t="s">
-        <v>226</v>
+        <v>56</v>
       </c>
       <c r="H44" t="s">
-        <v>208</v>
+        <v>1</v>
       </c>
     </row>
     <row r="45" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A45" t="s">
-        <v>227</v>
+        <v>257</v>
       </c>
       <c r="C45" t="s">
-        <v>29</v>
+        <v>21</v>
       </c>
       <c r="D45" t="s">
-        <v>228</v>
+        <v>258</v>
       </c>
       <c r="E45" t="s">
-        <v>229</v>
+        <v>259</v>
       </c>
       <c r="F45" t="s">
-        <v>230</v>
+        <v>0</v>
       </c>
       <c r="G45" t="s">
-        <v>231</v>
+        <v>260</v>
       </c>
       <c r="H45" t="s">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="46" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A46" t="s">
-        <v>232</v>
+        <v>261</v>
       </c>
       <c r="C46" t="s">
-        <v>26</v>
+        <v>7</v>
       </c>
       <c r="D46" t="s">
-        <v>233</v>
+        <v>262</v>
       </c>
       <c r="E46" t="s">
-        <v>234</v>
+        <v>263</v>
       </c>
       <c r="F46" t="s">
         <v>0</v>
       </c>
       <c r="G46" t="s">
-        <v>235</v>
+        <v>264</v>
       </c>
       <c r="H46" t="s">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="47" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A47" t="s">
-        <v>236</v>
+        <v>265</v>
       </c>
       <c r="C47" t="s">
-        <v>26</v>
+        <v>74</v>
       </c>
       <c r="D47" t="s">
-        <v>233</v>
+        <v>266</v>
       </c>
       <c r="E47" t="s">
-        <v>234</v>
+        <v>65</v>
       </c>
       <c r="F47" t="s">
-        <v>0</v>
+        <v>66</v>
       </c>
       <c r="G47" t="s">
-        <v>235</v>
+        <v>267</v>
       </c>
       <c r="H47" t="s">
-        <v>3</v>
+        <v>28</v>
       </c>
     </row>
     <row r="48" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A48" t="s">
-        <v>237</v>
+        <v>268</v>
       </c>
       <c r="C48" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="D48" t="s">
-        <v>233</v>
+        <v>269</v>
       </c>
       <c r="E48" t="s">
-        <v>234</v>
+        <v>31</v>
       </c>
       <c r="F48" t="s">
         <v>0</v>
       </c>
       <c r="G48" t="s">
-        <v>235</v>
+        <v>270</v>
       </c>
       <c r="H48" t="s">
-        <v>3</v>
+        <v>28</v>
       </c>
     </row>
     <row r="49" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A49" t="s">
-        <v>238</v>
+        <v>271</v>
       </c>
       <c r="C49" t="s">
-        <v>6</v>
+        <v>81</v>
       </c>
       <c r="D49" t="s">
-        <v>239</v>
+        <v>272</v>
       </c>
       <c r="E49" t="s">
-        <v>48</v>
+        <v>273</v>
       </c>
       <c r="F49" t="s">
-        <v>0</v>
+        <v>274</v>
       </c>
       <c r="G49" t="s">
-        <v>240</v>
+        <v>275</v>
       </c>
       <c r="H49" t="s">
-        <v>3</v>
+        <v>28</v>
       </c>
     </row>
     <row r="50" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A50" t="s">
-        <v>241</v>
+        <v>276</v>
       </c>
       <c r="C50" t="s">
-        <v>6</v>
+        <v>29</v>
       </c>
       <c r="D50" t="s">
-        <v>239</v>
+        <v>277</v>
       </c>
       <c r="E50" t="s">
-        <v>48</v>
+        <v>30</v>
       </c>
       <c r="F50" t="s">
         <v>0</v>
       </c>
       <c r="G50" t="s">
-        <v>240</v>
+        <v>278</v>
       </c>
       <c r="H50" t="s">
-        <v>3</v>
+        <v>28</v>
       </c>
     </row>
     <row r="51" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A51" t="s">
-        <v>242</v>
+        <v>279</v>
       </c>
       <c r="C51" t="s">
+        <v>25</v>
+      </c>
+      <c r="D51" t="s">
+        <v>280</v>
+      </c>
+      <c r="E51" t="s">
+        <v>102</v>
+      </c>
+      <c r="F51" t="s">
+        <v>103</v>
+      </c>
+      <c r="G51" t="s">
+        <v>281</v>
+      </c>
+      <c r="H51" t="s">
         <v>28</v>
-      </c>
-      <c r="D51" t="s">
-        <v>243</v>
-      </c>
-      <c r="E51" t="s">
-        <v>186</v>
-      </c>
-      <c r="F51" t="s">
-        <v>0</v>
-      </c>
-      <c r="G51" t="s">
-        <v>244</v>
-      </c>
-      <c r="H51" t="s">
-        <v>3</v>
       </c>
     </row>
     <row r="52" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A52" t="s">
-        <v>245</v>
+        <v>282</v>
       </c>
       <c r="C52" t="s">
-        <v>5</v>
+        <v>21</v>
       </c>
       <c r="D52" t="s">
-        <v>246</v>
+        <v>283</v>
       </c>
       <c r="E52" t="s">
-        <v>219</v>
+        <v>284</v>
       </c>
       <c r="F52" t="s">
-        <v>220</v>
+        <v>285</v>
       </c>
       <c r="G52" t="s">
-        <v>247</v>
+        <v>286</v>
       </c>
       <c r="H52" t="s">
-        <v>3</v>
+        <v>28</v>
       </c>
     </row>
     <row r="53" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A53" t="s">
-        <v>248</v>
+        <v>287</v>
       </c>
       <c r="C53" t="s">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="D53" t="s">
-        <v>246</v>
+        <v>288</v>
       </c>
       <c r="E53" t="s">
-        <v>219</v>
+        <v>289</v>
       </c>
       <c r="F53" t="s">
-        <v>220</v>
+        <v>0</v>
       </c>
       <c r="G53" t="s">
-        <v>247</v>
+        <v>290</v>
       </c>
       <c r="H53" t="s">
-        <v>3</v>
+        <v>28</v>
       </c>
     </row>
     <row r="54" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A54" t="s">
-        <v>249</v>
+        <v>291</v>
       </c>
       <c r="C54" t="s">
-        <v>8</v>
+        <v>29</v>
       </c>
       <c r="D54" t="s">
-        <v>250</v>
+        <v>292</v>
       </c>
       <c r="E54" t="s">
-        <v>62</v>
+        <v>106</v>
       </c>
       <c r="F54" t="s">
         <v>0</v>
       </c>
       <c r="G54" t="s">
-        <v>251</v>
+        <v>293</v>
       </c>
       <c r="H54" t="s">
         <v>3</v>
@@ -3190,22 +3916,22 @@
     </row>
     <row r="55" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A55" t="s">
-        <v>252</v>
+        <v>294</v>
       </c>
       <c r="C55" t="s">
-        <v>176</v>
+        <v>27</v>
       </c>
       <c r="D55" t="s">
-        <v>253</v>
+        <v>295</v>
       </c>
       <c r="E55" t="s">
-        <v>254</v>
+        <v>128</v>
       </c>
       <c r="F55" t="s">
-        <v>0</v>
+        <v>129</v>
       </c>
       <c r="G55" t="s">
-        <v>255</v>
+        <v>296</v>
       </c>
       <c r="H55" t="s">
         <v>3</v>
@@ -3213,22 +3939,22 @@
     </row>
     <row r="56" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A56" t="s">
-        <v>256</v>
+        <v>297</v>
       </c>
       <c r="C56" t="s">
-        <v>176</v>
+        <v>27</v>
       </c>
       <c r="D56" t="s">
-        <v>253</v>
+        <v>295</v>
       </c>
       <c r="E56" t="s">
-        <v>254</v>
+        <v>128</v>
       </c>
       <c r="F56" t="s">
-        <v>0</v>
+        <v>129</v>
       </c>
       <c r="G56" t="s">
-        <v>255</v>
+        <v>296</v>
       </c>
       <c r="H56" t="s">
         <v>3</v>
@@ -3236,22 +3962,22 @@
     </row>
     <row r="57" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A57" t="s">
-        <v>257</v>
+        <v>298</v>
       </c>
       <c r="C57" t="s">
-        <v>43</v>
+        <v>177</v>
       </c>
       <c r="D57" t="s">
-        <v>258</v>
+        <v>299</v>
       </c>
       <c r="E57" t="s">
-        <v>259</v>
+        <v>300</v>
       </c>
       <c r="F57" t="s">
-        <v>260</v>
+        <v>0</v>
       </c>
       <c r="G57" t="s">
-        <v>261</v>
+        <v>301</v>
       </c>
       <c r="H57" t="s">
         <v>3</v>
@@ -3259,22 +3985,22 @@
     </row>
     <row r="58" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A58" t="s">
-        <v>262</v>
+        <v>302</v>
       </c>
       <c r="C58" t="s">
-        <v>43</v>
+        <v>177</v>
       </c>
       <c r="D58" t="s">
-        <v>258</v>
+        <v>299</v>
       </c>
       <c r="E58" t="s">
-        <v>259</v>
+        <v>300</v>
       </c>
       <c r="F58" t="s">
-        <v>260</v>
+        <v>0</v>
       </c>
       <c r="G58" t="s">
-        <v>261</v>
+        <v>301</v>
       </c>
       <c r="H58" t="s">
         <v>3</v>
@@ -3282,22 +4008,22 @@
     </row>
     <row r="59" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A59" t="s">
-        <v>263</v>
+        <v>303</v>
       </c>
       <c r="C59" t="s">
-        <v>2</v>
+        <v>81</v>
       </c>
       <c r="D59" t="s">
-        <v>264</v>
+        <v>304</v>
       </c>
       <c r="E59" t="s">
-        <v>265</v>
+        <v>305</v>
       </c>
       <c r="F59" t="s">
-        <v>266</v>
+        <v>306</v>
       </c>
       <c r="G59" t="s">
-        <v>267</v>
+        <v>307</v>
       </c>
       <c r="H59" t="s">
         <v>3</v>
@@ -3305,22 +4031,22 @@
     </row>
     <row r="60" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A60" t="s">
-        <v>268</v>
+        <v>308</v>
       </c>
       <c r="C60" t="s">
-        <v>43</v>
+        <v>18</v>
       </c>
       <c r="D60" t="s">
-        <v>269</v>
+        <v>309</v>
       </c>
       <c r="E60" t="s">
-        <v>270</v>
+        <v>52</v>
       </c>
       <c r="F60" t="s">
-        <v>271</v>
+        <v>0</v>
       </c>
       <c r="G60" t="s">
-        <v>272</v>
+        <v>310</v>
       </c>
       <c r="H60" t="s">
         <v>3</v>
@@ -3328,22 +4054,22 @@
     </row>
     <row r="61" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A61" t="s">
-        <v>273</v>
+        <v>311</v>
       </c>
       <c r="C61" t="s">
-        <v>43</v>
+        <v>149</v>
       </c>
       <c r="D61" t="s">
-        <v>269</v>
+        <v>312</v>
       </c>
       <c r="E61" t="s">
-        <v>270</v>
+        <v>313</v>
       </c>
       <c r="F61" t="s">
-        <v>271</v>
+        <v>314</v>
       </c>
       <c r="G61" t="s">
-        <v>272</v>
+        <v>315</v>
       </c>
       <c r="H61" t="s">
         <v>3</v>
@@ -3351,22 +4077,22 @@
     </row>
     <row r="62" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A62" t="s">
-        <v>274</v>
+        <v>316</v>
       </c>
       <c r="C62" t="s">
-        <v>43</v>
+        <v>5</v>
       </c>
       <c r="D62" t="s">
-        <v>269</v>
+        <v>317</v>
       </c>
       <c r="E62" t="s">
-        <v>270</v>
+        <v>8</v>
       </c>
       <c r="F62" t="s">
-        <v>271</v>
+        <v>9</v>
       </c>
       <c r="G62" t="s">
-        <v>272</v>
+        <v>117</v>
       </c>
       <c r="H62" t="s">
         <v>3</v>
@@ -3374,22 +4100,22 @@
     </row>
     <row r="63" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A63" t="s">
-        <v>275</v>
+        <v>318</v>
       </c>
       <c r="C63" t="s">
-        <v>22</v>
+        <v>5</v>
       </c>
       <c r="D63" t="s">
-        <v>276</v>
+        <v>317</v>
       </c>
       <c r="E63" t="s">
-        <v>277</v>
+        <v>8</v>
       </c>
       <c r="F63" t="s">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="G63" t="s">
-        <v>165</v>
+        <v>117</v>
       </c>
       <c r="H63" t="s">
         <v>3</v>
@@ -3397,22 +4123,22 @@
     </row>
     <row r="64" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A64" t="s">
-        <v>278</v>
+        <v>319</v>
       </c>
       <c r="C64" t="s">
-        <v>124</v>
+        <v>26</v>
       </c>
       <c r="D64" t="s">
-        <v>279</v>
+        <v>320</v>
       </c>
       <c r="E64" t="s">
-        <v>36</v>
+        <v>321</v>
       </c>
       <c r="F64" t="s">
         <v>0</v>
       </c>
       <c r="G64" t="s">
-        <v>280</v>
+        <v>322</v>
       </c>
       <c r="H64" t="s">
         <v>3</v>
@@ -3420,22 +4146,22 @@
     </row>
     <row r="65" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A65" t="s">
-        <v>281</v>
+        <v>323</v>
       </c>
       <c r="C65" t="s">
-        <v>43</v>
+        <v>26</v>
       </c>
       <c r="D65" t="s">
-        <v>282</v>
+        <v>320</v>
       </c>
       <c r="E65" t="s">
-        <v>259</v>
+        <v>321</v>
       </c>
       <c r="F65" t="s">
-        <v>260</v>
+        <v>0</v>
       </c>
       <c r="G65" t="s">
-        <v>283</v>
+        <v>322</v>
       </c>
       <c r="H65" t="s">
         <v>3</v>
@@ -3443,22 +4169,22 @@
     </row>
     <row r="66" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A66" t="s">
-        <v>284</v>
+        <v>324</v>
       </c>
       <c r="C66" t="s">
-        <v>43</v>
+        <v>74</v>
       </c>
       <c r="D66" t="s">
-        <v>282</v>
+        <v>325</v>
       </c>
       <c r="E66" t="s">
-        <v>259</v>
+        <v>326</v>
       </c>
       <c r="F66" t="s">
-        <v>260</v>
+        <v>327</v>
       </c>
       <c r="G66" t="s">
-        <v>283</v>
+        <v>328</v>
       </c>
       <c r="H66" t="s">
         <v>3</v>
@@ -3466,22 +4192,22 @@
     </row>
     <row r="67" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A67" t="s">
-        <v>285</v>
+        <v>329</v>
       </c>
       <c r="C67" t="s">
-        <v>105</v>
+        <v>74</v>
       </c>
       <c r="D67" t="s">
-        <v>286</v>
+        <v>325</v>
       </c>
       <c r="E67" t="s">
-        <v>52</v>
+        <v>326</v>
       </c>
       <c r="F67" t="s">
-        <v>42</v>
+        <v>327</v>
       </c>
       <c r="G67" t="s">
-        <v>287</v>
+        <v>328</v>
       </c>
       <c r="H67" t="s">
         <v>3</v>
@@ -3489,22 +4215,22 @@
     </row>
     <row r="68" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A68" t="s">
-        <v>288</v>
+        <v>91</v>
       </c>
       <c r="C68" t="s">
         <v>18</v>
       </c>
       <c r="D68" t="s">
-        <v>289</v>
+        <v>92</v>
       </c>
       <c r="E68" t="s">
-        <v>290</v>
+        <v>34</v>
       </c>
       <c r="F68" t="s">
-        <v>291</v>
+        <v>0</v>
       </c>
       <c r="G68" t="s">
-        <v>292</v>
+        <v>93</v>
       </c>
       <c r="H68" t="s">
         <v>3</v>
@@ -3512,22 +4238,22 @@
     </row>
     <row r="69" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A69" t="s">
-        <v>293</v>
+        <v>330</v>
       </c>
       <c r="C69" t="s">
-        <v>31</v>
+        <v>7</v>
       </c>
       <c r="D69" t="s">
-        <v>294</v>
+        <v>331</v>
       </c>
       <c r="E69" t="s">
-        <v>37</v>
+        <v>89</v>
       </c>
       <c r="F69" t="s">
-        <v>0</v>
+        <v>90</v>
       </c>
       <c r="G69" t="s">
-        <v>295</v>
+        <v>332</v>
       </c>
       <c r="H69" t="s">
         <v>3</v>
@@ -3535,22 +4261,22 @@
     </row>
     <row r="70" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A70" t="s">
-        <v>296</v>
+        <v>333</v>
       </c>
       <c r="C70" t="s">
-        <v>142</v>
+        <v>7</v>
       </c>
       <c r="D70" t="s">
-        <v>297</v>
+        <v>331</v>
       </c>
       <c r="E70" t="s">
-        <v>298</v>
+        <v>89</v>
       </c>
       <c r="F70" t="s">
-        <v>0</v>
+        <v>90</v>
       </c>
       <c r="G70" t="s">
-        <v>299</v>
+        <v>332</v>
       </c>
       <c r="H70" t="s">
         <v>3</v>
@@ -3558,22 +4284,22 @@
     </row>
     <row r="71" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A71" t="s">
-        <v>300</v>
+        <v>334</v>
       </c>
       <c r="C71" t="s">
-        <v>301</v>
+        <v>7</v>
       </c>
       <c r="D71" t="s">
-        <v>302</v>
+        <v>331</v>
       </c>
       <c r="E71" t="s">
-        <v>58</v>
+        <v>89</v>
       </c>
       <c r="F71" t="s">
-        <v>0</v>
+        <v>90</v>
       </c>
       <c r="G71" t="s">
-        <v>303</v>
+        <v>332</v>
       </c>
       <c r="H71" t="s">
         <v>3</v>
@@ -3581,22 +4307,22 @@
     </row>
     <row r="72" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A72" t="s">
-        <v>304</v>
+        <v>335</v>
       </c>
       <c r="C72" t="s">
-        <v>2</v>
+        <v>77</v>
       </c>
       <c r="D72" t="s">
-        <v>305</v>
+        <v>336</v>
       </c>
       <c r="E72" t="s">
-        <v>306</v>
+        <v>337</v>
       </c>
       <c r="F72" t="s">
-        <v>307</v>
+        <v>338</v>
       </c>
       <c r="G72" t="s">
-        <v>308</v>
+        <v>339</v>
       </c>
       <c r="H72" t="s">
         <v>3</v>
@@ -3604,22 +4330,22 @@
     </row>
     <row r="73" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A73" t="s">
-        <v>309</v>
+        <v>340</v>
       </c>
       <c r="C73" t="s">
+        <v>149</v>
+      </c>
+      <c r="D73" t="s">
+        <v>341</v>
+      </c>
+      <c r="E73" t="s">
+        <v>78</v>
+      </c>
+      <c r="F73" t="s">
+        <v>79</v>
+      </c>
+      <c r="G73" t="s">
         <v>43</v>
-      </c>
-      <c r="D73" t="s">
-        <v>310</v>
-      </c>
-      <c r="E73" t="s">
-        <v>211</v>
-      </c>
-      <c r="F73" t="s">
-        <v>212</v>
-      </c>
-      <c r="G73" t="s">
-        <v>74</v>
       </c>
       <c r="H73" t="s">
         <v>3</v>
@@ -3627,22 +4353,22 @@
     </row>
     <row r="74" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A74" t="s">
-        <v>311</v>
+        <v>342</v>
       </c>
       <c r="C74" t="s">
+        <v>149</v>
+      </c>
+      <c r="D74" t="s">
+        <v>341</v>
+      </c>
+      <c r="E74" t="s">
+        <v>78</v>
+      </c>
+      <c r="F74" t="s">
+        <v>79</v>
+      </c>
+      <c r="G74" t="s">
         <v>43</v>
-      </c>
-      <c r="D74" t="s">
-        <v>312</v>
-      </c>
-      <c r="E74" t="s">
-        <v>63</v>
-      </c>
-      <c r="F74" t="s">
-        <v>64</v>
-      </c>
-      <c r="G74" t="s">
-        <v>313</v>
       </c>
       <c r="H74" t="s">
         <v>3</v>
@@ -3650,22 +4376,22 @@
     </row>
     <row r="75" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A75" t="s">
-        <v>314</v>
+        <v>343</v>
       </c>
       <c r="C75" t="s">
-        <v>142</v>
+        <v>67</v>
       </c>
       <c r="D75" t="s">
-        <v>315</v>
+        <v>344</v>
       </c>
       <c r="E75" t="s">
-        <v>65</v>
+        <v>345</v>
       </c>
       <c r="F75" t="s">
         <v>0</v>
       </c>
       <c r="G75" t="s">
-        <v>316</v>
+        <v>346</v>
       </c>
       <c r="H75" t="s">
         <v>3</v>
@@ -3673,22 +4399,22 @@
     </row>
     <row r="76" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A76" t="s">
-        <v>317</v>
+        <v>347</v>
       </c>
       <c r="C76" t="s">
-        <v>29</v>
+        <v>25</v>
       </c>
       <c r="D76" t="s">
-        <v>318</v>
+        <v>348</v>
       </c>
       <c r="E76" t="s">
-        <v>319</v>
+        <v>44</v>
       </c>
       <c r="F76" t="s">
-        <v>320</v>
+        <v>0</v>
       </c>
       <c r="G76" t="s">
-        <v>321</v>
+        <v>349</v>
       </c>
       <c r="H76" t="s">
         <v>3</v>
@@ -3696,22 +4422,22 @@
     </row>
     <row r="77" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A77" t="s">
-        <v>322</v>
+        <v>350</v>
       </c>
       <c r="C77" t="s">
-        <v>29</v>
+        <v>33</v>
       </c>
       <c r="D77" t="s">
-        <v>323</v>
+        <v>351</v>
       </c>
       <c r="E77" t="s">
-        <v>324</v>
+        <v>63</v>
       </c>
       <c r="F77" t="s">
-        <v>325</v>
+        <v>0</v>
       </c>
       <c r="G77" t="s">
-        <v>326</v>
+        <v>64</v>
       </c>
       <c r="H77" t="s">
         <v>3</v>
@@ -3719,22 +4445,22 @@
     </row>
     <row r="78" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A78" t="s">
-        <v>327</v>
+        <v>352</v>
       </c>
       <c r="C78" t="s">
-        <v>27</v>
+        <v>21</v>
       </c>
       <c r="D78" t="s">
-        <v>328</v>
+        <v>353</v>
       </c>
       <c r="E78" t="s">
-        <v>25</v>
+        <v>354</v>
       </c>
       <c r="F78" t="s">
-        <v>0</v>
+        <v>355</v>
       </c>
       <c r="G78" t="s">
-        <v>329</v>
+        <v>356</v>
       </c>
       <c r="H78" t="s">
         <v>3</v>
@@ -3742,22 +4468,22 @@
     </row>
     <row r="79" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A79" t="s">
-        <v>330</v>
+        <v>357</v>
       </c>
       <c r="C79" t="s">
-        <v>2</v>
+        <v>17</v>
       </c>
       <c r="D79" t="s">
-        <v>331</v>
+        <v>358</v>
       </c>
       <c r="E79" t="s">
-        <v>332</v>
+        <v>36</v>
       </c>
       <c r="F79" t="s">
-        <v>0</v>
+        <v>37</v>
       </c>
       <c r="G79" t="s">
-        <v>333</v>
+        <v>359</v>
       </c>
       <c r="H79" t="s">
         <v>3</v>
@@ -3765,22 +4491,22 @@
     </row>
     <row r="80" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A80" t="s">
-        <v>334</v>
+        <v>360</v>
       </c>
       <c r="C80" t="s">
-        <v>124</v>
+        <v>17</v>
       </c>
       <c r="D80" t="s">
-        <v>335</v>
+        <v>358</v>
       </c>
       <c r="E80" t="s">
-        <v>336</v>
+        <v>36</v>
       </c>
       <c r="F80" t="s">
-        <v>0</v>
+        <v>37</v>
       </c>
       <c r="G80" t="s">
-        <v>337</v>
+        <v>359</v>
       </c>
       <c r="H80" t="s">
         <v>3</v>
@@ -3788,22 +4514,22 @@
     </row>
     <row r="81" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A81" t="s">
-        <v>338</v>
+        <v>361</v>
       </c>
       <c r="C81" t="s">
-        <v>124</v>
+        <v>5</v>
       </c>
       <c r="D81" t="s">
-        <v>335</v>
+        <v>362</v>
       </c>
       <c r="E81" t="s">
-        <v>336</v>
+        <v>363</v>
       </c>
       <c r="F81" t="s">
-        <v>0</v>
+        <v>364</v>
       </c>
       <c r="G81" t="s">
-        <v>337</v>
+        <v>365</v>
       </c>
       <c r="H81" t="s">
         <v>3</v>
@@ -3811,22 +4537,22 @@
     </row>
     <row r="82" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A82" t="s">
-        <v>339</v>
+        <v>366</v>
       </c>
       <c r="C82" t="s">
-        <v>27</v>
+        <v>5</v>
       </c>
       <c r="D82" t="s">
-        <v>340</v>
+        <v>362</v>
       </c>
       <c r="E82" t="s">
-        <v>341</v>
+        <v>363</v>
       </c>
       <c r="F82" t="s">
-        <v>342</v>
+        <v>364</v>
       </c>
       <c r="G82" t="s">
-        <v>343</v>
+        <v>365</v>
       </c>
       <c r="H82" t="s">
         <v>3</v>
@@ -3834,22 +4560,22 @@
     </row>
     <row r="83" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A83" t="s">
-        <v>344</v>
+        <v>367</v>
       </c>
       <c r="C83" t="s">
-        <v>138</v>
+        <v>149</v>
       </c>
       <c r="D83" t="s">
-        <v>345</v>
+        <v>368</v>
       </c>
       <c r="E83" t="s">
-        <v>9</v>
+        <v>19</v>
       </c>
       <c r="F83" t="s">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="G83" t="s">
-        <v>346</v>
+        <v>369</v>
       </c>
       <c r="H83" t="s">
         <v>3</v>
@@ -3857,22 +4583,22 @@
     </row>
     <row r="84" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A84" t="s">
-        <v>347</v>
+        <v>370</v>
       </c>
       <c r="C84" t="s">
-        <v>22</v>
+        <v>67</v>
       </c>
       <c r="D84" t="s">
-        <v>348</v>
+        <v>371</v>
       </c>
       <c r="E84" t="s">
-        <v>79</v>
+        <v>372</v>
       </c>
       <c r="F84" t="s">
         <v>0</v>
       </c>
       <c r="G84" t="s">
-        <v>349</v>
+        <v>373</v>
       </c>
       <c r="H84" t="s">
         <v>3</v>
@@ -3880,22 +4606,22 @@
     </row>
     <row r="85" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A85" t="s">
-        <v>350</v>
+        <v>374</v>
       </c>
       <c r="C85" t="s">
-        <v>31</v>
+        <v>67</v>
       </c>
       <c r="D85" t="s">
-        <v>351</v>
+        <v>371</v>
       </c>
       <c r="E85" t="s">
-        <v>75</v>
+        <v>372</v>
       </c>
       <c r="F85" t="s">
         <v>0</v>
       </c>
       <c r="G85" t="s">
-        <v>352</v>
+        <v>373</v>
       </c>
       <c r="H85" t="s">
         <v>3</v>
@@ -3903,22 +4629,22 @@
     </row>
     <row r="86" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A86" t="s">
-        <v>353</v>
+        <v>375</v>
       </c>
       <c r="C86" t="s">
-        <v>7</v>
+        <v>67</v>
       </c>
       <c r="D86" t="s">
-        <v>354</v>
+        <v>376</v>
       </c>
       <c r="E86" t="s">
-        <v>355</v>
+        <v>345</v>
       </c>
       <c r="F86" t="s">
         <v>0</v>
       </c>
       <c r="G86" t="s">
-        <v>356</v>
+        <v>377</v>
       </c>
       <c r="H86" t="s">
         <v>3</v>
@@ -3926,22 +4652,22 @@
     </row>
     <row r="87" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A87" t="s">
-        <v>357</v>
+        <v>378</v>
       </c>
       <c r="C87" t="s">
-        <v>27</v>
+        <v>81</v>
       </c>
       <c r="D87" t="s">
-        <v>358</v>
+        <v>379</v>
       </c>
       <c r="E87" t="s">
-        <v>359</v>
+        <v>232</v>
       </c>
       <c r="F87" t="s">
-        <v>360</v>
+        <v>0</v>
       </c>
       <c r="G87" t="s">
-        <v>361</v>
+        <v>380</v>
       </c>
       <c r="H87" t="s">
         <v>3</v>
@@ -3949,22 +4675,22 @@
     </row>
     <row r="88" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A88" t="s">
-        <v>362</v>
+        <v>381</v>
       </c>
       <c r="C88" t="s">
-        <v>28</v>
+        <v>25</v>
       </c>
       <c r="D88" t="s">
-        <v>363</v>
+        <v>382</v>
       </c>
       <c r="E88" t="s">
-        <v>364</v>
+        <v>80</v>
       </c>
       <c r="F88" t="s">
         <v>0</v>
       </c>
       <c r="G88" t="s">
-        <v>365</v>
+        <v>383</v>
       </c>
       <c r="H88" t="s">
         <v>3</v>
@@ -3972,22 +4698,22 @@
     </row>
     <row r="89" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A89" t="s">
-        <v>366</v>
+        <v>384</v>
       </c>
       <c r="C89" t="s">
-        <v>22</v>
+        <v>177</v>
       </c>
       <c r="D89" t="s">
-        <v>367</v>
+        <v>385</v>
       </c>
       <c r="E89" t="s">
-        <v>193</v>
+        <v>386</v>
       </c>
       <c r="F89" t="s">
-        <v>0</v>
+        <v>387</v>
       </c>
       <c r="G89" t="s">
-        <v>368</v>
+        <v>388</v>
       </c>
       <c r="H89" t="s">
         <v>3</v>
@@ -3995,22 +4721,22 @@
     </row>
     <row r="90" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A90" t="s">
-        <v>369</v>
+        <v>389</v>
       </c>
       <c r="C90" t="s">
-        <v>142</v>
+        <v>74</v>
       </c>
       <c r="D90" t="s">
-        <v>370</v>
+        <v>390</v>
       </c>
       <c r="E90" t="s">
-        <v>371</v>
+        <v>58</v>
       </c>
       <c r="F90" t="s">
-        <v>0</v>
+        <v>59</v>
       </c>
       <c r="G90" t="s">
-        <v>372</v>
+        <v>391</v>
       </c>
       <c r="H90" t="s">
         <v>3</v>
@@ -4018,22 +4744,22 @@
     </row>
     <row r="91" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A91" t="s">
-        <v>373</v>
+        <v>392</v>
       </c>
       <c r="C91" t="s">
-        <v>124</v>
+        <v>26</v>
       </c>
       <c r="D91" t="s">
-        <v>374</v>
+        <v>393</v>
       </c>
       <c r="E91" t="s">
-        <v>36</v>
+        <v>394</v>
       </c>
       <c r="F91" t="s">
         <v>0</v>
       </c>
       <c r="G91" t="s">
-        <v>280</v>
+        <v>395</v>
       </c>
       <c r="H91" t="s">
         <v>3</v>
@@ -4041,22 +4767,22 @@
     </row>
     <row r="92" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A92" t="s">
-        <v>375</v>
+        <v>396</v>
       </c>
       <c r="C92" t="s">
-        <v>124</v>
+        <v>74</v>
       </c>
       <c r="D92" t="s">
-        <v>374</v>
+        <v>397</v>
       </c>
       <c r="E92" t="s">
-        <v>36</v>
+        <v>398</v>
       </c>
       <c r="F92" t="s">
-        <v>0</v>
+        <v>399</v>
       </c>
       <c r="G92" t="s">
-        <v>280</v>
+        <v>400</v>
       </c>
       <c r="H92" t="s">
         <v>3</v>
@@ -4064,22 +4790,22 @@
     </row>
     <row r="93" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A93" t="s">
-        <v>376</v>
+        <v>401</v>
       </c>
       <c r="C93" t="s">
-        <v>142</v>
+        <v>29</v>
       </c>
       <c r="D93" t="s">
-        <v>377</v>
+        <v>402</v>
       </c>
       <c r="E93" t="s">
-        <v>71</v>
+        <v>35</v>
       </c>
       <c r="F93" t="s">
         <v>0</v>
       </c>
       <c r="G93" t="s">
-        <v>49</v>
+        <v>403</v>
       </c>
       <c r="H93" t="s">
         <v>3</v>
@@ -4087,22 +4813,22 @@
     </row>
     <row r="94" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A94" t="s">
-        <v>378</v>
+        <v>404</v>
       </c>
       <c r="C94" t="s">
-        <v>43</v>
+        <v>177</v>
       </c>
       <c r="D94" t="s">
-        <v>379</v>
+        <v>405</v>
       </c>
       <c r="E94" t="s">
-        <v>56</v>
+        <v>386</v>
       </c>
       <c r="F94" t="s">
-        <v>57</v>
+        <v>387</v>
       </c>
       <c r="G94" t="s">
-        <v>380</v>
+        <v>117</v>
       </c>
       <c r="H94" t="s">
         <v>3</v>
@@ -4110,22 +4836,22 @@
     </row>
     <row r="95" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A95" t="s">
-        <v>381</v>
+        <v>406</v>
       </c>
       <c r="C95" t="s">
-        <v>18</v>
+        <v>26</v>
       </c>
       <c r="D95" t="s">
-        <v>382</v>
+        <v>407</v>
       </c>
       <c r="E95" t="s">
-        <v>38</v>
+        <v>321</v>
       </c>
       <c r="F95" t="s">
-        <v>39</v>
+        <v>0</v>
       </c>
       <c r="G95" t="s">
-        <v>383</v>
+        <v>408</v>
       </c>
       <c r="H95" t="s">
         <v>3</v>
@@ -4133,22 +4859,22 @@
     </row>
     <row r="96" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A96" t="s">
-        <v>384</v>
+        <v>409</v>
       </c>
       <c r="C96" t="s">
-        <v>18</v>
+        <v>26</v>
       </c>
       <c r="D96" t="s">
-        <v>382</v>
+        <v>410</v>
       </c>
       <c r="E96" t="s">
-        <v>38</v>
+        <v>411</v>
       </c>
       <c r="F96" t="s">
-        <v>39</v>
+        <v>0</v>
       </c>
       <c r="G96" t="s">
-        <v>383</v>
+        <v>412</v>
       </c>
       <c r="H96" t="s">
         <v>3</v>
@@ -4156,22 +4882,22 @@
     </row>
     <row r="97" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A97" t="s">
-        <v>385</v>
+        <v>413</v>
       </c>
       <c r="C97" t="s">
-        <v>28</v>
+        <v>414</v>
       </c>
       <c r="D97" t="s">
-        <v>386</v>
+        <v>415</v>
       </c>
       <c r="E97" t="s">
-        <v>70</v>
+        <v>416</v>
       </c>
       <c r="F97" t="s">
         <v>0</v>
       </c>
       <c r="G97" t="s">
-        <v>387</v>
+        <v>417</v>
       </c>
       <c r="H97" t="s">
         <v>3</v>
@@ -4179,22 +4905,22 @@
     </row>
     <row r="98" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A98" t="s">
-        <v>388</v>
+        <v>418</v>
       </c>
       <c r="C98" t="s">
-        <v>27</v>
+        <v>67</v>
       </c>
       <c r="D98" t="s">
-        <v>389</v>
+        <v>419</v>
       </c>
       <c r="E98" t="s">
-        <v>50</v>
+        <v>345</v>
       </c>
       <c r="F98" t="s">
         <v>0</v>
       </c>
       <c r="G98" t="s">
-        <v>390</v>
+        <v>420</v>
       </c>
       <c r="H98" t="s">
         <v>3</v>
@@ -4202,22 +4928,22 @@
     </row>
     <row r="99" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A99" t="s">
-        <v>391</v>
+        <v>421</v>
       </c>
       <c r="C99" t="s">
-        <v>22</v>
+        <v>81</v>
       </c>
       <c r="D99" t="s">
-        <v>392</v>
+        <v>422</v>
       </c>
       <c r="E99" t="s">
-        <v>393</v>
+        <v>273</v>
       </c>
       <c r="F99" t="s">
-        <v>0</v>
+        <v>274</v>
       </c>
       <c r="G99" t="s">
-        <v>394</v>
+        <v>423</v>
       </c>
       <c r="H99" t="s">
         <v>3</v>
@@ -4225,22 +4951,22 @@
     </row>
     <row r="100" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A100" t="s">
-        <v>395</v>
+        <v>424</v>
       </c>
       <c r="C100" t="s">
-        <v>105</v>
+        <v>81</v>
       </c>
       <c r="D100" t="s">
-        <v>396</v>
+        <v>422</v>
       </c>
       <c r="E100" t="s">
-        <v>397</v>
+        <v>273</v>
       </c>
       <c r="F100" t="s">
-        <v>398</v>
+        <v>274</v>
       </c>
       <c r="G100" t="s">
-        <v>399</v>
+        <v>423</v>
       </c>
       <c r="H100" t="s">
         <v>3</v>
@@ -4248,22 +4974,22 @@
     </row>
     <row r="101" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A101" t="s">
-        <v>400</v>
+        <v>425</v>
       </c>
       <c r="C101" t="s">
-        <v>31</v>
+        <v>77</v>
       </c>
       <c r="D101" t="s">
-        <v>401</v>
+        <v>426</v>
       </c>
       <c r="E101" t="s">
-        <v>402</v>
+        <v>427</v>
       </c>
       <c r="F101" t="s">
-        <v>0</v>
+        <v>428</v>
       </c>
       <c r="G101" t="s">
-        <v>76</v>
+        <v>429</v>
       </c>
       <c r="H101" t="s">
         <v>3</v>
@@ -4271,22 +4997,22 @@
     </row>
     <row r="102" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A102" t="s">
-        <v>403</v>
+        <v>430</v>
       </c>
       <c r="C102" t="s">
-        <v>31</v>
+        <v>77</v>
       </c>
       <c r="D102" t="s">
-        <v>404</v>
+        <v>426</v>
       </c>
       <c r="E102" t="s">
-        <v>405</v>
+        <v>427</v>
       </c>
       <c r="F102" t="s">
-        <v>0</v>
+        <v>428</v>
       </c>
       <c r="G102" t="s">
-        <v>406</v>
+        <v>429</v>
       </c>
       <c r="H102" t="s">
         <v>3</v>
@@ -4294,22 +5020,22 @@
     </row>
     <row r="103" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A103" t="s">
-        <v>407</v>
+        <v>431</v>
       </c>
       <c r="C103" t="s">
-        <v>6</v>
+        <v>29</v>
       </c>
       <c r="D103" t="s">
-        <v>408</v>
+        <v>432</v>
       </c>
       <c r="E103" t="s">
-        <v>48</v>
+        <v>244</v>
       </c>
       <c r="F103" t="s">
         <v>0</v>
       </c>
       <c r="G103" t="s">
-        <v>409</v>
+        <v>433</v>
       </c>
       <c r="H103" t="s">
         <v>3</v>
@@ -4317,22 +5043,22 @@
     </row>
     <row r="104" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A104" t="s">
-        <v>410</v>
+        <v>434</v>
       </c>
       <c r="C104" t="s">
-        <v>27</v>
+        <v>21</v>
       </c>
       <c r="D104" t="s">
-        <v>411</v>
+        <v>435</v>
       </c>
       <c r="E104" t="s">
-        <v>412</v>
+        <v>259</v>
       </c>
       <c r="F104" t="s">
         <v>0</v>
       </c>
       <c r="G104" t="s">
-        <v>413</v>
+        <v>328</v>
       </c>
       <c r="H104" t="s">
         <v>3</v>
@@ -4340,22 +5066,22 @@
     </row>
     <row r="105" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A105" t="s">
-        <v>414</v>
+        <v>436</v>
       </c>
       <c r="C105" t="s">
-        <v>27</v>
+        <v>33</v>
       </c>
       <c r="D105" t="s">
-        <v>411</v>
+        <v>437</v>
       </c>
       <c r="E105" t="s">
-        <v>412</v>
+        <v>41</v>
       </c>
       <c r="F105" t="s">
         <v>0</v>
       </c>
       <c r="G105" t="s">
-        <v>413</v>
+        <v>42</v>
       </c>
       <c r="H105" t="s">
         <v>3</v>
@@ -4363,22 +5089,22 @@
     </row>
     <row r="106" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A106" t="s">
-        <v>415</v>
+        <v>438</v>
       </c>
       <c r="C106" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="D106" t="s">
-        <v>411</v>
+        <v>439</v>
       </c>
       <c r="E106" t="s">
-        <v>412</v>
+        <v>107</v>
       </c>
       <c r="F106" t="s">
         <v>0</v>
       </c>
       <c r="G106" t="s">
-        <v>413</v>
+        <v>440</v>
       </c>
       <c r="H106" t="s">
         <v>3</v>
@@ -4386,22 +5112,22 @@
     </row>
     <row r="107" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A107" t="s">
-        <v>416</v>
+        <v>441</v>
       </c>
       <c r="C107" t="s">
-        <v>35</v>
+        <v>29</v>
       </c>
       <c r="D107" t="s">
-        <v>417</v>
+        <v>442</v>
       </c>
       <c r="E107" t="s">
-        <v>418</v>
+        <v>244</v>
       </c>
       <c r="F107" t="s">
-        <v>419</v>
+        <v>0</v>
       </c>
       <c r="G107" t="s">
-        <v>420</v>
+        <v>443</v>
       </c>
       <c r="H107" t="s">
         <v>3</v>
@@ -4409,22 +5135,22 @@
     </row>
     <row r="108" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A108" t="s">
-        <v>421</v>
+        <v>444</v>
       </c>
       <c r="C108" t="s">
-        <v>105</v>
+        <v>177</v>
       </c>
       <c r="D108" t="s">
-        <v>422</v>
+        <v>445</v>
       </c>
       <c r="E108" t="s">
-        <v>423</v>
+        <v>446</v>
       </c>
       <c r="F108" t="s">
-        <v>424</v>
+        <v>0</v>
       </c>
       <c r="G108" t="s">
-        <v>425</v>
+        <v>447</v>
       </c>
       <c r="H108" t="s">
         <v>3</v>
@@ -4432,22 +5158,22 @@
     </row>
     <row r="109" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A109" t="s">
-        <v>426</v>
+        <v>109</v>
       </c>
       <c r="C109" t="s">
-        <v>105</v>
+        <v>76</v>
       </c>
       <c r="D109" t="s">
-        <v>427</v>
+        <v>110</v>
       </c>
       <c r="E109" t="s">
-        <v>67</v>
+        <v>111</v>
       </c>
       <c r="F109" t="s">
         <v>0</v>
       </c>
       <c r="G109" t="s">
-        <v>428</v>
+        <v>112</v>
       </c>
       <c r="H109" t="s">
         <v>3</v>
@@ -4455,22 +5181,22 @@
     </row>
     <row r="110" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A110" t="s">
-        <v>429</v>
+        <v>113</v>
       </c>
       <c r="C110" t="s">
-        <v>18</v>
+        <v>76</v>
       </c>
       <c r="D110" t="s">
-        <v>430</v>
+        <v>110</v>
       </c>
       <c r="E110" t="s">
-        <v>38</v>
+        <v>111</v>
       </c>
       <c r="F110" t="s">
-        <v>39</v>
+        <v>0</v>
       </c>
       <c r="G110" t="s">
-        <v>431</v>
+        <v>112</v>
       </c>
       <c r="H110" t="s">
         <v>3</v>
@@ -4478,22 +5204,22 @@
     </row>
     <row r="111" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A111" t="s">
-        <v>432</v>
+        <v>448</v>
       </c>
       <c r="C111" t="s">
-        <v>124</v>
+        <v>21</v>
       </c>
       <c r="D111" t="s">
-        <v>433</v>
+        <v>449</v>
       </c>
       <c r="E111" t="s">
-        <v>434</v>
+        <v>47</v>
       </c>
       <c r="F111" t="s">
-        <v>0</v>
+        <v>48</v>
       </c>
       <c r="G111" t="s">
-        <v>435</v>
+        <v>181</v>
       </c>
       <c r="H111" t="s">
         <v>3</v>
@@ -4501,22 +5227,22 @@
     </row>
     <row r="112" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A112" t="s">
-        <v>436</v>
+        <v>450</v>
       </c>
       <c r="C112" t="s">
-        <v>18</v>
+        <v>33</v>
       </c>
       <c r="D112" t="s">
-        <v>437</v>
+        <v>451</v>
       </c>
       <c r="E112" t="s">
-        <v>438</v>
+        <v>252</v>
       </c>
       <c r="F112" t="s">
         <v>0</v>
       </c>
       <c r="G112" t="s">
-        <v>439</v>
+        <v>452</v>
       </c>
       <c r="H112" t="s">
         <v>3</v>
@@ -4524,22 +5250,22 @@
     </row>
     <row r="113" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A113" t="s">
-        <v>440</v>
+        <v>453</v>
       </c>
       <c r="C113" t="s">
-        <v>22</v>
+        <v>29</v>
       </c>
       <c r="D113" t="s">
-        <v>441</v>
+        <v>454</v>
       </c>
       <c r="E113" t="s">
-        <v>442</v>
+        <v>455</v>
       </c>
       <c r="F113" t="s">
         <v>0</v>
       </c>
       <c r="G113" t="s">
-        <v>443</v>
+        <v>456</v>
       </c>
       <c r="H113" t="s">
         <v>3</v>
@@ -4547,22 +5273,22 @@
     </row>
     <row r="114" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A114" t="s">
-        <v>444</v>
+        <v>457</v>
       </c>
       <c r="C114" t="s">
-        <v>22</v>
+        <v>29</v>
       </c>
       <c r="D114" t="s">
-        <v>445</v>
+        <v>454</v>
       </c>
       <c r="E114" t="s">
-        <v>442</v>
+        <v>455</v>
       </c>
       <c r="F114" t="s">
         <v>0</v>
       </c>
       <c r="G114" t="s">
-        <v>446</v>
+        <v>456</v>
       </c>
       <c r="H114" t="s">
         <v>3</v>
@@ -4570,22 +5296,22 @@
     </row>
     <row r="115" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A115" t="s">
-        <v>447</v>
+        <v>458</v>
       </c>
       <c r="C115" t="s">
-        <v>5</v>
+        <v>27</v>
       </c>
       <c r="D115" t="s">
-        <v>448</v>
+        <v>459</v>
       </c>
       <c r="E115" t="s">
-        <v>23</v>
+        <v>31</v>
       </c>
       <c r="F115" t="s">
-        <v>24</v>
+        <v>0</v>
       </c>
       <c r="G115" t="s">
-        <v>449</v>
+        <v>460</v>
       </c>
       <c r="H115" t="s">
         <v>3</v>
@@ -4593,22 +5319,22 @@
     </row>
     <row r="116" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A116" t="s">
-        <v>450</v>
+        <v>461</v>
       </c>
       <c r="C116" t="s">
-        <v>176</v>
+        <v>21</v>
       </c>
       <c r="D116" t="s">
-        <v>451</v>
+        <v>462</v>
       </c>
       <c r="E116" t="s">
-        <v>452</v>
+        <v>47</v>
       </c>
       <c r="F116" t="s">
-        <v>0</v>
+        <v>48</v>
       </c>
       <c r="G116" t="s">
-        <v>453</v>
+        <v>463</v>
       </c>
       <c r="H116" t="s">
         <v>3</v>
@@ -4616,22 +5342,22 @@
     </row>
     <row r="117" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A117" t="s">
-        <v>454</v>
+        <v>464</v>
       </c>
       <c r="C117" t="s">
-        <v>176</v>
+        <v>26</v>
       </c>
       <c r="D117" t="s">
-        <v>451</v>
+        <v>465</v>
       </c>
       <c r="E117" t="s">
-        <v>452</v>
+        <v>98</v>
       </c>
       <c r="F117" t="s">
-        <v>0</v>
+        <v>99</v>
       </c>
       <c r="G117" t="s">
-        <v>453</v>
+        <v>466</v>
       </c>
       <c r="H117" t="s">
         <v>3</v>
@@ -4639,22 +5365,22 @@
     </row>
     <row r="118" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A118" t="s">
-        <v>455</v>
+        <v>467</v>
       </c>
       <c r="C118" t="s">
-        <v>22</v>
+        <v>74</v>
       </c>
       <c r="D118" t="s">
-        <v>456</v>
+        <v>468</v>
       </c>
       <c r="E118" t="s">
-        <v>457</v>
+        <v>65</v>
       </c>
       <c r="F118" t="s">
-        <v>0</v>
+        <v>66</v>
       </c>
       <c r="G118" t="s">
-        <v>458</v>
+        <v>469</v>
       </c>
       <c r="H118" t="s">
         <v>3</v>
@@ -4662,22 +5388,22 @@
     </row>
     <row r="119" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A119" t="s">
-        <v>459</v>
+        <v>470</v>
       </c>
       <c r="C119" t="s">
-        <v>29</v>
+        <v>67</v>
       </c>
       <c r="D119" t="s">
-        <v>460</v>
+        <v>471</v>
       </c>
       <c r="E119" t="s">
-        <v>40</v>
+        <v>51</v>
       </c>
       <c r="F119" t="s">
-        <v>41</v>
+        <v>0</v>
       </c>
       <c r="G119" t="s">
-        <v>461</v>
+        <v>472</v>
       </c>
       <c r="H119" t="s">
         <v>3</v>
@@ -4685,22 +5411,22 @@
     </row>
     <row r="120" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A120" t="s">
-        <v>462</v>
+        <v>473</v>
       </c>
       <c r="C120" t="s">
-        <v>176</v>
+        <v>21</v>
       </c>
       <c r="D120" t="s">
-        <v>463</v>
+        <v>474</v>
       </c>
       <c r="E120" t="s">
-        <v>464</v>
+        <v>68</v>
       </c>
       <c r="F120" t="s">
-        <v>0</v>
+        <v>69</v>
       </c>
       <c r="G120" t="s">
-        <v>178</v>
+        <v>70</v>
       </c>
       <c r="H120" t="s">
         <v>3</v>
@@ -4708,22 +5434,22 @@
     </row>
     <row r="121" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A121" t="s">
-        <v>465</v>
+        <v>475</v>
       </c>
       <c r="C121" t="s">
-        <v>5</v>
+        <v>21</v>
       </c>
       <c r="D121" t="s">
-        <v>466</v>
+        <v>476</v>
       </c>
       <c r="E121" t="s">
-        <v>467</v>
+        <v>477</v>
       </c>
       <c r="F121" t="s">
-        <v>468</v>
+        <v>0</v>
       </c>
       <c r="G121" t="s">
-        <v>313</v>
+        <v>478</v>
       </c>
       <c r="H121" t="s">
         <v>3</v>
@@ -4731,22 +5457,22 @@
     </row>
     <row r="122" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A122" t="s">
-        <v>469</v>
+        <v>479</v>
       </c>
       <c r="C122" t="s">
-        <v>2</v>
+        <v>21</v>
       </c>
       <c r="D122" t="s">
-        <v>470</v>
+        <v>480</v>
       </c>
       <c r="E122" t="s">
-        <v>116</v>
+        <v>477</v>
       </c>
       <c r="F122" t="s">
         <v>0</v>
       </c>
       <c r="G122" t="s">
-        <v>471</v>
+        <v>481</v>
       </c>
       <c r="H122" t="s">
         <v>3</v>
@@ -4754,22 +5480,22 @@
     </row>
     <row r="123" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A123" t="s">
-        <v>472</v>
+        <v>482</v>
       </c>
       <c r="C123" t="s">
-        <v>2</v>
+        <v>77</v>
       </c>
       <c r="D123" t="s">
-        <v>470</v>
+        <v>483</v>
       </c>
       <c r="E123" t="s">
-        <v>116</v>
+        <v>484</v>
       </c>
       <c r="F123" t="s">
-        <v>0</v>
+        <v>485</v>
       </c>
       <c r="G123" t="s">
-        <v>471</v>
+        <v>486</v>
       </c>
       <c r="H123" t="s">
         <v>3</v>
@@ -4777,22 +5503,22 @@
     </row>
     <row r="124" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A124" t="s">
-        <v>473</v>
+        <v>487</v>
       </c>
       <c r="C124" t="s">
-        <v>176</v>
+        <v>26</v>
       </c>
       <c r="D124" t="s">
-        <v>474</v>
+        <v>488</v>
       </c>
       <c r="E124" t="s">
-        <v>464</v>
+        <v>98</v>
       </c>
       <c r="F124" t="s">
-        <v>0</v>
+        <v>99</v>
       </c>
       <c r="G124" t="s">
-        <v>47</v>
+        <v>100</v>
       </c>
       <c r="H124" t="s">
         <v>3</v>
@@ -4800,22 +5526,22 @@
     </row>
     <row r="125" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A125" t="s">
-        <v>475</v>
+        <v>489</v>
       </c>
       <c r="C125" t="s">
-        <v>18</v>
+        <v>29</v>
       </c>
       <c r="D125" t="s">
-        <v>476</v>
+        <v>490</v>
       </c>
       <c r="E125" t="s">
-        <v>477</v>
+        <v>455</v>
       </c>
       <c r="F125" t="s">
         <v>0</v>
       </c>
       <c r="G125" t="s">
-        <v>478</v>
+        <v>491</v>
       </c>
       <c r="H125" t="s">
         <v>3</v>
@@ -4823,22 +5549,22 @@
     </row>
     <row r="126" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A126" t="s">
-        <v>479</v>
+        <v>492</v>
       </c>
       <c r="C126" t="s">
-        <v>7</v>
+        <v>25</v>
       </c>
       <c r="D126" t="s">
-        <v>480</v>
+        <v>493</v>
       </c>
       <c r="E126" t="s">
-        <v>355</v>
+        <v>44</v>
       </c>
       <c r="F126" t="s">
         <v>0</v>
       </c>
       <c r="G126" t="s">
-        <v>481</v>
+        <v>349</v>
       </c>
       <c r="H126" t="s">
         <v>3</v>
@@ -4846,22 +5572,22 @@
     </row>
     <row r="127" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A127" t="s">
-        <v>482</v>
+        <v>494</v>
       </c>
       <c r="C127" t="s">
         <v>5</v>
       </c>
       <c r="D127" t="s">
-        <v>483</v>
+        <v>495</v>
       </c>
       <c r="E127" t="s">
-        <v>23</v>
+        <v>123</v>
       </c>
       <c r="F127" t="s">
-        <v>24</v>
+        <v>124</v>
       </c>
       <c r="G127" t="s">
-        <v>484</v>
+        <v>496</v>
       </c>
       <c r="H127" t="s">
         <v>3</v>
@@ -4869,370 +5595,2256 @@
     </row>
     <row r="128" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A128" t="s">
-        <v>485</v>
+        <v>497</v>
       </c>
       <c r="C128" t="s">
-        <v>31</v>
+        <v>149</v>
       </c>
       <c r="D128" t="s">
-        <v>486</v>
+        <v>498</v>
       </c>
       <c r="E128" t="s">
-        <v>75</v>
+        <v>19</v>
       </c>
       <c r="F128" t="s">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="G128" t="s">
-        <v>76</v>
+        <v>499</v>
       </c>
       <c r="H128" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="129" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A129" t="s">
-        <v>487</v>
+        <v>500</v>
       </c>
       <c r="C129" t="s">
-        <v>22</v>
+        <v>149</v>
       </c>
       <c r="D129" t="s">
-        <v>488</v>
+        <v>501</v>
       </c>
       <c r="E129" t="s">
-        <v>277</v>
+        <v>19</v>
       </c>
       <c r="F129" t="s">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="G129" t="s">
-        <v>489</v>
+        <v>115</v>
       </c>
       <c r="H129" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="130" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A130" t="s">
-        <v>490</v>
+        <v>502</v>
       </c>
       <c r="C130" t="s">
-        <v>22</v>
+        <v>149</v>
       </c>
       <c r="D130" t="s">
-        <v>488</v>
+        <v>503</v>
       </c>
       <c r="E130" t="s">
-        <v>277</v>
+        <v>19</v>
       </c>
       <c r="F130" t="s">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="G130" t="s">
-        <v>489</v>
+        <v>504</v>
       </c>
       <c r="H130" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="131" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A131" t="s">
-        <v>491</v>
+        <v>505</v>
       </c>
       <c r="C131" t="s">
-        <v>22</v>
+        <v>26</v>
       </c>
       <c r="D131" t="s">
-        <v>488</v>
+        <v>506</v>
       </c>
       <c r="E131" t="s">
-        <v>277</v>
+        <v>98</v>
       </c>
       <c r="F131" t="s">
-        <v>0</v>
+        <v>99</v>
       </c>
       <c r="G131" t="s">
-        <v>489</v>
+        <v>507</v>
       </c>
       <c r="H131" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="132" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A132" t="s">
-        <v>492</v>
+        <v>508</v>
       </c>
       <c r="C132" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="D132" t="s">
-        <v>493</v>
+        <v>509</v>
       </c>
       <c r="E132" t="s">
-        <v>72</v>
+        <v>510</v>
       </c>
       <c r="F132" t="s">
-        <v>73</v>
+        <v>0</v>
       </c>
       <c r="G132" t="s">
-        <v>494</v>
+        <v>511</v>
       </c>
       <c r="H132" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="133" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A133" t="s">
-        <v>495</v>
+        <v>512</v>
       </c>
       <c r="C133" t="s">
-        <v>7</v>
+        <v>26</v>
       </c>
       <c r="D133" t="s">
-        <v>496</v>
+        <v>513</v>
       </c>
       <c r="E133" t="s">
-        <v>72</v>
+        <v>38</v>
       </c>
       <c r="F133" t="s">
-        <v>73</v>
+        <v>39</v>
       </c>
       <c r="G133" t="s">
-        <v>497</v>
+        <v>514</v>
       </c>
       <c r="H133" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="134" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A134" t="s">
-        <v>498</v>
+        <v>515</v>
       </c>
       <c r="C134" t="s">
-        <v>18</v>
+        <v>26</v>
       </c>
       <c r="D134" t="s">
-        <v>499</v>
+        <v>513</v>
       </c>
       <c r="E134" t="s">
-        <v>438</v>
+        <v>38</v>
       </c>
       <c r="F134" t="s">
-        <v>0</v>
+        <v>39</v>
       </c>
       <c r="G134" t="s">
-        <v>500</v>
+        <v>514</v>
       </c>
       <c r="H134" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="135" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A135" t="s">
-        <v>501</v>
+        <v>516</v>
       </c>
       <c r="C135" t="s">
-        <v>35</v>
+        <v>6</v>
       </c>
       <c r="D135" t="s">
-        <v>502</v>
+        <v>517</v>
       </c>
       <c r="E135" t="s">
-        <v>20</v>
+        <v>518</v>
       </c>
       <c r="F135" t="s">
-        <v>21</v>
+        <v>0</v>
       </c>
       <c r="G135" t="s">
-        <v>503</v>
+        <v>519</v>
       </c>
       <c r="H135" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="136" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A136" t="s">
-        <v>504</v>
+        <v>520</v>
       </c>
       <c r="C136" t="s">
-        <v>27</v>
+        <v>74</v>
       </c>
       <c r="D136" t="s">
-        <v>505</v>
+        <v>521</v>
       </c>
       <c r="E136" t="s">
-        <v>50</v>
+        <v>58</v>
       </c>
       <c r="F136" t="s">
-        <v>0</v>
+        <v>59</v>
       </c>
       <c r="G136" t="s">
-        <v>506</v>
+        <v>522</v>
       </c>
       <c r="H136" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="137" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A137" t="s">
-        <v>507</v>
+        <v>523</v>
       </c>
       <c r="C137" t="s">
-        <v>35</v>
+        <v>7</v>
       </c>
       <c r="D137" t="s">
-        <v>508</v>
+        <v>524</v>
       </c>
       <c r="E137" t="s">
-        <v>224</v>
+        <v>49</v>
       </c>
       <c r="F137" t="s">
-        <v>225</v>
+        <v>50</v>
       </c>
       <c r="G137" t="s">
-        <v>509</v>
+        <v>525</v>
       </c>
       <c r="H137" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="138" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A138" t="s">
-        <v>510</v>
+        <v>526</v>
       </c>
       <c r="C138" t="s">
-        <v>301</v>
+        <v>74</v>
       </c>
       <c r="D138" t="s">
-        <v>511</v>
+        <v>527</v>
       </c>
       <c r="E138" t="s">
-        <v>512</v>
+        <v>528</v>
       </c>
       <c r="F138" t="s">
-        <v>0</v>
+        <v>529</v>
       </c>
       <c r="G138" t="s">
-        <v>513</v>
+        <v>530</v>
       </c>
       <c r="H138" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="139" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A139" t="s">
-        <v>514</v>
+        <v>531</v>
       </c>
       <c r="C139" t="s">
-        <v>7</v>
+        <v>74</v>
       </c>
       <c r="D139" t="s">
-        <v>515</v>
+        <v>532</v>
       </c>
       <c r="E139" t="s">
-        <v>355</v>
+        <v>65</v>
       </c>
       <c r="F139" t="s">
-        <v>0</v>
+        <v>66</v>
       </c>
       <c r="G139" t="s">
-        <v>516</v>
+        <v>533</v>
       </c>
       <c r="H139" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="140" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A140" t="s">
-        <v>517</v>
+        <v>534</v>
       </c>
       <c r="C140" t="s">
-        <v>8</v>
+        <v>29</v>
       </c>
       <c r="D140" t="s">
-        <v>518</v>
+        <v>535</v>
       </c>
       <c r="E140" t="s">
-        <v>62</v>
+        <v>536</v>
       </c>
       <c r="F140" t="s">
         <v>0</v>
       </c>
       <c r="G140" t="s">
-        <v>519</v>
+        <v>537</v>
       </c>
       <c r="H140" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="141" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A141" t="s">
-        <v>520</v>
+        <v>538</v>
       </c>
       <c r="C141" t="s">
-        <v>105</v>
+        <v>18</v>
       </c>
       <c r="D141" t="s">
-        <v>521</v>
+        <v>539</v>
       </c>
       <c r="E141" t="s">
-        <v>67</v>
+        <v>52</v>
       </c>
       <c r="F141" t="s">
         <v>0</v>
       </c>
       <c r="G141" t="s">
-        <v>522</v>
+        <v>540</v>
       </c>
       <c r="H141" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="142" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A142" t="s">
-        <v>523</v>
+        <v>541</v>
       </c>
       <c r="C142" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="D142" t="s">
-        <v>524</v>
+        <v>542</v>
       </c>
       <c r="E142" t="s">
-        <v>37</v>
+        <v>107</v>
       </c>
       <c r="F142" t="s">
         <v>0</v>
       </c>
       <c r="G142" t="s">
-        <v>525</v>
+        <v>543</v>
       </c>
       <c r="H142" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="143" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A143" t="s">
-        <v>526</v>
+        <v>544</v>
       </c>
       <c r="C143" t="s">
+        <v>27</v>
+      </c>
+      <c r="D143" t="s">
+        <v>545</v>
+      </c>
+      <c r="E143" t="s">
+        <v>82</v>
+      </c>
+      <c r="F143" t="s">
+        <v>0</v>
+      </c>
+      <c r="G143" t="s">
+        <v>546</v>
+      </c>
+      <c r="H143" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="144" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A144" t="s">
+        <v>547</v>
+      </c>
+      <c r="C144" t="s">
+        <v>27</v>
+      </c>
+      <c r="D144" t="s">
+        <v>545</v>
+      </c>
+      <c r="E144" t="s">
+        <v>82</v>
+      </c>
+      <c r="F144" t="s">
+        <v>0</v>
+      </c>
+      <c r="G144" t="s">
+        <v>546</v>
+      </c>
+      <c r="H144" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="145" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A145" t="s">
+        <v>548</v>
+      </c>
+      <c r="C145" t="s">
+        <v>27</v>
+      </c>
+      <c r="D145" t="s">
+        <v>545</v>
+      </c>
+      <c r="E145" t="s">
+        <v>82</v>
+      </c>
+      <c r="F145" t="s">
+        <v>0</v>
+      </c>
+      <c r="G145" t="s">
+        <v>546</v>
+      </c>
+      <c r="H145" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="146" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A146" t="s">
+        <v>549</v>
+      </c>
+      <c r="C146" t="s">
+        <v>27</v>
+      </c>
+      <c r="D146" t="s">
+        <v>550</v>
+      </c>
+      <c r="E146" t="s">
+        <v>82</v>
+      </c>
+      <c r="F146" t="s">
+        <v>0</v>
+      </c>
+      <c r="G146" t="s">
+        <v>551</v>
+      </c>
+      <c r="H146" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="147" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A147" t="s">
+        <v>552</v>
+      </c>
+      <c r="C147" t="s">
+        <v>33</v>
+      </c>
+      <c r="D147" t="s">
+        <v>553</v>
+      </c>
+      <c r="E147" t="s">
+        <v>554</v>
+      </c>
+      <c r="F147" t="s">
+        <v>0</v>
+      </c>
+      <c r="G147" t="s">
+        <v>555</v>
+      </c>
+      <c r="H147" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="148" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A148" t="s">
+        <v>556</v>
+      </c>
+      <c r="C148" t="s">
         <v>5</v>
       </c>
-      <c r="D143" t="s">
-        <v>527</v>
-      </c>
-      <c r="E143" t="s">
-        <v>9</v>
-      </c>
-      <c r="F143" t="s">
-        <v>10</v>
-      </c>
-      <c r="G143" t="s">
-        <v>528</v>
-      </c>
-      <c r="H143" t="s">
+      <c r="D148" t="s">
+        <v>557</v>
+      </c>
+      <c r="E148" t="s">
+        <v>558</v>
+      </c>
+      <c r="F148" t="s">
+        <v>559</v>
+      </c>
+      <c r="G148" t="s">
+        <v>560</v>
+      </c>
+      <c r="H148" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="149" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A149" t="s">
+        <v>561</v>
+      </c>
+      <c r="C149" t="s">
+        <v>2</v>
+      </c>
+      <c r="D149" t="s">
+        <v>562</v>
+      </c>
+      <c r="E149" t="s">
+        <v>563</v>
+      </c>
+      <c r="F149" t="s">
+        <v>564</v>
+      </c>
+      <c r="G149" t="s">
+        <v>565</v>
+      </c>
+      <c r="H149" t="s">
         <v>4</v>
+      </c>
+    </row>
+    <row r="150" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A150" t="s">
+        <v>566</v>
+      </c>
+      <c r="C150" t="s">
+        <v>17</v>
+      </c>
+      <c r="D150" t="s">
+        <v>567</v>
+      </c>
+      <c r="E150" t="s">
+        <v>568</v>
+      </c>
+      <c r="F150" t="s">
+        <v>569</v>
+      </c>
+      <c r="G150" t="s">
+        <v>570</v>
+      </c>
+      <c r="H150" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="151" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A151" t="s">
+        <v>571</v>
+      </c>
+      <c r="C151" t="s">
+        <v>5</v>
+      </c>
+      <c r="D151" t="s">
+        <v>572</v>
+      </c>
+      <c r="E151" t="s">
+        <v>123</v>
+      </c>
+      <c r="F151" t="s">
+        <v>124</v>
+      </c>
+      <c r="G151" t="s">
+        <v>573</v>
+      </c>
+      <c r="H151" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="152" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A152" t="s">
+        <v>574</v>
+      </c>
+      <c r="C152" t="s">
+        <v>26</v>
+      </c>
+      <c r="D152" t="s">
+        <v>575</v>
+      </c>
+      <c r="E152" t="s">
+        <v>576</v>
+      </c>
+      <c r="F152" t="s">
+        <v>577</v>
+      </c>
+      <c r="G152" t="s">
+        <v>578</v>
+      </c>
+      <c r="H152" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="153" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A153" t="s">
+        <v>579</v>
+      </c>
+      <c r="C153" t="s">
+        <v>17</v>
+      </c>
+      <c r="D153" t="s">
+        <v>580</v>
+      </c>
+      <c r="E153" t="s">
+        <v>581</v>
+      </c>
+      <c r="F153" t="s">
+        <v>582</v>
+      </c>
+      <c r="G153" t="s">
+        <v>583</v>
+      </c>
+      <c r="H153" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="154" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A154" t="s">
+        <v>584</v>
+      </c>
+      <c r="C154" t="s">
+        <v>17</v>
+      </c>
+      <c r="D154" t="s">
+        <v>580</v>
+      </c>
+      <c r="E154" t="s">
+        <v>581</v>
+      </c>
+      <c r="F154" t="s">
+        <v>582</v>
+      </c>
+      <c r="G154" t="s">
+        <v>583</v>
+      </c>
+      <c r="H154" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="155" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A155" t="s">
+        <v>585</v>
+      </c>
+      <c r="C155" t="s">
+        <v>17</v>
+      </c>
+      <c r="D155" t="s">
+        <v>580</v>
+      </c>
+      <c r="E155" t="s">
+        <v>581</v>
+      </c>
+      <c r="F155" t="s">
+        <v>582</v>
+      </c>
+      <c r="G155" t="s">
+        <v>583</v>
+      </c>
+      <c r="H155" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="156" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A156" t="s">
+        <v>586</v>
+      </c>
+      <c r="C156" t="s">
+        <v>17</v>
+      </c>
+      <c r="D156" t="s">
+        <v>580</v>
+      </c>
+      <c r="E156" t="s">
+        <v>581</v>
+      </c>
+      <c r="F156" t="s">
+        <v>582</v>
+      </c>
+      <c r="G156" t="s">
+        <v>583</v>
+      </c>
+      <c r="H156" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="157" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A157" t="s">
+        <v>587</v>
+      </c>
+      <c r="C157" t="s">
+        <v>17</v>
+      </c>
+      <c r="D157" t="s">
+        <v>580</v>
+      </c>
+      <c r="E157" t="s">
+        <v>581</v>
+      </c>
+      <c r="F157" t="s">
+        <v>582</v>
+      </c>
+      <c r="G157" t="s">
+        <v>583</v>
+      </c>
+      <c r="H157" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="158" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A158" t="s">
+        <v>588</v>
+      </c>
+      <c r="C158" t="s">
+        <v>17</v>
+      </c>
+      <c r="D158" t="s">
+        <v>580</v>
+      </c>
+      <c r="E158" t="s">
+        <v>581</v>
+      </c>
+      <c r="F158" t="s">
+        <v>582</v>
+      </c>
+      <c r="G158" t="s">
+        <v>583</v>
+      </c>
+      <c r="H158" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="159" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A159" t="s">
+        <v>589</v>
+      </c>
+      <c r="C159" t="s">
+        <v>17</v>
+      </c>
+      <c r="D159" t="s">
+        <v>580</v>
+      </c>
+      <c r="E159" t="s">
+        <v>581</v>
+      </c>
+      <c r="F159" t="s">
+        <v>582</v>
+      </c>
+      <c r="G159" t="s">
+        <v>583</v>
+      </c>
+      <c r="H159" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="160" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A160" t="s">
+        <v>590</v>
+      </c>
+      <c r="C160" t="s">
+        <v>17</v>
+      </c>
+      <c r="D160" t="s">
+        <v>591</v>
+      </c>
+      <c r="E160" t="s">
+        <v>114</v>
+      </c>
+      <c r="F160" t="s">
+        <v>0</v>
+      </c>
+      <c r="G160" t="s">
+        <v>592</v>
+      </c>
+      <c r="H160" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="161" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A161" t="s">
+        <v>593</v>
+      </c>
+      <c r="C161" t="s">
+        <v>25</v>
+      </c>
+      <c r="D161" t="s">
+        <v>594</v>
+      </c>
+      <c r="E161" t="s">
+        <v>595</v>
+      </c>
+      <c r="F161" t="s">
+        <v>0</v>
+      </c>
+      <c r="G161" t="s">
+        <v>596</v>
+      </c>
+      <c r="H161" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="162" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A162" t="s">
+        <v>597</v>
+      </c>
+      <c r="C162" t="s">
+        <v>27</v>
+      </c>
+      <c r="D162" t="s">
+        <v>598</v>
+      </c>
+      <c r="E162" t="s">
+        <v>599</v>
+      </c>
+      <c r="F162" t="s">
+        <v>0</v>
+      </c>
+      <c r="G162" t="s">
+        <v>600</v>
+      </c>
+      <c r="H162" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="163" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A163" t="s">
+        <v>601</v>
+      </c>
+      <c r="C163" t="s">
+        <v>74</v>
+      </c>
+      <c r="D163" t="s">
+        <v>602</v>
+      </c>
+      <c r="E163" t="s">
+        <v>603</v>
+      </c>
+      <c r="F163" t="s">
+        <v>604</v>
+      </c>
+      <c r="G163" t="s">
+        <v>605</v>
+      </c>
+      <c r="H163" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="164" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A164" t="s">
+        <v>606</v>
+      </c>
+      <c r="C164" t="s">
+        <v>2</v>
+      </c>
+      <c r="D164" t="s">
+        <v>607</v>
+      </c>
+      <c r="E164" t="s">
+        <v>161</v>
+      </c>
+      <c r="F164" t="s">
+        <v>162</v>
+      </c>
+      <c r="G164" t="s">
+        <v>608</v>
+      </c>
+      <c r="H164" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="165" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A165" t="s">
+        <v>609</v>
+      </c>
+      <c r="C165" t="s">
+        <v>33</v>
+      </c>
+      <c r="D165" t="s">
+        <v>610</v>
+      </c>
+      <c r="E165" t="s">
+        <v>611</v>
+      </c>
+      <c r="F165" t="s">
+        <v>0</v>
+      </c>
+      <c r="G165" t="s">
+        <v>612</v>
+      </c>
+      <c r="H165" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="166" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A166" t="s">
+        <v>613</v>
+      </c>
+      <c r="C166" t="s">
+        <v>29</v>
+      </c>
+      <c r="D166" t="s">
+        <v>614</v>
+      </c>
+      <c r="E166" t="s">
+        <v>45</v>
+      </c>
+      <c r="F166" t="s">
+        <v>0</v>
+      </c>
+      <c r="G166" t="s">
+        <v>61</v>
+      </c>
+      <c r="H166" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="167" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A167" t="s">
+        <v>615</v>
+      </c>
+      <c r="C167" t="s">
+        <v>81</v>
+      </c>
+      <c r="D167" t="s">
+        <v>616</v>
+      </c>
+      <c r="E167" t="s">
+        <v>273</v>
+      </c>
+      <c r="F167" t="s">
+        <v>617</v>
+      </c>
+      <c r="G167" t="s">
+        <v>618</v>
+      </c>
+      <c r="H167" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="168" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A168" t="s">
+        <v>619</v>
+      </c>
+      <c r="C168" t="s">
+        <v>77</v>
+      </c>
+      <c r="D168" t="s">
+        <v>620</v>
+      </c>
+      <c r="E168" t="s">
+        <v>86</v>
+      </c>
+      <c r="F168" t="s">
+        <v>87</v>
+      </c>
+      <c r="G168" t="s">
+        <v>621</v>
+      </c>
+      <c r="H168" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="169" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A169" t="s">
+        <v>622</v>
+      </c>
+      <c r="C169" t="s">
+        <v>74</v>
+      </c>
+      <c r="D169" t="s">
+        <v>623</v>
+      </c>
+      <c r="E169" t="s">
+        <v>65</v>
+      </c>
+      <c r="F169" t="s">
+        <v>66</v>
+      </c>
+      <c r="G169" t="s">
+        <v>624</v>
+      </c>
+      <c r="H169" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="170" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A170" t="s">
+        <v>625</v>
+      </c>
+      <c r="C170" t="s">
+        <v>67</v>
+      </c>
+      <c r="D170" t="s">
+        <v>626</v>
+      </c>
+      <c r="E170" t="s">
+        <v>116</v>
+      </c>
+      <c r="F170" t="s">
+        <v>0</v>
+      </c>
+      <c r="G170" t="s">
+        <v>307</v>
+      </c>
+      <c r="H170" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="171" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A171" t="s">
+        <v>627</v>
+      </c>
+      <c r="C171" t="s">
+        <v>81</v>
+      </c>
+      <c r="D171" t="s">
+        <v>628</v>
+      </c>
+      <c r="E171" t="s">
+        <v>629</v>
+      </c>
+      <c r="F171" t="s">
+        <v>630</v>
+      </c>
+      <c r="G171" t="s">
+        <v>631</v>
+      </c>
+      <c r="H171" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="172" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A172" t="s">
+        <v>632</v>
+      </c>
+      <c r="C172" t="s">
+        <v>81</v>
+      </c>
+      <c r="D172" t="s">
+        <v>628</v>
+      </c>
+      <c r="E172" t="s">
+        <v>629</v>
+      </c>
+      <c r="F172" t="s">
+        <v>630</v>
+      </c>
+      <c r="G172" t="s">
+        <v>631</v>
+      </c>
+      <c r="H172" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="173" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A173" t="s">
+        <v>633</v>
+      </c>
+      <c r="C173" t="s">
+        <v>26</v>
+      </c>
+      <c r="D173" t="s">
+        <v>634</v>
+      </c>
+      <c r="E173" t="s">
+        <v>411</v>
+      </c>
+      <c r="F173" t="s">
+        <v>0</v>
+      </c>
+      <c r="G173" t="s">
+        <v>635</v>
+      </c>
+      <c r="H173" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="174" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A174" t="s">
+        <v>636</v>
+      </c>
+      <c r="C174" t="s">
+        <v>81</v>
+      </c>
+      <c r="D174" t="s">
+        <v>637</v>
+      </c>
+      <c r="E174" t="s">
+        <v>219</v>
+      </c>
+      <c r="F174" t="s">
+        <v>0</v>
+      </c>
+      <c r="G174" t="s">
+        <v>220</v>
+      </c>
+      <c r="H174" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="175" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A175" t="s">
+        <v>638</v>
+      </c>
+      <c r="C175" t="s">
+        <v>2</v>
+      </c>
+      <c r="D175" t="s">
+        <v>639</v>
+      </c>
+      <c r="E175" t="s">
+        <v>640</v>
+      </c>
+      <c r="F175" t="s">
+        <v>0</v>
+      </c>
+      <c r="G175" t="s">
+        <v>641</v>
+      </c>
+      <c r="H175" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="176" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A176" t="s">
+        <v>642</v>
+      </c>
+      <c r="C176" t="s">
+        <v>177</v>
+      </c>
+      <c r="D176" t="s">
+        <v>643</v>
+      </c>
+      <c r="E176" t="s">
+        <v>644</v>
+      </c>
+      <c r="F176" t="s">
+        <v>0</v>
+      </c>
+      <c r="G176" t="s">
+        <v>645</v>
+      </c>
+      <c r="H176" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="177" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A177" t="s">
+        <v>646</v>
+      </c>
+      <c r="C177" t="s">
+        <v>81</v>
+      </c>
+      <c r="D177" t="s">
+        <v>647</v>
+      </c>
+      <c r="E177" t="s">
+        <v>232</v>
+      </c>
+      <c r="F177" t="s">
+        <v>0</v>
+      </c>
+      <c r="G177" t="s">
+        <v>648</v>
+      </c>
+      <c r="H177" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="178" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A178" t="s">
+        <v>649</v>
+      </c>
+      <c r="C178" t="s">
+        <v>29</v>
+      </c>
+      <c r="D178" t="s">
+        <v>650</v>
+      </c>
+      <c r="E178" t="s">
+        <v>651</v>
+      </c>
+      <c r="F178" t="s">
+        <v>0</v>
+      </c>
+      <c r="G178" t="s">
+        <v>652</v>
+      </c>
+      <c r="H178" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="179" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A179" t="s">
+        <v>653</v>
+      </c>
+      <c r="C179" t="s">
+        <v>7</v>
+      </c>
+      <c r="D179" t="s">
+        <v>654</v>
+      </c>
+      <c r="E179" t="s">
+        <v>88</v>
+      </c>
+      <c r="F179" t="s">
+        <v>0</v>
+      </c>
+      <c r="G179" t="s">
+        <v>655</v>
+      </c>
+      <c r="H179" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="180" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A180" t="s">
+        <v>656</v>
+      </c>
+      <c r="C180" t="s">
+        <v>77</v>
+      </c>
+      <c r="D180" t="s">
+        <v>657</v>
+      </c>
+      <c r="E180" t="s">
+        <v>658</v>
+      </c>
+      <c r="F180" t="s">
+        <v>659</v>
+      </c>
+      <c r="G180" t="s">
+        <v>660</v>
+      </c>
+      <c r="H180" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="181" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A181" t="s">
+        <v>661</v>
+      </c>
+      <c r="C181" t="s">
+        <v>17</v>
+      </c>
+      <c r="D181" t="s">
+        <v>662</v>
+      </c>
+      <c r="E181" t="s">
+        <v>663</v>
+      </c>
+      <c r="F181" t="s">
+        <v>0</v>
+      </c>
+      <c r="G181" t="s">
+        <v>664</v>
+      </c>
+      <c r="H181" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="182" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A182" t="s">
+        <v>665</v>
+      </c>
+      <c r="C182" t="s">
+        <v>17</v>
+      </c>
+      <c r="D182" t="s">
+        <v>662</v>
+      </c>
+      <c r="E182" t="s">
+        <v>663</v>
+      </c>
+      <c r="F182" t="s">
+        <v>0</v>
+      </c>
+      <c r="G182" t="s">
+        <v>664</v>
+      </c>
+      <c r="H182" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="183" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A183" t="s">
+        <v>666</v>
+      </c>
+      <c r="C183" t="s">
+        <v>25</v>
+      </c>
+      <c r="D183" t="s">
+        <v>667</v>
+      </c>
+      <c r="E183" t="s">
+        <v>668</v>
+      </c>
+      <c r="F183" t="s">
+        <v>669</v>
+      </c>
+      <c r="G183" t="s">
+        <v>670</v>
+      </c>
+      <c r="H183" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="184" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A184" t="s">
+        <v>671</v>
+      </c>
+      <c r="C184" t="s">
+        <v>21</v>
+      </c>
+      <c r="D184" t="s">
+        <v>672</v>
+      </c>
+      <c r="E184" t="s">
+        <v>673</v>
+      </c>
+      <c r="F184" t="s">
+        <v>0</v>
+      </c>
+      <c r="G184" t="s">
+        <v>674</v>
+      </c>
+      <c r="H184" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="185" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A185" t="s">
+        <v>675</v>
+      </c>
+      <c r="C185" t="s">
+        <v>24</v>
+      </c>
+      <c r="D185" t="s">
+        <v>676</v>
+      </c>
+      <c r="E185" t="s">
+        <v>677</v>
+      </c>
+      <c r="F185" t="s">
+        <v>0</v>
+      </c>
+      <c r="G185" t="s">
+        <v>678</v>
+      </c>
+      <c r="H185" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="186" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A186" t="s">
+        <v>679</v>
+      </c>
+      <c r="C186" t="s">
+        <v>21</v>
+      </c>
+      <c r="D186" t="s">
+        <v>680</v>
+      </c>
+      <c r="E186" t="s">
+        <v>104</v>
+      </c>
+      <c r="F186" t="s">
+        <v>105</v>
+      </c>
+      <c r="G186" t="s">
+        <v>681</v>
+      </c>
+      <c r="H186" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="187" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A187" t="s">
+        <v>682</v>
+      </c>
+      <c r="C187" t="s">
+        <v>2</v>
+      </c>
+      <c r="D187" t="s">
+        <v>683</v>
+      </c>
+      <c r="E187" t="s">
+        <v>640</v>
+      </c>
+      <c r="F187" t="s">
+        <v>0</v>
+      </c>
+      <c r="G187" t="s">
+        <v>641</v>
+      </c>
+      <c r="H187" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="188" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A188" t="s">
+        <v>684</v>
+      </c>
+      <c r="C188" t="s">
+        <v>77</v>
+      </c>
+      <c r="D188" t="s">
+        <v>685</v>
+      </c>
+      <c r="E188" t="s">
+        <v>686</v>
+      </c>
+      <c r="F188" t="s">
+        <v>687</v>
+      </c>
+      <c r="G188" t="s">
+        <v>688</v>
+      </c>
+      <c r="H188" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="189" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A189" t="s">
+        <v>689</v>
+      </c>
+      <c r="C189" t="s">
+        <v>25</v>
+      </c>
+      <c r="D189" t="s">
+        <v>690</v>
+      </c>
+      <c r="E189" t="s">
+        <v>691</v>
+      </c>
+      <c r="F189" t="s">
+        <v>692</v>
+      </c>
+      <c r="G189" t="s">
+        <v>693</v>
+      </c>
+      <c r="H189" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="190" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A190" t="s">
+        <v>694</v>
+      </c>
+      <c r="C190" t="s">
+        <v>5</v>
+      </c>
+      <c r="D190" t="s">
+        <v>695</v>
+      </c>
+      <c r="E190" t="s">
+        <v>696</v>
+      </c>
+      <c r="F190" t="s">
+        <v>697</v>
+      </c>
+      <c r="G190" t="s">
+        <v>117</v>
+      </c>
+      <c r="H190" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="191" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A191" t="s">
+        <v>698</v>
+      </c>
+      <c r="C191" t="s">
+        <v>17</v>
+      </c>
+      <c r="D191" t="s">
+        <v>699</v>
+      </c>
+      <c r="E191" t="s">
+        <v>700</v>
+      </c>
+      <c r="F191" t="s">
+        <v>210</v>
+      </c>
+      <c r="G191" t="s">
+        <v>701</v>
+      </c>
+      <c r="H191" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="192" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A192" t="s">
+        <v>702</v>
+      </c>
+      <c r="C192" t="s">
+        <v>17</v>
+      </c>
+      <c r="D192" t="s">
+        <v>699</v>
+      </c>
+      <c r="E192" t="s">
+        <v>700</v>
+      </c>
+      <c r="F192" t="s">
+        <v>210</v>
+      </c>
+      <c r="G192" t="s">
+        <v>701</v>
+      </c>
+      <c r="H192" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="193" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A193" t="s">
+        <v>703</v>
+      </c>
+      <c r="C193" t="s">
+        <v>29</v>
+      </c>
+      <c r="D193" t="s">
+        <v>704</v>
+      </c>
+      <c r="E193" t="s">
+        <v>60</v>
+      </c>
+      <c r="F193" t="s">
+        <v>0</v>
+      </c>
+      <c r="G193" t="s">
+        <v>75</v>
+      </c>
+      <c r="H193" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="194" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A194" t="s">
+        <v>705</v>
+      </c>
+      <c r="C194" t="s">
+        <v>33</v>
+      </c>
+      <c r="D194" t="s">
+        <v>706</v>
+      </c>
+      <c r="E194" t="s">
+        <v>611</v>
+      </c>
+      <c r="F194" t="s">
+        <v>0</v>
+      </c>
+      <c r="G194" t="s">
+        <v>707</v>
+      </c>
+      <c r="H194" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="195" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A195" t="s">
+        <v>708</v>
+      </c>
+      <c r="C195" t="s">
+        <v>81</v>
+      </c>
+      <c r="D195" t="s">
+        <v>709</v>
+      </c>
+      <c r="E195" t="s">
+        <v>232</v>
+      </c>
+      <c r="F195" t="s">
+        <v>0</v>
+      </c>
+      <c r="G195" t="s">
+        <v>710</v>
+      </c>
+      <c r="H195" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="196" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A196" t="s">
+        <v>711</v>
+      </c>
+      <c r="C196" t="s">
+        <v>24</v>
+      </c>
+      <c r="D196" t="s">
+        <v>712</v>
+      </c>
+      <c r="E196" t="s">
+        <v>83</v>
+      </c>
+      <c r="F196" t="s">
+        <v>0</v>
+      </c>
+      <c r="G196" t="s">
+        <v>486</v>
+      </c>
+      <c r="H196" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="197" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A197" t="s">
+        <v>713</v>
+      </c>
+      <c r="C197" t="s">
+        <v>24</v>
+      </c>
+      <c r="D197" t="s">
+        <v>712</v>
+      </c>
+      <c r="E197" t="s">
+        <v>83</v>
+      </c>
+      <c r="F197" t="s">
+        <v>0</v>
+      </c>
+      <c r="G197" t="s">
+        <v>486</v>
+      </c>
+      <c r="H197" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="198" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A198" t="s">
+        <v>714</v>
+      </c>
+      <c r="C198" t="s">
+        <v>24</v>
+      </c>
+      <c r="D198" t="s">
+        <v>712</v>
+      </c>
+      <c r="E198" t="s">
+        <v>83</v>
+      </c>
+      <c r="F198" t="s">
+        <v>0</v>
+      </c>
+      <c r="G198" t="s">
+        <v>486</v>
+      </c>
+      <c r="H198" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="199" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A199" t="s">
+        <v>715</v>
+      </c>
+      <c r="C199" t="s">
+        <v>24</v>
+      </c>
+      <c r="D199" t="s">
+        <v>712</v>
+      </c>
+      <c r="E199" t="s">
+        <v>83</v>
+      </c>
+      <c r="F199" t="s">
+        <v>0</v>
+      </c>
+      <c r="G199" t="s">
+        <v>486</v>
+      </c>
+      <c r="H199" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="200" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A200" t="s">
+        <v>716</v>
+      </c>
+      <c r="C200" t="s">
+        <v>24</v>
+      </c>
+      <c r="D200" t="s">
+        <v>712</v>
+      </c>
+      <c r="E200" t="s">
+        <v>83</v>
+      </c>
+      <c r="F200" t="s">
+        <v>0</v>
+      </c>
+      <c r="G200" t="s">
+        <v>486</v>
+      </c>
+      <c r="H200" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="201" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A201" t="s">
+        <v>717</v>
+      </c>
+      <c r="C201" t="s">
+        <v>2</v>
+      </c>
+      <c r="D201" t="s">
+        <v>718</v>
+      </c>
+      <c r="E201" t="s">
+        <v>161</v>
+      </c>
+      <c r="F201" t="s">
+        <v>162</v>
+      </c>
+      <c r="G201" t="s">
+        <v>719</v>
+      </c>
+      <c r="H201" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="202" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A202" t="s">
+        <v>720</v>
+      </c>
+      <c r="C202" t="s">
+        <v>2</v>
+      </c>
+      <c r="D202" t="s">
+        <v>718</v>
+      </c>
+      <c r="E202" t="s">
+        <v>161</v>
+      </c>
+      <c r="F202" t="s">
+        <v>162</v>
+      </c>
+      <c r="G202" t="s">
+        <v>719</v>
+      </c>
+      <c r="H202" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="203" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A203" t="s">
+        <v>721</v>
+      </c>
+      <c r="C203" t="s">
+        <v>2</v>
+      </c>
+      <c r="D203" t="s">
+        <v>718</v>
+      </c>
+      <c r="E203" t="s">
+        <v>161</v>
+      </c>
+      <c r="F203" t="s">
+        <v>162</v>
+      </c>
+      <c r="G203" t="s">
+        <v>719</v>
+      </c>
+      <c r="H203" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="204" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A204" t="s">
+        <v>722</v>
+      </c>
+      <c r="C204" t="s">
+        <v>2</v>
+      </c>
+      <c r="D204" t="s">
+        <v>718</v>
+      </c>
+      <c r="E204" t="s">
+        <v>161</v>
+      </c>
+      <c r="F204" t="s">
+        <v>162</v>
+      </c>
+      <c r="G204" t="s">
+        <v>719</v>
+      </c>
+      <c r="H204" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="205" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A205" t="s">
+        <v>723</v>
+      </c>
+      <c r="C205" t="s">
+        <v>26</v>
+      </c>
+      <c r="D205" t="s">
+        <v>724</v>
+      </c>
+      <c r="E205" t="s">
+        <v>576</v>
+      </c>
+      <c r="F205" t="s">
+        <v>577</v>
+      </c>
+      <c r="G205" t="s">
+        <v>725</v>
+      </c>
+      <c r="H205" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="206" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A206" t="s">
+        <v>726</v>
+      </c>
+      <c r="C206" t="s">
+        <v>25</v>
+      </c>
+      <c r="D206" t="s">
+        <v>727</v>
+      </c>
+      <c r="E206" t="s">
+        <v>140</v>
+      </c>
+      <c r="F206" t="s">
+        <v>141</v>
+      </c>
+      <c r="G206" t="s">
+        <v>728</v>
+      </c>
+      <c r="H206" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="207" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A207" t="s">
+        <v>729</v>
+      </c>
+      <c r="C207" t="s">
+        <v>2</v>
+      </c>
+      <c r="D207" t="s">
+        <v>730</v>
+      </c>
+      <c r="E207" t="s">
+        <v>731</v>
+      </c>
+      <c r="F207" t="s">
+        <v>0</v>
+      </c>
+      <c r="G207" t="s">
+        <v>732</v>
+      </c>
+      <c r="H207" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="208" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A208" t="s">
+        <v>733</v>
+      </c>
+      <c r="C208" t="s">
+        <v>29</v>
+      </c>
+      <c r="D208" t="s">
+        <v>734</v>
+      </c>
+      <c r="E208" t="s">
+        <v>35</v>
+      </c>
+      <c r="F208" t="s">
+        <v>0</v>
+      </c>
+      <c r="G208" t="s">
+        <v>735</v>
+      </c>
+      <c r="H208" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="209" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A209" t="s">
+        <v>736</v>
+      </c>
+      <c r="C209" t="s">
+        <v>29</v>
+      </c>
+      <c r="D209" t="s">
+        <v>737</v>
+      </c>
+      <c r="E209" t="s">
+        <v>455</v>
+      </c>
+      <c r="F209" t="s">
+        <v>0</v>
+      </c>
+      <c r="G209" t="s">
+        <v>738</v>
+      </c>
+      <c r="H209" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="210" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A210" t="s">
+        <v>739</v>
+      </c>
+      <c r="C210" t="s">
+        <v>7</v>
+      </c>
+      <c r="D210" t="s">
+        <v>740</v>
+      </c>
+      <c r="E210" t="s">
+        <v>32</v>
+      </c>
+      <c r="F210" t="s">
+        <v>0</v>
+      </c>
+      <c r="G210" t="s">
+        <v>741</v>
+      </c>
+      <c r="H210" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="211" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A211" t="s">
+        <v>742</v>
+      </c>
+      <c r="C211" t="s">
+        <v>74</v>
+      </c>
+      <c r="D211" t="s">
+        <v>743</v>
+      </c>
+      <c r="E211" t="s">
+        <v>65</v>
+      </c>
+      <c r="F211" t="s">
+        <v>66</v>
+      </c>
+      <c r="G211" t="s">
+        <v>744</v>
+      </c>
+      <c r="H211" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="212" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A212" t="s">
+        <v>745</v>
+      </c>
+      <c r="C212" t="s">
+        <v>7</v>
+      </c>
+      <c r="D212" t="s">
+        <v>746</v>
+      </c>
+      <c r="E212" t="s">
+        <v>747</v>
+      </c>
+      <c r="F212" t="s">
+        <v>0</v>
+      </c>
+      <c r="G212" t="s">
+        <v>748</v>
+      </c>
+      <c r="H212" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="213" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A213" t="s">
+        <v>749</v>
+      </c>
+      <c r="C213" t="s">
+        <v>7</v>
+      </c>
+      <c r="D213" t="s">
+        <v>746</v>
+      </c>
+      <c r="E213" t="s">
+        <v>747</v>
+      </c>
+      <c r="F213" t="s">
+        <v>0</v>
+      </c>
+      <c r="G213" t="s">
+        <v>748</v>
+      </c>
+      <c r="H213" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="214" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A214" t="s">
+        <v>750</v>
+      </c>
+      <c r="C214" t="s">
+        <v>7</v>
+      </c>
+      <c r="D214" t="s">
+        <v>751</v>
+      </c>
+      <c r="E214" t="s">
+        <v>88</v>
+      </c>
+      <c r="F214" t="s">
+        <v>0</v>
+      </c>
+      <c r="G214" t="s">
+        <v>108</v>
+      </c>
+      <c r="H214" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="215" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A215" t="s">
+        <v>752</v>
+      </c>
+      <c r="C215" t="s">
+        <v>7</v>
+      </c>
+      <c r="D215" t="s">
+        <v>751</v>
+      </c>
+      <c r="E215" t="s">
+        <v>88</v>
+      </c>
+      <c r="F215" t="s">
+        <v>0</v>
+      </c>
+      <c r="G215" t="s">
+        <v>108</v>
+      </c>
+      <c r="H215" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="216" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A216" t="s">
+        <v>753</v>
+      </c>
+      <c r="C216" t="s">
+        <v>7</v>
+      </c>
+      <c r="D216" t="s">
+        <v>751</v>
+      </c>
+      <c r="E216" t="s">
+        <v>88</v>
+      </c>
+      <c r="F216" t="s">
+        <v>0</v>
+      </c>
+      <c r="G216" t="s">
+        <v>108</v>
+      </c>
+      <c r="H216" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="217" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A217" t="s">
+        <v>754</v>
+      </c>
+      <c r="C217" t="s">
+        <v>7</v>
+      </c>
+      <c r="D217" t="s">
+        <v>751</v>
+      </c>
+      <c r="E217" t="s">
+        <v>88</v>
+      </c>
+      <c r="F217" t="s">
+        <v>0</v>
+      </c>
+      <c r="G217" t="s">
+        <v>108</v>
+      </c>
+      <c r="H217" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="218" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A218" t="s">
+        <v>755</v>
+      </c>
+      <c r="C218" t="s">
+        <v>5</v>
+      </c>
+      <c r="D218" t="s">
+        <v>756</v>
+      </c>
+      <c r="E218" t="s">
+        <v>22</v>
+      </c>
+      <c r="F218" t="s">
+        <v>23</v>
+      </c>
+      <c r="G218" t="s">
+        <v>757</v>
+      </c>
+      <c r="H218" t="s">
+        <v>758</v>
+      </c>
+    </row>
+    <row r="219" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A219" t="s">
+        <v>759</v>
+      </c>
+      <c r="C219" t="s">
+        <v>5</v>
+      </c>
+      <c r="D219" t="s">
+        <v>756</v>
+      </c>
+      <c r="E219" t="s">
+        <v>22</v>
+      </c>
+      <c r="F219" t="s">
+        <v>23</v>
+      </c>
+      <c r="G219" t="s">
+        <v>757</v>
+      </c>
+      <c r="H219" t="s">
+        <v>758</v>
+      </c>
+    </row>
+    <row r="220" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A220" t="s">
+        <v>760</v>
+      </c>
+      <c r="C220" t="s">
+        <v>5</v>
+      </c>
+      <c r="D220" t="s">
+        <v>756</v>
+      </c>
+      <c r="E220" t="s">
+        <v>22</v>
+      </c>
+      <c r="F220" t="s">
+        <v>23</v>
+      </c>
+      <c r="G220" t="s">
+        <v>757</v>
+      </c>
+      <c r="H220" t="s">
+        <v>758</v>
+      </c>
+    </row>
+    <row r="221" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A221" t="s">
+        <v>761</v>
+      </c>
+      <c r="C221" t="s">
+        <v>5</v>
+      </c>
+      <c r="D221" t="s">
+        <v>756</v>
+      </c>
+      <c r="E221" t="s">
+        <v>22</v>
+      </c>
+      <c r="F221" t="s">
+        <v>23</v>
+      </c>
+      <c r="G221" t="s">
+        <v>757</v>
+      </c>
+      <c r="H221" t="s">
+        <v>758</v>
+      </c>
+    </row>
+    <row r="222" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A222" t="s">
+        <v>762</v>
+      </c>
+      <c r="C222" t="s">
+        <v>5</v>
+      </c>
+      <c r="D222" t="s">
+        <v>756</v>
+      </c>
+      <c r="E222" t="s">
+        <v>22</v>
+      </c>
+      <c r="F222" t="s">
+        <v>23</v>
+      </c>
+      <c r="G222" t="s">
+        <v>757</v>
+      </c>
+      <c r="H222" t="s">
+        <v>758</v>
+      </c>
+    </row>
+    <row r="223" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A223" t="s">
+        <v>763</v>
+      </c>
+      <c r="C223" t="s">
+        <v>27</v>
+      </c>
+      <c r="D223" t="s">
+        <v>764</v>
+      </c>
+      <c r="E223" t="s">
+        <v>128</v>
+      </c>
+      <c r="F223" t="s">
+        <v>129</v>
+      </c>
+      <c r="G223" t="s">
+        <v>765</v>
+      </c>
+      <c r="H223" t="s">
+        <v>758</v>
+      </c>
+    </row>
+    <row r="224" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A224" t="s">
+        <v>766</v>
+      </c>
+      <c r="C224" t="s">
+        <v>24</v>
+      </c>
+      <c r="D224" t="s">
+        <v>767</v>
+      </c>
+      <c r="E224" t="s">
+        <v>101</v>
+      </c>
+      <c r="F224" t="s">
+        <v>0</v>
+      </c>
+      <c r="G224" t="s">
+        <v>768</v>
+      </c>
+      <c r="H224" t="s">
+        <v>769</v>
+      </c>
+    </row>
+    <row r="225" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A225" t="s">
+        <v>770</v>
+      </c>
+      <c r="C225" t="s">
+        <v>24</v>
+      </c>
+      <c r="D225" t="s">
+        <v>767</v>
+      </c>
+      <c r="E225" t="s">
+        <v>101</v>
+      </c>
+      <c r="F225" t="s">
+        <v>0</v>
+      </c>
+      <c r="G225" t="s">
+        <v>768</v>
+      </c>
+      <c r="H225" t="s">
+        <v>769</v>
       </c>
     </row>
   </sheetData>

--- a/1.xlsx
+++ b/1.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="\\wh.local\fs\UserProfile_TSSWH19\_TSSWH19_redirected_folders\HunyaCs1\Desktop\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{69AFBB93-F62C-40D9-8B07-81D021D7CEA8}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CFB27933-7F76-4466-B885-A62576A105C5}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="0" windowWidth="22260" windowHeight="12648" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1575" uniqueCount="771">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1554" uniqueCount="761">
   <si>
     <t>BUDAPEST</t>
   </si>
@@ -126,9 +126,6 @@
     <t>1181</t>
   </si>
   <si>
-    <t>1204</t>
-  </si>
-  <si>
     <t>SZ-835</t>
   </si>
   <si>
@@ -2227,33 +2224,6 @@
   </si>
   <si>
     <t>Páskomliget utca</t>
-  </si>
-  <si>
-    <t>NFD6-04-13-YYWP-1</t>
-  </si>
-  <si>
-    <t>NFD6-04-13-YYWP</t>
-  </si>
-  <si>
-    <t>Kapisztrán utca</t>
-  </si>
-  <si>
-    <t>NFD6-04-14-8VL5-1</t>
-  </si>
-  <si>
-    <t>NFD6-04-14-8VL5</t>
-  </si>
-  <si>
-    <t>Tétényi út</t>
-  </si>
-  <si>
-    <t>NFD6-04-14-JTNX-1</t>
-  </si>
-  <si>
-    <t>NFD6-04-14-JTNX</t>
-  </si>
-  <si>
-    <t>Eperjes utca</t>
   </si>
   <si>
     <t>202604102600830801</t>
@@ -2659,7 +2629,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <sheetPr codeName="Munka1"/>
-  <dimension ref="A1:H225"/>
+  <dimension ref="A1:H222"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="24.88671875" bestFit="1" customWidth="1"/>
@@ -2697,45 +2667,45 @@
     </row>
     <row r="2" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="C2" t="s">
         <v>21</v>
       </c>
       <c r="D2" t="s">
+        <v>118</v>
+      </c>
+      <c r="E2" t="s">
+        <v>103</v>
+      </c>
+      <c r="F2" t="s">
+        <v>104</v>
+      </c>
+      <c r="G2" t="s">
+        <v>84</v>
+      </c>
+      <c r="H2" t="s">
         <v>119</v>
-      </c>
-      <c r="E2" t="s">
-        <v>104</v>
-      </c>
-      <c r="F2" t="s">
-        <v>105</v>
-      </c>
-      <c r="G2" t="s">
-        <v>85</v>
-      </c>
-      <c r="H2" t="s">
-        <v>120</v>
       </c>
     </row>
     <row r="3" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="C3" t="s">
         <v>5</v>
       </c>
       <c r="D3" t="s">
+        <v>121</v>
+      </c>
+      <c r="E3" t="s">
         <v>122</v>
       </c>
-      <c r="E3" t="s">
+      <c r="F3" t="s">
         <v>123</v>
       </c>
-      <c r="F3" t="s">
+      <c r="G3" t="s">
         <v>124</v>
-      </c>
-      <c r="G3" t="s">
-        <v>125</v>
       </c>
       <c r="H3" t="s">
         <v>3</v>
@@ -2743,22 +2713,22 @@
     </row>
     <row r="4" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="C4" t="s">
         <v>27</v>
       </c>
       <c r="D4" t="s">
+        <v>126</v>
+      </c>
+      <c r="E4" t="s">
         <v>127</v>
       </c>
-      <c r="E4" t="s">
+      <c r="F4" t="s">
         <v>128</v>
       </c>
-      <c r="F4" t="s">
+      <c r="G4" t="s">
         <v>129</v>
-      </c>
-      <c r="G4" t="s">
-        <v>130</v>
       </c>
       <c r="H4" t="s">
         <v>1</v>
@@ -2766,22 +2736,22 @@
     </row>
     <row r="5" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="C5" t="s">
         <v>18</v>
       </c>
       <c r="D5" t="s">
+        <v>131</v>
+      </c>
+      <c r="E5" t="s">
+        <v>51</v>
+      </c>
+      <c r="F5" t="s">
+        <v>0</v>
+      </c>
+      <c r="G5" t="s">
         <v>132</v>
-      </c>
-      <c r="E5" t="s">
-        <v>52</v>
-      </c>
-      <c r="F5" t="s">
-        <v>0</v>
-      </c>
-      <c r="G5" t="s">
-        <v>133</v>
       </c>
       <c r="H5" t="s">
         <v>1</v>
@@ -2789,22 +2759,22 @@
     </row>
     <row r="6" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="C6" t="s">
         <v>27</v>
       </c>
       <c r="D6" t="s">
+        <v>134</v>
+      </c>
+      <c r="E6" t="s">
         <v>135</v>
       </c>
-      <c r="E6" t="s">
+      <c r="F6" t="s">
+        <v>0</v>
+      </c>
+      <c r="G6" t="s">
         <v>136</v>
-      </c>
-      <c r="F6" t="s">
-        <v>0</v>
-      </c>
-      <c r="G6" t="s">
-        <v>137</v>
       </c>
       <c r="H6" t="s">
         <v>1</v>
@@ -2812,22 +2782,22 @@
     </row>
     <row r="7" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="C7" t="s">
         <v>25</v>
       </c>
       <c r="D7" t="s">
+        <v>138</v>
+      </c>
+      <c r="E7" t="s">
         <v>139</v>
       </c>
-      <c r="E7" t="s">
+      <c r="F7" t="s">
         <v>140</v>
       </c>
-      <c r="F7" t="s">
+      <c r="G7" t="s">
         <v>141</v>
-      </c>
-      <c r="G7" t="s">
-        <v>142</v>
       </c>
       <c r="H7" t="s">
         <v>1</v>
@@ -2835,22 +2805,22 @@
     </row>
     <row r="8" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
+        <v>142</v>
+      </c>
+      <c r="C8" t="s">
+        <v>73</v>
+      </c>
+      <c r="D8" t="s">
         <v>143</v>
       </c>
-      <c r="C8" t="s">
-        <v>74</v>
-      </c>
-      <c r="D8" t="s">
+      <c r="E8" t="s">
         <v>144</v>
       </c>
-      <c r="E8" t="s">
+      <c r="F8" t="s">
         <v>145</v>
       </c>
-      <c r="F8" t="s">
+      <c r="G8" t="s">
         <v>146</v>
-      </c>
-      <c r="G8" t="s">
-        <v>147</v>
       </c>
       <c r="H8" t="s">
         <v>1</v>
@@ -2858,22 +2828,22 @@
     </row>
     <row r="9" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="C9" t="s">
         <v>25</v>
       </c>
       <c r="D9" t="s">
+        <v>71</v>
+      </c>
+      <c r="E9" t="s">
+        <v>56</v>
+      </c>
+      <c r="F9" t="s">
+        <v>0</v>
+      </c>
+      <c r="G9" t="s">
         <v>72</v>
-      </c>
-      <c r="E9" t="s">
-        <v>57</v>
-      </c>
-      <c r="F9" t="s">
-        <v>0</v>
-      </c>
-      <c r="G9" t="s">
-        <v>73</v>
       </c>
       <c r="H9" t="s">
         <v>1</v>
@@ -2881,22 +2851,22 @@
     </row>
     <row r="10" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
+        <v>147</v>
+      </c>
+      <c r="C10" t="s">
         <v>148</v>
       </c>
-      <c r="C10" t="s">
+      <c r="D10" t="s">
         <v>149</v>
       </c>
-      <c r="D10" t="s">
+      <c r="E10" t="s">
         <v>150</v>
       </c>
-      <c r="E10" t="s">
+      <c r="F10" t="s">
         <v>151</v>
       </c>
-      <c r="F10" t="s">
+      <c r="G10" t="s">
         <v>152</v>
-      </c>
-      <c r="G10" t="s">
-        <v>153</v>
       </c>
       <c r="H10" t="s">
         <v>1</v>
@@ -2904,22 +2874,22 @@
     </row>
     <row r="11" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A11" t="s">
+        <v>153</v>
+      </c>
+      <c r="C11" t="s">
+        <v>148</v>
+      </c>
+      <c r="D11" t="s">
         <v>154</v>
       </c>
-      <c r="C11" t="s">
-        <v>149</v>
-      </c>
-      <c r="D11" t="s">
+      <c r="E11" t="s">
         <v>155</v>
       </c>
-      <c r="E11" t="s">
+      <c r="F11" t="s">
         <v>156</v>
       </c>
-      <c r="F11" t="s">
+      <c r="G11" t="s">
         <v>157</v>
-      </c>
-      <c r="G11" t="s">
-        <v>158</v>
       </c>
       <c r="H11" t="s">
         <v>1</v>
@@ -2927,22 +2897,22 @@
     </row>
     <row r="12" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A12" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="C12" t="s">
         <v>2</v>
       </c>
       <c r="D12" t="s">
+        <v>159</v>
+      </c>
+      <c r="E12" t="s">
         <v>160</v>
       </c>
-      <c r="E12" t="s">
+      <c r="F12" t="s">
         <v>161</v>
       </c>
-      <c r="F12" t="s">
+      <c r="G12" t="s">
         <v>162</v>
-      </c>
-      <c r="G12" t="s">
-        <v>163</v>
       </c>
       <c r="H12" t="s">
         <v>1</v>
@@ -2950,22 +2920,22 @@
     </row>
     <row r="13" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A13" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="C13" t="s">
         <v>2</v>
       </c>
       <c r="D13" t="s">
+        <v>159</v>
+      </c>
+      <c r="E13" t="s">
         <v>160</v>
       </c>
-      <c r="E13" t="s">
+      <c r="F13" t="s">
         <v>161</v>
       </c>
-      <c r="F13" t="s">
+      <c r="G13" t="s">
         <v>162</v>
-      </c>
-      <c r="G13" t="s">
-        <v>163</v>
       </c>
       <c r="H13" t="s">
         <v>1</v>
@@ -2973,22 +2943,22 @@
     </row>
     <row r="14" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A14" t="s">
+        <v>164</v>
+      </c>
+      <c r="C14" t="s">
+        <v>148</v>
+      </c>
+      <c r="D14" t="s">
         <v>165</v>
       </c>
-      <c r="C14" t="s">
-        <v>149</v>
-      </c>
-      <c r="D14" t="s">
+      <c r="E14" t="s">
+        <v>155</v>
+      </c>
+      <c r="F14" t="s">
+        <v>156</v>
+      </c>
+      <c r="G14" t="s">
         <v>166</v>
-      </c>
-      <c r="E14" t="s">
-        <v>156</v>
-      </c>
-      <c r="F14" t="s">
-        <v>157</v>
-      </c>
-      <c r="G14" t="s">
-        <v>167</v>
       </c>
       <c r="H14" t="s">
         <v>1</v>
@@ -2996,13 +2966,13 @@
     </row>
     <row r="15" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A15" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="C15" t="s">
         <v>5</v>
       </c>
       <c r="D15" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="E15" t="s">
         <v>8</v>
@@ -3011,7 +2981,7 @@
         <v>9</v>
       </c>
       <c r="G15" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="H15" t="s">
         <v>1</v>
@@ -3019,22 +2989,22 @@
     </row>
     <row r="16" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A16" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="C16" t="s">
         <v>21</v>
       </c>
       <c r="D16" t="s">
+        <v>171</v>
+      </c>
+      <c r="E16" t="s">
         <v>172</v>
       </c>
-      <c r="E16" t="s">
+      <c r="F16" t="s">
         <v>173</v>
       </c>
-      <c r="F16" t="s">
+      <c r="G16" t="s">
         <v>174</v>
-      </c>
-      <c r="G16" t="s">
-        <v>175</v>
       </c>
       <c r="H16" t="s">
         <v>1</v>
@@ -3042,22 +3012,22 @@
     </row>
     <row r="17" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A17" t="s">
+        <v>175</v>
+      </c>
+      <c r="C17" t="s">
         <v>176</v>
       </c>
-      <c r="C17" t="s">
+      <c r="D17" t="s">
         <v>177</v>
       </c>
-      <c r="D17" t="s">
+      <c r="E17" t="s">
         <v>178</v>
       </c>
-      <c r="E17" t="s">
+      <c r="F17" t="s">
         <v>179</v>
       </c>
-      <c r="F17" t="s">
+      <c r="G17" t="s">
         <v>180</v>
-      </c>
-      <c r="G17" t="s">
-        <v>181</v>
       </c>
       <c r="H17" t="s">
         <v>1</v>
@@ -3065,22 +3035,22 @@
     </row>
     <row r="18" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A18" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="C18" t="s">
+        <v>176</v>
+      </c>
+      <c r="D18" t="s">
         <v>177</v>
       </c>
-      <c r="D18" t="s">
+      <c r="E18" t="s">
         <v>178</v>
       </c>
-      <c r="E18" t="s">
+      <c r="F18" t="s">
         <v>179</v>
       </c>
-      <c r="F18" t="s">
+      <c r="G18" t="s">
         <v>180</v>
-      </c>
-      <c r="G18" t="s">
-        <v>181</v>
       </c>
       <c r="H18" t="s">
         <v>1</v>
@@ -3088,22 +3058,22 @@
     </row>
     <row r="19" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A19" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="C19" t="s">
+        <v>176</v>
+      </c>
+      <c r="D19" t="s">
         <v>177</v>
       </c>
-      <c r="D19" t="s">
+      <c r="E19" t="s">
         <v>178</v>
       </c>
-      <c r="E19" t="s">
+      <c r="F19" t="s">
         <v>179</v>
       </c>
-      <c r="F19" t="s">
+      <c r="G19" t="s">
         <v>180</v>
-      </c>
-      <c r="G19" t="s">
-        <v>181</v>
       </c>
       <c r="H19" t="s">
         <v>1</v>
@@ -3111,22 +3081,22 @@
     </row>
     <row r="20" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A20" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="C20" t="s">
         <v>18</v>
       </c>
       <c r="D20" t="s">
+        <v>184</v>
+      </c>
+      <c r="E20" t="s">
         <v>185</v>
       </c>
-      <c r="E20" t="s">
+      <c r="F20" t="s">
+        <v>0</v>
+      </c>
+      <c r="G20" t="s">
         <v>186</v>
-      </c>
-      <c r="F20" t="s">
-        <v>0</v>
-      </c>
-      <c r="G20" t="s">
-        <v>187</v>
       </c>
       <c r="H20" t="s">
         <v>1</v>
@@ -3134,22 +3104,22 @@
     </row>
     <row r="21" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A21" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="C21" t="s">
         <v>21</v>
       </c>
       <c r="D21" t="s">
+        <v>188</v>
+      </c>
+      <c r="E21" t="s">
+        <v>45</v>
+      </c>
+      <c r="F21" t="s">
+        <v>39</v>
+      </c>
+      <c r="G21" t="s">
         <v>189</v>
-      </c>
-      <c r="E21" t="s">
-        <v>46</v>
-      </c>
-      <c r="F21" t="s">
-        <v>40</v>
-      </c>
-      <c r="G21" t="s">
-        <v>190</v>
       </c>
       <c r="H21" t="s">
         <v>1</v>
@@ -3157,22 +3127,22 @@
     </row>
     <row r="22" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A22" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="C22" t="s">
         <v>21</v>
       </c>
       <c r="D22" t="s">
+        <v>188</v>
+      </c>
+      <c r="E22" t="s">
+        <v>45</v>
+      </c>
+      <c r="F22" t="s">
+        <v>39</v>
+      </c>
+      <c r="G22" t="s">
         <v>189</v>
-      </c>
-      <c r="E22" t="s">
-        <v>46</v>
-      </c>
-      <c r="F22" t="s">
-        <v>40</v>
-      </c>
-      <c r="G22" t="s">
-        <v>190</v>
       </c>
       <c r="H22" t="s">
         <v>1</v>
@@ -3180,22 +3150,22 @@
     </row>
     <row r="23" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A23" t="s">
+        <v>191</v>
+      </c>
+      <c r="C23" t="s">
+        <v>75</v>
+      </c>
+      <c r="D23" t="s">
         <v>192</v>
       </c>
-      <c r="C23" t="s">
-        <v>76</v>
-      </c>
-      <c r="D23" t="s">
+      <c r="E23" t="s">
         <v>193</v>
       </c>
-      <c r="E23" t="s">
+      <c r="F23" t="s">
+        <v>0</v>
+      </c>
+      <c r="G23" t="s">
         <v>194</v>
-      </c>
-      <c r="F23" t="s">
-        <v>0</v>
-      </c>
-      <c r="G23" t="s">
-        <v>195</v>
       </c>
       <c r="H23" t="s">
         <v>1</v>
@@ -3203,22 +3173,22 @@
     </row>
     <row r="24" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A24" t="s">
+        <v>195</v>
+      </c>
+      <c r="C24" t="s">
+        <v>148</v>
+      </c>
+      <c r="D24" t="s">
         <v>196</v>
       </c>
-      <c r="C24" t="s">
-        <v>149</v>
-      </c>
-      <c r="D24" t="s">
+      <c r="E24" t="s">
         <v>197</v>
       </c>
-      <c r="E24" t="s">
+      <c r="F24" t="s">
         <v>198</v>
       </c>
-      <c r="F24" t="s">
+      <c r="G24" t="s">
         <v>199</v>
-      </c>
-      <c r="G24" t="s">
-        <v>200</v>
       </c>
       <c r="H24" t="s">
         <v>1</v>
@@ -3226,22 +3196,22 @@
     </row>
     <row r="25" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A25" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="C25" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="D25" t="s">
+        <v>196</v>
+      </c>
+      <c r="E25" t="s">
         <v>197</v>
       </c>
-      <c r="E25" t="s">
+      <c r="F25" t="s">
         <v>198</v>
       </c>
-      <c r="F25" t="s">
+      <c r="G25" t="s">
         <v>199</v>
-      </c>
-      <c r="G25" t="s">
-        <v>200</v>
       </c>
       <c r="H25" t="s">
         <v>1</v>
@@ -3249,22 +3219,22 @@
     </row>
     <row r="26" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A26" t="s">
+        <v>201</v>
+      </c>
+      <c r="C26" t="s">
+        <v>148</v>
+      </c>
+      <c r="D26" t="s">
         <v>202</v>
       </c>
-      <c r="C26" t="s">
-        <v>149</v>
-      </c>
-      <c r="D26" t="s">
+      <c r="E26" t="s">
         <v>203</v>
       </c>
-      <c r="E26" t="s">
+      <c r="F26" t="s">
         <v>204</v>
       </c>
-      <c r="F26" t="s">
+      <c r="G26" t="s">
         <v>205</v>
-      </c>
-      <c r="G26" t="s">
-        <v>206</v>
       </c>
       <c r="H26" t="s">
         <v>1</v>
@@ -3272,22 +3242,22 @@
     </row>
     <row r="27" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A27" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="C27" t="s">
         <v>17</v>
       </c>
       <c r="D27" t="s">
+        <v>207</v>
+      </c>
+      <c r="E27" t="s">
         <v>208</v>
       </c>
-      <c r="E27" t="s">
+      <c r="F27" t="s">
         <v>209</v>
       </c>
-      <c r="F27" t="s">
-        <v>210</v>
-      </c>
       <c r="G27" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="H27" t="s">
         <v>1</v>
@@ -3295,22 +3265,22 @@
     </row>
     <row r="28" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A28" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="C28" t="s">
         <v>7</v>
       </c>
       <c r="D28" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="E28" t="s">
+        <v>53</v>
+      </c>
+      <c r="F28" t="s">
         <v>54</v>
       </c>
-      <c r="F28" t="s">
-        <v>55</v>
-      </c>
       <c r="G28" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="H28" t="s">
         <v>1</v>
@@ -3318,22 +3288,22 @@
     </row>
     <row r="29" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A29" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="C29" t="s">
         <v>7</v>
       </c>
       <c r="D29" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="E29" t="s">
+        <v>53</v>
+      </c>
+      <c r="F29" t="s">
         <v>54</v>
       </c>
-      <c r="F29" t="s">
-        <v>55</v>
-      </c>
       <c r="G29" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="H29" t="s">
         <v>1</v>
@@ -3341,22 +3311,22 @@
     </row>
     <row r="30" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A30" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="C30" t="s">
         <v>6</v>
       </c>
       <c r="D30" t="s">
+        <v>214</v>
+      </c>
+      <c r="E30" t="s">
+        <v>93</v>
+      </c>
+      <c r="F30" t="s">
+        <v>0</v>
+      </c>
+      <c r="G30" t="s">
         <v>215</v>
-      </c>
-      <c r="E30" t="s">
-        <v>94</v>
-      </c>
-      <c r="F30" t="s">
-        <v>0</v>
-      </c>
-      <c r="G30" t="s">
-        <v>216</v>
       </c>
       <c r="H30" t="s">
         <v>1</v>
@@ -3364,22 +3334,22 @@
     </row>
     <row r="31" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A31" t="s">
+        <v>216</v>
+      </c>
+      <c r="C31" t="s">
+        <v>80</v>
+      </c>
+      <c r="D31" t="s">
         <v>217</v>
       </c>
-      <c r="C31" t="s">
-        <v>81</v>
-      </c>
-      <c r="D31" t="s">
+      <c r="E31" t="s">
         <v>218</v>
       </c>
-      <c r="E31" t="s">
+      <c r="F31" t="s">
+        <v>0</v>
+      </c>
+      <c r="G31" t="s">
         <v>219</v>
-      </c>
-      <c r="F31" t="s">
-        <v>0</v>
-      </c>
-      <c r="G31" t="s">
-        <v>220</v>
       </c>
       <c r="H31" t="s">
         <v>1</v>
@@ -3387,22 +3357,22 @@
     </row>
     <row r="32" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A32" t="s">
+        <v>220</v>
+      </c>
+      <c r="C32" t="s">
+        <v>66</v>
+      </c>
+      <c r="D32" t="s">
         <v>221</v>
       </c>
-      <c r="C32" t="s">
-        <v>67</v>
-      </c>
-      <c r="D32" t="s">
+      <c r="E32" t="s">
         <v>222</v>
       </c>
-      <c r="E32" t="s">
-        <v>223</v>
-      </c>
       <c r="F32" t="s">
         <v>0</v>
       </c>
       <c r="G32" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="H32" t="s">
         <v>1</v>
@@ -3410,22 +3380,22 @@
     </row>
     <row r="33" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A33" t="s">
+        <v>223</v>
+      </c>
+      <c r="C33" t="s">
+        <v>80</v>
+      </c>
+      <c r="D33" t="s">
         <v>224</v>
       </c>
-      <c r="C33" t="s">
-        <v>81</v>
-      </c>
-      <c r="D33" t="s">
-        <v>225</v>
-      </c>
       <c r="E33" t="s">
+        <v>218</v>
+      </c>
+      <c r="F33" t="s">
+        <v>0</v>
+      </c>
+      <c r="G33" t="s">
         <v>219</v>
-      </c>
-      <c r="F33" t="s">
-        <v>0</v>
-      </c>
-      <c r="G33" t="s">
-        <v>220</v>
       </c>
       <c r="H33" t="s">
         <v>1</v>
@@ -3433,22 +3403,22 @@
     </row>
     <row r="34" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A34" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="C34" t="s">
         <v>2</v>
       </c>
       <c r="D34" t="s">
+        <v>226</v>
+      </c>
+      <c r="E34" t="s">
+        <v>94</v>
+      </c>
+      <c r="F34" t="s">
+        <v>95</v>
+      </c>
+      <c r="G34" t="s">
         <v>227</v>
-      </c>
-      <c r="E34" t="s">
-        <v>95</v>
-      </c>
-      <c r="F34" t="s">
-        <v>96</v>
-      </c>
-      <c r="G34" t="s">
-        <v>228</v>
       </c>
       <c r="H34" t="s">
         <v>1</v>
@@ -3456,22 +3426,22 @@
     </row>
     <row r="35" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A35" t="s">
-        <v>229</v>
+        <v>228</v>
       </c>
       <c r="C35" t="s">
         <v>2</v>
       </c>
       <c r="D35" t="s">
+        <v>226</v>
+      </c>
+      <c r="E35" t="s">
+        <v>94</v>
+      </c>
+      <c r="F35" t="s">
+        <v>95</v>
+      </c>
+      <c r="G35" t="s">
         <v>227</v>
-      </c>
-      <c r="E35" t="s">
-        <v>95</v>
-      </c>
-      <c r="F35" t="s">
-        <v>96</v>
-      </c>
-      <c r="G35" t="s">
-        <v>228</v>
       </c>
       <c r="H35" t="s">
         <v>1</v>
@@ -3479,22 +3449,22 @@
     </row>
     <row r="36" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A36" t="s">
+        <v>229</v>
+      </c>
+      <c r="C36" t="s">
+        <v>80</v>
+      </c>
+      <c r="D36" t="s">
         <v>230</v>
       </c>
-      <c r="C36" t="s">
-        <v>81</v>
-      </c>
-      <c r="D36" t="s">
+      <c r="E36" t="s">
         <v>231</v>
       </c>
-      <c r="E36" t="s">
+      <c r="F36" t="s">
+        <v>0</v>
+      </c>
+      <c r="G36" t="s">
         <v>232</v>
-      </c>
-      <c r="F36" t="s">
-        <v>0</v>
-      </c>
-      <c r="G36" t="s">
-        <v>233</v>
       </c>
       <c r="H36" t="s">
         <v>1</v>
@@ -3502,22 +3472,22 @@
     </row>
     <row r="37" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A37" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="C37" t="s">
         <v>18</v>
       </c>
       <c r="D37" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="E37" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="F37" t="s">
         <v>0</v>
       </c>
       <c r="G37" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="H37" t="s">
         <v>1</v>
@@ -3525,22 +3495,22 @@
     </row>
     <row r="38" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A38" t="s">
-        <v>236</v>
+        <v>235</v>
       </c>
       <c r="C38" t="s">
         <v>27</v>
       </c>
       <c r="D38" t="s">
+        <v>236</v>
+      </c>
+      <c r="E38" t="s">
+        <v>52</v>
+      </c>
+      <c r="F38" t="s">
+        <v>0</v>
+      </c>
+      <c r="G38" t="s">
         <v>237</v>
-      </c>
-      <c r="E38" t="s">
-        <v>53</v>
-      </c>
-      <c r="F38" t="s">
-        <v>0</v>
-      </c>
-      <c r="G38" t="s">
-        <v>238</v>
       </c>
       <c r="H38" t="s">
         <v>1</v>
@@ -3548,22 +3518,22 @@
     </row>
     <row r="39" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A39" t="s">
-        <v>239</v>
+        <v>238</v>
       </c>
       <c r="C39" t="s">
         <v>24</v>
       </c>
       <c r="D39" t="s">
+        <v>239</v>
+      </c>
+      <c r="E39" t="s">
+        <v>61</v>
+      </c>
+      <c r="F39" t="s">
+        <v>0</v>
+      </c>
+      <c r="G39" t="s">
         <v>240</v>
-      </c>
-      <c r="E39" t="s">
-        <v>62</v>
-      </c>
-      <c r="F39" t="s">
-        <v>0</v>
-      </c>
-      <c r="G39" t="s">
-        <v>241</v>
       </c>
       <c r="H39" t="s">
         <v>1</v>
@@ -3571,22 +3541,22 @@
     </row>
     <row r="40" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A40" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
       <c r="C40" t="s">
         <v>29</v>
       </c>
       <c r="D40" t="s">
+        <v>242</v>
+      </c>
+      <c r="E40" t="s">
         <v>243</v>
       </c>
-      <c r="E40" t="s">
+      <c r="F40" t="s">
+        <v>0</v>
+      </c>
+      <c r="G40" t="s">
         <v>244</v>
-      </c>
-      <c r="F40" t="s">
-        <v>0</v>
-      </c>
-      <c r="G40" t="s">
-        <v>245</v>
       </c>
       <c r="H40" t="s">
         <v>1</v>
@@ -3594,22 +3564,22 @@
     </row>
     <row r="41" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A41" t="s">
-        <v>246</v>
+        <v>245</v>
       </c>
       <c r="C41" t="s">
         <v>18</v>
       </c>
       <c r="D41" t="s">
+        <v>246</v>
+      </c>
+      <c r="E41" t="s">
         <v>247</v>
       </c>
-      <c r="E41" t="s">
+      <c r="F41" t="s">
+        <v>0</v>
+      </c>
+      <c r="G41" t="s">
         <v>248</v>
-      </c>
-      <c r="F41" t="s">
-        <v>0</v>
-      </c>
-      <c r="G41" t="s">
-        <v>249</v>
       </c>
       <c r="H41" t="s">
         <v>1</v>
@@ -3617,22 +3587,22 @@
     </row>
     <row r="42" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A42" t="s">
+        <v>249</v>
+      </c>
+      <c r="C42" t="s">
+        <v>32</v>
+      </c>
+      <c r="D42" t="s">
         <v>250</v>
       </c>
-      <c r="C42" t="s">
-        <v>33</v>
-      </c>
-      <c r="D42" t="s">
+      <c r="E42" t="s">
         <v>251</v>
       </c>
-      <c r="E42" t="s">
+      <c r="F42" t="s">
+        <v>0</v>
+      </c>
+      <c r="G42" t="s">
         <v>252</v>
-      </c>
-      <c r="F42" t="s">
-        <v>0</v>
-      </c>
-      <c r="G42" t="s">
-        <v>253</v>
       </c>
       <c r="H42" t="s">
         <v>1</v>
@@ -3640,13 +3610,13 @@
     </row>
     <row r="43" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A43" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="C43" t="s">
         <v>27</v>
       </c>
       <c r="D43" t="s">
-        <v>255</v>
+        <v>254</v>
       </c>
       <c r="E43" t="s">
         <v>31</v>
@@ -3655,7 +3625,7 @@
         <v>0</v>
       </c>
       <c r="G43" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="H43" t="s">
         <v>1</v>
@@ -3663,13 +3633,13 @@
     </row>
     <row r="44" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A44" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="C44" t="s">
         <v>27</v>
       </c>
       <c r="D44" t="s">
-        <v>255</v>
+        <v>254</v>
       </c>
       <c r="E44" t="s">
         <v>31</v>
@@ -3678,7 +3648,7 @@
         <v>0</v>
       </c>
       <c r="G44" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="H44" t="s">
         <v>1</v>
@@ -3686,22 +3656,22 @@
     </row>
     <row r="45" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A45" t="s">
-        <v>257</v>
+        <v>256</v>
       </c>
       <c r="C45" t="s">
         <v>21</v>
       </c>
       <c r="D45" t="s">
+        <v>257</v>
+      </c>
+      <c r="E45" t="s">
         <v>258</v>
       </c>
-      <c r="E45" t="s">
+      <c r="F45" t="s">
+        <v>0</v>
+      </c>
+      <c r="G45" t="s">
         <v>259</v>
-      </c>
-      <c r="F45" t="s">
-        <v>0</v>
-      </c>
-      <c r="G45" t="s">
-        <v>260</v>
       </c>
       <c r="H45" t="s">
         <v>1</v>
@@ -3709,22 +3679,22 @@
     </row>
     <row r="46" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A46" t="s">
-        <v>261</v>
+        <v>260</v>
       </c>
       <c r="C46" t="s">
         <v>7</v>
       </c>
       <c r="D46" t="s">
+        <v>261</v>
+      </c>
+      <c r="E46" t="s">
         <v>262</v>
       </c>
-      <c r="E46" t="s">
+      <c r="F46" t="s">
+        <v>0</v>
+      </c>
+      <c r="G46" t="s">
         <v>263</v>
-      </c>
-      <c r="F46" t="s">
-        <v>0</v>
-      </c>
-      <c r="G46" t="s">
-        <v>264</v>
       </c>
       <c r="H46" t="s">
         <v>1</v>
@@ -3732,22 +3702,22 @@
     </row>
     <row r="47" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A47" t="s">
+        <v>264</v>
+      </c>
+      <c r="C47" t="s">
+        <v>73</v>
+      </c>
+      <c r="D47" t="s">
         <v>265</v>
       </c>
-      <c r="C47" t="s">
-        <v>74</v>
-      </c>
-      <c r="D47" t="s">
+      <c r="E47" t="s">
+        <v>64</v>
+      </c>
+      <c r="F47" t="s">
+        <v>65</v>
+      </c>
+      <c r="G47" t="s">
         <v>266</v>
-      </c>
-      <c r="E47" t="s">
-        <v>65</v>
-      </c>
-      <c r="F47" t="s">
-        <v>66</v>
-      </c>
-      <c r="G47" t="s">
-        <v>267</v>
       </c>
       <c r="H47" t="s">
         <v>28</v>
@@ -3755,13 +3725,13 @@
     </row>
     <row r="48" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A48" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
       <c r="C48" t="s">
         <v>27</v>
       </c>
       <c r="D48" t="s">
-        <v>269</v>
+        <v>268</v>
       </c>
       <c r="E48" t="s">
         <v>31</v>
@@ -3770,7 +3740,7 @@
         <v>0</v>
       </c>
       <c r="G48" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
       <c r="H48" t="s">
         <v>28</v>
@@ -3778,22 +3748,22 @@
     </row>
     <row r="49" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A49" t="s">
+        <v>270</v>
+      </c>
+      <c r="C49" t="s">
+        <v>80</v>
+      </c>
+      <c r="D49" t="s">
         <v>271</v>
       </c>
-      <c r="C49" t="s">
-        <v>81</v>
-      </c>
-      <c r="D49" t="s">
+      <c r="E49" t="s">
         <v>272</v>
       </c>
-      <c r="E49" t="s">
+      <c r="F49" t="s">
         <v>273</v>
       </c>
-      <c r="F49" t="s">
+      <c r="G49" t=